--- a/database/ASAI3.xlsx
+++ b/database/ASAI3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1351"/>
+  <dimension ref="A1:F1352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44256</v>
       </c>
       <c r="B2" t="n">
-        <v>13.55914974212646</v>
+        <v>13.55914783477783</v>
       </c>
       <c r="C2" t="n">
-        <v>14.43840611222086</v>
+        <v>14.43840408118833</v>
       </c>
       <c r="D2" t="n">
-        <v>13.17554417526233</v>
+        <v>13.17554232187502</v>
       </c>
       <c r="E2" t="n">
-        <v>13.67499187890868</v>
+        <v>13.67498995526467</v>
       </c>
       <c r="F2" t="n">
         <v>64088000</v>
@@ -472,16 +472,16 @@
         <v>44257</v>
       </c>
       <c r="B3" t="n">
-        <v>13.76804447174072</v>
+        <v>13.76804351806641</v>
       </c>
       <c r="C3" t="n">
-        <v>14.05290074536612</v>
+        <v>14.0528997719606</v>
       </c>
       <c r="D3" t="n">
-        <v>13.00463023796586</v>
+        <v>13.00462933717113</v>
       </c>
       <c r="E3" t="n">
-        <v>13.37114477274755</v>
+        <v>13.37114384656537</v>
       </c>
       <c r="F3" t="n">
         <v>14717000</v>
@@ -552,16 +552,16 @@
         <v>44263</v>
       </c>
       <c r="B7" t="n">
-        <v>13.48508548736572</v>
+        <v>13.48508644104004</v>
       </c>
       <c r="C7" t="n">
-        <v>14.29787472337838</v>
+        <v>14.2978757345337</v>
       </c>
       <c r="D7" t="n">
-        <v>13.05210487258059</v>
+        <v>13.05210579563423</v>
       </c>
       <c r="E7" t="n">
-        <v>14.21051885821534</v>
+        <v>14.21051986319279</v>
       </c>
       <c r="F7" t="n">
         <v>12366000</v>
@@ -572,16 +572,16 @@
         <v>44264</v>
       </c>
       <c r="B8" t="n">
-        <v>13.44520664215088</v>
+        <v>13.44520568847656</v>
       </c>
       <c r="C8" t="n">
-        <v>13.44520664215088</v>
+        <v>13.44520568847656</v>
       </c>
       <c r="D8" t="n">
-        <v>13.01032619226716</v>
+        <v>13.0103252694391</v>
       </c>
       <c r="E8" t="n">
-        <v>13.29138464363907</v>
+        <v>13.29138370087542</v>
       </c>
       <c r="F8" t="n">
         <v>10167000</v>
@@ -592,16 +592,16 @@
         <v>44265</v>
       </c>
       <c r="B9" t="n">
-        <v>13.48318672180176</v>
+        <v>13.48318576812744</v>
       </c>
       <c r="C9" t="n">
-        <v>13.95794682401684</v>
+        <v>13.95794583676244</v>
       </c>
       <c r="D9" t="n">
-        <v>13.23631125132199</v>
+        <v>13.23631031510933</v>
       </c>
       <c r="E9" t="n">
-        <v>13.4850856245696</v>
+        <v>13.48508467076097</v>
       </c>
       <c r="F9" t="n">
         <v>15699500</v>
@@ -632,16 +632,16 @@
         <v>44267</v>
       </c>
       <c r="B11" t="n">
-        <v>13.82121562957764</v>
+        <v>13.82121658325195</v>
       </c>
       <c r="C11" t="n">
-        <v>14.06049457939686</v>
+        <v>14.06049554958161</v>
       </c>
       <c r="D11" t="n">
-        <v>13.57813887428711</v>
+        <v>13.57813981118895</v>
       </c>
       <c r="E11" t="n">
-        <v>13.57813887428711</v>
+        <v>13.57813981118895</v>
       </c>
       <c r="F11" t="n">
         <v>7509000</v>
@@ -672,16 +672,16 @@
         <v>44271</v>
       </c>
       <c r="B13" t="n">
-        <v>13.58763408660889</v>
+        <v>13.5876350402832</v>
       </c>
       <c r="C13" t="n">
-        <v>13.91047018507921</v>
+        <v>13.9104711614124</v>
       </c>
       <c r="D13" t="n">
-        <v>13.49458060971476</v>
+        <v>13.49458155685794</v>
       </c>
       <c r="E13" t="n">
-        <v>13.84400406267841</v>
+        <v>13.84400503434655</v>
       </c>
       <c r="F13" t="n">
         <v>7789500</v>
@@ -692,16 +692,16 @@
         <v>44272</v>
       </c>
       <c r="B14" t="n">
-        <v>14.05289936065674</v>
+        <v>14.05290126800537</v>
       </c>
       <c r="C14" t="n">
-        <v>14.07188929407625</v>
+        <v>14.07189120400231</v>
       </c>
       <c r="D14" t="n">
-        <v>13.49458119180776</v>
+        <v>13.49458302337791</v>
       </c>
       <c r="E14" t="n">
-        <v>13.58763467271578</v>
+        <v>13.58763651691574</v>
       </c>
       <c r="F14" t="n">
         <v>4753000</v>
@@ -712,16 +712,16 @@
         <v>44273</v>
       </c>
       <c r="B15" t="n">
-        <v>13.91047096252441</v>
+        <v>13.9104700088501</v>
       </c>
       <c r="C15" t="n">
-        <v>14.0130198642166</v>
+        <v>14.01301890351174</v>
       </c>
       <c r="D15" t="n">
-        <v>13.69018284217017</v>
+        <v>13.69018190359837</v>
       </c>
       <c r="E15" t="n">
-        <v>13.69018284217017</v>
+        <v>13.69018190359837</v>
       </c>
       <c r="F15" t="n">
         <v>2304000</v>
@@ -732,16 +732,16 @@
         <v>44274</v>
       </c>
       <c r="B16" t="n">
-        <v>13.54775524139404</v>
+        <v>13.54775333404541</v>
       </c>
       <c r="C16" t="n">
-        <v>14.03580861527059</v>
+        <v>14.03580663921036</v>
       </c>
       <c r="D16" t="n">
-        <v>13.46419807840647</v>
+        <v>13.46419618282161</v>
       </c>
       <c r="E16" t="n">
-        <v>13.95415035523277</v>
+        <v>13.95414839066896</v>
       </c>
       <c r="F16" t="n">
         <v>14098000</v>
@@ -752,16 +752,16 @@
         <v>44277</v>
       </c>
       <c r="B17" t="n">
-        <v>13.29328346252441</v>
+        <v>13.2932825088501</v>
       </c>
       <c r="C17" t="n">
-        <v>13.63511042556885</v>
+        <v>13.6351094473715</v>
       </c>
       <c r="D17" t="n">
-        <v>13.15655249620002</v>
+        <v>13.15655155233494</v>
       </c>
       <c r="E17" t="n">
-        <v>13.63511042556885</v>
+        <v>13.6351094473715</v>
       </c>
       <c r="F17" t="n">
         <v>5803000</v>
@@ -772,16 +772,16 @@
         <v>44278</v>
       </c>
       <c r="B18" t="n">
-        <v>13.44140815734863</v>
+        <v>13.44141006469727</v>
       </c>
       <c r="C18" t="n">
-        <v>13.44140815734863</v>
+        <v>13.44141006469727</v>
       </c>
       <c r="D18" t="n">
-        <v>13.01982095435623</v>
+        <v>13.01982280188124</v>
       </c>
       <c r="E18" t="n">
-        <v>13.29328287491709</v>
+        <v>13.2932847612466</v>
       </c>
       <c r="F18" t="n">
         <v>7916000</v>
@@ -792,16 +792,16 @@
         <v>44279</v>
       </c>
       <c r="B19" t="n">
-        <v>13.00842666625977</v>
+        <v>13.00842761993408</v>
       </c>
       <c r="C19" t="n">
-        <v>13.4717924479973</v>
+        <v>13.4717934356419</v>
       </c>
       <c r="D19" t="n">
-        <v>12.86599899729744</v>
+        <v>12.86599994053009</v>
       </c>
       <c r="E19" t="n">
-        <v>13.31417265130471</v>
+        <v>13.31417362739389</v>
       </c>
       <c r="F19" t="n">
         <v>12174500</v>
@@ -852,16 +852,16 @@
         <v>44284</v>
       </c>
       <c r="B22" t="n">
-        <v>13.95794773101807</v>
+        <v>13.95794677734375</v>
       </c>
       <c r="C22" t="n">
-        <v>13.95794773101807</v>
+        <v>13.95794677734375</v>
       </c>
       <c r="D22" t="n">
-        <v>13.48698630926816</v>
+        <v>13.4869853877722</v>
       </c>
       <c r="E22" t="n">
-        <v>13.71487095581164</v>
+        <v>13.7148700187455</v>
       </c>
       <c r="F22" t="n">
         <v>6557000</v>
@@ -872,16 +872,16 @@
         <v>44285</v>
       </c>
       <c r="B23" t="n">
-        <v>13.95794773101807</v>
+        <v>13.95794677734375</v>
       </c>
       <c r="C23" t="n">
-        <v>14.08138547427906</v>
+        <v>14.08138451217088</v>
       </c>
       <c r="D23" t="n">
-        <v>13.7680438588985</v>
+        <v>13.76804291819933</v>
       </c>
       <c r="E23" t="n">
-        <v>13.7680438588985</v>
+        <v>13.76804291819933</v>
       </c>
       <c r="F23" t="n">
         <v>8433000</v>
@@ -892,16 +892,16 @@
         <v>44286</v>
       </c>
       <c r="B24" t="n">
-        <v>14.02251434326172</v>
+        <v>14.02251529693604</v>
       </c>
       <c r="C24" t="n">
-        <v>14.04150518240905</v>
+        <v>14.04150613737493</v>
       </c>
       <c r="D24" t="n">
-        <v>13.67499067998287</v>
+        <v>13.67499161002203</v>
       </c>
       <c r="E24" t="n">
-        <v>13.96744253969395</v>
+        <v>13.96744348962283</v>
       </c>
       <c r="F24" t="n">
         <v>3663000</v>
@@ -912,16 +912,16 @@
         <v>44287</v>
       </c>
       <c r="B25" t="n">
-        <v>14.2541971206665</v>
+        <v>14.25419807434082</v>
       </c>
       <c r="C25" t="n">
-        <v>14.40232240017016</v>
+        <v>14.40232336375477</v>
       </c>
       <c r="D25" t="n">
-        <v>14.02631249321458</v>
+        <v>14.02631343164232</v>
       </c>
       <c r="E25" t="n">
-        <v>14.09087971377266</v>
+        <v>14.09088065652025</v>
       </c>
       <c r="F25" t="n">
         <v>9940000</v>
@@ -932,16 +932,16 @@
         <v>44291</v>
       </c>
       <c r="B26" t="n">
-        <v>14.71756553649902</v>
+        <v>14.71756458282471</v>
       </c>
       <c r="C26" t="n">
-        <v>14.88658058749112</v>
+        <v>14.88657962286491</v>
       </c>
       <c r="D26" t="n">
-        <v>14.29977697776849</v>
+        <v>14.29977605116619</v>
       </c>
       <c r="E26" t="n">
-        <v>14.29977697776849</v>
+        <v>14.29977605116619</v>
       </c>
       <c r="F26" t="n">
         <v>6073500</v>
@@ -972,16 +972,16 @@
         <v>44293</v>
       </c>
       <c r="B28" t="n">
-        <v>14.49347591400146</v>
+        <v>14.49347686767578</v>
       </c>
       <c r="C28" t="n">
-        <v>14.7802310507277</v>
+        <v>14.78023202327058</v>
       </c>
       <c r="D28" t="n">
-        <v>13.92756215692881</v>
+        <v>13.92756307336586</v>
       </c>
       <c r="E28" t="n">
-        <v>14.45359624045669</v>
+        <v>14.45359719150692</v>
       </c>
       <c r="F28" t="n">
         <v>10992000</v>
@@ -992,16 +992,16 @@
         <v>44294</v>
       </c>
       <c r="B29" t="n">
-        <v>14.70237255096436</v>
+        <v>14.70237159729004</v>
       </c>
       <c r="C29" t="n">
-        <v>14.74035332682097</v>
+        <v>14.74035237068301</v>
       </c>
       <c r="D29" t="n">
-        <v>14.26559317584676</v>
+        <v>14.26559225050429</v>
       </c>
       <c r="E29" t="n">
-        <v>14.43270840850923</v>
+        <v>14.43270747232676</v>
       </c>
       <c r="F29" t="n">
         <v>6395000</v>
@@ -1012,16 +1012,16 @@
         <v>44295</v>
       </c>
       <c r="B30" t="n">
-        <v>14.71756553649902</v>
+        <v>14.71756458282471</v>
       </c>
       <c r="C30" t="n">
-        <v>14.73655637829882</v>
+        <v>14.73655542339393</v>
       </c>
       <c r="D30" t="n">
-        <v>14.40802169721452</v>
+        <v>14.40802076359814</v>
       </c>
       <c r="E30" t="n">
-        <v>14.6321085594663</v>
+        <v>14.63210761132946</v>
       </c>
       <c r="F30" t="n">
         <v>7012500</v>
@@ -1032,16 +1032,16 @@
         <v>44298</v>
       </c>
       <c r="B31" t="n">
-        <v>14.69857311248779</v>
+        <v>14.69857215881348</v>
       </c>
       <c r="C31" t="n">
-        <v>14.8011220172082</v>
+        <v>14.8011210568803</v>
       </c>
       <c r="D31" t="n">
-        <v>14.52766008235327</v>
+        <v>14.52765913976815</v>
       </c>
       <c r="E31" t="n">
-        <v>14.69857311248779</v>
+        <v>14.69857215881348</v>
       </c>
       <c r="F31" t="n">
         <v>4711000</v>
@@ -1052,16 +1052,16 @@
         <v>44299</v>
       </c>
       <c r="B32" t="n">
-        <v>14.67008686065674</v>
+        <v>14.67008781433105</v>
       </c>
       <c r="C32" t="n">
-        <v>14.81251543350823</v>
+        <v>14.81251639644156</v>
       </c>
       <c r="D32" t="n">
-        <v>14.52765919333826</v>
+        <v>14.52766013775363</v>
       </c>
       <c r="E32" t="n">
-        <v>14.69667331026109</v>
+        <v>14.69667426566374</v>
       </c>
       <c r="F32" t="n">
         <v>5449500</v>
@@ -1092,16 +1092,16 @@
         <v>44301</v>
       </c>
       <c r="B34" t="n">
-        <v>15.18662548065186</v>
+        <v>15.18662738800049</v>
       </c>
       <c r="C34" t="n">
-        <v>15.20371560434488</v>
+        <v>15.20371751383992</v>
       </c>
       <c r="D34" t="n">
-        <v>14.84099984660328</v>
+        <v>14.84100171054341</v>
       </c>
       <c r="E34" t="n">
-        <v>14.84099984660328</v>
+        <v>14.84100171054341</v>
       </c>
       <c r="F34" t="n">
         <v>11554500</v>
@@ -1132,16 +1132,16 @@
         <v>44305</v>
       </c>
       <c r="B36" t="n">
-        <v>15.28727626800537</v>
+        <v>15.28727531433105</v>
       </c>
       <c r="C36" t="n">
-        <v>15.50756529752376</v>
+        <v>15.50756433010704</v>
       </c>
       <c r="D36" t="n">
-        <v>15.00431891696419</v>
+        <v>15.00431798094175</v>
       </c>
       <c r="E36" t="n">
-        <v>15.14484768829616</v>
+        <v>15.14484674350704</v>
       </c>
       <c r="F36" t="n">
         <v>5017000</v>
@@ -1172,16 +1172,16 @@
         <v>44308</v>
       </c>
       <c r="B38" t="n">
-        <v>15.27967834472656</v>
+        <v>15.27967929840088</v>
       </c>
       <c r="C38" t="n">
-        <v>15.75254045321392</v>
+        <v>15.75254143640172</v>
       </c>
       <c r="D38" t="n">
-        <v>15.19422319187483</v>
+        <v>15.1942241402155</v>
       </c>
       <c r="E38" t="n">
-        <v>15.50376517258819</v>
+        <v>15.50376614024878</v>
       </c>
       <c r="F38" t="n">
         <v>8470500</v>
@@ -1192,16 +1192,16 @@
         <v>44309</v>
       </c>
       <c r="B39" t="n">
-        <v>15.41261196136475</v>
+        <v>15.41261291503906</v>
       </c>
       <c r="C39" t="n">
-        <v>15.53794859668741</v>
+        <v>15.53794955811708</v>
       </c>
       <c r="D39" t="n">
-        <v>15.21890939466627</v>
+        <v>15.218910336355</v>
       </c>
       <c r="E39" t="n">
-        <v>15.45818924894863</v>
+        <v>15.45819020544309</v>
       </c>
       <c r="F39" t="n">
         <v>4653000</v>
@@ -1232,16 +1232,16 @@
         <v>44313</v>
       </c>
       <c r="B41" t="n">
-        <v>15.12775707244873</v>
+        <v>15.12775611877441</v>
       </c>
       <c r="C41" t="n">
-        <v>15.29677210768214</v>
+        <v>15.29677114335289</v>
       </c>
       <c r="D41" t="n">
-        <v>15.10117062083444</v>
+        <v>15.10116966883617</v>
       </c>
       <c r="E41" t="n">
-        <v>15.24929500760934</v>
+        <v>15.24929404627311</v>
       </c>
       <c r="F41" t="n">
         <v>4986500</v>
@@ -1252,16 +1252,16 @@
         <v>44314</v>
       </c>
       <c r="B42" t="n">
-        <v>15.18852615356445</v>
+        <v>15.18852519989014</v>
       </c>
       <c r="C42" t="n">
-        <v>15.35564228216909</v>
+        <v>15.35564131800169</v>
       </c>
       <c r="D42" t="n">
-        <v>15.04799647598031</v>
+        <v>15.04799553112973</v>
       </c>
       <c r="E42" t="n">
-        <v>15.14864647703371</v>
+        <v>15.14864552586341</v>
       </c>
       <c r="F42" t="n">
         <v>5371500</v>
@@ -1272,16 +1272,16 @@
         <v>44315</v>
       </c>
       <c r="B43" t="n">
-        <v>15.21646499633789</v>
+        <v>15.21646404266357</v>
       </c>
       <c r="C43" t="n">
-        <v>15.32323336252505</v>
+        <v>15.32323240215915</v>
       </c>
       <c r="D43" t="n">
-        <v>14.90950503441863</v>
+        <v>14.90950409998268</v>
       </c>
       <c r="E43" t="n">
-        <v>15.26222338706449</v>
+        <v>15.26222243052232</v>
       </c>
       <c r="F43" t="n">
         <v>5343000</v>
@@ -1352,16 +1352,16 @@
         <v>44321</v>
       </c>
       <c r="B47" t="n">
-        <v>16.32228469848633</v>
+        <v>16.32228660583496</v>
       </c>
       <c r="C47" t="n">
-        <v>16.58730007183393</v>
+        <v>16.58730201015107</v>
       </c>
       <c r="D47" t="n">
-        <v>16.01532383109572</v>
+        <v>16.01532570257429</v>
       </c>
       <c r="E47" t="n">
-        <v>16.08396141636727</v>
+        <v>16.08396329586652</v>
       </c>
       <c r="F47" t="n">
         <v>17262500</v>
@@ -1372,16 +1372,16 @@
         <v>44322</v>
       </c>
       <c r="B48" t="n">
-        <v>16.61971282958984</v>
+        <v>16.61971092224121</v>
       </c>
       <c r="C48" t="n">
-        <v>16.64449756423438</v>
+        <v>16.64449565404135</v>
       </c>
       <c r="D48" t="n">
-        <v>16.16022519568053</v>
+        <v>16.16022334106464</v>
       </c>
       <c r="E48" t="n">
-        <v>16.31847220804819</v>
+        <v>16.31847033527121</v>
       </c>
       <c r="F48" t="n">
         <v>9404500</v>
@@ -1392,16 +1392,16 @@
         <v>44323</v>
       </c>
       <c r="B49" t="n">
-        <v>16.9628963470459</v>
+        <v>16.96289825439453</v>
       </c>
       <c r="C49" t="n">
-        <v>17.04487814914574</v>
+        <v>17.0448800657126</v>
       </c>
       <c r="D49" t="n">
-        <v>16.42905095447764</v>
+        <v>16.42905280179942</v>
       </c>
       <c r="E49" t="n">
-        <v>16.66356131035563</v>
+        <v>16.66356318404632</v>
       </c>
       <c r="F49" t="n">
         <v>8422500</v>
@@ -1412,16 +1412,16 @@
         <v>44326</v>
       </c>
       <c r="B50" t="n">
-        <v>16.81418418884277</v>
+        <v>16.81418609619141</v>
       </c>
       <c r="C50" t="n">
-        <v>17.01628222452739</v>
+        <v>17.0162841548014</v>
       </c>
       <c r="D50" t="n">
-        <v>16.55298171903851</v>
+        <v>16.55298359675715</v>
       </c>
       <c r="E50" t="n">
-        <v>16.97052383564365</v>
+        <v>16.97052576072697</v>
       </c>
       <c r="F50" t="n">
         <v>7669500</v>
@@ -1432,16 +1432,16 @@
         <v>44327</v>
       </c>
       <c r="B51" t="n">
-        <v>16.58730125427246</v>
+        <v>16.5872974395752</v>
       </c>
       <c r="C51" t="n">
-        <v>16.78368087460993</v>
+        <v>16.78367701474988</v>
       </c>
       <c r="D51" t="n">
-        <v>16.49197157097672</v>
+        <v>16.49196777820309</v>
       </c>
       <c r="E51" t="n">
-        <v>16.62543385489575</v>
+        <v>16.62543003142886</v>
       </c>
       <c r="F51" t="n">
         <v>6191000</v>
@@ -1452,16 +1452,16 @@
         <v>44328</v>
       </c>
       <c r="B52" t="n">
-        <v>16.12590789794922</v>
+        <v>16.12590599060059</v>
       </c>
       <c r="C52" t="n">
-        <v>16.57776793756821</v>
+        <v>16.57776597677424</v>
       </c>
       <c r="D52" t="n">
-        <v>16.04201690472579</v>
+        <v>16.04201500729966</v>
       </c>
       <c r="E52" t="n">
-        <v>16.49006586623571</v>
+        <v>16.49006391581501</v>
       </c>
       <c r="F52" t="n">
         <v>6728500</v>
@@ -1472,16 +1472,16 @@
         <v>44329</v>
       </c>
       <c r="B53" t="n">
-        <v>16.4328670501709</v>
+        <v>16.43286514282227</v>
       </c>
       <c r="C53" t="n">
-        <v>16.5186617551335</v>
+        <v>16.51865983782675</v>
       </c>
       <c r="D53" t="n">
-        <v>16.12781173522566</v>
+        <v>16.12780986328454</v>
       </c>
       <c r="E53" t="n">
-        <v>16.17547748049629</v>
+        <v>16.17547560302264</v>
       </c>
       <c r="F53" t="n">
         <v>6595000</v>
@@ -1512,16 +1512,16 @@
         <v>44333</v>
       </c>
       <c r="B55" t="n">
-        <v>16.34706878662109</v>
+        <v>16.34707260131836</v>
       </c>
       <c r="C55" t="n">
-        <v>16.52819314458002</v>
+        <v>16.52819700154386</v>
       </c>
       <c r="D55" t="n">
-        <v>16.06107980023078</v>
+        <v>16.06108354819061</v>
       </c>
       <c r="E55" t="n">
-        <v>16.50531395293831</v>
+        <v>16.50531780456314</v>
       </c>
       <c r="F55" t="n">
         <v>4728000</v>
@@ -1532,16 +1532,16 @@
         <v>44334</v>
       </c>
       <c r="B56" t="n">
-        <v>16.06108474731445</v>
+        <v>16.06108283996582</v>
       </c>
       <c r="C56" t="n">
-        <v>16.39092486167181</v>
+        <v>16.39092291515271</v>
       </c>
       <c r="D56" t="n">
-        <v>15.88758612704159</v>
+        <v>15.88758424029694</v>
       </c>
       <c r="E56" t="n">
-        <v>16.34897936103174</v>
+        <v>16.34897741949393</v>
       </c>
       <c r="F56" t="n">
         <v>6527500</v>
@@ -1552,16 +1552,16 @@
         <v>44335</v>
       </c>
       <c r="B57" t="n">
-        <v>15.82847881317139</v>
+        <v>15.8284797668457</v>
       </c>
       <c r="C57" t="n">
-        <v>16.36804269641236</v>
+        <v>16.36804368259568</v>
       </c>
       <c r="D57" t="n">
-        <v>15.67595206173143</v>
+        <v>15.67595300621593</v>
       </c>
       <c r="E57" t="n">
-        <v>15.98481846065799</v>
+        <v>15.98481942375186</v>
       </c>
       <c r="F57" t="n">
         <v>6358000</v>
@@ -1572,16 +1572,16 @@
         <v>44336</v>
       </c>
       <c r="B58" t="n">
-        <v>16.03248596191406</v>
+        <v>16.03248405456543</v>
       </c>
       <c r="C58" t="n">
-        <v>16.03248596191406</v>
+        <v>16.03248405456543</v>
       </c>
       <c r="D58" t="n">
-        <v>15.69692561740377</v>
+        <v>15.69692374997599</v>
       </c>
       <c r="E58" t="n">
-        <v>15.90283657256179</v>
+        <v>15.90283468063725</v>
       </c>
       <c r="F58" t="n">
         <v>7278000</v>
@@ -1592,16 +1592,16 @@
         <v>44337</v>
       </c>
       <c r="B59" t="n">
-        <v>16.43477249145508</v>
+        <v>16.43477439880371</v>
       </c>
       <c r="C59" t="n">
-        <v>16.62543183488117</v>
+        <v>16.6254337643569</v>
       </c>
       <c r="D59" t="n">
-        <v>15.75984081583289</v>
+        <v>15.75984264485187</v>
       </c>
       <c r="E59" t="n">
-        <v>16.03438932487009</v>
+        <v>16.03439118575198</v>
       </c>
       <c r="F59" t="n">
         <v>10145000</v>
@@ -1612,16 +1612,16 @@
         <v>44340</v>
       </c>
       <c r="B60" t="n">
-        <v>17.0086555480957</v>
+        <v>17.00865364074707</v>
       </c>
       <c r="C60" t="n">
-        <v>17.06204155023285</v>
+        <v>17.06203963689752</v>
       </c>
       <c r="D60" t="n">
-        <v>16.39664297252445</v>
+        <v>16.39664113380684</v>
       </c>
       <c r="E60" t="n">
-        <v>16.54154212092919</v>
+        <v>16.5415402659626</v>
       </c>
       <c r="F60" t="n">
         <v>10386000</v>
@@ -1692,16 +1692,16 @@
         <v>44344</v>
       </c>
       <c r="B64" t="n">
-        <v>16.98577690124512</v>
+        <v>16.98577499389648</v>
       </c>
       <c r="C64" t="n">
-        <v>17.14974233685488</v>
+        <v>17.14974041109441</v>
       </c>
       <c r="D64" t="n">
-        <v>16.56442007870208</v>
+        <v>16.564418218668</v>
       </c>
       <c r="E64" t="n">
-        <v>16.91141906621777</v>
+        <v>16.91141716721885</v>
       </c>
       <c r="F64" t="n">
         <v>4590500</v>
@@ -1712,16 +1712,16 @@
         <v>44347</v>
       </c>
       <c r="B65" t="n">
-        <v>17.05441474914551</v>
+        <v>17.05441093444824</v>
       </c>
       <c r="C65" t="n">
-        <v>17.25460726644232</v>
+        <v>17.2546034069664</v>
       </c>
       <c r="D65" t="n">
-        <v>16.87138299313376</v>
+        <v>16.87137921937667</v>
       </c>
       <c r="E65" t="n">
-        <v>17.09254734987347</v>
+        <v>17.09254352664678</v>
       </c>
       <c r="F65" t="n">
         <v>4641000</v>
@@ -1732,16 +1732,16 @@
         <v>44348</v>
       </c>
       <c r="B66" t="n">
-        <v>16.96861457824707</v>
+        <v>16.96861839294434</v>
       </c>
       <c r="C66" t="n">
-        <v>17.4109431969055</v>
+        <v>17.41094711104222</v>
       </c>
       <c r="D66" t="n">
-        <v>16.8256209926954</v>
+        <v>16.82562477524642</v>
       </c>
       <c r="E66" t="n">
-        <v>17.17834020076747</v>
+        <v>17.17834406261295</v>
       </c>
       <c r="F66" t="n">
         <v>13722000</v>
@@ -1752,16 +1752,16 @@
         <v>44349</v>
       </c>
       <c r="B67" t="n">
-        <v>16.76651954650879</v>
+        <v>16.76651763916016</v>
       </c>
       <c r="C67" t="n">
-        <v>17.26032688926774</v>
+        <v>17.26032492574389</v>
       </c>
       <c r="D67" t="n">
-        <v>16.73982745427992</v>
+        <v>16.73982554996776</v>
       </c>
       <c r="E67" t="n">
-        <v>17.06394727556971</v>
+        <v>17.06394533438589</v>
       </c>
       <c r="F67" t="n">
         <v>9352500</v>
@@ -1772,16 +1772,16 @@
         <v>44351</v>
       </c>
       <c r="B68" t="n">
-        <v>16.77224159240723</v>
+        <v>16.77223968505859</v>
       </c>
       <c r="C68" t="n">
-        <v>16.81609263171755</v>
+        <v>16.81609071938215</v>
       </c>
       <c r="D68" t="n">
-        <v>16.40617623638331</v>
+        <v>16.40617437066384</v>
       </c>
       <c r="E68" t="n">
-        <v>16.72267029893303</v>
+        <v>16.72266839722167</v>
       </c>
       <c r="F68" t="n">
         <v>8097000</v>
@@ -1792,16 +1792,16 @@
         <v>44354</v>
       </c>
       <c r="B69" t="n">
-        <v>16.53772735595703</v>
+        <v>16.53772926330566</v>
       </c>
       <c r="C69" t="n">
-        <v>16.77223772166646</v>
+        <v>16.77223965606192</v>
       </c>
       <c r="D69" t="n">
-        <v>16.03057584819165</v>
+        <v>16.03057769704888</v>
       </c>
       <c r="E69" t="n">
-        <v>16.77223772166646</v>
+        <v>16.77223965606192</v>
       </c>
       <c r="F69" t="n">
         <v>10336000</v>
@@ -1812,16 +1812,16 @@
         <v>44355</v>
       </c>
       <c r="B70" t="n">
-        <v>16.08205795288086</v>
+        <v>16.08205604553223</v>
       </c>
       <c r="C70" t="n">
-        <v>16.61018141053224</v>
+        <v>16.61017944054762</v>
       </c>
       <c r="D70" t="n">
-        <v>15.9295293598389</v>
+        <v>15.92952747058032</v>
       </c>
       <c r="E70" t="n">
-        <v>16.60064825982571</v>
+        <v>16.60064629097173</v>
       </c>
       <c r="F70" t="n">
         <v>9246000</v>
@@ -1832,16 +1832,16 @@
         <v>44356</v>
       </c>
       <c r="B71" t="n">
-        <v>16.16403770446777</v>
+        <v>16.16403961181641</v>
       </c>
       <c r="C71" t="n">
-        <v>16.39664255171839</v>
+        <v>16.39664448651429</v>
       </c>
       <c r="D71" t="n">
-        <v>15.82466631047011</v>
+        <v>15.82466817777308</v>
       </c>
       <c r="E71" t="n">
-        <v>16.08205589177119</v>
+        <v>16.08205778944601</v>
       </c>
       <c r="F71" t="n">
         <v>10294500</v>
@@ -1852,16 +1852,16 @@
         <v>44357</v>
       </c>
       <c r="B72" t="n">
-        <v>16.30321884155273</v>
+        <v>16.30322074890137</v>
       </c>
       <c r="C72" t="n">
-        <v>16.34707169398488</v>
+        <v>16.34707360646395</v>
       </c>
       <c r="D72" t="n">
-        <v>15.97719348463267</v>
+        <v>15.97719535383889</v>
       </c>
       <c r="E72" t="n">
-        <v>16.15641233581547</v>
+        <v>16.15641422598889</v>
       </c>
       <c r="F72" t="n">
         <v>4720000</v>
@@ -1872,16 +1872,16 @@
         <v>44358</v>
       </c>
       <c r="B73" t="n">
-        <v>16.07061386108398</v>
+        <v>16.07061576843262</v>
       </c>
       <c r="C73" t="n">
-        <v>16.30512422503518</v>
+        <v>16.30512616021678</v>
       </c>
       <c r="D73" t="n">
-        <v>15.8742360914556</v>
+        <v>15.87423797549705</v>
       </c>
       <c r="E73" t="n">
-        <v>16.30321686801416</v>
+        <v>16.3032188029694</v>
       </c>
       <c r="F73" t="n">
         <v>5133000</v>
@@ -1952,16 +1952,16 @@
         <v>44364</v>
       </c>
       <c r="B77" t="n">
-        <v>15.97719097137451</v>
+        <v>15.97719478607178</v>
       </c>
       <c r="C77" t="n">
-        <v>16.00769595476963</v>
+        <v>16.00769977675023</v>
       </c>
       <c r="D77" t="n">
-        <v>15.69120197910729</v>
+        <v>15.69120572552212</v>
       </c>
       <c r="E77" t="n">
-        <v>15.89711470811405</v>
+        <v>15.89711850369239</v>
       </c>
       <c r="F77" t="n">
         <v>7246000</v>
@@ -1972,16 +1972,16 @@
         <v>44365</v>
       </c>
       <c r="B78" t="n">
-        <v>16.20788955688477</v>
+        <v>16.2078914642334</v>
       </c>
       <c r="C78" t="n">
-        <v>16.36422919862247</v>
+        <v>16.36423112436919</v>
       </c>
       <c r="D78" t="n">
-        <v>15.67976438120391</v>
+        <v>15.67976622640263</v>
       </c>
       <c r="E78" t="n">
-        <v>15.98863076877287</v>
+        <v>15.98863265031907</v>
       </c>
       <c r="F78" t="n">
         <v>12012000</v>
@@ -1992,16 +1992,16 @@
         <v>44368</v>
       </c>
       <c r="B79" t="n">
-        <v>16.48434448242188</v>
+        <v>16.48434638977051</v>
       </c>
       <c r="C79" t="n">
-        <v>16.59302020374093</v>
+        <v>16.59302212366407</v>
       </c>
       <c r="D79" t="n">
-        <v>16.00007212945171</v>
+        <v>16.0000739807668</v>
       </c>
       <c r="E79" t="n">
-        <v>16.20789042268334</v>
+        <v>16.20789229804439</v>
       </c>
       <c r="F79" t="n">
         <v>6798000</v>
@@ -2012,16 +2012,16 @@
         <v>44369</v>
       </c>
       <c r="B80" t="n">
-        <v>16.4729061126709</v>
+        <v>16.47290420532227</v>
       </c>
       <c r="C80" t="n">
-        <v>16.49578530803645</v>
+        <v>16.49578339803871</v>
       </c>
       <c r="D80" t="n">
-        <v>16.13162735767305</v>
+        <v>16.13162548984007</v>
       </c>
       <c r="E80" t="n">
-        <v>16.46718585926392</v>
+        <v>16.46718395257762</v>
       </c>
       <c r="F80" t="n">
         <v>6518000</v>
@@ -2032,16 +2032,16 @@
         <v>44370</v>
       </c>
       <c r="B81" t="n">
-        <v>16.39664268493652</v>
+        <v>16.39664459228516</v>
       </c>
       <c r="C81" t="n">
-        <v>16.45574530300238</v>
+        <v>16.45574721722616</v>
       </c>
       <c r="D81" t="n">
-        <v>16.20979622638967</v>
+        <v>16.20979811200328</v>
       </c>
       <c r="E81" t="n">
-        <v>16.40045558110893</v>
+        <v>16.4004574889011</v>
       </c>
       <c r="F81" t="n">
         <v>5819500</v>
@@ -2052,16 +2052,16 @@
         <v>44371</v>
       </c>
       <c r="B82" t="n">
-        <v>16.64640426635742</v>
+        <v>16.64640617370605</v>
       </c>
       <c r="C82" t="n">
-        <v>16.72648053888243</v>
+        <v>16.72648245540622</v>
       </c>
       <c r="D82" t="n">
-        <v>16.39664229944431</v>
+        <v>16.39664417817516</v>
       </c>
       <c r="E82" t="n">
-        <v>16.46909096154148</v>
+        <v>16.46909284857351</v>
       </c>
       <c r="F82" t="n">
         <v>8527500</v>
@@ -2072,16 +2072,16 @@
         <v>44372</v>
       </c>
       <c r="B83" t="n">
-        <v>16.18501091003418</v>
+        <v>16.18501281738281</v>
       </c>
       <c r="C83" t="n">
-        <v>16.74745398613881</v>
+        <v>16.74745595976945</v>
       </c>
       <c r="D83" t="n">
-        <v>16.05345599637458</v>
+        <v>16.05345788821992</v>
       </c>
       <c r="E83" t="n">
-        <v>16.64640405902371</v>
+        <v>16.64640602074596</v>
       </c>
       <c r="F83" t="n">
         <v>6078000</v>
@@ -2092,16 +2092,16 @@
         <v>44375</v>
       </c>
       <c r="B84" t="n">
-        <v>16.37376403808594</v>
+        <v>16.3737621307373</v>
       </c>
       <c r="C84" t="n">
-        <v>16.37948247340491</v>
+        <v>16.37948056539015</v>
       </c>
       <c r="D84" t="n">
-        <v>15.93906113114842</v>
+        <v>15.9390592744375</v>
       </c>
       <c r="E84" t="n">
-        <v>16.22505017280664</v>
+        <v>16.2250482827814</v>
       </c>
       <c r="F84" t="n">
         <v>6202500</v>
@@ -2112,16 +2112,16 @@
         <v>44376</v>
       </c>
       <c r="B85" t="n">
-        <v>16.42333602905273</v>
+        <v>16.4233341217041</v>
       </c>
       <c r="C85" t="n">
-        <v>16.53963755336238</v>
+        <v>16.5396356325069</v>
       </c>
       <c r="D85" t="n">
-        <v>16.120188031945</v>
+        <v>16.12018615980291</v>
       </c>
       <c r="E85" t="n">
-        <v>16.3680444846797</v>
+        <v>16.36804258375244</v>
       </c>
       <c r="F85" t="n">
         <v>8958000</v>
@@ -2132,16 +2132,16 @@
         <v>44377</v>
       </c>
       <c r="B86" t="n">
-        <v>16.49960136413574</v>
+        <v>16.49959754943848</v>
       </c>
       <c r="C86" t="n">
-        <v>16.49960136413574</v>
+        <v>16.49959754943848</v>
       </c>
       <c r="D86" t="n">
-        <v>16.19073307667912</v>
+        <v>16.19072933339201</v>
       </c>
       <c r="E86" t="n">
-        <v>16.38901826231355</v>
+        <v>16.38901447318302</v>
       </c>
       <c r="F86" t="n">
         <v>6685000</v>
@@ -2172,16 +2172,16 @@
         <v>44379</v>
       </c>
       <c r="B88" t="n">
-        <v>16.39664268493652</v>
+        <v>16.39664459228516</v>
       </c>
       <c r="C88" t="n">
-        <v>16.45765266021977</v>
+        <v>16.45765457466542</v>
       </c>
       <c r="D88" t="n">
-        <v>16.21551647977946</v>
+        <v>16.21551836605848</v>
       </c>
       <c r="E88" t="n">
-        <v>16.36804323624992</v>
+        <v>16.36804514027171</v>
       </c>
       <c r="F88" t="n">
         <v>5948000</v>
@@ -2192,16 +2192,16 @@
         <v>44382</v>
       </c>
       <c r="B89" t="n">
-        <v>16.41570663452148</v>
+        <v>16.41570854187012</v>
       </c>
       <c r="C89" t="n">
-        <v>16.54726154865489</v>
+        <v>16.54726347128895</v>
       </c>
       <c r="D89" t="n">
-        <v>16.25174119484036</v>
+        <v>16.25174308313778</v>
       </c>
       <c r="E89" t="n">
-        <v>16.40808084242347</v>
+        <v>16.40808274888606</v>
       </c>
       <c r="F89" t="n">
         <v>3871000</v>
@@ -2212,16 +2212,16 @@
         <v>44383</v>
       </c>
       <c r="B90" t="n">
-        <v>16.33944511413574</v>
+        <v>16.33944320678711</v>
       </c>
       <c r="C90" t="n">
-        <v>16.38901640492637</v>
+        <v>16.38901449179115</v>
       </c>
       <c r="D90" t="n">
-        <v>16.11256231822719</v>
+        <v>16.11256043736321</v>
       </c>
       <c r="E90" t="n">
-        <v>16.38901640492637</v>
+        <v>16.38901449179115</v>
       </c>
       <c r="F90" t="n">
         <v>3828000</v>
@@ -2232,16 +2232,16 @@
         <v>44384</v>
       </c>
       <c r="B91" t="n">
-        <v>16.44430541992188</v>
+        <v>16.44430732727051</v>
       </c>
       <c r="C91" t="n">
-        <v>16.58348612054724</v>
+        <v>16.58348804403921</v>
       </c>
       <c r="D91" t="n">
-        <v>16.15069061682722</v>
+        <v>16.15069249011994</v>
       </c>
       <c r="E91" t="n">
-        <v>16.39664149383569</v>
+        <v>16.39664339565586</v>
       </c>
       <c r="F91" t="n">
         <v>12086500</v>
@@ -2252,16 +2252,16 @@
         <v>44385</v>
       </c>
       <c r="B92" t="n">
-        <v>16.43477249145508</v>
+        <v>16.43477439880371</v>
       </c>
       <c r="C92" t="n">
-        <v>16.79893041915436</v>
+        <v>16.79893236876558</v>
       </c>
       <c r="D92" t="n">
-        <v>16.24411496629124</v>
+        <v>16.24411685151298</v>
       </c>
       <c r="E92" t="n">
-        <v>16.26317944602405</v>
+        <v>16.26318133345833</v>
       </c>
       <c r="F92" t="n">
         <v>7435000</v>
@@ -2272,16 +2272,16 @@
         <v>44389</v>
       </c>
       <c r="B93" t="n">
-        <v>16.50150489807129</v>
+        <v>16.50150299072266</v>
       </c>
       <c r="C93" t="n">
-        <v>16.60255483619654</v>
+        <v>16.60255291716791</v>
       </c>
       <c r="D93" t="n">
-        <v>16.27462210402238</v>
+        <v>16.2746202228983</v>
       </c>
       <c r="E93" t="n">
-        <v>16.43096176807677</v>
+        <v>16.43095986888196</v>
       </c>
       <c r="F93" t="n">
         <v>4327500</v>
@@ -2312,16 +2312,16 @@
         <v>44391</v>
       </c>
       <c r="B95" t="n">
-        <v>16.7226676940918</v>
+        <v>16.72266960144043</v>
       </c>
       <c r="C95" t="n">
-        <v>17.08873299309478</v>
+        <v>17.08873494219598</v>
       </c>
       <c r="D95" t="n">
-        <v>16.67309640833917</v>
+        <v>16.67309831003382</v>
       </c>
       <c r="E95" t="n">
-        <v>16.9304859864696</v>
+        <v>16.93048791752151</v>
       </c>
       <c r="F95" t="n">
         <v>5548000</v>
@@ -2332,16 +2332,16 @@
         <v>44392</v>
       </c>
       <c r="B96" t="n">
-        <v>16.45002555847168</v>
+        <v>16.45002746582031</v>
       </c>
       <c r="C96" t="n">
-        <v>16.86375476157448</v>
+        <v>16.86375671689422</v>
       </c>
       <c r="D96" t="n">
-        <v>16.44049240966831</v>
+        <v>16.44049431591159</v>
       </c>
       <c r="E96" t="n">
-        <v>16.72266670485169</v>
+        <v>16.72266864381253</v>
       </c>
       <c r="F96" t="n">
         <v>3746000</v>
@@ -2352,16 +2352,16 @@
         <v>44393</v>
       </c>
       <c r="B97" t="n">
-        <v>16.67119216918945</v>
+        <v>16.67119407653809</v>
       </c>
       <c r="C97" t="n">
-        <v>16.86947550939675</v>
+        <v>16.86947743943095</v>
       </c>
       <c r="D97" t="n">
-        <v>16.52247830033713</v>
+        <v>16.52248019067143</v>
       </c>
       <c r="E97" t="n">
-        <v>16.54154278229579</v>
+        <v>16.54154467481126</v>
       </c>
       <c r="F97" t="n">
         <v>7965000</v>
@@ -2372,16 +2372,16 @@
         <v>44396</v>
       </c>
       <c r="B98" t="n">
-        <v>16.65402793884277</v>
+        <v>16.65402984619141</v>
       </c>
       <c r="C98" t="n">
-        <v>16.79702334245145</v>
+        <v>16.79702526617702</v>
       </c>
       <c r="D98" t="n">
-        <v>16.4042660037187</v>
+        <v>16.40426788246265</v>
       </c>
       <c r="E98" t="n">
-        <v>16.58539218156415</v>
+        <v>16.58539408105208</v>
       </c>
       <c r="F98" t="n">
         <v>7763500</v>
@@ -2392,16 +2392,16 @@
         <v>44397</v>
       </c>
       <c r="B99" t="n">
-        <v>16.51103782653809</v>
+        <v>16.51103973388672</v>
       </c>
       <c r="C99" t="n">
-        <v>16.71694877821082</v>
+        <v>16.7169507093462</v>
       </c>
       <c r="D99" t="n">
-        <v>16.45956099775114</v>
+        <v>16.45956289915319</v>
       </c>
       <c r="E99" t="n">
-        <v>16.6540314419629</v>
+        <v>16.6540333658301</v>
       </c>
       <c r="F99" t="n">
         <v>3835500</v>
@@ -2412,16 +2412,16 @@
         <v>44398</v>
       </c>
       <c r="B100" t="n">
-        <v>16.59683609008789</v>
+        <v>16.59683227539062</v>
       </c>
       <c r="C100" t="n">
-        <v>16.59683609008789</v>
+        <v>16.59683227539062</v>
       </c>
       <c r="D100" t="n">
-        <v>16.41570985525612</v>
+        <v>16.41570608218979</v>
       </c>
       <c r="E100" t="n">
-        <v>16.516759802561</v>
+        <v>16.51675600626886</v>
       </c>
       <c r="F100" t="n">
         <v>4032000</v>
@@ -2492,16 +2492,16 @@
         <v>44404</v>
       </c>
       <c r="B104" t="n">
-        <v>16.96861457824707</v>
+        <v>16.96861839294434</v>
       </c>
       <c r="C104" t="n">
-        <v>17.30036195137194</v>
+        <v>17.300365840649</v>
       </c>
       <c r="D104" t="n">
-        <v>16.87328673338735</v>
+        <v>16.87329052665406</v>
       </c>
       <c r="E104" t="n">
-        <v>17.14402050381685</v>
+        <v>17.14402435794695</v>
       </c>
       <c r="F104" t="n">
         <v>6666500</v>
@@ -2512,16 +2512,16 @@
         <v>44405</v>
       </c>
       <c r="B105" t="n">
-        <v>16.79321098327637</v>
+        <v>16.79320907592773</v>
       </c>
       <c r="C105" t="n">
-        <v>17.38044062591602</v>
+        <v>17.38043865187069</v>
       </c>
       <c r="D105" t="n">
-        <v>16.42333460278985</v>
+        <v>16.42333273745124</v>
       </c>
       <c r="E105" t="n">
-        <v>17.34993563859687</v>
+        <v>17.34993366801626</v>
       </c>
       <c r="F105" t="n">
         <v>14614500</v>
@@ -2532,16 +2532,16 @@
         <v>44406</v>
       </c>
       <c r="B106" t="n">
-        <v>16.62543106079102</v>
+        <v>16.62543487548828</v>
       </c>
       <c r="C106" t="n">
-        <v>16.77795780112525</v>
+        <v>16.7779616508197</v>
       </c>
       <c r="D106" t="n">
-        <v>16.27461919436984</v>
+        <v>16.27462292857349</v>
       </c>
       <c r="E106" t="n">
-        <v>16.77795780112525</v>
+        <v>16.7779616508197</v>
       </c>
       <c r="F106" t="n">
         <v>12625000</v>
@@ -2612,16 +2612,16 @@
         <v>44412</v>
       </c>
       <c r="B110" t="n">
-        <v>16.60255432128906</v>
+        <v>16.6025562286377</v>
       </c>
       <c r="C110" t="n">
-        <v>16.83134446559894</v>
+        <v>16.83134639923163</v>
       </c>
       <c r="D110" t="n">
-        <v>16.3489776234245</v>
+        <v>16.34897950164152</v>
       </c>
       <c r="E110" t="n">
-        <v>16.48243990463543</v>
+        <v>16.48244179818497</v>
       </c>
       <c r="F110" t="n">
         <v>6533500</v>
@@ -2632,16 +2632,16 @@
         <v>44413</v>
       </c>
       <c r="B111" t="n">
-        <v>16.58730125427246</v>
+        <v>16.5872974395752</v>
       </c>
       <c r="C111" t="n">
-        <v>16.93811317965181</v>
+        <v>16.93810928427588</v>
       </c>
       <c r="D111" t="n">
-        <v>16.47481262800123</v>
+        <v>16.47480883917376</v>
       </c>
       <c r="E111" t="n">
-        <v>16.59302150801845</v>
+        <v>16.59301769200566</v>
       </c>
       <c r="F111" t="n">
         <v>13427000</v>
@@ -2652,16 +2652,16 @@
         <v>44414</v>
       </c>
       <c r="B112" t="n">
-        <v>16.73982620239258</v>
+        <v>16.73982810974121</v>
       </c>
       <c r="C112" t="n">
-        <v>16.78367905199969</v>
+        <v>16.78368096434495</v>
       </c>
       <c r="D112" t="n">
-        <v>16.37566826999301</v>
+        <v>16.37567013584921</v>
       </c>
       <c r="E112" t="n">
-        <v>16.63115048433273</v>
+        <v>16.63115237929877</v>
       </c>
       <c r="F112" t="n">
         <v>15424500</v>
@@ -2692,16 +2692,16 @@
         <v>44418</v>
       </c>
       <c r="B114" t="n">
-        <v>17.55012702941895</v>
+        <v>17.55012512207031</v>
       </c>
       <c r="C114" t="n">
-        <v>17.66452300930153</v>
+        <v>17.66452108952034</v>
       </c>
       <c r="D114" t="n">
-        <v>17.10589279254452</v>
+        <v>17.10589093347529</v>
       </c>
       <c r="E114" t="n">
-        <v>17.22219431143875</v>
+        <v>17.22219243972985</v>
       </c>
       <c r="F114" t="n">
         <v>10281500</v>
@@ -2712,16 +2712,16 @@
         <v>44419</v>
       </c>
       <c r="B115" t="n">
-        <v>17.2088451385498</v>
+        <v>17.20884704589844</v>
       </c>
       <c r="C115" t="n">
-        <v>17.57872328499242</v>
+        <v>17.57872523333663</v>
       </c>
       <c r="D115" t="n">
-        <v>17.1974064517711</v>
+        <v>17.19740835785192</v>
       </c>
       <c r="E115" t="n">
-        <v>17.57872328499242</v>
+        <v>17.57872523333663</v>
       </c>
       <c r="F115" t="n">
         <v>6265000</v>
@@ -2772,16 +2772,16 @@
         <v>44424</v>
       </c>
       <c r="B118" t="n">
-        <v>16.44430541992188</v>
+        <v>16.44430732727051</v>
       </c>
       <c r="C118" t="n">
-        <v>17.04487925261408</v>
+        <v>17.04488122962231</v>
       </c>
       <c r="D118" t="n">
-        <v>16.27271237679204</v>
+        <v>16.27271426423787</v>
       </c>
       <c r="E118" t="n">
-        <v>16.86375487887679</v>
+        <v>16.86375683487669</v>
       </c>
       <c r="F118" t="n">
         <v>7814500</v>
@@ -2792,16 +2792,16 @@
         <v>44425</v>
       </c>
       <c r="B119" t="n">
-        <v>16.16784858703613</v>
+        <v>16.16785049438477</v>
       </c>
       <c r="C119" t="n">
-        <v>16.39664050965117</v>
+        <v>16.39664244399077</v>
       </c>
       <c r="D119" t="n">
-        <v>15.70073523003284</v>
+        <v>15.70073708227531</v>
       </c>
       <c r="E119" t="n">
-        <v>16.16784858703613</v>
+        <v>16.16785049438477</v>
       </c>
       <c r="F119" t="n">
         <v>9967800</v>
@@ -2832,16 +2832,16 @@
         <v>44427</v>
       </c>
       <c r="B121" t="n">
-        <v>16.6635627746582</v>
+        <v>16.66356468200684</v>
       </c>
       <c r="C121" t="n">
-        <v>16.87328841811889</v>
+        <v>16.87329034947318</v>
       </c>
       <c r="D121" t="n">
-        <v>15.57680923404292</v>
+        <v>15.57681101699932</v>
       </c>
       <c r="E121" t="n">
-        <v>15.71026968478171</v>
+        <v>15.71027148301428</v>
       </c>
       <c r="F121" t="n">
         <v>14455000</v>
@@ -2872,16 +2872,16 @@
         <v>44431</v>
       </c>
       <c r="B123" t="n">
-        <v>16.69216156005859</v>
+        <v>16.69216346740723</v>
       </c>
       <c r="C123" t="n">
-        <v>17.16880808609706</v>
+        <v>17.16881004791025</v>
       </c>
       <c r="D123" t="n">
-        <v>16.52056851976279</v>
+        <v>16.52057040750415</v>
       </c>
       <c r="E123" t="n">
-        <v>16.9781487483768</v>
+        <v>16.97815068840407</v>
       </c>
       <c r="F123" t="n">
         <v>5050600</v>
@@ -2912,16 +2912,16 @@
         <v>44433</v>
       </c>
       <c r="B125" t="n">
-        <v>17.01628303527832</v>
+        <v>17.01628112792969</v>
       </c>
       <c r="C125" t="n">
-        <v>17.19740924229705</v>
+        <v>17.19740731464605</v>
       </c>
       <c r="D125" t="n">
-        <v>16.78749289822105</v>
+        <v>16.78749101651742</v>
       </c>
       <c r="E125" t="n">
-        <v>17.0258161849385</v>
+        <v>17.02581427652131</v>
       </c>
       <c r="F125" t="n">
         <v>4269900</v>
@@ -2932,16 +2932,16 @@
         <v>44434</v>
       </c>
       <c r="B126" t="n">
-        <v>16.5587043762207</v>
+        <v>16.55870246887207</v>
       </c>
       <c r="C126" t="n">
-        <v>17.00675154437543</v>
+        <v>17.00674958541756</v>
       </c>
       <c r="D126" t="n">
-        <v>16.5587043762207</v>
+        <v>16.55870246887207</v>
       </c>
       <c r="E126" t="n">
-        <v>16.93048815791797</v>
+        <v>16.93048620774466</v>
       </c>
       <c r="F126" t="n">
         <v>4969900</v>
@@ -2952,16 +2952,16 @@
         <v>44435</v>
       </c>
       <c r="B127" t="n">
-        <v>16.58730125427246</v>
+        <v>16.5872974395752</v>
       </c>
       <c r="C127" t="n">
-        <v>16.72076353819149</v>
+        <v>16.72075969280097</v>
       </c>
       <c r="D127" t="n">
-        <v>16.39664370594345</v>
+        <v>16.39663993509303</v>
       </c>
       <c r="E127" t="n">
-        <v>16.55870362206747</v>
+        <v>16.558699813947</v>
       </c>
       <c r="F127" t="n">
         <v>5662600</v>
@@ -2992,16 +2992,16 @@
         <v>44439</v>
       </c>
       <c r="B129" t="n">
-        <v>16.02485466003418</v>
+        <v>16.02485656738281</v>
       </c>
       <c r="C129" t="n">
-        <v>16.63496341032833</v>
+        <v>16.63496539029478</v>
       </c>
       <c r="D129" t="n">
-        <v>16.02485466003418</v>
+        <v>16.02485656738281</v>
       </c>
       <c r="E129" t="n">
-        <v>16.37757386652902</v>
+        <v>16.37757581585984</v>
       </c>
       <c r="F129" t="n">
         <v>8477100</v>
@@ -3012,16 +3012,16 @@
         <v>44440</v>
       </c>
       <c r="B130" t="n">
-        <v>16.23458099365234</v>
+        <v>16.23458290100098</v>
       </c>
       <c r="C130" t="n">
-        <v>16.77795773110823</v>
+        <v>16.77795970229644</v>
       </c>
       <c r="D130" t="n">
-        <v>15.8913949202014</v>
+        <v>15.89139678723021</v>
       </c>
       <c r="E130" t="n">
-        <v>16.30131121498732</v>
+        <v>16.30131313017587</v>
       </c>
       <c r="F130" t="n">
         <v>7651500</v>
@@ -3032,16 +3032,16 @@
         <v>44441</v>
       </c>
       <c r="B131" t="n">
-        <v>16.72076225280762</v>
+        <v>16.72076034545898</v>
       </c>
       <c r="C131" t="n">
-        <v>17.03534891071645</v>
+        <v>17.0353469674827</v>
       </c>
       <c r="D131" t="n">
-        <v>16.10112026815059</v>
+        <v>16.10111843148494</v>
       </c>
       <c r="E131" t="n">
-        <v>16.16785049584908</v>
+        <v>16.16784865157147</v>
       </c>
       <c r="F131" t="n">
         <v>17566400</v>
@@ -3072,16 +3072,16 @@
         <v>44445</v>
       </c>
       <c r="B133" t="n">
-        <v>17.49292945861816</v>
+        <v>17.4929313659668</v>
       </c>
       <c r="C133" t="n">
-        <v>17.66452251450438</v>
+        <v>17.66452444056273</v>
       </c>
       <c r="D133" t="n">
-        <v>17.04488051974584</v>
+        <v>17.04488237824128</v>
       </c>
       <c r="E133" t="n">
-        <v>17.30227010357517</v>
+        <v>17.30227199013519</v>
       </c>
       <c r="F133" t="n">
         <v>6471000</v>
@@ -3092,16 +3092,16 @@
         <v>44447</v>
       </c>
       <c r="B134" t="n">
-        <v>17.07348251342773</v>
+        <v>17.0734806060791</v>
       </c>
       <c r="C134" t="n">
-        <v>17.55012915382106</v>
+        <v>17.55012719322427</v>
       </c>
       <c r="D134" t="n">
-        <v>16.84469234423046</v>
+        <v>16.84469046244091</v>
       </c>
       <c r="E134" t="n">
-        <v>17.49293206608739</v>
+        <v>17.49293011188033</v>
       </c>
       <c r="F134" t="n">
         <v>11069100</v>
@@ -3112,16 +3112,16 @@
         <v>44448</v>
       </c>
       <c r="B135" t="n">
-        <v>17.34993553161621</v>
+        <v>17.34993743896484</v>
       </c>
       <c r="C135" t="n">
-        <v>17.44526338911795</v>
+        <v>17.44526530694636</v>
       </c>
       <c r="D135" t="n">
-        <v>16.92095289980908</v>
+        <v>16.92095475999791</v>
       </c>
       <c r="E135" t="n">
-        <v>17.07347965372665</v>
+        <v>17.07348153068337</v>
       </c>
       <c r="F135" t="n">
         <v>12544000</v>
@@ -3152,16 +3152,16 @@
         <v>44452</v>
       </c>
       <c r="B137" t="n">
-        <v>17.79798316955566</v>
+        <v>17.79798126220703</v>
       </c>
       <c r="C137" t="n">
-        <v>17.9695762273458</v>
+        <v>17.96957430160813</v>
       </c>
       <c r="D137" t="n">
-        <v>17.49292965271203</v>
+        <v>17.49292777805493</v>
       </c>
       <c r="E137" t="n">
-        <v>17.5787261816071</v>
+        <v>17.57872429775548</v>
       </c>
       <c r="F137" t="n">
         <v>17075500</v>
@@ -3172,16 +3172,16 @@
         <v>44453</v>
       </c>
       <c r="B138" t="n">
-        <v>17.4738655090332</v>
+        <v>17.47386169433594</v>
       </c>
       <c r="C138" t="n">
-        <v>18.15070467400888</v>
+        <v>18.15070071155172</v>
       </c>
       <c r="D138" t="n">
-        <v>17.39760212041395</v>
+        <v>17.39759832236565</v>
       </c>
       <c r="E138" t="n">
-        <v>17.82658481781139</v>
+        <v>17.82658092611242</v>
       </c>
       <c r="F138" t="n">
         <v>6594500</v>
@@ -3192,16 +3192,16 @@
         <v>44454</v>
       </c>
       <c r="B139" t="n">
-        <v>17.72171974182129</v>
+        <v>17.72172164916992</v>
       </c>
       <c r="C139" t="n">
-        <v>17.82658256979756</v>
+        <v>17.82658448843234</v>
       </c>
       <c r="D139" t="n">
-        <v>17.27367261746679</v>
+        <v>17.27367447659312</v>
       </c>
       <c r="E139" t="n">
-        <v>17.46433015584083</v>
+        <v>17.46433203548721</v>
       </c>
       <c r="F139" t="n">
         <v>8756500</v>
@@ -3212,16 +3212,16 @@
         <v>44455</v>
       </c>
       <c r="B140" t="n">
-        <v>18.26509475708008</v>
+        <v>18.26509857177734</v>
       </c>
       <c r="C140" t="n">
-        <v>18.33182497989392</v>
+        <v>18.33182880852791</v>
       </c>
       <c r="D140" t="n">
-        <v>17.72171800758197</v>
+        <v>17.72172170879404</v>
       </c>
       <c r="E140" t="n">
-        <v>17.72171800758197</v>
+        <v>17.72172170879404</v>
       </c>
       <c r="F140" t="n">
         <v>17281800</v>
@@ -3292,16 +3292,16 @@
         <v>44461</v>
       </c>
       <c r="B144" t="n">
-        <v>18.3890266418457</v>
+        <v>18.38902473449707</v>
       </c>
       <c r="C144" t="n">
-        <v>18.68454702378533</v>
+        <v>18.6845450857847</v>
       </c>
       <c r="D144" t="n">
-        <v>18.21743357547351</v>
+        <v>18.21743168592287</v>
       </c>
       <c r="E144" t="n">
-        <v>18.61781679092114</v>
+        <v>18.61781485984191</v>
       </c>
       <c r="F144" t="n">
         <v>5973600</v>
@@ -3312,16 +3312,16 @@
         <v>44462</v>
       </c>
       <c r="B145" t="n">
-        <v>18.29369735717773</v>
+        <v>18.2936954498291</v>
       </c>
       <c r="C145" t="n">
-        <v>18.53202066160796</v>
+        <v>18.53201872941112</v>
       </c>
       <c r="D145" t="n">
-        <v>18.07443853522241</v>
+        <v>18.07443665073428</v>
       </c>
       <c r="E145" t="n">
-        <v>18.34136129075877</v>
+        <v>18.34135937844058</v>
       </c>
       <c r="F145" t="n">
         <v>20822300</v>
@@ -3332,16 +3332,16 @@
         <v>44463</v>
       </c>
       <c r="B146" t="n">
-        <v>18.09350204467773</v>
+        <v>18.09350395202637</v>
       </c>
       <c r="C146" t="n">
-        <v>18.26509508831786</v>
+        <v>18.26509701375519</v>
       </c>
       <c r="D146" t="n">
-        <v>17.87424507480967</v>
+        <v>17.87424695904506</v>
       </c>
       <c r="E146" t="n">
-        <v>18.13163464026987</v>
+        <v>18.13163655163829</v>
       </c>
       <c r="F146" t="n">
         <v>18657800</v>
@@ -3352,16 +3352,16 @@
         <v>44466</v>
       </c>
       <c r="B147" t="n">
-        <v>18.35089683532715</v>
+        <v>18.35089302062988</v>
       </c>
       <c r="C147" t="n">
-        <v>18.46529283641415</v>
+        <v>18.46528899793678</v>
       </c>
       <c r="D147" t="n">
-        <v>17.83611755782977</v>
+        <v>17.83611385014238</v>
       </c>
       <c r="E147" t="n">
-        <v>18.01724380194138</v>
+        <v>18.01724005660232</v>
       </c>
       <c r="F147" t="n">
         <v>7788100</v>
@@ -3372,16 +3372,16 @@
         <v>44467</v>
       </c>
       <c r="B148" t="n">
-        <v>18.28416061401367</v>
+        <v>18.28416633605957</v>
       </c>
       <c r="C148" t="n">
-        <v>18.29369376250914</v>
+        <v>18.29369948753845</v>
       </c>
       <c r="D148" t="n">
-        <v>18.01723791092701</v>
+        <v>18.01724354943918</v>
       </c>
       <c r="E148" t="n">
-        <v>18.23649487153633</v>
+        <v>18.23650057866518</v>
       </c>
       <c r="F148" t="n">
         <v>11310100</v>
@@ -3432,16 +3432,16 @@
         <v>44470</v>
       </c>
       <c r="B151" t="n">
-        <v>18.45575523376465</v>
+        <v>18.45575714111328</v>
       </c>
       <c r="C151" t="n">
-        <v>18.56061623968673</v>
+        <v>18.56061815787245</v>
       </c>
       <c r="D151" t="n">
-        <v>18.00770630734936</v>
+        <v>18.00770816839343</v>
       </c>
       <c r="E151" t="n">
-        <v>18.19836565709148</v>
+        <v>18.19836753783964</v>
       </c>
       <c r="F151" t="n">
         <v>5841800</v>
@@ -3472,16 +3472,16 @@
         <v>44474</v>
       </c>
       <c r="B153" t="n">
-        <v>18.32229614257812</v>
+        <v>18.32229232788086</v>
       </c>
       <c r="C153" t="n">
-        <v>18.49388922348389</v>
+        <v>18.49388537306099</v>
       </c>
       <c r="D153" t="n">
-        <v>18.04584203754533</v>
+        <v>18.04583828040574</v>
       </c>
       <c r="E153" t="n">
-        <v>18.3413624445149</v>
+        <v>18.34135862584804</v>
       </c>
       <c r="F153" t="n">
         <v>8000200</v>
@@ -3552,16 +3552,16 @@
         <v>44480</v>
       </c>
       <c r="B157" t="n">
-        <v>16.62799072265625</v>
+        <v>16.62798690795898</v>
       </c>
       <c r="C157" t="n">
-        <v>17.52628500439614</v>
+        <v>17.5262809836174</v>
       </c>
       <c r="D157" t="n">
-        <v>16.47508980100556</v>
+        <v>16.47508602138593</v>
       </c>
       <c r="E157" t="n">
-        <v>17.42116493724025</v>
+        <v>17.42116094057755</v>
       </c>
       <c r="F157" t="n">
         <v>31512800</v>
@@ -3572,16 +3572,16 @@
         <v>44482</v>
       </c>
       <c r="B158" t="n">
-        <v>17.12491989135742</v>
+        <v>17.12492179870605</v>
       </c>
       <c r="C158" t="n">
-        <v>17.4020521325678</v>
+        <v>17.40205407078302</v>
       </c>
       <c r="D158" t="n">
-        <v>16.62799097702933</v>
+        <v>16.62799282903075</v>
       </c>
       <c r="E158" t="n">
-        <v>16.62799097702933</v>
+        <v>16.62799282903075</v>
       </c>
       <c r="F158" t="n">
         <v>10150700</v>
@@ -3612,16 +3612,16 @@
         <v>44484</v>
       </c>
       <c r="B160" t="n">
-        <v>16.76177978515625</v>
+        <v>16.76177787780762</v>
       </c>
       <c r="C160" t="n">
-        <v>16.93379194870116</v>
+        <v>16.933790021779</v>
       </c>
       <c r="D160" t="n">
-        <v>15.86348553616024</v>
+        <v>15.86348373102988</v>
       </c>
       <c r="E160" t="n">
-        <v>15.95904906438921</v>
+        <v>15.95904724838453</v>
       </c>
       <c r="F160" t="n">
         <v>78021300</v>
@@ -3632,16 +3632,16 @@
         <v>44487</v>
       </c>
       <c r="B161" t="n">
-        <v>16.20750999450684</v>
+        <v>16.20751190185547</v>
       </c>
       <c r="C161" t="n">
-        <v>16.67577105168735</v>
+        <v>16.67577301414236</v>
       </c>
       <c r="D161" t="n">
-        <v>16.10239176487586</v>
+        <v>16.10239365985386</v>
       </c>
       <c r="E161" t="n">
-        <v>16.5897640675295</v>
+        <v>16.58976601986295</v>
       </c>
       <c r="F161" t="n">
         <v>13070300</v>
@@ -3652,16 +3652,16 @@
         <v>44488</v>
       </c>
       <c r="B162" t="n">
-        <v>15.81570148468018</v>
+        <v>15.81570243835449</v>
       </c>
       <c r="C162" t="n">
-        <v>16.07372244163314</v>
+        <v>16.07372341086592</v>
       </c>
       <c r="D162" t="n">
-        <v>15.63413280183701</v>
+        <v>15.63413374456288</v>
       </c>
       <c r="E162" t="n">
-        <v>16.05460937310569</v>
+        <v>16.05461034118597</v>
       </c>
       <c r="F162" t="n">
         <v>17605400</v>
@@ -3672,16 +3672,16 @@
         <v>44489</v>
       </c>
       <c r="B163" t="n">
-        <v>15.98771476745605</v>
+        <v>15.98771667480469</v>
       </c>
       <c r="C163" t="n">
-        <v>16.21706611174061</v>
+        <v>16.21706804645106</v>
       </c>
       <c r="D163" t="n">
-        <v>15.71058257663313</v>
+        <v>15.71058445091965</v>
       </c>
       <c r="E163" t="n">
-        <v>15.93993392091769</v>
+        <v>15.93993582256603</v>
       </c>
       <c r="F163" t="n">
         <v>11472200</v>
@@ -3692,16 +3692,16 @@
         <v>44490</v>
       </c>
       <c r="B164" t="n">
-        <v>15.70102787017822</v>
+        <v>15.70102882385254</v>
       </c>
       <c r="C164" t="n">
-        <v>16.21706799919828</v>
+        <v>16.21706898421667</v>
       </c>
       <c r="D164" t="n">
-        <v>15.31877558521472</v>
+        <v>15.31877651567118</v>
       </c>
       <c r="E164" t="n">
-        <v>15.81570264430594</v>
+        <v>15.81570360494555</v>
       </c>
       <c r="F164" t="n">
         <v>11995800</v>
@@ -3712,16 +3712,16 @@
         <v>44491</v>
       </c>
       <c r="B165" t="n">
-        <v>15.39522647857666</v>
+        <v>15.39522552490234</v>
       </c>
       <c r="C165" t="n">
-        <v>15.64369092652619</v>
+        <v>15.64368995746047</v>
       </c>
       <c r="D165" t="n">
-        <v>14.76450882346753</v>
+        <v>14.76450790886372</v>
       </c>
       <c r="E165" t="n">
-        <v>15.39522647857666</v>
+        <v>15.39522552490234</v>
       </c>
       <c r="F165" t="n">
         <v>24678500</v>
@@ -3772,16 +3772,16 @@
         <v>44496</v>
       </c>
       <c r="B168" t="n">
-        <v>14.94607830047607</v>
+        <v>14.94608020782471</v>
       </c>
       <c r="C168" t="n">
-        <v>15.38566886553011</v>
+        <v>15.38567082897724</v>
       </c>
       <c r="D168" t="n">
-        <v>14.81228955063831</v>
+        <v>14.81229144091344</v>
       </c>
       <c r="E168" t="n">
-        <v>15.38566886553011</v>
+        <v>15.38567082897724</v>
       </c>
       <c r="F168" t="n">
         <v>9783700</v>
@@ -3792,16 +3792,16 @@
         <v>44497</v>
       </c>
       <c r="B169" t="n">
-        <v>14.95563507080078</v>
+        <v>14.95563411712646</v>
       </c>
       <c r="C169" t="n">
-        <v>15.13720559603315</v>
+        <v>15.13720463078065</v>
       </c>
       <c r="D169" t="n">
-        <v>14.69761499726184</v>
+        <v>14.69761406004066</v>
       </c>
       <c r="E169" t="n">
-        <v>15.02252990653125</v>
+        <v>15.02252894859126</v>
       </c>
       <c r="F169" t="n">
         <v>8208600</v>
@@ -3832,16 +3832,16 @@
         <v>44501</v>
       </c>
       <c r="B171" t="n">
-        <v>14.31536197662354</v>
+        <v>14.31536102294922</v>
       </c>
       <c r="C171" t="n">
-        <v>14.77406565205061</v>
+        <v>14.77406466781794</v>
       </c>
       <c r="D171" t="n">
-        <v>14.20068628560711</v>
+        <v>14.20068533957237</v>
       </c>
       <c r="E171" t="n">
-        <v>14.76450911662556</v>
+        <v>14.76450813302954</v>
       </c>
       <c r="F171" t="n">
         <v>10277500</v>
@@ -3852,16 +3852,16 @@
         <v>44503</v>
       </c>
       <c r="B172" t="n">
-        <v>14.74539566040039</v>
+        <v>14.74539470672607</v>
       </c>
       <c r="C172" t="n">
-        <v>14.86962787591666</v>
+        <v>14.86962691420749</v>
       </c>
       <c r="D172" t="n">
-        <v>14.07645282125721</v>
+        <v>14.07645191084749</v>
       </c>
       <c r="E172" t="n">
-        <v>14.14334765198831</v>
+        <v>14.1433467372521</v>
       </c>
       <c r="F172" t="n">
         <v>21906500</v>
@@ -3872,16 +3872,16 @@
         <v>44504</v>
       </c>
       <c r="B173" t="n">
-        <v>14.52560043334961</v>
+        <v>14.52560138702393</v>
       </c>
       <c r="C173" t="n">
-        <v>14.73583964480952</v>
+        <v>14.73584061228703</v>
       </c>
       <c r="D173" t="n">
-        <v>14.30580559832982</v>
+        <v>14.30580653757357</v>
       </c>
       <c r="E173" t="n">
-        <v>14.69761441648602</v>
+        <v>14.69761538145387</v>
       </c>
       <c r="F173" t="n">
         <v>4262500</v>
@@ -3892,16 +3892,16 @@
         <v>44505</v>
       </c>
       <c r="B174" t="n">
-        <v>14.5638256072998</v>
+        <v>14.56382465362549</v>
       </c>
       <c r="C174" t="n">
-        <v>14.71672652002295</v>
+        <v>14.71672555633632</v>
       </c>
       <c r="D174" t="n">
-        <v>14.1720167906064</v>
+        <v>14.17201586258867</v>
       </c>
       <c r="E174" t="n">
-        <v>14.54471344889008</v>
+        <v>14.54471249646727</v>
       </c>
       <c r="F174" t="n">
         <v>8161700</v>
@@ -3912,16 +3912,16 @@
         <v>44508</v>
       </c>
       <c r="B175" t="n">
-        <v>14.73583889007568</v>
+        <v>14.73583984375</v>
       </c>
       <c r="C175" t="n">
-        <v>14.89829632997021</v>
+        <v>14.89829729415845</v>
       </c>
       <c r="D175" t="n">
-        <v>14.28669179675779</v>
+        <v>14.2866927213642</v>
       </c>
       <c r="E175" t="n">
-        <v>14.39181185278442</v>
+        <v>14.39181278419399</v>
       </c>
       <c r="F175" t="n">
         <v>8290300</v>
@@ -3972,16 +3972,16 @@
         <v>44511</v>
       </c>
       <c r="B178" t="n">
-        <v>15.19454383850098</v>
+        <v>15.19454193115234</v>
       </c>
       <c r="C178" t="n">
-        <v>15.51945876601915</v>
+        <v>15.51945681788442</v>
       </c>
       <c r="D178" t="n">
-        <v>15.07986814255834</v>
+        <v>15.07986624960478</v>
       </c>
       <c r="E178" t="n">
-        <v>15.43345176622182</v>
+        <v>15.43344982888343</v>
       </c>
       <c r="F178" t="n">
         <v>5555700</v>
@@ -3992,16 +3992,16 @@
         <v>44512</v>
       </c>
       <c r="B179" t="n">
-        <v>14.8409595489502</v>
+        <v>14.84095764160156</v>
       </c>
       <c r="C179" t="n">
-        <v>15.23276838701479</v>
+        <v>15.23276642931119</v>
       </c>
       <c r="D179" t="n">
-        <v>14.82184738949799</v>
+        <v>14.82184548460564</v>
       </c>
       <c r="E179" t="n">
-        <v>15.08942400135846</v>
+        <v>15.08942206207736</v>
       </c>
       <c r="F179" t="n">
         <v>7831400</v>
@@ -4132,16 +4132,16 @@
         <v>44524</v>
       </c>
       <c r="B186" t="n">
-        <v>13.11126708984375</v>
+        <v>13.11126613616943</v>
       </c>
       <c r="C186" t="n">
-        <v>13.38840024450097</v>
+        <v>13.38839927066881</v>
       </c>
       <c r="D186" t="n">
-        <v>12.97747832466525</v>
+        <v>12.97747738072233</v>
       </c>
       <c r="E186" t="n">
-        <v>13.09215401852051</v>
+        <v>13.09215306623642</v>
       </c>
       <c r="F186" t="n">
         <v>5705900</v>
@@ -4192,16 +4192,16 @@
         <v>44529</v>
       </c>
       <c r="B189" t="n">
-        <v>12.47099208831787</v>
+        <v>12.4709939956665</v>
       </c>
       <c r="C189" t="n">
-        <v>13.11126530889348</v>
+        <v>13.1112673141673</v>
       </c>
       <c r="D189" t="n">
-        <v>12.42321032786153</v>
+        <v>12.42321222790229</v>
       </c>
       <c r="E189" t="n">
-        <v>12.88191304097531</v>
+        <v>12.88191501117135</v>
       </c>
       <c r="F189" t="n">
         <v>13464500</v>
@@ -4232,16 +4232,16 @@
         <v>44531</v>
       </c>
       <c r="B191" t="n">
-        <v>11.91672611236572</v>
+        <v>11.91672706604004</v>
       </c>
       <c r="C191" t="n">
-        <v>12.37542883541339</v>
+        <v>12.37542982579687</v>
       </c>
       <c r="D191" t="n">
-        <v>11.81160605481299</v>
+        <v>11.81160700007474</v>
       </c>
       <c r="E191" t="n">
-        <v>12.29897838157211</v>
+        <v>12.2989793658374</v>
       </c>
       <c r="F191" t="n">
         <v>5991300</v>
@@ -4272,16 +4272,16 @@
         <v>44533</v>
       </c>
       <c r="B193" t="n">
-        <v>12.70990180969238</v>
+        <v>12.70990085601807</v>
       </c>
       <c r="C193" t="n">
-        <v>12.74812704129032</v>
+        <v>12.74812608474781</v>
       </c>
       <c r="D193" t="n">
-        <v>11.95495280211211</v>
+        <v>11.95495190508461</v>
       </c>
       <c r="E193" t="n">
-        <v>11.99317803371005</v>
+        <v>11.99317713381436</v>
       </c>
       <c r="F193" t="n">
         <v>16852000</v>
@@ -4312,16 +4312,16 @@
         <v>44537</v>
       </c>
       <c r="B195" t="n">
-        <v>13.42662525177002</v>
+        <v>13.42662334442139</v>
       </c>
       <c r="C195" t="n">
-        <v>13.7610957920937</v>
+        <v>13.76109383723112</v>
       </c>
       <c r="D195" t="n">
-        <v>13.40751218076567</v>
+        <v>13.40751027613218</v>
       </c>
       <c r="E195" t="n">
-        <v>13.56996963885711</v>
+        <v>13.56996771114538</v>
       </c>
       <c r="F195" t="n">
         <v>14090400</v>
@@ -4332,16 +4332,16 @@
         <v>44538</v>
       </c>
       <c r="B196" t="n">
-        <v>13.75153827667236</v>
+        <v>13.75153923034668</v>
       </c>
       <c r="C196" t="n">
-        <v>14.02867138859101</v>
+        <v>14.02867236148461</v>
       </c>
       <c r="D196" t="n">
-        <v>13.2737225036153</v>
+        <v>13.27372342415291</v>
       </c>
       <c r="E196" t="n">
-        <v>13.42662340517576</v>
+        <v>13.42662433631711</v>
       </c>
       <c r="F196" t="n">
         <v>14295000</v>
@@ -4352,16 +4352,16 @@
         <v>44539</v>
       </c>
       <c r="B197" t="n">
-        <v>13.58908176422119</v>
+        <v>13.58908271789551</v>
       </c>
       <c r="C197" t="n">
-        <v>13.74198267617036</v>
+        <v>13.74198364057517</v>
       </c>
       <c r="D197" t="n">
-        <v>13.43618085227203</v>
+        <v>13.43618179521584</v>
       </c>
       <c r="E197" t="n">
-        <v>13.74198267617036</v>
+        <v>13.74198364057517</v>
       </c>
       <c r="F197" t="n">
         <v>9843600</v>
@@ -4372,16 +4372,16 @@
         <v>44540</v>
       </c>
       <c r="B198" t="n">
-        <v>13.91399765014648</v>
+        <v>13.91399669647217</v>
       </c>
       <c r="C198" t="n">
-        <v>14.19113080065994</v>
+        <v>14.19112982799074</v>
       </c>
       <c r="D198" t="n">
-        <v>13.7419836562549</v>
+        <v>13.74198271437053</v>
       </c>
       <c r="E198" t="n">
-        <v>13.7419836562549</v>
+        <v>13.74198271437053</v>
       </c>
       <c r="F198" t="n">
         <v>8247400</v>
@@ -4392,16 +4392,16 @@
         <v>44543</v>
       </c>
       <c r="B199" t="n">
-        <v>13.74198246002197</v>
+        <v>13.74198341369629</v>
       </c>
       <c r="C199" t="n">
-        <v>14.12423473388242</v>
+        <v>14.12423571408451</v>
       </c>
       <c r="D199" t="n">
-        <v>13.66553200524988</v>
+        <v>13.66553295361865</v>
       </c>
       <c r="E199" t="n">
-        <v>13.9617772896514</v>
+        <v>13.96177825857917</v>
       </c>
       <c r="F199" t="n">
         <v>11783000</v>
@@ -4412,16 +4412,16 @@
         <v>44544</v>
       </c>
       <c r="B200" t="n">
-        <v>13.76109504699707</v>
+        <v>13.76109409332275</v>
       </c>
       <c r="C200" t="n">
-        <v>14.14334824413447</v>
+        <v>14.14334726396917</v>
       </c>
       <c r="D200" t="n">
-        <v>13.56996890410904</v>
+        <v>13.56996796368018</v>
       </c>
       <c r="E200" t="n">
-        <v>13.88532726771463</v>
+        <v>13.88532630543074</v>
       </c>
       <c r="F200" t="n">
         <v>6761100</v>
@@ -4452,16 +4452,16 @@
         <v>44546</v>
       </c>
       <c r="B202" t="n">
-        <v>13.89488315582275</v>
+        <v>13.89488410949707</v>
       </c>
       <c r="C202" t="n">
-        <v>14.28669195834289</v>
+        <v>14.28669293890897</v>
       </c>
       <c r="D202" t="n">
-        <v>13.82798923676653</v>
+        <v>13.82799018584958</v>
       </c>
       <c r="E202" t="n">
-        <v>14.21024150474683</v>
+        <v>14.21024248006574</v>
       </c>
       <c r="F202" t="n">
         <v>5287600</v>
@@ -4572,16 +4572,16 @@
         <v>44557</v>
       </c>
       <c r="B208" t="n">
-        <v>13.03481578826904</v>
+        <v>13.03481674194336</v>
       </c>
       <c r="C208" t="n">
-        <v>13.56041245676783</v>
+        <v>13.5604134488967</v>
       </c>
       <c r="D208" t="n">
-        <v>12.90102703170205</v>
+        <v>12.9010279755879</v>
       </c>
       <c r="E208" t="n">
-        <v>13.46484984038684</v>
+        <v>13.46485082552401</v>
       </c>
       <c r="F208" t="n">
         <v>14666400</v>
@@ -4592,16 +4592,16 @@
         <v>44558</v>
       </c>
       <c r="B209" t="n">
-        <v>12.51877403259277</v>
+        <v>12.51877498626709</v>
       </c>
       <c r="C209" t="n">
-        <v>13.12082112455441</v>
+        <v>13.12082212409239</v>
       </c>
       <c r="D209" t="n">
-        <v>12.31809136481846</v>
+        <v>12.31809230320487</v>
       </c>
       <c r="E209" t="n">
-        <v>13.12082112455441</v>
+        <v>13.12082212409239</v>
       </c>
       <c r="F209" t="n">
         <v>22962600</v>
@@ -4612,16 +4612,16 @@
         <v>44559</v>
       </c>
       <c r="B210" t="n">
-        <v>12.2703104019165</v>
+        <v>12.27030944824219</v>
       </c>
       <c r="C210" t="n">
-        <v>12.53788700590259</v>
+        <v>12.53788603143165</v>
       </c>
       <c r="D210" t="n">
-        <v>12.2511973316654</v>
+        <v>12.25119637947659</v>
       </c>
       <c r="E210" t="n">
-        <v>12.51877484701283</v>
+        <v>12.51877387402733</v>
       </c>
       <c r="F210" t="n">
         <v>10451000</v>
@@ -4652,16 +4652,16 @@
         <v>44564</v>
       </c>
       <c r="B212" t="n">
-        <v>12.15563488006592</v>
+        <v>12.1556339263916</v>
       </c>
       <c r="C212" t="n">
-        <v>12.49966194701974</v>
+        <v>12.49966096635466</v>
       </c>
       <c r="D212" t="n">
-        <v>11.84983213141227</v>
+        <v>11.84983120172981</v>
       </c>
       <c r="E212" t="n">
-        <v>12.49966194701974</v>
+        <v>12.49966096635466</v>
       </c>
       <c r="F212" t="n">
         <v>16124600</v>
@@ -4672,16 +4672,16 @@
         <v>44565</v>
       </c>
       <c r="B213" t="n">
-        <v>12.15563488006592</v>
+        <v>12.1556339263916</v>
       </c>
       <c r="C213" t="n">
-        <v>12.25119749853907</v>
+        <v>12.25119653736736</v>
       </c>
       <c r="D213" t="n">
-        <v>11.89761389632953</v>
+        <v>11.89761296289834</v>
       </c>
       <c r="E213" t="n">
-        <v>12.20341664498318</v>
+        <v>12.20341568756013</v>
       </c>
       <c r="F213" t="n">
         <v>9389900</v>
@@ -4692,16 +4692,16 @@
         <v>44566</v>
       </c>
       <c r="B214" t="n">
-        <v>11.45802211761475</v>
+        <v>11.45802307128906</v>
       </c>
       <c r="C214" t="n">
-        <v>12.13652055763904</v>
+        <v>12.13652156778615</v>
       </c>
       <c r="D214" t="n">
-        <v>11.41024035762631</v>
+        <v>11.41024130732365</v>
       </c>
       <c r="E214" t="n">
-        <v>12.11740840046043</v>
+        <v>12.1174094090168</v>
       </c>
       <c r="F214" t="n">
         <v>11220000</v>
@@ -4752,16 +4752,16 @@
         <v>44571</v>
       </c>
       <c r="B217" t="n">
-        <v>10.79863739013672</v>
+        <v>10.79863834381104</v>
       </c>
       <c r="C217" t="n">
-        <v>10.8559747764533</v>
+        <v>10.85597573519133</v>
       </c>
       <c r="D217" t="n">
-        <v>10.54061641762812</v>
+        <v>10.54061734851548</v>
       </c>
       <c r="E217" t="n">
-        <v>10.76041216213855</v>
+        <v>10.76041311243704</v>
       </c>
       <c r="F217" t="n">
         <v>8755800</v>
@@ -4772,16 +4772,16 @@
         <v>44572</v>
       </c>
       <c r="B218" t="n">
-        <v>10.94198322296143</v>
+        <v>10.94198226928711</v>
       </c>
       <c r="C218" t="n">
-        <v>10.96109629518389</v>
+        <v>10.96109533984372</v>
       </c>
       <c r="D218" t="n">
-        <v>10.66485005526586</v>
+        <v>10.66484912574574</v>
       </c>
       <c r="E218" t="n">
-        <v>10.70307528834934</v>
+        <v>10.7030743554976</v>
       </c>
       <c r="F218" t="n">
         <v>6045500</v>
@@ -4792,16 +4792,16 @@
         <v>44573</v>
       </c>
       <c r="B219" t="n">
-        <v>11.27645301818848</v>
+        <v>11.27645397186279</v>
       </c>
       <c r="C219" t="n">
-        <v>11.28600955287783</v>
+        <v>11.28601050736037</v>
       </c>
       <c r="D219" t="n">
-        <v>10.80819375474579</v>
+        <v>10.80819466881839</v>
       </c>
       <c r="E219" t="n">
-        <v>10.94198159495152</v>
+        <v>10.94198252033886</v>
       </c>
       <c r="F219" t="n">
         <v>7862000</v>
@@ -4812,16 +4812,16 @@
         <v>44574</v>
       </c>
       <c r="B220" t="n">
-        <v>11.48669242858887</v>
+        <v>11.48669338226318</v>
       </c>
       <c r="C220" t="n">
-        <v>11.57269850823688</v>
+        <v>11.57269946905179</v>
       </c>
       <c r="D220" t="n">
-        <v>11.15222099941061</v>
+        <v>11.15222192531568</v>
       </c>
       <c r="E220" t="n">
-        <v>11.27645321849507</v>
+        <v>11.27645415471443</v>
       </c>
       <c r="F220" t="n">
         <v>9668300</v>
@@ -4852,16 +4852,16 @@
         <v>44578</v>
       </c>
       <c r="B222" t="n">
-        <v>11.47713661193848</v>
+        <v>11.47713470458984</v>
       </c>
       <c r="C222" t="n">
-        <v>11.61092446289281</v>
+        <v>11.6109225333104</v>
       </c>
       <c r="D222" t="n">
-        <v>11.41024177509993</v>
+        <v>11.41023987886834</v>
       </c>
       <c r="E222" t="n">
-        <v>11.59181230333992</v>
+        <v>11.5918103769337</v>
       </c>
       <c r="F222" t="n">
         <v>4569300</v>
@@ -4892,16 +4892,16 @@
         <v>44580</v>
       </c>
       <c r="B224" t="n">
-        <v>11.49624729156494</v>
+        <v>11.49624824523926</v>
       </c>
       <c r="C224" t="n">
-        <v>11.69692995352369</v>
+        <v>11.69693092384569</v>
       </c>
       <c r="D224" t="n">
-        <v>11.41979684047221</v>
+        <v>11.41979778780455</v>
       </c>
       <c r="E224" t="n">
-        <v>11.41979684047221</v>
+        <v>11.41979778780455</v>
       </c>
       <c r="F224" t="n">
         <v>5074700</v>
@@ -4912,16 +4912,16 @@
         <v>44581</v>
       </c>
       <c r="B225" t="n">
-        <v>11.41979694366455</v>
+        <v>11.41979789733887</v>
       </c>
       <c r="C225" t="n">
-        <v>11.69693005922028</v>
+        <v>11.69693103603816</v>
       </c>
       <c r="D225" t="n">
-        <v>11.36245956050752</v>
+        <v>11.36246050939355</v>
       </c>
       <c r="E225" t="n">
-        <v>11.56314222427969</v>
+        <v>11.56314318992485</v>
       </c>
       <c r="F225" t="n">
         <v>7365800</v>
@@ -4932,16 +4932,16 @@
         <v>44582</v>
       </c>
       <c r="B226" t="n">
-        <v>11.48669242858887</v>
+        <v>11.48669338226318</v>
       </c>
       <c r="C226" t="n">
-        <v>11.63003680603022</v>
+        <v>11.6300377716056</v>
       </c>
       <c r="D226" t="n">
-        <v>11.21911492070173</v>
+        <v>11.21911585216062</v>
       </c>
       <c r="E226" t="n">
-        <v>11.37201583300219</v>
+        <v>11.37201677715557</v>
       </c>
       <c r="F226" t="n">
         <v>8537100</v>
@@ -4952,16 +4952,16 @@
         <v>44585</v>
       </c>
       <c r="B227" t="n">
-        <v>11.50580406188965</v>
+        <v>11.50580501556396</v>
       </c>
       <c r="C227" t="n">
-        <v>11.6395928097279</v>
+        <v>11.63959377449148</v>
       </c>
       <c r="D227" t="n">
-        <v>11.32423446465893</v>
+        <v>11.3242354032836</v>
       </c>
       <c r="E227" t="n">
-        <v>11.4675788355589</v>
+        <v>11.46757978606487</v>
       </c>
       <c r="F227" t="n">
         <v>6551900</v>
@@ -4972,16 +4972,16 @@
         <v>44586</v>
       </c>
       <c r="B228" t="n">
-        <v>11.75426959991455</v>
+        <v>11.75426864624023</v>
       </c>
       <c r="C228" t="n">
-        <v>11.8880574490392</v>
+        <v>11.8880564845101</v>
       </c>
       <c r="D228" t="n">
-        <v>10.98020755433911</v>
+        <v>10.98020666346776</v>
       </c>
       <c r="E228" t="n">
-        <v>11.42935468970662</v>
+        <v>11.42935376239404</v>
       </c>
       <c r="F228" t="n">
         <v>40426700</v>
@@ -5012,16 +5012,16 @@
         <v>44588</v>
       </c>
       <c r="B230" t="n">
-        <v>11.99317741394043</v>
+        <v>11.99317646026611</v>
       </c>
       <c r="C230" t="n">
-        <v>12.13652179718475</v>
+        <v>12.13652083211196</v>
       </c>
       <c r="D230" t="n">
-        <v>11.66826250646786</v>
+        <v>11.66826157863015</v>
       </c>
       <c r="E230" t="n">
-        <v>11.85938865458074</v>
+        <v>11.85938771154504</v>
       </c>
       <c r="F230" t="n">
         <v>13761300</v>
@@ -5032,16 +5032,16 @@
         <v>44589</v>
       </c>
       <c r="B231" t="n">
-        <v>11.83071994781494</v>
+        <v>11.83072090148926</v>
       </c>
       <c r="C231" t="n">
-        <v>12.04095916619962</v>
+        <v>12.04096013682132</v>
       </c>
       <c r="D231" t="n">
-        <v>11.4580232758641</v>
+        <v>11.45802419949534</v>
       </c>
       <c r="E231" t="n">
-        <v>11.94539563656258</v>
+        <v>11.9453965994809</v>
       </c>
       <c r="F231" t="n">
         <v>14924100</v>
@@ -5092,16 +5092,16 @@
         <v>44594</v>
       </c>
       <c r="B234" t="n">
-        <v>11.94539451599121</v>
+        <v>11.94539546966553</v>
       </c>
       <c r="C234" t="n">
-        <v>12.27986592698347</v>
+        <v>12.2798669073607</v>
       </c>
       <c r="D234" t="n">
-        <v>11.81160576932205</v>
+        <v>11.81160671231519</v>
       </c>
       <c r="E234" t="n">
-        <v>12.02184496798465</v>
+        <v>12.02184592776248</v>
       </c>
       <c r="F234" t="n">
         <v>9442200</v>
@@ -5112,16 +5112,16 @@
         <v>44595</v>
       </c>
       <c r="B235" t="n">
-        <v>11.94539451599121</v>
+        <v>11.94539546966553</v>
       </c>
       <c r="C235" t="n">
-        <v>12.21297109796826</v>
+        <v>12.21297207300486</v>
       </c>
       <c r="D235" t="n">
-        <v>11.89761275565499</v>
+        <v>11.8976137055146</v>
       </c>
       <c r="E235" t="n">
-        <v>12.04095803666365</v>
+        <v>12.04095899796739</v>
       </c>
       <c r="F235" t="n">
         <v>8796800</v>
@@ -5192,16 +5192,16 @@
         <v>44601</v>
       </c>
       <c r="B239" t="n">
-        <v>12.05051326751709</v>
+        <v>12.05051422119141</v>
       </c>
       <c r="C239" t="n">
-        <v>12.28942115006283</v>
+        <v>12.28942212264425</v>
       </c>
       <c r="D239" t="n">
-        <v>11.91672543656267</v>
+        <v>11.91672637964906</v>
       </c>
       <c r="E239" t="n">
-        <v>11.95495066131554</v>
+        <v>11.95495160742706</v>
       </c>
       <c r="F239" t="n">
         <v>9060800</v>
@@ -5252,16 +5252,16 @@
         <v>44606</v>
       </c>
       <c r="B242" t="n">
-        <v>11.78293800354004</v>
+        <v>11.78293895721436</v>
       </c>
       <c r="C242" t="n">
-        <v>11.97406414854188</v>
+        <v>11.97406511768535</v>
       </c>
       <c r="D242" t="n">
-        <v>11.639593622629</v>
+        <v>11.63959456470146</v>
       </c>
       <c r="E242" t="n">
-        <v>11.79249453863047</v>
+        <v>11.79249549307826</v>
       </c>
       <c r="F242" t="n">
         <v>5445000</v>
@@ -5272,16 +5272,16 @@
         <v>44607</v>
       </c>
       <c r="B243" t="n">
-        <v>11.63959312438965</v>
+        <v>11.63959407806396</v>
       </c>
       <c r="C243" t="n">
-        <v>11.95495147798393</v>
+        <v>11.95495245749671</v>
       </c>
       <c r="D243" t="n">
-        <v>11.53447306561735</v>
+        <v>11.5344740106788</v>
       </c>
       <c r="E243" t="n">
-        <v>11.92628187393986</v>
+        <v>11.92628285110363</v>
       </c>
       <c r="F243" t="n">
         <v>11329100</v>
@@ -5292,16 +5292,16 @@
         <v>44608</v>
       </c>
       <c r="B244" t="n">
-        <v>12.47099208831787</v>
+        <v>12.4709939956665</v>
       </c>
       <c r="C244" t="n">
-        <v>12.6430051500549</v>
+        <v>12.64300708371169</v>
       </c>
       <c r="D244" t="n">
-        <v>11.56314228509255</v>
+        <v>11.56314405359208</v>
       </c>
       <c r="E244" t="n">
-        <v>11.65870489464395</v>
+        <v>11.65870667775909</v>
       </c>
       <c r="F244" t="n">
         <v>21489000</v>
@@ -5332,16 +5332,16 @@
         <v>44610</v>
       </c>
       <c r="B246" t="n">
-        <v>12.13652038574219</v>
+        <v>12.1365213394165</v>
       </c>
       <c r="C246" t="n">
-        <v>12.83413188442568</v>
+        <v>12.83413289291753</v>
       </c>
       <c r="D246" t="n">
-        <v>12.13652038574219</v>
+        <v>12.1365213394165</v>
       </c>
       <c r="E246" t="n">
-        <v>12.80546228202191</v>
+        <v>12.80546328826094</v>
       </c>
       <c r="F246" t="n">
         <v>11604500</v>
@@ -5372,16 +5372,16 @@
         <v>44614</v>
       </c>
       <c r="B248" t="n">
-        <v>12.51877403259277</v>
+        <v>12.51877498626709</v>
       </c>
       <c r="C248" t="n">
-        <v>12.63344971255505</v>
+        <v>12.63345067496531</v>
       </c>
       <c r="D248" t="n">
-        <v>12.08873909353262</v>
+        <v>12.08874001444707</v>
       </c>
       <c r="E248" t="n">
-        <v>12.1460773891944</v>
+        <v>12.14607831447686</v>
       </c>
       <c r="F248" t="n">
         <v>15416600</v>
@@ -5392,16 +5392,16 @@
         <v>44615</v>
       </c>
       <c r="B249" t="n">
-        <v>12.73856925964355</v>
+        <v>12.73856735229492</v>
       </c>
       <c r="C249" t="n">
-        <v>12.87235801283171</v>
+        <v>12.87235608545085</v>
       </c>
       <c r="D249" t="n">
-        <v>12.51877442729301</v>
+        <v>12.5187725528543</v>
       </c>
       <c r="E249" t="n">
-        <v>12.51877442729301</v>
+        <v>12.5187725528543</v>
       </c>
       <c r="F249" t="n">
         <v>5598100</v>
@@ -5432,16 +5432,16 @@
         <v>44617</v>
       </c>
       <c r="B251" t="n">
-        <v>12.86280059814453</v>
+        <v>12.86280155181885</v>
       </c>
       <c r="C251" t="n">
-        <v>13.13993370900733</v>
+        <v>13.13993468322886</v>
       </c>
       <c r="D251" t="n">
-        <v>12.72901185410822</v>
+        <v>12.72901279786317</v>
       </c>
       <c r="E251" t="n">
-        <v>12.83413190705149</v>
+        <v>12.83413285860025</v>
       </c>
       <c r="F251" t="n">
         <v>8089600</v>
@@ -5472,16 +5472,16 @@
         <v>44623</v>
       </c>
       <c r="B253" t="n">
-        <v>12.56655502319336</v>
+        <v>12.56655597686768</v>
       </c>
       <c r="C253" t="n">
-        <v>12.95836473998952</v>
+        <v>12.95836572339823</v>
       </c>
       <c r="D253" t="n">
-        <v>12.337203660699</v>
+        <v>12.33720459696787</v>
       </c>
       <c r="E253" t="n">
-        <v>12.80546292029864</v>
+        <v>12.80546389210365</v>
       </c>
       <c r="F253" t="n">
         <v>12631200</v>
@@ -5532,16 +5532,16 @@
         <v>44628</v>
       </c>
       <c r="B256" t="n">
-        <v>11.75426959991455</v>
+        <v>11.75426864624023</v>
       </c>
       <c r="C256" t="n">
-        <v>11.99317751490728</v>
+        <v>11.99317654184934</v>
       </c>
       <c r="D256" t="n">
-        <v>11.52491822024826</v>
+        <v>11.52491728518221</v>
       </c>
       <c r="E256" t="n">
-        <v>11.74471306458811</v>
+        <v>11.74471211168916</v>
       </c>
       <c r="F256" t="n">
         <v>10151100</v>
@@ -5592,16 +5592,16 @@
         <v>44631</v>
       </c>
       <c r="B259" t="n">
-        <v>12.40409755706787</v>
+        <v>12.40409851074219</v>
       </c>
       <c r="C259" t="n">
-        <v>12.92969511198934</v>
+        <v>12.9296961060736</v>
       </c>
       <c r="D259" t="n">
-        <v>12.20341579878139</v>
+        <v>12.20341673702652</v>
       </c>
       <c r="E259" t="n">
-        <v>12.92969511198934</v>
+        <v>12.9296961060736</v>
       </c>
       <c r="F259" t="n">
         <v>7293900</v>
@@ -5612,16 +5612,16 @@
         <v>44634</v>
       </c>
       <c r="B260" t="n">
-        <v>12.51877403259277</v>
+        <v>12.51877498626709</v>
       </c>
       <c r="C260" t="n">
-        <v>12.74812539251733</v>
+        <v>12.74812636366353</v>
       </c>
       <c r="D260" t="n">
-        <v>12.3849852836228</v>
+        <v>12.38498622710516</v>
       </c>
       <c r="E260" t="n">
-        <v>12.43276704478074</v>
+        <v>12.43276799190309</v>
       </c>
       <c r="F260" t="n">
         <v>4274300</v>
@@ -5672,16 +5672,16 @@
         <v>44637</v>
       </c>
       <c r="B263" t="n">
-        <v>13.12082195281982</v>
+        <v>13.12082290649414</v>
       </c>
       <c r="C263" t="n">
-        <v>13.24505417512824</v>
+        <v>13.24505513783225</v>
       </c>
       <c r="D263" t="n">
-        <v>12.87235841956435</v>
+        <v>12.87235935517934</v>
       </c>
       <c r="E263" t="n">
-        <v>13.09215325885984</v>
+        <v>13.0921542104504</v>
       </c>
       <c r="F263" t="n">
         <v>6159800</v>
@@ -5692,16 +5692,16 @@
         <v>44638</v>
       </c>
       <c r="B264" t="n">
-        <v>13.58908176422119</v>
+        <v>13.58908271789551</v>
       </c>
       <c r="C264" t="n">
-        <v>13.78020790415765</v>
+        <v>13.78020887124509</v>
       </c>
       <c r="D264" t="n">
-        <v>12.98703373990036</v>
+        <v>12.98703465132328</v>
       </c>
       <c r="E264" t="n">
-        <v>13.04437112620064</v>
+        <v>13.04437204164746</v>
       </c>
       <c r="F264" t="n">
         <v>10366600</v>
@@ -5712,16 +5712,16 @@
         <v>44641</v>
       </c>
       <c r="B265" t="n">
-        <v>13.56041240692139</v>
+        <v>13.5604133605957</v>
       </c>
       <c r="C265" t="n">
-        <v>13.62730724063966</v>
+        <v>13.62730819901854</v>
       </c>
       <c r="D265" t="n">
-        <v>13.18771665509124</v>
+        <v>13.18771758255467</v>
       </c>
       <c r="E265" t="n">
-        <v>13.58908201195551</v>
+        <v>13.58908296764609</v>
       </c>
       <c r="F265" t="n">
         <v>3916100</v>
@@ -5772,16 +5772,16 @@
         <v>44644</v>
       </c>
       <c r="B268" t="n">
-        <v>14.6307201385498</v>
+        <v>14.63071918487549</v>
       </c>
       <c r="C268" t="n">
-        <v>14.74539582072832</v>
+        <v>14.7453948595791</v>
       </c>
       <c r="D268" t="n">
-        <v>14.35358701211139</v>
+        <v>14.35358607650145</v>
       </c>
       <c r="E268" t="n">
-        <v>14.39181223950423</v>
+        <v>14.39181130140265</v>
       </c>
       <c r="F268" t="n">
         <v>7986800</v>
@@ -5792,16 +5792,16 @@
         <v>44645</v>
       </c>
       <c r="B269" t="n">
-        <v>15.13720607757568</v>
+        <v>15.13720512390137</v>
       </c>
       <c r="C269" t="n">
-        <v>15.24232523512279</v>
+        <v>15.24232427482575</v>
       </c>
       <c r="D269" t="n">
-        <v>14.64027716256451</v>
+        <v>14.64027624019771</v>
       </c>
       <c r="E269" t="n">
-        <v>14.71672762466447</v>
+        <v>14.71672669748114</v>
       </c>
       <c r="F269" t="n">
         <v>8426200</v>
@@ -5852,16 +5852,16 @@
         <v>44650</v>
       </c>
       <c r="B272" t="n">
-        <v>15.45256328582764</v>
+        <v>15.45256423950195</v>
       </c>
       <c r="C272" t="n">
-        <v>15.82525903236704</v>
+        <v>15.82526000904275</v>
       </c>
       <c r="D272" t="n">
-        <v>15.39522589929603</v>
+        <v>15.3952268494317</v>
       </c>
       <c r="E272" t="n">
-        <v>15.51945720723495</v>
+        <v>15.51945816503771</v>
       </c>
       <c r="F272" t="n">
         <v>8944100</v>
@@ -5872,16 +5872,16 @@
         <v>44651</v>
       </c>
       <c r="B273" t="n">
-        <v>15.56723880767822</v>
+        <v>15.56723976135254</v>
       </c>
       <c r="C273" t="n">
-        <v>15.8157014064154</v>
+        <v>15.81570237531094</v>
       </c>
       <c r="D273" t="n">
-        <v>15.42389261715424</v>
+        <v>15.42389356204693</v>
       </c>
       <c r="E273" t="n">
-        <v>15.42389261715424</v>
+        <v>15.42389356204693</v>
       </c>
       <c r="F273" t="n">
         <v>17319900</v>
@@ -5892,16 +5892,16 @@
         <v>44652</v>
       </c>
       <c r="B274" t="n">
-        <v>15.74880886077881</v>
+        <v>15.74880981445312</v>
       </c>
       <c r="C274" t="n">
-        <v>15.97816023377391</v>
+        <v>15.97816120133668</v>
       </c>
       <c r="D274" t="n">
-        <v>15.47167663526406</v>
+        <v>15.47167757215655</v>
       </c>
       <c r="E274" t="n">
-        <v>15.7201410783561</v>
+        <v>15.72014203029443</v>
       </c>
       <c r="F274" t="n">
         <v>8302400</v>
@@ -5912,16 +5912,16 @@
         <v>44655</v>
       </c>
       <c r="B275" t="n">
-        <v>15.56723880767822</v>
+        <v>15.56723976135254</v>
       </c>
       <c r="C275" t="n">
-        <v>15.86348407749757</v>
+        <v>15.86348504932035</v>
       </c>
       <c r="D275" t="n">
-        <v>15.52901267081248</v>
+        <v>15.52901362214501</v>
       </c>
       <c r="E275" t="n">
-        <v>15.75836402383932</v>
+        <v>15.75836498922228</v>
       </c>
       <c r="F275" t="n">
         <v>2672100</v>
@@ -5932,16 +5932,16 @@
         <v>44656</v>
       </c>
       <c r="B276" t="n">
-        <v>15.45256328582764</v>
+        <v>15.45256423950195</v>
       </c>
       <c r="C276" t="n">
-        <v>15.65324505004958</v>
+        <v>15.65324601610922</v>
       </c>
       <c r="D276" t="n">
-        <v>15.35699975979319</v>
+        <v>15.35700070756969</v>
       </c>
       <c r="E276" t="n">
-        <v>15.57679459376655</v>
+        <v>15.57679555510796</v>
       </c>
       <c r="F276" t="n">
         <v>10716200</v>
@@ -5952,16 +5952,16 @@
         <v>44657</v>
       </c>
       <c r="B277" t="n">
-        <v>15.56723880767822</v>
+        <v>15.56723976135254</v>
       </c>
       <c r="C277" t="n">
-        <v>15.70102664126324</v>
+        <v>15.70102760313362</v>
       </c>
       <c r="D277" t="n">
-        <v>15.13720388155133</v>
+        <v>15.13720480888101</v>
       </c>
       <c r="E277" t="n">
-        <v>15.38566830301103</v>
+        <v>15.38566924556204</v>
       </c>
       <c r="F277" t="n">
         <v>10924400</v>
@@ -5972,16 +5972,16 @@
         <v>44658</v>
       </c>
       <c r="B278" t="n">
-        <v>15.38566875457764</v>
+        <v>15.38567066192627</v>
       </c>
       <c r="C278" t="n">
-        <v>15.52901312658622</v>
+        <v>15.52901505170514</v>
       </c>
       <c r="D278" t="n">
-        <v>15.25188000570468</v>
+        <v>15.25188189646763</v>
       </c>
       <c r="E278" t="n">
-        <v>15.3665556855838</v>
+        <v>15.366557590563</v>
       </c>
       <c r="F278" t="n">
         <v>6566700</v>
@@ -5992,16 +5992,16 @@
         <v>44659</v>
       </c>
       <c r="B279" t="n">
-        <v>15.40478420257568</v>
+        <v>15.40478324890137</v>
       </c>
       <c r="C279" t="n">
-        <v>15.57679638191676</v>
+        <v>15.57679541759357</v>
       </c>
       <c r="D279" t="n">
-        <v>15.07031273442055</v>
+        <v>15.07031180145259</v>
       </c>
       <c r="E279" t="n">
-        <v>15.32833373751647</v>
+        <v>15.32833278857503</v>
       </c>
       <c r="F279" t="n">
         <v>3069100</v>
@@ -6012,16 +6012,16 @@
         <v>44662</v>
       </c>
       <c r="B280" t="n">
-        <v>15.29010486602783</v>
+        <v>15.29010677337646</v>
       </c>
       <c r="C280" t="n">
-        <v>15.49078661748763</v>
+        <v>15.4907885498701</v>
       </c>
       <c r="D280" t="n">
-        <v>15.21365441460659</v>
+        <v>15.21365631241849</v>
       </c>
       <c r="E280" t="n">
-        <v>15.38566838598501</v>
+        <v>15.38567030525462</v>
       </c>
       <c r="F280" t="n">
         <v>10289300</v>
@@ -6032,16 +6032,16 @@
         <v>44663</v>
       </c>
       <c r="B281" t="n">
-        <v>15.72014236450195</v>
+        <v>15.72014141082764</v>
       </c>
       <c r="C281" t="n">
-        <v>15.82526061318996</v>
+        <v>15.82525965313857</v>
       </c>
       <c r="D281" t="n">
-        <v>15.39522743716192</v>
+        <v>15.39522650319881</v>
       </c>
       <c r="E281" t="n">
-        <v>15.48123443691209</v>
+        <v>15.48123349773131</v>
       </c>
       <c r="F281" t="n">
         <v>9798400</v>
@@ -6052,16 +6052,16 @@
         <v>44664</v>
       </c>
       <c r="B282" t="n">
-        <v>15.76792335510254</v>
+        <v>15.76792240142822</v>
       </c>
       <c r="C282" t="n">
-        <v>16.02594435654861</v>
+        <v>16.02594338726869</v>
       </c>
       <c r="D282" t="n">
-        <v>15.69147289053217</v>
+        <v>15.69147194148172</v>
       </c>
       <c r="E282" t="n">
-        <v>15.78703642692584</v>
+        <v>15.78703547209553</v>
       </c>
       <c r="F282" t="n">
         <v>7212700</v>
@@ -6072,16 +6072,16 @@
         <v>44665</v>
       </c>
       <c r="B283" t="n">
-        <v>15.64369106292725</v>
+        <v>15.64369010925293</v>
       </c>
       <c r="C283" t="n">
-        <v>15.79659198257972</v>
+        <v>15.79659101958422</v>
       </c>
       <c r="D283" t="n">
-        <v>15.48123360795615</v>
+        <v>15.4812326641856</v>
       </c>
       <c r="E283" t="n">
-        <v>15.72014152275348</v>
+        <v>15.72014056441858</v>
       </c>
       <c r="F283" t="n">
         <v>4607000</v>
@@ -6092,16 +6092,16 @@
         <v>44669</v>
       </c>
       <c r="B284" t="n">
-        <v>15.31877613067627</v>
+        <v>15.31877517700195</v>
       </c>
       <c r="C284" t="n">
-        <v>15.67235882333666</v>
+        <v>15.67235784764996</v>
       </c>
       <c r="D284" t="n">
-        <v>15.31877613067627</v>
+        <v>15.31877517700195</v>
       </c>
       <c r="E284" t="n">
-        <v>15.56724058043038</v>
+        <v>15.56723961128785</v>
       </c>
       <c r="F284" t="n">
         <v>3539900</v>
@@ -6112,16 +6112,16 @@
         <v>44670</v>
       </c>
       <c r="B285" t="n">
-        <v>15.61502265930176</v>
+        <v>15.61502075195312</v>
       </c>
       <c r="C285" t="n">
-        <v>15.7774801267818</v>
+        <v>15.77747819958926</v>
       </c>
       <c r="D285" t="n">
-        <v>15.18498856182694</v>
+        <v>15.18498670700624</v>
       </c>
       <c r="E285" t="n">
-        <v>15.3283338685595</v>
+        <v>15.32833199622942</v>
       </c>
       <c r="F285" t="n">
         <v>7756800</v>
@@ -6132,16 +6132,16 @@
         <v>44671</v>
       </c>
       <c r="B286" t="n">
-        <v>15.85393047332764</v>
+        <v>15.853928565979</v>
       </c>
       <c r="C286" t="n">
-        <v>16.33174633612178</v>
+        <v>16.33174437128826</v>
       </c>
       <c r="D286" t="n">
-        <v>15.72014261501659</v>
+        <v>15.72014072376366</v>
       </c>
       <c r="E286" t="n">
-        <v>15.74881040024161</v>
+        <v>15.74880850553972</v>
       </c>
       <c r="F286" t="n">
         <v>12326800</v>
@@ -6152,16 +6152,16 @@
         <v>44673</v>
       </c>
       <c r="B287" t="n">
-        <v>15.31877613067627</v>
+        <v>15.31877517700195</v>
       </c>
       <c r="C287" t="n">
-        <v>15.74880928305156</v>
+        <v>15.74880830260542</v>
       </c>
       <c r="D287" t="n">
-        <v>15.14676214063706</v>
+        <v>15.14676119767152</v>
       </c>
       <c r="E287" t="n">
-        <v>15.74880928305156</v>
+        <v>15.74880830260542</v>
       </c>
       <c r="F287" t="n">
         <v>8878800</v>
@@ -6192,16 +6192,16 @@
         <v>44677</v>
       </c>
       <c r="B289" t="n">
-        <v>15.12764739990234</v>
+        <v>15.12764835357666</v>
       </c>
       <c r="C289" t="n">
-        <v>15.30921790520048</v>
+        <v>15.30921887032133</v>
       </c>
       <c r="D289" t="n">
-        <v>15.02252825724008</v>
+        <v>15.02252920428749</v>
       </c>
       <c r="E289" t="n">
-        <v>15.21365438542659</v>
+        <v>15.21365534452294</v>
       </c>
       <c r="F289" t="n">
         <v>9387600</v>
@@ -6212,16 +6212,16 @@
         <v>44678</v>
       </c>
       <c r="B290" t="n">
-        <v>15.18498706817627</v>
+        <v>15.18498611450195</v>
       </c>
       <c r="C290" t="n">
-        <v>15.48123327719457</v>
+        <v>15.48123230491487</v>
       </c>
       <c r="D290" t="n">
-        <v>14.96519131735082</v>
+        <v>14.9651903774805</v>
       </c>
       <c r="E290" t="n">
-        <v>15.2901062203511</v>
+        <v>15.2901052600749</v>
       </c>
       <c r="F290" t="n">
         <v>7959000</v>
@@ -6232,16 +6232,16 @@
         <v>44679</v>
       </c>
       <c r="B291" t="n">
-        <v>14.8409595489502</v>
+        <v>14.84095764160156</v>
       </c>
       <c r="C291" t="n">
-        <v>15.38567021943929</v>
+        <v>15.38566824208486</v>
       </c>
       <c r="D291" t="n">
-        <v>14.8409595489502</v>
+        <v>14.84095764160156</v>
       </c>
       <c r="E291" t="n">
-        <v>15.3283328297213</v>
+        <v>15.32833085973584</v>
       </c>
       <c r="F291" t="n">
         <v>5384600</v>
@@ -6252,16 +6252,16 @@
         <v>44680</v>
       </c>
       <c r="B292" t="n">
-        <v>14.72057247161865</v>
+        <v>14.72057151794434</v>
       </c>
       <c r="C292" t="n">
-        <v>15.13482972068782</v>
+        <v>15.13482874017579</v>
       </c>
       <c r="D292" t="n">
-        <v>14.72057247161865</v>
+        <v>14.72057151794434</v>
       </c>
       <c r="E292" t="n">
-        <v>15.06739283595885</v>
+        <v>15.06739185981573</v>
       </c>
       <c r="F292" t="n">
         <v>7651000</v>
@@ -6272,16 +6272,16 @@
         <v>44683</v>
       </c>
       <c r="B293" t="n">
-        <v>14.69167137145996</v>
+        <v>14.69167041778564</v>
       </c>
       <c r="C293" t="n">
-        <v>14.97105393783902</v>
+        <v>14.97105296602926</v>
       </c>
       <c r="D293" t="n">
-        <v>14.44119019642807</v>
+        <v>14.44118925901314</v>
       </c>
       <c r="E293" t="n">
-        <v>14.54716349596546</v>
+        <v>14.54716255167152</v>
       </c>
       <c r="F293" t="n">
         <v>5536000</v>
@@ -6312,16 +6312,16 @@
         <v>44685</v>
       </c>
       <c r="B295" t="n">
-        <v>14.79764270782471</v>
+        <v>14.79764175415039</v>
       </c>
       <c r="C295" t="n">
-        <v>14.95178559456712</v>
+        <v>14.95178463095864</v>
       </c>
       <c r="D295" t="n">
-        <v>14.25814581988137</v>
+        <v>14.2581449009764</v>
       </c>
       <c r="E295" t="n">
-        <v>14.43155507448386</v>
+        <v>14.43155414440306</v>
       </c>
       <c r="F295" t="n">
         <v>5127000</v>
@@ -6372,16 +6372,16 @@
         <v>44690</v>
       </c>
       <c r="B298" t="n">
-        <v>14.21961116790771</v>
+        <v>14.2196102142334</v>
       </c>
       <c r="C298" t="n">
-        <v>14.32558354746724</v>
+        <v>14.32558258668562</v>
       </c>
       <c r="D298" t="n">
-        <v>13.92096039822737</v>
+        <v>13.92095946458282</v>
       </c>
       <c r="E298" t="n">
-        <v>14.04620098430244</v>
+        <v>14.04620004225831</v>
       </c>
       <c r="F298" t="n">
         <v>11844800</v>
@@ -6392,16 +6392,16 @@
         <v>44691</v>
       </c>
       <c r="B299" t="n">
-        <v>14.71094036102295</v>
+        <v>14.71093940734863</v>
       </c>
       <c r="C299" t="n">
-        <v>14.97105473450647</v>
+        <v>14.97105376396958</v>
       </c>
       <c r="D299" t="n">
-        <v>14.14254109464951</v>
+        <v>14.14254017782313</v>
       </c>
       <c r="E299" t="n">
-        <v>14.21961208818231</v>
+        <v>14.21961116635961</v>
       </c>
       <c r="F299" t="n">
         <v>13119700</v>
@@ -6412,16 +6412,16 @@
         <v>44692</v>
       </c>
       <c r="B300" t="n">
-        <v>14.60496616363525</v>
+        <v>14.60496520996094</v>
       </c>
       <c r="C300" t="n">
-        <v>14.7880104511626</v>
+        <v>14.78800948553586</v>
       </c>
       <c r="D300" t="n">
-        <v>14.4026545882811</v>
+        <v>14.40265364781732</v>
       </c>
       <c r="E300" t="n">
-        <v>14.45082418598612</v>
+        <v>14.45082324237696</v>
       </c>
       <c r="F300" t="n">
         <v>6181500</v>
@@ -6432,16 +6432,16 @@
         <v>44693</v>
       </c>
       <c r="B301" t="n">
-        <v>14.68203639984131</v>
+        <v>14.68203544616699</v>
       </c>
       <c r="C301" t="n">
-        <v>15.07702542700927</v>
+        <v>15.07702444767837</v>
       </c>
       <c r="D301" t="n">
-        <v>14.42192205558183</v>
+        <v>14.42192111880329</v>
       </c>
       <c r="E301" t="n">
-        <v>14.42192205558183</v>
+        <v>14.42192111880329</v>
       </c>
       <c r="F301" t="n">
         <v>8258700</v>
@@ -6452,16 +6452,16 @@
         <v>44694</v>
       </c>
       <c r="B302" t="n">
-        <v>14.91324901580811</v>
+        <v>14.91324806213379</v>
       </c>
       <c r="C302" t="n">
-        <v>15.09629328979575</v>
+        <v>15.0962923244161</v>
       </c>
       <c r="D302" t="n">
-        <v>14.62423328847366</v>
+        <v>14.62423235328135</v>
       </c>
       <c r="E302" t="n">
-        <v>14.72057155799894</v>
+        <v>14.72057061664599</v>
       </c>
       <c r="F302" t="n">
         <v>5016200</v>
@@ -6492,16 +6492,16 @@
         <v>44698</v>
       </c>
       <c r="B304" t="n">
-        <v>15.2504358291626</v>
+        <v>15.25043678283691</v>
       </c>
       <c r="C304" t="n">
-        <v>15.26970403504692</v>
+        <v>15.26970498992616</v>
       </c>
       <c r="D304" t="n">
-        <v>14.84581269317811</v>
+        <v>14.84581362154963</v>
       </c>
       <c r="E304" t="n">
-        <v>14.84581269317811</v>
+        <v>14.84581362154963</v>
       </c>
       <c r="F304" t="n">
         <v>7407200</v>
@@ -6552,16 +6552,16 @@
         <v>44701</v>
       </c>
       <c r="B307" t="n">
-        <v>15.37567615509033</v>
+        <v>15.37567520141602</v>
       </c>
       <c r="C307" t="n">
-        <v>15.49128263219524</v>
+        <v>15.49128167135044</v>
       </c>
       <c r="D307" t="n">
-        <v>14.93251753347555</v>
+        <v>14.93251660728809</v>
       </c>
       <c r="E307" t="n">
-        <v>15.02885672377561</v>
+        <v>15.02885579161273</v>
       </c>
       <c r="F307" t="n">
         <v>8142900</v>
@@ -6612,16 +6612,16 @@
         <v>44706</v>
       </c>
       <c r="B310" t="n">
-        <v>15.14446353912354</v>
+        <v>15.14446258544922</v>
       </c>
       <c r="C310" t="n">
-        <v>15.44311430071703</v>
+        <v>15.44311332823613</v>
       </c>
       <c r="D310" t="n">
-        <v>14.94215196998178</v>
+        <v>14.94215102904739</v>
       </c>
       <c r="E310" t="n">
-        <v>15.16373082635871</v>
+        <v>15.16372987147109</v>
       </c>
       <c r="F310" t="n">
         <v>8129200</v>
@@ -6632,16 +6632,16 @@
         <v>44707</v>
       </c>
       <c r="B311" t="n">
-        <v>15.50091743469238</v>
+        <v>15.50091648101807</v>
       </c>
       <c r="C311" t="n">
-        <v>15.60689073255783</v>
+        <v>15.60688977236364</v>
       </c>
       <c r="D311" t="n">
-        <v>15.03849058664008</v>
+        <v>15.03848966141599</v>
       </c>
       <c r="E311" t="n">
-        <v>15.07702608074788</v>
+        <v>15.07702515315295</v>
       </c>
       <c r="F311" t="n">
         <v>6641000</v>
@@ -6652,16 +6652,16 @@
         <v>44708</v>
       </c>
       <c r="B312" t="n">
-        <v>15.22153282165527</v>
+        <v>15.22153472900391</v>
       </c>
       <c r="C312" t="n">
-        <v>15.51054944789882</v>
+        <v>15.51055139146295</v>
       </c>
       <c r="D312" t="n">
-        <v>15.13482774190636</v>
+        <v>15.13482963839033</v>
       </c>
       <c r="E312" t="n">
-        <v>15.43347847006834</v>
+        <v>15.43348040397503</v>
       </c>
       <c r="F312" t="n">
         <v>3408100</v>
@@ -6672,16 +6672,16 @@
         <v>44711</v>
       </c>
       <c r="B313" t="n">
-        <v>15.26970291137695</v>
+        <v>15.26970386505127</v>
       </c>
       <c r="C313" t="n">
-        <v>15.49128175018931</v>
+        <v>15.4912827177024</v>
       </c>
       <c r="D313" t="n">
-        <v>15.16372962432882</v>
+        <v>15.16373057138454</v>
       </c>
       <c r="E313" t="n">
-        <v>15.23116742120269</v>
+        <v>15.23116837247026</v>
       </c>
       <c r="F313" t="n">
         <v>1706700</v>
@@ -6692,16 +6692,16 @@
         <v>44712</v>
       </c>
       <c r="B314" t="n">
-        <v>15.26006984710693</v>
+        <v>15.26006889343262</v>
       </c>
       <c r="C314" t="n">
-        <v>15.39494361251144</v>
+        <v>15.39494265040822</v>
       </c>
       <c r="D314" t="n">
-        <v>15.05775828024155</v>
+        <v>15.05775733921065</v>
       </c>
       <c r="E314" t="n">
-        <v>15.29860533990231</v>
+        <v>15.29860438381973</v>
       </c>
       <c r="F314" t="n">
         <v>5708500</v>
@@ -6832,16 +6832,16 @@
         <v>44721</v>
       </c>
       <c r="B321" t="n">
-        <v>15.02885723114014</v>
+        <v>15.0288553237915</v>
       </c>
       <c r="C321" t="n">
-        <v>15.50091725827793</v>
+        <v>15.50091529101902</v>
       </c>
       <c r="D321" t="n">
-        <v>14.76874195980382</v>
+        <v>14.76874008546704</v>
       </c>
       <c r="E321" t="n">
-        <v>15.38531077727023</v>
+        <v>15.38530882468321</v>
       </c>
       <c r="F321" t="n">
         <v>9688900</v>
@@ -6872,16 +6872,16 @@
         <v>44725</v>
       </c>
       <c r="B323" t="n">
-        <v>14.03656578063965</v>
+        <v>14.03656673431396</v>
       </c>
       <c r="C323" t="n">
-        <v>14.35448381315351</v>
+        <v>14.35448478842786</v>
       </c>
       <c r="D323" t="n">
-        <v>13.89205791813647</v>
+        <v>13.89205886199261</v>
       </c>
       <c r="E323" t="n">
-        <v>14.25814554440425</v>
+        <v>14.25814651313317</v>
       </c>
       <c r="F323" t="n">
         <v>9104400</v>
@@ -6892,16 +6892,16 @@
         <v>44726</v>
       </c>
       <c r="B324" t="n">
-        <v>14.05583477020264</v>
+        <v>14.05583381652832</v>
       </c>
       <c r="C324" t="n">
-        <v>14.2099767438121</v>
+        <v>14.2099757796794</v>
       </c>
       <c r="D324" t="n">
-        <v>13.84388909711031</v>
+        <v>13.84388815781629</v>
       </c>
       <c r="E324" t="n">
-        <v>14.01729927680027</v>
+        <v>14.01729832574055</v>
       </c>
       <c r="F324" t="n">
         <v>10130900</v>
@@ -6912,16 +6912,16 @@
         <v>44727</v>
       </c>
       <c r="B325" t="n">
-        <v>14.91324901580811</v>
+        <v>14.91324806213379</v>
       </c>
       <c r="C325" t="n">
-        <v>15.06739190081403</v>
+        <v>15.06739093728256</v>
       </c>
       <c r="D325" t="n">
-        <v>14.25814565925695</v>
+        <v>14.25814474747527</v>
       </c>
       <c r="E325" t="n">
-        <v>14.34485074496072</v>
+        <v>14.34484982763441</v>
       </c>
       <c r="F325" t="n">
         <v>25461900</v>
@@ -6972,16 +6972,16 @@
         <v>44733</v>
       </c>
       <c r="B328" t="n">
-        <v>14.84581279754639</v>
+        <v>14.84581184387207</v>
       </c>
       <c r="C328" t="n">
-        <v>15.6454249721946</v>
+        <v>15.64542396715431</v>
       </c>
       <c r="D328" t="n">
-        <v>14.81691140727535</v>
+        <v>14.81691045545762</v>
       </c>
       <c r="E328" t="n">
-        <v>15.37567651922811</v>
+        <v>15.37567553151609</v>
       </c>
       <c r="F328" t="n">
         <v>9398400</v>
@@ -7012,16 +7012,16 @@
         <v>44735</v>
       </c>
       <c r="B330" t="n">
-        <v>14.72057247161865</v>
+        <v>14.72057151794434</v>
       </c>
       <c r="C330" t="n">
-        <v>14.90361675696679</v>
+        <v>14.90361579143392</v>
       </c>
       <c r="D330" t="n">
-        <v>14.39302031363454</v>
+        <v>14.39301938118073</v>
       </c>
       <c r="E330" t="n">
-        <v>14.39302031363454</v>
+        <v>14.39301938118073</v>
       </c>
       <c r="F330" t="n">
         <v>3851900</v>
@@ -7032,16 +7032,16 @@
         <v>44736</v>
       </c>
       <c r="B331" t="n">
-        <v>14.4219217300415</v>
+        <v>14.42192268371582</v>
       </c>
       <c r="C331" t="n">
-        <v>14.86508034244202</v>
+        <v>14.86508132542095</v>
       </c>
       <c r="D331" t="n">
-        <v>14.25814566119184</v>
+        <v>14.25814660403618</v>
       </c>
       <c r="E331" t="n">
-        <v>14.86508034244202</v>
+        <v>14.86508132542095</v>
       </c>
       <c r="F331" t="n">
         <v>5803600</v>
@@ -7072,16 +7072,16 @@
         <v>44740</v>
       </c>
       <c r="B333" t="n">
-        <v>14.08473587036133</v>
+        <v>14.08473682403564</v>
       </c>
       <c r="C333" t="n">
-        <v>14.48935900212858</v>
+        <v>14.48935998319984</v>
       </c>
       <c r="D333" t="n">
-        <v>13.9691293925362</v>
+        <v>13.96913033838283</v>
       </c>
       <c r="E333" t="n">
-        <v>14.23887784079483</v>
+        <v>14.23887880490607</v>
       </c>
       <c r="F333" t="n">
         <v>7081400</v>
@@ -7132,16 +7132,16 @@
         <v>44743</v>
       </c>
       <c r="B336" t="n">
-        <v>14.06546783447266</v>
+        <v>14.06546974182129</v>
       </c>
       <c r="C336" t="n">
-        <v>14.28704667548244</v>
+        <v>14.28704861287829</v>
       </c>
       <c r="D336" t="n">
-        <v>13.54523825258167</v>
+        <v>13.54524008938454</v>
       </c>
       <c r="E336" t="n">
-        <v>13.64157651959344</v>
+        <v>13.64157836946027</v>
       </c>
       <c r="F336" t="n">
         <v>10271400</v>
@@ -7152,16 +7152,16 @@
         <v>44746</v>
       </c>
       <c r="B337" t="n">
-        <v>13.8727912902832</v>
+        <v>13.87279033660889</v>
       </c>
       <c r="C337" t="n">
-        <v>14.14254067846864</v>
+        <v>14.14253970625061</v>
       </c>
       <c r="D337" t="n">
-        <v>13.76681890698379</v>
+        <v>13.76681796059447</v>
       </c>
       <c r="E337" t="n">
-        <v>13.95949638514576</v>
+        <v>13.95949542551097</v>
       </c>
       <c r="F337" t="n">
         <v>1980900</v>
@@ -7172,16 +7172,16 @@
         <v>44747</v>
       </c>
       <c r="B338" t="n">
-        <v>14.17144107818604</v>
+        <v>14.17144012451172</v>
       </c>
       <c r="C338" t="n">
-        <v>14.19070836527375</v>
+        <v>14.19070741030283</v>
       </c>
       <c r="D338" t="n">
-        <v>13.46816718369137</v>
+        <v>13.46816627734423</v>
       </c>
       <c r="E338" t="n">
-        <v>13.67047875128478</v>
+        <v>13.67047783132298</v>
       </c>
       <c r="F338" t="n">
         <v>7354200</v>
@@ -7212,16 +7212,16 @@
         <v>44749</v>
       </c>
       <c r="B340" t="n">
-        <v>14.57606506347656</v>
+        <v>14.57606410980225</v>
       </c>
       <c r="C340" t="n">
-        <v>14.95178683056531</v>
+        <v>14.95178585230849</v>
       </c>
       <c r="D340" t="n">
-        <v>14.47009268141707</v>
+        <v>14.47009173467626</v>
       </c>
       <c r="E340" t="n">
-        <v>14.49899407311354</v>
+        <v>14.49899312448178</v>
       </c>
       <c r="F340" t="n">
         <v>6763400</v>
@@ -7232,16 +7232,16 @@
         <v>44750</v>
       </c>
       <c r="B341" t="n">
-        <v>14.72057247161865</v>
+        <v>14.72057151794434</v>
       </c>
       <c r="C341" t="n">
-        <v>14.82654576905978</v>
+        <v>14.82654480851997</v>
       </c>
       <c r="D341" t="n">
-        <v>14.41228851999061</v>
+        <v>14.41228758628851</v>
       </c>
       <c r="E341" t="n">
-        <v>14.73984067797473</v>
+        <v>14.73983972305212</v>
       </c>
       <c r="F341" t="n">
         <v>3792400</v>
@@ -7252,16 +7252,16 @@
         <v>44753</v>
       </c>
       <c r="B342" t="n">
-        <v>14.78800964355469</v>
+        <v>14.788010597229</v>
       </c>
       <c r="C342" t="n">
-        <v>14.8939820177114</v>
+        <v>14.89398297821984</v>
       </c>
       <c r="D342" t="n">
-        <v>14.52789438140829</v>
+        <v>14.52789531830785</v>
       </c>
       <c r="E342" t="n">
-        <v>14.57606397648265</v>
+        <v>14.57606491648865</v>
       </c>
       <c r="F342" t="n">
         <v>3654100</v>
@@ -7272,16 +7272,16 @@
         <v>44754</v>
       </c>
       <c r="B343" t="n">
-        <v>14.68203639984131</v>
+        <v>14.68203544616699</v>
       </c>
       <c r="C343" t="n">
-        <v>14.97105305249743</v>
+        <v>14.97105208004998</v>
       </c>
       <c r="D343" t="n">
-        <v>14.59533131216861</v>
+        <v>14.59533036412624</v>
       </c>
       <c r="E343" t="n">
-        <v>14.79764287715203</v>
+        <v>14.79764191596848</v>
       </c>
       <c r="F343" t="n">
         <v>4929100</v>
@@ -7332,16 +7332,16 @@
         <v>44757</v>
       </c>
       <c r="B346" t="n">
-        <v>15.00958919525146</v>
+        <v>15.00958824157715</v>
       </c>
       <c r="C346" t="n">
-        <v>15.16373117167757</v>
+        <v>15.16373020820944</v>
       </c>
       <c r="D346" t="n">
-        <v>14.56643055364708</v>
+        <v>14.56642962813003</v>
       </c>
       <c r="E346" t="n">
-        <v>14.83617901239277</v>
+        <v>14.83617806973653</v>
       </c>
       <c r="F346" t="n">
         <v>3973400</v>
@@ -7412,16 +7412,16 @@
         <v>44763</v>
       </c>
       <c r="B350" t="n">
-        <v>14.84581279754639</v>
+        <v>14.84581184387207</v>
       </c>
       <c r="C350" t="n">
-        <v>14.95178609313791</v>
+        <v>14.95178513265602</v>
       </c>
       <c r="D350" t="n">
-        <v>14.60496573485093</v>
+        <v>14.6049647966483</v>
       </c>
       <c r="E350" t="n">
-        <v>14.74947452372338</v>
+        <v>14.7494735762377</v>
       </c>
       <c r="F350" t="n">
         <v>4662200</v>
@@ -7432,16 +7432,16 @@
         <v>44764</v>
       </c>
       <c r="B351" t="n">
-        <v>15.0770263671875</v>
+        <v>15.07702541351318</v>
       </c>
       <c r="C351" t="n">
-        <v>15.14446417222636</v>
+        <v>15.14446321428636</v>
       </c>
       <c r="D351" t="n">
-        <v>14.78801061526745</v>
+        <v>14.78800967987438</v>
       </c>
       <c r="E351" t="n">
-        <v>14.84581339814799</v>
+        <v>14.8458124590987</v>
       </c>
       <c r="F351" t="n">
         <v>3071000</v>
@@ -7452,16 +7452,16 @@
         <v>44767</v>
       </c>
       <c r="B352" t="n">
-        <v>14.93251895904541</v>
+        <v>14.93251800537109</v>
       </c>
       <c r="C352" t="n">
-        <v>15.43348132641756</v>
+        <v>15.43348034074898</v>
       </c>
       <c r="D352" t="n">
-        <v>14.91325075164247</v>
+        <v>14.91324979919873</v>
       </c>
       <c r="E352" t="n">
-        <v>15.2119015350772</v>
+        <v>15.21190056355995</v>
       </c>
       <c r="F352" t="n">
         <v>6226600</v>
@@ -7472,16 +7472,16 @@
         <v>44768</v>
       </c>
       <c r="B353" t="n">
-        <v>14.95178508758545</v>
+        <v>14.95178604125977</v>
       </c>
       <c r="C353" t="n">
-        <v>15.03848925256745</v>
+        <v>15.03849021177204</v>
       </c>
       <c r="D353" t="n">
-        <v>14.76874081774235</v>
+        <v>14.76874175974149</v>
       </c>
       <c r="E353" t="n">
-        <v>14.82654451315558</v>
+        <v>14.82654545884164</v>
       </c>
       <c r="F353" t="n">
         <v>3874000</v>
@@ -7492,16 +7492,16 @@
         <v>44769</v>
       </c>
       <c r="B354" t="n">
-        <v>15.7610330581665</v>
+        <v>15.76103210449219</v>
       </c>
       <c r="C354" t="n">
-        <v>15.93444324487276</v>
+        <v>15.93444228070568</v>
       </c>
       <c r="D354" t="n">
-        <v>15.03849091980999</v>
+        <v>15.03849000985551</v>
       </c>
       <c r="E354" t="n">
-        <v>15.04812502324004</v>
+        <v>15.04812411270262</v>
       </c>
       <c r="F354" t="n">
         <v>22102600</v>
@@ -7512,16 +7512,16 @@
         <v>44770</v>
       </c>
       <c r="B355" t="n">
-        <v>15.59725570678711</v>
+        <v>15.59725666046143</v>
       </c>
       <c r="C355" t="n">
-        <v>16.13675259238595</v>
+        <v>16.13675357904711</v>
       </c>
       <c r="D355" t="n">
-        <v>15.31787224258232</v>
+        <v>15.31787317917409</v>
       </c>
       <c r="E355" t="n">
-        <v>15.91517374406179</v>
+        <v>15.9151747171748</v>
       </c>
       <c r="F355" t="n">
         <v>25902000</v>
@@ -7532,16 +7532,16 @@
         <v>44771</v>
       </c>
       <c r="B356" t="n">
-        <v>15.26970291137695</v>
+        <v>15.26970386505127</v>
       </c>
       <c r="C356" t="n">
-        <v>15.66469191535275</v>
+        <v>15.66469289369624</v>
       </c>
       <c r="D356" t="n">
-        <v>15.26970291137695</v>
+        <v>15.26970386505127</v>
       </c>
       <c r="E356" t="n">
-        <v>15.59725503723744</v>
+        <v>15.59725601136913</v>
       </c>
       <c r="F356" t="n">
         <v>15825800</v>
@@ -7592,16 +7592,16 @@
         <v>44776</v>
       </c>
       <c r="B359" t="n">
-        <v>15.95371055603027</v>
+        <v>15.95370864868164</v>
       </c>
       <c r="C359" t="n">
-        <v>16.00188107602424</v>
+        <v>16.00187916291658</v>
       </c>
       <c r="D359" t="n">
-        <v>15.0673941195919</v>
+        <v>15.06739231820699</v>
       </c>
       <c r="E359" t="n">
-        <v>15.12519690606722</v>
+        <v>15.12519509777168</v>
       </c>
       <c r="F359" t="n">
         <v>9465300</v>
@@ -7632,16 +7632,16 @@
         <v>44778</v>
       </c>
       <c r="B361" t="n">
-        <v>16.4064998626709</v>
+        <v>16.40650177001953</v>
       </c>
       <c r="C361" t="n">
-        <v>16.57027591175573</v>
+        <v>16.57027783814425</v>
       </c>
       <c r="D361" t="n">
-        <v>16.10784823124054</v>
+        <v>16.10785010386923</v>
       </c>
       <c r="E361" t="n">
-        <v>16.26199017890661</v>
+        <v>16.26199206945518</v>
       </c>
       <c r="F361" t="n">
         <v>6244900</v>
@@ -7672,16 +7672,16 @@
         <v>44782</v>
       </c>
       <c r="B363" t="n">
-        <v>16.61844825744629</v>
+        <v>16.61844635009766</v>
       </c>
       <c r="C363" t="n">
-        <v>16.87856354074092</v>
+        <v>16.87856160353808</v>
       </c>
       <c r="D363" t="n">
-        <v>16.51247495591499</v>
+        <v>16.51247306072922</v>
       </c>
       <c r="E363" t="n">
-        <v>16.65698467164581</v>
+        <v>16.65698275987423</v>
       </c>
       <c r="F363" t="n">
         <v>6314800</v>
@@ -7692,16 +7692,16 @@
         <v>44783</v>
       </c>
       <c r="B364" t="n">
-        <v>16.8978328704834</v>
+        <v>16.89782905578613</v>
       </c>
       <c r="C364" t="n">
-        <v>17.20611685449155</v>
+        <v>17.20611297019896</v>
       </c>
       <c r="D364" t="n">
-        <v>16.73405677428938</v>
+        <v>16.73405299656468</v>
       </c>
       <c r="E364" t="n">
-        <v>17.16758043773178</v>
+        <v>17.16757656213882</v>
       </c>
       <c r="F364" t="n">
         <v>6533000</v>
@@ -7712,16 +7712,16 @@
         <v>44784</v>
       </c>
       <c r="B365" t="n">
-        <v>16.99416923522949</v>
+        <v>16.99416542053223</v>
       </c>
       <c r="C365" t="n">
-        <v>17.34098961554597</v>
+        <v>17.34098572299761</v>
       </c>
       <c r="D365" t="n">
-        <v>16.86892956318042</v>
+        <v>16.86892577659582</v>
       </c>
       <c r="E365" t="n">
-        <v>16.91709824377221</v>
+        <v>16.91709444637514</v>
       </c>
       <c r="F365" t="n">
         <v>8667500</v>
@@ -7732,16 +7732,16 @@
         <v>44785</v>
       </c>
       <c r="B366" t="n">
-        <v>17.34099006652832</v>
+        <v>17.34098815917969</v>
       </c>
       <c r="C366" t="n">
-        <v>17.64927404037492</v>
+        <v>17.6492720991179</v>
       </c>
       <c r="D366" t="n">
-        <v>17.06160656678144</v>
+        <v>17.06160469016241</v>
       </c>
       <c r="E366" t="n">
-        <v>17.16757987186025</v>
+        <v>17.16757798358513</v>
       </c>
       <c r="F366" t="n">
         <v>11729000</v>
@@ -7772,16 +7772,16 @@
         <v>44789</v>
       </c>
       <c r="B368" t="n">
-        <v>17.42769432067871</v>
+        <v>17.42769241333008</v>
       </c>
       <c r="C368" t="n">
-        <v>17.63000497965835</v>
+        <v>17.63000305016812</v>
       </c>
       <c r="D368" t="n">
-        <v>17.19648135148026</v>
+        <v>17.1964794694364</v>
       </c>
       <c r="E368" t="n">
-        <v>17.52403351722407</v>
+        <v>17.52403159933173</v>
       </c>
       <c r="F368" t="n">
         <v>4828900</v>
@@ -7792,16 +7792,16 @@
         <v>44790</v>
       </c>
       <c r="B369" t="n">
-        <v>17.27355194091797</v>
+        <v>17.27355003356934</v>
       </c>
       <c r="C369" t="n">
-        <v>17.52403311112434</v>
+        <v>17.52403117611753</v>
       </c>
       <c r="D369" t="n">
-        <v>17.16757864342216</v>
+        <v>17.16757674777512</v>
       </c>
       <c r="E369" t="n">
-        <v>17.31208651613271</v>
+        <v>17.31208460452908</v>
       </c>
       <c r="F369" t="n">
         <v>8548600</v>
@@ -7812,16 +7812,16 @@
         <v>44791</v>
       </c>
       <c r="B370" t="n">
-        <v>17.45659637451172</v>
+        <v>17.45659446716309</v>
       </c>
       <c r="C370" t="n">
-        <v>17.59147014518392</v>
+        <v>17.59146822309866</v>
       </c>
       <c r="D370" t="n">
-        <v>17.2928202940452</v>
+        <v>17.29281840459113</v>
       </c>
       <c r="E370" t="n">
-        <v>17.34098897285176</v>
+        <v>17.34098707813466</v>
       </c>
       <c r="F370" t="n">
         <v>13968800</v>
@@ -7832,16 +7832,16 @@
         <v>44792</v>
       </c>
       <c r="B371" t="n">
-        <v>17.12904357910156</v>
+        <v>17.1290454864502</v>
       </c>
       <c r="C371" t="n">
-        <v>17.57220128776223</v>
+        <v>17.57220324445724</v>
       </c>
       <c r="D371" t="n">
-        <v>17.07123896165407</v>
+        <v>17.07124086256606</v>
       </c>
       <c r="E371" t="n">
-        <v>17.45659572790173</v>
+        <v>17.45659767172386</v>
       </c>
       <c r="F371" t="n">
         <v>7571900</v>
@@ -7892,16 +7892,16 @@
         <v>44797</v>
       </c>
       <c r="B374" t="n">
-        <v>17.14830780029297</v>
+        <v>17.14831161499023</v>
       </c>
       <c r="C374" t="n">
-        <v>17.26391518319573</v>
+        <v>17.26391902361024</v>
       </c>
       <c r="D374" t="n">
-        <v>16.99416584810063</v>
+        <v>16.99416962850851</v>
       </c>
       <c r="E374" t="n">
-        <v>17.14830780029297</v>
+        <v>17.14831161499023</v>
       </c>
       <c r="F374" t="n">
         <v>5807100</v>
@@ -7912,16 +7912,16 @@
         <v>44798</v>
       </c>
       <c r="B375" t="n">
-        <v>17.29281806945801</v>
+        <v>17.29281997680664</v>
       </c>
       <c r="C375" t="n">
-        <v>17.32171853801719</v>
+        <v>17.32172044855347</v>
       </c>
       <c r="D375" t="n">
-        <v>16.98453231719579</v>
+        <v>16.98453419054138</v>
       </c>
       <c r="E375" t="n">
-        <v>17.19647888672088</v>
+        <v>17.19648078344358</v>
       </c>
       <c r="F375" t="n">
         <v>6074000</v>
@@ -7932,16 +7932,16 @@
         <v>44799</v>
       </c>
       <c r="B376" t="n">
-        <v>17.29281806945801</v>
+        <v>17.29281997680664</v>
       </c>
       <c r="C376" t="n">
-        <v>17.41805772075432</v>
+        <v>17.41805964191653</v>
       </c>
       <c r="D376" t="n">
-        <v>17.10977380600918</v>
+        <v>17.10977569316855</v>
       </c>
       <c r="E376" t="n">
-        <v>17.30245033396635</v>
+        <v>17.3024522423774</v>
       </c>
       <c r="F376" t="n">
         <v>3647900</v>
@@ -7992,16 +7992,16 @@
         <v>44804</v>
       </c>
       <c r="B379" t="n">
-        <v>17.71670913696289</v>
+        <v>17.71671104431152</v>
       </c>
       <c r="C379" t="n">
-        <v>17.98645850553768</v>
+        <v>17.98646044192704</v>
       </c>
       <c r="D379" t="n">
-        <v>17.51439848866973</v>
+        <v>17.51440037423797</v>
       </c>
       <c r="E379" t="n">
-        <v>17.74561144565502</v>
+        <v>17.74561335611522</v>
       </c>
       <c r="F379" t="n">
         <v>9759800</v>
@@ -8072,16 +8072,16 @@
         <v>44810</v>
       </c>
       <c r="B383" t="n">
-        <v>18.75716590881348</v>
+        <v>18.75716781616211</v>
       </c>
       <c r="C383" t="n">
-        <v>18.83423688439475</v>
+        <v>18.83423879958045</v>
       </c>
       <c r="D383" t="n">
-        <v>18.33327646187499</v>
+        <v>18.33327832611984</v>
       </c>
       <c r="E383" t="n">
-        <v>18.68972903486949</v>
+        <v>18.68973093536071</v>
       </c>
       <c r="F383" t="n">
         <v>7863100</v>
@@ -8092,16 +8092,16 @@
         <v>44812</v>
       </c>
       <c r="B384" t="n">
-        <v>18.40071678161621</v>
+        <v>18.40071487426758</v>
       </c>
       <c r="C384" t="n">
-        <v>18.94984781515502</v>
+        <v>18.94984585088554</v>
       </c>
       <c r="D384" t="n">
-        <v>18.34291399848511</v>
+        <v>18.3429120971281</v>
       </c>
       <c r="E384" t="n">
-        <v>18.91131140138939</v>
+        <v>18.91130944111445</v>
       </c>
       <c r="F384" t="n">
         <v>6653400</v>
@@ -8172,16 +8172,16 @@
         <v>44818</v>
       </c>
       <c r="B388" t="n">
-        <v>17.70707702636719</v>
+        <v>17.70707511901855</v>
       </c>
       <c r="C388" t="n">
-        <v>17.87085311901526</v>
+        <v>17.8708511940252</v>
       </c>
       <c r="D388" t="n">
-        <v>17.36989257460714</v>
+        <v>17.36989070357892</v>
       </c>
       <c r="E388" t="n">
-        <v>17.4469635689405</v>
+        <v>17.44696168961044</v>
       </c>
       <c r="F388" t="n">
         <v>7347400</v>
@@ -8252,16 +8252,16 @@
         <v>44824</v>
       </c>
       <c r="B392" t="n">
-        <v>17.60110473632812</v>
+        <v>17.60110282897949</v>
       </c>
       <c r="C392" t="n">
-        <v>17.83231770853966</v>
+        <v>17.83231577613557</v>
       </c>
       <c r="D392" t="n">
-        <v>17.43732865132195</v>
+        <v>17.43732676172096</v>
       </c>
       <c r="E392" t="n">
-        <v>17.55293421866904</v>
+        <v>17.55293231654042</v>
       </c>
       <c r="F392" t="n">
         <v>8039000</v>
@@ -8332,16 +8332,16 @@
         <v>44830</v>
       </c>
       <c r="B396" t="n">
-        <v>17.09050559997559</v>
+        <v>17.09050750732422</v>
       </c>
       <c r="C396" t="n">
-        <v>17.20611298675014</v>
+        <v>17.20611490700088</v>
       </c>
       <c r="D396" t="n">
-        <v>16.71478480861316</v>
+        <v>16.7147866740303</v>
       </c>
       <c r="E396" t="n">
-        <v>16.89782907204076</v>
+        <v>16.89783095788615</v>
       </c>
       <c r="F396" t="n">
         <v>7980700</v>
@@ -8352,16 +8352,16 @@
         <v>44831</v>
       </c>
       <c r="B397" t="n">
-        <v>17.12904357910156</v>
+        <v>17.1290454864502</v>
       </c>
       <c r="C397" t="n">
-        <v>17.49513030201615</v>
+        <v>17.49513225012917</v>
       </c>
       <c r="D397" t="n">
-        <v>16.86892831313957</v>
+        <v>16.86893019152391</v>
       </c>
       <c r="E397" t="n">
-        <v>17.25428324186998</v>
+        <v>17.25428516316427</v>
       </c>
       <c r="F397" t="n">
         <v>9260100</v>
@@ -8372,16 +8372,16 @@
         <v>44832</v>
       </c>
       <c r="B398" t="n">
-        <v>17.29281806945801</v>
+        <v>17.29281997680664</v>
       </c>
       <c r="C398" t="n">
-        <v>17.36025494611888</v>
+        <v>17.3602568609056</v>
       </c>
       <c r="D398" t="n">
-        <v>16.97490005268744</v>
+        <v>16.97490192497062</v>
       </c>
       <c r="E398" t="n">
-        <v>17.13867611208543</v>
+        <v>17.13867800243265</v>
       </c>
       <c r="F398" t="n">
         <v>11092900</v>
@@ -8392,16 +8392,16 @@
         <v>44833</v>
       </c>
       <c r="B399" t="n">
-        <v>17.29281806945801</v>
+        <v>17.29281997680664</v>
       </c>
       <c r="C399" t="n">
-        <v>17.456594128856</v>
+        <v>17.45659605426867</v>
       </c>
       <c r="D399" t="n">
-        <v>16.9556318486366</v>
+        <v>16.95563371879456</v>
       </c>
       <c r="E399" t="n">
-        <v>17.1194079080346</v>
+        <v>17.11940979625658</v>
       </c>
       <c r="F399" t="n">
         <v>8404000</v>
@@ -8412,16 +8412,16 @@
         <v>44834</v>
       </c>
       <c r="B400" t="n">
-        <v>16.90746307373047</v>
+        <v>16.90746116638184</v>
       </c>
       <c r="C400" t="n">
-        <v>17.28318574121415</v>
+        <v>17.28318379147985</v>
       </c>
       <c r="D400" t="n">
-        <v>16.85929439617687</v>
+        <v>16.8592924942622</v>
       </c>
       <c r="E400" t="n">
-        <v>17.24464932915746</v>
+        <v>17.24464738377049</v>
       </c>
       <c r="F400" t="n">
         <v>11790900</v>
@@ -8452,16 +8452,16 @@
         <v>44838</v>
       </c>
       <c r="B402" t="n">
-        <v>17.41805839538574</v>
+        <v>17.41806030273438</v>
       </c>
       <c r="C402" t="n">
-        <v>18.07316265835103</v>
+        <v>18.07316463743626</v>
       </c>
       <c r="D402" t="n">
-        <v>17.3313533113158</v>
+        <v>17.33135520916987</v>
       </c>
       <c r="E402" t="n">
-        <v>17.98645757428108</v>
+        <v>17.98645954387175</v>
       </c>
       <c r="F402" t="n">
         <v>18594600</v>
@@ -8472,16 +8472,16 @@
         <v>44839</v>
       </c>
       <c r="B403" t="n">
-        <v>17.45659637451172</v>
+        <v>17.45659446716309</v>
       </c>
       <c r="C403" t="n">
-        <v>17.74561212238566</v>
+        <v>17.74561018345848</v>
       </c>
       <c r="D403" t="n">
-        <v>17.14831058259092</v>
+        <v>17.14830870892632</v>
       </c>
       <c r="E403" t="n">
-        <v>17.4276940647174</v>
+        <v>17.4276921605267</v>
       </c>
       <c r="F403" t="n">
         <v>8852300</v>
@@ -8492,16 +8492,16 @@
         <v>44840</v>
       </c>
       <c r="B404" t="n">
-        <v>17.44696044921875</v>
+        <v>17.44696426391602</v>
       </c>
       <c r="C404" t="n">
-        <v>17.6396369818406</v>
+        <v>17.6396408386657</v>
       </c>
       <c r="D404" t="n">
-        <v>17.30245075285597</v>
+        <v>17.30245453595685</v>
       </c>
       <c r="E404" t="n">
-        <v>17.63000287958194</v>
+        <v>17.63000673430058</v>
       </c>
       <c r="F404" t="n">
         <v>6691000</v>
@@ -8512,16 +8512,16 @@
         <v>44841</v>
       </c>
       <c r="B405" t="n">
-        <v>17.49513053894043</v>
+        <v>17.49513244628906</v>
       </c>
       <c r="C405" t="n">
-        <v>17.68780892467357</v>
+        <v>17.68781085302832</v>
       </c>
       <c r="D405" t="n">
-        <v>17.32172035928406</v>
+        <v>17.32172224772722</v>
       </c>
       <c r="E405" t="n">
-        <v>17.44696186126578</v>
+        <v>17.44696376336298</v>
       </c>
       <c r="F405" t="n">
         <v>11897600</v>
@@ -8532,16 +8532,16 @@
         <v>44844</v>
       </c>
       <c r="B406" t="n">
-        <v>18.10206604003906</v>
+        <v>18.1020679473877</v>
       </c>
       <c r="C406" t="n">
-        <v>18.12133240846265</v>
+        <v>18.12133431784131</v>
       </c>
       <c r="D406" t="n">
-        <v>17.58183550473985</v>
+        <v>17.58183735727369</v>
       </c>
       <c r="E406" t="n">
-        <v>17.73597747723208</v>
+        <v>17.73597934600729</v>
       </c>
       <c r="F406" t="n">
         <v>7333800</v>
@@ -8552,16 +8552,16 @@
         <v>44845</v>
       </c>
       <c r="B407" t="n">
-        <v>18.32364273071289</v>
+        <v>18.32364463806152</v>
       </c>
       <c r="C407" t="n">
-        <v>18.5933902319427</v>
+        <v>18.59339216736995</v>
       </c>
       <c r="D407" t="n">
-        <v>17.85158276604368</v>
+        <v>17.85158462425454</v>
       </c>
       <c r="E407" t="n">
-        <v>18.1502325727697</v>
+        <v>18.15023446206769</v>
       </c>
       <c r="F407" t="n">
         <v>12287200</v>
@@ -8572,16 +8572,16 @@
         <v>44847</v>
       </c>
       <c r="B408" t="n">
-        <v>18.75716590881348</v>
+        <v>18.75716781616211</v>
       </c>
       <c r="C408" t="n">
-        <v>18.99801293719457</v>
+        <v>18.99801486903407</v>
       </c>
       <c r="D408" t="n">
-        <v>17.93828748233136</v>
+        <v>17.93828930641119</v>
       </c>
       <c r="E408" t="n">
-        <v>18.17913451071245</v>
+        <v>18.17913635928316</v>
       </c>
       <c r="F408" t="n">
         <v>20665700</v>
@@ -8592,16 +8592,16 @@
         <v>44848</v>
       </c>
       <c r="B409" t="n">
-        <v>18.39108276367188</v>
+        <v>18.39108085632324</v>
       </c>
       <c r="C409" t="n">
-        <v>18.9402137997635</v>
+        <v>18.94021183546421</v>
       </c>
       <c r="D409" t="n">
-        <v>18.29474356632728</v>
+        <v>18.29474166897004</v>
       </c>
       <c r="E409" t="n">
-        <v>18.80534002599148</v>
+        <v>18.80533807568002</v>
       </c>
       <c r="F409" t="n">
         <v>11391600</v>
@@ -8612,16 +8612,16 @@
         <v>44851</v>
       </c>
       <c r="B410" t="n">
-        <v>19.01728439331055</v>
+        <v>19.01728248596191</v>
       </c>
       <c r="C410" t="n">
-        <v>19.06545490973637</v>
+        <v>19.06545299755645</v>
       </c>
       <c r="D410" t="n">
-        <v>18.3621800700579</v>
+        <v>18.3621782284133</v>
       </c>
       <c r="E410" t="n">
-        <v>18.49705567853288</v>
+        <v>18.49705382336087</v>
       </c>
       <c r="F410" t="n">
         <v>20683400</v>
@@ -8632,16 +8632,16 @@
         <v>44852</v>
       </c>
       <c r="B411" t="n">
-        <v>17.263916015625</v>
+        <v>17.26391983032227</v>
       </c>
       <c r="C411" t="n">
-        <v>19.16179004195282</v>
+        <v>19.16179427601119</v>
       </c>
       <c r="D411" t="n">
-        <v>17.263916015625</v>
+        <v>17.26391983032227</v>
       </c>
       <c r="E411" t="n">
-        <v>19.10398726647282</v>
+        <v>19.10399148775888</v>
       </c>
       <c r="F411" t="n">
         <v>33355700</v>
@@ -8652,16 +8652,16 @@
         <v>44853</v>
       </c>
       <c r="B412" t="n">
-        <v>17.67817497253418</v>
+        <v>17.67817687988281</v>
       </c>
       <c r="C412" t="n">
-        <v>17.97682481920425</v>
+        <v>17.97682675877506</v>
       </c>
       <c r="D412" t="n">
-        <v>17.2831859321752</v>
+        <v>17.28318779690735</v>
       </c>
       <c r="E412" t="n">
-        <v>17.47586248203574</v>
+        <v>17.4758643675563</v>
       </c>
       <c r="F412" t="n">
         <v>27062400</v>
@@ -8672,16 +8672,16 @@
         <v>44854</v>
       </c>
       <c r="B413" t="n">
-        <v>17.35062026977539</v>
+        <v>17.35062408447266</v>
       </c>
       <c r="C413" t="n">
-        <v>18.11169592942068</v>
+        <v>18.11169991144759</v>
       </c>
       <c r="D413" t="n">
-        <v>17.19647831750503</v>
+        <v>17.19648209831274</v>
       </c>
       <c r="E413" t="n">
-        <v>17.7359751504513</v>
+        <v>17.73597904987246</v>
       </c>
       <c r="F413" t="n">
         <v>15810900</v>
@@ -8692,16 +8692,16 @@
         <v>44855</v>
       </c>
       <c r="B414" t="n">
-        <v>17.91901969909668</v>
+        <v>17.91902351379395</v>
       </c>
       <c r="C414" t="n">
-        <v>18.2562059142376</v>
+        <v>18.25620980071688</v>
       </c>
       <c r="D414" t="n">
-        <v>17.34098644992897</v>
+        <v>17.34099014157141</v>
       </c>
       <c r="E414" t="n">
-        <v>17.53366481215722</v>
+        <v>17.53366854481807</v>
       </c>
       <c r="F414" t="n">
         <v>27105700</v>
@@ -8712,16 +8712,16 @@
         <v>44858</v>
       </c>
       <c r="B415" t="n">
-        <v>18.0057258605957</v>
+        <v>18.00572776794434</v>
       </c>
       <c r="C415" t="n">
-        <v>18.36217846337067</v>
+        <v>18.36218040847837</v>
       </c>
       <c r="D415" t="n">
-        <v>17.54329813095674</v>
+        <v>17.54329998932035</v>
       </c>
       <c r="E415" t="n">
-        <v>17.91902077613322</v>
+        <v>17.91902267429717</v>
       </c>
       <c r="F415" t="n">
         <v>16227000</v>
@@ -8732,16 +8732,16 @@
         <v>44859</v>
       </c>
       <c r="B416" t="n">
-        <v>17.04233551025391</v>
+        <v>17.04233741760254</v>
       </c>
       <c r="C416" t="n">
-        <v>18.00572358237087</v>
+        <v>18.00572559754023</v>
       </c>
       <c r="D416" t="n">
-        <v>16.80148849222466</v>
+        <v>16.80149037261812</v>
       </c>
       <c r="E416" t="n">
-        <v>18.00572358237087</v>
+        <v>18.00572559754023</v>
       </c>
       <c r="F416" t="n">
         <v>27810400</v>
@@ -8752,16 +8752,16 @@
         <v>44860</v>
       </c>
       <c r="B417" t="n">
-        <v>16.45467185974121</v>
+        <v>16.45466995239258</v>
       </c>
       <c r="C417" t="n">
-        <v>17.07123977508899</v>
+        <v>17.07123779627069</v>
       </c>
       <c r="D417" t="n">
-        <v>16.36796676695576</v>
+        <v>16.36796486965758</v>
       </c>
       <c r="E417" t="n">
-        <v>17.0423393025054</v>
+        <v>17.0423373270371</v>
       </c>
       <c r="F417" t="n">
         <v>12823000</v>
@@ -8852,16 +8852,16 @@
         <v>44868</v>
       </c>
       <c r="B422" t="n">
-        <v>19.62421989440918</v>
+        <v>19.62421798706055</v>
       </c>
       <c r="C422" t="n">
-        <v>19.74945956116751</v>
+        <v>19.74945764164638</v>
       </c>
       <c r="D422" t="n">
-        <v>18.69936619847478</v>
+        <v>18.69936438101601</v>
       </c>
       <c r="E422" t="n">
-        <v>18.69936619847478</v>
+        <v>18.69936438101601</v>
       </c>
       <c r="F422" t="n">
         <v>9732300</v>
@@ -8972,16 +8972,16 @@
         <v>44876</v>
       </c>
       <c r="B428" t="n">
-        <v>18.64156532287598</v>
+        <v>18.64156341552734</v>
       </c>
       <c r="C428" t="n">
-        <v>18.96911751560485</v>
+        <v>18.96911557474207</v>
       </c>
       <c r="D428" t="n">
-        <v>18.03462962090057</v>
+        <v>18.03462777565176</v>
       </c>
       <c r="E428" t="n">
-        <v>18.88241241532265</v>
+        <v>18.88241048333127</v>
       </c>
       <c r="F428" t="n">
         <v>19344200</v>
@@ -9012,16 +9012,16 @@
         <v>44881</v>
       </c>
       <c r="B430" t="n">
-        <v>18.92094230651855</v>
+        <v>18.92094421386719</v>
       </c>
       <c r="C430" t="n">
-        <v>19.24849441808907</v>
+        <v>19.24849635845699</v>
       </c>
       <c r="D430" t="n">
-        <v>18.44888234278859</v>
+        <v>18.44888420255064</v>
       </c>
       <c r="E430" t="n">
-        <v>18.99801328350473</v>
+        <v>18.9980151986226</v>
       </c>
       <c r="F430" t="n">
         <v>21887300</v>
@@ -9032,16 +9032,16 @@
         <v>44882</v>
       </c>
       <c r="B431" t="n">
-        <v>18.78606796264648</v>
+        <v>18.78606986999512</v>
       </c>
       <c r="C431" t="n">
-        <v>18.90167534323178</v>
+        <v>18.90167726231802</v>
       </c>
       <c r="D431" t="n">
-        <v>18.05389278565156</v>
+        <v>18.05389461866248</v>
       </c>
       <c r="E431" t="n">
-        <v>18.66082831806964</v>
+        <v>18.6608302127027</v>
       </c>
       <c r="F431" t="n">
         <v>10826800</v>
@@ -9052,16 +9052,16 @@
         <v>44883</v>
       </c>
       <c r="B432" t="n">
-        <v>18.44888496398926</v>
+        <v>18.44888305664062</v>
       </c>
       <c r="C432" t="n">
-        <v>19.02691829227056</v>
+        <v>19.02691632516161</v>
       </c>
       <c r="D432" t="n">
-        <v>18.44888496398926</v>
+        <v>18.44888305664062</v>
       </c>
       <c r="E432" t="n">
-        <v>18.78607122527979</v>
+        <v>18.78606928307096</v>
       </c>
       <c r="F432" t="n">
         <v>9969800</v>
@@ -9072,16 +9072,16 @@
         <v>44886</v>
       </c>
       <c r="B433" t="n">
-        <v>18.98838043212891</v>
+        <v>18.98838233947754</v>
       </c>
       <c r="C433" t="n">
-        <v>19.02691684191824</v>
+        <v>19.02691875313779</v>
       </c>
       <c r="D433" t="n">
-        <v>18.58375915444382</v>
+        <v>18.58376102114898</v>
       </c>
       <c r="E433" t="n">
-        <v>18.60302552182134</v>
+        <v>18.60302739046176</v>
       </c>
       <c r="F433" t="n">
         <v>10461100</v>
@@ -9092,16 +9092,16 @@
         <v>44887</v>
       </c>
       <c r="B434" t="n">
-        <v>18.75716590881348</v>
+        <v>18.75716781616211</v>
       </c>
       <c r="C434" t="n">
-        <v>19.3930019167382</v>
+        <v>19.39300388874271</v>
       </c>
       <c r="D434" t="n">
-        <v>18.6222921609255</v>
+        <v>18.62229405455931</v>
       </c>
       <c r="E434" t="n">
-        <v>19.07508391277584</v>
+        <v>19.07508585245241</v>
       </c>
       <c r="F434" t="n">
         <v>9653000</v>
@@ -9112,16 +9112,16 @@
         <v>44888</v>
       </c>
       <c r="B435" t="n">
-        <v>18.64156532287598</v>
+        <v>18.64156341552734</v>
       </c>
       <c r="C435" t="n">
-        <v>19.14252771616925</v>
+        <v>19.14252575756366</v>
       </c>
       <c r="D435" t="n">
-        <v>18.46815512231158</v>
+        <v>18.46815323270575</v>
       </c>
       <c r="E435" t="n">
-        <v>18.69936811055828</v>
+        <v>18.69936619729544</v>
       </c>
       <c r="F435" t="n">
         <v>10423000</v>
@@ -9132,16 +9132,16 @@
         <v>44889</v>
       </c>
       <c r="B436" t="n">
-        <v>19.0847225189209</v>
+        <v>19.08471870422363</v>
       </c>
       <c r="C436" t="n">
-        <v>19.26776681819867</v>
+        <v>19.26776296691409</v>
       </c>
       <c r="D436" t="n">
-        <v>18.58376197816099</v>
+        <v>18.58375826359684</v>
       </c>
       <c r="E436" t="n">
-        <v>18.67046523832684</v>
+        <v>18.67046150643225</v>
       </c>
       <c r="F436" t="n">
         <v>7241600</v>
@@ -9172,16 +9172,16 @@
         <v>44893</v>
       </c>
       <c r="B438" t="n">
-        <v>18.61266326904297</v>
+        <v>18.61266136169434</v>
       </c>
       <c r="C438" t="n">
-        <v>19.04618877648117</v>
+        <v>19.04618682470663</v>
       </c>
       <c r="D438" t="n">
-        <v>18.2176741789404</v>
+        <v>18.21767231206861</v>
       </c>
       <c r="E438" t="n">
-        <v>18.35254796458005</v>
+        <v>18.35254608388696</v>
       </c>
       <c r="F438" t="n">
         <v>12132600</v>
@@ -9192,16 +9192,16 @@
         <v>44894</v>
       </c>
       <c r="B439" t="n">
-        <v>18.68972969055176</v>
+        <v>18.68973159790039</v>
       </c>
       <c r="C439" t="n">
-        <v>18.98837950171693</v>
+        <v>18.98838143954377</v>
       </c>
       <c r="D439" t="n">
-        <v>18.29474069715092</v>
+        <v>18.29474256418963</v>
       </c>
       <c r="E439" t="n">
-        <v>18.53558773398153</v>
+        <v>18.53558962559947</v>
       </c>
       <c r="F439" t="n">
         <v>13403400</v>
@@ -9212,16 +9212,16 @@
         <v>44895</v>
       </c>
       <c r="B440" t="n">
-        <v>19.3159351348877</v>
+        <v>19.31593132019043</v>
       </c>
       <c r="C440" t="n">
-        <v>19.38337386099047</v>
+        <v>19.38337003297476</v>
       </c>
       <c r="D440" t="n">
-        <v>18.15987025017252</v>
+        <v>18.1598666637861</v>
       </c>
       <c r="E440" t="n">
-        <v>18.30437813107224</v>
+        <v>18.30437451614701</v>
       </c>
       <c r="F440" t="n">
         <v>128079800</v>
@@ -9272,16 +9272,16 @@
         <v>44900</v>
       </c>
       <c r="B443" t="n">
-        <v>19.63384819030762</v>
+        <v>19.63385200500488</v>
       </c>
       <c r="C443" t="n">
-        <v>19.75908966926047</v>
+        <v>19.75909350829114</v>
       </c>
       <c r="D443" t="n">
-        <v>19.29666383355054</v>
+        <v>19.29666758273562</v>
       </c>
       <c r="E443" t="n">
-        <v>19.60494772402383</v>
+        <v>19.60495153310597</v>
       </c>
       <c r="F443" t="n">
         <v>17246700</v>
@@ -9312,16 +9312,16 @@
         <v>44902</v>
       </c>
       <c r="B445" t="n">
-        <v>19.36410522460938</v>
+        <v>19.36410331726074</v>
       </c>
       <c r="C445" t="n">
-        <v>19.48934489527705</v>
+        <v>19.48934297559241</v>
       </c>
       <c r="D445" t="n">
-        <v>18.82460829035904</v>
+        <v>18.82460643615043</v>
       </c>
       <c r="E445" t="n">
-        <v>19.17142682933272</v>
+        <v>19.17142494096275</v>
       </c>
       <c r="F445" t="n">
         <v>7439200</v>
@@ -9352,16 +9352,16 @@
         <v>44904</v>
       </c>
       <c r="B447" t="n">
-        <v>18.57412719726562</v>
+        <v>18.57412528991699</v>
       </c>
       <c r="C447" t="n">
-        <v>18.75716965235448</v>
+        <v>18.7571677262095</v>
       </c>
       <c r="D447" t="n">
-        <v>18.25620912985342</v>
+        <v>18.25620725515131</v>
       </c>
       <c r="E447" t="n">
-        <v>18.57412719726562</v>
+        <v>18.57412528991699</v>
       </c>
       <c r="F447" t="n">
         <v>14833900</v>
@@ -9392,16 +9392,16 @@
         <v>44908</v>
       </c>
       <c r="B449" t="n">
-        <v>17.94791984558105</v>
+        <v>17.94792366027832</v>
       </c>
       <c r="C449" t="n">
-        <v>18.52595308439166</v>
+        <v>18.5259570219456</v>
       </c>
       <c r="D449" t="n">
-        <v>17.89975117464559</v>
+        <v>17.89975497910497</v>
       </c>
       <c r="E449" t="n">
-        <v>18.52595308439166</v>
+        <v>18.5259570219456</v>
       </c>
       <c r="F449" t="n">
         <v>13648600</v>
@@ -9432,16 +9432,16 @@
         <v>44910</v>
       </c>
       <c r="B451" t="n">
-        <v>18.41998291015625</v>
+        <v>18.41998481750488</v>
       </c>
       <c r="C451" t="n">
-        <v>18.75716730497398</v>
+        <v>18.75716924723731</v>
       </c>
       <c r="D451" t="n">
-        <v>18.09243078017577</v>
+        <v>18.0924326536071</v>
       </c>
       <c r="E451" t="n">
-        <v>18.1116971473674</v>
+        <v>18.11169902279372</v>
       </c>
       <c r="F451" t="n">
         <v>15735500</v>
@@ -9472,16 +9472,16 @@
         <v>44914</v>
       </c>
       <c r="B453" t="n">
-        <v>18.83423805236816</v>
+        <v>18.8342399597168</v>
       </c>
       <c r="C453" t="n">
-        <v>18.90167676801125</v>
+        <v>18.90167868218942</v>
       </c>
       <c r="D453" t="n">
-        <v>18.13096512688717</v>
+        <v>18.13096696301515</v>
       </c>
       <c r="E453" t="n">
-        <v>18.15023333135662</v>
+        <v>18.1502351694359</v>
       </c>
       <c r="F453" t="n">
         <v>7150400</v>
@@ -9512,16 +9512,16 @@
         <v>44916</v>
       </c>
       <c r="B455" t="n">
-        <v>19.44117546081543</v>
+        <v>19.4411735534668</v>
       </c>
       <c r="C455" t="n">
-        <v>19.67238842366494</v>
+        <v>19.6723864936323</v>
       </c>
       <c r="D455" t="n">
-        <v>19.07508689149907</v>
+        <v>19.07508502006691</v>
       </c>
       <c r="E455" t="n">
-        <v>19.30630169186587</v>
+        <v>19.30629979774953</v>
       </c>
       <c r="F455" t="n">
         <v>13319200</v>
@@ -9552,16 +9552,16 @@
         <v>44918</v>
       </c>
       <c r="B457" t="n">
-        <v>19.28703498840332</v>
+        <v>19.28703308105469</v>
       </c>
       <c r="C457" t="n">
-        <v>20.03847671683629</v>
+        <v>20.03847473517549</v>
       </c>
       <c r="D457" t="n">
-        <v>19.06545611143039</v>
+        <v>19.06545422599431</v>
       </c>
       <c r="E457" t="n">
-        <v>19.47007744980665</v>
+        <v>19.47007552435644</v>
       </c>
       <c r="F457" t="n">
         <v>9067600</v>
@@ -9612,16 +9612,16 @@
         <v>44923</v>
       </c>
       <c r="B460" t="n">
-        <v>18.71863174438477</v>
+        <v>18.7186336517334</v>
       </c>
       <c r="C460" t="n">
-        <v>18.94984467612624</v>
+        <v>18.94984660703449</v>
       </c>
       <c r="D460" t="n">
-        <v>18.26583814523029</v>
+        <v>18.26584000644119</v>
       </c>
       <c r="E460" t="n">
-        <v>18.68972943884819</v>
+        <v>18.6897313432518</v>
       </c>
       <c r="F460" t="n">
         <v>8329700</v>
@@ -9732,16 +9732,16 @@
         <v>44932</v>
       </c>
       <c r="B466" t="n">
-        <v>18.37796783447266</v>
+        <v>18.37796592712402</v>
       </c>
       <c r="C466" t="n">
-        <v>18.85092999831188</v>
+        <v>18.85092804187709</v>
       </c>
       <c r="D466" t="n">
-        <v>18.20422625570949</v>
+        <v>18.20422436639255</v>
       </c>
       <c r="E466" t="n">
-        <v>18.33935777651244</v>
+        <v>18.33935587317094</v>
       </c>
       <c r="F466" t="n">
         <v>4999100</v>
@@ -9812,16 +9812,16 @@
         <v>44938</v>
       </c>
       <c r="B470" t="n">
-        <v>19.30458450317383</v>
+        <v>19.30458641052246</v>
       </c>
       <c r="C470" t="n">
-        <v>19.77754660257815</v>
+        <v>19.7775485566568</v>
       </c>
       <c r="D470" t="n">
-        <v>18.84127491694453</v>
+        <v>18.84127677851684</v>
       </c>
       <c r="E470" t="n">
-        <v>19.09223473640923</v>
+        <v>19.09223662277709</v>
       </c>
       <c r="F470" t="n">
         <v>10710500</v>
@@ -9892,16 +9892,16 @@
         <v>44944</v>
       </c>
       <c r="B474" t="n">
-        <v>19.70032691955566</v>
+        <v>19.7003288269043</v>
       </c>
       <c r="C474" t="n">
-        <v>19.96093923342829</v>
+        <v>19.96094116600892</v>
       </c>
       <c r="D474" t="n">
-        <v>19.40110639679182</v>
+        <v>19.40110827517049</v>
       </c>
       <c r="E474" t="n">
-        <v>19.59415112330493</v>
+        <v>19.59415302037382</v>
       </c>
       <c r="F474" t="n">
         <v>9224700</v>
@@ -9932,16 +9932,16 @@
         <v>44946</v>
       </c>
       <c r="B476" t="n">
-        <v>19.30458450317383</v>
+        <v>19.30458641052246</v>
       </c>
       <c r="C476" t="n">
-        <v>19.43971600556688</v>
+        <v>19.43971792626689</v>
       </c>
       <c r="D476" t="n">
-        <v>19.03431965735908</v>
+        <v>19.03432153800477</v>
       </c>
       <c r="E476" t="n">
-        <v>19.3914552807204</v>
+        <v>19.39145719665212</v>
       </c>
       <c r="F476" t="n">
         <v>5910600</v>
@@ -9952,16 +9952,16 @@
         <v>44949</v>
       </c>
       <c r="B477" t="n">
-        <v>19.56519508361816</v>
+        <v>19.5651969909668</v>
       </c>
       <c r="C477" t="n">
-        <v>19.78719734367598</v>
+        <v>19.78719927266691</v>
       </c>
       <c r="D477" t="n">
-        <v>19.25632205379363</v>
+        <v>19.25632393103121</v>
       </c>
       <c r="E477" t="n">
-        <v>19.28527774969688</v>
+        <v>19.28527962975727</v>
       </c>
       <c r="F477" t="n">
         <v>3499900</v>
@@ -10032,16 +10032,16 @@
         <v>44953</v>
       </c>
       <c r="B481" t="n">
-        <v>20.28912162780762</v>
+        <v>20.28911972045898</v>
       </c>
       <c r="C481" t="n">
-        <v>20.5111239391848</v>
+        <v>20.51112201096608</v>
       </c>
       <c r="D481" t="n">
-        <v>20.10572753356917</v>
+        <v>20.10572564346113</v>
       </c>
       <c r="E481" t="n">
-        <v>20.21190335250126</v>
+        <v>20.21190145241179</v>
       </c>
       <c r="F481" t="n">
         <v>6872200</v>
@@ -10052,16 +10052,16 @@
         <v>44956</v>
       </c>
       <c r="B482" t="n">
-        <v>20.05746650695801</v>
+        <v>20.05746459960938</v>
       </c>
       <c r="C482" t="n">
-        <v>20.5014711231836</v>
+        <v>20.50146917361271</v>
       </c>
       <c r="D482" t="n">
-        <v>19.85476738661628</v>
+        <v>19.85476549854316</v>
       </c>
       <c r="E482" t="n">
-        <v>20.35668708924173</v>
+        <v>20.35668515343896</v>
       </c>
       <c r="F482" t="n">
         <v>14094800</v>
@@ -10092,16 +10092,16 @@
         <v>44958</v>
       </c>
       <c r="B484" t="n">
-        <v>18.94745063781738</v>
+        <v>18.94744873046875</v>
       </c>
       <c r="C484" t="n">
-        <v>19.0922365078478</v>
+        <v>19.09223458592427</v>
       </c>
       <c r="D484" t="n">
-        <v>18.60962185048992</v>
+        <v>18.60961997714889</v>
       </c>
       <c r="E484" t="n">
-        <v>18.85092917916886</v>
+        <v>18.85092728153658</v>
       </c>
       <c r="F484" t="n">
         <v>17126000</v>
@@ -10132,16 +10132,16 @@
         <v>44960</v>
       </c>
       <c r="B486" t="n">
-        <v>18.45518493652344</v>
+        <v>18.45518684387207</v>
       </c>
       <c r="C486" t="n">
-        <v>18.82197125869143</v>
+        <v>18.82197320394753</v>
       </c>
       <c r="D486" t="n">
-        <v>18.35866163878593</v>
+        <v>18.35866353615885</v>
       </c>
       <c r="E486" t="n">
-        <v>18.69649226035282</v>
+        <v>18.69649419264063</v>
       </c>
       <c r="F486" t="n">
         <v>6859200</v>
@@ -10152,16 +10152,16 @@
         <v>44963</v>
       </c>
       <c r="B487" t="n">
-        <v>18.55170822143555</v>
+        <v>18.55170631408691</v>
       </c>
       <c r="C487" t="n">
-        <v>18.66753655834077</v>
+        <v>18.66753463908353</v>
       </c>
       <c r="D487" t="n">
-        <v>18.24283511106023</v>
+        <v>18.24283323546763</v>
       </c>
       <c r="E487" t="n">
-        <v>18.45518675521498</v>
+        <v>18.45518485778996</v>
       </c>
       <c r="F487" t="n">
         <v>7136600</v>
@@ -10232,16 +10232,16 @@
         <v>44967</v>
       </c>
       <c r="B491" t="n">
-        <v>17.98221778869629</v>
+        <v>17.98221969604492</v>
       </c>
       <c r="C491" t="n">
-        <v>18.0980460937488</v>
+        <v>18.09804801338318</v>
       </c>
       <c r="D491" t="n">
-        <v>17.62508404342224</v>
+        <v>17.6250859128902</v>
       </c>
       <c r="E491" t="n">
-        <v>17.79882558048678</v>
+        <v>17.79882746838327</v>
       </c>
       <c r="F491" t="n">
         <v>6326900</v>
@@ -10292,16 +10292,16 @@
         <v>44972</v>
       </c>
       <c r="B494" t="n">
-        <v>18.55170822143555</v>
+        <v>18.55170631408691</v>
       </c>
       <c r="C494" t="n">
-        <v>18.77371238041815</v>
+        <v>18.7737104502447</v>
       </c>
       <c r="D494" t="n">
-        <v>17.76022041584155</v>
+        <v>17.7602185898678</v>
       </c>
       <c r="E494" t="n">
-        <v>17.80848298998079</v>
+        <v>17.80848115904505</v>
       </c>
       <c r="F494" t="n">
         <v>12677500</v>
@@ -10312,16 +10312,16 @@
         <v>44973</v>
       </c>
       <c r="B495" t="n">
-        <v>18.3490104675293</v>
+        <v>18.34900856018066</v>
       </c>
       <c r="C495" t="n">
-        <v>18.55170775068378</v>
+        <v>18.5517058222651</v>
       </c>
       <c r="D495" t="n">
-        <v>17.88570081372285</v>
+        <v>17.88569895453448</v>
       </c>
       <c r="E495" t="n">
-        <v>18.43588125774662</v>
+        <v>18.43587934136792</v>
       </c>
       <c r="F495" t="n">
         <v>33990600</v>
@@ -10332,16 +10332,16 @@
         <v>44974</v>
       </c>
       <c r="B496" t="n">
-        <v>18.45518493652344</v>
+        <v>18.45518684387207</v>
       </c>
       <c r="C496" t="n">
-        <v>18.62892466321642</v>
+        <v>18.6289265885211</v>
       </c>
       <c r="D496" t="n">
-        <v>18.01117850334242</v>
+        <v>18.01118036480286</v>
       </c>
       <c r="E496" t="n">
-        <v>18.24283331329517</v>
+        <v>18.2428351986972</v>
       </c>
       <c r="F496" t="n">
         <v>11362300</v>
@@ -10412,16 +10412,16 @@
         <v>44984</v>
       </c>
       <c r="B500" t="n">
-        <v>17.75056457519531</v>
+        <v>17.75056648254395</v>
       </c>
       <c r="C500" t="n">
-        <v>18.25248420602797</v>
+        <v>18.2524861673093</v>
       </c>
       <c r="D500" t="n">
-        <v>17.67334631206941</v>
+        <v>17.67334821112072</v>
       </c>
       <c r="E500" t="n">
-        <v>18.09804767977617</v>
+        <v>18.09804962446285</v>
       </c>
       <c r="F500" t="n">
         <v>7297600</v>
@@ -10432,16 +10432,16 @@
         <v>44985</v>
       </c>
       <c r="B501" t="n">
-        <v>17.5092601776123</v>
+        <v>17.50925827026367</v>
       </c>
       <c r="C501" t="n">
-        <v>17.81813328135845</v>
+        <v>17.81813134036312</v>
       </c>
       <c r="D501" t="n">
-        <v>17.23899713234889</v>
+        <v>17.23899525444101</v>
       </c>
       <c r="E501" t="n">
-        <v>17.74091500542191</v>
+        <v>17.74091307283826</v>
       </c>
       <c r="F501" t="n">
         <v>18187200</v>
@@ -10452,16 +10452,16 @@
         <v>44986</v>
       </c>
       <c r="B502" t="n">
-        <v>17.02664566040039</v>
+        <v>17.02664375305176</v>
       </c>
       <c r="C502" t="n">
-        <v>17.77952523896634</v>
+        <v>17.77952324727908</v>
       </c>
       <c r="D502" t="n">
-        <v>16.67916433577905</v>
+        <v>16.67916246735577</v>
       </c>
       <c r="E502" t="n">
-        <v>17.50926035001291</v>
+        <v>17.5092583886011</v>
       </c>
       <c r="F502" t="n">
         <v>19714300</v>
@@ -10492,16 +10492,16 @@
         <v>44988</v>
       </c>
       <c r="B504" t="n">
-        <v>16.92046928405762</v>
+        <v>16.92047119140625</v>
       </c>
       <c r="C504" t="n">
-        <v>17.22934234709782</v>
+        <v>17.22934428926396</v>
       </c>
       <c r="D504" t="n">
-        <v>16.72742269914315</v>
+        <v>16.72742458473074</v>
       </c>
       <c r="E504" t="n">
-        <v>16.92046928405762</v>
+        <v>16.92047119140625</v>
       </c>
       <c r="F504" t="n">
         <v>8320600</v>
@@ -10552,16 +10552,16 @@
         <v>44993</v>
       </c>
       <c r="B507" t="n">
-        <v>17.41273498535156</v>
+        <v>17.4127368927002</v>
       </c>
       <c r="C507" t="n">
-        <v>17.50925642883505</v>
+        <v>17.50925834675641</v>
       </c>
       <c r="D507" t="n">
-        <v>16.77568204398369</v>
+        <v>16.77568388155109</v>
       </c>
       <c r="E507" t="n">
-        <v>17.09420759415336</v>
+        <v>17.09420946661128</v>
       </c>
       <c r="F507" t="n">
         <v>19181400</v>
@@ -10572,16 +10572,16 @@
         <v>44994</v>
       </c>
       <c r="B508" t="n">
-        <v>17.24864768981934</v>
+        <v>17.24864959716797</v>
       </c>
       <c r="C508" t="n">
-        <v>17.80848058709395</v>
+        <v>17.80848255634869</v>
       </c>
       <c r="D508" t="n">
-        <v>17.18108009514125</v>
+        <v>17.18108199501829</v>
       </c>
       <c r="E508" t="n">
-        <v>17.36447417006721</v>
+        <v>17.36447609022389</v>
       </c>
       <c r="F508" t="n">
         <v>10746400</v>
@@ -10592,16 +10592,16 @@
         <v>44995</v>
       </c>
       <c r="B509" t="n">
-        <v>16.28341865539551</v>
+        <v>16.28341674804688</v>
       </c>
       <c r="C509" t="n">
-        <v>17.20038536068198</v>
+        <v>17.200383345925</v>
       </c>
       <c r="D509" t="n">
-        <v>16.10967709158599</v>
+        <v>16.10967520458848</v>
       </c>
       <c r="E509" t="n">
-        <v>17.11351457877723</v>
+        <v>17.1135125741958</v>
       </c>
       <c r="F509" t="n">
         <v>24597700</v>
@@ -10672,16 +10672,16 @@
         <v>45001</v>
       </c>
       <c r="B513" t="n">
-        <v>15.68497562408447</v>
+        <v>15.68497467041016</v>
       </c>
       <c r="C513" t="n">
-        <v>16.33167930807249</v>
+        <v>16.33167831507744</v>
       </c>
       <c r="D513" t="n">
-        <v>15.64636556962371</v>
+        <v>15.64636461829695</v>
       </c>
       <c r="E513" t="n">
-        <v>16.03245875011646</v>
+        <v>16.03245777531455</v>
       </c>
       <c r="F513" t="n">
         <v>11501700</v>
@@ -10692,16 +10692,16 @@
         <v>45002</v>
       </c>
       <c r="B514" t="n">
-        <v>15.3664493560791</v>
+        <v>15.36645030975342</v>
       </c>
       <c r="C514" t="n">
-        <v>15.63671420220887</v>
+        <v>15.6367151726564</v>
       </c>
       <c r="D514" t="n">
-        <v>15.26992606524499</v>
+        <v>15.26992701292887</v>
       </c>
       <c r="E514" t="n">
-        <v>15.34714432970655</v>
+        <v>15.34714528218276</v>
       </c>
       <c r="F514" t="n">
         <v>38654600</v>
@@ -10752,16 +10752,16 @@
         <v>45007</v>
       </c>
       <c r="B517" t="n">
-        <v>14.68113708496094</v>
+        <v>14.68113803863525</v>
       </c>
       <c r="C517" t="n">
-        <v>15.4919288903244</v>
+        <v>15.49192989666707</v>
       </c>
       <c r="D517" t="n">
-        <v>14.54600465714318</v>
+        <v>14.54600560203941</v>
       </c>
       <c r="E517" t="n">
-        <v>15.38575400308397</v>
+        <v>15.3857550025296</v>
       </c>
       <c r="F517" t="n">
         <v>42950800</v>
@@ -10772,16 +10772,16 @@
         <v>45008</v>
       </c>
       <c r="B518" t="n">
-        <v>14.71974754333496</v>
+        <v>14.71974658966064</v>
       </c>
       <c r="C518" t="n">
-        <v>15.01896904596353</v>
+        <v>15.01896807290302</v>
       </c>
       <c r="D518" t="n">
-        <v>14.256437898572</v>
+        <v>14.25643697491495</v>
       </c>
       <c r="E518" t="n">
-        <v>14.74870416600404</v>
+        <v>14.74870321045366</v>
       </c>
       <c r="F518" t="n">
         <v>25394300</v>
@@ -10792,16 +10792,16 @@
         <v>45009</v>
       </c>
       <c r="B519" t="n">
-        <v>14.43017768859863</v>
+        <v>14.43017673492432</v>
       </c>
       <c r="C519" t="n">
-        <v>14.95140146791577</v>
+        <v>14.95140047979436</v>
       </c>
       <c r="D519" t="n">
-        <v>14.01512972021653</v>
+        <v>14.01512879397227</v>
       </c>
       <c r="E519" t="n">
-        <v>14.74870328037497</v>
+        <v>14.74870230564966</v>
       </c>
       <c r="F519" t="n">
         <v>32819700</v>
@@ -10832,16 +10832,16 @@
         <v>45013</v>
       </c>
       <c r="B521" t="n">
-        <v>14.82592105865479</v>
+        <v>14.82592010498047</v>
       </c>
       <c r="C521" t="n">
-        <v>14.99001010601382</v>
+        <v>14.99000914178451</v>
       </c>
       <c r="D521" t="n">
-        <v>14.410873104024</v>
+        <v>14.41087217704756</v>
       </c>
       <c r="E521" t="n">
-        <v>14.57496215138304</v>
+        <v>14.5749612138516</v>
       </c>
       <c r="F521" t="n">
         <v>12984500</v>
@@ -10852,16 +10852,16 @@
         <v>45014</v>
       </c>
       <c r="B522" t="n">
-        <v>14.89348793029785</v>
+        <v>14.89348697662354</v>
       </c>
       <c r="C522" t="n">
-        <v>14.96105368463159</v>
+        <v>14.96105272663084</v>
       </c>
       <c r="D522" t="n">
-        <v>14.42052488841858</v>
+        <v>14.4205239650295</v>
       </c>
       <c r="E522" t="n">
-        <v>14.84522628269617</v>
+        <v>14.84522533211219</v>
       </c>
       <c r="F522" t="n">
         <v>19793200</v>
@@ -10872,16 +10872,16 @@
         <v>45015</v>
       </c>
       <c r="B523" t="n">
-        <v>15.41471195220947</v>
+        <v>15.41471099853516</v>
       </c>
       <c r="C523" t="n">
-        <v>15.73323662237289</v>
+        <v>15.73323564899215</v>
       </c>
       <c r="D523" t="n">
-        <v>14.82592149873313</v>
+        <v>14.82592058148598</v>
       </c>
       <c r="E523" t="n">
-        <v>15.15409960319252</v>
+        <v>15.15409866564172</v>
       </c>
       <c r="F523" t="n">
         <v>28286400</v>
@@ -10972,16 +10972,16 @@
         <v>45022</v>
       </c>
       <c r="B528" t="n">
-        <v>13.1560754776001</v>
+        <v>13.15607452392578</v>
       </c>
       <c r="C528" t="n">
-        <v>13.57112437142145</v>
+        <v>13.57112338766055</v>
       </c>
       <c r="D528" t="n">
-        <v>13.00163893678686</v>
+        <v>13.00163799430754</v>
       </c>
       <c r="E528" t="n">
-        <v>13.33946863968721</v>
+        <v>13.33946767271886</v>
       </c>
       <c r="F528" t="n">
         <v>26117400</v>
@@ -11012,16 +11012,16 @@
         <v>45027</v>
       </c>
       <c r="B530" t="n">
-        <v>14.19852352142334</v>
+        <v>14.19852256774902</v>
       </c>
       <c r="C530" t="n">
-        <v>14.32400344514125</v>
+        <v>14.3240024830388</v>
       </c>
       <c r="D530" t="n">
-        <v>13.51321065835749</v>
+        <v>13.51320975071368</v>
       </c>
       <c r="E530" t="n">
-        <v>13.52286317260835</v>
+        <v>13.52286226431621</v>
       </c>
       <c r="F530" t="n">
         <v>23105700</v>
@@ -11052,16 +11052,16 @@
         <v>45029</v>
       </c>
       <c r="B532" t="n">
-        <v>13.2719030380249</v>
+        <v>13.27190208435059</v>
       </c>
       <c r="C532" t="n">
-        <v>14.14060905048986</v>
+        <v>14.14060803439325</v>
       </c>
       <c r="D532" t="n">
-        <v>13.2719030380249</v>
+        <v>13.27190208435059</v>
       </c>
       <c r="E532" t="n">
-        <v>14.09234832130857</v>
+        <v>14.09234730867981</v>
       </c>
       <c r="F532" t="n">
         <v>20136100</v>
@@ -11072,16 +11072,16 @@
         <v>45030</v>
       </c>
       <c r="B533" t="n">
-        <v>12.76033020019531</v>
+        <v>12.76033115386963</v>
       </c>
       <c r="C533" t="n">
-        <v>13.29120644090545</v>
+        <v>13.29120743425609</v>
       </c>
       <c r="D533" t="n">
-        <v>12.59624116360283</v>
+        <v>12.59624210501355</v>
       </c>
       <c r="E533" t="n">
-        <v>13.20433566617834</v>
+        <v>13.20433665303648</v>
       </c>
       <c r="F533" t="n">
         <v>26653800</v>
@@ -11112,16 +11112,16 @@
         <v>45034</v>
       </c>
       <c r="B535" t="n">
-        <v>12.70241641998291</v>
+        <v>12.70241737365723</v>
       </c>
       <c r="C535" t="n">
-        <v>12.95337623873985</v>
+        <v>12.95337721125578</v>
       </c>
       <c r="D535" t="n">
-        <v>12.61554564268133</v>
+        <v>12.61554658983354</v>
       </c>
       <c r="E535" t="n">
-        <v>12.87615797458607</v>
+        <v>12.87615894130459</v>
       </c>
       <c r="F535" t="n">
         <v>12417000</v>
@@ -11172,16 +11172,16 @@
         <v>45040</v>
       </c>
       <c r="B538" t="n">
-        <v>12.45145797729492</v>
+        <v>12.45145702362061</v>
       </c>
       <c r="C538" t="n">
-        <v>12.88581191180532</v>
+        <v>12.88581092486324</v>
       </c>
       <c r="D538" t="n">
-        <v>12.35493559669272</v>
+        <v>12.35493465041118</v>
       </c>
       <c r="E538" t="n">
-        <v>12.54798127841155</v>
+        <v>12.54798031734438</v>
       </c>
       <c r="F538" t="n">
         <v>8287100</v>
@@ -11392,16 +11392,16 @@
         <v>45056</v>
       </c>
       <c r="B549" t="n">
-        <v>11.33929538726807</v>
+        <v>11.33929443359375</v>
       </c>
       <c r="C549" t="n">
-        <v>11.50405445670229</v>
+        <v>11.50405348917116</v>
       </c>
       <c r="D549" t="n">
-        <v>11.24237888565992</v>
+        <v>11.24237794013662</v>
       </c>
       <c r="E549" t="n">
-        <v>11.29083667432746</v>
+        <v>11.29083572472869</v>
       </c>
       <c r="F549" t="n">
         <v>11154600</v>
@@ -11532,16 +11532,16 @@
         <v>45065</v>
       </c>
       <c r="B556" t="n">
-        <v>11.45559597015381</v>
+        <v>11.45559501647949</v>
       </c>
       <c r="C556" t="n">
-        <v>11.70758054300638</v>
+        <v>11.70757956835444</v>
       </c>
       <c r="D556" t="n">
-        <v>10.74810188976746</v>
+        <v>10.74810099499177</v>
       </c>
       <c r="E556" t="n">
-        <v>11.01946939361549</v>
+        <v>11.01946847624856</v>
       </c>
       <c r="F556" t="n">
         <v>25040300</v>
@@ -11552,16 +11552,16 @@
         <v>45068</v>
       </c>
       <c r="B557" t="n">
-        <v>11.63973808288574</v>
+        <v>11.63973712921143</v>
       </c>
       <c r="C557" t="n">
-        <v>11.89172263808976</v>
+        <v>11.89172166376968</v>
       </c>
       <c r="D557" t="n">
-        <v>11.36836967377079</v>
+        <v>11.3683687423304</v>
       </c>
       <c r="E557" t="n">
-        <v>11.48467094869036</v>
+        <v>11.4846700077211</v>
       </c>
       <c r="F557" t="n">
         <v>13575900</v>
@@ -11592,16 +11592,16 @@
         <v>45070</v>
       </c>
       <c r="B559" t="n">
-        <v>10.86440181732178</v>
+        <v>10.86440086364746</v>
       </c>
       <c r="C559" t="n">
-        <v>11.058235740948</v>
+        <v>11.05823477025899</v>
       </c>
       <c r="D559" t="n">
-        <v>10.68025982094513</v>
+        <v>10.68025888343475</v>
       </c>
       <c r="E559" t="n">
-        <v>11.02916088347233</v>
+        <v>11.02915991533551</v>
       </c>
       <c r="F559" t="n">
         <v>30388700</v>
@@ -11632,16 +11632,16 @@
         <v>45072</v>
       </c>
       <c r="B561" t="n">
-        <v>11.04854393005371</v>
+        <v>11.04854297637939</v>
       </c>
       <c r="C561" t="n">
-        <v>11.38775399317671</v>
+        <v>11.38775301022289</v>
       </c>
       <c r="D561" t="n">
-        <v>10.77717643411915</v>
+        <v>10.77717550386839</v>
       </c>
       <c r="E561" t="n">
-        <v>11.38775399317671</v>
+        <v>11.38775301022289</v>
       </c>
       <c r="F561" t="n">
         <v>33081400</v>
@@ -11692,16 +11692,16 @@
         <v>45077</v>
       </c>
       <c r="B564" t="n">
-        <v>10.41858291625977</v>
+        <v>10.41858196258545</v>
       </c>
       <c r="C564" t="n">
-        <v>10.89347624131492</v>
+        <v>10.89347524417082</v>
       </c>
       <c r="D564" t="n">
-        <v>10.36043227934935</v>
+        <v>10.3604313309979</v>
       </c>
       <c r="E564" t="n">
-        <v>10.89347624131492</v>
+        <v>10.89347524417082</v>
       </c>
       <c r="F564" t="n">
         <v>32506900</v>
@@ -11712,16 +11712,16 @@
         <v>45078</v>
       </c>
       <c r="B565" t="n">
-        <v>10.67056655883789</v>
+        <v>10.67056751251221</v>
       </c>
       <c r="C565" t="n">
-        <v>10.70933333871352</v>
+        <v>10.70933429585259</v>
       </c>
       <c r="D565" t="n">
-        <v>10.21505620209453</v>
+        <v>10.21505711505793</v>
       </c>
       <c r="E565" t="n">
-        <v>10.51549943933537</v>
+        <v>10.51550037915067</v>
       </c>
       <c r="F565" t="n">
         <v>22690400</v>
@@ -11752,16 +11752,16 @@
         <v>45082</v>
       </c>
       <c r="B567" t="n">
-        <v>10.81594276428223</v>
+        <v>10.81594181060791</v>
       </c>
       <c r="C567" t="n">
-        <v>11.23268638014201</v>
+        <v>11.23268538972215</v>
       </c>
       <c r="D567" t="n">
-        <v>10.68025948415897</v>
+        <v>10.68025854244826</v>
       </c>
       <c r="E567" t="n">
-        <v>11.12607703230456</v>
+        <v>11.12607605128477</v>
       </c>
       <c r="F567" t="n">
         <v>24462400</v>
@@ -11792,16 +11792,16 @@
         <v>45084</v>
       </c>
       <c r="B569" t="n">
-        <v>12.38599872589111</v>
+        <v>12.3859977722168</v>
       </c>
       <c r="C569" t="n">
-        <v>13.103185598031</v>
+        <v>13.10318458913605</v>
       </c>
       <c r="D569" t="n">
-        <v>12.09524739116122</v>
+        <v>12.09524645987364</v>
       </c>
       <c r="E569" t="n">
-        <v>12.42476550890357</v>
+        <v>12.42476455224435</v>
       </c>
       <c r="F569" t="n">
         <v>35775900</v>
@@ -11832,16 +11832,16 @@
         <v>45089</v>
       </c>
       <c r="B571" t="n">
-        <v>13.29701995849609</v>
+        <v>13.29701900482178</v>
       </c>
       <c r="C571" t="n">
-        <v>13.5296206643621</v>
+        <v>13.52961969400545</v>
       </c>
       <c r="D571" t="n">
-        <v>12.72520919670404</v>
+        <v>12.72520828404051</v>
       </c>
       <c r="E571" t="n">
-        <v>12.80274276532604</v>
+        <v>12.80274184710173</v>
       </c>
       <c r="F571" t="n">
         <v>31653900</v>
@@ -11912,16 +11912,16 @@
         <v>45093</v>
       </c>
       <c r="B575" t="n">
-        <v>13.0934944152832</v>
+        <v>13.09349346160889</v>
       </c>
       <c r="C575" t="n">
-        <v>13.60715455045659</v>
+        <v>13.60715355936946</v>
       </c>
       <c r="D575" t="n">
-        <v>12.93842727442128</v>
+        <v>12.93842633204139</v>
       </c>
       <c r="E575" t="n">
-        <v>13.60715455045659</v>
+        <v>13.60715355936946</v>
       </c>
       <c r="F575" t="n">
         <v>29424500</v>
@@ -11952,16 +11952,16 @@
         <v>45097</v>
       </c>
       <c r="B577" t="n">
-        <v>12.91904258728027</v>
+        <v>12.91904163360596</v>
       </c>
       <c r="C577" t="n">
-        <v>13.00626807946328</v>
+        <v>13.00626711935004</v>
       </c>
       <c r="D577" t="n">
-        <v>12.60890832553893</v>
+        <v>12.6089073947585</v>
       </c>
       <c r="E577" t="n">
-        <v>12.77366738315727</v>
+        <v>12.77366644021444</v>
       </c>
       <c r="F577" t="n">
         <v>13900100</v>
@@ -11972,16 +11972,16 @@
         <v>45098</v>
       </c>
       <c r="B578" t="n">
-        <v>12.98688411712646</v>
+        <v>12.98688507080078</v>
       </c>
       <c r="C578" t="n">
-        <v>13.03534282618567</v>
+        <v>13.03534378341849</v>
       </c>
       <c r="D578" t="n">
-        <v>12.70582471371064</v>
+        <v>12.70582564674574</v>
       </c>
       <c r="E578" t="n">
-        <v>12.99657604379291</v>
+        <v>12.99657699817894</v>
       </c>
       <c r="F578" t="n">
         <v>18033300</v>
@@ -12032,16 +12032,16 @@
         <v>45103</v>
       </c>
       <c r="B581" t="n">
-        <v>13.47146892547607</v>
+        <v>13.47146987915039</v>
       </c>
       <c r="C581" t="n">
-        <v>14.14019705556374</v>
+        <v>14.14019805657877</v>
       </c>
       <c r="D581" t="n">
-        <v>13.35516858204191</v>
+        <v>13.35516952748307</v>
       </c>
       <c r="E581" t="n">
-        <v>13.85913766119627</v>
+        <v>13.85913864231449</v>
       </c>
       <c r="F581" t="n">
         <v>23023000</v>
@@ -12052,16 +12052,16 @@
         <v>45104</v>
       </c>
       <c r="B582" t="n">
-        <v>12.68644237518311</v>
+        <v>12.68644142150879</v>
       </c>
       <c r="C582" t="n">
-        <v>13.85913875249263</v>
+        <v>13.85913771066354</v>
       </c>
       <c r="D582" t="n">
-        <v>12.56045009547363</v>
+        <v>12.5604491512705</v>
       </c>
       <c r="E582" t="n">
-        <v>13.77191325698045</v>
+        <v>13.77191222170834</v>
       </c>
       <c r="F582" t="n">
         <v>64278500</v>
@@ -12112,16 +12112,16 @@
         <v>45107</v>
       </c>
       <c r="B585" t="n">
-        <v>13.32609462738037</v>
+        <v>13.32609367370605</v>
       </c>
       <c r="C585" t="n">
-        <v>13.48116176243347</v>
+        <v>13.48116079766187</v>
       </c>
       <c r="D585" t="n">
-        <v>12.96750164650181</v>
+        <v>12.96750071848999</v>
       </c>
       <c r="E585" t="n">
-        <v>13.08380199779164</v>
+        <v>13.08380106145685</v>
       </c>
       <c r="F585" t="n">
         <v>19641600</v>
@@ -12172,16 +12172,16 @@
         <v>45112</v>
       </c>
       <c r="B588" t="n">
-        <v>13.29701995849609</v>
+        <v>13.29701900482178</v>
       </c>
       <c r="C588" t="n">
-        <v>13.59746230583809</v>
+        <v>13.59746133061578</v>
       </c>
       <c r="D588" t="n">
-        <v>13.14195282125209</v>
+        <v>13.14195187869933</v>
       </c>
       <c r="E588" t="n">
-        <v>13.17102767841708</v>
+        <v>13.17102673377904</v>
       </c>
       <c r="F588" t="n">
         <v>9442900</v>
@@ -12192,16 +12192,16 @@
         <v>45113</v>
       </c>
       <c r="B589" t="n">
-        <v>13.1710262298584</v>
+        <v>13.17102718353271</v>
       </c>
       <c r="C589" t="n">
-        <v>13.32609335004801</v>
+        <v>13.32609431495027</v>
       </c>
       <c r="D589" t="n">
-        <v>13.03534203755601</v>
+        <v>13.03534298140585</v>
       </c>
       <c r="E589" t="n">
-        <v>13.22917593779303</v>
+        <v>13.22917689567779</v>
       </c>
       <c r="F589" t="n">
         <v>10770700</v>
@@ -12232,16 +12232,16 @@
         <v>45117</v>
       </c>
       <c r="B591" t="n">
-        <v>13.28732681274414</v>
+        <v>13.28732776641846</v>
       </c>
       <c r="C591" t="n">
-        <v>13.70407039907184</v>
+        <v>13.70407138265719</v>
       </c>
       <c r="D591" t="n">
-        <v>13.21948517749003</v>
+        <v>13.21948612629514</v>
       </c>
       <c r="E591" t="n">
-        <v>13.55869427803353</v>
+        <v>13.55869525118476</v>
       </c>
       <c r="F591" t="n">
         <v>9043800</v>
@@ -12332,16 +12332,16 @@
         <v>45124</v>
       </c>
       <c r="B596" t="n">
-        <v>12.42476463317871</v>
+        <v>12.42476558685303</v>
       </c>
       <c r="C596" t="n">
-        <v>12.44414848545523</v>
+        <v>12.44414944061737</v>
       </c>
       <c r="D596" t="n">
-        <v>11.97894619782127</v>
+        <v>11.97894711727638</v>
       </c>
       <c r="E596" t="n">
-        <v>12.11463039093804</v>
+        <v>12.11463132080772</v>
       </c>
       <c r="F596" t="n">
         <v>11160300</v>
@@ -12372,16 +12372,16 @@
         <v>45126</v>
       </c>
       <c r="B598" t="n">
-        <v>11.7657299041748</v>
+        <v>11.76573085784912</v>
       </c>
       <c r="C598" t="n">
-        <v>12.20185643325319</v>
+        <v>12.20185742227786</v>
       </c>
       <c r="D598" t="n">
-        <v>11.71727119554988</v>
+        <v>11.71727214529636</v>
       </c>
       <c r="E598" t="n">
-        <v>12.08555608711715</v>
+        <v>12.08555706671507</v>
       </c>
       <c r="F598" t="n">
         <v>18624600</v>
@@ -12432,16 +12432,16 @@
         <v>45131</v>
       </c>
       <c r="B601" t="n">
-        <v>12.38599872589111</v>
+        <v>12.3859977722168</v>
       </c>
       <c r="C601" t="n">
-        <v>12.54106585794092</v>
+        <v>12.54106489232703</v>
       </c>
       <c r="D601" t="n">
-        <v>12.03709767877904</v>
+        <v>12.03709675196877</v>
       </c>
       <c r="E601" t="n">
-        <v>12.19216481082885</v>
+        <v>12.192163872079</v>
       </c>
       <c r="F601" t="n">
         <v>10834500</v>
@@ -12472,16 +12472,16 @@
         <v>45133</v>
       </c>
       <c r="B603" t="n">
-        <v>12.47322368621826</v>
+        <v>12.47322463989258</v>
       </c>
       <c r="C603" t="n">
-        <v>12.75428308212753</v>
+        <v>12.75428405729101</v>
       </c>
       <c r="D603" t="n">
-        <v>12.19216429030899</v>
+        <v>12.19216522249415</v>
       </c>
       <c r="E603" t="n">
-        <v>12.52168239398323</v>
+        <v>12.52168335136259</v>
       </c>
       <c r="F603" t="n">
         <v>40141600</v>
@@ -12532,16 +12532,16 @@
         <v>45138</v>
       </c>
       <c r="B606" t="n">
-        <v>13.05472660064697</v>
+        <v>13.05472755432129</v>
       </c>
       <c r="C606" t="n">
-        <v>13.18071887373052</v>
+        <v>13.18071983660883</v>
       </c>
       <c r="D606" t="n">
-        <v>12.72520849016276</v>
+        <v>12.72520941976511</v>
       </c>
       <c r="E606" t="n">
-        <v>12.89965947201275</v>
+        <v>12.8996604143591</v>
       </c>
       <c r="F606" t="n">
         <v>32856600</v>
@@ -12632,16 +12632,16 @@
         <v>45145</v>
       </c>
       <c r="B611" t="n">
-        <v>13.44239521026611</v>
+        <v>13.4423942565918</v>
       </c>
       <c r="C611" t="n">
-        <v>13.85913883610609</v>
+        <v>13.85913785286578</v>
       </c>
       <c r="D611" t="n">
-        <v>13.38424549575587</v>
+        <v>13.384244546207</v>
       </c>
       <c r="E611" t="n">
-        <v>13.58777134508783</v>
+        <v>13.58777038109976</v>
       </c>
       <c r="F611" t="n">
         <v>31957200</v>
@@ -12792,16 +12792,16 @@
         <v>45155</v>
       </c>
       <c r="B619" t="n">
-        <v>12.60890769958496</v>
+        <v>12.60890865325928</v>
       </c>
       <c r="C619" t="n">
-        <v>12.81243352981718</v>
+        <v>12.81243449888516</v>
       </c>
       <c r="D619" t="n">
-        <v>12.45384057641241</v>
+        <v>12.45384151835823</v>
       </c>
       <c r="E619" t="n">
-        <v>12.67674933490471</v>
+        <v>12.67675029371023</v>
       </c>
       <c r="F619" t="n">
         <v>17965700</v>
@@ -12832,16 +12832,16 @@
         <v>45159</v>
       </c>
       <c r="B621" t="n">
-        <v>12.68644237518311</v>
+        <v>12.68644142150879</v>
       </c>
       <c r="C621" t="n">
-        <v>13.07411021715607</v>
+        <v>13.07410923433971</v>
       </c>
       <c r="D621" t="n">
-        <v>12.68644237518311</v>
+        <v>12.68644142150879</v>
       </c>
       <c r="E621" t="n">
-        <v>13.03534343295877</v>
+        <v>13.03534245305662</v>
       </c>
       <c r="F621" t="n">
         <v>19861900</v>
@@ -12852,16 +12852,16 @@
         <v>45160</v>
       </c>
       <c r="B622" t="n">
-        <v>12.57014179229736</v>
+        <v>12.57014083862305</v>
       </c>
       <c r="C622" t="n">
-        <v>12.86089313058684</v>
+        <v>12.86089215485373</v>
       </c>
       <c r="D622" t="n">
-        <v>12.40538273140909</v>
+        <v>12.40538179023475</v>
       </c>
       <c r="E622" t="n">
-        <v>12.84150927670679</v>
+        <v>12.84150830244431</v>
       </c>
       <c r="F622" t="n">
         <v>10646800</v>
@@ -12912,16 +12912,16 @@
         <v>45163</v>
       </c>
       <c r="B625" t="n">
-        <v>11.98863887786865</v>
+        <v>11.98863792419434</v>
       </c>
       <c r="C625" t="n">
-        <v>12.50229897994967</v>
+        <v>12.50229798541463</v>
       </c>
       <c r="D625" t="n">
-        <v>11.94018016840297</v>
+        <v>11.94017921858345</v>
       </c>
       <c r="E625" t="n">
-        <v>12.40538248529131</v>
+        <v>12.4053814984658</v>
       </c>
       <c r="F625" t="n">
         <v>23324500</v>
@@ -13032,16 +13032,16 @@
         <v>45173</v>
       </c>
       <c r="B631" t="n">
-        <v>11.87233924865723</v>
+        <v>11.87233829498291</v>
       </c>
       <c r="C631" t="n">
-        <v>11.96925667345753</v>
+        <v>11.96925571199809</v>
       </c>
       <c r="D631" t="n">
-        <v>11.48467139800213</v>
+        <v>11.48467047546817</v>
       </c>
       <c r="E631" t="n">
-        <v>11.49436240106371</v>
+        <v>11.4943614777513</v>
       </c>
       <c r="F631" t="n">
         <v>7669300</v>
@@ -13112,16 +13112,16 @@
         <v>45180</v>
       </c>
       <c r="B635" t="n">
-        <v>11.84326457977295</v>
+        <v>11.84326362609863</v>
       </c>
       <c r="C635" t="n">
-        <v>11.99833172250761</v>
+        <v>11.99833075634657</v>
       </c>
       <c r="D635" t="n">
-        <v>11.6978884402544</v>
+        <v>11.69788749828644</v>
       </c>
       <c r="E635" t="n">
-        <v>11.87233943796743</v>
+        <v>11.87233848195187</v>
       </c>
       <c r="F635" t="n">
         <v>12088600</v>
@@ -13132,16 +13132,16 @@
         <v>45181</v>
       </c>
       <c r="B636" t="n">
-        <v>12.47322368621826</v>
+        <v>12.47322463989258</v>
       </c>
       <c r="C636" t="n">
-        <v>12.5701411017482</v>
+        <v>12.57014206283261</v>
       </c>
       <c r="D636" t="n">
-        <v>11.85295426022717</v>
+        <v>11.85295516647709</v>
       </c>
       <c r="E636" t="n">
-        <v>11.85295426022717</v>
+        <v>11.85295516647709</v>
       </c>
       <c r="F636" t="n">
         <v>14965900</v>
@@ -13212,16 +13212,16 @@
         <v>45187</v>
       </c>
       <c r="B640" t="n">
-        <v>11.88203048706055</v>
+        <v>11.88203144073486</v>
       </c>
       <c r="C640" t="n">
-        <v>12.11463118396719</v>
+        <v>12.11463215631048</v>
       </c>
       <c r="D640" t="n">
-        <v>11.82387985069738</v>
+        <v>11.82388079970442</v>
       </c>
       <c r="E640" t="n">
-        <v>12.00802276228657</v>
+        <v>12.00802372607326</v>
       </c>
       <c r="F640" t="n">
         <v>10083800</v>
@@ -13252,16 +13252,16 @@
         <v>45189</v>
       </c>
       <c r="B642" t="n">
-        <v>11.7657299041748</v>
+        <v>11.76573085784912</v>
       </c>
       <c r="C642" t="n">
-        <v>11.85295447057209</v>
+        <v>11.85295543131642</v>
       </c>
       <c r="D642" t="n">
-        <v>11.45559472353905</v>
+        <v>11.45559565207528</v>
       </c>
       <c r="E642" t="n">
-        <v>11.72696312212946</v>
+        <v>11.72696407266152</v>
       </c>
       <c r="F642" t="n">
         <v>16179800</v>
@@ -13592,16 +13592,16 @@
         <v>45215</v>
       </c>
       <c r="B659" t="n">
-        <v>11.40713787078857</v>
+        <v>11.40713691711426</v>
       </c>
       <c r="C659" t="n">
-        <v>11.5331292295207</v>
+        <v>11.5331282653131</v>
       </c>
       <c r="D659" t="n">
-        <v>11.14546137740708</v>
+        <v>11.14546044560978</v>
       </c>
       <c r="E659" t="n">
-        <v>11.3586791582061</v>
+        <v>11.3586782085831</v>
       </c>
       <c r="F659" t="n">
         <v>7162600</v>
@@ -13632,16 +13632,16 @@
         <v>45217</v>
       </c>
       <c r="B661" t="n">
-        <v>10.48642444610596</v>
+        <v>10.48642539978027</v>
       </c>
       <c r="C661" t="n">
-        <v>11.16484453111691</v>
+        <v>11.16484554648926</v>
       </c>
       <c r="D661" t="n">
-        <v>10.44765766332873</v>
+        <v>10.44765861347745</v>
       </c>
       <c r="E661" t="n">
-        <v>11.16484453111691</v>
+        <v>11.16484554648926</v>
       </c>
       <c r="F661" t="n">
         <v>15312800</v>
@@ -13652,16 +13652,16 @@
         <v>45218</v>
       </c>
       <c r="B662" t="n">
-        <v>10.65118408203125</v>
+        <v>10.65118312835693</v>
       </c>
       <c r="C662" t="n">
-        <v>10.9128605731838</v>
+        <v>10.91285959607978</v>
       </c>
       <c r="D662" t="n">
-        <v>10.38950851515176</v>
+        <v>10.38950758490707</v>
       </c>
       <c r="E662" t="n">
-        <v>10.41858337274435</v>
+        <v>10.41858243989639</v>
       </c>
       <c r="F662" t="n">
         <v>8209500</v>
@@ -13672,16 +13672,16 @@
         <v>45219</v>
       </c>
       <c r="B663" t="n">
-        <v>10.73840808868408</v>
+        <v>10.7384090423584</v>
       </c>
       <c r="C663" t="n">
-        <v>10.74810001462748</v>
+        <v>10.74810096916253</v>
       </c>
       <c r="D663" t="n">
-        <v>10.5445741911808</v>
+        <v>10.5445751276408</v>
       </c>
       <c r="E663" t="n">
-        <v>10.58334097068145</v>
+        <v>10.58334191058432</v>
       </c>
       <c r="F663" t="n">
         <v>9727700</v>
@@ -13752,16 +13752,16 @@
         <v>45225</v>
       </c>
       <c r="B667" t="n">
-        <v>11.33929538726807</v>
+        <v>11.33929443359375</v>
       </c>
       <c r="C667" t="n">
-        <v>11.5718961002553</v>
+        <v>11.57189512701845</v>
       </c>
       <c r="D667" t="n">
-        <v>10.75779360479998</v>
+        <v>10.75779270003199</v>
       </c>
       <c r="E667" t="n">
-        <v>10.76748460796964</v>
+        <v>10.76748370238661</v>
       </c>
       <c r="F667" t="n">
         <v>21852600</v>
@@ -13772,16 +13772,16 @@
         <v>45226</v>
       </c>
       <c r="B668" t="n">
-        <v>10.78686714172363</v>
+        <v>10.78686809539795</v>
       </c>
       <c r="C668" t="n">
-        <v>11.45559434072722</v>
+        <v>11.45559535352417</v>
       </c>
       <c r="D668" t="n">
-        <v>10.74810036097376</v>
+        <v>10.74810131122068</v>
       </c>
       <c r="E668" t="n">
-        <v>11.3392939984776</v>
+        <v>11.33929500099235</v>
       </c>
       <c r="F668" t="n">
         <v>13292000</v>
@@ -13812,16 +13812,16 @@
         <v>45230</v>
       </c>
       <c r="B670" t="n">
-        <v>10.6027250289917</v>
+        <v>10.60272598266602</v>
       </c>
       <c r="C670" t="n">
-        <v>11.13576899717533</v>
+        <v>11.1357699987949</v>
       </c>
       <c r="D670" t="n">
-        <v>10.52519146172205</v>
+        <v>10.52519240842252</v>
       </c>
       <c r="E670" t="n">
-        <v>10.77717601748493</v>
+        <v>10.77717698685044</v>
       </c>
       <c r="F670" t="n">
         <v>15178600</v>
@@ -13832,16 +13832,16 @@
         <v>45231</v>
       </c>
       <c r="B671" t="n">
-        <v>10.73840808868408</v>
+        <v>10.7384090423584</v>
       </c>
       <c r="C671" t="n">
-        <v>10.84501650124265</v>
+        <v>10.84501746438483</v>
       </c>
       <c r="D671" t="n">
-        <v>10.35074029367752</v>
+        <v>10.35074121292319</v>
       </c>
       <c r="E671" t="n">
-        <v>10.66087452968277</v>
+        <v>10.66087547647136</v>
       </c>
       <c r="F671" t="n">
         <v>19375400</v>
@@ -13852,16 +13852,16 @@
         <v>45233</v>
       </c>
       <c r="B672" t="n">
-        <v>11.57189559936523</v>
+        <v>11.57189464569092</v>
       </c>
       <c r="C672" t="n">
-        <v>11.61066238318509</v>
+        <v>11.61066142631588</v>
       </c>
       <c r="D672" t="n">
-        <v>11.24237839903302</v>
+        <v>11.2423774725152</v>
       </c>
       <c r="E672" t="n">
-        <v>11.25206940178321</v>
+        <v>11.25206847446672</v>
       </c>
       <c r="F672" t="n">
         <v>16636800</v>
@@ -14012,16 +14012,16 @@
         <v>45246</v>
       </c>
       <c r="B680" t="n">
-        <v>12.92873382568359</v>
+        <v>12.92873477935791</v>
       </c>
       <c r="C680" t="n">
-        <v>13.1322596551836</v>
+        <v>13.13226062387078</v>
       </c>
       <c r="D680" t="n">
-        <v>12.16308921456891</v>
+        <v>12.16309011176626</v>
       </c>
       <c r="E680" t="n">
-        <v>12.40538182472258</v>
+        <v>12.40538273979239</v>
       </c>
       <c r="F680" t="n">
         <v>22426900</v>
@@ -14072,16 +14072,16 @@
         <v>45251</v>
       </c>
       <c r="B683" t="n">
-        <v>12.38599872589111</v>
+        <v>12.3859977722168</v>
       </c>
       <c r="C683" t="n">
-        <v>12.48291614555875</v>
+        <v>12.48291518442216</v>
       </c>
       <c r="D683" t="n">
-        <v>12.22123966701994</v>
+        <v>12.22123872603144</v>
       </c>
       <c r="E683" t="n">
-        <v>12.4441493625463</v>
+        <v>12.44414840439461</v>
       </c>
       <c r="F683" t="n">
         <v>9484000</v>
@@ -14092,16 +14092,16 @@
         <v>45252</v>
       </c>
       <c r="B684" t="n">
-        <v>12.57014179229736</v>
+        <v>12.57014083862305</v>
       </c>
       <c r="C684" t="n">
-        <v>12.72520892624561</v>
+        <v>12.72520796080663</v>
       </c>
       <c r="D684" t="n">
-        <v>12.39569080446907</v>
+        <v>12.39568986403004</v>
       </c>
       <c r="E684" t="n">
-        <v>12.48291629838322</v>
+        <v>12.48291535132654</v>
       </c>
       <c r="F684" t="n">
         <v>10478000</v>
@@ -14112,16 +14112,16 @@
         <v>45253</v>
       </c>
       <c r="B685" t="n">
-        <v>13.18071937561035</v>
+        <v>13.18071842193604</v>
       </c>
       <c r="C685" t="n">
-        <v>13.29701972651436</v>
+        <v>13.29701876442528</v>
       </c>
       <c r="D685" t="n">
-        <v>12.62829155347501</v>
+        <v>12.62829063977091</v>
       </c>
       <c r="E685" t="n">
-        <v>12.63798348045194</v>
+        <v>12.63798256604659</v>
       </c>
       <c r="F685" t="n">
         <v>8829200</v>
@@ -14172,16 +14172,16 @@
         <v>45258</v>
       </c>
       <c r="B688" t="n">
-        <v>13.10318565368652</v>
+        <v>13.10318660736084</v>
       </c>
       <c r="C688" t="n">
-        <v>13.48116155859512</v>
+        <v>13.48116253977923</v>
       </c>
       <c r="D688" t="n">
-        <v>12.98688437988217</v>
+        <v>12.98688532509186</v>
       </c>
       <c r="E688" t="n">
-        <v>13.14195243686364</v>
+        <v>13.14195339335947</v>
       </c>
       <c r="F688" t="n">
         <v>17069200</v>
@@ -14272,16 +14272,16 @@
         <v>45265</v>
       </c>
       <c r="B693" t="n">
-        <v>12.30846500396729</v>
+        <v>12.3084659576416</v>
       </c>
       <c r="C693" t="n">
-        <v>12.65736697093318</v>
+        <v>12.65736795164083</v>
       </c>
       <c r="D693" t="n">
-        <v>12.23093143892442</v>
+        <v>12.23093238659134</v>
       </c>
       <c r="E693" t="n">
-        <v>12.33753985979011</v>
+        <v>12.33754081571718</v>
       </c>
       <c r="F693" t="n">
         <v>12428700</v>
@@ -14292,16 +14292,16 @@
         <v>45266</v>
       </c>
       <c r="B694" t="n">
-        <v>11.87233924865723</v>
+        <v>11.87233829498291</v>
       </c>
       <c r="C694" t="n">
-        <v>12.62829201957119</v>
+        <v>12.62829100517314</v>
       </c>
       <c r="D694" t="n">
-        <v>11.84326439092636</v>
+        <v>11.84326343958755</v>
       </c>
       <c r="E694" t="n">
-        <v>12.43445809424364</v>
+        <v>12.43445709541577</v>
       </c>
       <c r="F694" t="n">
         <v>16842800</v>
@@ -14332,16 +14332,16 @@
         <v>45268</v>
       </c>
       <c r="B696" t="n">
-        <v>11.61066246032715</v>
+        <v>11.61066150665283</v>
       </c>
       <c r="C696" t="n">
-        <v>11.96925636838458</v>
+        <v>11.96925538525615</v>
       </c>
       <c r="D696" t="n">
-        <v>11.58158760333734</v>
+        <v>11.58158665205117</v>
       </c>
       <c r="E696" t="n">
-        <v>11.85295509187928</v>
+        <v>11.85295411830358</v>
       </c>
       <c r="F696" t="n">
         <v>16929900</v>
@@ -14352,16 +14352,16 @@
         <v>45271</v>
       </c>
       <c r="B697" t="n">
-        <v>11.54282093048096</v>
+        <v>11.54281997680664</v>
       </c>
       <c r="C697" t="n">
-        <v>11.64943028092588</v>
+        <v>11.64942931844344</v>
       </c>
       <c r="D697" t="n">
-        <v>11.40713764703913</v>
+        <v>11.40713670457504</v>
       </c>
       <c r="E697" t="n">
-        <v>11.63004642656387</v>
+        <v>11.63004546568294</v>
       </c>
       <c r="F697" t="n">
         <v>10547700</v>
@@ -14392,16 +14392,16 @@
         <v>45273</v>
       </c>
       <c r="B699" t="n">
-        <v>12.54106521606445</v>
+        <v>12.54106616973877</v>
       </c>
       <c r="C699" t="n">
-        <v>12.59921584974338</v>
+        <v>12.5992168078397</v>
       </c>
       <c r="D699" t="n">
-        <v>11.55251183770653</v>
+        <v>11.55251271620717</v>
       </c>
       <c r="E699" t="n">
-        <v>11.6203534734378</v>
+        <v>11.6203543570974</v>
       </c>
       <c r="F699" t="n">
         <v>24349900</v>
@@ -14432,16 +14432,16 @@
         <v>45275</v>
       </c>
       <c r="B701" t="n">
-        <v>12.47322368621826</v>
+        <v>12.47322463989258</v>
       </c>
       <c r="C701" t="n">
-        <v>12.93842598677983</v>
+        <v>12.93842697602245</v>
       </c>
       <c r="D701" t="n">
-        <v>12.26969785302376</v>
+        <v>12.26969879113695</v>
       </c>
       <c r="E701" t="n">
-        <v>12.93842598677983</v>
+        <v>12.93842697602245</v>
       </c>
       <c r="F701" t="n">
         <v>13438600</v>
@@ -14452,16 +14452,16 @@
         <v>45278</v>
       </c>
       <c r="B702" t="n">
-        <v>12.80274200439453</v>
+        <v>12.80274105072021</v>
       </c>
       <c r="C702" t="n">
-        <v>12.97719298556206</v>
+        <v>12.97719201889291</v>
       </c>
       <c r="D702" t="n">
-        <v>12.34723162260876</v>
+        <v>12.34723070286534</v>
       </c>
       <c r="E702" t="n">
-        <v>12.55075745921321</v>
+        <v>12.55075652430919</v>
       </c>
       <c r="F702" t="n">
         <v>9094600</v>
@@ -14472,16 +14472,16 @@
         <v>45279</v>
       </c>
       <c r="B703" t="n">
-        <v>12.98688411712646</v>
+        <v>12.98688507080078</v>
       </c>
       <c r="C703" t="n">
-        <v>13.05472667951856</v>
+        <v>13.0547276381748</v>
       </c>
       <c r="D703" t="n">
-        <v>12.87058376994816</v>
+        <v>12.87058471508212</v>
       </c>
       <c r="E703" t="n">
-        <v>12.98688411712646</v>
+        <v>12.98688507080078</v>
       </c>
       <c r="F703" t="n">
         <v>5248800</v>
@@ -14612,16 +14612,16 @@
         <v>45293</v>
       </c>
       <c r="B710" t="n">
-        <v>12.61860084533691</v>
+        <v>12.6185998916626</v>
       </c>
       <c r="C710" t="n">
-        <v>13.03534354806971</v>
+        <v>13.03534256289929</v>
       </c>
       <c r="D710" t="n">
-        <v>12.50229956744496</v>
+        <v>12.50229862256033</v>
       </c>
       <c r="E710" t="n">
-        <v>13.03534354806971</v>
+        <v>13.03534256289929</v>
       </c>
       <c r="F710" t="n">
         <v>7348700</v>
@@ -14632,16 +14632,16 @@
         <v>45294</v>
       </c>
       <c r="B711" t="n">
-        <v>12.54106521606445</v>
+        <v>12.54106616973877</v>
       </c>
       <c r="C711" t="n">
-        <v>12.71551619282825</v>
+        <v>12.71551715976854</v>
       </c>
       <c r="D711" t="n">
-        <v>12.31815645622002</v>
+        <v>12.31815739294343</v>
       </c>
       <c r="E711" t="n">
-        <v>12.62829070444635</v>
+        <v>12.62829166475365</v>
       </c>
       <c r="F711" t="n">
         <v>6830500</v>
@@ -14652,16 +14652,16 @@
         <v>45295</v>
       </c>
       <c r="B712" t="n">
-        <v>12.80274200439453</v>
+        <v>12.80274105072021</v>
       </c>
       <c r="C712" t="n">
-        <v>12.91904235041522</v>
+        <v>12.91904138807771</v>
       </c>
       <c r="D712" t="n">
-        <v>12.44414903976249</v>
+        <v>12.44414811279971</v>
       </c>
       <c r="E712" t="n">
-        <v>12.50229875063634</v>
+        <v>12.502297819342</v>
       </c>
       <c r="F712" t="n">
         <v>8604100</v>
@@ -14752,16 +14752,16 @@
         <v>45302</v>
       </c>
       <c r="B717" t="n">
-        <v>13.44239521026611</v>
+        <v>13.4423942565918</v>
       </c>
       <c r="C717" t="n">
-        <v>13.71376270128438</v>
+        <v>13.71376172835782</v>
       </c>
       <c r="D717" t="n">
-        <v>13.20979450367903</v>
+        <v>13.20979356650663</v>
       </c>
       <c r="E717" t="n">
-        <v>13.20979450367903</v>
+        <v>13.20979356650663</v>
       </c>
       <c r="F717" t="n">
         <v>14967000</v>
@@ -14812,16 +14812,16 @@
         <v>45307</v>
       </c>
       <c r="B720" t="n">
-        <v>14.03358745574951</v>
+        <v>14.03358840942383</v>
       </c>
       <c r="C720" t="n">
-        <v>14.30495584303765</v>
+        <v>14.30495681515323</v>
       </c>
       <c r="D720" t="n">
-        <v>13.93667096680914</v>
+        <v>13.93667191389734</v>
       </c>
       <c r="E720" t="n">
-        <v>14.30495584303765</v>
+        <v>14.30495681515323</v>
       </c>
       <c r="F720" t="n">
         <v>11210600</v>
@@ -14852,16 +14852,16 @@
         <v>45309</v>
       </c>
       <c r="B722" t="n">
-        <v>13.36486148834229</v>
+        <v>13.36486053466797</v>
       </c>
       <c r="C722" t="n">
-        <v>13.85913867738389</v>
+        <v>13.85913768843952</v>
       </c>
       <c r="D722" t="n">
-        <v>13.24856113638068</v>
+        <v>13.24856019100519</v>
       </c>
       <c r="E722" t="n">
-        <v>13.71376254422711</v>
+        <v>13.71376156565631</v>
       </c>
       <c r="F722" t="n">
         <v>8302800</v>
@@ -14912,16 +14912,16 @@
         <v>45314</v>
       </c>
       <c r="B725" t="n">
-        <v>13.21948528289795</v>
+        <v>13.21948623657227</v>
       </c>
       <c r="C725" t="n">
-        <v>13.4811608240167</v>
+        <v>13.4811617965687</v>
       </c>
       <c r="D725" t="n">
-        <v>13.18071850183321</v>
+        <v>13.18071945271083</v>
       </c>
       <c r="E725" t="n">
-        <v>13.24856013762826</v>
+        <v>13.24856109340008</v>
       </c>
       <c r="F725" t="n">
         <v>9537600</v>
@@ -15072,16 +15072,16 @@
         <v>45324</v>
       </c>
       <c r="B733" t="n">
-        <v>13.10318565368652</v>
+        <v>13.10318660736084</v>
       </c>
       <c r="C733" t="n">
-        <v>13.28732764270956</v>
+        <v>13.28732860978607</v>
       </c>
       <c r="D733" t="n">
-        <v>12.85120110089878</v>
+        <v>12.85120203623319</v>
       </c>
       <c r="E733" t="n">
-        <v>13.11287665627604</v>
+        <v>13.11287761065569</v>
       </c>
       <c r="F733" t="n">
         <v>9537000</v>
@@ -15112,16 +15112,16 @@
         <v>45328</v>
       </c>
       <c r="B735" t="n">
-        <v>13.36486148834229</v>
+        <v>13.36486053466797</v>
       </c>
       <c r="C735" t="n">
-        <v>13.45208698338175</v>
+        <v>13.4520860234833</v>
       </c>
       <c r="D735" t="n">
-        <v>12.9675017214052</v>
+        <v>12.96750079608522</v>
       </c>
       <c r="E735" t="n">
-        <v>13.05472721644466</v>
+        <v>13.05472628490055</v>
       </c>
       <c r="F735" t="n">
         <v>13604000</v>
@@ -15152,16 +15152,16 @@
         <v>45330</v>
       </c>
       <c r="B737" t="n">
-        <v>13.40362739562988</v>
+        <v>13.4036283493042</v>
       </c>
       <c r="C737" t="n">
-        <v>13.60715322931881</v>
+        <v>13.60715419747408</v>
       </c>
       <c r="D737" t="n">
-        <v>13.22917641696138</v>
+        <v>13.22917735822343</v>
       </c>
       <c r="E737" t="n">
-        <v>13.37455254060946</v>
+        <v>13.37455349221508</v>
       </c>
       <c r="F737" t="n">
         <v>12424500</v>
@@ -15192,16 +15192,16 @@
         <v>45336</v>
       </c>
       <c r="B739" t="n">
-        <v>12.75428295135498</v>
+        <v>12.7542839050293</v>
       </c>
       <c r="C739" t="n">
-        <v>12.94811685615447</v>
+        <v>12.9481178243223</v>
       </c>
       <c r="D739" t="n">
-        <v>12.67674938943519</v>
+        <v>12.67675033731209</v>
       </c>
       <c r="E739" t="n">
-        <v>12.85120036589121</v>
+        <v>12.85120132681232</v>
       </c>
       <c r="F739" t="n">
         <v>7875600</v>
@@ -15212,16 +15212,16 @@
         <v>45337</v>
       </c>
       <c r="B740" t="n">
-        <v>12.97719383239746</v>
+        <v>12.97719287872314</v>
       </c>
       <c r="C740" t="n">
-        <v>13.18071968228313</v>
+        <v>13.180718713652</v>
       </c>
       <c r="D740" t="n">
-        <v>12.65736762890185</v>
+        <v>12.65736669873108</v>
       </c>
       <c r="E740" t="n">
-        <v>12.80274283984602</v>
+        <v>12.80274189899184</v>
       </c>
       <c r="F740" t="n">
         <v>6962800</v>
@@ -15232,16 +15232,16 @@
         <v>45338</v>
       </c>
       <c r="B741" t="n">
-        <v>13.18071937561035</v>
+        <v>13.18071842193604</v>
       </c>
       <c r="C741" t="n">
-        <v>13.30671072921826</v>
+        <v>13.306709766428</v>
       </c>
       <c r="D741" t="n">
-        <v>12.84150932560221</v>
+        <v>12.84150839647101</v>
       </c>
       <c r="E741" t="n">
-        <v>13.05472709772942</v>
+        <v>13.05472615317111</v>
       </c>
       <c r="F741" t="n">
         <v>4964600</v>
@@ -15312,16 +15312,16 @@
         <v>45344</v>
       </c>
       <c r="B745" t="n">
-        <v>14.37279891967773</v>
+        <v>14.37279796600342</v>
       </c>
       <c r="C745" t="n">
-        <v>14.61509155274617</v>
+        <v>14.61509058299508</v>
       </c>
       <c r="D745" t="n">
-        <v>13.95605529503265</v>
+        <v>13.95605436901041</v>
       </c>
       <c r="E745" t="n">
-        <v>13.95605529503265</v>
+        <v>13.95605436901041</v>
       </c>
       <c r="F745" t="n">
         <v>21828500</v>
@@ -15332,16 +15332,16 @@
         <v>45345</v>
       </c>
       <c r="B746" t="n">
-        <v>14.26618957519531</v>
+        <v>14.26619052886963</v>
       </c>
       <c r="C746" t="n">
-        <v>14.46002348431353</v>
+        <v>14.46002445094536</v>
       </c>
       <c r="D746" t="n">
-        <v>13.98513017590566</v>
+        <v>13.98513111079155</v>
       </c>
       <c r="E746" t="n">
-        <v>14.46002348431353</v>
+        <v>14.46002445094536</v>
       </c>
       <c r="F746" t="n">
         <v>7821200</v>
@@ -15352,16 +15352,16 @@
         <v>45348</v>
       </c>
       <c r="B747" t="n">
-        <v>14.15958118438721</v>
+        <v>14.15958023071289</v>
       </c>
       <c r="C747" t="n">
-        <v>14.44064060258168</v>
+        <v>14.44063962997748</v>
       </c>
       <c r="D747" t="n">
-        <v>14.13050632713207</v>
+        <v>14.130505375416</v>
       </c>
       <c r="E747" t="n">
-        <v>14.32434024928807</v>
+        <v>14.32433928451693</v>
       </c>
       <c r="F747" t="n">
         <v>6009200</v>
@@ -15372,16 +15372,16 @@
         <v>45349</v>
       </c>
       <c r="B748" t="n">
-        <v>14.25649833679199</v>
+        <v>14.25649738311768</v>
       </c>
       <c r="C748" t="n">
-        <v>14.36310676088445</v>
+        <v>14.36310580007867</v>
       </c>
       <c r="D748" t="n">
-        <v>14.08204734802885</v>
+        <v>14.08204640602426</v>
       </c>
       <c r="E748" t="n">
-        <v>14.26619026378395</v>
+        <v>14.2661893094613</v>
       </c>
       <c r="F748" t="n">
         <v>8891500</v>
@@ -15452,16 +15452,16 @@
         <v>45355</v>
       </c>
       <c r="B752" t="n">
-        <v>13.59746170043945</v>
+        <v>13.59746074676514</v>
       </c>
       <c r="C752" t="n">
-        <v>13.77191268420841</v>
+        <v>13.77191171829877</v>
       </c>
       <c r="D752" t="n">
-        <v>13.48116135268448</v>
+        <v>13.48116040716703</v>
       </c>
       <c r="E752" t="n">
-        <v>13.67499526560944</v>
+        <v>13.67499430649721</v>
       </c>
       <c r="F752" t="n">
         <v>6926800</v>
@@ -15472,16 +15472,16 @@
         <v>45356</v>
       </c>
       <c r="B753" t="n">
-        <v>14.02389717102051</v>
+        <v>14.02389621734619</v>
       </c>
       <c r="C753" t="n">
-        <v>14.1305055915887</v>
+        <v>14.13050463066464</v>
       </c>
       <c r="D753" t="n">
-        <v>13.58777063780318</v>
+        <v>13.587769713787</v>
       </c>
       <c r="E753" t="n">
-        <v>13.64592034928656</v>
+        <v>13.64591942131599</v>
       </c>
       <c r="F753" t="n">
         <v>16007800</v>
@@ -15492,16 +15492,16 @@
         <v>45357</v>
       </c>
       <c r="B754" t="n">
-        <v>13.97543811798096</v>
+        <v>13.97543907165527</v>
       </c>
       <c r="C754" t="n">
-        <v>14.3824897854385</v>
+        <v>14.38249076688974</v>
       </c>
       <c r="D754" t="n">
-        <v>13.91728748365575</v>
+        <v>13.9172884333619</v>
       </c>
       <c r="E754" t="n">
-        <v>14.0917384623584</v>
+        <v>14.09173942396897</v>
       </c>
       <c r="F754" t="n">
         <v>10982800</v>
@@ -15572,16 +15572,16 @@
         <v>45363</v>
       </c>
       <c r="B758" t="n">
-        <v>14.26618957519531</v>
+        <v>14.26619052886963</v>
       </c>
       <c r="C758" t="n">
-        <v>14.37279799414208</v>
+        <v>14.37279895494302</v>
       </c>
       <c r="D758" t="n">
-        <v>13.74283755843964</v>
+        <v>13.74283847712863</v>
       </c>
       <c r="E758" t="n">
-        <v>14.00451310468098</v>
+        <v>14.0045140408626</v>
       </c>
       <c r="F758" t="n">
         <v>5196700</v>
@@ -15632,16 +15632,16 @@
         <v>45366</v>
       </c>
       <c r="B761" t="n">
-        <v>14.17896366119385</v>
+        <v>14.17896461486816</v>
       </c>
       <c r="C761" t="n">
-        <v>14.19834658938979</v>
+        <v>14.1983475443678</v>
       </c>
       <c r="D761" t="n">
-        <v>13.89790427030547</v>
+        <v>13.89790520507579</v>
       </c>
       <c r="E761" t="n">
-        <v>14.0917381736297</v>
+        <v>14.09173912143725</v>
       </c>
       <c r="F761" t="n">
         <v>7761200</v>
@@ -15672,16 +15672,16 @@
         <v>45370</v>
       </c>
       <c r="B763" t="n">
-        <v>14.27588176727295</v>
+        <v>14.27588081359863</v>
       </c>
       <c r="C763" t="n">
-        <v>14.35341626165535</v>
+        <v>14.35341530280148</v>
       </c>
       <c r="D763" t="n">
-        <v>14.00451427189027</v>
+        <v>14.00451333634416</v>
       </c>
       <c r="E763" t="n">
-        <v>14.09173976933154</v>
+        <v>14.09173882795849</v>
       </c>
       <c r="F763" t="n">
         <v>3066400</v>
@@ -15712,16 +15712,16 @@
         <v>45372</v>
       </c>
       <c r="B765" t="n">
-        <v>14.36310768127441</v>
+        <v>14.3631067276001</v>
       </c>
       <c r="C765" t="n">
-        <v>14.47940803981137</v>
+        <v>14.47940707841501</v>
       </c>
       <c r="D765" t="n">
-        <v>14.19834860894545</v>
+        <v>14.19834766621072</v>
       </c>
       <c r="E765" t="n">
-        <v>14.46002510885842</v>
+        <v>14.46002414874904</v>
       </c>
       <c r="F765" t="n">
         <v>19402800</v>
@@ -15812,16 +15812,16 @@
         <v>45379</v>
       </c>
       <c r="B770" t="n">
-        <v>14.25649833679199</v>
+        <v>14.25649738311768</v>
       </c>
       <c r="C770" t="n">
-        <v>14.73139166812162</v>
+        <v>14.73139068267979</v>
       </c>
       <c r="D770" t="n">
-        <v>14.25649833679199</v>
+        <v>14.25649738311768</v>
       </c>
       <c r="E770" t="n">
-        <v>14.45033225526602</v>
+        <v>14.45033128862538</v>
       </c>
       <c r="F770" t="n">
         <v>7122000</v>
@@ -15852,16 +15852,16 @@
         <v>45384</v>
       </c>
       <c r="B772" t="n">
-        <v>13.58776950836182</v>
+        <v>13.58777046203613</v>
       </c>
       <c r="C772" t="n">
-        <v>13.859136962698</v>
+        <v>13.85913793541857</v>
       </c>
       <c r="D772" t="n">
-        <v>13.43270146732536</v>
+        <v>13.43270241011604</v>
       </c>
       <c r="E772" t="n">
-        <v>13.82037018350711</v>
+        <v>13.82037115350679</v>
       </c>
       <c r="F772" t="n">
         <v>14898200</v>
@@ -16112,16 +16112,16 @@
         <v>45401</v>
       </c>
       <c r="B785" t="n">
-        <v>12.96750164031982</v>
+        <v>12.96750068664551</v>
       </c>
       <c r="C785" t="n">
-        <v>13.20979426979305</v>
+        <v>13.20979329829971</v>
       </c>
       <c r="D785" t="n">
-        <v>12.77366772159585</v>
+        <v>12.77366678217674</v>
       </c>
       <c r="E785" t="n">
-        <v>12.80274257833619</v>
+        <v>12.80274163677882</v>
       </c>
       <c r="F785" t="n">
         <v>12837800</v>
@@ -16212,16 +16212,16 @@
         <v>45408</v>
       </c>
       <c r="B790" t="n">
-        <v>12.90935134887695</v>
+        <v>12.90935039520264</v>
       </c>
       <c r="C790" t="n">
-        <v>13.10318619707384</v>
+        <v>13.10318522908003</v>
       </c>
       <c r="D790" t="n">
-        <v>12.7736680642668</v>
+        <v>12.77366712061604</v>
       </c>
       <c r="E790" t="n">
-        <v>13.03534363049571</v>
+        <v>13.03534266751375</v>
       </c>
       <c r="F790" t="n">
         <v>14489900</v>
@@ -16232,16 +16232,16 @@
         <v>45411</v>
       </c>
       <c r="B791" t="n">
-        <v>13.1710262298584</v>
+        <v>13.17102718353271</v>
       </c>
       <c r="C791" t="n">
-        <v>13.21948493598589</v>
+        <v>13.21948589316895</v>
       </c>
       <c r="D791" t="n">
-        <v>12.89965876952657</v>
+        <v>12.89965970355199</v>
       </c>
       <c r="E791" t="n">
-        <v>12.98688333142852</v>
+        <v>12.98688427176961</v>
       </c>
       <c r="F791" t="n">
         <v>6604200</v>
@@ -16312,16 +16312,16 @@
         <v>45418</v>
       </c>
       <c r="B795" t="n">
-        <v>12.92873382568359</v>
+        <v>12.92873477935791</v>
       </c>
       <c r="C795" t="n">
-        <v>13.20979321649093</v>
+        <v>13.2097941908973</v>
       </c>
       <c r="D795" t="n">
-        <v>12.81243348372259</v>
+        <v>12.81243442881813</v>
       </c>
       <c r="E795" t="n">
-        <v>13.11287580272028</v>
+        <v>13.11287676997764</v>
       </c>
       <c r="F795" t="n">
         <v>7469100</v>
@@ -16352,16 +16352,16 @@
         <v>45420</v>
       </c>
       <c r="B797" t="n">
-        <v>13.10318565368652</v>
+        <v>13.10318660736084</v>
       </c>
       <c r="C797" t="n">
-        <v>13.2001021494928</v>
+        <v>13.20010311022088</v>
       </c>
       <c r="D797" t="n">
-        <v>12.97719337729265</v>
+        <v>12.97719432179701</v>
       </c>
       <c r="E797" t="n">
-        <v>13.00626823360723</v>
+        <v>13.00626918022772</v>
       </c>
       <c r="F797" t="n">
         <v>4964400</v>
@@ -16412,16 +16412,16 @@
         <v>45425</v>
       </c>
       <c r="B800" t="n">
-        <v>12.92873382568359</v>
+        <v>12.92873477935791</v>
       </c>
       <c r="C800" t="n">
-        <v>13.15164258337395</v>
+        <v>13.1516435534909</v>
       </c>
       <c r="D800" t="n">
-        <v>12.79304963125927</v>
+        <v>12.79305057492499</v>
       </c>
       <c r="E800" t="n">
-        <v>12.98688353452762</v>
+        <v>12.98688449249129</v>
       </c>
       <c r="F800" t="n">
         <v>6951300</v>
@@ -16432,16 +16432,16 @@
         <v>45426</v>
       </c>
       <c r="B801" t="n">
-        <v>12.75428295135498</v>
+        <v>12.7542839050293</v>
       </c>
       <c r="C801" t="n">
-        <v>12.9675007087709</v>
+        <v>12.96750167838812</v>
       </c>
       <c r="D801" t="n">
-        <v>12.66705746312697</v>
+        <v>12.66705841027919</v>
       </c>
       <c r="E801" t="n">
-        <v>12.84150843958299</v>
+        <v>12.84150939977941</v>
       </c>
       <c r="F801" t="n">
         <v>10701800</v>
@@ -16472,16 +16472,16 @@
         <v>45428</v>
       </c>
       <c r="B803" t="n">
-        <v>13.05472660064697</v>
+        <v>13.05472755432129</v>
       </c>
       <c r="C803" t="n">
-        <v>13.21948565588908</v>
+        <v>13.21948662159938</v>
       </c>
       <c r="D803" t="n">
-        <v>12.9481172565062</v>
+        <v>12.94811820239249</v>
       </c>
       <c r="E803" t="n">
-        <v>13.2001018026733</v>
+        <v>13.20010276696758</v>
       </c>
       <c r="F803" t="n">
         <v>4347100</v>
@@ -16492,16 +16492,16 @@
         <v>45429</v>
       </c>
       <c r="B804" t="n">
-        <v>13.20979404449463</v>
+        <v>13.20979309082031</v>
       </c>
       <c r="C804" t="n">
-        <v>13.2582527544174</v>
+        <v>13.25825179724463</v>
       </c>
       <c r="D804" t="n">
-        <v>12.97719334599296</v>
+        <v>12.97719240911113</v>
       </c>
       <c r="E804" t="n">
-        <v>12.99657627539826</v>
+        <v>12.99657533711709</v>
       </c>
       <c r="F804" t="n">
         <v>6205200</v>
@@ -16632,16 +16632,16 @@
         <v>45440</v>
       </c>
       <c r="B811" t="n">
-        <v>12.30846500396729</v>
+        <v>12.3084659576416</v>
       </c>
       <c r="C811" t="n">
-        <v>12.75428346510026</v>
+        <v>12.75428445331711</v>
       </c>
       <c r="D811" t="n">
-        <v>12.17278172727877</v>
+        <v>12.17278267044019</v>
       </c>
       <c r="E811" t="n">
-        <v>12.72520860927743</v>
+        <v>12.72520959524153</v>
       </c>
       <c r="F811" t="n">
         <v>7568500</v>
@@ -16712,16 +16712,16 @@
         <v>45447</v>
       </c>
       <c r="B815" t="n">
-        <v>11.7657299041748</v>
+        <v>11.76573085784912</v>
       </c>
       <c r="C815" t="n">
-        <v>11.98863866986729</v>
+        <v>11.98863964160954</v>
       </c>
       <c r="D815" t="n">
-        <v>11.68819634008411</v>
+        <v>11.68819728747393</v>
       </c>
       <c r="E815" t="n">
-        <v>11.86264639715167</v>
+        <v>11.86264735868158</v>
       </c>
       <c r="F815" t="n">
         <v>3975700</v>
@@ -16792,16 +16792,16 @@
         <v>45453</v>
       </c>
       <c r="B819" t="n">
-        <v>11.5622034072876</v>
+        <v>11.56220436096191</v>
       </c>
       <c r="C819" t="n">
-        <v>11.74634538042216</v>
+        <v>11.74634634928489</v>
       </c>
       <c r="D819" t="n">
-        <v>11.52343662745543</v>
+        <v>11.52343757793218</v>
       </c>
       <c r="E819" t="n">
-        <v>11.58158633506721</v>
+        <v>11.58158729034027</v>
       </c>
       <c r="F819" t="n">
         <v>12105900</v>
@@ -16872,16 +16872,16 @@
         <v>45457</v>
       </c>
       <c r="B823" t="n">
-        <v>11.30052757263184</v>
+        <v>11.30052852630615</v>
       </c>
       <c r="C823" t="n">
-        <v>11.40713691624688</v>
+        <v>11.40713787891818</v>
       </c>
       <c r="D823" t="n">
-        <v>11.05823495426744</v>
+        <v>11.05823588749419</v>
       </c>
       <c r="E823" t="n">
-        <v>11.09700173623482</v>
+        <v>11.09700267273318</v>
       </c>
       <c r="F823" t="n">
         <v>4784200</v>
@@ -16932,16 +16932,16 @@
         <v>45462</v>
       </c>
       <c r="B826" t="n">
-        <v>10.70933437347412</v>
+        <v>10.7093334197998</v>
       </c>
       <c r="C826" t="n">
-        <v>10.76748408676966</v>
+        <v>10.76748312791706</v>
       </c>
       <c r="D826" t="n">
-        <v>10.43796688812455</v>
+        <v>10.43796595861572</v>
       </c>
       <c r="E826" t="n">
-        <v>10.71902630044772</v>
+        <v>10.71902534591033</v>
       </c>
       <c r="F826" t="n">
         <v>8916100</v>
@@ -17012,16 +17012,16 @@
         <v>45468</v>
       </c>
       <c r="B830" t="n">
-        <v>10.55426692962646</v>
+        <v>10.55426788330078</v>
       </c>
       <c r="C830" t="n">
-        <v>10.85470926281736</v>
+        <v>10.85471024363938</v>
       </c>
       <c r="D830" t="n">
-        <v>10.52519114955792</v>
+        <v>10.52519210060498</v>
       </c>
       <c r="E830" t="n">
-        <v>10.68995020618764</v>
+        <v>10.68995117212218</v>
       </c>
       <c r="F830" t="n">
         <v>9834800</v>
@@ -17092,16 +17092,16 @@
         <v>45474</v>
       </c>
       <c r="B834" t="n">
-        <v>9.691704750061035</v>
+        <v>9.691705703735352</v>
       </c>
       <c r="C834" t="n">
-        <v>10.08906449692986</v>
+        <v>10.08906548970481</v>
       </c>
       <c r="D834" t="n">
-        <v>9.594787332851229</v>
+        <v>9.594788276988766</v>
       </c>
       <c r="E834" t="n">
-        <v>9.982456077417465</v>
+        <v>9.982457059702028</v>
       </c>
       <c r="F834" t="n">
         <v>19240000</v>
@@ -17172,16 +17172,16 @@
         <v>45478</v>
       </c>
       <c r="B838" t="n">
-        <v>11.09700202941895</v>
+        <v>11.09700107574463</v>
       </c>
       <c r="C838" t="n">
-        <v>11.18422752221831</v>
+        <v>11.18422656104786</v>
       </c>
       <c r="D838" t="n">
-        <v>10.66087548969511</v>
+        <v>10.66087457350143</v>
       </c>
       <c r="E838" t="n">
-        <v>10.73840905567833</v>
+        <v>10.73840813282142</v>
       </c>
       <c r="F838" t="n">
         <v>25549700</v>
@@ -17252,16 +17252,16 @@
         <v>45484</v>
       </c>
       <c r="B842" t="n">
-        <v>10.90316772460938</v>
+        <v>10.90316867828369</v>
       </c>
       <c r="C842" t="n">
-        <v>11.22299390392275</v>
+        <v>11.2229948855715</v>
       </c>
       <c r="D842" t="n">
-        <v>10.72871674524827</v>
+        <v>10.72871768366377</v>
       </c>
       <c r="E842" t="n">
-        <v>11.09700163263672</v>
+        <v>11.09700260326523</v>
       </c>
       <c r="F842" t="n">
         <v>13851900</v>
@@ -17292,16 +17292,16 @@
         <v>45488</v>
       </c>
       <c r="B844" t="n">
-        <v>10.78686714172363</v>
+        <v>10.78686809539795</v>
       </c>
       <c r="C844" t="n">
-        <v>10.91285941022897</v>
+        <v>10.91286037504235</v>
       </c>
       <c r="D844" t="n">
-        <v>10.76748328921222</v>
+        <v>10.76748424117279</v>
       </c>
       <c r="E844" t="n">
-        <v>10.87409262947909</v>
+        <v>10.87409359086507</v>
       </c>
       <c r="F844" t="n">
         <v>5840400</v>
@@ -17312,16 +17312,16 @@
         <v>45489</v>
       </c>
       <c r="B845" t="n">
-        <v>10.76748275756836</v>
+        <v>10.76748371124268</v>
       </c>
       <c r="C845" t="n">
-        <v>10.90316694563</v>
+        <v>10.90316791132185</v>
       </c>
       <c r="D845" t="n">
-        <v>10.69964112567399</v>
+        <v>10.69964207333959</v>
       </c>
       <c r="E845" t="n">
-        <v>10.76748275756836</v>
+        <v>10.76748371124268</v>
       </c>
       <c r="F845" t="n">
         <v>9437300</v>
@@ -17332,16 +17332,16 @@
         <v>45490</v>
       </c>
       <c r="B846" t="n">
-        <v>10.41858291625977</v>
+        <v>10.41858196258545</v>
       </c>
       <c r="C846" t="n">
-        <v>10.82563460181362</v>
+        <v>10.82563361087946</v>
       </c>
       <c r="D846" t="n">
-        <v>10.41858291625977</v>
+        <v>10.41858196258545</v>
       </c>
       <c r="E846" t="n">
-        <v>10.75779296231231</v>
+        <v>10.7577919775881</v>
       </c>
       <c r="F846" t="n">
         <v>8121300</v>
@@ -17432,16 +17432,16 @@
         <v>45497</v>
       </c>
       <c r="B851" t="n">
-        <v>9.691704750061035</v>
+        <v>9.691705703735352</v>
       </c>
       <c r="C851" t="n">
-        <v>10.26351547819831</v>
+        <v>10.26351648813943</v>
       </c>
       <c r="D851" t="n">
-        <v>9.691704750061035</v>
+        <v>9.691705703735352</v>
       </c>
       <c r="E851" t="n">
-        <v>10.09875642350544</v>
+        <v>10.09875741723408</v>
       </c>
       <c r="F851" t="n">
         <v>20101500</v>
@@ -17492,16 +17492,16 @@
         <v>45502</v>
       </c>
       <c r="B854" t="n">
-        <v>9.255578994750977</v>
+        <v>9.25557804107666</v>
       </c>
       <c r="C854" t="n">
-        <v>9.652938774831423</v>
+        <v>9.652937780214037</v>
       </c>
       <c r="D854" t="n">
-        <v>9.110202856785623</v>
+        <v>9.11020191809054</v>
       </c>
       <c r="E854" t="n">
-        <v>9.575405204292462</v>
+        <v>9.575404217663962</v>
       </c>
       <c r="F854" t="n">
         <v>14084800</v>
@@ -17512,16 +17512,16 @@
         <v>45503</v>
       </c>
       <c r="B855" t="n">
-        <v>9.148968696594238</v>
+        <v>9.148969650268555</v>
       </c>
       <c r="C855" t="n">
-        <v>9.439720018205433</v>
+        <v>9.439721002187216</v>
       </c>
       <c r="D855" t="n">
-        <v>9.139277694483143</v>
+        <v>9.139278647147284</v>
       </c>
       <c r="E855" t="n">
-        <v>9.207119330625666</v>
+        <v>9.207120290361514</v>
       </c>
       <c r="F855" t="n">
         <v>13878900</v>
@@ -17532,16 +17532,16 @@
         <v>45504</v>
       </c>
       <c r="B856" t="n">
-        <v>9.517252922058105</v>
+        <v>9.517253875732422</v>
       </c>
       <c r="C856" t="n">
-        <v>9.556019700638412</v>
+        <v>9.556020658197346</v>
       </c>
       <c r="D856" t="n">
-        <v>9.21681061912895</v>
+        <v>9.216811542697508</v>
       </c>
       <c r="E856" t="n">
-        <v>9.255577397709256</v>
+        <v>9.255578325162432</v>
       </c>
       <c r="F856" t="n">
         <v>17487100</v>
@@ -17572,16 +17572,16 @@
         <v>45506</v>
       </c>
       <c r="B858" t="n">
-        <v>9.885539054870605</v>
+        <v>9.885538101196289</v>
       </c>
       <c r="C858" t="n">
-        <v>9.953381619335163</v>
+        <v>9.953380659115961</v>
       </c>
       <c r="D858" t="n">
-        <v>9.58509671321695</v>
+        <v>9.585095788526804</v>
       </c>
       <c r="E858" t="n">
-        <v>9.604479642868947</v>
+        <v>9.604478716308897</v>
       </c>
       <c r="F858" t="n">
         <v>10117700</v>
@@ -17672,16 +17672,16 @@
         <v>45513</v>
       </c>
       <c r="B863" t="n">
-        <v>9.953381538391113</v>
+        <v>9.953380584716797</v>
       </c>
       <c r="C863" t="n">
-        <v>10.1375235278162</v>
+        <v>10.13752255649849</v>
       </c>
       <c r="D863" t="n">
-        <v>9.662630201791425</v>
+        <v>9.662629275975187</v>
       </c>
       <c r="E863" t="n">
-        <v>10.12783160093251</v>
+        <v>10.12783063054342</v>
       </c>
       <c r="F863" t="n">
         <v>24889300</v>
@@ -17752,16 +17752,16 @@
         <v>45519</v>
       </c>
       <c r="B867" t="n">
-        <v>10.07937240600586</v>
+        <v>10.07937335968018</v>
       </c>
       <c r="C867" t="n">
-        <v>10.30228209224458</v>
+        <v>10.30228306700982</v>
       </c>
       <c r="D867" t="n">
-        <v>9.933997206834544</v>
+        <v>9.933998146753977</v>
       </c>
       <c r="E867" t="n">
-        <v>10.30228209224458</v>
+        <v>10.30228306700982</v>
       </c>
       <c r="F867" t="n">
         <v>11390800</v>
@@ -17792,16 +17792,16 @@
         <v>45523</v>
       </c>
       <c r="B869" t="n">
-        <v>10.37981510162354</v>
+        <v>10.37981605529785</v>
       </c>
       <c r="C869" t="n">
-        <v>10.43796573275546</v>
+        <v>10.43796669177252</v>
       </c>
       <c r="D869" t="n">
-        <v>9.701396001206707</v>
+        <v>9.701396892549386</v>
       </c>
       <c r="E869" t="n">
-        <v>10.02122216174997</v>
+        <v>10.02122308247756</v>
       </c>
       <c r="F869" t="n">
         <v>15557600</v>
@@ -17852,16 +17852,16 @@
         <v>45526</v>
       </c>
       <c r="B872" t="n">
-        <v>9.449411392211914</v>
+        <v>9.44941234588623</v>
       </c>
       <c r="C872" t="n">
-        <v>9.691703992012219</v>
+        <v>9.691704970139725</v>
       </c>
       <c r="D872" t="n">
-        <v>9.34280298103803</v>
+        <v>9.342803923952978</v>
       </c>
       <c r="E872" t="n">
-        <v>9.546328801841204</v>
+        <v>9.546329765296832</v>
       </c>
       <c r="F872" t="n">
         <v>16152200</v>
@@ -18012,16 +18012,16 @@
         <v>45538</v>
       </c>
       <c r="B880" t="n">
-        <v>9.691704750061035</v>
+        <v>9.691705703735352</v>
       </c>
       <c r="C880" t="n">
-        <v>9.817697022724587</v>
+        <v>9.817697988796681</v>
       </c>
       <c r="D880" t="n">
-        <v>9.497870839914412</v>
+        <v>9.497871774515261</v>
       </c>
       <c r="E880" t="n">
-        <v>9.556020550821904</v>
+        <v>9.556021491144747</v>
       </c>
       <c r="F880" t="n">
         <v>16401400</v>
@@ -18112,16 +18112,16 @@
         <v>45545</v>
       </c>
       <c r="B885" t="n">
-        <v>8.625616073608398</v>
+        <v>8.625617027282715</v>
       </c>
       <c r="C885" t="n">
-        <v>8.896984447413983</v>
+        <v>8.896985431091611</v>
       </c>
       <c r="D885" t="n">
-        <v>8.52869958948318</v>
+        <v>8.528700532442116</v>
       </c>
       <c r="E885" t="n">
-        <v>8.896984447413983</v>
+        <v>8.896985431091611</v>
       </c>
       <c r="F885" t="n">
         <v>19808800</v>
@@ -18152,16 +18152,16 @@
         <v>45547</v>
       </c>
       <c r="B887" t="n">
-        <v>8.790376663208008</v>
+        <v>8.790375709533691</v>
       </c>
       <c r="C887" t="n">
-        <v>8.916368946630897</v>
+        <v>8.916367979287587</v>
       </c>
       <c r="D887" t="n">
-        <v>8.722535019931478</v>
+        <v>8.722534073617352</v>
       </c>
       <c r="E887" t="n">
-        <v>8.819452445417722</v>
+        <v>8.819451488588953</v>
       </c>
       <c r="F887" t="n">
         <v>11088400</v>
@@ -18212,16 +18212,16 @@
         <v>45552</v>
       </c>
       <c r="B890" t="n">
-        <v>8.548084259033203</v>
+        <v>8.548083305358887</v>
       </c>
       <c r="C890" t="n">
-        <v>8.606234900780036</v>
+        <v>8.606233940618093</v>
       </c>
       <c r="D890" t="n">
-        <v>8.402709041075765</v>
+        <v>8.402708103620357</v>
       </c>
       <c r="E890" t="n">
-        <v>8.480242613889478</v>
+        <v>8.480241667783972</v>
       </c>
       <c r="F890" t="n">
         <v>13563600</v>
@@ -18232,16 +18232,16 @@
         <v>45553</v>
       </c>
       <c r="B891" t="n">
-        <v>8.470549583435059</v>
+        <v>8.470550537109375</v>
       </c>
       <c r="C891" t="n">
-        <v>8.761300905769993</v>
+        <v>8.761301892179148</v>
       </c>
       <c r="D891" t="n">
-        <v>8.470549583435059</v>
+        <v>8.470550537109375</v>
       </c>
       <c r="E891" t="n">
-        <v>8.548083146154644</v>
+        <v>8.548084108558237</v>
       </c>
       <c r="F891" t="n">
         <v>22128100</v>
@@ -18252,16 +18252,16 @@
         <v>45554</v>
       </c>
       <c r="B892" t="n">
-        <v>7.985964775085449</v>
+        <v>7.985965251922607</v>
       </c>
       <c r="C892" t="n">
-        <v>8.567467450394972</v>
+        <v>8.567467961953305</v>
       </c>
       <c r="D892" t="n">
-        <v>7.985964775085449</v>
+        <v>7.985965251922607</v>
       </c>
       <c r="E892" t="n">
-        <v>8.538392593911404</v>
+        <v>8.538393103733693</v>
       </c>
       <c r="F892" t="n">
         <v>19129200</v>
@@ -18272,16 +18272,16 @@
         <v>45555</v>
       </c>
       <c r="B893" t="n">
-        <v>7.462612152099609</v>
+        <v>7.462612628936768</v>
       </c>
       <c r="C893" t="n">
-        <v>8.073189636035888</v>
+        <v>8.073190151887005</v>
       </c>
       <c r="D893" t="n">
-        <v>7.462612152099609</v>
+        <v>7.462612628936768</v>
       </c>
       <c r="E893" t="n">
-        <v>8.005348001467285</v>
+        <v>8.005348512983536</v>
       </c>
       <c r="F893" t="n">
         <v>27842200</v>
@@ -18292,16 +18292,16 @@
         <v>45558</v>
       </c>
       <c r="B894" t="n">
-        <v>7.617680549621582</v>
+        <v>7.617680072784424</v>
       </c>
       <c r="C894" t="n">
-        <v>7.675830726380644</v>
+        <v>7.675830245903511</v>
       </c>
       <c r="D894" t="n">
-        <v>7.433538092149622</v>
+        <v>7.433537626839064</v>
       </c>
       <c r="E894" t="n">
-        <v>7.44322955720787</v>
+        <v>7.443229091290664</v>
       </c>
       <c r="F894" t="n">
         <v>19916000</v>
@@ -18312,16 +18312,16 @@
         <v>45559</v>
       </c>
       <c r="B895" t="n">
-        <v>7.898739337921143</v>
+        <v>7.898738861083984</v>
       </c>
       <c r="C895" t="n">
-        <v>8.024731615949483</v>
+        <v>8.024731131506325</v>
       </c>
       <c r="D895" t="n">
-        <v>7.753364130189305</v>
+        <v>7.753363662128269</v>
       </c>
       <c r="E895" t="n">
-        <v>7.859972554241117</v>
+        <v>7.859972079744262</v>
       </c>
       <c r="F895" t="n">
         <v>22551600</v>
@@ -18352,16 +18352,16 @@
         <v>45561</v>
       </c>
       <c r="B897" t="n">
-        <v>7.801822662353516</v>
+        <v>7.801823139190674</v>
       </c>
       <c r="C897" t="n">
-        <v>7.8696643011731</v>
+        <v>7.869664782156651</v>
       </c>
       <c r="D897" t="n">
-        <v>7.54983811206219</v>
+        <v>7.549838573498384</v>
       </c>
       <c r="E897" t="n">
-        <v>7.559530038828704</v>
+        <v>7.559530500857256</v>
       </c>
       <c r="F897" t="n">
         <v>14720200</v>
@@ -18512,16 +18512,16 @@
         <v>45573</v>
       </c>
       <c r="B905" t="n">
-        <v>6.609742641448975</v>
+        <v>6.609743118286133</v>
       </c>
       <c r="C905" t="n">
-        <v>6.648509422513715</v>
+        <v>6.648509902147569</v>
       </c>
       <c r="D905" t="n">
-        <v>6.512825226650641</v>
+        <v>6.512825696496025</v>
       </c>
       <c r="E905" t="n">
-        <v>6.551592469851864</v>
+        <v>6.551592942493978</v>
       </c>
       <c r="F905" t="n">
         <v>17971800</v>
@@ -18592,16 +18592,16 @@
         <v>45579</v>
       </c>
       <c r="B909" t="n">
-        <v>6.919877529144287</v>
+        <v>6.919877052307129</v>
       </c>
       <c r="C909" t="n">
-        <v>6.997411098435412</v>
+        <v>6.997410616255546</v>
       </c>
       <c r="D909" t="n">
-        <v>6.64851003662535</v>
+        <v>6.648509578487669</v>
       </c>
       <c r="E909" t="n">
-        <v>6.813269102437253</v>
+        <v>6.813268632946302</v>
       </c>
       <c r="F909" t="n">
         <v>42118900</v>
@@ -18612,16 +18612,16 @@
         <v>45580</v>
       </c>
       <c r="B910" t="n">
-        <v>6.793884754180908</v>
+        <v>6.793885231018066</v>
       </c>
       <c r="C910" t="n">
-        <v>7.08463559811253</v>
+        <v>7.084636095356394</v>
       </c>
       <c r="D910" t="n">
-        <v>6.716350733662682</v>
+        <v>6.716351205058019</v>
       </c>
       <c r="E910" t="n">
-        <v>6.997410113864813</v>
+        <v>6.997410604986649</v>
       </c>
       <c r="F910" t="n">
         <v>30694500</v>
@@ -18792,16 +18792,16 @@
         <v>45593</v>
       </c>
       <c r="B919" t="n">
-        <v>7.191245079040527</v>
+        <v>7.191245555877686</v>
       </c>
       <c r="C919" t="n">
-        <v>7.375387526810755</v>
+        <v>7.375388015858033</v>
       </c>
       <c r="D919" t="n">
-        <v>7.084636196197448</v>
+        <v>7.084636665965583</v>
       </c>
       <c r="E919" t="n">
-        <v>7.084636196197448</v>
+        <v>7.084636665965583</v>
       </c>
       <c r="F919" t="n">
         <v>17455800</v>
@@ -18832,16 +18832,16 @@
         <v>45595</v>
       </c>
       <c r="B921" t="n">
-        <v>7.443229198455811</v>
+        <v>7.443228721618652</v>
       </c>
       <c r="C921" t="n">
-        <v>7.598296791142485</v>
+        <v>7.598296304371199</v>
       </c>
       <c r="D921" t="n">
-        <v>7.249395285268095</v>
+        <v>7.249394820848559</v>
       </c>
       <c r="E921" t="n">
-        <v>7.317237385952047</v>
+        <v>7.317236917186328</v>
       </c>
       <c r="F921" t="n">
         <v>17976200</v>
@@ -18912,16 +18912,16 @@
         <v>45601</v>
       </c>
       <c r="B925" t="n">
-        <v>7.443229198455811</v>
+        <v>7.443228721618652</v>
       </c>
       <c r="C925" t="n">
-        <v>7.569221473096077</v>
+        <v>7.569220988187449</v>
       </c>
       <c r="D925" t="n">
-        <v>7.191245111311781</v>
+        <v>7.191244650617532</v>
       </c>
       <c r="E925" t="n">
-        <v>7.472304516502219</v>
+        <v>7.472304037802402</v>
       </c>
       <c r="F925" t="n">
         <v>13215900</v>
@@ -18972,16 +18972,16 @@
         <v>45604</v>
       </c>
       <c r="B928" t="n">
-        <v>6.793884754180908</v>
+        <v>6.793885231018066</v>
       </c>
       <c r="C928" t="n">
-        <v>7.133094303169364</v>
+        <v>7.133094803814362</v>
       </c>
       <c r="D928" t="n">
-        <v>6.68727588033775</v>
+        <v>6.687276349692433</v>
       </c>
       <c r="E928" t="n">
-        <v>6.939259945078488</v>
+        <v>6.939260432118983</v>
       </c>
       <c r="F928" t="n">
         <v>34800800</v>
@@ -19012,16 +19012,16 @@
         <v>45608</v>
       </c>
       <c r="B930" t="n">
-        <v>6.987719058990479</v>
+        <v>6.987719535827637</v>
       </c>
       <c r="C930" t="n">
-        <v>7.055561157612231</v>
+        <v>7.055561639078888</v>
       </c>
       <c r="D930" t="n">
-        <v>6.784193225261708</v>
+        <v>6.784193688210403</v>
       </c>
       <c r="E930" t="n">
-        <v>6.861726788180004</v>
+        <v>6.861727256419536</v>
       </c>
       <c r="F930" t="n">
         <v>26167100</v>
@@ -19112,16 +19112,16 @@
         <v>45617</v>
       </c>
       <c r="B935" t="n">
-        <v>6.726043224334717</v>
+        <v>6.726043701171875</v>
       </c>
       <c r="C935" t="n">
-        <v>6.842343571673456</v>
+        <v>6.842344056755628</v>
       </c>
       <c r="D935" t="n">
-        <v>6.512825458743863</v>
+        <v>6.512825920465128</v>
       </c>
       <c r="E935" t="n">
-        <v>6.696967906431782</v>
+        <v>6.69696838120767</v>
       </c>
       <c r="F935" t="n">
         <v>32015400</v>
@@ -19132,16 +19132,16 @@
         <v>45618</v>
       </c>
       <c r="B936" t="n">
-        <v>6.978027820587158</v>
+        <v>6.97802734375</v>
       </c>
       <c r="C936" t="n">
-        <v>7.045869925898105</v>
+        <v>7.045869444425019</v>
       </c>
       <c r="D936" t="n">
-        <v>6.726043716257203</v>
+        <v>6.726043256639149</v>
       </c>
       <c r="E936" t="n">
-        <v>6.774501966790851</v>
+        <v>6.774501503861446</v>
       </c>
       <c r="F936" t="n">
         <v>20807700</v>
@@ -19192,16 +19192,16 @@
         <v>45623</v>
       </c>
       <c r="B939" t="n">
-        <v>7.181553840637207</v>
+        <v>7.181553363800049</v>
       </c>
       <c r="C939" t="n">
-        <v>7.801823343774085</v>
+        <v>7.801822825752589</v>
       </c>
       <c r="D939" t="n">
-        <v>7.133095588981745</v>
+        <v>7.133095115362094</v>
       </c>
       <c r="E939" t="n">
-        <v>7.675831057624106</v>
+        <v>7.675830547968181</v>
       </c>
       <c r="F939" t="n">
         <v>36141700</v>
@@ -19352,16 +19352,16 @@
         <v>45635</v>
       </c>
       <c r="B947" t="n">
-        <v>5.873172760009766</v>
+        <v>5.873173236846924</v>
       </c>
       <c r="C947" t="n">
-        <v>6.008856491034863</v>
+        <v>6.008856978888051</v>
       </c>
       <c r="D947" t="n">
-        <v>5.776255809277553</v>
+        <v>5.776256278246119</v>
       </c>
       <c r="E947" t="n">
-        <v>5.989473100888421</v>
+        <v>5.98947358716789</v>
       </c>
       <c r="F947" t="n">
         <v>18041800</v>
@@ -19392,16 +19392,16 @@
         <v>45637</v>
       </c>
       <c r="B949" t="n">
-        <v>6.270532608032227</v>
+        <v>6.270533084869385</v>
       </c>
       <c r="C949" t="n">
-        <v>6.638817489937481</v>
+        <v>6.63881799478054</v>
       </c>
       <c r="D949" t="n">
-        <v>5.98947321450887</v>
+        <v>5.989473669973113</v>
       </c>
       <c r="E949" t="n">
-        <v>6.231765827003935</v>
+        <v>6.231766300893107</v>
       </c>
       <c r="F949" t="n">
         <v>30797400</v>
@@ -19412,16 +19412,16 @@
         <v>45638</v>
       </c>
       <c r="B950" t="n">
-        <v>5.873172760009766</v>
+        <v>5.873173236846924</v>
       </c>
       <c r="C950" t="n">
-        <v>6.086390513757107</v>
+        <v>6.086391007905207</v>
       </c>
       <c r="D950" t="n">
-        <v>5.737489028984668</v>
+        <v>5.737489494805797</v>
       </c>
       <c r="E950" t="n">
-        <v>6.047623271327748</v>
+        <v>6.047623762328373</v>
       </c>
       <c r="F950" t="n">
         <v>28228300</v>
@@ -19472,16 +19472,16 @@
         <v>45643</v>
       </c>
       <c r="B953" t="n">
-        <v>5.340129852294922</v>
+        <v>5.340129375457764</v>
       </c>
       <c r="C953" t="n">
-        <v>5.398280028749276</v>
+        <v>5.398279546719705</v>
       </c>
       <c r="D953" t="n">
-        <v>5.146295468643883</v>
+        <v>5.146295009114813</v>
       </c>
       <c r="E953" t="n">
-        <v>5.243212429401142</v>
+        <v>5.243211961218048</v>
       </c>
       <c r="F953" t="n">
         <v>32812100</v>
@@ -19492,16 +19492,16 @@
         <v>45644</v>
       </c>
       <c r="B954" t="n">
-        <v>4.981535911560059</v>
+        <v>4.981536388397217</v>
       </c>
       <c r="C954" t="n">
-        <v>5.340129324097897</v>
+        <v>5.340129835259944</v>
       </c>
       <c r="D954" t="n">
-        <v>4.894310886574293</v>
+        <v>4.894311355062193</v>
       </c>
       <c r="E954" t="n">
-        <v>5.233520446741433</v>
+        <v>5.23352094769878</v>
       </c>
       <c r="F954" t="n">
         <v>36135800</v>
@@ -19532,16 +19532,16 @@
         <v>45646</v>
       </c>
       <c r="B956" t="n">
-        <v>5.592113494873047</v>
+        <v>5.592113971710205</v>
       </c>
       <c r="C956" t="n">
-        <v>5.659955592946704</v>
+        <v>5.659956075568729</v>
       </c>
       <c r="D956" t="n">
-        <v>5.165678440131098</v>
+        <v>5.165678880606319</v>
       </c>
       <c r="E956" t="n">
-        <v>5.223828611850025</v>
+        <v>5.223829057283687</v>
       </c>
       <c r="F956" t="n">
         <v>45865200</v>
@@ -19572,16 +19572,16 @@
         <v>45652</v>
       </c>
       <c r="B958" t="n">
-        <v>5.727797985076904</v>
+        <v>5.727797508239746</v>
       </c>
       <c r="C958" t="n">
-        <v>5.747181378208906</v>
+        <v>5.747180899758088</v>
       </c>
       <c r="D958" t="n">
-        <v>5.504888732990607</v>
+        <v>5.504888274710566</v>
       </c>
       <c r="E958" t="n">
-        <v>5.601806160787163</v>
+        <v>5.60180569443878</v>
       </c>
       <c r="F958" t="n">
         <v>25976300</v>
@@ -27432,19 +27432,39 @@
         <v>46230</v>
       </c>
       <c r="B1351" t="n">
-        <v>8.109999999999999</v>
+        <v>8.109999656677246</v>
       </c>
       <c r="C1351" t="n">
-        <v>8.140000000000001</v>
+        <v>8.140000343322754</v>
       </c>
       <c r="D1351" t="n">
-        <v>7.72</v>
+        <v>7.71999979019165</v>
       </c>
       <c r="E1351" t="n">
-        <v>7.91</v>
+        <v>7.909999847412109</v>
       </c>
       <c r="F1351" t="n">
         <v>9648500</v>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B1352" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="C1352" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="D1352" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="E1352" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="F1352" t="n">
+        <v>1019700</v>
       </c>
     </row>
   </sheetData>

--- a/database/ASAI3.xlsx
+++ b/database/ASAI3.xlsx
@@ -452,16 +452,16 @@
         <v>44256</v>
       </c>
       <c r="B2" t="n">
-        <v>13.55914783477783</v>
+        <v>13.55914878845215</v>
       </c>
       <c r="C2" t="n">
-        <v>14.43840408118833</v>
+        <v>14.43840509670459</v>
       </c>
       <c r="D2" t="n">
-        <v>13.17554232187502</v>
+        <v>13.17554324856868</v>
       </c>
       <c r="E2" t="n">
-        <v>13.67498995526467</v>
+        <v>13.67499091708668</v>
       </c>
       <c r="F2" t="n">
         <v>64088000</v>
@@ -472,16 +472,16 @@
         <v>44257</v>
       </c>
       <c r="B3" t="n">
-        <v>13.76804351806641</v>
+        <v>13.76804256439209</v>
       </c>
       <c r="C3" t="n">
-        <v>14.0528997719606</v>
+        <v>14.05289879855508</v>
       </c>
       <c r="D3" t="n">
-        <v>13.00462933717113</v>
+        <v>13.0046284363764</v>
       </c>
       <c r="E3" t="n">
-        <v>13.37114384656537</v>
+        <v>13.3711429203832</v>
       </c>
       <c r="F3" t="n">
         <v>14717000</v>
@@ -552,16 +552,16 @@
         <v>44263</v>
       </c>
       <c r="B7" t="n">
-        <v>13.48508644104004</v>
+        <v>13.48508548736572</v>
       </c>
       <c r="C7" t="n">
-        <v>14.2978757345337</v>
+        <v>14.29787472337838</v>
       </c>
       <c r="D7" t="n">
-        <v>13.05210579563423</v>
+        <v>13.05210487258059</v>
       </c>
       <c r="E7" t="n">
-        <v>14.21051986319279</v>
+        <v>14.21051885821534</v>
       </c>
       <c r="F7" t="n">
         <v>12366000</v>
@@ -572,16 +572,16 @@
         <v>44264</v>
       </c>
       <c r="B8" t="n">
-        <v>13.44520568847656</v>
+        <v>13.4452075958252</v>
       </c>
       <c r="C8" t="n">
-        <v>13.44520568847656</v>
+        <v>13.4452075958252</v>
       </c>
       <c r="D8" t="n">
-        <v>13.0103252694391</v>
+        <v>13.01032711509522</v>
       </c>
       <c r="E8" t="n">
-        <v>13.29138370087542</v>
+        <v>13.29138558640273</v>
       </c>
       <c r="F8" t="n">
         <v>10167000</v>
@@ -592,16 +592,16 @@
         <v>44265</v>
       </c>
       <c r="B9" t="n">
-        <v>13.48318576812744</v>
+        <v>13.48318672180176</v>
       </c>
       <c r="C9" t="n">
-        <v>13.95794583676244</v>
+        <v>13.95794682401684</v>
       </c>
       <c r="D9" t="n">
-        <v>13.23631031510933</v>
+        <v>13.23631125132199</v>
       </c>
       <c r="E9" t="n">
-        <v>13.48508467076097</v>
+        <v>13.4850856245696</v>
       </c>
       <c r="F9" t="n">
         <v>15699500</v>
@@ -652,16 +652,16 @@
         <v>44270</v>
       </c>
       <c r="B12" t="n">
-        <v>13.83450984954834</v>
+        <v>13.83450889587402</v>
       </c>
       <c r="C12" t="n">
-        <v>14.01681810828169</v>
+        <v>14.01681714204006</v>
       </c>
       <c r="D12" t="n">
-        <v>13.62181733379263</v>
+        <v>13.62181639478016</v>
       </c>
       <c r="E12" t="n">
-        <v>13.81931772103716</v>
+        <v>13.81931676841011</v>
       </c>
       <c r="F12" t="n">
         <v>11593000</v>
@@ -692,16 +692,16 @@
         <v>44272</v>
       </c>
       <c r="B14" t="n">
-        <v>14.05290126800537</v>
+        <v>14.05289840698242</v>
       </c>
       <c r="C14" t="n">
-        <v>14.07189120400231</v>
+        <v>14.07188833911321</v>
       </c>
       <c r="D14" t="n">
-        <v>13.49458302337791</v>
+        <v>13.49458027602269</v>
       </c>
       <c r="E14" t="n">
-        <v>13.58763651691574</v>
+        <v>13.5876337506158</v>
       </c>
       <c r="F14" t="n">
         <v>4753000</v>
@@ -712,16 +712,16 @@
         <v>44273</v>
       </c>
       <c r="B15" t="n">
-        <v>13.9104700088501</v>
+        <v>13.91047096252441</v>
       </c>
       <c r="C15" t="n">
-        <v>14.01301890351174</v>
+        <v>14.0130198642166</v>
       </c>
       <c r="D15" t="n">
-        <v>13.69018190359837</v>
+        <v>13.69018284217017</v>
       </c>
       <c r="E15" t="n">
-        <v>13.69018190359837</v>
+        <v>13.69018284217017</v>
       </c>
       <c r="F15" t="n">
         <v>2304000</v>
@@ -752,16 +752,16 @@
         <v>44277</v>
       </c>
       <c r="B17" t="n">
-        <v>13.2932825088501</v>
+        <v>13.29328441619873</v>
       </c>
       <c r="C17" t="n">
-        <v>13.6351094473715</v>
+        <v>13.6351114037662</v>
       </c>
       <c r="D17" t="n">
-        <v>13.15655155233494</v>
+        <v>13.15655344006512</v>
       </c>
       <c r="E17" t="n">
-        <v>13.6351094473715</v>
+        <v>13.6351114037662</v>
       </c>
       <c r="F17" t="n">
         <v>5803000</v>
@@ -772,16 +772,16 @@
         <v>44278</v>
       </c>
       <c r="B18" t="n">
-        <v>13.44141006469727</v>
+        <v>13.44140911102295</v>
       </c>
       <c r="C18" t="n">
-        <v>13.44141006469727</v>
+        <v>13.44140911102295</v>
       </c>
       <c r="D18" t="n">
-        <v>13.01982280188124</v>
+        <v>13.01982187811874</v>
       </c>
       <c r="E18" t="n">
-        <v>13.2932847612466</v>
+        <v>13.29328381808184</v>
       </c>
       <c r="F18" t="n">
         <v>7916000</v>
@@ -792,16 +792,16 @@
         <v>44279</v>
       </c>
       <c r="B19" t="n">
-        <v>13.00842761993408</v>
+        <v>13.00842571258545</v>
       </c>
       <c r="C19" t="n">
-        <v>13.4717934356419</v>
+        <v>13.47179146035269</v>
       </c>
       <c r="D19" t="n">
-        <v>12.86599994053009</v>
+        <v>12.86599805406478</v>
       </c>
       <c r="E19" t="n">
-        <v>13.31417362739389</v>
+        <v>13.31417167521553</v>
       </c>
       <c r="F19" t="n">
         <v>12174500</v>
@@ -832,16 +832,16 @@
         <v>44281</v>
       </c>
       <c r="B21" t="n">
-        <v>13.80602359771729</v>
+        <v>13.8060245513916</v>
       </c>
       <c r="C21" t="n">
-        <v>14.12696170612194</v>
+        <v>14.1269626819656</v>
       </c>
       <c r="D21" t="n">
-        <v>13.48888420034324</v>
+        <v>13.48888513211062</v>
       </c>
       <c r="E21" t="n">
-        <v>13.54965361596974</v>
+        <v>13.54965455193487</v>
       </c>
       <c r="F21" t="n">
         <v>4396500</v>
@@ -852,16 +852,16 @@
         <v>44284</v>
       </c>
       <c r="B22" t="n">
-        <v>13.95794677734375</v>
+        <v>13.95794773101807</v>
       </c>
       <c r="C22" t="n">
-        <v>13.95794677734375</v>
+        <v>13.95794773101807</v>
       </c>
       <c r="D22" t="n">
-        <v>13.4869853877722</v>
+        <v>13.48698630926816</v>
       </c>
       <c r="E22" t="n">
-        <v>13.7148700187455</v>
+        <v>13.71487095581164</v>
       </c>
       <c r="F22" t="n">
         <v>6557000</v>
@@ -872,16 +872,16 @@
         <v>44285</v>
       </c>
       <c r="B23" t="n">
-        <v>13.95794677734375</v>
+        <v>13.95794773101807</v>
       </c>
       <c r="C23" t="n">
-        <v>14.08138451217088</v>
+        <v>14.08138547427906</v>
       </c>
       <c r="D23" t="n">
-        <v>13.76804291819933</v>
+        <v>13.7680438588985</v>
       </c>
       <c r="E23" t="n">
-        <v>13.76804291819933</v>
+        <v>13.7680438588985</v>
       </c>
       <c r="F23" t="n">
         <v>8433000</v>
@@ -912,16 +912,16 @@
         <v>44287</v>
       </c>
       <c r="B25" t="n">
-        <v>14.25419807434082</v>
+        <v>14.2541971206665</v>
       </c>
       <c r="C25" t="n">
-        <v>14.40232336375477</v>
+        <v>14.40232240017016</v>
       </c>
       <c r="D25" t="n">
-        <v>14.02631343164232</v>
+        <v>14.02631249321458</v>
       </c>
       <c r="E25" t="n">
-        <v>14.09088065652025</v>
+        <v>14.09087971377266</v>
       </c>
       <c r="F25" t="n">
         <v>9940000</v>
@@ -952,16 +952,16 @@
         <v>44292</v>
       </c>
       <c r="B27" t="n">
-        <v>14.58652973175049</v>
+        <v>14.5865306854248</v>
       </c>
       <c r="C27" t="n">
-        <v>14.72136088275989</v>
+        <v>14.72136184524953</v>
       </c>
       <c r="D27" t="n">
-        <v>14.52765921864798</v>
+        <v>14.52766016847332</v>
       </c>
       <c r="E27" t="n">
-        <v>14.7175630772478</v>
+        <v>14.71756403948914</v>
       </c>
       <c r="F27" t="n">
         <v>5821500</v>
@@ -972,16 +972,16 @@
         <v>44293</v>
       </c>
       <c r="B28" t="n">
-        <v>14.49347686767578</v>
+        <v>14.49347496032715</v>
       </c>
       <c r="C28" t="n">
-        <v>14.78023202327058</v>
+        <v>14.78023007818483</v>
       </c>
       <c r="D28" t="n">
-        <v>13.92756307336586</v>
+        <v>13.92756124049176</v>
       </c>
       <c r="E28" t="n">
-        <v>14.45359719150692</v>
+        <v>14.45359528940647</v>
       </c>
       <c r="F28" t="n">
         <v>10992000</v>
@@ -992,16 +992,16 @@
         <v>44294</v>
       </c>
       <c r="B29" t="n">
-        <v>14.70237159729004</v>
+        <v>14.70237255096436</v>
       </c>
       <c r="C29" t="n">
-        <v>14.74035237068301</v>
+        <v>14.74035332682097</v>
       </c>
       <c r="D29" t="n">
-        <v>14.26559225050429</v>
+        <v>14.26559317584676</v>
       </c>
       <c r="E29" t="n">
-        <v>14.43270747232676</v>
+        <v>14.43270840850923</v>
       </c>
       <c r="F29" t="n">
         <v>6395000</v>
@@ -1052,16 +1052,16 @@
         <v>44299</v>
       </c>
       <c r="B32" t="n">
-        <v>14.67008781433105</v>
+        <v>14.67008590698242</v>
       </c>
       <c r="C32" t="n">
-        <v>14.81251639644156</v>
+        <v>14.81251447057491</v>
       </c>
       <c r="D32" t="n">
-        <v>14.52766013775363</v>
+        <v>14.5276582489229</v>
       </c>
       <c r="E32" t="n">
-        <v>14.69667426566374</v>
+        <v>14.69667235485844</v>
       </c>
       <c r="F32" t="n">
         <v>5449500</v>
@@ -1092,16 +1092,16 @@
         <v>44301</v>
       </c>
       <c r="B34" t="n">
-        <v>15.18662738800049</v>
+        <v>15.18662548065186</v>
       </c>
       <c r="C34" t="n">
-        <v>15.20371751383992</v>
+        <v>15.20371560434488</v>
       </c>
       <c r="D34" t="n">
-        <v>14.84100171054341</v>
+        <v>14.84099984660328</v>
       </c>
       <c r="E34" t="n">
-        <v>14.84100171054341</v>
+        <v>14.84099984660328</v>
       </c>
       <c r="F34" t="n">
         <v>11554500</v>
@@ -1112,16 +1112,16 @@
         <v>44302</v>
       </c>
       <c r="B35" t="n">
-        <v>15.14484786987305</v>
+        <v>15.14484691619873</v>
       </c>
       <c r="C35" t="n">
-        <v>15.72785270454275</v>
+        <v>15.7278517141565</v>
       </c>
       <c r="D35" t="n">
-        <v>15.00052129112236</v>
+        <v>15.00052034653632</v>
       </c>
       <c r="E35" t="n">
-        <v>15.72785270454275</v>
+        <v>15.7278517141565</v>
       </c>
       <c r="F35" t="n">
         <v>13035000</v>
@@ -1132,16 +1132,16 @@
         <v>44305</v>
       </c>
       <c r="B36" t="n">
-        <v>15.28727531433105</v>
+        <v>15.28727626800537</v>
       </c>
       <c r="C36" t="n">
-        <v>15.50756433010704</v>
+        <v>15.50756529752376</v>
       </c>
       <c r="D36" t="n">
-        <v>15.00431798094175</v>
+        <v>15.00431891696419</v>
       </c>
       <c r="E36" t="n">
-        <v>15.14484674350704</v>
+        <v>15.14484768829616</v>
       </c>
       <c r="F36" t="n">
         <v>5017000</v>
@@ -1152,16 +1152,16 @@
         <v>44306</v>
       </c>
       <c r="B37" t="n">
-        <v>15.47717952728271</v>
+        <v>15.4771785736084</v>
       </c>
       <c r="C37" t="n">
-        <v>15.65569088659348</v>
+        <v>15.65568992191963</v>
       </c>
       <c r="D37" t="n">
-        <v>15.06698752800291</v>
+        <v>15.06698659960384</v>
       </c>
       <c r="E37" t="n">
-        <v>15.35944030441754</v>
+        <v>15.35943935799809</v>
       </c>
       <c r="F37" t="n">
         <v>6029000</v>
@@ -1172,16 +1172,16 @@
         <v>44308</v>
       </c>
       <c r="B38" t="n">
-        <v>15.27967929840088</v>
+        <v>15.27967834472656</v>
       </c>
       <c r="C38" t="n">
-        <v>15.75254143640172</v>
+        <v>15.75254045321392</v>
       </c>
       <c r="D38" t="n">
-        <v>15.1942241402155</v>
+        <v>15.19422319187483</v>
       </c>
       <c r="E38" t="n">
-        <v>15.50376614024878</v>
+        <v>15.50376517258819</v>
       </c>
       <c r="F38" t="n">
         <v>8470500</v>
@@ -1192,16 +1192,16 @@
         <v>44309</v>
       </c>
       <c r="B39" t="n">
-        <v>15.41261291503906</v>
+        <v>15.41261196136475</v>
       </c>
       <c r="C39" t="n">
-        <v>15.53794955811708</v>
+        <v>15.53794859668741</v>
       </c>
       <c r="D39" t="n">
-        <v>15.218910336355</v>
+        <v>15.21890939466627</v>
       </c>
       <c r="E39" t="n">
-        <v>15.45819020544309</v>
+        <v>15.45818924894863</v>
       </c>
       <c r="F39" t="n">
         <v>4653000</v>
@@ -1232,16 +1232,16 @@
         <v>44313</v>
       </c>
       <c r="B41" t="n">
-        <v>15.12775611877441</v>
+        <v>15.12775802612305</v>
       </c>
       <c r="C41" t="n">
-        <v>15.29677114335289</v>
+        <v>15.2967730720114</v>
       </c>
       <c r="D41" t="n">
-        <v>15.10116966883617</v>
+        <v>15.10117157283271</v>
       </c>
       <c r="E41" t="n">
-        <v>15.24929404627311</v>
+        <v>15.24929596894558</v>
       </c>
       <c r="F41" t="n">
         <v>4986500</v>
@@ -1272,16 +1272,16 @@
         <v>44315</v>
       </c>
       <c r="B43" t="n">
-        <v>15.21646404266357</v>
+        <v>15.21646499633789</v>
       </c>
       <c r="C43" t="n">
-        <v>15.32323240215915</v>
+        <v>15.32323336252505</v>
       </c>
       <c r="D43" t="n">
-        <v>14.90950409998268</v>
+        <v>14.90950503441863</v>
       </c>
       <c r="E43" t="n">
-        <v>15.26222243052232</v>
+        <v>15.26222338706449</v>
       </c>
       <c r="F43" t="n">
         <v>5343000</v>
@@ -1332,16 +1332,16 @@
         <v>44320</v>
       </c>
       <c r="B46" t="n">
-        <v>15.72933769226074</v>
+        <v>15.72933673858643</v>
       </c>
       <c r="C46" t="n">
-        <v>15.74840399251314</v>
+        <v>15.74840303768283</v>
       </c>
       <c r="D46" t="n">
-        <v>15.35945946771906</v>
+        <v>15.35945853647056</v>
       </c>
       <c r="E46" t="n">
-        <v>15.63400800926121</v>
+        <v>15.63400706136676</v>
       </c>
       <c r="F46" t="n">
         <v>9407500</v>
@@ -1352,16 +1352,16 @@
         <v>44321</v>
       </c>
       <c r="B47" t="n">
-        <v>16.32228660583496</v>
+        <v>16.32228469848633</v>
       </c>
       <c r="C47" t="n">
-        <v>16.58730201015107</v>
+        <v>16.58730007183393</v>
       </c>
       <c r="D47" t="n">
-        <v>16.01532570257429</v>
+        <v>16.01532383109572</v>
       </c>
       <c r="E47" t="n">
-        <v>16.08396329586652</v>
+        <v>16.08396141636727</v>
       </c>
       <c r="F47" t="n">
         <v>17262500</v>
@@ -1412,16 +1412,16 @@
         <v>44326</v>
       </c>
       <c r="B50" t="n">
-        <v>16.81418609619141</v>
+        <v>16.81418418884277</v>
       </c>
       <c r="C50" t="n">
-        <v>17.0162841548014</v>
+        <v>17.01628222452739</v>
       </c>
       <c r="D50" t="n">
-        <v>16.55298359675715</v>
+        <v>16.55298171903851</v>
       </c>
       <c r="E50" t="n">
-        <v>16.97052576072697</v>
+        <v>16.97052383564365</v>
       </c>
       <c r="F50" t="n">
         <v>7669500</v>
@@ -1432,16 +1432,16 @@
         <v>44327</v>
       </c>
       <c r="B51" t="n">
-        <v>16.5872974395752</v>
+        <v>16.58729934692383</v>
       </c>
       <c r="C51" t="n">
-        <v>16.78367701474988</v>
+        <v>16.78367894467991</v>
       </c>
       <c r="D51" t="n">
-        <v>16.49196777820309</v>
+        <v>16.4919696745899</v>
       </c>
       <c r="E51" t="n">
-        <v>16.62543003142886</v>
+        <v>16.6254319431623</v>
       </c>
       <c r="F51" t="n">
         <v>6191000</v>
@@ -1472,16 +1472,16 @@
         <v>44329</v>
       </c>
       <c r="B53" t="n">
-        <v>16.43286514282227</v>
+        <v>16.4328670501709</v>
       </c>
       <c r="C53" t="n">
-        <v>16.51865983782675</v>
+        <v>16.5186617551335</v>
       </c>
       <c r="D53" t="n">
-        <v>16.12780986328454</v>
+        <v>16.12781173522566</v>
       </c>
       <c r="E53" t="n">
-        <v>16.17547560302264</v>
+        <v>16.17547748049629</v>
       </c>
       <c r="F53" t="n">
         <v>6595000</v>
@@ -1492,16 +1492,16 @@
         <v>44330</v>
       </c>
       <c r="B54" t="n">
-        <v>16.52629089355469</v>
+        <v>16.52628898620605</v>
       </c>
       <c r="C54" t="n">
-        <v>16.66356425245107</v>
+        <v>16.66356232925931</v>
       </c>
       <c r="D54" t="n">
-        <v>16.13734637653381</v>
+        <v>16.13734451407442</v>
       </c>
       <c r="E54" t="n">
-        <v>16.54726273245572</v>
+        <v>16.54726082268666</v>
       </c>
       <c r="F54" t="n">
         <v>5923000</v>
@@ -1512,16 +1512,16 @@
         <v>44333</v>
       </c>
       <c r="B55" t="n">
-        <v>16.34707260131836</v>
+        <v>16.34707069396973</v>
       </c>
       <c r="C55" t="n">
-        <v>16.52819700154386</v>
+        <v>16.52819507306194</v>
       </c>
       <c r="D55" t="n">
-        <v>16.06108354819061</v>
+        <v>16.06108167421069</v>
       </c>
       <c r="E55" t="n">
-        <v>16.50531780456314</v>
+        <v>16.50531587875072</v>
       </c>
       <c r="F55" t="n">
         <v>4728000</v>
@@ -1592,16 +1592,16 @@
         <v>44337</v>
       </c>
       <c r="B59" t="n">
-        <v>16.43477439880371</v>
+        <v>16.43477249145508</v>
       </c>
       <c r="C59" t="n">
-        <v>16.6254337643569</v>
+        <v>16.62543183488117</v>
       </c>
       <c r="D59" t="n">
-        <v>15.75984264485187</v>
+        <v>15.75984081583289</v>
       </c>
       <c r="E59" t="n">
-        <v>16.03439118575198</v>
+        <v>16.03438932487009</v>
       </c>
       <c r="F59" t="n">
         <v>10145000</v>
@@ -1612,16 +1612,16 @@
         <v>44340</v>
       </c>
       <c r="B60" t="n">
-        <v>17.00865364074707</v>
+        <v>17.00865745544434</v>
       </c>
       <c r="C60" t="n">
-        <v>17.06203963689752</v>
+        <v>17.06204346356818</v>
       </c>
       <c r="D60" t="n">
-        <v>16.39664113380684</v>
+        <v>16.39664481124207</v>
       </c>
       <c r="E60" t="n">
-        <v>16.5415402659626</v>
+        <v>16.54154397589578</v>
       </c>
       <c r="F60" t="n">
         <v>10386000</v>
@@ -1692,16 +1692,16 @@
         <v>44344</v>
       </c>
       <c r="B64" t="n">
-        <v>16.98577499389648</v>
+        <v>16.98577690124512</v>
       </c>
       <c r="C64" t="n">
-        <v>17.14974041109441</v>
+        <v>17.14974233685488</v>
       </c>
       <c r="D64" t="n">
-        <v>16.564418218668</v>
+        <v>16.56442007870208</v>
       </c>
       <c r="E64" t="n">
-        <v>16.91141716721885</v>
+        <v>16.91141906621777</v>
       </c>
       <c r="F64" t="n">
         <v>4590500</v>
@@ -1712,16 +1712,16 @@
         <v>44347</v>
       </c>
       <c r="B65" t="n">
-        <v>17.05441093444824</v>
+        <v>17.05441474914551</v>
       </c>
       <c r="C65" t="n">
-        <v>17.2546034069664</v>
+        <v>17.25460726644232</v>
       </c>
       <c r="D65" t="n">
-        <v>16.87137921937667</v>
+        <v>16.87138299313376</v>
       </c>
       <c r="E65" t="n">
-        <v>17.09254352664678</v>
+        <v>17.09254734987347</v>
       </c>
       <c r="F65" t="n">
         <v>4641000</v>
@@ -1732,16 +1732,16 @@
         <v>44348</v>
       </c>
       <c r="B66" t="n">
-        <v>16.96861839294434</v>
+        <v>16.96861457824707</v>
       </c>
       <c r="C66" t="n">
-        <v>17.41094711104222</v>
+        <v>17.4109431969055</v>
       </c>
       <c r="D66" t="n">
-        <v>16.82562477524642</v>
+        <v>16.8256209926954</v>
       </c>
       <c r="E66" t="n">
-        <v>17.17834406261295</v>
+        <v>17.17834020076747</v>
       </c>
       <c r="F66" t="n">
         <v>13722000</v>
@@ -1812,16 +1812,16 @@
         <v>44355</v>
       </c>
       <c r="B70" t="n">
-        <v>16.08205604553223</v>
+        <v>16.08205795288086</v>
       </c>
       <c r="C70" t="n">
-        <v>16.61017944054762</v>
+        <v>16.61018141053224</v>
       </c>
       <c r="D70" t="n">
-        <v>15.92952747058032</v>
+        <v>15.9295293598389</v>
       </c>
       <c r="E70" t="n">
-        <v>16.60064629097173</v>
+        <v>16.60064825982571</v>
       </c>
       <c r="F70" t="n">
         <v>9246000</v>
@@ -1832,16 +1832,16 @@
         <v>44356</v>
       </c>
       <c r="B71" t="n">
-        <v>16.16403961181641</v>
+        <v>16.16403770446777</v>
       </c>
       <c r="C71" t="n">
-        <v>16.39664448651429</v>
+        <v>16.39664255171839</v>
       </c>
       <c r="D71" t="n">
-        <v>15.82466817777308</v>
+        <v>15.82466631047011</v>
       </c>
       <c r="E71" t="n">
-        <v>16.08205778944601</v>
+        <v>16.08205589177119</v>
       </c>
       <c r="F71" t="n">
         <v>10294500</v>
@@ -1852,16 +1852,16 @@
         <v>44357</v>
       </c>
       <c r="B72" t="n">
-        <v>16.30322074890137</v>
+        <v>16.30321884155273</v>
       </c>
       <c r="C72" t="n">
-        <v>16.34707360646395</v>
+        <v>16.34707169398488</v>
       </c>
       <c r="D72" t="n">
-        <v>15.97719535383889</v>
+        <v>15.97719348463267</v>
       </c>
       <c r="E72" t="n">
-        <v>16.15641422598889</v>
+        <v>16.15641233581547</v>
       </c>
       <c r="F72" t="n">
         <v>4720000</v>
@@ -1872,16 +1872,16 @@
         <v>44358</v>
       </c>
       <c r="B73" t="n">
-        <v>16.07061576843262</v>
+        <v>16.07061386108398</v>
       </c>
       <c r="C73" t="n">
-        <v>16.30512616021678</v>
+        <v>16.30512422503518</v>
       </c>
       <c r="D73" t="n">
-        <v>15.87423797549705</v>
+        <v>15.8742360914556</v>
       </c>
       <c r="E73" t="n">
-        <v>16.3032188029694</v>
+        <v>16.30321686801416</v>
       </c>
       <c r="F73" t="n">
         <v>5133000</v>
@@ -1912,16 +1912,16 @@
         <v>44362</v>
       </c>
       <c r="B75" t="n">
-        <v>15.85898303985596</v>
+        <v>15.85898399353027</v>
       </c>
       <c r="C75" t="n">
-        <v>16.02676318570492</v>
+        <v>16.02676414946864</v>
       </c>
       <c r="D75" t="n">
-        <v>15.48719932831946</v>
+        <v>15.4872002596367</v>
       </c>
       <c r="E75" t="n">
-        <v>16.01532267985088</v>
+        <v>16.01532364292663</v>
       </c>
       <c r="F75" t="n">
         <v>8432500</v>
@@ -1952,16 +1952,16 @@
         <v>44364</v>
       </c>
       <c r="B77" t="n">
-        <v>15.97719478607178</v>
+        <v>15.97719287872314</v>
       </c>
       <c r="C77" t="n">
-        <v>16.00769977675023</v>
+        <v>16.00769786575993</v>
       </c>
       <c r="D77" t="n">
-        <v>15.69120572552212</v>
+        <v>15.6912038523147</v>
       </c>
       <c r="E77" t="n">
-        <v>15.89711850369239</v>
+        <v>15.89711660590322</v>
       </c>
       <c r="F77" t="n">
         <v>7246000</v>
@@ -1972,16 +1972,16 @@
         <v>44365</v>
       </c>
       <c r="B78" t="n">
-        <v>16.2078914642334</v>
+        <v>16.20788955688477</v>
       </c>
       <c r="C78" t="n">
-        <v>16.36423112436919</v>
+        <v>16.36422919862247</v>
       </c>
       <c r="D78" t="n">
-        <v>15.67976622640263</v>
+        <v>15.67976438120391</v>
       </c>
       <c r="E78" t="n">
-        <v>15.98863265031907</v>
+        <v>15.98863076877287</v>
       </c>
       <c r="F78" t="n">
         <v>12012000</v>
@@ -1992,16 +1992,16 @@
         <v>44368</v>
       </c>
       <c r="B79" t="n">
-        <v>16.48434638977051</v>
+        <v>16.48434257507324</v>
       </c>
       <c r="C79" t="n">
-        <v>16.59302212366407</v>
+        <v>16.59301828381779</v>
       </c>
       <c r="D79" t="n">
-        <v>16.0000739807668</v>
+        <v>16.00007027813662</v>
       </c>
       <c r="E79" t="n">
-        <v>16.20789229804439</v>
+        <v>16.20788854732228</v>
       </c>
       <c r="F79" t="n">
         <v>6798000</v>
@@ -2012,16 +2012,16 @@
         <v>44369</v>
       </c>
       <c r="B80" t="n">
-        <v>16.47290420532227</v>
+        <v>16.4729061126709</v>
       </c>
       <c r="C80" t="n">
-        <v>16.49578339803871</v>
+        <v>16.49578530803645</v>
       </c>
       <c r="D80" t="n">
-        <v>16.13162548984007</v>
+        <v>16.13162735767305</v>
       </c>
       <c r="E80" t="n">
-        <v>16.46718395257762</v>
+        <v>16.46718585926392</v>
       </c>
       <c r="F80" t="n">
         <v>6518000</v>
@@ -2032,16 +2032,16 @@
         <v>44370</v>
       </c>
       <c r="B81" t="n">
-        <v>16.39664459228516</v>
+        <v>16.39664268493652</v>
       </c>
       <c r="C81" t="n">
-        <v>16.45574721722616</v>
+        <v>16.45574530300238</v>
       </c>
       <c r="D81" t="n">
-        <v>16.20979811200328</v>
+        <v>16.20979622638967</v>
       </c>
       <c r="E81" t="n">
-        <v>16.4004574889011</v>
+        <v>16.40045558110893</v>
       </c>
       <c r="F81" t="n">
         <v>5819500</v>
@@ -2052,16 +2052,16 @@
         <v>44371</v>
       </c>
       <c r="B82" t="n">
-        <v>16.64640617370605</v>
+        <v>16.64640426635742</v>
       </c>
       <c r="C82" t="n">
-        <v>16.72648245540622</v>
+        <v>16.72648053888243</v>
       </c>
       <c r="D82" t="n">
-        <v>16.39664417817516</v>
+        <v>16.39664229944431</v>
       </c>
       <c r="E82" t="n">
-        <v>16.46909284857351</v>
+        <v>16.46909096154148</v>
       </c>
       <c r="F82" t="n">
         <v>8527500</v>
@@ -2072,16 +2072,16 @@
         <v>44372</v>
       </c>
       <c r="B83" t="n">
-        <v>16.18501281738281</v>
+        <v>16.18501091003418</v>
       </c>
       <c r="C83" t="n">
-        <v>16.74745595976945</v>
+        <v>16.74745398613881</v>
       </c>
       <c r="D83" t="n">
-        <v>16.05345788821992</v>
+        <v>16.05345599637458</v>
       </c>
       <c r="E83" t="n">
-        <v>16.64640602074596</v>
+        <v>16.64640405902371</v>
       </c>
       <c r="F83" t="n">
         <v>6078000</v>
@@ -2092,16 +2092,16 @@
         <v>44375</v>
       </c>
       <c r="B84" t="n">
-        <v>16.3737621307373</v>
+        <v>16.37376403808594</v>
       </c>
       <c r="C84" t="n">
-        <v>16.37948056539015</v>
+        <v>16.37948247340491</v>
       </c>
       <c r="D84" t="n">
-        <v>15.9390592744375</v>
+        <v>15.93906113114842</v>
       </c>
       <c r="E84" t="n">
-        <v>16.2250482827814</v>
+        <v>16.22505017280664</v>
       </c>
       <c r="F84" t="n">
         <v>6202500</v>
@@ -2132,16 +2132,16 @@
         <v>44377</v>
       </c>
       <c r="B86" t="n">
-        <v>16.49959754943848</v>
+        <v>16.49959945678711</v>
       </c>
       <c r="C86" t="n">
-        <v>16.49959754943848</v>
+        <v>16.49959945678711</v>
       </c>
       <c r="D86" t="n">
-        <v>16.19072933339201</v>
+        <v>16.19073120503556</v>
       </c>
       <c r="E86" t="n">
-        <v>16.38901447318302</v>
+        <v>16.38901636774828</v>
       </c>
       <c r="F86" t="n">
         <v>6685000</v>
@@ -2172,16 +2172,16 @@
         <v>44379</v>
       </c>
       <c r="B88" t="n">
-        <v>16.39664459228516</v>
+        <v>16.39664268493652</v>
       </c>
       <c r="C88" t="n">
-        <v>16.45765457466542</v>
+        <v>16.45765266021977</v>
       </c>
       <c r="D88" t="n">
-        <v>16.21551836605848</v>
+        <v>16.21551647977946</v>
       </c>
       <c r="E88" t="n">
-        <v>16.36804514027171</v>
+        <v>16.36804323624992</v>
       </c>
       <c r="F88" t="n">
         <v>5948000</v>
@@ -2192,16 +2192,16 @@
         <v>44382</v>
       </c>
       <c r="B89" t="n">
-        <v>16.41570854187012</v>
+        <v>16.41570663452148</v>
       </c>
       <c r="C89" t="n">
-        <v>16.54726347128895</v>
+        <v>16.54726154865489</v>
       </c>
       <c r="D89" t="n">
-        <v>16.25174308313778</v>
+        <v>16.25174119484036</v>
       </c>
       <c r="E89" t="n">
-        <v>16.40808274888606</v>
+        <v>16.40808084242347</v>
       </c>
       <c r="F89" t="n">
         <v>3871000</v>
@@ -2212,16 +2212,16 @@
         <v>44383</v>
       </c>
       <c r="B90" t="n">
-        <v>16.33944320678711</v>
+        <v>16.33944702148438</v>
       </c>
       <c r="C90" t="n">
-        <v>16.38901449179115</v>
+        <v>16.3890183180616</v>
       </c>
       <c r="D90" t="n">
-        <v>16.11256043736321</v>
+        <v>16.11256419909116</v>
       </c>
       <c r="E90" t="n">
-        <v>16.38901449179115</v>
+        <v>16.3890183180616</v>
       </c>
       <c r="F90" t="n">
         <v>3828000</v>
@@ -2232,16 +2232,16 @@
         <v>44384</v>
       </c>
       <c r="B91" t="n">
-        <v>16.44430732727051</v>
+        <v>16.44430541992188</v>
       </c>
       <c r="C91" t="n">
-        <v>16.58348804403921</v>
+        <v>16.58348612054724</v>
       </c>
       <c r="D91" t="n">
-        <v>16.15069249011994</v>
+        <v>16.15069061682722</v>
       </c>
       <c r="E91" t="n">
-        <v>16.39664339565586</v>
+        <v>16.39664149383569</v>
       </c>
       <c r="F91" t="n">
         <v>12086500</v>
@@ -2252,16 +2252,16 @@
         <v>44385</v>
       </c>
       <c r="B92" t="n">
-        <v>16.43477439880371</v>
+        <v>16.43477249145508</v>
       </c>
       <c r="C92" t="n">
-        <v>16.79893236876558</v>
+        <v>16.79893041915436</v>
       </c>
       <c r="D92" t="n">
-        <v>16.24411685151298</v>
+        <v>16.24411496629124</v>
       </c>
       <c r="E92" t="n">
-        <v>16.26318133345833</v>
+        <v>16.26317944602405</v>
       </c>
       <c r="F92" t="n">
         <v>7435000</v>
@@ -2292,16 +2292,16 @@
         <v>44390</v>
       </c>
       <c r="B94" t="n">
-        <v>16.7874927520752</v>
+        <v>16.78749465942383</v>
       </c>
       <c r="C94" t="n">
-        <v>16.91142006005396</v>
+        <v>16.91142198148287</v>
       </c>
       <c r="D94" t="n">
-        <v>16.43096059459017</v>
+        <v>16.4309624614306</v>
       </c>
       <c r="E94" t="n">
-        <v>16.45383978992295</v>
+        <v>16.45384165936285</v>
       </c>
       <c r="F94" t="n">
         <v>6446000</v>
@@ -2312,16 +2312,16 @@
         <v>44391</v>
       </c>
       <c r="B95" t="n">
-        <v>16.72266960144043</v>
+        <v>16.7226676940918</v>
       </c>
       <c r="C95" t="n">
-        <v>17.08873494219598</v>
+        <v>17.08873299309478</v>
       </c>
       <c r="D95" t="n">
-        <v>16.67309831003382</v>
+        <v>16.67309640833917</v>
       </c>
       <c r="E95" t="n">
-        <v>16.93048791752151</v>
+        <v>16.9304859864696</v>
       </c>
       <c r="F95" t="n">
         <v>5548000</v>
@@ -2332,16 +2332,16 @@
         <v>44392</v>
       </c>
       <c r="B96" t="n">
-        <v>16.45002746582031</v>
+        <v>16.45002555847168</v>
       </c>
       <c r="C96" t="n">
-        <v>16.86375671689422</v>
+        <v>16.86375476157448</v>
       </c>
       <c r="D96" t="n">
-        <v>16.44049431591159</v>
+        <v>16.44049240966831</v>
       </c>
       <c r="E96" t="n">
-        <v>16.72266864381253</v>
+        <v>16.72266670485169</v>
       </c>
       <c r="F96" t="n">
         <v>3746000</v>
@@ -2352,16 +2352,16 @@
         <v>44393</v>
       </c>
       <c r="B97" t="n">
-        <v>16.67119407653809</v>
+        <v>16.67119216918945</v>
       </c>
       <c r="C97" t="n">
-        <v>16.86947743943095</v>
+        <v>16.86947550939675</v>
       </c>
       <c r="D97" t="n">
-        <v>16.52248019067143</v>
+        <v>16.52247830033713</v>
       </c>
       <c r="E97" t="n">
-        <v>16.54154467481126</v>
+        <v>16.54154278229579</v>
       </c>
       <c r="F97" t="n">
         <v>7965000</v>
@@ -2412,16 +2412,16 @@
         <v>44398</v>
       </c>
       <c r="B100" t="n">
-        <v>16.59683227539062</v>
+        <v>16.59683609008789</v>
       </c>
       <c r="C100" t="n">
-        <v>16.59683227539062</v>
+        <v>16.59683609008789</v>
       </c>
       <c r="D100" t="n">
-        <v>16.41570608218979</v>
+        <v>16.41570985525612</v>
       </c>
       <c r="E100" t="n">
-        <v>16.51675600626886</v>
+        <v>16.516759802561</v>
       </c>
       <c r="F100" t="n">
         <v>4032000</v>
@@ -2492,16 +2492,16 @@
         <v>44404</v>
       </c>
       <c r="B104" t="n">
-        <v>16.96861839294434</v>
+        <v>16.96861457824707</v>
       </c>
       <c r="C104" t="n">
-        <v>17.300365840649</v>
+        <v>17.30036195137194</v>
       </c>
       <c r="D104" t="n">
-        <v>16.87329052665406</v>
+        <v>16.87328673338735</v>
       </c>
       <c r="E104" t="n">
-        <v>17.14402435794695</v>
+        <v>17.14402050381685</v>
       </c>
       <c r="F104" t="n">
         <v>6666500</v>
@@ -2512,16 +2512,16 @@
         <v>44405</v>
       </c>
       <c r="B105" t="n">
-        <v>16.79320907592773</v>
+        <v>16.79321098327637</v>
       </c>
       <c r="C105" t="n">
-        <v>17.38043865187069</v>
+        <v>17.38044062591602</v>
       </c>
       <c r="D105" t="n">
-        <v>16.42333273745124</v>
+        <v>16.42333460278985</v>
       </c>
       <c r="E105" t="n">
-        <v>17.34993366801626</v>
+        <v>17.34993563859687</v>
       </c>
       <c r="F105" t="n">
         <v>14614500</v>
@@ -2532,16 +2532,16 @@
         <v>44406</v>
       </c>
       <c r="B106" t="n">
-        <v>16.62543487548828</v>
+        <v>16.62543106079102</v>
       </c>
       <c r="C106" t="n">
-        <v>16.7779616508197</v>
+        <v>16.77795780112525</v>
       </c>
       <c r="D106" t="n">
-        <v>16.27462292857349</v>
+        <v>16.27461919436984</v>
       </c>
       <c r="E106" t="n">
-        <v>16.7779616508197</v>
+        <v>16.77795780112525</v>
       </c>
       <c r="F106" t="n">
         <v>12625000</v>
@@ -2552,16 +2552,16 @@
         <v>44407</v>
       </c>
       <c r="B107" t="n">
-        <v>16.52629089355469</v>
+        <v>16.52628898620605</v>
       </c>
       <c r="C107" t="n">
-        <v>16.73220184103048</v>
+        <v>16.73219990991705</v>
       </c>
       <c r="D107" t="n">
-        <v>16.30893943885111</v>
+        <v>16.30893755658766</v>
       </c>
       <c r="E107" t="n">
-        <v>16.6254334709708</v>
+        <v>16.62543155217983</v>
       </c>
       <c r="F107" t="n">
         <v>16469000</v>
@@ -2572,16 +2572,16 @@
         <v>44410</v>
       </c>
       <c r="B108" t="n">
-        <v>16.52247619628906</v>
+        <v>16.52247428894043</v>
       </c>
       <c r="C108" t="n">
-        <v>16.83896837564879</v>
+        <v>16.83896643176442</v>
       </c>
       <c r="D108" t="n">
-        <v>16.36232184039388</v>
+        <v>16.3623199515334</v>
       </c>
       <c r="E108" t="n">
-        <v>16.68262873392202</v>
+        <v>16.68262680808543</v>
       </c>
       <c r="F108" t="n">
         <v>8100500</v>
@@ -2612,16 +2612,16 @@
         <v>44412</v>
       </c>
       <c r="B110" t="n">
-        <v>16.6025562286377</v>
+        <v>16.60255432128906</v>
       </c>
       <c r="C110" t="n">
-        <v>16.83134639923163</v>
+        <v>16.83134446559894</v>
       </c>
       <c r="D110" t="n">
-        <v>16.34897950164152</v>
+        <v>16.3489776234245</v>
       </c>
       <c r="E110" t="n">
-        <v>16.48244179818497</v>
+        <v>16.48243990463543</v>
       </c>
       <c r="F110" t="n">
         <v>6533500</v>
@@ -2632,16 +2632,16 @@
         <v>44413</v>
       </c>
       <c r="B111" t="n">
-        <v>16.5872974395752</v>
+        <v>16.58729934692383</v>
       </c>
       <c r="C111" t="n">
-        <v>16.93810928427588</v>
+        <v>16.93811123196384</v>
       </c>
       <c r="D111" t="n">
-        <v>16.47480883917376</v>
+        <v>16.47481073358749</v>
       </c>
       <c r="E111" t="n">
-        <v>16.59301769200566</v>
+        <v>16.59301960001205</v>
       </c>
       <c r="F111" t="n">
         <v>13427000</v>
@@ -2692,16 +2692,16 @@
         <v>44418</v>
       </c>
       <c r="B114" t="n">
-        <v>17.55012512207031</v>
+        <v>17.55012893676758</v>
       </c>
       <c r="C114" t="n">
-        <v>17.66452108952034</v>
+        <v>17.66452492908273</v>
       </c>
       <c r="D114" t="n">
-        <v>17.10589093347529</v>
+        <v>17.10589465161376</v>
       </c>
       <c r="E114" t="n">
-        <v>17.22219243972985</v>
+        <v>17.22219618314763</v>
       </c>
       <c r="F114" t="n">
         <v>10281500</v>
@@ -2712,16 +2712,16 @@
         <v>44419</v>
       </c>
       <c r="B115" t="n">
-        <v>17.20884704589844</v>
+        <v>17.2088451385498</v>
       </c>
       <c r="C115" t="n">
-        <v>17.57872523333663</v>
+        <v>17.57872328499242</v>
       </c>
       <c r="D115" t="n">
-        <v>17.19740835785192</v>
+        <v>17.1974064517711</v>
       </c>
       <c r="E115" t="n">
-        <v>17.57872523333663</v>
+        <v>17.57872328499242</v>
       </c>
       <c r="F115" t="n">
         <v>6265000</v>
@@ -2752,16 +2752,16 @@
         <v>44421</v>
       </c>
       <c r="B117" t="n">
-        <v>16.91141891479492</v>
+        <v>16.91142082214355</v>
       </c>
       <c r="C117" t="n">
-        <v>17.27367130114663</v>
+        <v>17.27367324935177</v>
       </c>
       <c r="D117" t="n">
-        <v>16.53010204884227</v>
+        <v>16.53010391318421</v>
       </c>
       <c r="E117" t="n">
-        <v>16.82562239267279</v>
+        <v>16.82562429034489</v>
       </c>
       <c r="F117" t="n">
         <v>5547600</v>
@@ -2772,16 +2772,16 @@
         <v>44424</v>
       </c>
       <c r="B118" t="n">
-        <v>16.44430732727051</v>
+        <v>16.44430541992188</v>
       </c>
       <c r="C118" t="n">
-        <v>17.04488122962231</v>
+        <v>17.04487925261408</v>
       </c>
       <c r="D118" t="n">
-        <v>16.27271426423787</v>
+        <v>16.27271237679204</v>
       </c>
       <c r="E118" t="n">
-        <v>16.86375683487669</v>
+        <v>16.86375487887679</v>
       </c>
       <c r="F118" t="n">
         <v>7814500</v>
@@ -2792,16 +2792,16 @@
         <v>44425</v>
       </c>
       <c r="B119" t="n">
-        <v>16.16785049438477</v>
+        <v>16.16784858703613</v>
       </c>
       <c r="C119" t="n">
-        <v>16.39664244399077</v>
+        <v>16.39664050965117</v>
       </c>
       <c r="D119" t="n">
-        <v>15.70073708227531</v>
+        <v>15.70073523003284</v>
       </c>
       <c r="E119" t="n">
-        <v>16.16785049438477</v>
+        <v>16.16784858703613</v>
       </c>
       <c r="F119" t="n">
         <v>9967800</v>
@@ -2832,16 +2832,16 @@
         <v>44427</v>
       </c>
       <c r="B121" t="n">
-        <v>16.66356468200684</v>
+        <v>16.6635627746582</v>
       </c>
       <c r="C121" t="n">
-        <v>16.87329034947318</v>
+        <v>16.87328841811889</v>
       </c>
       <c r="D121" t="n">
-        <v>15.57681101699932</v>
+        <v>15.57680923404292</v>
       </c>
       <c r="E121" t="n">
-        <v>15.71027148301428</v>
+        <v>15.71026968478171</v>
       </c>
       <c r="F121" t="n">
         <v>14455000</v>
@@ -2872,16 +2872,16 @@
         <v>44431</v>
       </c>
       <c r="B123" t="n">
-        <v>16.69216346740723</v>
+        <v>16.69216156005859</v>
       </c>
       <c r="C123" t="n">
-        <v>17.16881004791025</v>
+        <v>17.16880808609706</v>
       </c>
       <c r="D123" t="n">
-        <v>16.52057040750415</v>
+        <v>16.52056851976279</v>
       </c>
       <c r="E123" t="n">
-        <v>16.97815068840407</v>
+        <v>16.9781487483768</v>
       </c>
       <c r="F123" t="n">
         <v>5050600</v>
@@ -2892,16 +2892,16 @@
         <v>44432</v>
       </c>
       <c r="B124" t="n">
-        <v>16.91141891479492</v>
+        <v>16.91142082214355</v>
       </c>
       <c r="C124" t="n">
-        <v>17.05441251224439</v>
+        <v>17.05441443572051</v>
       </c>
       <c r="D124" t="n">
-        <v>16.66356249736014</v>
+        <v>16.66356437675437</v>
       </c>
       <c r="E124" t="n">
-        <v>16.78749161520865</v>
+        <v>16.78749350858018</v>
       </c>
       <c r="F124" t="n">
         <v>4198100</v>
@@ -2912,16 +2912,16 @@
         <v>44433</v>
       </c>
       <c r="B125" t="n">
-        <v>17.01628112792969</v>
+        <v>17.01628303527832</v>
       </c>
       <c r="C125" t="n">
-        <v>17.19740731464605</v>
+        <v>17.19740924229705</v>
       </c>
       <c r="D125" t="n">
-        <v>16.78749101651742</v>
+        <v>16.78749289822105</v>
       </c>
       <c r="E125" t="n">
-        <v>17.02581427652131</v>
+        <v>17.0258161849385</v>
       </c>
       <c r="F125" t="n">
         <v>4269900</v>
@@ -2932,16 +2932,16 @@
         <v>44434</v>
       </c>
       <c r="B126" t="n">
-        <v>16.55870246887207</v>
+        <v>16.5587043762207</v>
       </c>
       <c r="C126" t="n">
-        <v>17.00674958541756</v>
+        <v>17.00675154437543</v>
       </c>
       <c r="D126" t="n">
-        <v>16.55870246887207</v>
+        <v>16.5587043762207</v>
       </c>
       <c r="E126" t="n">
-        <v>16.93048620774466</v>
+        <v>16.93048815791797</v>
       </c>
       <c r="F126" t="n">
         <v>4969900</v>
@@ -2952,16 +2952,16 @@
         <v>44435</v>
       </c>
       <c r="B127" t="n">
-        <v>16.5872974395752</v>
+        <v>16.58729934692383</v>
       </c>
       <c r="C127" t="n">
-        <v>16.72075969280097</v>
+        <v>16.72076161549623</v>
       </c>
       <c r="D127" t="n">
-        <v>16.39663993509303</v>
+        <v>16.39664182051824</v>
       </c>
       <c r="E127" t="n">
-        <v>16.558699813947</v>
+        <v>16.55870171800724</v>
       </c>
       <c r="F127" t="n">
         <v>5662600</v>
@@ -3072,16 +3072,16 @@
         <v>44445</v>
       </c>
       <c r="B133" t="n">
-        <v>17.4929313659668</v>
+        <v>17.49292755126953</v>
       </c>
       <c r="C133" t="n">
-        <v>17.66452444056273</v>
+        <v>17.66452058844603</v>
       </c>
       <c r="D133" t="n">
-        <v>17.04488237824128</v>
+        <v>17.04487866125041</v>
       </c>
       <c r="E133" t="n">
-        <v>17.30227199013519</v>
+        <v>17.30226821701516</v>
       </c>
       <c r="F133" t="n">
         <v>6471000</v>
@@ -3112,16 +3112,16 @@
         <v>44448</v>
       </c>
       <c r="B135" t="n">
-        <v>17.34993743896484</v>
+        <v>17.34993553161621</v>
       </c>
       <c r="C135" t="n">
-        <v>17.44526530694636</v>
+        <v>17.44526338911795</v>
       </c>
       <c r="D135" t="n">
-        <v>16.92095475999791</v>
+        <v>16.92095289980908</v>
       </c>
       <c r="E135" t="n">
-        <v>17.07348153068337</v>
+        <v>17.07347965372665</v>
       </c>
       <c r="F135" t="n">
         <v>12544000</v>
@@ -3132,16 +3132,16 @@
         <v>44449</v>
       </c>
       <c r="B136" t="n">
-        <v>17.33086967468262</v>
+        <v>17.33087158203125</v>
       </c>
       <c r="C136" t="n">
-        <v>17.60732374135838</v>
+        <v>17.60732567913216</v>
       </c>
       <c r="D136" t="n">
-        <v>17.01628300942406</v>
+        <v>17.01628488215086</v>
       </c>
       <c r="E136" t="n">
-        <v>17.33086967468262</v>
+        <v>17.33087158203125</v>
       </c>
       <c r="F136" t="n">
         <v>19125200</v>
@@ -3152,16 +3152,16 @@
         <v>44452</v>
       </c>
       <c r="B137" t="n">
-        <v>17.79798126220703</v>
+        <v>17.79798316955566</v>
       </c>
       <c r="C137" t="n">
-        <v>17.96957430160813</v>
+        <v>17.9695762273458</v>
       </c>
       <c r="D137" t="n">
-        <v>17.49292777805493</v>
+        <v>17.49292965271203</v>
       </c>
       <c r="E137" t="n">
-        <v>17.57872429775548</v>
+        <v>17.5787261816071</v>
       </c>
       <c r="F137" t="n">
         <v>17075500</v>
@@ -3172,16 +3172,16 @@
         <v>44453</v>
       </c>
       <c r="B138" t="n">
-        <v>17.47386169433594</v>
+        <v>17.4738655090332</v>
       </c>
       <c r="C138" t="n">
-        <v>18.15070071155172</v>
+        <v>18.15070467400888</v>
       </c>
       <c r="D138" t="n">
-        <v>17.39759832236565</v>
+        <v>17.39760212041395</v>
       </c>
       <c r="E138" t="n">
-        <v>17.82658092611242</v>
+        <v>17.82658481781139</v>
       </c>
       <c r="F138" t="n">
         <v>6594500</v>
@@ -3192,16 +3192,16 @@
         <v>44454</v>
       </c>
       <c r="B139" t="n">
-        <v>17.72172164916992</v>
+        <v>17.72172355651855</v>
       </c>
       <c r="C139" t="n">
-        <v>17.82658448843234</v>
+        <v>17.82658640706712</v>
       </c>
       <c r="D139" t="n">
-        <v>17.27367447659312</v>
+        <v>17.27367633571945</v>
       </c>
       <c r="E139" t="n">
-        <v>17.46433203548721</v>
+        <v>17.46433391513358</v>
       </c>
       <c r="F139" t="n">
         <v>8756500</v>
@@ -3212,16 +3212,16 @@
         <v>44455</v>
       </c>
       <c r="B140" t="n">
-        <v>18.26509857177734</v>
+        <v>18.26509666442871</v>
       </c>
       <c r="C140" t="n">
-        <v>18.33182880852791</v>
+        <v>18.33182689421092</v>
       </c>
       <c r="D140" t="n">
-        <v>17.72172170879404</v>
+        <v>17.72171985818801</v>
       </c>
       <c r="E140" t="n">
-        <v>17.72172170879404</v>
+        <v>17.72171985818801</v>
       </c>
       <c r="F140" t="n">
         <v>17281800</v>
@@ -3232,16 +3232,16 @@
         <v>44456</v>
       </c>
       <c r="B141" t="n">
-        <v>18.11256980895996</v>
+        <v>18.11256790161133</v>
       </c>
       <c r="C141" t="n">
-        <v>18.44622277435644</v>
+        <v>18.4462208318724</v>
       </c>
       <c r="D141" t="n">
-        <v>18.11256980895996</v>
+        <v>18.11256790161133</v>
       </c>
       <c r="E141" t="n">
-        <v>18.28416286649314</v>
+        <v>18.28416094107486</v>
       </c>
       <c r="F141" t="n">
         <v>23104900</v>
@@ -3252,16 +3252,16 @@
         <v>44459</v>
       </c>
       <c r="B142" t="n">
-        <v>17.94097709655762</v>
+        <v>17.94097518920898</v>
       </c>
       <c r="C142" t="n">
-        <v>18.12210330724501</v>
+        <v>18.12210138064041</v>
       </c>
       <c r="D142" t="n">
-        <v>17.63592357430248</v>
+        <v>17.63592169938482</v>
       </c>
       <c r="E142" t="n">
-        <v>18.02677362697468</v>
+        <v>18.02677171050481</v>
       </c>
       <c r="F142" t="n">
         <v>15522000</v>
@@ -3272,16 +3272,16 @@
         <v>44460</v>
       </c>
       <c r="B143" t="n">
-        <v>18.57968139648438</v>
+        <v>18.57968330383301</v>
       </c>
       <c r="C143" t="n">
-        <v>18.74174128832697</v>
+        <v>18.7417432123123</v>
       </c>
       <c r="D143" t="n">
-        <v>17.82658082963624</v>
+        <v>17.82658265967325</v>
       </c>
       <c r="E143" t="n">
-        <v>18.06490409303639</v>
+        <v>18.06490594753913</v>
       </c>
       <c r="F143" t="n">
         <v>17756900</v>
@@ -3312,16 +3312,16 @@
         <v>44462</v>
       </c>
       <c r="B145" t="n">
-        <v>18.2936954498291</v>
+        <v>18.29369735717773</v>
       </c>
       <c r="C145" t="n">
-        <v>18.53201872941112</v>
+        <v>18.53202066160796</v>
       </c>
       <c r="D145" t="n">
-        <v>18.07443665073428</v>
+        <v>18.07443853522241</v>
       </c>
       <c r="E145" t="n">
-        <v>18.34135937844058</v>
+        <v>18.34136129075877</v>
       </c>
       <c r="F145" t="n">
         <v>20822300</v>
@@ -3352,16 +3352,16 @@
         <v>44466</v>
       </c>
       <c r="B147" t="n">
-        <v>18.35089302062988</v>
+        <v>18.35089683532715</v>
       </c>
       <c r="C147" t="n">
-        <v>18.46528899793678</v>
+        <v>18.46529283641415</v>
       </c>
       <c r="D147" t="n">
-        <v>17.83611385014238</v>
+        <v>17.83611755782977</v>
       </c>
       <c r="E147" t="n">
-        <v>18.01724005660232</v>
+        <v>18.01724380194138</v>
       </c>
       <c r="F147" t="n">
         <v>7788100</v>
@@ -3372,16 +3372,16 @@
         <v>44467</v>
       </c>
       <c r="B148" t="n">
-        <v>18.28416633605957</v>
+        <v>18.2841625213623</v>
       </c>
       <c r="C148" t="n">
-        <v>18.29369948753845</v>
+        <v>18.29369567085224</v>
       </c>
       <c r="D148" t="n">
-        <v>18.01724354943918</v>
+        <v>18.01723979043107</v>
       </c>
       <c r="E148" t="n">
-        <v>18.23650057866518</v>
+        <v>18.23649677391261</v>
       </c>
       <c r="F148" t="n">
         <v>11310100</v>
@@ -3392,16 +3392,16 @@
         <v>44468</v>
       </c>
       <c r="B149" t="n">
-        <v>18.08396911621094</v>
+        <v>18.08397102355957</v>
       </c>
       <c r="C149" t="n">
-        <v>18.4271552076744</v>
+        <v>18.42715715121949</v>
       </c>
       <c r="D149" t="n">
-        <v>17.96957496456462</v>
+        <v>17.9695768598479</v>
       </c>
       <c r="E149" t="n">
-        <v>18.29369475799961</v>
+        <v>18.29369668746839</v>
       </c>
       <c r="F149" t="n">
         <v>10203400</v>
@@ -3412,16 +3412,16 @@
         <v>44469</v>
       </c>
       <c r="B150" t="n">
-        <v>18.15070343017578</v>
+        <v>18.15070152282715</v>
       </c>
       <c r="C150" t="n">
-        <v>18.6273500309481</v>
+        <v>18.62734807351153</v>
       </c>
       <c r="D150" t="n">
-        <v>18.04584059616188</v>
+        <v>18.04583869983265</v>
       </c>
       <c r="E150" t="n">
-        <v>18.30323019696192</v>
+        <v>18.30322827358517</v>
       </c>
       <c r="F150" t="n">
         <v>10293000</v>
@@ -3472,16 +3472,16 @@
         <v>44474</v>
       </c>
       <c r="B153" t="n">
-        <v>18.32229232788086</v>
+        <v>18.32229423522949</v>
       </c>
       <c r="C153" t="n">
-        <v>18.49388537306099</v>
+        <v>18.49388729827244</v>
       </c>
       <c r="D153" t="n">
-        <v>18.04583828040574</v>
+        <v>18.04584015897554</v>
       </c>
       <c r="E153" t="n">
-        <v>18.34135862584804</v>
+        <v>18.34136053518147</v>
       </c>
       <c r="F153" t="n">
         <v>8000200</v>
@@ -3512,16 +3512,16 @@
         <v>44476</v>
       </c>
       <c r="B155" t="n">
-        <v>18.08055114746094</v>
+        <v>18.08055305480957</v>
       </c>
       <c r="C155" t="n">
-        <v>18.36723991743979</v>
+        <v>18.36724185503171</v>
       </c>
       <c r="D155" t="n">
-        <v>17.99454415192273</v>
+        <v>17.99454605019834</v>
       </c>
       <c r="E155" t="n">
-        <v>18.271678209262</v>
+        <v>18.27168013677296</v>
       </c>
       <c r="F155" t="n">
         <v>7169200</v>
@@ -3552,16 +3552,16 @@
         <v>44480</v>
       </c>
       <c r="B157" t="n">
-        <v>16.62798690795898</v>
+        <v>16.62798881530762</v>
       </c>
       <c r="C157" t="n">
-        <v>17.5262809836174</v>
+        <v>17.52628299400677</v>
       </c>
       <c r="D157" t="n">
-        <v>16.47508602138593</v>
+        <v>16.47508791119575</v>
       </c>
       <c r="E157" t="n">
-        <v>17.42116094057755</v>
+        <v>17.4211629389089</v>
       </c>
       <c r="F157" t="n">
         <v>31512800</v>
@@ -3572,16 +3572,16 @@
         <v>44482</v>
       </c>
       <c r="B158" t="n">
-        <v>17.12492179870605</v>
+        <v>17.12491989135742</v>
       </c>
       <c r="C158" t="n">
-        <v>17.40205407078302</v>
+        <v>17.4020521325678</v>
       </c>
       <c r="D158" t="n">
-        <v>16.62799282903075</v>
+        <v>16.62799097702933</v>
       </c>
       <c r="E158" t="n">
-        <v>16.62799282903075</v>
+        <v>16.62799097702933</v>
       </c>
       <c r="F158" t="n">
         <v>10150700</v>
@@ -3632,16 +3632,16 @@
         <v>44487</v>
       </c>
       <c r="B161" t="n">
-        <v>16.20751190185547</v>
+        <v>16.20750999450684</v>
       </c>
       <c r="C161" t="n">
-        <v>16.67577301414236</v>
+        <v>16.67577105168735</v>
       </c>
       <c r="D161" t="n">
-        <v>16.10239365985386</v>
+        <v>16.10239176487586</v>
       </c>
       <c r="E161" t="n">
-        <v>16.58976601986295</v>
+        <v>16.5897640675295</v>
       </c>
       <c r="F161" t="n">
         <v>13070300</v>
@@ -3652,16 +3652,16 @@
         <v>44488</v>
       </c>
       <c r="B162" t="n">
-        <v>15.81570243835449</v>
+        <v>15.81570053100586</v>
       </c>
       <c r="C162" t="n">
-        <v>16.07372341086592</v>
+        <v>16.07372147240036</v>
       </c>
       <c r="D162" t="n">
-        <v>15.63413374456288</v>
+        <v>15.63413185911114</v>
       </c>
       <c r="E162" t="n">
-        <v>16.05461034118597</v>
+        <v>16.05460840502542</v>
       </c>
       <c r="F162" t="n">
         <v>17605400</v>
@@ -3672,16 +3672,16 @@
         <v>44489</v>
       </c>
       <c r="B163" t="n">
-        <v>15.98771667480469</v>
+        <v>15.98771476745605</v>
       </c>
       <c r="C163" t="n">
-        <v>16.21706804645106</v>
+        <v>16.21706611174061</v>
       </c>
       <c r="D163" t="n">
-        <v>15.71058445091965</v>
+        <v>15.71058257663313</v>
       </c>
       <c r="E163" t="n">
-        <v>15.93993582256603</v>
+        <v>15.93993392091769</v>
       </c>
       <c r="F163" t="n">
         <v>11472200</v>
@@ -3712,16 +3712,16 @@
         <v>44491</v>
       </c>
       <c r="B165" t="n">
-        <v>15.39522552490234</v>
+        <v>15.39522647857666</v>
       </c>
       <c r="C165" t="n">
-        <v>15.64368995746047</v>
+        <v>15.64369092652619</v>
       </c>
       <c r="D165" t="n">
-        <v>14.76450790886372</v>
+        <v>14.76450882346753</v>
       </c>
       <c r="E165" t="n">
-        <v>15.39522552490234</v>
+        <v>15.39522647857666</v>
       </c>
       <c r="F165" t="n">
         <v>24678500</v>
@@ -3752,16 +3752,16 @@
         <v>44495</v>
       </c>
       <c r="B167" t="n">
-        <v>15.24232387542725</v>
+        <v>15.24232292175293</v>
       </c>
       <c r="C167" t="n">
-        <v>15.44300654837805</v>
+        <v>15.44300558214752</v>
       </c>
       <c r="D167" t="n">
-        <v>15.0129725095867</v>
+        <v>15.01297157026232</v>
       </c>
       <c r="E167" t="n">
-        <v>15.38566916259858</v>
+        <v>15.3856681999555</v>
       </c>
       <c r="F167" t="n">
         <v>7090300</v>
@@ -3772,16 +3772,16 @@
         <v>44496</v>
       </c>
       <c r="B168" t="n">
-        <v>14.94608020782471</v>
+        <v>14.94607925415039</v>
       </c>
       <c r="C168" t="n">
-        <v>15.38567082897724</v>
+        <v>15.38566984725368</v>
       </c>
       <c r="D168" t="n">
-        <v>14.81229144091344</v>
+        <v>14.81229049577588</v>
       </c>
       <c r="E168" t="n">
-        <v>15.38567082897724</v>
+        <v>15.38566984725368</v>
       </c>
       <c r="F168" t="n">
         <v>9783700</v>
@@ -3792,16 +3792,16 @@
         <v>44497</v>
       </c>
       <c r="B169" t="n">
-        <v>14.95563411712646</v>
+        <v>14.95563507080078</v>
       </c>
       <c r="C169" t="n">
-        <v>15.13720463078065</v>
+        <v>15.13720559603315</v>
       </c>
       <c r="D169" t="n">
-        <v>14.69761406004066</v>
+        <v>14.69761499726184</v>
       </c>
       <c r="E169" t="n">
-        <v>15.02252894859126</v>
+        <v>15.02252990653125</v>
       </c>
       <c r="F169" t="n">
         <v>8208600</v>
@@ -3812,16 +3812,16 @@
         <v>44498</v>
       </c>
       <c r="B170" t="n">
-        <v>14.61160755157471</v>
+        <v>14.61160659790039</v>
       </c>
       <c r="C170" t="n">
-        <v>15.21365558640951</v>
+        <v>15.21365459344056</v>
       </c>
       <c r="D170" t="n">
-        <v>14.50648840061422</v>
+        <v>14.50648745380085</v>
       </c>
       <c r="E170" t="n">
-        <v>15.0034163731272</v>
+        <v>15.0034153938802</v>
       </c>
       <c r="F170" t="n">
         <v>13706000</v>
@@ -3852,16 +3852,16 @@
         <v>44503</v>
       </c>
       <c r="B172" t="n">
-        <v>14.74539470672607</v>
+        <v>14.74539566040039</v>
       </c>
       <c r="C172" t="n">
-        <v>14.86962691420749</v>
+        <v>14.86962787591666</v>
       </c>
       <c r="D172" t="n">
-        <v>14.07645191084749</v>
+        <v>14.07645282125721</v>
       </c>
       <c r="E172" t="n">
-        <v>14.1433467372521</v>
+        <v>14.14334765198831</v>
       </c>
       <c r="F172" t="n">
         <v>21906500</v>
@@ -3952,16 +3952,16 @@
         <v>44510</v>
       </c>
       <c r="B177" t="n">
-        <v>15.26143741607666</v>
+        <v>15.26143646240234</v>
       </c>
       <c r="C177" t="n">
-        <v>15.38566963758256</v>
+        <v>15.38566867614508</v>
       </c>
       <c r="D177" t="n">
-        <v>14.71672676618749</v>
+        <v>14.71672584655168</v>
       </c>
       <c r="E177" t="n">
-        <v>14.84095898769339</v>
+        <v>14.84095806029442</v>
       </c>
       <c r="F177" t="n">
         <v>10223900</v>
@@ -3972,16 +3972,16 @@
         <v>44511</v>
       </c>
       <c r="B178" t="n">
-        <v>15.19454193115234</v>
+        <v>15.19454288482666</v>
       </c>
       <c r="C178" t="n">
-        <v>15.51945681788442</v>
+        <v>15.51945779195179</v>
       </c>
       <c r="D178" t="n">
-        <v>15.07986624960478</v>
+        <v>15.07986719608156</v>
       </c>
       <c r="E178" t="n">
-        <v>15.43344982888343</v>
+        <v>15.43345079755262</v>
       </c>
       <c r="F178" t="n">
         <v>5555700</v>
@@ -3992,16 +3992,16 @@
         <v>44512</v>
       </c>
       <c r="B179" t="n">
-        <v>14.84095764160156</v>
+        <v>14.8409595489502</v>
       </c>
       <c r="C179" t="n">
-        <v>15.23276642931119</v>
+        <v>15.23276838701479</v>
       </c>
       <c r="D179" t="n">
-        <v>14.82184548460564</v>
+        <v>14.82184738949799</v>
       </c>
       <c r="E179" t="n">
-        <v>15.08942206207736</v>
+        <v>15.08942400135846</v>
       </c>
       <c r="F179" t="n">
         <v>7831400</v>
@@ -4012,16 +4012,16 @@
         <v>44516</v>
       </c>
       <c r="B180" t="n">
-        <v>14.18157386779785</v>
+        <v>14.18157291412354</v>
       </c>
       <c r="C180" t="n">
-        <v>14.86007237747372</v>
+        <v>14.86007137817213</v>
       </c>
       <c r="D180" t="n">
-        <v>14.00000334347483</v>
+        <v>14.00000240201066</v>
       </c>
       <c r="E180" t="n">
-        <v>14.81229061258022</v>
+        <v>14.81228961649183</v>
       </c>
       <c r="F180" t="n">
         <v>11424100</v>
@@ -4092,16 +4092,16 @@
         <v>44522</v>
       </c>
       <c r="B184" t="n">
-        <v>13.17815971374512</v>
+        <v>13.17816066741943</v>
       </c>
       <c r="C184" t="n">
-        <v>13.569968523517</v>
+        <v>13.56996950554565</v>
       </c>
       <c r="D184" t="n">
-        <v>13.12082141680619</v>
+        <v>13.12082236633105</v>
       </c>
       <c r="E184" t="n">
-        <v>13.52218676129477</v>
+        <v>13.52218773986557</v>
       </c>
       <c r="F184" t="n">
         <v>12046100</v>
@@ -4132,16 +4132,16 @@
         <v>44524</v>
       </c>
       <c r="B186" t="n">
-        <v>13.11126613616943</v>
+        <v>13.11126708984375</v>
       </c>
       <c r="C186" t="n">
-        <v>13.38839927066881</v>
+        <v>13.38840024450097</v>
       </c>
       <c r="D186" t="n">
-        <v>12.97747738072233</v>
+        <v>12.97747832466525</v>
       </c>
       <c r="E186" t="n">
-        <v>13.09215306623642</v>
+        <v>13.09215401852051</v>
       </c>
       <c r="F186" t="n">
         <v>5705900</v>
@@ -4172,16 +4172,16 @@
         <v>44526</v>
       </c>
       <c r="B188" t="n">
-        <v>12.76723861694336</v>
+        <v>12.76723957061768</v>
       </c>
       <c r="C188" t="n">
-        <v>13.02525960193866</v>
+        <v>13.02526057488637</v>
       </c>
       <c r="D188" t="n">
-        <v>12.64300639209688</v>
+        <v>12.64300733649143</v>
       </c>
       <c r="E188" t="n">
-        <v>12.93925260694023</v>
+        <v>12.93925357346347</v>
       </c>
       <c r="F188" t="n">
         <v>6311300</v>
@@ -4252,16 +4252,16 @@
         <v>44532</v>
       </c>
       <c r="B192" t="n">
-        <v>11.89761352539062</v>
+        <v>11.89761257171631</v>
       </c>
       <c r="C192" t="n">
-        <v>12.14607796612476</v>
+        <v>12.14607699253434</v>
       </c>
       <c r="D192" t="n">
-        <v>11.71604391799958</v>
+        <v>11.71604297887929</v>
       </c>
       <c r="E192" t="n">
-        <v>12.14607796612476</v>
+        <v>12.14607699253434</v>
       </c>
       <c r="F192" t="n">
         <v>7306700</v>
@@ -4292,16 +4292,16 @@
         <v>44536</v>
       </c>
       <c r="B194" t="n">
-        <v>13.13993453979492</v>
+        <v>13.13993549346924</v>
       </c>
       <c r="C194" t="n">
-        <v>13.28327891568452</v>
+        <v>13.28327987976253</v>
       </c>
       <c r="D194" t="n">
-        <v>12.77679442133178</v>
+        <v>12.77679534865</v>
       </c>
       <c r="E194" t="n">
-        <v>12.83413271850441</v>
+        <v>12.83413364998414</v>
       </c>
       <c r="F194" t="n">
         <v>6605800</v>
@@ -4312,16 +4312,16 @@
         <v>44537</v>
       </c>
       <c r="B195" t="n">
-        <v>13.42662334442139</v>
+        <v>13.4266242980957</v>
       </c>
       <c r="C195" t="n">
-        <v>13.76109383723112</v>
+        <v>13.76109481466241</v>
       </c>
       <c r="D195" t="n">
-        <v>13.40751027613218</v>
+        <v>13.40751122844893</v>
       </c>
       <c r="E195" t="n">
-        <v>13.56996771114538</v>
+        <v>13.56996867500125</v>
       </c>
       <c r="F195" t="n">
         <v>14090400</v>
@@ -4332,16 +4332,16 @@
         <v>44538</v>
       </c>
       <c r="B196" t="n">
-        <v>13.75153923034668</v>
+        <v>13.75153827667236</v>
       </c>
       <c r="C196" t="n">
-        <v>14.02867236148461</v>
+        <v>14.02867138859101</v>
       </c>
       <c r="D196" t="n">
-        <v>13.27372342415291</v>
+        <v>13.2737225036153</v>
       </c>
       <c r="E196" t="n">
-        <v>13.42662433631711</v>
+        <v>13.42662340517576</v>
       </c>
       <c r="F196" t="n">
         <v>14295000</v>
@@ -4392,16 +4392,16 @@
         <v>44543</v>
       </c>
       <c r="B199" t="n">
-        <v>13.74198341369629</v>
+        <v>13.74198246002197</v>
       </c>
       <c r="C199" t="n">
-        <v>14.12423571408451</v>
+        <v>14.12423473388242</v>
       </c>
       <c r="D199" t="n">
-        <v>13.66553295361865</v>
+        <v>13.66553200524988</v>
       </c>
       <c r="E199" t="n">
-        <v>13.96177825857917</v>
+        <v>13.9617772896514</v>
       </c>
       <c r="F199" t="n">
         <v>11783000</v>
@@ -4412,16 +4412,16 @@
         <v>44544</v>
       </c>
       <c r="B200" t="n">
-        <v>13.76109409332275</v>
+        <v>13.76109504699707</v>
       </c>
       <c r="C200" t="n">
-        <v>14.14334726396917</v>
+        <v>14.14334824413447</v>
       </c>
       <c r="D200" t="n">
-        <v>13.56996796368018</v>
+        <v>13.56996890410904</v>
       </c>
       <c r="E200" t="n">
-        <v>13.88532630543074</v>
+        <v>13.88532726771463</v>
       </c>
       <c r="F200" t="n">
         <v>6761100</v>
@@ -4532,16 +4532,16 @@
         <v>44552</v>
       </c>
       <c r="B206" t="n">
-        <v>13.53174304962158</v>
+        <v>13.5317440032959</v>
       </c>
       <c r="C206" t="n">
-        <v>13.66553179913548</v>
+        <v>13.66553276223881</v>
       </c>
       <c r="D206" t="n">
-        <v>13.29283515422187</v>
+        <v>13.29283609105872</v>
       </c>
       <c r="E206" t="n">
-        <v>13.58908134551648</v>
+        <v>13.58908230323182</v>
       </c>
       <c r="F206" t="n">
         <v>6990400</v>
@@ -4592,16 +4592,16 @@
         <v>44558</v>
       </c>
       <c r="B209" t="n">
-        <v>12.51877498626709</v>
+        <v>12.51877403259277</v>
       </c>
       <c r="C209" t="n">
-        <v>13.12082212409239</v>
+        <v>13.12082112455441</v>
       </c>
       <c r="D209" t="n">
-        <v>12.31809230320487</v>
+        <v>12.31809136481846</v>
       </c>
       <c r="E209" t="n">
-        <v>13.12082212409239</v>
+        <v>13.12082112455441</v>
       </c>
       <c r="F209" t="n">
         <v>22962600</v>
@@ -4612,16 +4612,16 @@
         <v>44559</v>
       </c>
       <c r="B210" t="n">
-        <v>12.27030944824219</v>
+        <v>12.2703104019165</v>
       </c>
       <c r="C210" t="n">
-        <v>12.53788603143165</v>
+        <v>12.53788700590259</v>
       </c>
       <c r="D210" t="n">
-        <v>12.25119637947659</v>
+        <v>12.2511973316654</v>
       </c>
       <c r="E210" t="n">
-        <v>12.51877387402733</v>
+        <v>12.51877484701283</v>
       </c>
       <c r="F210" t="n">
         <v>10451000</v>
@@ -4632,16 +4632,16 @@
         <v>44560</v>
       </c>
       <c r="B211" t="n">
-        <v>12.38498497009277</v>
+        <v>12.38498592376709</v>
       </c>
       <c r="C211" t="n">
-        <v>12.499660647152</v>
+        <v>12.49966160965662</v>
       </c>
       <c r="D211" t="n">
-        <v>12.25119622450971</v>
+        <v>12.25119716788196</v>
       </c>
       <c r="E211" t="n">
-        <v>12.32764667588253</v>
+        <v>12.32764762514165</v>
       </c>
       <c r="F211" t="n">
         <v>5913100</v>
@@ -4652,16 +4652,16 @@
         <v>44564</v>
       </c>
       <c r="B212" t="n">
-        <v>12.1556339263916</v>
+        <v>12.15563488006592</v>
       </c>
       <c r="C212" t="n">
-        <v>12.49966096635466</v>
+        <v>12.49966194701974</v>
       </c>
       <c r="D212" t="n">
-        <v>11.84983120172981</v>
+        <v>11.84983213141227</v>
       </c>
       <c r="E212" t="n">
-        <v>12.49966096635466</v>
+        <v>12.49966194701974</v>
       </c>
       <c r="F212" t="n">
         <v>16124600</v>
@@ -4672,16 +4672,16 @@
         <v>44565</v>
       </c>
       <c r="B213" t="n">
-        <v>12.1556339263916</v>
+        <v>12.15563488006592</v>
       </c>
       <c r="C213" t="n">
-        <v>12.25119653736736</v>
+        <v>12.25119749853907</v>
       </c>
       <c r="D213" t="n">
-        <v>11.89761296289834</v>
+        <v>11.89761389632953</v>
       </c>
       <c r="E213" t="n">
-        <v>12.20341568756013</v>
+        <v>12.20341664498318</v>
       </c>
       <c r="F213" t="n">
         <v>9389900</v>
@@ -4752,16 +4752,16 @@
         <v>44571</v>
       </c>
       <c r="B217" t="n">
-        <v>10.79863834381104</v>
+        <v>10.79863739013672</v>
       </c>
       <c r="C217" t="n">
-        <v>10.85597573519133</v>
+        <v>10.8559747764533</v>
       </c>
       <c r="D217" t="n">
-        <v>10.54061734851548</v>
+        <v>10.54061641762812</v>
       </c>
       <c r="E217" t="n">
-        <v>10.76041311243704</v>
+        <v>10.76041216213855</v>
       </c>
       <c r="F217" t="n">
         <v>8755800</v>
@@ -4772,16 +4772,16 @@
         <v>44572</v>
       </c>
       <c r="B218" t="n">
-        <v>10.94198226928711</v>
+        <v>10.94198322296143</v>
       </c>
       <c r="C218" t="n">
-        <v>10.96109533984372</v>
+        <v>10.96109629518389</v>
       </c>
       <c r="D218" t="n">
-        <v>10.66484912574574</v>
+        <v>10.66485005526586</v>
       </c>
       <c r="E218" t="n">
-        <v>10.7030743554976</v>
+        <v>10.70307528834934</v>
       </c>
       <c r="F218" t="n">
         <v>6045500</v>
@@ -4812,16 +4812,16 @@
         <v>44574</v>
       </c>
       <c r="B220" t="n">
-        <v>11.48669338226318</v>
+        <v>11.48669242858887</v>
       </c>
       <c r="C220" t="n">
-        <v>11.57269946905179</v>
+        <v>11.57269850823688</v>
       </c>
       <c r="D220" t="n">
-        <v>11.15222192531568</v>
+        <v>11.15222099941061</v>
       </c>
       <c r="E220" t="n">
-        <v>11.27645415471443</v>
+        <v>11.27645321849507</v>
       </c>
       <c r="F220" t="n">
         <v>9668300</v>
@@ -4832,16 +4832,16 @@
         <v>44575</v>
       </c>
       <c r="B221" t="n">
-        <v>11.59181118011475</v>
+        <v>11.59181213378906</v>
       </c>
       <c r="C221" t="n">
-        <v>11.65870509911001</v>
+        <v>11.65870605828779</v>
       </c>
       <c r="D221" t="n">
-        <v>11.39112851176765</v>
+        <v>11.39112944893152</v>
       </c>
       <c r="E221" t="n">
-        <v>11.4102406694686</v>
+        <v>11.41024160820486</v>
       </c>
       <c r="F221" t="n">
         <v>7586600</v>
@@ -4852,16 +4852,16 @@
         <v>44578</v>
       </c>
       <c r="B222" t="n">
-        <v>11.47713470458984</v>
+        <v>11.47713565826416</v>
       </c>
       <c r="C222" t="n">
-        <v>11.6109225333104</v>
+        <v>11.6109234981016</v>
       </c>
       <c r="D222" t="n">
-        <v>11.41023987886834</v>
+        <v>11.41024082698413</v>
       </c>
       <c r="E222" t="n">
-        <v>11.5918103769337</v>
+        <v>11.59181134013681</v>
       </c>
       <c r="F222" t="n">
         <v>4569300</v>
@@ -4892,16 +4892,16 @@
         <v>44580</v>
       </c>
       <c r="B224" t="n">
-        <v>11.49624824523926</v>
+        <v>11.49624729156494</v>
       </c>
       <c r="C224" t="n">
-        <v>11.69693092384569</v>
+        <v>11.69692995352369</v>
       </c>
       <c r="D224" t="n">
-        <v>11.41979778780455</v>
+        <v>11.41979684047221</v>
       </c>
       <c r="E224" t="n">
-        <v>11.41979778780455</v>
+        <v>11.41979684047221</v>
       </c>
       <c r="F224" t="n">
         <v>5074700</v>
@@ -4932,16 +4932,16 @@
         <v>44582</v>
       </c>
       <c r="B226" t="n">
-        <v>11.48669338226318</v>
+        <v>11.48669242858887</v>
       </c>
       <c r="C226" t="n">
-        <v>11.6300377716056</v>
+        <v>11.63003680603022</v>
       </c>
       <c r="D226" t="n">
-        <v>11.21911585216062</v>
+        <v>11.21911492070173</v>
       </c>
       <c r="E226" t="n">
-        <v>11.37201677715557</v>
+        <v>11.37201583300219</v>
       </c>
       <c r="F226" t="n">
         <v>8537100</v>
@@ -4972,16 +4972,16 @@
         <v>44586</v>
       </c>
       <c r="B228" t="n">
-        <v>11.75426864624023</v>
+        <v>11.75426959991455</v>
       </c>
       <c r="C228" t="n">
-        <v>11.8880564845101</v>
+        <v>11.8880574490392</v>
       </c>
       <c r="D228" t="n">
-        <v>10.98020666346776</v>
+        <v>10.98020755433911</v>
       </c>
       <c r="E228" t="n">
-        <v>11.42935376239404</v>
+        <v>11.42935468970662</v>
       </c>
       <c r="F228" t="n">
         <v>40426700</v>
@@ -5032,16 +5032,16 @@
         <v>44589</v>
       </c>
       <c r="B231" t="n">
-        <v>11.83072090148926</v>
+        <v>11.83071994781494</v>
       </c>
       <c r="C231" t="n">
-        <v>12.04096013682132</v>
+        <v>12.04095916619962</v>
       </c>
       <c r="D231" t="n">
-        <v>11.45802419949534</v>
+        <v>11.4580232758641</v>
       </c>
       <c r="E231" t="n">
-        <v>11.9453965994809</v>
+        <v>11.94539563656258</v>
       </c>
       <c r="F231" t="n">
         <v>14924100</v>
@@ -5092,16 +5092,16 @@
         <v>44594</v>
       </c>
       <c r="B234" t="n">
-        <v>11.94539546966553</v>
+        <v>11.94539451599121</v>
       </c>
       <c r="C234" t="n">
-        <v>12.2798669073607</v>
+        <v>12.27986592698347</v>
       </c>
       <c r="D234" t="n">
-        <v>11.81160671231519</v>
+        <v>11.81160576932205</v>
       </c>
       <c r="E234" t="n">
-        <v>12.02184592776248</v>
+        <v>12.02184496798465</v>
       </c>
       <c r="F234" t="n">
         <v>9442200</v>
@@ -5112,16 +5112,16 @@
         <v>44595</v>
       </c>
       <c r="B235" t="n">
-        <v>11.94539546966553</v>
+        <v>11.94539451599121</v>
       </c>
       <c r="C235" t="n">
-        <v>12.21297207300486</v>
+        <v>12.21297109796826</v>
       </c>
       <c r="D235" t="n">
-        <v>11.8976137055146</v>
+        <v>11.89761275565499</v>
       </c>
       <c r="E235" t="n">
-        <v>12.04095899796739</v>
+        <v>12.04095803666365</v>
       </c>
       <c r="F235" t="n">
         <v>8796800</v>
@@ -5152,16 +5152,16 @@
         <v>44599</v>
       </c>
       <c r="B237" t="n">
-        <v>12.20341682434082</v>
+        <v>12.20341777801514</v>
       </c>
       <c r="C237" t="n">
-        <v>12.60478128600524</v>
+        <v>12.60478227104545</v>
       </c>
       <c r="D237" t="n">
-        <v>12.20341682434082</v>
+        <v>12.20341777801514</v>
       </c>
       <c r="E237" t="n">
-        <v>12.29897944421849</v>
+        <v>12.29898040536085</v>
       </c>
       <c r="F237" t="n">
         <v>7212000</v>
@@ -5212,16 +5212,16 @@
         <v>44602</v>
       </c>
       <c r="B240" t="n">
-        <v>12.11740970611572</v>
+        <v>12.11741065979004</v>
       </c>
       <c r="C240" t="n">
-        <v>12.29897932000246</v>
+        <v>12.29898028796682</v>
       </c>
       <c r="D240" t="n">
-        <v>11.88805741573067</v>
+        <v>11.88805835135432</v>
       </c>
       <c r="E240" t="n">
-        <v>11.95495225146694</v>
+        <v>11.9549531923554</v>
       </c>
       <c r="F240" t="n">
         <v>4310600</v>
@@ -5232,16 +5232,16 @@
         <v>44603</v>
       </c>
       <c r="B241" t="n">
-        <v>11.79249477386475</v>
+        <v>11.79249382019043</v>
       </c>
       <c r="C241" t="n">
-        <v>12.2129723012564</v>
+        <v>12.21297131357752</v>
       </c>
       <c r="D241" t="n">
-        <v>11.74471300882081</v>
+        <v>11.74471205901066</v>
       </c>
       <c r="E241" t="n">
-        <v>12.18430360677458</v>
+        <v>12.18430262141418</v>
       </c>
       <c r="F241" t="n">
         <v>7316000</v>
@@ -5252,16 +5252,16 @@
         <v>44606</v>
       </c>
       <c r="B242" t="n">
-        <v>11.78293895721436</v>
+        <v>11.78293800354004</v>
       </c>
       <c r="C242" t="n">
-        <v>11.97406511768535</v>
+        <v>11.97406414854188</v>
       </c>
       <c r="D242" t="n">
-        <v>11.63959456470146</v>
+        <v>11.639593622629</v>
       </c>
       <c r="E242" t="n">
-        <v>11.79249549307826</v>
+        <v>11.79249453863047</v>
       </c>
       <c r="F242" t="n">
         <v>5445000</v>
@@ -5372,16 +5372,16 @@
         <v>44614</v>
       </c>
       <c r="B248" t="n">
-        <v>12.51877498626709</v>
+        <v>12.51877403259277</v>
       </c>
       <c r="C248" t="n">
-        <v>12.63345067496531</v>
+        <v>12.63344971255505</v>
       </c>
       <c r="D248" t="n">
-        <v>12.08874001444707</v>
+        <v>12.08873909353262</v>
       </c>
       <c r="E248" t="n">
-        <v>12.14607831447686</v>
+        <v>12.1460773891944</v>
       </c>
       <c r="F248" t="n">
         <v>15416600</v>
@@ -5392,16 +5392,16 @@
         <v>44615</v>
       </c>
       <c r="B249" t="n">
-        <v>12.73856735229492</v>
+        <v>12.73856830596924</v>
       </c>
       <c r="C249" t="n">
-        <v>12.87235608545085</v>
+        <v>12.87235704914128</v>
       </c>
       <c r="D249" t="n">
-        <v>12.5187725528543</v>
+        <v>12.51877349007365</v>
       </c>
       <c r="E249" t="n">
-        <v>12.5187725528543</v>
+        <v>12.51877349007365</v>
       </c>
       <c r="F249" t="n">
         <v>5598100</v>
@@ -5452,16 +5452,16 @@
         <v>44622</v>
       </c>
       <c r="B252" t="n">
-        <v>12.68123245239258</v>
+        <v>12.68123340606689</v>
       </c>
       <c r="C252" t="n">
-        <v>12.95836559486294</v>
+        <v>12.95836656937867</v>
       </c>
       <c r="D252" t="n">
-        <v>12.64300631142708</v>
+        <v>12.64300726222665</v>
       </c>
       <c r="E252" t="n">
-        <v>12.86280206517191</v>
+        <v>12.86280303250091</v>
       </c>
       <c r="F252" t="n">
         <v>4196000</v>
@@ -5532,16 +5532,16 @@
         <v>44628</v>
       </c>
       <c r="B256" t="n">
-        <v>11.75426864624023</v>
+        <v>11.75426959991455</v>
       </c>
       <c r="C256" t="n">
-        <v>11.99317654184934</v>
+        <v>11.99317751490728</v>
       </c>
       <c r="D256" t="n">
-        <v>11.52491728518221</v>
+        <v>11.52491822024826</v>
       </c>
       <c r="E256" t="n">
-        <v>11.74471211168916</v>
+        <v>11.74471306458811</v>
       </c>
       <c r="F256" t="n">
         <v>10151100</v>
@@ -5552,16 +5552,16 @@
         <v>44629</v>
       </c>
       <c r="B257" t="n">
-        <v>12.80546379089355</v>
+        <v>12.80546283721924</v>
       </c>
       <c r="C257" t="n">
-        <v>13.03481608034201</v>
+        <v>13.0348151095869</v>
       </c>
       <c r="D257" t="n">
-        <v>11.75426951898038</v>
+        <v>11.75426864359272</v>
       </c>
       <c r="E257" t="n">
-        <v>11.89761390244447</v>
+        <v>11.89761301638138</v>
       </c>
       <c r="F257" t="n">
         <v>14771600</v>
@@ -5612,16 +5612,16 @@
         <v>44634</v>
       </c>
       <c r="B260" t="n">
-        <v>12.51877498626709</v>
+        <v>12.51877403259277</v>
       </c>
       <c r="C260" t="n">
-        <v>12.74812636366353</v>
+        <v>12.74812539251733</v>
       </c>
       <c r="D260" t="n">
-        <v>12.38498622710516</v>
+        <v>12.3849852836228</v>
       </c>
       <c r="E260" t="n">
-        <v>12.43276799190309</v>
+        <v>12.43276704478074</v>
       </c>
       <c r="F260" t="n">
         <v>4274300</v>
@@ -5672,16 +5672,16 @@
         <v>44637</v>
       </c>
       <c r="B263" t="n">
-        <v>13.12082290649414</v>
+        <v>13.12082195281982</v>
       </c>
       <c r="C263" t="n">
-        <v>13.24505513783225</v>
+        <v>13.24505417512824</v>
       </c>
       <c r="D263" t="n">
-        <v>12.87235935517934</v>
+        <v>12.87235841956435</v>
       </c>
       <c r="E263" t="n">
-        <v>13.0921542104504</v>
+        <v>13.09215325885984</v>
       </c>
       <c r="F263" t="n">
         <v>6159800</v>
@@ -5712,16 +5712,16 @@
         <v>44641</v>
       </c>
       <c r="B265" t="n">
-        <v>13.5604133605957</v>
+        <v>13.56041240692139</v>
       </c>
       <c r="C265" t="n">
-        <v>13.62730819901854</v>
+        <v>13.62730724063966</v>
       </c>
       <c r="D265" t="n">
-        <v>13.18771758255467</v>
+        <v>13.18771665509124</v>
       </c>
       <c r="E265" t="n">
-        <v>13.58908296764609</v>
+        <v>13.58908201195551</v>
       </c>
       <c r="F265" t="n">
         <v>3916100</v>
@@ -5772,16 +5772,16 @@
         <v>44644</v>
       </c>
       <c r="B268" t="n">
-        <v>14.63071918487549</v>
+        <v>14.6307201385498</v>
       </c>
       <c r="C268" t="n">
-        <v>14.7453948595791</v>
+        <v>14.74539582072832</v>
       </c>
       <c r="D268" t="n">
-        <v>14.35358607650145</v>
+        <v>14.35358701211139</v>
       </c>
       <c r="E268" t="n">
-        <v>14.39181130140265</v>
+        <v>14.39181223950423</v>
       </c>
       <c r="F268" t="n">
         <v>7986800</v>
@@ -5792,16 +5792,16 @@
         <v>44645</v>
       </c>
       <c r="B269" t="n">
-        <v>15.13720512390137</v>
+        <v>15.13720607757568</v>
       </c>
       <c r="C269" t="n">
-        <v>15.24232427482575</v>
+        <v>15.24232523512279</v>
       </c>
       <c r="D269" t="n">
-        <v>14.64027624019771</v>
+        <v>14.64027716256451</v>
       </c>
       <c r="E269" t="n">
-        <v>14.71672669748114</v>
+        <v>14.71672762466447</v>
       </c>
       <c r="F269" t="n">
         <v>8426200</v>
@@ -5852,16 +5852,16 @@
         <v>44650</v>
       </c>
       <c r="B272" t="n">
-        <v>15.45256423950195</v>
+        <v>15.45256328582764</v>
       </c>
       <c r="C272" t="n">
-        <v>15.82526000904275</v>
+        <v>15.82525903236704</v>
       </c>
       <c r="D272" t="n">
-        <v>15.3952268494317</v>
+        <v>15.39522589929603</v>
       </c>
       <c r="E272" t="n">
-        <v>15.51945816503771</v>
+        <v>15.51945720723495</v>
       </c>
       <c r="F272" t="n">
         <v>8944100</v>
@@ -5932,16 +5932,16 @@
         <v>44656</v>
       </c>
       <c r="B276" t="n">
-        <v>15.45256423950195</v>
+        <v>15.45256328582764</v>
       </c>
       <c r="C276" t="n">
-        <v>15.65324601610922</v>
+        <v>15.65324505004958</v>
       </c>
       <c r="D276" t="n">
-        <v>15.35700070756969</v>
+        <v>15.35699975979319</v>
       </c>
       <c r="E276" t="n">
-        <v>15.57679555510796</v>
+        <v>15.57679459376655</v>
       </c>
       <c r="F276" t="n">
         <v>10716200</v>
@@ -5972,16 +5972,16 @@
         <v>44658</v>
       </c>
       <c r="B278" t="n">
-        <v>15.38567066192627</v>
+        <v>15.38566970825195</v>
       </c>
       <c r="C278" t="n">
-        <v>15.52901505170514</v>
+        <v>15.52901408914568</v>
       </c>
       <c r="D278" t="n">
-        <v>15.25188189646763</v>
+        <v>15.25188095108615</v>
       </c>
       <c r="E278" t="n">
-        <v>15.366557590563</v>
+        <v>15.3665566380734</v>
       </c>
       <c r="F278" t="n">
         <v>6566700</v>
@@ -6012,16 +6012,16 @@
         <v>44662</v>
       </c>
       <c r="B280" t="n">
-        <v>15.29010677337646</v>
+        <v>15.29010581970215</v>
       </c>
       <c r="C280" t="n">
-        <v>15.4907885498701</v>
+        <v>15.49078758367887</v>
       </c>
       <c r="D280" t="n">
-        <v>15.21365631241849</v>
+        <v>15.21365536351254</v>
       </c>
       <c r="E280" t="n">
-        <v>15.38567030525462</v>
+        <v>15.38566934561982</v>
       </c>
       <c r="F280" t="n">
         <v>10289300</v>
@@ -6072,16 +6072,16 @@
         <v>44665</v>
       </c>
       <c r="B283" t="n">
-        <v>15.64369010925293</v>
+        <v>15.64369106292725</v>
       </c>
       <c r="C283" t="n">
-        <v>15.79659101958422</v>
+        <v>15.79659198257972</v>
       </c>
       <c r="D283" t="n">
-        <v>15.4812326641856</v>
+        <v>15.48123360795615</v>
       </c>
       <c r="E283" t="n">
-        <v>15.72014056441858</v>
+        <v>15.72014152275348</v>
       </c>
       <c r="F283" t="n">
         <v>4607000</v>
@@ -6112,16 +6112,16 @@
         <v>44670</v>
       </c>
       <c r="B285" t="n">
-        <v>15.61502075195312</v>
+        <v>15.61502170562744</v>
       </c>
       <c r="C285" t="n">
-        <v>15.77747819958926</v>
+        <v>15.77747916318553</v>
       </c>
       <c r="D285" t="n">
-        <v>15.18498670700624</v>
+        <v>15.18498763441659</v>
       </c>
       <c r="E285" t="n">
-        <v>15.32833199622942</v>
+        <v>15.32833293239446</v>
       </c>
       <c r="F285" t="n">
         <v>7756800</v>
@@ -6132,16 +6132,16 @@
         <v>44671</v>
       </c>
       <c r="B286" t="n">
-        <v>15.853928565979</v>
+        <v>15.85392951965332</v>
       </c>
       <c r="C286" t="n">
-        <v>16.33174437128826</v>
+        <v>16.33174535370502</v>
       </c>
       <c r="D286" t="n">
-        <v>15.72014072376366</v>
+        <v>15.72014166939012</v>
       </c>
       <c r="E286" t="n">
-        <v>15.74880850553972</v>
+        <v>15.74880945289066</v>
       </c>
       <c r="F286" t="n">
         <v>12326800</v>
@@ -6172,16 +6172,16 @@
         <v>44676</v>
       </c>
       <c r="B288" t="n">
-        <v>15.29966163635254</v>
+        <v>15.29966259002686</v>
       </c>
       <c r="C288" t="n">
-        <v>15.46211907596952</v>
+        <v>15.4621200397703</v>
       </c>
       <c r="D288" t="n">
-        <v>15.01297198341896</v>
+        <v>15.01297291922304</v>
       </c>
       <c r="E288" t="n">
-        <v>15.2805485675217</v>
+        <v>15.28054952000464</v>
       </c>
       <c r="F288" t="n">
         <v>6454900</v>
@@ -6192,16 +6192,16 @@
         <v>44677</v>
       </c>
       <c r="B289" t="n">
-        <v>15.12764835357666</v>
+        <v>15.12764739990234</v>
       </c>
       <c r="C289" t="n">
-        <v>15.30921887032133</v>
+        <v>15.30921790520048</v>
       </c>
       <c r="D289" t="n">
-        <v>15.02252920428749</v>
+        <v>15.02252825724008</v>
       </c>
       <c r="E289" t="n">
-        <v>15.21365534452294</v>
+        <v>15.21365438542659</v>
       </c>
       <c r="F289" t="n">
         <v>9387600</v>
@@ -6212,16 +6212,16 @@
         <v>44678</v>
       </c>
       <c r="B290" t="n">
-        <v>15.18498611450195</v>
+        <v>15.18498706817627</v>
       </c>
       <c r="C290" t="n">
-        <v>15.48123230491487</v>
+        <v>15.48123327719457</v>
       </c>
       <c r="D290" t="n">
-        <v>14.9651903774805</v>
+        <v>14.96519131735082</v>
       </c>
       <c r="E290" t="n">
-        <v>15.2901052600749</v>
+        <v>15.2901062203511</v>
       </c>
       <c r="F290" t="n">
         <v>7959000</v>
@@ -6232,16 +6232,16 @@
         <v>44679</v>
       </c>
       <c r="B291" t="n">
-        <v>14.84095764160156</v>
+        <v>14.8409595489502</v>
       </c>
       <c r="C291" t="n">
-        <v>15.38566824208486</v>
+        <v>15.38567021943929</v>
       </c>
       <c r="D291" t="n">
-        <v>14.84095764160156</v>
+        <v>14.8409595489502</v>
       </c>
       <c r="E291" t="n">
-        <v>15.32833085973584</v>
+        <v>15.3283328297213</v>
       </c>
       <c r="F291" t="n">
         <v>5384600</v>
@@ -6372,16 +6372,16 @@
         <v>44690</v>
       </c>
       <c r="B298" t="n">
-        <v>14.2196102142334</v>
+        <v>14.21961116790771</v>
       </c>
       <c r="C298" t="n">
-        <v>14.32558258668562</v>
+        <v>14.32558354746724</v>
       </c>
       <c r="D298" t="n">
-        <v>13.92095946458282</v>
+        <v>13.92096039822737</v>
       </c>
       <c r="E298" t="n">
-        <v>14.04620004225831</v>
+        <v>14.04620098430244</v>
       </c>
       <c r="F298" t="n">
         <v>11844800</v>
@@ -6512,16 +6512,16 @@
         <v>44699</v>
       </c>
       <c r="B305" t="n">
-        <v>14.83617782592773</v>
+        <v>14.83617687225342</v>
       </c>
       <c r="C305" t="n">
-        <v>15.2504350435133</v>
+        <v>15.25043406321039</v>
       </c>
       <c r="D305" t="n">
-        <v>14.81691053979462</v>
+        <v>14.81690958735881</v>
       </c>
       <c r="E305" t="n">
-        <v>15.23116775738018</v>
+        <v>15.23116677831579</v>
       </c>
       <c r="F305" t="n">
         <v>6842800</v>
@@ -6552,16 +6552,16 @@
         <v>44701</v>
       </c>
       <c r="B307" t="n">
-        <v>15.37567520141602</v>
+        <v>15.37567615509033</v>
       </c>
       <c r="C307" t="n">
-        <v>15.49128167135044</v>
+        <v>15.49128263219524</v>
       </c>
       <c r="D307" t="n">
-        <v>14.93251660728809</v>
+        <v>14.93251753347555</v>
       </c>
       <c r="E307" t="n">
-        <v>15.02885579161273</v>
+        <v>15.02885672377561</v>
       </c>
       <c r="F307" t="n">
         <v>8142900</v>
@@ -6572,16 +6572,16 @@
         <v>44704</v>
       </c>
       <c r="B308" t="n">
-        <v>15.28897190093994</v>
+        <v>15.28897285461426</v>
       </c>
       <c r="C308" t="n">
-        <v>15.63579135115902</v>
+        <v>15.63579232646676</v>
       </c>
       <c r="D308" t="n">
-        <v>15.17336541753358</v>
+        <v>15.17336636399676</v>
       </c>
       <c r="E308" t="n">
-        <v>15.52981988981818</v>
+        <v>15.52982085851578</v>
       </c>
       <c r="F308" t="n">
         <v>8474400</v>
@@ -6592,16 +6592,16 @@
         <v>44705</v>
       </c>
       <c r="B309" t="n">
-        <v>15.31787300109863</v>
+        <v>15.31787395477295</v>
       </c>
       <c r="C309" t="n">
-        <v>15.34677531047014</v>
+        <v>15.34677626594388</v>
       </c>
       <c r="D309" t="n">
-        <v>14.99995494808117</v>
+        <v>14.99995588196225</v>
       </c>
       <c r="E309" t="n">
-        <v>15.19263333552333</v>
+        <v>15.19263428140036</v>
       </c>
       <c r="F309" t="n">
         <v>5652100</v>
@@ -6612,16 +6612,16 @@
         <v>44706</v>
       </c>
       <c r="B310" t="n">
-        <v>15.14446258544922</v>
+        <v>15.14446353912354</v>
       </c>
       <c r="C310" t="n">
-        <v>15.44311332823613</v>
+        <v>15.44311430071703</v>
       </c>
       <c r="D310" t="n">
-        <v>14.94215102904739</v>
+        <v>14.94215196998178</v>
       </c>
       <c r="E310" t="n">
-        <v>15.16372987147109</v>
+        <v>15.16373082635871</v>
       </c>
       <c r="F310" t="n">
         <v>8129200</v>
@@ -6632,16 +6632,16 @@
         <v>44707</v>
       </c>
       <c r="B311" t="n">
-        <v>15.50091648101807</v>
+        <v>15.50091743469238</v>
       </c>
       <c r="C311" t="n">
-        <v>15.60688977236364</v>
+        <v>15.60689073255783</v>
       </c>
       <c r="D311" t="n">
-        <v>15.03848966141599</v>
+        <v>15.03849058664008</v>
       </c>
       <c r="E311" t="n">
-        <v>15.07702515315295</v>
+        <v>15.07702608074788</v>
       </c>
       <c r="F311" t="n">
         <v>6641000</v>
@@ -6652,16 +6652,16 @@
         <v>44708</v>
       </c>
       <c r="B312" t="n">
-        <v>15.22153472900391</v>
+        <v>15.22153377532959</v>
       </c>
       <c r="C312" t="n">
-        <v>15.51055139146295</v>
+        <v>15.51055041968089</v>
       </c>
       <c r="D312" t="n">
-        <v>15.13482963839033</v>
+        <v>15.13482869014834</v>
       </c>
       <c r="E312" t="n">
-        <v>15.43348040397503</v>
+        <v>15.43347943702168</v>
       </c>
       <c r="F312" t="n">
         <v>3408100</v>
@@ -6692,16 +6692,16 @@
         <v>44712</v>
       </c>
       <c r="B314" t="n">
-        <v>15.26006889343262</v>
+        <v>15.26006984710693</v>
       </c>
       <c r="C314" t="n">
-        <v>15.39494265040822</v>
+        <v>15.39494361251144</v>
       </c>
       <c r="D314" t="n">
-        <v>15.05775733921065</v>
+        <v>15.05775828024155</v>
       </c>
       <c r="E314" t="n">
-        <v>15.29860438381973</v>
+        <v>15.29860533990231</v>
       </c>
       <c r="F314" t="n">
         <v>5708500</v>
@@ -6812,16 +6812,16 @@
         <v>44720</v>
       </c>
       <c r="B320" t="n">
-        <v>15.35640811920166</v>
+        <v>15.35640907287598</v>
       </c>
       <c r="C320" t="n">
-        <v>15.74176396590114</v>
+        <v>15.74176494350709</v>
       </c>
       <c r="D320" t="n">
-        <v>14.99032139703716</v>
+        <v>14.9903223279765</v>
       </c>
       <c r="E320" t="n">
-        <v>15.00958868405489</v>
+        <v>15.00958961619079</v>
       </c>
       <c r="F320" t="n">
         <v>10420600</v>
@@ -6832,16 +6832,16 @@
         <v>44721</v>
       </c>
       <c r="B321" t="n">
-        <v>15.0288553237915</v>
+        <v>15.02885627746582</v>
       </c>
       <c r="C321" t="n">
-        <v>15.50091529101902</v>
+        <v>15.50091627464848</v>
       </c>
       <c r="D321" t="n">
-        <v>14.76874008546704</v>
+        <v>14.76874102263543</v>
       </c>
       <c r="E321" t="n">
-        <v>15.38530882468321</v>
+        <v>15.38530980097672</v>
       </c>
       <c r="F321" t="n">
         <v>9688900</v>
@@ -6872,16 +6872,16 @@
         <v>44725</v>
       </c>
       <c r="B323" t="n">
-        <v>14.03656673431396</v>
+        <v>14.03656578063965</v>
       </c>
       <c r="C323" t="n">
-        <v>14.35448478842786</v>
+        <v>14.35448381315351</v>
       </c>
       <c r="D323" t="n">
-        <v>13.89205886199261</v>
+        <v>13.89205791813647</v>
       </c>
       <c r="E323" t="n">
-        <v>14.25814651313317</v>
+        <v>14.25814554440425</v>
       </c>
       <c r="F323" t="n">
         <v>9104400</v>
@@ -6892,16 +6892,16 @@
         <v>44726</v>
       </c>
       <c r="B324" t="n">
-        <v>14.05583381652832</v>
+        <v>14.05583477020264</v>
       </c>
       <c r="C324" t="n">
-        <v>14.2099757796794</v>
+        <v>14.2099767438121</v>
       </c>
       <c r="D324" t="n">
-        <v>13.84388815781629</v>
+        <v>13.84388909711031</v>
       </c>
       <c r="E324" t="n">
-        <v>14.01729832574055</v>
+        <v>14.01729927680027</v>
       </c>
       <c r="F324" t="n">
         <v>10130900</v>
@@ -6952,16 +6952,16 @@
         <v>44732</v>
       </c>
       <c r="B327" t="n">
-        <v>15.31787300109863</v>
+        <v>15.31787395477295</v>
       </c>
       <c r="C327" t="n">
-        <v>15.50091728541696</v>
+        <v>15.50091825048741</v>
       </c>
       <c r="D327" t="n">
-        <v>14.83617887001052</v>
+        <v>14.83617979369507</v>
       </c>
       <c r="E327" t="n">
-        <v>15.09629414180225</v>
+        <v>15.0962950816813</v>
       </c>
       <c r="F327" t="n">
         <v>7611300</v>
@@ -6972,16 +6972,16 @@
         <v>44733</v>
       </c>
       <c r="B328" t="n">
-        <v>14.84581184387207</v>
+        <v>14.84581279754639</v>
       </c>
       <c r="C328" t="n">
-        <v>15.64542396715431</v>
+        <v>15.6454249721946</v>
       </c>
       <c r="D328" t="n">
-        <v>14.81691045545762</v>
+        <v>14.81691140727535</v>
       </c>
       <c r="E328" t="n">
-        <v>15.37567553151609</v>
+        <v>15.37567651922811</v>
       </c>
       <c r="F328" t="n">
         <v>9398400</v>
@@ -7032,16 +7032,16 @@
         <v>44736</v>
       </c>
       <c r="B331" t="n">
-        <v>14.42192268371582</v>
+        <v>14.4219217300415</v>
       </c>
       <c r="C331" t="n">
-        <v>14.86508132542095</v>
+        <v>14.86508034244202</v>
       </c>
       <c r="D331" t="n">
-        <v>14.25814660403618</v>
+        <v>14.25814566119184</v>
       </c>
       <c r="E331" t="n">
-        <v>14.86508132542095</v>
+        <v>14.86508034244202</v>
       </c>
       <c r="F331" t="n">
         <v>5803600</v>
@@ -7052,16 +7052,16 @@
         <v>44739</v>
       </c>
       <c r="B332" t="n">
-        <v>14.1618070602417</v>
+        <v>14.16180801391602</v>
       </c>
       <c r="C332" t="n">
-        <v>14.4989933145069</v>
+        <v>14.49899429088777</v>
       </c>
       <c r="D332" t="n">
-        <v>14.10400427987309</v>
+        <v>14.10400522965489</v>
       </c>
       <c r="E332" t="n">
-        <v>14.47972510854494</v>
+        <v>14.47972608362827</v>
       </c>
       <c r="F332" t="n">
         <v>8041800</v>
@@ -7092,16 +7092,16 @@
         <v>44741</v>
       </c>
       <c r="B334" t="n">
-        <v>13.85352420806885</v>
+        <v>13.85352325439453</v>
       </c>
       <c r="C334" t="n">
-        <v>14.18107638519945</v>
+        <v>14.1810754089765</v>
       </c>
       <c r="D334" t="n">
-        <v>13.59340891960912</v>
+        <v>13.5934079838411</v>
       </c>
       <c r="E334" t="n">
-        <v>14.18107638519945</v>
+        <v>14.1810754089765</v>
       </c>
       <c r="F334" t="n">
         <v>8408900</v>
@@ -7132,16 +7132,16 @@
         <v>44743</v>
       </c>
       <c r="B336" t="n">
-        <v>14.06546974182129</v>
+        <v>14.06546878814697</v>
       </c>
       <c r="C336" t="n">
-        <v>14.28704861287829</v>
+        <v>14.28704764418037</v>
       </c>
       <c r="D336" t="n">
-        <v>13.54524008938454</v>
+        <v>13.54523917098311</v>
       </c>
       <c r="E336" t="n">
-        <v>13.64157836946027</v>
+        <v>13.64157744452686</v>
       </c>
       <c r="F336" t="n">
         <v>10271400</v>
@@ -7152,16 +7152,16 @@
         <v>44746</v>
       </c>
       <c r="B337" t="n">
-        <v>13.87279033660889</v>
+        <v>13.8727912902832</v>
       </c>
       <c r="C337" t="n">
-        <v>14.14253970625061</v>
+        <v>14.14254067846864</v>
       </c>
       <c r="D337" t="n">
-        <v>13.76681796059447</v>
+        <v>13.76681890698379</v>
       </c>
       <c r="E337" t="n">
-        <v>13.95949542551097</v>
+        <v>13.95949638514576</v>
       </c>
       <c r="F337" t="n">
         <v>1980900</v>
@@ -7172,16 +7172,16 @@
         <v>44747</v>
       </c>
       <c r="B338" t="n">
-        <v>14.17144012451172</v>
+        <v>14.17144107818604</v>
       </c>
       <c r="C338" t="n">
-        <v>14.19070741030283</v>
+        <v>14.19070836527375</v>
       </c>
       <c r="D338" t="n">
-        <v>13.46816627734423</v>
+        <v>13.46816718369137</v>
       </c>
       <c r="E338" t="n">
-        <v>13.67047783132298</v>
+        <v>13.67047875128478</v>
       </c>
       <c r="F338" t="n">
         <v>7354200</v>
@@ -7312,16 +7312,16 @@
         <v>44756</v>
       </c>
       <c r="B345" t="n">
-        <v>14.75910758972168</v>
+        <v>14.75910663604736</v>
       </c>
       <c r="C345" t="n">
-        <v>14.99995465048742</v>
+        <v>14.99995368125053</v>
       </c>
       <c r="D345" t="n">
-        <v>14.51826052895594</v>
+        <v>14.5182595908442</v>
       </c>
       <c r="E345" t="n">
-        <v>14.52789463188864</v>
+        <v>14.52789369315438</v>
       </c>
       <c r="F345" t="n">
         <v>8175300</v>
@@ -7352,16 +7352,16 @@
         <v>44760</v>
       </c>
       <c r="B347" t="n">
-        <v>14.87471389770508</v>
+        <v>14.87471294403076</v>
       </c>
       <c r="C347" t="n">
-        <v>15.19263285952041</v>
+        <v>15.19263188546311</v>
       </c>
       <c r="D347" t="n">
-        <v>14.80727701546838</v>
+        <v>14.8072760661177</v>
       </c>
       <c r="E347" t="n">
-        <v>15.07702546317377</v>
+        <v>15.0770244965285</v>
       </c>
       <c r="F347" t="n">
         <v>3805700</v>
@@ -7412,16 +7412,16 @@
         <v>44763</v>
       </c>
       <c r="B350" t="n">
-        <v>14.84581184387207</v>
+        <v>14.84581279754639</v>
       </c>
       <c r="C350" t="n">
-        <v>14.95178513265602</v>
+        <v>14.95178609313791</v>
       </c>
       <c r="D350" t="n">
-        <v>14.6049647966483</v>
+        <v>14.60496573485093</v>
       </c>
       <c r="E350" t="n">
-        <v>14.7494735762377</v>
+        <v>14.74947452372338</v>
       </c>
       <c r="F350" t="n">
         <v>4662200</v>
@@ -7432,16 +7432,16 @@
         <v>44764</v>
       </c>
       <c r="B351" t="n">
-        <v>15.07702541351318</v>
+        <v>15.0770263671875</v>
       </c>
       <c r="C351" t="n">
-        <v>15.14446321428636</v>
+        <v>15.14446417222636</v>
       </c>
       <c r="D351" t="n">
-        <v>14.78800967987438</v>
+        <v>14.78801061526745</v>
       </c>
       <c r="E351" t="n">
-        <v>14.8458124590987</v>
+        <v>14.84581339814799</v>
       </c>
       <c r="F351" t="n">
         <v>3071000</v>
@@ -7472,16 +7472,16 @@
         <v>44768</v>
       </c>
       <c r="B353" t="n">
-        <v>14.95178604125977</v>
+        <v>14.95178508758545</v>
       </c>
       <c r="C353" t="n">
-        <v>15.03849021177204</v>
+        <v>15.03848925256745</v>
       </c>
       <c r="D353" t="n">
-        <v>14.76874175974149</v>
+        <v>14.76874081774235</v>
       </c>
       <c r="E353" t="n">
-        <v>14.82654545884164</v>
+        <v>14.82654451315558</v>
       </c>
       <c r="F353" t="n">
         <v>3874000</v>
@@ -7512,16 +7512,16 @@
         <v>44770</v>
       </c>
       <c r="B355" t="n">
-        <v>15.59725666046143</v>
+        <v>15.59725570678711</v>
       </c>
       <c r="C355" t="n">
-        <v>16.13675357904711</v>
+        <v>16.13675259238595</v>
       </c>
       <c r="D355" t="n">
-        <v>15.31787317917409</v>
+        <v>15.31787224258232</v>
       </c>
       <c r="E355" t="n">
-        <v>15.9151747171748</v>
+        <v>15.91517374406179</v>
       </c>
       <c r="F355" t="n">
         <v>25902000</v>
@@ -7612,16 +7612,16 @@
         <v>44777</v>
       </c>
       <c r="B360" t="n">
-        <v>16.21382331848145</v>
+        <v>16.21382522583008</v>
       </c>
       <c r="C360" t="n">
-        <v>16.42576806079203</v>
+        <v>16.42576999307324</v>
       </c>
       <c r="D360" t="n">
-        <v>15.92480759373818</v>
+        <v>15.92480946708782</v>
       </c>
       <c r="E360" t="n">
-        <v>16.02114494364116</v>
+        <v>16.02114682832365</v>
       </c>
       <c r="F360" t="n">
         <v>10048700</v>
@@ -7632,16 +7632,16 @@
         <v>44778</v>
       </c>
       <c r="B361" t="n">
-        <v>16.40650177001953</v>
+        <v>16.4064998626709</v>
       </c>
       <c r="C361" t="n">
-        <v>16.57027783814425</v>
+        <v>16.57027591175573</v>
       </c>
       <c r="D361" t="n">
-        <v>16.10785010386923</v>
+        <v>16.10784823124054</v>
       </c>
       <c r="E361" t="n">
-        <v>16.26199206945518</v>
+        <v>16.26199017890661</v>
       </c>
       <c r="F361" t="n">
         <v>6244900</v>
@@ -7652,16 +7652,16 @@
         <v>44781</v>
       </c>
       <c r="B362" t="n">
-        <v>16.68588447570801</v>
+        <v>16.68588256835938</v>
       </c>
       <c r="C362" t="n">
-        <v>16.88819696710841</v>
+        <v>16.88819503663362</v>
       </c>
       <c r="D362" t="n">
-        <v>16.26199312409735</v>
+        <v>16.26199126520336</v>
       </c>
       <c r="E362" t="n">
-        <v>16.53174250012546</v>
+        <v>16.53174061039666</v>
       </c>
       <c r="F362" t="n">
         <v>10381400</v>
@@ -7692,16 +7692,16 @@
         <v>44783</v>
       </c>
       <c r="B364" t="n">
-        <v>16.89782905578613</v>
+        <v>16.89783096313477</v>
       </c>
       <c r="C364" t="n">
-        <v>17.20611297019896</v>
+        <v>17.20611491234526</v>
       </c>
       <c r="D364" t="n">
-        <v>16.73405299656468</v>
+        <v>16.73405488542704</v>
       </c>
       <c r="E364" t="n">
-        <v>17.16757656213882</v>
+        <v>17.1675784999353</v>
       </c>
       <c r="F364" t="n">
         <v>6533000</v>
@@ -7732,16 +7732,16 @@
         <v>44785</v>
       </c>
       <c r="B366" t="n">
-        <v>17.34098815917969</v>
+        <v>17.34099006652832</v>
       </c>
       <c r="C366" t="n">
-        <v>17.6492720991179</v>
+        <v>17.64927404037492</v>
       </c>
       <c r="D366" t="n">
-        <v>17.06160469016241</v>
+        <v>17.06160656678144</v>
       </c>
       <c r="E366" t="n">
-        <v>17.16757798358513</v>
+        <v>17.16757987186025</v>
       </c>
       <c r="F366" t="n">
         <v>11729000</v>
@@ -7772,16 +7772,16 @@
         <v>44789</v>
       </c>
       <c r="B368" t="n">
-        <v>17.42769241333008</v>
+        <v>17.42769432067871</v>
       </c>
       <c r="C368" t="n">
-        <v>17.63000305016812</v>
+        <v>17.63000497965835</v>
       </c>
       <c r="D368" t="n">
-        <v>17.1964794694364</v>
+        <v>17.19648135148026</v>
       </c>
       <c r="E368" t="n">
-        <v>17.52403159933173</v>
+        <v>17.52403351722407</v>
       </c>
       <c r="F368" t="n">
         <v>4828900</v>
@@ -7792,16 +7792,16 @@
         <v>44790</v>
       </c>
       <c r="B369" t="n">
-        <v>17.27355003356934</v>
+        <v>17.27355194091797</v>
       </c>
       <c r="C369" t="n">
-        <v>17.52403117611753</v>
+        <v>17.52403311112434</v>
       </c>
       <c r="D369" t="n">
-        <v>17.16757674777512</v>
+        <v>17.16757864342216</v>
       </c>
       <c r="E369" t="n">
-        <v>17.31208460452908</v>
+        <v>17.31208651613271</v>
       </c>
       <c r="F369" t="n">
         <v>8548600</v>
@@ -7812,16 +7812,16 @@
         <v>44791</v>
       </c>
       <c r="B370" t="n">
-        <v>17.45659446716309</v>
+        <v>17.45659637451172</v>
       </c>
       <c r="C370" t="n">
-        <v>17.59146822309866</v>
+        <v>17.59147014518392</v>
       </c>
       <c r="D370" t="n">
-        <v>17.29281840459113</v>
+        <v>17.2928202940452</v>
       </c>
       <c r="E370" t="n">
-        <v>17.34098707813466</v>
+        <v>17.34098897285176</v>
       </c>
       <c r="F370" t="n">
         <v>13968800</v>
@@ -7892,16 +7892,16 @@
         <v>44797</v>
       </c>
       <c r="B374" t="n">
-        <v>17.14831161499023</v>
+        <v>17.14830780029297</v>
       </c>
       <c r="C374" t="n">
-        <v>17.26391902361024</v>
+        <v>17.26391518319573</v>
       </c>
       <c r="D374" t="n">
-        <v>16.99416962850851</v>
+        <v>16.99416584810063</v>
       </c>
       <c r="E374" t="n">
-        <v>17.14831161499023</v>
+        <v>17.14830780029297</v>
       </c>
       <c r="F374" t="n">
         <v>5807100</v>
@@ -7992,16 +7992,16 @@
         <v>44804</v>
       </c>
       <c r="B379" t="n">
-        <v>17.71671104431152</v>
+        <v>17.71670913696289</v>
       </c>
       <c r="C379" t="n">
-        <v>17.98646044192704</v>
+        <v>17.98645850553768</v>
       </c>
       <c r="D379" t="n">
-        <v>17.51440037423797</v>
+        <v>17.51439848866973</v>
       </c>
       <c r="E379" t="n">
-        <v>17.74561335611522</v>
+        <v>17.74561144565502</v>
       </c>
       <c r="F379" t="n">
         <v>9759800</v>
@@ -8072,16 +8072,16 @@
         <v>44810</v>
       </c>
       <c r="B383" t="n">
-        <v>18.75716781616211</v>
+        <v>18.75716590881348</v>
       </c>
       <c r="C383" t="n">
-        <v>18.83423879958045</v>
+        <v>18.83423688439475</v>
       </c>
       <c r="D383" t="n">
-        <v>18.33327832611984</v>
+        <v>18.33327646187499</v>
       </c>
       <c r="E383" t="n">
-        <v>18.68973093536071</v>
+        <v>18.68972903486949</v>
       </c>
       <c r="F383" t="n">
         <v>7863100</v>
@@ -8092,16 +8092,16 @@
         <v>44812</v>
       </c>
       <c r="B384" t="n">
-        <v>18.40071487426758</v>
+        <v>18.40071678161621</v>
       </c>
       <c r="C384" t="n">
-        <v>18.94984585088554</v>
+        <v>18.94984781515502</v>
       </c>
       <c r="D384" t="n">
-        <v>18.3429120971281</v>
+        <v>18.34291399848511</v>
       </c>
       <c r="E384" t="n">
-        <v>18.91130944111445</v>
+        <v>18.91131140138939</v>
       </c>
       <c r="F384" t="n">
         <v>6653400</v>
@@ -8212,16 +8212,16 @@
         <v>44820</v>
       </c>
       <c r="B390" t="n">
-        <v>17.24464797973633</v>
+        <v>17.24464988708496</v>
       </c>
       <c r="C390" t="n">
-        <v>17.62037061781912</v>
+        <v>17.62037256672464</v>
       </c>
       <c r="D390" t="n">
-        <v>17.06160371182508</v>
+        <v>17.06160559892805</v>
       </c>
       <c r="E390" t="n">
-        <v>17.49512912595248</v>
+        <v>17.49513106100564</v>
       </c>
       <c r="F390" t="n">
         <v>10140200</v>
@@ -8252,16 +8252,16 @@
         <v>44824</v>
       </c>
       <c r="B392" t="n">
-        <v>17.60110282897949</v>
+        <v>17.60110473632812</v>
       </c>
       <c r="C392" t="n">
-        <v>17.83231577613557</v>
+        <v>17.83231770853966</v>
       </c>
       <c r="D392" t="n">
-        <v>17.43732676172096</v>
+        <v>17.43732865132195</v>
       </c>
       <c r="E392" t="n">
-        <v>17.55293231654042</v>
+        <v>17.55293421866904</v>
       </c>
       <c r="F392" t="n">
         <v>8039000</v>
@@ -8312,16 +8312,16 @@
         <v>44827</v>
       </c>
       <c r="B395" t="n">
-        <v>17.1386775970459</v>
+        <v>17.13867950439453</v>
       </c>
       <c r="C395" t="n">
-        <v>17.42769333278163</v>
+        <v>17.42769527229457</v>
       </c>
       <c r="D395" t="n">
-        <v>16.96526742059757</v>
+        <v>16.96526930864753</v>
       </c>
       <c r="E395" t="n">
-        <v>17.10977528846543</v>
+        <v>17.10977719259755</v>
       </c>
       <c r="F395" t="n">
         <v>12048200</v>
@@ -8412,16 +8412,16 @@
         <v>44834</v>
       </c>
       <c r="B400" t="n">
-        <v>16.90746116638184</v>
+        <v>16.90746307373047</v>
       </c>
       <c r="C400" t="n">
-        <v>17.28318379147985</v>
+        <v>17.28318574121415</v>
       </c>
       <c r="D400" t="n">
-        <v>16.8592924942622</v>
+        <v>16.85929439617687</v>
       </c>
       <c r="E400" t="n">
-        <v>17.24464738377049</v>
+        <v>17.24464932915746</v>
       </c>
       <c r="F400" t="n">
         <v>11790900</v>
@@ -8472,16 +8472,16 @@
         <v>44839</v>
       </c>
       <c r="B403" t="n">
-        <v>17.45659446716309</v>
+        <v>17.45659637451172</v>
       </c>
       <c r="C403" t="n">
-        <v>17.74561018345848</v>
+        <v>17.74561212238566</v>
       </c>
       <c r="D403" t="n">
-        <v>17.14830870892632</v>
+        <v>17.14831058259092</v>
       </c>
       <c r="E403" t="n">
-        <v>17.4276921605267</v>
+        <v>17.4276940647174</v>
       </c>
       <c r="F403" t="n">
         <v>8852300</v>
@@ -8492,16 +8492,16 @@
         <v>44840</v>
       </c>
       <c r="B404" t="n">
-        <v>17.44696426391602</v>
+        <v>17.44696235656738</v>
       </c>
       <c r="C404" t="n">
-        <v>17.6396408386657</v>
+        <v>17.63963891025314</v>
       </c>
       <c r="D404" t="n">
-        <v>17.30245453595685</v>
+        <v>17.30245264440641</v>
       </c>
       <c r="E404" t="n">
-        <v>17.63000673430058</v>
+        <v>17.63000480694126</v>
       </c>
       <c r="F404" t="n">
         <v>6691000</v>
@@ -8512,16 +8512,16 @@
         <v>44841</v>
       </c>
       <c r="B405" t="n">
-        <v>17.49513244628906</v>
+        <v>17.49513053894043</v>
       </c>
       <c r="C405" t="n">
-        <v>17.68781085302832</v>
+        <v>17.68780892467357</v>
       </c>
       <c r="D405" t="n">
-        <v>17.32172224772722</v>
+        <v>17.32172035928406</v>
       </c>
       <c r="E405" t="n">
-        <v>17.44696376336298</v>
+        <v>17.44696186126578</v>
       </c>
       <c r="F405" t="n">
         <v>11897600</v>
@@ -8532,16 +8532,16 @@
         <v>44844</v>
       </c>
       <c r="B406" t="n">
-        <v>18.1020679473877</v>
+        <v>18.10206604003906</v>
       </c>
       <c r="C406" t="n">
-        <v>18.12133431784131</v>
+        <v>18.12133240846265</v>
       </c>
       <c r="D406" t="n">
-        <v>17.58183735727369</v>
+        <v>17.58183550473985</v>
       </c>
       <c r="E406" t="n">
-        <v>17.73597934600729</v>
+        <v>17.73597747723208</v>
       </c>
       <c r="F406" t="n">
         <v>7333800</v>
@@ -8572,16 +8572,16 @@
         <v>44847</v>
       </c>
       <c r="B408" t="n">
-        <v>18.75716781616211</v>
+        <v>18.75716590881348</v>
       </c>
       <c r="C408" t="n">
-        <v>18.99801486903407</v>
+        <v>18.99801293719457</v>
       </c>
       <c r="D408" t="n">
-        <v>17.93828930641119</v>
+        <v>17.93828748233136</v>
       </c>
       <c r="E408" t="n">
-        <v>18.17913635928316</v>
+        <v>18.17913451071245</v>
       </c>
       <c r="F408" t="n">
         <v>20665700</v>
@@ -8632,16 +8632,16 @@
         <v>44852</v>
       </c>
       <c r="B411" t="n">
-        <v>17.26391983032227</v>
+        <v>17.26391792297363</v>
       </c>
       <c r="C411" t="n">
-        <v>19.16179427601119</v>
+        <v>19.16179215898201</v>
       </c>
       <c r="D411" t="n">
-        <v>17.26391983032227</v>
+        <v>17.26391792297363</v>
       </c>
       <c r="E411" t="n">
-        <v>19.10399148775888</v>
+        <v>19.10398937711585</v>
       </c>
       <c r="F411" t="n">
         <v>33355700</v>
@@ -8652,16 +8652,16 @@
         <v>44853</v>
       </c>
       <c r="B412" t="n">
-        <v>17.67817687988281</v>
+        <v>17.67817497253418</v>
       </c>
       <c r="C412" t="n">
-        <v>17.97682675877506</v>
+        <v>17.97682481920425</v>
       </c>
       <c r="D412" t="n">
-        <v>17.28318779690735</v>
+        <v>17.2831859321752</v>
       </c>
       <c r="E412" t="n">
-        <v>17.4758643675563</v>
+        <v>17.47586248203574</v>
       </c>
       <c r="F412" t="n">
         <v>27062400</v>
@@ -8672,16 +8672,16 @@
         <v>44854</v>
       </c>
       <c r="B413" t="n">
-        <v>17.35062408447266</v>
+        <v>17.35062217712402</v>
       </c>
       <c r="C413" t="n">
-        <v>18.11169991144759</v>
+        <v>18.11169792043414</v>
       </c>
       <c r="D413" t="n">
-        <v>17.19648209831274</v>
+        <v>17.19648020790888</v>
       </c>
       <c r="E413" t="n">
-        <v>17.73597904987246</v>
+        <v>17.73597710016188</v>
       </c>
       <c r="F413" t="n">
         <v>15810900</v>
@@ -8692,16 +8692,16 @@
         <v>44855</v>
       </c>
       <c r="B414" t="n">
-        <v>17.91902351379395</v>
+        <v>17.91902160644531</v>
       </c>
       <c r="C414" t="n">
-        <v>18.25620980071688</v>
+        <v>18.25620785747724</v>
       </c>
       <c r="D414" t="n">
-        <v>17.34099014157141</v>
+        <v>17.34098829575019</v>
       </c>
       <c r="E414" t="n">
-        <v>17.53366854481807</v>
+        <v>17.53366667848764</v>
       </c>
       <c r="F414" t="n">
         <v>27105700</v>
@@ -8712,16 +8712,16 @@
         <v>44858</v>
       </c>
       <c r="B415" t="n">
-        <v>18.00572776794434</v>
+        <v>18.0057258605957</v>
       </c>
       <c r="C415" t="n">
-        <v>18.36218040847837</v>
+        <v>18.36217846337067</v>
       </c>
       <c r="D415" t="n">
-        <v>17.54329998932035</v>
+        <v>17.54329813095674</v>
       </c>
       <c r="E415" t="n">
-        <v>17.91902267429717</v>
+        <v>17.91902077613322</v>
       </c>
       <c r="F415" t="n">
         <v>16227000</v>
@@ -8732,16 +8732,16 @@
         <v>44859</v>
       </c>
       <c r="B416" t="n">
-        <v>17.04233741760254</v>
+        <v>17.04233932495117</v>
       </c>
       <c r="C416" t="n">
-        <v>18.00572559754023</v>
+        <v>18.00572761270958</v>
       </c>
       <c r="D416" t="n">
-        <v>16.80149037261812</v>
+        <v>16.80149225301157</v>
       </c>
       <c r="E416" t="n">
-        <v>18.00572559754023</v>
+        <v>18.00572761270958</v>
       </c>
       <c r="F416" t="n">
         <v>27810400</v>
@@ -8792,16 +8792,16 @@
         <v>44862</v>
       </c>
       <c r="B419" t="n">
-        <v>18.12133026123047</v>
+        <v>18.1213321685791</v>
       </c>
       <c r="C419" t="n">
-        <v>18.21766944200201</v>
+        <v>18.21767135949075</v>
       </c>
       <c r="D419" t="n">
-        <v>17.27354951297842</v>
+        <v>17.27355133109445</v>
       </c>
       <c r="E419" t="n">
-        <v>17.40842326354835</v>
+        <v>17.40842509586043</v>
       </c>
       <c r="F419" t="n">
         <v>12193800</v>
@@ -8872,16 +8872,16 @@
         <v>44869</v>
       </c>
       <c r="B423" t="n">
-        <v>19.79762840270996</v>
+        <v>19.79763031005859</v>
       </c>
       <c r="C423" t="n">
-        <v>19.98067269026426</v>
+        <v>19.9806746152478</v>
       </c>
       <c r="D423" t="n">
-        <v>19.60495184937882</v>
+        <v>19.60495373816456</v>
       </c>
       <c r="E423" t="n">
-        <v>19.81689660929827</v>
+        <v>19.81689851850324</v>
       </c>
       <c r="F423" t="n">
         <v>15655600</v>
@@ -8892,16 +8892,16 @@
         <v>44872</v>
       </c>
       <c r="B424" t="n">
-        <v>19.51824569702148</v>
+        <v>19.51824378967285</v>
       </c>
       <c r="C424" t="n">
-        <v>19.942137031352</v>
+        <v>19.94213508258015</v>
       </c>
       <c r="D424" t="n">
-        <v>19.14252487654513</v>
+        <v>19.14252300591243</v>
       </c>
       <c r="E424" t="n">
-        <v>19.69165587186202</v>
+        <v>19.69165394756752</v>
       </c>
       <c r="F424" t="n">
         <v>17754600</v>
@@ -8932,16 +8932,16 @@
         <v>44874</v>
       </c>
       <c r="B426" t="n">
-        <v>19.65312004089355</v>
+        <v>19.65312194824219</v>
       </c>
       <c r="C426" t="n">
-        <v>20.09627959384678</v>
+        <v>20.09628154420435</v>
       </c>
       <c r="D426" t="n">
-        <v>19.1328913385332</v>
+        <v>19.13289319539329</v>
       </c>
       <c r="E426" t="n">
-        <v>19.1328913385332</v>
+        <v>19.13289319539329</v>
       </c>
       <c r="F426" t="n">
         <v>19633400</v>
@@ -9072,16 +9072,16 @@
         <v>44886</v>
       </c>
       <c r="B433" t="n">
-        <v>18.98838233947754</v>
+        <v>18.98838043212891</v>
       </c>
       <c r="C433" t="n">
-        <v>19.02691875313779</v>
+        <v>19.02691684191824</v>
       </c>
       <c r="D433" t="n">
-        <v>18.58376102114898</v>
+        <v>18.58375915444382</v>
       </c>
       <c r="E433" t="n">
-        <v>18.60302739046176</v>
+        <v>18.60302552182134</v>
       </c>
       <c r="F433" t="n">
         <v>10461100</v>
@@ -9092,16 +9092,16 @@
         <v>44887</v>
       </c>
       <c r="B434" t="n">
-        <v>18.75716781616211</v>
+        <v>18.75716590881348</v>
       </c>
       <c r="C434" t="n">
-        <v>19.39300388874271</v>
+        <v>19.3930019167382</v>
       </c>
       <c r="D434" t="n">
-        <v>18.62229405455931</v>
+        <v>18.6222921609255</v>
       </c>
       <c r="E434" t="n">
-        <v>19.07508585245241</v>
+        <v>19.07508391277584</v>
       </c>
       <c r="F434" t="n">
         <v>9653000</v>
@@ -9132,16 +9132,16 @@
         <v>44889</v>
       </c>
       <c r="B436" t="n">
-        <v>19.08471870422363</v>
+        <v>19.08472061157227</v>
       </c>
       <c r="C436" t="n">
-        <v>19.26776296691409</v>
+        <v>19.26776489255638</v>
       </c>
       <c r="D436" t="n">
-        <v>18.58375826359684</v>
+        <v>18.58376012087891</v>
       </c>
       <c r="E436" t="n">
-        <v>18.67046150643225</v>
+        <v>18.67046337237954</v>
       </c>
       <c r="F436" t="n">
         <v>7241600</v>
@@ -9212,16 +9212,16 @@
         <v>44895</v>
       </c>
       <c r="B440" t="n">
-        <v>19.31593132019043</v>
+        <v>19.31593322753906</v>
       </c>
       <c r="C440" t="n">
-        <v>19.38337003297476</v>
+        <v>19.38337194698261</v>
       </c>
       <c r="D440" t="n">
-        <v>18.1598666637861</v>
+        <v>18.15986845697931</v>
       </c>
       <c r="E440" t="n">
-        <v>18.30437451614701</v>
+        <v>18.30437632360963</v>
       </c>
       <c r="F440" t="n">
         <v>128079800</v>
@@ -9252,16 +9252,16 @@
         <v>44897</v>
       </c>
       <c r="B442" t="n">
-        <v>19.78799438476562</v>
+        <v>19.78799629211426</v>
       </c>
       <c r="C442" t="n">
-        <v>19.97103681859475</v>
+        <v>19.97103874358669</v>
       </c>
       <c r="D442" t="n">
-        <v>19.01728272713333</v>
+        <v>19.01728456019369</v>
       </c>
       <c r="E442" t="n">
-        <v>19.11362191402701</v>
+        <v>19.11362375637343</v>
       </c>
       <c r="F442" t="n">
         <v>24428900</v>
@@ -9352,16 +9352,16 @@
         <v>44904</v>
       </c>
       <c r="B447" t="n">
-        <v>18.57412528991699</v>
+        <v>18.57412719726562</v>
       </c>
       <c r="C447" t="n">
-        <v>18.7571677262095</v>
+        <v>18.75716965235448</v>
       </c>
       <c r="D447" t="n">
-        <v>18.25620725515131</v>
+        <v>18.25620912985342</v>
       </c>
       <c r="E447" t="n">
-        <v>18.57412528991699</v>
+        <v>18.57412719726562</v>
       </c>
       <c r="F447" t="n">
         <v>14833900</v>
@@ -9372,16 +9372,16 @@
         <v>44907</v>
       </c>
       <c r="B448" t="n">
-        <v>18.2562084197998</v>
+        <v>18.25621032714844</v>
       </c>
       <c r="C448" t="n">
-        <v>18.6704638316658</v>
+        <v>18.67046578229448</v>
       </c>
       <c r="D448" t="n">
-        <v>17.87085164245525</v>
+        <v>17.87085350954307</v>
       </c>
       <c r="E448" t="n">
-        <v>18.45851907414013</v>
+        <v>18.45852100262552</v>
       </c>
       <c r="F448" t="n">
         <v>10851800</v>
@@ -9392,16 +9392,16 @@
         <v>44908</v>
       </c>
       <c r="B449" t="n">
-        <v>17.94792366027832</v>
+        <v>17.94792175292969</v>
       </c>
       <c r="C449" t="n">
-        <v>18.5259570219456</v>
+        <v>18.52595505316863</v>
       </c>
       <c r="D449" t="n">
-        <v>17.89975497910497</v>
+        <v>17.89975307687528</v>
       </c>
       <c r="E449" t="n">
-        <v>18.5259570219456</v>
+        <v>18.52595505316863</v>
       </c>
       <c r="F449" t="n">
         <v>13648600</v>
@@ -9412,16 +9412,16 @@
         <v>44909</v>
       </c>
       <c r="B450" t="n">
-        <v>18.3718147277832</v>
+        <v>18.37181282043457</v>
       </c>
       <c r="C450" t="n">
-        <v>18.46815392602494</v>
+        <v>18.46815200867444</v>
       </c>
       <c r="D450" t="n">
-        <v>17.64927349724626</v>
+        <v>17.64927166491134</v>
       </c>
       <c r="E450" t="n">
-        <v>17.86122010088155</v>
+        <v>17.86121824654248</v>
       </c>
       <c r="F450" t="n">
         <v>10673700</v>
@@ -9472,16 +9472,16 @@
         <v>44914</v>
       </c>
       <c r="B453" t="n">
-        <v>18.8342399597168</v>
+        <v>18.83423805236816</v>
       </c>
       <c r="C453" t="n">
-        <v>18.90167868218942</v>
+        <v>18.90167676801125</v>
       </c>
       <c r="D453" t="n">
-        <v>18.13096696301515</v>
+        <v>18.13096512688717</v>
       </c>
       <c r="E453" t="n">
-        <v>18.1502351694359</v>
+        <v>18.15023333135662</v>
       </c>
       <c r="F453" t="n">
         <v>7150400</v>
@@ -9492,16 +9492,16 @@
         <v>44915</v>
       </c>
       <c r="B454" t="n">
-        <v>19.26776504516602</v>
+        <v>19.26776313781738</v>
       </c>
       <c r="C454" t="n">
-        <v>19.66275408159054</v>
+        <v>19.66275213514127</v>
       </c>
       <c r="D454" t="n">
-        <v>18.86314190571684</v>
+        <v>18.86314003842253</v>
       </c>
       <c r="E454" t="n">
-        <v>18.91131058332285</v>
+        <v>18.91130871126024</v>
       </c>
       <c r="F454" t="n">
         <v>10658900</v>
@@ -9532,16 +9532,16 @@
         <v>44917</v>
       </c>
       <c r="B456" t="n">
-        <v>19.38337326049805</v>
+        <v>19.38337135314941</v>
       </c>
       <c r="C456" t="n">
-        <v>19.52788113692095</v>
+        <v>19.52787921535256</v>
       </c>
       <c r="D456" t="n">
-        <v>19.07508746327389</v>
+        <v>19.07508558626097</v>
       </c>
       <c r="E456" t="n">
-        <v>19.52788113692095</v>
+        <v>19.52787921535256</v>
       </c>
       <c r="F456" t="n">
         <v>7183700</v>
@@ -9572,16 +9572,16 @@
         <v>44921</v>
       </c>
       <c r="B458" t="n">
-        <v>19.2003288269043</v>
+        <v>19.20033073425293</v>
       </c>
       <c r="C458" t="n">
-        <v>19.3255684955305</v>
+        <v>19.32557041532036</v>
       </c>
       <c r="D458" t="n">
-        <v>18.84387435270808</v>
+        <v>18.84387622464675</v>
       </c>
       <c r="E458" t="n">
-        <v>19.07508732076077</v>
+        <v>19.07508921566799</v>
       </c>
       <c r="F458" t="n">
         <v>2369600</v>
@@ -9732,16 +9732,16 @@
         <v>44932</v>
       </c>
       <c r="B466" t="n">
-        <v>18.37796592712402</v>
+        <v>18.37796783447266</v>
       </c>
       <c r="C466" t="n">
-        <v>18.85092804187709</v>
+        <v>18.85092999831188</v>
       </c>
       <c r="D466" t="n">
-        <v>18.20422436639255</v>
+        <v>18.20422625570949</v>
       </c>
       <c r="E466" t="n">
-        <v>18.33935587317094</v>
+        <v>18.33935777651244</v>
       </c>
       <c r="F466" t="n">
         <v>4999100</v>
@@ -9812,16 +9812,16 @@
         <v>44938</v>
       </c>
       <c r="B470" t="n">
-        <v>19.30458641052246</v>
+        <v>19.30458450317383</v>
       </c>
       <c r="C470" t="n">
-        <v>19.7775485566568</v>
+        <v>19.77754660257815</v>
       </c>
       <c r="D470" t="n">
-        <v>18.84127677851684</v>
+        <v>18.84127491694453</v>
       </c>
       <c r="E470" t="n">
-        <v>19.09223662277709</v>
+        <v>19.09223473640923</v>
       </c>
       <c r="F470" t="n">
         <v>10710500</v>
@@ -9892,16 +9892,16 @@
         <v>44944</v>
       </c>
       <c r="B474" t="n">
-        <v>19.7003288269043</v>
+        <v>19.70032691955566</v>
       </c>
       <c r="C474" t="n">
-        <v>19.96094116600892</v>
+        <v>19.96093923342829</v>
       </c>
       <c r="D474" t="n">
-        <v>19.40110827517049</v>
+        <v>19.40110639679182</v>
       </c>
       <c r="E474" t="n">
-        <v>19.59415302037382</v>
+        <v>19.59415112330493</v>
       </c>
       <c r="F474" t="n">
         <v>9224700</v>
@@ -9932,16 +9932,16 @@
         <v>44946</v>
       </c>
       <c r="B476" t="n">
-        <v>19.30458641052246</v>
+        <v>19.30458450317383</v>
       </c>
       <c r="C476" t="n">
-        <v>19.43971792626689</v>
+        <v>19.43971600556688</v>
       </c>
       <c r="D476" t="n">
-        <v>19.03432153800477</v>
+        <v>19.03431965735908</v>
       </c>
       <c r="E476" t="n">
-        <v>19.39145719665212</v>
+        <v>19.3914552807204</v>
       </c>
       <c r="F476" t="n">
         <v>5910600</v>
@@ -9952,16 +9952,16 @@
         <v>44949</v>
       </c>
       <c r="B477" t="n">
-        <v>19.5651969909668</v>
+        <v>19.56519508361816</v>
       </c>
       <c r="C477" t="n">
-        <v>19.78719927266691</v>
+        <v>19.78719734367598</v>
       </c>
       <c r="D477" t="n">
-        <v>19.25632393103121</v>
+        <v>19.25632205379363</v>
       </c>
       <c r="E477" t="n">
-        <v>19.28527962975727</v>
+        <v>19.28527774969688</v>
       </c>
       <c r="F477" t="n">
         <v>3499900</v>
@@ -10032,16 +10032,16 @@
         <v>44953</v>
       </c>
       <c r="B481" t="n">
-        <v>20.28911972045898</v>
+        <v>20.28912162780762</v>
       </c>
       <c r="C481" t="n">
-        <v>20.51112201096608</v>
+        <v>20.5111239391848</v>
       </c>
       <c r="D481" t="n">
-        <v>20.10572564346113</v>
+        <v>20.10572753356917</v>
       </c>
       <c r="E481" t="n">
-        <v>20.21190145241179</v>
+        <v>20.21190335250126</v>
       </c>
       <c r="F481" t="n">
         <v>6872200</v>
@@ -10052,16 +10052,16 @@
         <v>44956</v>
       </c>
       <c r="B482" t="n">
-        <v>20.05746459960938</v>
+        <v>20.05746650695801</v>
       </c>
       <c r="C482" t="n">
-        <v>20.50146917361271</v>
+        <v>20.5014711231836</v>
       </c>
       <c r="D482" t="n">
-        <v>19.85476549854316</v>
+        <v>19.85476738661628</v>
       </c>
       <c r="E482" t="n">
-        <v>20.35668515343896</v>
+        <v>20.35668708924173</v>
       </c>
       <c r="F482" t="n">
         <v>14094800</v>
@@ -10092,16 +10092,16 @@
         <v>44958</v>
       </c>
       <c r="B484" t="n">
-        <v>18.94744873046875</v>
+        <v>18.94745063781738</v>
       </c>
       <c r="C484" t="n">
-        <v>19.09223458592427</v>
+        <v>19.0922365078478</v>
       </c>
       <c r="D484" t="n">
-        <v>18.60961997714889</v>
+        <v>18.60962185048992</v>
       </c>
       <c r="E484" t="n">
-        <v>18.85092728153658</v>
+        <v>18.85092917916886</v>
       </c>
       <c r="F484" t="n">
         <v>17126000</v>
@@ -10132,16 +10132,16 @@
         <v>44960</v>
       </c>
       <c r="B486" t="n">
-        <v>18.45518684387207</v>
+        <v>18.45518493652344</v>
       </c>
       <c r="C486" t="n">
-        <v>18.82197320394753</v>
+        <v>18.82197125869143</v>
       </c>
       <c r="D486" t="n">
-        <v>18.35866353615885</v>
+        <v>18.35866163878593</v>
       </c>
       <c r="E486" t="n">
-        <v>18.69649419264063</v>
+        <v>18.69649226035282</v>
       </c>
       <c r="F486" t="n">
         <v>6859200</v>
@@ -10152,16 +10152,16 @@
         <v>44963</v>
       </c>
       <c r="B487" t="n">
-        <v>18.55170631408691</v>
+        <v>18.55170822143555</v>
       </c>
       <c r="C487" t="n">
-        <v>18.66753463908353</v>
+        <v>18.66753655834077</v>
       </c>
       <c r="D487" t="n">
-        <v>18.24283323546763</v>
+        <v>18.24283511106023</v>
       </c>
       <c r="E487" t="n">
-        <v>18.45518485778996</v>
+        <v>18.45518675521498</v>
       </c>
       <c r="F487" t="n">
         <v>7136600</v>
@@ -10232,16 +10232,16 @@
         <v>44967</v>
       </c>
       <c r="B491" t="n">
-        <v>17.98221969604492</v>
+        <v>17.98221778869629</v>
       </c>
       <c r="C491" t="n">
-        <v>18.09804801338318</v>
+        <v>18.0980460937488</v>
       </c>
       <c r="D491" t="n">
-        <v>17.6250859128902</v>
+        <v>17.62508404342224</v>
       </c>
       <c r="E491" t="n">
-        <v>17.79882746838327</v>
+        <v>17.79882558048678</v>
       </c>
       <c r="F491" t="n">
         <v>6326900</v>
@@ -10292,16 +10292,16 @@
         <v>44972</v>
       </c>
       <c r="B494" t="n">
-        <v>18.55170631408691</v>
+        <v>18.55170822143555</v>
       </c>
       <c r="C494" t="n">
-        <v>18.7737104502447</v>
+        <v>18.77371238041815</v>
       </c>
       <c r="D494" t="n">
-        <v>17.7602185898678</v>
+        <v>17.76022041584155</v>
       </c>
       <c r="E494" t="n">
-        <v>17.80848115904505</v>
+        <v>17.80848298998079</v>
       </c>
       <c r="F494" t="n">
         <v>12677500</v>
@@ -10312,16 +10312,16 @@
         <v>44973</v>
       </c>
       <c r="B495" t="n">
-        <v>18.34900856018066</v>
+        <v>18.3490104675293</v>
       </c>
       <c r="C495" t="n">
-        <v>18.5517058222651</v>
+        <v>18.55170775068378</v>
       </c>
       <c r="D495" t="n">
-        <v>17.88569895453448</v>
+        <v>17.88570081372285</v>
       </c>
       <c r="E495" t="n">
-        <v>18.43587934136792</v>
+        <v>18.43588125774662</v>
       </c>
       <c r="F495" t="n">
         <v>33990600</v>
@@ -10332,16 +10332,16 @@
         <v>44974</v>
       </c>
       <c r="B496" t="n">
-        <v>18.45518684387207</v>
+        <v>18.45518493652344</v>
       </c>
       <c r="C496" t="n">
-        <v>18.6289265885211</v>
+        <v>18.62892466321642</v>
       </c>
       <c r="D496" t="n">
-        <v>18.01118036480286</v>
+        <v>18.01117850334242</v>
       </c>
       <c r="E496" t="n">
-        <v>18.2428351986972</v>
+        <v>18.24283331329517</v>
       </c>
       <c r="F496" t="n">
         <v>11362300</v>
@@ -10412,16 +10412,16 @@
         <v>44984</v>
       </c>
       <c r="B500" t="n">
-        <v>17.75056648254395</v>
+        <v>17.75056457519531</v>
       </c>
       <c r="C500" t="n">
-        <v>18.2524861673093</v>
+        <v>18.25248420602797</v>
       </c>
       <c r="D500" t="n">
-        <v>17.67334821112072</v>
+        <v>17.67334631206941</v>
       </c>
       <c r="E500" t="n">
-        <v>18.09804962446285</v>
+        <v>18.09804767977617</v>
       </c>
       <c r="F500" t="n">
         <v>7297600</v>
@@ -10432,16 +10432,16 @@
         <v>44985</v>
       </c>
       <c r="B501" t="n">
-        <v>17.50925827026367</v>
+        <v>17.5092601776123</v>
       </c>
       <c r="C501" t="n">
-        <v>17.81813134036312</v>
+        <v>17.81813328135845</v>
       </c>
       <c r="D501" t="n">
-        <v>17.23899525444101</v>
+        <v>17.23899713234889</v>
       </c>
       <c r="E501" t="n">
-        <v>17.74091307283826</v>
+        <v>17.74091500542191</v>
       </c>
       <c r="F501" t="n">
         <v>18187200</v>
@@ -10452,16 +10452,16 @@
         <v>44986</v>
       </c>
       <c r="B502" t="n">
-        <v>17.02664375305176</v>
+        <v>17.02664566040039</v>
       </c>
       <c r="C502" t="n">
-        <v>17.77952324727908</v>
+        <v>17.77952523896634</v>
       </c>
       <c r="D502" t="n">
-        <v>16.67916246735577</v>
+        <v>16.67916433577905</v>
       </c>
       <c r="E502" t="n">
-        <v>17.5092583886011</v>
+        <v>17.50926035001291</v>
       </c>
       <c r="F502" t="n">
         <v>19714300</v>
@@ -10492,16 +10492,16 @@
         <v>44988</v>
       </c>
       <c r="B504" t="n">
-        <v>16.92047119140625</v>
+        <v>16.92046928405762</v>
       </c>
       <c r="C504" t="n">
-        <v>17.22934428926396</v>
+        <v>17.22934234709782</v>
       </c>
       <c r="D504" t="n">
-        <v>16.72742458473074</v>
+        <v>16.72742269914315</v>
       </c>
       <c r="E504" t="n">
-        <v>16.92047119140625</v>
+        <v>16.92046928405762</v>
       </c>
       <c r="F504" t="n">
         <v>8320600</v>
@@ -10552,16 +10552,16 @@
         <v>44993</v>
       </c>
       <c r="B507" t="n">
-        <v>17.4127368927002</v>
+        <v>17.41273498535156</v>
       </c>
       <c r="C507" t="n">
-        <v>17.50925834675641</v>
+        <v>17.50925642883505</v>
       </c>
       <c r="D507" t="n">
-        <v>16.77568388155109</v>
+        <v>16.77568204398369</v>
       </c>
       <c r="E507" t="n">
-        <v>17.09420946661128</v>
+        <v>17.09420759415336</v>
       </c>
       <c r="F507" t="n">
         <v>19181400</v>
@@ -10572,16 +10572,16 @@
         <v>44994</v>
       </c>
       <c r="B508" t="n">
-        <v>17.24864959716797</v>
+        <v>17.24864768981934</v>
       </c>
       <c r="C508" t="n">
-        <v>17.80848255634869</v>
+        <v>17.80848058709395</v>
       </c>
       <c r="D508" t="n">
-        <v>17.18108199501829</v>
+        <v>17.18108009514125</v>
       </c>
       <c r="E508" t="n">
-        <v>17.36447609022389</v>
+        <v>17.36447417006721</v>
       </c>
       <c r="F508" t="n">
         <v>10746400</v>
@@ -10592,16 +10592,16 @@
         <v>44995</v>
       </c>
       <c r="B509" t="n">
-        <v>16.28341674804688</v>
+        <v>16.28341865539551</v>
       </c>
       <c r="C509" t="n">
-        <v>17.200383345925</v>
+        <v>17.20038536068198</v>
       </c>
       <c r="D509" t="n">
-        <v>16.10967520458848</v>
+        <v>16.10967709158599</v>
       </c>
       <c r="E509" t="n">
-        <v>17.1135125741958</v>
+        <v>17.11351457877723</v>
       </c>
       <c r="F509" t="n">
         <v>24597700</v>
@@ -10672,16 +10672,16 @@
         <v>45001</v>
       </c>
       <c r="B513" t="n">
-        <v>15.68497467041016</v>
+        <v>15.68497562408447</v>
       </c>
       <c r="C513" t="n">
-        <v>16.33167831507744</v>
+        <v>16.33167930807249</v>
       </c>
       <c r="D513" t="n">
-        <v>15.64636461829695</v>
+        <v>15.64636556962371</v>
       </c>
       <c r="E513" t="n">
-        <v>16.03245777531455</v>
+        <v>16.03245875011646</v>
       </c>
       <c r="F513" t="n">
         <v>11501700</v>
@@ -10692,16 +10692,16 @@
         <v>45002</v>
       </c>
       <c r="B514" t="n">
-        <v>15.36645030975342</v>
+        <v>15.3664493560791</v>
       </c>
       <c r="C514" t="n">
-        <v>15.6367151726564</v>
+        <v>15.63671420220887</v>
       </c>
       <c r="D514" t="n">
-        <v>15.26992701292887</v>
+        <v>15.26992606524499</v>
       </c>
       <c r="E514" t="n">
-        <v>15.34714528218276</v>
+        <v>15.34714432970655</v>
       </c>
       <c r="F514" t="n">
         <v>38654600</v>
@@ -10752,16 +10752,16 @@
         <v>45007</v>
       </c>
       <c r="B517" t="n">
-        <v>14.68113803863525</v>
+        <v>14.68113708496094</v>
       </c>
       <c r="C517" t="n">
-        <v>15.49192989666707</v>
+        <v>15.4919288903244</v>
       </c>
       <c r="D517" t="n">
-        <v>14.54600560203941</v>
+        <v>14.54600465714318</v>
       </c>
       <c r="E517" t="n">
-        <v>15.3857550025296</v>
+        <v>15.38575400308397</v>
       </c>
       <c r="F517" t="n">
         <v>42950800</v>
@@ -10772,16 +10772,16 @@
         <v>45008</v>
       </c>
       <c r="B518" t="n">
-        <v>14.71974658966064</v>
+        <v>14.71974754333496</v>
       </c>
       <c r="C518" t="n">
-        <v>15.01896807290302</v>
+        <v>15.01896904596353</v>
       </c>
       <c r="D518" t="n">
-        <v>14.25643697491495</v>
+        <v>14.256437898572</v>
       </c>
       <c r="E518" t="n">
-        <v>14.74870321045366</v>
+        <v>14.74870416600404</v>
       </c>
       <c r="F518" t="n">
         <v>25394300</v>
@@ -10792,16 +10792,16 @@
         <v>45009</v>
       </c>
       <c r="B519" t="n">
-        <v>14.43017673492432</v>
+        <v>14.43017768859863</v>
       </c>
       <c r="C519" t="n">
-        <v>14.95140047979436</v>
+        <v>14.95140146791577</v>
       </c>
       <c r="D519" t="n">
-        <v>14.01512879397227</v>
+        <v>14.01512972021653</v>
       </c>
       <c r="E519" t="n">
-        <v>14.74870230564966</v>
+        <v>14.74870328037497</v>
       </c>
       <c r="F519" t="n">
         <v>32819700</v>
@@ -10832,16 +10832,16 @@
         <v>45013</v>
       </c>
       <c r="B521" t="n">
-        <v>14.82592010498047</v>
+        <v>14.82592105865479</v>
       </c>
       <c r="C521" t="n">
-        <v>14.99000914178451</v>
+        <v>14.99001010601382</v>
       </c>
       <c r="D521" t="n">
-        <v>14.41087217704756</v>
+        <v>14.410873104024</v>
       </c>
       <c r="E521" t="n">
-        <v>14.5749612138516</v>
+        <v>14.57496215138304</v>
       </c>
       <c r="F521" t="n">
         <v>12984500</v>
@@ -10852,16 +10852,16 @@
         <v>45014</v>
       </c>
       <c r="B522" t="n">
-        <v>14.89348697662354</v>
+        <v>14.89348793029785</v>
       </c>
       <c r="C522" t="n">
-        <v>14.96105272663084</v>
+        <v>14.96105368463159</v>
       </c>
       <c r="D522" t="n">
-        <v>14.4205239650295</v>
+        <v>14.42052488841858</v>
       </c>
       <c r="E522" t="n">
-        <v>14.84522533211219</v>
+        <v>14.84522628269617</v>
       </c>
       <c r="F522" t="n">
         <v>19793200</v>
@@ -10872,16 +10872,16 @@
         <v>45015</v>
       </c>
       <c r="B523" t="n">
-        <v>15.41471099853516</v>
+        <v>15.41471195220947</v>
       </c>
       <c r="C523" t="n">
-        <v>15.73323564899215</v>
+        <v>15.73323662237289</v>
       </c>
       <c r="D523" t="n">
-        <v>14.82592058148598</v>
+        <v>14.82592149873313</v>
       </c>
       <c r="E523" t="n">
-        <v>15.15409866564172</v>
+        <v>15.15409960319252</v>
       </c>
       <c r="F523" t="n">
         <v>28286400</v>
@@ -10972,16 +10972,16 @@
         <v>45022</v>
       </c>
       <c r="B528" t="n">
-        <v>13.15607452392578</v>
+        <v>13.1560754776001</v>
       </c>
       <c r="C528" t="n">
-        <v>13.57112338766055</v>
+        <v>13.57112437142145</v>
       </c>
       <c r="D528" t="n">
-        <v>13.00163799430754</v>
+        <v>13.00163893678686</v>
       </c>
       <c r="E528" t="n">
-        <v>13.33946767271886</v>
+        <v>13.33946863968721</v>
       </c>
       <c r="F528" t="n">
         <v>26117400</v>
@@ -11012,16 +11012,16 @@
         <v>45027</v>
       </c>
       <c r="B530" t="n">
-        <v>14.19852256774902</v>
+        <v>14.19852352142334</v>
       </c>
       <c r="C530" t="n">
-        <v>14.3240024830388</v>
+        <v>14.32400344514125</v>
       </c>
       <c r="D530" t="n">
-        <v>13.51320975071368</v>
+        <v>13.51321065835749</v>
       </c>
       <c r="E530" t="n">
-        <v>13.52286226431621</v>
+        <v>13.52286317260835</v>
       </c>
       <c r="F530" t="n">
         <v>23105700</v>
@@ -11052,16 +11052,16 @@
         <v>45029</v>
       </c>
       <c r="B532" t="n">
-        <v>13.27190208435059</v>
+        <v>13.2719030380249</v>
       </c>
       <c r="C532" t="n">
-        <v>14.14060803439325</v>
+        <v>14.14060905048986</v>
       </c>
       <c r="D532" t="n">
-        <v>13.27190208435059</v>
+        <v>13.2719030380249</v>
       </c>
       <c r="E532" t="n">
-        <v>14.09234730867981</v>
+        <v>14.09234832130857</v>
       </c>
       <c r="F532" t="n">
         <v>20136100</v>
@@ -11072,16 +11072,16 @@
         <v>45030</v>
       </c>
       <c r="B533" t="n">
-        <v>12.76033115386963</v>
+        <v>12.76033020019531</v>
       </c>
       <c r="C533" t="n">
-        <v>13.29120743425609</v>
+        <v>13.29120644090545</v>
       </c>
       <c r="D533" t="n">
-        <v>12.59624210501355</v>
+        <v>12.59624116360283</v>
       </c>
       <c r="E533" t="n">
-        <v>13.20433665303648</v>
+        <v>13.20433566617834</v>
       </c>
       <c r="F533" t="n">
         <v>26653800</v>
@@ -11112,16 +11112,16 @@
         <v>45034</v>
       </c>
       <c r="B535" t="n">
-        <v>12.70241737365723</v>
+        <v>12.70241641998291</v>
       </c>
       <c r="C535" t="n">
-        <v>12.95337721125578</v>
+        <v>12.95337623873985</v>
       </c>
       <c r="D535" t="n">
-        <v>12.61554658983354</v>
+        <v>12.61554564268133</v>
       </c>
       <c r="E535" t="n">
-        <v>12.87615894130459</v>
+        <v>12.87615797458607</v>
       </c>
       <c r="F535" t="n">
         <v>12417000</v>
@@ -11172,16 +11172,16 @@
         <v>45040</v>
       </c>
       <c r="B538" t="n">
-        <v>12.45145702362061</v>
+        <v>12.45145797729492</v>
       </c>
       <c r="C538" t="n">
-        <v>12.88581092486324</v>
+        <v>12.88581191180532</v>
       </c>
       <c r="D538" t="n">
-        <v>12.35493465041118</v>
+        <v>12.35493559669272</v>
       </c>
       <c r="E538" t="n">
-        <v>12.54798031734438</v>
+        <v>12.54798127841155</v>
       </c>
       <c r="F538" t="n">
         <v>8287100</v>
@@ -11392,16 +11392,16 @@
         <v>45056</v>
       </c>
       <c r="B549" t="n">
-        <v>11.33929443359375</v>
+        <v>11.33929538726807</v>
       </c>
       <c r="C549" t="n">
-        <v>11.50405348917116</v>
+        <v>11.50405445670229</v>
       </c>
       <c r="D549" t="n">
-        <v>11.24237794013662</v>
+        <v>11.24237888565992</v>
       </c>
       <c r="E549" t="n">
-        <v>11.29083572472869</v>
+        <v>11.29083667432746</v>
       </c>
       <c r="F549" t="n">
         <v>11154600</v>
@@ -11532,16 +11532,16 @@
         <v>45065</v>
       </c>
       <c r="B556" t="n">
-        <v>11.45559501647949</v>
+        <v>11.45559597015381</v>
       </c>
       <c r="C556" t="n">
-        <v>11.70757956835444</v>
+        <v>11.70758054300638</v>
       </c>
       <c r="D556" t="n">
-        <v>10.74810099499177</v>
+        <v>10.74810188976746</v>
       </c>
       <c r="E556" t="n">
-        <v>11.01946847624856</v>
+        <v>11.01946939361549</v>
       </c>
       <c r="F556" t="n">
         <v>25040300</v>
@@ -11552,16 +11552,16 @@
         <v>45068</v>
       </c>
       <c r="B557" t="n">
-        <v>11.63973712921143</v>
+        <v>11.63973808288574</v>
       </c>
       <c r="C557" t="n">
-        <v>11.89172166376968</v>
+        <v>11.89172263808976</v>
       </c>
       <c r="D557" t="n">
-        <v>11.3683687423304</v>
+        <v>11.36836967377079</v>
       </c>
       <c r="E557" t="n">
-        <v>11.4846700077211</v>
+        <v>11.48467094869036</v>
       </c>
       <c r="F557" t="n">
         <v>13575900</v>
@@ -11592,16 +11592,16 @@
         <v>45070</v>
       </c>
       <c r="B559" t="n">
-        <v>10.86440086364746</v>
+        <v>10.86440181732178</v>
       </c>
       <c r="C559" t="n">
-        <v>11.05823477025899</v>
+        <v>11.058235740948</v>
       </c>
       <c r="D559" t="n">
-        <v>10.68025888343475</v>
+        <v>10.68025982094513</v>
       </c>
       <c r="E559" t="n">
-        <v>11.02915991533551</v>
+        <v>11.02916088347233</v>
       </c>
       <c r="F559" t="n">
         <v>30388700</v>
@@ -11632,16 +11632,16 @@
         <v>45072</v>
       </c>
       <c r="B561" t="n">
-        <v>11.04854297637939</v>
+        <v>11.04854393005371</v>
       </c>
       <c r="C561" t="n">
-        <v>11.38775301022289</v>
+        <v>11.38775399317671</v>
       </c>
       <c r="D561" t="n">
-        <v>10.77717550386839</v>
+        <v>10.77717643411915</v>
       </c>
       <c r="E561" t="n">
-        <v>11.38775301022289</v>
+        <v>11.38775399317671</v>
       </c>
       <c r="F561" t="n">
         <v>33081400</v>
@@ -11692,16 +11692,16 @@
         <v>45077</v>
       </c>
       <c r="B564" t="n">
-        <v>10.41858196258545</v>
+        <v>10.41858291625977</v>
       </c>
       <c r="C564" t="n">
-        <v>10.89347524417082</v>
+        <v>10.89347624131492</v>
       </c>
       <c r="D564" t="n">
-        <v>10.3604313309979</v>
+        <v>10.36043227934935</v>
       </c>
       <c r="E564" t="n">
-        <v>10.89347524417082</v>
+        <v>10.89347624131492</v>
       </c>
       <c r="F564" t="n">
         <v>32506900</v>
@@ -11712,16 +11712,16 @@
         <v>45078</v>
       </c>
       <c r="B565" t="n">
-        <v>10.67056751251221</v>
+        <v>10.67056655883789</v>
       </c>
       <c r="C565" t="n">
-        <v>10.70933429585259</v>
+        <v>10.70933333871352</v>
       </c>
       <c r="D565" t="n">
-        <v>10.21505711505793</v>
+        <v>10.21505620209453</v>
       </c>
       <c r="E565" t="n">
-        <v>10.51550037915067</v>
+        <v>10.51549943933537</v>
       </c>
       <c r="F565" t="n">
         <v>22690400</v>
@@ -11752,16 +11752,16 @@
         <v>45082</v>
       </c>
       <c r="B567" t="n">
-        <v>10.81594181060791</v>
+        <v>10.81594276428223</v>
       </c>
       <c r="C567" t="n">
-        <v>11.23268538972215</v>
+        <v>11.23268638014201</v>
       </c>
       <c r="D567" t="n">
-        <v>10.68025854244826</v>
+        <v>10.68025948415897</v>
       </c>
       <c r="E567" t="n">
-        <v>11.12607605128477</v>
+        <v>11.12607703230456</v>
       </c>
       <c r="F567" t="n">
         <v>24462400</v>
@@ -11792,16 +11792,16 @@
         <v>45084</v>
       </c>
       <c r="B569" t="n">
-        <v>12.3859977722168</v>
+        <v>12.38599872589111</v>
       </c>
       <c r="C569" t="n">
-        <v>13.10318458913605</v>
+        <v>13.103185598031</v>
       </c>
       <c r="D569" t="n">
-        <v>12.09524645987364</v>
+        <v>12.09524739116122</v>
       </c>
       <c r="E569" t="n">
-        <v>12.42476455224435</v>
+        <v>12.42476550890357</v>
       </c>
       <c r="F569" t="n">
         <v>35775900</v>
@@ -11832,16 +11832,16 @@
         <v>45089</v>
       </c>
       <c r="B571" t="n">
-        <v>13.29701900482178</v>
+        <v>13.29701995849609</v>
       </c>
       <c r="C571" t="n">
-        <v>13.52961969400545</v>
+        <v>13.5296206643621</v>
       </c>
       <c r="D571" t="n">
-        <v>12.72520828404051</v>
+        <v>12.72520919670404</v>
       </c>
       <c r="E571" t="n">
-        <v>12.80274184710173</v>
+        <v>12.80274276532604</v>
       </c>
       <c r="F571" t="n">
         <v>31653900</v>
@@ -11912,16 +11912,16 @@
         <v>45093</v>
       </c>
       <c r="B575" t="n">
-        <v>13.09349346160889</v>
+        <v>13.0934944152832</v>
       </c>
       <c r="C575" t="n">
-        <v>13.60715355936946</v>
+        <v>13.60715455045659</v>
       </c>
       <c r="D575" t="n">
-        <v>12.93842633204139</v>
+        <v>12.93842727442128</v>
       </c>
       <c r="E575" t="n">
-        <v>13.60715355936946</v>
+        <v>13.60715455045659</v>
       </c>
       <c r="F575" t="n">
         <v>29424500</v>
@@ -11952,16 +11952,16 @@
         <v>45097</v>
       </c>
       <c r="B577" t="n">
-        <v>12.91904163360596</v>
+        <v>12.91904258728027</v>
       </c>
       <c r="C577" t="n">
-        <v>13.00626711935004</v>
+        <v>13.00626807946328</v>
       </c>
       <c r="D577" t="n">
-        <v>12.6089073947585</v>
+        <v>12.60890832553893</v>
       </c>
       <c r="E577" t="n">
-        <v>12.77366644021444</v>
+        <v>12.77366738315727</v>
       </c>
       <c r="F577" t="n">
         <v>13900100</v>
@@ -11972,16 +11972,16 @@
         <v>45098</v>
       </c>
       <c r="B578" t="n">
-        <v>12.98688507080078</v>
+        <v>12.98688411712646</v>
       </c>
       <c r="C578" t="n">
-        <v>13.03534378341849</v>
+        <v>13.03534282618567</v>
       </c>
       <c r="D578" t="n">
-        <v>12.70582564674574</v>
+        <v>12.70582471371064</v>
       </c>
       <c r="E578" t="n">
-        <v>12.99657699817894</v>
+        <v>12.99657604379291</v>
       </c>
       <c r="F578" t="n">
         <v>18033300</v>
@@ -12032,16 +12032,16 @@
         <v>45103</v>
       </c>
       <c r="B581" t="n">
-        <v>13.47146987915039</v>
+        <v>13.47146892547607</v>
       </c>
       <c r="C581" t="n">
-        <v>14.14019805657877</v>
+        <v>14.14019705556374</v>
       </c>
       <c r="D581" t="n">
-        <v>13.35516952748307</v>
+        <v>13.35516858204191</v>
       </c>
       <c r="E581" t="n">
-        <v>13.85913864231449</v>
+        <v>13.85913766119627</v>
       </c>
       <c r="F581" t="n">
         <v>23023000</v>
@@ -12052,16 +12052,16 @@
         <v>45104</v>
       </c>
       <c r="B582" t="n">
-        <v>12.68644142150879</v>
+        <v>12.68644237518311</v>
       </c>
       <c r="C582" t="n">
-        <v>13.85913771066354</v>
+        <v>13.85913875249263</v>
       </c>
       <c r="D582" t="n">
-        <v>12.5604491512705</v>
+        <v>12.56045009547363</v>
       </c>
       <c r="E582" t="n">
-        <v>13.77191222170834</v>
+        <v>13.77191325698045</v>
       </c>
       <c r="F582" t="n">
         <v>64278500</v>
@@ -12112,16 +12112,16 @@
         <v>45107</v>
       </c>
       <c r="B585" t="n">
-        <v>13.32609367370605</v>
+        <v>13.32609462738037</v>
       </c>
       <c r="C585" t="n">
-        <v>13.48116079766187</v>
+        <v>13.48116176243347</v>
       </c>
       <c r="D585" t="n">
-        <v>12.96750071848999</v>
+        <v>12.96750164650181</v>
       </c>
       <c r="E585" t="n">
-        <v>13.08380106145685</v>
+        <v>13.08380199779164</v>
       </c>
       <c r="F585" t="n">
         <v>19641600</v>
@@ -12172,16 +12172,16 @@
         <v>45112</v>
       </c>
       <c r="B588" t="n">
-        <v>13.29701900482178</v>
+        <v>13.29701995849609</v>
       </c>
       <c r="C588" t="n">
-        <v>13.59746133061578</v>
+        <v>13.59746230583809</v>
       </c>
       <c r="D588" t="n">
-        <v>13.14195187869933</v>
+        <v>13.14195282125209</v>
       </c>
       <c r="E588" t="n">
-        <v>13.17102673377904</v>
+        <v>13.17102767841708</v>
       </c>
       <c r="F588" t="n">
         <v>9442900</v>
@@ -12192,16 +12192,16 @@
         <v>45113</v>
       </c>
       <c r="B589" t="n">
-        <v>13.17102718353271</v>
+        <v>13.1710262298584</v>
       </c>
       <c r="C589" t="n">
-        <v>13.32609431495027</v>
+        <v>13.32609335004801</v>
       </c>
       <c r="D589" t="n">
-        <v>13.03534298140585</v>
+        <v>13.03534203755601</v>
       </c>
       <c r="E589" t="n">
-        <v>13.22917689567779</v>
+        <v>13.22917593779303</v>
       </c>
       <c r="F589" t="n">
         <v>10770700</v>
@@ -12232,16 +12232,16 @@
         <v>45117</v>
       </c>
       <c r="B591" t="n">
-        <v>13.28732776641846</v>
+        <v>13.28732681274414</v>
       </c>
       <c r="C591" t="n">
-        <v>13.70407138265719</v>
+        <v>13.70407039907184</v>
       </c>
       <c r="D591" t="n">
-        <v>13.21948612629514</v>
+        <v>13.21948517749003</v>
       </c>
       <c r="E591" t="n">
-        <v>13.55869525118476</v>
+        <v>13.55869427803353</v>
       </c>
       <c r="F591" t="n">
         <v>9043800</v>
@@ -12332,16 +12332,16 @@
         <v>45124</v>
       </c>
       <c r="B596" t="n">
-        <v>12.42476558685303</v>
+        <v>12.42476463317871</v>
       </c>
       <c r="C596" t="n">
-        <v>12.44414944061737</v>
+        <v>12.44414848545523</v>
       </c>
       <c r="D596" t="n">
-        <v>11.97894711727638</v>
+        <v>11.97894619782127</v>
       </c>
       <c r="E596" t="n">
-        <v>12.11463132080772</v>
+        <v>12.11463039093804</v>
       </c>
       <c r="F596" t="n">
         <v>11160300</v>
@@ -12372,16 +12372,16 @@
         <v>45126</v>
       </c>
       <c r="B598" t="n">
-        <v>11.76573085784912</v>
+        <v>11.7657299041748</v>
       </c>
       <c r="C598" t="n">
-        <v>12.20185742227786</v>
+        <v>12.20185643325319</v>
       </c>
       <c r="D598" t="n">
-        <v>11.71727214529636</v>
+        <v>11.71727119554988</v>
       </c>
       <c r="E598" t="n">
-        <v>12.08555706671507</v>
+        <v>12.08555608711715</v>
       </c>
       <c r="F598" t="n">
         <v>18624600</v>
@@ -12432,16 +12432,16 @@
         <v>45131</v>
       </c>
       <c r="B601" t="n">
-        <v>12.3859977722168</v>
+        <v>12.38599872589111</v>
       </c>
       <c r="C601" t="n">
-        <v>12.54106489232703</v>
+        <v>12.54106585794092</v>
       </c>
       <c r="D601" t="n">
-        <v>12.03709675196877</v>
+        <v>12.03709767877904</v>
       </c>
       <c r="E601" t="n">
-        <v>12.192163872079</v>
+        <v>12.19216481082885</v>
       </c>
       <c r="F601" t="n">
         <v>10834500</v>
@@ -12472,16 +12472,16 @@
         <v>45133</v>
       </c>
       <c r="B603" t="n">
-        <v>12.47322463989258</v>
+        <v>12.47322368621826</v>
       </c>
       <c r="C603" t="n">
-        <v>12.75428405729101</v>
+        <v>12.75428308212753</v>
       </c>
       <c r="D603" t="n">
-        <v>12.19216522249415</v>
+        <v>12.19216429030899</v>
       </c>
       <c r="E603" t="n">
-        <v>12.52168335136259</v>
+        <v>12.52168239398323</v>
       </c>
       <c r="F603" t="n">
         <v>40141600</v>
@@ -12532,16 +12532,16 @@
         <v>45138</v>
       </c>
       <c r="B606" t="n">
-        <v>13.05472755432129</v>
+        <v>13.05472660064697</v>
       </c>
       <c r="C606" t="n">
-        <v>13.18071983660883</v>
+        <v>13.18071887373052</v>
       </c>
       <c r="D606" t="n">
-        <v>12.72520941976511</v>
+        <v>12.72520849016276</v>
       </c>
       <c r="E606" t="n">
-        <v>12.8996604143591</v>
+        <v>12.89965947201275</v>
       </c>
       <c r="F606" t="n">
         <v>32856600</v>
@@ -12632,16 +12632,16 @@
         <v>45145</v>
       </c>
       <c r="B611" t="n">
-        <v>13.4423942565918</v>
+        <v>13.44239521026611</v>
       </c>
       <c r="C611" t="n">
-        <v>13.85913785286578</v>
+        <v>13.85913883610609</v>
       </c>
       <c r="D611" t="n">
-        <v>13.384244546207</v>
+        <v>13.38424549575587</v>
       </c>
       <c r="E611" t="n">
-        <v>13.58777038109976</v>
+        <v>13.58777134508783</v>
       </c>
       <c r="F611" t="n">
         <v>31957200</v>
@@ -12792,16 +12792,16 @@
         <v>45155</v>
       </c>
       <c r="B619" t="n">
-        <v>12.60890865325928</v>
+        <v>12.60890769958496</v>
       </c>
       <c r="C619" t="n">
-        <v>12.81243449888516</v>
+        <v>12.81243352981718</v>
       </c>
       <c r="D619" t="n">
-        <v>12.45384151835823</v>
+        <v>12.45384057641241</v>
       </c>
       <c r="E619" t="n">
-        <v>12.67675029371023</v>
+        <v>12.67674933490471</v>
       </c>
       <c r="F619" t="n">
         <v>17965700</v>
@@ -12832,16 +12832,16 @@
         <v>45159</v>
       </c>
       <c r="B621" t="n">
-        <v>12.68644142150879</v>
+        <v>12.68644237518311</v>
       </c>
       <c r="C621" t="n">
-        <v>13.07410923433971</v>
+        <v>13.07411021715607</v>
       </c>
       <c r="D621" t="n">
-        <v>12.68644142150879</v>
+        <v>12.68644237518311</v>
       </c>
       <c r="E621" t="n">
-        <v>13.03534245305662</v>
+        <v>13.03534343295877</v>
       </c>
       <c r="F621" t="n">
         <v>19861900</v>
@@ -12852,16 +12852,16 @@
         <v>45160</v>
       </c>
       <c r="B622" t="n">
-        <v>12.57014083862305</v>
+        <v>12.57014179229736</v>
       </c>
       <c r="C622" t="n">
-        <v>12.86089215485373</v>
+        <v>12.86089313058684</v>
       </c>
       <c r="D622" t="n">
-        <v>12.40538179023475</v>
+        <v>12.40538273140909</v>
       </c>
       <c r="E622" t="n">
-        <v>12.84150830244431</v>
+        <v>12.84150927670679</v>
       </c>
       <c r="F622" t="n">
         <v>10646800</v>
@@ -12912,16 +12912,16 @@
         <v>45163</v>
       </c>
       <c r="B625" t="n">
-        <v>11.98863792419434</v>
+        <v>11.98863887786865</v>
       </c>
       <c r="C625" t="n">
-        <v>12.50229798541463</v>
+        <v>12.50229897994967</v>
       </c>
       <c r="D625" t="n">
-        <v>11.94017921858345</v>
+        <v>11.94018016840297</v>
       </c>
       <c r="E625" t="n">
-        <v>12.4053814984658</v>
+        <v>12.40538248529131</v>
       </c>
       <c r="F625" t="n">
         <v>23324500</v>
@@ -13032,16 +13032,16 @@
         <v>45173</v>
       </c>
       <c r="B631" t="n">
-        <v>11.87233829498291</v>
+        <v>11.87233924865723</v>
       </c>
       <c r="C631" t="n">
-        <v>11.96925571199809</v>
+        <v>11.96925667345753</v>
       </c>
       <c r="D631" t="n">
-        <v>11.48467047546817</v>
+        <v>11.48467139800213</v>
       </c>
       <c r="E631" t="n">
-        <v>11.4943614777513</v>
+        <v>11.49436240106371</v>
       </c>
       <c r="F631" t="n">
         <v>7669300</v>
@@ -13112,16 +13112,16 @@
         <v>45180</v>
       </c>
       <c r="B635" t="n">
-        <v>11.84326362609863</v>
+        <v>11.84326457977295</v>
       </c>
       <c r="C635" t="n">
-        <v>11.99833075634657</v>
+        <v>11.99833172250761</v>
       </c>
       <c r="D635" t="n">
-        <v>11.69788749828644</v>
+        <v>11.6978884402544</v>
       </c>
       <c r="E635" t="n">
-        <v>11.87233848195187</v>
+        <v>11.87233943796743</v>
       </c>
       <c r="F635" t="n">
         <v>12088600</v>
@@ -13132,16 +13132,16 @@
         <v>45181</v>
       </c>
       <c r="B636" t="n">
-        <v>12.47322463989258</v>
+        <v>12.47322368621826</v>
       </c>
       <c r="C636" t="n">
-        <v>12.57014206283261</v>
+        <v>12.5701411017482</v>
       </c>
       <c r="D636" t="n">
-        <v>11.85295516647709</v>
+        <v>11.85295426022717</v>
       </c>
       <c r="E636" t="n">
-        <v>11.85295516647709</v>
+        <v>11.85295426022717</v>
       </c>
       <c r="F636" t="n">
         <v>14965900</v>
@@ -13212,16 +13212,16 @@
         <v>45187</v>
       </c>
       <c r="B640" t="n">
-        <v>11.88203144073486</v>
+        <v>11.88203048706055</v>
       </c>
       <c r="C640" t="n">
-        <v>12.11463215631048</v>
+        <v>12.11463118396719</v>
       </c>
       <c r="D640" t="n">
-        <v>11.82388079970442</v>
+        <v>11.82387985069738</v>
       </c>
       <c r="E640" t="n">
-        <v>12.00802372607326</v>
+        <v>12.00802276228657</v>
       </c>
       <c r="F640" t="n">
         <v>10083800</v>
@@ -13252,16 +13252,16 @@
         <v>45189</v>
       </c>
       <c r="B642" t="n">
-        <v>11.76573085784912</v>
+        <v>11.7657299041748</v>
       </c>
       <c r="C642" t="n">
-        <v>11.85295543131642</v>
+        <v>11.85295447057209</v>
       </c>
       <c r="D642" t="n">
-        <v>11.45559565207528</v>
+        <v>11.45559472353905</v>
       </c>
       <c r="E642" t="n">
-        <v>11.72696407266152</v>
+        <v>11.72696312212946</v>
       </c>
       <c r="F642" t="n">
         <v>16179800</v>
@@ -13592,16 +13592,16 @@
         <v>45215</v>
       </c>
       <c r="B659" t="n">
-        <v>11.40713691711426</v>
+        <v>11.40713787078857</v>
       </c>
       <c r="C659" t="n">
-        <v>11.5331282653131</v>
+        <v>11.5331292295207</v>
       </c>
       <c r="D659" t="n">
-        <v>11.14546044560978</v>
+        <v>11.14546137740708</v>
       </c>
       <c r="E659" t="n">
-        <v>11.3586782085831</v>
+        <v>11.3586791582061</v>
       </c>
       <c r="F659" t="n">
         <v>7162600</v>
@@ -13632,16 +13632,16 @@
         <v>45217</v>
       </c>
       <c r="B661" t="n">
-        <v>10.48642539978027</v>
+        <v>10.48642444610596</v>
       </c>
       <c r="C661" t="n">
-        <v>11.16484554648926</v>
+        <v>11.16484453111691</v>
       </c>
       <c r="D661" t="n">
-        <v>10.44765861347745</v>
+        <v>10.44765766332873</v>
       </c>
       <c r="E661" t="n">
-        <v>11.16484554648926</v>
+        <v>11.16484453111691</v>
       </c>
       <c r="F661" t="n">
         <v>15312800</v>
@@ -13652,16 +13652,16 @@
         <v>45218</v>
       </c>
       <c r="B662" t="n">
-        <v>10.65118312835693</v>
+        <v>10.65118408203125</v>
       </c>
       <c r="C662" t="n">
-        <v>10.91285959607978</v>
+        <v>10.9128605731838</v>
       </c>
       <c r="D662" t="n">
-        <v>10.38950758490707</v>
+        <v>10.38950851515176</v>
       </c>
       <c r="E662" t="n">
-        <v>10.41858243989639</v>
+        <v>10.41858337274435</v>
       </c>
       <c r="F662" t="n">
         <v>8209500</v>
@@ -13672,16 +13672,16 @@
         <v>45219</v>
       </c>
       <c r="B663" t="n">
-        <v>10.7384090423584</v>
+        <v>10.73840808868408</v>
       </c>
       <c r="C663" t="n">
-        <v>10.74810096916253</v>
+        <v>10.74810001462748</v>
       </c>
       <c r="D663" t="n">
-        <v>10.5445751276408</v>
+        <v>10.5445741911808</v>
       </c>
       <c r="E663" t="n">
-        <v>10.58334191058432</v>
+        <v>10.58334097068145</v>
       </c>
       <c r="F663" t="n">
         <v>9727700</v>
@@ -13752,16 +13752,16 @@
         <v>45225</v>
       </c>
       <c r="B667" t="n">
-        <v>11.33929443359375</v>
+        <v>11.33929538726807</v>
       </c>
       <c r="C667" t="n">
-        <v>11.57189512701845</v>
+        <v>11.5718961002553</v>
       </c>
       <c r="D667" t="n">
-        <v>10.75779270003199</v>
+        <v>10.75779360479998</v>
       </c>
       <c r="E667" t="n">
-        <v>10.76748370238661</v>
+        <v>10.76748460796964</v>
       </c>
       <c r="F667" t="n">
         <v>21852600</v>
@@ -13772,16 +13772,16 @@
         <v>45226</v>
       </c>
       <c r="B668" t="n">
-        <v>10.78686809539795</v>
+        <v>10.78686714172363</v>
       </c>
       <c r="C668" t="n">
-        <v>11.45559535352417</v>
+        <v>11.45559434072722</v>
       </c>
       <c r="D668" t="n">
-        <v>10.74810131122068</v>
+        <v>10.74810036097376</v>
       </c>
       <c r="E668" t="n">
-        <v>11.33929500099235</v>
+        <v>11.3392939984776</v>
       </c>
       <c r="F668" t="n">
         <v>13292000</v>
@@ -13812,16 +13812,16 @@
         <v>45230</v>
       </c>
       <c r="B670" t="n">
-        <v>10.60272598266602</v>
+        <v>10.6027250289917</v>
       </c>
       <c r="C670" t="n">
-        <v>11.1357699987949</v>
+        <v>11.13576899717533</v>
       </c>
       <c r="D670" t="n">
-        <v>10.52519240842252</v>
+        <v>10.52519146172205</v>
       </c>
       <c r="E670" t="n">
-        <v>10.77717698685044</v>
+        <v>10.77717601748493</v>
       </c>
       <c r="F670" t="n">
         <v>15178600</v>
@@ -13832,16 +13832,16 @@
         <v>45231</v>
       </c>
       <c r="B671" t="n">
-        <v>10.7384090423584</v>
+        <v>10.73840808868408</v>
       </c>
       <c r="C671" t="n">
-        <v>10.84501746438483</v>
+        <v>10.84501650124265</v>
       </c>
       <c r="D671" t="n">
-        <v>10.35074121292319</v>
+        <v>10.35074029367752</v>
       </c>
       <c r="E671" t="n">
-        <v>10.66087547647136</v>
+        <v>10.66087452968277</v>
       </c>
       <c r="F671" t="n">
         <v>19375400</v>
@@ -13852,16 +13852,16 @@
         <v>45233</v>
       </c>
       <c r="B672" t="n">
-        <v>11.57189464569092</v>
+        <v>11.57189559936523</v>
       </c>
       <c r="C672" t="n">
-        <v>11.61066142631588</v>
+        <v>11.61066238318509</v>
       </c>
       <c r="D672" t="n">
-        <v>11.2423774725152</v>
+        <v>11.24237839903302</v>
       </c>
       <c r="E672" t="n">
-        <v>11.25206847446672</v>
+        <v>11.25206940178321</v>
       </c>
       <c r="F672" t="n">
         <v>16636800</v>
@@ -14012,16 +14012,16 @@
         <v>45246</v>
       </c>
       <c r="B680" t="n">
-        <v>12.92873477935791</v>
+        <v>12.92873382568359</v>
       </c>
       <c r="C680" t="n">
-        <v>13.13226062387078</v>
+        <v>13.1322596551836</v>
       </c>
       <c r="D680" t="n">
-        <v>12.16309011176626</v>
+        <v>12.16308921456891</v>
       </c>
       <c r="E680" t="n">
-        <v>12.40538273979239</v>
+        <v>12.40538182472258</v>
       </c>
       <c r="F680" t="n">
         <v>22426900</v>
@@ -14072,16 +14072,16 @@
         <v>45251</v>
       </c>
       <c r="B683" t="n">
-        <v>12.3859977722168</v>
+        <v>12.38599872589111</v>
       </c>
       <c r="C683" t="n">
-        <v>12.48291518442216</v>
+        <v>12.48291614555875</v>
       </c>
       <c r="D683" t="n">
-        <v>12.22123872603144</v>
+        <v>12.22123966701994</v>
       </c>
       <c r="E683" t="n">
-        <v>12.44414840439461</v>
+        <v>12.4441493625463</v>
       </c>
       <c r="F683" t="n">
         <v>9484000</v>
@@ -14092,16 +14092,16 @@
         <v>45252</v>
       </c>
       <c r="B684" t="n">
-        <v>12.57014083862305</v>
+        <v>12.57014179229736</v>
       </c>
       <c r="C684" t="n">
-        <v>12.72520796080663</v>
+        <v>12.72520892624561</v>
       </c>
       <c r="D684" t="n">
-        <v>12.39568986403004</v>
+        <v>12.39569080446907</v>
       </c>
       <c r="E684" t="n">
-        <v>12.48291535132654</v>
+        <v>12.48291629838322</v>
       </c>
       <c r="F684" t="n">
         <v>10478000</v>
@@ -14112,16 +14112,16 @@
         <v>45253</v>
       </c>
       <c r="B685" t="n">
-        <v>13.18071842193604</v>
+        <v>13.18071937561035</v>
       </c>
       <c r="C685" t="n">
-        <v>13.29701876442528</v>
+        <v>13.29701972651436</v>
       </c>
       <c r="D685" t="n">
-        <v>12.62829063977091</v>
+        <v>12.62829155347501</v>
       </c>
       <c r="E685" t="n">
-        <v>12.63798256604659</v>
+        <v>12.63798348045194</v>
       </c>
       <c r="F685" t="n">
         <v>8829200</v>
@@ -14172,16 +14172,16 @@
         <v>45258</v>
       </c>
       <c r="B688" t="n">
-        <v>13.10318660736084</v>
+        <v>13.10318565368652</v>
       </c>
       <c r="C688" t="n">
-        <v>13.48116253977923</v>
+        <v>13.48116155859512</v>
       </c>
       <c r="D688" t="n">
-        <v>12.98688532509186</v>
+        <v>12.98688437988217</v>
       </c>
       <c r="E688" t="n">
-        <v>13.14195339335947</v>
+        <v>13.14195243686364</v>
       </c>
       <c r="F688" t="n">
         <v>17069200</v>
@@ -14272,16 +14272,16 @@
         <v>45265</v>
       </c>
       <c r="B693" t="n">
-        <v>12.3084659576416</v>
+        <v>12.30846500396729</v>
       </c>
       <c r="C693" t="n">
-        <v>12.65736795164083</v>
+        <v>12.65736697093318</v>
       </c>
       <c r="D693" t="n">
-        <v>12.23093238659134</v>
+        <v>12.23093143892442</v>
       </c>
       <c r="E693" t="n">
-        <v>12.33754081571718</v>
+        <v>12.33753985979011</v>
       </c>
       <c r="F693" t="n">
         <v>12428700</v>
@@ -14292,16 +14292,16 @@
         <v>45266</v>
       </c>
       <c r="B694" t="n">
-        <v>11.87233829498291</v>
+        <v>11.87233924865723</v>
       </c>
       <c r="C694" t="n">
-        <v>12.62829100517314</v>
+        <v>12.62829201957119</v>
       </c>
       <c r="D694" t="n">
-        <v>11.84326343958755</v>
+        <v>11.84326439092636</v>
       </c>
       <c r="E694" t="n">
-        <v>12.43445709541577</v>
+        <v>12.43445809424364</v>
       </c>
       <c r="F694" t="n">
         <v>16842800</v>
@@ -14332,16 +14332,16 @@
         <v>45268</v>
       </c>
       <c r="B696" t="n">
-        <v>11.61066150665283</v>
+        <v>11.61066246032715</v>
       </c>
       <c r="C696" t="n">
-        <v>11.96925538525615</v>
+        <v>11.96925636838458</v>
       </c>
       <c r="D696" t="n">
-        <v>11.58158665205117</v>
+        <v>11.58158760333734</v>
       </c>
       <c r="E696" t="n">
-        <v>11.85295411830358</v>
+        <v>11.85295509187928</v>
       </c>
       <c r="F696" t="n">
         <v>16929900</v>
@@ -14352,16 +14352,16 @@
         <v>45271</v>
       </c>
       <c r="B697" t="n">
-        <v>11.54281997680664</v>
+        <v>11.54282093048096</v>
       </c>
       <c r="C697" t="n">
-        <v>11.64942931844344</v>
+        <v>11.64943028092588</v>
       </c>
       <c r="D697" t="n">
-        <v>11.40713670457504</v>
+        <v>11.40713764703913</v>
       </c>
       <c r="E697" t="n">
-        <v>11.63004546568294</v>
+        <v>11.63004642656387</v>
       </c>
       <c r="F697" t="n">
         <v>10547700</v>
@@ -14392,16 +14392,16 @@
         <v>45273</v>
       </c>
       <c r="B699" t="n">
-        <v>12.54106616973877</v>
+        <v>12.54106521606445</v>
       </c>
       <c r="C699" t="n">
-        <v>12.5992168078397</v>
+        <v>12.59921584974338</v>
       </c>
       <c r="D699" t="n">
-        <v>11.55251271620717</v>
+        <v>11.55251183770653</v>
       </c>
       <c r="E699" t="n">
-        <v>11.6203543570974</v>
+        <v>11.6203534734378</v>
       </c>
       <c r="F699" t="n">
         <v>24349900</v>
@@ -14432,16 +14432,16 @@
         <v>45275</v>
       </c>
       <c r="B701" t="n">
-        <v>12.47322463989258</v>
+        <v>12.47322368621826</v>
       </c>
       <c r="C701" t="n">
-        <v>12.93842697602245</v>
+        <v>12.93842598677983</v>
       </c>
       <c r="D701" t="n">
-        <v>12.26969879113695</v>
+        <v>12.26969785302376</v>
       </c>
       <c r="E701" t="n">
-        <v>12.93842697602245</v>
+        <v>12.93842598677983</v>
       </c>
       <c r="F701" t="n">
         <v>13438600</v>
@@ -14452,16 +14452,16 @@
         <v>45278</v>
       </c>
       <c r="B702" t="n">
-        <v>12.80274105072021</v>
+        <v>12.80274200439453</v>
       </c>
       <c r="C702" t="n">
-        <v>12.97719201889291</v>
+        <v>12.97719298556206</v>
       </c>
       <c r="D702" t="n">
-        <v>12.34723070286534</v>
+        <v>12.34723162260876</v>
       </c>
       <c r="E702" t="n">
-        <v>12.55075652430919</v>
+        <v>12.55075745921321</v>
       </c>
       <c r="F702" t="n">
         <v>9094600</v>
@@ -14472,16 +14472,16 @@
         <v>45279</v>
       </c>
       <c r="B703" t="n">
-        <v>12.98688507080078</v>
+        <v>12.98688411712646</v>
       </c>
       <c r="C703" t="n">
-        <v>13.0547276381748</v>
+        <v>13.05472667951856</v>
       </c>
       <c r="D703" t="n">
-        <v>12.87058471508212</v>
+        <v>12.87058376994816</v>
       </c>
       <c r="E703" t="n">
-        <v>12.98688507080078</v>
+        <v>12.98688411712646</v>
       </c>
       <c r="F703" t="n">
         <v>5248800</v>
@@ -14612,16 +14612,16 @@
         <v>45293</v>
       </c>
       <c r="B710" t="n">
-        <v>12.6185998916626</v>
+        <v>12.61860084533691</v>
       </c>
       <c r="C710" t="n">
-        <v>13.03534256289929</v>
+        <v>13.03534354806971</v>
       </c>
       <c r="D710" t="n">
-        <v>12.50229862256033</v>
+        <v>12.50229956744496</v>
       </c>
       <c r="E710" t="n">
-        <v>13.03534256289929</v>
+        <v>13.03534354806971</v>
       </c>
       <c r="F710" t="n">
         <v>7348700</v>
@@ -14632,16 +14632,16 @@
         <v>45294</v>
       </c>
       <c r="B711" t="n">
-        <v>12.54106616973877</v>
+        <v>12.54106521606445</v>
       </c>
       <c r="C711" t="n">
-        <v>12.71551715976854</v>
+        <v>12.71551619282825</v>
       </c>
       <c r="D711" t="n">
-        <v>12.31815739294343</v>
+        <v>12.31815645622002</v>
       </c>
       <c r="E711" t="n">
-        <v>12.62829166475365</v>
+        <v>12.62829070444635</v>
       </c>
       <c r="F711" t="n">
         <v>6830500</v>
@@ -14652,16 +14652,16 @@
         <v>45295</v>
       </c>
       <c r="B712" t="n">
-        <v>12.80274105072021</v>
+        <v>12.80274200439453</v>
       </c>
       <c r="C712" t="n">
-        <v>12.91904138807771</v>
+        <v>12.91904235041522</v>
       </c>
       <c r="D712" t="n">
-        <v>12.44414811279971</v>
+        <v>12.44414903976249</v>
       </c>
       <c r="E712" t="n">
-        <v>12.502297819342</v>
+        <v>12.50229875063634</v>
       </c>
       <c r="F712" t="n">
         <v>8604100</v>
@@ -14752,16 +14752,16 @@
         <v>45302</v>
       </c>
       <c r="B717" t="n">
-        <v>13.4423942565918</v>
+        <v>13.44239521026611</v>
       </c>
       <c r="C717" t="n">
-        <v>13.71376172835782</v>
+        <v>13.71376270128438</v>
       </c>
       <c r="D717" t="n">
-        <v>13.20979356650663</v>
+        <v>13.20979450367903</v>
       </c>
       <c r="E717" t="n">
-        <v>13.20979356650663</v>
+        <v>13.20979450367903</v>
       </c>
       <c r="F717" t="n">
         <v>14967000</v>
@@ -14812,16 +14812,16 @@
         <v>45307</v>
       </c>
       <c r="B720" t="n">
-        <v>14.03358840942383</v>
+        <v>14.03358745574951</v>
       </c>
       <c r="C720" t="n">
-        <v>14.30495681515323</v>
+        <v>14.30495584303765</v>
       </c>
       <c r="D720" t="n">
-        <v>13.93667191389734</v>
+        <v>13.93667096680914</v>
       </c>
       <c r="E720" t="n">
-        <v>14.30495681515323</v>
+        <v>14.30495584303765</v>
       </c>
       <c r="F720" t="n">
         <v>11210600</v>
@@ -14852,16 +14852,16 @@
         <v>45309</v>
       </c>
       <c r="B722" t="n">
-        <v>13.36486053466797</v>
+        <v>13.36486148834229</v>
       </c>
       <c r="C722" t="n">
-        <v>13.85913768843952</v>
+        <v>13.85913867738389</v>
       </c>
       <c r="D722" t="n">
-        <v>13.24856019100519</v>
+        <v>13.24856113638068</v>
       </c>
       <c r="E722" t="n">
-        <v>13.71376156565631</v>
+        <v>13.71376254422711</v>
       </c>
       <c r="F722" t="n">
         <v>8302800</v>
@@ -14912,16 +14912,16 @@
         <v>45314</v>
       </c>
       <c r="B725" t="n">
-        <v>13.21948623657227</v>
+        <v>13.21948528289795</v>
       </c>
       <c r="C725" t="n">
-        <v>13.4811617965687</v>
+        <v>13.4811608240167</v>
       </c>
       <c r="D725" t="n">
-        <v>13.18071945271083</v>
+        <v>13.18071850183321</v>
       </c>
       <c r="E725" t="n">
-        <v>13.24856109340008</v>
+        <v>13.24856013762826</v>
       </c>
       <c r="F725" t="n">
         <v>9537600</v>
@@ -15072,16 +15072,16 @@
         <v>45324</v>
       </c>
       <c r="B733" t="n">
-        <v>13.10318660736084</v>
+        <v>13.10318565368652</v>
       </c>
       <c r="C733" t="n">
-        <v>13.28732860978607</v>
+        <v>13.28732764270956</v>
       </c>
       <c r="D733" t="n">
-        <v>12.85120203623319</v>
+        <v>12.85120110089878</v>
       </c>
       <c r="E733" t="n">
-        <v>13.11287761065569</v>
+        <v>13.11287665627604</v>
       </c>
       <c r="F733" t="n">
         <v>9537000</v>
@@ -15112,16 +15112,16 @@
         <v>45328</v>
       </c>
       <c r="B735" t="n">
-        <v>13.36486053466797</v>
+        <v>13.36486148834229</v>
       </c>
       <c r="C735" t="n">
-        <v>13.4520860234833</v>
+        <v>13.45208698338175</v>
       </c>
       <c r="D735" t="n">
-        <v>12.96750079608522</v>
+        <v>12.9675017214052</v>
       </c>
       <c r="E735" t="n">
-        <v>13.05472628490055</v>
+        <v>13.05472721644466</v>
       </c>
       <c r="F735" t="n">
         <v>13604000</v>
@@ -15152,16 +15152,16 @@
         <v>45330</v>
       </c>
       <c r="B737" t="n">
-        <v>13.4036283493042</v>
+        <v>13.40362739562988</v>
       </c>
       <c r="C737" t="n">
-        <v>13.60715419747408</v>
+        <v>13.60715322931881</v>
       </c>
       <c r="D737" t="n">
-        <v>13.22917735822343</v>
+        <v>13.22917641696138</v>
       </c>
       <c r="E737" t="n">
-        <v>13.37455349221508</v>
+        <v>13.37455254060946</v>
       </c>
       <c r="F737" t="n">
         <v>12424500</v>
@@ -15192,16 +15192,16 @@
         <v>45336</v>
       </c>
       <c r="B739" t="n">
-        <v>12.7542839050293</v>
+        <v>12.75428295135498</v>
       </c>
       <c r="C739" t="n">
-        <v>12.9481178243223</v>
+        <v>12.94811685615447</v>
       </c>
       <c r="D739" t="n">
-        <v>12.67675033731209</v>
+        <v>12.67674938943519</v>
       </c>
       <c r="E739" t="n">
-        <v>12.85120132681232</v>
+        <v>12.85120036589121</v>
       </c>
       <c r="F739" t="n">
         <v>7875600</v>
@@ -15212,16 +15212,16 @@
         <v>45337</v>
       </c>
       <c r="B740" t="n">
-        <v>12.97719287872314</v>
+        <v>12.97719383239746</v>
       </c>
       <c r="C740" t="n">
-        <v>13.180718713652</v>
+        <v>13.18071968228313</v>
       </c>
       <c r="D740" t="n">
-        <v>12.65736669873108</v>
+        <v>12.65736762890185</v>
       </c>
       <c r="E740" t="n">
-        <v>12.80274189899184</v>
+        <v>12.80274283984602</v>
       </c>
       <c r="F740" t="n">
         <v>6962800</v>
@@ -15232,16 +15232,16 @@
         <v>45338</v>
       </c>
       <c r="B741" t="n">
-        <v>13.18071842193604</v>
+        <v>13.18071937561035</v>
       </c>
       <c r="C741" t="n">
-        <v>13.306709766428</v>
+        <v>13.30671072921826</v>
       </c>
       <c r="D741" t="n">
-        <v>12.84150839647101</v>
+        <v>12.84150932560221</v>
       </c>
       <c r="E741" t="n">
-        <v>13.05472615317111</v>
+        <v>13.05472709772942</v>
       </c>
       <c r="F741" t="n">
         <v>4964600</v>
@@ -15312,16 +15312,16 @@
         <v>45344</v>
       </c>
       <c r="B745" t="n">
-        <v>14.37279796600342</v>
+        <v>14.37279891967773</v>
       </c>
       <c r="C745" t="n">
-        <v>14.61509058299508</v>
+        <v>14.61509155274617</v>
       </c>
       <c r="D745" t="n">
-        <v>13.95605436901041</v>
+        <v>13.95605529503265</v>
       </c>
       <c r="E745" t="n">
-        <v>13.95605436901041</v>
+        <v>13.95605529503265</v>
       </c>
       <c r="F745" t="n">
         <v>21828500</v>
@@ -15332,16 +15332,16 @@
         <v>45345</v>
       </c>
       <c r="B746" t="n">
-        <v>14.26619052886963</v>
+        <v>14.26618957519531</v>
       </c>
       <c r="C746" t="n">
-        <v>14.46002445094536</v>
+        <v>14.46002348431353</v>
       </c>
       <c r="D746" t="n">
-        <v>13.98513111079155</v>
+        <v>13.98513017590566</v>
       </c>
       <c r="E746" t="n">
-        <v>14.46002445094536</v>
+        <v>14.46002348431353</v>
       </c>
       <c r="F746" t="n">
         <v>7821200</v>
@@ -15352,16 +15352,16 @@
         <v>45348</v>
       </c>
       <c r="B747" t="n">
-        <v>14.15958023071289</v>
+        <v>14.15958118438721</v>
       </c>
       <c r="C747" t="n">
-        <v>14.44063962997748</v>
+        <v>14.44064060258168</v>
       </c>
       <c r="D747" t="n">
-        <v>14.130505375416</v>
+        <v>14.13050632713207</v>
       </c>
       <c r="E747" t="n">
-        <v>14.32433928451693</v>
+        <v>14.32434024928807</v>
       </c>
       <c r="F747" t="n">
         <v>6009200</v>
@@ -15372,16 +15372,16 @@
         <v>45349</v>
       </c>
       <c r="B748" t="n">
-        <v>14.25649738311768</v>
+        <v>14.25649833679199</v>
       </c>
       <c r="C748" t="n">
-        <v>14.36310580007867</v>
+        <v>14.36310676088445</v>
       </c>
       <c r="D748" t="n">
-        <v>14.08204640602426</v>
+        <v>14.08204734802885</v>
       </c>
       <c r="E748" t="n">
-        <v>14.2661893094613</v>
+        <v>14.26619026378395</v>
       </c>
       <c r="F748" t="n">
         <v>8891500</v>
@@ -15452,16 +15452,16 @@
         <v>45355</v>
       </c>
       <c r="B752" t="n">
-        <v>13.59746074676514</v>
+        <v>13.59746170043945</v>
       </c>
       <c r="C752" t="n">
-        <v>13.77191171829877</v>
+        <v>13.77191268420841</v>
       </c>
       <c r="D752" t="n">
-        <v>13.48116040716703</v>
+        <v>13.48116135268448</v>
       </c>
       <c r="E752" t="n">
-        <v>13.67499430649721</v>
+        <v>13.67499526560944</v>
       </c>
       <c r="F752" t="n">
         <v>6926800</v>
@@ -15472,16 +15472,16 @@
         <v>45356</v>
       </c>
       <c r="B753" t="n">
-        <v>14.02389621734619</v>
+        <v>14.02389717102051</v>
       </c>
       <c r="C753" t="n">
-        <v>14.13050463066464</v>
+        <v>14.1305055915887</v>
       </c>
       <c r="D753" t="n">
-        <v>13.587769713787</v>
+        <v>13.58777063780318</v>
       </c>
       <c r="E753" t="n">
-        <v>13.64591942131599</v>
+        <v>13.64592034928656</v>
       </c>
       <c r="F753" t="n">
         <v>16007800</v>
@@ -15492,16 +15492,16 @@
         <v>45357</v>
       </c>
       <c r="B754" t="n">
-        <v>13.97543907165527</v>
+        <v>13.97543811798096</v>
       </c>
       <c r="C754" t="n">
-        <v>14.38249076688974</v>
+        <v>14.3824897854385</v>
       </c>
       <c r="D754" t="n">
-        <v>13.9172884333619</v>
+        <v>13.91728748365575</v>
       </c>
       <c r="E754" t="n">
-        <v>14.09173942396897</v>
+        <v>14.0917384623584</v>
       </c>
       <c r="F754" t="n">
         <v>10982800</v>
@@ -15572,16 +15572,16 @@
         <v>45363</v>
       </c>
       <c r="B758" t="n">
-        <v>14.26619052886963</v>
+        <v>14.26618957519531</v>
       </c>
       <c r="C758" t="n">
-        <v>14.37279895494302</v>
+        <v>14.37279799414208</v>
       </c>
       <c r="D758" t="n">
-        <v>13.74283847712863</v>
+        <v>13.74283755843964</v>
       </c>
       <c r="E758" t="n">
-        <v>14.0045140408626</v>
+        <v>14.00451310468098</v>
       </c>
       <c r="F758" t="n">
         <v>5196700</v>
@@ -15632,16 +15632,16 @@
         <v>45366</v>
       </c>
       <c r="B761" t="n">
-        <v>14.17896461486816</v>
+        <v>14.17896366119385</v>
       </c>
       <c r="C761" t="n">
-        <v>14.1983475443678</v>
+        <v>14.19834658938979</v>
       </c>
       <c r="D761" t="n">
-        <v>13.89790520507579</v>
+        <v>13.89790427030547</v>
       </c>
       <c r="E761" t="n">
-        <v>14.09173912143725</v>
+        <v>14.0917381736297</v>
       </c>
       <c r="F761" t="n">
         <v>7761200</v>
@@ -15672,16 +15672,16 @@
         <v>45370</v>
       </c>
       <c r="B763" t="n">
-        <v>14.27588081359863</v>
+        <v>14.27588176727295</v>
       </c>
       <c r="C763" t="n">
-        <v>14.35341530280148</v>
+        <v>14.35341626165535</v>
       </c>
       <c r="D763" t="n">
-        <v>14.00451333634416</v>
+        <v>14.00451427189027</v>
       </c>
       <c r="E763" t="n">
-        <v>14.09173882795849</v>
+        <v>14.09173976933154</v>
       </c>
       <c r="F763" t="n">
         <v>3066400</v>
@@ -15712,16 +15712,16 @@
         <v>45372</v>
       </c>
       <c r="B765" t="n">
-        <v>14.3631067276001</v>
+        <v>14.36310768127441</v>
       </c>
       <c r="C765" t="n">
-        <v>14.47940707841501</v>
+        <v>14.47940803981137</v>
       </c>
       <c r="D765" t="n">
-        <v>14.19834766621072</v>
+        <v>14.19834860894545</v>
       </c>
       <c r="E765" t="n">
-        <v>14.46002414874904</v>
+        <v>14.46002510885842</v>
       </c>
       <c r="F765" t="n">
         <v>19402800</v>
@@ -15812,16 +15812,16 @@
         <v>45379</v>
       </c>
       <c r="B770" t="n">
-        <v>14.25649738311768</v>
+        <v>14.25649833679199</v>
       </c>
       <c r="C770" t="n">
-        <v>14.73139068267979</v>
+        <v>14.73139166812162</v>
       </c>
       <c r="D770" t="n">
-        <v>14.25649738311768</v>
+        <v>14.25649833679199</v>
       </c>
       <c r="E770" t="n">
-        <v>14.45033128862538</v>
+        <v>14.45033225526602</v>
       </c>
       <c r="F770" t="n">
         <v>7122000</v>
@@ -15852,16 +15852,16 @@
         <v>45384</v>
       </c>
       <c r="B772" t="n">
-        <v>13.58777046203613</v>
+        <v>13.58776950836182</v>
       </c>
       <c r="C772" t="n">
-        <v>13.85913793541857</v>
+        <v>13.859136962698</v>
       </c>
       <c r="D772" t="n">
-        <v>13.43270241011604</v>
+        <v>13.43270146732536</v>
       </c>
       <c r="E772" t="n">
-        <v>13.82037115350679</v>
+        <v>13.82037018350711</v>
       </c>
       <c r="F772" t="n">
         <v>14898200</v>
@@ -16112,16 +16112,16 @@
         <v>45401</v>
       </c>
       <c r="B785" t="n">
-        <v>12.96750068664551</v>
+        <v>12.96750164031982</v>
       </c>
       <c r="C785" t="n">
-        <v>13.20979329829971</v>
+        <v>13.20979426979305</v>
       </c>
       <c r="D785" t="n">
-        <v>12.77366678217674</v>
+        <v>12.77366772159585</v>
       </c>
       <c r="E785" t="n">
-        <v>12.80274163677882</v>
+        <v>12.80274257833619</v>
       </c>
       <c r="F785" t="n">
         <v>12837800</v>
@@ -16212,16 +16212,16 @@
         <v>45408</v>
       </c>
       <c r="B790" t="n">
-        <v>12.90935039520264</v>
+        <v>12.90935134887695</v>
       </c>
       <c r="C790" t="n">
-        <v>13.10318522908003</v>
+        <v>13.10318619707384</v>
       </c>
       <c r="D790" t="n">
-        <v>12.77366712061604</v>
+        <v>12.7736680642668</v>
       </c>
       <c r="E790" t="n">
-        <v>13.03534266751375</v>
+        <v>13.03534363049571</v>
       </c>
       <c r="F790" t="n">
         <v>14489900</v>
@@ -16232,16 +16232,16 @@
         <v>45411</v>
       </c>
       <c r="B791" t="n">
-        <v>13.17102718353271</v>
+        <v>13.1710262298584</v>
       </c>
       <c r="C791" t="n">
-        <v>13.21948589316895</v>
+        <v>13.21948493598589</v>
       </c>
       <c r="D791" t="n">
-        <v>12.89965970355199</v>
+        <v>12.89965876952657</v>
       </c>
       <c r="E791" t="n">
-        <v>12.98688427176961</v>
+        <v>12.98688333142852</v>
       </c>
       <c r="F791" t="n">
         <v>6604200</v>
@@ -16312,16 +16312,16 @@
         <v>45418</v>
       </c>
       <c r="B795" t="n">
-        <v>12.92873477935791</v>
+        <v>12.92873382568359</v>
       </c>
       <c r="C795" t="n">
-        <v>13.2097941908973</v>
+        <v>13.20979321649093</v>
       </c>
       <c r="D795" t="n">
-        <v>12.81243442881813</v>
+        <v>12.81243348372259</v>
       </c>
       <c r="E795" t="n">
-        <v>13.11287676997764</v>
+        <v>13.11287580272028</v>
       </c>
       <c r="F795" t="n">
         <v>7469100</v>
@@ -16352,16 +16352,16 @@
         <v>45420</v>
       </c>
       <c r="B797" t="n">
-        <v>13.10318660736084</v>
+        <v>13.10318565368652</v>
       </c>
       <c r="C797" t="n">
-        <v>13.20010311022088</v>
+        <v>13.2001021494928</v>
       </c>
       <c r="D797" t="n">
-        <v>12.97719432179701</v>
+        <v>12.97719337729265</v>
       </c>
       <c r="E797" t="n">
-        <v>13.00626918022772</v>
+        <v>13.00626823360723</v>
       </c>
       <c r="F797" t="n">
         <v>4964400</v>
@@ -16412,16 +16412,16 @@
         <v>45425</v>
       </c>
       <c r="B800" t="n">
-        <v>12.92873477935791</v>
+        <v>12.92873382568359</v>
       </c>
       <c r="C800" t="n">
-        <v>13.1516435534909</v>
+        <v>13.15164258337395</v>
       </c>
       <c r="D800" t="n">
-        <v>12.79305057492499</v>
+        <v>12.79304963125927</v>
       </c>
       <c r="E800" t="n">
-        <v>12.98688449249129</v>
+        <v>12.98688353452762</v>
       </c>
       <c r="F800" t="n">
         <v>6951300</v>
@@ -16432,16 +16432,16 @@
         <v>45426</v>
       </c>
       <c r="B801" t="n">
-        <v>12.7542839050293</v>
+        <v>12.75428295135498</v>
       </c>
       <c r="C801" t="n">
-        <v>12.96750167838812</v>
+        <v>12.9675007087709</v>
       </c>
       <c r="D801" t="n">
-        <v>12.66705841027919</v>
+        <v>12.66705746312697</v>
       </c>
       <c r="E801" t="n">
-        <v>12.84150939977941</v>
+        <v>12.84150843958299</v>
       </c>
       <c r="F801" t="n">
         <v>10701800</v>
@@ -16472,16 +16472,16 @@
         <v>45428</v>
       </c>
       <c r="B803" t="n">
-        <v>13.05472755432129</v>
+        <v>13.05472660064697</v>
       </c>
       <c r="C803" t="n">
-        <v>13.21948662159938</v>
+        <v>13.21948565588908</v>
       </c>
       <c r="D803" t="n">
-        <v>12.94811820239249</v>
+        <v>12.9481172565062</v>
       </c>
       <c r="E803" t="n">
-        <v>13.20010276696758</v>
+        <v>13.2001018026733</v>
       </c>
       <c r="F803" t="n">
         <v>4347100</v>
@@ -16492,16 +16492,16 @@
         <v>45429</v>
       </c>
       <c r="B804" t="n">
-        <v>13.20979309082031</v>
+        <v>13.20979404449463</v>
       </c>
       <c r="C804" t="n">
-        <v>13.25825179724463</v>
+        <v>13.2582527544174</v>
       </c>
       <c r="D804" t="n">
-        <v>12.97719240911113</v>
+        <v>12.97719334599296</v>
       </c>
       <c r="E804" t="n">
-        <v>12.99657533711709</v>
+        <v>12.99657627539826</v>
       </c>
       <c r="F804" t="n">
         <v>6205200</v>
@@ -16632,16 +16632,16 @@
         <v>45440</v>
       </c>
       <c r="B811" t="n">
-        <v>12.3084659576416</v>
+        <v>12.30846500396729</v>
       </c>
       <c r="C811" t="n">
-        <v>12.75428445331711</v>
+        <v>12.75428346510026</v>
       </c>
       <c r="D811" t="n">
-        <v>12.17278267044019</v>
+        <v>12.17278172727877</v>
       </c>
       <c r="E811" t="n">
-        <v>12.72520959524153</v>
+        <v>12.72520860927743</v>
       </c>
       <c r="F811" t="n">
         <v>7568500</v>
@@ -16712,16 +16712,16 @@
         <v>45447</v>
       </c>
       <c r="B815" t="n">
-        <v>11.76573085784912</v>
+        <v>11.7657299041748</v>
       </c>
       <c r="C815" t="n">
-        <v>11.98863964160954</v>
+        <v>11.98863866986729</v>
       </c>
       <c r="D815" t="n">
-        <v>11.68819728747393</v>
+        <v>11.68819634008411</v>
       </c>
       <c r="E815" t="n">
-        <v>11.86264735868158</v>
+        <v>11.86264639715167</v>
       </c>
       <c r="F815" t="n">
         <v>3975700</v>
@@ -16792,16 +16792,16 @@
         <v>45453</v>
       </c>
       <c r="B819" t="n">
-        <v>11.56220436096191</v>
+        <v>11.5622034072876</v>
       </c>
       <c r="C819" t="n">
-        <v>11.74634634928489</v>
+        <v>11.74634538042216</v>
       </c>
       <c r="D819" t="n">
-        <v>11.52343757793218</v>
+        <v>11.52343662745543</v>
       </c>
       <c r="E819" t="n">
-        <v>11.58158729034027</v>
+        <v>11.58158633506721</v>
       </c>
       <c r="F819" t="n">
         <v>12105900</v>
@@ -16872,16 +16872,16 @@
         <v>45457</v>
       </c>
       <c r="B823" t="n">
-        <v>11.30052852630615</v>
+        <v>11.30052757263184</v>
       </c>
       <c r="C823" t="n">
-        <v>11.40713787891818</v>
+        <v>11.40713691624688</v>
       </c>
       <c r="D823" t="n">
-        <v>11.05823588749419</v>
+        <v>11.05823495426744</v>
       </c>
       <c r="E823" t="n">
-        <v>11.09700267273318</v>
+        <v>11.09700173623482</v>
       </c>
       <c r="F823" t="n">
         <v>4784200</v>
@@ -16932,16 +16932,16 @@
         <v>45462</v>
       </c>
       <c r="B826" t="n">
-        <v>10.7093334197998</v>
+        <v>10.70933437347412</v>
       </c>
       <c r="C826" t="n">
-        <v>10.76748312791706</v>
+        <v>10.76748408676966</v>
       </c>
       <c r="D826" t="n">
-        <v>10.43796595861572</v>
+        <v>10.43796688812455</v>
       </c>
       <c r="E826" t="n">
-        <v>10.71902534591033</v>
+        <v>10.71902630044772</v>
       </c>
       <c r="F826" t="n">
         <v>8916100</v>
@@ -17012,16 +17012,16 @@
         <v>45468</v>
       </c>
       <c r="B830" t="n">
-        <v>10.55426788330078</v>
+        <v>10.55426692962646</v>
       </c>
       <c r="C830" t="n">
-        <v>10.85471024363938</v>
+        <v>10.85470926281736</v>
       </c>
       <c r="D830" t="n">
-        <v>10.52519210060498</v>
+        <v>10.52519114955792</v>
       </c>
       <c r="E830" t="n">
-        <v>10.68995117212218</v>
+        <v>10.68995020618764</v>
       </c>
       <c r="F830" t="n">
         <v>9834800</v>
@@ -17092,16 +17092,16 @@
         <v>45474</v>
       </c>
       <c r="B834" t="n">
-        <v>9.691705703735352</v>
+        <v>9.691704750061035</v>
       </c>
       <c r="C834" t="n">
-        <v>10.08906548970481</v>
+        <v>10.08906449692986</v>
       </c>
       <c r="D834" t="n">
-        <v>9.594788276988766</v>
+        <v>9.594787332851229</v>
       </c>
       <c r="E834" t="n">
-        <v>9.982457059702028</v>
+        <v>9.982456077417465</v>
       </c>
       <c r="F834" t="n">
         <v>19240000</v>
@@ -17172,16 +17172,16 @@
         <v>45478</v>
       </c>
       <c r="B838" t="n">
-        <v>11.09700107574463</v>
+        <v>11.09700202941895</v>
       </c>
       <c r="C838" t="n">
-        <v>11.18422656104786</v>
+        <v>11.18422752221831</v>
       </c>
       <c r="D838" t="n">
-        <v>10.66087457350143</v>
+        <v>10.66087548969511</v>
       </c>
       <c r="E838" t="n">
-        <v>10.73840813282142</v>
+        <v>10.73840905567833</v>
       </c>
       <c r="F838" t="n">
         <v>25549700</v>
@@ -17252,16 +17252,16 @@
         <v>45484</v>
       </c>
       <c r="B842" t="n">
-        <v>10.90316867828369</v>
+        <v>10.90316772460938</v>
       </c>
       <c r="C842" t="n">
-        <v>11.2229948855715</v>
+        <v>11.22299390392275</v>
       </c>
       <c r="D842" t="n">
-        <v>10.72871768366377</v>
+        <v>10.72871674524827</v>
       </c>
       <c r="E842" t="n">
-        <v>11.09700260326523</v>
+        <v>11.09700163263672</v>
       </c>
       <c r="F842" t="n">
         <v>13851900</v>
@@ -17292,16 +17292,16 @@
         <v>45488</v>
       </c>
       <c r="B844" t="n">
-        <v>10.78686809539795</v>
+        <v>10.78686714172363</v>
       </c>
       <c r="C844" t="n">
-        <v>10.91286037504235</v>
+        <v>10.91285941022897</v>
       </c>
       <c r="D844" t="n">
-        <v>10.76748424117279</v>
+        <v>10.76748328921222</v>
       </c>
       <c r="E844" t="n">
-        <v>10.87409359086507</v>
+        <v>10.87409262947909</v>
       </c>
       <c r="F844" t="n">
         <v>5840400</v>
@@ -17312,16 +17312,16 @@
         <v>45489</v>
       </c>
       <c r="B845" t="n">
-        <v>10.76748371124268</v>
+        <v>10.76748275756836</v>
       </c>
       <c r="C845" t="n">
-        <v>10.90316791132185</v>
+        <v>10.90316694563</v>
       </c>
       <c r="D845" t="n">
-        <v>10.69964207333959</v>
+        <v>10.69964112567399</v>
       </c>
       <c r="E845" t="n">
-        <v>10.76748371124268</v>
+        <v>10.76748275756836</v>
       </c>
       <c r="F845" t="n">
         <v>9437300</v>
@@ -17332,16 +17332,16 @@
         <v>45490</v>
       </c>
       <c r="B846" t="n">
-        <v>10.41858196258545</v>
+        <v>10.41858291625977</v>
       </c>
       <c r="C846" t="n">
-        <v>10.82563361087946</v>
+        <v>10.82563460181362</v>
       </c>
       <c r="D846" t="n">
-        <v>10.41858196258545</v>
+        <v>10.41858291625977</v>
       </c>
       <c r="E846" t="n">
-        <v>10.7577919775881</v>
+        <v>10.75779296231231</v>
       </c>
       <c r="F846" t="n">
         <v>8121300</v>
@@ -17432,16 +17432,16 @@
         <v>45497</v>
       </c>
       <c r="B851" t="n">
-        <v>9.691705703735352</v>
+        <v>9.691704750061035</v>
       </c>
       <c r="C851" t="n">
-        <v>10.26351648813943</v>
+        <v>10.26351547819831</v>
       </c>
       <c r="D851" t="n">
-        <v>9.691705703735352</v>
+        <v>9.691704750061035</v>
       </c>
       <c r="E851" t="n">
-        <v>10.09875741723408</v>
+        <v>10.09875642350544</v>
       </c>
       <c r="F851" t="n">
         <v>20101500</v>
@@ -17492,16 +17492,16 @@
         <v>45502</v>
       </c>
       <c r="B854" t="n">
-        <v>9.25557804107666</v>
+        <v>9.255578994750977</v>
       </c>
       <c r="C854" t="n">
-        <v>9.652937780214037</v>
+        <v>9.652938774831423</v>
       </c>
       <c r="D854" t="n">
-        <v>9.11020191809054</v>
+        <v>9.110202856785623</v>
       </c>
       <c r="E854" t="n">
-        <v>9.575404217663962</v>
+        <v>9.575405204292462</v>
       </c>
       <c r="F854" t="n">
         <v>14084800</v>
@@ -17512,16 +17512,16 @@
         <v>45503</v>
       </c>
       <c r="B855" t="n">
-        <v>9.148969650268555</v>
+        <v>9.148968696594238</v>
       </c>
       <c r="C855" t="n">
-        <v>9.439721002187216</v>
+        <v>9.439720018205433</v>
       </c>
       <c r="D855" t="n">
-        <v>9.139278647147284</v>
+        <v>9.139277694483143</v>
       </c>
       <c r="E855" t="n">
-        <v>9.207120290361514</v>
+        <v>9.207119330625666</v>
       </c>
       <c r="F855" t="n">
         <v>13878900</v>
@@ -17532,16 +17532,16 @@
         <v>45504</v>
       </c>
       <c r="B856" t="n">
-        <v>9.517253875732422</v>
+        <v>9.517252922058105</v>
       </c>
       <c r="C856" t="n">
-        <v>9.556020658197346</v>
+        <v>9.556019700638412</v>
       </c>
       <c r="D856" t="n">
-        <v>9.216811542697508</v>
+        <v>9.21681061912895</v>
       </c>
       <c r="E856" t="n">
-        <v>9.255578325162432</v>
+        <v>9.255577397709256</v>
       </c>
       <c r="F856" t="n">
         <v>17487100</v>
@@ -17572,16 +17572,16 @@
         <v>45506</v>
       </c>
       <c r="B858" t="n">
-        <v>9.885538101196289</v>
+        <v>9.885539054870605</v>
       </c>
       <c r="C858" t="n">
-        <v>9.953380659115961</v>
+        <v>9.953381619335163</v>
       </c>
       <c r="D858" t="n">
-        <v>9.585095788526804</v>
+        <v>9.58509671321695</v>
       </c>
       <c r="E858" t="n">
-        <v>9.604478716308897</v>
+        <v>9.604479642868947</v>
       </c>
       <c r="F858" t="n">
         <v>10117700</v>
@@ -17672,16 +17672,16 @@
         <v>45513</v>
       </c>
       <c r="B863" t="n">
-        <v>9.953380584716797</v>
+        <v>9.953381538391113</v>
       </c>
       <c r="C863" t="n">
-        <v>10.13752255649849</v>
+        <v>10.1375235278162</v>
       </c>
       <c r="D863" t="n">
-        <v>9.662629275975187</v>
+        <v>9.662630201791425</v>
       </c>
       <c r="E863" t="n">
-        <v>10.12783063054342</v>
+        <v>10.12783160093251</v>
       </c>
       <c r="F863" t="n">
         <v>24889300</v>
@@ -17752,16 +17752,16 @@
         <v>45519</v>
       </c>
       <c r="B867" t="n">
-        <v>10.07937335968018</v>
+        <v>10.07937240600586</v>
       </c>
       <c r="C867" t="n">
-        <v>10.30228306700982</v>
+        <v>10.30228209224458</v>
       </c>
       <c r="D867" t="n">
-        <v>9.933998146753977</v>
+        <v>9.933997206834544</v>
       </c>
       <c r="E867" t="n">
-        <v>10.30228306700982</v>
+        <v>10.30228209224458</v>
       </c>
       <c r="F867" t="n">
         <v>11390800</v>
@@ -17792,16 +17792,16 @@
         <v>45523</v>
       </c>
       <c r="B869" t="n">
-        <v>10.37981605529785</v>
+        <v>10.37981510162354</v>
       </c>
       <c r="C869" t="n">
-        <v>10.43796669177252</v>
+        <v>10.43796573275546</v>
       </c>
       <c r="D869" t="n">
-        <v>9.701396892549386</v>
+        <v>9.701396001206707</v>
       </c>
       <c r="E869" t="n">
-        <v>10.02122308247756</v>
+        <v>10.02122216174997</v>
       </c>
       <c r="F869" t="n">
         <v>15557600</v>
@@ -17852,16 +17852,16 @@
         <v>45526</v>
       </c>
       <c r="B872" t="n">
-        <v>9.44941234588623</v>
+        <v>9.449411392211914</v>
       </c>
       <c r="C872" t="n">
-        <v>9.691704970139725</v>
+        <v>9.691703992012219</v>
       </c>
       <c r="D872" t="n">
-        <v>9.342803923952978</v>
+        <v>9.34280298103803</v>
       </c>
       <c r="E872" t="n">
-        <v>9.546329765296832</v>
+        <v>9.546328801841204</v>
       </c>
       <c r="F872" t="n">
         <v>16152200</v>
@@ -18012,16 +18012,16 @@
         <v>45538</v>
       </c>
       <c r="B880" t="n">
-        <v>9.691705703735352</v>
+        <v>9.691704750061035</v>
       </c>
       <c r="C880" t="n">
-        <v>9.817697988796681</v>
+        <v>9.817697022724587</v>
       </c>
       <c r="D880" t="n">
-        <v>9.497871774515261</v>
+        <v>9.497870839914412</v>
       </c>
       <c r="E880" t="n">
-        <v>9.556021491144747</v>
+        <v>9.556020550821904</v>
       </c>
       <c r="F880" t="n">
         <v>16401400</v>
@@ -18112,16 +18112,16 @@
         <v>45545</v>
       </c>
       <c r="B885" t="n">
-        <v>8.625617027282715</v>
+        <v>8.625616073608398</v>
       </c>
       <c r="C885" t="n">
-        <v>8.896985431091611</v>
+        <v>8.896984447413983</v>
       </c>
       <c r="D885" t="n">
-        <v>8.528700532442116</v>
+        <v>8.52869958948318</v>
       </c>
       <c r="E885" t="n">
-        <v>8.896985431091611</v>
+        <v>8.896984447413983</v>
       </c>
       <c r="F885" t="n">
         <v>19808800</v>
@@ -18152,16 +18152,16 @@
         <v>45547</v>
       </c>
       <c r="B887" t="n">
-        <v>8.790375709533691</v>
+        <v>8.790376663208008</v>
       </c>
       <c r="C887" t="n">
-        <v>8.916367979287587</v>
+        <v>8.916368946630897</v>
       </c>
       <c r="D887" t="n">
-        <v>8.722534073617352</v>
+        <v>8.722535019931478</v>
       </c>
       <c r="E887" t="n">
-        <v>8.819451488588953</v>
+        <v>8.819452445417722</v>
       </c>
       <c r="F887" t="n">
         <v>11088400</v>
@@ -18212,16 +18212,16 @@
         <v>45552</v>
       </c>
       <c r="B890" t="n">
-        <v>8.548083305358887</v>
+        <v>8.548084259033203</v>
       </c>
       <c r="C890" t="n">
-        <v>8.606233940618093</v>
+        <v>8.606234900780036</v>
       </c>
       <c r="D890" t="n">
-        <v>8.402708103620357</v>
+        <v>8.402709041075765</v>
       </c>
       <c r="E890" t="n">
-        <v>8.480241667783972</v>
+        <v>8.480242613889478</v>
       </c>
       <c r="F890" t="n">
         <v>13563600</v>
@@ -18232,16 +18232,16 @@
         <v>45553</v>
       </c>
       <c r="B891" t="n">
-        <v>8.470550537109375</v>
+        <v>8.470549583435059</v>
       </c>
       <c r="C891" t="n">
-        <v>8.761301892179148</v>
+        <v>8.761300905769993</v>
       </c>
       <c r="D891" t="n">
-        <v>8.470550537109375</v>
+        <v>8.470549583435059</v>
       </c>
       <c r="E891" t="n">
-        <v>8.548084108558237</v>
+        <v>8.548083146154644</v>
       </c>
       <c r="F891" t="n">
         <v>22128100</v>
@@ -18252,16 +18252,16 @@
         <v>45554</v>
       </c>
       <c r="B892" t="n">
-        <v>7.985965251922607</v>
+        <v>7.985964775085449</v>
       </c>
       <c r="C892" t="n">
-        <v>8.567467961953305</v>
+        <v>8.567467450394972</v>
       </c>
       <c r="D892" t="n">
-        <v>7.985965251922607</v>
+        <v>7.985964775085449</v>
       </c>
       <c r="E892" t="n">
-        <v>8.538393103733693</v>
+        <v>8.538392593911404</v>
       </c>
       <c r="F892" t="n">
         <v>19129200</v>
@@ -18272,16 +18272,16 @@
         <v>45555</v>
       </c>
       <c r="B893" t="n">
-        <v>7.462612628936768</v>
+        <v>7.462612152099609</v>
       </c>
       <c r="C893" t="n">
-        <v>8.073190151887005</v>
+        <v>8.073189636035888</v>
       </c>
       <c r="D893" t="n">
-        <v>7.462612628936768</v>
+        <v>7.462612152099609</v>
       </c>
       <c r="E893" t="n">
-        <v>8.005348512983536</v>
+        <v>8.005348001467285</v>
       </c>
       <c r="F893" t="n">
         <v>27842200</v>
@@ -18292,16 +18292,16 @@
         <v>45558</v>
       </c>
       <c r="B894" t="n">
-        <v>7.617680072784424</v>
+        <v>7.617680549621582</v>
       </c>
       <c r="C894" t="n">
-        <v>7.675830245903511</v>
+        <v>7.675830726380644</v>
       </c>
       <c r="D894" t="n">
-        <v>7.433537626839064</v>
+        <v>7.433538092149622</v>
       </c>
       <c r="E894" t="n">
-        <v>7.443229091290664</v>
+        <v>7.44322955720787</v>
       </c>
       <c r="F894" t="n">
         <v>19916000</v>
@@ -18312,16 +18312,16 @@
         <v>45559</v>
       </c>
       <c r="B895" t="n">
-        <v>7.898738861083984</v>
+        <v>7.898739337921143</v>
       </c>
       <c r="C895" t="n">
-        <v>8.024731131506325</v>
+        <v>8.024731615949483</v>
       </c>
       <c r="D895" t="n">
-        <v>7.753363662128269</v>
+        <v>7.753364130189305</v>
       </c>
       <c r="E895" t="n">
-        <v>7.859972079744262</v>
+        <v>7.859972554241117</v>
       </c>
       <c r="F895" t="n">
         <v>22551600</v>
@@ -18352,16 +18352,16 @@
         <v>45561</v>
       </c>
       <c r="B897" t="n">
-        <v>7.801823139190674</v>
+        <v>7.801822662353516</v>
       </c>
       <c r="C897" t="n">
-        <v>7.869664782156651</v>
+        <v>7.8696643011731</v>
       </c>
       <c r="D897" t="n">
-        <v>7.549838573498384</v>
+        <v>7.54983811206219</v>
       </c>
       <c r="E897" t="n">
-        <v>7.559530500857256</v>
+        <v>7.559530038828704</v>
       </c>
       <c r="F897" t="n">
         <v>14720200</v>
@@ -18512,16 +18512,16 @@
         <v>45573</v>
       </c>
       <c r="B905" t="n">
-        <v>6.609743118286133</v>
+        <v>6.609742641448975</v>
       </c>
       <c r="C905" t="n">
-        <v>6.648509902147569</v>
+        <v>6.648509422513715</v>
       </c>
       <c r="D905" t="n">
-        <v>6.512825696496025</v>
+        <v>6.512825226650641</v>
       </c>
       <c r="E905" t="n">
-        <v>6.551592942493978</v>
+        <v>6.551592469851864</v>
       </c>
       <c r="F905" t="n">
         <v>17971800</v>
@@ -18592,16 +18592,16 @@
         <v>45579</v>
       </c>
       <c r="B909" t="n">
-        <v>6.919877052307129</v>
+        <v>6.919877529144287</v>
       </c>
       <c r="C909" t="n">
-        <v>6.997410616255546</v>
+        <v>6.997411098435412</v>
       </c>
       <c r="D909" t="n">
-        <v>6.648509578487669</v>
+        <v>6.64851003662535</v>
       </c>
       <c r="E909" t="n">
-        <v>6.813268632946302</v>
+        <v>6.813269102437253</v>
       </c>
       <c r="F909" t="n">
         <v>42118900</v>
@@ -18612,16 +18612,16 @@
         <v>45580</v>
       </c>
       <c r="B910" t="n">
-        <v>6.793885231018066</v>
+        <v>6.793884754180908</v>
       </c>
       <c r="C910" t="n">
-        <v>7.084636095356394</v>
+        <v>7.08463559811253</v>
       </c>
       <c r="D910" t="n">
-        <v>6.716351205058019</v>
+        <v>6.716350733662682</v>
       </c>
       <c r="E910" t="n">
-        <v>6.997410604986649</v>
+        <v>6.997410113864813</v>
       </c>
       <c r="F910" t="n">
         <v>30694500</v>
@@ -18792,16 +18792,16 @@
         <v>45593</v>
       </c>
       <c r="B919" t="n">
-        <v>7.191245555877686</v>
+        <v>7.191245079040527</v>
       </c>
       <c r="C919" t="n">
-        <v>7.375388015858033</v>
+        <v>7.375387526810755</v>
       </c>
       <c r="D919" t="n">
-        <v>7.084636665965583</v>
+        <v>7.084636196197448</v>
       </c>
       <c r="E919" t="n">
-        <v>7.084636665965583</v>
+        <v>7.084636196197448</v>
       </c>
       <c r="F919" t="n">
         <v>17455800</v>
@@ -18832,16 +18832,16 @@
         <v>45595</v>
       </c>
       <c r="B921" t="n">
-        <v>7.443228721618652</v>
+        <v>7.443229198455811</v>
       </c>
       <c r="C921" t="n">
-        <v>7.598296304371199</v>
+        <v>7.598296791142485</v>
       </c>
       <c r="D921" t="n">
-        <v>7.249394820848559</v>
+        <v>7.249395285268095</v>
       </c>
       <c r="E921" t="n">
-        <v>7.317236917186328</v>
+        <v>7.317237385952047</v>
       </c>
       <c r="F921" t="n">
         <v>17976200</v>
@@ -18912,16 +18912,16 @@
         <v>45601</v>
       </c>
       <c r="B925" t="n">
-        <v>7.443228721618652</v>
+        <v>7.443229198455811</v>
       </c>
       <c r="C925" t="n">
-        <v>7.569220988187449</v>
+        <v>7.569221473096077</v>
       </c>
       <c r="D925" t="n">
-        <v>7.191244650617532</v>
+        <v>7.191245111311781</v>
       </c>
       <c r="E925" t="n">
-        <v>7.472304037802402</v>
+        <v>7.472304516502219</v>
       </c>
       <c r="F925" t="n">
         <v>13215900</v>
@@ -18972,16 +18972,16 @@
         <v>45604</v>
       </c>
       <c r="B928" t="n">
-        <v>6.793885231018066</v>
+        <v>6.793884754180908</v>
       </c>
       <c r="C928" t="n">
-        <v>7.133094803814362</v>
+        <v>7.133094303169364</v>
       </c>
       <c r="D928" t="n">
-        <v>6.687276349692433</v>
+        <v>6.68727588033775</v>
       </c>
       <c r="E928" t="n">
-        <v>6.939260432118983</v>
+        <v>6.939259945078488</v>
       </c>
       <c r="F928" t="n">
         <v>34800800</v>
@@ -19012,16 +19012,16 @@
         <v>45608</v>
       </c>
       <c r="B930" t="n">
-        <v>6.987719535827637</v>
+        <v>6.987719058990479</v>
       </c>
       <c r="C930" t="n">
-        <v>7.055561639078888</v>
+        <v>7.055561157612231</v>
       </c>
       <c r="D930" t="n">
-        <v>6.784193688210403</v>
+        <v>6.784193225261708</v>
       </c>
       <c r="E930" t="n">
-        <v>6.861727256419536</v>
+        <v>6.861726788180004</v>
       </c>
       <c r="F930" t="n">
         <v>26167100</v>
@@ -19112,16 +19112,16 @@
         <v>45617</v>
       </c>
       <c r="B935" t="n">
-        <v>6.726043701171875</v>
+        <v>6.726043224334717</v>
       </c>
       <c r="C935" t="n">
-        <v>6.842344056755628</v>
+        <v>6.842343571673456</v>
       </c>
       <c r="D935" t="n">
-        <v>6.512825920465128</v>
+        <v>6.512825458743863</v>
       </c>
       <c r="E935" t="n">
-        <v>6.69696838120767</v>
+        <v>6.696967906431782</v>
       </c>
       <c r="F935" t="n">
         <v>32015400</v>
@@ -19132,16 +19132,16 @@
         <v>45618</v>
       </c>
       <c r="B936" t="n">
-        <v>6.97802734375</v>
+        <v>6.978027820587158</v>
       </c>
       <c r="C936" t="n">
-        <v>7.045869444425019</v>
+        <v>7.045869925898105</v>
       </c>
       <c r="D936" t="n">
-        <v>6.726043256639149</v>
+        <v>6.726043716257203</v>
       </c>
       <c r="E936" t="n">
-        <v>6.774501503861446</v>
+        <v>6.774501966790851</v>
       </c>
       <c r="F936" t="n">
         <v>20807700</v>
@@ -19192,16 +19192,16 @@
         <v>45623</v>
       </c>
       <c r="B939" t="n">
-        <v>7.181553363800049</v>
+        <v>7.181553840637207</v>
       </c>
       <c r="C939" t="n">
-        <v>7.801822825752589</v>
+        <v>7.801823343774085</v>
       </c>
       <c r="D939" t="n">
-        <v>7.133095115362094</v>
+        <v>7.133095588981745</v>
       </c>
       <c r="E939" t="n">
-        <v>7.675830547968181</v>
+        <v>7.675831057624106</v>
       </c>
       <c r="F939" t="n">
         <v>36141700</v>
@@ -19352,16 +19352,16 @@
         <v>45635</v>
       </c>
       <c r="B947" t="n">
-        <v>5.873173236846924</v>
+        <v>5.873172760009766</v>
       </c>
       <c r="C947" t="n">
-        <v>6.008856978888051</v>
+        <v>6.008856491034863</v>
       </c>
       <c r="D947" t="n">
-        <v>5.776256278246119</v>
+        <v>5.776255809277553</v>
       </c>
       <c r="E947" t="n">
-        <v>5.98947358716789</v>
+        <v>5.989473100888421</v>
       </c>
       <c r="F947" t="n">
         <v>18041800</v>
@@ -19392,16 +19392,16 @@
         <v>45637</v>
       </c>
       <c r="B949" t="n">
-        <v>6.270533084869385</v>
+        <v>6.270532608032227</v>
       </c>
       <c r="C949" t="n">
-        <v>6.63881799478054</v>
+        <v>6.638817489937481</v>
       </c>
       <c r="D949" t="n">
-        <v>5.989473669973113</v>
+        <v>5.98947321450887</v>
       </c>
       <c r="E949" t="n">
-        <v>6.231766300893107</v>
+        <v>6.231765827003935</v>
       </c>
       <c r="F949" t="n">
         <v>30797400</v>
@@ -19412,16 +19412,16 @@
         <v>45638</v>
       </c>
       <c r="B950" t="n">
-        <v>5.873173236846924</v>
+        <v>5.873172760009766</v>
       </c>
       <c r="C950" t="n">
-        <v>6.086391007905207</v>
+        <v>6.086390513757107</v>
       </c>
       <c r="D950" t="n">
-        <v>5.737489494805797</v>
+        <v>5.737489028984668</v>
       </c>
       <c r="E950" t="n">
-        <v>6.047623762328373</v>
+        <v>6.047623271327748</v>
       </c>
       <c r="F950" t="n">
         <v>28228300</v>
@@ -19472,16 +19472,16 @@
         <v>45643</v>
       </c>
       <c r="B953" t="n">
-        <v>5.340129375457764</v>
+        <v>5.340129852294922</v>
       </c>
       <c r="C953" t="n">
-        <v>5.398279546719705</v>
+        <v>5.398280028749276</v>
       </c>
       <c r="D953" t="n">
-        <v>5.146295009114813</v>
+        <v>5.146295468643883</v>
       </c>
       <c r="E953" t="n">
-        <v>5.243211961218048</v>
+        <v>5.243212429401142</v>
       </c>
       <c r="F953" t="n">
         <v>32812100</v>
@@ -19492,16 +19492,16 @@
         <v>45644</v>
       </c>
       <c r="B954" t="n">
-        <v>4.981536388397217</v>
+        <v>4.981535911560059</v>
       </c>
       <c r="C954" t="n">
-        <v>5.340129835259944</v>
+        <v>5.340129324097897</v>
       </c>
       <c r="D954" t="n">
-        <v>4.894311355062193</v>
+        <v>4.894310886574293</v>
       </c>
       <c r="E954" t="n">
-        <v>5.23352094769878</v>
+        <v>5.233520446741433</v>
       </c>
       <c r="F954" t="n">
         <v>36135800</v>
@@ -19532,16 +19532,16 @@
         <v>45646</v>
       </c>
       <c r="B956" t="n">
-        <v>5.592113971710205</v>
+        <v>5.592113494873047</v>
       </c>
       <c r="C956" t="n">
-        <v>5.659956075568729</v>
+        <v>5.659955592946704</v>
       </c>
       <c r="D956" t="n">
-        <v>5.165678880606319</v>
+        <v>5.165678440131098</v>
       </c>
       <c r="E956" t="n">
-        <v>5.223829057283687</v>
+        <v>5.223828611850025</v>
       </c>
       <c r="F956" t="n">
         <v>45865200</v>
@@ -19572,16 +19572,16 @@
         <v>45652</v>
       </c>
       <c r="B958" t="n">
-        <v>5.727797508239746</v>
+        <v>5.727797985076904</v>
       </c>
       <c r="C958" t="n">
-        <v>5.747180899758088</v>
+        <v>5.747181378208906</v>
       </c>
       <c r="D958" t="n">
-        <v>5.504888274710566</v>
+        <v>5.504888732990607</v>
       </c>
       <c r="E958" t="n">
-        <v>5.60180569443878</v>
+        <v>5.601806160787163</v>
       </c>
       <c r="F958" t="n">
         <v>25976300</v>
@@ -27452,19 +27452,19 @@
         <v>46231</v>
       </c>
       <c r="B1352" t="n">
-        <v>8.25</v>
+        <v>8.31</v>
       </c>
       <c r="C1352" t="n">
-        <v>8.4</v>
+        <v>8.42</v>
       </c>
       <c r="D1352" t="n">
-        <v>8.24</v>
+        <v>8.23</v>
       </c>
       <c r="E1352" t="n">
         <v>8.31</v>
       </c>
       <c r="F1352" t="n">
-        <v>1019700</v>
+        <v>3386000</v>
       </c>
     </row>
   </sheetData>

--- a/database/ASAI3.xlsx
+++ b/database/ASAI3.xlsx
@@ -452,16 +452,16 @@
         <v>44256</v>
       </c>
       <c r="B2" t="n">
-        <v>13.55914878845215</v>
+        <v>13.55914783477783</v>
       </c>
       <c r="C2" t="n">
-        <v>14.43840509670459</v>
+        <v>14.43840408118833</v>
       </c>
       <c r="D2" t="n">
-        <v>13.17554324856868</v>
+        <v>13.17554232187502</v>
       </c>
       <c r="E2" t="n">
-        <v>13.67499091708668</v>
+        <v>13.67498995526467</v>
       </c>
       <c r="F2" t="n">
         <v>64088000</v>
@@ -472,16 +472,16 @@
         <v>44257</v>
       </c>
       <c r="B3" t="n">
-        <v>13.76804256439209</v>
+        <v>13.76804351806641</v>
       </c>
       <c r="C3" t="n">
-        <v>14.05289879855508</v>
+        <v>14.0528997719606</v>
       </c>
       <c r="D3" t="n">
-        <v>13.0046284363764</v>
+        <v>13.00462933717113</v>
       </c>
       <c r="E3" t="n">
-        <v>13.3711429203832</v>
+        <v>13.37114384656537</v>
       </c>
       <c r="F3" t="n">
         <v>14717000</v>
@@ -492,16 +492,16 @@
         <v>44258</v>
       </c>
       <c r="B4" t="n">
-        <v>13.54015922546387</v>
+        <v>13.54016017913818</v>
       </c>
       <c r="C4" t="n">
-        <v>13.82881329247169</v>
+        <v>13.82881426647678</v>
       </c>
       <c r="D4" t="n">
-        <v>13.17934141532082</v>
+        <v>13.17934234358165</v>
       </c>
       <c r="E4" t="n">
-        <v>13.63321180595596</v>
+        <v>13.63321276618425</v>
       </c>
       <c r="F4" t="n">
         <v>17545000</v>
@@ -512,16 +512,16 @@
         <v>44259</v>
       </c>
       <c r="B5" t="n">
-        <v>13.90097618103027</v>
+        <v>13.90097713470459</v>
       </c>
       <c r="C5" t="n">
-        <v>14.04340385011868</v>
+        <v>14.04340481356423</v>
       </c>
       <c r="D5" t="n">
-        <v>13.44330710721157</v>
+        <v>13.44330802948757</v>
       </c>
       <c r="E5" t="n">
-        <v>13.53256187643049</v>
+        <v>13.53256280482981</v>
       </c>
       <c r="F5" t="n">
         <v>12300000</v>
@@ -532,16 +532,16 @@
         <v>44260</v>
       </c>
       <c r="B6" t="n">
-        <v>14.24280261993408</v>
+        <v>14.2428035736084</v>
       </c>
       <c r="C6" t="n">
-        <v>14.90746656109107</v>
+        <v>14.90746755927018</v>
       </c>
       <c r="D6" t="n">
-        <v>13.67309015292352</v>
+        <v>13.67309106845084</v>
       </c>
       <c r="E6" t="n">
-        <v>13.76994143531125</v>
+        <v>13.76994235732357</v>
       </c>
       <c r="F6" t="n">
         <v>18499500</v>
@@ -572,16 +572,16 @@
         <v>44264</v>
       </c>
       <c r="B8" t="n">
-        <v>13.4452075958252</v>
+        <v>13.44520568847656</v>
       </c>
       <c r="C8" t="n">
-        <v>13.4452075958252</v>
+        <v>13.44520568847656</v>
       </c>
       <c r="D8" t="n">
-        <v>13.01032711509522</v>
+        <v>13.0103252694391</v>
       </c>
       <c r="E8" t="n">
-        <v>13.29138558640273</v>
+        <v>13.29138370087542</v>
       </c>
       <c r="F8" t="n">
         <v>10167000</v>
@@ -592,16 +592,16 @@
         <v>44265</v>
       </c>
       <c r="B9" t="n">
-        <v>13.48318672180176</v>
+        <v>13.48318767547607</v>
       </c>
       <c r="C9" t="n">
-        <v>13.95794682401684</v>
+        <v>13.95794781127124</v>
       </c>
       <c r="D9" t="n">
-        <v>13.23631125132199</v>
+        <v>13.23631218753465</v>
       </c>
       <c r="E9" t="n">
-        <v>13.4850856245696</v>
+        <v>13.48508657837822</v>
       </c>
       <c r="F9" t="n">
         <v>15699500</v>
@@ -612,16 +612,16 @@
         <v>44266</v>
       </c>
       <c r="B10" t="n">
-        <v>13.95604801177979</v>
+        <v>13.9560489654541</v>
       </c>
       <c r="C10" t="n">
-        <v>14.15544729222492</v>
+        <v>14.15544825952501</v>
       </c>
       <c r="D10" t="n">
-        <v>13.63510989807421</v>
+        <v>13.6351108298175</v>
       </c>
       <c r="E10" t="n">
-        <v>13.71297125079192</v>
+        <v>13.7129721878558</v>
       </c>
       <c r="F10" t="n">
         <v>16646000</v>
@@ -632,16 +632,16 @@
         <v>44267</v>
       </c>
       <c r="B11" t="n">
-        <v>13.82121658325195</v>
+        <v>13.82121753692627</v>
       </c>
       <c r="C11" t="n">
-        <v>14.06049554958161</v>
+        <v>14.06049651976635</v>
       </c>
       <c r="D11" t="n">
-        <v>13.57813981118895</v>
+        <v>13.57814074809079</v>
       </c>
       <c r="E11" t="n">
-        <v>13.57813981118895</v>
+        <v>13.57814074809079</v>
       </c>
       <c r="F11" t="n">
         <v>7509000</v>
@@ -652,16 +652,16 @@
         <v>44270</v>
       </c>
       <c r="B12" t="n">
-        <v>13.83450889587402</v>
+        <v>13.83450984954834</v>
       </c>
       <c r="C12" t="n">
-        <v>14.01681714204006</v>
+        <v>14.01681810828169</v>
       </c>
       <c r="D12" t="n">
-        <v>13.62181639478016</v>
+        <v>13.62181733379263</v>
       </c>
       <c r="E12" t="n">
-        <v>13.81931676841011</v>
+        <v>13.81931772103716</v>
       </c>
       <c r="F12" t="n">
         <v>11593000</v>
@@ -672,16 +672,16 @@
         <v>44271</v>
       </c>
       <c r="B13" t="n">
-        <v>13.5876350402832</v>
+        <v>13.58763408660889</v>
       </c>
       <c r="C13" t="n">
-        <v>13.9104711614124</v>
+        <v>13.91047018507921</v>
       </c>
       <c r="D13" t="n">
-        <v>13.49458155685794</v>
+        <v>13.49458060971476</v>
       </c>
       <c r="E13" t="n">
-        <v>13.84400503434655</v>
+        <v>13.84400406267841</v>
       </c>
       <c r="F13" t="n">
         <v>7789500</v>
@@ -732,16 +732,16 @@
         <v>44274</v>
       </c>
       <c r="B16" t="n">
-        <v>13.54775333404541</v>
+        <v>13.54775428771973</v>
       </c>
       <c r="C16" t="n">
-        <v>14.03580663921036</v>
+        <v>14.03580762724047</v>
       </c>
       <c r="D16" t="n">
-        <v>13.46419618282161</v>
+        <v>13.46419713061404</v>
       </c>
       <c r="E16" t="n">
-        <v>13.95414839066896</v>
+        <v>13.95414937295086</v>
       </c>
       <c r="F16" t="n">
         <v>14098000</v>
@@ -752,16 +752,16 @@
         <v>44277</v>
       </c>
       <c r="B17" t="n">
-        <v>13.29328441619873</v>
+        <v>13.29328346252441</v>
       </c>
       <c r="C17" t="n">
-        <v>13.6351114037662</v>
+        <v>13.63511042556885</v>
       </c>
       <c r="D17" t="n">
-        <v>13.15655344006512</v>
+        <v>13.15655249620002</v>
       </c>
       <c r="E17" t="n">
-        <v>13.6351114037662</v>
+        <v>13.63511042556885</v>
       </c>
       <c r="F17" t="n">
         <v>5803000</v>
@@ -772,16 +772,16 @@
         <v>44278</v>
       </c>
       <c r="B18" t="n">
-        <v>13.44140911102295</v>
+        <v>13.44140720367432</v>
       </c>
       <c r="C18" t="n">
-        <v>13.44140911102295</v>
+        <v>13.44140720367432</v>
       </c>
       <c r="D18" t="n">
-        <v>13.01982187811874</v>
+        <v>13.01982003059373</v>
       </c>
       <c r="E18" t="n">
-        <v>13.29328381808184</v>
+        <v>13.29328193175233</v>
       </c>
       <c r="F18" t="n">
         <v>7916000</v>
@@ -792,16 +792,16 @@
         <v>44279</v>
       </c>
       <c r="B19" t="n">
-        <v>13.00842571258545</v>
+        <v>13.00842666625977</v>
       </c>
       <c r="C19" t="n">
-        <v>13.47179146035269</v>
+        <v>13.4717924479973</v>
       </c>
       <c r="D19" t="n">
-        <v>12.86599805406478</v>
+        <v>12.86599899729744</v>
       </c>
       <c r="E19" t="n">
-        <v>13.31417167521553</v>
+        <v>13.31417265130471</v>
       </c>
       <c r="F19" t="n">
         <v>12174500</v>
@@ -832,16 +832,16 @@
         <v>44281</v>
       </c>
       <c r="B21" t="n">
-        <v>13.8060245513916</v>
+        <v>13.80602359771729</v>
       </c>
       <c r="C21" t="n">
-        <v>14.1269626819656</v>
+        <v>14.12696170612194</v>
       </c>
       <c r="D21" t="n">
-        <v>13.48888513211062</v>
+        <v>13.48888420034324</v>
       </c>
       <c r="E21" t="n">
-        <v>13.54965455193487</v>
+        <v>13.54965361596974</v>
       </c>
       <c r="F21" t="n">
         <v>4396500</v>
@@ -852,16 +852,16 @@
         <v>44284</v>
       </c>
       <c r="B22" t="n">
-        <v>13.95794773101807</v>
+        <v>13.95794677734375</v>
       </c>
       <c r="C22" t="n">
-        <v>13.95794773101807</v>
+        <v>13.95794677734375</v>
       </c>
       <c r="D22" t="n">
-        <v>13.48698630926816</v>
+        <v>13.4869853877722</v>
       </c>
       <c r="E22" t="n">
-        <v>13.71487095581164</v>
+        <v>13.7148700187455</v>
       </c>
       <c r="F22" t="n">
         <v>6557000</v>
@@ -872,16 +872,16 @@
         <v>44285</v>
       </c>
       <c r="B23" t="n">
-        <v>13.95794773101807</v>
+        <v>13.95794677734375</v>
       </c>
       <c r="C23" t="n">
-        <v>14.08138547427906</v>
+        <v>14.08138451217088</v>
       </c>
       <c r="D23" t="n">
-        <v>13.7680438588985</v>
+        <v>13.76804291819933</v>
       </c>
       <c r="E23" t="n">
-        <v>13.7680438588985</v>
+        <v>13.76804291819933</v>
       </c>
       <c r="F23" t="n">
         <v>8433000</v>
@@ -892,16 +892,16 @@
         <v>44286</v>
       </c>
       <c r="B24" t="n">
-        <v>14.02251529693604</v>
+        <v>14.0225133895874</v>
       </c>
       <c r="C24" t="n">
-        <v>14.04150613737493</v>
+        <v>14.04150422744316</v>
       </c>
       <c r="D24" t="n">
-        <v>13.67499161002203</v>
+        <v>13.67498974994372</v>
       </c>
       <c r="E24" t="n">
-        <v>13.96744348962283</v>
+        <v>13.96744158976508</v>
       </c>
       <c r="F24" t="n">
         <v>3663000</v>
@@ -932,16 +932,16 @@
         <v>44291</v>
       </c>
       <c r="B26" t="n">
-        <v>14.71756458282471</v>
+        <v>14.71756362915039</v>
       </c>
       <c r="C26" t="n">
-        <v>14.88657962286491</v>
+        <v>14.88657865823869</v>
       </c>
       <c r="D26" t="n">
-        <v>14.29977605116619</v>
+        <v>14.29977512456389</v>
       </c>
       <c r="E26" t="n">
-        <v>14.29977605116619</v>
+        <v>14.29977512456389</v>
       </c>
       <c r="F26" t="n">
         <v>6073500</v>
@@ -952,16 +952,16 @@
         <v>44292</v>
       </c>
       <c r="B27" t="n">
-        <v>14.5865306854248</v>
+        <v>14.58653163909912</v>
       </c>
       <c r="C27" t="n">
-        <v>14.72136184524953</v>
+        <v>14.72136280773917</v>
       </c>
       <c r="D27" t="n">
-        <v>14.52766016847332</v>
+        <v>14.52766111829865</v>
       </c>
       <c r="E27" t="n">
-        <v>14.71756403948914</v>
+        <v>14.71756500173048</v>
       </c>
       <c r="F27" t="n">
         <v>5821500</v>
@@ -972,16 +972,16 @@
         <v>44293</v>
       </c>
       <c r="B28" t="n">
-        <v>14.49347496032715</v>
+        <v>14.4934778213501</v>
       </c>
       <c r="C28" t="n">
-        <v>14.78023007818483</v>
+        <v>14.78023299581345</v>
       </c>
       <c r="D28" t="n">
-        <v>13.92756124049176</v>
+        <v>13.92756398980291</v>
       </c>
       <c r="E28" t="n">
-        <v>14.45359528940647</v>
+        <v>14.45359814255714</v>
       </c>
       <c r="F28" t="n">
         <v>10992000</v>
@@ -992,16 +992,16 @@
         <v>44294</v>
       </c>
       <c r="B29" t="n">
-        <v>14.70237255096436</v>
+        <v>14.70237159729004</v>
       </c>
       <c r="C29" t="n">
-        <v>14.74035332682097</v>
+        <v>14.74035237068301</v>
       </c>
       <c r="D29" t="n">
-        <v>14.26559317584676</v>
+        <v>14.26559225050429</v>
       </c>
       <c r="E29" t="n">
-        <v>14.43270840850923</v>
+        <v>14.43270747232676</v>
       </c>
       <c r="F29" t="n">
         <v>6395000</v>
@@ -1012,16 +1012,16 @@
         <v>44295</v>
       </c>
       <c r="B30" t="n">
-        <v>14.71756458282471</v>
+        <v>14.71756362915039</v>
       </c>
       <c r="C30" t="n">
-        <v>14.73655542339393</v>
+        <v>14.73655446848903</v>
       </c>
       <c r="D30" t="n">
-        <v>14.40802076359814</v>
+        <v>14.40801982998176</v>
       </c>
       <c r="E30" t="n">
-        <v>14.63210761132946</v>
+        <v>14.63210666319261</v>
       </c>
       <c r="F30" t="n">
         <v>7012500</v>
@@ -1052,16 +1052,16 @@
         <v>44299</v>
       </c>
       <c r="B32" t="n">
-        <v>14.67008590698242</v>
+        <v>14.67008781433105</v>
       </c>
       <c r="C32" t="n">
-        <v>14.81251447057491</v>
+        <v>14.81251639644156</v>
       </c>
       <c r="D32" t="n">
-        <v>14.5276582489229</v>
+        <v>14.52766013775363</v>
       </c>
       <c r="E32" t="n">
-        <v>14.69667235485844</v>
+        <v>14.69667426566374</v>
       </c>
       <c r="F32" t="n">
         <v>5449500</v>
@@ -1072,16 +1072,16 @@
         <v>44300</v>
       </c>
       <c r="B33" t="n">
-        <v>14.93785190582275</v>
+        <v>14.93785285949707</v>
       </c>
       <c r="C33" t="n">
-        <v>14.94544751674995</v>
+        <v>14.9454484709092</v>
       </c>
       <c r="D33" t="n">
-        <v>14.62261050848561</v>
+        <v>14.62261144203403</v>
       </c>
       <c r="E33" t="n">
-        <v>14.65109676606165</v>
+        <v>14.65109770142871</v>
       </c>
       <c r="F33" t="n">
         <v>5841000</v>
@@ -1092,16 +1092,16 @@
         <v>44301</v>
       </c>
       <c r="B34" t="n">
-        <v>15.18662548065186</v>
+        <v>15.18662643432617</v>
       </c>
       <c r="C34" t="n">
-        <v>15.20371560434488</v>
+        <v>15.2037165590924</v>
       </c>
       <c r="D34" t="n">
-        <v>14.84099984660328</v>
+        <v>14.84100077857334</v>
       </c>
       <c r="E34" t="n">
-        <v>14.84099984660328</v>
+        <v>14.84100077857334</v>
       </c>
       <c r="F34" t="n">
         <v>11554500</v>
@@ -1152,16 +1152,16 @@
         <v>44306</v>
       </c>
       <c r="B37" t="n">
-        <v>15.4771785736084</v>
+        <v>15.47717952728271</v>
       </c>
       <c r="C37" t="n">
-        <v>15.65568992191963</v>
+        <v>15.65569088659348</v>
       </c>
       <c r="D37" t="n">
-        <v>15.06698659960384</v>
+        <v>15.06698752800291</v>
       </c>
       <c r="E37" t="n">
-        <v>15.35943935799809</v>
+        <v>15.35944030441754</v>
       </c>
       <c r="F37" t="n">
         <v>6029000</v>
@@ -1172,16 +1172,16 @@
         <v>44308</v>
       </c>
       <c r="B38" t="n">
-        <v>15.27967834472656</v>
+        <v>15.27967739105225</v>
       </c>
       <c r="C38" t="n">
-        <v>15.75254045321392</v>
+        <v>15.75253947002613</v>
       </c>
       <c r="D38" t="n">
-        <v>15.19422319187483</v>
+        <v>15.19422224353416</v>
       </c>
       <c r="E38" t="n">
-        <v>15.50376517258819</v>
+        <v>15.50376420492759</v>
       </c>
       <c r="F38" t="n">
         <v>8470500</v>
@@ -1212,16 +1212,16 @@
         <v>44312</v>
       </c>
       <c r="B40" t="n">
-        <v>15.26069068908691</v>
+        <v>15.2606897354126</v>
       </c>
       <c r="C40" t="n">
-        <v>15.51705979282594</v>
+        <v>15.51705882313055</v>
       </c>
       <c r="D40" t="n">
-        <v>15.16573829718871</v>
+        <v>15.16573734944818</v>
       </c>
       <c r="E40" t="n">
-        <v>15.48477753709752</v>
+        <v>15.48477656941952</v>
       </c>
       <c r="F40" t="n">
         <v>3662000</v>
@@ -1232,16 +1232,16 @@
         <v>44313</v>
       </c>
       <c r="B41" t="n">
-        <v>15.12775802612305</v>
+        <v>15.12775611877441</v>
       </c>
       <c r="C41" t="n">
-        <v>15.2967730720114</v>
+        <v>15.29677114335289</v>
       </c>
       <c r="D41" t="n">
-        <v>15.10117157283271</v>
+        <v>15.10116966883617</v>
       </c>
       <c r="E41" t="n">
-        <v>15.24929596894558</v>
+        <v>15.24929404627311</v>
       </c>
       <c r="F41" t="n">
         <v>4986500</v>
@@ -1272,16 +1272,16 @@
         <v>44315</v>
       </c>
       <c r="B43" t="n">
-        <v>15.21646499633789</v>
+        <v>15.21646595001221</v>
       </c>
       <c r="C43" t="n">
-        <v>15.32323336252505</v>
+        <v>15.32323432289095</v>
       </c>
       <c r="D43" t="n">
-        <v>14.90950503441863</v>
+        <v>14.90950596885459</v>
       </c>
       <c r="E43" t="n">
-        <v>15.26222338706449</v>
+        <v>15.26222434360666</v>
       </c>
       <c r="F43" t="n">
         <v>5343000</v>
@@ -1292,16 +1292,16 @@
         <v>44316</v>
       </c>
       <c r="B44" t="n">
-        <v>15.42237663269043</v>
+        <v>15.42237567901611</v>
       </c>
       <c r="C44" t="n">
-        <v>15.46813502548309</v>
+        <v>15.46813406897922</v>
       </c>
       <c r="D44" t="n">
-        <v>14.92857109851635</v>
+        <v>14.92857017537751</v>
       </c>
       <c r="E44" t="n">
-        <v>15.10016416235762</v>
+        <v>15.10016322860797</v>
       </c>
       <c r="F44" t="n">
         <v>22683000</v>
@@ -1332,16 +1332,16 @@
         <v>44320</v>
       </c>
       <c r="B46" t="n">
-        <v>15.72933673858643</v>
+        <v>15.72933769226074</v>
       </c>
       <c r="C46" t="n">
-        <v>15.74840303768283</v>
+        <v>15.74840399251314</v>
       </c>
       <c r="D46" t="n">
-        <v>15.35945853647056</v>
+        <v>15.35945946771906</v>
       </c>
       <c r="E46" t="n">
-        <v>15.63400706136676</v>
+        <v>15.63400800926121</v>
       </c>
       <c r="F46" t="n">
         <v>9407500</v>
@@ -1372,16 +1372,16 @@
         <v>44322</v>
       </c>
       <c r="B48" t="n">
-        <v>16.61971092224121</v>
+        <v>16.61971282958984</v>
       </c>
       <c r="C48" t="n">
-        <v>16.64449565404135</v>
+        <v>16.64449756423438</v>
       </c>
       <c r="D48" t="n">
-        <v>16.16022334106464</v>
+        <v>16.16022519568053</v>
       </c>
       <c r="E48" t="n">
-        <v>16.31847033527121</v>
+        <v>16.31847220804819</v>
       </c>
       <c r="F48" t="n">
         <v>9404500</v>
@@ -1412,16 +1412,16 @@
         <v>44326</v>
       </c>
       <c r="B50" t="n">
-        <v>16.81418418884277</v>
+        <v>16.81418609619141</v>
       </c>
       <c r="C50" t="n">
-        <v>17.01628222452739</v>
+        <v>17.0162841548014</v>
       </c>
       <c r="D50" t="n">
-        <v>16.55298171903851</v>
+        <v>16.55298359675715</v>
       </c>
       <c r="E50" t="n">
-        <v>16.97052383564365</v>
+        <v>16.97052576072697</v>
       </c>
       <c r="F50" t="n">
         <v>7669500</v>
@@ -1472,16 +1472,16 @@
         <v>44329</v>
       </c>
       <c r="B53" t="n">
-        <v>16.4328670501709</v>
+        <v>16.43286895751953</v>
       </c>
       <c r="C53" t="n">
-        <v>16.5186617551335</v>
+        <v>16.51866367244025</v>
       </c>
       <c r="D53" t="n">
-        <v>16.12781173522566</v>
+        <v>16.12781360716679</v>
       </c>
       <c r="E53" t="n">
-        <v>16.17547748049629</v>
+        <v>16.17547935796994</v>
       </c>
       <c r="F53" t="n">
         <v>6595000</v>
@@ -1512,16 +1512,16 @@
         <v>44333</v>
       </c>
       <c r="B55" t="n">
-        <v>16.34707069396973</v>
+        <v>16.34707450866699</v>
       </c>
       <c r="C55" t="n">
-        <v>16.52819507306194</v>
+        <v>16.52819893002578</v>
       </c>
       <c r="D55" t="n">
-        <v>16.06108167421069</v>
+        <v>16.06108542217052</v>
       </c>
       <c r="E55" t="n">
-        <v>16.50531587875072</v>
+        <v>16.50531973037555</v>
       </c>
       <c r="F55" t="n">
         <v>4728000</v>
@@ -1572,16 +1572,16 @@
         <v>44336</v>
       </c>
       <c r="B58" t="n">
-        <v>16.03248405456543</v>
+        <v>16.03248596191406</v>
       </c>
       <c r="C58" t="n">
-        <v>16.03248405456543</v>
+        <v>16.03248596191406</v>
       </c>
       <c r="D58" t="n">
-        <v>15.69692374997599</v>
+        <v>15.69692561740377</v>
       </c>
       <c r="E58" t="n">
-        <v>15.90283468063725</v>
+        <v>15.90283657256179</v>
       </c>
       <c r="F58" t="n">
         <v>7278000</v>
@@ -1592,16 +1592,16 @@
         <v>44337</v>
       </c>
       <c r="B59" t="n">
-        <v>16.43477249145508</v>
+        <v>16.43477439880371</v>
       </c>
       <c r="C59" t="n">
-        <v>16.62543183488117</v>
+        <v>16.6254337643569</v>
       </c>
       <c r="D59" t="n">
-        <v>15.75984081583289</v>
+        <v>15.75984264485187</v>
       </c>
       <c r="E59" t="n">
-        <v>16.03438932487009</v>
+        <v>16.03439118575198</v>
       </c>
       <c r="F59" t="n">
         <v>10145000</v>
@@ -1672,16 +1672,16 @@
         <v>44343</v>
       </c>
       <c r="B63" t="n">
-        <v>16.94955253601074</v>
+        <v>16.94955444335938</v>
       </c>
       <c r="C63" t="n">
-        <v>17.26223183953111</v>
+        <v>17.26223378206583</v>
       </c>
       <c r="D63" t="n">
-        <v>16.70550899973091</v>
+        <v>16.7055108796171</v>
       </c>
       <c r="E63" t="n">
-        <v>16.94955253601074</v>
+        <v>16.94955444335938</v>
       </c>
       <c r="F63" t="n">
         <v>5669000</v>
@@ -1692,16 +1692,16 @@
         <v>44344</v>
       </c>
       <c r="B64" t="n">
-        <v>16.98577690124512</v>
+        <v>16.98577880859375</v>
       </c>
       <c r="C64" t="n">
-        <v>17.14974233685488</v>
+        <v>17.14974426261534</v>
       </c>
       <c r="D64" t="n">
-        <v>16.56442007870208</v>
+        <v>16.56442193873616</v>
       </c>
       <c r="E64" t="n">
-        <v>16.91141906621777</v>
+        <v>16.91142096521669</v>
       </c>
       <c r="F64" t="n">
         <v>4590500</v>
@@ -1732,16 +1732,16 @@
         <v>44348</v>
       </c>
       <c r="B66" t="n">
-        <v>16.96861457824707</v>
+        <v>16.9686164855957</v>
       </c>
       <c r="C66" t="n">
-        <v>17.4109431969055</v>
+        <v>17.41094515397386</v>
       </c>
       <c r="D66" t="n">
-        <v>16.8256209926954</v>
+        <v>16.82562288397091</v>
       </c>
       <c r="E66" t="n">
-        <v>17.17834020076747</v>
+        <v>17.17834213169021</v>
       </c>
       <c r="F66" t="n">
         <v>13722000</v>
@@ -1752,16 +1752,16 @@
         <v>44349</v>
       </c>
       <c r="B67" t="n">
-        <v>16.76651763916016</v>
+        <v>16.76651954650879</v>
       </c>
       <c r="C67" t="n">
-        <v>17.26032492574389</v>
+        <v>17.26032688926774</v>
       </c>
       <c r="D67" t="n">
-        <v>16.73982554996776</v>
+        <v>16.73982745427992</v>
       </c>
       <c r="E67" t="n">
-        <v>17.06394533438589</v>
+        <v>17.06394727556971</v>
       </c>
       <c r="F67" t="n">
         <v>9352500</v>
@@ -1772,16 +1772,16 @@
         <v>44351</v>
       </c>
       <c r="B68" t="n">
-        <v>16.77223968505859</v>
+        <v>16.77223777770996</v>
       </c>
       <c r="C68" t="n">
-        <v>16.81609071938215</v>
+        <v>16.81608880704675</v>
       </c>
       <c r="D68" t="n">
-        <v>16.40617437066384</v>
+        <v>16.40617250494436</v>
       </c>
       <c r="E68" t="n">
-        <v>16.72266839722167</v>
+        <v>16.72266649551031</v>
       </c>
       <c r="F68" t="n">
         <v>8097000</v>
@@ -1792,16 +1792,16 @@
         <v>44354</v>
       </c>
       <c r="B69" t="n">
-        <v>16.53772926330566</v>
+        <v>16.53772735595703</v>
       </c>
       <c r="C69" t="n">
-        <v>16.77223965606192</v>
+        <v>16.77223772166646</v>
       </c>
       <c r="D69" t="n">
-        <v>16.03057769704888</v>
+        <v>16.03057584819165</v>
       </c>
       <c r="E69" t="n">
-        <v>16.77223965606192</v>
+        <v>16.77223772166646</v>
       </c>
       <c r="F69" t="n">
         <v>10336000</v>
@@ -1812,16 +1812,16 @@
         <v>44355</v>
       </c>
       <c r="B70" t="n">
-        <v>16.08205795288086</v>
+        <v>16.08205604553223</v>
       </c>
       <c r="C70" t="n">
-        <v>16.61018141053224</v>
+        <v>16.61017944054762</v>
       </c>
       <c r="D70" t="n">
-        <v>15.9295293598389</v>
+        <v>15.92952747058032</v>
       </c>
       <c r="E70" t="n">
-        <v>16.60064825982571</v>
+        <v>16.60064629097173</v>
       </c>
       <c r="F70" t="n">
         <v>9246000</v>
@@ -1892,16 +1892,16 @@
         <v>44361</v>
       </c>
       <c r="B74" t="n">
-        <v>16.01532363891602</v>
+        <v>16.01532554626465</v>
       </c>
       <c r="C74" t="n">
-        <v>16.19263694417421</v>
+        <v>16.19263887264001</v>
       </c>
       <c r="D74" t="n">
-        <v>15.85135819737426</v>
+        <v>15.8513600851954</v>
       </c>
       <c r="E74" t="n">
-        <v>16.16403749608867</v>
+        <v>16.16403942114841</v>
       </c>
       <c r="F74" t="n">
         <v>4317000</v>
@@ -1912,16 +1912,16 @@
         <v>44362</v>
       </c>
       <c r="B75" t="n">
-        <v>15.85898399353027</v>
+        <v>15.85898494720459</v>
       </c>
       <c r="C75" t="n">
-        <v>16.02676414946864</v>
+        <v>16.02676511323235</v>
       </c>
       <c r="D75" t="n">
-        <v>15.4872002596367</v>
+        <v>15.48720119095393</v>
       </c>
       <c r="E75" t="n">
-        <v>16.01532364292663</v>
+        <v>16.01532460600237</v>
       </c>
       <c r="F75" t="n">
         <v>8432500</v>
@@ -1972,16 +1972,16 @@
         <v>44365</v>
       </c>
       <c r="B78" t="n">
-        <v>16.20788955688477</v>
+        <v>16.2078914642334</v>
       </c>
       <c r="C78" t="n">
-        <v>16.36422919862247</v>
+        <v>16.36423112436919</v>
       </c>
       <c r="D78" t="n">
-        <v>15.67976438120391</v>
+        <v>15.67976622640263</v>
       </c>
       <c r="E78" t="n">
-        <v>15.98863076877287</v>
+        <v>15.98863265031907</v>
       </c>
       <c r="F78" t="n">
         <v>12012000</v>
@@ -1992,16 +1992,16 @@
         <v>44368</v>
       </c>
       <c r="B79" t="n">
-        <v>16.48434257507324</v>
+        <v>16.48434448242188</v>
       </c>
       <c r="C79" t="n">
-        <v>16.59301828381779</v>
+        <v>16.59302020374093</v>
       </c>
       <c r="D79" t="n">
-        <v>16.00007027813662</v>
+        <v>16.00007212945171</v>
       </c>
       <c r="E79" t="n">
-        <v>16.20788854732228</v>
+        <v>16.20789042268334</v>
       </c>
       <c r="F79" t="n">
         <v>6798000</v>
@@ -2072,16 +2072,16 @@
         <v>44372</v>
       </c>
       <c r="B83" t="n">
-        <v>16.18501091003418</v>
+        <v>16.18501281738281</v>
       </c>
       <c r="C83" t="n">
-        <v>16.74745398613881</v>
+        <v>16.74745595976945</v>
       </c>
       <c r="D83" t="n">
-        <v>16.05345599637458</v>
+        <v>16.05345788821992</v>
       </c>
       <c r="E83" t="n">
-        <v>16.64640405902371</v>
+        <v>16.64640602074596</v>
       </c>
       <c r="F83" t="n">
         <v>6078000</v>
@@ -2132,16 +2132,16 @@
         <v>44377</v>
       </c>
       <c r="B86" t="n">
-        <v>16.49959945678711</v>
+        <v>16.49959564208984</v>
       </c>
       <c r="C86" t="n">
-        <v>16.49959945678711</v>
+        <v>16.49959564208984</v>
       </c>
       <c r="D86" t="n">
-        <v>16.19073120503556</v>
+        <v>16.19072746174845</v>
       </c>
       <c r="E86" t="n">
-        <v>16.38901636774828</v>
+        <v>16.38901257861776</v>
       </c>
       <c r="F86" t="n">
         <v>6685000</v>
@@ -2212,16 +2212,16 @@
         <v>44383</v>
       </c>
       <c r="B90" t="n">
-        <v>16.33944702148438</v>
+        <v>16.33944320678711</v>
       </c>
       <c r="C90" t="n">
-        <v>16.3890183180616</v>
+        <v>16.38901449179115</v>
       </c>
       <c r="D90" t="n">
-        <v>16.11256419909116</v>
+        <v>16.11256043736321</v>
       </c>
       <c r="E90" t="n">
-        <v>16.3890183180616</v>
+        <v>16.38901449179115</v>
       </c>
       <c r="F90" t="n">
         <v>3828000</v>
@@ -2252,16 +2252,16 @@
         <v>44385</v>
       </c>
       <c r="B92" t="n">
-        <v>16.43477249145508</v>
+        <v>16.43477439880371</v>
       </c>
       <c r="C92" t="n">
-        <v>16.79893041915436</v>
+        <v>16.79893236876558</v>
       </c>
       <c r="D92" t="n">
-        <v>16.24411496629124</v>
+        <v>16.24411685151298</v>
       </c>
       <c r="E92" t="n">
-        <v>16.26317944602405</v>
+        <v>16.26318133345833</v>
       </c>
       <c r="F92" t="n">
         <v>7435000</v>
@@ -2272,16 +2272,16 @@
         <v>44389</v>
       </c>
       <c r="B93" t="n">
-        <v>16.50150299072266</v>
+        <v>16.50150108337402</v>
       </c>
       <c r="C93" t="n">
-        <v>16.60255291716791</v>
+        <v>16.60255099813928</v>
       </c>
       <c r="D93" t="n">
-        <v>16.2746202228983</v>
+        <v>16.27461834177422</v>
       </c>
       <c r="E93" t="n">
-        <v>16.43095986888196</v>
+        <v>16.43095796968715</v>
       </c>
       <c r="F93" t="n">
         <v>4327500</v>
@@ -2292,16 +2292,16 @@
         <v>44390</v>
       </c>
       <c r="B94" t="n">
-        <v>16.78749465942383</v>
+        <v>16.7874927520752</v>
       </c>
       <c r="C94" t="n">
-        <v>16.91142198148287</v>
+        <v>16.91142006005396</v>
       </c>
       <c r="D94" t="n">
-        <v>16.4309624614306</v>
+        <v>16.43096059459017</v>
       </c>
       <c r="E94" t="n">
-        <v>16.45384165936285</v>
+        <v>16.45383978992295</v>
       </c>
       <c r="F94" t="n">
         <v>6446000</v>
@@ -2312,16 +2312,16 @@
         <v>44391</v>
       </c>
       <c r="B95" t="n">
-        <v>16.7226676940918</v>
+        <v>16.72266578674316</v>
       </c>
       <c r="C95" t="n">
-        <v>17.08873299309478</v>
+        <v>17.08873104399359</v>
       </c>
       <c r="D95" t="n">
-        <v>16.67309640833917</v>
+        <v>16.67309450664453</v>
       </c>
       <c r="E95" t="n">
-        <v>16.9304859864696</v>
+        <v>16.9304840554177</v>
       </c>
       <c r="F95" t="n">
         <v>5548000</v>
@@ -2332,16 +2332,16 @@
         <v>44392</v>
       </c>
       <c r="B96" t="n">
-        <v>16.45002555847168</v>
+        <v>16.45002746582031</v>
       </c>
       <c r="C96" t="n">
-        <v>16.86375476157448</v>
+        <v>16.86375671689422</v>
       </c>
       <c r="D96" t="n">
-        <v>16.44049240966831</v>
+        <v>16.44049431591159</v>
       </c>
       <c r="E96" t="n">
-        <v>16.72266670485169</v>
+        <v>16.72266864381253</v>
       </c>
       <c r="F96" t="n">
         <v>3746000</v>
@@ -2352,16 +2352,16 @@
         <v>44393</v>
       </c>
       <c r="B97" t="n">
-        <v>16.67119216918945</v>
+        <v>16.67119026184082</v>
       </c>
       <c r="C97" t="n">
-        <v>16.86947550939675</v>
+        <v>16.86947357936254</v>
       </c>
       <c r="D97" t="n">
-        <v>16.52247830033713</v>
+        <v>16.52247641000283</v>
       </c>
       <c r="E97" t="n">
-        <v>16.54154278229579</v>
+        <v>16.54154088978033</v>
       </c>
       <c r="F97" t="n">
         <v>7965000</v>
@@ -2392,16 +2392,16 @@
         <v>44397</v>
       </c>
       <c r="B99" t="n">
-        <v>16.51103973388672</v>
+        <v>16.51103782653809</v>
       </c>
       <c r="C99" t="n">
-        <v>16.7169507093462</v>
+        <v>16.71694877821082</v>
       </c>
       <c r="D99" t="n">
-        <v>16.45956289915319</v>
+        <v>16.45956099775114</v>
       </c>
       <c r="E99" t="n">
-        <v>16.6540333658301</v>
+        <v>16.6540314419629</v>
       </c>
       <c r="F99" t="n">
         <v>3835500</v>
@@ -2412,16 +2412,16 @@
         <v>44398</v>
       </c>
       <c r="B100" t="n">
-        <v>16.59683609008789</v>
+        <v>16.59683418273926</v>
       </c>
       <c r="C100" t="n">
-        <v>16.59683609008789</v>
+        <v>16.59683418273926</v>
       </c>
       <c r="D100" t="n">
-        <v>16.41570985525612</v>
+        <v>16.41570796872296</v>
       </c>
       <c r="E100" t="n">
-        <v>16.516759802561</v>
+        <v>16.51675790441493</v>
       </c>
       <c r="F100" t="n">
         <v>4032000</v>
@@ -2432,16 +2432,16 @@
         <v>44399</v>
       </c>
       <c r="B101" t="n">
-        <v>16.64449882507324</v>
+        <v>16.64449501037598</v>
       </c>
       <c r="C101" t="n">
-        <v>16.68072406942274</v>
+        <v>16.68072024642313</v>
       </c>
       <c r="D101" t="n">
-        <v>16.44430812071748</v>
+        <v>16.44430435190125</v>
       </c>
       <c r="E101" t="n">
-        <v>16.58730174072338</v>
+        <v>16.58729793913493</v>
       </c>
       <c r="F101" t="n">
         <v>2829500</v>
@@ -2452,16 +2452,16 @@
         <v>44400</v>
       </c>
       <c r="B102" t="n">
-        <v>16.6826286315918</v>
+        <v>16.68262672424316</v>
       </c>
       <c r="C102" t="n">
-        <v>16.73029255752003</v>
+        <v>16.73029064472191</v>
       </c>
       <c r="D102" t="n">
-        <v>16.56060687203135</v>
+        <v>16.56060497863364</v>
       </c>
       <c r="E102" t="n">
-        <v>16.64449603623943</v>
+        <v>16.64449413325056</v>
       </c>
       <c r="F102" t="n">
         <v>4154500</v>
@@ -2492,16 +2492,16 @@
         <v>44404</v>
       </c>
       <c r="B104" t="n">
-        <v>16.96861457824707</v>
+        <v>16.9686164855957</v>
       </c>
       <c r="C104" t="n">
-        <v>17.30036195137194</v>
+        <v>17.30036389601047</v>
       </c>
       <c r="D104" t="n">
-        <v>16.87328673338735</v>
+        <v>16.8732886300207</v>
       </c>
       <c r="E104" t="n">
-        <v>17.14402050381685</v>
+        <v>17.1440224308819</v>
       </c>
       <c r="F104" t="n">
         <v>6666500</v>
@@ -2532,16 +2532,16 @@
         <v>44406</v>
       </c>
       <c r="B106" t="n">
-        <v>16.62543106079102</v>
+        <v>16.62543487548828</v>
       </c>
       <c r="C106" t="n">
-        <v>16.77795780112525</v>
+        <v>16.7779616508197</v>
       </c>
       <c r="D106" t="n">
-        <v>16.27461919436984</v>
+        <v>16.27462292857349</v>
       </c>
       <c r="E106" t="n">
-        <v>16.77795780112525</v>
+        <v>16.7779616508197</v>
       </c>
       <c r="F106" t="n">
         <v>12625000</v>
@@ -2572,16 +2572,16 @@
         <v>44410</v>
       </c>
       <c r="B108" t="n">
-        <v>16.52247428894043</v>
+        <v>16.52247619628906</v>
       </c>
       <c r="C108" t="n">
-        <v>16.83896643176442</v>
+        <v>16.83896837564879</v>
       </c>
       <c r="D108" t="n">
-        <v>16.3623199515334</v>
+        <v>16.36232184039388</v>
       </c>
       <c r="E108" t="n">
-        <v>16.68262680808543</v>
+        <v>16.68262873392202</v>
       </c>
       <c r="F108" t="n">
         <v>8100500</v>
@@ -2592,16 +2592,16 @@
         <v>44411</v>
       </c>
       <c r="B109" t="n">
-        <v>16.53010368347168</v>
+        <v>16.53010177612305</v>
       </c>
       <c r="C109" t="n">
-        <v>16.68072308765598</v>
+        <v>16.68072116292792</v>
       </c>
       <c r="D109" t="n">
-        <v>16.26127540276083</v>
+        <v>16.26127352643131</v>
       </c>
       <c r="E109" t="n">
-        <v>16.68072308765598</v>
+        <v>16.68072116292792</v>
       </c>
       <c r="F109" t="n">
         <v>5450500</v>
@@ -2652,16 +2652,16 @@
         <v>44414</v>
       </c>
       <c r="B112" t="n">
-        <v>16.73982810974121</v>
+        <v>16.73982429504395</v>
       </c>
       <c r="C112" t="n">
-        <v>16.78368096434495</v>
+        <v>16.78367713965443</v>
       </c>
       <c r="D112" t="n">
-        <v>16.37567013584921</v>
+        <v>16.37566640413682</v>
       </c>
       <c r="E112" t="n">
-        <v>16.63115237929877</v>
+        <v>16.6311485893667</v>
       </c>
       <c r="F112" t="n">
         <v>15424500</v>
@@ -2672,16 +2672,16 @@
         <v>44417</v>
       </c>
       <c r="B113" t="n">
-        <v>17.31942939758301</v>
+        <v>17.31942749023438</v>
       </c>
       <c r="C113" t="n">
-        <v>17.35756199667172</v>
+        <v>17.35756008512363</v>
       </c>
       <c r="D113" t="n">
-        <v>16.6178055750599</v>
+        <v>16.61780374497947</v>
       </c>
       <c r="E113" t="n">
-        <v>16.6178055750599</v>
+        <v>16.61780374497947</v>
       </c>
       <c r="F113" t="n">
         <v>10558500</v>
@@ -2692,16 +2692,16 @@
         <v>44418</v>
       </c>
       <c r="B114" t="n">
-        <v>17.55012893676758</v>
+        <v>17.55012702941895</v>
       </c>
       <c r="C114" t="n">
-        <v>17.66452492908273</v>
+        <v>17.66452300930153</v>
       </c>
       <c r="D114" t="n">
-        <v>17.10589465161376</v>
+        <v>17.10589279254452</v>
       </c>
       <c r="E114" t="n">
-        <v>17.22219618314763</v>
+        <v>17.22219431143875</v>
       </c>
       <c r="F114" t="n">
         <v>10281500</v>
@@ -2712,16 +2712,16 @@
         <v>44419</v>
       </c>
       <c r="B115" t="n">
-        <v>17.2088451385498</v>
+        <v>17.20884704589844</v>
       </c>
       <c r="C115" t="n">
-        <v>17.57872328499242</v>
+        <v>17.57872523333663</v>
       </c>
       <c r="D115" t="n">
-        <v>17.1974064517711</v>
+        <v>17.19740835785192</v>
       </c>
       <c r="E115" t="n">
-        <v>17.57872328499242</v>
+        <v>17.57872523333663</v>
       </c>
       <c r="F115" t="n">
         <v>6265000</v>
@@ -2732,16 +2732,16 @@
         <v>44420</v>
       </c>
       <c r="B116" t="n">
-        <v>16.92095375061035</v>
+        <v>16.92094993591309</v>
       </c>
       <c r="C116" t="n">
-        <v>17.24507357354782</v>
+        <v>17.24506968578027</v>
       </c>
       <c r="D116" t="n">
-        <v>16.68263045834824</v>
+        <v>16.6826266973791</v>
       </c>
       <c r="E116" t="n">
-        <v>16.98768398152176</v>
+        <v>16.98768015178068</v>
       </c>
       <c r="F116" t="n">
         <v>14059400</v>
@@ -2752,16 +2752,16 @@
         <v>44421</v>
       </c>
       <c r="B117" t="n">
-        <v>16.91142082214355</v>
+        <v>16.91141891479492</v>
       </c>
       <c r="C117" t="n">
-        <v>17.27367324935177</v>
+        <v>17.27367130114663</v>
       </c>
       <c r="D117" t="n">
-        <v>16.53010391318421</v>
+        <v>16.53010204884227</v>
       </c>
       <c r="E117" t="n">
-        <v>16.82562429034489</v>
+        <v>16.82562239267279</v>
       </c>
       <c r="F117" t="n">
         <v>5547600</v>
@@ -2792,16 +2792,16 @@
         <v>44425</v>
       </c>
       <c r="B119" t="n">
-        <v>16.16784858703613</v>
+        <v>16.1678524017334</v>
       </c>
       <c r="C119" t="n">
-        <v>16.39664050965117</v>
+        <v>16.39664437833038</v>
       </c>
       <c r="D119" t="n">
-        <v>15.70073523003284</v>
+        <v>15.70073893451779</v>
       </c>
       <c r="E119" t="n">
-        <v>16.16784858703613</v>
+        <v>16.1678524017334</v>
       </c>
       <c r="F119" t="n">
         <v>9967800</v>
@@ -2852,16 +2852,16 @@
         <v>44428</v>
       </c>
       <c r="B122" t="n">
-        <v>16.94955253601074</v>
+        <v>16.94955444335938</v>
       </c>
       <c r="C122" t="n">
-        <v>17.41666595234703</v>
+        <v>17.41666791226037</v>
       </c>
       <c r="D122" t="n">
-        <v>16.37757629334467</v>
+        <v>16.3775781363283</v>
       </c>
       <c r="E122" t="n">
-        <v>16.53963619846235</v>
+        <v>16.53963805968273</v>
       </c>
       <c r="F122" t="n">
         <v>9513400</v>
@@ -2872,16 +2872,16 @@
         <v>44431</v>
       </c>
       <c r="B123" t="n">
-        <v>16.69216156005859</v>
+        <v>16.69216537475586</v>
       </c>
       <c r="C123" t="n">
-        <v>17.16880808609706</v>
+        <v>17.16881200972343</v>
       </c>
       <c r="D123" t="n">
-        <v>16.52056851976279</v>
+        <v>16.52057229524551</v>
       </c>
       <c r="E123" t="n">
-        <v>16.9781487483768</v>
+        <v>16.97815262843136</v>
       </c>
       <c r="F123" t="n">
         <v>5050600</v>
@@ -2892,16 +2892,16 @@
         <v>44432</v>
       </c>
       <c r="B124" t="n">
-        <v>16.91142082214355</v>
+        <v>16.91141891479492</v>
       </c>
       <c r="C124" t="n">
-        <v>17.05441443572051</v>
+        <v>17.05441251224439</v>
       </c>
       <c r="D124" t="n">
-        <v>16.66356437675437</v>
+        <v>16.66356249736014</v>
       </c>
       <c r="E124" t="n">
-        <v>16.78749350858018</v>
+        <v>16.78749161520865</v>
       </c>
       <c r="F124" t="n">
         <v>4198100</v>
@@ -2912,16 +2912,16 @@
         <v>44433</v>
       </c>
       <c r="B125" t="n">
-        <v>17.01628303527832</v>
+        <v>17.01628494262695</v>
       </c>
       <c r="C125" t="n">
-        <v>17.19740924229705</v>
+        <v>17.19741116994805</v>
       </c>
       <c r="D125" t="n">
-        <v>16.78749289822105</v>
+        <v>16.78749477992469</v>
       </c>
       <c r="E125" t="n">
-        <v>17.0258161849385</v>
+        <v>17.0258180933557</v>
       </c>
       <c r="F125" t="n">
         <v>4269900</v>
@@ -2932,16 +2932,16 @@
         <v>44434</v>
       </c>
       <c r="B126" t="n">
-        <v>16.5587043762207</v>
+        <v>16.55870246887207</v>
       </c>
       <c r="C126" t="n">
-        <v>17.00675154437543</v>
+        <v>17.00674958541756</v>
       </c>
       <c r="D126" t="n">
-        <v>16.5587043762207</v>
+        <v>16.55870246887207</v>
       </c>
       <c r="E126" t="n">
-        <v>16.93048815791797</v>
+        <v>16.93048620774466</v>
       </c>
       <c r="F126" t="n">
         <v>4969900</v>
@@ -2992,16 +2992,16 @@
         <v>44439</v>
       </c>
       <c r="B129" t="n">
-        <v>16.02485656738281</v>
+        <v>16.02485275268555</v>
       </c>
       <c r="C129" t="n">
-        <v>16.63496539029478</v>
+        <v>16.63496143036187</v>
       </c>
       <c r="D129" t="n">
-        <v>16.02485656738281</v>
+        <v>16.02485275268555</v>
       </c>
       <c r="E129" t="n">
-        <v>16.37757581585984</v>
+        <v>16.3775719171982</v>
       </c>
       <c r="F129" t="n">
         <v>8477100</v>
@@ -3032,16 +3032,16 @@
         <v>44441</v>
       </c>
       <c r="B131" t="n">
-        <v>16.72076034545898</v>
+        <v>16.72076225280762</v>
       </c>
       <c r="C131" t="n">
-        <v>17.0353469674827</v>
+        <v>17.03534891071645</v>
       </c>
       <c r="D131" t="n">
-        <v>16.10111843148494</v>
+        <v>16.10112026815059</v>
       </c>
       <c r="E131" t="n">
-        <v>16.16784865157147</v>
+        <v>16.16785049584908</v>
       </c>
       <c r="F131" t="n">
         <v>17566400</v>
@@ -3052,16 +3052,16 @@
         <v>44442</v>
       </c>
       <c r="B132" t="n">
-        <v>17.31180381774902</v>
+        <v>17.31180191040039</v>
       </c>
       <c r="C132" t="n">
-        <v>17.35946774893307</v>
+        <v>17.359465836333</v>
       </c>
       <c r="D132" t="n">
-        <v>16.69216362104432</v>
+        <v>16.69216178196529</v>
       </c>
       <c r="E132" t="n">
-        <v>16.90188746382151</v>
+        <v>16.9018856016359</v>
       </c>
       <c r="F132" t="n">
         <v>19565300</v>
@@ -3072,16 +3072,16 @@
         <v>44445</v>
       </c>
       <c r="B133" t="n">
-        <v>17.49292755126953</v>
+        <v>17.4929313659668</v>
       </c>
       <c r="C133" t="n">
-        <v>17.66452058844603</v>
+        <v>17.66452444056273</v>
       </c>
       <c r="D133" t="n">
-        <v>17.04487866125041</v>
+        <v>17.04488237824128</v>
       </c>
       <c r="E133" t="n">
-        <v>17.30226821701516</v>
+        <v>17.30227199013519</v>
       </c>
       <c r="F133" t="n">
         <v>6471000</v>
@@ -3092,16 +3092,16 @@
         <v>44447</v>
       </c>
       <c r="B134" t="n">
-        <v>17.0734806060791</v>
+        <v>17.07347679138184</v>
       </c>
       <c r="C134" t="n">
-        <v>17.55012719322427</v>
+        <v>17.55012327203071</v>
       </c>
       <c r="D134" t="n">
-        <v>16.84469046244091</v>
+        <v>16.84468669886182</v>
       </c>
       <c r="E134" t="n">
-        <v>17.49293011188033</v>
+        <v>17.49292620346622</v>
       </c>
       <c r="F134" t="n">
         <v>11069100</v>
@@ -3172,16 +3172,16 @@
         <v>44453</v>
       </c>
       <c r="B138" t="n">
-        <v>17.4738655090332</v>
+        <v>17.47386360168457</v>
       </c>
       <c r="C138" t="n">
-        <v>18.15070467400888</v>
+        <v>18.1507026927803</v>
       </c>
       <c r="D138" t="n">
-        <v>17.39760212041395</v>
+        <v>17.3976002213898</v>
       </c>
       <c r="E138" t="n">
-        <v>17.82658481781139</v>
+        <v>17.82658287196191</v>
       </c>
       <c r="F138" t="n">
         <v>6594500</v>
@@ -3192,16 +3192,16 @@
         <v>44454</v>
       </c>
       <c r="B139" t="n">
-        <v>17.72172355651855</v>
+        <v>17.72171974182129</v>
       </c>
       <c r="C139" t="n">
-        <v>17.82658640706712</v>
+        <v>17.82658256979756</v>
       </c>
       <c r="D139" t="n">
-        <v>17.27367633571945</v>
+        <v>17.27367261746679</v>
       </c>
       <c r="E139" t="n">
-        <v>17.46433391513358</v>
+        <v>17.46433015584083</v>
       </c>
       <c r="F139" t="n">
         <v>8756500</v>
@@ -3232,16 +3232,16 @@
         <v>44456</v>
       </c>
       <c r="B141" t="n">
-        <v>18.11256790161133</v>
+        <v>18.11256980895996</v>
       </c>
       <c r="C141" t="n">
-        <v>18.4462208318724</v>
+        <v>18.44622277435644</v>
       </c>
       <c r="D141" t="n">
-        <v>18.11256790161133</v>
+        <v>18.11256980895996</v>
       </c>
       <c r="E141" t="n">
-        <v>18.28416094107486</v>
+        <v>18.28416286649314</v>
       </c>
       <c r="F141" t="n">
         <v>23104900</v>
@@ -3252,16 +3252,16 @@
         <v>44459</v>
       </c>
       <c r="B142" t="n">
-        <v>17.94097518920898</v>
+        <v>17.94097709655762</v>
       </c>
       <c r="C142" t="n">
-        <v>18.12210138064041</v>
+        <v>18.12210330724501</v>
       </c>
       <c r="D142" t="n">
-        <v>17.63592169938482</v>
+        <v>17.63592357430248</v>
       </c>
       <c r="E142" t="n">
-        <v>18.02677171050481</v>
+        <v>18.02677362697468</v>
       </c>
       <c r="F142" t="n">
         <v>15522000</v>
@@ -3272,16 +3272,16 @@
         <v>44460</v>
       </c>
       <c r="B143" t="n">
-        <v>18.57968330383301</v>
+        <v>18.57968139648438</v>
       </c>
       <c r="C143" t="n">
-        <v>18.7417432123123</v>
+        <v>18.74174128832697</v>
       </c>
       <c r="D143" t="n">
-        <v>17.82658265967325</v>
+        <v>17.82658082963624</v>
       </c>
       <c r="E143" t="n">
-        <v>18.06490594753913</v>
+        <v>18.06490409303639</v>
       </c>
       <c r="F143" t="n">
         <v>17756900</v>
@@ -3312,16 +3312,16 @@
         <v>44462</v>
       </c>
       <c r="B145" t="n">
-        <v>18.29369735717773</v>
+        <v>18.2936954498291</v>
       </c>
       <c r="C145" t="n">
-        <v>18.53202066160796</v>
+        <v>18.53201872941112</v>
       </c>
       <c r="D145" t="n">
-        <v>18.07443853522241</v>
+        <v>18.07443665073428</v>
       </c>
       <c r="E145" t="n">
-        <v>18.34136129075877</v>
+        <v>18.34135937844058</v>
       </c>
       <c r="F145" t="n">
         <v>20822300</v>
@@ -3352,16 +3352,16 @@
         <v>44466</v>
       </c>
       <c r="B147" t="n">
-        <v>18.35089683532715</v>
+        <v>18.35089302062988</v>
       </c>
       <c r="C147" t="n">
-        <v>18.46529283641415</v>
+        <v>18.46528899793678</v>
       </c>
       <c r="D147" t="n">
-        <v>17.83611755782977</v>
+        <v>17.83611385014238</v>
       </c>
       <c r="E147" t="n">
-        <v>18.01724380194138</v>
+        <v>18.01724005660232</v>
       </c>
       <c r="F147" t="n">
         <v>7788100</v>
@@ -3412,16 +3412,16 @@
         <v>44469</v>
       </c>
       <c r="B150" t="n">
-        <v>18.15070152282715</v>
+        <v>18.15069961547852</v>
       </c>
       <c r="C150" t="n">
-        <v>18.62734807351153</v>
+        <v>18.62734611607496</v>
       </c>
       <c r="D150" t="n">
-        <v>18.04583869983265</v>
+        <v>18.04583680350343</v>
       </c>
       <c r="E150" t="n">
-        <v>18.30322827358517</v>
+        <v>18.30322635020841</v>
       </c>
       <c r="F150" t="n">
         <v>10293000</v>
@@ -3472,16 +3472,16 @@
         <v>44474</v>
       </c>
       <c r="B153" t="n">
-        <v>18.32229423522949</v>
+        <v>18.32229232788086</v>
       </c>
       <c r="C153" t="n">
-        <v>18.49388729827244</v>
+        <v>18.49388537306099</v>
       </c>
       <c r="D153" t="n">
-        <v>18.04584015897554</v>
+        <v>18.04583828040574</v>
       </c>
       <c r="E153" t="n">
-        <v>18.34136053518147</v>
+        <v>18.34135862584804</v>
       </c>
       <c r="F153" t="n">
         <v>8000200</v>
@@ -3492,16 +3492,16 @@
         <v>44475</v>
       </c>
       <c r="B154" t="n">
-        <v>18.27167892456055</v>
+        <v>18.27167701721191</v>
       </c>
       <c r="C154" t="n">
-        <v>18.63481816893143</v>
+        <v>18.63481622367532</v>
       </c>
       <c r="D154" t="n">
-        <v>18.06143878380436</v>
+        <v>18.06143689840233</v>
       </c>
       <c r="E154" t="n">
-        <v>18.11877617550022</v>
+        <v>18.11877428411284</v>
       </c>
       <c r="F154" t="n">
         <v>10611600</v>
@@ -3512,16 +3512,16 @@
         <v>44476</v>
       </c>
       <c r="B155" t="n">
-        <v>18.08055305480957</v>
+        <v>18.08055114746094</v>
       </c>
       <c r="C155" t="n">
-        <v>18.36724185503171</v>
+        <v>18.36723991743979</v>
       </c>
       <c r="D155" t="n">
-        <v>17.99454605019834</v>
+        <v>17.99454415192273</v>
       </c>
       <c r="E155" t="n">
-        <v>18.27168013677296</v>
+        <v>18.271678209262</v>
       </c>
       <c r="F155" t="n">
         <v>7169200</v>
@@ -3532,16 +3532,16 @@
         <v>44477</v>
       </c>
       <c r="B156" t="n">
-        <v>17.48805999755859</v>
+        <v>17.48805809020996</v>
       </c>
       <c r="C156" t="n">
-        <v>18.32901694393641</v>
+        <v>18.32901494486817</v>
       </c>
       <c r="D156" t="n">
-        <v>17.3638286741761</v>
+        <v>17.36382678037685</v>
       </c>
       <c r="E156" t="n">
-        <v>18.06143940232113</v>
+        <v>18.06143743243643</v>
       </c>
       <c r="F156" t="n">
         <v>14612800</v>
@@ -3592,16 +3592,16 @@
         <v>44483</v>
       </c>
       <c r="B159" t="n">
-        <v>17.06758117675781</v>
+        <v>17.06757926940918</v>
       </c>
       <c r="C159" t="n">
-        <v>17.14403163282309</v>
+        <v>17.14402971693091</v>
       </c>
       <c r="D159" t="n">
-        <v>16.6088766176435</v>
+        <v>16.60887476155634</v>
       </c>
       <c r="E159" t="n">
-        <v>16.96246111614706</v>
+        <v>16.96245922054588</v>
       </c>
       <c r="F159" t="n">
         <v>10051300</v>
@@ -3612,16 +3612,16 @@
         <v>44484</v>
       </c>
       <c r="B160" t="n">
-        <v>16.76177787780762</v>
+        <v>16.76177978515625</v>
       </c>
       <c r="C160" t="n">
-        <v>16.933790021779</v>
+        <v>16.93379194870116</v>
       </c>
       <c r="D160" t="n">
-        <v>15.86348373102988</v>
+        <v>15.86348553616024</v>
       </c>
       <c r="E160" t="n">
-        <v>15.95904724838453</v>
+        <v>15.95904906438921</v>
       </c>
       <c r="F160" t="n">
         <v>78021300</v>
@@ -3632,16 +3632,16 @@
         <v>44487</v>
       </c>
       <c r="B161" t="n">
-        <v>16.20750999450684</v>
+        <v>16.2075138092041</v>
       </c>
       <c r="C161" t="n">
-        <v>16.67577105168735</v>
+        <v>16.67577497659736</v>
       </c>
       <c r="D161" t="n">
-        <v>16.10239176487586</v>
+        <v>16.10239555483187</v>
       </c>
       <c r="E161" t="n">
-        <v>16.5897640675295</v>
+        <v>16.58976797219639</v>
       </c>
       <c r="F161" t="n">
         <v>13070300</v>
@@ -3652,16 +3652,16 @@
         <v>44488</v>
       </c>
       <c r="B162" t="n">
-        <v>15.81570053100586</v>
+        <v>15.81570339202881</v>
       </c>
       <c r="C162" t="n">
-        <v>16.07372147240036</v>
+        <v>16.0737243800987</v>
       </c>
       <c r="D162" t="n">
-        <v>15.63413185911114</v>
+        <v>15.63413468728875</v>
       </c>
       <c r="E162" t="n">
-        <v>16.05460840502542</v>
+        <v>16.05461130926624</v>
       </c>
       <c r="F162" t="n">
         <v>17605400</v>
@@ -3672,16 +3672,16 @@
         <v>44489</v>
       </c>
       <c r="B163" t="n">
-        <v>15.98771476745605</v>
+        <v>15.98771667480469</v>
       </c>
       <c r="C163" t="n">
-        <v>16.21706611174061</v>
+        <v>16.21706804645106</v>
       </c>
       <c r="D163" t="n">
-        <v>15.71058257663313</v>
+        <v>15.71058445091965</v>
       </c>
       <c r="E163" t="n">
-        <v>15.93993392091769</v>
+        <v>15.93993582256603</v>
       </c>
       <c r="F163" t="n">
         <v>11472200</v>
@@ -3692,16 +3692,16 @@
         <v>44490</v>
       </c>
       <c r="B164" t="n">
-        <v>15.70102882385254</v>
+        <v>15.70102977752686</v>
       </c>
       <c r="C164" t="n">
-        <v>16.21706898421667</v>
+        <v>16.21706996923507</v>
       </c>
       <c r="D164" t="n">
-        <v>15.31877651567118</v>
+        <v>15.31877744612764</v>
       </c>
       <c r="E164" t="n">
-        <v>15.81570360494555</v>
+        <v>15.81570456558517</v>
       </c>
       <c r="F164" t="n">
         <v>11995800</v>
@@ -3712,16 +3712,16 @@
         <v>44491</v>
       </c>
       <c r="B165" t="n">
-        <v>15.39522647857666</v>
+        <v>15.39522552490234</v>
       </c>
       <c r="C165" t="n">
-        <v>15.64369092652619</v>
+        <v>15.64368995746047</v>
       </c>
       <c r="D165" t="n">
-        <v>14.76450882346753</v>
+        <v>14.76450790886372</v>
       </c>
       <c r="E165" t="n">
-        <v>15.39522647857666</v>
+        <v>15.39522552490234</v>
       </c>
       <c r="F165" t="n">
         <v>24678500</v>
@@ -3752,16 +3752,16 @@
         <v>44495</v>
       </c>
       <c r="B167" t="n">
-        <v>15.24232292175293</v>
+        <v>15.24232387542725</v>
       </c>
       <c r="C167" t="n">
-        <v>15.44300558214752</v>
+        <v>15.44300654837805</v>
       </c>
       <c r="D167" t="n">
-        <v>15.01297157026232</v>
+        <v>15.0129725095867</v>
       </c>
       <c r="E167" t="n">
-        <v>15.3856681999555</v>
+        <v>15.38566916259858</v>
       </c>
       <c r="F167" t="n">
         <v>7090300</v>
@@ -3772,16 +3772,16 @@
         <v>44496</v>
       </c>
       <c r="B168" t="n">
-        <v>14.94607925415039</v>
+        <v>14.94607830047607</v>
       </c>
       <c r="C168" t="n">
-        <v>15.38566984725368</v>
+        <v>15.38566886553011</v>
       </c>
       <c r="D168" t="n">
-        <v>14.81229049577588</v>
+        <v>14.81228955063831</v>
       </c>
       <c r="E168" t="n">
-        <v>15.38566984725368</v>
+        <v>15.38566886553011</v>
       </c>
       <c r="F168" t="n">
         <v>9783700</v>
@@ -3852,16 +3852,16 @@
         <v>44503</v>
       </c>
       <c r="B172" t="n">
-        <v>14.74539566040039</v>
+        <v>14.74539661407471</v>
       </c>
       <c r="C172" t="n">
-        <v>14.86962787591666</v>
+        <v>14.86962883762583</v>
       </c>
       <c r="D172" t="n">
-        <v>14.07645282125721</v>
+        <v>14.07645373166693</v>
       </c>
       <c r="E172" t="n">
-        <v>14.14334765198831</v>
+        <v>14.14334856672452</v>
       </c>
       <c r="F172" t="n">
         <v>21906500</v>
@@ -3872,16 +3872,16 @@
         <v>44504</v>
       </c>
       <c r="B173" t="n">
-        <v>14.52560138702393</v>
+        <v>14.52560043334961</v>
       </c>
       <c r="C173" t="n">
-        <v>14.73584061228703</v>
+        <v>14.73583964480952</v>
       </c>
       <c r="D173" t="n">
-        <v>14.30580653757357</v>
+        <v>14.30580559832982</v>
       </c>
       <c r="E173" t="n">
-        <v>14.69761538145387</v>
+        <v>14.69761441648602</v>
       </c>
       <c r="F173" t="n">
         <v>4262500</v>
@@ -3892,16 +3892,16 @@
         <v>44505</v>
       </c>
       <c r="B174" t="n">
-        <v>14.56382465362549</v>
+        <v>14.56382656097412</v>
       </c>
       <c r="C174" t="n">
-        <v>14.71672555633632</v>
+        <v>14.71672748370959</v>
       </c>
       <c r="D174" t="n">
-        <v>14.17201586258867</v>
+        <v>14.17201771862414</v>
       </c>
       <c r="E174" t="n">
-        <v>14.54471249646727</v>
+        <v>14.54471440131288</v>
       </c>
       <c r="F174" t="n">
         <v>8161700</v>
@@ -3912,16 +3912,16 @@
         <v>44508</v>
       </c>
       <c r="B175" t="n">
-        <v>14.73583984375</v>
+        <v>14.73583889007568</v>
       </c>
       <c r="C175" t="n">
-        <v>14.89829729415845</v>
+        <v>14.89829632997021</v>
       </c>
       <c r="D175" t="n">
-        <v>14.2866927213642</v>
+        <v>14.28669179675779</v>
       </c>
       <c r="E175" t="n">
-        <v>14.39181278419399</v>
+        <v>14.39181185278442</v>
       </c>
       <c r="F175" t="n">
         <v>8290300</v>
@@ -3972,16 +3972,16 @@
         <v>44511</v>
       </c>
       <c r="B178" t="n">
-        <v>15.19454288482666</v>
+        <v>15.19454193115234</v>
       </c>
       <c r="C178" t="n">
-        <v>15.51945779195179</v>
+        <v>15.51945681788442</v>
       </c>
       <c r="D178" t="n">
-        <v>15.07986719608156</v>
+        <v>15.07986624960478</v>
       </c>
       <c r="E178" t="n">
-        <v>15.43345079755262</v>
+        <v>15.43344982888343</v>
       </c>
       <c r="F178" t="n">
         <v>5555700</v>
@@ -4012,16 +4012,16 @@
         <v>44516</v>
       </c>
       <c r="B180" t="n">
-        <v>14.18157291412354</v>
+        <v>14.18157386779785</v>
       </c>
       <c r="C180" t="n">
-        <v>14.86007137817213</v>
+        <v>14.86007237747372</v>
       </c>
       <c r="D180" t="n">
-        <v>14.00000240201066</v>
+        <v>14.00000334347483</v>
       </c>
       <c r="E180" t="n">
-        <v>14.81228961649183</v>
+        <v>14.81229061258022</v>
       </c>
       <c r="F180" t="n">
         <v>11424100</v>
@@ -4132,16 +4132,16 @@
         <v>44524</v>
       </c>
       <c r="B186" t="n">
-        <v>13.11126708984375</v>
+        <v>13.11126518249512</v>
       </c>
       <c r="C186" t="n">
-        <v>13.38840024450097</v>
+        <v>13.38839829683666</v>
       </c>
       <c r="D186" t="n">
-        <v>12.97747832466525</v>
+        <v>12.97747643677941</v>
       </c>
       <c r="E186" t="n">
-        <v>13.09215401852051</v>
+        <v>13.09215211395233</v>
       </c>
       <c r="F186" t="n">
         <v>5705900</v>
@@ -4152,16 +4152,16 @@
         <v>44525</v>
       </c>
       <c r="B187" t="n">
-        <v>13.23549938201904</v>
+        <v>13.23549842834473</v>
       </c>
       <c r="C187" t="n">
-        <v>13.27372461348509</v>
+        <v>13.27372365705648</v>
       </c>
       <c r="D187" t="n">
-        <v>12.89147138746321</v>
+        <v>12.89147045857758</v>
       </c>
       <c r="E187" t="n">
-        <v>13.13037931196636</v>
+        <v>13.13037836586639</v>
       </c>
       <c r="F187" t="n">
         <v>5547700</v>
@@ -4172,16 +4172,16 @@
         <v>44526</v>
       </c>
       <c r="B188" t="n">
-        <v>12.76723957061768</v>
+        <v>12.76723766326904</v>
       </c>
       <c r="C188" t="n">
-        <v>13.02526057488637</v>
+        <v>13.02525862899095</v>
       </c>
       <c r="D188" t="n">
-        <v>12.64300733649143</v>
+        <v>12.64300544770234</v>
       </c>
       <c r="E188" t="n">
-        <v>12.93925357346347</v>
+        <v>12.93925164041698</v>
       </c>
       <c r="F188" t="n">
         <v>6311300</v>
@@ -4192,16 +4192,16 @@
         <v>44529</v>
       </c>
       <c r="B189" t="n">
-        <v>12.4709939956665</v>
+        <v>12.47099304199219</v>
       </c>
       <c r="C189" t="n">
-        <v>13.1112673141673</v>
+        <v>13.11126631153039</v>
       </c>
       <c r="D189" t="n">
-        <v>12.42321222790229</v>
+        <v>12.42321127788191</v>
       </c>
       <c r="E189" t="n">
-        <v>12.88191501117135</v>
+        <v>12.88191402607333</v>
       </c>
       <c r="F189" t="n">
         <v>13464500</v>
@@ -4212,16 +4212,16 @@
         <v>44530</v>
       </c>
       <c r="B190" t="n">
-        <v>12.18430328369141</v>
+        <v>12.18430233001709</v>
       </c>
       <c r="C190" t="n">
-        <v>12.44232426127008</v>
+        <v>12.44232328740027</v>
       </c>
       <c r="D190" t="n">
-        <v>11.84027622494785</v>
+        <v>11.84027529820078</v>
       </c>
       <c r="E190" t="n">
-        <v>12.38498596246548</v>
+        <v>12.38498499308359</v>
       </c>
       <c r="F190" t="n">
         <v>16793700</v>
@@ -4252,16 +4252,16 @@
         <v>44532</v>
       </c>
       <c r="B192" t="n">
-        <v>11.89761257171631</v>
+        <v>11.89761447906494</v>
       </c>
       <c r="C192" t="n">
-        <v>12.14607699253434</v>
+        <v>12.14607893971519</v>
       </c>
       <c r="D192" t="n">
-        <v>11.71604297887929</v>
+        <v>11.71604485711986</v>
       </c>
       <c r="E192" t="n">
-        <v>12.14607699253434</v>
+        <v>12.14607893971519</v>
       </c>
       <c r="F192" t="n">
         <v>7306700</v>
@@ -4352,16 +4352,16 @@
         <v>44539</v>
       </c>
       <c r="B197" t="n">
-        <v>13.58908271789551</v>
+        <v>13.58908176422119</v>
       </c>
       <c r="C197" t="n">
-        <v>13.74198364057517</v>
+        <v>13.74198267617036</v>
       </c>
       <c r="D197" t="n">
-        <v>13.43618179521584</v>
+        <v>13.43618085227203</v>
       </c>
       <c r="E197" t="n">
-        <v>13.74198364057517</v>
+        <v>13.74198267617036</v>
       </c>
       <c r="F197" t="n">
         <v>9843600</v>
@@ -4412,16 +4412,16 @@
         <v>44544</v>
       </c>
       <c r="B200" t="n">
-        <v>13.76109504699707</v>
+        <v>13.76109409332275</v>
       </c>
       <c r="C200" t="n">
-        <v>14.14334824413447</v>
+        <v>14.14334726396917</v>
       </c>
       <c r="D200" t="n">
-        <v>13.56996890410904</v>
+        <v>13.56996796368018</v>
       </c>
       <c r="E200" t="n">
-        <v>13.88532726771463</v>
+        <v>13.88532630543074</v>
       </c>
       <c r="F200" t="n">
         <v>6761100</v>
@@ -4432,16 +4432,16 @@
         <v>44545</v>
       </c>
       <c r="B201" t="n">
-        <v>14.03822803497314</v>
+        <v>14.03822898864746</v>
       </c>
       <c r="C201" t="n">
-        <v>14.0573411047424</v>
+        <v>14.05734205971515</v>
       </c>
       <c r="D201" t="n">
-        <v>13.7324262095556</v>
+        <v>13.73242714245554</v>
       </c>
       <c r="E201" t="n">
-        <v>13.92355235044156</v>
+        <v>13.92355329632549</v>
       </c>
       <c r="F201" t="n">
         <v>6373000</v>
@@ -4452,16 +4452,16 @@
         <v>44546</v>
       </c>
       <c r="B202" t="n">
-        <v>13.89488410949707</v>
+        <v>13.89488506317139</v>
       </c>
       <c r="C202" t="n">
-        <v>14.28669293890897</v>
+        <v>14.28669391947506</v>
       </c>
       <c r="D202" t="n">
-        <v>13.82799018584958</v>
+        <v>13.82799113493264</v>
       </c>
       <c r="E202" t="n">
-        <v>14.21024248006574</v>
+        <v>14.21024345538466</v>
       </c>
       <c r="F202" t="n">
         <v>5287600</v>
@@ -4472,16 +4472,16 @@
         <v>44547</v>
       </c>
       <c r="B203" t="n">
-        <v>13.81843376159668</v>
+        <v>13.81843280792236</v>
       </c>
       <c r="C203" t="n">
-        <v>14.00955991023924</v>
+        <v>14.00955894337442</v>
       </c>
       <c r="D203" t="n">
-        <v>13.6464197721377</v>
+        <v>13.64641883033486</v>
       </c>
       <c r="E203" t="n">
-        <v>13.84710245605272</v>
+        <v>13.84710150039985</v>
       </c>
       <c r="F203" t="n">
         <v>8250000</v>
@@ -4492,16 +4492,16 @@
         <v>44550</v>
       </c>
       <c r="B204" t="n">
-        <v>13.47440624237061</v>
+        <v>13.47440719604492</v>
       </c>
       <c r="C204" t="n">
-        <v>13.86621506179454</v>
+        <v>13.8662160431998</v>
       </c>
       <c r="D204" t="n">
-        <v>13.29283572372549</v>
+        <v>13.29283666454885</v>
       </c>
       <c r="E204" t="n">
-        <v>13.81843329839523</v>
+        <v>13.81843427641866</v>
       </c>
       <c r="F204" t="n">
         <v>6680500</v>
@@ -4552,16 +4552,16 @@
         <v>44553</v>
       </c>
       <c r="B207" t="n">
-        <v>13.46485042572021</v>
+        <v>13.4648494720459</v>
       </c>
       <c r="C207" t="n">
-        <v>13.65597657815202</v>
+        <v>13.65597561094082</v>
       </c>
       <c r="D207" t="n">
-        <v>13.32150512787533</v>
+        <v>13.32150418435372</v>
       </c>
       <c r="E207" t="n">
-        <v>13.41706865977192</v>
+        <v>13.41706770948184</v>
       </c>
       <c r="F207" t="n">
         <v>4198000</v>
@@ -4612,16 +4612,16 @@
         <v>44559</v>
       </c>
       <c r="B210" t="n">
-        <v>12.2703104019165</v>
+        <v>12.27030944824219</v>
       </c>
       <c r="C210" t="n">
-        <v>12.53788700590259</v>
+        <v>12.53788603143165</v>
       </c>
       <c r="D210" t="n">
-        <v>12.2511973316654</v>
+        <v>12.25119637947659</v>
       </c>
       <c r="E210" t="n">
-        <v>12.51877484701283</v>
+        <v>12.51877387402733</v>
       </c>
       <c r="F210" t="n">
         <v>10451000</v>
@@ -4632,16 +4632,16 @@
         <v>44560</v>
       </c>
       <c r="B211" t="n">
-        <v>12.38498592376709</v>
+        <v>12.38498687744141</v>
       </c>
       <c r="C211" t="n">
-        <v>12.49966160965662</v>
+        <v>12.49966257216125</v>
       </c>
       <c r="D211" t="n">
-        <v>12.25119716788196</v>
+        <v>12.25119811125422</v>
       </c>
       <c r="E211" t="n">
-        <v>12.32764762514165</v>
+        <v>12.32764857440078</v>
       </c>
       <c r="F211" t="n">
         <v>5913100</v>
@@ -4652,16 +4652,16 @@
         <v>44564</v>
       </c>
       <c r="B212" t="n">
-        <v>12.15563488006592</v>
+        <v>12.1556339263916</v>
       </c>
       <c r="C212" t="n">
-        <v>12.49966194701974</v>
+        <v>12.49966096635466</v>
       </c>
       <c r="D212" t="n">
-        <v>11.84983213141227</v>
+        <v>11.84983120172981</v>
       </c>
       <c r="E212" t="n">
-        <v>12.49966194701974</v>
+        <v>12.49966096635466</v>
       </c>
       <c r="F212" t="n">
         <v>16124600</v>
@@ -4672,16 +4672,16 @@
         <v>44565</v>
       </c>
       <c r="B213" t="n">
-        <v>12.15563488006592</v>
+        <v>12.1556339263916</v>
       </c>
       <c r="C213" t="n">
-        <v>12.25119749853907</v>
+        <v>12.25119653736736</v>
       </c>
       <c r="D213" t="n">
-        <v>11.89761389632953</v>
+        <v>11.89761296289834</v>
       </c>
       <c r="E213" t="n">
-        <v>12.20341664498318</v>
+        <v>12.20341568756013</v>
       </c>
       <c r="F213" t="n">
         <v>9389900</v>
@@ -4732,16 +4732,16 @@
         <v>44568</v>
       </c>
       <c r="B216" t="n">
-        <v>10.85597610473633</v>
+        <v>10.8559741973877</v>
       </c>
       <c r="C216" t="n">
-        <v>11.11399710881509</v>
+        <v>11.11399515613327</v>
       </c>
       <c r="D216" t="n">
-        <v>10.71263171004464</v>
+        <v>10.712629827881</v>
       </c>
       <c r="E216" t="n">
-        <v>11.00887794679861</v>
+        <v>11.00887601258578</v>
       </c>
       <c r="F216" t="n">
         <v>11641900</v>
@@ -4772,16 +4772,16 @@
         <v>44572</v>
       </c>
       <c r="B218" t="n">
-        <v>10.94198322296143</v>
+        <v>10.94198226928711</v>
       </c>
       <c r="C218" t="n">
-        <v>10.96109629518389</v>
+        <v>10.96109533984372</v>
       </c>
       <c r="D218" t="n">
-        <v>10.66485005526586</v>
+        <v>10.66484912574574</v>
       </c>
       <c r="E218" t="n">
-        <v>10.70307528834934</v>
+        <v>10.7030743554976</v>
       </c>
       <c r="F218" t="n">
         <v>6045500</v>
@@ -4792,16 +4792,16 @@
         <v>44573</v>
       </c>
       <c r="B219" t="n">
-        <v>11.27645397186279</v>
+        <v>11.27645206451416</v>
       </c>
       <c r="C219" t="n">
-        <v>11.28601050736037</v>
+        <v>11.2860085983953</v>
       </c>
       <c r="D219" t="n">
-        <v>10.80819466881839</v>
+        <v>10.80819284067318</v>
       </c>
       <c r="E219" t="n">
-        <v>10.94198252033886</v>
+        <v>10.94198066956419</v>
       </c>
       <c r="F219" t="n">
         <v>7862000</v>
@@ -4832,16 +4832,16 @@
         <v>44575</v>
       </c>
       <c r="B221" t="n">
-        <v>11.59181213378906</v>
+        <v>11.59181118011475</v>
       </c>
       <c r="C221" t="n">
-        <v>11.65870605828779</v>
+        <v>11.65870509911001</v>
       </c>
       <c r="D221" t="n">
-        <v>11.39112944893152</v>
+        <v>11.39112851176765</v>
       </c>
       <c r="E221" t="n">
-        <v>11.41024160820486</v>
+        <v>11.4102406694686</v>
       </c>
       <c r="F221" t="n">
         <v>7586600</v>
@@ -4852,16 +4852,16 @@
         <v>44578</v>
       </c>
       <c r="B222" t="n">
-        <v>11.47713565826416</v>
+        <v>11.47713661193848</v>
       </c>
       <c r="C222" t="n">
-        <v>11.6109234981016</v>
+        <v>11.61092446289281</v>
       </c>
       <c r="D222" t="n">
-        <v>11.41024082698413</v>
+        <v>11.41024177509993</v>
       </c>
       <c r="E222" t="n">
-        <v>11.59181134013681</v>
+        <v>11.59181230333992</v>
       </c>
       <c r="F222" t="n">
         <v>4569300</v>
@@ -4892,16 +4892,16 @@
         <v>44580</v>
       </c>
       <c r="B224" t="n">
-        <v>11.49624729156494</v>
+        <v>11.49624824523926</v>
       </c>
       <c r="C224" t="n">
-        <v>11.69692995352369</v>
+        <v>11.69693092384569</v>
       </c>
       <c r="D224" t="n">
-        <v>11.41979684047221</v>
+        <v>11.41979778780455</v>
       </c>
       <c r="E224" t="n">
-        <v>11.41979684047221</v>
+        <v>11.41979778780455</v>
       </c>
       <c r="F224" t="n">
         <v>5074700</v>
@@ -4912,16 +4912,16 @@
         <v>44581</v>
       </c>
       <c r="B225" t="n">
-        <v>11.41979789733887</v>
+        <v>11.41979885101318</v>
       </c>
       <c r="C225" t="n">
-        <v>11.69693103603816</v>
+        <v>11.69693201285603</v>
       </c>
       <c r="D225" t="n">
-        <v>11.36246050939355</v>
+        <v>11.36246145827959</v>
       </c>
       <c r="E225" t="n">
-        <v>11.56314318992485</v>
+        <v>11.56314415557002</v>
       </c>
       <c r="F225" t="n">
         <v>7365800</v>
@@ -4992,16 +4992,16 @@
         <v>44587</v>
       </c>
       <c r="B229" t="n">
-        <v>11.73515701293945</v>
+        <v>11.73515605926514</v>
       </c>
       <c r="C229" t="n">
-        <v>12.21297286261863</v>
+        <v>12.21297187011393</v>
       </c>
       <c r="D229" t="n">
-        <v>11.73515701293945</v>
+        <v>11.73515605926514</v>
       </c>
       <c r="E229" t="n">
-        <v>11.81160747597921</v>
+        <v>11.81160651609204</v>
       </c>
       <c r="F229" t="n">
         <v>11052300</v>
@@ -5012,16 +5012,16 @@
         <v>44588</v>
       </c>
       <c r="B230" t="n">
-        <v>11.99317646026611</v>
+        <v>11.99317836761475</v>
       </c>
       <c r="C230" t="n">
-        <v>12.13652083211196</v>
+        <v>12.13652276225753</v>
       </c>
       <c r="D230" t="n">
-        <v>11.66826157863015</v>
+        <v>11.66826343430557</v>
       </c>
       <c r="E230" t="n">
-        <v>11.85938771154504</v>
+        <v>11.85938959761643</v>
       </c>
       <c r="F230" t="n">
         <v>13761300</v>
@@ -5032,16 +5032,16 @@
         <v>44589</v>
       </c>
       <c r="B231" t="n">
-        <v>11.83071994781494</v>
+        <v>11.83071804046631</v>
       </c>
       <c r="C231" t="n">
-        <v>12.04095916619962</v>
+        <v>12.04095722495622</v>
       </c>
       <c r="D231" t="n">
-        <v>11.4580232758641</v>
+        <v>11.45802142860162</v>
       </c>
       <c r="E231" t="n">
-        <v>11.94539563656258</v>
+        <v>11.94539371072593</v>
       </c>
       <c r="F231" t="n">
         <v>14924100</v>
@@ -5052,16 +5052,16 @@
         <v>44592</v>
       </c>
       <c r="B232" t="n">
-        <v>11.97406482696533</v>
+        <v>11.97406387329102</v>
       </c>
       <c r="C232" t="n">
-        <v>12.12696575162983</v>
+        <v>12.12696478577772</v>
       </c>
       <c r="D232" t="n">
-        <v>11.76382651123235</v>
+        <v>11.76382557430247</v>
       </c>
       <c r="E232" t="n">
-        <v>11.81160736666896</v>
+        <v>11.81160642593357</v>
       </c>
       <c r="F232" t="n">
         <v>12073700</v>
@@ -5072,16 +5072,16 @@
         <v>44593</v>
       </c>
       <c r="B233" t="n">
-        <v>12.02184581756592</v>
+        <v>12.0218448638916</v>
       </c>
       <c r="C233" t="n">
-        <v>12.0982962749621</v>
+        <v>12.09829531522309</v>
       </c>
       <c r="D233" t="n">
-        <v>11.83071967407547</v>
+        <v>11.83071873556289</v>
       </c>
       <c r="E233" t="n">
-        <v>11.93583882515488</v>
+        <v>11.93583787830337</v>
       </c>
       <c r="F233" t="n">
         <v>5991900</v>
@@ -5092,16 +5092,16 @@
         <v>44594</v>
       </c>
       <c r="B234" t="n">
-        <v>11.94539451599121</v>
+        <v>11.94539546966553</v>
       </c>
       <c r="C234" t="n">
-        <v>12.27986592698347</v>
+        <v>12.2798669073607</v>
       </c>
       <c r="D234" t="n">
-        <v>11.81160576932205</v>
+        <v>11.81160671231519</v>
       </c>
       <c r="E234" t="n">
-        <v>12.02184496798465</v>
+        <v>12.02184592776248</v>
       </c>
       <c r="F234" t="n">
         <v>9442200</v>
@@ -5112,16 +5112,16 @@
         <v>44595</v>
       </c>
       <c r="B235" t="n">
-        <v>11.94539451599121</v>
+        <v>11.94539546966553</v>
       </c>
       <c r="C235" t="n">
-        <v>12.21297109796826</v>
+        <v>12.21297207300486</v>
       </c>
       <c r="D235" t="n">
-        <v>11.89761275565499</v>
+        <v>11.8976137055146</v>
       </c>
       <c r="E235" t="n">
-        <v>12.04095803666365</v>
+        <v>12.04095899796739</v>
       </c>
       <c r="F235" t="n">
         <v>8796800</v>
@@ -5132,16 +5132,16 @@
         <v>44596</v>
       </c>
       <c r="B236" t="n">
-        <v>12.3276481628418</v>
+        <v>12.32764911651611</v>
       </c>
       <c r="C236" t="n">
-        <v>12.3276481628418</v>
+        <v>12.32764911651611</v>
       </c>
       <c r="D236" t="n">
-        <v>11.56314355689919</v>
+        <v>11.56314445143097</v>
       </c>
       <c r="E236" t="n">
-        <v>11.91672716498799</v>
+        <v>11.91672808687321</v>
       </c>
       <c r="F236" t="n">
         <v>17676100</v>
@@ -5152,16 +5152,16 @@
         <v>44599</v>
       </c>
       <c r="B237" t="n">
-        <v>12.20341777801514</v>
+        <v>12.2034158706665</v>
       </c>
       <c r="C237" t="n">
-        <v>12.60478227104545</v>
+        <v>12.60478030096504</v>
       </c>
       <c r="D237" t="n">
-        <v>12.20341777801514</v>
+        <v>12.2034158706665</v>
       </c>
       <c r="E237" t="n">
-        <v>12.29898040536085</v>
+        <v>12.29897848307614</v>
       </c>
       <c r="F237" t="n">
         <v>7212000</v>
@@ -5192,16 +5192,16 @@
         <v>44601</v>
       </c>
       <c r="B239" t="n">
-        <v>12.05051422119141</v>
+        <v>12.05051517486572</v>
       </c>
       <c r="C239" t="n">
-        <v>12.28942212264425</v>
+        <v>12.28942309522567</v>
       </c>
       <c r="D239" t="n">
-        <v>11.91672637964906</v>
+        <v>11.91672732273544</v>
       </c>
       <c r="E239" t="n">
-        <v>11.95495160742706</v>
+        <v>11.95495255353858</v>
       </c>
       <c r="F239" t="n">
         <v>9060800</v>
@@ -5212,16 +5212,16 @@
         <v>44602</v>
       </c>
       <c r="B240" t="n">
-        <v>12.11741065979004</v>
+        <v>12.11740875244141</v>
       </c>
       <c r="C240" t="n">
-        <v>12.29898028796682</v>
+        <v>12.29897835203811</v>
       </c>
       <c r="D240" t="n">
-        <v>11.88805835135432</v>
+        <v>11.88805648010703</v>
       </c>
       <c r="E240" t="n">
-        <v>11.9549531923554</v>
+        <v>11.95495131057848</v>
       </c>
       <c r="F240" t="n">
         <v>4310600</v>
@@ -5232,16 +5232,16 @@
         <v>44603</v>
       </c>
       <c r="B241" t="n">
-        <v>11.79249382019043</v>
+        <v>11.79249477386475</v>
       </c>
       <c r="C241" t="n">
-        <v>12.21297131357752</v>
+        <v>12.2129723012564</v>
       </c>
       <c r="D241" t="n">
-        <v>11.74471205901066</v>
+        <v>11.74471300882081</v>
       </c>
       <c r="E241" t="n">
-        <v>12.18430262141418</v>
+        <v>12.18430360677458</v>
       </c>
       <c r="F241" t="n">
         <v>7316000</v>
@@ -5252,16 +5252,16 @@
         <v>44606</v>
       </c>
       <c r="B242" t="n">
-        <v>11.78293800354004</v>
+        <v>11.78293704986572</v>
       </c>
       <c r="C242" t="n">
-        <v>11.97406414854188</v>
+        <v>11.97406317939841</v>
       </c>
       <c r="D242" t="n">
-        <v>11.639593622629</v>
+        <v>11.63959268055653</v>
       </c>
       <c r="E242" t="n">
-        <v>11.79249453863047</v>
+        <v>11.79249358418268</v>
       </c>
       <c r="F242" t="n">
         <v>5445000</v>
@@ -5272,16 +5272,16 @@
         <v>44607</v>
       </c>
       <c r="B243" t="n">
-        <v>11.63959407806396</v>
+        <v>11.63959312438965</v>
       </c>
       <c r="C243" t="n">
-        <v>11.95495245749671</v>
+        <v>11.95495147798393</v>
       </c>
       <c r="D243" t="n">
-        <v>11.5344740106788</v>
+        <v>11.53447306561735</v>
       </c>
       <c r="E243" t="n">
-        <v>11.92628285110363</v>
+        <v>11.92628187393986</v>
       </c>
       <c r="F243" t="n">
         <v>11329100</v>
@@ -5292,16 +5292,16 @@
         <v>44608</v>
       </c>
       <c r="B244" t="n">
-        <v>12.4709939956665</v>
+        <v>12.47099304199219</v>
       </c>
       <c r="C244" t="n">
-        <v>12.64300708371169</v>
+        <v>12.6430061168833</v>
       </c>
       <c r="D244" t="n">
-        <v>11.56314405359208</v>
+        <v>11.56314316934232</v>
       </c>
       <c r="E244" t="n">
-        <v>11.65870667775909</v>
+        <v>11.65870578620152</v>
       </c>
       <c r="F244" t="n">
         <v>21489000</v>
@@ -5312,16 +5312,16 @@
         <v>44609</v>
       </c>
       <c r="B245" t="n">
-        <v>12.66211891174316</v>
+        <v>12.66211986541748</v>
       </c>
       <c r="C245" t="n">
-        <v>12.94880857880961</v>
+        <v>12.94880955407657</v>
       </c>
       <c r="D245" t="n">
-        <v>12.46143623593278</v>
+        <v>12.46143717449226</v>
       </c>
       <c r="E245" t="n">
-        <v>12.46143623593278</v>
+        <v>12.46143717449226</v>
       </c>
       <c r="F245" t="n">
         <v>10362100</v>
@@ -5352,16 +5352,16 @@
         <v>44613</v>
       </c>
       <c r="B247" t="n">
-        <v>11.90717124938965</v>
+        <v>11.90717029571533</v>
       </c>
       <c r="C247" t="n">
-        <v>12.27986794770807</v>
+        <v>12.27986696418357</v>
       </c>
       <c r="D247" t="n">
-        <v>11.72560162386719</v>
+        <v>11.72560068473523</v>
       </c>
       <c r="E247" t="n">
-        <v>12.1365226431111</v>
+        <v>12.13652167106747</v>
       </c>
       <c r="F247" t="n">
         <v>4718800</v>
@@ -5412,16 +5412,16 @@
         <v>44616</v>
       </c>
       <c r="B250" t="n">
-        <v>12.93925189971924</v>
+        <v>12.93925285339355</v>
       </c>
       <c r="C250" t="n">
-        <v>13.04437104821551</v>
+        <v>13.04437200963752</v>
       </c>
       <c r="D250" t="n">
-        <v>12.21297166094141</v>
+        <v>12.21297256108599</v>
       </c>
       <c r="E250" t="n">
-        <v>12.41365433451525</v>
+        <v>12.41365524945094</v>
       </c>
       <c r="F250" t="n">
         <v>6603100</v>
@@ -5432,16 +5432,16 @@
         <v>44617</v>
       </c>
       <c r="B251" t="n">
-        <v>12.86280155181885</v>
+        <v>12.86280250549316</v>
       </c>
       <c r="C251" t="n">
-        <v>13.13993468322886</v>
+        <v>13.13993565745039</v>
       </c>
       <c r="D251" t="n">
-        <v>12.72901279786317</v>
+        <v>12.72901374161811</v>
       </c>
       <c r="E251" t="n">
-        <v>12.83413285860025</v>
+        <v>12.83413381014901</v>
       </c>
       <c r="F251" t="n">
         <v>8089600</v>
@@ -5452,16 +5452,16 @@
         <v>44622</v>
       </c>
       <c r="B252" t="n">
-        <v>12.68123340606689</v>
+        <v>12.68123245239258</v>
       </c>
       <c r="C252" t="n">
-        <v>12.95836656937867</v>
+        <v>12.95836559486294</v>
       </c>
       <c r="D252" t="n">
-        <v>12.64300726222665</v>
+        <v>12.64300631142708</v>
       </c>
       <c r="E252" t="n">
-        <v>12.86280303250091</v>
+        <v>12.86280206517191</v>
       </c>
       <c r="F252" t="n">
         <v>4196000</v>
@@ -5492,16 +5492,16 @@
         <v>44624</v>
       </c>
       <c r="B254" t="n">
-        <v>12.14607810974121</v>
+        <v>12.14607715606689</v>
       </c>
       <c r="C254" t="n">
-        <v>12.64300608572388</v>
+        <v>12.64300509303224</v>
       </c>
       <c r="D254" t="n">
-        <v>12.13652157467044</v>
+        <v>12.13652062174647</v>
       </c>
       <c r="E254" t="n">
-        <v>12.64300608572388</v>
+        <v>12.64300509303224</v>
       </c>
       <c r="F254" t="n">
         <v>6563400</v>
@@ -5512,16 +5512,16 @@
         <v>44627</v>
       </c>
       <c r="B255" t="n">
-        <v>11.73515701293945</v>
+        <v>11.73515605926514</v>
       </c>
       <c r="C255" t="n">
-        <v>12.17474763109875</v>
+        <v>12.17474664170048</v>
       </c>
       <c r="D255" t="n">
-        <v>11.68737524569925</v>
+        <v>11.68737429590799</v>
       </c>
       <c r="E255" t="n">
-        <v>12.08874063233868</v>
+        <v>12.08873964992988</v>
       </c>
       <c r="F255" t="n">
         <v>12255900</v>
@@ -5552,16 +5552,16 @@
         <v>44629</v>
       </c>
       <c r="B257" t="n">
-        <v>12.80546283721924</v>
+        <v>12.80546379089355</v>
       </c>
       <c r="C257" t="n">
-        <v>13.0348151095869</v>
+        <v>13.03481608034201</v>
       </c>
       <c r="D257" t="n">
-        <v>11.75426864359272</v>
+        <v>11.75426951898038</v>
       </c>
       <c r="E257" t="n">
-        <v>11.89761301638138</v>
+        <v>11.89761390244447</v>
       </c>
       <c r="F257" t="n">
         <v>14771600</v>
@@ -5572,16 +5572,16 @@
         <v>44630</v>
       </c>
       <c r="B258" t="n">
-        <v>12.71945667266846</v>
+        <v>12.71945762634277</v>
       </c>
       <c r="C258" t="n">
-        <v>13.02525848523527</v>
+        <v>13.02525946183787</v>
       </c>
       <c r="D258" t="n">
-        <v>12.24164088485217</v>
+        <v>12.24164180270101</v>
       </c>
       <c r="E258" t="n">
-        <v>12.67167491161457</v>
+        <v>12.67167586170632</v>
       </c>
       <c r="F258" t="n">
         <v>9185900</v>
@@ -5632,16 +5632,16 @@
         <v>44635</v>
       </c>
       <c r="B261" t="n">
-        <v>12.82457637786865</v>
+        <v>12.82457733154297</v>
       </c>
       <c r="C261" t="n">
-        <v>12.90102683434848</v>
+        <v>12.90102779370788</v>
       </c>
       <c r="D261" t="n">
-        <v>12.29897880604886</v>
+        <v>12.29897972063815</v>
       </c>
       <c r="E261" t="n">
-        <v>12.29897880604886</v>
+        <v>12.29897972063815</v>
       </c>
       <c r="F261" t="n">
         <v>8181800</v>
@@ -5652,16 +5652,16 @@
         <v>44636</v>
       </c>
       <c r="B262" t="n">
-        <v>12.99659061431885</v>
+        <v>12.99659156799316</v>
       </c>
       <c r="C262" t="n">
-        <v>13.09215323110332</v>
+        <v>13.09215419178991</v>
       </c>
       <c r="D262" t="n">
-        <v>12.73856963514194</v>
+        <v>12.73857056988299</v>
       </c>
       <c r="E262" t="n">
-        <v>12.91058362125988</v>
+        <v>12.91058456862311</v>
       </c>
       <c r="F262" t="n">
         <v>7731200</v>
@@ -5672,16 +5672,16 @@
         <v>44637</v>
       </c>
       <c r="B263" t="n">
-        <v>13.12082195281982</v>
+        <v>13.12082099914551</v>
       </c>
       <c r="C263" t="n">
-        <v>13.24505417512824</v>
+        <v>13.24505321242422</v>
       </c>
       <c r="D263" t="n">
-        <v>12.87235841956435</v>
+        <v>12.87235748394937</v>
       </c>
       <c r="E263" t="n">
-        <v>13.09215325885984</v>
+        <v>13.09215230726928</v>
       </c>
       <c r="F263" t="n">
         <v>6159800</v>
@@ -5692,16 +5692,16 @@
         <v>44638</v>
       </c>
       <c r="B264" t="n">
-        <v>13.58908271789551</v>
+        <v>13.58908176422119</v>
       </c>
       <c r="C264" t="n">
-        <v>13.78020887124509</v>
+        <v>13.78020790415765</v>
       </c>
       <c r="D264" t="n">
-        <v>12.98703465132328</v>
+        <v>12.98703373990036</v>
       </c>
       <c r="E264" t="n">
-        <v>13.04437204164746</v>
+        <v>13.04437112620064</v>
       </c>
       <c r="F264" t="n">
         <v>10366600</v>
@@ -5712,16 +5712,16 @@
         <v>44641</v>
       </c>
       <c r="B265" t="n">
-        <v>13.56041240692139</v>
+        <v>13.5604133605957</v>
       </c>
       <c r="C265" t="n">
-        <v>13.62730724063966</v>
+        <v>13.62730819901854</v>
       </c>
       <c r="D265" t="n">
-        <v>13.18771665509124</v>
+        <v>13.18771758255467</v>
       </c>
       <c r="E265" t="n">
-        <v>13.58908201195551</v>
+        <v>13.58908296764609</v>
       </c>
       <c r="F265" t="n">
         <v>3916100</v>
@@ -5772,16 +5772,16 @@
         <v>44644</v>
       </c>
       <c r="B268" t="n">
-        <v>14.6307201385498</v>
+        <v>14.63071918487549</v>
       </c>
       <c r="C268" t="n">
-        <v>14.74539582072832</v>
+        <v>14.7453948595791</v>
       </c>
       <c r="D268" t="n">
-        <v>14.35358701211139</v>
+        <v>14.35358607650145</v>
       </c>
       <c r="E268" t="n">
-        <v>14.39181223950423</v>
+        <v>14.39181130140265</v>
       </c>
       <c r="F268" t="n">
         <v>7986800</v>
@@ -5792,16 +5792,16 @@
         <v>44645</v>
       </c>
       <c r="B269" t="n">
-        <v>15.13720607757568</v>
+        <v>15.13720512390137</v>
       </c>
       <c r="C269" t="n">
-        <v>15.24232523512279</v>
+        <v>15.24232427482575</v>
       </c>
       <c r="D269" t="n">
-        <v>14.64027716256451</v>
+        <v>14.64027624019771</v>
       </c>
       <c r="E269" t="n">
-        <v>14.71672762466447</v>
+        <v>14.71672669748114</v>
       </c>
       <c r="F269" t="n">
         <v>8426200</v>
@@ -5832,16 +5832,16 @@
         <v>44649</v>
       </c>
       <c r="B271" t="n">
-        <v>15.50034618377686</v>
+        <v>15.50034332275391</v>
       </c>
       <c r="C271" t="n">
-        <v>15.93038119634201</v>
+        <v>15.93037825594406</v>
       </c>
       <c r="D271" t="n">
-        <v>15.43345225353847</v>
+        <v>15.43344940486267</v>
       </c>
       <c r="E271" t="n">
-        <v>15.72969758290397</v>
+        <v>15.7296946795478</v>
       </c>
       <c r="F271" t="n">
         <v>7323700</v>
@@ -5852,16 +5852,16 @@
         <v>44650</v>
       </c>
       <c r="B272" t="n">
-        <v>15.45256328582764</v>
+        <v>15.45256233215332</v>
       </c>
       <c r="C272" t="n">
-        <v>15.82525903236704</v>
+        <v>15.82525805569134</v>
       </c>
       <c r="D272" t="n">
-        <v>15.39522589929603</v>
+        <v>15.39522494916037</v>
       </c>
       <c r="E272" t="n">
-        <v>15.51945720723495</v>
+        <v>15.51945624943219</v>
       </c>
       <c r="F272" t="n">
         <v>8944100</v>
@@ -5932,16 +5932,16 @@
         <v>44656</v>
       </c>
       <c r="B276" t="n">
-        <v>15.45256328582764</v>
+        <v>15.45256233215332</v>
       </c>
       <c r="C276" t="n">
-        <v>15.65324505004958</v>
+        <v>15.65324408398994</v>
       </c>
       <c r="D276" t="n">
-        <v>15.35699975979319</v>
+        <v>15.3569988120167</v>
       </c>
       <c r="E276" t="n">
-        <v>15.57679459376655</v>
+        <v>15.57679363242515</v>
       </c>
       <c r="F276" t="n">
         <v>10716200</v>
@@ -5972,16 +5972,16 @@
         <v>44658</v>
       </c>
       <c r="B278" t="n">
-        <v>15.38566970825195</v>
+        <v>15.38567066192627</v>
       </c>
       <c r="C278" t="n">
-        <v>15.52901408914568</v>
+        <v>15.52901505170514</v>
       </c>
       <c r="D278" t="n">
-        <v>15.25188095108615</v>
+        <v>15.25188189646763</v>
       </c>
       <c r="E278" t="n">
-        <v>15.3665566380734</v>
+        <v>15.366557590563</v>
       </c>
       <c r="F278" t="n">
         <v>6566700</v>
@@ -5992,16 +5992,16 @@
         <v>44659</v>
       </c>
       <c r="B279" t="n">
-        <v>15.40478324890137</v>
+        <v>15.40478229522705</v>
       </c>
       <c r="C279" t="n">
-        <v>15.57679541759357</v>
+        <v>15.57679445327038</v>
       </c>
       <c r="D279" t="n">
-        <v>15.07031180145259</v>
+        <v>15.07031086848462</v>
       </c>
       <c r="E279" t="n">
-        <v>15.32833278857503</v>
+        <v>15.32833183963358</v>
       </c>
       <c r="F279" t="n">
         <v>3069100</v>
@@ -6012,16 +6012,16 @@
         <v>44662</v>
       </c>
       <c r="B280" t="n">
-        <v>15.29010581970215</v>
+        <v>15.29010677337646</v>
       </c>
       <c r="C280" t="n">
-        <v>15.49078758367887</v>
+        <v>15.4907885498701</v>
       </c>
       <c r="D280" t="n">
-        <v>15.21365536351254</v>
+        <v>15.21365631241849</v>
       </c>
       <c r="E280" t="n">
-        <v>15.38566934561982</v>
+        <v>15.38567030525462</v>
       </c>
       <c r="F280" t="n">
         <v>10289300</v>
@@ -6032,16 +6032,16 @@
         <v>44663</v>
       </c>
       <c r="B281" t="n">
-        <v>15.72014141082764</v>
+        <v>15.720139503479</v>
       </c>
       <c r="C281" t="n">
-        <v>15.82525965313857</v>
+        <v>15.82525773303578</v>
       </c>
       <c r="D281" t="n">
-        <v>15.39522650319881</v>
+        <v>15.3952246352726</v>
       </c>
       <c r="E281" t="n">
-        <v>15.48123349773131</v>
+        <v>15.48123161936973</v>
       </c>
       <c r="F281" t="n">
         <v>9798400</v>
@@ -6052,16 +6052,16 @@
         <v>44664</v>
       </c>
       <c r="B282" t="n">
-        <v>15.76792240142822</v>
+        <v>15.76792144775391</v>
       </c>
       <c r="C282" t="n">
-        <v>16.02594338726869</v>
+        <v>16.02594241798877</v>
       </c>
       <c r="D282" t="n">
-        <v>15.69147194148172</v>
+        <v>15.69147099243128</v>
       </c>
       <c r="E282" t="n">
-        <v>15.78703547209553</v>
+        <v>15.78703451726522</v>
       </c>
       <c r="F282" t="n">
         <v>7212700</v>
@@ -6072,16 +6072,16 @@
         <v>44665</v>
       </c>
       <c r="B283" t="n">
-        <v>15.64369106292725</v>
+        <v>15.64369010925293</v>
       </c>
       <c r="C283" t="n">
-        <v>15.79659198257972</v>
+        <v>15.79659101958422</v>
       </c>
       <c r="D283" t="n">
-        <v>15.48123360795615</v>
+        <v>15.4812326641856</v>
       </c>
       <c r="E283" t="n">
-        <v>15.72014152275348</v>
+        <v>15.72014056441858</v>
       </c>
       <c r="F283" t="n">
         <v>4607000</v>
@@ -6092,16 +6092,16 @@
         <v>44669</v>
       </c>
       <c r="B284" t="n">
-        <v>15.31877517700195</v>
+        <v>15.31877613067627</v>
       </c>
       <c r="C284" t="n">
-        <v>15.67235784764996</v>
+        <v>15.67235882333666</v>
       </c>
       <c r="D284" t="n">
-        <v>15.31877517700195</v>
+        <v>15.31877613067627</v>
       </c>
       <c r="E284" t="n">
-        <v>15.56723961128785</v>
+        <v>15.56724058043038</v>
       </c>
       <c r="F284" t="n">
         <v>3539900</v>
@@ -6112,16 +6112,16 @@
         <v>44670</v>
       </c>
       <c r="B285" t="n">
-        <v>15.61502170562744</v>
+        <v>15.61502075195312</v>
       </c>
       <c r="C285" t="n">
-        <v>15.77747916318553</v>
+        <v>15.77747819958926</v>
       </c>
       <c r="D285" t="n">
-        <v>15.18498763441659</v>
+        <v>15.18498670700624</v>
       </c>
       <c r="E285" t="n">
-        <v>15.32833293239446</v>
+        <v>15.32833199622942</v>
       </c>
       <c r="F285" t="n">
         <v>7756800</v>
@@ -6152,16 +6152,16 @@
         <v>44673</v>
       </c>
       <c r="B287" t="n">
-        <v>15.31877517700195</v>
+        <v>15.31877613067627</v>
       </c>
       <c r="C287" t="n">
-        <v>15.74880830260542</v>
+        <v>15.74880928305156</v>
       </c>
       <c r="D287" t="n">
-        <v>15.14676119767152</v>
+        <v>15.14676214063706</v>
       </c>
       <c r="E287" t="n">
-        <v>15.74880830260542</v>
+        <v>15.74880928305156</v>
       </c>
       <c r="F287" t="n">
         <v>8878800</v>
@@ -6192,16 +6192,16 @@
         <v>44677</v>
       </c>
       <c r="B289" t="n">
-        <v>15.12764739990234</v>
+        <v>15.12764835357666</v>
       </c>
       <c r="C289" t="n">
-        <v>15.30921790520048</v>
+        <v>15.30921887032133</v>
       </c>
       <c r="D289" t="n">
-        <v>15.02252825724008</v>
+        <v>15.02252920428749</v>
       </c>
       <c r="E289" t="n">
-        <v>15.21365438542659</v>
+        <v>15.21365534452294</v>
       </c>
       <c r="F289" t="n">
         <v>9387600</v>
@@ -6252,16 +6252,16 @@
         <v>44680</v>
       </c>
       <c r="B292" t="n">
-        <v>14.72057151794434</v>
+        <v>14.72057247161865</v>
       </c>
       <c r="C292" t="n">
-        <v>15.13482874017579</v>
+        <v>15.13482972068782</v>
       </c>
       <c r="D292" t="n">
-        <v>14.72057151794434</v>
+        <v>14.72057247161865</v>
       </c>
       <c r="E292" t="n">
-        <v>15.06739185981573</v>
+        <v>15.06739283595885</v>
       </c>
       <c r="F292" t="n">
         <v>7651000</v>
@@ -6352,16 +6352,16 @@
         <v>44687</v>
       </c>
       <c r="B297" t="n">
-        <v>14.15217304229736</v>
+        <v>14.15217208862305</v>
       </c>
       <c r="C297" t="n">
-        <v>14.51826068894659</v>
+        <v>14.51825971060268</v>
       </c>
       <c r="D297" t="n">
-        <v>14.0558347681846</v>
+        <v>14.05583382100224</v>
       </c>
       <c r="E297" t="n">
-        <v>14.45082380519179</v>
+        <v>14.45082283139226</v>
       </c>
       <c r="F297" t="n">
         <v>6832100</v>
@@ -6372,16 +6372,16 @@
         <v>44690</v>
       </c>
       <c r="B298" t="n">
-        <v>14.21961116790771</v>
+        <v>14.2196102142334</v>
       </c>
       <c r="C298" t="n">
-        <v>14.32558354746724</v>
+        <v>14.32558258668562</v>
       </c>
       <c r="D298" t="n">
-        <v>13.92096039822737</v>
+        <v>13.92095946458282</v>
       </c>
       <c r="E298" t="n">
-        <v>14.04620098430244</v>
+        <v>14.04620004225831</v>
       </c>
       <c r="F298" t="n">
         <v>11844800</v>
@@ -6412,16 +6412,16 @@
         <v>44692</v>
       </c>
       <c r="B300" t="n">
-        <v>14.60496520996094</v>
+        <v>14.60496616363525</v>
       </c>
       <c r="C300" t="n">
-        <v>14.78800948553586</v>
+        <v>14.7880104511626</v>
       </c>
       <c r="D300" t="n">
-        <v>14.40265364781732</v>
+        <v>14.4026545882811</v>
       </c>
       <c r="E300" t="n">
-        <v>14.45082324237696</v>
+        <v>14.45082418598612</v>
       </c>
       <c r="F300" t="n">
         <v>6181500</v>
@@ -6432,16 +6432,16 @@
         <v>44693</v>
       </c>
       <c r="B301" t="n">
-        <v>14.68203544616699</v>
+        <v>14.68203639984131</v>
       </c>
       <c r="C301" t="n">
-        <v>15.07702444767837</v>
+        <v>15.07702542700927</v>
       </c>
       <c r="D301" t="n">
-        <v>14.42192111880329</v>
+        <v>14.42192205558183</v>
       </c>
       <c r="E301" t="n">
-        <v>14.42192111880329</v>
+        <v>14.42192205558183</v>
       </c>
       <c r="F301" t="n">
         <v>8258700</v>
@@ -6452,16 +6452,16 @@
         <v>44694</v>
       </c>
       <c r="B302" t="n">
-        <v>14.91324806213379</v>
+        <v>14.91324901580811</v>
       </c>
       <c r="C302" t="n">
-        <v>15.0962923244161</v>
+        <v>15.09629328979575</v>
       </c>
       <c r="D302" t="n">
-        <v>14.62423235328135</v>
+        <v>14.62423328847366</v>
       </c>
       <c r="E302" t="n">
-        <v>14.72057061664599</v>
+        <v>14.72057155799894</v>
       </c>
       <c r="F302" t="n">
         <v>5016200</v>
@@ -6512,16 +6512,16 @@
         <v>44699</v>
       </c>
       <c r="B305" t="n">
-        <v>14.83617687225342</v>
+        <v>14.83617782592773</v>
       </c>
       <c r="C305" t="n">
-        <v>15.25043406321039</v>
+        <v>15.2504350435133</v>
       </c>
       <c r="D305" t="n">
-        <v>14.81690958735881</v>
+        <v>14.81691053979462</v>
       </c>
       <c r="E305" t="n">
-        <v>15.23116677831579</v>
+        <v>15.23116775738018</v>
       </c>
       <c r="F305" t="n">
         <v>6842800</v>
@@ -6532,16 +6532,16 @@
         <v>44700</v>
       </c>
       <c r="B306" t="n">
-        <v>14.88434791564941</v>
+        <v>14.88434886932373</v>
       </c>
       <c r="C306" t="n">
-        <v>14.95178571626016</v>
+        <v>14.95178667425537</v>
       </c>
       <c r="D306" t="n">
-        <v>14.6627690645589</v>
+        <v>14.66277000403615</v>
       </c>
       <c r="E306" t="n">
-        <v>14.92288340795901</v>
+        <v>14.92288436410238</v>
       </c>
       <c r="F306" t="n">
         <v>6219800</v>
@@ -6552,16 +6552,16 @@
         <v>44701</v>
       </c>
       <c r="B307" t="n">
-        <v>15.37567615509033</v>
+        <v>15.37567710876465</v>
       </c>
       <c r="C307" t="n">
-        <v>15.49128263219524</v>
+        <v>15.49128359304003</v>
       </c>
       <c r="D307" t="n">
-        <v>14.93251753347555</v>
+        <v>14.93251845966301</v>
       </c>
       <c r="E307" t="n">
-        <v>15.02885672377561</v>
+        <v>15.0288576559385</v>
       </c>
       <c r="F307" t="n">
         <v>8142900</v>
@@ -6572,16 +6572,16 @@
         <v>44704</v>
       </c>
       <c r="B308" t="n">
-        <v>15.28897285461426</v>
+        <v>15.28897190093994</v>
       </c>
       <c r="C308" t="n">
-        <v>15.63579232646676</v>
+        <v>15.63579135115902</v>
       </c>
       <c r="D308" t="n">
-        <v>15.17336636399676</v>
+        <v>15.17336541753358</v>
       </c>
       <c r="E308" t="n">
-        <v>15.52982085851578</v>
+        <v>15.52981988981818</v>
       </c>
       <c r="F308" t="n">
         <v>8474400</v>
@@ -6592,16 +6592,16 @@
         <v>44705</v>
       </c>
       <c r="B309" t="n">
-        <v>15.31787395477295</v>
+        <v>15.31787300109863</v>
       </c>
       <c r="C309" t="n">
-        <v>15.34677626594388</v>
+        <v>15.34677531047014</v>
       </c>
       <c r="D309" t="n">
-        <v>14.99995588196225</v>
+        <v>14.99995494808117</v>
       </c>
       <c r="E309" t="n">
-        <v>15.19263428140036</v>
+        <v>15.19263333552333</v>
       </c>
       <c r="F309" t="n">
         <v>5652100</v>
@@ -6612,16 +6612,16 @@
         <v>44706</v>
       </c>
       <c r="B310" t="n">
-        <v>15.14446353912354</v>
+        <v>15.14446258544922</v>
       </c>
       <c r="C310" t="n">
-        <v>15.44311430071703</v>
+        <v>15.44311332823613</v>
       </c>
       <c r="D310" t="n">
-        <v>14.94215196998178</v>
+        <v>14.94215102904739</v>
       </c>
       <c r="E310" t="n">
-        <v>15.16373082635871</v>
+        <v>15.16372987147109</v>
       </c>
       <c r="F310" t="n">
         <v>8129200</v>
@@ -6632,16 +6632,16 @@
         <v>44707</v>
       </c>
       <c r="B311" t="n">
-        <v>15.50091743469238</v>
+        <v>15.50091648101807</v>
       </c>
       <c r="C311" t="n">
-        <v>15.60689073255783</v>
+        <v>15.60688977236364</v>
       </c>
       <c r="D311" t="n">
-        <v>15.03849058664008</v>
+        <v>15.03848966141599</v>
       </c>
       <c r="E311" t="n">
-        <v>15.07702608074788</v>
+        <v>15.07702515315295</v>
       </c>
       <c r="F311" t="n">
         <v>6641000</v>
@@ -6652,16 +6652,16 @@
         <v>44708</v>
       </c>
       <c r="B312" t="n">
-        <v>15.22153377532959</v>
+        <v>15.22153472900391</v>
       </c>
       <c r="C312" t="n">
-        <v>15.51055041968089</v>
+        <v>15.51055139146295</v>
       </c>
       <c r="D312" t="n">
-        <v>15.13482869014834</v>
+        <v>15.13482963839033</v>
       </c>
       <c r="E312" t="n">
-        <v>15.43347943702168</v>
+        <v>15.43348040397503</v>
       </c>
       <c r="F312" t="n">
         <v>3408100</v>
@@ -6672,16 +6672,16 @@
         <v>44711</v>
       </c>
       <c r="B313" t="n">
-        <v>15.26970386505127</v>
+        <v>15.26970291137695</v>
       </c>
       <c r="C313" t="n">
-        <v>15.4912827177024</v>
+        <v>15.49128175018931</v>
       </c>
       <c r="D313" t="n">
-        <v>15.16373057138454</v>
+        <v>15.16372962432882</v>
       </c>
       <c r="E313" t="n">
-        <v>15.23116837247026</v>
+        <v>15.23116742120269</v>
       </c>
       <c r="F313" t="n">
         <v>1706700</v>
@@ -6732,16 +6732,16 @@
         <v>44714</v>
       </c>
       <c r="B316" t="n">
-        <v>15.3082389831543</v>
+        <v>15.30823993682861</v>
       </c>
       <c r="C316" t="n">
-        <v>15.41421135547006</v>
+        <v>15.41421231574625</v>
       </c>
       <c r="D316" t="n">
-        <v>14.88434765637406</v>
+        <v>14.88434858364075</v>
       </c>
       <c r="E316" t="n">
-        <v>15.06739193072508</v>
+        <v>15.06739286939508</v>
       </c>
       <c r="F316" t="n">
         <v>5285700</v>
@@ -6752,16 +6752,16 @@
         <v>44715</v>
       </c>
       <c r="B317" t="n">
-        <v>14.88434791564941</v>
+        <v>14.88434886932373</v>
       </c>
       <c r="C317" t="n">
-        <v>15.23116826519437</v>
+        <v>15.23116924109026</v>
       </c>
       <c r="D317" t="n">
-        <v>14.78800964425473</v>
+        <v>14.78801059175644</v>
       </c>
       <c r="E317" t="n">
-        <v>15.17336456735067</v>
+        <v>15.17336553954295</v>
       </c>
       <c r="F317" t="n">
         <v>4184100</v>
@@ -6772,16 +6772,16 @@
         <v>44718</v>
       </c>
       <c r="B318" t="n">
-        <v>14.9036169052124</v>
+        <v>14.90361595153809</v>
       </c>
       <c r="C318" t="n">
-        <v>15.1348298712333</v>
+        <v>15.13482890276379</v>
       </c>
       <c r="D318" t="n">
-        <v>14.84581320432785</v>
+        <v>14.84581225435236</v>
       </c>
       <c r="E318" t="n">
-        <v>15.01922338822285</v>
+        <v>15.01922242715094</v>
       </c>
       <c r="F318" t="n">
         <v>2626600</v>
@@ -6792,16 +6792,16 @@
         <v>44719</v>
       </c>
       <c r="B319" t="n">
-        <v>15.12519550323486</v>
+        <v>15.12519645690918</v>
       </c>
       <c r="C319" t="n">
-        <v>15.31787297154666</v>
+        <v>15.31787393736968</v>
       </c>
       <c r="D319" t="n">
-        <v>14.70130507294891</v>
+        <v>14.70130599989608</v>
       </c>
       <c r="E319" t="n">
-        <v>14.82654565704124</v>
+        <v>14.82654659188508</v>
       </c>
       <c r="F319" t="n">
         <v>7316900</v>
@@ -6812,16 +6812,16 @@
         <v>44720</v>
       </c>
       <c r="B320" t="n">
-        <v>15.35640907287598</v>
+        <v>15.35640716552734</v>
       </c>
       <c r="C320" t="n">
-        <v>15.74176494350709</v>
+        <v>15.74176298829518</v>
       </c>
       <c r="D320" t="n">
-        <v>14.9903223279765</v>
+        <v>14.99032046609781</v>
       </c>
       <c r="E320" t="n">
-        <v>15.00958961619079</v>
+        <v>15.00958775191899</v>
       </c>
       <c r="F320" t="n">
         <v>10420600</v>
@@ -6912,16 +6912,16 @@
         <v>44727</v>
       </c>
       <c r="B325" t="n">
-        <v>14.91324806213379</v>
+        <v>14.91324901580811</v>
       </c>
       <c r="C325" t="n">
-        <v>15.06739093728256</v>
+        <v>15.06739190081403</v>
       </c>
       <c r="D325" t="n">
-        <v>14.25814474747527</v>
+        <v>14.25814565925695</v>
       </c>
       <c r="E325" t="n">
-        <v>14.34484982763441</v>
+        <v>14.34485074496072</v>
       </c>
       <c r="F325" t="n">
         <v>25461900</v>
@@ -6952,16 +6952,16 @@
         <v>44732</v>
       </c>
       <c r="B327" t="n">
-        <v>15.31787395477295</v>
+        <v>15.31787300109863</v>
       </c>
       <c r="C327" t="n">
-        <v>15.50091825048741</v>
+        <v>15.50091728541696</v>
       </c>
       <c r="D327" t="n">
-        <v>14.83617979369507</v>
+        <v>14.83617887001052</v>
       </c>
       <c r="E327" t="n">
-        <v>15.0962950816813</v>
+        <v>15.09629414180225</v>
       </c>
       <c r="F327" t="n">
         <v>7611300</v>
@@ -7012,16 +7012,16 @@
         <v>44735</v>
       </c>
       <c r="B330" t="n">
-        <v>14.72057151794434</v>
+        <v>14.72057247161865</v>
       </c>
       <c r="C330" t="n">
-        <v>14.90361579143392</v>
+        <v>14.90361675696679</v>
       </c>
       <c r="D330" t="n">
-        <v>14.39301938118073</v>
+        <v>14.39302031363454</v>
       </c>
       <c r="E330" t="n">
-        <v>14.39301938118073</v>
+        <v>14.39302031363454</v>
       </c>
       <c r="F330" t="n">
         <v>3851900</v>
@@ -7032,16 +7032,16 @@
         <v>44736</v>
       </c>
       <c r="B331" t="n">
-        <v>14.4219217300415</v>
+        <v>14.42192268371582</v>
       </c>
       <c r="C331" t="n">
-        <v>14.86508034244202</v>
+        <v>14.86508132542095</v>
       </c>
       <c r="D331" t="n">
-        <v>14.25814566119184</v>
+        <v>14.25814660403618</v>
       </c>
       <c r="E331" t="n">
-        <v>14.86508034244202</v>
+        <v>14.86508132542095</v>
       </c>
       <c r="F331" t="n">
         <v>5803600</v>
@@ -7052,16 +7052,16 @@
         <v>44739</v>
       </c>
       <c r="B332" t="n">
-        <v>14.16180801391602</v>
+        <v>14.16180610656738</v>
       </c>
       <c r="C332" t="n">
-        <v>14.49899429088777</v>
+        <v>14.49899233812603</v>
       </c>
       <c r="D332" t="n">
-        <v>14.10400522965489</v>
+        <v>14.10400333009129</v>
       </c>
       <c r="E332" t="n">
-        <v>14.47972608362827</v>
+        <v>14.47972413346162</v>
       </c>
       <c r="F332" t="n">
         <v>8041800</v>
@@ -7072,16 +7072,16 @@
         <v>44740</v>
       </c>
       <c r="B333" t="n">
-        <v>14.08473682403564</v>
+        <v>14.08473587036133</v>
       </c>
       <c r="C333" t="n">
-        <v>14.48935998319984</v>
+        <v>14.48935900212858</v>
       </c>
       <c r="D333" t="n">
-        <v>13.96913033838283</v>
+        <v>13.9691293925362</v>
       </c>
       <c r="E333" t="n">
-        <v>14.23887880490607</v>
+        <v>14.23887784079483</v>
       </c>
       <c r="F333" t="n">
         <v>7081400</v>
@@ -7132,16 +7132,16 @@
         <v>44743</v>
       </c>
       <c r="B336" t="n">
-        <v>14.06546878814697</v>
+        <v>14.06546974182129</v>
       </c>
       <c r="C336" t="n">
-        <v>14.28704764418037</v>
+        <v>14.28704861287829</v>
       </c>
       <c r="D336" t="n">
-        <v>13.54523917098311</v>
+        <v>13.54524008938454</v>
       </c>
       <c r="E336" t="n">
-        <v>13.64157744452686</v>
+        <v>13.64157836946027</v>
       </c>
       <c r="F336" t="n">
         <v>10271400</v>
@@ -7152,16 +7152,16 @@
         <v>44746</v>
       </c>
       <c r="B337" t="n">
-        <v>13.8727912902832</v>
+        <v>13.87278938293457</v>
       </c>
       <c r="C337" t="n">
-        <v>14.14254067846864</v>
+        <v>14.14253873403259</v>
       </c>
       <c r="D337" t="n">
-        <v>13.76681890698379</v>
+        <v>13.76681701420514</v>
       </c>
       <c r="E337" t="n">
-        <v>13.95949638514576</v>
+        <v>13.95949446587618</v>
       </c>
       <c r="F337" t="n">
         <v>1980900</v>
@@ -7172,16 +7172,16 @@
         <v>44747</v>
       </c>
       <c r="B338" t="n">
-        <v>14.17144107818604</v>
+        <v>14.17144012451172</v>
       </c>
       <c r="C338" t="n">
-        <v>14.19070836527375</v>
+        <v>14.19070741030283</v>
       </c>
       <c r="D338" t="n">
-        <v>13.46816718369137</v>
+        <v>13.46816627734423</v>
       </c>
       <c r="E338" t="n">
-        <v>13.67047875128478</v>
+        <v>13.67047783132298</v>
       </c>
       <c r="F338" t="n">
         <v>7354200</v>
@@ -7212,16 +7212,16 @@
         <v>44749</v>
       </c>
       <c r="B340" t="n">
-        <v>14.57606410980225</v>
+        <v>14.57606506347656</v>
       </c>
       <c r="C340" t="n">
-        <v>14.95178585230849</v>
+        <v>14.95178683056531</v>
       </c>
       <c r="D340" t="n">
-        <v>14.47009173467626</v>
+        <v>14.47009268141707</v>
       </c>
       <c r="E340" t="n">
-        <v>14.49899312448178</v>
+        <v>14.49899407311354</v>
       </c>
       <c r="F340" t="n">
         <v>6763400</v>
@@ -7232,16 +7232,16 @@
         <v>44750</v>
       </c>
       <c r="B341" t="n">
-        <v>14.72057151794434</v>
+        <v>14.72057247161865</v>
       </c>
       <c r="C341" t="n">
-        <v>14.82654480851997</v>
+        <v>14.82654576905978</v>
       </c>
       <c r="D341" t="n">
-        <v>14.41228758628851</v>
+        <v>14.41228851999061</v>
       </c>
       <c r="E341" t="n">
-        <v>14.73983972305212</v>
+        <v>14.73984067797473</v>
       </c>
       <c r="F341" t="n">
         <v>3792400</v>
@@ -7252,16 +7252,16 @@
         <v>44753</v>
       </c>
       <c r="B342" t="n">
-        <v>14.788010597229</v>
+        <v>14.78800964355469</v>
       </c>
       <c r="C342" t="n">
-        <v>14.89398297821984</v>
+        <v>14.8939820177114</v>
       </c>
       <c r="D342" t="n">
-        <v>14.52789531830785</v>
+        <v>14.52789438140829</v>
       </c>
       <c r="E342" t="n">
-        <v>14.57606491648865</v>
+        <v>14.57606397648265</v>
       </c>
       <c r="F342" t="n">
         <v>3654100</v>
@@ -7272,16 +7272,16 @@
         <v>44754</v>
       </c>
       <c r="B343" t="n">
-        <v>14.68203544616699</v>
+        <v>14.68203639984131</v>
       </c>
       <c r="C343" t="n">
-        <v>14.97105208004998</v>
+        <v>14.97105305249743</v>
       </c>
       <c r="D343" t="n">
-        <v>14.59533036412624</v>
+        <v>14.59533131216861</v>
       </c>
       <c r="E343" t="n">
-        <v>14.79764191596848</v>
+        <v>14.79764287715203</v>
       </c>
       <c r="F343" t="n">
         <v>4929100</v>
@@ -7312,16 +7312,16 @@
         <v>44756</v>
       </c>
       <c r="B345" t="n">
-        <v>14.75910663604736</v>
+        <v>14.759108543396</v>
       </c>
       <c r="C345" t="n">
-        <v>14.99995368125053</v>
+        <v>14.99995561972431</v>
       </c>
       <c r="D345" t="n">
-        <v>14.5182595908442</v>
+        <v>14.51826146706769</v>
       </c>
       <c r="E345" t="n">
-        <v>14.52789369315438</v>
+        <v>14.5278955706229</v>
       </c>
       <c r="F345" t="n">
         <v>8175300</v>
@@ -7332,16 +7332,16 @@
         <v>44757</v>
       </c>
       <c r="B346" t="n">
-        <v>15.00958824157715</v>
+        <v>15.00959014892578</v>
       </c>
       <c r="C346" t="n">
-        <v>15.16373020820944</v>
+        <v>15.16373213514571</v>
       </c>
       <c r="D346" t="n">
-        <v>14.56642962813003</v>
+        <v>14.56643147916412</v>
       </c>
       <c r="E346" t="n">
-        <v>14.83617806973653</v>
+        <v>14.836179955049</v>
       </c>
       <c r="F346" t="n">
         <v>3973400</v>
@@ -7352,16 +7352,16 @@
         <v>44760</v>
       </c>
       <c r="B347" t="n">
-        <v>14.87471294403076</v>
+        <v>14.87471485137939</v>
       </c>
       <c r="C347" t="n">
-        <v>15.19263188546311</v>
+        <v>15.19263383357772</v>
       </c>
       <c r="D347" t="n">
-        <v>14.8072760661177</v>
+        <v>14.80727796481907</v>
       </c>
       <c r="E347" t="n">
-        <v>15.0770244965285</v>
+        <v>15.07702642981905</v>
       </c>
       <c r="F347" t="n">
         <v>3805700</v>
@@ -7432,16 +7432,16 @@
         <v>44764</v>
       </c>
       <c r="B351" t="n">
-        <v>15.0770263671875</v>
+        <v>15.07702541351318</v>
       </c>
       <c r="C351" t="n">
-        <v>15.14446417222636</v>
+        <v>15.14446321428636</v>
       </c>
       <c r="D351" t="n">
-        <v>14.78801061526745</v>
+        <v>14.78800967987438</v>
       </c>
       <c r="E351" t="n">
-        <v>14.84581339814799</v>
+        <v>14.8458124590987</v>
       </c>
       <c r="F351" t="n">
         <v>3071000</v>
@@ -7472,16 +7472,16 @@
         <v>44768</v>
       </c>
       <c r="B353" t="n">
-        <v>14.95178508758545</v>
+        <v>14.95178604125977</v>
       </c>
       <c r="C353" t="n">
-        <v>15.03848925256745</v>
+        <v>15.03849021177204</v>
       </c>
       <c r="D353" t="n">
-        <v>14.76874081774235</v>
+        <v>14.76874175974149</v>
       </c>
       <c r="E353" t="n">
-        <v>14.82654451315558</v>
+        <v>14.82654545884164</v>
       </c>
       <c r="F353" t="n">
         <v>3874000</v>
@@ -7532,16 +7532,16 @@
         <v>44771</v>
       </c>
       <c r="B356" t="n">
-        <v>15.26970386505127</v>
+        <v>15.26970291137695</v>
       </c>
       <c r="C356" t="n">
-        <v>15.66469289369624</v>
+        <v>15.66469191535275</v>
       </c>
       <c r="D356" t="n">
-        <v>15.26970386505127</v>
+        <v>15.26970291137695</v>
       </c>
       <c r="E356" t="n">
-        <v>15.59725601136913</v>
+        <v>15.59725503723744</v>
       </c>
       <c r="F356" t="n">
         <v>15825800</v>
@@ -7552,16 +7552,16 @@
         <v>44774</v>
       </c>
       <c r="B357" t="n">
-        <v>15.05775928497314</v>
+        <v>15.05775833129883</v>
       </c>
       <c r="C357" t="n">
-        <v>15.40457874327312</v>
+        <v>15.4045777676332</v>
       </c>
       <c r="D357" t="n">
-        <v>14.85544770460849</v>
+        <v>14.85544676374746</v>
       </c>
       <c r="E357" t="n">
-        <v>14.96142008717714</v>
+        <v>14.96141913960441</v>
       </c>
       <c r="F357" t="n">
         <v>9649400</v>
@@ -7572,16 +7572,16 @@
         <v>44775</v>
       </c>
       <c r="B358" t="n">
-        <v>15.09629440307617</v>
+        <v>15.09629344940186</v>
       </c>
       <c r="C358" t="n">
-        <v>15.2119008862871</v>
+        <v>15.21189992530961</v>
       </c>
       <c r="D358" t="n">
-        <v>14.80727773566952</v>
+        <v>14.80727680025318</v>
       </c>
       <c r="E358" t="n">
-        <v>15.04812480538195</v>
+        <v>15.04812385475064</v>
       </c>
       <c r="F358" t="n">
         <v>7865200</v>
@@ -7612,16 +7612,16 @@
         <v>44777</v>
       </c>
       <c r="B360" t="n">
-        <v>16.21382522583008</v>
+        <v>16.21382331848145</v>
       </c>
       <c r="C360" t="n">
-        <v>16.42576999307324</v>
+        <v>16.42576806079203</v>
       </c>
       <c r="D360" t="n">
-        <v>15.92480946708782</v>
+        <v>15.92480759373818</v>
       </c>
       <c r="E360" t="n">
-        <v>16.02114682832365</v>
+        <v>16.02114494364116</v>
       </c>
       <c r="F360" t="n">
         <v>10048700</v>
@@ -7632,16 +7632,16 @@
         <v>44778</v>
       </c>
       <c r="B361" t="n">
-        <v>16.4064998626709</v>
+        <v>16.40650367736816</v>
       </c>
       <c r="C361" t="n">
-        <v>16.57027591175573</v>
+        <v>16.57027976453278</v>
       </c>
       <c r="D361" t="n">
-        <v>16.10784823124054</v>
+        <v>16.10785197649791</v>
       </c>
       <c r="E361" t="n">
-        <v>16.26199017890661</v>
+        <v>16.26199396000374</v>
       </c>
       <c r="F361" t="n">
         <v>6244900</v>
@@ -7652,16 +7652,16 @@
         <v>44781</v>
       </c>
       <c r="B362" t="n">
-        <v>16.68588256835938</v>
+        <v>16.68588447570801</v>
       </c>
       <c r="C362" t="n">
-        <v>16.88819503663362</v>
+        <v>16.88819696710841</v>
       </c>
       <c r="D362" t="n">
-        <v>16.26199126520336</v>
+        <v>16.26199312409735</v>
       </c>
       <c r="E362" t="n">
-        <v>16.53174061039666</v>
+        <v>16.53174250012546</v>
       </c>
       <c r="F362" t="n">
         <v>10381400</v>
@@ -7712,16 +7712,16 @@
         <v>44784</v>
       </c>
       <c r="B365" t="n">
-        <v>16.99416542053223</v>
+        <v>16.99416732788086</v>
       </c>
       <c r="C365" t="n">
-        <v>17.34098572299761</v>
+        <v>17.34098766927179</v>
       </c>
       <c r="D365" t="n">
-        <v>16.86892577659582</v>
+        <v>16.86892766988812</v>
       </c>
       <c r="E365" t="n">
-        <v>16.91709444637514</v>
+        <v>16.91709634507367</v>
       </c>
       <c r="F365" t="n">
         <v>8667500</v>
@@ -7732,16 +7732,16 @@
         <v>44785</v>
       </c>
       <c r="B366" t="n">
-        <v>17.34099006652832</v>
+        <v>17.34098625183105</v>
       </c>
       <c r="C366" t="n">
-        <v>17.64927404037492</v>
+        <v>17.64927015786088</v>
       </c>
       <c r="D366" t="n">
-        <v>17.06160656678144</v>
+        <v>17.06160281354338</v>
       </c>
       <c r="E366" t="n">
-        <v>17.16757987186025</v>
+        <v>17.16757609531002</v>
       </c>
       <c r="F366" t="n">
         <v>11729000</v>
@@ -7752,16 +7752,16 @@
         <v>44788</v>
       </c>
       <c r="B367" t="n">
-        <v>17.53366661071777</v>
+        <v>17.53366851806641</v>
       </c>
       <c r="C367" t="n">
-        <v>17.66854037560234</v>
+        <v>17.66854229762282</v>
       </c>
       <c r="D367" t="n">
-        <v>17.06160475858731</v>
+        <v>17.06160661458408</v>
       </c>
       <c r="E367" t="n">
-        <v>17.20611446384048</v>
+        <v>17.20611633555731</v>
       </c>
       <c r="F367" t="n">
         <v>7999500</v>
@@ -7772,16 +7772,16 @@
         <v>44789</v>
       </c>
       <c r="B368" t="n">
-        <v>17.42769432067871</v>
+        <v>17.42769241333008</v>
       </c>
       <c r="C368" t="n">
-        <v>17.63000497965835</v>
+        <v>17.63000305016812</v>
       </c>
       <c r="D368" t="n">
-        <v>17.19648135148026</v>
+        <v>17.1964794694364</v>
       </c>
       <c r="E368" t="n">
-        <v>17.52403351722407</v>
+        <v>17.52403159933173</v>
       </c>
       <c r="F368" t="n">
         <v>4828900</v>
@@ -7832,16 +7832,16 @@
         <v>44792</v>
       </c>
       <c r="B371" t="n">
-        <v>17.1290454864502</v>
+        <v>17.12904357910156</v>
       </c>
       <c r="C371" t="n">
-        <v>17.57220324445724</v>
+        <v>17.57220128776223</v>
       </c>
       <c r="D371" t="n">
-        <v>17.07124086256606</v>
+        <v>17.07123896165407</v>
       </c>
       <c r="E371" t="n">
-        <v>17.45659767172386</v>
+        <v>17.45659572790173</v>
       </c>
       <c r="F371" t="n">
         <v>7571900</v>
@@ -7852,16 +7852,16 @@
         <v>44795</v>
       </c>
       <c r="B372" t="n">
-        <v>17.36025810241699</v>
+        <v>17.36025619506836</v>
       </c>
       <c r="C372" t="n">
-        <v>17.45659730266971</v>
+        <v>17.45659538473642</v>
       </c>
       <c r="D372" t="n">
-        <v>16.82075931600872</v>
+        <v>16.82075746793411</v>
       </c>
       <c r="E372" t="n">
-        <v>16.98453540518312</v>
+        <v>16.98453353911465</v>
       </c>
       <c r="F372" t="n">
         <v>10077700</v>
@@ -7892,16 +7892,16 @@
         <v>44797</v>
       </c>
       <c r="B374" t="n">
-        <v>17.14830780029297</v>
+        <v>17.14831161499023</v>
       </c>
       <c r="C374" t="n">
-        <v>17.26391518319573</v>
+        <v>17.26391902361024</v>
       </c>
       <c r="D374" t="n">
-        <v>16.99416584810063</v>
+        <v>16.99416962850851</v>
       </c>
       <c r="E374" t="n">
-        <v>17.14830780029297</v>
+        <v>17.14831161499023</v>
       </c>
       <c r="F374" t="n">
         <v>5807100</v>
@@ -7952,16 +7952,16 @@
         <v>44802</v>
       </c>
       <c r="B377" t="n">
-        <v>17.68780899047852</v>
+        <v>17.68780708312988</v>
       </c>
       <c r="C377" t="n">
-        <v>17.98645883571042</v>
+        <v>17.98645689615716</v>
       </c>
       <c r="D377" t="n">
-        <v>17.19648075879664</v>
+        <v>17.19647890442993</v>
       </c>
       <c r="E377" t="n">
-        <v>17.29281995202162</v>
+        <v>17.29281808726627</v>
       </c>
       <c r="F377" t="n">
         <v>7263100</v>
@@ -7992,16 +7992,16 @@
         <v>44804</v>
       </c>
       <c r="B379" t="n">
-        <v>17.71670913696289</v>
+        <v>17.71671104431152</v>
       </c>
       <c r="C379" t="n">
-        <v>17.98645850553768</v>
+        <v>17.98646044192704</v>
       </c>
       <c r="D379" t="n">
-        <v>17.51439848866973</v>
+        <v>17.51440037423797</v>
       </c>
       <c r="E379" t="n">
-        <v>17.74561144565502</v>
+        <v>17.74561335611522</v>
       </c>
       <c r="F379" t="n">
         <v>9759800</v>
@@ -8032,16 +8032,16 @@
         <v>44806</v>
       </c>
       <c r="B381" t="n">
-        <v>18.20803833007812</v>
+        <v>18.20803642272949</v>
       </c>
       <c r="C381" t="n">
-        <v>18.54522459938866</v>
+        <v>18.54522265671872</v>
       </c>
       <c r="D381" t="n">
-        <v>17.95755715394794</v>
+        <v>17.95755527283799</v>
       </c>
       <c r="E381" t="n">
-        <v>18.20803833007812</v>
+        <v>18.20803642272949</v>
       </c>
       <c r="F381" t="n">
         <v>12423600</v>
@@ -8072,16 +8072,16 @@
         <v>44810</v>
       </c>
       <c r="B383" t="n">
-        <v>18.75716590881348</v>
+        <v>18.75716781616211</v>
       </c>
       <c r="C383" t="n">
-        <v>18.83423688439475</v>
+        <v>18.83423879958045</v>
       </c>
       <c r="D383" t="n">
-        <v>18.33327646187499</v>
+        <v>18.33327832611984</v>
       </c>
       <c r="E383" t="n">
-        <v>18.68972903486949</v>
+        <v>18.68973093536071</v>
       </c>
       <c r="F383" t="n">
         <v>7863100</v>
@@ -8092,16 +8092,16 @@
         <v>44812</v>
       </c>
       <c r="B384" t="n">
-        <v>18.40071678161621</v>
+        <v>18.40071487426758</v>
       </c>
       <c r="C384" t="n">
-        <v>18.94984781515502</v>
+        <v>18.94984585088554</v>
       </c>
       <c r="D384" t="n">
-        <v>18.34291399848511</v>
+        <v>18.3429120971281</v>
       </c>
       <c r="E384" t="n">
-        <v>18.91131140138939</v>
+        <v>18.91130944111445</v>
       </c>
       <c r="F384" t="n">
         <v>6653400</v>
@@ -8112,16 +8112,16 @@
         <v>44813</v>
       </c>
       <c r="B385" t="n">
-        <v>18.15986824035645</v>
+        <v>18.15987014770508</v>
       </c>
       <c r="C385" t="n">
-        <v>18.62229414306423</v>
+        <v>18.6222960989819</v>
       </c>
       <c r="D385" t="n">
-        <v>18.08279725657182</v>
+        <v>18.08279915582561</v>
       </c>
       <c r="E385" t="n">
-        <v>18.47778627815769</v>
+        <v>18.47778821889757</v>
       </c>
       <c r="F385" t="n">
         <v>8752700</v>
@@ -8132,16 +8132,16 @@
         <v>44816</v>
       </c>
       <c r="B386" t="n">
-        <v>17.78414535522461</v>
+        <v>17.78414726257324</v>
       </c>
       <c r="C386" t="n">
-        <v>18.38144684992308</v>
+        <v>18.38144882133227</v>
       </c>
       <c r="D386" t="n">
-        <v>17.7070743724426</v>
+        <v>17.70707627152537</v>
       </c>
       <c r="E386" t="n">
-        <v>18.25620719197125</v>
+        <v>18.25620914994849</v>
       </c>
       <c r="F386" t="n">
         <v>10149200</v>
@@ -8172,16 +8172,16 @@
         <v>44818</v>
       </c>
       <c r="B388" t="n">
-        <v>17.70707511901855</v>
+        <v>17.70707321166992</v>
       </c>
       <c r="C388" t="n">
-        <v>17.8708511940252</v>
+        <v>17.87084926903514</v>
       </c>
       <c r="D388" t="n">
-        <v>17.36989070357892</v>
+        <v>17.3698888325507</v>
       </c>
       <c r="E388" t="n">
-        <v>17.44696168961044</v>
+        <v>17.44695981028038</v>
       </c>
       <c r="F388" t="n">
         <v>7347400</v>
@@ -8192,16 +8192,16 @@
         <v>44819</v>
       </c>
       <c r="B389" t="n">
-        <v>17.6203727722168</v>
+        <v>17.62037086486816</v>
       </c>
       <c r="C389" t="n">
-        <v>17.84195163874396</v>
+        <v>17.84194970741013</v>
       </c>
       <c r="D389" t="n">
-        <v>17.48549716159898</v>
+        <v>17.4854952688502</v>
       </c>
       <c r="E389" t="n">
-        <v>17.69744376220526</v>
+        <v>17.69744184651394</v>
       </c>
       <c r="F389" t="n">
         <v>7203900</v>
@@ -8292,16 +8292,16 @@
         <v>44826</v>
       </c>
       <c r="B394" t="n">
-        <v>17.36025810241699</v>
+        <v>17.36025619506836</v>
       </c>
       <c r="C394" t="n">
-        <v>17.88048684375383</v>
+        <v>17.88048487924835</v>
       </c>
       <c r="D394" t="n">
-        <v>16.94600082759248</v>
+        <v>16.94599896575775</v>
       </c>
       <c r="E394" t="n">
-        <v>17.66854207321177</v>
+        <v>17.66854013199238</v>
       </c>
       <c r="F394" t="n">
         <v>12903600</v>
@@ -8312,16 +8312,16 @@
         <v>44827</v>
       </c>
       <c r="B395" t="n">
-        <v>17.13867950439453</v>
+        <v>17.1386775970459</v>
       </c>
       <c r="C395" t="n">
-        <v>17.42769527229457</v>
+        <v>17.42769333278163</v>
       </c>
       <c r="D395" t="n">
-        <v>16.96526930864753</v>
+        <v>16.96526742059757</v>
       </c>
       <c r="E395" t="n">
-        <v>17.10977719259755</v>
+        <v>17.10977528846543</v>
       </c>
       <c r="F395" t="n">
         <v>12048200</v>
@@ -8352,16 +8352,16 @@
         <v>44831</v>
       </c>
       <c r="B397" t="n">
-        <v>17.1290454864502</v>
+        <v>17.12904357910156</v>
       </c>
       <c r="C397" t="n">
-        <v>17.49513225012917</v>
+        <v>17.49513030201615</v>
       </c>
       <c r="D397" t="n">
-        <v>16.86893019152391</v>
+        <v>16.86892831313957</v>
       </c>
       <c r="E397" t="n">
-        <v>17.25428516316427</v>
+        <v>17.25428324186998</v>
       </c>
       <c r="F397" t="n">
         <v>9260100</v>
@@ -8412,16 +8412,16 @@
         <v>44834</v>
       </c>
       <c r="B400" t="n">
-        <v>16.90746307373047</v>
+        <v>16.9074649810791</v>
       </c>
       <c r="C400" t="n">
-        <v>17.28318574121415</v>
+        <v>17.28318769094845</v>
       </c>
       <c r="D400" t="n">
-        <v>16.85929439617687</v>
+        <v>16.85929629809154</v>
       </c>
       <c r="E400" t="n">
-        <v>17.24464932915746</v>
+        <v>17.24465127454443</v>
       </c>
       <c r="F400" t="n">
         <v>11790900</v>
@@ -8512,16 +8512,16 @@
         <v>44841</v>
       </c>
       <c r="B405" t="n">
-        <v>17.49513053894043</v>
+        <v>17.49513244628906</v>
       </c>
       <c r="C405" t="n">
-        <v>17.68780892467357</v>
+        <v>17.68781085302832</v>
       </c>
       <c r="D405" t="n">
-        <v>17.32172035928406</v>
+        <v>17.32172224772722</v>
       </c>
       <c r="E405" t="n">
-        <v>17.44696186126578</v>
+        <v>17.44696376336298</v>
       </c>
       <c r="F405" t="n">
         <v>11897600</v>
@@ -8572,16 +8572,16 @@
         <v>44847</v>
       </c>
       <c r="B408" t="n">
-        <v>18.75716590881348</v>
+        <v>18.75716781616211</v>
       </c>
       <c r="C408" t="n">
-        <v>18.99801293719457</v>
+        <v>18.99801486903407</v>
       </c>
       <c r="D408" t="n">
-        <v>17.93828748233136</v>
+        <v>17.93828930641119</v>
       </c>
       <c r="E408" t="n">
-        <v>18.17913451071245</v>
+        <v>18.17913635928316</v>
       </c>
       <c r="F408" t="n">
         <v>20665700</v>
@@ -8592,16 +8592,16 @@
         <v>44848</v>
       </c>
       <c r="B409" t="n">
-        <v>18.39108085632324</v>
+        <v>18.39108276367188</v>
       </c>
       <c r="C409" t="n">
-        <v>18.94021183546421</v>
+        <v>18.9402137997635</v>
       </c>
       <c r="D409" t="n">
-        <v>18.29474166897004</v>
+        <v>18.29474356632728</v>
       </c>
       <c r="E409" t="n">
-        <v>18.80533807568002</v>
+        <v>18.80534002599148</v>
       </c>
       <c r="F409" t="n">
         <v>11391600</v>
@@ -8612,16 +8612,16 @@
         <v>44851</v>
       </c>
       <c r="B410" t="n">
-        <v>19.01728248596191</v>
+        <v>19.01728439331055</v>
       </c>
       <c r="C410" t="n">
-        <v>19.06545299755645</v>
+        <v>19.06545490973637</v>
       </c>
       <c r="D410" t="n">
-        <v>18.3621782284133</v>
+        <v>18.3621800700579</v>
       </c>
       <c r="E410" t="n">
-        <v>18.49705382336087</v>
+        <v>18.49705567853288</v>
       </c>
       <c r="F410" t="n">
         <v>20683400</v>
@@ -8632,16 +8632,16 @@
         <v>44852</v>
       </c>
       <c r="B411" t="n">
-        <v>17.26391792297363</v>
+        <v>17.26391983032227</v>
       </c>
       <c r="C411" t="n">
-        <v>19.16179215898201</v>
+        <v>19.16179427601119</v>
       </c>
       <c r="D411" t="n">
-        <v>17.26391792297363</v>
+        <v>17.26391983032227</v>
       </c>
       <c r="E411" t="n">
-        <v>19.10398937711585</v>
+        <v>19.10399148775888</v>
       </c>
       <c r="F411" t="n">
         <v>33355700</v>
@@ -8652,16 +8652,16 @@
         <v>44853</v>
       </c>
       <c r="B412" t="n">
-        <v>17.67817497253418</v>
+        <v>17.67817306518555</v>
       </c>
       <c r="C412" t="n">
-        <v>17.97682481920425</v>
+        <v>17.97682287963343</v>
       </c>
       <c r="D412" t="n">
-        <v>17.2831859321752</v>
+        <v>17.28318406744306</v>
       </c>
       <c r="E412" t="n">
-        <v>17.47586248203574</v>
+        <v>17.47586059651518</v>
       </c>
       <c r="F412" t="n">
         <v>27062400</v>
@@ -8752,16 +8752,16 @@
         <v>44860</v>
       </c>
       <c r="B417" t="n">
-        <v>16.45466995239258</v>
+        <v>16.45467185974121</v>
       </c>
       <c r="C417" t="n">
-        <v>17.07123779627069</v>
+        <v>17.07123977508899</v>
       </c>
       <c r="D417" t="n">
-        <v>16.36796486965758</v>
+        <v>16.36796676695576</v>
       </c>
       <c r="E417" t="n">
-        <v>17.0423373270371</v>
+        <v>17.0423393025054</v>
       </c>
       <c r="F417" t="n">
         <v>12823000</v>
@@ -8792,16 +8792,16 @@
         <v>44862</v>
       </c>
       <c r="B419" t="n">
-        <v>18.1213321685791</v>
+        <v>18.12133026123047</v>
       </c>
       <c r="C419" t="n">
-        <v>18.21767135949075</v>
+        <v>18.21766944200201</v>
       </c>
       <c r="D419" t="n">
-        <v>17.27355133109445</v>
+        <v>17.27354951297842</v>
       </c>
       <c r="E419" t="n">
-        <v>17.40842509586043</v>
+        <v>17.40842326354835</v>
       </c>
       <c r="F419" t="n">
         <v>12193800</v>
@@ -8812,16 +8812,16 @@
         <v>44865</v>
       </c>
       <c r="B420" t="n">
-        <v>19.09435272216797</v>
+        <v>19.0943546295166</v>
       </c>
       <c r="C420" t="n">
-        <v>19.24849467822348</v>
+        <v>19.24849660096946</v>
       </c>
       <c r="D420" t="n">
-        <v>18.13096457806249</v>
+        <v>18.13096638917758</v>
       </c>
       <c r="E420" t="n">
-        <v>18.2947406360611</v>
+        <v>18.2947424635359</v>
       </c>
       <c r="F420" t="n">
         <v>18379300</v>
@@ -8852,16 +8852,16 @@
         <v>44868</v>
       </c>
       <c r="B422" t="n">
-        <v>19.62421798706055</v>
+        <v>19.62421989440918</v>
       </c>
       <c r="C422" t="n">
-        <v>19.74945764164638</v>
+        <v>19.74945956116751</v>
       </c>
       <c r="D422" t="n">
-        <v>18.69936438101601</v>
+        <v>18.69936619847478</v>
       </c>
       <c r="E422" t="n">
-        <v>18.69936438101601</v>
+        <v>18.69936619847478</v>
       </c>
       <c r="F422" t="n">
         <v>9732300</v>
@@ -8872,16 +8872,16 @@
         <v>44869</v>
       </c>
       <c r="B423" t="n">
-        <v>19.79763031005859</v>
+        <v>19.79762649536133</v>
       </c>
       <c r="C423" t="n">
-        <v>19.9806746152478</v>
+        <v>19.98067076528072</v>
       </c>
       <c r="D423" t="n">
-        <v>19.60495373816456</v>
+        <v>19.60494996059309</v>
       </c>
       <c r="E423" t="n">
-        <v>19.81689851850324</v>
+        <v>19.81689470009329</v>
       </c>
       <c r="F423" t="n">
         <v>15655600</v>
@@ -8892,16 +8892,16 @@
         <v>44872</v>
       </c>
       <c r="B424" t="n">
-        <v>19.51824378967285</v>
+        <v>19.51824569702148</v>
       </c>
       <c r="C424" t="n">
-        <v>19.94213508258015</v>
+        <v>19.942137031352</v>
       </c>
       <c r="D424" t="n">
-        <v>19.14252300591243</v>
+        <v>19.14252487654513</v>
       </c>
       <c r="E424" t="n">
-        <v>19.69165394756752</v>
+        <v>19.69165587186202</v>
       </c>
       <c r="F424" t="n">
         <v>17754600</v>
@@ -8932,16 +8932,16 @@
         <v>44874</v>
       </c>
       <c r="B426" t="n">
-        <v>19.65312194824219</v>
+        <v>19.65312004089355</v>
       </c>
       <c r="C426" t="n">
-        <v>20.09628154420435</v>
+        <v>20.09627959384678</v>
       </c>
       <c r="D426" t="n">
-        <v>19.13289319539329</v>
+        <v>19.1328913385332</v>
       </c>
       <c r="E426" t="n">
-        <v>19.13289319539329</v>
+        <v>19.1328913385332</v>
       </c>
       <c r="F426" t="n">
         <v>19633400</v>
@@ -8952,16 +8952,16 @@
         <v>44875</v>
       </c>
       <c r="B427" t="n">
-        <v>18.80533790588379</v>
+        <v>18.80533981323242</v>
       </c>
       <c r="C427" t="n">
-        <v>19.64348460199946</v>
+        <v>19.64348659435789</v>
       </c>
       <c r="D427" t="n">
-        <v>18.43924936475051</v>
+        <v>18.43925123496827</v>
       </c>
       <c r="E427" t="n">
-        <v>19.64348460199946</v>
+        <v>19.64348659435789</v>
       </c>
       <c r="F427" t="n">
         <v>13893700</v>
@@ -9032,16 +9032,16 @@
         <v>44882</v>
       </c>
       <c r="B431" t="n">
-        <v>18.78606986999512</v>
+        <v>18.78607368469238</v>
       </c>
       <c r="C431" t="n">
-        <v>18.90167726231802</v>
+        <v>18.90168110049051</v>
       </c>
       <c r="D431" t="n">
-        <v>18.05389461866248</v>
+        <v>18.05389828468432</v>
       </c>
       <c r="E431" t="n">
-        <v>18.6608302127027</v>
+        <v>18.66083400196882</v>
       </c>
       <c r="F431" t="n">
         <v>10826800</v>
@@ -9092,16 +9092,16 @@
         <v>44887</v>
       </c>
       <c r="B434" t="n">
-        <v>18.75716590881348</v>
+        <v>18.75716781616211</v>
       </c>
       <c r="C434" t="n">
-        <v>19.3930019167382</v>
+        <v>19.39300388874271</v>
       </c>
       <c r="D434" t="n">
-        <v>18.6222921609255</v>
+        <v>18.62229405455931</v>
       </c>
       <c r="E434" t="n">
-        <v>19.07508391277584</v>
+        <v>19.07508585245241</v>
       </c>
       <c r="F434" t="n">
         <v>9653000</v>
@@ -9132,16 +9132,16 @@
         <v>44889</v>
       </c>
       <c r="B436" t="n">
-        <v>19.08472061157227</v>
+        <v>19.0847225189209</v>
       </c>
       <c r="C436" t="n">
-        <v>19.26776489255638</v>
+        <v>19.26776681819867</v>
       </c>
       <c r="D436" t="n">
-        <v>18.58376012087891</v>
+        <v>18.58376197816099</v>
       </c>
       <c r="E436" t="n">
-        <v>18.67046337237954</v>
+        <v>18.67046523832684</v>
       </c>
       <c r="F436" t="n">
         <v>7241600</v>
@@ -9152,16 +9152,16 @@
         <v>44890</v>
       </c>
       <c r="B437" t="n">
-        <v>18.50668716430664</v>
+        <v>18.50668907165527</v>
       </c>
       <c r="C437" t="n">
-        <v>19.16179145994887</v>
+        <v>19.1617934348143</v>
       </c>
       <c r="D437" t="n">
-        <v>18.41998391342904</v>
+        <v>18.4199858118418</v>
       </c>
       <c r="E437" t="n">
-        <v>19.16179145994887</v>
+        <v>19.1617934348143</v>
       </c>
       <c r="F437" t="n">
         <v>6509300</v>
@@ -9212,16 +9212,16 @@
         <v>44895</v>
       </c>
       <c r="B440" t="n">
-        <v>19.31593322753906</v>
+        <v>19.3159351348877</v>
       </c>
       <c r="C440" t="n">
-        <v>19.38337194698261</v>
+        <v>19.38337386099047</v>
       </c>
       <c r="D440" t="n">
-        <v>18.15986845697931</v>
+        <v>18.15987025017252</v>
       </c>
       <c r="E440" t="n">
-        <v>18.30437632360963</v>
+        <v>18.30437813107224</v>
       </c>
       <c r="F440" t="n">
         <v>128079800</v>
@@ -9312,16 +9312,16 @@
         <v>44902</v>
       </c>
       <c r="B445" t="n">
-        <v>19.36410331726074</v>
+        <v>19.36410522460938</v>
       </c>
       <c r="C445" t="n">
-        <v>19.48934297559241</v>
+        <v>19.48934489527705</v>
       </c>
       <c r="D445" t="n">
-        <v>18.82460643615043</v>
+        <v>18.82460829035904</v>
       </c>
       <c r="E445" t="n">
-        <v>19.17142494096275</v>
+        <v>19.17142682933272</v>
       </c>
       <c r="F445" t="n">
         <v>7439200</v>
@@ -9352,16 +9352,16 @@
         <v>44904</v>
       </c>
       <c r="B447" t="n">
-        <v>18.57412719726562</v>
+        <v>18.57412528991699</v>
       </c>
       <c r="C447" t="n">
-        <v>18.75716965235448</v>
+        <v>18.7571677262095</v>
       </c>
       <c r="D447" t="n">
-        <v>18.25620912985342</v>
+        <v>18.25620725515131</v>
       </c>
       <c r="E447" t="n">
-        <v>18.57412719726562</v>
+        <v>18.57412528991699</v>
       </c>
       <c r="F447" t="n">
         <v>14833900</v>
@@ -9412,16 +9412,16 @@
         <v>44909</v>
       </c>
       <c r="B450" t="n">
-        <v>18.37181282043457</v>
+        <v>18.3718147277832</v>
       </c>
       <c r="C450" t="n">
-        <v>18.46815200867444</v>
+        <v>18.46815392602494</v>
       </c>
       <c r="D450" t="n">
-        <v>17.64927166491134</v>
+        <v>17.64927349724626</v>
       </c>
       <c r="E450" t="n">
-        <v>17.86121824654248</v>
+        <v>17.86122010088155</v>
       </c>
       <c r="F450" t="n">
         <v>10673700</v>
@@ -9432,16 +9432,16 @@
         <v>44910</v>
       </c>
       <c r="B451" t="n">
-        <v>18.41998481750488</v>
+        <v>18.41998291015625</v>
       </c>
       <c r="C451" t="n">
-        <v>18.75716924723731</v>
+        <v>18.75716730497398</v>
       </c>
       <c r="D451" t="n">
-        <v>18.0924326536071</v>
+        <v>18.09243078017577</v>
       </c>
       <c r="E451" t="n">
-        <v>18.11169902279372</v>
+        <v>18.1116971473674</v>
       </c>
       <c r="F451" t="n">
         <v>15735500</v>
@@ -9452,16 +9452,16 @@
         <v>44911</v>
       </c>
       <c r="B452" t="n">
-        <v>18.02499389648438</v>
+        <v>18.02499580383301</v>
       </c>
       <c r="C452" t="n">
-        <v>18.69936642972459</v>
+        <v>18.69936840843323</v>
       </c>
       <c r="D452" t="n">
-        <v>17.55293385822315</v>
+        <v>17.55293571561986</v>
       </c>
       <c r="E452" t="n">
-        <v>18.38144836977245</v>
+        <v>18.38145031483998</v>
       </c>
       <c r="F452" t="n">
         <v>14090800</v>
@@ -9472,16 +9472,16 @@
         <v>44914</v>
       </c>
       <c r="B453" t="n">
-        <v>18.83423805236816</v>
+        <v>18.83424186706543</v>
       </c>
       <c r="C453" t="n">
-        <v>18.90167676801125</v>
+        <v>18.90168059636759</v>
       </c>
       <c r="D453" t="n">
-        <v>18.13096512688717</v>
+        <v>18.13096879914314</v>
       </c>
       <c r="E453" t="n">
-        <v>18.15023333135662</v>
+        <v>18.15023700751518</v>
       </c>
       <c r="F453" t="n">
         <v>7150400</v>
@@ -9492,16 +9492,16 @@
         <v>44915</v>
       </c>
       <c r="B454" t="n">
-        <v>19.26776313781738</v>
+        <v>19.26776504516602</v>
       </c>
       <c r="C454" t="n">
-        <v>19.66275213514127</v>
+        <v>19.66275408159054</v>
       </c>
       <c r="D454" t="n">
-        <v>18.86314003842253</v>
+        <v>18.86314190571684</v>
       </c>
       <c r="E454" t="n">
-        <v>18.91130871126024</v>
+        <v>18.91131058332285</v>
       </c>
       <c r="F454" t="n">
         <v>10658900</v>
@@ -9532,16 +9532,16 @@
         <v>44917</v>
       </c>
       <c r="B456" t="n">
-        <v>19.38337135314941</v>
+        <v>19.38337326049805</v>
       </c>
       <c r="C456" t="n">
-        <v>19.52787921535256</v>
+        <v>19.52788113692095</v>
       </c>
       <c r="D456" t="n">
-        <v>19.07508558626097</v>
+        <v>19.07508746327389</v>
       </c>
       <c r="E456" t="n">
-        <v>19.52787921535256</v>
+        <v>19.52788113692095</v>
       </c>
       <c r="F456" t="n">
         <v>7183700</v>
@@ -9572,16 +9572,16 @@
         <v>44921</v>
       </c>
       <c r="B458" t="n">
-        <v>19.20033073425293</v>
+        <v>19.2003288269043</v>
       </c>
       <c r="C458" t="n">
-        <v>19.32557041532036</v>
+        <v>19.3255684955305</v>
       </c>
       <c r="D458" t="n">
-        <v>18.84387622464675</v>
+        <v>18.84387435270808</v>
       </c>
       <c r="E458" t="n">
-        <v>19.07508921566799</v>
+        <v>19.07508732076077</v>
       </c>
       <c r="F458" t="n">
         <v>2369600</v>
@@ -9592,16 +9592,16 @@
         <v>44922</v>
       </c>
       <c r="B459" t="n">
-        <v>18.59339332580566</v>
+        <v>18.59339141845703</v>
       </c>
       <c r="C459" t="n">
-        <v>19.36410506296115</v>
+        <v>19.36410307655132</v>
       </c>
       <c r="D459" t="n">
-        <v>18.41998497652509</v>
+        <v>18.41998308696504</v>
       </c>
       <c r="E459" t="n">
-        <v>19.28703407299734</v>
+        <v>19.28703209449361</v>
       </c>
       <c r="F459" t="n">
         <v>8606100</v>
@@ -9612,16 +9612,16 @@
         <v>44923</v>
       </c>
       <c r="B460" t="n">
-        <v>18.7186336517334</v>
+        <v>18.71863555908203</v>
       </c>
       <c r="C460" t="n">
-        <v>18.94984660703449</v>
+        <v>18.94984853794273</v>
       </c>
       <c r="D460" t="n">
-        <v>18.26584000644119</v>
+        <v>18.26584186765209</v>
       </c>
       <c r="E460" t="n">
-        <v>18.6897313432518</v>
+        <v>18.68973324765541</v>
       </c>
       <c r="F460" t="n">
         <v>8329700</v>
@@ -9732,16 +9732,16 @@
         <v>44932</v>
       </c>
       <c r="B466" t="n">
-        <v>18.37796783447266</v>
+        <v>18.37796592712402</v>
       </c>
       <c r="C466" t="n">
-        <v>18.85092999831188</v>
+        <v>18.85092804187709</v>
       </c>
       <c r="D466" t="n">
-        <v>18.20422625570949</v>
+        <v>18.20422436639255</v>
       </c>
       <c r="E466" t="n">
-        <v>18.33935777651244</v>
+        <v>18.33935587317094</v>
       </c>
       <c r="F466" t="n">
         <v>4999100</v>
@@ -9772,16 +9772,16 @@
         <v>44936</v>
       </c>
       <c r="B468" t="n">
-        <v>18.57101249694824</v>
+        <v>18.57101058959961</v>
       </c>
       <c r="C468" t="n">
-        <v>18.68684082914984</v>
+        <v>18.68683890990498</v>
       </c>
       <c r="D468" t="n">
-        <v>18.14631106691423</v>
+        <v>18.14630920318485</v>
       </c>
       <c r="E468" t="n">
-        <v>18.29109694242345</v>
+        <v>18.29109506382374</v>
       </c>
       <c r="F468" t="n">
         <v>7152400</v>
@@ -9812,16 +9812,16 @@
         <v>44938</v>
       </c>
       <c r="B470" t="n">
-        <v>19.30458450317383</v>
+        <v>19.30458641052246</v>
       </c>
       <c r="C470" t="n">
-        <v>19.77754660257815</v>
+        <v>19.7775485566568</v>
       </c>
       <c r="D470" t="n">
-        <v>18.84127491694453</v>
+        <v>18.84127677851684</v>
       </c>
       <c r="E470" t="n">
-        <v>19.09223473640923</v>
+        <v>19.09223662277709</v>
       </c>
       <c r="F470" t="n">
         <v>10710500</v>
@@ -9892,16 +9892,16 @@
         <v>44944</v>
       </c>
       <c r="B474" t="n">
-        <v>19.70032691955566</v>
+        <v>19.70033073425293</v>
       </c>
       <c r="C474" t="n">
-        <v>19.96093923342829</v>
+        <v>19.96094309858955</v>
       </c>
       <c r="D474" t="n">
-        <v>19.40110639679182</v>
+        <v>19.40111015354915</v>
       </c>
       <c r="E474" t="n">
-        <v>19.59415112330493</v>
+        <v>19.59415491744271</v>
       </c>
       <c r="F474" t="n">
         <v>9224700</v>
@@ -9932,16 +9932,16 @@
         <v>44946</v>
       </c>
       <c r="B476" t="n">
-        <v>19.30458450317383</v>
+        <v>19.30458641052246</v>
       </c>
       <c r="C476" t="n">
-        <v>19.43971600556688</v>
+        <v>19.43971792626689</v>
       </c>
       <c r="D476" t="n">
-        <v>19.03431965735908</v>
+        <v>19.03432153800477</v>
       </c>
       <c r="E476" t="n">
-        <v>19.3914552807204</v>
+        <v>19.39145719665212</v>
       </c>
       <c r="F476" t="n">
         <v>5910600</v>
@@ -9952,16 +9952,16 @@
         <v>44949</v>
       </c>
       <c r="B477" t="n">
-        <v>19.56519508361816</v>
+        <v>19.56519889831543</v>
       </c>
       <c r="C477" t="n">
-        <v>19.78719734367598</v>
+        <v>19.78720120165784</v>
       </c>
       <c r="D477" t="n">
-        <v>19.25632205379363</v>
+        <v>19.2563258082688</v>
       </c>
       <c r="E477" t="n">
-        <v>19.28527774969688</v>
+        <v>19.28528150981765</v>
       </c>
       <c r="F477" t="n">
         <v>3499900</v>
@@ -9972,16 +9972,16 @@
         <v>44950</v>
       </c>
       <c r="B478" t="n">
-        <v>20.31807708740234</v>
+        <v>20.31807518005371</v>
       </c>
       <c r="C478" t="n">
-        <v>20.46286296277044</v>
+        <v>20.46286104183011</v>
       </c>
       <c r="D478" t="n">
-        <v>19.66172267566264</v>
+        <v>19.66172082992893</v>
       </c>
       <c r="E478" t="n">
-        <v>19.67137334906023</v>
+        <v>19.67137150242056</v>
       </c>
       <c r="F478" t="n">
         <v>6625300</v>
@@ -9992,16 +9992,16 @@
         <v>44951</v>
       </c>
       <c r="B479" t="n">
-        <v>20.37599182128906</v>
+        <v>20.37598991394043</v>
       </c>
       <c r="C479" t="n">
-        <v>20.61729915468745</v>
+        <v>20.6172972247506</v>
       </c>
       <c r="D479" t="n">
-        <v>20.12503197363128</v>
+        <v>20.12503008977441</v>
       </c>
       <c r="E479" t="n">
-        <v>20.57868909764986</v>
+        <v>20.57868717132721</v>
       </c>
       <c r="F479" t="n">
         <v>2807800</v>
@@ -10032,16 +10032,16 @@
         <v>44953</v>
       </c>
       <c r="B481" t="n">
-        <v>20.28912162780762</v>
+        <v>20.28911781311035</v>
       </c>
       <c r="C481" t="n">
-        <v>20.5111239391848</v>
+        <v>20.51112008274735</v>
       </c>
       <c r="D481" t="n">
-        <v>20.10572753356917</v>
+        <v>20.10572375335309</v>
       </c>
       <c r="E481" t="n">
-        <v>20.21190335250126</v>
+        <v>20.21189955232233</v>
       </c>
       <c r="F481" t="n">
         <v>6872200</v>
@@ -10052,16 +10052,16 @@
         <v>44956</v>
       </c>
       <c r="B482" t="n">
-        <v>20.05746650695801</v>
+        <v>20.05746459960938</v>
       </c>
       <c r="C482" t="n">
-        <v>20.5014711231836</v>
+        <v>20.50146917361271</v>
       </c>
       <c r="D482" t="n">
-        <v>19.85476738661628</v>
+        <v>19.85476549854316</v>
       </c>
       <c r="E482" t="n">
-        <v>20.35668708924173</v>
+        <v>20.35668515343896</v>
       </c>
       <c r="F482" t="n">
         <v>14094800</v>
@@ -10092,16 +10092,16 @@
         <v>44958</v>
       </c>
       <c r="B484" t="n">
-        <v>18.94745063781738</v>
+        <v>18.94744873046875</v>
       </c>
       <c r="C484" t="n">
-        <v>19.0922365078478</v>
+        <v>19.09223458592427</v>
       </c>
       <c r="D484" t="n">
-        <v>18.60962185048992</v>
+        <v>18.60961997714889</v>
       </c>
       <c r="E484" t="n">
-        <v>18.85092917916886</v>
+        <v>18.85092728153658</v>
       </c>
       <c r="F484" t="n">
         <v>17126000</v>
@@ -10112,16 +10112,16 @@
         <v>44959</v>
       </c>
       <c r="B485" t="n">
-        <v>18.84127426147461</v>
+        <v>18.84127616882324</v>
       </c>
       <c r="C485" t="n">
-        <v>19.19840803138294</v>
+        <v>19.19840997488511</v>
       </c>
       <c r="D485" t="n">
-        <v>18.55170439938368</v>
+        <v>18.55170627741844</v>
       </c>
       <c r="E485" t="n">
-        <v>18.60961947641901</v>
+        <v>18.60962136031666</v>
       </c>
       <c r="F485" t="n">
         <v>8708800</v>
@@ -10152,16 +10152,16 @@
         <v>44963</v>
       </c>
       <c r="B487" t="n">
-        <v>18.55170822143555</v>
+        <v>18.55170440673828</v>
       </c>
       <c r="C487" t="n">
-        <v>18.66753655834077</v>
+        <v>18.66753271982629</v>
       </c>
       <c r="D487" t="n">
-        <v>18.24283511106023</v>
+        <v>18.24283135987503</v>
       </c>
       <c r="E487" t="n">
-        <v>18.45518675521498</v>
+        <v>18.45518296036495</v>
       </c>
       <c r="F487" t="n">
         <v>7136600</v>
@@ -10192,16 +10192,16 @@
         <v>44965</v>
       </c>
       <c r="B489" t="n">
-        <v>18.10770225524902</v>
+        <v>18.10770034790039</v>
       </c>
       <c r="C489" t="n">
-        <v>18.39727031469558</v>
+        <v>18.39726837684571</v>
       </c>
       <c r="D489" t="n">
-        <v>17.76987162520883</v>
+        <v>17.76986975344509</v>
       </c>
       <c r="E489" t="n">
-        <v>18.29109634144721</v>
+        <v>18.29109441478103</v>
       </c>
       <c r="F489" t="n">
         <v>14424900</v>
@@ -10212,16 +10212,16 @@
         <v>44966</v>
       </c>
       <c r="B490" t="n">
-        <v>17.87604904174805</v>
+        <v>17.87604713439941</v>
       </c>
       <c r="C490" t="n">
-        <v>18.04979062940028</v>
+        <v>18.04978870351367</v>
       </c>
       <c r="D490" t="n">
-        <v>17.69265493911191</v>
+        <v>17.69265305133117</v>
       </c>
       <c r="E490" t="n">
-        <v>17.91465726065466</v>
+        <v>17.91465534918659</v>
       </c>
       <c r="F490" t="n">
         <v>11653900</v>
@@ -10232,16 +10232,16 @@
         <v>44967</v>
       </c>
       <c r="B491" t="n">
-        <v>17.98221778869629</v>
+        <v>17.98222160339355</v>
       </c>
       <c r="C491" t="n">
-        <v>18.0980460937488</v>
+        <v>18.09804993301756</v>
       </c>
       <c r="D491" t="n">
-        <v>17.62508404342224</v>
+        <v>17.62508778235816</v>
       </c>
       <c r="E491" t="n">
-        <v>17.79882558048678</v>
+        <v>17.79882935627974</v>
       </c>
       <c r="F491" t="n">
         <v>6326900</v>
@@ -10292,16 +10292,16 @@
         <v>44972</v>
       </c>
       <c r="B494" t="n">
-        <v>18.55170822143555</v>
+        <v>18.55170440673828</v>
       </c>
       <c r="C494" t="n">
-        <v>18.77371238041815</v>
+        <v>18.77370852007125</v>
       </c>
       <c r="D494" t="n">
-        <v>17.76022041584155</v>
+        <v>17.76021676389406</v>
       </c>
       <c r="E494" t="n">
-        <v>17.80848298998079</v>
+        <v>17.8084793281093</v>
       </c>
       <c r="F494" t="n">
         <v>12677500</v>
@@ -10312,16 +10312,16 @@
         <v>44973</v>
       </c>
       <c r="B495" t="n">
-        <v>18.3490104675293</v>
+        <v>18.34900856018066</v>
       </c>
       <c r="C495" t="n">
-        <v>18.55170775068378</v>
+        <v>18.5517058222651</v>
       </c>
       <c r="D495" t="n">
-        <v>17.88570081372285</v>
+        <v>17.88569895453448</v>
       </c>
       <c r="E495" t="n">
-        <v>18.43588125774662</v>
+        <v>18.43587934136792</v>
       </c>
       <c r="F495" t="n">
         <v>33990600</v>
@@ -10352,16 +10352,16 @@
         <v>44979</v>
       </c>
       <c r="B497" t="n">
-        <v>18.17526817321777</v>
+        <v>18.17527008056641</v>
       </c>
       <c r="C497" t="n">
-        <v>18.42622801942978</v>
+        <v>18.42622995311464</v>
       </c>
       <c r="D497" t="n">
-        <v>18.03048414221861</v>
+        <v>18.03048603437332</v>
       </c>
       <c r="E497" t="n">
-        <v>18.32970471842073</v>
+        <v>18.32970664197623</v>
       </c>
       <c r="F497" t="n">
         <v>5044700</v>
@@ -10412,16 +10412,16 @@
         <v>44984</v>
       </c>
       <c r="B500" t="n">
-        <v>17.75056457519531</v>
+        <v>17.75056648254395</v>
       </c>
       <c r="C500" t="n">
-        <v>18.25248420602797</v>
+        <v>18.2524861673093</v>
       </c>
       <c r="D500" t="n">
-        <v>17.67334631206941</v>
+        <v>17.67334821112072</v>
       </c>
       <c r="E500" t="n">
-        <v>18.09804767977617</v>
+        <v>18.09804962446285</v>
       </c>
       <c r="F500" t="n">
         <v>7297600</v>
@@ -10432,16 +10432,16 @@
         <v>44985</v>
       </c>
       <c r="B501" t="n">
-        <v>17.5092601776123</v>
+        <v>17.50925827026367</v>
       </c>
       <c r="C501" t="n">
-        <v>17.81813328135845</v>
+        <v>17.81813134036312</v>
       </c>
       <c r="D501" t="n">
-        <v>17.23899713234889</v>
+        <v>17.23899525444101</v>
       </c>
       <c r="E501" t="n">
-        <v>17.74091500542191</v>
+        <v>17.74091307283826</v>
       </c>
       <c r="F501" t="n">
         <v>18187200</v>
@@ -10452,16 +10452,16 @@
         <v>44986</v>
       </c>
       <c r="B502" t="n">
-        <v>17.02664566040039</v>
+        <v>17.02664184570312</v>
       </c>
       <c r="C502" t="n">
-        <v>17.77952523896634</v>
+        <v>17.77952125559183</v>
       </c>
       <c r="D502" t="n">
-        <v>16.67916433577905</v>
+        <v>16.67916059893248</v>
       </c>
       <c r="E502" t="n">
-        <v>17.50926035001291</v>
+        <v>17.5092564271893</v>
       </c>
       <c r="F502" t="n">
         <v>19714300</v>
@@ -10492,16 +10492,16 @@
         <v>44988</v>
       </c>
       <c r="B504" t="n">
-        <v>16.92046928405762</v>
+        <v>16.92047119140625</v>
       </c>
       <c r="C504" t="n">
-        <v>17.22934234709782</v>
+        <v>17.22934428926396</v>
       </c>
       <c r="D504" t="n">
-        <v>16.72742269914315</v>
+        <v>16.72742458473074</v>
       </c>
       <c r="E504" t="n">
-        <v>16.92046928405762</v>
+        <v>16.92047119140625</v>
       </c>
       <c r="F504" t="n">
         <v>8320600</v>
@@ -10552,16 +10552,16 @@
         <v>44993</v>
       </c>
       <c r="B507" t="n">
-        <v>17.41273498535156</v>
+        <v>17.41273880004883</v>
       </c>
       <c r="C507" t="n">
-        <v>17.50925642883505</v>
+        <v>17.50926026467776</v>
       </c>
       <c r="D507" t="n">
-        <v>16.77568204398369</v>
+        <v>16.7756857191185</v>
       </c>
       <c r="E507" t="n">
-        <v>17.09420759415336</v>
+        <v>17.0942113390692</v>
       </c>
       <c r="F507" t="n">
         <v>19181400</v>
@@ -10592,16 +10592,16 @@
         <v>44995</v>
       </c>
       <c r="B509" t="n">
-        <v>16.28341865539551</v>
+        <v>16.28341674804688</v>
       </c>
       <c r="C509" t="n">
-        <v>17.20038536068198</v>
+        <v>17.200383345925</v>
       </c>
       <c r="D509" t="n">
-        <v>16.10967709158599</v>
+        <v>16.10967520458848</v>
       </c>
       <c r="E509" t="n">
-        <v>17.11351457877723</v>
+        <v>17.1135125741958</v>
       </c>
       <c r="F509" t="n">
         <v>24597700</v>
@@ -10652,16 +10652,16 @@
         <v>45000</v>
       </c>
       <c r="B512" t="n">
-        <v>16.15793991088867</v>
+        <v>16.15793800354004</v>
       </c>
       <c r="C512" t="n">
-        <v>16.43785732016355</v>
+        <v>16.43785537977234</v>
       </c>
       <c r="D512" t="n">
-        <v>15.60775944827691</v>
+        <v>15.6077576058738</v>
       </c>
       <c r="E512" t="n">
-        <v>15.79115354949049</v>
+        <v>15.7911516854388</v>
       </c>
       <c r="F512" t="n">
         <v>24755700</v>
@@ -10672,16 +10672,16 @@
         <v>45001</v>
       </c>
       <c r="B513" t="n">
-        <v>15.68497562408447</v>
+        <v>15.68497467041016</v>
       </c>
       <c r="C513" t="n">
-        <v>16.33167930807249</v>
+        <v>16.33167831507744</v>
       </c>
       <c r="D513" t="n">
-        <v>15.64636556962371</v>
+        <v>15.64636461829695</v>
       </c>
       <c r="E513" t="n">
-        <v>16.03245875011646</v>
+        <v>16.03245777531455</v>
       </c>
       <c r="F513" t="n">
         <v>11501700</v>
@@ -10692,16 +10692,16 @@
         <v>45002</v>
       </c>
       <c r="B514" t="n">
-        <v>15.3664493560791</v>
+        <v>15.36645030975342</v>
       </c>
       <c r="C514" t="n">
-        <v>15.63671420220887</v>
+        <v>15.6367151726564</v>
       </c>
       <c r="D514" t="n">
-        <v>15.26992606524499</v>
+        <v>15.26992701292887</v>
       </c>
       <c r="E514" t="n">
-        <v>15.34714432970655</v>
+        <v>15.34714528218276</v>
       </c>
       <c r="F514" t="n">
         <v>38654600</v>
@@ -10712,16 +10712,16 @@
         <v>45005</v>
       </c>
       <c r="B515" t="n">
-        <v>15.49193000793457</v>
+        <v>15.49192905426025</v>
       </c>
       <c r="C515" t="n">
-        <v>15.59810582334904</v>
+        <v>15.5981048631386</v>
       </c>
       <c r="D515" t="n">
-        <v>15.31818935450853</v>
+        <v>15.31818841152959</v>
       </c>
       <c r="E515" t="n">
-        <v>15.44366927785282</v>
+        <v>15.4436683271494</v>
       </c>
       <c r="F515" t="n">
         <v>20828100</v>
@@ -10752,16 +10752,16 @@
         <v>45007</v>
       </c>
       <c r="B517" t="n">
-        <v>14.68113708496094</v>
+        <v>14.68113803863525</v>
       </c>
       <c r="C517" t="n">
-        <v>15.4919288903244</v>
+        <v>15.49192989666707</v>
       </c>
       <c r="D517" t="n">
-        <v>14.54600465714318</v>
+        <v>14.54600560203941</v>
       </c>
       <c r="E517" t="n">
-        <v>15.38575400308397</v>
+        <v>15.3857550025296</v>
       </c>
       <c r="F517" t="n">
         <v>42950800</v>
@@ -10772,16 +10772,16 @@
         <v>45008</v>
       </c>
       <c r="B518" t="n">
-        <v>14.71974754333496</v>
+        <v>14.71974658966064</v>
       </c>
       <c r="C518" t="n">
-        <v>15.01896904596353</v>
+        <v>15.01896807290302</v>
       </c>
       <c r="D518" t="n">
-        <v>14.256437898572</v>
+        <v>14.25643697491495</v>
       </c>
       <c r="E518" t="n">
-        <v>14.74870416600404</v>
+        <v>14.74870321045366</v>
       </c>
       <c r="F518" t="n">
         <v>25394300</v>
@@ -10792,16 +10792,16 @@
         <v>45009</v>
       </c>
       <c r="B519" t="n">
-        <v>14.43017768859863</v>
+        <v>14.43017673492432</v>
       </c>
       <c r="C519" t="n">
-        <v>14.95140146791577</v>
+        <v>14.95140047979436</v>
       </c>
       <c r="D519" t="n">
-        <v>14.01512972021653</v>
+        <v>14.01512879397227</v>
       </c>
       <c r="E519" t="n">
-        <v>14.74870328037497</v>
+        <v>14.74870230564966</v>
       </c>
       <c r="F519" t="n">
         <v>32819700</v>
@@ -10832,16 +10832,16 @@
         <v>45013</v>
       </c>
       <c r="B521" t="n">
-        <v>14.82592105865479</v>
+        <v>14.82592010498047</v>
       </c>
       <c r="C521" t="n">
-        <v>14.99001010601382</v>
+        <v>14.99000914178451</v>
       </c>
       <c r="D521" t="n">
-        <v>14.410873104024</v>
+        <v>14.41087217704756</v>
       </c>
       <c r="E521" t="n">
-        <v>14.57496215138304</v>
+        <v>14.5749612138516</v>
       </c>
       <c r="F521" t="n">
         <v>12984500</v>
@@ -10852,16 +10852,16 @@
         <v>45014</v>
       </c>
       <c r="B522" t="n">
-        <v>14.89348793029785</v>
+        <v>14.89348697662354</v>
       </c>
       <c r="C522" t="n">
-        <v>14.96105368463159</v>
+        <v>14.96105272663084</v>
       </c>
       <c r="D522" t="n">
-        <v>14.42052488841858</v>
+        <v>14.4205239650295</v>
       </c>
       <c r="E522" t="n">
-        <v>14.84522628269617</v>
+        <v>14.84522533211219</v>
       </c>
       <c r="F522" t="n">
         <v>19793200</v>
@@ -10872,16 +10872,16 @@
         <v>45015</v>
       </c>
       <c r="B523" t="n">
-        <v>15.41471195220947</v>
+        <v>15.41471099853516</v>
       </c>
       <c r="C523" t="n">
-        <v>15.73323662237289</v>
+        <v>15.73323564899215</v>
       </c>
       <c r="D523" t="n">
-        <v>14.82592149873313</v>
+        <v>14.82592058148598</v>
       </c>
       <c r="E523" t="n">
-        <v>15.15409960319252</v>
+        <v>15.15409866564172</v>
       </c>
       <c r="F523" t="n">
         <v>28286400</v>
@@ -10912,16 +10912,16 @@
         <v>45019</v>
       </c>
       <c r="B525" t="n">
-        <v>14.25643730163574</v>
+        <v>14.25643634796143</v>
       </c>
       <c r="C525" t="n">
-        <v>14.97070676766176</v>
+        <v>14.97070576620689</v>
       </c>
       <c r="D525" t="n">
-        <v>14.23713227365506</v>
+        <v>14.23713132127214</v>
       </c>
       <c r="E525" t="n">
-        <v>14.96105425367142</v>
+        <v>14.96105325286225</v>
       </c>
       <c r="F525" t="n">
         <v>17443100</v>
@@ -10972,16 +10972,16 @@
         <v>45022</v>
       </c>
       <c r="B528" t="n">
-        <v>13.1560754776001</v>
+        <v>13.15607452392578</v>
       </c>
       <c r="C528" t="n">
-        <v>13.57112437142145</v>
+        <v>13.57112338766055</v>
       </c>
       <c r="D528" t="n">
-        <v>13.00163893678686</v>
+        <v>13.00163799430754</v>
       </c>
       <c r="E528" t="n">
-        <v>13.33946863968721</v>
+        <v>13.33946767271886</v>
       </c>
       <c r="F528" t="n">
         <v>26117400</v>
@@ -11012,16 +11012,16 @@
         <v>45027</v>
       </c>
       <c r="B530" t="n">
-        <v>14.19852352142334</v>
+        <v>14.19852256774902</v>
       </c>
       <c r="C530" t="n">
-        <v>14.32400344514125</v>
+        <v>14.3240024830388</v>
       </c>
       <c r="D530" t="n">
-        <v>13.51321065835749</v>
+        <v>13.51320975071368</v>
       </c>
       <c r="E530" t="n">
-        <v>13.52286317260835</v>
+        <v>13.52286226431621</v>
       </c>
       <c r="F530" t="n">
         <v>23105700</v>
@@ -11052,16 +11052,16 @@
         <v>45029</v>
       </c>
       <c r="B532" t="n">
-        <v>13.2719030380249</v>
+        <v>13.27190208435059</v>
       </c>
       <c r="C532" t="n">
-        <v>14.14060905048986</v>
+        <v>14.14060803439325</v>
       </c>
       <c r="D532" t="n">
-        <v>13.2719030380249</v>
+        <v>13.27190208435059</v>
       </c>
       <c r="E532" t="n">
-        <v>14.09234832130857</v>
+        <v>14.09234730867981</v>
       </c>
       <c r="F532" t="n">
         <v>20136100</v>
@@ -11072,16 +11072,16 @@
         <v>45030</v>
       </c>
       <c r="B533" t="n">
-        <v>12.76033020019531</v>
+        <v>12.76033115386963</v>
       </c>
       <c r="C533" t="n">
-        <v>13.29120644090545</v>
+        <v>13.29120743425609</v>
       </c>
       <c r="D533" t="n">
-        <v>12.59624116360283</v>
+        <v>12.59624210501355</v>
       </c>
       <c r="E533" t="n">
-        <v>13.20433566617834</v>
+        <v>13.20433665303648</v>
       </c>
       <c r="F533" t="n">
         <v>26653800</v>
@@ -11112,16 +11112,16 @@
         <v>45034</v>
       </c>
       <c r="B535" t="n">
-        <v>12.70241641998291</v>
+        <v>12.70241737365723</v>
       </c>
       <c r="C535" t="n">
-        <v>12.95337623873985</v>
+        <v>12.95337721125578</v>
       </c>
       <c r="D535" t="n">
-        <v>12.61554564268133</v>
+        <v>12.61554658983354</v>
       </c>
       <c r="E535" t="n">
-        <v>12.87615797458607</v>
+        <v>12.87615894130459</v>
       </c>
       <c r="F535" t="n">
         <v>12417000</v>
@@ -11152,16 +11152,16 @@
         <v>45036</v>
       </c>
       <c r="B537" t="n">
-        <v>12.54798030853271</v>
+        <v>12.54798126220703</v>
       </c>
       <c r="C537" t="n">
-        <v>12.62519857525177</v>
+        <v>12.62519953479485</v>
       </c>
       <c r="D537" t="n">
-        <v>12.34528212826661</v>
+        <v>12.34528306653542</v>
       </c>
       <c r="E537" t="n">
-        <v>12.46110952834519</v>
+        <v>12.46111047541714</v>
       </c>
       <c r="F537" t="n">
         <v>12742300</v>
@@ -11172,16 +11172,16 @@
         <v>45040</v>
       </c>
       <c r="B538" t="n">
-        <v>12.45145797729492</v>
+        <v>12.45145702362061</v>
       </c>
       <c r="C538" t="n">
-        <v>12.88581191180532</v>
+        <v>12.88581092486324</v>
       </c>
       <c r="D538" t="n">
-        <v>12.35493559669272</v>
+        <v>12.35493465041118</v>
       </c>
       <c r="E538" t="n">
-        <v>12.54798127841155</v>
+        <v>12.54798031734438</v>
       </c>
       <c r="F538" t="n">
         <v>8287100</v>
@@ -11232,16 +11232,16 @@
         <v>45043</v>
       </c>
       <c r="B541" t="n">
-        <v>11.87231922149658</v>
+        <v>11.8723201751709</v>
       </c>
       <c r="C541" t="n">
-        <v>12.16188816260904</v>
+        <v>12.16188913954372</v>
       </c>
       <c r="D541" t="n">
-        <v>11.65996854194554</v>
+        <v>11.65996947856225</v>
       </c>
       <c r="E541" t="n">
-        <v>12.00745071897192</v>
+        <v>12.00745168350102</v>
       </c>
       <c r="F541" t="n">
         <v>19434000</v>
@@ -11392,16 +11392,16 @@
         <v>45056</v>
       </c>
       <c r="B549" t="n">
-        <v>11.33929538726807</v>
+        <v>11.33929443359375</v>
       </c>
       <c r="C549" t="n">
-        <v>11.50405445670229</v>
+        <v>11.50405348917116</v>
       </c>
       <c r="D549" t="n">
-        <v>11.24237888565992</v>
+        <v>11.24237794013662</v>
       </c>
       <c r="E549" t="n">
-        <v>11.29083667432746</v>
+        <v>11.29083572472869</v>
       </c>
       <c r="F549" t="n">
         <v>11154600</v>
@@ -11532,16 +11532,16 @@
         <v>45065</v>
       </c>
       <c r="B556" t="n">
-        <v>11.45559597015381</v>
+        <v>11.45559501647949</v>
       </c>
       <c r="C556" t="n">
-        <v>11.70758054300638</v>
+        <v>11.70757956835444</v>
       </c>
       <c r="D556" t="n">
-        <v>10.74810188976746</v>
+        <v>10.74810099499177</v>
       </c>
       <c r="E556" t="n">
-        <v>11.01946939361549</v>
+        <v>11.01946847624856</v>
       </c>
       <c r="F556" t="n">
         <v>25040300</v>
@@ -11552,16 +11552,16 @@
         <v>45068</v>
       </c>
       <c r="B557" t="n">
-        <v>11.63973808288574</v>
+        <v>11.63973712921143</v>
       </c>
       <c r="C557" t="n">
-        <v>11.89172263808976</v>
+        <v>11.89172166376968</v>
       </c>
       <c r="D557" t="n">
-        <v>11.36836967377079</v>
+        <v>11.3683687423304</v>
       </c>
       <c r="E557" t="n">
-        <v>11.48467094869036</v>
+        <v>11.4846700077211</v>
       </c>
       <c r="F557" t="n">
         <v>13575900</v>
@@ -11592,16 +11592,16 @@
         <v>45070</v>
       </c>
       <c r="B559" t="n">
-        <v>10.86440181732178</v>
+        <v>10.86440086364746</v>
       </c>
       <c r="C559" t="n">
-        <v>11.058235740948</v>
+        <v>11.05823477025899</v>
       </c>
       <c r="D559" t="n">
-        <v>10.68025982094513</v>
+        <v>10.68025888343475</v>
       </c>
       <c r="E559" t="n">
-        <v>11.02916088347233</v>
+        <v>11.02915991533551</v>
       </c>
       <c r="F559" t="n">
         <v>30388700</v>
@@ -11632,16 +11632,16 @@
         <v>45072</v>
       </c>
       <c r="B561" t="n">
-        <v>11.04854393005371</v>
+        <v>11.04854297637939</v>
       </c>
       <c r="C561" t="n">
-        <v>11.38775399317671</v>
+        <v>11.38775301022289</v>
       </c>
       <c r="D561" t="n">
-        <v>10.77717643411915</v>
+        <v>10.77717550386839</v>
       </c>
       <c r="E561" t="n">
-        <v>11.38775399317671</v>
+        <v>11.38775301022289</v>
       </c>
       <c r="F561" t="n">
         <v>33081400</v>
@@ -11692,16 +11692,16 @@
         <v>45077</v>
       </c>
       <c r="B564" t="n">
-        <v>10.41858291625977</v>
+        <v>10.41858196258545</v>
       </c>
       <c r="C564" t="n">
-        <v>10.89347624131492</v>
+        <v>10.89347524417082</v>
       </c>
       <c r="D564" t="n">
-        <v>10.36043227934935</v>
+        <v>10.3604313309979</v>
       </c>
       <c r="E564" t="n">
-        <v>10.89347624131492</v>
+        <v>10.89347524417082</v>
       </c>
       <c r="F564" t="n">
         <v>32506900</v>
@@ -11712,16 +11712,16 @@
         <v>45078</v>
       </c>
       <c r="B565" t="n">
-        <v>10.67056655883789</v>
+        <v>10.67056751251221</v>
       </c>
       <c r="C565" t="n">
-        <v>10.70933333871352</v>
+        <v>10.70933429585259</v>
       </c>
       <c r="D565" t="n">
-        <v>10.21505620209453</v>
+        <v>10.21505711505793</v>
       </c>
       <c r="E565" t="n">
-        <v>10.51549943933537</v>
+        <v>10.51550037915067</v>
       </c>
       <c r="F565" t="n">
         <v>22690400</v>
@@ -11752,16 +11752,16 @@
         <v>45082</v>
       </c>
       <c r="B567" t="n">
-        <v>10.81594276428223</v>
+        <v>10.81594181060791</v>
       </c>
       <c r="C567" t="n">
-        <v>11.23268638014201</v>
+        <v>11.23268538972215</v>
       </c>
       <c r="D567" t="n">
-        <v>10.68025948415897</v>
+        <v>10.68025854244826</v>
       </c>
       <c r="E567" t="n">
-        <v>11.12607703230456</v>
+        <v>11.12607605128477</v>
       </c>
       <c r="F567" t="n">
         <v>24462400</v>
@@ -11792,16 +11792,16 @@
         <v>45084</v>
       </c>
       <c r="B569" t="n">
-        <v>12.38599872589111</v>
+        <v>12.3859977722168</v>
       </c>
       <c r="C569" t="n">
-        <v>13.103185598031</v>
+        <v>13.10318458913605</v>
       </c>
       <c r="D569" t="n">
-        <v>12.09524739116122</v>
+        <v>12.09524645987364</v>
       </c>
       <c r="E569" t="n">
-        <v>12.42476550890357</v>
+        <v>12.42476455224435</v>
       </c>
       <c r="F569" t="n">
         <v>35775900</v>
@@ -11832,16 +11832,16 @@
         <v>45089</v>
       </c>
       <c r="B571" t="n">
-        <v>13.29701995849609</v>
+        <v>13.29701900482178</v>
       </c>
       <c r="C571" t="n">
-        <v>13.5296206643621</v>
+        <v>13.52961969400545</v>
       </c>
       <c r="D571" t="n">
-        <v>12.72520919670404</v>
+        <v>12.72520828404051</v>
       </c>
       <c r="E571" t="n">
-        <v>12.80274276532604</v>
+        <v>12.80274184710173</v>
       </c>
       <c r="F571" t="n">
         <v>31653900</v>
@@ -11912,16 +11912,16 @@
         <v>45093</v>
       </c>
       <c r="B575" t="n">
-        <v>13.0934944152832</v>
+        <v>13.09349346160889</v>
       </c>
       <c r="C575" t="n">
-        <v>13.60715455045659</v>
+        <v>13.60715355936946</v>
       </c>
       <c r="D575" t="n">
-        <v>12.93842727442128</v>
+        <v>12.93842633204139</v>
       </c>
       <c r="E575" t="n">
-        <v>13.60715455045659</v>
+        <v>13.60715355936946</v>
       </c>
       <c r="F575" t="n">
         <v>29424500</v>
@@ -11952,16 +11952,16 @@
         <v>45097</v>
       </c>
       <c r="B577" t="n">
-        <v>12.91904258728027</v>
+        <v>12.91904163360596</v>
       </c>
       <c r="C577" t="n">
-        <v>13.00626807946328</v>
+        <v>13.00626711935004</v>
       </c>
       <c r="D577" t="n">
-        <v>12.60890832553893</v>
+        <v>12.6089073947585</v>
       </c>
       <c r="E577" t="n">
-        <v>12.77366738315727</v>
+        <v>12.77366644021444</v>
       </c>
       <c r="F577" t="n">
         <v>13900100</v>
@@ -11972,16 +11972,16 @@
         <v>45098</v>
       </c>
       <c r="B578" t="n">
-        <v>12.98688411712646</v>
+        <v>12.98688507080078</v>
       </c>
       <c r="C578" t="n">
-        <v>13.03534282618567</v>
+        <v>13.03534378341849</v>
       </c>
       <c r="D578" t="n">
-        <v>12.70582471371064</v>
+        <v>12.70582564674574</v>
       </c>
       <c r="E578" t="n">
-        <v>12.99657604379291</v>
+        <v>12.99657699817894</v>
       </c>
       <c r="F578" t="n">
         <v>18033300</v>
@@ -12032,16 +12032,16 @@
         <v>45103</v>
       </c>
       <c r="B581" t="n">
-        <v>13.47146892547607</v>
+        <v>13.47146987915039</v>
       </c>
       <c r="C581" t="n">
-        <v>14.14019705556374</v>
+        <v>14.14019805657877</v>
       </c>
       <c r="D581" t="n">
-        <v>13.35516858204191</v>
+        <v>13.35516952748307</v>
       </c>
       <c r="E581" t="n">
-        <v>13.85913766119627</v>
+        <v>13.85913864231449</v>
       </c>
       <c r="F581" t="n">
         <v>23023000</v>
@@ -12052,16 +12052,16 @@
         <v>45104</v>
       </c>
       <c r="B582" t="n">
-        <v>12.68644237518311</v>
+        <v>12.68644142150879</v>
       </c>
       <c r="C582" t="n">
-        <v>13.85913875249263</v>
+        <v>13.85913771066354</v>
       </c>
       <c r="D582" t="n">
-        <v>12.56045009547363</v>
+        <v>12.5604491512705</v>
       </c>
       <c r="E582" t="n">
-        <v>13.77191325698045</v>
+        <v>13.77191222170834</v>
       </c>
       <c r="F582" t="n">
         <v>64278500</v>
@@ -12112,16 +12112,16 @@
         <v>45107</v>
       </c>
       <c r="B585" t="n">
-        <v>13.32609462738037</v>
+        <v>13.32609367370605</v>
       </c>
       <c r="C585" t="n">
-        <v>13.48116176243347</v>
+        <v>13.48116079766187</v>
       </c>
       <c r="D585" t="n">
-        <v>12.96750164650181</v>
+        <v>12.96750071848999</v>
       </c>
       <c r="E585" t="n">
-        <v>13.08380199779164</v>
+        <v>13.08380106145685</v>
       </c>
       <c r="F585" t="n">
         <v>19641600</v>
@@ -12172,16 +12172,16 @@
         <v>45112</v>
       </c>
       <c r="B588" t="n">
-        <v>13.29701995849609</v>
+        <v>13.29701900482178</v>
       </c>
       <c r="C588" t="n">
-        <v>13.59746230583809</v>
+        <v>13.59746133061578</v>
       </c>
       <c r="D588" t="n">
-        <v>13.14195282125209</v>
+        <v>13.14195187869933</v>
       </c>
       <c r="E588" t="n">
-        <v>13.17102767841708</v>
+        <v>13.17102673377904</v>
       </c>
       <c r="F588" t="n">
         <v>9442900</v>
@@ -12192,16 +12192,16 @@
         <v>45113</v>
       </c>
       <c r="B589" t="n">
-        <v>13.1710262298584</v>
+        <v>13.17102718353271</v>
       </c>
       <c r="C589" t="n">
-        <v>13.32609335004801</v>
+        <v>13.32609431495027</v>
       </c>
       <c r="D589" t="n">
-        <v>13.03534203755601</v>
+        <v>13.03534298140585</v>
       </c>
       <c r="E589" t="n">
-        <v>13.22917593779303</v>
+        <v>13.22917689567779</v>
       </c>
       <c r="F589" t="n">
         <v>10770700</v>
@@ -12232,16 +12232,16 @@
         <v>45117</v>
       </c>
       <c r="B591" t="n">
-        <v>13.28732681274414</v>
+        <v>13.28732776641846</v>
       </c>
       <c r="C591" t="n">
-        <v>13.70407039907184</v>
+        <v>13.70407138265719</v>
       </c>
       <c r="D591" t="n">
-        <v>13.21948517749003</v>
+        <v>13.21948612629514</v>
       </c>
       <c r="E591" t="n">
-        <v>13.55869427803353</v>
+        <v>13.55869525118476</v>
       </c>
       <c r="F591" t="n">
         <v>9043800</v>
@@ -12332,16 +12332,16 @@
         <v>45124</v>
       </c>
       <c r="B596" t="n">
-        <v>12.42476463317871</v>
+        <v>12.42476558685303</v>
       </c>
       <c r="C596" t="n">
-        <v>12.44414848545523</v>
+        <v>12.44414944061737</v>
       </c>
       <c r="D596" t="n">
-        <v>11.97894619782127</v>
+        <v>11.97894711727638</v>
       </c>
       <c r="E596" t="n">
-        <v>12.11463039093804</v>
+        <v>12.11463132080772</v>
       </c>
       <c r="F596" t="n">
         <v>11160300</v>
@@ -12372,16 +12372,16 @@
         <v>45126</v>
       </c>
       <c r="B598" t="n">
-        <v>11.7657299041748</v>
+        <v>11.76573085784912</v>
       </c>
       <c r="C598" t="n">
-        <v>12.20185643325319</v>
+        <v>12.20185742227786</v>
       </c>
       <c r="D598" t="n">
-        <v>11.71727119554988</v>
+        <v>11.71727214529636</v>
       </c>
       <c r="E598" t="n">
-        <v>12.08555608711715</v>
+        <v>12.08555706671507</v>
       </c>
       <c r="F598" t="n">
         <v>18624600</v>
@@ -12432,16 +12432,16 @@
         <v>45131</v>
       </c>
       <c r="B601" t="n">
-        <v>12.38599872589111</v>
+        <v>12.3859977722168</v>
       </c>
       <c r="C601" t="n">
-        <v>12.54106585794092</v>
+        <v>12.54106489232703</v>
       </c>
       <c r="D601" t="n">
-        <v>12.03709767877904</v>
+        <v>12.03709675196877</v>
       </c>
       <c r="E601" t="n">
-        <v>12.19216481082885</v>
+        <v>12.192163872079</v>
       </c>
       <c r="F601" t="n">
         <v>10834500</v>
@@ -12472,16 +12472,16 @@
         <v>45133</v>
       </c>
       <c r="B603" t="n">
-        <v>12.47322368621826</v>
+        <v>12.47322463989258</v>
       </c>
       <c r="C603" t="n">
-        <v>12.75428308212753</v>
+        <v>12.75428405729101</v>
       </c>
       <c r="D603" t="n">
-        <v>12.19216429030899</v>
+        <v>12.19216522249415</v>
       </c>
       <c r="E603" t="n">
-        <v>12.52168239398323</v>
+        <v>12.52168335136259</v>
       </c>
       <c r="F603" t="n">
         <v>40141600</v>
@@ -12532,16 +12532,16 @@
         <v>45138</v>
       </c>
       <c r="B606" t="n">
-        <v>13.05472660064697</v>
+        <v>13.05472755432129</v>
       </c>
       <c r="C606" t="n">
-        <v>13.18071887373052</v>
+        <v>13.18071983660883</v>
       </c>
       <c r="D606" t="n">
-        <v>12.72520849016276</v>
+        <v>12.72520941976511</v>
       </c>
       <c r="E606" t="n">
-        <v>12.89965947201275</v>
+        <v>12.8996604143591</v>
       </c>
       <c r="F606" t="n">
         <v>32856600</v>
@@ -12632,16 +12632,16 @@
         <v>45145</v>
       </c>
       <c r="B611" t="n">
-        <v>13.44239521026611</v>
+        <v>13.4423942565918</v>
       </c>
       <c r="C611" t="n">
-        <v>13.85913883610609</v>
+        <v>13.85913785286578</v>
       </c>
       <c r="D611" t="n">
-        <v>13.38424549575587</v>
+        <v>13.384244546207</v>
       </c>
       <c r="E611" t="n">
-        <v>13.58777134508783</v>
+        <v>13.58777038109976</v>
       </c>
       <c r="F611" t="n">
         <v>31957200</v>
@@ -12792,16 +12792,16 @@
         <v>45155</v>
       </c>
       <c r="B619" t="n">
-        <v>12.60890769958496</v>
+        <v>12.60890865325928</v>
       </c>
       <c r="C619" t="n">
-        <v>12.81243352981718</v>
+        <v>12.81243449888516</v>
       </c>
       <c r="D619" t="n">
-        <v>12.45384057641241</v>
+        <v>12.45384151835823</v>
       </c>
       <c r="E619" t="n">
-        <v>12.67674933490471</v>
+        <v>12.67675029371023</v>
       </c>
       <c r="F619" t="n">
         <v>17965700</v>
@@ -12832,16 +12832,16 @@
         <v>45159</v>
       </c>
       <c r="B621" t="n">
-        <v>12.68644237518311</v>
+        <v>12.68644142150879</v>
       </c>
       <c r="C621" t="n">
-        <v>13.07411021715607</v>
+        <v>13.07410923433971</v>
       </c>
       <c r="D621" t="n">
-        <v>12.68644237518311</v>
+        <v>12.68644142150879</v>
       </c>
       <c r="E621" t="n">
-        <v>13.03534343295877</v>
+        <v>13.03534245305662</v>
       </c>
       <c r="F621" t="n">
         <v>19861900</v>
@@ -12852,16 +12852,16 @@
         <v>45160</v>
       </c>
       <c r="B622" t="n">
-        <v>12.57014179229736</v>
+        <v>12.57014083862305</v>
       </c>
       <c r="C622" t="n">
-        <v>12.86089313058684</v>
+        <v>12.86089215485373</v>
       </c>
       <c r="D622" t="n">
-        <v>12.40538273140909</v>
+        <v>12.40538179023475</v>
       </c>
       <c r="E622" t="n">
-        <v>12.84150927670679</v>
+        <v>12.84150830244431</v>
       </c>
       <c r="F622" t="n">
         <v>10646800</v>
@@ -12912,16 +12912,16 @@
         <v>45163</v>
       </c>
       <c r="B625" t="n">
-        <v>11.98863887786865</v>
+        <v>11.98863792419434</v>
       </c>
       <c r="C625" t="n">
-        <v>12.50229897994967</v>
+        <v>12.50229798541463</v>
       </c>
       <c r="D625" t="n">
-        <v>11.94018016840297</v>
+        <v>11.94017921858345</v>
       </c>
       <c r="E625" t="n">
-        <v>12.40538248529131</v>
+        <v>12.4053814984658</v>
       </c>
       <c r="F625" t="n">
         <v>23324500</v>
@@ -13032,16 +13032,16 @@
         <v>45173</v>
       </c>
       <c r="B631" t="n">
-        <v>11.87233924865723</v>
+        <v>11.87233829498291</v>
       </c>
       <c r="C631" t="n">
-        <v>11.96925667345753</v>
+        <v>11.96925571199809</v>
       </c>
       <c r="D631" t="n">
-        <v>11.48467139800213</v>
+        <v>11.48467047546817</v>
       </c>
       <c r="E631" t="n">
-        <v>11.49436240106371</v>
+        <v>11.4943614777513</v>
       </c>
       <c r="F631" t="n">
         <v>7669300</v>
@@ -13112,16 +13112,16 @@
         <v>45180</v>
       </c>
       <c r="B635" t="n">
-        <v>11.84326457977295</v>
+        <v>11.84326362609863</v>
       </c>
       <c r="C635" t="n">
-        <v>11.99833172250761</v>
+        <v>11.99833075634657</v>
       </c>
       <c r="D635" t="n">
-        <v>11.6978884402544</v>
+        <v>11.69788749828644</v>
       </c>
       <c r="E635" t="n">
-        <v>11.87233943796743</v>
+        <v>11.87233848195187</v>
       </c>
       <c r="F635" t="n">
         <v>12088600</v>
@@ -13132,16 +13132,16 @@
         <v>45181</v>
       </c>
       <c r="B636" t="n">
-        <v>12.47322368621826</v>
+        <v>12.47322463989258</v>
       </c>
       <c r="C636" t="n">
-        <v>12.5701411017482</v>
+        <v>12.57014206283261</v>
       </c>
       <c r="D636" t="n">
-        <v>11.85295426022717</v>
+        <v>11.85295516647709</v>
       </c>
       <c r="E636" t="n">
-        <v>11.85295426022717</v>
+        <v>11.85295516647709</v>
       </c>
       <c r="F636" t="n">
         <v>14965900</v>
@@ -13212,16 +13212,16 @@
         <v>45187</v>
       </c>
       <c r="B640" t="n">
-        <v>11.88203048706055</v>
+        <v>11.88203144073486</v>
       </c>
       <c r="C640" t="n">
-        <v>12.11463118396719</v>
+        <v>12.11463215631048</v>
       </c>
       <c r="D640" t="n">
-        <v>11.82387985069738</v>
+        <v>11.82388079970442</v>
       </c>
       <c r="E640" t="n">
-        <v>12.00802276228657</v>
+        <v>12.00802372607326</v>
       </c>
       <c r="F640" t="n">
         <v>10083800</v>
@@ -13252,16 +13252,16 @@
         <v>45189</v>
       </c>
       <c r="B642" t="n">
-        <v>11.7657299041748</v>
+        <v>11.76573085784912</v>
       </c>
       <c r="C642" t="n">
-        <v>11.85295447057209</v>
+        <v>11.85295543131642</v>
       </c>
       <c r="D642" t="n">
-        <v>11.45559472353905</v>
+        <v>11.45559565207528</v>
       </c>
       <c r="E642" t="n">
-        <v>11.72696312212946</v>
+        <v>11.72696407266152</v>
       </c>
       <c r="F642" t="n">
         <v>16179800</v>
@@ -13592,16 +13592,16 @@
         <v>45215</v>
       </c>
       <c r="B659" t="n">
-        <v>11.40713787078857</v>
+        <v>11.40713691711426</v>
       </c>
       <c r="C659" t="n">
-        <v>11.5331292295207</v>
+        <v>11.5331282653131</v>
       </c>
       <c r="D659" t="n">
-        <v>11.14546137740708</v>
+        <v>11.14546044560978</v>
       </c>
       <c r="E659" t="n">
-        <v>11.3586791582061</v>
+        <v>11.3586782085831</v>
       </c>
       <c r="F659" t="n">
         <v>7162600</v>
@@ -13632,16 +13632,16 @@
         <v>45217</v>
       </c>
       <c r="B661" t="n">
-        <v>10.48642444610596</v>
+        <v>10.48642539978027</v>
       </c>
       <c r="C661" t="n">
-        <v>11.16484453111691</v>
+        <v>11.16484554648926</v>
       </c>
       <c r="D661" t="n">
-        <v>10.44765766332873</v>
+        <v>10.44765861347745</v>
       </c>
       <c r="E661" t="n">
-        <v>11.16484453111691</v>
+        <v>11.16484554648926</v>
       </c>
       <c r="F661" t="n">
         <v>15312800</v>
@@ -13652,16 +13652,16 @@
         <v>45218</v>
       </c>
       <c r="B662" t="n">
-        <v>10.65118408203125</v>
+        <v>10.65118312835693</v>
       </c>
       <c r="C662" t="n">
-        <v>10.9128605731838</v>
+        <v>10.91285959607978</v>
       </c>
       <c r="D662" t="n">
-        <v>10.38950851515176</v>
+        <v>10.38950758490707</v>
       </c>
       <c r="E662" t="n">
-        <v>10.41858337274435</v>
+        <v>10.41858243989639</v>
       </c>
       <c r="F662" t="n">
         <v>8209500</v>
@@ -13672,16 +13672,16 @@
         <v>45219</v>
       </c>
       <c r="B663" t="n">
-        <v>10.73840808868408</v>
+        <v>10.7384090423584</v>
       </c>
       <c r="C663" t="n">
-        <v>10.74810001462748</v>
+        <v>10.74810096916253</v>
       </c>
       <c r="D663" t="n">
-        <v>10.5445741911808</v>
+        <v>10.5445751276408</v>
       </c>
       <c r="E663" t="n">
-        <v>10.58334097068145</v>
+        <v>10.58334191058432</v>
       </c>
       <c r="F663" t="n">
         <v>9727700</v>
@@ -13752,16 +13752,16 @@
         <v>45225</v>
       </c>
       <c r="B667" t="n">
-        <v>11.33929538726807</v>
+        <v>11.33929443359375</v>
       </c>
       <c r="C667" t="n">
-        <v>11.5718961002553</v>
+        <v>11.57189512701845</v>
       </c>
       <c r="D667" t="n">
-        <v>10.75779360479998</v>
+        <v>10.75779270003199</v>
       </c>
       <c r="E667" t="n">
-        <v>10.76748460796964</v>
+        <v>10.76748370238661</v>
       </c>
       <c r="F667" t="n">
         <v>21852600</v>
@@ -13772,16 +13772,16 @@
         <v>45226</v>
       </c>
       <c r="B668" t="n">
-        <v>10.78686714172363</v>
+        <v>10.78686809539795</v>
       </c>
       <c r="C668" t="n">
-        <v>11.45559434072722</v>
+        <v>11.45559535352417</v>
       </c>
       <c r="D668" t="n">
-        <v>10.74810036097376</v>
+        <v>10.74810131122068</v>
       </c>
       <c r="E668" t="n">
-        <v>11.3392939984776</v>
+        <v>11.33929500099235</v>
       </c>
       <c r="F668" t="n">
         <v>13292000</v>
@@ -13812,16 +13812,16 @@
         <v>45230</v>
       </c>
       <c r="B670" t="n">
-        <v>10.6027250289917</v>
+        <v>10.60272598266602</v>
       </c>
       <c r="C670" t="n">
-        <v>11.13576899717533</v>
+        <v>11.1357699987949</v>
       </c>
       <c r="D670" t="n">
-        <v>10.52519146172205</v>
+        <v>10.52519240842252</v>
       </c>
       <c r="E670" t="n">
-        <v>10.77717601748493</v>
+        <v>10.77717698685044</v>
       </c>
       <c r="F670" t="n">
         <v>15178600</v>
@@ -13832,16 +13832,16 @@
         <v>45231</v>
       </c>
       <c r="B671" t="n">
-        <v>10.73840808868408</v>
+        <v>10.7384090423584</v>
       </c>
       <c r="C671" t="n">
-        <v>10.84501650124265</v>
+        <v>10.84501746438483</v>
       </c>
       <c r="D671" t="n">
-        <v>10.35074029367752</v>
+        <v>10.35074121292319</v>
       </c>
       <c r="E671" t="n">
-        <v>10.66087452968277</v>
+        <v>10.66087547647136</v>
       </c>
       <c r="F671" t="n">
         <v>19375400</v>
@@ -13852,16 +13852,16 @@
         <v>45233</v>
       </c>
       <c r="B672" t="n">
-        <v>11.57189559936523</v>
+        <v>11.57189464569092</v>
       </c>
       <c r="C672" t="n">
-        <v>11.61066238318509</v>
+        <v>11.61066142631588</v>
       </c>
       <c r="D672" t="n">
-        <v>11.24237839903302</v>
+        <v>11.2423774725152</v>
       </c>
       <c r="E672" t="n">
-        <v>11.25206940178321</v>
+        <v>11.25206847446672</v>
       </c>
       <c r="F672" t="n">
         <v>16636800</v>
@@ -14012,16 +14012,16 @@
         <v>45246</v>
       </c>
       <c r="B680" t="n">
-        <v>12.92873382568359</v>
+        <v>12.92873477935791</v>
       </c>
       <c r="C680" t="n">
-        <v>13.1322596551836</v>
+        <v>13.13226062387078</v>
       </c>
       <c r="D680" t="n">
-        <v>12.16308921456891</v>
+        <v>12.16309011176626</v>
       </c>
       <c r="E680" t="n">
-        <v>12.40538182472258</v>
+        <v>12.40538273979239</v>
       </c>
       <c r="F680" t="n">
         <v>22426900</v>
@@ -14072,16 +14072,16 @@
         <v>45251</v>
       </c>
       <c r="B683" t="n">
-        <v>12.38599872589111</v>
+        <v>12.3859977722168</v>
       </c>
       <c r="C683" t="n">
-        <v>12.48291614555875</v>
+        <v>12.48291518442216</v>
       </c>
       <c r="D683" t="n">
-        <v>12.22123966701994</v>
+        <v>12.22123872603144</v>
       </c>
       <c r="E683" t="n">
-        <v>12.4441493625463</v>
+        <v>12.44414840439461</v>
       </c>
       <c r="F683" t="n">
         <v>9484000</v>
@@ -14092,16 +14092,16 @@
         <v>45252</v>
       </c>
       <c r="B684" t="n">
-        <v>12.57014179229736</v>
+        <v>12.57014083862305</v>
       </c>
       <c r="C684" t="n">
-        <v>12.72520892624561</v>
+        <v>12.72520796080663</v>
       </c>
       <c r="D684" t="n">
-        <v>12.39569080446907</v>
+        <v>12.39568986403004</v>
       </c>
       <c r="E684" t="n">
-        <v>12.48291629838322</v>
+        <v>12.48291535132654</v>
       </c>
       <c r="F684" t="n">
         <v>10478000</v>
@@ -14112,16 +14112,16 @@
         <v>45253</v>
       </c>
       <c r="B685" t="n">
-        <v>13.18071937561035</v>
+        <v>13.18071842193604</v>
       </c>
       <c r="C685" t="n">
-        <v>13.29701972651436</v>
+        <v>13.29701876442528</v>
       </c>
       <c r="D685" t="n">
-        <v>12.62829155347501</v>
+        <v>12.62829063977091</v>
       </c>
       <c r="E685" t="n">
-        <v>12.63798348045194</v>
+        <v>12.63798256604659</v>
       </c>
       <c r="F685" t="n">
         <v>8829200</v>
@@ -14172,16 +14172,16 @@
         <v>45258</v>
       </c>
       <c r="B688" t="n">
-        <v>13.10318565368652</v>
+        <v>13.10318660736084</v>
       </c>
       <c r="C688" t="n">
-        <v>13.48116155859512</v>
+        <v>13.48116253977923</v>
       </c>
       <c r="D688" t="n">
-        <v>12.98688437988217</v>
+        <v>12.98688532509186</v>
       </c>
       <c r="E688" t="n">
-        <v>13.14195243686364</v>
+        <v>13.14195339335947</v>
       </c>
       <c r="F688" t="n">
         <v>17069200</v>
@@ -14272,16 +14272,16 @@
         <v>45265</v>
       </c>
       <c r="B693" t="n">
-        <v>12.30846500396729</v>
+        <v>12.3084659576416</v>
       </c>
       <c r="C693" t="n">
-        <v>12.65736697093318</v>
+        <v>12.65736795164083</v>
       </c>
       <c r="D693" t="n">
-        <v>12.23093143892442</v>
+        <v>12.23093238659134</v>
       </c>
       <c r="E693" t="n">
-        <v>12.33753985979011</v>
+        <v>12.33754081571718</v>
       </c>
       <c r="F693" t="n">
         <v>12428700</v>
@@ -14292,16 +14292,16 @@
         <v>45266</v>
       </c>
       <c r="B694" t="n">
-        <v>11.87233924865723</v>
+        <v>11.87233829498291</v>
       </c>
       <c r="C694" t="n">
-        <v>12.62829201957119</v>
+        <v>12.62829100517314</v>
       </c>
       <c r="D694" t="n">
-        <v>11.84326439092636</v>
+        <v>11.84326343958755</v>
       </c>
       <c r="E694" t="n">
-        <v>12.43445809424364</v>
+        <v>12.43445709541577</v>
       </c>
       <c r="F694" t="n">
         <v>16842800</v>
@@ -14332,16 +14332,16 @@
         <v>45268</v>
       </c>
       <c r="B696" t="n">
-        <v>11.61066246032715</v>
+        <v>11.61066150665283</v>
       </c>
       <c r="C696" t="n">
-        <v>11.96925636838458</v>
+        <v>11.96925538525615</v>
       </c>
       <c r="D696" t="n">
-        <v>11.58158760333734</v>
+        <v>11.58158665205117</v>
       </c>
       <c r="E696" t="n">
-        <v>11.85295509187928</v>
+        <v>11.85295411830358</v>
       </c>
       <c r="F696" t="n">
         <v>16929900</v>
@@ -14352,16 +14352,16 @@
         <v>45271</v>
       </c>
       <c r="B697" t="n">
-        <v>11.54282093048096</v>
+        <v>11.54281997680664</v>
       </c>
       <c r="C697" t="n">
-        <v>11.64943028092588</v>
+        <v>11.64942931844344</v>
       </c>
       <c r="D697" t="n">
-        <v>11.40713764703913</v>
+        <v>11.40713670457504</v>
       </c>
       <c r="E697" t="n">
-        <v>11.63004642656387</v>
+        <v>11.63004546568294</v>
       </c>
       <c r="F697" t="n">
         <v>10547700</v>
@@ -14392,16 +14392,16 @@
         <v>45273</v>
       </c>
       <c r="B699" t="n">
-        <v>12.54106521606445</v>
+        <v>12.54106616973877</v>
       </c>
       <c r="C699" t="n">
-        <v>12.59921584974338</v>
+        <v>12.5992168078397</v>
       </c>
       <c r="D699" t="n">
-        <v>11.55251183770653</v>
+        <v>11.55251271620717</v>
       </c>
       <c r="E699" t="n">
-        <v>11.6203534734378</v>
+        <v>11.6203543570974</v>
       </c>
       <c r="F699" t="n">
         <v>24349900</v>
@@ -14432,16 +14432,16 @@
         <v>45275</v>
       </c>
       <c r="B701" t="n">
-        <v>12.47322368621826</v>
+        <v>12.47322463989258</v>
       </c>
       <c r="C701" t="n">
-        <v>12.93842598677983</v>
+        <v>12.93842697602245</v>
       </c>
       <c r="D701" t="n">
-        <v>12.26969785302376</v>
+        <v>12.26969879113695</v>
       </c>
       <c r="E701" t="n">
-        <v>12.93842598677983</v>
+        <v>12.93842697602245</v>
       </c>
       <c r="F701" t="n">
         <v>13438600</v>
@@ -14452,16 +14452,16 @@
         <v>45278</v>
       </c>
       <c r="B702" t="n">
-        <v>12.80274200439453</v>
+        <v>12.80274105072021</v>
       </c>
       <c r="C702" t="n">
-        <v>12.97719298556206</v>
+        <v>12.97719201889291</v>
       </c>
       <c r="D702" t="n">
-        <v>12.34723162260876</v>
+        <v>12.34723070286534</v>
       </c>
       <c r="E702" t="n">
-        <v>12.55075745921321</v>
+        <v>12.55075652430919</v>
       </c>
       <c r="F702" t="n">
         <v>9094600</v>
@@ -14472,16 +14472,16 @@
         <v>45279</v>
       </c>
       <c r="B703" t="n">
-        <v>12.98688411712646</v>
+        <v>12.98688507080078</v>
       </c>
       <c r="C703" t="n">
-        <v>13.05472667951856</v>
+        <v>13.0547276381748</v>
       </c>
       <c r="D703" t="n">
-        <v>12.87058376994816</v>
+        <v>12.87058471508212</v>
       </c>
       <c r="E703" t="n">
-        <v>12.98688411712646</v>
+        <v>12.98688507080078</v>
       </c>
       <c r="F703" t="n">
         <v>5248800</v>
@@ -14612,16 +14612,16 @@
         <v>45293</v>
       </c>
       <c r="B710" t="n">
-        <v>12.61860084533691</v>
+        <v>12.6185998916626</v>
       </c>
       <c r="C710" t="n">
-        <v>13.03534354806971</v>
+        <v>13.03534256289929</v>
       </c>
       <c r="D710" t="n">
-        <v>12.50229956744496</v>
+        <v>12.50229862256033</v>
       </c>
       <c r="E710" t="n">
-        <v>13.03534354806971</v>
+        <v>13.03534256289929</v>
       </c>
       <c r="F710" t="n">
         <v>7348700</v>
@@ -14632,16 +14632,16 @@
         <v>45294</v>
       </c>
       <c r="B711" t="n">
-        <v>12.54106521606445</v>
+        <v>12.54106616973877</v>
       </c>
       <c r="C711" t="n">
-        <v>12.71551619282825</v>
+        <v>12.71551715976854</v>
       </c>
       <c r="D711" t="n">
-        <v>12.31815645622002</v>
+        <v>12.31815739294343</v>
       </c>
       <c r="E711" t="n">
-        <v>12.62829070444635</v>
+        <v>12.62829166475365</v>
       </c>
       <c r="F711" t="n">
         <v>6830500</v>
@@ -14652,16 +14652,16 @@
         <v>45295</v>
       </c>
       <c r="B712" t="n">
-        <v>12.80274200439453</v>
+        <v>12.80274105072021</v>
       </c>
       <c r="C712" t="n">
-        <v>12.91904235041522</v>
+        <v>12.91904138807771</v>
       </c>
       <c r="D712" t="n">
-        <v>12.44414903976249</v>
+        <v>12.44414811279971</v>
       </c>
       <c r="E712" t="n">
-        <v>12.50229875063634</v>
+        <v>12.502297819342</v>
       </c>
       <c r="F712" t="n">
         <v>8604100</v>
@@ -14752,16 +14752,16 @@
         <v>45302</v>
       </c>
       <c r="B717" t="n">
-        <v>13.44239521026611</v>
+        <v>13.4423942565918</v>
       </c>
       <c r="C717" t="n">
-        <v>13.71376270128438</v>
+        <v>13.71376172835782</v>
       </c>
       <c r="D717" t="n">
-        <v>13.20979450367903</v>
+        <v>13.20979356650663</v>
       </c>
       <c r="E717" t="n">
-        <v>13.20979450367903</v>
+        <v>13.20979356650663</v>
       </c>
       <c r="F717" t="n">
         <v>14967000</v>
@@ -14812,16 +14812,16 @@
         <v>45307</v>
       </c>
       <c r="B720" t="n">
-        <v>14.03358745574951</v>
+        <v>14.03358840942383</v>
       </c>
       <c r="C720" t="n">
-        <v>14.30495584303765</v>
+        <v>14.30495681515323</v>
       </c>
       <c r="D720" t="n">
-        <v>13.93667096680914</v>
+        <v>13.93667191389734</v>
       </c>
       <c r="E720" t="n">
-        <v>14.30495584303765</v>
+        <v>14.30495681515323</v>
       </c>
       <c r="F720" t="n">
         <v>11210600</v>
@@ -14852,16 +14852,16 @@
         <v>45309</v>
       </c>
       <c r="B722" t="n">
-        <v>13.36486148834229</v>
+        <v>13.36486053466797</v>
       </c>
       <c r="C722" t="n">
-        <v>13.85913867738389</v>
+        <v>13.85913768843952</v>
       </c>
       <c r="D722" t="n">
-        <v>13.24856113638068</v>
+        <v>13.24856019100519</v>
       </c>
       <c r="E722" t="n">
-        <v>13.71376254422711</v>
+        <v>13.71376156565631</v>
       </c>
       <c r="F722" t="n">
         <v>8302800</v>
@@ -14912,16 +14912,16 @@
         <v>45314</v>
       </c>
       <c r="B725" t="n">
-        <v>13.21948528289795</v>
+        <v>13.21948623657227</v>
       </c>
       <c r="C725" t="n">
-        <v>13.4811608240167</v>
+        <v>13.4811617965687</v>
       </c>
       <c r="D725" t="n">
-        <v>13.18071850183321</v>
+        <v>13.18071945271083</v>
       </c>
       <c r="E725" t="n">
-        <v>13.24856013762826</v>
+        <v>13.24856109340008</v>
       </c>
       <c r="F725" t="n">
         <v>9537600</v>
@@ -15072,16 +15072,16 @@
         <v>45324</v>
       </c>
       <c r="B733" t="n">
-        <v>13.10318565368652</v>
+        <v>13.10318660736084</v>
       </c>
       <c r="C733" t="n">
-        <v>13.28732764270956</v>
+        <v>13.28732860978607</v>
       </c>
       <c r="D733" t="n">
-        <v>12.85120110089878</v>
+        <v>12.85120203623319</v>
       </c>
       <c r="E733" t="n">
-        <v>13.11287665627604</v>
+        <v>13.11287761065569</v>
       </c>
       <c r="F733" t="n">
         <v>9537000</v>
@@ -15112,16 +15112,16 @@
         <v>45328</v>
       </c>
       <c r="B735" t="n">
-        <v>13.36486148834229</v>
+        <v>13.36486053466797</v>
       </c>
       <c r="C735" t="n">
-        <v>13.45208698338175</v>
+        <v>13.4520860234833</v>
       </c>
       <c r="D735" t="n">
-        <v>12.9675017214052</v>
+        <v>12.96750079608522</v>
       </c>
       <c r="E735" t="n">
-        <v>13.05472721644466</v>
+        <v>13.05472628490055</v>
       </c>
       <c r="F735" t="n">
         <v>13604000</v>
@@ -15152,16 +15152,16 @@
         <v>45330</v>
       </c>
       <c r="B737" t="n">
-        <v>13.40362739562988</v>
+        <v>13.4036283493042</v>
       </c>
       <c r="C737" t="n">
-        <v>13.60715322931881</v>
+        <v>13.60715419747408</v>
       </c>
       <c r="D737" t="n">
-        <v>13.22917641696138</v>
+        <v>13.22917735822343</v>
       </c>
       <c r="E737" t="n">
-        <v>13.37455254060946</v>
+        <v>13.37455349221508</v>
       </c>
       <c r="F737" t="n">
         <v>12424500</v>
@@ -15192,16 +15192,16 @@
         <v>45336</v>
       </c>
       <c r="B739" t="n">
-        <v>12.75428295135498</v>
+        <v>12.7542839050293</v>
       </c>
       <c r="C739" t="n">
-        <v>12.94811685615447</v>
+        <v>12.9481178243223</v>
       </c>
       <c r="D739" t="n">
-        <v>12.67674938943519</v>
+        <v>12.67675033731209</v>
       </c>
       <c r="E739" t="n">
-        <v>12.85120036589121</v>
+        <v>12.85120132681232</v>
       </c>
       <c r="F739" t="n">
         <v>7875600</v>
@@ -15212,16 +15212,16 @@
         <v>45337</v>
       </c>
       <c r="B740" t="n">
-        <v>12.97719383239746</v>
+        <v>12.97719287872314</v>
       </c>
       <c r="C740" t="n">
-        <v>13.18071968228313</v>
+        <v>13.180718713652</v>
       </c>
       <c r="D740" t="n">
-        <v>12.65736762890185</v>
+        <v>12.65736669873108</v>
       </c>
       <c r="E740" t="n">
-        <v>12.80274283984602</v>
+        <v>12.80274189899184</v>
       </c>
       <c r="F740" t="n">
         <v>6962800</v>
@@ -15232,16 +15232,16 @@
         <v>45338</v>
       </c>
       <c r="B741" t="n">
-        <v>13.18071937561035</v>
+        <v>13.18071842193604</v>
       </c>
       <c r="C741" t="n">
-        <v>13.30671072921826</v>
+        <v>13.306709766428</v>
       </c>
       <c r="D741" t="n">
-        <v>12.84150932560221</v>
+        <v>12.84150839647101</v>
       </c>
       <c r="E741" t="n">
-        <v>13.05472709772942</v>
+        <v>13.05472615317111</v>
       </c>
       <c r="F741" t="n">
         <v>4964600</v>
@@ -15312,16 +15312,16 @@
         <v>45344</v>
       </c>
       <c r="B745" t="n">
-        <v>14.37279891967773</v>
+        <v>14.37279796600342</v>
       </c>
       <c r="C745" t="n">
-        <v>14.61509155274617</v>
+        <v>14.61509058299508</v>
       </c>
       <c r="D745" t="n">
-        <v>13.95605529503265</v>
+        <v>13.95605436901041</v>
       </c>
       <c r="E745" t="n">
-        <v>13.95605529503265</v>
+        <v>13.95605436901041</v>
       </c>
       <c r="F745" t="n">
         <v>21828500</v>
@@ -15332,16 +15332,16 @@
         <v>45345</v>
       </c>
       <c r="B746" t="n">
-        <v>14.26618957519531</v>
+        <v>14.26619052886963</v>
       </c>
       <c r="C746" t="n">
-        <v>14.46002348431353</v>
+        <v>14.46002445094536</v>
       </c>
       <c r="D746" t="n">
-        <v>13.98513017590566</v>
+        <v>13.98513111079155</v>
       </c>
       <c r="E746" t="n">
-        <v>14.46002348431353</v>
+        <v>14.46002445094536</v>
       </c>
       <c r="F746" t="n">
         <v>7821200</v>
@@ -15352,16 +15352,16 @@
         <v>45348</v>
       </c>
       <c r="B747" t="n">
-        <v>14.15958118438721</v>
+        <v>14.15958023071289</v>
       </c>
       <c r="C747" t="n">
-        <v>14.44064060258168</v>
+        <v>14.44063962997748</v>
       </c>
       <c r="D747" t="n">
-        <v>14.13050632713207</v>
+        <v>14.130505375416</v>
       </c>
       <c r="E747" t="n">
-        <v>14.32434024928807</v>
+        <v>14.32433928451693</v>
       </c>
       <c r="F747" t="n">
         <v>6009200</v>
@@ -15372,16 +15372,16 @@
         <v>45349</v>
       </c>
       <c r="B748" t="n">
-        <v>14.25649833679199</v>
+        <v>14.25649738311768</v>
       </c>
       <c r="C748" t="n">
-        <v>14.36310676088445</v>
+        <v>14.36310580007867</v>
       </c>
       <c r="D748" t="n">
-        <v>14.08204734802885</v>
+        <v>14.08204640602426</v>
       </c>
       <c r="E748" t="n">
-        <v>14.26619026378395</v>
+        <v>14.2661893094613</v>
       </c>
       <c r="F748" t="n">
         <v>8891500</v>
@@ -15452,16 +15452,16 @@
         <v>45355</v>
       </c>
       <c r="B752" t="n">
-        <v>13.59746170043945</v>
+        <v>13.59746074676514</v>
       </c>
       <c r="C752" t="n">
-        <v>13.77191268420841</v>
+        <v>13.77191171829877</v>
       </c>
       <c r="D752" t="n">
-        <v>13.48116135268448</v>
+        <v>13.48116040716703</v>
       </c>
       <c r="E752" t="n">
-        <v>13.67499526560944</v>
+        <v>13.67499430649721</v>
       </c>
       <c r="F752" t="n">
         <v>6926800</v>
@@ -15472,16 +15472,16 @@
         <v>45356</v>
       </c>
       <c r="B753" t="n">
-        <v>14.02389717102051</v>
+        <v>14.02389621734619</v>
       </c>
       <c r="C753" t="n">
-        <v>14.1305055915887</v>
+        <v>14.13050463066464</v>
       </c>
       <c r="D753" t="n">
-        <v>13.58777063780318</v>
+        <v>13.587769713787</v>
       </c>
       <c r="E753" t="n">
-        <v>13.64592034928656</v>
+        <v>13.64591942131599</v>
       </c>
       <c r="F753" t="n">
         <v>16007800</v>
@@ -15492,16 +15492,16 @@
         <v>45357</v>
       </c>
       <c r="B754" t="n">
-        <v>13.97543811798096</v>
+        <v>13.97543907165527</v>
       </c>
       <c r="C754" t="n">
-        <v>14.3824897854385</v>
+        <v>14.38249076688974</v>
       </c>
       <c r="D754" t="n">
-        <v>13.91728748365575</v>
+        <v>13.9172884333619</v>
       </c>
       <c r="E754" t="n">
-        <v>14.0917384623584</v>
+        <v>14.09173942396897</v>
       </c>
       <c r="F754" t="n">
         <v>10982800</v>
@@ -15572,16 +15572,16 @@
         <v>45363</v>
       </c>
       <c r="B758" t="n">
-        <v>14.26618957519531</v>
+        <v>14.26619052886963</v>
       </c>
       <c r="C758" t="n">
-        <v>14.37279799414208</v>
+        <v>14.37279895494302</v>
       </c>
       <c r="D758" t="n">
-        <v>13.74283755843964</v>
+        <v>13.74283847712863</v>
       </c>
       <c r="E758" t="n">
-        <v>14.00451310468098</v>
+        <v>14.0045140408626</v>
       </c>
       <c r="F758" t="n">
         <v>5196700</v>
@@ -15632,16 +15632,16 @@
         <v>45366</v>
       </c>
       <c r="B761" t="n">
-        <v>14.17896366119385</v>
+        <v>14.17896461486816</v>
       </c>
       <c r="C761" t="n">
-        <v>14.19834658938979</v>
+        <v>14.1983475443678</v>
       </c>
       <c r="D761" t="n">
-        <v>13.89790427030547</v>
+        <v>13.89790520507579</v>
       </c>
       <c r="E761" t="n">
-        <v>14.0917381736297</v>
+        <v>14.09173912143725</v>
       </c>
       <c r="F761" t="n">
         <v>7761200</v>
@@ -15672,16 +15672,16 @@
         <v>45370</v>
       </c>
       <c r="B763" t="n">
-        <v>14.27588176727295</v>
+        <v>14.27588081359863</v>
       </c>
       <c r="C763" t="n">
-        <v>14.35341626165535</v>
+        <v>14.35341530280148</v>
       </c>
       <c r="D763" t="n">
-        <v>14.00451427189027</v>
+        <v>14.00451333634416</v>
       </c>
       <c r="E763" t="n">
-        <v>14.09173976933154</v>
+        <v>14.09173882795849</v>
       </c>
       <c r="F763" t="n">
         <v>3066400</v>
@@ -15712,16 +15712,16 @@
         <v>45372</v>
       </c>
       <c r="B765" t="n">
-        <v>14.36310768127441</v>
+        <v>14.3631067276001</v>
       </c>
       <c r="C765" t="n">
-        <v>14.47940803981137</v>
+        <v>14.47940707841501</v>
       </c>
       <c r="D765" t="n">
-        <v>14.19834860894545</v>
+        <v>14.19834766621072</v>
       </c>
       <c r="E765" t="n">
-        <v>14.46002510885842</v>
+        <v>14.46002414874904</v>
       </c>
       <c r="F765" t="n">
         <v>19402800</v>
@@ -15812,16 +15812,16 @@
         <v>45379</v>
       </c>
       <c r="B770" t="n">
-        <v>14.25649833679199</v>
+        <v>14.25649738311768</v>
       </c>
       <c r="C770" t="n">
-        <v>14.73139166812162</v>
+        <v>14.73139068267979</v>
       </c>
       <c r="D770" t="n">
-        <v>14.25649833679199</v>
+        <v>14.25649738311768</v>
       </c>
       <c r="E770" t="n">
-        <v>14.45033225526602</v>
+        <v>14.45033128862538</v>
       </c>
       <c r="F770" t="n">
         <v>7122000</v>
@@ -15852,16 +15852,16 @@
         <v>45384</v>
       </c>
       <c r="B772" t="n">
-        <v>13.58776950836182</v>
+        <v>13.58777046203613</v>
       </c>
       <c r="C772" t="n">
-        <v>13.859136962698</v>
+        <v>13.85913793541857</v>
       </c>
       <c r="D772" t="n">
-        <v>13.43270146732536</v>
+        <v>13.43270241011604</v>
       </c>
       <c r="E772" t="n">
-        <v>13.82037018350711</v>
+        <v>13.82037115350679</v>
       </c>
       <c r="F772" t="n">
         <v>14898200</v>
@@ -16112,16 +16112,16 @@
         <v>45401</v>
       </c>
       <c r="B785" t="n">
-        <v>12.96750164031982</v>
+        <v>12.96750068664551</v>
       </c>
       <c r="C785" t="n">
-        <v>13.20979426979305</v>
+        <v>13.20979329829971</v>
       </c>
       <c r="D785" t="n">
-        <v>12.77366772159585</v>
+        <v>12.77366678217674</v>
       </c>
       <c r="E785" t="n">
-        <v>12.80274257833619</v>
+        <v>12.80274163677882</v>
       </c>
       <c r="F785" t="n">
         <v>12837800</v>
@@ -16212,16 +16212,16 @@
         <v>45408</v>
       </c>
       <c r="B790" t="n">
-        <v>12.90935134887695</v>
+        <v>12.90935039520264</v>
       </c>
       <c r="C790" t="n">
-        <v>13.10318619707384</v>
+        <v>13.10318522908003</v>
       </c>
       <c r="D790" t="n">
-        <v>12.7736680642668</v>
+        <v>12.77366712061604</v>
       </c>
       <c r="E790" t="n">
-        <v>13.03534363049571</v>
+        <v>13.03534266751375</v>
       </c>
       <c r="F790" t="n">
         <v>14489900</v>
@@ -16232,16 +16232,16 @@
         <v>45411</v>
       </c>
       <c r="B791" t="n">
-        <v>13.1710262298584</v>
+        <v>13.17102718353271</v>
       </c>
       <c r="C791" t="n">
-        <v>13.21948493598589</v>
+        <v>13.21948589316895</v>
       </c>
       <c r="D791" t="n">
-        <v>12.89965876952657</v>
+        <v>12.89965970355199</v>
       </c>
       <c r="E791" t="n">
-        <v>12.98688333142852</v>
+        <v>12.98688427176961</v>
       </c>
       <c r="F791" t="n">
         <v>6604200</v>
@@ -16312,16 +16312,16 @@
         <v>45418</v>
       </c>
       <c r="B795" t="n">
-        <v>12.92873382568359</v>
+        <v>12.92873477935791</v>
       </c>
       <c r="C795" t="n">
-        <v>13.20979321649093</v>
+        <v>13.2097941908973</v>
       </c>
       <c r="D795" t="n">
-        <v>12.81243348372259</v>
+        <v>12.81243442881813</v>
       </c>
       <c r="E795" t="n">
-        <v>13.11287580272028</v>
+        <v>13.11287676997764</v>
       </c>
       <c r="F795" t="n">
         <v>7469100</v>
@@ -16352,16 +16352,16 @@
         <v>45420</v>
       </c>
       <c r="B797" t="n">
-        <v>13.10318565368652</v>
+        <v>13.10318660736084</v>
       </c>
       <c r="C797" t="n">
-        <v>13.2001021494928</v>
+        <v>13.20010311022088</v>
       </c>
       <c r="D797" t="n">
-        <v>12.97719337729265</v>
+        <v>12.97719432179701</v>
       </c>
       <c r="E797" t="n">
-        <v>13.00626823360723</v>
+        <v>13.00626918022772</v>
       </c>
       <c r="F797" t="n">
         <v>4964400</v>
@@ -16412,16 +16412,16 @@
         <v>45425</v>
       </c>
       <c r="B800" t="n">
-        <v>12.92873382568359</v>
+        <v>12.92873477935791</v>
       </c>
       <c r="C800" t="n">
-        <v>13.15164258337395</v>
+        <v>13.1516435534909</v>
       </c>
       <c r="D800" t="n">
-        <v>12.79304963125927</v>
+        <v>12.79305057492499</v>
       </c>
       <c r="E800" t="n">
-        <v>12.98688353452762</v>
+        <v>12.98688449249129</v>
       </c>
       <c r="F800" t="n">
         <v>6951300</v>
@@ -16432,16 +16432,16 @@
         <v>45426</v>
       </c>
       <c r="B801" t="n">
-        <v>12.75428295135498</v>
+        <v>12.7542839050293</v>
       </c>
       <c r="C801" t="n">
-        <v>12.9675007087709</v>
+        <v>12.96750167838812</v>
       </c>
       <c r="D801" t="n">
-        <v>12.66705746312697</v>
+        <v>12.66705841027919</v>
       </c>
       <c r="E801" t="n">
-        <v>12.84150843958299</v>
+        <v>12.84150939977941</v>
       </c>
       <c r="F801" t="n">
         <v>10701800</v>
@@ -16472,16 +16472,16 @@
         <v>45428</v>
       </c>
       <c r="B803" t="n">
-        <v>13.05472660064697</v>
+        <v>13.05472755432129</v>
       </c>
       <c r="C803" t="n">
-        <v>13.21948565588908</v>
+        <v>13.21948662159938</v>
       </c>
       <c r="D803" t="n">
-        <v>12.9481172565062</v>
+        <v>12.94811820239249</v>
       </c>
       <c r="E803" t="n">
-        <v>13.2001018026733</v>
+        <v>13.20010276696758</v>
       </c>
       <c r="F803" t="n">
         <v>4347100</v>
@@ -16492,16 +16492,16 @@
         <v>45429</v>
       </c>
       <c r="B804" t="n">
-        <v>13.20979404449463</v>
+        <v>13.20979309082031</v>
       </c>
       <c r="C804" t="n">
-        <v>13.2582527544174</v>
+        <v>13.25825179724463</v>
       </c>
       <c r="D804" t="n">
-        <v>12.97719334599296</v>
+        <v>12.97719240911113</v>
       </c>
       <c r="E804" t="n">
-        <v>12.99657627539826</v>
+        <v>12.99657533711709</v>
       </c>
       <c r="F804" t="n">
         <v>6205200</v>
@@ -16632,16 +16632,16 @@
         <v>45440</v>
       </c>
       <c r="B811" t="n">
-        <v>12.30846500396729</v>
+        <v>12.3084659576416</v>
       </c>
       <c r="C811" t="n">
-        <v>12.75428346510026</v>
+        <v>12.75428445331711</v>
       </c>
       <c r="D811" t="n">
-        <v>12.17278172727877</v>
+        <v>12.17278267044019</v>
       </c>
       <c r="E811" t="n">
-        <v>12.72520860927743</v>
+        <v>12.72520959524153</v>
       </c>
       <c r="F811" t="n">
         <v>7568500</v>
@@ -16712,16 +16712,16 @@
         <v>45447</v>
       </c>
       <c r="B815" t="n">
-        <v>11.7657299041748</v>
+        <v>11.76573085784912</v>
       </c>
       <c r="C815" t="n">
-        <v>11.98863866986729</v>
+        <v>11.98863964160954</v>
       </c>
       <c r="D815" t="n">
-        <v>11.68819634008411</v>
+        <v>11.68819728747393</v>
       </c>
       <c r="E815" t="n">
-        <v>11.86264639715167</v>
+        <v>11.86264735868158</v>
       </c>
       <c r="F815" t="n">
         <v>3975700</v>
@@ -16792,16 +16792,16 @@
         <v>45453</v>
       </c>
       <c r="B819" t="n">
-        <v>11.5622034072876</v>
+        <v>11.56220436096191</v>
       </c>
       <c r="C819" t="n">
-        <v>11.74634538042216</v>
+        <v>11.74634634928489</v>
       </c>
       <c r="D819" t="n">
-        <v>11.52343662745543</v>
+        <v>11.52343757793218</v>
       </c>
       <c r="E819" t="n">
-        <v>11.58158633506721</v>
+        <v>11.58158729034027</v>
       </c>
       <c r="F819" t="n">
         <v>12105900</v>
@@ -16872,16 +16872,16 @@
         <v>45457</v>
       </c>
       <c r="B823" t="n">
-        <v>11.30052757263184</v>
+        <v>11.30052852630615</v>
       </c>
       <c r="C823" t="n">
-        <v>11.40713691624688</v>
+        <v>11.40713787891818</v>
       </c>
       <c r="D823" t="n">
-        <v>11.05823495426744</v>
+        <v>11.05823588749419</v>
       </c>
       <c r="E823" t="n">
-        <v>11.09700173623482</v>
+        <v>11.09700267273318</v>
       </c>
       <c r="F823" t="n">
         <v>4784200</v>
@@ -16932,16 +16932,16 @@
         <v>45462</v>
       </c>
       <c r="B826" t="n">
-        <v>10.70933437347412</v>
+        <v>10.7093334197998</v>
       </c>
       <c r="C826" t="n">
-        <v>10.76748408676966</v>
+        <v>10.76748312791706</v>
       </c>
       <c r="D826" t="n">
-        <v>10.43796688812455</v>
+        <v>10.43796595861572</v>
       </c>
       <c r="E826" t="n">
-        <v>10.71902630044772</v>
+        <v>10.71902534591033</v>
       </c>
       <c r="F826" t="n">
         <v>8916100</v>
@@ -17012,16 +17012,16 @@
         <v>45468</v>
       </c>
       <c r="B830" t="n">
-        <v>10.55426692962646</v>
+        <v>10.55426788330078</v>
       </c>
       <c r="C830" t="n">
-        <v>10.85470926281736</v>
+        <v>10.85471024363938</v>
       </c>
       <c r="D830" t="n">
-        <v>10.52519114955792</v>
+        <v>10.52519210060498</v>
       </c>
       <c r="E830" t="n">
-        <v>10.68995020618764</v>
+        <v>10.68995117212218</v>
       </c>
       <c r="F830" t="n">
         <v>9834800</v>
@@ -17092,16 +17092,16 @@
         <v>45474</v>
       </c>
       <c r="B834" t="n">
-        <v>9.691704750061035</v>
+        <v>9.691705703735352</v>
       </c>
       <c r="C834" t="n">
-        <v>10.08906449692986</v>
+        <v>10.08906548970481</v>
       </c>
       <c r="D834" t="n">
-        <v>9.594787332851229</v>
+        <v>9.594788276988766</v>
       </c>
       <c r="E834" t="n">
-        <v>9.982456077417465</v>
+        <v>9.982457059702028</v>
       </c>
       <c r="F834" t="n">
         <v>19240000</v>
@@ -17172,16 +17172,16 @@
         <v>45478</v>
       </c>
       <c r="B838" t="n">
-        <v>11.09700202941895</v>
+        <v>11.09700107574463</v>
       </c>
       <c r="C838" t="n">
-        <v>11.18422752221831</v>
+        <v>11.18422656104786</v>
       </c>
       <c r="D838" t="n">
-        <v>10.66087548969511</v>
+        <v>10.66087457350143</v>
       </c>
       <c r="E838" t="n">
-        <v>10.73840905567833</v>
+        <v>10.73840813282142</v>
       </c>
       <c r="F838" t="n">
         <v>25549700</v>
@@ -17252,16 +17252,16 @@
         <v>45484</v>
       </c>
       <c r="B842" t="n">
-        <v>10.90316772460938</v>
+        <v>10.90316867828369</v>
       </c>
       <c r="C842" t="n">
-        <v>11.22299390392275</v>
+        <v>11.2229948855715</v>
       </c>
       <c r="D842" t="n">
-        <v>10.72871674524827</v>
+        <v>10.72871768366377</v>
       </c>
       <c r="E842" t="n">
-        <v>11.09700163263672</v>
+        <v>11.09700260326523</v>
       </c>
       <c r="F842" t="n">
         <v>13851900</v>
@@ -17292,16 +17292,16 @@
         <v>45488</v>
       </c>
       <c r="B844" t="n">
-        <v>10.78686714172363</v>
+        <v>10.78686809539795</v>
       </c>
       <c r="C844" t="n">
-        <v>10.91285941022897</v>
+        <v>10.91286037504235</v>
       </c>
       <c r="D844" t="n">
-        <v>10.76748328921222</v>
+        <v>10.76748424117279</v>
       </c>
       <c r="E844" t="n">
-        <v>10.87409262947909</v>
+        <v>10.87409359086507</v>
       </c>
       <c r="F844" t="n">
         <v>5840400</v>
@@ -17312,16 +17312,16 @@
         <v>45489</v>
       </c>
       <c r="B845" t="n">
-        <v>10.76748275756836</v>
+        <v>10.76748371124268</v>
       </c>
       <c r="C845" t="n">
-        <v>10.90316694563</v>
+        <v>10.90316791132185</v>
       </c>
       <c r="D845" t="n">
-        <v>10.69964112567399</v>
+        <v>10.69964207333959</v>
       </c>
       <c r="E845" t="n">
-        <v>10.76748275756836</v>
+        <v>10.76748371124268</v>
       </c>
       <c r="F845" t="n">
         <v>9437300</v>
@@ -17332,16 +17332,16 @@
         <v>45490</v>
       </c>
       <c r="B846" t="n">
-        <v>10.41858291625977</v>
+        <v>10.41858196258545</v>
       </c>
       <c r="C846" t="n">
-        <v>10.82563460181362</v>
+        <v>10.82563361087946</v>
       </c>
       <c r="D846" t="n">
-        <v>10.41858291625977</v>
+        <v>10.41858196258545</v>
       </c>
       <c r="E846" t="n">
-        <v>10.75779296231231</v>
+        <v>10.7577919775881</v>
       </c>
       <c r="F846" t="n">
         <v>8121300</v>
@@ -17432,16 +17432,16 @@
         <v>45497</v>
       </c>
       <c r="B851" t="n">
-        <v>9.691704750061035</v>
+        <v>9.691705703735352</v>
       </c>
       <c r="C851" t="n">
-        <v>10.26351547819831</v>
+        <v>10.26351648813943</v>
       </c>
       <c r="D851" t="n">
-        <v>9.691704750061035</v>
+        <v>9.691705703735352</v>
       </c>
       <c r="E851" t="n">
-        <v>10.09875642350544</v>
+        <v>10.09875741723408</v>
       </c>
       <c r="F851" t="n">
         <v>20101500</v>
@@ -17492,16 +17492,16 @@
         <v>45502</v>
       </c>
       <c r="B854" t="n">
-        <v>9.255578994750977</v>
+        <v>9.25557804107666</v>
       </c>
       <c r="C854" t="n">
-        <v>9.652938774831423</v>
+        <v>9.652937780214037</v>
       </c>
       <c r="D854" t="n">
-        <v>9.110202856785623</v>
+        <v>9.11020191809054</v>
       </c>
       <c r="E854" t="n">
-        <v>9.575405204292462</v>
+        <v>9.575404217663962</v>
       </c>
       <c r="F854" t="n">
         <v>14084800</v>
@@ -17512,16 +17512,16 @@
         <v>45503</v>
       </c>
       <c r="B855" t="n">
-        <v>9.148968696594238</v>
+        <v>9.148969650268555</v>
       </c>
       <c r="C855" t="n">
-        <v>9.439720018205433</v>
+        <v>9.439721002187216</v>
       </c>
       <c r="D855" t="n">
-        <v>9.139277694483143</v>
+        <v>9.139278647147284</v>
       </c>
       <c r="E855" t="n">
-        <v>9.207119330625666</v>
+        <v>9.207120290361514</v>
       </c>
       <c r="F855" t="n">
         <v>13878900</v>
@@ -17532,16 +17532,16 @@
         <v>45504</v>
       </c>
       <c r="B856" t="n">
-        <v>9.517252922058105</v>
+        <v>9.517253875732422</v>
       </c>
       <c r="C856" t="n">
-        <v>9.556019700638412</v>
+        <v>9.556020658197346</v>
       </c>
       <c r="D856" t="n">
-        <v>9.21681061912895</v>
+        <v>9.216811542697508</v>
       </c>
       <c r="E856" t="n">
-        <v>9.255577397709256</v>
+        <v>9.255578325162432</v>
       </c>
       <c r="F856" t="n">
         <v>17487100</v>
@@ -17572,16 +17572,16 @@
         <v>45506</v>
       </c>
       <c r="B858" t="n">
-        <v>9.885539054870605</v>
+        <v>9.885538101196289</v>
       </c>
       <c r="C858" t="n">
-        <v>9.953381619335163</v>
+        <v>9.953380659115961</v>
       </c>
       <c r="D858" t="n">
-        <v>9.58509671321695</v>
+        <v>9.585095788526804</v>
       </c>
       <c r="E858" t="n">
-        <v>9.604479642868947</v>
+        <v>9.604478716308897</v>
       </c>
       <c r="F858" t="n">
         <v>10117700</v>
@@ -17672,16 +17672,16 @@
         <v>45513</v>
       </c>
       <c r="B863" t="n">
-        <v>9.953381538391113</v>
+        <v>9.953380584716797</v>
       </c>
       <c r="C863" t="n">
-        <v>10.1375235278162</v>
+        <v>10.13752255649849</v>
       </c>
       <c r="D863" t="n">
-        <v>9.662630201791425</v>
+        <v>9.662629275975187</v>
       </c>
       <c r="E863" t="n">
-        <v>10.12783160093251</v>
+        <v>10.12783063054342</v>
       </c>
       <c r="F863" t="n">
         <v>24889300</v>
@@ -17752,16 +17752,16 @@
         <v>45519</v>
       </c>
       <c r="B867" t="n">
-        <v>10.07937240600586</v>
+        <v>10.07937335968018</v>
       </c>
       <c r="C867" t="n">
-        <v>10.30228209224458</v>
+        <v>10.30228306700982</v>
       </c>
       <c r="D867" t="n">
-        <v>9.933997206834544</v>
+        <v>9.933998146753977</v>
       </c>
       <c r="E867" t="n">
-        <v>10.30228209224458</v>
+        <v>10.30228306700982</v>
       </c>
       <c r="F867" t="n">
         <v>11390800</v>
@@ -17792,16 +17792,16 @@
         <v>45523</v>
       </c>
       <c r="B869" t="n">
-        <v>10.37981510162354</v>
+        <v>10.37981605529785</v>
       </c>
       <c r="C869" t="n">
-        <v>10.43796573275546</v>
+        <v>10.43796669177252</v>
       </c>
       <c r="D869" t="n">
-        <v>9.701396001206707</v>
+        <v>9.701396892549386</v>
       </c>
       <c r="E869" t="n">
-        <v>10.02122216174997</v>
+        <v>10.02122308247756</v>
       </c>
       <c r="F869" t="n">
         <v>15557600</v>
@@ -17852,16 +17852,16 @@
         <v>45526</v>
       </c>
       <c r="B872" t="n">
-        <v>9.449411392211914</v>
+        <v>9.44941234588623</v>
       </c>
       <c r="C872" t="n">
-        <v>9.691703992012219</v>
+        <v>9.691704970139725</v>
       </c>
       <c r="D872" t="n">
-        <v>9.34280298103803</v>
+        <v>9.342803923952978</v>
       </c>
       <c r="E872" t="n">
-        <v>9.546328801841204</v>
+        <v>9.546329765296832</v>
       </c>
       <c r="F872" t="n">
         <v>16152200</v>
@@ -18012,16 +18012,16 @@
         <v>45538</v>
       </c>
       <c r="B880" t="n">
-        <v>9.691704750061035</v>
+        <v>9.691705703735352</v>
       </c>
       <c r="C880" t="n">
-        <v>9.817697022724587</v>
+        <v>9.817697988796681</v>
       </c>
       <c r="D880" t="n">
-        <v>9.497870839914412</v>
+        <v>9.497871774515261</v>
       </c>
       <c r="E880" t="n">
-        <v>9.556020550821904</v>
+        <v>9.556021491144747</v>
       </c>
       <c r="F880" t="n">
         <v>16401400</v>
@@ -18112,16 +18112,16 @@
         <v>45545</v>
       </c>
       <c r="B885" t="n">
-        <v>8.625616073608398</v>
+        <v>8.625617027282715</v>
       </c>
       <c r="C885" t="n">
-        <v>8.896984447413983</v>
+        <v>8.896985431091611</v>
       </c>
       <c r="D885" t="n">
-        <v>8.52869958948318</v>
+        <v>8.528700532442116</v>
       </c>
       <c r="E885" t="n">
-        <v>8.896984447413983</v>
+        <v>8.896985431091611</v>
       </c>
       <c r="F885" t="n">
         <v>19808800</v>
@@ -18152,16 +18152,16 @@
         <v>45547</v>
       </c>
       <c r="B887" t="n">
-        <v>8.790376663208008</v>
+        <v>8.790375709533691</v>
       </c>
       <c r="C887" t="n">
-        <v>8.916368946630897</v>
+        <v>8.916367979287587</v>
       </c>
       <c r="D887" t="n">
-        <v>8.722535019931478</v>
+        <v>8.722534073617352</v>
       </c>
       <c r="E887" t="n">
-        <v>8.819452445417722</v>
+        <v>8.819451488588953</v>
       </c>
       <c r="F887" t="n">
         <v>11088400</v>
@@ -18212,16 +18212,16 @@
         <v>45552</v>
       </c>
       <c r="B890" t="n">
-        <v>8.548084259033203</v>
+        <v>8.548083305358887</v>
       </c>
       <c r="C890" t="n">
-        <v>8.606234900780036</v>
+        <v>8.606233940618093</v>
       </c>
       <c r="D890" t="n">
-        <v>8.402709041075765</v>
+        <v>8.402708103620357</v>
       </c>
       <c r="E890" t="n">
-        <v>8.480242613889478</v>
+        <v>8.480241667783972</v>
       </c>
       <c r="F890" t="n">
         <v>13563600</v>
@@ -18232,16 +18232,16 @@
         <v>45553</v>
       </c>
       <c r="B891" t="n">
-        <v>8.470549583435059</v>
+        <v>8.470550537109375</v>
       </c>
       <c r="C891" t="n">
-        <v>8.761300905769993</v>
+        <v>8.761301892179148</v>
       </c>
       <c r="D891" t="n">
-        <v>8.470549583435059</v>
+        <v>8.470550537109375</v>
       </c>
       <c r="E891" t="n">
-        <v>8.548083146154644</v>
+        <v>8.548084108558237</v>
       </c>
       <c r="F891" t="n">
         <v>22128100</v>
@@ -18252,16 +18252,16 @@
         <v>45554</v>
       </c>
       <c r="B892" t="n">
-        <v>7.985964775085449</v>
+        <v>7.985965251922607</v>
       </c>
       <c r="C892" t="n">
-        <v>8.567467450394972</v>
+        <v>8.567467961953305</v>
       </c>
       <c r="D892" t="n">
-        <v>7.985964775085449</v>
+        <v>7.985965251922607</v>
       </c>
       <c r="E892" t="n">
-        <v>8.538392593911404</v>
+        <v>8.538393103733693</v>
       </c>
       <c r="F892" t="n">
         <v>19129200</v>
@@ -18272,16 +18272,16 @@
         <v>45555</v>
       </c>
       <c r="B893" t="n">
-        <v>7.462612152099609</v>
+        <v>7.462612628936768</v>
       </c>
       <c r="C893" t="n">
-        <v>8.073189636035888</v>
+        <v>8.073190151887005</v>
       </c>
       <c r="D893" t="n">
-        <v>7.462612152099609</v>
+        <v>7.462612628936768</v>
       </c>
       <c r="E893" t="n">
-        <v>8.005348001467285</v>
+        <v>8.005348512983536</v>
       </c>
       <c r="F893" t="n">
         <v>27842200</v>
@@ -18292,16 +18292,16 @@
         <v>45558</v>
       </c>
       <c r="B894" t="n">
-        <v>7.617680549621582</v>
+        <v>7.617680072784424</v>
       </c>
       <c r="C894" t="n">
-        <v>7.675830726380644</v>
+        <v>7.675830245903511</v>
       </c>
       <c r="D894" t="n">
-        <v>7.433538092149622</v>
+        <v>7.433537626839064</v>
       </c>
       <c r="E894" t="n">
-        <v>7.44322955720787</v>
+        <v>7.443229091290664</v>
       </c>
       <c r="F894" t="n">
         <v>19916000</v>
@@ -18312,16 +18312,16 @@
         <v>45559</v>
       </c>
       <c r="B895" t="n">
-        <v>7.898739337921143</v>
+        <v>7.898738861083984</v>
       </c>
       <c r="C895" t="n">
-        <v>8.024731615949483</v>
+        <v>8.024731131506325</v>
       </c>
       <c r="D895" t="n">
-        <v>7.753364130189305</v>
+        <v>7.753363662128269</v>
       </c>
       <c r="E895" t="n">
-        <v>7.859972554241117</v>
+        <v>7.859972079744262</v>
       </c>
       <c r="F895" t="n">
         <v>22551600</v>
@@ -18352,16 +18352,16 @@
         <v>45561</v>
       </c>
       <c r="B897" t="n">
-        <v>7.801822662353516</v>
+        <v>7.801823139190674</v>
       </c>
       <c r="C897" t="n">
-        <v>7.8696643011731</v>
+        <v>7.869664782156651</v>
       </c>
       <c r="D897" t="n">
-        <v>7.54983811206219</v>
+        <v>7.549838573498384</v>
       </c>
       <c r="E897" t="n">
-        <v>7.559530038828704</v>
+        <v>7.559530500857256</v>
       </c>
       <c r="F897" t="n">
         <v>14720200</v>
@@ -18512,16 +18512,16 @@
         <v>45573</v>
       </c>
       <c r="B905" t="n">
-        <v>6.609742641448975</v>
+        <v>6.609743118286133</v>
       </c>
       <c r="C905" t="n">
-        <v>6.648509422513715</v>
+        <v>6.648509902147569</v>
       </c>
       <c r="D905" t="n">
-        <v>6.512825226650641</v>
+        <v>6.512825696496025</v>
       </c>
       <c r="E905" t="n">
-        <v>6.551592469851864</v>
+        <v>6.551592942493978</v>
       </c>
       <c r="F905" t="n">
         <v>17971800</v>
@@ -18592,16 +18592,16 @@
         <v>45579</v>
       </c>
       <c r="B909" t="n">
-        <v>6.919877529144287</v>
+        <v>6.919877052307129</v>
       </c>
       <c r="C909" t="n">
-        <v>6.997411098435412</v>
+        <v>6.997410616255546</v>
       </c>
       <c r="D909" t="n">
-        <v>6.64851003662535</v>
+        <v>6.648509578487669</v>
       </c>
       <c r="E909" t="n">
-        <v>6.813269102437253</v>
+        <v>6.813268632946302</v>
       </c>
       <c r="F909" t="n">
         <v>42118900</v>
@@ -18612,16 +18612,16 @@
         <v>45580</v>
       </c>
       <c r="B910" t="n">
-        <v>6.793884754180908</v>
+        <v>6.793885231018066</v>
       </c>
       <c r="C910" t="n">
-        <v>7.08463559811253</v>
+        <v>7.084636095356394</v>
       </c>
       <c r="D910" t="n">
-        <v>6.716350733662682</v>
+        <v>6.716351205058019</v>
       </c>
       <c r="E910" t="n">
-        <v>6.997410113864813</v>
+        <v>6.997410604986649</v>
       </c>
       <c r="F910" t="n">
         <v>30694500</v>
@@ -18792,16 +18792,16 @@
         <v>45593</v>
       </c>
       <c r="B919" t="n">
-        <v>7.191245079040527</v>
+        <v>7.191245555877686</v>
       </c>
       <c r="C919" t="n">
-        <v>7.375387526810755</v>
+        <v>7.375388015858033</v>
       </c>
       <c r="D919" t="n">
-        <v>7.084636196197448</v>
+        <v>7.084636665965583</v>
       </c>
       <c r="E919" t="n">
-        <v>7.084636196197448</v>
+        <v>7.084636665965583</v>
       </c>
       <c r="F919" t="n">
         <v>17455800</v>
@@ -18832,16 +18832,16 @@
         <v>45595</v>
       </c>
       <c r="B921" t="n">
-        <v>7.443229198455811</v>
+        <v>7.443228721618652</v>
       </c>
       <c r="C921" t="n">
-        <v>7.598296791142485</v>
+        <v>7.598296304371199</v>
       </c>
       <c r="D921" t="n">
-        <v>7.249395285268095</v>
+        <v>7.249394820848559</v>
       </c>
       <c r="E921" t="n">
-        <v>7.317237385952047</v>
+        <v>7.317236917186328</v>
       </c>
       <c r="F921" t="n">
         <v>17976200</v>
@@ -18912,16 +18912,16 @@
         <v>45601</v>
       </c>
       <c r="B925" t="n">
-        <v>7.443229198455811</v>
+        <v>7.443228721618652</v>
       </c>
       <c r="C925" t="n">
-        <v>7.569221473096077</v>
+        <v>7.569220988187449</v>
       </c>
       <c r="D925" t="n">
-        <v>7.191245111311781</v>
+        <v>7.191244650617532</v>
       </c>
       <c r="E925" t="n">
-        <v>7.472304516502219</v>
+        <v>7.472304037802402</v>
       </c>
       <c r="F925" t="n">
         <v>13215900</v>
@@ -18972,16 +18972,16 @@
         <v>45604</v>
       </c>
       <c r="B928" t="n">
-        <v>6.793884754180908</v>
+        <v>6.793885231018066</v>
       </c>
       <c r="C928" t="n">
-        <v>7.133094303169364</v>
+        <v>7.133094803814362</v>
       </c>
       <c r="D928" t="n">
-        <v>6.68727588033775</v>
+        <v>6.687276349692433</v>
       </c>
       <c r="E928" t="n">
-        <v>6.939259945078488</v>
+        <v>6.939260432118983</v>
       </c>
       <c r="F928" t="n">
         <v>34800800</v>
@@ -19012,16 +19012,16 @@
         <v>45608</v>
       </c>
       <c r="B930" t="n">
-        <v>6.987719058990479</v>
+        <v>6.987719535827637</v>
       </c>
       <c r="C930" t="n">
-        <v>7.055561157612231</v>
+        <v>7.055561639078888</v>
       </c>
       <c r="D930" t="n">
-        <v>6.784193225261708</v>
+        <v>6.784193688210403</v>
       </c>
       <c r="E930" t="n">
-        <v>6.861726788180004</v>
+        <v>6.861727256419536</v>
       </c>
       <c r="F930" t="n">
         <v>26167100</v>
@@ -19112,16 +19112,16 @@
         <v>45617</v>
       </c>
       <c r="B935" t="n">
-        <v>6.726043224334717</v>
+        <v>6.726043701171875</v>
       </c>
       <c r="C935" t="n">
-        <v>6.842343571673456</v>
+        <v>6.842344056755628</v>
       </c>
       <c r="D935" t="n">
-        <v>6.512825458743863</v>
+        <v>6.512825920465128</v>
       </c>
       <c r="E935" t="n">
-        <v>6.696967906431782</v>
+        <v>6.69696838120767</v>
       </c>
       <c r="F935" t="n">
         <v>32015400</v>
@@ -19132,16 +19132,16 @@
         <v>45618</v>
       </c>
       <c r="B936" t="n">
-        <v>6.978027820587158</v>
+        <v>6.97802734375</v>
       </c>
       <c r="C936" t="n">
-        <v>7.045869925898105</v>
+        <v>7.045869444425019</v>
       </c>
       <c r="D936" t="n">
-        <v>6.726043716257203</v>
+        <v>6.726043256639149</v>
       </c>
       <c r="E936" t="n">
-        <v>6.774501966790851</v>
+        <v>6.774501503861446</v>
       </c>
       <c r="F936" t="n">
         <v>20807700</v>
@@ -19192,16 +19192,16 @@
         <v>45623</v>
       </c>
       <c r="B939" t="n">
-        <v>7.181553840637207</v>
+        <v>7.181553363800049</v>
       </c>
       <c r="C939" t="n">
-        <v>7.801823343774085</v>
+        <v>7.801822825752589</v>
       </c>
       <c r="D939" t="n">
-        <v>7.133095588981745</v>
+        <v>7.133095115362094</v>
       </c>
       <c r="E939" t="n">
-        <v>7.675831057624106</v>
+        <v>7.675830547968181</v>
       </c>
       <c r="F939" t="n">
         <v>36141700</v>
@@ -19352,16 +19352,16 @@
         <v>45635</v>
       </c>
       <c r="B947" t="n">
-        <v>5.873172760009766</v>
+        <v>5.873173236846924</v>
       </c>
       <c r="C947" t="n">
-        <v>6.008856491034863</v>
+        <v>6.008856978888051</v>
       </c>
       <c r="D947" t="n">
-        <v>5.776255809277553</v>
+        <v>5.776256278246119</v>
       </c>
       <c r="E947" t="n">
-        <v>5.989473100888421</v>
+        <v>5.98947358716789</v>
       </c>
       <c r="F947" t="n">
         <v>18041800</v>
@@ -19392,16 +19392,16 @@
         <v>45637</v>
       </c>
       <c r="B949" t="n">
-        <v>6.270532608032227</v>
+        <v>6.270533084869385</v>
       </c>
       <c r="C949" t="n">
-        <v>6.638817489937481</v>
+        <v>6.63881799478054</v>
       </c>
       <c r="D949" t="n">
-        <v>5.98947321450887</v>
+        <v>5.989473669973113</v>
       </c>
       <c r="E949" t="n">
-        <v>6.231765827003935</v>
+        <v>6.231766300893107</v>
       </c>
       <c r="F949" t="n">
         <v>30797400</v>
@@ -19412,16 +19412,16 @@
         <v>45638</v>
       </c>
       <c r="B950" t="n">
-        <v>5.873172760009766</v>
+        <v>5.873173236846924</v>
       </c>
       <c r="C950" t="n">
-        <v>6.086390513757107</v>
+        <v>6.086391007905207</v>
       </c>
       <c r="D950" t="n">
-        <v>5.737489028984668</v>
+        <v>5.737489494805797</v>
       </c>
       <c r="E950" t="n">
-        <v>6.047623271327748</v>
+        <v>6.047623762328373</v>
       </c>
       <c r="F950" t="n">
         <v>28228300</v>
@@ -19472,16 +19472,16 @@
         <v>45643</v>
       </c>
       <c r="B953" t="n">
-        <v>5.340129852294922</v>
+        <v>5.340129375457764</v>
       </c>
       <c r="C953" t="n">
-        <v>5.398280028749276</v>
+        <v>5.398279546719705</v>
       </c>
       <c r="D953" t="n">
-        <v>5.146295468643883</v>
+        <v>5.146295009114813</v>
       </c>
       <c r="E953" t="n">
-        <v>5.243212429401142</v>
+        <v>5.243211961218048</v>
       </c>
       <c r="F953" t="n">
         <v>32812100</v>
@@ -19492,16 +19492,16 @@
         <v>45644</v>
       </c>
       <c r="B954" t="n">
-        <v>4.981535911560059</v>
+        <v>4.981536388397217</v>
       </c>
       <c r="C954" t="n">
-        <v>5.340129324097897</v>
+        <v>5.340129835259944</v>
       </c>
       <c r="D954" t="n">
-        <v>4.894310886574293</v>
+        <v>4.894311355062193</v>
       </c>
       <c r="E954" t="n">
-        <v>5.233520446741433</v>
+        <v>5.23352094769878</v>
       </c>
       <c r="F954" t="n">
         <v>36135800</v>
@@ -19532,16 +19532,16 @@
         <v>45646</v>
       </c>
       <c r="B956" t="n">
-        <v>5.592113494873047</v>
+        <v>5.592113971710205</v>
       </c>
       <c r="C956" t="n">
-        <v>5.659955592946704</v>
+        <v>5.659956075568729</v>
       </c>
       <c r="D956" t="n">
-        <v>5.165678440131098</v>
+        <v>5.165678880606319</v>
       </c>
       <c r="E956" t="n">
-        <v>5.223828611850025</v>
+        <v>5.223829057283687</v>
       </c>
       <c r="F956" t="n">
         <v>45865200</v>
@@ -19572,16 +19572,16 @@
         <v>45652</v>
       </c>
       <c r="B958" t="n">
-        <v>5.727797985076904</v>
+        <v>5.727797508239746</v>
       </c>
       <c r="C958" t="n">
-        <v>5.747181378208906</v>
+        <v>5.747180899758088</v>
       </c>
       <c r="D958" t="n">
-        <v>5.504888732990607</v>
+        <v>5.504888274710566</v>
       </c>
       <c r="E958" t="n">
-        <v>5.601806160787163</v>
+        <v>5.60180569443878</v>
       </c>
       <c r="F958" t="n">
         <v>25976300</v>
@@ -27452,19 +27452,19 @@
         <v>46231</v>
       </c>
       <c r="B1352" t="n">
-        <v>8.31</v>
+        <v>8.24</v>
       </c>
       <c r="C1352" t="n">
         <v>8.42</v>
       </c>
       <c r="D1352" t="n">
-        <v>8.23</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="E1352" t="n">
         <v>8.31</v>
       </c>
       <c r="F1352" t="n">
-        <v>3386000</v>
+        <v>5647400</v>
       </c>
     </row>
   </sheetData>

--- a/database/ASAI3.xlsx
+++ b/database/ASAI3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1352"/>
+  <dimension ref="A1:F1353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,16 +512,16 @@
         <v>44259</v>
       </c>
       <c r="B5" t="n">
-        <v>13.90097713470459</v>
+        <v>13.90097618103027</v>
       </c>
       <c r="C5" t="n">
-        <v>14.04340481356423</v>
+        <v>14.04340385011868</v>
       </c>
       <c r="D5" t="n">
-        <v>13.44330802948757</v>
+        <v>13.44330710721157</v>
       </c>
       <c r="E5" t="n">
-        <v>13.53256280482981</v>
+        <v>13.53256187643049</v>
       </c>
       <c r="F5" t="n">
         <v>12300000</v>
@@ -692,16 +692,16 @@
         <v>44272</v>
       </c>
       <c r="B14" t="n">
-        <v>14.05289936065674</v>
+        <v>14.05290031433105</v>
       </c>
       <c r="C14" t="n">
-        <v>14.07188929407625</v>
+        <v>14.07189024903928</v>
       </c>
       <c r="D14" t="n">
-        <v>13.49458119180776</v>
+        <v>13.49458210759284</v>
       </c>
       <c r="E14" t="n">
-        <v>13.58763467271578</v>
+        <v>13.58763559481576</v>
       </c>
       <c r="F14" t="n">
         <v>4753000</v>
@@ -732,16 +732,16 @@
         <v>44274</v>
       </c>
       <c r="B16" t="n">
-        <v>13.54775238037109</v>
+        <v>13.54775428771973</v>
       </c>
       <c r="C16" t="n">
-        <v>14.03580565118024</v>
+        <v>14.03580762724047</v>
       </c>
       <c r="D16" t="n">
-        <v>13.46419523502917</v>
+        <v>13.46419713061404</v>
       </c>
       <c r="E16" t="n">
-        <v>13.95414740838706</v>
+        <v>13.95414937295086</v>
       </c>
       <c r="F16" t="n">
         <v>14098000</v>
@@ -752,16 +752,16 @@
         <v>44277</v>
       </c>
       <c r="B17" t="n">
-        <v>13.29328346252441</v>
+        <v>13.2932825088501</v>
       </c>
       <c r="C17" t="n">
-        <v>13.63511042556885</v>
+        <v>13.6351094473715</v>
       </c>
       <c r="D17" t="n">
-        <v>13.15655249620002</v>
+        <v>13.15655155233494</v>
       </c>
       <c r="E17" t="n">
-        <v>13.63511042556885</v>
+        <v>13.6351094473715</v>
       </c>
       <c r="F17" t="n">
         <v>5803000</v>
@@ -772,16 +772,16 @@
         <v>44278</v>
       </c>
       <c r="B18" t="n">
-        <v>13.44140815734863</v>
+        <v>13.44140911102295</v>
       </c>
       <c r="C18" t="n">
-        <v>13.44140815734863</v>
+        <v>13.44140911102295</v>
       </c>
       <c r="D18" t="n">
-        <v>13.01982095435623</v>
+        <v>13.01982187811874</v>
       </c>
       <c r="E18" t="n">
-        <v>13.29328287491709</v>
+        <v>13.29328381808184</v>
       </c>
       <c r="F18" t="n">
         <v>7916000</v>
@@ -812,16 +812,16 @@
         <v>44280</v>
       </c>
       <c r="B20" t="n">
-        <v>13.64840412139893</v>
+        <v>13.64840221405029</v>
       </c>
       <c r="C20" t="n">
-        <v>13.67309167041285</v>
+        <v>13.67308975961416</v>
       </c>
       <c r="D20" t="n">
-        <v>12.83941352376278</v>
+        <v>12.83941172946964</v>
       </c>
       <c r="E20" t="n">
-        <v>12.91347617080455</v>
+        <v>12.91347436616125</v>
       </c>
       <c r="F20" t="n">
         <v>6602000</v>
@@ -832,16 +832,16 @@
         <v>44281</v>
       </c>
       <c r="B21" t="n">
-        <v>13.8060245513916</v>
+        <v>13.80602359771729</v>
       </c>
       <c r="C21" t="n">
-        <v>14.1269626819656</v>
+        <v>14.12696170612194</v>
       </c>
       <c r="D21" t="n">
-        <v>13.48888513211062</v>
+        <v>13.48888420034324</v>
       </c>
       <c r="E21" t="n">
-        <v>13.54965455193487</v>
+        <v>13.54965361596974</v>
       </c>
       <c r="F21" t="n">
         <v>4396500</v>
@@ -912,16 +912,16 @@
         <v>44287</v>
       </c>
       <c r="B25" t="n">
-        <v>14.25419902801514</v>
+        <v>14.25419807434082</v>
       </c>
       <c r="C25" t="n">
-        <v>14.40232432733938</v>
+        <v>14.40232336375477</v>
       </c>
       <c r="D25" t="n">
-        <v>14.02631437007006</v>
+        <v>14.02631343164232</v>
       </c>
       <c r="E25" t="n">
-        <v>14.09088159926785</v>
+        <v>14.09088065652025</v>
       </c>
       <c r="F25" t="n">
         <v>9940000</v>
@@ -932,16 +932,16 @@
         <v>44291</v>
       </c>
       <c r="B26" t="n">
-        <v>14.71756267547607</v>
+        <v>14.71756362915039</v>
       </c>
       <c r="C26" t="n">
-        <v>14.88657769361247</v>
+        <v>14.88657865823869</v>
       </c>
       <c r="D26" t="n">
-        <v>14.2997741979616</v>
+        <v>14.29977512456389</v>
       </c>
       <c r="E26" t="n">
-        <v>14.2997741979616</v>
+        <v>14.29977512456389</v>
       </c>
       <c r="F26" t="n">
         <v>6073500</v>
@@ -952,16 +952,16 @@
         <v>44292</v>
       </c>
       <c r="B27" t="n">
-        <v>14.58653163909912</v>
+        <v>14.58652973175049</v>
       </c>
       <c r="C27" t="n">
-        <v>14.72136280773917</v>
+        <v>14.72136088275989</v>
       </c>
       <c r="D27" t="n">
-        <v>14.52766111829865</v>
+        <v>14.52765921864798</v>
       </c>
       <c r="E27" t="n">
-        <v>14.71756500173048</v>
+        <v>14.7175630772478</v>
       </c>
       <c r="F27" t="n">
         <v>5821500</v>
@@ -972,16 +972,16 @@
         <v>44293</v>
       </c>
       <c r="B28" t="n">
-        <v>14.49347686767578</v>
+        <v>14.4934778213501</v>
       </c>
       <c r="C28" t="n">
-        <v>14.78023202327058</v>
+        <v>14.78023299581345</v>
       </c>
       <c r="D28" t="n">
-        <v>13.92756307336586</v>
+        <v>13.92756398980291</v>
       </c>
       <c r="E28" t="n">
-        <v>14.45359719150692</v>
+        <v>14.45359814255714</v>
       </c>
       <c r="F28" t="n">
         <v>10992000</v>
@@ -992,16 +992,16 @@
         <v>44294</v>
       </c>
       <c r="B29" t="n">
-        <v>14.70237159729004</v>
+        <v>14.70237064361572</v>
       </c>
       <c r="C29" t="n">
-        <v>14.74035237068301</v>
+        <v>14.74035141454506</v>
       </c>
       <c r="D29" t="n">
-        <v>14.26559225050429</v>
+        <v>14.26559132516181</v>
       </c>
       <c r="E29" t="n">
-        <v>14.43270747232676</v>
+        <v>14.4327065361443</v>
       </c>
       <c r="F29" t="n">
         <v>6395000</v>
@@ -1012,16 +1012,16 @@
         <v>44295</v>
       </c>
       <c r="B30" t="n">
-        <v>14.71756267547607</v>
+        <v>14.71756362915039</v>
       </c>
       <c r="C30" t="n">
-        <v>14.73655351358414</v>
+        <v>14.73655446848903</v>
       </c>
       <c r="D30" t="n">
-        <v>14.40801889636538</v>
+        <v>14.40801982998176</v>
       </c>
       <c r="E30" t="n">
-        <v>14.63210571505577</v>
+        <v>14.63210666319261</v>
       </c>
       <c r="F30" t="n">
         <v>7012500</v>
@@ -1032,16 +1032,16 @@
         <v>44298</v>
       </c>
       <c r="B31" t="n">
-        <v>14.69857215881348</v>
+        <v>14.69857311248779</v>
       </c>
       <c r="C31" t="n">
-        <v>14.8011210568803</v>
+        <v>14.8011220172082</v>
       </c>
       <c r="D31" t="n">
-        <v>14.52765913976815</v>
+        <v>14.52766008235327</v>
       </c>
       <c r="E31" t="n">
-        <v>14.69857215881348</v>
+        <v>14.69857311248779</v>
       </c>
       <c r="F31" t="n">
         <v>4711000</v>
@@ -1072,16 +1072,16 @@
         <v>44300</v>
       </c>
       <c r="B33" t="n">
-        <v>14.93785285949707</v>
+        <v>14.93785381317139</v>
       </c>
       <c r="C33" t="n">
-        <v>14.9454484709092</v>
+        <v>14.94544942506844</v>
       </c>
       <c r="D33" t="n">
-        <v>14.62261144203403</v>
+        <v>14.62261237558245</v>
       </c>
       <c r="E33" t="n">
-        <v>14.65109770142871</v>
+        <v>14.65109863679578</v>
       </c>
       <c r="F33" t="n">
         <v>5841000</v>
@@ -1092,16 +1092,16 @@
         <v>44301</v>
       </c>
       <c r="B34" t="n">
-        <v>15.1866283416748</v>
+        <v>15.18662643432617</v>
       </c>
       <c r="C34" t="n">
-        <v>15.20371846858745</v>
+        <v>15.2037165590924</v>
       </c>
       <c r="D34" t="n">
-        <v>14.84100264251348</v>
+        <v>14.84100077857334</v>
       </c>
       <c r="E34" t="n">
-        <v>14.84100264251348</v>
+        <v>14.84100077857334</v>
       </c>
       <c r="F34" t="n">
         <v>11554500</v>
@@ -1132,16 +1132,16 @@
         <v>44305</v>
       </c>
       <c r="B36" t="n">
-        <v>15.28727626800537</v>
+        <v>15.28727722167969</v>
       </c>
       <c r="C36" t="n">
-        <v>15.50756529752376</v>
+        <v>15.50756626494049</v>
       </c>
       <c r="D36" t="n">
-        <v>15.00431891696419</v>
+        <v>15.00431985298662</v>
       </c>
       <c r="E36" t="n">
-        <v>15.14484768829616</v>
+        <v>15.14484863308528</v>
       </c>
       <c r="F36" t="n">
         <v>5017000</v>
@@ -1152,16 +1152,16 @@
         <v>44306</v>
       </c>
       <c r="B37" t="n">
-        <v>15.47717952728271</v>
+        <v>15.4771785736084</v>
       </c>
       <c r="C37" t="n">
-        <v>15.65569088659348</v>
+        <v>15.65568992191963</v>
       </c>
       <c r="D37" t="n">
-        <v>15.06698752800291</v>
+        <v>15.06698659960384</v>
       </c>
       <c r="E37" t="n">
-        <v>15.35944030441754</v>
+        <v>15.35943935799809</v>
       </c>
       <c r="F37" t="n">
         <v>6029000</v>
@@ -1232,16 +1232,16 @@
         <v>44313</v>
       </c>
       <c r="B41" t="n">
-        <v>15.12775707244873</v>
+        <v>15.12775611877441</v>
       </c>
       <c r="C41" t="n">
-        <v>15.29677210768214</v>
+        <v>15.29677114335289</v>
       </c>
       <c r="D41" t="n">
-        <v>15.10117062083444</v>
+        <v>15.10116966883617</v>
       </c>
       <c r="E41" t="n">
-        <v>15.24929500760934</v>
+        <v>15.24929404627311</v>
       </c>
       <c r="F41" t="n">
         <v>4986500</v>
@@ -1252,16 +1252,16 @@
         <v>44314</v>
       </c>
       <c r="B42" t="n">
-        <v>15.18852615356445</v>
+        <v>15.18852519989014</v>
       </c>
       <c r="C42" t="n">
-        <v>15.35564228216909</v>
+        <v>15.35564131800169</v>
       </c>
       <c r="D42" t="n">
-        <v>15.04799647598031</v>
+        <v>15.04799553112973</v>
       </c>
       <c r="E42" t="n">
-        <v>15.14864647703371</v>
+        <v>15.14864552586341</v>
       </c>
       <c r="F42" t="n">
         <v>5371500</v>
@@ -1272,16 +1272,16 @@
         <v>44315</v>
       </c>
       <c r="B43" t="n">
-        <v>15.21646499633789</v>
+        <v>15.21646404266357</v>
       </c>
       <c r="C43" t="n">
-        <v>15.32323336252505</v>
+        <v>15.32323240215915</v>
       </c>
       <c r="D43" t="n">
-        <v>14.90950503441863</v>
+        <v>14.90950409998268</v>
       </c>
       <c r="E43" t="n">
-        <v>15.26222338706449</v>
+        <v>15.26222243052232</v>
       </c>
       <c r="F43" t="n">
         <v>5343000</v>
@@ -1312,16 +1312,16 @@
         <v>44319</v>
       </c>
       <c r="B45" t="n">
-        <v>15.53295803070068</v>
+        <v>15.532958984375</v>
       </c>
       <c r="C45" t="n">
-        <v>15.67023137590184</v>
+        <v>15.6702323380043</v>
       </c>
       <c r="D45" t="n">
-        <v>15.29463476087267</v>
+        <v>15.29463569991469</v>
       </c>
       <c r="E45" t="n">
-        <v>15.44334861216023</v>
+        <v>15.44334956033281</v>
       </c>
       <c r="F45" t="n">
         <v>8474000</v>
@@ -1332,16 +1332,16 @@
         <v>44320</v>
       </c>
       <c r="B46" t="n">
-        <v>15.72933578491211</v>
+        <v>15.72933769226074</v>
       </c>
       <c r="C46" t="n">
-        <v>15.74840208285252</v>
+        <v>15.74840399251314</v>
       </c>
       <c r="D46" t="n">
-        <v>15.35945760522207</v>
+        <v>15.35945946771906</v>
       </c>
       <c r="E46" t="n">
-        <v>15.63400611347231</v>
+        <v>15.63400800926121</v>
       </c>
       <c r="F46" t="n">
         <v>9407500</v>
@@ -1352,16 +1352,16 @@
         <v>44321</v>
       </c>
       <c r="B47" t="n">
-        <v>16.32228469848633</v>
+        <v>16.32228660583496</v>
       </c>
       <c r="C47" t="n">
-        <v>16.58730007183393</v>
+        <v>16.58730201015107</v>
       </c>
       <c r="D47" t="n">
-        <v>16.01532383109572</v>
+        <v>16.01532570257429</v>
       </c>
       <c r="E47" t="n">
-        <v>16.08396141636727</v>
+        <v>16.08396329586652</v>
       </c>
       <c r="F47" t="n">
         <v>17262500</v>
@@ -1372,16 +1372,16 @@
         <v>44322</v>
       </c>
       <c r="B48" t="n">
-        <v>16.61971473693848</v>
+        <v>16.61971282958984</v>
       </c>
       <c r="C48" t="n">
-        <v>16.64449947442742</v>
+        <v>16.64449756423438</v>
       </c>
       <c r="D48" t="n">
-        <v>16.16022705029641</v>
+        <v>16.16022519568053</v>
       </c>
       <c r="E48" t="n">
-        <v>16.31847408082518</v>
+        <v>16.31847220804819</v>
       </c>
       <c r="F48" t="n">
         <v>9404500</v>
@@ -1392,16 +1392,16 @@
         <v>44323</v>
       </c>
       <c r="B49" t="n">
-        <v>16.96290016174316</v>
+        <v>16.96289825439453</v>
       </c>
       <c r="C49" t="n">
-        <v>17.04488198227947</v>
+        <v>17.0448800657126</v>
       </c>
       <c r="D49" t="n">
-        <v>16.4290546491212</v>
+        <v>16.42905280179942</v>
       </c>
       <c r="E49" t="n">
-        <v>16.663565057737</v>
+        <v>16.66356318404632</v>
       </c>
       <c r="F49" t="n">
         <v>8422500</v>
@@ -1412,16 +1412,16 @@
         <v>44326</v>
       </c>
       <c r="B50" t="n">
-        <v>16.81418609619141</v>
+        <v>16.81418418884277</v>
       </c>
       <c r="C50" t="n">
-        <v>17.0162841548014</v>
+        <v>17.01628222452739</v>
       </c>
       <c r="D50" t="n">
-        <v>16.55298359675715</v>
+        <v>16.55298171903851</v>
       </c>
       <c r="E50" t="n">
-        <v>16.97052576072697</v>
+        <v>16.97052383564365</v>
       </c>
       <c r="F50" t="n">
         <v>7669500</v>
@@ -1432,16 +1432,16 @@
         <v>44327</v>
       </c>
       <c r="B51" t="n">
-        <v>16.58729934692383</v>
+        <v>16.5872974395752</v>
       </c>
       <c r="C51" t="n">
-        <v>16.78367894467991</v>
+        <v>16.78367701474988</v>
       </c>
       <c r="D51" t="n">
-        <v>16.4919696745899</v>
+        <v>16.49196777820309</v>
       </c>
       <c r="E51" t="n">
-        <v>16.6254319431623</v>
+        <v>16.62543003142886</v>
       </c>
       <c r="F51" t="n">
         <v>6191000</v>
@@ -1452,16 +1452,16 @@
         <v>44328</v>
       </c>
       <c r="B52" t="n">
-        <v>16.12590980529785</v>
+        <v>16.12590789794922</v>
       </c>
       <c r="C52" t="n">
-        <v>16.57776989836218</v>
+        <v>16.57776793756821</v>
       </c>
       <c r="D52" t="n">
-        <v>16.04201880215192</v>
+        <v>16.04201690472579</v>
       </c>
       <c r="E52" t="n">
-        <v>16.49006781665641</v>
+        <v>16.49006586623571</v>
       </c>
       <c r="F52" t="n">
         <v>6728500</v>
@@ -1492,16 +1492,16 @@
         <v>44330</v>
       </c>
       <c r="B54" t="n">
-        <v>16.52628898620605</v>
+        <v>16.52629089355469</v>
       </c>
       <c r="C54" t="n">
-        <v>16.66356232925931</v>
+        <v>16.66356425245107</v>
       </c>
       <c r="D54" t="n">
-        <v>16.13734451407442</v>
+        <v>16.13734637653381</v>
       </c>
       <c r="E54" t="n">
-        <v>16.54726082268666</v>
+        <v>16.54726273245572</v>
       </c>
       <c r="F54" t="n">
         <v>5923000</v>
@@ -1512,16 +1512,16 @@
         <v>44333</v>
       </c>
       <c r="B55" t="n">
-        <v>16.34706878662109</v>
+        <v>16.34707069396973</v>
       </c>
       <c r="C55" t="n">
-        <v>16.52819314458002</v>
+        <v>16.52819507306194</v>
       </c>
       <c r="D55" t="n">
-        <v>16.06107980023078</v>
+        <v>16.06108167421069</v>
       </c>
       <c r="E55" t="n">
-        <v>16.50531395293831</v>
+        <v>16.50531587875072</v>
       </c>
       <c r="F55" t="n">
         <v>4728000</v>
@@ -1552,16 +1552,16 @@
         <v>44335</v>
       </c>
       <c r="B57" t="n">
-        <v>15.82847881317139</v>
+        <v>15.82847690582275</v>
       </c>
       <c r="C57" t="n">
-        <v>16.36804269641236</v>
+        <v>16.3680407240457</v>
       </c>
       <c r="D57" t="n">
-        <v>15.67595206173143</v>
+        <v>15.67595017276244</v>
       </c>
       <c r="E57" t="n">
-        <v>15.98481846065799</v>
+        <v>15.98481653447027</v>
       </c>
       <c r="F57" t="n">
         <v>6358000</v>
@@ -1572,16 +1572,16 @@
         <v>44336</v>
       </c>
       <c r="B58" t="n">
-        <v>16.03248596191406</v>
+        <v>16.03248405456543</v>
       </c>
       <c r="C58" t="n">
-        <v>16.03248596191406</v>
+        <v>16.03248405456543</v>
       </c>
       <c r="D58" t="n">
-        <v>15.69692561740377</v>
+        <v>15.69692374997599</v>
       </c>
       <c r="E58" t="n">
-        <v>15.90283657256179</v>
+        <v>15.90283468063725</v>
       </c>
       <c r="F58" t="n">
         <v>7278000</v>
@@ -1592,16 +1592,16 @@
         <v>44337</v>
       </c>
       <c r="B59" t="n">
-        <v>16.43477249145508</v>
+        <v>16.43477439880371</v>
       </c>
       <c r="C59" t="n">
-        <v>16.62543183488117</v>
+        <v>16.6254337643569</v>
       </c>
       <c r="D59" t="n">
-        <v>15.75984081583289</v>
+        <v>15.75984264485187</v>
       </c>
       <c r="E59" t="n">
-        <v>16.03438932487009</v>
+        <v>16.03439118575198</v>
       </c>
       <c r="F59" t="n">
         <v>10145000</v>
@@ -1632,16 +1632,16 @@
         <v>44341</v>
       </c>
       <c r="B61" t="n">
-        <v>16.88472747802734</v>
+        <v>16.88472938537598</v>
       </c>
       <c r="C61" t="n">
-        <v>17.06394632104241</v>
+        <v>17.06394824863613</v>
       </c>
       <c r="D61" t="n">
-        <v>16.77986465398696</v>
+        <v>16.77986654948997</v>
       </c>
       <c r="E61" t="n">
-        <v>17.0162823928035</v>
+        <v>17.01628431501296</v>
       </c>
       <c r="F61" t="n">
         <v>5307000</v>
@@ -1652,16 +1652,16 @@
         <v>44342</v>
       </c>
       <c r="B62" t="n">
-        <v>16.94192695617676</v>
+        <v>16.94192504882812</v>
       </c>
       <c r="C62" t="n">
-        <v>17.11161449219801</v>
+        <v>17.11161256574568</v>
       </c>
       <c r="D62" t="n">
-        <v>16.65975260630318</v>
+        <v>16.65975073072218</v>
       </c>
       <c r="E62" t="n">
-        <v>17.02391059716581</v>
+        <v>17.02390868058733</v>
       </c>
       <c r="F62" t="n">
         <v>5462000</v>
@@ -1672,16 +1672,16 @@
         <v>44343</v>
       </c>
       <c r="B63" t="n">
-        <v>16.94955253601074</v>
+        <v>16.94955444335938</v>
       </c>
       <c r="C63" t="n">
-        <v>17.26223183953111</v>
+        <v>17.26223378206583</v>
       </c>
       <c r="D63" t="n">
-        <v>16.70550899973091</v>
+        <v>16.7055108796171</v>
       </c>
       <c r="E63" t="n">
-        <v>16.94955253601074</v>
+        <v>16.94955444335938</v>
       </c>
       <c r="F63" t="n">
         <v>5669000</v>
@@ -1692,16 +1692,16 @@
         <v>44344</v>
       </c>
       <c r="B64" t="n">
-        <v>16.98577690124512</v>
+        <v>16.98577880859375</v>
       </c>
       <c r="C64" t="n">
-        <v>17.14974233685488</v>
+        <v>17.14974426261534</v>
       </c>
       <c r="D64" t="n">
-        <v>16.56442007870208</v>
+        <v>16.56442193873616</v>
       </c>
       <c r="E64" t="n">
-        <v>16.91141906621777</v>
+        <v>16.91142096521669</v>
       </c>
       <c r="F64" t="n">
         <v>4590500</v>
@@ -1732,16 +1732,16 @@
         <v>44348</v>
       </c>
       <c r="B66" t="n">
-        <v>16.96861457824707</v>
+        <v>16.9686164855957</v>
       </c>
       <c r="C66" t="n">
-        <v>17.4109431969055</v>
+        <v>17.41094515397386</v>
       </c>
       <c r="D66" t="n">
-        <v>16.8256209926954</v>
+        <v>16.82562288397091</v>
       </c>
       <c r="E66" t="n">
-        <v>17.17834020076747</v>
+        <v>17.17834213169021</v>
       </c>
       <c r="F66" t="n">
         <v>13722000</v>
@@ -1772,16 +1772,16 @@
         <v>44351</v>
       </c>
       <c r="B68" t="n">
-        <v>16.77223587036133</v>
+        <v>16.77223968505859</v>
       </c>
       <c r="C68" t="n">
-        <v>16.81608689471135</v>
+        <v>16.81609071938215</v>
       </c>
       <c r="D68" t="n">
-        <v>16.40617063922488</v>
+        <v>16.40617437066384</v>
       </c>
       <c r="E68" t="n">
-        <v>16.72266459379896</v>
+        <v>16.72266839722167</v>
       </c>
       <c r="F68" t="n">
         <v>8097000</v>
@@ -1852,16 +1852,16 @@
         <v>44357</v>
       </c>
       <c r="B72" t="n">
-        <v>16.30321884155273</v>
+        <v>16.30321502685547</v>
       </c>
       <c r="C72" t="n">
-        <v>16.34707169398488</v>
+        <v>16.34706786902673</v>
       </c>
       <c r="D72" t="n">
-        <v>15.97719348463267</v>
+        <v>15.97718974622022</v>
       </c>
       <c r="E72" t="n">
-        <v>16.15641233581547</v>
+        <v>16.15640855546862</v>
       </c>
       <c r="F72" t="n">
         <v>4720000</v>
@@ -1892,16 +1892,16 @@
         <v>44361</v>
       </c>
       <c r="B74" t="n">
-        <v>16.01532173156738</v>
+        <v>16.01532554626465</v>
       </c>
       <c r="C74" t="n">
-        <v>16.19263501570841</v>
+        <v>16.19263887264001</v>
       </c>
       <c r="D74" t="n">
-        <v>15.85135630955313</v>
+        <v>15.8513600851954</v>
       </c>
       <c r="E74" t="n">
-        <v>16.16403557102893</v>
+        <v>16.16403942114841</v>
       </c>
       <c r="F74" t="n">
         <v>4317000</v>
@@ -1912,16 +1912,16 @@
         <v>44362</v>
       </c>
       <c r="B75" t="n">
-        <v>15.85898494720459</v>
+        <v>15.85898303985596</v>
       </c>
       <c r="C75" t="n">
-        <v>16.02676511323235</v>
+        <v>16.02676318570492</v>
       </c>
       <c r="D75" t="n">
-        <v>15.48720119095393</v>
+        <v>15.48719932831946</v>
       </c>
       <c r="E75" t="n">
-        <v>16.01532460600237</v>
+        <v>16.01532267985088</v>
       </c>
       <c r="F75" t="n">
         <v>8432500</v>
@@ -1932,16 +1932,16 @@
         <v>44363</v>
       </c>
       <c r="B76" t="n">
-        <v>15.89902305603027</v>
+        <v>15.89902114868164</v>
       </c>
       <c r="C76" t="n">
-        <v>16.11446715307724</v>
+        <v>16.11446521988256</v>
       </c>
       <c r="D76" t="n">
-        <v>15.66260712011776</v>
+        <v>15.6626052411311</v>
       </c>
       <c r="E76" t="n">
-        <v>15.7026452588224</v>
+        <v>15.70264337503251</v>
       </c>
       <c r="F76" t="n">
         <v>10606500</v>
@@ -1952,16 +1952,16 @@
         <v>44364</v>
       </c>
       <c r="B77" t="n">
-        <v>15.97719383239746</v>
+        <v>15.97719192504883</v>
       </c>
       <c r="C77" t="n">
-        <v>16.00769882125508</v>
+        <v>16.00769691026478</v>
       </c>
       <c r="D77" t="n">
-        <v>15.69120478891841</v>
+        <v>15.691202915711</v>
       </c>
       <c r="E77" t="n">
-        <v>15.8971175547978</v>
+        <v>15.89711565700863</v>
       </c>
       <c r="F77" t="n">
         <v>7246000</v>
@@ -1972,16 +1972,16 @@
         <v>44365</v>
       </c>
       <c r="B78" t="n">
-        <v>16.2078914642334</v>
+        <v>16.20789337158203</v>
       </c>
       <c r="C78" t="n">
-        <v>16.36423112436919</v>
+        <v>16.36423305011592</v>
       </c>
       <c r="D78" t="n">
-        <v>15.67976622640263</v>
+        <v>15.67976807160136</v>
       </c>
       <c r="E78" t="n">
-        <v>15.98863265031907</v>
+        <v>15.98863453186528</v>
       </c>
       <c r="F78" t="n">
         <v>12012000</v>
@@ -1992,16 +1992,16 @@
         <v>44368</v>
       </c>
       <c r="B79" t="n">
-        <v>16.48434448242188</v>
+        <v>16.48434257507324</v>
       </c>
       <c r="C79" t="n">
-        <v>16.59302020374093</v>
+        <v>16.59301828381779</v>
       </c>
       <c r="D79" t="n">
-        <v>16.00007212945171</v>
+        <v>16.00007027813662</v>
       </c>
       <c r="E79" t="n">
-        <v>16.20789042268334</v>
+        <v>16.20788854732228</v>
       </c>
       <c r="F79" t="n">
         <v>6798000</v>
@@ -2012,16 +2012,16 @@
         <v>44369</v>
       </c>
       <c r="B80" t="n">
-        <v>16.47290420532227</v>
+        <v>16.4729061126709</v>
       </c>
       <c r="C80" t="n">
-        <v>16.49578339803871</v>
+        <v>16.49578530803645</v>
       </c>
       <c r="D80" t="n">
-        <v>16.13162548984007</v>
+        <v>16.13162735767305</v>
       </c>
       <c r="E80" t="n">
-        <v>16.46718395257762</v>
+        <v>16.46718585926392</v>
       </c>
       <c r="F80" t="n">
         <v>6518000</v>
@@ -2052,16 +2052,16 @@
         <v>44371</v>
       </c>
       <c r="B82" t="n">
-        <v>16.64640617370605</v>
+        <v>16.64640426635742</v>
       </c>
       <c r="C82" t="n">
-        <v>16.72648245540622</v>
+        <v>16.72648053888243</v>
       </c>
       <c r="D82" t="n">
-        <v>16.39664417817516</v>
+        <v>16.39664229944431</v>
       </c>
       <c r="E82" t="n">
-        <v>16.46909284857351</v>
+        <v>16.46909096154148</v>
       </c>
       <c r="F82" t="n">
         <v>8527500</v>
@@ -2092,16 +2092,16 @@
         <v>44375</v>
       </c>
       <c r="B84" t="n">
-        <v>16.3737621307373</v>
+        <v>16.37376403808594</v>
       </c>
       <c r="C84" t="n">
-        <v>16.37948056539015</v>
+        <v>16.37948247340491</v>
       </c>
       <c r="D84" t="n">
-        <v>15.9390592744375</v>
+        <v>15.93906113114842</v>
       </c>
       <c r="E84" t="n">
-        <v>16.2250482827814</v>
+        <v>16.22505017280664</v>
       </c>
       <c r="F84" t="n">
         <v>6202500</v>
@@ -2152,16 +2152,16 @@
         <v>44378</v>
       </c>
       <c r="B87" t="n">
-        <v>16.35851097106934</v>
+        <v>16.3585090637207</v>
       </c>
       <c r="C87" t="n">
-        <v>16.66356450050222</v>
+        <v>16.66356255758535</v>
       </c>
       <c r="D87" t="n">
-        <v>16.14878712414984</v>
+        <v>16.14878524125432</v>
       </c>
       <c r="E87" t="n">
-        <v>16.66356450050222</v>
+        <v>16.66356255758535</v>
       </c>
       <c r="F87" t="n">
         <v>8503000</v>
@@ -2192,16 +2192,16 @@
         <v>44382</v>
       </c>
       <c r="B89" t="n">
-        <v>16.41570854187012</v>
+        <v>16.41570663452148</v>
       </c>
       <c r="C89" t="n">
-        <v>16.54726347128895</v>
+        <v>16.54726154865489</v>
       </c>
       <c r="D89" t="n">
-        <v>16.25174308313778</v>
+        <v>16.25174119484036</v>
       </c>
       <c r="E89" t="n">
-        <v>16.40808274888606</v>
+        <v>16.40808084242347</v>
       </c>
       <c r="F89" t="n">
         <v>3871000</v>
@@ -2232,16 +2232,16 @@
         <v>44384</v>
       </c>
       <c r="B91" t="n">
-        <v>16.44430541992188</v>
+        <v>16.44430732727051</v>
       </c>
       <c r="C91" t="n">
-        <v>16.58348612054724</v>
+        <v>16.58348804403921</v>
       </c>
       <c r="D91" t="n">
-        <v>16.15069061682722</v>
+        <v>16.15069249011994</v>
       </c>
       <c r="E91" t="n">
-        <v>16.39664149383569</v>
+        <v>16.39664339565586</v>
       </c>
       <c r="F91" t="n">
         <v>12086500</v>
@@ -2252,16 +2252,16 @@
         <v>44385</v>
       </c>
       <c r="B92" t="n">
-        <v>16.43477249145508</v>
+        <v>16.43477439880371</v>
       </c>
       <c r="C92" t="n">
-        <v>16.79893041915436</v>
+        <v>16.79893236876558</v>
       </c>
       <c r="D92" t="n">
-        <v>16.24411496629124</v>
+        <v>16.24411685151298</v>
       </c>
       <c r="E92" t="n">
-        <v>16.26317944602405</v>
+        <v>16.26318133345833</v>
       </c>
       <c r="F92" t="n">
         <v>7435000</v>
@@ -2272,16 +2272,16 @@
         <v>44389</v>
       </c>
       <c r="B93" t="n">
-        <v>16.50150108337402</v>
+        <v>16.50150299072266</v>
       </c>
       <c r="C93" t="n">
-        <v>16.60255099813928</v>
+        <v>16.60255291716791</v>
       </c>
       <c r="D93" t="n">
-        <v>16.27461834177422</v>
+        <v>16.2746202228983</v>
       </c>
       <c r="E93" t="n">
-        <v>16.43095796968715</v>
+        <v>16.43095986888196</v>
       </c>
       <c r="F93" t="n">
         <v>4327500</v>
@@ -2292,16 +2292,16 @@
         <v>44390</v>
       </c>
       <c r="B94" t="n">
-        <v>16.78749084472656</v>
+        <v>16.7874927520752</v>
       </c>
       <c r="C94" t="n">
-        <v>16.91141813862505</v>
+        <v>16.91142006005396</v>
       </c>
       <c r="D94" t="n">
-        <v>16.43095872774974</v>
+        <v>16.43096059459017</v>
       </c>
       <c r="E94" t="n">
-        <v>16.45383792048305</v>
+        <v>16.45383978992295</v>
       </c>
       <c r="F94" t="n">
         <v>6446000</v>
@@ -2312,16 +2312,16 @@
         <v>44391</v>
       </c>
       <c r="B95" t="n">
-        <v>16.7226676940918</v>
+        <v>16.72266578674316</v>
       </c>
       <c r="C95" t="n">
-        <v>17.08873299309478</v>
+        <v>17.08873104399359</v>
       </c>
       <c r="D95" t="n">
-        <v>16.67309640833917</v>
+        <v>16.67309450664453</v>
       </c>
       <c r="E95" t="n">
-        <v>16.9304859864696</v>
+        <v>16.9304840554177</v>
       </c>
       <c r="F95" t="n">
         <v>5548000</v>
@@ -2332,16 +2332,16 @@
         <v>44392</v>
       </c>
       <c r="B96" t="n">
-        <v>16.45002555847168</v>
+        <v>16.45002746582031</v>
       </c>
       <c r="C96" t="n">
-        <v>16.86375476157448</v>
+        <v>16.86375671689422</v>
       </c>
       <c r="D96" t="n">
-        <v>16.44049240966831</v>
+        <v>16.44049431591159</v>
       </c>
       <c r="E96" t="n">
-        <v>16.72266670485169</v>
+        <v>16.72266864381253</v>
       </c>
       <c r="F96" t="n">
         <v>3746000</v>
@@ -2352,16 +2352,16 @@
         <v>44393</v>
       </c>
       <c r="B97" t="n">
-        <v>16.67119026184082</v>
+        <v>16.67119216918945</v>
       </c>
       <c r="C97" t="n">
-        <v>16.86947357936254</v>
+        <v>16.86947550939675</v>
       </c>
       <c r="D97" t="n">
-        <v>16.52247641000283</v>
+        <v>16.52247830033713</v>
       </c>
       <c r="E97" t="n">
-        <v>16.54154088978033</v>
+        <v>16.54154278229579</v>
       </c>
       <c r="F97" t="n">
         <v>7965000</v>
@@ -2372,16 +2372,16 @@
         <v>44396</v>
       </c>
       <c r="B98" t="n">
-        <v>16.65402984619141</v>
+        <v>16.65402793884277</v>
       </c>
       <c r="C98" t="n">
-        <v>16.79702526617702</v>
+        <v>16.79702334245145</v>
       </c>
       <c r="D98" t="n">
-        <v>16.40426788246265</v>
+        <v>16.4042660037187</v>
       </c>
       <c r="E98" t="n">
-        <v>16.58539408105208</v>
+        <v>16.58539218156415</v>
       </c>
       <c r="F98" t="n">
         <v>7763500</v>
@@ -2392,16 +2392,16 @@
         <v>44397</v>
       </c>
       <c r="B99" t="n">
-        <v>16.51103591918945</v>
+        <v>16.51103782653809</v>
       </c>
       <c r="C99" t="n">
-        <v>16.71694684707543</v>
+        <v>16.71694877821082</v>
       </c>
       <c r="D99" t="n">
-        <v>16.45955909634909</v>
+        <v>16.45956099775114</v>
       </c>
       <c r="E99" t="n">
-        <v>16.6540295180957</v>
+        <v>16.6540314419629</v>
       </c>
       <c r="F99" t="n">
         <v>3835500</v>
@@ -2432,16 +2432,16 @@
         <v>44399</v>
       </c>
       <c r="B101" t="n">
-        <v>16.64449501037598</v>
+        <v>16.64449691772461</v>
       </c>
       <c r="C101" t="n">
-        <v>16.68072024642313</v>
+        <v>16.68072215792294</v>
       </c>
       <c r="D101" t="n">
-        <v>16.44430435190125</v>
+        <v>16.44430623630937</v>
       </c>
       <c r="E101" t="n">
-        <v>16.58729793913493</v>
+        <v>16.58729983992916</v>
       </c>
       <c r="F101" t="n">
         <v>2829500</v>
@@ -2492,16 +2492,16 @@
         <v>44404</v>
       </c>
       <c r="B104" t="n">
-        <v>16.96861457824707</v>
+        <v>16.9686164855957</v>
       </c>
       <c r="C104" t="n">
-        <v>17.30036195137194</v>
+        <v>17.30036389601047</v>
       </c>
       <c r="D104" t="n">
-        <v>16.87328673338735</v>
+        <v>16.8732886300207</v>
       </c>
       <c r="E104" t="n">
-        <v>17.14402050381685</v>
+        <v>17.1440224308819</v>
       </c>
       <c r="F104" t="n">
         <v>6666500</v>
@@ -2512,16 +2512,16 @@
         <v>44405</v>
       </c>
       <c r="B105" t="n">
-        <v>16.793212890625</v>
+        <v>16.79321098327637</v>
       </c>
       <c r="C105" t="n">
-        <v>17.38044259996134</v>
+        <v>17.38044062591602</v>
       </c>
       <c r="D105" t="n">
-        <v>16.42333646812846</v>
+        <v>16.42333460278985</v>
       </c>
       <c r="E105" t="n">
-        <v>17.34993760917749</v>
+        <v>17.34993563859687</v>
       </c>
       <c r="F105" t="n">
         <v>14614500</v>
@@ -2552,16 +2552,16 @@
         <v>44407</v>
       </c>
       <c r="B107" t="n">
-        <v>16.52628898620605</v>
+        <v>16.52629089355469</v>
       </c>
       <c r="C107" t="n">
-        <v>16.73219990991705</v>
+        <v>16.73220184103048</v>
       </c>
       <c r="D107" t="n">
-        <v>16.30893755658766</v>
+        <v>16.30893943885111</v>
       </c>
       <c r="E107" t="n">
-        <v>16.62543155217983</v>
+        <v>16.6254334709708</v>
       </c>
       <c r="F107" t="n">
         <v>16469000</v>
@@ -2572,16 +2572,16 @@
         <v>44410</v>
       </c>
       <c r="B108" t="n">
-        <v>16.5224781036377</v>
+        <v>16.52247619628906</v>
       </c>
       <c r="C108" t="n">
-        <v>16.83897031953316</v>
+        <v>16.83896837564879</v>
       </c>
       <c r="D108" t="n">
-        <v>16.36232372925435</v>
+        <v>16.36232184039388</v>
       </c>
       <c r="E108" t="n">
-        <v>16.6826306597586</v>
+        <v>16.68262873392202</v>
       </c>
       <c r="F108" t="n">
         <v>8100500</v>
@@ -2592,16 +2592,16 @@
         <v>44411</v>
       </c>
       <c r="B109" t="n">
-        <v>16.53010368347168</v>
+        <v>16.53010559082031</v>
       </c>
       <c r="C109" t="n">
-        <v>16.68072308765598</v>
+        <v>16.68072501238404</v>
       </c>
       <c r="D109" t="n">
-        <v>16.26127540276083</v>
+        <v>16.26127727909034</v>
       </c>
       <c r="E109" t="n">
-        <v>16.68072308765598</v>
+        <v>16.68072501238404</v>
       </c>
       <c r="F109" t="n">
         <v>5450500</v>
@@ -2632,16 +2632,16 @@
         <v>44413</v>
       </c>
       <c r="B111" t="n">
-        <v>16.58729934692383</v>
+        <v>16.5872974395752</v>
       </c>
       <c r="C111" t="n">
-        <v>16.93811123196384</v>
+        <v>16.93810928427588</v>
       </c>
       <c r="D111" t="n">
-        <v>16.47481073358749</v>
+        <v>16.47480883917376</v>
       </c>
       <c r="E111" t="n">
-        <v>16.59301960001205</v>
+        <v>16.59301769200566</v>
       </c>
       <c r="F111" t="n">
         <v>13427000</v>
@@ -2652,16 +2652,16 @@
         <v>44414</v>
       </c>
       <c r="B112" t="n">
-        <v>16.73982620239258</v>
+        <v>16.73983001708984</v>
       </c>
       <c r="C112" t="n">
-        <v>16.78367905199969</v>
+        <v>16.78368287669021</v>
       </c>
       <c r="D112" t="n">
-        <v>16.37566826999301</v>
+        <v>16.37567200170541</v>
       </c>
       <c r="E112" t="n">
-        <v>16.63115048433273</v>
+        <v>16.63115427426481</v>
       </c>
       <c r="F112" t="n">
         <v>15424500</v>
@@ -2712,16 +2712,16 @@
         <v>44419</v>
       </c>
       <c r="B115" t="n">
-        <v>17.20884895324707</v>
+        <v>17.2088451385498</v>
       </c>
       <c r="C115" t="n">
-        <v>17.57872718168084</v>
+        <v>17.57872328499242</v>
       </c>
       <c r="D115" t="n">
-        <v>17.19741026393275</v>
+        <v>17.1974064517711</v>
       </c>
       <c r="E115" t="n">
-        <v>17.57872718168084</v>
+        <v>17.57872328499242</v>
       </c>
       <c r="F115" t="n">
         <v>6265000</v>
@@ -2752,16 +2752,16 @@
         <v>44421</v>
       </c>
       <c r="B117" t="n">
-        <v>16.91142082214355</v>
+        <v>16.91141891479492</v>
       </c>
       <c r="C117" t="n">
-        <v>17.27367324935177</v>
+        <v>17.27367130114663</v>
       </c>
       <c r="D117" t="n">
-        <v>16.53010391318421</v>
+        <v>16.53010204884227</v>
       </c>
       <c r="E117" t="n">
-        <v>16.82562429034489</v>
+        <v>16.82562239267279</v>
       </c>
       <c r="F117" t="n">
         <v>5547600</v>
@@ -2772,16 +2772,16 @@
         <v>44424</v>
       </c>
       <c r="B118" t="n">
-        <v>16.44430541992188</v>
+        <v>16.44430732727051</v>
       </c>
       <c r="C118" t="n">
-        <v>17.04487925261408</v>
+        <v>17.04488122962231</v>
       </c>
       <c r="D118" t="n">
-        <v>16.27271237679204</v>
+        <v>16.27271426423787</v>
       </c>
       <c r="E118" t="n">
-        <v>16.86375487887679</v>
+        <v>16.86375683487669</v>
       </c>
       <c r="F118" t="n">
         <v>7814500</v>
@@ -2812,16 +2812,16 @@
         <v>44426</v>
       </c>
       <c r="B120" t="n">
-        <v>15.88186264038086</v>
+        <v>15.88186454772949</v>
       </c>
       <c r="C120" t="n">
-        <v>16.30131210662337</v>
+        <v>16.30131406434622</v>
       </c>
       <c r="D120" t="n">
-        <v>15.64353936928479</v>
+        <v>15.64354124801175</v>
       </c>
       <c r="E120" t="n">
-        <v>16.16784983839123</v>
+        <v>16.16785178008579</v>
       </c>
       <c r="F120" t="n">
         <v>10736900</v>
@@ -2852,16 +2852,16 @@
         <v>44428</v>
       </c>
       <c r="B122" t="n">
-        <v>16.94955253601074</v>
+        <v>16.94955444335938</v>
       </c>
       <c r="C122" t="n">
-        <v>17.41666595234703</v>
+        <v>17.41666791226037</v>
       </c>
       <c r="D122" t="n">
-        <v>16.37757629334467</v>
+        <v>16.3775781363283</v>
       </c>
       <c r="E122" t="n">
-        <v>16.53963619846235</v>
+        <v>16.53963805968273</v>
       </c>
       <c r="F122" t="n">
         <v>9513400</v>
@@ -2872,16 +2872,16 @@
         <v>44431</v>
       </c>
       <c r="B123" t="n">
-        <v>16.69216537475586</v>
+        <v>16.69216346740723</v>
       </c>
       <c r="C123" t="n">
-        <v>17.16881200972343</v>
+        <v>17.16881004791025</v>
       </c>
       <c r="D123" t="n">
-        <v>16.52057229524551</v>
+        <v>16.52057040750415</v>
       </c>
       <c r="E123" t="n">
-        <v>16.97815262843136</v>
+        <v>16.97815068840407</v>
       </c>
       <c r="F123" t="n">
         <v>5050600</v>
@@ -2892,16 +2892,16 @@
         <v>44432</v>
       </c>
       <c r="B124" t="n">
-        <v>16.91142082214355</v>
+        <v>16.91141891479492</v>
       </c>
       <c r="C124" t="n">
-        <v>17.05441443572051</v>
+        <v>17.05441251224439</v>
       </c>
       <c r="D124" t="n">
-        <v>16.66356437675437</v>
+        <v>16.66356249736014</v>
       </c>
       <c r="E124" t="n">
-        <v>16.78749350858018</v>
+        <v>16.78749161520865</v>
       </c>
       <c r="F124" t="n">
         <v>4198100</v>
@@ -2912,16 +2912,16 @@
         <v>44433</v>
       </c>
       <c r="B125" t="n">
-        <v>17.01628494262695</v>
+        <v>17.01628303527832</v>
       </c>
       <c r="C125" t="n">
-        <v>17.19741116994805</v>
+        <v>17.19740924229705</v>
       </c>
       <c r="D125" t="n">
-        <v>16.78749477992469</v>
+        <v>16.78749289822105</v>
       </c>
       <c r="E125" t="n">
-        <v>17.0258180933557</v>
+        <v>17.0258161849385</v>
       </c>
       <c r="F125" t="n">
         <v>4269900</v>
@@ -2952,16 +2952,16 @@
         <v>44435</v>
       </c>
       <c r="B127" t="n">
-        <v>16.58729934692383</v>
+        <v>16.5872974395752</v>
       </c>
       <c r="C127" t="n">
-        <v>16.72076161549623</v>
+        <v>16.72075969280097</v>
       </c>
       <c r="D127" t="n">
-        <v>16.39664182051824</v>
+        <v>16.39663993509303</v>
       </c>
       <c r="E127" t="n">
-        <v>16.55870171800724</v>
+        <v>16.558699813947</v>
       </c>
       <c r="F127" t="n">
         <v>5662600</v>
@@ -2972,16 +2972,16 @@
         <v>44438</v>
       </c>
       <c r="B128" t="n">
-        <v>16.35851097106934</v>
+        <v>16.3585090637207</v>
       </c>
       <c r="C128" t="n">
-        <v>16.79702678332595</v>
+        <v>16.79702482484782</v>
       </c>
       <c r="D128" t="n">
-        <v>16.16785160604255</v>
+        <v>16.16784972092418</v>
       </c>
       <c r="E128" t="n">
-        <v>16.4729069537379</v>
+        <v>16.47290503305107</v>
       </c>
       <c r="F128" t="n">
         <v>16747200</v>
@@ -3032,16 +3032,16 @@
         <v>44441</v>
       </c>
       <c r="B131" t="n">
-        <v>16.72076416015625</v>
+        <v>16.72076225280762</v>
       </c>
       <c r="C131" t="n">
-        <v>17.03535085395019</v>
+        <v>17.03534891071645</v>
       </c>
       <c r="D131" t="n">
-        <v>16.10112210481625</v>
+        <v>16.10112026815059</v>
       </c>
       <c r="E131" t="n">
-        <v>16.1678523401267</v>
+        <v>16.16785049584908</v>
       </c>
       <c r="F131" t="n">
         <v>17566400</v>
@@ -3112,16 +3112,16 @@
         <v>44448</v>
       </c>
       <c r="B135" t="n">
-        <v>17.34993553161621</v>
+        <v>17.34993362426758</v>
       </c>
       <c r="C135" t="n">
-        <v>17.44526338911795</v>
+        <v>17.44526147128954</v>
       </c>
       <c r="D135" t="n">
-        <v>16.92095289980908</v>
+        <v>16.92095103962024</v>
       </c>
       <c r="E135" t="n">
-        <v>17.07347965372665</v>
+        <v>17.07347777676993</v>
       </c>
       <c r="F135" t="n">
         <v>12544000</v>
@@ -3132,16 +3132,16 @@
         <v>44449</v>
       </c>
       <c r="B136" t="n">
-        <v>17.33086776733398</v>
+        <v>17.33086967468262</v>
       </c>
       <c r="C136" t="n">
-        <v>17.6073218035846</v>
+        <v>17.60732374135838</v>
       </c>
       <c r="D136" t="n">
-        <v>17.01628113669726</v>
+        <v>17.01628300942406</v>
       </c>
       <c r="E136" t="n">
-        <v>17.33086776733398</v>
+        <v>17.33086967468262</v>
       </c>
       <c r="F136" t="n">
         <v>19125200</v>
@@ -3172,16 +3172,16 @@
         <v>44453</v>
       </c>
       <c r="B138" t="n">
-        <v>17.47386360168457</v>
+        <v>17.4738597869873</v>
       </c>
       <c r="C138" t="n">
-        <v>18.1507026927803</v>
+        <v>18.15069873032314</v>
       </c>
       <c r="D138" t="n">
-        <v>17.3976002213898</v>
+        <v>17.39759642334149</v>
       </c>
       <c r="E138" t="n">
-        <v>17.82658287196191</v>
+        <v>17.82657898026294</v>
       </c>
       <c r="F138" t="n">
         <v>6594500</v>
@@ -3192,16 +3192,16 @@
         <v>44454</v>
       </c>
       <c r="B139" t="n">
-        <v>17.72171783447266</v>
+        <v>17.72171974182129</v>
       </c>
       <c r="C139" t="n">
-        <v>17.82658065116278</v>
+        <v>17.82658256979756</v>
       </c>
       <c r="D139" t="n">
-        <v>17.27367075834045</v>
+        <v>17.27367261746679</v>
       </c>
       <c r="E139" t="n">
-        <v>17.46432827619446</v>
+        <v>17.46433015584083</v>
       </c>
       <c r="F139" t="n">
         <v>8756500</v>
@@ -3212,16 +3212,16 @@
         <v>44455</v>
       </c>
       <c r="B140" t="n">
-        <v>18.26509666442871</v>
+        <v>18.26509857177734</v>
       </c>
       <c r="C140" t="n">
-        <v>18.33182689421092</v>
+        <v>18.33182880852791</v>
       </c>
       <c r="D140" t="n">
-        <v>17.72171985818801</v>
+        <v>17.72172170879404</v>
       </c>
       <c r="E140" t="n">
-        <v>17.72171985818801</v>
+        <v>17.72172170879404</v>
       </c>
       <c r="F140" t="n">
         <v>17281800</v>
@@ -3232,16 +3232,16 @@
         <v>44456</v>
       </c>
       <c r="B141" t="n">
-        <v>18.11256980895996</v>
+        <v>18.11256790161133</v>
       </c>
       <c r="C141" t="n">
-        <v>18.44622277435644</v>
+        <v>18.4462208318724</v>
       </c>
       <c r="D141" t="n">
-        <v>18.11256980895996</v>
+        <v>18.11256790161133</v>
       </c>
       <c r="E141" t="n">
-        <v>18.28416286649314</v>
+        <v>18.28416094107486</v>
       </c>
       <c r="F141" t="n">
         <v>23104900</v>
@@ -3272,16 +3272,16 @@
         <v>44460</v>
       </c>
       <c r="B143" t="n">
-        <v>18.57968330383301</v>
+        <v>18.57968139648438</v>
       </c>
       <c r="C143" t="n">
-        <v>18.7417432123123</v>
+        <v>18.74174128832697</v>
       </c>
       <c r="D143" t="n">
-        <v>17.82658265967325</v>
+        <v>17.82658082963624</v>
       </c>
       <c r="E143" t="n">
-        <v>18.06490594753913</v>
+        <v>18.06490409303639</v>
       </c>
       <c r="F143" t="n">
         <v>17756900</v>
@@ -3352,16 +3352,16 @@
         <v>44466</v>
       </c>
       <c r="B147" t="n">
-        <v>18.35089302062988</v>
+        <v>18.35089492797852</v>
       </c>
       <c r="C147" t="n">
-        <v>18.46528899793678</v>
+        <v>18.46529091717547</v>
       </c>
       <c r="D147" t="n">
-        <v>17.83611385014238</v>
+        <v>17.83611570398607</v>
       </c>
       <c r="E147" t="n">
-        <v>18.01724005660232</v>
+        <v>18.01724192927185</v>
       </c>
       <c r="F147" t="n">
         <v>7788100</v>
@@ -3432,16 +3432,16 @@
         <v>44470</v>
       </c>
       <c r="B151" t="n">
-        <v>18.45575523376465</v>
+        <v>18.45575332641602</v>
       </c>
       <c r="C151" t="n">
-        <v>18.56061623968673</v>
+        <v>18.56061432150102</v>
       </c>
       <c r="D151" t="n">
-        <v>18.00770630734936</v>
+        <v>18.00770444630528</v>
       </c>
       <c r="E151" t="n">
-        <v>18.19836565709148</v>
+        <v>18.19836377634331</v>
       </c>
       <c r="F151" t="n">
         <v>5841800</v>
@@ -3452,16 +3452,16 @@
         <v>44473</v>
       </c>
       <c r="B152" t="n">
-        <v>18.41762733459473</v>
+        <v>18.41762542724609</v>
       </c>
       <c r="C152" t="n">
-        <v>18.49389073029286</v>
+        <v>18.49388881504631</v>
       </c>
       <c r="D152" t="n">
-        <v>18.07444114482175</v>
+        <v>18.07443927301384</v>
       </c>
       <c r="E152" t="n">
-        <v>18.38902969762216</v>
+        <v>18.38902779323513</v>
       </c>
       <c r="F152" t="n">
         <v>9789400</v>
@@ -3472,16 +3472,16 @@
         <v>44474</v>
       </c>
       <c r="B153" t="n">
-        <v>18.32229423522949</v>
+        <v>18.32229232788086</v>
       </c>
       <c r="C153" t="n">
-        <v>18.49388729827244</v>
+        <v>18.49388537306099</v>
       </c>
       <c r="D153" t="n">
-        <v>18.04584015897554</v>
+        <v>18.04583828040574</v>
       </c>
       <c r="E153" t="n">
-        <v>18.34136053518147</v>
+        <v>18.34135862584804</v>
       </c>
       <c r="F153" t="n">
         <v>8000200</v>
@@ -3492,16 +3492,16 @@
         <v>44475</v>
       </c>
       <c r="B154" t="n">
-        <v>18.27167701721191</v>
+        <v>18.27167892456055</v>
       </c>
       <c r="C154" t="n">
-        <v>18.63481622367532</v>
+        <v>18.63481816893143</v>
       </c>
       <c r="D154" t="n">
-        <v>18.06143689840233</v>
+        <v>18.06143878380436</v>
       </c>
       <c r="E154" t="n">
-        <v>18.11877428411284</v>
+        <v>18.11877617550022</v>
       </c>
       <c r="F154" t="n">
         <v>10611600</v>
@@ -3532,16 +3532,16 @@
         <v>44477</v>
       </c>
       <c r="B156" t="n">
-        <v>17.48805618286133</v>
+        <v>17.48805809020996</v>
       </c>
       <c r="C156" t="n">
-        <v>18.32901294579992</v>
+        <v>18.32901494486817</v>
       </c>
       <c r="D156" t="n">
-        <v>17.36382488657761</v>
+        <v>17.36382678037685</v>
       </c>
       <c r="E156" t="n">
-        <v>18.06143546255174</v>
+        <v>18.06143743243643</v>
       </c>
       <c r="F156" t="n">
         <v>14612800</v>
@@ -3552,16 +3552,16 @@
         <v>44480</v>
       </c>
       <c r="B157" t="n">
-        <v>16.62799072265625</v>
+        <v>16.62798690795898</v>
       </c>
       <c r="C157" t="n">
-        <v>17.52628500439614</v>
+        <v>17.5262809836174</v>
       </c>
       <c r="D157" t="n">
-        <v>16.47508980100556</v>
+        <v>16.47508602138593</v>
       </c>
       <c r="E157" t="n">
-        <v>17.42116493724025</v>
+        <v>17.42116094057755</v>
       </c>
       <c r="F157" t="n">
         <v>31512800</v>
@@ -3572,16 +3572,16 @@
         <v>44482</v>
       </c>
       <c r="B158" t="n">
-        <v>17.12491798400879</v>
+        <v>17.12491607666016</v>
       </c>
       <c r="C158" t="n">
-        <v>17.40205019435258</v>
+        <v>17.40204825613737</v>
       </c>
       <c r="D158" t="n">
-        <v>16.62798912502792</v>
+        <v>16.6279872730265</v>
       </c>
       <c r="E158" t="n">
-        <v>16.62798912502792</v>
+        <v>16.6279872730265</v>
       </c>
       <c r="F158" t="n">
         <v>10150700</v>
@@ -3592,16 +3592,16 @@
         <v>44483</v>
       </c>
       <c r="B159" t="n">
-        <v>17.06758308410645</v>
+        <v>17.06757926940918</v>
       </c>
       <c r="C159" t="n">
-        <v>17.14403354871527</v>
+        <v>17.14402971693091</v>
       </c>
       <c r="D159" t="n">
-        <v>16.60887847373064</v>
+        <v>16.60887476155634</v>
       </c>
       <c r="E159" t="n">
-        <v>16.96246301174824</v>
+        <v>16.96245922054588</v>
       </c>
       <c r="F159" t="n">
         <v>10051300</v>
@@ -3632,16 +3632,16 @@
         <v>44487</v>
       </c>
       <c r="B161" t="n">
-        <v>16.20751190185547</v>
+        <v>16.20750999450684</v>
       </c>
       <c r="C161" t="n">
-        <v>16.67577301414236</v>
+        <v>16.67577105168735</v>
       </c>
       <c r="D161" t="n">
-        <v>16.10239365985386</v>
+        <v>16.10239176487586</v>
       </c>
       <c r="E161" t="n">
-        <v>16.58976601986295</v>
+        <v>16.5897640675295</v>
       </c>
       <c r="F161" t="n">
         <v>13070300</v>
@@ -3672,16 +3672,16 @@
         <v>44489</v>
       </c>
       <c r="B163" t="n">
-        <v>15.987717628479</v>
+        <v>15.98771572113037</v>
       </c>
       <c r="C163" t="n">
-        <v>16.21706901380629</v>
+        <v>16.21706707909584</v>
       </c>
       <c r="D163" t="n">
-        <v>15.71058538806291</v>
+        <v>15.71058351377639</v>
       </c>
       <c r="E163" t="n">
-        <v>15.9399367733902</v>
+        <v>15.93993487174186</v>
       </c>
       <c r="F163" t="n">
         <v>11472200</v>
@@ -3692,16 +3692,16 @@
         <v>44490</v>
       </c>
       <c r="B164" t="n">
-        <v>15.70102691650391</v>
+        <v>15.70102882385254</v>
       </c>
       <c r="C164" t="n">
-        <v>16.21706701417989</v>
+        <v>16.21706898421667</v>
       </c>
       <c r="D164" t="n">
-        <v>15.31877465475826</v>
+        <v>15.31877651567118</v>
       </c>
       <c r="E164" t="n">
-        <v>15.81570168366632</v>
+        <v>15.81570360494555</v>
       </c>
       <c r="F164" t="n">
         <v>11995800</v>
@@ -3752,16 +3752,16 @@
         <v>44495</v>
       </c>
       <c r="B167" t="n">
-        <v>15.24232387542725</v>
+        <v>15.24232482910156</v>
       </c>
       <c r="C167" t="n">
-        <v>15.44300654837805</v>
+        <v>15.44300751460859</v>
       </c>
       <c r="D167" t="n">
-        <v>15.0129725095867</v>
+        <v>15.01297344891107</v>
       </c>
       <c r="E167" t="n">
-        <v>15.38566916259858</v>
+        <v>15.38567012524165</v>
       </c>
       <c r="F167" t="n">
         <v>7090300</v>
@@ -3872,16 +3872,16 @@
         <v>44504</v>
       </c>
       <c r="B173" t="n">
-        <v>14.52560043334961</v>
+        <v>14.52560138702393</v>
       </c>
       <c r="C173" t="n">
-        <v>14.73583964480952</v>
+        <v>14.73584061228703</v>
       </c>
       <c r="D173" t="n">
-        <v>14.30580559832982</v>
+        <v>14.30580653757357</v>
       </c>
       <c r="E173" t="n">
-        <v>14.69761441648602</v>
+        <v>14.69761538145387</v>
       </c>
       <c r="F173" t="n">
         <v>4262500</v>
@@ -3972,16 +3972,16 @@
         <v>44511</v>
       </c>
       <c r="B178" t="n">
-        <v>15.19454193115234</v>
+        <v>15.19454288482666</v>
       </c>
       <c r="C178" t="n">
-        <v>15.51945681788442</v>
+        <v>15.51945779195179</v>
       </c>
       <c r="D178" t="n">
-        <v>15.07986624960478</v>
+        <v>15.07986719608156</v>
       </c>
       <c r="E178" t="n">
-        <v>15.43344982888343</v>
+        <v>15.43345079755262</v>
       </c>
       <c r="F178" t="n">
         <v>5555700</v>
@@ -4012,16 +4012,16 @@
         <v>44516</v>
       </c>
       <c r="B180" t="n">
-        <v>14.18157291412354</v>
+        <v>14.18157196044922</v>
       </c>
       <c r="C180" t="n">
-        <v>14.86007137817213</v>
+        <v>14.86007037887054</v>
       </c>
       <c r="D180" t="n">
-        <v>14.00000240201066</v>
+        <v>14.0000014605465</v>
       </c>
       <c r="E180" t="n">
-        <v>14.81228961649183</v>
+        <v>14.81228862040344</v>
       </c>
       <c r="F180" t="n">
         <v>11424100</v>
@@ -4032,16 +4032,16 @@
         <v>44517</v>
       </c>
       <c r="B181" t="n">
-        <v>13.62730884552002</v>
+        <v>13.6273078918457</v>
       </c>
       <c r="C181" t="n">
-        <v>14.42048311764886</v>
+        <v>14.42048210846616</v>
       </c>
       <c r="D181" t="n">
-        <v>13.49352007368859</v>
+        <v>13.49351912937716</v>
       </c>
       <c r="E181" t="n">
-        <v>14.42048311764886</v>
+        <v>14.42048210846616</v>
       </c>
       <c r="F181" t="n">
         <v>10535200</v>
@@ -4052,16 +4052,16 @@
         <v>44518</v>
       </c>
       <c r="B182" t="n">
-        <v>13.35973072052002</v>
+        <v>13.3597297668457</v>
       </c>
       <c r="C182" t="n">
-        <v>13.69420217986363</v>
+        <v>13.69420120231332</v>
       </c>
       <c r="D182" t="n">
-        <v>13.13993586710555</v>
+        <v>13.13993492912112</v>
       </c>
       <c r="E182" t="n">
-        <v>13.65597694834105</v>
+        <v>13.65597597351942</v>
       </c>
       <c r="F182" t="n">
         <v>21252300</v>
@@ -4092,16 +4092,16 @@
         <v>44522</v>
       </c>
       <c r="B184" t="n">
-        <v>13.17815971374512</v>
+        <v>13.17816066741943</v>
       </c>
       <c r="C184" t="n">
-        <v>13.569968523517</v>
+        <v>13.56996950554565</v>
       </c>
       <c r="D184" t="n">
-        <v>13.12082141680619</v>
+        <v>13.12082236633105</v>
       </c>
       <c r="E184" t="n">
-        <v>13.52218676129477</v>
+        <v>13.52218773986557</v>
       </c>
       <c r="F184" t="n">
         <v>12046100</v>
@@ -4132,16 +4132,16 @@
         <v>44524</v>
       </c>
       <c r="B186" t="n">
-        <v>13.11126613616943</v>
+        <v>13.11126708984375</v>
       </c>
       <c r="C186" t="n">
-        <v>13.38839927066881</v>
+        <v>13.38840024450097</v>
       </c>
       <c r="D186" t="n">
-        <v>12.97747738072233</v>
+        <v>12.97747832466525</v>
       </c>
       <c r="E186" t="n">
-        <v>13.09215306623642</v>
+        <v>13.09215401852051</v>
       </c>
       <c r="F186" t="n">
         <v>5705900</v>
@@ -4192,16 +4192,16 @@
         <v>44529</v>
       </c>
       <c r="B189" t="n">
-        <v>12.47099208831787</v>
+        <v>12.47099304199219</v>
       </c>
       <c r="C189" t="n">
-        <v>13.11126530889348</v>
+        <v>13.11126631153039</v>
       </c>
       <c r="D189" t="n">
-        <v>12.42321032786153</v>
+        <v>12.42321127788191</v>
       </c>
       <c r="E189" t="n">
-        <v>12.88191304097531</v>
+        <v>12.88191402607333</v>
       </c>
       <c r="F189" t="n">
         <v>13464500</v>
@@ -4232,16 +4232,16 @@
         <v>44531</v>
       </c>
       <c r="B191" t="n">
-        <v>11.91672706604004</v>
+        <v>11.91672611236572</v>
       </c>
       <c r="C191" t="n">
-        <v>12.37542982579687</v>
+        <v>12.37542883541339</v>
       </c>
       <c r="D191" t="n">
-        <v>11.81160700007474</v>
+        <v>11.81160605481299</v>
       </c>
       <c r="E191" t="n">
-        <v>12.2989793658374</v>
+        <v>12.29897838157211</v>
       </c>
       <c r="F191" t="n">
         <v>5991300</v>
@@ -4252,16 +4252,16 @@
         <v>44532</v>
       </c>
       <c r="B192" t="n">
-        <v>11.89761257171631</v>
+        <v>11.89761447906494</v>
       </c>
       <c r="C192" t="n">
-        <v>12.14607699253434</v>
+        <v>12.14607893971519</v>
       </c>
       <c r="D192" t="n">
-        <v>11.71604297887929</v>
+        <v>11.71604485711986</v>
       </c>
       <c r="E192" t="n">
-        <v>12.14607699253434</v>
+        <v>12.14607893971519</v>
       </c>
       <c r="F192" t="n">
         <v>7306700</v>
@@ -4292,16 +4292,16 @@
         <v>44536</v>
       </c>
       <c r="B194" t="n">
-        <v>13.13993549346924</v>
+        <v>13.13993453979492</v>
       </c>
       <c r="C194" t="n">
-        <v>13.28327987976253</v>
+        <v>13.28327891568452</v>
       </c>
       <c r="D194" t="n">
-        <v>12.77679534865</v>
+        <v>12.77679442133178</v>
       </c>
       <c r="E194" t="n">
-        <v>12.83413364998414</v>
+        <v>12.83413271850441</v>
       </c>
       <c r="F194" t="n">
         <v>6605800</v>
@@ -4332,16 +4332,16 @@
         <v>44538</v>
       </c>
       <c r="B196" t="n">
-        <v>13.75153827667236</v>
+        <v>13.75153923034668</v>
       </c>
       <c r="C196" t="n">
-        <v>14.02867138859101</v>
+        <v>14.02867236148461</v>
       </c>
       <c r="D196" t="n">
-        <v>13.2737225036153</v>
+        <v>13.27372342415291</v>
       </c>
       <c r="E196" t="n">
-        <v>13.42662340517576</v>
+        <v>13.42662433631711</v>
       </c>
       <c r="F196" t="n">
         <v>14295000</v>
@@ -4372,16 +4372,16 @@
         <v>44540</v>
       </c>
       <c r="B198" t="n">
-        <v>13.91399574279785</v>
+        <v>13.91399669647217</v>
       </c>
       <c r="C198" t="n">
-        <v>14.19112885532154</v>
+        <v>14.19112982799074</v>
       </c>
       <c r="D198" t="n">
-        <v>13.74198177248616</v>
+        <v>13.74198271437053</v>
       </c>
       <c r="E198" t="n">
-        <v>13.74198177248616</v>
+        <v>13.74198271437053</v>
       </c>
       <c r="F198" t="n">
         <v>8247400</v>
@@ -4452,16 +4452,16 @@
         <v>44546</v>
       </c>
       <c r="B202" t="n">
-        <v>13.89488410949707</v>
+        <v>13.89488506317139</v>
       </c>
       <c r="C202" t="n">
-        <v>14.28669293890897</v>
+        <v>14.28669391947506</v>
       </c>
       <c r="D202" t="n">
-        <v>13.82799018584958</v>
+        <v>13.82799113493264</v>
       </c>
       <c r="E202" t="n">
-        <v>14.21024248006574</v>
+        <v>14.21024345538466</v>
       </c>
       <c r="F202" t="n">
         <v>5287600</v>
@@ -4472,16 +4472,16 @@
         <v>44547</v>
       </c>
       <c r="B203" t="n">
-        <v>13.818434715271</v>
+        <v>13.81843280792236</v>
       </c>
       <c r="C203" t="n">
-        <v>14.00956087710406</v>
+        <v>14.00955894337442</v>
       </c>
       <c r="D203" t="n">
-        <v>13.64642071394053</v>
+        <v>13.64641883033486</v>
       </c>
       <c r="E203" t="n">
-        <v>13.8471034117056</v>
+        <v>13.84710150039985</v>
       </c>
       <c r="F203" t="n">
         <v>8250000</v>
@@ -4492,16 +4492,16 @@
         <v>44550</v>
       </c>
       <c r="B204" t="n">
-        <v>13.47440719604492</v>
+        <v>13.47440624237061</v>
       </c>
       <c r="C204" t="n">
-        <v>13.8662160431998</v>
+        <v>13.86621506179454</v>
       </c>
       <c r="D204" t="n">
-        <v>13.29283666454885</v>
+        <v>13.29283572372549</v>
       </c>
       <c r="E204" t="n">
-        <v>13.81843427641866</v>
+        <v>13.81843329839523</v>
       </c>
       <c r="F204" t="n">
         <v>6680500</v>
@@ -4512,16 +4512,16 @@
         <v>44551</v>
       </c>
       <c r="B205" t="n">
-        <v>13.617751121521</v>
+        <v>13.61775016784668</v>
       </c>
       <c r="C205" t="n">
-        <v>13.6655328866758</v>
+        <v>13.66553192965524</v>
       </c>
       <c r="D205" t="n">
-        <v>13.36928667180511</v>
+        <v>13.36928573553119</v>
       </c>
       <c r="E205" t="n">
-        <v>13.48396236135982</v>
+        <v>13.48396141705496</v>
       </c>
       <c r="F205" t="n">
         <v>4083800</v>
@@ -4552,16 +4552,16 @@
         <v>44553</v>
       </c>
       <c r="B207" t="n">
-        <v>13.4648494720459</v>
+        <v>13.46484851837158</v>
       </c>
       <c r="C207" t="n">
-        <v>13.65597561094082</v>
+        <v>13.65597464372962</v>
       </c>
       <c r="D207" t="n">
-        <v>13.32150418435372</v>
+        <v>13.32150324083211</v>
       </c>
       <c r="E207" t="n">
-        <v>13.41706770948184</v>
+        <v>13.41706675919176</v>
       </c>
       <c r="F207" t="n">
         <v>4198000</v>
@@ -4572,16 +4572,16 @@
         <v>44557</v>
       </c>
       <c r="B208" t="n">
-        <v>13.03481578826904</v>
+        <v>13.03481483459473</v>
       </c>
       <c r="C208" t="n">
-        <v>13.56041245676783</v>
+        <v>13.56041146463896</v>
       </c>
       <c r="D208" t="n">
-        <v>12.90102703170205</v>
+        <v>12.9010260878162</v>
       </c>
       <c r="E208" t="n">
-        <v>13.46484984038684</v>
+        <v>13.46484885524968</v>
       </c>
       <c r="F208" t="n">
         <v>14666400</v>
@@ -4692,16 +4692,16 @@
         <v>44566</v>
       </c>
       <c r="B214" t="n">
-        <v>11.45802211761475</v>
+        <v>11.45802307128906</v>
       </c>
       <c r="C214" t="n">
-        <v>12.13652055763904</v>
+        <v>12.13652156778615</v>
       </c>
       <c r="D214" t="n">
-        <v>11.41024035762631</v>
+        <v>11.41024130732365</v>
       </c>
       <c r="E214" t="n">
-        <v>12.11740840046043</v>
+        <v>12.1174094090168</v>
       </c>
       <c r="F214" t="n">
         <v>11220000</v>
@@ -4732,16 +4732,16 @@
         <v>44568</v>
       </c>
       <c r="B216" t="n">
-        <v>10.85597515106201</v>
+        <v>10.85597610473633</v>
       </c>
       <c r="C216" t="n">
-        <v>11.11399613247418</v>
+        <v>11.11399710881509</v>
       </c>
       <c r="D216" t="n">
-        <v>10.71263076896282</v>
+        <v>10.71263171004464</v>
       </c>
       <c r="E216" t="n">
-        <v>11.0088769796922</v>
+        <v>11.00887794679861</v>
       </c>
       <c r="F216" t="n">
         <v>11641900</v>
@@ -4752,16 +4752,16 @@
         <v>44571</v>
       </c>
       <c r="B217" t="n">
-        <v>10.79863739013672</v>
+        <v>10.7986364364624</v>
       </c>
       <c r="C217" t="n">
-        <v>10.8559747764533</v>
+        <v>10.85597381771528</v>
       </c>
       <c r="D217" t="n">
-        <v>10.54061641762812</v>
+        <v>10.54061548674074</v>
       </c>
       <c r="E217" t="n">
-        <v>10.76041216213855</v>
+        <v>10.76041121184007</v>
       </c>
       <c r="F217" t="n">
         <v>8755800</v>
@@ -4812,16 +4812,16 @@
         <v>44574</v>
       </c>
       <c r="B220" t="n">
-        <v>11.48669338226318</v>
+        <v>11.48669147491455</v>
       </c>
       <c r="C220" t="n">
-        <v>11.57269946905179</v>
+        <v>11.57269754742197</v>
       </c>
       <c r="D220" t="n">
-        <v>11.15222192531568</v>
+        <v>11.15222007350554</v>
       </c>
       <c r="E220" t="n">
-        <v>11.27645415471443</v>
+        <v>11.27645228227571</v>
       </c>
       <c r="F220" t="n">
         <v>9668300</v>
@@ -4832,16 +4832,16 @@
         <v>44575</v>
       </c>
       <c r="B221" t="n">
-        <v>11.59181118011475</v>
+        <v>11.59181213378906</v>
       </c>
       <c r="C221" t="n">
-        <v>11.65870509911001</v>
+        <v>11.65870605828779</v>
       </c>
       <c r="D221" t="n">
-        <v>11.39112851176765</v>
+        <v>11.39112944893152</v>
       </c>
       <c r="E221" t="n">
-        <v>11.4102406694686</v>
+        <v>11.41024160820486</v>
       </c>
       <c r="F221" t="n">
         <v>7586600</v>
@@ -4872,16 +4872,16 @@
         <v>44579</v>
       </c>
       <c r="B223" t="n">
-        <v>11.3911304473877</v>
+        <v>11.39112949371338</v>
       </c>
       <c r="C223" t="n">
-        <v>11.49624961100837</v>
+        <v>11.49624864853339</v>
       </c>
       <c r="D223" t="n">
-        <v>11.29556690856058</v>
+        <v>11.29556596288691</v>
       </c>
       <c r="E223" t="n">
-        <v>11.47713745005981</v>
+        <v>11.47713648918492</v>
       </c>
       <c r="F223" t="n">
         <v>7771300</v>
@@ -4912,16 +4912,16 @@
         <v>44581</v>
       </c>
       <c r="B225" t="n">
-        <v>11.41979789733887</v>
+        <v>11.41979885101318</v>
       </c>
       <c r="C225" t="n">
-        <v>11.69693103603816</v>
+        <v>11.69693201285603</v>
       </c>
       <c r="D225" t="n">
-        <v>11.36246050939355</v>
+        <v>11.36246145827959</v>
       </c>
       <c r="E225" t="n">
-        <v>11.56314318992485</v>
+        <v>11.56314415557002</v>
       </c>
       <c r="F225" t="n">
         <v>7365800</v>
@@ -4932,16 +4932,16 @@
         <v>44582</v>
       </c>
       <c r="B226" t="n">
-        <v>11.48669338226318</v>
+        <v>11.48669147491455</v>
       </c>
       <c r="C226" t="n">
-        <v>11.6300377716056</v>
+        <v>11.63003584045484</v>
       </c>
       <c r="D226" t="n">
-        <v>11.21911585216062</v>
+        <v>11.21911398924284</v>
       </c>
       <c r="E226" t="n">
-        <v>11.37201677715557</v>
+        <v>11.37201488884882</v>
       </c>
       <c r="F226" t="n">
         <v>8537100</v>
@@ -4952,16 +4952,16 @@
         <v>44585</v>
       </c>
       <c r="B227" t="n">
-        <v>11.50580501556396</v>
+        <v>11.50580406188965</v>
       </c>
       <c r="C227" t="n">
-        <v>11.63959377449148</v>
+        <v>11.6395928097279</v>
       </c>
       <c r="D227" t="n">
-        <v>11.3242354032836</v>
+        <v>11.32423446465893</v>
       </c>
       <c r="E227" t="n">
-        <v>11.46757978606487</v>
+        <v>11.4675788355589</v>
       </c>
       <c r="F227" t="n">
         <v>6551900</v>
@@ -5012,16 +5012,16 @@
         <v>44588</v>
       </c>
       <c r="B230" t="n">
-        <v>11.99317646026611</v>
+        <v>11.99317741394043</v>
       </c>
       <c r="C230" t="n">
-        <v>12.13652083211196</v>
+        <v>12.13652179718475</v>
       </c>
       <c r="D230" t="n">
-        <v>11.66826157863015</v>
+        <v>11.66826250646786</v>
       </c>
       <c r="E230" t="n">
-        <v>11.85938771154504</v>
+        <v>11.85938865458074</v>
       </c>
       <c r="F230" t="n">
         <v>13761300</v>
@@ -5032,16 +5032,16 @@
         <v>44589</v>
       </c>
       <c r="B231" t="n">
-        <v>11.83071994781494</v>
+        <v>11.83072090148926</v>
       </c>
       <c r="C231" t="n">
-        <v>12.04095916619962</v>
+        <v>12.04096013682132</v>
       </c>
       <c r="D231" t="n">
-        <v>11.4580232758641</v>
+        <v>11.45802419949534</v>
       </c>
       <c r="E231" t="n">
-        <v>11.94539563656258</v>
+        <v>11.9453965994809</v>
       </c>
       <c r="F231" t="n">
         <v>14924100</v>
@@ -5072,16 +5072,16 @@
         <v>44593</v>
       </c>
       <c r="B233" t="n">
-        <v>12.0218448638916</v>
+        <v>12.02184581756592</v>
       </c>
       <c r="C233" t="n">
-        <v>12.09829531522309</v>
+        <v>12.0982962749621</v>
       </c>
       <c r="D233" t="n">
-        <v>11.83071873556289</v>
+        <v>11.83071967407547</v>
       </c>
       <c r="E233" t="n">
-        <v>11.93583787830337</v>
+        <v>11.93583882515488</v>
       </c>
       <c r="F233" t="n">
         <v>5991900</v>
@@ -5092,16 +5092,16 @@
         <v>44594</v>
       </c>
       <c r="B234" t="n">
-        <v>11.94539451599121</v>
+        <v>11.94539356231689</v>
       </c>
       <c r="C234" t="n">
-        <v>12.27986592698347</v>
+        <v>12.27986494660625</v>
       </c>
       <c r="D234" t="n">
-        <v>11.81160576932205</v>
+        <v>11.81160482632891</v>
       </c>
       <c r="E234" t="n">
-        <v>12.02184496798465</v>
+        <v>12.02184400820683</v>
       </c>
       <c r="F234" t="n">
         <v>9442200</v>
@@ -5112,16 +5112,16 @@
         <v>44595</v>
       </c>
       <c r="B235" t="n">
-        <v>11.94539451599121</v>
+        <v>11.94539356231689</v>
       </c>
       <c r="C235" t="n">
-        <v>12.21297109796826</v>
+        <v>12.21297012293166</v>
       </c>
       <c r="D235" t="n">
-        <v>11.89761275565499</v>
+        <v>11.89761180579539</v>
       </c>
       <c r="E235" t="n">
-        <v>12.04095803666365</v>
+        <v>12.04095707535991</v>
       </c>
       <c r="F235" t="n">
         <v>8796800</v>
@@ -5132,16 +5132,16 @@
         <v>44596</v>
       </c>
       <c r="B236" t="n">
-        <v>12.32764720916748</v>
+        <v>12.3276481628418</v>
       </c>
       <c r="C236" t="n">
-        <v>12.32764720916748</v>
+        <v>12.3276481628418</v>
       </c>
       <c r="D236" t="n">
-        <v>11.56314266236741</v>
+        <v>11.56314355689919</v>
       </c>
       <c r="E236" t="n">
-        <v>11.91672624310277</v>
+        <v>11.91672716498799</v>
       </c>
       <c r="F236" t="n">
         <v>17676100</v>
@@ -5152,16 +5152,16 @@
         <v>44599</v>
       </c>
       <c r="B237" t="n">
-        <v>12.20341682434082</v>
+        <v>12.2034158706665</v>
       </c>
       <c r="C237" t="n">
-        <v>12.60478128600524</v>
+        <v>12.60478030096504</v>
       </c>
       <c r="D237" t="n">
-        <v>12.20341682434082</v>
+        <v>12.2034158706665</v>
       </c>
       <c r="E237" t="n">
-        <v>12.29897944421849</v>
+        <v>12.29897848307614</v>
       </c>
       <c r="F237" t="n">
         <v>7212000</v>
@@ -5252,16 +5252,16 @@
         <v>44606</v>
       </c>
       <c r="B242" t="n">
-        <v>11.78293800354004</v>
+        <v>11.78293704986572</v>
       </c>
       <c r="C242" t="n">
-        <v>11.97406414854188</v>
+        <v>11.97406317939841</v>
       </c>
       <c r="D242" t="n">
-        <v>11.639593622629</v>
+        <v>11.63959268055653</v>
       </c>
       <c r="E242" t="n">
-        <v>11.79249453863047</v>
+        <v>11.79249358418268</v>
       </c>
       <c r="F242" t="n">
         <v>5445000</v>
@@ -5272,16 +5272,16 @@
         <v>44607</v>
       </c>
       <c r="B243" t="n">
-        <v>11.63959407806396</v>
+        <v>11.63959312438965</v>
       </c>
       <c r="C243" t="n">
-        <v>11.95495245749671</v>
+        <v>11.95495147798393</v>
       </c>
       <c r="D243" t="n">
-        <v>11.5344740106788</v>
+        <v>11.53447306561735</v>
       </c>
       <c r="E243" t="n">
-        <v>11.92628285110363</v>
+        <v>11.92628187393986</v>
       </c>
       <c r="F243" t="n">
         <v>11329100</v>
@@ -5292,16 +5292,16 @@
         <v>44608</v>
       </c>
       <c r="B244" t="n">
-        <v>12.47099208831787</v>
+        <v>12.47099304199219</v>
       </c>
       <c r="C244" t="n">
-        <v>12.6430051500549</v>
+        <v>12.6430061168833</v>
       </c>
       <c r="D244" t="n">
-        <v>11.56314228509255</v>
+        <v>11.56314316934232</v>
       </c>
       <c r="E244" t="n">
-        <v>11.65870489464395</v>
+        <v>11.65870578620152</v>
       </c>
       <c r="F244" t="n">
         <v>21489000</v>
@@ -5312,16 +5312,16 @@
         <v>44609</v>
       </c>
       <c r="B245" t="n">
-        <v>12.66211986541748</v>
+        <v>12.66211795806885</v>
       </c>
       <c r="C245" t="n">
-        <v>12.94880955407657</v>
+        <v>12.94880760354266</v>
       </c>
       <c r="D245" t="n">
-        <v>12.46143717449226</v>
+        <v>12.46143529737331</v>
       </c>
       <c r="E245" t="n">
-        <v>12.46143717449226</v>
+        <v>12.46143529737331</v>
       </c>
       <c r="F245" t="n">
         <v>10362100</v>
@@ -5332,16 +5332,16 @@
         <v>44610</v>
       </c>
       <c r="B246" t="n">
-        <v>12.13652229309082</v>
+        <v>12.1365213394165</v>
       </c>
       <c r="C246" t="n">
-        <v>12.83413390140938</v>
+        <v>12.83413289291753</v>
       </c>
       <c r="D246" t="n">
-        <v>12.13652229309082</v>
+        <v>12.1365213394165</v>
       </c>
       <c r="E246" t="n">
-        <v>12.80546429449997</v>
+        <v>12.80546328826094</v>
       </c>
       <c r="F246" t="n">
         <v>11604500</v>
@@ -5392,16 +5392,16 @@
         <v>44615</v>
       </c>
       <c r="B249" t="n">
-        <v>12.73856830596924</v>
+        <v>12.73857021331787</v>
       </c>
       <c r="C249" t="n">
-        <v>12.87235704914128</v>
+        <v>12.87235897652213</v>
       </c>
       <c r="D249" t="n">
-        <v>12.51877349007365</v>
+        <v>12.51877536451236</v>
       </c>
       <c r="E249" t="n">
-        <v>12.51877349007365</v>
+        <v>12.51877536451236</v>
       </c>
       <c r="F249" t="n">
         <v>5598100</v>
@@ -5452,16 +5452,16 @@
         <v>44622</v>
       </c>
       <c r="B252" t="n">
-        <v>12.68123245239258</v>
+        <v>12.68123149871826</v>
       </c>
       <c r="C252" t="n">
-        <v>12.95836559486294</v>
+        <v>12.95836462034722</v>
       </c>
       <c r="D252" t="n">
-        <v>12.64300631142708</v>
+        <v>12.6430053606275</v>
       </c>
       <c r="E252" t="n">
-        <v>12.86280206517191</v>
+        <v>12.8628010978429</v>
       </c>
       <c r="F252" t="n">
         <v>4196000</v>
@@ -5592,16 +5592,16 @@
         <v>44631</v>
       </c>
       <c r="B259" t="n">
-        <v>12.40409851074219</v>
+        <v>12.40409755706787</v>
       </c>
       <c r="C259" t="n">
-        <v>12.9296961060736</v>
+        <v>12.92969511198934</v>
       </c>
       <c r="D259" t="n">
-        <v>12.20341673702652</v>
+        <v>12.20341579878139</v>
       </c>
       <c r="E259" t="n">
-        <v>12.9296961060736</v>
+        <v>12.92969511198934</v>
       </c>
       <c r="F259" t="n">
         <v>7293900</v>
@@ -5632,16 +5632,16 @@
         <v>44635</v>
       </c>
       <c r="B261" t="n">
-        <v>12.82457447052002</v>
+        <v>12.82457542419434</v>
       </c>
       <c r="C261" t="n">
-        <v>12.90102491562967</v>
+        <v>12.90102587498907</v>
       </c>
       <c r="D261" t="n">
-        <v>12.29897697687028</v>
+        <v>12.29897789145957</v>
       </c>
       <c r="E261" t="n">
-        <v>12.29897697687028</v>
+        <v>12.29897789145957</v>
       </c>
       <c r="F261" t="n">
         <v>8181800</v>
@@ -5772,16 +5772,16 @@
         <v>44644</v>
       </c>
       <c r="B268" t="n">
-        <v>14.63071918487549</v>
+        <v>14.63072109222412</v>
       </c>
       <c r="C268" t="n">
-        <v>14.7453948595791</v>
+        <v>14.74539678187754</v>
       </c>
       <c r="D268" t="n">
-        <v>14.35358607650145</v>
+        <v>14.35358794772134</v>
       </c>
       <c r="E268" t="n">
-        <v>14.39181130140265</v>
+        <v>14.39181317760581</v>
       </c>
       <c r="F268" t="n">
         <v>7986800</v>
@@ -5792,16 +5792,16 @@
         <v>44645</v>
       </c>
       <c r="B269" t="n">
-        <v>15.13720512390137</v>
+        <v>15.13720417022705</v>
       </c>
       <c r="C269" t="n">
-        <v>15.24232427482575</v>
+        <v>15.24232331452872</v>
       </c>
       <c r="D269" t="n">
-        <v>14.64027624019771</v>
+        <v>14.64027531783091</v>
       </c>
       <c r="E269" t="n">
-        <v>14.71672669748114</v>
+        <v>14.71672577029781</v>
       </c>
       <c r="F269" t="n">
         <v>8426200</v>
@@ -5812,16 +5812,16 @@
         <v>44648</v>
       </c>
       <c r="B270" t="n">
-        <v>15.51945686340332</v>
+        <v>15.519455909729</v>
       </c>
       <c r="C270" t="n">
-        <v>15.7774778311631</v>
+        <v>15.77747686163333</v>
       </c>
       <c r="D270" t="n">
-        <v>14.97474714661442</v>
+        <v>14.97474622641265</v>
       </c>
       <c r="E270" t="n">
-        <v>15.19454197571826</v>
+        <v>15.19454104201004</v>
       </c>
       <c r="F270" t="n">
         <v>14496800</v>
@@ -5832,16 +5832,16 @@
         <v>44649</v>
       </c>
       <c r="B271" t="n">
-        <v>15.50034427642822</v>
+        <v>15.50034236907959</v>
       </c>
       <c r="C271" t="n">
-        <v>15.93037923607671</v>
+        <v>15.93037727581141</v>
       </c>
       <c r="D271" t="n">
-        <v>15.43345035442127</v>
+        <v>15.43344845530407</v>
       </c>
       <c r="E271" t="n">
-        <v>15.72969564733319</v>
+        <v>15.72969371176241</v>
       </c>
       <c r="F271" t="n">
         <v>7323700</v>
@@ -5852,16 +5852,16 @@
         <v>44650</v>
       </c>
       <c r="B272" t="n">
-        <v>15.45256423950195</v>
+        <v>15.45256328582764</v>
       </c>
       <c r="C272" t="n">
-        <v>15.82526000904275</v>
+        <v>15.82525903236704</v>
       </c>
       <c r="D272" t="n">
-        <v>15.3952268494317</v>
+        <v>15.39522589929603</v>
       </c>
       <c r="E272" t="n">
-        <v>15.51945816503771</v>
+        <v>15.51945720723495</v>
       </c>
       <c r="F272" t="n">
         <v>8944100</v>
@@ -5932,16 +5932,16 @@
         <v>44656</v>
       </c>
       <c r="B276" t="n">
-        <v>15.45256423950195</v>
+        <v>15.45256328582764</v>
       </c>
       <c r="C276" t="n">
-        <v>15.65324601610922</v>
+        <v>15.65324505004958</v>
       </c>
       <c r="D276" t="n">
-        <v>15.35700070756969</v>
+        <v>15.35699975979319</v>
       </c>
       <c r="E276" t="n">
-        <v>15.57679555510796</v>
+        <v>15.57679459376655</v>
       </c>
       <c r="F276" t="n">
         <v>10716200</v>
@@ -5972,16 +5972,16 @@
         <v>44658</v>
       </c>
       <c r="B278" t="n">
-        <v>15.38566970825195</v>
+        <v>15.38567066192627</v>
       </c>
       <c r="C278" t="n">
-        <v>15.52901408914568</v>
+        <v>15.52901505170514</v>
       </c>
       <c r="D278" t="n">
-        <v>15.25188095108615</v>
+        <v>15.25188189646763</v>
       </c>
       <c r="E278" t="n">
-        <v>15.3665566380734</v>
+        <v>15.366557590563</v>
       </c>
       <c r="F278" t="n">
         <v>6566700</v>
@@ -5992,16 +5992,16 @@
         <v>44659</v>
       </c>
       <c r="B279" t="n">
-        <v>15.40478134155273</v>
+        <v>15.40478420257568</v>
       </c>
       <c r="C279" t="n">
-        <v>15.5767934889472</v>
+        <v>15.57679638191676</v>
       </c>
       <c r="D279" t="n">
-        <v>15.07030993551665</v>
+        <v>15.07031273442055</v>
       </c>
       <c r="E279" t="n">
-        <v>15.32833089069213</v>
+        <v>15.32833373751647</v>
       </c>
       <c r="F279" t="n">
         <v>3069100</v>
@@ -6012,16 +6012,16 @@
         <v>44662</v>
       </c>
       <c r="B280" t="n">
-        <v>15.29010581970215</v>
+        <v>15.29010486602783</v>
       </c>
       <c r="C280" t="n">
-        <v>15.49078758367887</v>
+        <v>15.49078661748763</v>
       </c>
       <c r="D280" t="n">
-        <v>15.21365536351254</v>
+        <v>15.21365441460659</v>
       </c>
       <c r="E280" t="n">
-        <v>15.38566934561982</v>
+        <v>15.38566838598501</v>
       </c>
       <c r="F280" t="n">
         <v>10289300</v>
@@ -6032,16 +6032,16 @@
         <v>44663</v>
       </c>
       <c r="B281" t="n">
-        <v>15.72014236450195</v>
+        <v>15.72014045715332</v>
       </c>
       <c r="C281" t="n">
-        <v>15.82526061318996</v>
+        <v>15.82525869308717</v>
       </c>
       <c r="D281" t="n">
-        <v>15.39522743716192</v>
+        <v>15.3952255692357</v>
       </c>
       <c r="E281" t="n">
-        <v>15.48123443691209</v>
+        <v>15.48123255855052</v>
       </c>
       <c r="F281" t="n">
         <v>9798400</v>
@@ -6072,16 +6072,16 @@
         <v>44665</v>
       </c>
       <c r="B283" t="n">
-        <v>15.64369010925293</v>
+        <v>15.64368915557861</v>
       </c>
       <c r="C283" t="n">
-        <v>15.79659101958422</v>
+        <v>15.79659005658872</v>
       </c>
       <c r="D283" t="n">
-        <v>15.4812326641856</v>
+        <v>15.48123172041506</v>
       </c>
       <c r="E283" t="n">
-        <v>15.72014056441858</v>
+        <v>15.72013960608367</v>
       </c>
       <c r="F283" t="n">
         <v>4607000</v>
@@ -6092,16 +6092,16 @@
         <v>44669</v>
       </c>
       <c r="B284" t="n">
-        <v>15.31877517700195</v>
+        <v>15.31877422332764</v>
       </c>
       <c r="C284" t="n">
-        <v>15.67235784764996</v>
+        <v>15.67235687196327</v>
       </c>
       <c r="D284" t="n">
-        <v>15.31877517700195</v>
+        <v>15.31877422332764</v>
       </c>
       <c r="E284" t="n">
-        <v>15.56723961128785</v>
+        <v>15.56723864214531</v>
       </c>
       <c r="F284" t="n">
         <v>3539900</v>
@@ -6152,16 +6152,16 @@
         <v>44673</v>
       </c>
       <c r="B287" t="n">
-        <v>15.31877517700195</v>
+        <v>15.31877422332764</v>
       </c>
       <c r="C287" t="n">
-        <v>15.74880830260542</v>
+        <v>15.74880732215928</v>
       </c>
       <c r="D287" t="n">
-        <v>15.14676119767152</v>
+        <v>15.14676025470597</v>
       </c>
       <c r="E287" t="n">
-        <v>15.74880830260542</v>
+        <v>15.74880732215928</v>
       </c>
       <c r="F287" t="n">
         <v>8878800</v>
@@ -6292,16 +6292,16 @@
         <v>44684</v>
       </c>
       <c r="B294" t="n">
-        <v>14.62423324584961</v>
+        <v>14.62423419952393</v>
       </c>
       <c r="C294" t="n">
-        <v>14.85544619454671</v>
+        <v>14.85544716329886</v>
       </c>
       <c r="D294" t="n">
-        <v>14.47972446384498</v>
+        <v>14.4797254080956</v>
       </c>
       <c r="E294" t="n">
-        <v>14.70130422874864</v>
+        <v>14.70130518744891</v>
       </c>
       <c r="F294" t="n">
         <v>5388000</v>
@@ -6372,16 +6372,16 @@
         <v>44690</v>
       </c>
       <c r="B298" t="n">
-        <v>14.21961212158203</v>
+        <v>14.21961116790771</v>
       </c>
       <c r="C298" t="n">
-        <v>14.32558450824887</v>
+        <v>14.32558354746724</v>
       </c>
       <c r="D298" t="n">
-        <v>13.92096133187191</v>
+        <v>13.92096039822737</v>
       </c>
       <c r="E298" t="n">
-        <v>14.04620192634656</v>
+        <v>14.04620098430244</v>
       </c>
       <c r="F298" t="n">
         <v>11844800</v>
@@ -6452,16 +6452,16 @@
         <v>44694</v>
       </c>
       <c r="B302" t="n">
-        <v>14.91324996948242</v>
+        <v>14.91324901580811</v>
       </c>
       <c r="C302" t="n">
-        <v>15.09629425517541</v>
+        <v>15.09629328979575</v>
       </c>
       <c r="D302" t="n">
-        <v>14.62423422366596</v>
+        <v>14.62423328847366</v>
       </c>
       <c r="E302" t="n">
-        <v>14.7205724993519</v>
+        <v>14.72057155799894</v>
       </c>
       <c r="F302" t="n">
         <v>5016200</v>
@@ -6472,16 +6472,16 @@
         <v>44697</v>
       </c>
       <c r="B303" t="n">
-        <v>14.80727577209473</v>
+        <v>14.80727672576904</v>
       </c>
       <c r="C303" t="n">
-        <v>14.93251634198823</v>
+        <v>14.93251730372877</v>
       </c>
       <c r="D303" t="n">
-        <v>14.64349971290772</v>
+        <v>14.64350065603391</v>
       </c>
       <c r="E303" t="n">
-        <v>14.93251634198823</v>
+        <v>14.93251730372877</v>
       </c>
       <c r="F303" t="n">
         <v>6824600</v>
@@ -6532,16 +6532,16 @@
         <v>44700</v>
       </c>
       <c r="B306" t="n">
-        <v>14.88434791564941</v>
+        <v>14.88434886932373</v>
       </c>
       <c r="C306" t="n">
-        <v>14.95178571626016</v>
+        <v>14.95178667425537</v>
       </c>
       <c r="D306" t="n">
-        <v>14.6627690645589</v>
+        <v>14.66277000403615</v>
       </c>
       <c r="E306" t="n">
-        <v>14.92288340795901</v>
+        <v>14.92288436410238</v>
       </c>
       <c r="F306" t="n">
         <v>6219800</v>
@@ -6552,16 +6552,16 @@
         <v>44701</v>
       </c>
       <c r="B307" t="n">
-        <v>15.37567710876465</v>
+        <v>15.37567615509033</v>
       </c>
       <c r="C307" t="n">
-        <v>15.49128359304003</v>
+        <v>15.49128263219524</v>
       </c>
       <c r="D307" t="n">
-        <v>14.93251845966301</v>
+        <v>14.93251753347555</v>
       </c>
       <c r="E307" t="n">
-        <v>15.0288576559385</v>
+        <v>15.02885672377561</v>
       </c>
       <c r="F307" t="n">
         <v>8142900</v>
@@ -6752,16 +6752,16 @@
         <v>44715</v>
       </c>
       <c r="B317" t="n">
-        <v>14.88434791564941</v>
+        <v>14.88434886932373</v>
       </c>
       <c r="C317" t="n">
-        <v>15.23116826519437</v>
+        <v>15.23116924109026</v>
       </c>
       <c r="D317" t="n">
-        <v>14.78800964425473</v>
+        <v>14.78801059175644</v>
       </c>
       <c r="E317" t="n">
-        <v>15.17336456735067</v>
+        <v>15.17336553954295</v>
       </c>
       <c r="F317" t="n">
         <v>4184100</v>
@@ -6852,16 +6852,16 @@
         <v>44722</v>
       </c>
       <c r="B322" t="n">
-        <v>14.48935985565186</v>
+        <v>14.48935890197754</v>
       </c>
       <c r="C322" t="n">
-        <v>15.01922359929862</v>
+        <v>15.01922261074923</v>
       </c>
       <c r="D322" t="n">
-        <v>14.22924549491244</v>
+        <v>14.22924455835858</v>
       </c>
       <c r="E322" t="n">
-        <v>14.85544751637582</v>
+        <v>14.85544653860601</v>
       </c>
       <c r="F322" t="n">
         <v>15101900</v>
@@ -6912,16 +6912,16 @@
         <v>44727</v>
       </c>
       <c r="B325" t="n">
-        <v>14.91324996948242</v>
+        <v>14.91324901580811</v>
       </c>
       <c r="C325" t="n">
-        <v>15.06739286434549</v>
+        <v>15.06739190081403</v>
       </c>
       <c r="D325" t="n">
-        <v>14.25814657103863</v>
+        <v>14.25814565925695</v>
       </c>
       <c r="E325" t="n">
-        <v>14.34485166228703</v>
+        <v>14.34485074496072</v>
       </c>
       <c r="F325" t="n">
         <v>25461900</v>
@@ -6992,16 +6992,16 @@
         <v>44734</v>
       </c>
       <c r="B329" t="n">
-        <v>14.44118976593018</v>
+        <v>14.44119071960449</v>
       </c>
       <c r="C329" t="n">
-        <v>15.13482956889515</v>
+        <v>15.13483056837639</v>
       </c>
       <c r="D329" t="n">
-        <v>14.32558328522912</v>
+        <v>14.32558423126896</v>
       </c>
       <c r="E329" t="n">
-        <v>14.6820368304137</v>
+        <v>14.68203779999319</v>
       </c>
       <c r="F329" t="n">
         <v>8791300</v>
@@ -7032,16 +7032,16 @@
         <v>44736</v>
       </c>
       <c r="B331" t="n">
-        <v>14.4219217300415</v>
+        <v>14.42192268371582</v>
       </c>
       <c r="C331" t="n">
-        <v>14.86508034244202</v>
+        <v>14.86508132542095</v>
       </c>
       <c r="D331" t="n">
-        <v>14.25814566119184</v>
+        <v>14.25814660403618</v>
       </c>
       <c r="E331" t="n">
-        <v>14.86508034244202</v>
+        <v>14.86508132542095</v>
       </c>
       <c r="F331" t="n">
         <v>5803600</v>
@@ -7052,16 +7052,16 @@
         <v>44739</v>
       </c>
       <c r="B332" t="n">
-        <v>14.1618070602417</v>
+        <v>14.16180801391602</v>
       </c>
       <c r="C332" t="n">
-        <v>14.4989933145069</v>
+        <v>14.49899429088777</v>
       </c>
       <c r="D332" t="n">
-        <v>14.10400427987309</v>
+        <v>14.10400522965489</v>
       </c>
       <c r="E332" t="n">
-        <v>14.47972510854494</v>
+        <v>14.47972608362827</v>
       </c>
       <c r="F332" t="n">
         <v>8041800</v>
@@ -7072,16 +7072,16 @@
         <v>44740</v>
       </c>
       <c r="B333" t="n">
-        <v>14.08473491668701</v>
+        <v>14.08473587036133</v>
       </c>
       <c r="C333" t="n">
-        <v>14.48935802105732</v>
+        <v>14.48935900212858</v>
       </c>
       <c r="D333" t="n">
-        <v>13.96912844668957</v>
+        <v>13.9691293925362</v>
       </c>
       <c r="E333" t="n">
-        <v>14.2388768766836</v>
+        <v>14.23887784079483</v>
       </c>
       <c r="F333" t="n">
         <v>7081400</v>
@@ -7292,16 +7292,16 @@
         <v>44755</v>
       </c>
       <c r="B344" t="n">
-        <v>14.77837467193604</v>
+        <v>14.77837562561035</v>
       </c>
       <c r="C344" t="n">
-        <v>15.01922171438934</v>
+        <v>15.01922268360593</v>
       </c>
       <c r="D344" t="n">
-        <v>14.44118844499799</v>
+        <v>14.44118937691309</v>
       </c>
       <c r="E344" t="n">
-        <v>14.5856972217251</v>
+        <v>14.58569816296561</v>
       </c>
       <c r="F344" t="n">
         <v>3964800</v>
@@ -7392,16 +7392,16 @@
         <v>44762</v>
       </c>
       <c r="B349" t="n">
-        <v>14.82654571533203</v>
+        <v>14.82654476165771</v>
       </c>
       <c r="C349" t="n">
-        <v>15.10592827517219</v>
+        <v>15.10592730352741</v>
       </c>
       <c r="D349" t="n">
-        <v>14.57606454616261</v>
+        <v>14.57606360859976</v>
       </c>
       <c r="E349" t="n">
-        <v>14.89398259981663</v>
+        <v>14.89398164180463</v>
       </c>
       <c r="F349" t="n">
         <v>5599700</v>
@@ -7652,16 +7652,16 @@
         <v>44781</v>
       </c>
       <c r="B362" t="n">
-        <v>16.68588256835938</v>
+        <v>16.68588447570801</v>
       </c>
       <c r="C362" t="n">
-        <v>16.88819503663362</v>
+        <v>16.88819696710841</v>
       </c>
       <c r="D362" t="n">
-        <v>16.26199126520336</v>
+        <v>16.26199312409735</v>
       </c>
       <c r="E362" t="n">
-        <v>16.53174061039666</v>
+        <v>16.53174250012546</v>
       </c>
       <c r="F362" t="n">
         <v>10381400</v>
@@ -7692,16 +7692,16 @@
         <v>44783</v>
       </c>
       <c r="B364" t="n">
-        <v>16.89782905578613</v>
+        <v>16.89783096313477</v>
       </c>
       <c r="C364" t="n">
-        <v>17.20611297019896</v>
+        <v>17.20611491234526</v>
       </c>
       <c r="D364" t="n">
-        <v>16.73405299656468</v>
+        <v>16.73405488542704</v>
       </c>
       <c r="E364" t="n">
-        <v>17.16757656213882</v>
+        <v>17.1675784999353</v>
       </c>
       <c r="F364" t="n">
         <v>6533000</v>
@@ -7812,16 +7812,16 @@
         <v>44791</v>
       </c>
       <c r="B370" t="n">
-        <v>17.45659446716309</v>
+        <v>17.45659637451172</v>
       </c>
       <c r="C370" t="n">
-        <v>17.59146822309866</v>
+        <v>17.59147014518392</v>
       </c>
       <c r="D370" t="n">
-        <v>17.29281840459113</v>
+        <v>17.2928202940452</v>
       </c>
       <c r="E370" t="n">
-        <v>17.34098707813466</v>
+        <v>17.34098897285176</v>
       </c>
       <c r="F370" t="n">
         <v>13968800</v>
@@ -7832,16 +7832,16 @@
         <v>44792</v>
       </c>
       <c r="B371" t="n">
-        <v>17.12904357910156</v>
+        <v>17.12904167175293</v>
       </c>
       <c r="C371" t="n">
-        <v>17.57220128776223</v>
+        <v>17.57219933106722</v>
       </c>
       <c r="D371" t="n">
-        <v>17.07123896165407</v>
+        <v>17.07123706074208</v>
       </c>
       <c r="E371" t="n">
-        <v>17.45659572790173</v>
+        <v>17.4565937840796</v>
       </c>
       <c r="F371" t="n">
         <v>7571900</v>
@@ -7872,16 +7872,16 @@
         <v>44796</v>
       </c>
       <c r="B373" t="n">
-        <v>17.20611190795898</v>
+        <v>17.20611381530762</v>
       </c>
       <c r="C373" t="n">
-        <v>17.7937773944593</v>
+        <v>17.7937793669524</v>
       </c>
       <c r="D373" t="n">
-        <v>17.10977273127332</v>
+        <v>17.10977462794247</v>
       </c>
       <c r="E373" t="n">
-        <v>17.49512760049901</v>
+        <v>17.49512953988589</v>
       </c>
       <c r="F373" t="n">
         <v>12142000</v>
@@ -7952,16 +7952,16 @@
         <v>44802</v>
       </c>
       <c r="B377" t="n">
-        <v>17.68780899047852</v>
+        <v>17.68780708312988</v>
       </c>
       <c r="C377" t="n">
-        <v>17.98645883571042</v>
+        <v>17.98645689615716</v>
       </c>
       <c r="D377" t="n">
-        <v>17.19648075879664</v>
+        <v>17.19647890442993</v>
       </c>
       <c r="E377" t="n">
-        <v>17.29281995202162</v>
+        <v>17.29281808726627</v>
       </c>
       <c r="F377" t="n">
         <v>7263100</v>
@@ -7992,16 +7992,16 @@
         <v>44804</v>
       </c>
       <c r="B379" t="n">
-        <v>17.71670913696289</v>
+        <v>17.71671104431152</v>
       </c>
       <c r="C379" t="n">
-        <v>17.98645850553768</v>
+        <v>17.98646044192704</v>
       </c>
       <c r="D379" t="n">
-        <v>17.51439848866973</v>
+        <v>17.51440037423797</v>
       </c>
       <c r="E379" t="n">
-        <v>17.74561144565502</v>
+        <v>17.74561335611522</v>
       </c>
       <c r="F379" t="n">
         <v>9759800</v>
@@ -8032,16 +8032,16 @@
         <v>44806</v>
       </c>
       <c r="B381" t="n">
-        <v>18.20803642272949</v>
+        <v>18.20803451538086</v>
       </c>
       <c r="C381" t="n">
-        <v>18.54522265671872</v>
+        <v>18.54522071404877</v>
       </c>
       <c r="D381" t="n">
-        <v>17.95755527283799</v>
+        <v>17.95755339172804</v>
       </c>
       <c r="E381" t="n">
-        <v>18.20803642272949</v>
+        <v>18.20803451538086</v>
       </c>
       <c r="F381" t="n">
         <v>12423600</v>
@@ -8152,16 +8152,16 @@
         <v>44817</v>
       </c>
       <c r="B387" t="n">
-        <v>17.48549652099609</v>
+        <v>17.48549461364746</v>
       </c>
       <c r="C387" t="n">
-        <v>17.84195098508192</v>
+        <v>17.84194903885061</v>
       </c>
       <c r="D387" t="n">
-        <v>17.32172044358108</v>
+        <v>17.32171855409743</v>
       </c>
       <c r="E387" t="n">
-        <v>17.64927259841111</v>
+        <v>17.64927067319749</v>
       </c>
       <c r="F387" t="n">
         <v>10161300</v>
@@ -8172,16 +8172,16 @@
         <v>44818</v>
       </c>
       <c r="B388" t="n">
-        <v>17.70707511901855</v>
+        <v>17.70707702636719</v>
       </c>
       <c r="C388" t="n">
-        <v>17.8708511940252</v>
+        <v>17.87085311901526</v>
       </c>
       <c r="D388" t="n">
-        <v>17.36989070357892</v>
+        <v>17.36989257460714</v>
       </c>
       <c r="E388" t="n">
-        <v>17.44696168961044</v>
+        <v>17.4469635689405</v>
       </c>
       <c r="F388" t="n">
         <v>7347400</v>
@@ -8212,16 +8212,16 @@
         <v>44820</v>
       </c>
       <c r="B390" t="n">
-        <v>17.24464797973633</v>
+        <v>17.24464988708496</v>
       </c>
       <c r="C390" t="n">
-        <v>17.62037061781912</v>
+        <v>17.62037256672464</v>
       </c>
       <c r="D390" t="n">
-        <v>17.06160371182508</v>
+        <v>17.06160559892805</v>
       </c>
       <c r="E390" t="n">
-        <v>17.49512912595248</v>
+        <v>17.49513106100564</v>
       </c>
       <c r="F390" t="n">
         <v>10140200</v>
@@ -8232,16 +8232,16 @@
         <v>44823</v>
       </c>
       <c r="B391" t="n">
-        <v>17.46623039245605</v>
+        <v>17.46622848510742</v>
       </c>
       <c r="C391" t="n">
-        <v>17.58183780571365</v>
+        <v>17.58183588574045</v>
       </c>
       <c r="D391" t="n">
-        <v>17.14831230289454</v>
+        <v>17.14831043026322</v>
       </c>
       <c r="E391" t="n">
-        <v>17.14831230289454</v>
+        <v>17.14831043026322</v>
       </c>
       <c r="F391" t="n">
         <v>7719100</v>
@@ -8332,16 +8332,16 @@
         <v>44830</v>
       </c>
       <c r="B396" t="n">
-        <v>17.09050559997559</v>
+        <v>17.09050750732422</v>
       </c>
       <c r="C396" t="n">
-        <v>17.20611298675014</v>
+        <v>17.20611490700088</v>
       </c>
       <c r="D396" t="n">
-        <v>16.71478480861316</v>
+        <v>16.7147866740303</v>
       </c>
       <c r="E396" t="n">
-        <v>16.89782907204076</v>
+        <v>16.89783095788615</v>
       </c>
       <c r="F396" t="n">
         <v>7980700</v>
@@ -8352,16 +8352,16 @@
         <v>44831</v>
       </c>
       <c r="B397" t="n">
-        <v>17.12904357910156</v>
+        <v>17.12904167175293</v>
       </c>
       <c r="C397" t="n">
-        <v>17.49513030201615</v>
+        <v>17.49512835390313</v>
       </c>
       <c r="D397" t="n">
-        <v>16.86892831313957</v>
+        <v>16.86892643475522</v>
       </c>
       <c r="E397" t="n">
-        <v>17.25428324186998</v>
+        <v>17.2542813205757</v>
       </c>
       <c r="F397" t="n">
         <v>9260100</v>
@@ -8432,16 +8432,16 @@
         <v>44837</v>
       </c>
       <c r="B401" t="n">
-        <v>17.75524520874023</v>
+        <v>17.75524711608887</v>
       </c>
       <c r="C401" t="n">
-        <v>17.81304798750098</v>
+        <v>17.81304990105905</v>
       </c>
       <c r="D401" t="n">
-        <v>16.96526716144702</v>
+        <v>16.96526898393264</v>
       </c>
       <c r="E401" t="n">
-        <v>17.24464879005494</v>
+        <v>17.244650642553</v>
       </c>
       <c r="F401" t="n">
         <v>18011200</v>
@@ -8472,16 +8472,16 @@
         <v>44839</v>
       </c>
       <c r="B403" t="n">
-        <v>17.45659446716309</v>
+        <v>17.45659637451172</v>
       </c>
       <c r="C403" t="n">
-        <v>17.74561018345848</v>
+        <v>17.74561212238566</v>
       </c>
       <c r="D403" t="n">
-        <v>17.14830870892632</v>
+        <v>17.14831058259092</v>
       </c>
       <c r="E403" t="n">
-        <v>17.4276921605267</v>
+        <v>17.4276940647174</v>
       </c>
       <c r="F403" t="n">
         <v>8852300</v>
@@ -8492,16 +8492,16 @@
         <v>44840</v>
       </c>
       <c r="B404" t="n">
-        <v>17.44696044921875</v>
+        <v>17.44696235656738</v>
       </c>
       <c r="C404" t="n">
-        <v>17.6396369818406</v>
+        <v>17.63963891025314</v>
       </c>
       <c r="D404" t="n">
-        <v>17.30245075285597</v>
+        <v>17.30245264440641</v>
       </c>
       <c r="E404" t="n">
-        <v>17.63000287958194</v>
+        <v>17.63000480694126</v>
       </c>
       <c r="F404" t="n">
         <v>6691000</v>
@@ -8652,16 +8652,16 @@
         <v>44853</v>
       </c>
       <c r="B412" t="n">
-        <v>17.67817687988281</v>
+        <v>17.67817497253418</v>
       </c>
       <c r="C412" t="n">
-        <v>17.97682675877506</v>
+        <v>17.97682481920425</v>
       </c>
       <c r="D412" t="n">
-        <v>17.28318779690735</v>
+        <v>17.2831859321752</v>
       </c>
       <c r="E412" t="n">
-        <v>17.4758643675563</v>
+        <v>17.47586248203574</v>
       </c>
       <c r="F412" t="n">
         <v>27062400</v>
@@ -8692,16 +8692,16 @@
         <v>44855</v>
       </c>
       <c r="B414" t="n">
-        <v>17.91902160644531</v>
+        <v>17.91902351379395</v>
       </c>
       <c r="C414" t="n">
-        <v>18.25620785747724</v>
+        <v>18.25620980071688</v>
       </c>
       <c r="D414" t="n">
-        <v>17.34098829575019</v>
+        <v>17.34099014157141</v>
       </c>
       <c r="E414" t="n">
-        <v>17.53366667848764</v>
+        <v>17.53366854481807</v>
       </c>
       <c r="F414" t="n">
         <v>27105700</v>
@@ -8712,16 +8712,16 @@
         <v>44858</v>
       </c>
       <c r="B415" t="n">
-        <v>18.00572776794434</v>
+        <v>18.0057258605957</v>
       </c>
       <c r="C415" t="n">
-        <v>18.36218040847837</v>
+        <v>18.36217846337067</v>
       </c>
       <c r="D415" t="n">
-        <v>17.54329998932035</v>
+        <v>17.54329813095674</v>
       </c>
       <c r="E415" t="n">
-        <v>17.91902267429717</v>
+        <v>17.91902077613322</v>
       </c>
       <c r="F415" t="n">
         <v>16227000</v>
@@ -8732,16 +8732,16 @@
         <v>44859</v>
       </c>
       <c r="B416" t="n">
-        <v>17.04233741760254</v>
+        <v>17.04233932495117</v>
       </c>
       <c r="C416" t="n">
-        <v>18.00572559754023</v>
+        <v>18.00572761270958</v>
       </c>
       <c r="D416" t="n">
-        <v>16.80149037261812</v>
+        <v>16.80149225301157</v>
       </c>
       <c r="E416" t="n">
-        <v>18.00572559754023</v>
+        <v>18.00572761270958</v>
       </c>
       <c r="F416" t="n">
         <v>27810400</v>
@@ -8772,16 +8772,16 @@
         <v>44861</v>
       </c>
       <c r="B418" t="n">
-        <v>17.47586250305176</v>
+        <v>17.47586059570312</v>
       </c>
       <c r="C418" t="n">
-        <v>17.74561187820164</v>
+        <v>17.74560994141206</v>
       </c>
       <c r="D418" t="n">
-        <v>15.9922455335206</v>
+        <v>15.99224378809673</v>
       </c>
       <c r="E418" t="n">
-        <v>16.13675340546911</v>
+        <v>16.13675164427337</v>
       </c>
       <c r="F418" t="n">
         <v>30122400</v>
@@ -8792,16 +8792,16 @@
         <v>44862</v>
       </c>
       <c r="B419" t="n">
-        <v>18.12133026123047</v>
+        <v>18.1213321685791</v>
       </c>
       <c r="C419" t="n">
-        <v>18.21766944200201</v>
+        <v>18.21767135949075</v>
       </c>
       <c r="D419" t="n">
-        <v>17.27354951297842</v>
+        <v>17.27355133109445</v>
       </c>
       <c r="E419" t="n">
-        <v>17.40842326354835</v>
+        <v>17.40842509586043</v>
       </c>
       <c r="F419" t="n">
         <v>12193800</v>
@@ -8852,16 +8852,16 @@
         <v>44868</v>
       </c>
       <c r="B422" t="n">
-        <v>19.62422180175781</v>
+        <v>19.62421989440918</v>
       </c>
       <c r="C422" t="n">
-        <v>19.74946148068863</v>
+        <v>19.74945956116751</v>
       </c>
       <c r="D422" t="n">
-        <v>18.69936801593355</v>
+        <v>18.69936619847478</v>
       </c>
       <c r="E422" t="n">
-        <v>18.69936801593355</v>
+        <v>18.69936619847478</v>
       </c>
       <c r="F422" t="n">
         <v>9732300</v>
@@ -8892,16 +8892,16 @@
         <v>44872</v>
       </c>
       <c r="B424" t="n">
-        <v>19.51824760437012</v>
+        <v>19.51824569702148</v>
       </c>
       <c r="C424" t="n">
-        <v>19.94213898012385</v>
+        <v>19.942137031352</v>
       </c>
       <c r="D424" t="n">
-        <v>19.14252674717783</v>
+        <v>19.14252487654513</v>
       </c>
       <c r="E424" t="n">
-        <v>19.69165779615653</v>
+        <v>19.69165587186202</v>
       </c>
       <c r="F424" t="n">
         <v>17754600</v>
@@ -8972,16 +8972,16 @@
         <v>44876</v>
       </c>
       <c r="B428" t="n">
-        <v>18.64156341552734</v>
+        <v>18.64156532287598</v>
       </c>
       <c r="C428" t="n">
-        <v>18.96911557474207</v>
+        <v>18.96911751560485</v>
       </c>
       <c r="D428" t="n">
-        <v>18.03462777565176</v>
+        <v>18.03462962090057</v>
       </c>
       <c r="E428" t="n">
-        <v>18.88241048333127</v>
+        <v>18.88241241532265</v>
       </c>
       <c r="F428" t="n">
         <v>19344200</v>
@@ -9112,16 +9112,16 @@
         <v>44888</v>
       </c>
       <c r="B435" t="n">
-        <v>18.64156341552734</v>
+        <v>18.64156532287598</v>
       </c>
       <c r="C435" t="n">
-        <v>19.14252575756366</v>
+        <v>19.14252771616925</v>
       </c>
       <c r="D435" t="n">
-        <v>18.46815323270575</v>
+        <v>18.46815512231158</v>
       </c>
       <c r="E435" t="n">
-        <v>18.69936619729544</v>
+        <v>18.69936811055828</v>
       </c>
       <c r="F435" t="n">
         <v>10423000</v>
@@ -9312,16 +9312,16 @@
         <v>44902</v>
       </c>
       <c r="B445" t="n">
-        <v>19.36410522460938</v>
+        <v>19.36410331726074</v>
       </c>
       <c r="C445" t="n">
-        <v>19.48934489527705</v>
+        <v>19.48934297559241</v>
       </c>
       <c r="D445" t="n">
-        <v>18.82460829035904</v>
+        <v>18.82460643615043</v>
       </c>
       <c r="E445" t="n">
-        <v>19.17142682933272</v>
+        <v>19.17142494096275</v>
       </c>
       <c r="F445" t="n">
         <v>7439200</v>
@@ -9412,16 +9412,16 @@
         <v>44909</v>
       </c>
       <c r="B450" t="n">
-        <v>18.3718147277832</v>
+        <v>18.37181282043457</v>
       </c>
       <c r="C450" t="n">
-        <v>18.46815392602494</v>
+        <v>18.46815200867444</v>
       </c>
       <c r="D450" t="n">
-        <v>17.64927349724626</v>
+        <v>17.64927166491134</v>
       </c>
       <c r="E450" t="n">
-        <v>17.86122010088155</v>
+        <v>17.86121824654248</v>
       </c>
       <c r="F450" t="n">
         <v>10673700</v>
@@ -9612,16 +9612,16 @@
         <v>44923</v>
       </c>
       <c r="B460" t="n">
-        <v>18.71863555908203</v>
+        <v>18.7186336517334</v>
       </c>
       <c r="C460" t="n">
-        <v>18.94984853794273</v>
+        <v>18.94984660703449</v>
       </c>
       <c r="D460" t="n">
-        <v>18.26584186765209</v>
+        <v>18.26584000644119</v>
       </c>
       <c r="E460" t="n">
-        <v>18.68973324765541</v>
+        <v>18.6897313432518</v>
       </c>
       <c r="F460" t="n">
         <v>8329700</v>
@@ -27465,6 +27465,26 @@
       </c>
       <c r="F1352" t="n">
         <v>5647400</v>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B1353" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="C1353" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="D1353" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="E1353" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="F1353" t="n">
+        <v>6610600</v>
       </c>
     </row>
   </sheetData>

--- a/database/ASAI3.xlsx
+++ b/database/ASAI3.xlsx
@@ -472,16 +472,16 @@
         <v>44257</v>
       </c>
       <c r="B3" t="n">
-        <v>13.76804351806641</v>
+        <v>13.76804256439209</v>
       </c>
       <c r="C3" t="n">
-        <v>14.0528997719606</v>
+        <v>14.05289879855508</v>
       </c>
       <c r="D3" t="n">
-        <v>13.00462933717113</v>
+        <v>13.0046284363764</v>
       </c>
       <c r="E3" t="n">
-        <v>13.37114384656537</v>
+        <v>13.3711429203832</v>
       </c>
       <c r="F3" t="n">
         <v>14717000</v>
@@ -532,16 +532,16 @@
         <v>44260</v>
       </c>
       <c r="B6" t="n">
-        <v>14.24280261993408</v>
+        <v>14.2428035736084</v>
       </c>
       <c r="C6" t="n">
-        <v>14.90746656109107</v>
+        <v>14.90746755927018</v>
       </c>
       <c r="D6" t="n">
-        <v>13.67309015292352</v>
+        <v>13.67309106845084</v>
       </c>
       <c r="E6" t="n">
-        <v>13.76994143531125</v>
+        <v>13.76994235732357</v>
       </c>
       <c r="F6" t="n">
         <v>18499500</v>
@@ -592,16 +592,16 @@
         <v>44265</v>
       </c>
       <c r="B9" t="n">
-        <v>13.48318767547607</v>
+        <v>13.48318672180176</v>
       </c>
       <c r="C9" t="n">
-        <v>13.95794781127124</v>
+        <v>13.95794682401684</v>
       </c>
       <c r="D9" t="n">
-        <v>13.23631218753465</v>
+        <v>13.23631125132199</v>
       </c>
       <c r="E9" t="n">
-        <v>13.48508657837822</v>
+        <v>13.4850856245696</v>
       </c>
       <c r="F9" t="n">
         <v>15699500</v>
@@ -612,16 +612,16 @@
         <v>44266</v>
       </c>
       <c r="B10" t="n">
-        <v>13.95604801177979</v>
+        <v>13.9560489654541</v>
       </c>
       <c r="C10" t="n">
-        <v>14.15544729222492</v>
+        <v>14.15544825952501</v>
       </c>
       <c r="D10" t="n">
-        <v>13.63510989807421</v>
+        <v>13.6351108298175</v>
       </c>
       <c r="E10" t="n">
-        <v>13.71297125079192</v>
+        <v>13.7129721878558</v>
       </c>
       <c r="F10" t="n">
         <v>16646000</v>
@@ -632,16 +632,16 @@
         <v>44267</v>
       </c>
       <c r="B11" t="n">
-        <v>13.82121467590332</v>
+        <v>13.82121658325195</v>
       </c>
       <c r="C11" t="n">
-        <v>14.06049360921212</v>
+        <v>14.06049554958161</v>
       </c>
       <c r="D11" t="n">
-        <v>13.57813793738528</v>
+        <v>13.57813981118895</v>
       </c>
       <c r="E11" t="n">
-        <v>13.57813793738528</v>
+        <v>13.57813981118895</v>
       </c>
       <c r="F11" t="n">
         <v>7509000</v>
@@ -652,16 +652,16 @@
         <v>44270</v>
       </c>
       <c r="B12" t="n">
-        <v>13.83450984954834</v>
+        <v>13.83450889587402</v>
       </c>
       <c r="C12" t="n">
-        <v>14.01681810828169</v>
+        <v>14.01681714204006</v>
       </c>
       <c r="D12" t="n">
-        <v>13.62181733379263</v>
+        <v>13.62181639478016</v>
       </c>
       <c r="E12" t="n">
-        <v>13.81931772103716</v>
+        <v>13.81931676841011</v>
       </c>
       <c r="F12" t="n">
         <v>11593000</v>
@@ -672,16 +672,16 @@
         <v>44271</v>
       </c>
       <c r="B13" t="n">
-        <v>13.58763408660889</v>
+        <v>13.5876350402832</v>
       </c>
       <c r="C13" t="n">
-        <v>13.91047018507921</v>
+        <v>13.9104711614124</v>
       </c>
       <c r="D13" t="n">
-        <v>13.49458060971476</v>
+        <v>13.49458155685794</v>
       </c>
       <c r="E13" t="n">
-        <v>13.84400406267841</v>
+        <v>13.84400503434655</v>
       </c>
       <c r="F13" t="n">
         <v>7789500</v>
@@ -712,16 +712,16 @@
         <v>44273</v>
       </c>
       <c r="B15" t="n">
-        <v>13.91047096252441</v>
+        <v>13.91047191619873</v>
       </c>
       <c r="C15" t="n">
-        <v>14.0130198642166</v>
+        <v>14.01302082492147</v>
       </c>
       <c r="D15" t="n">
-        <v>13.69018284217017</v>
+        <v>13.69018378074197</v>
       </c>
       <c r="E15" t="n">
-        <v>13.69018284217017</v>
+        <v>13.69018378074197</v>
       </c>
       <c r="F15" t="n">
         <v>2304000</v>
@@ -752,16 +752,16 @@
         <v>44277</v>
       </c>
       <c r="B17" t="n">
-        <v>13.2932825088501</v>
+        <v>13.29328441619873</v>
       </c>
       <c r="C17" t="n">
-        <v>13.6351094473715</v>
+        <v>13.6351114037662</v>
       </c>
       <c r="D17" t="n">
-        <v>13.15655155233494</v>
+        <v>13.15655344006512</v>
       </c>
       <c r="E17" t="n">
-        <v>13.6351094473715</v>
+        <v>13.6351114037662</v>
       </c>
       <c r="F17" t="n">
         <v>5803000</v>
@@ -772,16 +772,16 @@
         <v>44278</v>
       </c>
       <c r="B18" t="n">
-        <v>13.44140911102295</v>
+        <v>13.44140815734863</v>
       </c>
       <c r="C18" t="n">
-        <v>13.44140911102295</v>
+        <v>13.44140815734863</v>
       </c>
       <c r="D18" t="n">
-        <v>13.01982187811874</v>
+        <v>13.01982095435623</v>
       </c>
       <c r="E18" t="n">
-        <v>13.29328381808184</v>
+        <v>13.29328287491709</v>
       </c>
       <c r="F18" t="n">
         <v>7916000</v>
@@ -852,16 +852,16 @@
         <v>44284</v>
       </c>
       <c r="B22" t="n">
-        <v>13.95794677734375</v>
+        <v>13.95794773101807</v>
       </c>
       <c r="C22" t="n">
-        <v>13.95794677734375</v>
+        <v>13.95794773101807</v>
       </c>
       <c r="D22" t="n">
-        <v>13.4869853877722</v>
+        <v>13.48698630926816</v>
       </c>
       <c r="E22" t="n">
-        <v>13.7148700187455</v>
+        <v>13.71487095581164</v>
       </c>
       <c r="F22" t="n">
         <v>6557000</v>
@@ -872,16 +872,16 @@
         <v>44285</v>
       </c>
       <c r="B23" t="n">
-        <v>13.95794677734375</v>
+        <v>13.95794773101807</v>
       </c>
       <c r="C23" t="n">
-        <v>14.08138451217088</v>
+        <v>14.08138547427906</v>
       </c>
       <c r="D23" t="n">
-        <v>13.76804291819933</v>
+        <v>13.7680438588985</v>
       </c>
       <c r="E23" t="n">
-        <v>13.76804291819933</v>
+        <v>13.7680438588985</v>
       </c>
       <c r="F23" t="n">
         <v>8433000</v>
@@ -932,16 +932,16 @@
         <v>44291</v>
       </c>
       <c r="B26" t="n">
-        <v>14.71756362915039</v>
+        <v>14.71756458282471</v>
       </c>
       <c r="C26" t="n">
-        <v>14.88657865823869</v>
+        <v>14.88657962286491</v>
       </c>
       <c r="D26" t="n">
-        <v>14.29977512456389</v>
+        <v>14.29977605116619</v>
       </c>
       <c r="E26" t="n">
-        <v>14.29977512456389</v>
+        <v>14.29977605116619</v>
       </c>
       <c r="F26" t="n">
         <v>6073500</v>
@@ -992,16 +992,16 @@
         <v>44294</v>
       </c>
       <c r="B29" t="n">
-        <v>14.70237064361572</v>
+        <v>14.70237159729004</v>
       </c>
       <c r="C29" t="n">
-        <v>14.74035141454506</v>
+        <v>14.74035237068301</v>
       </c>
       <c r="D29" t="n">
-        <v>14.26559132516181</v>
+        <v>14.26559225050429</v>
       </c>
       <c r="E29" t="n">
-        <v>14.4327065361443</v>
+        <v>14.43270747232676</v>
       </c>
       <c r="F29" t="n">
         <v>6395000</v>
@@ -1012,16 +1012,16 @@
         <v>44295</v>
       </c>
       <c r="B30" t="n">
-        <v>14.71756362915039</v>
+        <v>14.71756458282471</v>
       </c>
       <c r="C30" t="n">
-        <v>14.73655446848903</v>
+        <v>14.73655542339393</v>
       </c>
       <c r="D30" t="n">
-        <v>14.40801982998176</v>
+        <v>14.40802076359814</v>
       </c>
       <c r="E30" t="n">
-        <v>14.63210666319261</v>
+        <v>14.63210761132946</v>
       </c>
       <c r="F30" t="n">
         <v>7012500</v>
@@ -1032,16 +1032,16 @@
         <v>44298</v>
       </c>
       <c r="B31" t="n">
-        <v>14.69857311248779</v>
+        <v>14.69857406616211</v>
       </c>
       <c r="C31" t="n">
-        <v>14.8011220172082</v>
+        <v>14.80112297753611</v>
       </c>
       <c r="D31" t="n">
-        <v>14.52766008235327</v>
+        <v>14.52766102493839</v>
       </c>
       <c r="E31" t="n">
-        <v>14.69857311248779</v>
+        <v>14.69857406616211</v>
       </c>
       <c r="F31" t="n">
         <v>4711000</v>
@@ -1072,16 +1072,16 @@
         <v>44300</v>
       </c>
       <c r="B33" t="n">
-        <v>14.93785381317139</v>
+        <v>14.93785285949707</v>
       </c>
       <c r="C33" t="n">
-        <v>14.94544942506844</v>
+        <v>14.9454484709092</v>
       </c>
       <c r="D33" t="n">
-        <v>14.62261237558245</v>
+        <v>14.62261144203403</v>
       </c>
       <c r="E33" t="n">
-        <v>14.65109863679578</v>
+        <v>14.65109770142871</v>
       </c>
       <c r="F33" t="n">
         <v>5841000</v>
@@ -1092,16 +1092,16 @@
         <v>44301</v>
       </c>
       <c r="B34" t="n">
-        <v>15.18662643432617</v>
+        <v>15.1866283416748</v>
       </c>
       <c r="C34" t="n">
-        <v>15.2037165590924</v>
+        <v>15.20371846858745</v>
       </c>
       <c r="D34" t="n">
-        <v>14.84100077857334</v>
+        <v>14.84100264251348</v>
       </c>
       <c r="E34" t="n">
-        <v>14.84100077857334</v>
+        <v>14.84100264251348</v>
       </c>
       <c r="F34" t="n">
         <v>11554500</v>
@@ -1132,16 +1132,16 @@
         <v>44305</v>
       </c>
       <c r="B36" t="n">
-        <v>15.28727722167969</v>
+        <v>15.28727626800537</v>
       </c>
       <c r="C36" t="n">
-        <v>15.50756626494049</v>
+        <v>15.50756529752376</v>
       </c>
       <c r="D36" t="n">
-        <v>15.00431985298662</v>
+        <v>15.00431891696419</v>
       </c>
       <c r="E36" t="n">
-        <v>15.14484863308528</v>
+        <v>15.14484768829616</v>
       </c>
       <c r="F36" t="n">
         <v>5017000</v>
@@ -1152,16 +1152,16 @@
         <v>44306</v>
       </c>
       <c r="B37" t="n">
-        <v>15.4771785736084</v>
+        <v>15.47717666625977</v>
       </c>
       <c r="C37" t="n">
-        <v>15.65568992191963</v>
+        <v>15.65568799257194</v>
       </c>
       <c r="D37" t="n">
-        <v>15.06698659960384</v>
+        <v>15.06698474280571</v>
       </c>
       <c r="E37" t="n">
-        <v>15.35943935799809</v>
+        <v>15.35943746515919</v>
       </c>
       <c r="F37" t="n">
         <v>6029000</v>
@@ -1212,16 +1212,16 @@
         <v>44312</v>
       </c>
       <c r="B40" t="n">
-        <v>15.26068878173828</v>
+        <v>15.2606897354126</v>
       </c>
       <c r="C40" t="n">
-        <v>15.51705785343516</v>
+        <v>15.51705882313055</v>
       </c>
       <c r="D40" t="n">
-        <v>15.16573640170765</v>
+        <v>15.16573734944818</v>
       </c>
       <c r="E40" t="n">
-        <v>15.48477560174152</v>
+        <v>15.48477656941952</v>
       </c>
       <c r="F40" t="n">
         <v>3662000</v>
@@ -1232,16 +1232,16 @@
         <v>44313</v>
       </c>
       <c r="B41" t="n">
-        <v>15.12775611877441</v>
+        <v>15.12775707244873</v>
       </c>
       <c r="C41" t="n">
-        <v>15.29677114335289</v>
+        <v>15.29677210768214</v>
       </c>
       <c r="D41" t="n">
-        <v>15.10116966883617</v>
+        <v>15.10117062083444</v>
       </c>
       <c r="E41" t="n">
-        <v>15.24929404627311</v>
+        <v>15.24929500760934</v>
       </c>
       <c r="F41" t="n">
         <v>4986500</v>
@@ -1272,16 +1272,16 @@
         <v>44315</v>
       </c>
       <c r="B43" t="n">
-        <v>15.21646404266357</v>
+        <v>15.21646499633789</v>
       </c>
       <c r="C43" t="n">
-        <v>15.32323240215915</v>
+        <v>15.32323336252505</v>
       </c>
       <c r="D43" t="n">
-        <v>14.90950409998268</v>
+        <v>14.90950503441863</v>
       </c>
       <c r="E43" t="n">
-        <v>15.26222243052232</v>
+        <v>15.26222338706449</v>
       </c>
       <c r="F43" t="n">
         <v>5343000</v>
@@ -1312,16 +1312,16 @@
         <v>44319</v>
       </c>
       <c r="B45" t="n">
-        <v>15.532958984375</v>
+        <v>15.53295803070068</v>
       </c>
       <c r="C45" t="n">
-        <v>15.6702323380043</v>
+        <v>15.67023137590184</v>
       </c>
       <c r="D45" t="n">
-        <v>15.29463569991469</v>
+        <v>15.29463476087267</v>
       </c>
       <c r="E45" t="n">
-        <v>15.44334956033281</v>
+        <v>15.44334861216023</v>
       </c>
       <c r="F45" t="n">
         <v>8474000</v>
@@ -1332,16 +1332,16 @@
         <v>44320</v>
       </c>
       <c r="B46" t="n">
-        <v>15.72933769226074</v>
+        <v>15.72933483123779</v>
       </c>
       <c r="C46" t="n">
-        <v>15.74840399251314</v>
+        <v>15.74840112802221</v>
       </c>
       <c r="D46" t="n">
-        <v>15.35945946771906</v>
+        <v>15.35945667397358</v>
       </c>
       <c r="E46" t="n">
-        <v>15.63400800926121</v>
+        <v>15.63400516557786</v>
       </c>
       <c r="F46" t="n">
         <v>9407500</v>
@@ -1352,16 +1352,16 @@
         <v>44321</v>
       </c>
       <c r="B47" t="n">
-        <v>16.32228660583496</v>
+        <v>16.32228469848633</v>
       </c>
       <c r="C47" t="n">
-        <v>16.58730201015107</v>
+        <v>16.58730007183393</v>
       </c>
       <c r="D47" t="n">
-        <v>16.01532570257429</v>
+        <v>16.01532383109572</v>
       </c>
       <c r="E47" t="n">
-        <v>16.08396329586652</v>
+        <v>16.08396141636727</v>
       </c>
       <c r="F47" t="n">
         <v>17262500</v>
@@ -1372,16 +1372,16 @@
         <v>44322</v>
       </c>
       <c r="B48" t="n">
-        <v>16.61971282958984</v>
+        <v>16.61971473693848</v>
       </c>
       <c r="C48" t="n">
-        <v>16.64449756423438</v>
+        <v>16.64449947442742</v>
       </c>
       <c r="D48" t="n">
-        <v>16.16022519568053</v>
+        <v>16.16022705029641</v>
       </c>
       <c r="E48" t="n">
-        <v>16.31847220804819</v>
+        <v>16.31847408082518</v>
       </c>
       <c r="F48" t="n">
         <v>9404500</v>
@@ -1432,16 +1432,16 @@
         <v>44327</v>
       </c>
       <c r="B51" t="n">
-        <v>16.5872974395752</v>
+        <v>16.58729934692383</v>
       </c>
       <c r="C51" t="n">
-        <v>16.78367701474988</v>
+        <v>16.78367894467991</v>
       </c>
       <c r="D51" t="n">
-        <v>16.49196777820309</v>
+        <v>16.4919696745899</v>
       </c>
       <c r="E51" t="n">
-        <v>16.62543003142886</v>
+        <v>16.6254319431623</v>
       </c>
       <c r="F51" t="n">
         <v>6191000</v>
@@ -1532,16 +1532,16 @@
         <v>44334</v>
       </c>
       <c r="B56" t="n">
-        <v>16.06108283996582</v>
+        <v>16.06108093261719</v>
       </c>
       <c r="C56" t="n">
-        <v>16.39092291515271</v>
+        <v>16.39092096863362</v>
       </c>
       <c r="D56" t="n">
-        <v>15.88758424029694</v>
+        <v>15.88758235355229</v>
       </c>
       <c r="E56" t="n">
-        <v>16.34897741949393</v>
+        <v>16.34897547795611</v>
       </c>
       <c r="F56" t="n">
         <v>6527500</v>
@@ -1552,16 +1552,16 @@
         <v>44335</v>
       </c>
       <c r="B57" t="n">
-        <v>15.82847690582275</v>
+        <v>15.82847881317139</v>
       </c>
       <c r="C57" t="n">
-        <v>16.3680407240457</v>
+        <v>16.36804269641236</v>
       </c>
       <c r="D57" t="n">
-        <v>15.67595017276244</v>
+        <v>15.67595206173143</v>
       </c>
       <c r="E57" t="n">
-        <v>15.98481653447027</v>
+        <v>15.98481846065799</v>
       </c>
       <c r="F57" t="n">
         <v>6358000</v>
@@ -1572,16 +1572,16 @@
         <v>44336</v>
       </c>
       <c r="B58" t="n">
-        <v>16.03248405456543</v>
+        <v>16.03248596191406</v>
       </c>
       <c r="C58" t="n">
-        <v>16.03248405456543</v>
+        <v>16.03248596191406</v>
       </c>
       <c r="D58" t="n">
-        <v>15.69692374997599</v>
+        <v>15.69692561740377</v>
       </c>
       <c r="E58" t="n">
-        <v>15.90283468063725</v>
+        <v>15.90283657256179</v>
       </c>
       <c r="F58" t="n">
         <v>7278000</v>
@@ -1592,16 +1592,16 @@
         <v>44337</v>
       </c>
       <c r="B59" t="n">
-        <v>16.43477439880371</v>
+        <v>16.43477630615234</v>
       </c>
       <c r="C59" t="n">
-        <v>16.6254337643569</v>
+        <v>16.62543569383264</v>
       </c>
       <c r="D59" t="n">
-        <v>15.75984264485187</v>
+        <v>15.75984447387085</v>
       </c>
       <c r="E59" t="n">
-        <v>16.03439118575198</v>
+        <v>16.03439304663388</v>
       </c>
       <c r="F59" t="n">
         <v>10145000</v>
@@ -1632,16 +1632,16 @@
         <v>44341</v>
       </c>
       <c r="B61" t="n">
-        <v>16.88472938537598</v>
+        <v>16.88472747802734</v>
       </c>
       <c r="C61" t="n">
-        <v>17.06394824863613</v>
+        <v>17.06394632104241</v>
       </c>
       <c r="D61" t="n">
-        <v>16.77986654948997</v>
+        <v>16.77986465398696</v>
       </c>
       <c r="E61" t="n">
-        <v>17.01628431501296</v>
+        <v>17.0162823928035</v>
       </c>
       <c r="F61" t="n">
         <v>5307000</v>
@@ -1652,16 +1652,16 @@
         <v>44342</v>
       </c>
       <c r="B62" t="n">
-        <v>16.94192504882812</v>
+        <v>16.94192695617676</v>
       </c>
       <c r="C62" t="n">
-        <v>17.11161256574568</v>
+        <v>17.11161449219801</v>
       </c>
       <c r="D62" t="n">
-        <v>16.65975073072218</v>
+        <v>16.65975260630318</v>
       </c>
       <c r="E62" t="n">
-        <v>17.02390868058733</v>
+        <v>17.02391059716581</v>
       </c>
       <c r="F62" t="n">
         <v>5462000</v>
@@ -1772,16 +1772,16 @@
         <v>44351</v>
       </c>
       <c r="B68" t="n">
-        <v>16.77223968505859</v>
+        <v>16.77223777770996</v>
       </c>
       <c r="C68" t="n">
-        <v>16.81609071938215</v>
+        <v>16.81608880704675</v>
       </c>
       <c r="D68" t="n">
-        <v>16.40617437066384</v>
+        <v>16.40617250494436</v>
       </c>
       <c r="E68" t="n">
-        <v>16.72266839722167</v>
+        <v>16.72266649551031</v>
       </c>
       <c r="F68" t="n">
         <v>8097000</v>
@@ -1792,16 +1792,16 @@
         <v>44354</v>
       </c>
       <c r="B69" t="n">
-        <v>16.53772926330566</v>
+        <v>16.5377311706543</v>
       </c>
       <c r="C69" t="n">
-        <v>16.77223965606192</v>
+        <v>16.77224159045738</v>
       </c>
       <c r="D69" t="n">
-        <v>16.03057769704888</v>
+        <v>16.03057954590612</v>
       </c>
       <c r="E69" t="n">
-        <v>16.77223965606192</v>
+        <v>16.77224159045738</v>
       </c>
       <c r="F69" t="n">
         <v>10336000</v>
@@ -1812,16 +1812,16 @@
         <v>44355</v>
       </c>
       <c r="B70" t="n">
-        <v>16.08205604553223</v>
+        <v>16.08205413818359</v>
       </c>
       <c r="C70" t="n">
-        <v>16.61017944054762</v>
+        <v>16.610177470563</v>
       </c>
       <c r="D70" t="n">
-        <v>15.92952747058032</v>
+        <v>15.92952558132173</v>
       </c>
       <c r="E70" t="n">
-        <v>16.60064629097173</v>
+        <v>16.60064432211775</v>
       </c>
       <c r="F70" t="n">
         <v>9246000</v>
@@ -1832,16 +1832,16 @@
         <v>44356</v>
       </c>
       <c r="B71" t="n">
-        <v>16.16403770446777</v>
+        <v>16.16403579711914</v>
       </c>
       <c r="C71" t="n">
-        <v>16.39664255171839</v>
+        <v>16.3966406169225</v>
       </c>
       <c r="D71" t="n">
-        <v>15.82466631047011</v>
+        <v>15.82466444316714</v>
       </c>
       <c r="E71" t="n">
-        <v>16.08205589177119</v>
+        <v>16.08205399409637</v>
       </c>
       <c r="F71" t="n">
         <v>10294500</v>
@@ -1852,16 +1852,16 @@
         <v>44357</v>
       </c>
       <c r="B72" t="n">
-        <v>16.30321502685547</v>
+        <v>16.30321884155273</v>
       </c>
       <c r="C72" t="n">
-        <v>16.34706786902673</v>
+        <v>16.34707169398488</v>
       </c>
       <c r="D72" t="n">
-        <v>15.97718974622022</v>
+        <v>15.97719348463267</v>
       </c>
       <c r="E72" t="n">
-        <v>16.15640855546862</v>
+        <v>16.15641233581547</v>
       </c>
       <c r="F72" t="n">
         <v>4720000</v>
@@ -1872,16 +1872,16 @@
         <v>44358</v>
       </c>
       <c r="B73" t="n">
-        <v>16.07061576843262</v>
+        <v>16.07061767578125</v>
       </c>
       <c r="C73" t="n">
-        <v>16.30512616021678</v>
+        <v>16.30512809539839</v>
       </c>
       <c r="D73" t="n">
-        <v>15.87423797549705</v>
+        <v>15.87423985953849</v>
       </c>
       <c r="E73" t="n">
-        <v>16.3032188029694</v>
+        <v>16.30322073792463</v>
       </c>
       <c r="F73" t="n">
         <v>5133000</v>
@@ -1892,16 +1892,16 @@
         <v>44361</v>
       </c>
       <c r="B74" t="n">
-        <v>16.01532554626465</v>
+        <v>16.01532173156738</v>
       </c>
       <c r="C74" t="n">
-        <v>16.19263887264001</v>
+        <v>16.19263501570841</v>
       </c>
       <c r="D74" t="n">
-        <v>15.8513600851954</v>
+        <v>15.85135630955313</v>
       </c>
       <c r="E74" t="n">
-        <v>16.16403942114841</v>
+        <v>16.16403557102893</v>
       </c>
       <c r="F74" t="n">
         <v>4317000</v>
@@ -1912,16 +1912,16 @@
         <v>44362</v>
       </c>
       <c r="B75" t="n">
-        <v>15.85898303985596</v>
+        <v>15.85898494720459</v>
       </c>
       <c r="C75" t="n">
-        <v>16.02676318570492</v>
+        <v>16.02676511323235</v>
       </c>
       <c r="D75" t="n">
-        <v>15.48719932831946</v>
+        <v>15.48720119095393</v>
       </c>
       <c r="E75" t="n">
-        <v>16.01532267985088</v>
+        <v>16.01532460600237</v>
       </c>
       <c r="F75" t="n">
         <v>8432500</v>
@@ -1932,16 +1932,16 @@
         <v>44363</v>
       </c>
       <c r="B76" t="n">
-        <v>15.89902114868164</v>
+        <v>15.89902019500732</v>
       </c>
       <c r="C76" t="n">
-        <v>16.11446521988256</v>
+        <v>16.11446425328521</v>
       </c>
       <c r="D76" t="n">
-        <v>15.6626052411311</v>
+        <v>15.66260430163777</v>
       </c>
       <c r="E76" t="n">
-        <v>15.70264337503251</v>
+        <v>15.70264243313756</v>
       </c>
       <c r="F76" t="n">
         <v>10606500</v>
@@ -1952,16 +1952,16 @@
         <v>44364</v>
       </c>
       <c r="B77" t="n">
-        <v>15.97719192504883</v>
+        <v>15.97719478607178</v>
       </c>
       <c r="C77" t="n">
-        <v>16.00769691026478</v>
+        <v>16.00769977675023</v>
       </c>
       <c r="D77" t="n">
-        <v>15.691202915711</v>
+        <v>15.69120572552212</v>
       </c>
       <c r="E77" t="n">
-        <v>15.89711565700863</v>
+        <v>15.89711850369239</v>
       </c>
       <c r="F77" t="n">
         <v>7246000</v>
@@ -1972,16 +1972,16 @@
         <v>44365</v>
       </c>
       <c r="B78" t="n">
-        <v>16.20789337158203</v>
+        <v>16.20788955688477</v>
       </c>
       <c r="C78" t="n">
-        <v>16.36423305011592</v>
+        <v>16.36422919862247</v>
       </c>
       <c r="D78" t="n">
-        <v>15.67976807160136</v>
+        <v>15.67976438120391</v>
       </c>
       <c r="E78" t="n">
-        <v>15.98863453186528</v>
+        <v>15.98863076877287</v>
       </c>
       <c r="F78" t="n">
         <v>12012000</v>
@@ -1992,16 +1992,16 @@
         <v>44368</v>
       </c>
       <c r="B79" t="n">
-        <v>16.48434257507324</v>
+        <v>16.48434448242188</v>
       </c>
       <c r="C79" t="n">
-        <v>16.59301828381779</v>
+        <v>16.59302020374093</v>
       </c>
       <c r="D79" t="n">
-        <v>16.00007027813662</v>
+        <v>16.00007212945171</v>
       </c>
       <c r="E79" t="n">
-        <v>16.20788854732228</v>
+        <v>16.20789042268334</v>
       </c>
       <c r="F79" t="n">
         <v>6798000</v>
@@ -2052,16 +2052,16 @@
         <v>44371</v>
       </c>
       <c r="B82" t="n">
-        <v>16.64640426635742</v>
+        <v>16.64640808105469</v>
       </c>
       <c r="C82" t="n">
-        <v>16.72648053888243</v>
+        <v>16.72648437193001</v>
       </c>
       <c r="D82" t="n">
-        <v>16.39664229944431</v>
+        <v>16.39664605690602</v>
       </c>
       <c r="E82" t="n">
-        <v>16.46909096154148</v>
+        <v>16.46909473560555</v>
       </c>
       <c r="F82" t="n">
         <v>8527500</v>
@@ -2072,16 +2072,16 @@
         <v>44372</v>
       </c>
       <c r="B83" t="n">
-        <v>16.18501281738281</v>
+        <v>16.18501091003418</v>
       </c>
       <c r="C83" t="n">
-        <v>16.74745595976945</v>
+        <v>16.74745398613881</v>
       </c>
       <c r="D83" t="n">
-        <v>16.05345788821992</v>
+        <v>16.05345599637458</v>
       </c>
       <c r="E83" t="n">
-        <v>16.64640602074596</v>
+        <v>16.64640405902371</v>
       </c>
       <c r="F83" t="n">
         <v>6078000</v>
@@ -2132,16 +2132,16 @@
         <v>44377</v>
       </c>
       <c r="B86" t="n">
-        <v>16.49959754943848</v>
+        <v>16.49959945678711</v>
       </c>
       <c r="C86" t="n">
-        <v>16.49959754943848</v>
+        <v>16.49959945678711</v>
       </c>
       <c r="D86" t="n">
-        <v>16.19072933339201</v>
+        <v>16.19073120503556</v>
       </c>
       <c r="E86" t="n">
-        <v>16.38901447318302</v>
+        <v>16.38901636774828</v>
       </c>
       <c r="F86" t="n">
         <v>6685000</v>
@@ -2152,16 +2152,16 @@
         <v>44378</v>
       </c>
       <c r="B87" t="n">
-        <v>16.3585090637207</v>
+        <v>16.35851097106934</v>
       </c>
       <c r="C87" t="n">
-        <v>16.66356255758535</v>
+        <v>16.66356450050222</v>
       </c>
       <c r="D87" t="n">
-        <v>16.14878524125432</v>
+        <v>16.14878712414984</v>
       </c>
       <c r="E87" t="n">
-        <v>16.66356255758535</v>
+        <v>16.66356450050222</v>
       </c>
       <c r="F87" t="n">
         <v>8503000</v>
@@ -2212,16 +2212,16 @@
         <v>44383</v>
       </c>
       <c r="B90" t="n">
-        <v>16.33944320678711</v>
+        <v>16.33944129943848</v>
       </c>
       <c r="C90" t="n">
-        <v>16.38901449179115</v>
+        <v>16.38901257865592</v>
       </c>
       <c r="D90" t="n">
-        <v>16.11256043736321</v>
+        <v>16.11255855649923</v>
       </c>
       <c r="E90" t="n">
-        <v>16.38901449179115</v>
+        <v>16.38901257865592</v>
       </c>
       <c r="F90" t="n">
         <v>3828000</v>
@@ -2232,16 +2232,16 @@
         <v>44384</v>
       </c>
       <c r="B91" t="n">
-        <v>16.44430732727051</v>
+        <v>16.44430541992188</v>
       </c>
       <c r="C91" t="n">
-        <v>16.58348804403921</v>
+        <v>16.58348612054724</v>
       </c>
       <c r="D91" t="n">
-        <v>16.15069249011994</v>
+        <v>16.15069061682722</v>
       </c>
       <c r="E91" t="n">
-        <v>16.39664339565586</v>
+        <v>16.39664149383569</v>
       </c>
       <c r="F91" t="n">
         <v>12086500</v>
@@ -2252,16 +2252,16 @@
         <v>44385</v>
       </c>
       <c r="B92" t="n">
-        <v>16.43477439880371</v>
+        <v>16.43477630615234</v>
       </c>
       <c r="C92" t="n">
-        <v>16.79893236876558</v>
+        <v>16.79893431837681</v>
       </c>
       <c r="D92" t="n">
-        <v>16.24411685151298</v>
+        <v>16.24411873673473</v>
       </c>
       <c r="E92" t="n">
-        <v>16.26318133345833</v>
+        <v>16.26318322089262</v>
       </c>
       <c r="F92" t="n">
         <v>7435000</v>
@@ -2272,16 +2272,16 @@
         <v>44389</v>
       </c>
       <c r="B93" t="n">
-        <v>16.50150299072266</v>
+        <v>16.50150108337402</v>
       </c>
       <c r="C93" t="n">
-        <v>16.60255291716791</v>
+        <v>16.60255099813928</v>
       </c>
       <c r="D93" t="n">
-        <v>16.2746202228983</v>
+        <v>16.27461834177422</v>
       </c>
       <c r="E93" t="n">
-        <v>16.43095986888196</v>
+        <v>16.43095796968715</v>
       </c>
       <c r="F93" t="n">
         <v>4327500</v>
@@ -2292,16 +2292,16 @@
         <v>44390</v>
       </c>
       <c r="B94" t="n">
-        <v>16.7874927520752</v>
+        <v>16.78749084472656</v>
       </c>
       <c r="C94" t="n">
-        <v>16.91142006005396</v>
+        <v>16.91141813862505</v>
       </c>
       <c r="D94" t="n">
-        <v>16.43096059459017</v>
+        <v>16.43095872774974</v>
       </c>
       <c r="E94" t="n">
-        <v>16.45383978992295</v>
+        <v>16.45383792048305</v>
       </c>
       <c r="F94" t="n">
         <v>6446000</v>
@@ -2312,16 +2312,16 @@
         <v>44391</v>
       </c>
       <c r="B95" t="n">
-        <v>16.72266578674316</v>
+        <v>16.7226676940918</v>
       </c>
       <c r="C95" t="n">
-        <v>17.08873104399359</v>
+        <v>17.08873299309478</v>
       </c>
       <c r="D95" t="n">
-        <v>16.67309450664453</v>
+        <v>16.67309640833917</v>
       </c>
       <c r="E95" t="n">
-        <v>16.9304840554177</v>
+        <v>16.9304859864696</v>
       </c>
       <c r="F95" t="n">
         <v>5548000</v>
@@ -2352,16 +2352,16 @@
         <v>44393</v>
       </c>
       <c r="B97" t="n">
-        <v>16.67119216918945</v>
+        <v>16.67119026184082</v>
       </c>
       <c r="C97" t="n">
-        <v>16.86947550939675</v>
+        <v>16.86947357936254</v>
       </c>
       <c r="D97" t="n">
-        <v>16.52247830033713</v>
+        <v>16.52247641000283</v>
       </c>
       <c r="E97" t="n">
-        <v>16.54154278229579</v>
+        <v>16.54154088978033</v>
       </c>
       <c r="F97" t="n">
         <v>7965000</v>
@@ -2372,16 +2372,16 @@
         <v>44396</v>
       </c>
       <c r="B98" t="n">
-        <v>16.65402793884277</v>
+        <v>16.65403175354004</v>
       </c>
       <c r="C98" t="n">
-        <v>16.79702334245145</v>
+        <v>16.7970271899026</v>
       </c>
       <c r="D98" t="n">
-        <v>16.4042660037187</v>
+        <v>16.40426976120661</v>
       </c>
       <c r="E98" t="n">
-        <v>16.58539218156415</v>
+        <v>16.58539598054001</v>
       </c>
       <c r="F98" t="n">
         <v>7763500</v>
@@ -2392,16 +2392,16 @@
         <v>44397</v>
       </c>
       <c r="B99" t="n">
-        <v>16.51103782653809</v>
+        <v>16.51103591918945</v>
       </c>
       <c r="C99" t="n">
-        <v>16.71694877821082</v>
+        <v>16.71694684707543</v>
       </c>
       <c r="D99" t="n">
-        <v>16.45956099775114</v>
+        <v>16.45955909634909</v>
       </c>
       <c r="E99" t="n">
-        <v>16.6540314419629</v>
+        <v>16.6540295180957</v>
       </c>
       <c r="F99" t="n">
         <v>3835500</v>
@@ -2412,16 +2412,16 @@
         <v>44398</v>
       </c>
       <c r="B100" t="n">
-        <v>16.59683227539062</v>
+        <v>16.59683036804199</v>
       </c>
       <c r="C100" t="n">
-        <v>16.59683227539062</v>
+        <v>16.59683036804199</v>
       </c>
       <c r="D100" t="n">
-        <v>16.41570608218979</v>
+        <v>16.41570419565662</v>
       </c>
       <c r="E100" t="n">
-        <v>16.51675600626886</v>
+        <v>16.51675410812279</v>
       </c>
       <c r="F100" t="n">
         <v>4032000</v>
@@ -2452,16 +2452,16 @@
         <v>44400</v>
       </c>
       <c r="B102" t="n">
-        <v>16.68263053894043</v>
+        <v>16.68262672424316</v>
       </c>
       <c r="C102" t="n">
-        <v>16.73029447031815</v>
+        <v>16.73029064472191</v>
       </c>
       <c r="D102" t="n">
-        <v>16.56060876542906</v>
+        <v>16.56060497863364</v>
       </c>
       <c r="E102" t="n">
-        <v>16.64449793922831</v>
+        <v>16.64449413325056</v>
       </c>
       <c r="F102" t="n">
         <v>4154500</v>
@@ -2512,16 +2512,16 @@
         <v>44405</v>
       </c>
       <c r="B105" t="n">
-        <v>16.79321098327637</v>
+        <v>16.793212890625</v>
       </c>
       <c r="C105" t="n">
-        <v>17.38044062591602</v>
+        <v>17.38044259996134</v>
       </c>
       <c r="D105" t="n">
-        <v>16.42333460278985</v>
+        <v>16.42333646812846</v>
       </c>
       <c r="E105" t="n">
-        <v>17.34993563859687</v>
+        <v>17.34993760917749</v>
       </c>
       <c r="F105" t="n">
         <v>14614500</v>
@@ -2592,16 +2592,16 @@
         <v>44411</v>
       </c>
       <c r="B109" t="n">
-        <v>16.53010559082031</v>
+        <v>16.53010368347168</v>
       </c>
       <c r="C109" t="n">
-        <v>16.68072501238404</v>
+        <v>16.68072308765598</v>
       </c>
       <c r="D109" t="n">
-        <v>16.26127727909034</v>
+        <v>16.26127540276083</v>
       </c>
       <c r="E109" t="n">
-        <v>16.68072501238404</v>
+        <v>16.68072308765598</v>
       </c>
       <c r="F109" t="n">
         <v>5450500</v>
@@ -2632,16 +2632,16 @@
         <v>44413</v>
       </c>
       <c r="B111" t="n">
-        <v>16.5872974395752</v>
+        <v>16.58729934692383</v>
       </c>
       <c r="C111" t="n">
-        <v>16.93810928427588</v>
+        <v>16.93811123196384</v>
       </c>
       <c r="D111" t="n">
-        <v>16.47480883917376</v>
+        <v>16.47481073358749</v>
       </c>
       <c r="E111" t="n">
-        <v>16.59301769200566</v>
+        <v>16.59301960001205</v>
       </c>
       <c r="F111" t="n">
         <v>13427000</v>
@@ -2652,16 +2652,16 @@
         <v>44414</v>
       </c>
       <c r="B112" t="n">
-        <v>16.73983001708984</v>
+        <v>16.73982620239258</v>
       </c>
       <c r="C112" t="n">
-        <v>16.78368287669021</v>
+        <v>16.78367905199969</v>
       </c>
       <c r="D112" t="n">
-        <v>16.37567200170541</v>
+        <v>16.37566826999301</v>
       </c>
       <c r="E112" t="n">
-        <v>16.63115427426481</v>
+        <v>16.63115048433273</v>
       </c>
       <c r="F112" t="n">
         <v>15424500</v>
@@ -2712,16 +2712,16 @@
         <v>44419</v>
       </c>
       <c r="B115" t="n">
-        <v>17.2088451385498</v>
+        <v>17.20884895324707</v>
       </c>
       <c r="C115" t="n">
-        <v>17.57872328499242</v>
+        <v>17.57872718168084</v>
       </c>
       <c r="D115" t="n">
-        <v>17.1974064517711</v>
+        <v>17.19741026393275</v>
       </c>
       <c r="E115" t="n">
-        <v>17.57872328499242</v>
+        <v>17.57872718168084</v>
       </c>
       <c r="F115" t="n">
         <v>6265000</v>
@@ -2752,16 +2752,16 @@
         <v>44421</v>
       </c>
       <c r="B117" t="n">
-        <v>16.91141891479492</v>
+        <v>16.91142082214355</v>
       </c>
       <c r="C117" t="n">
-        <v>17.27367130114663</v>
+        <v>17.27367324935177</v>
       </c>
       <c r="D117" t="n">
-        <v>16.53010204884227</v>
+        <v>16.53010391318421</v>
       </c>
       <c r="E117" t="n">
-        <v>16.82562239267279</v>
+        <v>16.82562429034489</v>
       </c>
       <c r="F117" t="n">
         <v>5547600</v>
@@ -2772,16 +2772,16 @@
         <v>44424</v>
       </c>
       <c r="B118" t="n">
-        <v>16.44430732727051</v>
+        <v>16.44430541992188</v>
       </c>
       <c r="C118" t="n">
-        <v>17.04488122962231</v>
+        <v>17.04487925261408</v>
       </c>
       <c r="D118" t="n">
-        <v>16.27271426423787</v>
+        <v>16.27271237679204</v>
       </c>
       <c r="E118" t="n">
-        <v>16.86375683487669</v>
+        <v>16.86375487887679</v>
       </c>
       <c r="F118" t="n">
         <v>7814500</v>
@@ -2792,16 +2792,16 @@
         <v>44425</v>
       </c>
       <c r="B119" t="n">
-        <v>16.16785049438477</v>
+        <v>16.16784858703613</v>
       </c>
       <c r="C119" t="n">
-        <v>16.39664244399077</v>
+        <v>16.39664050965117</v>
       </c>
       <c r="D119" t="n">
-        <v>15.70073708227531</v>
+        <v>15.70073523003284</v>
       </c>
       <c r="E119" t="n">
-        <v>16.16785049438477</v>
+        <v>16.16784858703613</v>
       </c>
       <c r="F119" t="n">
         <v>9967800</v>
@@ -2812,16 +2812,16 @@
         <v>44426</v>
       </c>
       <c r="B120" t="n">
-        <v>15.88186454772949</v>
+        <v>15.88186550140381</v>
       </c>
       <c r="C120" t="n">
-        <v>16.30131406434622</v>
+        <v>16.30131504320764</v>
       </c>
       <c r="D120" t="n">
-        <v>15.64354124801175</v>
+        <v>15.64354218737522</v>
       </c>
       <c r="E120" t="n">
-        <v>16.16785178008579</v>
+        <v>16.16785275093307</v>
       </c>
       <c r="F120" t="n">
         <v>10736900</v>
@@ -2832,16 +2832,16 @@
         <v>44427</v>
       </c>
       <c r="B121" t="n">
-        <v>16.6635627746582</v>
+        <v>16.66356468200684</v>
       </c>
       <c r="C121" t="n">
-        <v>16.87328841811889</v>
+        <v>16.87329034947318</v>
       </c>
       <c r="D121" t="n">
-        <v>15.57680923404292</v>
+        <v>15.57681101699932</v>
       </c>
       <c r="E121" t="n">
-        <v>15.71026968478171</v>
+        <v>15.71027148301428</v>
       </c>
       <c r="F121" t="n">
         <v>14455000</v>
@@ -2872,16 +2872,16 @@
         <v>44431</v>
       </c>
       <c r="B123" t="n">
-        <v>16.69216346740723</v>
+        <v>16.69216537475586</v>
       </c>
       <c r="C123" t="n">
-        <v>17.16881004791025</v>
+        <v>17.16881200972343</v>
       </c>
       <c r="D123" t="n">
-        <v>16.52057040750415</v>
+        <v>16.52057229524551</v>
       </c>
       <c r="E123" t="n">
-        <v>16.97815068840407</v>
+        <v>16.97815262843136</v>
       </c>
       <c r="F123" t="n">
         <v>5050600</v>
@@ -2892,16 +2892,16 @@
         <v>44432</v>
       </c>
       <c r="B124" t="n">
-        <v>16.91141891479492</v>
+        <v>16.91142082214355</v>
       </c>
       <c r="C124" t="n">
-        <v>17.05441251224439</v>
+        <v>17.05441443572051</v>
       </c>
       <c r="D124" t="n">
-        <v>16.66356249736014</v>
+        <v>16.66356437675437</v>
       </c>
       <c r="E124" t="n">
-        <v>16.78749161520865</v>
+        <v>16.78749350858018</v>
       </c>
       <c r="F124" t="n">
         <v>4198100</v>
@@ -2932,16 +2932,16 @@
         <v>44434</v>
       </c>
       <c r="B126" t="n">
-        <v>16.55870246887207</v>
+        <v>16.5587043762207</v>
       </c>
       <c r="C126" t="n">
-        <v>17.00674958541756</v>
+        <v>17.00675154437543</v>
       </c>
       <c r="D126" t="n">
-        <v>16.55870246887207</v>
+        <v>16.5587043762207</v>
       </c>
       <c r="E126" t="n">
-        <v>16.93048620774466</v>
+        <v>16.93048815791797</v>
       </c>
       <c r="F126" t="n">
         <v>4969900</v>
@@ -2952,16 +2952,16 @@
         <v>44435</v>
       </c>
       <c r="B127" t="n">
-        <v>16.5872974395752</v>
+        <v>16.58729934692383</v>
       </c>
       <c r="C127" t="n">
-        <v>16.72075969280097</v>
+        <v>16.72076161549623</v>
       </c>
       <c r="D127" t="n">
-        <v>16.39663993509303</v>
+        <v>16.39664182051824</v>
       </c>
       <c r="E127" t="n">
-        <v>16.558699813947</v>
+        <v>16.55870171800724</v>
       </c>
       <c r="F127" t="n">
         <v>5662600</v>
@@ -2972,16 +2972,16 @@
         <v>44438</v>
       </c>
       <c r="B128" t="n">
-        <v>16.3585090637207</v>
+        <v>16.35851097106934</v>
       </c>
       <c r="C128" t="n">
-        <v>16.79702482484782</v>
+        <v>16.79702678332595</v>
       </c>
       <c r="D128" t="n">
-        <v>16.16784972092418</v>
+        <v>16.16785160604255</v>
       </c>
       <c r="E128" t="n">
-        <v>16.47290503305107</v>
+        <v>16.4729069537379</v>
       </c>
       <c r="F128" t="n">
         <v>16747200</v>
@@ -2992,16 +2992,16 @@
         <v>44439</v>
       </c>
       <c r="B129" t="n">
-        <v>16.02485656738281</v>
+        <v>16.02485847473145</v>
       </c>
       <c r="C129" t="n">
-        <v>16.63496539029478</v>
+        <v>16.63496737026124</v>
       </c>
       <c r="D129" t="n">
-        <v>16.02485656738281</v>
+        <v>16.02485847473145</v>
       </c>
       <c r="E129" t="n">
-        <v>16.37757581585984</v>
+        <v>16.37757776519067</v>
       </c>
       <c r="F129" t="n">
         <v>8477100</v>
@@ -3052,16 +3052,16 @@
         <v>44442</v>
       </c>
       <c r="B132" t="n">
-        <v>17.31180572509766</v>
+        <v>17.31180381774902</v>
       </c>
       <c r="C132" t="n">
-        <v>17.35946966153313</v>
+        <v>17.35946774893307</v>
       </c>
       <c r="D132" t="n">
-        <v>16.69216546012336</v>
+        <v>16.69216362104432</v>
       </c>
       <c r="E132" t="n">
-        <v>16.90188932600712</v>
+        <v>16.90188746382151</v>
       </c>
       <c r="F132" t="n">
         <v>19565300</v>
@@ -3072,16 +3072,16 @@
         <v>44445</v>
       </c>
       <c r="B133" t="n">
-        <v>17.49292945861816</v>
+        <v>17.49292755126953</v>
       </c>
       <c r="C133" t="n">
-        <v>17.66452251450438</v>
+        <v>17.66452058844603</v>
       </c>
       <c r="D133" t="n">
-        <v>17.04488051974584</v>
+        <v>17.04487866125041</v>
       </c>
       <c r="E133" t="n">
-        <v>17.30227010357517</v>
+        <v>17.30226821701516</v>
       </c>
       <c r="F133" t="n">
         <v>6471000</v>
@@ -3092,16 +3092,16 @@
         <v>44447</v>
       </c>
       <c r="B134" t="n">
-        <v>17.07347869873047</v>
+        <v>17.0734806060791</v>
       </c>
       <c r="C134" t="n">
-        <v>17.55012523262749</v>
+        <v>17.55012719322427</v>
       </c>
       <c r="D134" t="n">
-        <v>16.84468858065136</v>
+        <v>16.84469046244091</v>
       </c>
       <c r="E134" t="n">
-        <v>17.49292815767328</v>
+        <v>17.49293011188033</v>
       </c>
       <c r="F134" t="n">
         <v>11069100</v>
@@ -3172,16 +3172,16 @@
         <v>44453</v>
       </c>
       <c r="B138" t="n">
-        <v>17.4738597869873</v>
+        <v>17.47386360168457</v>
       </c>
       <c r="C138" t="n">
-        <v>18.15069873032314</v>
+        <v>18.1507026927803</v>
       </c>
       <c r="D138" t="n">
-        <v>17.39759642334149</v>
+        <v>17.3976002213898</v>
       </c>
       <c r="E138" t="n">
-        <v>17.82657898026294</v>
+        <v>17.82658287196191</v>
       </c>
       <c r="F138" t="n">
         <v>6594500</v>
@@ -3192,16 +3192,16 @@
         <v>44454</v>
       </c>
       <c r="B139" t="n">
-        <v>17.72171974182129</v>
+        <v>17.72172164916992</v>
       </c>
       <c r="C139" t="n">
-        <v>17.82658256979756</v>
+        <v>17.82658448843234</v>
       </c>
       <c r="D139" t="n">
-        <v>17.27367261746679</v>
+        <v>17.27367447659312</v>
       </c>
       <c r="E139" t="n">
-        <v>17.46433015584083</v>
+        <v>17.46433203548721</v>
       </c>
       <c r="F139" t="n">
         <v>8756500</v>
@@ -3212,16 +3212,16 @@
         <v>44455</v>
       </c>
       <c r="B140" t="n">
-        <v>18.26509857177734</v>
+        <v>18.26509475708008</v>
       </c>
       <c r="C140" t="n">
-        <v>18.33182880852791</v>
+        <v>18.33182497989392</v>
       </c>
       <c r="D140" t="n">
-        <v>17.72172170879404</v>
+        <v>17.72171800758197</v>
       </c>
       <c r="E140" t="n">
-        <v>17.72172170879404</v>
+        <v>17.72171800758197</v>
       </c>
       <c r="F140" t="n">
         <v>17281800</v>
@@ -3232,16 +3232,16 @@
         <v>44456</v>
       </c>
       <c r="B141" t="n">
-        <v>18.11256790161133</v>
+        <v>18.11256980895996</v>
       </c>
       <c r="C141" t="n">
-        <v>18.4462208318724</v>
+        <v>18.44622277435644</v>
       </c>
       <c r="D141" t="n">
-        <v>18.11256790161133</v>
+        <v>18.11256980895996</v>
       </c>
       <c r="E141" t="n">
-        <v>18.28416094107486</v>
+        <v>18.28416286649314</v>
       </c>
       <c r="F141" t="n">
         <v>23104900</v>
@@ -3252,16 +3252,16 @@
         <v>44459</v>
       </c>
       <c r="B142" t="n">
-        <v>17.94097709655762</v>
+        <v>17.94097900390625</v>
       </c>
       <c r="C142" t="n">
-        <v>18.12210330724501</v>
+        <v>18.12210523384961</v>
       </c>
       <c r="D142" t="n">
-        <v>17.63592357430248</v>
+        <v>17.63592544922014</v>
       </c>
       <c r="E142" t="n">
-        <v>18.02677362697468</v>
+        <v>18.02677554344455</v>
       </c>
       <c r="F142" t="n">
         <v>15522000</v>
@@ -3272,16 +3272,16 @@
         <v>44460</v>
       </c>
       <c r="B143" t="n">
-        <v>18.57968139648438</v>
+        <v>18.57968521118164</v>
       </c>
       <c r="C143" t="n">
-        <v>18.74174128832697</v>
+        <v>18.74174513629765</v>
       </c>
       <c r="D143" t="n">
-        <v>17.82658082963624</v>
+        <v>17.82658448971026</v>
       </c>
       <c r="E143" t="n">
-        <v>18.06490409303639</v>
+        <v>18.06490780204188</v>
       </c>
       <c r="F143" t="n">
         <v>17756900</v>
@@ -3312,16 +3312,16 @@
         <v>44462</v>
       </c>
       <c r="B145" t="n">
-        <v>18.29369735717773</v>
+        <v>18.2936954498291</v>
       </c>
       <c r="C145" t="n">
-        <v>18.53202066160796</v>
+        <v>18.53201872941112</v>
       </c>
       <c r="D145" t="n">
-        <v>18.07443853522241</v>
+        <v>18.07443665073428</v>
       </c>
       <c r="E145" t="n">
-        <v>18.34136129075877</v>
+        <v>18.34135937844058</v>
       </c>
       <c r="F145" t="n">
         <v>20822300</v>
@@ -3352,16 +3352,16 @@
         <v>44466</v>
       </c>
       <c r="B147" t="n">
-        <v>18.35089492797852</v>
+        <v>18.35089111328125</v>
       </c>
       <c r="C147" t="n">
-        <v>18.46529091717547</v>
+        <v>18.46528707869811</v>
       </c>
       <c r="D147" t="n">
-        <v>17.83611570398607</v>
+        <v>17.83611199629868</v>
       </c>
       <c r="E147" t="n">
-        <v>18.01724192927185</v>
+        <v>18.01723818393279</v>
       </c>
       <c r="F147" t="n">
         <v>7788100</v>
@@ -3372,16 +3372,16 @@
         <v>44467</v>
       </c>
       <c r="B148" t="n">
-        <v>18.2841625213623</v>
+        <v>18.28416442871094</v>
       </c>
       <c r="C148" t="n">
-        <v>18.29369567085224</v>
+        <v>18.29369757919535</v>
       </c>
       <c r="D148" t="n">
-        <v>18.01723979043107</v>
+        <v>18.01724166993512</v>
       </c>
       <c r="E148" t="n">
-        <v>18.23649677391261</v>
+        <v>18.2364986762889</v>
       </c>
       <c r="F148" t="n">
         <v>11310100</v>
@@ -3392,16 +3392,16 @@
         <v>44468</v>
       </c>
       <c r="B149" t="n">
-        <v>18.08397102355957</v>
+        <v>18.08396911621094</v>
       </c>
       <c r="C149" t="n">
-        <v>18.42715715121949</v>
+        <v>18.4271552076744</v>
       </c>
       <c r="D149" t="n">
-        <v>17.9695768598479</v>
+        <v>17.96957496456462</v>
       </c>
       <c r="E149" t="n">
-        <v>18.29369668746839</v>
+        <v>18.29369475799961</v>
       </c>
       <c r="F149" t="n">
         <v>10203400</v>
@@ -3412,16 +3412,16 @@
         <v>44469</v>
       </c>
       <c r="B150" t="n">
-        <v>18.15070152282715</v>
+        <v>18.15070533752441</v>
       </c>
       <c r="C150" t="n">
-        <v>18.62734807351153</v>
+        <v>18.62735198838466</v>
       </c>
       <c r="D150" t="n">
-        <v>18.04583869983265</v>
+        <v>18.0458424924911</v>
       </c>
       <c r="E150" t="n">
-        <v>18.30322827358517</v>
+        <v>18.30323212033868</v>
       </c>
       <c r="F150" t="n">
         <v>10293000</v>
@@ -3432,16 +3432,16 @@
         <v>44470</v>
       </c>
       <c r="B151" t="n">
-        <v>18.45575332641602</v>
+        <v>18.45575523376465</v>
       </c>
       <c r="C151" t="n">
-        <v>18.56061432150102</v>
+        <v>18.56061623968673</v>
       </c>
       <c r="D151" t="n">
-        <v>18.00770444630528</v>
+        <v>18.00770630734936</v>
       </c>
       <c r="E151" t="n">
-        <v>18.19836377634331</v>
+        <v>18.19836565709148</v>
       </c>
       <c r="F151" t="n">
         <v>5841800</v>
@@ -3452,16 +3452,16 @@
         <v>44473</v>
       </c>
       <c r="B152" t="n">
-        <v>18.41762542724609</v>
+        <v>18.41762351989746</v>
       </c>
       <c r="C152" t="n">
-        <v>18.49388881504631</v>
+        <v>18.49388689979976</v>
       </c>
       <c r="D152" t="n">
-        <v>18.07443927301384</v>
+        <v>18.07443740120593</v>
       </c>
       <c r="E152" t="n">
-        <v>18.38902779323513</v>
+        <v>18.3890258888481</v>
       </c>
       <c r="F152" t="n">
         <v>9789400</v>
@@ -3472,16 +3472,16 @@
         <v>44474</v>
       </c>
       <c r="B153" t="n">
-        <v>18.32229232788086</v>
+        <v>18.32229423522949</v>
       </c>
       <c r="C153" t="n">
-        <v>18.49388537306099</v>
+        <v>18.49388729827244</v>
       </c>
       <c r="D153" t="n">
-        <v>18.04583828040574</v>
+        <v>18.04584015897554</v>
       </c>
       <c r="E153" t="n">
-        <v>18.34135862584804</v>
+        <v>18.34136053518147</v>
       </c>
       <c r="F153" t="n">
         <v>8000200</v>
@@ -3492,16 +3492,16 @@
         <v>44475</v>
       </c>
       <c r="B154" t="n">
-        <v>18.27167892456055</v>
+        <v>18.27167701721191</v>
       </c>
       <c r="C154" t="n">
-        <v>18.63481816893143</v>
+        <v>18.63481622367532</v>
       </c>
       <c r="D154" t="n">
-        <v>18.06143878380436</v>
+        <v>18.06143689840233</v>
       </c>
       <c r="E154" t="n">
-        <v>18.11877617550022</v>
+        <v>18.11877428411284</v>
       </c>
       <c r="F154" t="n">
         <v>10611600</v>
@@ -3512,16 +3512,16 @@
         <v>44476</v>
       </c>
       <c r="B155" t="n">
-        <v>18.0805492401123</v>
+        <v>18.08055114746094</v>
       </c>
       <c r="C155" t="n">
-        <v>18.36723797984786</v>
+        <v>18.36723991743979</v>
       </c>
       <c r="D155" t="n">
-        <v>17.99454225364713</v>
+        <v>17.99454415192273</v>
       </c>
       <c r="E155" t="n">
-        <v>18.27167628175104</v>
+        <v>18.271678209262</v>
       </c>
       <c r="F155" t="n">
         <v>7169200</v>
@@ -3552,16 +3552,16 @@
         <v>44480</v>
       </c>
       <c r="B157" t="n">
-        <v>16.62798690795898</v>
+        <v>16.62798881530762</v>
       </c>
       <c r="C157" t="n">
-        <v>17.5262809836174</v>
+        <v>17.52628299400677</v>
       </c>
       <c r="D157" t="n">
-        <v>16.47508602138593</v>
+        <v>16.47508791119575</v>
       </c>
       <c r="E157" t="n">
-        <v>17.42116094057755</v>
+        <v>17.4211629389089</v>
       </c>
       <c r="F157" t="n">
         <v>31512800</v>
@@ -3592,16 +3592,16 @@
         <v>44483</v>
       </c>
       <c r="B159" t="n">
-        <v>17.06757926940918</v>
+        <v>17.06758117675781</v>
       </c>
       <c r="C159" t="n">
-        <v>17.14402971693091</v>
+        <v>17.14403163282309</v>
       </c>
       <c r="D159" t="n">
-        <v>16.60887476155634</v>
+        <v>16.6088766176435</v>
       </c>
       <c r="E159" t="n">
-        <v>16.96245922054588</v>
+        <v>16.96246111614706</v>
       </c>
       <c r="F159" t="n">
         <v>10051300</v>
@@ -3612,16 +3612,16 @@
         <v>44484</v>
       </c>
       <c r="B160" t="n">
-        <v>16.76177787780762</v>
+        <v>16.76177978515625</v>
       </c>
       <c r="C160" t="n">
-        <v>16.933790021779</v>
+        <v>16.93379194870116</v>
       </c>
       <c r="D160" t="n">
-        <v>15.86348373102988</v>
+        <v>15.86348553616024</v>
       </c>
       <c r="E160" t="n">
-        <v>15.95904724838453</v>
+        <v>15.95904906438921</v>
       </c>
       <c r="F160" t="n">
         <v>78021300</v>
@@ -3632,16 +3632,16 @@
         <v>44487</v>
       </c>
       <c r="B161" t="n">
-        <v>16.20750999450684</v>
+        <v>16.20751190185547</v>
       </c>
       <c r="C161" t="n">
-        <v>16.67577105168735</v>
+        <v>16.67577301414236</v>
       </c>
       <c r="D161" t="n">
-        <v>16.10239176487586</v>
+        <v>16.10239365985386</v>
       </c>
       <c r="E161" t="n">
-        <v>16.5897640675295</v>
+        <v>16.58976601986295</v>
       </c>
       <c r="F161" t="n">
         <v>13070300</v>
@@ -3652,16 +3652,16 @@
         <v>44488</v>
       </c>
       <c r="B162" t="n">
-        <v>15.81570339202881</v>
+        <v>15.81570148468018</v>
       </c>
       <c r="C162" t="n">
-        <v>16.0737243800987</v>
+        <v>16.07372244163314</v>
       </c>
       <c r="D162" t="n">
-        <v>15.63413468728875</v>
+        <v>15.63413280183701</v>
       </c>
       <c r="E162" t="n">
-        <v>16.05461130926624</v>
+        <v>16.05460937310569</v>
       </c>
       <c r="F162" t="n">
         <v>17605400</v>
@@ -3692,16 +3692,16 @@
         <v>44490</v>
       </c>
       <c r="B164" t="n">
-        <v>15.70102882385254</v>
+        <v>15.70102787017822</v>
       </c>
       <c r="C164" t="n">
-        <v>16.21706898421667</v>
+        <v>16.21706799919828</v>
       </c>
       <c r="D164" t="n">
-        <v>15.31877651567118</v>
+        <v>15.31877558521472</v>
       </c>
       <c r="E164" t="n">
-        <v>15.81570360494555</v>
+        <v>15.81570264430594</v>
       </c>
       <c r="F164" t="n">
         <v>11995800</v>
@@ -3732,16 +3732,16 @@
         <v>44494</v>
       </c>
       <c r="B166" t="n">
-        <v>15.41433715820312</v>
+        <v>15.41433620452881</v>
       </c>
       <c r="C166" t="n">
-        <v>15.66280159699508</v>
+        <v>15.66280062794844</v>
       </c>
       <c r="D166" t="n">
-        <v>15.1372049374846</v>
+        <v>15.13720400095626</v>
       </c>
       <c r="E166" t="n">
-        <v>15.39522591115963</v>
+        <v>15.39522495866771</v>
       </c>
       <c r="F166" t="n">
         <v>20484500</v>
@@ -3772,16 +3772,16 @@
         <v>44496</v>
       </c>
       <c r="B168" t="n">
-        <v>14.94607925415039</v>
+        <v>14.94607830047607</v>
       </c>
       <c r="C168" t="n">
-        <v>15.38566984725368</v>
+        <v>15.38566886553011</v>
       </c>
       <c r="D168" t="n">
-        <v>14.81229049577588</v>
+        <v>14.81228955063831</v>
       </c>
       <c r="E168" t="n">
-        <v>15.38566984725368</v>
+        <v>15.38566886553011</v>
       </c>
       <c r="F168" t="n">
         <v>9783700</v>
@@ -3812,16 +3812,16 @@
         <v>44498</v>
       </c>
       <c r="B170" t="n">
-        <v>14.61160755157471</v>
+        <v>14.61160945892334</v>
       </c>
       <c r="C170" t="n">
-        <v>15.21365558640951</v>
+        <v>15.21365757234741</v>
       </c>
       <c r="D170" t="n">
-        <v>14.50648840061422</v>
+        <v>14.50649029424096</v>
       </c>
       <c r="E170" t="n">
-        <v>15.0034163731272</v>
+        <v>15.0034183316212</v>
       </c>
       <c r="F170" t="n">
         <v>13706000</v>
@@ -3872,16 +3872,16 @@
         <v>44504</v>
       </c>
       <c r="B173" t="n">
-        <v>14.52560138702393</v>
+        <v>14.52560043334961</v>
       </c>
       <c r="C173" t="n">
-        <v>14.73584061228703</v>
+        <v>14.73583964480952</v>
       </c>
       <c r="D173" t="n">
-        <v>14.30580653757357</v>
+        <v>14.30580559832982</v>
       </c>
       <c r="E173" t="n">
-        <v>14.69761538145387</v>
+        <v>14.69761441648602</v>
       </c>
       <c r="F173" t="n">
         <v>4262500</v>
@@ -4012,16 +4012,16 @@
         <v>44516</v>
       </c>
       <c r="B180" t="n">
-        <v>14.18157196044922</v>
+        <v>14.18157386779785</v>
       </c>
       <c r="C180" t="n">
-        <v>14.86007037887054</v>
+        <v>14.86007237747372</v>
       </c>
       <c r="D180" t="n">
-        <v>14.0000014605465</v>
+        <v>14.00000334347483</v>
       </c>
       <c r="E180" t="n">
-        <v>14.81228862040344</v>
+        <v>14.81229061258022</v>
       </c>
       <c r="F180" t="n">
         <v>11424100</v>
@@ -4032,16 +4032,16 @@
         <v>44517</v>
       </c>
       <c r="B181" t="n">
-        <v>13.6273078918457</v>
+        <v>13.62730693817139</v>
       </c>
       <c r="C181" t="n">
-        <v>14.42048210846616</v>
+        <v>14.42048109928345</v>
       </c>
       <c r="D181" t="n">
-        <v>13.49351912937716</v>
+        <v>13.49351818506572</v>
       </c>
       <c r="E181" t="n">
-        <v>14.42048210846616</v>
+        <v>14.42048109928345</v>
       </c>
       <c r="F181" t="n">
         <v>10535200</v>
@@ -4092,16 +4092,16 @@
         <v>44522</v>
       </c>
       <c r="B184" t="n">
-        <v>13.17816066741943</v>
+        <v>13.17815971374512</v>
       </c>
       <c r="C184" t="n">
-        <v>13.56996950554565</v>
+        <v>13.569968523517</v>
       </c>
       <c r="D184" t="n">
-        <v>13.12082236633105</v>
+        <v>13.12082141680619</v>
       </c>
       <c r="E184" t="n">
-        <v>13.52218773986557</v>
+        <v>13.52218676129477</v>
       </c>
       <c r="F184" t="n">
         <v>12046100</v>
@@ -4132,16 +4132,16 @@
         <v>44524</v>
       </c>
       <c r="B186" t="n">
-        <v>13.11126708984375</v>
+        <v>13.11126613616943</v>
       </c>
       <c r="C186" t="n">
-        <v>13.38840024450097</v>
+        <v>13.38839927066881</v>
       </c>
       <c r="D186" t="n">
-        <v>12.97747832466525</v>
+        <v>12.97747738072233</v>
       </c>
       <c r="E186" t="n">
-        <v>13.09215401852051</v>
+        <v>13.09215306623642</v>
       </c>
       <c r="F186" t="n">
         <v>5705900</v>
@@ -4192,16 +4192,16 @@
         <v>44529</v>
       </c>
       <c r="B189" t="n">
-        <v>12.47099304199219</v>
+        <v>12.47099208831787</v>
       </c>
       <c r="C189" t="n">
-        <v>13.11126631153039</v>
+        <v>13.11126530889348</v>
       </c>
       <c r="D189" t="n">
-        <v>12.42321127788191</v>
+        <v>12.42321032786153</v>
       </c>
       <c r="E189" t="n">
-        <v>12.88191402607333</v>
+        <v>12.88191304097531</v>
       </c>
       <c r="F189" t="n">
         <v>13464500</v>
@@ -4232,16 +4232,16 @@
         <v>44531</v>
       </c>
       <c r="B191" t="n">
-        <v>11.91672611236572</v>
+        <v>11.91672706604004</v>
       </c>
       <c r="C191" t="n">
-        <v>12.37542883541339</v>
+        <v>12.37542982579687</v>
       </c>
       <c r="D191" t="n">
-        <v>11.81160605481299</v>
+        <v>11.81160700007474</v>
       </c>
       <c r="E191" t="n">
-        <v>12.29897838157211</v>
+        <v>12.2989793658374</v>
       </c>
       <c r="F191" t="n">
         <v>5991300</v>
@@ -4312,16 +4312,16 @@
         <v>44537</v>
       </c>
       <c r="B195" t="n">
-        <v>13.4266242980957</v>
+        <v>13.42662334442139</v>
       </c>
       <c r="C195" t="n">
-        <v>13.76109481466241</v>
+        <v>13.76109383723112</v>
       </c>
       <c r="D195" t="n">
-        <v>13.40751122844893</v>
+        <v>13.40751027613218</v>
       </c>
       <c r="E195" t="n">
-        <v>13.56996867500125</v>
+        <v>13.56996771114538</v>
       </c>
       <c r="F195" t="n">
         <v>14090400</v>
@@ -4392,16 +4392,16 @@
         <v>44543</v>
       </c>
       <c r="B199" t="n">
-        <v>13.74198246002197</v>
+        <v>13.74198436737061</v>
       </c>
       <c r="C199" t="n">
-        <v>14.12423473388242</v>
+        <v>14.12423669428659</v>
       </c>
       <c r="D199" t="n">
-        <v>13.66553200524988</v>
+        <v>13.66553390198741</v>
       </c>
       <c r="E199" t="n">
-        <v>13.9617772896514</v>
+        <v>13.96177922750694</v>
       </c>
       <c r="F199" t="n">
         <v>11783000</v>
@@ -4452,16 +4452,16 @@
         <v>44546</v>
       </c>
       <c r="B202" t="n">
-        <v>13.89488506317139</v>
+        <v>13.89488410949707</v>
       </c>
       <c r="C202" t="n">
-        <v>14.28669391947506</v>
+        <v>14.28669293890897</v>
       </c>
       <c r="D202" t="n">
-        <v>13.82799113493264</v>
+        <v>13.82799018584958</v>
       </c>
       <c r="E202" t="n">
-        <v>14.21024345538466</v>
+        <v>14.21024248006574</v>
       </c>
       <c r="F202" t="n">
         <v>5287600</v>
@@ -4472,16 +4472,16 @@
         <v>44547</v>
       </c>
       <c r="B203" t="n">
-        <v>13.81843280792236</v>
+        <v>13.81843376159668</v>
       </c>
       <c r="C203" t="n">
-        <v>14.00955894337442</v>
+        <v>14.00955991023924</v>
       </c>
       <c r="D203" t="n">
-        <v>13.64641883033486</v>
+        <v>13.6464197721377</v>
       </c>
       <c r="E203" t="n">
-        <v>13.84710150039985</v>
+        <v>13.84710245605272</v>
       </c>
       <c r="F203" t="n">
         <v>8250000</v>
@@ -4492,16 +4492,16 @@
         <v>44550</v>
       </c>
       <c r="B204" t="n">
-        <v>13.47440624237061</v>
+        <v>13.47440719604492</v>
       </c>
       <c r="C204" t="n">
-        <v>13.86621506179454</v>
+        <v>13.8662160431998</v>
       </c>
       <c r="D204" t="n">
-        <v>13.29283572372549</v>
+        <v>13.29283666454885</v>
       </c>
       <c r="E204" t="n">
-        <v>13.81843329839523</v>
+        <v>13.81843427641866</v>
       </c>
       <c r="F204" t="n">
         <v>6680500</v>
@@ -4512,16 +4512,16 @@
         <v>44551</v>
       </c>
       <c r="B205" t="n">
-        <v>13.61775016784668</v>
+        <v>13.61774921417236</v>
       </c>
       <c r="C205" t="n">
-        <v>13.66553192965524</v>
+        <v>13.66553097263469</v>
       </c>
       <c r="D205" t="n">
-        <v>13.36928573553119</v>
+        <v>13.36928479925726</v>
       </c>
       <c r="E205" t="n">
-        <v>13.48396141705496</v>
+        <v>13.4839604727501</v>
       </c>
       <c r="F205" t="n">
         <v>4083800</v>
@@ -4552,16 +4552,16 @@
         <v>44553</v>
       </c>
       <c r="B207" t="n">
-        <v>13.46484851837158</v>
+        <v>13.4648494720459</v>
       </c>
       <c r="C207" t="n">
-        <v>13.65597464372962</v>
+        <v>13.65597561094082</v>
       </c>
       <c r="D207" t="n">
-        <v>13.32150324083211</v>
+        <v>13.32150418435372</v>
       </c>
       <c r="E207" t="n">
-        <v>13.41706675919176</v>
+        <v>13.41706770948184</v>
       </c>
       <c r="F207" t="n">
         <v>4198000</v>
@@ -4572,16 +4572,16 @@
         <v>44557</v>
       </c>
       <c r="B208" t="n">
-        <v>13.03481483459473</v>
+        <v>13.03481578826904</v>
       </c>
       <c r="C208" t="n">
-        <v>13.56041146463896</v>
+        <v>13.56041245676783</v>
       </c>
       <c r="D208" t="n">
-        <v>12.9010260878162</v>
+        <v>12.90102703170205</v>
       </c>
       <c r="E208" t="n">
-        <v>13.46484885524968</v>
+        <v>13.46484984038684</v>
       </c>
       <c r="F208" t="n">
         <v>14666400</v>
@@ -4592,16 +4592,16 @@
         <v>44558</v>
       </c>
       <c r="B209" t="n">
-        <v>12.51877403259277</v>
+        <v>12.51877498626709</v>
       </c>
       <c r="C209" t="n">
-        <v>13.12082112455441</v>
+        <v>13.12082212409239</v>
       </c>
       <c r="D209" t="n">
-        <v>12.31809136481846</v>
+        <v>12.31809230320487</v>
       </c>
       <c r="E209" t="n">
-        <v>13.12082112455441</v>
+        <v>13.12082212409239</v>
       </c>
       <c r="F209" t="n">
         <v>22962600</v>
@@ -4712,16 +4712,16 @@
         <v>44567</v>
       </c>
       <c r="B215" t="n">
-        <v>11.07577037811279</v>
+        <v>11.07577133178711</v>
       </c>
       <c r="C215" t="n">
-        <v>11.62048009790152</v>
+        <v>11.62048109847782</v>
       </c>
       <c r="D215" t="n">
-        <v>11.02798861589103</v>
+        <v>11.02798956545112</v>
       </c>
       <c r="E215" t="n">
-        <v>11.56314271232445</v>
+        <v>11.56314370796374</v>
       </c>
       <c r="F215" t="n">
         <v>15779400</v>
@@ -4732,16 +4732,16 @@
         <v>44568</v>
       </c>
       <c r="B216" t="n">
-        <v>10.85597610473633</v>
+        <v>10.85597515106201</v>
       </c>
       <c r="C216" t="n">
-        <v>11.11399710881509</v>
+        <v>11.11399613247418</v>
       </c>
       <c r="D216" t="n">
-        <v>10.71263171004464</v>
+        <v>10.71263076896282</v>
       </c>
       <c r="E216" t="n">
-        <v>11.00887794679861</v>
+        <v>11.0088769796922</v>
       </c>
       <c r="F216" t="n">
         <v>11641900</v>
@@ -4752,16 +4752,16 @@
         <v>44571</v>
       </c>
       <c r="B217" t="n">
-        <v>10.7986364364624</v>
+        <v>10.79863739013672</v>
       </c>
       <c r="C217" t="n">
-        <v>10.85597381771528</v>
+        <v>10.8559747764533</v>
       </c>
       <c r="D217" t="n">
-        <v>10.54061548674074</v>
+        <v>10.54061641762812</v>
       </c>
       <c r="E217" t="n">
-        <v>10.76041121184007</v>
+        <v>10.76041216213855</v>
       </c>
       <c r="F217" t="n">
         <v>8755800</v>
@@ -4812,16 +4812,16 @@
         <v>44574</v>
       </c>
       <c r="B220" t="n">
-        <v>11.48669147491455</v>
+        <v>11.48669242858887</v>
       </c>
       <c r="C220" t="n">
-        <v>11.57269754742197</v>
+        <v>11.57269850823688</v>
       </c>
       <c r="D220" t="n">
-        <v>11.15222007350554</v>
+        <v>11.15222099941061</v>
       </c>
       <c r="E220" t="n">
-        <v>11.27645228227571</v>
+        <v>11.27645321849507</v>
       </c>
       <c r="F220" t="n">
         <v>9668300</v>
@@ -4932,16 +4932,16 @@
         <v>44582</v>
       </c>
       <c r="B226" t="n">
-        <v>11.48669147491455</v>
+        <v>11.48669242858887</v>
       </c>
       <c r="C226" t="n">
-        <v>11.63003584045484</v>
+        <v>11.63003680603022</v>
       </c>
       <c r="D226" t="n">
-        <v>11.21911398924284</v>
+        <v>11.21911492070173</v>
       </c>
       <c r="E226" t="n">
-        <v>11.37201488884882</v>
+        <v>11.37201583300219</v>
       </c>
       <c r="F226" t="n">
         <v>8537100</v>
@@ -4952,16 +4952,16 @@
         <v>44585</v>
       </c>
       <c r="B227" t="n">
-        <v>11.50580406188965</v>
+        <v>11.50580596923828</v>
       </c>
       <c r="C227" t="n">
-        <v>11.6395928097279</v>
+        <v>11.63959473925506</v>
       </c>
       <c r="D227" t="n">
-        <v>11.32423446465893</v>
+        <v>11.32423634190827</v>
       </c>
       <c r="E227" t="n">
-        <v>11.4675788355589</v>
+        <v>11.46758073657084</v>
       </c>
       <c r="F227" t="n">
         <v>6551900</v>
@@ -4972,16 +4972,16 @@
         <v>44586</v>
       </c>
       <c r="B228" t="n">
-        <v>11.75426959991455</v>
+        <v>11.75426864624023</v>
       </c>
       <c r="C228" t="n">
-        <v>11.8880574490392</v>
+        <v>11.8880564845101</v>
       </c>
       <c r="D228" t="n">
-        <v>10.98020755433911</v>
+        <v>10.98020666346776</v>
       </c>
       <c r="E228" t="n">
-        <v>11.42935468970662</v>
+        <v>11.42935376239404</v>
       </c>
       <c r="F228" t="n">
         <v>40426700</v>
@@ -4992,16 +4992,16 @@
         <v>44587</v>
       </c>
       <c r="B229" t="n">
-        <v>11.73515605926514</v>
+        <v>11.73515701293945</v>
       </c>
       <c r="C229" t="n">
-        <v>12.21297187011393</v>
+        <v>12.21297286261863</v>
       </c>
       <c r="D229" t="n">
-        <v>11.73515605926514</v>
+        <v>11.73515701293945</v>
       </c>
       <c r="E229" t="n">
-        <v>11.81160651609204</v>
+        <v>11.81160747597921</v>
       </c>
       <c r="F229" t="n">
         <v>11052300</v>
@@ -5032,16 +5032,16 @@
         <v>44589</v>
       </c>
       <c r="B231" t="n">
-        <v>11.83072090148926</v>
+        <v>11.83071899414062</v>
       </c>
       <c r="C231" t="n">
-        <v>12.04096013682132</v>
+        <v>12.04095819557792</v>
       </c>
       <c r="D231" t="n">
-        <v>11.45802419949534</v>
+        <v>11.45802235223286</v>
       </c>
       <c r="E231" t="n">
-        <v>11.9453965994809</v>
+        <v>11.94539467364426</v>
       </c>
       <c r="F231" t="n">
         <v>14924100</v>
@@ -5072,16 +5072,16 @@
         <v>44593</v>
       </c>
       <c r="B233" t="n">
-        <v>12.02184581756592</v>
+        <v>12.0218448638916</v>
       </c>
       <c r="C233" t="n">
-        <v>12.0982962749621</v>
+        <v>12.09829531522309</v>
       </c>
       <c r="D233" t="n">
-        <v>11.83071967407547</v>
+        <v>11.83071873556289</v>
       </c>
       <c r="E233" t="n">
-        <v>11.93583882515488</v>
+        <v>11.93583787830337</v>
       </c>
       <c r="F233" t="n">
         <v>5991900</v>
@@ -5092,16 +5092,16 @@
         <v>44594</v>
       </c>
       <c r="B234" t="n">
-        <v>11.94539356231689</v>
+        <v>11.94539546966553</v>
       </c>
       <c r="C234" t="n">
-        <v>12.27986494660625</v>
+        <v>12.2798669073607</v>
       </c>
       <c r="D234" t="n">
-        <v>11.81160482632891</v>
+        <v>11.81160671231519</v>
       </c>
       <c r="E234" t="n">
-        <v>12.02184400820683</v>
+        <v>12.02184592776248</v>
       </c>
       <c r="F234" t="n">
         <v>9442200</v>
@@ -5112,16 +5112,16 @@
         <v>44595</v>
       </c>
       <c r="B235" t="n">
-        <v>11.94539356231689</v>
+        <v>11.94539546966553</v>
       </c>
       <c r="C235" t="n">
-        <v>12.21297012293166</v>
+        <v>12.21297207300486</v>
       </c>
       <c r="D235" t="n">
-        <v>11.89761180579539</v>
+        <v>11.8976137055146</v>
       </c>
       <c r="E235" t="n">
-        <v>12.04095707535991</v>
+        <v>12.04095899796739</v>
       </c>
       <c r="F235" t="n">
         <v>8796800</v>
@@ -5132,16 +5132,16 @@
         <v>44596</v>
       </c>
       <c r="B236" t="n">
-        <v>12.3276481628418</v>
+        <v>12.32764911651611</v>
       </c>
       <c r="C236" t="n">
-        <v>12.3276481628418</v>
+        <v>12.32764911651611</v>
       </c>
       <c r="D236" t="n">
-        <v>11.56314355689919</v>
+        <v>11.56314445143097</v>
       </c>
       <c r="E236" t="n">
-        <v>11.91672716498799</v>
+        <v>11.91672808687321</v>
       </c>
       <c r="F236" t="n">
         <v>17676100</v>
@@ -5172,16 +5172,16 @@
         <v>44600</v>
       </c>
       <c r="B238" t="n">
-        <v>11.95495128631592</v>
+        <v>11.95495223999023</v>
       </c>
       <c r="C238" t="n">
-        <v>12.20341571587981</v>
+        <v>12.20341668937472</v>
       </c>
       <c r="D238" t="n">
-        <v>11.83071907153397</v>
+        <v>11.83072001529799</v>
       </c>
       <c r="E238" t="n">
-        <v>12.14607742007226</v>
+        <v>12.14607838899316</v>
       </c>
       <c r="F238" t="n">
         <v>8002100</v>
@@ -5232,16 +5232,16 @@
         <v>44603</v>
       </c>
       <c r="B241" t="n">
-        <v>11.79249572753906</v>
+        <v>11.79249477386475</v>
       </c>
       <c r="C241" t="n">
-        <v>12.21297328893528</v>
+        <v>12.2129723012564</v>
       </c>
       <c r="D241" t="n">
-        <v>11.74471395863095</v>
+        <v>11.74471300882081</v>
       </c>
       <c r="E241" t="n">
-        <v>12.18430459213499</v>
+        <v>12.18430360677458</v>
       </c>
       <c r="F241" t="n">
         <v>7316000</v>
@@ -5252,16 +5252,16 @@
         <v>44606</v>
       </c>
       <c r="B242" t="n">
-        <v>11.78293704986572</v>
+        <v>11.78293800354004</v>
       </c>
       <c r="C242" t="n">
-        <v>11.97406317939841</v>
+        <v>11.97406414854188</v>
       </c>
       <c r="D242" t="n">
-        <v>11.63959268055653</v>
+        <v>11.639593622629</v>
       </c>
       <c r="E242" t="n">
-        <v>11.79249358418268</v>
+        <v>11.79249453863047</v>
       </c>
       <c r="F242" t="n">
         <v>5445000</v>
@@ -5292,16 +5292,16 @@
         <v>44608</v>
       </c>
       <c r="B244" t="n">
-        <v>12.47099304199219</v>
+        <v>12.47099208831787</v>
       </c>
       <c r="C244" t="n">
-        <v>12.6430061168833</v>
+        <v>12.6430051500549</v>
       </c>
       <c r="D244" t="n">
-        <v>11.56314316934232</v>
+        <v>11.56314228509255</v>
       </c>
       <c r="E244" t="n">
-        <v>11.65870578620152</v>
+        <v>11.65870489464395</v>
       </c>
       <c r="F244" t="n">
         <v>21489000</v>
@@ -5332,16 +5332,16 @@
         <v>44610</v>
       </c>
       <c r="B246" t="n">
-        <v>12.1365213394165</v>
+        <v>12.13652229309082</v>
       </c>
       <c r="C246" t="n">
-        <v>12.83413289291753</v>
+        <v>12.83413390140938</v>
       </c>
       <c r="D246" t="n">
-        <v>12.1365213394165</v>
+        <v>12.13652229309082</v>
       </c>
       <c r="E246" t="n">
-        <v>12.80546328826094</v>
+        <v>12.80546429449997</v>
       </c>
       <c r="F246" t="n">
         <v>11604500</v>
@@ -5372,16 +5372,16 @@
         <v>44614</v>
       </c>
       <c r="B248" t="n">
-        <v>12.51877403259277</v>
+        <v>12.51877498626709</v>
       </c>
       <c r="C248" t="n">
-        <v>12.63344971255505</v>
+        <v>12.63345067496531</v>
       </c>
       <c r="D248" t="n">
-        <v>12.08873909353262</v>
+        <v>12.08874001444707</v>
       </c>
       <c r="E248" t="n">
-        <v>12.1460773891944</v>
+        <v>12.14607831447686</v>
       </c>
       <c r="F248" t="n">
         <v>15416600</v>
@@ -5392,16 +5392,16 @@
         <v>44615</v>
       </c>
       <c r="B249" t="n">
-        <v>12.73857021331787</v>
+        <v>12.73856925964355</v>
       </c>
       <c r="C249" t="n">
-        <v>12.87235897652213</v>
+        <v>12.87235801283171</v>
       </c>
       <c r="D249" t="n">
-        <v>12.51877536451236</v>
+        <v>12.51877442729301</v>
       </c>
       <c r="E249" t="n">
-        <v>12.51877536451236</v>
+        <v>12.51877442729301</v>
       </c>
       <c r="F249" t="n">
         <v>5598100</v>
@@ -5432,16 +5432,16 @@
         <v>44617</v>
       </c>
       <c r="B251" t="n">
-        <v>12.86280059814453</v>
+        <v>12.86280155181885</v>
       </c>
       <c r="C251" t="n">
-        <v>13.13993370900733</v>
+        <v>13.13993468322886</v>
       </c>
       <c r="D251" t="n">
-        <v>12.72901185410822</v>
+        <v>12.72901279786317</v>
       </c>
       <c r="E251" t="n">
-        <v>12.83413190705149</v>
+        <v>12.83413285860025</v>
       </c>
       <c r="F251" t="n">
         <v>8089600</v>
@@ -5472,16 +5472,16 @@
         <v>44623</v>
       </c>
       <c r="B253" t="n">
-        <v>12.56655597686768</v>
+        <v>12.56655502319336</v>
       </c>
       <c r="C253" t="n">
-        <v>12.95836572339823</v>
+        <v>12.95836473998952</v>
       </c>
       <c r="D253" t="n">
-        <v>12.33720459696787</v>
+        <v>12.337203660699</v>
       </c>
       <c r="E253" t="n">
-        <v>12.80546389210365</v>
+        <v>12.80546292029864</v>
       </c>
       <c r="F253" t="n">
         <v>12631200</v>
@@ -5492,16 +5492,16 @@
         <v>44624</v>
       </c>
       <c r="B254" t="n">
-        <v>12.14607715606689</v>
+        <v>12.14607810974121</v>
       </c>
       <c r="C254" t="n">
-        <v>12.64300509303224</v>
+        <v>12.64300608572388</v>
       </c>
       <c r="D254" t="n">
-        <v>12.13652062174647</v>
+        <v>12.13652157467044</v>
       </c>
       <c r="E254" t="n">
-        <v>12.64300509303224</v>
+        <v>12.64300608572388</v>
       </c>
       <c r="F254" t="n">
         <v>6563400</v>
@@ -5512,16 +5512,16 @@
         <v>44627</v>
       </c>
       <c r="B255" t="n">
-        <v>11.73515605926514</v>
+        <v>11.73515701293945</v>
       </c>
       <c r="C255" t="n">
-        <v>12.17474664170048</v>
+        <v>12.17474763109875</v>
       </c>
       <c r="D255" t="n">
-        <v>11.68737429590799</v>
+        <v>11.68737524569925</v>
       </c>
       <c r="E255" t="n">
-        <v>12.08873964992988</v>
+        <v>12.08874063233868</v>
       </c>
       <c r="F255" t="n">
         <v>12255900</v>
@@ -5532,16 +5532,16 @@
         <v>44628</v>
       </c>
       <c r="B256" t="n">
-        <v>11.75426959991455</v>
+        <v>11.75426864624023</v>
       </c>
       <c r="C256" t="n">
-        <v>11.99317751490728</v>
+        <v>11.99317654184934</v>
       </c>
       <c r="D256" t="n">
-        <v>11.52491822024826</v>
+        <v>11.52491728518221</v>
       </c>
       <c r="E256" t="n">
-        <v>11.74471306458811</v>
+        <v>11.74471211168916</v>
       </c>
       <c r="F256" t="n">
         <v>10151100</v>
@@ -5592,16 +5592,16 @@
         <v>44631</v>
       </c>
       <c r="B259" t="n">
-        <v>12.40409755706787</v>
+        <v>12.40409851074219</v>
       </c>
       <c r="C259" t="n">
-        <v>12.92969511198934</v>
+        <v>12.9296961060736</v>
       </c>
       <c r="D259" t="n">
-        <v>12.20341579878139</v>
+        <v>12.20341673702652</v>
       </c>
       <c r="E259" t="n">
-        <v>12.92969511198934</v>
+        <v>12.9296961060736</v>
       </c>
       <c r="F259" t="n">
         <v>7293900</v>
@@ -5612,16 +5612,16 @@
         <v>44634</v>
       </c>
       <c r="B260" t="n">
-        <v>12.51877403259277</v>
+        <v>12.51877498626709</v>
       </c>
       <c r="C260" t="n">
-        <v>12.74812539251733</v>
+        <v>12.74812636366353</v>
       </c>
       <c r="D260" t="n">
-        <v>12.3849852836228</v>
+        <v>12.38498622710516</v>
       </c>
       <c r="E260" t="n">
-        <v>12.43276704478074</v>
+        <v>12.43276799190309</v>
       </c>
       <c r="F260" t="n">
         <v>4274300</v>
@@ -5632,16 +5632,16 @@
         <v>44635</v>
       </c>
       <c r="B261" t="n">
-        <v>12.82457542419434</v>
+        <v>12.82457637786865</v>
       </c>
       <c r="C261" t="n">
-        <v>12.90102587498907</v>
+        <v>12.90102683434848</v>
       </c>
       <c r="D261" t="n">
-        <v>12.29897789145957</v>
+        <v>12.29897880604886</v>
       </c>
       <c r="E261" t="n">
-        <v>12.29897789145957</v>
+        <v>12.29897880604886</v>
       </c>
       <c r="F261" t="n">
         <v>8181800</v>
@@ -5652,16 +5652,16 @@
         <v>44636</v>
       </c>
       <c r="B262" t="n">
-        <v>12.99659061431885</v>
+        <v>12.99658966064453</v>
       </c>
       <c r="C262" t="n">
-        <v>13.09215323110332</v>
+        <v>13.09215227041673</v>
       </c>
       <c r="D262" t="n">
-        <v>12.73856963514194</v>
+        <v>12.7385687004009</v>
       </c>
       <c r="E262" t="n">
-        <v>12.91058362125988</v>
+        <v>12.91058267389665</v>
       </c>
       <c r="F262" t="n">
         <v>7731200</v>
@@ -5672,16 +5672,16 @@
         <v>44637</v>
       </c>
       <c r="B263" t="n">
-        <v>13.12082290649414</v>
+        <v>13.12082195281982</v>
       </c>
       <c r="C263" t="n">
-        <v>13.24505513783225</v>
+        <v>13.24505417512824</v>
       </c>
       <c r="D263" t="n">
-        <v>12.87235935517934</v>
+        <v>12.87235841956435</v>
       </c>
       <c r="E263" t="n">
-        <v>13.0921542104504</v>
+        <v>13.09215325885984</v>
       </c>
       <c r="F263" t="n">
         <v>6159800</v>
@@ -5712,16 +5712,16 @@
         <v>44641</v>
       </c>
       <c r="B265" t="n">
-        <v>13.56041240692139</v>
+        <v>13.56041145324707</v>
       </c>
       <c r="C265" t="n">
-        <v>13.62730724063966</v>
+        <v>13.62730628226077</v>
       </c>
       <c r="D265" t="n">
-        <v>13.18771665509124</v>
+        <v>13.1877157276278</v>
       </c>
       <c r="E265" t="n">
-        <v>13.58908201195551</v>
+        <v>13.58908105626492</v>
       </c>
       <c r="F265" t="n">
         <v>3916100</v>
@@ -5752,16 +5752,16 @@
         <v>44643</v>
       </c>
       <c r="B267" t="n">
-        <v>14.38225555419922</v>
+        <v>14.38225650787354</v>
       </c>
       <c r="C267" t="n">
-        <v>14.59249475833878</v>
+        <v>14.59249572595387</v>
       </c>
       <c r="D267" t="n">
-        <v>13.87577106870787</v>
+        <v>13.87577198879766</v>
       </c>
       <c r="E267" t="n">
-        <v>14.02867197667799</v>
+        <v>14.0286729069065</v>
       </c>
       <c r="F267" t="n">
         <v>8813400</v>
@@ -5772,16 +5772,16 @@
         <v>44644</v>
       </c>
       <c r="B268" t="n">
-        <v>14.63072109222412</v>
+        <v>14.63072204589844</v>
       </c>
       <c r="C268" t="n">
-        <v>14.74539678187754</v>
+        <v>14.74539774302677</v>
       </c>
       <c r="D268" t="n">
-        <v>14.35358794772134</v>
+        <v>14.35358888333129</v>
       </c>
       <c r="E268" t="n">
-        <v>14.39181317760581</v>
+        <v>14.3918141157074</v>
       </c>
       <c r="F268" t="n">
         <v>7986800</v>
@@ -5792,16 +5792,16 @@
         <v>44645</v>
       </c>
       <c r="B269" t="n">
-        <v>15.13720417022705</v>
+        <v>15.13720512390137</v>
       </c>
       <c r="C269" t="n">
-        <v>15.24232331452872</v>
+        <v>15.24232427482575</v>
       </c>
       <c r="D269" t="n">
-        <v>14.64027531783091</v>
+        <v>14.64027624019771</v>
       </c>
       <c r="E269" t="n">
-        <v>14.71672577029781</v>
+        <v>14.71672669748114</v>
       </c>
       <c r="F269" t="n">
         <v>8426200</v>
@@ -5812,16 +5812,16 @@
         <v>44648</v>
       </c>
       <c r="B270" t="n">
-        <v>15.519455909729</v>
+        <v>15.51945781707764</v>
       </c>
       <c r="C270" t="n">
-        <v>15.77747686163333</v>
+        <v>15.77747880069286</v>
       </c>
       <c r="D270" t="n">
-        <v>14.97474622641265</v>
+        <v>14.9747480668162</v>
       </c>
       <c r="E270" t="n">
-        <v>15.19454104201004</v>
+        <v>15.19454290942648</v>
       </c>
       <c r="F270" t="n">
         <v>14496800</v>
@@ -5832,16 +5832,16 @@
         <v>44649</v>
       </c>
       <c r="B271" t="n">
-        <v>15.50034236907959</v>
+        <v>15.50034427642822</v>
       </c>
       <c r="C271" t="n">
-        <v>15.93037727581141</v>
+        <v>15.93037923607671</v>
       </c>
       <c r="D271" t="n">
-        <v>15.43344845530407</v>
+        <v>15.43345035442127</v>
       </c>
       <c r="E271" t="n">
-        <v>15.72969371176241</v>
+        <v>15.72969564733319</v>
       </c>
       <c r="F271" t="n">
         <v>7323700</v>
@@ -5852,16 +5852,16 @@
         <v>44650</v>
       </c>
       <c r="B272" t="n">
-        <v>15.45256328582764</v>
+        <v>15.45256423950195</v>
       </c>
       <c r="C272" t="n">
-        <v>15.82525903236704</v>
+        <v>15.82526000904275</v>
       </c>
       <c r="D272" t="n">
-        <v>15.39522589929603</v>
+        <v>15.3952268494317</v>
       </c>
       <c r="E272" t="n">
-        <v>15.51945720723495</v>
+        <v>15.51945816503771</v>
       </c>
       <c r="F272" t="n">
         <v>8944100</v>
@@ -5892,16 +5892,16 @@
         <v>44652</v>
       </c>
       <c r="B274" t="n">
-        <v>15.74880981445312</v>
+        <v>15.74881076812744</v>
       </c>
       <c r="C274" t="n">
-        <v>15.97816120133668</v>
+        <v>15.97816216889944</v>
       </c>
       <c r="D274" t="n">
-        <v>15.47167757215655</v>
+        <v>15.47167850904903</v>
       </c>
       <c r="E274" t="n">
-        <v>15.72014203029443</v>
+        <v>15.72014298223276</v>
       </c>
       <c r="F274" t="n">
         <v>8302400</v>
@@ -5932,16 +5932,16 @@
         <v>44656</v>
       </c>
       <c r="B276" t="n">
-        <v>15.45256328582764</v>
+        <v>15.45256423950195</v>
       </c>
       <c r="C276" t="n">
-        <v>15.65324505004958</v>
+        <v>15.65324601610922</v>
       </c>
       <c r="D276" t="n">
-        <v>15.35699975979319</v>
+        <v>15.35700070756969</v>
       </c>
       <c r="E276" t="n">
-        <v>15.57679459376655</v>
+        <v>15.57679555510796</v>
       </c>
       <c r="F276" t="n">
         <v>10716200</v>
@@ -5972,16 +5972,16 @@
         <v>44658</v>
       </c>
       <c r="B278" t="n">
-        <v>15.38567066192627</v>
+        <v>15.38566970825195</v>
       </c>
       <c r="C278" t="n">
-        <v>15.52901505170514</v>
+        <v>15.52901408914568</v>
       </c>
       <c r="D278" t="n">
-        <v>15.25188189646763</v>
+        <v>15.25188095108615</v>
       </c>
       <c r="E278" t="n">
-        <v>15.366557590563</v>
+        <v>15.3665566380734</v>
       </c>
       <c r="F278" t="n">
         <v>6566700</v>
@@ -5992,16 +5992,16 @@
         <v>44659</v>
       </c>
       <c r="B279" t="n">
-        <v>15.40478420257568</v>
+        <v>15.40478324890137</v>
       </c>
       <c r="C279" t="n">
-        <v>15.57679638191676</v>
+        <v>15.57679541759357</v>
       </c>
       <c r="D279" t="n">
-        <v>15.07031273442055</v>
+        <v>15.07031180145259</v>
       </c>
       <c r="E279" t="n">
-        <v>15.32833373751647</v>
+        <v>15.32833278857503</v>
       </c>
       <c r="F279" t="n">
         <v>3069100</v>
@@ -6012,16 +6012,16 @@
         <v>44662</v>
       </c>
       <c r="B280" t="n">
-        <v>15.29010486602783</v>
+        <v>15.29010581970215</v>
       </c>
       <c r="C280" t="n">
-        <v>15.49078661748763</v>
+        <v>15.49078758367887</v>
       </c>
       <c r="D280" t="n">
-        <v>15.21365441460659</v>
+        <v>15.21365536351254</v>
       </c>
       <c r="E280" t="n">
-        <v>15.38566838598501</v>
+        <v>15.38566934561982</v>
       </c>
       <c r="F280" t="n">
         <v>10289300</v>
@@ -6072,16 +6072,16 @@
         <v>44665</v>
       </c>
       <c r="B283" t="n">
-        <v>15.64368915557861</v>
+        <v>15.64369010925293</v>
       </c>
       <c r="C283" t="n">
-        <v>15.79659005658872</v>
+        <v>15.79659101958422</v>
       </c>
       <c r="D283" t="n">
-        <v>15.48123172041506</v>
+        <v>15.4812326641856</v>
       </c>
       <c r="E283" t="n">
-        <v>15.72013960608367</v>
+        <v>15.72014056441858</v>
       </c>
       <c r="F283" t="n">
         <v>4607000</v>
@@ -6092,16 +6092,16 @@
         <v>44669</v>
       </c>
       <c r="B284" t="n">
-        <v>15.31877422332764</v>
+        <v>15.31877517700195</v>
       </c>
       <c r="C284" t="n">
-        <v>15.67235687196327</v>
+        <v>15.67235784764996</v>
       </c>
       <c r="D284" t="n">
-        <v>15.31877422332764</v>
+        <v>15.31877517700195</v>
       </c>
       <c r="E284" t="n">
-        <v>15.56723864214531</v>
+        <v>15.56723961128785</v>
       </c>
       <c r="F284" t="n">
         <v>3539900</v>
@@ -6152,16 +6152,16 @@
         <v>44673</v>
       </c>
       <c r="B287" t="n">
-        <v>15.31877422332764</v>
+        <v>15.31877517700195</v>
       </c>
       <c r="C287" t="n">
-        <v>15.74880732215928</v>
+        <v>15.74880830260542</v>
       </c>
       <c r="D287" t="n">
-        <v>15.14676025470597</v>
+        <v>15.14676119767152</v>
       </c>
       <c r="E287" t="n">
-        <v>15.74880732215928</v>
+        <v>15.74880830260542</v>
       </c>
       <c r="F287" t="n">
         <v>8878800</v>
@@ -6192,16 +6192,16 @@
         <v>44677</v>
       </c>
       <c r="B289" t="n">
-        <v>15.12764930725098</v>
+        <v>15.12764835357666</v>
       </c>
       <c r="C289" t="n">
-        <v>15.30921983544218</v>
+        <v>15.30921887032133</v>
       </c>
       <c r="D289" t="n">
-        <v>15.02253015133491</v>
+        <v>15.02252920428749</v>
       </c>
       <c r="E289" t="n">
-        <v>15.2136563036193</v>
+        <v>15.21365534452294</v>
       </c>
       <c r="F289" t="n">
         <v>9387600</v>
@@ -6212,16 +6212,16 @@
         <v>44678</v>
       </c>
       <c r="B290" t="n">
-        <v>15.18498706817627</v>
+        <v>15.18498611450195</v>
       </c>
       <c r="C290" t="n">
-        <v>15.48123327719457</v>
+        <v>15.48123230491487</v>
       </c>
       <c r="D290" t="n">
-        <v>14.96519131735082</v>
+        <v>14.9651903774805</v>
       </c>
       <c r="E290" t="n">
-        <v>15.2901062203511</v>
+        <v>15.2901052600749</v>
       </c>
       <c r="F290" t="n">
         <v>7959000</v>
@@ -6312,16 +6312,16 @@
         <v>44685</v>
       </c>
       <c r="B295" t="n">
-        <v>14.79764366149902</v>
+        <v>14.79764270782471</v>
       </c>
       <c r="C295" t="n">
-        <v>14.95178655817559</v>
+        <v>14.95178559456712</v>
       </c>
       <c r="D295" t="n">
-        <v>14.25814673878635</v>
+        <v>14.25814581988137</v>
       </c>
       <c r="E295" t="n">
-        <v>14.43155600456466</v>
+        <v>14.43155507448386</v>
       </c>
       <c r="F295" t="n">
         <v>5127000</v>
@@ -6332,16 +6332,16 @@
         <v>44686</v>
       </c>
       <c r="B296" t="n">
-        <v>14.47009181976318</v>
+        <v>14.4700927734375</v>
       </c>
       <c r="C296" t="n">
-        <v>14.74947437288235</v>
+        <v>14.74947534496982</v>
       </c>
       <c r="D296" t="n">
-        <v>14.32558303236861</v>
+        <v>14.32558397651884</v>
       </c>
       <c r="E296" t="n">
-        <v>14.54716280553684</v>
+        <v>14.54716376429064</v>
       </c>
       <c r="F296" t="n">
         <v>6151000</v>
@@ -6412,16 +6412,16 @@
         <v>44692</v>
       </c>
       <c r="B300" t="n">
-        <v>14.60496616363525</v>
+        <v>14.60496520996094</v>
       </c>
       <c r="C300" t="n">
-        <v>14.7880104511626</v>
+        <v>14.78800948553586</v>
       </c>
       <c r="D300" t="n">
-        <v>14.4026545882811</v>
+        <v>14.40265364781732</v>
       </c>
       <c r="E300" t="n">
-        <v>14.45082418598612</v>
+        <v>14.45082324237696</v>
       </c>
       <c r="F300" t="n">
         <v>6181500</v>
@@ -6452,16 +6452,16 @@
         <v>44694</v>
       </c>
       <c r="B302" t="n">
-        <v>14.91324901580811</v>
+        <v>14.91324996948242</v>
       </c>
       <c r="C302" t="n">
-        <v>15.09629328979575</v>
+        <v>15.09629425517541</v>
       </c>
       <c r="D302" t="n">
-        <v>14.62423328847366</v>
+        <v>14.62423422366596</v>
       </c>
       <c r="E302" t="n">
-        <v>14.72057155799894</v>
+        <v>14.7205724993519</v>
       </c>
       <c r="F302" t="n">
         <v>5016200</v>
@@ -6532,16 +6532,16 @@
         <v>44700</v>
       </c>
       <c r="B306" t="n">
-        <v>14.88434886932373</v>
+        <v>14.88434791564941</v>
       </c>
       <c r="C306" t="n">
-        <v>14.95178667425537</v>
+        <v>14.95178571626016</v>
       </c>
       <c r="D306" t="n">
-        <v>14.66277000403615</v>
+        <v>14.6627690645589</v>
       </c>
       <c r="E306" t="n">
-        <v>14.92288436410238</v>
+        <v>14.92288340795901</v>
       </c>
       <c r="F306" t="n">
         <v>6219800</v>
@@ -6552,16 +6552,16 @@
         <v>44701</v>
       </c>
       <c r="B307" t="n">
-        <v>15.37567615509033</v>
+        <v>15.37567710876465</v>
       </c>
       <c r="C307" t="n">
-        <v>15.49128263219524</v>
+        <v>15.49128359304003</v>
       </c>
       <c r="D307" t="n">
-        <v>14.93251753347555</v>
+        <v>14.93251845966301</v>
       </c>
       <c r="E307" t="n">
-        <v>15.02885672377561</v>
+        <v>15.0288576559385</v>
       </c>
       <c r="F307" t="n">
         <v>8142900</v>
@@ -6572,16 +6572,16 @@
         <v>44704</v>
       </c>
       <c r="B308" t="n">
-        <v>15.28897094726562</v>
+        <v>15.28897190093994</v>
       </c>
       <c r="C308" t="n">
-        <v>15.63579037585128</v>
+        <v>15.63579135115902</v>
       </c>
       <c r="D308" t="n">
-        <v>15.17336447107041</v>
+        <v>15.17336541753358</v>
       </c>
       <c r="E308" t="n">
-        <v>15.52981892112058</v>
+        <v>15.52981988981818</v>
       </c>
       <c r="F308" t="n">
         <v>8474400</v>
@@ -6592,16 +6592,16 @@
         <v>44705</v>
       </c>
       <c r="B309" t="n">
-        <v>15.31787204742432</v>
+        <v>15.31787300109863</v>
       </c>
       <c r="C309" t="n">
-        <v>15.3467743549964</v>
+        <v>15.34677531047014</v>
       </c>
       <c r="D309" t="n">
-        <v>14.99995401420009</v>
+        <v>14.99995494808117</v>
       </c>
       <c r="E309" t="n">
-        <v>15.1926323896463</v>
+        <v>15.19263333552333</v>
       </c>
       <c r="F309" t="n">
         <v>5652100</v>
@@ -6612,16 +6612,16 @@
         <v>44706</v>
       </c>
       <c r="B310" t="n">
-        <v>15.14446449279785</v>
+        <v>15.14446353912354</v>
       </c>
       <c r="C310" t="n">
-        <v>15.44311527319793</v>
+        <v>15.44311430071703</v>
       </c>
       <c r="D310" t="n">
-        <v>14.94215291091617</v>
+        <v>14.94215196998178</v>
       </c>
       <c r="E310" t="n">
-        <v>15.16373178124632</v>
+        <v>15.16373082635871</v>
       </c>
       <c r="F310" t="n">
         <v>8129200</v>
@@ -6632,16 +6632,16 @@
         <v>44707</v>
       </c>
       <c r="B311" t="n">
-        <v>15.50091552734375</v>
+        <v>15.50091648101807</v>
       </c>
       <c r="C311" t="n">
-        <v>15.60688881216945</v>
+        <v>15.60688977236364</v>
       </c>
       <c r="D311" t="n">
-        <v>15.0384887361919</v>
+        <v>15.03848966141599</v>
       </c>
       <c r="E311" t="n">
-        <v>15.07702422555801</v>
+        <v>15.07702515315295</v>
       </c>
       <c r="F311" t="n">
         <v>6641000</v>
@@ -6692,16 +6692,16 @@
         <v>44712</v>
       </c>
       <c r="B314" t="n">
-        <v>15.26006889343262</v>
+        <v>15.26006984710693</v>
       </c>
       <c r="C314" t="n">
-        <v>15.39494265040822</v>
+        <v>15.39494361251144</v>
       </c>
       <c r="D314" t="n">
-        <v>15.05775733921065</v>
+        <v>15.05775828024155</v>
       </c>
       <c r="E314" t="n">
-        <v>15.29860438381973</v>
+        <v>15.29860533990231</v>
       </c>
       <c r="F314" t="n">
         <v>5708500</v>
@@ -6752,16 +6752,16 @@
         <v>44715</v>
       </c>
       <c r="B317" t="n">
-        <v>14.88434886932373</v>
+        <v>14.88434791564941</v>
       </c>
       <c r="C317" t="n">
-        <v>15.23116924109026</v>
+        <v>15.23116826519437</v>
       </c>
       <c r="D317" t="n">
-        <v>14.78801059175644</v>
+        <v>14.78800964425473</v>
       </c>
       <c r="E317" t="n">
-        <v>15.17336553954295</v>
+        <v>15.17336456735067</v>
       </c>
       <c r="F317" t="n">
         <v>4184100</v>
@@ -6772,16 +6772,16 @@
         <v>44718</v>
       </c>
       <c r="B318" t="n">
-        <v>14.90361595153809</v>
+        <v>14.9036169052124</v>
       </c>
       <c r="C318" t="n">
-        <v>15.13482890276379</v>
+        <v>15.1348298712333</v>
       </c>
       <c r="D318" t="n">
-        <v>14.84581225435236</v>
+        <v>14.84581320432785</v>
       </c>
       <c r="E318" t="n">
-        <v>15.01922242715094</v>
+        <v>15.01922338822285</v>
       </c>
       <c r="F318" t="n">
         <v>2626600</v>
@@ -6812,16 +6812,16 @@
         <v>44720</v>
       </c>
       <c r="B320" t="n">
-        <v>15.35640907287598</v>
+        <v>15.35640811920166</v>
       </c>
       <c r="C320" t="n">
-        <v>15.74176494350709</v>
+        <v>15.74176396590114</v>
       </c>
       <c r="D320" t="n">
-        <v>14.9903223279765</v>
+        <v>14.99032139703716</v>
       </c>
       <c r="E320" t="n">
-        <v>15.00958961619079</v>
+        <v>15.00958868405489</v>
       </c>
       <c r="F320" t="n">
         <v>10420600</v>
@@ -6852,16 +6852,16 @@
         <v>44722</v>
       </c>
       <c r="B322" t="n">
-        <v>14.48935890197754</v>
+        <v>14.48935985565186</v>
       </c>
       <c r="C322" t="n">
-        <v>15.01922261074923</v>
+        <v>15.01922359929862</v>
       </c>
       <c r="D322" t="n">
-        <v>14.22924455835858</v>
+        <v>14.22924549491244</v>
       </c>
       <c r="E322" t="n">
-        <v>14.85544653860601</v>
+        <v>14.85544751637582</v>
       </c>
       <c r="F322" t="n">
         <v>15101900</v>
@@ -6892,16 +6892,16 @@
         <v>44726</v>
       </c>
       <c r="B324" t="n">
-        <v>14.05583381652832</v>
+        <v>14.05583477020264</v>
       </c>
       <c r="C324" t="n">
-        <v>14.2099757796794</v>
+        <v>14.2099767438121</v>
       </c>
       <c r="D324" t="n">
-        <v>13.84388815781629</v>
+        <v>13.84388909711031</v>
       </c>
       <c r="E324" t="n">
-        <v>14.01729832574055</v>
+        <v>14.01729927680027</v>
       </c>
       <c r="F324" t="n">
         <v>10130900</v>
@@ -6912,16 +6912,16 @@
         <v>44727</v>
       </c>
       <c r="B325" t="n">
-        <v>14.91324901580811</v>
+        <v>14.91324996948242</v>
       </c>
       <c r="C325" t="n">
-        <v>15.06739190081403</v>
+        <v>15.06739286434549</v>
       </c>
       <c r="D325" t="n">
-        <v>14.25814565925695</v>
+        <v>14.25814657103863</v>
       </c>
       <c r="E325" t="n">
-        <v>14.34485074496072</v>
+        <v>14.34485166228703</v>
       </c>
       <c r="F325" t="n">
         <v>25461900</v>
@@ -6952,16 +6952,16 @@
         <v>44732</v>
       </c>
       <c r="B327" t="n">
-        <v>15.31787204742432</v>
+        <v>15.31787300109863</v>
       </c>
       <c r="C327" t="n">
-        <v>15.5009163203465</v>
+        <v>15.50091728541696</v>
       </c>
       <c r="D327" t="n">
-        <v>14.83617794632596</v>
+        <v>14.83617887001052</v>
       </c>
       <c r="E327" t="n">
-        <v>15.09629320192319</v>
+        <v>15.09629414180225</v>
       </c>
       <c r="F327" t="n">
         <v>7611300</v>
@@ -6992,16 +6992,16 @@
         <v>44734</v>
       </c>
       <c r="B329" t="n">
-        <v>14.44119071960449</v>
+        <v>14.44118976593018</v>
       </c>
       <c r="C329" t="n">
-        <v>15.13483056837639</v>
+        <v>15.13482956889515</v>
       </c>
       <c r="D329" t="n">
-        <v>14.32558423126896</v>
+        <v>14.32558328522912</v>
       </c>
       <c r="E329" t="n">
-        <v>14.68203779999319</v>
+        <v>14.6820368304137</v>
       </c>
       <c r="F329" t="n">
         <v>8791300</v>
@@ -7052,16 +7052,16 @@
         <v>44739</v>
       </c>
       <c r="B332" t="n">
-        <v>14.16180801391602</v>
+        <v>14.1618070602417</v>
       </c>
       <c r="C332" t="n">
-        <v>14.49899429088777</v>
+        <v>14.4989933145069</v>
       </c>
       <c r="D332" t="n">
-        <v>14.10400522965489</v>
+        <v>14.10400427987309</v>
       </c>
       <c r="E332" t="n">
-        <v>14.47972608362827</v>
+        <v>14.47972510854494</v>
       </c>
       <c r="F332" t="n">
         <v>8041800</v>
@@ -7092,16 +7092,16 @@
         <v>44741</v>
       </c>
       <c r="B334" t="n">
-        <v>13.85352325439453</v>
+        <v>13.85352420806885</v>
       </c>
       <c r="C334" t="n">
-        <v>14.1810754089765</v>
+        <v>14.18107638519945</v>
       </c>
       <c r="D334" t="n">
-        <v>13.5934079838411</v>
+        <v>13.59340891960912</v>
       </c>
       <c r="E334" t="n">
-        <v>14.1810754089765</v>
+        <v>14.18107638519945</v>
       </c>
       <c r="F334" t="n">
         <v>8408900</v>
@@ -7112,16 +7112,16 @@
         <v>44742</v>
       </c>
       <c r="B335" t="n">
-        <v>13.74755096435547</v>
+        <v>13.74755001068115</v>
       </c>
       <c r="C335" t="n">
-        <v>13.88242473327139</v>
+        <v>13.88242377024082</v>
       </c>
       <c r="D335" t="n">
-        <v>13.34292782009041</v>
+        <v>13.34292689448499</v>
       </c>
       <c r="E335" t="n">
-        <v>13.58377488602158</v>
+        <v>13.58377394370849</v>
       </c>
       <c r="F335" t="n">
         <v>10650900</v>
@@ -7132,16 +7132,16 @@
         <v>44743</v>
       </c>
       <c r="B336" t="n">
-        <v>14.06546974182129</v>
+        <v>14.06546878814697</v>
       </c>
       <c r="C336" t="n">
-        <v>14.28704861287829</v>
+        <v>14.28704764418037</v>
       </c>
       <c r="D336" t="n">
-        <v>13.54524008938454</v>
+        <v>13.54523917098311</v>
       </c>
       <c r="E336" t="n">
-        <v>13.64157836946027</v>
+        <v>13.64157744452686</v>
       </c>
       <c r="F336" t="n">
         <v>10271400</v>
@@ -7152,16 +7152,16 @@
         <v>44746</v>
       </c>
       <c r="B337" t="n">
-        <v>13.8727912902832</v>
+        <v>13.87279033660889</v>
       </c>
       <c r="C337" t="n">
-        <v>14.14254067846864</v>
+        <v>14.14253970625061</v>
       </c>
       <c r="D337" t="n">
-        <v>13.76681890698379</v>
+        <v>13.76681796059447</v>
       </c>
       <c r="E337" t="n">
-        <v>13.95949638514576</v>
+        <v>13.95949542551097</v>
       </c>
       <c r="F337" t="n">
         <v>1980900</v>
@@ -7192,16 +7192,16 @@
         <v>44748</v>
       </c>
       <c r="B339" t="n">
-        <v>14.35448551177979</v>
+        <v>14.35448455810547</v>
       </c>
       <c r="C339" t="n">
-        <v>14.63386808610274</v>
+        <v>14.63386711386697</v>
       </c>
       <c r="D339" t="n">
-        <v>13.92096095421089</v>
+        <v>13.9209600293388</v>
       </c>
       <c r="E339" t="n">
-        <v>13.96913055366492</v>
+        <v>13.96912962559257</v>
       </c>
       <c r="F339" t="n">
         <v>11107300</v>
@@ -7252,16 +7252,16 @@
         <v>44753</v>
       </c>
       <c r="B342" t="n">
-        <v>14.788010597229</v>
+        <v>14.78800964355469</v>
       </c>
       <c r="C342" t="n">
-        <v>14.89398297821984</v>
+        <v>14.8939820177114</v>
       </c>
       <c r="D342" t="n">
-        <v>14.52789531830785</v>
+        <v>14.52789438140829</v>
       </c>
       <c r="E342" t="n">
-        <v>14.57606491648865</v>
+        <v>14.57606397648265</v>
       </c>
       <c r="F342" t="n">
         <v>3654100</v>
@@ -7312,16 +7312,16 @@
         <v>44756</v>
       </c>
       <c r="B345" t="n">
-        <v>14.759108543396</v>
+        <v>14.75910758972168</v>
       </c>
       <c r="C345" t="n">
-        <v>14.99995561972431</v>
+        <v>14.99995465048742</v>
       </c>
       <c r="D345" t="n">
-        <v>14.51826146706769</v>
+        <v>14.51826052895594</v>
       </c>
       <c r="E345" t="n">
-        <v>14.5278955706229</v>
+        <v>14.52789463188864</v>
       </c>
       <c r="F345" t="n">
         <v>8175300</v>
@@ -7372,16 +7372,16 @@
         <v>44761</v>
       </c>
       <c r="B348" t="n">
-        <v>14.92288494110107</v>
+        <v>14.92288398742676</v>
       </c>
       <c r="C348" t="n">
-        <v>15.10592923744614</v>
+        <v>15.10592827207404</v>
       </c>
       <c r="D348" t="n">
-        <v>14.72057335600104</v>
+        <v>14.72057241525581</v>
       </c>
       <c r="E348" t="n">
-        <v>14.91325083734424</v>
+        <v>14.91324988428561</v>
       </c>
       <c r="F348" t="n">
         <v>3342100</v>
@@ -7392,16 +7392,16 @@
         <v>44762</v>
       </c>
       <c r="B349" t="n">
-        <v>14.82654476165771</v>
+        <v>14.82654571533203</v>
       </c>
       <c r="C349" t="n">
-        <v>15.10592730352741</v>
+        <v>15.10592827517219</v>
       </c>
       <c r="D349" t="n">
-        <v>14.57606360859976</v>
+        <v>14.57606454616261</v>
       </c>
       <c r="E349" t="n">
-        <v>14.89398164180463</v>
+        <v>14.89398259981663</v>
       </c>
       <c r="F349" t="n">
         <v>5599700</v>
@@ -7432,16 +7432,16 @@
         <v>44764</v>
       </c>
       <c r="B351" t="n">
-        <v>15.07702541351318</v>
+        <v>15.07702445983887</v>
       </c>
       <c r="C351" t="n">
-        <v>15.14446321428636</v>
+        <v>15.14446225634637</v>
       </c>
       <c r="D351" t="n">
-        <v>14.78800967987438</v>
+        <v>14.78800874448132</v>
       </c>
       <c r="E351" t="n">
-        <v>14.8458124590987</v>
+        <v>14.84581152004941</v>
       </c>
       <c r="F351" t="n">
         <v>3071000</v>
@@ -7452,16 +7452,16 @@
         <v>44767</v>
       </c>
       <c r="B352" t="n">
-        <v>14.93251705169678</v>
+        <v>14.93251800537109</v>
       </c>
       <c r="C352" t="n">
-        <v>15.4334793550804</v>
+        <v>15.43348034074898</v>
       </c>
       <c r="D352" t="n">
-        <v>14.91324884675499</v>
+        <v>14.91324979919873</v>
       </c>
       <c r="E352" t="n">
-        <v>15.2118995920427</v>
+        <v>15.21190056355995</v>
       </c>
       <c r="F352" t="n">
         <v>6226600</v>
@@ -7472,16 +7472,16 @@
         <v>44768</v>
       </c>
       <c r="B353" t="n">
-        <v>14.95178699493408</v>
+        <v>14.95178604125977</v>
       </c>
       <c r="C353" t="n">
-        <v>15.03849117097664</v>
+        <v>15.03849021177204</v>
       </c>
       <c r="D353" t="n">
-        <v>14.76874270174064</v>
+        <v>14.76874175974149</v>
       </c>
       <c r="E353" t="n">
-        <v>14.8265464045277</v>
+        <v>14.82654545884164</v>
       </c>
       <c r="F353" t="n">
         <v>3874000</v>
@@ -7492,16 +7492,16 @@
         <v>44769</v>
       </c>
       <c r="B354" t="n">
-        <v>15.76103019714355</v>
+        <v>15.76103115081787</v>
       </c>
       <c r="C354" t="n">
-        <v>15.93444035237151</v>
+        <v>15.9344413165386</v>
       </c>
       <c r="D354" t="n">
-        <v>15.03848818994657</v>
+        <v>15.03848909990104</v>
       </c>
       <c r="E354" t="n">
-        <v>15.04812229162779</v>
+        <v>15.04812320216521</v>
       </c>
       <c r="F354" t="n">
         <v>22102600</v>
@@ -7512,16 +7512,16 @@
         <v>44770</v>
       </c>
       <c r="B355" t="n">
-        <v>15.59725570678711</v>
+        <v>15.59725666046143</v>
       </c>
       <c r="C355" t="n">
-        <v>16.13675259238595</v>
+        <v>16.13675357904711</v>
       </c>
       <c r="D355" t="n">
-        <v>15.31787224258232</v>
+        <v>15.31787317917409</v>
       </c>
       <c r="E355" t="n">
-        <v>15.91517374406179</v>
+        <v>15.9151747171748</v>
       </c>
       <c r="F355" t="n">
         <v>25902000</v>
@@ -7552,16 +7552,16 @@
         <v>44774</v>
       </c>
       <c r="B357" t="n">
-        <v>15.05775833129883</v>
+        <v>15.05775928497314</v>
       </c>
       <c r="C357" t="n">
-        <v>15.4045777676332</v>
+        <v>15.40457874327312</v>
       </c>
       <c r="D357" t="n">
-        <v>14.85544676374746</v>
+        <v>14.85544770460849</v>
       </c>
       <c r="E357" t="n">
-        <v>14.96141913960441</v>
+        <v>14.96142008717714</v>
       </c>
       <c r="F357" t="n">
         <v>9649400</v>
@@ -7592,16 +7592,16 @@
         <v>44776</v>
       </c>
       <c r="B359" t="n">
-        <v>15.95370864868164</v>
+        <v>15.95370960235596</v>
       </c>
       <c r="C359" t="n">
-        <v>16.00187916291658</v>
+        <v>16.00188011947041</v>
       </c>
       <c r="D359" t="n">
-        <v>15.06739231820699</v>
+        <v>15.06739321889945</v>
       </c>
       <c r="E359" t="n">
-        <v>15.12519509777168</v>
+        <v>15.12519600191945</v>
       </c>
       <c r="F359" t="n">
         <v>9465300</v>
@@ -7792,16 +7792,16 @@
         <v>44790</v>
       </c>
       <c r="B369" t="n">
-        <v>17.27355194091797</v>
+        <v>17.27355003356934</v>
       </c>
       <c r="C369" t="n">
-        <v>17.52403311112434</v>
+        <v>17.52403117611753</v>
       </c>
       <c r="D369" t="n">
-        <v>17.16757864342216</v>
+        <v>17.16757674777512</v>
       </c>
       <c r="E369" t="n">
-        <v>17.31208651613271</v>
+        <v>17.31208460452908</v>
       </c>
       <c r="F369" t="n">
         <v>8548600</v>
@@ -7832,16 +7832,16 @@
         <v>44792</v>
       </c>
       <c r="B371" t="n">
-        <v>17.12904167175293</v>
+        <v>17.12904357910156</v>
       </c>
       <c r="C371" t="n">
-        <v>17.57219933106722</v>
+        <v>17.57220128776223</v>
       </c>
       <c r="D371" t="n">
-        <v>17.07123706074208</v>
+        <v>17.07123896165407</v>
       </c>
       <c r="E371" t="n">
-        <v>17.4565937840796</v>
+        <v>17.45659572790173</v>
       </c>
       <c r="F371" t="n">
         <v>7571900</v>
@@ -7892,16 +7892,16 @@
         <v>44797</v>
       </c>
       <c r="B374" t="n">
-        <v>17.1483097076416</v>
+        <v>17.14831161499023</v>
       </c>
       <c r="C374" t="n">
-        <v>17.26391710340299</v>
+        <v>17.26391902361024</v>
       </c>
       <c r="D374" t="n">
-        <v>16.99416773830457</v>
+        <v>16.99416962850851</v>
       </c>
       <c r="E374" t="n">
-        <v>17.1483097076416</v>
+        <v>17.14831161499023</v>
       </c>
       <c r="F374" t="n">
         <v>5807100</v>
@@ -7972,16 +7972,16 @@
         <v>44803</v>
       </c>
       <c r="B378" t="n">
-        <v>17.6300048828125</v>
+        <v>17.63000297546387</v>
       </c>
       <c r="C378" t="n">
-        <v>17.95755704675698</v>
+        <v>17.95755510397125</v>
       </c>
       <c r="D378" t="n">
-        <v>17.55293389350305</v>
+        <v>17.55293199449255</v>
       </c>
       <c r="E378" t="n">
-        <v>17.68780950293258</v>
+        <v>17.6878075893302</v>
       </c>
       <c r="F378" t="n">
         <v>6440300</v>
@@ -7992,16 +7992,16 @@
         <v>44804</v>
       </c>
       <c r="B379" t="n">
-        <v>17.71671104431152</v>
+        <v>17.71670913696289</v>
       </c>
       <c r="C379" t="n">
-        <v>17.98646044192704</v>
+        <v>17.98645850553768</v>
       </c>
       <c r="D379" t="n">
-        <v>17.51440037423797</v>
+        <v>17.51439848866973</v>
       </c>
       <c r="E379" t="n">
-        <v>17.74561335611522</v>
+        <v>17.74561144565502</v>
       </c>
       <c r="F379" t="n">
         <v>9759800</v>
@@ -8032,16 +8032,16 @@
         <v>44806</v>
       </c>
       <c r="B381" t="n">
-        <v>18.20803451538086</v>
+        <v>18.20803642272949</v>
       </c>
       <c r="C381" t="n">
-        <v>18.54522071404877</v>
+        <v>18.54522265671872</v>
       </c>
       <c r="D381" t="n">
-        <v>17.95755339172804</v>
+        <v>17.95755527283799</v>
       </c>
       <c r="E381" t="n">
-        <v>18.20803451538086</v>
+        <v>18.20803642272949</v>
       </c>
       <c r="F381" t="n">
         <v>12423600</v>
@@ -8112,16 +8112,16 @@
         <v>44813</v>
       </c>
       <c r="B385" t="n">
-        <v>18.15987014770508</v>
+        <v>18.15986824035645</v>
       </c>
       <c r="C385" t="n">
-        <v>18.6222960989819</v>
+        <v>18.62229414306423</v>
       </c>
       <c r="D385" t="n">
-        <v>18.08279915582561</v>
+        <v>18.08279725657182</v>
       </c>
       <c r="E385" t="n">
-        <v>18.47778821889757</v>
+        <v>18.47778627815769</v>
       </c>
       <c r="F385" t="n">
         <v>8752700</v>
@@ -8152,16 +8152,16 @@
         <v>44817</v>
       </c>
       <c r="B387" t="n">
-        <v>17.48549461364746</v>
+        <v>17.48549652099609</v>
       </c>
       <c r="C387" t="n">
-        <v>17.84194903885061</v>
+        <v>17.84195098508192</v>
       </c>
       <c r="D387" t="n">
-        <v>17.32171855409743</v>
+        <v>17.32172044358108</v>
       </c>
       <c r="E387" t="n">
-        <v>17.64927067319749</v>
+        <v>17.64927259841111</v>
       </c>
       <c r="F387" t="n">
         <v>10161300</v>
@@ -8172,16 +8172,16 @@
         <v>44818</v>
       </c>
       <c r="B388" t="n">
-        <v>17.70707702636719</v>
+        <v>17.70707511901855</v>
       </c>
       <c r="C388" t="n">
-        <v>17.87085311901526</v>
+        <v>17.8708511940252</v>
       </c>
       <c r="D388" t="n">
-        <v>17.36989257460714</v>
+        <v>17.36989070357892</v>
       </c>
       <c r="E388" t="n">
-        <v>17.4469635689405</v>
+        <v>17.44696168961044</v>
       </c>
       <c r="F388" t="n">
         <v>7347400</v>
@@ -8212,16 +8212,16 @@
         <v>44820</v>
       </c>
       <c r="B390" t="n">
-        <v>17.24464988708496</v>
+        <v>17.2446460723877</v>
       </c>
       <c r="C390" t="n">
-        <v>17.62037256672464</v>
+        <v>17.62036866891358</v>
       </c>
       <c r="D390" t="n">
-        <v>17.06160559892805</v>
+        <v>17.0616018247221</v>
       </c>
       <c r="E390" t="n">
-        <v>17.49513106100564</v>
+        <v>17.49512719089932</v>
       </c>
       <c r="F390" t="n">
         <v>10140200</v>
@@ -8252,16 +8252,16 @@
         <v>44824</v>
       </c>
       <c r="B392" t="n">
-        <v>17.60110282897949</v>
+        <v>17.60110092163086</v>
       </c>
       <c r="C392" t="n">
-        <v>17.83231577613557</v>
+        <v>17.83231384373147</v>
       </c>
       <c r="D392" t="n">
-        <v>17.43732676172096</v>
+        <v>17.43732487211997</v>
       </c>
       <c r="E392" t="n">
-        <v>17.55293231654042</v>
+        <v>17.55293041441179</v>
       </c>
       <c r="F392" t="n">
         <v>8039000</v>
@@ -8272,16 +8272,16 @@
         <v>44825</v>
       </c>
       <c r="B393" t="n">
-        <v>17.6300048828125</v>
+        <v>17.63000297546387</v>
       </c>
       <c r="C393" t="n">
-        <v>17.95755704675698</v>
+        <v>17.95755510397125</v>
       </c>
       <c r="D393" t="n">
-        <v>17.54329979014971</v>
+        <v>17.54329789218149</v>
       </c>
       <c r="E393" t="n">
-        <v>17.6300048828125</v>
+        <v>17.63000297546387</v>
       </c>
       <c r="F393" t="n">
         <v>11282800</v>
@@ -8332,16 +8332,16 @@
         <v>44830</v>
       </c>
       <c r="B396" t="n">
-        <v>17.09050750732422</v>
+        <v>17.09050559997559</v>
       </c>
       <c r="C396" t="n">
-        <v>17.20611490700088</v>
+        <v>17.20611298675014</v>
       </c>
       <c r="D396" t="n">
-        <v>16.7147866740303</v>
+        <v>16.71478480861316</v>
       </c>
       <c r="E396" t="n">
-        <v>16.89783095788615</v>
+        <v>16.89782907204076</v>
       </c>
       <c r="F396" t="n">
         <v>7980700</v>
@@ -8352,16 +8352,16 @@
         <v>44831</v>
       </c>
       <c r="B397" t="n">
-        <v>17.12904167175293</v>
+        <v>17.12904357910156</v>
       </c>
       <c r="C397" t="n">
-        <v>17.49512835390313</v>
+        <v>17.49513030201615</v>
       </c>
       <c r="D397" t="n">
-        <v>16.86892643475522</v>
+        <v>16.86892831313957</v>
       </c>
       <c r="E397" t="n">
-        <v>17.2542813205757</v>
+        <v>17.25428324186998</v>
       </c>
       <c r="F397" t="n">
         <v>9260100</v>
@@ -8432,16 +8432,16 @@
         <v>44837</v>
       </c>
       <c r="B401" t="n">
-        <v>17.75524711608887</v>
+        <v>17.75524520874023</v>
       </c>
       <c r="C401" t="n">
-        <v>17.81304990105905</v>
+        <v>17.81304798750098</v>
       </c>
       <c r="D401" t="n">
-        <v>16.96526898393264</v>
+        <v>16.96526716144702</v>
       </c>
       <c r="E401" t="n">
-        <v>17.244650642553</v>
+        <v>17.24464879005494</v>
       </c>
       <c r="F401" t="n">
         <v>18011200</v>
@@ -8492,16 +8492,16 @@
         <v>44840</v>
       </c>
       <c r="B404" t="n">
-        <v>17.44696235656738</v>
+        <v>17.44696044921875</v>
       </c>
       <c r="C404" t="n">
-        <v>17.63963891025314</v>
+        <v>17.6396369818406</v>
       </c>
       <c r="D404" t="n">
-        <v>17.30245264440641</v>
+        <v>17.30245075285597</v>
       </c>
       <c r="E404" t="n">
-        <v>17.63000480694126</v>
+        <v>17.63000287958194</v>
       </c>
       <c r="F404" t="n">
         <v>6691000</v>
@@ -8512,16 +8512,16 @@
         <v>44841</v>
       </c>
       <c r="B405" t="n">
-        <v>17.49513244628906</v>
+        <v>17.49513053894043</v>
       </c>
       <c r="C405" t="n">
-        <v>17.68781085302832</v>
+        <v>17.68780892467357</v>
       </c>
       <c r="D405" t="n">
-        <v>17.32172224772722</v>
+        <v>17.32172035928406</v>
       </c>
       <c r="E405" t="n">
-        <v>17.44696376336298</v>
+        <v>17.44696186126578</v>
       </c>
       <c r="F405" t="n">
         <v>11897600</v>
@@ -8532,16 +8532,16 @@
         <v>44844</v>
       </c>
       <c r="B406" t="n">
-        <v>18.1020679473877</v>
+        <v>18.10206604003906</v>
       </c>
       <c r="C406" t="n">
-        <v>18.12133431784131</v>
+        <v>18.12133240846265</v>
       </c>
       <c r="D406" t="n">
-        <v>17.58183735727369</v>
+        <v>17.58183550473985</v>
       </c>
       <c r="E406" t="n">
-        <v>17.73597934600729</v>
+        <v>17.73597747723208</v>
       </c>
       <c r="F406" t="n">
         <v>7333800</v>
@@ -8612,16 +8612,16 @@
         <v>44851</v>
       </c>
       <c r="B410" t="n">
-        <v>19.01728439331055</v>
+        <v>19.01728248596191</v>
       </c>
       <c r="C410" t="n">
-        <v>19.06545490973637</v>
+        <v>19.06545299755645</v>
       </c>
       <c r="D410" t="n">
-        <v>18.3621800700579</v>
+        <v>18.3621782284133</v>
       </c>
       <c r="E410" t="n">
-        <v>18.49705567853288</v>
+        <v>18.49705382336087</v>
       </c>
       <c r="F410" t="n">
         <v>20683400</v>
@@ -8652,16 +8652,16 @@
         <v>44853</v>
       </c>
       <c r="B412" t="n">
-        <v>17.67817497253418</v>
+        <v>17.67817687988281</v>
       </c>
       <c r="C412" t="n">
-        <v>17.97682481920425</v>
+        <v>17.97682675877506</v>
       </c>
       <c r="D412" t="n">
-        <v>17.2831859321752</v>
+        <v>17.28318779690735</v>
       </c>
       <c r="E412" t="n">
-        <v>17.47586248203574</v>
+        <v>17.4758643675563</v>
       </c>
       <c r="F412" t="n">
         <v>27062400</v>
@@ -8672,16 +8672,16 @@
         <v>44854</v>
       </c>
       <c r="B413" t="n">
-        <v>17.35062217712402</v>
+        <v>17.35062408447266</v>
       </c>
       <c r="C413" t="n">
-        <v>18.11169792043414</v>
+        <v>18.11169991144759</v>
       </c>
       <c r="D413" t="n">
-        <v>17.19648020790888</v>
+        <v>17.19648209831274</v>
       </c>
       <c r="E413" t="n">
-        <v>17.73597710016188</v>
+        <v>17.73597904987246</v>
       </c>
       <c r="F413" t="n">
         <v>15810900</v>
@@ -8712,16 +8712,16 @@
         <v>44858</v>
       </c>
       <c r="B415" t="n">
-        <v>18.0057258605957</v>
+        <v>18.00572776794434</v>
       </c>
       <c r="C415" t="n">
-        <v>18.36217846337067</v>
+        <v>18.36218040847837</v>
       </c>
       <c r="D415" t="n">
-        <v>17.54329813095674</v>
+        <v>17.54329998932035</v>
       </c>
       <c r="E415" t="n">
-        <v>17.91902077613322</v>
+        <v>17.91902267429717</v>
       </c>
       <c r="F415" t="n">
         <v>16227000</v>
@@ -8772,16 +8772,16 @@
         <v>44861</v>
       </c>
       <c r="B418" t="n">
-        <v>17.47586059570312</v>
+        <v>17.47586250305176</v>
       </c>
       <c r="C418" t="n">
-        <v>17.74560994141206</v>
+        <v>17.74561187820164</v>
       </c>
       <c r="D418" t="n">
-        <v>15.99224378809673</v>
+        <v>15.9922455335206</v>
       </c>
       <c r="E418" t="n">
-        <v>16.13675164427337</v>
+        <v>16.13675340546911</v>
       </c>
       <c r="F418" t="n">
         <v>30122400</v>
@@ -8812,16 +8812,16 @@
         <v>44865</v>
       </c>
       <c r="B420" t="n">
-        <v>19.0943546295166</v>
+        <v>19.09435653686523</v>
       </c>
       <c r="C420" t="n">
-        <v>19.24849660096946</v>
+        <v>19.24849852371545</v>
       </c>
       <c r="D420" t="n">
-        <v>18.13096638917758</v>
+        <v>18.13096820029268</v>
       </c>
       <c r="E420" t="n">
-        <v>18.2947424635359</v>
+        <v>18.29474429101071</v>
       </c>
       <c r="F420" t="n">
         <v>18379300</v>
@@ -8932,16 +8932,16 @@
         <v>44874</v>
       </c>
       <c r="B426" t="n">
-        <v>19.65312004089355</v>
+        <v>19.65311813354492</v>
       </c>
       <c r="C426" t="n">
-        <v>20.09627959384678</v>
+        <v>20.09627764348921</v>
       </c>
       <c r="D426" t="n">
-        <v>19.1328913385332</v>
+        <v>19.13288948167312</v>
       </c>
       <c r="E426" t="n">
-        <v>19.1328913385332</v>
+        <v>19.13288948167312</v>
       </c>
       <c r="F426" t="n">
         <v>19633400</v>
@@ -9032,16 +9032,16 @@
         <v>44882</v>
       </c>
       <c r="B431" t="n">
-        <v>18.78606986999512</v>
+        <v>18.78607177734375</v>
       </c>
       <c r="C431" t="n">
-        <v>18.90167726231802</v>
+        <v>18.90167918140427</v>
       </c>
       <c r="D431" t="n">
-        <v>18.05389461866248</v>
+        <v>18.0538964516734</v>
       </c>
       <c r="E431" t="n">
-        <v>18.6608302127027</v>
+        <v>18.66083210733576</v>
       </c>
       <c r="F431" t="n">
         <v>10826800</v>
@@ -9192,16 +9192,16 @@
         <v>44894</v>
       </c>
       <c r="B439" t="n">
-        <v>18.68972969055176</v>
+        <v>18.68973159790039</v>
       </c>
       <c r="C439" t="n">
-        <v>18.98837950171693</v>
+        <v>18.98838143954377</v>
       </c>
       <c r="D439" t="n">
-        <v>18.29474069715092</v>
+        <v>18.29474256418963</v>
       </c>
       <c r="E439" t="n">
-        <v>18.53558773398153</v>
+        <v>18.53558962559947</v>
       </c>
       <c r="F439" t="n">
         <v>13403400</v>
@@ -9232,16 +9232,16 @@
         <v>44896</v>
       </c>
       <c r="B441" t="n">
-        <v>18.95948219299316</v>
+        <v>18.95948028564453</v>
       </c>
       <c r="C441" t="n">
-        <v>19.08472186450934</v>
+        <v>19.08471994456143</v>
       </c>
       <c r="D441" t="n">
-        <v>18.41998525508773</v>
+        <v>18.41998340201319</v>
       </c>
       <c r="E441" t="n">
-        <v>19.0750877609285</v>
+        <v>19.0750858419498</v>
       </c>
       <c r="F441" t="n">
         <v>25518700</v>
@@ -9312,16 +9312,16 @@
         <v>44902</v>
       </c>
       <c r="B445" t="n">
-        <v>19.36410331726074</v>
+        <v>19.36410522460938</v>
       </c>
       <c r="C445" t="n">
-        <v>19.48934297559241</v>
+        <v>19.48934489527705</v>
       </c>
       <c r="D445" t="n">
-        <v>18.82460643615043</v>
+        <v>18.82460829035904</v>
       </c>
       <c r="E445" t="n">
-        <v>19.17142494096275</v>
+        <v>19.17142682933272</v>
       </c>
       <c r="F445" t="n">
         <v>7439200</v>
@@ -9352,16 +9352,16 @@
         <v>44904</v>
       </c>
       <c r="B447" t="n">
-        <v>18.57412719726562</v>
+        <v>18.57412528991699</v>
       </c>
       <c r="C447" t="n">
-        <v>18.75716965235448</v>
+        <v>18.7571677262095</v>
       </c>
       <c r="D447" t="n">
-        <v>18.25620912985342</v>
+        <v>18.25620725515131</v>
       </c>
       <c r="E447" t="n">
-        <v>18.57412719726562</v>
+        <v>18.57412528991699</v>
       </c>
       <c r="F447" t="n">
         <v>14833900</v>
@@ -9412,16 +9412,16 @@
         <v>44909</v>
       </c>
       <c r="B450" t="n">
-        <v>18.37181282043457</v>
+        <v>18.3718147277832</v>
       </c>
       <c r="C450" t="n">
-        <v>18.46815200867444</v>
+        <v>18.46815392602494</v>
       </c>
       <c r="D450" t="n">
-        <v>17.64927166491134</v>
+        <v>17.64927349724626</v>
       </c>
       <c r="E450" t="n">
-        <v>17.86121824654248</v>
+        <v>17.86122010088155</v>
       </c>
       <c r="F450" t="n">
         <v>10673700</v>
@@ -9452,16 +9452,16 @@
         <v>44911</v>
       </c>
       <c r="B452" t="n">
-        <v>18.02499389648438</v>
+        <v>18.02499580383301</v>
       </c>
       <c r="C452" t="n">
-        <v>18.69936642972459</v>
+        <v>18.69936840843323</v>
       </c>
       <c r="D452" t="n">
-        <v>17.55293385822315</v>
+        <v>17.55293571561986</v>
       </c>
       <c r="E452" t="n">
-        <v>18.38144836977245</v>
+        <v>18.38145031483998</v>
       </c>
       <c r="F452" t="n">
         <v>14090800</v>
@@ -9472,16 +9472,16 @@
         <v>44914</v>
       </c>
       <c r="B453" t="n">
-        <v>18.83423805236816</v>
+        <v>18.8342399597168</v>
       </c>
       <c r="C453" t="n">
-        <v>18.90167676801125</v>
+        <v>18.90167868218942</v>
       </c>
       <c r="D453" t="n">
-        <v>18.13096512688717</v>
+        <v>18.13096696301515</v>
       </c>
       <c r="E453" t="n">
-        <v>18.15023333135662</v>
+        <v>18.1502351694359</v>
       </c>
       <c r="F453" t="n">
         <v>7150400</v>
@@ -9492,16 +9492,16 @@
         <v>44915</v>
       </c>
       <c r="B454" t="n">
-        <v>19.26776695251465</v>
+        <v>19.26776504516602</v>
       </c>
       <c r="C454" t="n">
-        <v>19.66275602803981</v>
+        <v>19.66275408159054</v>
       </c>
       <c r="D454" t="n">
-        <v>18.86314377301114</v>
+        <v>18.86314190571684</v>
       </c>
       <c r="E454" t="n">
-        <v>18.91131245538545</v>
+        <v>18.91131058332285</v>
       </c>
       <c r="F454" t="n">
         <v>10658900</v>
@@ -9572,16 +9572,16 @@
         <v>44921</v>
       </c>
       <c r="B458" t="n">
-        <v>19.20032691955566</v>
+        <v>19.2003288269043</v>
       </c>
       <c r="C458" t="n">
-        <v>19.32556657574064</v>
+        <v>19.3255684955305</v>
       </c>
       <c r="D458" t="n">
-        <v>18.84387248076942</v>
+        <v>18.84387435270808</v>
       </c>
       <c r="E458" t="n">
-        <v>19.07508542585354</v>
+        <v>19.07508732076077</v>
       </c>
       <c r="F458" t="n">
         <v>2369600</v>
@@ -9612,16 +9612,16 @@
         <v>44923</v>
       </c>
       <c r="B460" t="n">
-        <v>18.7186336517334</v>
+        <v>18.71863555908203</v>
       </c>
       <c r="C460" t="n">
-        <v>18.94984660703449</v>
+        <v>18.94984853794273</v>
       </c>
       <c r="D460" t="n">
-        <v>18.26584000644119</v>
+        <v>18.26584186765209</v>
       </c>
       <c r="E460" t="n">
-        <v>18.6897313432518</v>
+        <v>18.68973324765541</v>
       </c>
       <c r="F460" t="n">
         <v>8329700</v>
@@ -27472,7 +27472,7 @@
         <v>46232</v>
       </c>
       <c r="B1353" t="n">
-        <v>8.23</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="C1353" t="n">
         <v>8.43</v>
@@ -27484,7 +27484,7 @@
         <v>8.26</v>
       </c>
       <c r="F1353" t="n">
-        <v>6610600</v>
+        <v>9145900</v>
       </c>
     </row>
   </sheetData>

--- a/database/ASAI3.xlsx
+++ b/database/ASAI3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1353"/>
+  <dimension ref="A1:F1354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44256</v>
       </c>
       <c r="B2" t="n">
-        <v>13.55914878845215</v>
+        <v>13.55914783477783</v>
       </c>
       <c r="C2" t="n">
-        <v>14.43840509670459</v>
+        <v>14.43840408118833</v>
       </c>
       <c r="D2" t="n">
-        <v>13.17554324856868</v>
+        <v>13.17554232187502</v>
       </c>
       <c r="E2" t="n">
-        <v>13.67499091708668</v>
+        <v>13.67498995526467</v>
       </c>
       <c r="F2" t="n">
         <v>64088000</v>
@@ -472,16 +472,16 @@
         <v>44257</v>
       </c>
       <c r="B3" t="n">
-        <v>13.76804256439209</v>
+        <v>13.76804351806641</v>
       </c>
       <c r="C3" t="n">
-        <v>14.05289879855508</v>
+        <v>14.0528997719606</v>
       </c>
       <c r="D3" t="n">
-        <v>13.0046284363764</v>
+        <v>13.00462933717113</v>
       </c>
       <c r="E3" t="n">
-        <v>13.3711429203832</v>
+        <v>13.37114384656537</v>
       </c>
       <c r="F3" t="n">
         <v>14717000</v>
@@ -492,16 +492,16 @@
         <v>44258</v>
       </c>
       <c r="B4" t="n">
-        <v>13.54015922546387</v>
+        <v>13.54015827178955</v>
       </c>
       <c r="C4" t="n">
-        <v>13.82881329247169</v>
+        <v>13.82881231846659</v>
       </c>
       <c r="D4" t="n">
-        <v>13.17934141532082</v>
+        <v>13.17934048705999</v>
       </c>
       <c r="E4" t="n">
-        <v>13.63321180595596</v>
+        <v>13.63321084572767</v>
       </c>
       <c r="F4" t="n">
         <v>17545000</v>
@@ -552,16 +552,16 @@
         <v>44263</v>
       </c>
       <c r="B7" t="n">
-        <v>13.48508548736572</v>
+        <v>13.48508644104004</v>
       </c>
       <c r="C7" t="n">
-        <v>14.29787472337838</v>
+        <v>14.2978757345337</v>
       </c>
       <c r="D7" t="n">
-        <v>13.05210487258059</v>
+        <v>13.05210579563423</v>
       </c>
       <c r="E7" t="n">
-        <v>14.21051885821534</v>
+        <v>14.21051986319279</v>
       </c>
       <c r="F7" t="n">
         <v>12366000</v>
@@ -592,16 +592,16 @@
         <v>44265</v>
       </c>
       <c r="B9" t="n">
-        <v>13.48318672180176</v>
+        <v>13.48318767547607</v>
       </c>
       <c r="C9" t="n">
-        <v>13.95794682401684</v>
+        <v>13.95794781127124</v>
       </c>
       <c r="D9" t="n">
-        <v>13.23631125132199</v>
+        <v>13.23631218753465</v>
       </c>
       <c r="E9" t="n">
-        <v>13.4850856245696</v>
+        <v>13.48508657837822</v>
       </c>
       <c r="F9" t="n">
         <v>15699500</v>
@@ -632,16 +632,16 @@
         <v>44267</v>
       </c>
       <c r="B11" t="n">
-        <v>13.82121658325195</v>
+        <v>13.82121467590332</v>
       </c>
       <c r="C11" t="n">
-        <v>14.06049554958161</v>
+        <v>14.06049360921212</v>
       </c>
       <c r="D11" t="n">
-        <v>13.57813981118895</v>
+        <v>13.57813793738528</v>
       </c>
       <c r="E11" t="n">
-        <v>13.57813981118895</v>
+        <v>13.57813793738528</v>
       </c>
       <c r="F11" t="n">
         <v>7509000</v>
@@ -652,16 +652,16 @@
         <v>44270</v>
       </c>
       <c r="B12" t="n">
-        <v>13.83450889587402</v>
+        <v>13.83451080322266</v>
       </c>
       <c r="C12" t="n">
-        <v>14.01681714204006</v>
+        <v>14.01681907452333</v>
       </c>
       <c r="D12" t="n">
-        <v>13.62181639478016</v>
+        <v>13.62181827280511</v>
       </c>
       <c r="E12" t="n">
-        <v>13.81931676841011</v>
+        <v>13.81931867366422</v>
       </c>
       <c r="F12" t="n">
         <v>11593000</v>
@@ -712,16 +712,16 @@
         <v>44273</v>
       </c>
       <c r="B15" t="n">
-        <v>13.91047191619873</v>
+        <v>13.91047096252441</v>
       </c>
       <c r="C15" t="n">
-        <v>14.01302082492147</v>
+        <v>14.0130198642166</v>
       </c>
       <c r="D15" t="n">
-        <v>13.69018378074197</v>
+        <v>13.69018284217017</v>
       </c>
       <c r="E15" t="n">
-        <v>13.69018378074197</v>
+        <v>13.69018284217017</v>
       </c>
       <c r="F15" t="n">
         <v>2304000</v>
@@ -732,16 +732,16 @@
         <v>44274</v>
       </c>
       <c r="B16" t="n">
-        <v>13.54775428771973</v>
+        <v>13.54775333404541</v>
       </c>
       <c r="C16" t="n">
-        <v>14.03580762724047</v>
+        <v>14.03580663921036</v>
       </c>
       <c r="D16" t="n">
-        <v>13.46419713061404</v>
+        <v>13.46419618282161</v>
       </c>
       <c r="E16" t="n">
-        <v>13.95414937295086</v>
+        <v>13.95414839066896</v>
       </c>
       <c r="F16" t="n">
         <v>14098000</v>
@@ -812,16 +812,16 @@
         <v>44280</v>
       </c>
       <c r="B20" t="n">
-        <v>13.64840221405029</v>
+        <v>13.64840316772461</v>
       </c>
       <c r="C20" t="n">
-        <v>13.67308975961416</v>
+        <v>13.67309071501351</v>
       </c>
       <c r="D20" t="n">
-        <v>12.83941172946964</v>
+        <v>12.83941262661621</v>
       </c>
       <c r="E20" t="n">
-        <v>12.91347436616125</v>
+        <v>12.9134752684829</v>
       </c>
       <c r="F20" t="n">
         <v>6602000</v>
@@ -832,16 +832,16 @@
         <v>44281</v>
       </c>
       <c r="B21" t="n">
-        <v>13.80602359771729</v>
+        <v>13.8060245513916</v>
       </c>
       <c r="C21" t="n">
-        <v>14.12696170612194</v>
+        <v>14.1269626819656</v>
       </c>
       <c r="D21" t="n">
-        <v>13.48888420034324</v>
+        <v>13.48888513211062</v>
       </c>
       <c r="E21" t="n">
-        <v>13.54965361596974</v>
+        <v>13.54965455193487</v>
       </c>
       <c r="F21" t="n">
         <v>4396500</v>
@@ -892,16 +892,16 @@
         <v>44286</v>
       </c>
       <c r="B24" t="n">
-        <v>14.02251434326172</v>
+        <v>14.0225133895874</v>
       </c>
       <c r="C24" t="n">
-        <v>14.04150518240905</v>
+        <v>14.04150422744316</v>
       </c>
       <c r="D24" t="n">
-        <v>13.67499067998287</v>
+        <v>13.67498974994372</v>
       </c>
       <c r="E24" t="n">
-        <v>13.96744253969395</v>
+        <v>13.96744158976508</v>
       </c>
       <c r="F24" t="n">
         <v>3663000</v>
@@ -952,16 +952,16 @@
         <v>44292</v>
       </c>
       <c r="B27" t="n">
-        <v>14.58652973175049</v>
+        <v>14.58653163909912</v>
       </c>
       <c r="C27" t="n">
-        <v>14.72136088275989</v>
+        <v>14.72136280773917</v>
       </c>
       <c r="D27" t="n">
-        <v>14.52765921864798</v>
+        <v>14.52766111829865</v>
       </c>
       <c r="E27" t="n">
-        <v>14.7175630772478</v>
+        <v>14.71756500173048</v>
       </c>
       <c r="F27" t="n">
         <v>5821500</v>
@@ -972,16 +972,16 @@
         <v>44293</v>
       </c>
       <c r="B28" t="n">
-        <v>14.4934778213501</v>
+        <v>14.49347591400146</v>
       </c>
       <c r="C28" t="n">
-        <v>14.78023299581345</v>
+        <v>14.7802310507277</v>
       </c>
       <c r="D28" t="n">
-        <v>13.92756398980291</v>
+        <v>13.92756215692881</v>
       </c>
       <c r="E28" t="n">
-        <v>14.45359814255714</v>
+        <v>14.45359624045669</v>
       </c>
       <c r="F28" t="n">
         <v>10992000</v>
@@ -992,16 +992,16 @@
         <v>44294</v>
       </c>
       <c r="B29" t="n">
-        <v>14.70237159729004</v>
+        <v>14.70237064361572</v>
       </c>
       <c r="C29" t="n">
-        <v>14.74035237068301</v>
+        <v>14.74035141454506</v>
       </c>
       <c r="D29" t="n">
-        <v>14.26559225050429</v>
+        <v>14.26559132516181</v>
       </c>
       <c r="E29" t="n">
-        <v>14.43270747232676</v>
+        <v>14.4327065361443</v>
       </c>
       <c r="F29" t="n">
         <v>6395000</v>
@@ -1032,16 +1032,16 @@
         <v>44298</v>
       </c>
       <c r="B31" t="n">
-        <v>14.69857406616211</v>
+        <v>14.69857215881348</v>
       </c>
       <c r="C31" t="n">
-        <v>14.80112297753611</v>
+        <v>14.8011210568803</v>
       </c>
       <c r="D31" t="n">
-        <v>14.52766102493839</v>
+        <v>14.52765913976815</v>
       </c>
       <c r="E31" t="n">
-        <v>14.69857406616211</v>
+        <v>14.69857215881348</v>
       </c>
       <c r="F31" t="n">
         <v>4711000</v>
@@ -1072,16 +1072,16 @@
         <v>44300</v>
       </c>
       <c r="B33" t="n">
-        <v>14.93785285949707</v>
+        <v>14.9378547668457</v>
       </c>
       <c r="C33" t="n">
-        <v>14.9454484709092</v>
+        <v>14.94545037922768</v>
       </c>
       <c r="D33" t="n">
-        <v>14.62261144203403</v>
+        <v>14.62261330913087</v>
       </c>
       <c r="E33" t="n">
-        <v>14.65109770142871</v>
+        <v>14.65109957216284</v>
       </c>
       <c r="F33" t="n">
         <v>5841000</v>
@@ -1092,16 +1092,16 @@
         <v>44301</v>
       </c>
       <c r="B34" t="n">
-        <v>15.1866283416748</v>
+        <v>15.18662738800049</v>
       </c>
       <c r="C34" t="n">
-        <v>15.20371846858745</v>
+        <v>15.20371751383992</v>
       </c>
       <c r="D34" t="n">
-        <v>14.84100264251348</v>
+        <v>14.84100171054341</v>
       </c>
       <c r="E34" t="n">
-        <v>14.84100264251348</v>
+        <v>14.84100171054341</v>
       </c>
       <c r="F34" t="n">
         <v>11554500</v>
@@ -1152,16 +1152,16 @@
         <v>44306</v>
       </c>
       <c r="B37" t="n">
-        <v>15.47717666625977</v>
+        <v>15.47717952728271</v>
       </c>
       <c r="C37" t="n">
-        <v>15.65568799257194</v>
+        <v>15.65569088659348</v>
       </c>
       <c r="D37" t="n">
-        <v>15.06698474280571</v>
+        <v>15.06698752800291</v>
       </c>
       <c r="E37" t="n">
-        <v>15.35943746515919</v>
+        <v>15.35944030441754</v>
       </c>
       <c r="F37" t="n">
         <v>6029000</v>
@@ -1172,16 +1172,16 @@
         <v>44308</v>
       </c>
       <c r="B38" t="n">
-        <v>15.27967929840088</v>
+        <v>15.27967834472656</v>
       </c>
       <c r="C38" t="n">
-        <v>15.75254143640172</v>
+        <v>15.75254045321392</v>
       </c>
       <c r="D38" t="n">
-        <v>15.1942241402155</v>
+        <v>15.19422319187483</v>
       </c>
       <c r="E38" t="n">
-        <v>15.50376614024878</v>
+        <v>15.50376517258819</v>
       </c>
       <c r="F38" t="n">
         <v>8470500</v>
@@ -1192,16 +1192,16 @@
         <v>44309</v>
       </c>
       <c r="B39" t="n">
-        <v>15.41261291503906</v>
+        <v>15.41261100769043</v>
       </c>
       <c r="C39" t="n">
-        <v>15.53794955811708</v>
+        <v>15.53794763525773</v>
       </c>
       <c r="D39" t="n">
-        <v>15.218910336355</v>
+        <v>15.21890845297754</v>
       </c>
       <c r="E39" t="n">
-        <v>15.45819020544309</v>
+        <v>15.45818829245416</v>
       </c>
       <c r="F39" t="n">
         <v>4653000</v>
@@ -1212,16 +1212,16 @@
         <v>44312</v>
       </c>
       <c r="B40" t="n">
-        <v>15.2606897354126</v>
+        <v>15.26068878173828</v>
       </c>
       <c r="C40" t="n">
-        <v>15.51705882313055</v>
+        <v>15.51705785343516</v>
       </c>
       <c r="D40" t="n">
-        <v>15.16573734944818</v>
+        <v>15.16573640170765</v>
       </c>
       <c r="E40" t="n">
-        <v>15.48477656941952</v>
+        <v>15.48477560174152</v>
       </c>
       <c r="F40" t="n">
         <v>3662000</v>
@@ -1232,16 +1232,16 @@
         <v>44313</v>
       </c>
       <c r="B41" t="n">
-        <v>15.12775707244873</v>
+        <v>15.12775611877441</v>
       </c>
       <c r="C41" t="n">
-        <v>15.29677210768214</v>
+        <v>15.29677114335289</v>
       </c>
       <c r="D41" t="n">
-        <v>15.10117062083444</v>
+        <v>15.10116966883617</v>
       </c>
       <c r="E41" t="n">
-        <v>15.24929500760934</v>
+        <v>15.24929404627311</v>
       </c>
       <c r="F41" t="n">
         <v>4986500</v>
@@ -1252,16 +1252,16 @@
         <v>44314</v>
       </c>
       <c r="B42" t="n">
-        <v>15.18852519989014</v>
+        <v>15.18852615356445</v>
       </c>
       <c r="C42" t="n">
-        <v>15.35564131800169</v>
+        <v>15.35564228216909</v>
       </c>
       <c r="D42" t="n">
-        <v>15.04799553112973</v>
+        <v>15.04799647598031</v>
       </c>
       <c r="E42" t="n">
-        <v>15.14864552586341</v>
+        <v>15.14864647703371</v>
       </c>
       <c r="F42" t="n">
         <v>5371500</v>
@@ -1272,16 +1272,16 @@
         <v>44315</v>
       </c>
       <c r="B43" t="n">
-        <v>15.21646499633789</v>
+        <v>15.21646404266357</v>
       </c>
       <c r="C43" t="n">
-        <v>15.32323336252505</v>
+        <v>15.32323240215915</v>
       </c>
       <c r="D43" t="n">
-        <v>14.90950503441863</v>
+        <v>14.90950409998268</v>
       </c>
       <c r="E43" t="n">
-        <v>15.26222338706449</v>
+        <v>15.26222243052232</v>
       </c>
       <c r="F43" t="n">
         <v>5343000</v>
@@ -1292,16 +1292,16 @@
         <v>44316</v>
       </c>
       <c r="B44" t="n">
-        <v>15.4223747253418</v>
+        <v>15.42237567901611</v>
       </c>
       <c r="C44" t="n">
-        <v>15.46813311247533</v>
+        <v>15.46813406897922</v>
       </c>
       <c r="D44" t="n">
-        <v>14.92856925223867</v>
+        <v>14.92857017537751</v>
       </c>
       <c r="E44" t="n">
-        <v>15.10016229485833</v>
+        <v>15.10016322860797</v>
       </c>
       <c r="F44" t="n">
         <v>22683000</v>
@@ -1312,16 +1312,16 @@
         <v>44319</v>
       </c>
       <c r="B45" t="n">
-        <v>15.53295803070068</v>
+        <v>15.532958984375</v>
       </c>
       <c r="C45" t="n">
-        <v>15.67023137590184</v>
+        <v>15.6702323380043</v>
       </c>
       <c r="D45" t="n">
-        <v>15.29463476087267</v>
+        <v>15.29463569991469</v>
       </c>
       <c r="E45" t="n">
-        <v>15.44334861216023</v>
+        <v>15.44334956033281</v>
       </c>
       <c r="F45" t="n">
         <v>8474000</v>
@@ -1352,16 +1352,16 @@
         <v>44321</v>
       </c>
       <c r="B47" t="n">
-        <v>16.32228469848633</v>
+        <v>16.32228660583496</v>
       </c>
       <c r="C47" t="n">
-        <v>16.58730007183393</v>
+        <v>16.58730201015107</v>
       </c>
       <c r="D47" t="n">
-        <v>16.01532383109572</v>
+        <v>16.01532570257429</v>
       </c>
       <c r="E47" t="n">
-        <v>16.08396141636727</v>
+        <v>16.08396329586652</v>
       </c>
       <c r="F47" t="n">
         <v>17262500</v>
@@ -1392,16 +1392,16 @@
         <v>44323</v>
       </c>
       <c r="B49" t="n">
-        <v>16.96289825439453</v>
+        <v>16.96290016174316</v>
       </c>
       <c r="C49" t="n">
-        <v>17.0448800657126</v>
+        <v>17.04488198227947</v>
       </c>
       <c r="D49" t="n">
-        <v>16.42905280179942</v>
+        <v>16.4290546491212</v>
       </c>
       <c r="E49" t="n">
-        <v>16.66356318404632</v>
+        <v>16.663565057737</v>
       </c>
       <c r="F49" t="n">
         <v>8422500</v>
@@ -1432,16 +1432,16 @@
         <v>44327</v>
       </c>
       <c r="B51" t="n">
-        <v>16.58729934692383</v>
+        <v>16.58729553222656</v>
       </c>
       <c r="C51" t="n">
-        <v>16.78367894467991</v>
+        <v>16.78367508481985</v>
       </c>
       <c r="D51" t="n">
-        <v>16.4919696745899</v>
+        <v>16.49196588181627</v>
       </c>
       <c r="E51" t="n">
-        <v>16.6254319431623</v>
+        <v>16.62542811969542</v>
       </c>
       <c r="F51" t="n">
         <v>6191000</v>
@@ -1472,16 +1472,16 @@
         <v>44329</v>
       </c>
       <c r="B53" t="n">
-        <v>16.4328670501709</v>
+        <v>16.43286895751953</v>
       </c>
       <c r="C53" t="n">
-        <v>16.5186617551335</v>
+        <v>16.51866367244025</v>
       </c>
       <c r="D53" t="n">
-        <v>16.12781173522566</v>
+        <v>16.12781360716679</v>
       </c>
       <c r="E53" t="n">
-        <v>16.17547748049629</v>
+        <v>16.17547935796994</v>
       </c>
       <c r="F53" t="n">
         <v>6595000</v>
@@ -1492,16 +1492,16 @@
         <v>44330</v>
       </c>
       <c r="B54" t="n">
-        <v>16.52629089355469</v>
+        <v>16.52628898620605</v>
       </c>
       <c r="C54" t="n">
-        <v>16.66356425245107</v>
+        <v>16.66356232925931</v>
       </c>
       <c r="D54" t="n">
-        <v>16.13734637653381</v>
+        <v>16.13734451407442</v>
       </c>
       <c r="E54" t="n">
-        <v>16.54726273245572</v>
+        <v>16.54726082268666</v>
       </c>
       <c r="F54" t="n">
         <v>5923000</v>
@@ -1592,16 +1592,16 @@
         <v>44337</v>
       </c>
       <c r="B59" t="n">
-        <v>16.43477630615234</v>
+        <v>16.43477249145508</v>
       </c>
       <c r="C59" t="n">
-        <v>16.62543569383264</v>
+        <v>16.62543183488117</v>
       </c>
       <c r="D59" t="n">
-        <v>15.75984447387085</v>
+        <v>15.75984081583289</v>
       </c>
       <c r="E59" t="n">
-        <v>16.03439304663388</v>
+        <v>16.03438932487009</v>
       </c>
       <c r="F59" t="n">
         <v>10145000</v>
@@ -1612,16 +1612,16 @@
         <v>44340</v>
       </c>
       <c r="B60" t="n">
-        <v>17.0086555480957</v>
+        <v>17.00865745544434</v>
       </c>
       <c r="C60" t="n">
-        <v>17.06204155023285</v>
+        <v>17.06204346356818</v>
       </c>
       <c r="D60" t="n">
-        <v>16.39664297252445</v>
+        <v>16.39664481124207</v>
       </c>
       <c r="E60" t="n">
-        <v>16.54154212092919</v>
+        <v>16.54154397589578</v>
       </c>
       <c r="F60" t="n">
         <v>10386000</v>
@@ -1652,16 +1652,16 @@
         <v>44342</v>
       </c>
       <c r="B62" t="n">
-        <v>16.94192695617676</v>
+        <v>16.94192314147949</v>
       </c>
       <c r="C62" t="n">
-        <v>17.11161449219801</v>
+        <v>17.11161063929336</v>
       </c>
       <c r="D62" t="n">
-        <v>16.65975260630318</v>
+        <v>16.65974885514118</v>
       </c>
       <c r="E62" t="n">
-        <v>17.02391059716581</v>
+        <v>17.02390676400885</v>
       </c>
       <c r="F62" t="n">
         <v>5462000</v>
@@ -1672,16 +1672,16 @@
         <v>44343</v>
       </c>
       <c r="B63" t="n">
-        <v>16.94955444335938</v>
+        <v>16.94955062866211</v>
       </c>
       <c r="C63" t="n">
-        <v>17.26223378206583</v>
+        <v>17.26222989699639</v>
       </c>
       <c r="D63" t="n">
-        <v>16.7055108796171</v>
+        <v>16.70550711984472</v>
       </c>
       <c r="E63" t="n">
-        <v>16.94955444335938</v>
+        <v>16.94955062866211</v>
       </c>
       <c r="F63" t="n">
         <v>5669000</v>
@@ -1692,16 +1692,16 @@
         <v>44344</v>
       </c>
       <c r="B64" t="n">
-        <v>16.98577880859375</v>
+        <v>16.98577690124512</v>
       </c>
       <c r="C64" t="n">
-        <v>17.14974426261534</v>
+        <v>17.14974233685488</v>
       </c>
       <c r="D64" t="n">
-        <v>16.56442193873616</v>
+        <v>16.56442007870208</v>
       </c>
       <c r="E64" t="n">
-        <v>16.91142096521669</v>
+        <v>16.91141906621777</v>
       </c>
       <c r="F64" t="n">
         <v>4590500</v>
@@ -1752,16 +1752,16 @@
         <v>44349</v>
       </c>
       <c r="B67" t="n">
-        <v>16.76651763916016</v>
+        <v>16.76651573181152</v>
       </c>
       <c r="C67" t="n">
-        <v>17.26032492574389</v>
+        <v>17.26032296222006</v>
       </c>
       <c r="D67" t="n">
-        <v>16.73982554996776</v>
+        <v>16.7398236456556</v>
       </c>
       <c r="E67" t="n">
-        <v>17.06394533438589</v>
+        <v>17.06394339320207</v>
       </c>
       <c r="F67" t="n">
         <v>9352500</v>
@@ -1812,16 +1812,16 @@
         <v>44355</v>
       </c>
       <c r="B70" t="n">
-        <v>16.08205413818359</v>
+        <v>16.08205604553223</v>
       </c>
       <c r="C70" t="n">
-        <v>16.610177470563</v>
+        <v>16.61017944054762</v>
       </c>
       <c r="D70" t="n">
-        <v>15.92952558132173</v>
+        <v>15.92952747058032</v>
       </c>
       <c r="E70" t="n">
-        <v>16.60064432211775</v>
+        <v>16.60064629097173</v>
       </c>
       <c r="F70" t="n">
         <v>9246000</v>
@@ -1832,16 +1832,16 @@
         <v>44356</v>
       </c>
       <c r="B71" t="n">
-        <v>16.16403579711914</v>
+        <v>16.16403770446777</v>
       </c>
       <c r="C71" t="n">
-        <v>16.3966406169225</v>
+        <v>16.39664255171839</v>
       </c>
       <c r="D71" t="n">
-        <v>15.82466444316714</v>
+        <v>15.82466631047011</v>
       </c>
       <c r="E71" t="n">
-        <v>16.08205399409637</v>
+        <v>16.08205589177119</v>
       </c>
       <c r="F71" t="n">
         <v>10294500</v>
@@ -1852,16 +1852,16 @@
         <v>44357</v>
       </c>
       <c r="B72" t="n">
-        <v>16.30321884155273</v>
+        <v>16.3032169342041</v>
       </c>
       <c r="C72" t="n">
-        <v>16.34707169398488</v>
+        <v>16.34706978150581</v>
       </c>
       <c r="D72" t="n">
-        <v>15.97719348463267</v>
+        <v>15.97719161542644</v>
       </c>
       <c r="E72" t="n">
-        <v>16.15641233581547</v>
+        <v>16.15641044564205</v>
       </c>
       <c r="F72" t="n">
         <v>4720000</v>
@@ -1872,16 +1872,16 @@
         <v>44358</v>
       </c>
       <c r="B73" t="n">
-        <v>16.07061767578125</v>
+        <v>16.07061576843262</v>
       </c>
       <c r="C73" t="n">
-        <v>16.30512809539839</v>
+        <v>16.30512616021678</v>
       </c>
       <c r="D73" t="n">
-        <v>15.87423985953849</v>
+        <v>15.87423797549705</v>
       </c>
       <c r="E73" t="n">
-        <v>16.30322073792463</v>
+        <v>16.3032188029694</v>
       </c>
       <c r="F73" t="n">
         <v>5133000</v>
@@ -1892,16 +1892,16 @@
         <v>44361</v>
       </c>
       <c r="B74" t="n">
-        <v>16.01532173156738</v>
+        <v>16.01532363891602</v>
       </c>
       <c r="C74" t="n">
-        <v>16.19263501570841</v>
+        <v>16.19263694417421</v>
       </c>
       <c r="D74" t="n">
-        <v>15.85135630955313</v>
+        <v>15.85135819737426</v>
       </c>
       <c r="E74" t="n">
-        <v>16.16403557102893</v>
+        <v>16.16403749608867</v>
       </c>
       <c r="F74" t="n">
         <v>4317000</v>
@@ -1912,16 +1912,16 @@
         <v>44362</v>
       </c>
       <c r="B75" t="n">
-        <v>15.85898494720459</v>
+        <v>15.85898303985596</v>
       </c>
       <c r="C75" t="n">
-        <v>16.02676511323235</v>
+        <v>16.02676318570492</v>
       </c>
       <c r="D75" t="n">
-        <v>15.48720119095393</v>
+        <v>15.48719932831946</v>
       </c>
       <c r="E75" t="n">
-        <v>16.01532460600237</v>
+        <v>16.01532267985088</v>
       </c>
       <c r="F75" t="n">
         <v>8432500</v>
@@ -1932,16 +1932,16 @@
         <v>44363</v>
       </c>
       <c r="B76" t="n">
-        <v>15.89902019500732</v>
+        <v>15.89902114868164</v>
       </c>
       <c r="C76" t="n">
-        <v>16.11446425328521</v>
+        <v>16.11446521988256</v>
       </c>
       <c r="D76" t="n">
-        <v>15.66260430163777</v>
+        <v>15.6626052411311</v>
       </c>
       <c r="E76" t="n">
-        <v>15.70264243313756</v>
+        <v>15.70264337503251</v>
       </c>
       <c r="F76" t="n">
         <v>10606500</v>
@@ -1952,16 +1952,16 @@
         <v>44364</v>
       </c>
       <c r="B77" t="n">
-        <v>15.97719478607178</v>
+        <v>15.97719573974609</v>
       </c>
       <c r="C77" t="n">
-        <v>16.00769977675023</v>
+        <v>16.00770073224538</v>
       </c>
       <c r="D77" t="n">
-        <v>15.69120572552212</v>
+        <v>15.69120666212583</v>
       </c>
       <c r="E77" t="n">
-        <v>15.89711850369239</v>
+        <v>15.89711945258697</v>
       </c>
       <c r="F77" t="n">
         <v>7246000</v>
@@ -1972,16 +1972,16 @@
         <v>44365</v>
       </c>
       <c r="B78" t="n">
-        <v>16.20788955688477</v>
+        <v>16.20789337158203</v>
       </c>
       <c r="C78" t="n">
-        <v>16.36422919862247</v>
+        <v>16.36423305011592</v>
       </c>
       <c r="D78" t="n">
-        <v>15.67976438120391</v>
+        <v>15.67976807160136</v>
       </c>
       <c r="E78" t="n">
-        <v>15.98863076877287</v>
+        <v>15.98863453186528</v>
       </c>
       <c r="F78" t="n">
         <v>12012000</v>
@@ -1992,16 +1992,16 @@
         <v>44368</v>
       </c>
       <c r="B79" t="n">
-        <v>16.48434448242188</v>
+        <v>16.48434257507324</v>
       </c>
       <c r="C79" t="n">
-        <v>16.59302020374093</v>
+        <v>16.59301828381779</v>
       </c>
       <c r="D79" t="n">
-        <v>16.00007212945171</v>
+        <v>16.00007027813662</v>
       </c>
       <c r="E79" t="n">
-        <v>16.20789042268334</v>
+        <v>16.20788854732228</v>
       </c>
       <c r="F79" t="n">
         <v>6798000</v>
@@ -2032,16 +2032,16 @@
         <v>44370</v>
       </c>
       <c r="B81" t="n">
-        <v>16.39664459228516</v>
+        <v>16.39664268493652</v>
       </c>
       <c r="C81" t="n">
-        <v>16.45574721722616</v>
+        <v>16.45574530300238</v>
       </c>
       <c r="D81" t="n">
-        <v>16.20979811200328</v>
+        <v>16.20979622638967</v>
       </c>
       <c r="E81" t="n">
-        <v>16.4004574889011</v>
+        <v>16.40045558110893</v>
       </c>
       <c r="F81" t="n">
         <v>5819500</v>
@@ -2052,16 +2052,16 @@
         <v>44371</v>
       </c>
       <c r="B82" t="n">
-        <v>16.64640808105469</v>
+        <v>16.64640426635742</v>
       </c>
       <c r="C82" t="n">
-        <v>16.72648437193001</v>
+        <v>16.72648053888243</v>
       </c>
       <c r="D82" t="n">
-        <v>16.39664605690602</v>
+        <v>16.39664229944431</v>
       </c>
       <c r="E82" t="n">
-        <v>16.46909473560555</v>
+        <v>16.46909096154148</v>
       </c>
       <c r="F82" t="n">
         <v>8527500</v>
@@ -2072,16 +2072,16 @@
         <v>44372</v>
       </c>
       <c r="B83" t="n">
-        <v>16.18501091003418</v>
+        <v>16.18501472473145</v>
       </c>
       <c r="C83" t="n">
-        <v>16.74745398613881</v>
+        <v>16.7474579334001</v>
       </c>
       <c r="D83" t="n">
-        <v>16.05345599637458</v>
+        <v>16.05345978006525</v>
       </c>
       <c r="E83" t="n">
-        <v>16.64640405902371</v>
+        <v>16.64640798246821</v>
       </c>
       <c r="F83" t="n">
         <v>6078000</v>
@@ -2112,16 +2112,16 @@
         <v>44376</v>
       </c>
       <c r="B85" t="n">
-        <v>16.4233341217041</v>
+        <v>16.42333602905273</v>
       </c>
       <c r="C85" t="n">
-        <v>16.5396356325069</v>
+        <v>16.53963755336238</v>
       </c>
       <c r="D85" t="n">
-        <v>16.12018615980291</v>
+        <v>16.120188031945</v>
       </c>
       <c r="E85" t="n">
-        <v>16.36804258375244</v>
+        <v>16.3680444846797</v>
       </c>
       <c r="F85" t="n">
         <v>8958000</v>
@@ -2132,16 +2132,16 @@
         <v>44377</v>
       </c>
       <c r="B86" t="n">
-        <v>16.49959945678711</v>
+        <v>16.49959754943848</v>
       </c>
       <c r="C86" t="n">
-        <v>16.49959945678711</v>
+        <v>16.49959754943848</v>
       </c>
       <c r="D86" t="n">
-        <v>16.19073120503556</v>
+        <v>16.19072933339201</v>
       </c>
       <c r="E86" t="n">
-        <v>16.38901636774828</v>
+        <v>16.38901447318302</v>
       </c>
       <c r="F86" t="n">
         <v>6685000</v>
@@ -2172,16 +2172,16 @@
         <v>44379</v>
       </c>
       <c r="B88" t="n">
-        <v>16.39664459228516</v>
+        <v>16.39664268493652</v>
       </c>
       <c r="C88" t="n">
-        <v>16.45765457466542</v>
+        <v>16.45765266021977</v>
       </c>
       <c r="D88" t="n">
-        <v>16.21551836605848</v>
+        <v>16.21551647977946</v>
       </c>
       <c r="E88" t="n">
-        <v>16.36804514027171</v>
+        <v>16.36804323624992</v>
       </c>
       <c r="F88" t="n">
         <v>5948000</v>
@@ -2212,16 +2212,16 @@
         <v>44383</v>
       </c>
       <c r="B90" t="n">
-        <v>16.33944129943848</v>
+        <v>16.33944320678711</v>
       </c>
       <c r="C90" t="n">
-        <v>16.38901257865592</v>
+        <v>16.38901449179115</v>
       </c>
       <c r="D90" t="n">
-        <v>16.11255855649923</v>
+        <v>16.11256043736321</v>
       </c>
       <c r="E90" t="n">
-        <v>16.38901257865592</v>
+        <v>16.38901449179115</v>
       </c>
       <c r="F90" t="n">
         <v>3828000</v>
@@ -2252,16 +2252,16 @@
         <v>44385</v>
       </c>
       <c r="B92" t="n">
-        <v>16.43477630615234</v>
+        <v>16.43477249145508</v>
       </c>
       <c r="C92" t="n">
-        <v>16.79893431837681</v>
+        <v>16.79893041915436</v>
       </c>
       <c r="D92" t="n">
-        <v>16.24411873673473</v>
+        <v>16.24411496629124</v>
       </c>
       <c r="E92" t="n">
-        <v>16.26318322089262</v>
+        <v>16.26317944602405</v>
       </c>
       <c r="F92" t="n">
         <v>7435000</v>
@@ -2272,16 +2272,16 @@
         <v>44389</v>
       </c>
       <c r="B93" t="n">
-        <v>16.50150108337402</v>
+        <v>16.50150299072266</v>
       </c>
       <c r="C93" t="n">
-        <v>16.60255099813928</v>
+        <v>16.60255291716791</v>
       </c>
       <c r="D93" t="n">
-        <v>16.27461834177422</v>
+        <v>16.2746202228983</v>
       </c>
       <c r="E93" t="n">
-        <v>16.43095796968715</v>
+        <v>16.43095986888196</v>
       </c>
       <c r="F93" t="n">
         <v>4327500</v>
@@ -2332,16 +2332,16 @@
         <v>44392</v>
       </c>
       <c r="B96" t="n">
-        <v>16.45002746582031</v>
+        <v>16.45002365112305</v>
       </c>
       <c r="C96" t="n">
-        <v>16.86375671689422</v>
+        <v>16.86375280625475</v>
       </c>
       <c r="D96" t="n">
-        <v>16.44049431591159</v>
+        <v>16.44049050342502</v>
       </c>
       <c r="E96" t="n">
-        <v>16.72266864381253</v>
+        <v>16.72266476589084</v>
       </c>
       <c r="F96" t="n">
         <v>3746000</v>
@@ -2392,16 +2392,16 @@
         <v>44397</v>
       </c>
       <c r="B99" t="n">
-        <v>16.51103591918945</v>
+        <v>16.51103782653809</v>
       </c>
       <c r="C99" t="n">
-        <v>16.71694684707543</v>
+        <v>16.71694877821082</v>
       </c>
       <c r="D99" t="n">
-        <v>16.45955909634909</v>
+        <v>16.45956099775114</v>
       </c>
       <c r="E99" t="n">
-        <v>16.6540295180957</v>
+        <v>16.6540314419629</v>
       </c>
       <c r="F99" t="n">
         <v>3835500</v>
@@ -2412,16 +2412,16 @@
         <v>44398</v>
       </c>
       <c r="B100" t="n">
-        <v>16.59683036804199</v>
+        <v>16.59683227539062</v>
       </c>
       <c r="C100" t="n">
-        <v>16.59683036804199</v>
+        <v>16.59683227539062</v>
       </c>
       <c r="D100" t="n">
-        <v>16.41570419565662</v>
+        <v>16.41570608218979</v>
       </c>
       <c r="E100" t="n">
-        <v>16.51675410812279</v>
+        <v>16.51675600626886</v>
       </c>
       <c r="F100" t="n">
         <v>4032000</v>
@@ -2452,16 +2452,16 @@
         <v>44400</v>
       </c>
       <c r="B102" t="n">
-        <v>16.68262672424316</v>
+        <v>16.68263244628906</v>
       </c>
       <c r="C102" t="n">
-        <v>16.73029064472191</v>
+        <v>16.73029638311626</v>
       </c>
       <c r="D102" t="n">
-        <v>16.56060497863364</v>
+        <v>16.56061065882677</v>
       </c>
       <c r="E102" t="n">
-        <v>16.64449413325056</v>
+        <v>16.64449984221719</v>
       </c>
       <c r="F102" t="n">
         <v>4154500</v>
@@ -2552,16 +2552,16 @@
         <v>44407</v>
       </c>
       <c r="B107" t="n">
-        <v>16.52629089355469</v>
+        <v>16.52628898620605</v>
       </c>
       <c r="C107" t="n">
-        <v>16.73220184103048</v>
+        <v>16.73219990991705</v>
       </c>
       <c r="D107" t="n">
-        <v>16.30893943885111</v>
+        <v>16.30893755658766</v>
       </c>
       <c r="E107" t="n">
-        <v>16.6254334709708</v>
+        <v>16.62543155217983</v>
       </c>
       <c r="F107" t="n">
         <v>16469000</v>
@@ -2572,16 +2572,16 @@
         <v>44410</v>
       </c>
       <c r="B108" t="n">
-        <v>16.52247619628906</v>
+        <v>16.5224781036377</v>
       </c>
       <c r="C108" t="n">
-        <v>16.83896837564879</v>
+        <v>16.83897031953316</v>
       </c>
       <c r="D108" t="n">
-        <v>16.36232184039388</v>
+        <v>16.36232372925435</v>
       </c>
       <c r="E108" t="n">
-        <v>16.68262873392202</v>
+        <v>16.6826306597586</v>
       </c>
       <c r="F108" t="n">
         <v>8100500</v>
@@ -2612,16 +2612,16 @@
         <v>44412</v>
       </c>
       <c r="B110" t="n">
-        <v>16.60255432128906</v>
+        <v>16.60255241394043</v>
       </c>
       <c r="C110" t="n">
-        <v>16.83134446559894</v>
+        <v>16.83134253196625</v>
       </c>
       <c r="D110" t="n">
-        <v>16.3489776234245</v>
+        <v>16.34897574520748</v>
       </c>
       <c r="E110" t="n">
-        <v>16.48243990463543</v>
+        <v>16.48243801108588</v>
       </c>
       <c r="F110" t="n">
         <v>6533500</v>
@@ -2632,16 +2632,16 @@
         <v>44413</v>
       </c>
       <c r="B111" t="n">
-        <v>16.58729934692383</v>
+        <v>16.58729553222656</v>
       </c>
       <c r="C111" t="n">
-        <v>16.93811123196384</v>
+        <v>16.93810733658792</v>
       </c>
       <c r="D111" t="n">
-        <v>16.47481073358749</v>
+        <v>16.47480694476002</v>
       </c>
       <c r="E111" t="n">
-        <v>16.59301960001205</v>
+        <v>16.59301578399926</v>
       </c>
       <c r="F111" t="n">
         <v>13427000</v>
@@ -2652,16 +2652,16 @@
         <v>44414</v>
       </c>
       <c r="B112" t="n">
-        <v>16.73982620239258</v>
+        <v>16.73982810974121</v>
       </c>
       <c r="C112" t="n">
-        <v>16.78367905199969</v>
+        <v>16.78368096434495</v>
       </c>
       <c r="D112" t="n">
-        <v>16.37566826999301</v>
+        <v>16.37567013584921</v>
       </c>
       <c r="E112" t="n">
-        <v>16.63115048433273</v>
+        <v>16.63115237929877</v>
       </c>
       <c r="F112" t="n">
         <v>15424500</v>
@@ -2692,16 +2692,16 @@
         <v>44418</v>
       </c>
       <c r="B114" t="n">
-        <v>17.55012702941895</v>
+        <v>17.55012512207031</v>
       </c>
       <c r="C114" t="n">
-        <v>17.66452300930153</v>
+        <v>17.66452108952034</v>
       </c>
       <c r="D114" t="n">
-        <v>17.10589279254452</v>
+        <v>17.10589093347529</v>
       </c>
       <c r="E114" t="n">
-        <v>17.22219431143875</v>
+        <v>17.22219243972985</v>
       </c>
       <c r="F114" t="n">
         <v>10281500</v>
@@ -2712,16 +2712,16 @@
         <v>44419</v>
       </c>
       <c r="B115" t="n">
-        <v>17.20884895324707</v>
+        <v>17.20884704589844</v>
       </c>
       <c r="C115" t="n">
-        <v>17.57872718168084</v>
+        <v>17.57872523333663</v>
       </c>
       <c r="D115" t="n">
-        <v>17.19741026393275</v>
+        <v>17.19740835785192</v>
       </c>
       <c r="E115" t="n">
-        <v>17.57872718168084</v>
+        <v>17.57872523333663</v>
       </c>
       <c r="F115" t="n">
         <v>6265000</v>
@@ -2752,16 +2752,16 @@
         <v>44421</v>
       </c>
       <c r="B117" t="n">
-        <v>16.91142082214355</v>
+        <v>16.91141891479492</v>
       </c>
       <c r="C117" t="n">
-        <v>17.27367324935177</v>
+        <v>17.27367130114663</v>
       </c>
       <c r="D117" t="n">
-        <v>16.53010391318421</v>
+        <v>16.53010204884227</v>
       </c>
       <c r="E117" t="n">
-        <v>16.82562429034489</v>
+        <v>16.82562239267279</v>
       </c>
       <c r="F117" t="n">
         <v>5547600</v>
@@ -2792,16 +2792,16 @@
         <v>44425</v>
       </c>
       <c r="B119" t="n">
-        <v>16.16784858703613</v>
+        <v>16.16785049438477</v>
       </c>
       <c r="C119" t="n">
-        <v>16.39664050965117</v>
+        <v>16.39664244399077</v>
       </c>
       <c r="D119" t="n">
-        <v>15.70073523003284</v>
+        <v>15.70073708227531</v>
       </c>
       <c r="E119" t="n">
-        <v>16.16784858703613</v>
+        <v>16.16785049438477</v>
       </c>
       <c r="F119" t="n">
         <v>9967800</v>
@@ -2812,16 +2812,16 @@
         <v>44426</v>
       </c>
       <c r="B120" t="n">
-        <v>15.88186550140381</v>
+        <v>15.88186454772949</v>
       </c>
       <c r="C120" t="n">
-        <v>16.30131504320764</v>
+        <v>16.30131406434622</v>
       </c>
       <c r="D120" t="n">
-        <v>15.64354218737522</v>
+        <v>15.64354124801175</v>
       </c>
       <c r="E120" t="n">
-        <v>16.16785275093307</v>
+        <v>16.16785178008579</v>
       </c>
       <c r="F120" t="n">
         <v>10736900</v>
@@ -2852,16 +2852,16 @@
         <v>44428</v>
       </c>
       <c r="B122" t="n">
-        <v>16.94955444335938</v>
+        <v>16.94955062866211</v>
       </c>
       <c r="C122" t="n">
-        <v>17.41666791226037</v>
+        <v>17.4166639924337</v>
       </c>
       <c r="D122" t="n">
-        <v>16.3775781363283</v>
+        <v>16.37757445036105</v>
       </c>
       <c r="E122" t="n">
-        <v>16.53963805968273</v>
+        <v>16.53963433724198</v>
       </c>
       <c r="F122" t="n">
         <v>9513400</v>
@@ -2872,16 +2872,16 @@
         <v>44431</v>
       </c>
       <c r="B123" t="n">
-        <v>16.69216537475586</v>
+        <v>16.69216346740723</v>
       </c>
       <c r="C123" t="n">
-        <v>17.16881200972343</v>
+        <v>17.16881004791025</v>
       </c>
       <c r="D123" t="n">
-        <v>16.52057229524551</v>
+        <v>16.52057040750415</v>
       </c>
       <c r="E123" t="n">
-        <v>16.97815262843136</v>
+        <v>16.97815068840407</v>
       </c>
       <c r="F123" t="n">
         <v>5050600</v>
@@ -2892,16 +2892,16 @@
         <v>44432</v>
       </c>
       <c r="B124" t="n">
-        <v>16.91142082214355</v>
+        <v>16.91141891479492</v>
       </c>
       <c r="C124" t="n">
-        <v>17.05441443572051</v>
+        <v>17.05441251224439</v>
       </c>
       <c r="D124" t="n">
-        <v>16.66356437675437</v>
+        <v>16.66356249736014</v>
       </c>
       <c r="E124" t="n">
-        <v>16.78749350858018</v>
+        <v>16.78749161520865</v>
       </c>
       <c r="F124" t="n">
         <v>4198100</v>
@@ -2912,16 +2912,16 @@
         <v>44433</v>
       </c>
       <c r="B125" t="n">
-        <v>17.01628303527832</v>
+        <v>17.01628494262695</v>
       </c>
       <c r="C125" t="n">
-        <v>17.19740924229705</v>
+        <v>17.19741116994805</v>
       </c>
       <c r="D125" t="n">
-        <v>16.78749289822105</v>
+        <v>16.78749477992469</v>
       </c>
       <c r="E125" t="n">
-        <v>17.0258161849385</v>
+        <v>17.0258180933557</v>
       </c>
       <c r="F125" t="n">
         <v>4269900</v>
@@ -2932,16 +2932,16 @@
         <v>44434</v>
       </c>
       <c r="B126" t="n">
-        <v>16.5587043762207</v>
+        <v>16.55870246887207</v>
       </c>
       <c r="C126" t="n">
-        <v>17.00675154437543</v>
+        <v>17.00674958541756</v>
       </c>
       <c r="D126" t="n">
-        <v>16.5587043762207</v>
+        <v>16.55870246887207</v>
       </c>
       <c r="E126" t="n">
-        <v>16.93048815791797</v>
+        <v>16.93048620774466</v>
       </c>
       <c r="F126" t="n">
         <v>4969900</v>
@@ -2952,16 +2952,16 @@
         <v>44435</v>
       </c>
       <c r="B127" t="n">
-        <v>16.58729934692383</v>
+        <v>16.58729553222656</v>
       </c>
       <c r="C127" t="n">
-        <v>16.72076161549623</v>
+        <v>16.72075777010571</v>
       </c>
       <c r="D127" t="n">
-        <v>16.39664182051824</v>
+        <v>16.39663804966782</v>
       </c>
       <c r="E127" t="n">
-        <v>16.55870171800724</v>
+        <v>16.55869790988677</v>
       </c>
       <c r="F127" t="n">
         <v>5662600</v>
@@ -3012,16 +3012,16 @@
         <v>44440</v>
       </c>
       <c r="B130" t="n">
-        <v>16.23458290100098</v>
+        <v>16.23458099365234</v>
       </c>
       <c r="C130" t="n">
-        <v>16.77795970229644</v>
+        <v>16.77795773110823</v>
       </c>
       <c r="D130" t="n">
-        <v>15.89139678723021</v>
+        <v>15.8913949202014</v>
       </c>
       <c r="E130" t="n">
-        <v>16.30131313017587</v>
+        <v>16.30131121498732</v>
       </c>
       <c r="F130" t="n">
         <v>7651500</v>
@@ -3032,16 +3032,16 @@
         <v>44441</v>
       </c>
       <c r="B131" t="n">
-        <v>16.72076225280762</v>
+        <v>16.72076416015625</v>
       </c>
       <c r="C131" t="n">
-        <v>17.03534891071645</v>
+        <v>17.03535085395019</v>
       </c>
       <c r="D131" t="n">
-        <v>16.10112026815059</v>
+        <v>16.10112210481625</v>
       </c>
       <c r="E131" t="n">
-        <v>16.16785049584908</v>
+        <v>16.1678523401267</v>
       </c>
       <c r="F131" t="n">
         <v>17566400</v>
@@ -3072,16 +3072,16 @@
         <v>44445</v>
       </c>
       <c r="B133" t="n">
-        <v>17.49292755126953</v>
+        <v>17.49292945861816</v>
       </c>
       <c r="C133" t="n">
-        <v>17.66452058844603</v>
+        <v>17.66452251450438</v>
       </c>
       <c r="D133" t="n">
-        <v>17.04487866125041</v>
+        <v>17.04488051974584</v>
       </c>
       <c r="E133" t="n">
-        <v>17.30226821701516</v>
+        <v>17.30227010357517</v>
       </c>
       <c r="F133" t="n">
         <v>6471000</v>
@@ -3092,16 +3092,16 @@
         <v>44447</v>
       </c>
       <c r="B134" t="n">
-        <v>17.0734806060791</v>
+        <v>17.07348251342773</v>
       </c>
       <c r="C134" t="n">
-        <v>17.55012719322427</v>
+        <v>17.55012915382106</v>
       </c>
       <c r="D134" t="n">
-        <v>16.84469046244091</v>
+        <v>16.84469234423046</v>
       </c>
       <c r="E134" t="n">
-        <v>17.49293011188033</v>
+        <v>17.49293206608739</v>
       </c>
       <c r="F134" t="n">
         <v>11069100</v>
@@ -3132,16 +3132,16 @@
         <v>44449</v>
       </c>
       <c r="B136" t="n">
-        <v>17.33086967468262</v>
+        <v>17.33086776733398</v>
       </c>
       <c r="C136" t="n">
-        <v>17.60732374135838</v>
+        <v>17.6073218035846</v>
       </c>
       <c r="D136" t="n">
-        <v>17.01628300942406</v>
+        <v>17.01628113669726</v>
       </c>
       <c r="E136" t="n">
-        <v>17.33086967468262</v>
+        <v>17.33086776733398</v>
       </c>
       <c r="F136" t="n">
         <v>19125200</v>
@@ -3172,16 +3172,16 @@
         <v>44453</v>
       </c>
       <c r="B138" t="n">
-        <v>17.47386360168457</v>
+        <v>17.47386169433594</v>
       </c>
       <c r="C138" t="n">
-        <v>18.1507026927803</v>
+        <v>18.15070071155172</v>
       </c>
       <c r="D138" t="n">
-        <v>17.3976002213898</v>
+        <v>17.39759832236565</v>
       </c>
       <c r="E138" t="n">
-        <v>17.82658287196191</v>
+        <v>17.82658092611242</v>
       </c>
       <c r="F138" t="n">
         <v>6594500</v>
@@ -3192,16 +3192,16 @@
         <v>44454</v>
       </c>
       <c r="B139" t="n">
-        <v>17.72172164916992</v>
+        <v>17.72171783447266</v>
       </c>
       <c r="C139" t="n">
-        <v>17.82658448843234</v>
+        <v>17.82658065116278</v>
       </c>
       <c r="D139" t="n">
-        <v>17.27367447659312</v>
+        <v>17.27367075834045</v>
       </c>
       <c r="E139" t="n">
-        <v>17.46433203548721</v>
+        <v>17.46432827619446</v>
       </c>
       <c r="F139" t="n">
         <v>8756500</v>
@@ -3212,16 +3212,16 @@
         <v>44455</v>
       </c>
       <c r="B140" t="n">
-        <v>18.26509475708008</v>
+        <v>18.26509666442871</v>
       </c>
       <c r="C140" t="n">
-        <v>18.33182497989392</v>
+        <v>18.33182689421092</v>
       </c>
       <c r="D140" t="n">
-        <v>17.72171800758197</v>
+        <v>17.72171985818801</v>
       </c>
       <c r="E140" t="n">
-        <v>17.72171800758197</v>
+        <v>17.72171985818801</v>
       </c>
       <c r="F140" t="n">
         <v>17281800</v>
@@ -3252,16 +3252,16 @@
         <v>44459</v>
       </c>
       <c r="B142" t="n">
-        <v>17.94097900390625</v>
+        <v>17.94097518920898</v>
       </c>
       <c r="C142" t="n">
-        <v>18.12210523384961</v>
+        <v>18.12210138064041</v>
       </c>
       <c r="D142" t="n">
-        <v>17.63592544922014</v>
+        <v>17.63592169938482</v>
       </c>
       <c r="E142" t="n">
-        <v>18.02677554344455</v>
+        <v>18.02677171050481</v>
       </c>
       <c r="F142" t="n">
         <v>15522000</v>
@@ -3272,16 +3272,16 @@
         <v>44460</v>
       </c>
       <c r="B143" t="n">
-        <v>18.57968521118164</v>
+        <v>18.57967948913574</v>
       </c>
       <c r="C143" t="n">
-        <v>18.74174513629765</v>
+        <v>18.74173936434163</v>
       </c>
       <c r="D143" t="n">
-        <v>17.82658448971026</v>
+        <v>17.82657899959923</v>
       </c>
       <c r="E143" t="n">
-        <v>18.06490780204188</v>
+        <v>18.06490223853365</v>
       </c>
       <c r="F143" t="n">
         <v>17756900</v>
@@ -3312,16 +3312,16 @@
         <v>44462</v>
       </c>
       <c r="B145" t="n">
-        <v>18.2936954498291</v>
+        <v>18.29369735717773</v>
       </c>
       <c r="C145" t="n">
-        <v>18.53201872941112</v>
+        <v>18.53202066160796</v>
       </c>
       <c r="D145" t="n">
-        <v>18.07443665073428</v>
+        <v>18.07443853522241</v>
       </c>
       <c r="E145" t="n">
-        <v>18.34135937844058</v>
+        <v>18.34136129075877</v>
       </c>
       <c r="F145" t="n">
         <v>20822300</v>
@@ -3352,16 +3352,16 @@
         <v>44466</v>
       </c>
       <c r="B147" t="n">
-        <v>18.35089111328125</v>
+        <v>18.35089302062988</v>
       </c>
       <c r="C147" t="n">
-        <v>18.46528707869811</v>
+        <v>18.46528899793678</v>
       </c>
       <c r="D147" t="n">
-        <v>17.83611199629868</v>
+        <v>17.83611385014238</v>
       </c>
       <c r="E147" t="n">
-        <v>18.01723818393279</v>
+        <v>18.01724005660232</v>
       </c>
       <c r="F147" t="n">
         <v>7788100</v>
@@ -3372,16 +3372,16 @@
         <v>44467</v>
       </c>
       <c r="B148" t="n">
-        <v>18.28416442871094</v>
+        <v>18.2841625213623</v>
       </c>
       <c r="C148" t="n">
-        <v>18.29369757919535</v>
+        <v>18.29369567085224</v>
       </c>
       <c r="D148" t="n">
-        <v>18.01724166993512</v>
+        <v>18.01723979043107</v>
       </c>
       <c r="E148" t="n">
-        <v>18.2364986762889</v>
+        <v>18.23649677391261</v>
       </c>
       <c r="F148" t="n">
         <v>11310100</v>
@@ -3392,16 +3392,16 @@
         <v>44468</v>
       </c>
       <c r="B149" t="n">
-        <v>18.08396911621094</v>
+        <v>18.08397102355957</v>
       </c>
       <c r="C149" t="n">
-        <v>18.4271552076744</v>
+        <v>18.42715715121949</v>
       </c>
       <c r="D149" t="n">
-        <v>17.96957496456462</v>
+        <v>17.9695768598479</v>
       </c>
       <c r="E149" t="n">
-        <v>18.29369475799961</v>
+        <v>18.29369668746839</v>
       </c>
       <c r="F149" t="n">
         <v>10203400</v>
@@ -3412,16 +3412,16 @@
         <v>44469</v>
       </c>
       <c r="B150" t="n">
-        <v>18.15070533752441</v>
+        <v>18.15070152282715</v>
       </c>
       <c r="C150" t="n">
-        <v>18.62735198838466</v>
+        <v>18.62734807351153</v>
       </c>
       <c r="D150" t="n">
-        <v>18.0458424924911</v>
+        <v>18.04583869983265</v>
       </c>
       <c r="E150" t="n">
-        <v>18.30323212033868</v>
+        <v>18.30322827358517</v>
       </c>
       <c r="F150" t="n">
         <v>10293000</v>
@@ -3432,16 +3432,16 @@
         <v>44470</v>
       </c>
       <c r="B151" t="n">
-        <v>18.45575523376465</v>
+        <v>18.45575714111328</v>
       </c>
       <c r="C151" t="n">
-        <v>18.56061623968673</v>
+        <v>18.56061815787245</v>
       </c>
       <c r="D151" t="n">
-        <v>18.00770630734936</v>
+        <v>18.00770816839343</v>
       </c>
       <c r="E151" t="n">
-        <v>18.19836565709148</v>
+        <v>18.19836753783964</v>
       </c>
       <c r="F151" t="n">
         <v>5841800</v>
@@ -3452,16 +3452,16 @@
         <v>44473</v>
       </c>
       <c r="B152" t="n">
-        <v>18.41762351989746</v>
+        <v>18.41762542724609</v>
       </c>
       <c r="C152" t="n">
-        <v>18.49388689979976</v>
+        <v>18.49388881504631</v>
       </c>
       <c r="D152" t="n">
-        <v>18.07443740120593</v>
+        <v>18.07443927301384</v>
       </c>
       <c r="E152" t="n">
-        <v>18.3890258888481</v>
+        <v>18.38902779323513</v>
       </c>
       <c r="F152" t="n">
         <v>9789400</v>
@@ -3472,16 +3472,16 @@
         <v>44474</v>
       </c>
       <c r="B153" t="n">
-        <v>18.32229423522949</v>
+        <v>18.32229232788086</v>
       </c>
       <c r="C153" t="n">
-        <v>18.49388729827244</v>
+        <v>18.49388537306099</v>
       </c>
       <c r="D153" t="n">
-        <v>18.04584015897554</v>
+        <v>18.04583828040574</v>
       </c>
       <c r="E153" t="n">
-        <v>18.34136053518147</v>
+        <v>18.34135862584804</v>
       </c>
       <c r="F153" t="n">
         <v>8000200</v>
@@ -3492,16 +3492,16 @@
         <v>44475</v>
       </c>
       <c r="B154" t="n">
-        <v>18.27167701721191</v>
+        <v>18.27167892456055</v>
       </c>
       <c r="C154" t="n">
-        <v>18.63481622367532</v>
+        <v>18.63481816893143</v>
       </c>
       <c r="D154" t="n">
-        <v>18.06143689840233</v>
+        <v>18.06143878380436</v>
       </c>
       <c r="E154" t="n">
-        <v>18.11877428411284</v>
+        <v>18.11877617550022</v>
       </c>
       <c r="F154" t="n">
         <v>10611600</v>
@@ -3512,16 +3512,16 @@
         <v>44476</v>
       </c>
       <c r="B155" t="n">
-        <v>18.08055114746094</v>
+        <v>18.0805492401123</v>
       </c>
       <c r="C155" t="n">
-        <v>18.36723991743979</v>
+        <v>18.36723797984786</v>
       </c>
       <c r="D155" t="n">
-        <v>17.99454415192273</v>
+        <v>17.99454225364713</v>
       </c>
       <c r="E155" t="n">
-        <v>18.271678209262</v>
+        <v>18.27167628175104</v>
       </c>
       <c r="F155" t="n">
         <v>7169200</v>
@@ -3552,16 +3552,16 @@
         <v>44480</v>
       </c>
       <c r="B157" t="n">
-        <v>16.62798881530762</v>
+        <v>16.62798690795898</v>
       </c>
       <c r="C157" t="n">
-        <v>17.52628299400677</v>
+        <v>17.5262809836174</v>
       </c>
       <c r="D157" t="n">
-        <v>16.47508791119575</v>
+        <v>16.47508602138593</v>
       </c>
       <c r="E157" t="n">
-        <v>17.4211629389089</v>
+        <v>17.42116094057755</v>
       </c>
       <c r="F157" t="n">
         <v>31512800</v>
@@ -3572,16 +3572,16 @@
         <v>44482</v>
       </c>
       <c r="B158" t="n">
-        <v>17.12491607666016</v>
+        <v>17.12491989135742</v>
       </c>
       <c r="C158" t="n">
-        <v>17.40204825613737</v>
+        <v>17.4020521325678</v>
       </c>
       <c r="D158" t="n">
-        <v>16.6279872730265</v>
+        <v>16.62799097702933</v>
       </c>
       <c r="E158" t="n">
-        <v>16.6279872730265</v>
+        <v>16.62799097702933</v>
       </c>
       <c r="F158" t="n">
         <v>10150700</v>
@@ -3632,16 +3632,16 @@
         <v>44487</v>
       </c>
       <c r="B161" t="n">
-        <v>16.20751190185547</v>
+        <v>16.20750999450684</v>
       </c>
       <c r="C161" t="n">
-        <v>16.67577301414236</v>
+        <v>16.67577105168735</v>
       </c>
       <c r="D161" t="n">
-        <v>16.10239365985386</v>
+        <v>16.10239176487586</v>
       </c>
       <c r="E161" t="n">
-        <v>16.58976601986295</v>
+        <v>16.5897640675295</v>
       </c>
       <c r="F161" t="n">
         <v>13070300</v>
@@ -3732,16 +3732,16 @@
         <v>44494</v>
       </c>
       <c r="B166" t="n">
-        <v>15.41433620452881</v>
+        <v>15.41433715820312</v>
       </c>
       <c r="C166" t="n">
-        <v>15.66280062794844</v>
+        <v>15.66280159699508</v>
       </c>
       <c r="D166" t="n">
-        <v>15.13720400095626</v>
+        <v>15.1372049374846</v>
       </c>
       <c r="E166" t="n">
-        <v>15.39522495866771</v>
+        <v>15.39522591115963</v>
       </c>
       <c r="F166" t="n">
         <v>20484500</v>
@@ -3772,16 +3772,16 @@
         <v>44496</v>
       </c>
       <c r="B168" t="n">
-        <v>14.94607830047607</v>
+        <v>14.94607925415039</v>
       </c>
       <c r="C168" t="n">
-        <v>15.38566886553011</v>
+        <v>15.38566984725368</v>
       </c>
       <c r="D168" t="n">
-        <v>14.81228955063831</v>
+        <v>14.81229049577588</v>
       </c>
       <c r="E168" t="n">
-        <v>15.38566886553011</v>
+        <v>15.38566984725368</v>
       </c>
       <c r="F168" t="n">
         <v>9783700</v>
@@ -3812,16 +3812,16 @@
         <v>44498</v>
       </c>
       <c r="B170" t="n">
-        <v>14.61160945892334</v>
+        <v>14.61160755157471</v>
       </c>
       <c r="C170" t="n">
-        <v>15.21365757234741</v>
+        <v>15.21365558640951</v>
       </c>
       <c r="D170" t="n">
-        <v>14.50649029424096</v>
+        <v>14.50648840061422</v>
       </c>
       <c r="E170" t="n">
-        <v>15.0034183316212</v>
+        <v>15.0034163731272</v>
       </c>
       <c r="F170" t="n">
         <v>13706000</v>
@@ -3832,16 +3832,16 @@
         <v>44501</v>
       </c>
       <c r="B171" t="n">
-        <v>14.31536102294922</v>
+        <v>14.3153600692749</v>
       </c>
       <c r="C171" t="n">
-        <v>14.77406466781794</v>
+        <v>14.77406368358527</v>
       </c>
       <c r="D171" t="n">
-        <v>14.20068533957237</v>
+        <v>14.20068439353763</v>
       </c>
       <c r="E171" t="n">
-        <v>14.76450813302954</v>
+        <v>14.76450714943351</v>
       </c>
       <c r="F171" t="n">
         <v>10277500</v>
@@ -3852,16 +3852,16 @@
         <v>44503</v>
       </c>
       <c r="B172" t="n">
-        <v>14.74539661407471</v>
+        <v>14.74539756774902</v>
       </c>
       <c r="C172" t="n">
-        <v>14.86962883762583</v>
+        <v>14.86962979933499</v>
       </c>
       <c r="D172" t="n">
-        <v>14.07645373166693</v>
+        <v>14.07645464207665</v>
       </c>
       <c r="E172" t="n">
-        <v>14.14334856672452</v>
+        <v>14.14334948146074</v>
       </c>
       <c r="F172" t="n">
         <v>21906500</v>
@@ -3892,16 +3892,16 @@
         <v>44505</v>
       </c>
       <c r="B174" t="n">
-        <v>14.56382656097412</v>
+        <v>14.5638256072998</v>
       </c>
       <c r="C174" t="n">
-        <v>14.71672748370959</v>
+        <v>14.71672652002295</v>
       </c>
       <c r="D174" t="n">
-        <v>14.17201771862414</v>
+        <v>14.1720167906064</v>
       </c>
       <c r="E174" t="n">
-        <v>14.54471440131288</v>
+        <v>14.54471344889008</v>
       </c>
       <c r="F174" t="n">
         <v>8161700</v>
@@ -3912,16 +3912,16 @@
         <v>44508</v>
       </c>
       <c r="B175" t="n">
-        <v>14.73583984375</v>
+        <v>14.73584079742432</v>
       </c>
       <c r="C175" t="n">
-        <v>14.89829729415845</v>
+        <v>14.89829825834669</v>
       </c>
       <c r="D175" t="n">
-        <v>14.2866927213642</v>
+        <v>14.28669364597061</v>
       </c>
       <c r="E175" t="n">
-        <v>14.39181278419399</v>
+        <v>14.39181371560356</v>
       </c>
       <c r="F175" t="n">
         <v>8290300</v>
@@ -3932,16 +3932,16 @@
         <v>44509</v>
       </c>
       <c r="B176" t="n">
-        <v>14.81229019165039</v>
+        <v>14.81228923797607</v>
       </c>
       <c r="C176" t="n">
-        <v>15.08942332652359</v>
+        <v>15.08942235500634</v>
       </c>
       <c r="D176" t="n">
-        <v>14.66894581240476</v>
+        <v>14.66894486795953</v>
       </c>
       <c r="E176" t="n">
-        <v>14.80273365667099</v>
+        <v>14.80273270361196</v>
       </c>
       <c r="F176" t="n">
         <v>6124400</v>
@@ -3972,16 +3972,16 @@
         <v>44511</v>
       </c>
       <c r="B178" t="n">
-        <v>15.19454288482666</v>
+        <v>15.19454193115234</v>
       </c>
       <c r="C178" t="n">
-        <v>15.51945779195179</v>
+        <v>15.51945681788442</v>
       </c>
       <c r="D178" t="n">
-        <v>15.07986719608156</v>
+        <v>15.07986624960478</v>
       </c>
       <c r="E178" t="n">
-        <v>15.43345079755262</v>
+        <v>15.43344982888343</v>
       </c>
       <c r="F178" t="n">
         <v>5555700</v>
@@ -3992,16 +3992,16 @@
         <v>44512</v>
       </c>
       <c r="B179" t="n">
-        <v>14.84095859527588</v>
+        <v>14.84095764160156</v>
       </c>
       <c r="C179" t="n">
-        <v>15.23276740816299</v>
+        <v>15.23276642931119</v>
       </c>
       <c r="D179" t="n">
-        <v>14.82184643705182</v>
+        <v>14.82184548460564</v>
       </c>
       <c r="E179" t="n">
-        <v>15.08942303171791</v>
+        <v>15.08942206207736</v>
       </c>
       <c r="F179" t="n">
         <v>7831400</v>
@@ -4012,16 +4012,16 @@
         <v>44516</v>
       </c>
       <c r="B180" t="n">
-        <v>14.18157386779785</v>
+        <v>14.18157291412354</v>
       </c>
       <c r="C180" t="n">
-        <v>14.86007237747372</v>
+        <v>14.86007137817213</v>
       </c>
       <c r="D180" t="n">
-        <v>14.00000334347483</v>
+        <v>14.00000240201066</v>
       </c>
       <c r="E180" t="n">
-        <v>14.81229061258022</v>
+        <v>14.81228961649183</v>
       </c>
       <c r="F180" t="n">
         <v>11424100</v>
@@ -4032,16 +4032,16 @@
         <v>44517</v>
       </c>
       <c r="B181" t="n">
-        <v>13.62730693817139</v>
+        <v>13.6273078918457</v>
       </c>
       <c r="C181" t="n">
-        <v>14.42048109928345</v>
+        <v>14.42048210846616</v>
       </c>
       <c r="D181" t="n">
-        <v>13.49351818506572</v>
+        <v>13.49351912937716</v>
       </c>
       <c r="E181" t="n">
-        <v>14.42048109928345</v>
+        <v>14.42048210846616</v>
       </c>
       <c r="F181" t="n">
         <v>10535200</v>
@@ -4092,16 +4092,16 @@
         <v>44522</v>
       </c>
       <c r="B184" t="n">
-        <v>13.17815971374512</v>
+        <v>13.17816066741943</v>
       </c>
       <c r="C184" t="n">
-        <v>13.569968523517</v>
+        <v>13.56996950554565</v>
       </c>
       <c r="D184" t="n">
-        <v>13.12082141680619</v>
+        <v>13.12082236633105</v>
       </c>
       <c r="E184" t="n">
-        <v>13.52218676129477</v>
+        <v>13.52218773986557</v>
       </c>
       <c r="F184" t="n">
         <v>12046100</v>
@@ -4192,16 +4192,16 @@
         <v>44529</v>
       </c>
       <c r="B189" t="n">
-        <v>12.47099208831787</v>
+        <v>12.47099304199219</v>
       </c>
       <c r="C189" t="n">
-        <v>13.11126530889348</v>
+        <v>13.11126631153039</v>
       </c>
       <c r="D189" t="n">
-        <v>12.42321032786153</v>
+        <v>12.42321127788191</v>
       </c>
       <c r="E189" t="n">
-        <v>12.88191304097531</v>
+        <v>12.88191402607333</v>
       </c>
       <c r="F189" t="n">
         <v>13464500</v>
@@ -4212,16 +4212,16 @@
         <v>44530</v>
       </c>
       <c r="B190" t="n">
-        <v>12.18430233001709</v>
+        <v>12.18430328369141</v>
       </c>
       <c r="C190" t="n">
-        <v>12.44232328740027</v>
+        <v>12.44232426127008</v>
       </c>
       <c r="D190" t="n">
-        <v>11.84027529820078</v>
+        <v>11.84027622494785</v>
       </c>
       <c r="E190" t="n">
-        <v>12.38498499308359</v>
+        <v>12.38498596246548</v>
       </c>
       <c r="F190" t="n">
         <v>16793700</v>
@@ -4232,16 +4232,16 @@
         <v>44531</v>
       </c>
       <c r="B191" t="n">
-        <v>11.91672706604004</v>
+        <v>11.91672611236572</v>
       </c>
       <c r="C191" t="n">
-        <v>12.37542982579687</v>
+        <v>12.37542883541339</v>
       </c>
       <c r="D191" t="n">
-        <v>11.81160700007474</v>
+        <v>11.81160605481299</v>
       </c>
       <c r="E191" t="n">
-        <v>12.2989793658374</v>
+        <v>12.29897838157211</v>
       </c>
       <c r="F191" t="n">
         <v>5991300</v>
@@ -4252,16 +4252,16 @@
         <v>44532</v>
       </c>
       <c r="B192" t="n">
-        <v>11.89761447906494</v>
+        <v>11.89761352539062</v>
       </c>
       <c r="C192" t="n">
-        <v>12.14607893971519</v>
+        <v>12.14607796612476</v>
       </c>
       <c r="D192" t="n">
-        <v>11.71604485711986</v>
+        <v>11.71604391799958</v>
       </c>
       <c r="E192" t="n">
-        <v>12.14607893971519</v>
+        <v>12.14607796612476</v>
       </c>
       <c r="F192" t="n">
         <v>7306700</v>
@@ -4292,16 +4292,16 @@
         <v>44536</v>
       </c>
       <c r="B194" t="n">
-        <v>13.13993453979492</v>
+        <v>13.13993549346924</v>
       </c>
       <c r="C194" t="n">
-        <v>13.28327891568452</v>
+        <v>13.28327987976253</v>
       </c>
       <c r="D194" t="n">
-        <v>12.77679442133178</v>
+        <v>12.77679534865</v>
       </c>
       <c r="E194" t="n">
-        <v>12.83413271850441</v>
+        <v>12.83413364998414</v>
       </c>
       <c r="F194" t="n">
         <v>6605800</v>
@@ -4312,16 +4312,16 @@
         <v>44537</v>
       </c>
       <c r="B195" t="n">
-        <v>13.42662334442139</v>
+        <v>13.4266242980957</v>
       </c>
       <c r="C195" t="n">
-        <v>13.76109383723112</v>
+        <v>13.76109481466241</v>
       </c>
       <c r="D195" t="n">
-        <v>13.40751027613218</v>
+        <v>13.40751122844893</v>
       </c>
       <c r="E195" t="n">
-        <v>13.56996771114538</v>
+        <v>13.56996867500125</v>
       </c>
       <c r="F195" t="n">
         <v>14090400</v>
@@ -4352,16 +4352,16 @@
         <v>44539</v>
       </c>
       <c r="B197" t="n">
-        <v>13.58908271789551</v>
+        <v>13.58908176422119</v>
       </c>
       <c r="C197" t="n">
-        <v>13.74198364057517</v>
+        <v>13.74198267617036</v>
       </c>
       <c r="D197" t="n">
-        <v>13.43618179521584</v>
+        <v>13.43618085227203</v>
       </c>
       <c r="E197" t="n">
-        <v>13.74198364057517</v>
+        <v>13.74198267617036</v>
       </c>
       <c r="F197" t="n">
         <v>9843600</v>
@@ -4372,16 +4372,16 @@
         <v>44540</v>
       </c>
       <c r="B198" t="n">
-        <v>13.91399669647217</v>
+        <v>13.91399574279785</v>
       </c>
       <c r="C198" t="n">
-        <v>14.19112982799074</v>
+        <v>14.19112885532154</v>
       </c>
       <c r="D198" t="n">
-        <v>13.74198271437053</v>
+        <v>13.74198177248616</v>
       </c>
       <c r="E198" t="n">
-        <v>13.74198271437053</v>
+        <v>13.74198177248616</v>
       </c>
       <c r="F198" t="n">
         <v>8247400</v>
@@ -4392,16 +4392,16 @@
         <v>44543</v>
       </c>
       <c r="B199" t="n">
-        <v>13.74198436737061</v>
+        <v>13.74198341369629</v>
       </c>
       <c r="C199" t="n">
-        <v>14.12423669428659</v>
+        <v>14.12423571408451</v>
       </c>
       <c r="D199" t="n">
-        <v>13.66553390198741</v>
+        <v>13.66553295361865</v>
       </c>
       <c r="E199" t="n">
-        <v>13.96177922750694</v>
+        <v>13.96177825857917</v>
       </c>
       <c r="F199" t="n">
         <v>11783000</v>
@@ -4492,16 +4492,16 @@
         <v>44550</v>
       </c>
       <c r="B204" t="n">
-        <v>13.47440719604492</v>
+        <v>13.47440624237061</v>
       </c>
       <c r="C204" t="n">
-        <v>13.8662160431998</v>
+        <v>13.86621506179454</v>
       </c>
       <c r="D204" t="n">
-        <v>13.29283666454885</v>
+        <v>13.29283572372549</v>
       </c>
       <c r="E204" t="n">
-        <v>13.81843427641866</v>
+        <v>13.81843329839523</v>
       </c>
       <c r="F204" t="n">
         <v>6680500</v>
@@ -4512,16 +4512,16 @@
         <v>44551</v>
       </c>
       <c r="B205" t="n">
-        <v>13.61774921417236</v>
+        <v>13.61775016784668</v>
       </c>
       <c r="C205" t="n">
-        <v>13.66553097263469</v>
+        <v>13.66553192965524</v>
       </c>
       <c r="D205" t="n">
-        <v>13.36928479925726</v>
+        <v>13.36928573553119</v>
       </c>
       <c r="E205" t="n">
-        <v>13.4839604727501</v>
+        <v>13.48396141705496</v>
       </c>
       <c r="F205" t="n">
         <v>4083800</v>
@@ -4552,16 +4552,16 @@
         <v>44553</v>
       </c>
       <c r="B207" t="n">
-        <v>13.4648494720459</v>
+        <v>13.46484851837158</v>
       </c>
       <c r="C207" t="n">
-        <v>13.65597561094082</v>
+        <v>13.65597464372962</v>
       </c>
       <c r="D207" t="n">
-        <v>13.32150418435372</v>
+        <v>13.32150324083211</v>
       </c>
       <c r="E207" t="n">
-        <v>13.41706770948184</v>
+        <v>13.41706675919176</v>
       </c>
       <c r="F207" t="n">
         <v>4198000</v>
@@ -4572,16 +4572,16 @@
         <v>44557</v>
       </c>
       <c r="B208" t="n">
-        <v>13.03481578826904</v>
+        <v>13.03481483459473</v>
       </c>
       <c r="C208" t="n">
-        <v>13.56041245676783</v>
+        <v>13.56041146463896</v>
       </c>
       <c r="D208" t="n">
-        <v>12.90102703170205</v>
+        <v>12.9010260878162</v>
       </c>
       <c r="E208" t="n">
-        <v>13.46484984038684</v>
+        <v>13.46484885524968</v>
       </c>
       <c r="F208" t="n">
         <v>14666400</v>
@@ -4652,16 +4652,16 @@
         <v>44564</v>
       </c>
       <c r="B212" t="n">
-        <v>12.1556339263916</v>
+        <v>12.15563488006592</v>
       </c>
       <c r="C212" t="n">
-        <v>12.49966096635466</v>
+        <v>12.49966194701974</v>
       </c>
       <c r="D212" t="n">
-        <v>11.84983120172981</v>
+        <v>11.84983213141227</v>
       </c>
       <c r="E212" t="n">
-        <v>12.49966096635466</v>
+        <v>12.49966194701974</v>
       </c>
       <c r="F212" t="n">
         <v>16124600</v>
@@ -4672,16 +4672,16 @@
         <v>44565</v>
       </c>
       <c r="B213" t="n">
-        <v>12.1556339263916</v>
+        <v>12.15563488006592</v>
       </c>
       <c r="C213" t="n">
-        <v>12.25119653736736</v>
+        <v>12.25119749853907</v>
       </c>
       <c r="D213" t="n">
-        <v>11.89761296289834</v>
+        <v>11.89761389632953</v>
       </c>
       <c r="E213" t="n">
-        <v>12.20341568756013</v>
+        <v>12.20341664498318</v>
       </c>
       <c r="F213" t="n">
         <v>9389900</v>
@@ -4692,16 +4692,16 @@
         <v>44566</v>
       </c>
       <c r="B214" t="n">
-        <v>11.45802307128906</v>
+        <v>11.45802211761475</v>
       </c>
       <c r="C214" t="n">
-        <v>12.13652156778615</v>
+        <v>12.13652055763904</v>
       </c>
       <c r="D214" t="n">
-        <v>11.41024130732365</v>
+        <v>11.41024035762631</v>
       </c>
       <c r="E214" t="n">
-        <v>12.1174094090168</v>
+        <v>12.11740840046043</v>
       </c>
       <c r="F214" t="n">
         <v>11220000</v>
@@ -4732,16 +4732,16 @@
         <v>44568</v>
       </c>
       <c r="B216" t="n">
-        <v>10.85597515106201</v>
+        <v>10.85597610473633</v>
       </c>
       <c r="C216" t="n">
-        <v>11.11399613247418</v>
+        <v>11.11399710881509</v>
       </c>
       <c r="D216" t="n">
-        <v>10.71263076896282</v>
+        <v>10.71263171004464</v>
       </c>
       <c r="E216" t="n">
-        <v>11.0088769796922</v>
+        <v>11.00887794679861</v>
       </c>
       <c r="F216" t="n">
         <v>11641900</v>
@@ -4772,16 +4772,16 @@
         <v>44572</v>
       </c>
       <c r="B218" t="n">
-        <v>10.94198131561279</v>
+        <v>10.94198226928711</v>
       </c>
       <c r="C218" t="n">
-        <v>10.96109438450356</v>
+        <v>10.96109533984372</v>
       </c>
       <c r="D218" t="n">
-        <v>10.66484819622561</v>
+        <v>10.66484912574574</v>
       </c>
       <c r="E218" t="n">
-        <v>10.70307342264587</v>
+        <v>10.7030743554976</v>
       </c>
       <c r="F218" t="n">
         <v>6045500</v>
@@ -4792,16 +4792,16 @@
         <v>44573</v>
       </c>
       <c r="B219" t="n">
-        <v>11.27645301818848</v>
+        <v>11.27645206451416</v>
       </c>
       <c r="C219" t="n">
-        <v>11.28600955287783</v>
+        <v>11.2860085983953</v>
       </c>
       <c r="D219" t="n">
-        <v>10.80819375474579</v>
+        <v>10.80819284067318</v>
       </c>
       <c r="E219" t="n">
-        <v>10.94198159495152</v>
+        <v>10.94198066956419</v>
       </c>
       <c r="F219" t="n">
         <v>7862000</v>
@@ -4812,16 +4812,16 @@
         <v>44574</v>
       </c>
       <c r="B220" t="n">
-        <v>11.48669242858887</v>
+        <v>11.48669147491455</v>
       </c>
       <c r="C220" t="n">
-        <v>11.57269850823688</v>
+        <v>11.57269754742197</v>
       </c>
       <c r="D220" t="n">
-        <v>11.15222099941061</v>
+        <v>11.15222007350554</v>
       </c>
       <c r="E220" t="n">
-        <v>11.27645321849507</v>
+        <v>11.27645228227571</v>
       </c>
       <c r="F220" t="n">
         <v>9668300</v>
@@ -4852,16 +4852,16 @@
         <v>44578</v>
       </c>
       <c r="B222" t="n">
-        <v>11.47713661193848</v>
+        <v>11.47713565826416</v>
       </c>
       <c r="C222" t="n">
-        <v>11.61092446289281</v>
+        <v>11.6109234981016</v>
       </c>
       <c r="D222" t="n">
-        <v>11.41024177509993</v>
+        <v>11.41024082698413</v>
       </c>
       <c r="E222" t="n">
-        <v>11.59181230333992</v>
+        <v>11.59181134013681</v>
       </c>
       <c r="F222" t="n">
         <v>4569300</v>
@@ -4892,16 +4892,16 @@
         <v>44580</v>
       </c>
       <c r="B224" t="n">
-        <v>11.49624824523926</v>
+        <v>11.49624919891357</v>
       </c>
       <c r="C224" t="n">
-        <v>11.69693092384569</v>
+        <v>11.69693189416769</v>
       </c>
       <c r="D224" t="n">
-        <v>11.41979778780455</v>
+        <v>11.4197987351369</v>
       </c>
       <c r="E224" t="n">
-        <v>11.41979778780455</v>
+        <v>11.4197987351369</v>
       </c>
       <c r="F224" t="n">
         <v>5074700</v>
@@ -4912,16 +4912,16 @@
         <v>44581</v>
       </c>
       <c r="B225" t="n">
-        <v>11.41979885101318</v>
+        <v>11.41979789733887</v>
       </c>
       <c r="C225" t="n">
-        <v>11.69693201285603</v>
+        <v>11.69693103603816</v>
       </c>
       <c r="D225" t="n">
-        <v>11.36246145827959</v>
+        <v>11.36246050939355</v>
       </c>
       <c r="E225" t="n">
-        <v>11.56314415557002</v>
+        <v>11.56314318992485</v>
       </c>
       <c r="F225" t="n">
         <v>7365800</v>
@@ -4932,16 +4932,16 @@
         <v>44582</v>
       </c>
       <c r="B226" t="n">
-        <v>11.48669242858887</v>
+        <v>11.48669147491455</v>
       </c>
       <c r="C226" t="n">
-        <v>11.63003680603022</v>
+        <v>11.63003584045484</v>
       </c>
       <c r="D226" t="n">
-        <v>11.21911492070173</v>
+        <v>11.21911398924284</v>
       </c>
       <c r="E226" t="n">
-        <v>11.37201583300219</v>
+        <v>11.37201488884882</v>
       </c>
       <c r="F226" t="n">
         <v>8537100</v>
@@ -4952,16 +4952,16 @@
         <v>44585</v>
       </c>
       <c r="B227" t="n">
-        <v>11.50580596923828</v>
+        <v>11.50580501556396</v>
       </c>
       <c r="C227" t="n">
-        <v>11.63959473925506</v>
+        <v>11.63959377449148</v>
       </c>
       <c r="D227" t="n">
-        <v>11.32423634190827</v>
+        <v>11.3242354032836</v>
       </c>
       <c r="E227" t="n">
-        <v>11.46758073657084</v>
+        <v>11.46757978606487</v>
       </c>
       <c r="F227" t="n">
         <v>6551900</v>
@@ -4972,16 +4972,16 @@
         <v>44586</v>
       </c>
       <c r="B228" t="n">
-        <v>11.75426864624023</v>
+        <v>11.75426959991455</v>
       </c>
       <c r="C228" t="n">
-        <v>11.8880564845101</v>
+        <v>11.8880574490392</v>
       </c>
       <c r="D228" t="n">
-        <v>10.98020666346776</v>
+        <v>10.98020755433911</v>
       </c>
       <c r="E228" t="n">
-        <v>11.42935376239404</v>
+        <v>11.42935468970662</v>
       </c>
       <c r="F228" t="n">
         <v>40426700</v>
@@ -4992,16 +4992,16 @@
         <v>44587</v>
       </c>
       <c r="B229" t="n">
-        <v>11.73515701293945</v>
+        <v>11.73515605926514</v>
       </c>
       <c r="C229" t="n">
-        <v>12.21297286261863</v>
+        <v>12.21297187011393</v>
       </c>
       <c r="D229" t="n">
-        <v>11.73515701293945</v>
+        <v>11.73515605926514</v>
       </c>
       <c r="E229" t="n">
-        <v>11.81160747597921</v>
+        <v>11.81160651609204</v>
       </c>
       <c r="F229" t="n">
         <v>11052300</v>
@@ -5032,16 +5032,16 @@
         <v>44589</v>
       </c>
       <c r="B231" t="n">
-        <v>11.83071899414062</v>
+        <v>11.83071994781494</v>
       </c>
       <c r="C231" t="n">
-        <v>12.04095819557792</v>
+        <v>12.04095916619962</v>
       </c>
       <c r="D231" t="n">
-        <v>11.45802235223286</v>
+        <v>11.4580232758641</v>
       </c>
       <c r="E231" t="n">
-        <v>11.94539467364426</v>
+        <v>11.94539563656258</v>
       </c>
       <c r="F231" t="n">
         <v>14924100</v>
@@ -5072,16 +5072,16 @@
         <v>44593</v>
       </c>
       <c r="B233" t="n">
-        <v>12.0218448638916</v>
+        <v>12.02184581756592</v>
       </c>
       <c r="C233" t="n">
-        <v>12.09829531522309</v>
+        <v>12.0982962749621</v>
       </c>
       <c r="D233" t="n">
-        <v>11.83071873556289</v>
+        <v>11.83071967407547</v>
       </c>
       <c r="E233" t="n">
-        <v>11.93583787830337</v>
+        <v>11.93583882515488</v>
       </c>
       <c r="F233" t="n">
         <v>5991900</v>
@@ -5132,16 +5132,16 @@
         <v>44596</v>
       </c>
       <c r="B236" t="n">
-        <v>12.32764911651611</v>
+        <v>12.32764720916748</v>
       </c>
       <c r="C236" t="n">
-        <v>12.32764911651611</v>
+        <v>12.32764720916748</v>
       </c>
       <c r="D236" t="n">
-        <v>11.56314445143097</v>
+        <v>11.56314266236741</v>
       </c>
       <c r="E236" t="n">
-        <v>11.91672808687321</v>
+        <v>11.91672624310277</v>
       </c>
       <c r="F236" t="n">
         <v>17676100</v>
@@ -5152,16 +5152,16 @@
         <v>44599</v>
       </c>
       <c r="B237" t="n">
-        <v>12.2034158706665</v>
+        <v>12.20341682434082</v>
       </c>
       <c r="C237" t="n">
-        <v>12.60478030096504</v>
+        <v>12.60478128600524</v>
       </c>
       <c r="D237" t="n">
-        <v>12.2034158706665</v>
+        <v>12.20341682434082</v>
       </c>
       <c r="E237" t="n">
-        <v>12.29897848307614</v>
+        <v>12.29897944421849</v>
       </c>
       <c r="F237" t="n">
         <v>7212000</v>
@@ -5192,16 +5192,16 @@
         <v>44601</v>
       </c>
       <c r="B239" t="n">
-        <v>12.05051422119141</v>
+        <v>12.05051517486572</v>
       </c>
       <c r="C239" t="n">
-        <v>12.28942212264425</v>
+        <v>12.28942309522567</v>
       </c>
       <c r="D239" t="n">
-        <v>11.91672637964906</v>
+        <v>11.91672732273544</v>
       </c>
       <c r="E239" t="n">
-        <v>11.95495160742706</v>
+        <v>11.95495255353858</v>
       </c>
       <c r="F239" t="n">
         <v>9060800</v>
@@ -5292,16 +5292,16 @@
         <v>44608</v>
       </c>
       <c r="B244" t="n">
-        <v>12.47099208831787</v>
+        <v>12.47099304199219</v>
       </c>
       <c r="C244" t="n">
-        <v>12.6430051500549</v>
+        <v>12.6430061168833</v>
       </c>
       <c r="D244" t="n">
-        <v>11.56314228509255</v>
+        <v>11.56314316934232</v>
       </c>
       <c r="E244" t="n">
-        <v>11.65870489464395</v>
+        <v>11.65870578620152</v>
       </c>
       <c r="F244" t="n">
         <v>21489000</v>
@@ -5312,16 +5312,16 @@
         <v>44609</v>
       </c>
       <c r="B245" t="n">
-        <v>12.66211795806885</v>
+        <v>12.66211891174316</v>
       </c>
       <c r="C245" t="n">
-        <v>12.94880760354266</v>
+        <v>12.94880857880961</v>
       </c>
       <c r="D245" t="n">
-        <v>12.46143529737331</v>
+        <v>12.46143623593278</v>
       </c>
       <c r="E245" t="n">
-        <v>12.46143529737331</v>
+        <v>12.46143623593278</v>
       </c>
       <c r="F245" t="n">
         <v>10362100</v>
@@ -5352,16 +5352,16 @@
         <v>44613</v>
       </c>
       <c r="B247" t="n">
-        <v>11.90716934204102</v>
+        <v>11.90717029571533</v>
       </c>
       <c r="C247" t="n">
-        <v>12.27986598065907</v>
+        <v>12.27986696418357</v>
       </c>
       <c r="D247" t="n">
-        <v>11.72559974560327</v>
+        <v>11.72560068473523</v>
       </c>
       <c r="E247" t="n">
-        <v>12.13652069902384</v>
+        <v>12.13652167106747</v>
       </c>
       <c r="F247" t="n">
         <v>4718800</v>
@@ -5392,16 +5392,16 @@
         <v>44615</v>
       </c>
       <c r="B249" t="n">
-        <v>12.73856925964355</v>
+        <v>12.73857021331787</v>
       </c>
       <c r="C249" t="n">
-        <v>12.87235801283171</v>
+        <v>12.87235897652213</v>
       </c>
       <c r="D249" t="n">
-        <v>12.51877442729301</v>
+        <v>12.51877536451236</v>
       </c>
       <c r="E249" t="n">
-        <v>12.51877442729301</v>
+        <v>12.51877536451236</v>
       </c>
       <c r="F249" t="n">
         <v>5598100</v>
@@ -5432,16 +5432,16 @@
         <v>44617</v>
       </c>
       <c r="B251" t="n">
-        <v>12.86280155181885</v>
+        <v>12.86280059814453</v>
       </c>
       <c r="C251" t="n">
-        <v>13.13993468322886</v>
+        <v>13.13993370900733</v>
       </c>
       <c r="D251" t="n">
-        <v>12.72901279786317</v>
+        <v>12.72901185410822</v>
       </c>
       <c r="E251" t="n">
-        <v>12.83413285860025</v>
+        <v>12.83413190705149</v>
       </c>
       <c r="F251" t="n">
         <v>8089600</v>
@@ -5492,16 +5492,16 @@
         <v>44624</v>
       </c>
       <c r="B254" t="n">
-        <v>12.14607810974121</v>
+        <v>12.14607715606689</v>
       </c>
       <c r="C254" t="n">
-        <v>12.64300608572388</v>
+        <v>12.64300509303224</v>
       </c>
       <c r="D254" t="n">
-        <v>12.13652157467044</v>
+        <v>12.13652062174647</v>
       </c>
       <c r="E254" t="n">
-        <v>12.64300608572388</v>
+        <v>12.64300509303224</v>
       </c>
       <c r="F254" t="n">
         <v>6563400</v>
@@ -5512,16 +5512,16 @@
         <v>44627</v>
       </c>
       <c r="B255" t="n">
-        <v>11.73515701293945</v>
+        <v>11.73515605926514</v>
       </c>
       <c r="C255" t="n">
-        <v>12.17474763109875</v>
+        <v>12.17474664170048</v>
       </c>
       <c r="D255" t="n">
-        <v>11.68737524569925</v>
+        <v>11.68737429590799</v>
       </c>
       <c r="E255" t="n">
-        <v>12.08874063233868</v>
+        <v>12.08873964992988</v>
       </c>
       <c r="F255" t="n">
         <v>12255900</v>
@@ -5532,16 +5532,16 @@
         <v>44628</v>
       </c>
       <c r="B256" t="n">
-        <v>11.75426864624023</v>
+        <v>11.75426959991455</v>
       </c>
       <c r="C256" t="n">
-        <v>11.99317654184934</v>
+        <v>11.99317751490728</v>
       </c>
       <c r="D256" t="n">
-        <v>11.52491728518221</v>
+        <v>11.52491822024826</v>
       </c>
       <c r="E256" t="n">
-        <v>11.74471211168916</v>
+        <v>11.74471306458811</v>
       </c>
       <c r="F256" t="n">
         <v>10151100</v>
@@ -5592,16 +5592,16 @@
         <v>44631</v>
       </c>
       <c r="B259" t="n">
-        <v>12.40409851074219</v>
+        <v>12.40409755706787</v>
       </c>
       <c r="C259" t="n">
-        <v>12.9296961060736</v>
+        <v>12.92969511198934</v>
       </c>
       <c r="D259" t="n">
-        <v>12.20341673702652</v>
+        <v>12.20341579878139</v>
       </c>
       <c r="E259" t="n">
-        <v>12.9296961060736</v>
+        <v>12.92969511198934</v>
       </c>
       <c r="F259" t="n">
         <v>7293900</v>
@@ -5652,16 +5652,16 @@
         <v>44636</v>
       </c>
       <c r="B262" t="n">
-        <v>12.99658966064453</v>
+        <v>12.99659156799316</v>
       </c>
       <c r="C262" t="n">
-        <v>13.09215227041673</v>
+        <v>13.09215419178991</v>
       </c>
       <c r="D262" t="n">
-        <v>12.7385687004009</v>
+        <v>12.73857056988299</v>
       </c>
       <c r="E262" t="n">
-        <v>12.91058267389665</v>
+        <v>12.91058456862311</v>
       </c>
       <c r="F262" t="n">
         <v>7731200</v>
@@ -5692,16 +5692,16 @@
         <v>44638</v>
       </c>
       <c r="B264" t="n">
-        <v>13.58908271789551</v>
+        <v>13.58908176422119</v>
       </c>
       <c r="C264" t="n">
-        <v>13.78020887124509</v>
+        <v>13.78020790415765</v>
       </c>
       <c r="D264" t="n">
-        <v>12.98703465132328</v>
+        <v>12.98703373990036</v>
       </c>
       <c r="E264" t="n">
-        <v>13.04437204164746</v>
+        <v>13.04437112620064</v>
       </c>
       <c r="F264" t="n">
         <v>10366600</v>
@@ -5712,16 +5712,16 @@
         <v>44641</v>
       </c>
       <c r="B265" t="n">
-        <v>13.56041145324707</v>
+        <v>13.56041240692139</v>
       </c>
       <c r="C265" t="n">
-        <v>13.62730628226077</v>
+        <v>13.62730724063966</v>
       </c>
       <c r="D265" t="n">
-        <v>13.1877157276278</v>
+        <v>13.18771665509124</v>
       </c>
       <c r="E265" t="n">
-        <v>13.58908105626492</v>
+        <v>13.58908201195551</v>
       </c>
       <c r="F265" t="n">
         <v>3916100</v>
@@ -5732,16 +5732,16 @@
         <v>44642</v>
       </c>
       <c r="B266" t="n">
-        <v>14.08601093292236</v>
+        <v>14.08600997924805</v>
       </c>
       <c r="C266" t="n">
-        <v>14.26758146491387</v>
+        <v>14.26758049894657</v>
       </c>
       <c r="D266" t="n">
-        <v>13.62730815783909</v>
+        <v>13.62730723522063</v>
       </c>
       <c r="E266" t="n">
-        <v>13.66553338909603</v>
+        <v>13.66553246388958</v>
       </c>
       <c r="F266" t="n">
         <v>13737200</v>
@@ -5772,16 +5772,16 @@
         <v>44644</v>
       </c>
       <c r="B268" t="n">
-        <v>14.63072204589844</v>
+        <v>14.6307201385498</v>
       </c>
       <c r="C268" t="n">
-        <v>14.74539774302677</v>
+        <v>14.74539582072832</v>
       </c>
       <c r="D268" t="n">
-        <v>14.35358888333129</v>
+        <v>14.35358701211139</v>
       </c>
       <c r="E268" t="n">
-        <v>14.3918141157074</v>
+        <v>14.39181223950423</v>
       </c>
       <c r="F268" t="n">
         <v>7986800</v>
@@ -5812,16 +5812,16 @@
         <v>44648</v>
       </c>
       <c r="B270" t="n">
-        <v>15.51945781707764</v>
+        <v>15.51945686340332</v>
       </c>
       <c r="C270" t="n">
-        <v>15.77747880069286</v>
+        <v>15.7774778311631</v>
       </c>
       <c r="D270" t="n">
-        <v>14.9747480668162</v>
+        <v>14.97474714661442</v>
       </c>
       <c r="E270" t="n">
-        <v>15.19454290942648</v>
+        <v>15.19454197571826</v>
       </c>
       <c r="F270" t="n">
         <v>14496800</v>
@@ -5872,16 +5872,16 @@
         <v>44651</v>
       </c>
       <c r="B273" t="n">
-        <v>15.56724071502686</v>
+        <v>15.56724166870117</v>
       </c>
       <c r="C273" t="n">
-        <v>15.81570334420647</v>
+        <v>15.81570431310201</v>
       </c>
       <c r="D273" t="n">
-        <v>15.42389450693963</v>
+        <v>15.42389545183233</v>
       </c>
       <c r="E273" t="n">
-        <v>15.42389450693963</v>
+        <v>15.42389545183233</v>
       </c>
       <c r="F273" t="n">
         <v>17319900</v>
@@ -5892,16 +5892,16 @@
         <v>44652</v>
       </c>
       <c r="B274" t="n">
-        <v>15.74881076812744</v>
+        <v>15.74880981445312</v>
       </c>
       <c r="C274" t="n">
-        <v>15.97816216889944</v>
+        <v>15.97816120133668</v>
       </c>
       <c r="D274" t="n">
-        <v>15.47167850904903</v>
+        <v>15.47167757215655</v>
       </c>
       <c r="E274" t="n">
-        <v>15.72014298223276</v>
+        <v>15.72014203029443</v>
       </c>
       <c r="F274" t="n">
         <v>8302400</v>
@@ -5912,16 +5912,16 @@
         <v>44655</v>
       </c>
       <c r="B275" t="n">
-        <v>15.56724071502686</v>
+        <v>15.56724166870117</v>
       </c>
       <c r="C275" t="n">
-        <v>15.86348602114313</v>
+        <v>15.86348699296592</v>
       </c>
       <c r="D275" t="n">
-        <v>15.52901457347753</v>
+        <v>15.52901552481005</v>
       </c>
       <c r="E275" t="n">
-        <v>15.75836595460524</v>
+        <v>15.75836691998819</v>
       </c>
       <c r="F275" t="n">
         <v>2672100</v>
@@ -5952,16 +5952,16 @@
         <v>44657</v>
       </c>
       <c r="B277" t="n">
-        <v>15.56724071502686</v>
+        <v>15.56724166870117</v>
       </c>
       <c r="C277" t="n">
-        <v>15.701028565004</v>
+        <v>15.70102952687437</v>
       </c>
       <c r="D277" t="n">
-        <v>15.13720573621069</v>
+        <v>15.13720666354036</v>
       </c>
       <c r="E277" t="n">
-        <v>15.38567018811306</v>
+        <v>15.38567113066407</v>
       </c>
       <c r="F277" t="n">
         <v>10924400</v>
@@ -5992,16 +5992,16 @@
         <v>44659</v>
       </c>
       <c r="B279" t="n">
-        <v>15.40478324890137</v>
+        <v>15.40478229522705</v>
       </c>
       <c r="C279" t="n">
-        <v>15.57679541759357</v>
+        <v>15.57679445327038</v>
       </c>
       <c r="D279" t="n">
-        <v>15.07031180145259</v>
+        <v>15.07031086848462</v>
       </c>
       <c r="E279" t="n">
-        <v>15.32833278857503</v>
+        <v>15.32833183963358</v>
       </c>
       <c r="F279" t="n">
         <v>3069100</v>
@@ -6032,16 +6032,16 @@
         <v>44663</v>
       </c>
       <c r="B281" t="n">
-        <v>15.72014045715332</v>
+        <v>15.72014427185059</v>
       </c>
       <c r="C281" t="n">
-        <v>15.82525869308717</v>
+        <v>15.82526253329275</v>
       </c>
       <c r="D281" t="n">
-        <v>15.3952255692357</v>
+        <v>15.39522930508813</v>
       </c>
       <c r="E281" t="n">
-        <v>15.48123255855052</v>
+        <v>15.48123631527367</v>
       </c>
       <c r="F281" t="n">
         <v>9798400</v>
@@ -6052,16 +6052,16 @@
         <v>44664</v>
       </c>
       <c r="B282" t="n">
-        <v>15.76792144775391</v>
+        <v>15.76791954040527</v>
       </c>
       <c r="C282" t="n">
-        <v>16.02594241798877</v>
+        <v>16.02594047942892</v>
       </c>
       <c r="D282" t="n">
-        <v>15.69147099243128</v>
+        <v>15.69146909433039</v>
       </c>
       <c r="E282" t="n">
-        <v>15.78703451726522</v>
+        <v>15.7870326076046</v>
       </c>
       <c r="F282" t="n">
         <v>7212700</v>
@@ -6072,16 +6072,16 @@
         <v>44665</v>
       </c>
       <c r="B283" t="n">
-        <v>15.64369010925293</v>
+        <v>15.64368915557861</v>
       </c>
       <c r="C283" t="n">
-        <v>15.79659101958422</v>
+        <v>15.79659005658872</v>
       </c>
       <c r="D283" t="n">
-        <v>15.4812326641856</v>
+        <v>15.48123172041506</v>
       </c>
       <c r="E283" t="n">
-        <v>15.72014056441858</v>
+        <v>15.72013960608367</v>
       </c>
       <c r="F283" t="n">
         <v>4607000</v>
@@ -6112,16 +6112,16 @@
         <v>44670</v>
       </c>
       <c r="B285" t="n">
-        <v>15.61502075195312</v>
+        <v>15.61502170562744</v>
       </c>
       <c r="C285" t="n">
-        <v>15.77747819958926</v>
+        <v>15.77747916318553</v>
       </c>
       <c r="D285" t="n">
-        <v>15.18498670700624</v>
+        <v>15.18498763441659</v>
       </c>
       <c r="E285" t="n">
-        <v>15.32833199622942</v>
+        <v>15.32833293239446</v>
       </c>
       <c r="F285" t="n">
         <v>7756800</v>
@@ -6172,16 +6172,16 @@
         <v>44676</v>
       </c>
       <c r="B288" t="n">
-        <v>15.29966163635254</v>
+        <v>15.29966259002686</v>
       </c>
       <c r="C288" t="n">
-        <v>15.46211907596952</v>
+        <v>15.4621200397703</v>
       </c>
       <c r="D288" t="n">
-        <v>15.01297198341896</v>
+        <v>15.01297291922304</v>
       </c>
       <c r="E288" t="n">
-        <v>15.2805485675217</v>
+        <v>15.28054952000464</v>
       </c>
       <c r="F288" t="n">
         <v>6454900</v>
@@ -6192,16 +6192,16 @@
         <v>44677</v>
       </c>
       <c r="B289" t="n">
-        <v>15.12764835357666</v>
+        <v>15.12764930725098</v>
       </c>
       <c r="C289" t="n">
-        <v>15.30921887032133</v>
+        <v>15.30921983544218</v>
       </c>
       <c r="D289" t="n">
-        <v>15.02252920428749</v>
+        <v>15.02253015133491</v>
       </c>
       <c r="E289" t="n">
-        <v>15.21365534452294</v>
+        <v>15.2136563036193</v>
       </c>
       <c r="F289" t="n">
         <v>9387600</v>
@@ -6212,16 +6212,16 @@
         <v>44678</v>
       </c>
       <c r="B290" t="n">
-        <v>15.18498611450195</v>
+        <v>15.18498706817627</v>
       </c>
       <c r="C290" t="n">
-        <v>15.48123230491487</v>
+        <v>15.48123327719457</v>
       </c>
       <c r="D290" t="n">
-        <v>14.9651903774805</v>
+        <v>14.96519131735082</v>
       </c>
       <c r="E290" t="n">
-        <v>15.2901052600749</v>
+        <v>15.2901062203511</v>
       </c>
       <c r="F290" t="n">
         <v>7959000</v>
@@ -6232,16 +6232,16 @@
         <v>44679</v>
       </c>
       <c r="B291" t="n">
-        <v>14.84095859527588</v>
+        <v>14.84095764160156</v>
       </c>
       <c r="C291" t="n">
-        <v>15.38566923076207</v>
+        <v>15.38566824208486</v>
       </c>
       <c r="D291" t="n">
-        <v>14.84095859527588</v>
+        <v>14.84095764160156</v>
       </c>
       <c r="E291" t="n">
-        <v>15.32833184472857</v>
+        <v>15.32833085973584</v>
       </c>
       <c r="F291" t="n">
         <v>5384600</v>
@@ -6252,16 +6252,16 @@
         <v>44680</v>
       </c>
       <c r="B292" t="n">
-        <v>14.72057151794434</v>
+        <v>14.72057247161865</v>
       </c>
       <c r="C292" t="n">
-        <v>15.13482874017579</v>
+        <v>15.13482972068782</v>
       </c>
       <c r="D292" t="n">
-        <v>14.72057151794434</v>
+        <v>14.72057247161865</v>
       </c>
       <c r="E292" t="n">
-        <v>15.06739185981573</v>
+        <v>15.06739283595885</v>
       </c>
       <c r="F292" t="n">
         <v>7651000</v>
@@ -6272,16 +6272,16 @@
         <v>44683</v>
       </c>
       <c r="B293" t="n">
-        <v>14.69167041778564</v>
+        <v>14.69167137145996</v>
       </c>
       <c r="C293" t="n">
-        <v>14.97105296602926</v>
+        <v>14.97105393783902</v>
       </c>
       <c r="D293" t="n">
-        <v>14.44118925901314</v>
+        <v>14.44119019642807</v>
       </c>
       <c r="E293" t="n">
-        <v>14.54716255167152</v>
+        <v>14.54716349596546</v>
       </c>
       <c r="F293" t="n">
         <v>5536000</v>
@@ -6292,16 +6292,16 @@
         <v>44684</v>
       </c>
       <c r="B294" t="n">
-        <v>14.62423419952393</v>
+        <v>14.62423324584961</v>
       </c>
       <c r="C294" t="n">
-        <v>14.85544716329886</v>
+        <v>14.85544619454671</v>
       </c>
       <c r="D294" t="n">
-        <v>14.4797254080956</v>
+        <v>14.47972446384498</v>
       </c>
       <c r="E294" t="n">
-        <v>14.70130518744891</v>
+        <v>14.70130422874864</v>
       </c>
       <c r="F294" t="n">
         <v>5388000</v>
@@ -6312,16 +6312,16 @@
         <v>44685</v>
       </c>
       <c r="B295" t="n">
-        <v>14.79764270782471</v>
+        <v>14.79764366149902</v>
       </c>
       <c r="C295" t="n">
-        <v>14.95178559456712</v>
+        <v>14.95178655817559</v>
       </c>
       <c r="D295" t="n">
-        <v>14.25814581988137</v>
+        <v>14.25814673878635</v>
       </c>
       <c r="E295" t="n">
-        <v>14.43155507448386</v>
+        <v>14.43155600456466</v>
       </c>
       <c r="F295" t="n">
         <v>5127000</v>
@@ -6372,16 +6372,16 @@
         <v>44690</v>
       </c>
       <c r="B298" t="n">
-        <v>14.21961116790771</v>
+        <v>14.21961212158203</v>
       </c>
       <c r="C298" t="n">
-        <v>14.32558354746724</v>
+        <v>14.32558450824887</v>
       </c>
       <c r="D298" t="n">
-        <v>13.92096039822737</v>
+        <v>13.92096133187191</v>
       </c>
       <c r="E298" t="n">
-        <v>14.04620098430244</v>
+        <v>14.04620192634656</v>
       </c>
       <c r="F298" t="n">
         <v>11844800</v>
@@ -6392,16 +6392,16 @@
         <v>44691</v>
       </c>
       <c r="B299" t="n">
-        <v>14.71093940734863</v>
+        <v>14.71093845367432</v>
       </c>
       <c r="C299" t="n">
-        <v>14.97105376396958</v>
+        <v>14.97105279343268</v>
       </c>
       <c r="D299" t="n">
-        <v>14.14254017782313</v>
+        <v>14.14253926099675</v>
       </c>
       <c r="E299" t="n">
-        <v>14.21961116635961</v>
+        <v>14.2196102445369</v>
       </c>
       <c r="F299" t="n">
         <v>13119700</v>
@@ -6412,16 +6412,16 @@
         <v>44692</v>
       </c>
       <c r="B300" t="n">
-        <v>14.60496520996094</v>
+        <v>14.60496711730957</v>
       </c>
       <c r="C300" t="n">
-        <v>14.78800948553586</v>
+        <v>14.78801141678933</v>
       </c>
       <c r="D300" t="n">
-        <v>14.40265364781732</v>
+        <v>14.40265552874489</v>
       </c>
       <c r="E300" t="n">
-        <v>14.45082324237696</v>
+        <v>14.45082512959528</v>
       </c>
       <c r="F300" t="n">
         <v>6181500</v>
@@ -6432,16 +6432,16 @@
         <v>44693</v>
       </c>
       <c r="B301" t="n">
-        <v>14.68203735351562</v>
+        <v>14.68203639984131</v>
       </c>
       <c r="C301" t="n">
-        <v>15.07702640634017</v>
+        <v>15.07702542700927</v>
       </c>
       <c r="D301" t="n">
-        <v>14.42192299236037</v>
+        <v>14.42192205558183</v>
       </c>
       <c r="E301" t="n">
-        <v>14.42192299236037</v>
+        <v>14.42192205558183</v>
       </c>
       <c r="F301" t="n">
         <v>8258700</v>
@@ -6512,16 +6512,16 @@
         <v>44699</v>
       </c>
       <c r="B305" t="n">
-        <v>14.83617877960205</v>
+        <v>14.83617782592773</v>
       </c>
       <c r="C305" t="n">
-        <v>15.2504360238162</v>
+        <v>15.2504350435133</v>
       </c>
       <c r="D305" t="n">
-        <v>14.81691149223043</v>
+        <v>14.81691053979462</v>
       </c>
       <c r="E305" t="n">
-        <v>15.23116873644458</v>
+        <v>15.23116775738018</v>
       </c>
       <c r="F305" t="n">
         <v>6842800</v>
@@ -6572,16 +6572,16 @@
         <v>44704</v>
       </c>
       <c r="B308" t="n">
-        <v>15.28897190093994</v>
+        <v>15.28897094726562</v>
       </c>
       <c r="C308" t="n">
-        <v>15.63579135115902</v>
+        <v>15.63579037585128</v>
       </c>
       <c r="D308" t="n">
-        <v>15.17336541753358</v>
+        <v>15.17336447107041</v>
       </c>
       <c r="E308" t="n">
-        <v>15.52981988981818</v>
+        <v>15.52981892112058</v>
       </c>
       <c r="F308" t="n">
         <v>8474400</v>
@@ -6592,16 +6592,16 @@
         <v>44705</v>
       </c>
       <c r="B309" t="n">
-        <v>15.31787300109863</v>
+        <v>15.31787204742432</v>
       </c>
       <c r="C309" t="n">
-        <v>15.34677531047014</v>
+        <v>15.3467743549964</v>
       </c>
       <c r="D309" t="n">
-        <v>14.99995494808117</v>
+        <v>14.99995401420009</v>
       </c>
       <c r="E309" t="n">
-        <v>15.19263333552333</v>
+        <v>15.1926323896463</v>
       </c>
       <c r="F309" t="n">
         <v>5652100</v>
@@ -6712,16 +6712,16 @@
         <v>44713</v>
       </c>
       <c r="B315" t="n">
-        <v>14.85544681549072</v>
+        <v>14.85544776916504</v>
       </c>
       <c r="C315" t="n">
-        <v>15.53945158762076</v>
+        <v>15.5394525852061</v>
       </c>
       <c r="D315" t="n">
-        <v>14.73020623335521</v>
+        <v>14.73020717898946</v>
       </c>
       <c r="E315" t="n">
-        <v>15.39494371833443</v>
+        <v>15.3949447066428</v>
       </c>
       <c r="F315" t="n">
         <v>6096700</v>
@@ -6772,16 +6772,16 @@
         <v>44718</v>
       </c>
       <c r="B318" t="n">
-        <v>14.9036169052124</v>
+        <v>14.90361595153809</v>
       </c>
       <c r="C318" t="n">
-        <v>15.1348298712333</v>
+        <v>15.13482890276379</v>
       </c>
       <c r="D318" t="n">
-        <v>14.84581320432785</v>
+        <v>14.84581225435236</v>
       </c>
       <c r="E318" t="n">
-        <v>15.01922338822285</v>
+        <v>15.01922242715094</v>
       </c>
       <c r="F318" t="n">
         <v>2626600</v>
@@ -6812,16 +6812,16 @@
         <v>44720</v>
       </c>
       <c r="B320" t="n">
-        <v>15.35640811920166</v>
+        <v>15.35640907287598</v>
       </c>
       <c r="C320" t="n">
-        <v>15.74176396590114</v>
+        <v>15.74176494350709</v>
       </c>
       <c r="D320" t="n">
-        <v>14.99032139703716</v>
+        <v>14.9903223279765</v>
       </c>
       <c r="E320" t="n">
-        <v>15.00958868405489</v>
+        <v>15.00958961619079</v>
       </c>
       <c r="F320" t="n">
         <v>10420600</v>
@@ -6952,16 +6952,16 @@
         <v>44732</v>
       </c>
       <c r="B327" t="n">
-        <v>15.31787300109863</v>
+        <v>15.31787204742432</v>
       </c>
       <c r="C327" t="n">
-        <v>15.50091728541696</v>
+        <v>15.5009163203465</v>
       </c>
       <c r="D327" t="n">
-        <v>14.83617887001052</v>
+        <v>14.83617794632596</v>
       </c>
       <c r="E327" t="n">
-        <v>15.09629414180225</v>
+        <v>15.09629320192319</v>
       </c>
       <c r="F327" t="n">
         <v>7611300</v>
@@ -7012,16 +7012,16 @@
         <v>44735</v>
       </c>
       <c r="B330" t="n">
-        <v>14.72057151794434</v>
+        <v>14.72057247161865</v>
       </c>
       <c r="C330" t="n">
-        <v>14.90361579143392</v>
+        <v>14.90361675696679</v>
       </c>
       <c r="D330" t="n">
-        <v>14.39301938118073</v>
+        <v>14.39302031363454</v>
       </c>
       <c r="E330" t="n">
-        <v>14.39301938118073</v>
+        <v>14.39302031363454</v>
       </c>
       <c r="F330" t="n">
         <v>3851900</v>
@@ -7032,16 +7032,16 @@
         <v>44736</v>
       </c>
       <c r="B331" t="n">
-        <v>14.42192268371582</v>
+        <v>14.4219217300415</v>
       </c>
       <c r="C331" t="n">
-        <v>14.86508132542095</v>
+        <v>14.86508034244202</v>
       </c>
       <c r="D331" t="n">
-        <v>14.25814660403618</v>
+        <v>14.25814566119184</v>
       </c>
       <c r="E331" t="n">
-        <v>14.86508132542095</v>
+        <v>14.86508034244202</v>
       </c>
       <c r="F331" t="n">
         <v>5803600</v>
@@ -7052,16 +7052,16 @@
         <v>44739</v>
       </c>
       <c r="B332" t="n">
-        <v>14.1618070602417</v>
+        <v>14.16180801391602</v>
       </c>
       <c r="C332" t="n">
-        <v>14.4989933145069</v>
+        <v>14.49899429088777</v>
       </c>
       <c r="D332" t="n">
-        <v>14.10400427987309</v>
+        <v>14.10400522965489</v>
       </c>
       <c r="E332" t="n">
-        <v>14.47972510854494</v>
+        <v>14.47972608362827</v>
       </c>
       <c r="F332" t="n">
         <v>8041800</v>
@@ -7072,16 +7072,16 @@
         <v>44740</v>
       </c>
       <c r="B333" t="n">
-        <v>14.08473587036133</v>
+        <v>14.08473491668701</v>
       </c>
       <c r="C333" t="n">
-        <v>14.48935900212858</v>
+        <v>14.48935802105732</v>
       </c>
       <c r="D333" t="n">
-        <v>13.9691293925362</v>
+        <v>13.96912844668957</v>
       </c>
       <c r="E333" t="n">
-        <v>14.23887784079483</v>
+        <v>14.2388768766836</v>
       </c>
       <c r="F333" t="n">
         <v>7081400</v>
@@ -7092,16 +7092,16 @@
         <v>44741</v>
       </c>
       <c r="B334" t="n">
-        <v>13.85352420806885</v>
+        <v>13.85352325439453</v>
       </c>
       <c r="C334" t="n">
-        <v>14.18107638519945</v>
+        <v>14.1810754089765</v>
       </c>
       <c r="D334" t="n">
-        <v>13.59340891960912</v>
+        <v>13.5934079838411</v>
       </c>
       <c r="E334" t="n">
-        <v>14.18107638519945</v>
+        <v>14.1810754089765</v>
       </c>
       <c r="F334" t="n">
         <v>8408900</v>
@@ -7112,16 +7112,16 @@
         <v>44742</v>
       </c>
       <c r="B335" t="n">
-        <v>13.74755001068115</v>
+        <v>13.74755096435547</v>
       </c>
       <c r="C335" t="n">
-        <v>13.88242377024082</v>
+        <v>13.88242473327139</v>
       </c>
       <c r="D335" t="n">
-        <v>13.34292689448499</v>
+        <v>13.34292782009041</v>
       </c>
       <c r="E335" t="n">
-        <v>13.58377394370849</v>
+        <v>13.58377488602158</v>
       </c>
       <c r="F335" t="n">
         <v>10650900</v>
@@ -7132,16 +7132,16 @@
         <v>44743</v>
       </c>
       <c r="B336" t="n">
-        <v>14.06546878814697</v>
+        <v>14.06546974182129</v>
       </c>
       <c r="C336" t="n">
-        <v>14.28704764418037</v>
+        <v>14.28704861287829</v>
       </c>
       <c r="D336" t="n">
-        <v>13.54523917098311</v>
+        <v>13.54524008938454</v>
       </c>
       <c r="E336" t="n">
-        <v>13.64157744452686</v>
+        <v>13.64157836946027</v>
       </c>
       <c r="F336" t="n">
         <v>10271400</v>
@@ -7172,16 +7172,16 @@
         <v>44747</v>
       </c>
       <c r="B338" t="n">
-        <v>14.17144107818604</v>
+        <v>14.17144012451172</v>
       </c>
       <c r="C338" t="n">
-        <v>14.19070836527375</v>
+        <v>14.19070741030283</v>
       </c>
       <c r="D338" t="n">
-        <v>13.46816718369137</v>
+        <v>13.46816627734423</v>
       </c>
       <c r="E338" t="n">
-        <v>13.67047875128478</v>
+        <v>13.67047783132298</v>
       </c>
       <c r="F338" t="n">
         <v>7354200</v>
@@ -7192,16 +7192,16 @@
         <v>44748</v>
       </c>
       <c r="B339" t="n">
-        <v>14.35448455810547</v>
+        <v>14.35448551177979</v>
       </c>
       <c r="C339" t="n">
-        <v>14.63386711386697</v>
+        <v>14.63386808610274</v>
       </c>
       <c r="D339" t="n">
-        <v>13.9209600293388</v>
+        <v>13.92096095421089</v>
       </c>
       <c r="E339" t="n">
-        <v>13.96912962559257</v>
+        <v>13.96913055366492</v>
       </c>
       <c r="F339" t="n">
         <v>11107300</v>
@@ -7232,16 +7232,16 @@
         <v>44750</v>
       </c>
       <c r="B341" t="n">
-        <v>14.72057151794434</v>
+        <v>14.72057247161865</v>
       </c>
       <c r="C341" t="n">
-        <v>14.82654480851997</v>
+        <v>14.82654576905978</v>
       </c>
       <c r="D341" t="n">
-        <v>14.41228758628851</v>
+        <v>14.41228851999061</v>
       </c>
       <c r="E341" t="n">
-        <v>14.73983972305212</v>
+        <v>14.73984067797473</v>
       </c>
       <c r="F341" t="n">
         <v>3792400</v>
@@ -7272,16 +7272,16 @@
         <v>44754</v>
       </c>
       <c r="B343" t="n">
-        <v>14.68203735351562</v>
+        <v>14.68203639984131</v>
       </c>
       <c r="C343" t="n">
-        <v>14.97105402494487</v>
+        <v>14.97105305249743</v>
       </c>
       <c r="D343" t="n">
-        <v>14.59533226021098</v>
+        <v>14.59533131216861</v>
       </c>
       <c r="E343" t="n">
-        <v>14.79764383833559</v>
+        <v>14.79764287715203</v>
       </c>
       <c r="F343" t="n">
         <v>4929100</v>
@@ -7312,16 +7312,16 @@
         <v>44756</v>
       </c>
       <c r="B345" t="n">
-        <v>14.75910758972168</v>
+        <v>14.759108543396</v>
       </c>
       <c r="C345" t="n">
-        <v>14.99995465048742</v>
+        <v>14.99995561972431</v>
       </c>
       <c r="D345" t="n">
-        <v>14.51826052895594</v>
+        <v>14.51826146706769</v>
       </c>
       <c r="E345" t="n">
-        <v>14.52789463188864</v>
+        <v>14.5278955706229</v>
       </c>
       <c r="F345" t="n">
         <v>8175300</v>
@@ -7352,16 +7352,16 @@
         <v>44760</v>
       </c>
       <c r="B347" t="n">
-        <v>14.87471389770508</v>
+        <v>14.87471294403076</v>
       </c>
       <c r="C347" t="n">
-        <v>15.19263285952041</v>
+        <v>15.19263188546311</v>
       </c>
       <c r="D347" t="n">
-        <v>14.80727701546838</v>
+        <v>14.8072760661177</v>
       </c>
       <c r="E347" t="n">
-        <v>15.07702546317377</v>
+        <v>15.0770244965285</v>
       </c>
       <c r="F347" t="n">
         <v>3805700</v>
@@ -7372,16 +7372,16 @@
         <v>44761</v>
       </c>
       <c r="B348" t="n">
-        <v>14.92288398742676</v>
+        <v>14.92288494110107</v>
       </c>
       <c r="C348" t="n">
-        <v>15.10592827207404</v>
+        <v>15.10592923744614</v>
       </c>
       <c r="D348" t="n">
-        <v>14.72057241525581</v>
+        <v>14.72057335600104</v>
       </c>
       <c r="E348" t="n">
-        <v>14.91324988428561</v>
+        <v>14.91325083734424</v>
       </c>
       <c r="F348" t="n">
         <v>3342100</v>
@@ -7432,16 +7432,16 @@
         <v>44764</v>
       </c>
       <c r="B351" t="n">
-        <v>15.07702445983887</v>
+        <v>15.07702541351318</v>
       </c>
       <c r="C351" t="n">
-        <v>15.14446225634637</v>
+        <v>15.14446321428636</v>
       </c>
       <c r="D351" t="n">
-        <v>14.78800874448132</v>
+        <v>14.78800967987438</v>
       </c>
       <c r="E351" t="n">
-        <v>14.84581152004941</v>
+        <v>14.8458124590987</v>
       </c>
       <c r="F351" t="n">
         <v>3071000</v>
@@ -7452,16 +7452,16 @@
         <v>44767</v>
       </c>
       <c r="B352" t="n">
-        <v>14.93251800537109</v>
+        <v>14.93251705169678</v>
       </c>
       <c r="C352" t="n">
-        <v>15.43348034074898</v>
+        <v>15.4334793550804</v>
       </c>
       <c r="D352" t="n">
-        <v>14.91324979919873</v>
+        <v>14.91324884675499</v>
       </c>
       <c r="E352" t="n">
-        <v>15.21190056355995</v>
+        <v>15.2118995920427</v>
       </c>
       <c r="F352" t="n">
         <v>6226600</v>
@@ -7472,16 +7472,16 @@
         <v>44768</v>
       </c>
       <c r="B353" t="n">
-        <v>14.95178604125977</v>
+        <v>14.95178699493408</v>
       </c>
       <c r="C353" t="n">
-        <v>15.03849021177204</v>
+        <v>15.03849117097664</v>
       </c>
       <c r="D353" t="n">
-        <v>14.76874175974149</v>
+        <v>14.76874270174064</v>
       </c>
       <c r="E353" t="n">
-        <v>14.82654545884164</v>
+        <v>14.8265464045277</v>
       </c>
       <c r="F353" t="n">
         <v>3874000</v>
@@ -7492,16 +7492,16 @@
         <v>44769</v>
       </c>
       <c r="B354" t="n">
-        <v>15.76103115081787</v>
+        <v>15.76103019714355</v>
       </c>
       <c r="C354" t="n">
-        <v>15.9344413165386</v>
+        <v>15.93444035237151</v>
       </c>
       <c r="D354" t="n">
-        <v>15.03848909990104</v>
+        <v>15.03848818994657</v>
       </c>
       <c r="E354" t="n">
-        <v>15.04812320216521</v>
+        <v>15.04812229162779</v>
       </c>
       <c r="F354" t="n">
         <v>22102600</v>
@@ -7512,16 +7512,16 @@
         <v>44770</v>
       </c>
       <c r="B355" t="n">
-        <v>15.59725666046143</v>
+        <v>15.59725570678711</v>
       </c>
       <c r="C355" t="n">
-        <v>16.13675357904711</v>
+        <v>16.13675259238595</v>
       </c>
       <c r="D355" t="n">
-        <v>15.31787317917409</v>
+        <v>15.31787224258232</v>
       </c>
       <c r="E355" t="n">
-        <v>15.9151747171748</v>
+        <v>15.91517374406179</v>
       </c>
       <c r="F355" t="n">
         <v>25902000</v>
@@ -7552,16 +7552,16 @@
         <v>44774</v>
       </c>
       <c r="B357" t="n">
-        <v>15.05775928497314</v>
+        <v>15.05775833129883</v>
       </c>
       <c r="C357" t="n">
-        <v>15.40457874327312</v>
+        <v>15.4045777676332</v>
       </c>
       <c r="D357" t="n">
-        <v>14.85544770460849</v>
+        <v>14.85544676374746</v>
       </c>
       <c r="E357" t="n">
-        <v>14.96142008717714</v>
+        <v>14.96141913960441</v>
       </c>
       <c r="F357" t="n">
         <v>9649400</v>
@@ -7572,16 +7572,16 @@
         <v>44775</v>
       </c>
       <c r="B358" t="n">
-        <v>15.09629440307617</v>
+        <v>15.09629344940186</v>
       </c>
       <c r="C358" t="n">
-        <v>15.2119008862871</v>
+        <v>15.21189992530961</v>
       </c>
       <c r="D358" t="n">
-        <v>14.80727773566952</v>
+        <v>14.80727680025318</v>
       </c>
       <c r="E358" t="n">
-        <v>15.04812480538195</v>
+        <v>15.04812385475064</v>
       </c>
       <c r="F358" t="n">
         <v>7865200</v>
@@ -7592,16 +7592,16 @@
         <v>44776</v>
       </c>
       <c r="B359" t="n">
-        <v>15.95370960235596</v>
+        <v>15.95370864868164</v>
       </c>
       <c r="C359" t="n">
-        <v>16.00188011947041</v>
+        <v>16.00187916291658</v>
       </c>
       <c r="D359" t="n">
-        <v>15.06739321889945</v>
+        <v>15.06739231820699</v>
       </c>
       <c r="E359" t="n">
-        <v>15.12519600191945</v>
+        <v>15.12519509777168</v>
       </c>
       <c r="F359" t="n">
         <v>9465300</v>
@@ -7632,16 +7632,16 @@
         <v>44778</v>
       </c>
       <c r="B361" t="n">
-        <v>16.40650367736816</v>
+        <v>16.40650177001953</v>
       </c>
       <c r="C361" t="n">
-        <v>16.57027976453278</v>
+        <v>16.57027783814425</v>
       </c>
       <c r="D361" t="n">
-        <v>16.10785197649791</v>
+        <v>16.10785010386923</v>
       </c>
       <c r="E361" t="n">
-        <v>16.26199396000374</v>
+        <v>16.26199206945518</v>
       </c>
       <c r="F361" t="n">
         <v>6244900</v>
@@ -7672,16 +7672,16 @@
         <v>44782</v>
       </c>
       <c r="B363" t="n">
-        <v>16.61844825744629</v>
+        <v>16.61844635009766</v>
       </c>
       <c r="C363" t="n">
-        <v>16.87856354074092</v>
+        <v>16.87856160353808</v>
       </c>
       <c r="D363" t="n">
-        <v>16.51247495591499</v>
+        <v>16.51247306072922</v>
       </c>
       <c r="E363" t="n">
-        <v>16.65698467164581</v>
+        <v>16.65698275987423</v>
       </c>
       <c r="F363" t="n">
         <v>6314800</v>
@@ -7772,16 +7772,16 @@
         <v>44789</v>
       </c>
       <c r="B368" t="n">
-        <v>17.42769241333008</v>
+        <v>17.42769432067871</v>
       </c>
       <c r="C368" t="n">
-        <v>17.63000305016812</v>
+        <v>17.63000497965835</v>
       </c>
       <c r="D368" t="n">
-        <v>17.1964794694364</v>
+        <v>17.19648135148026</v>
       </c>
       <c r="E368" t="n">
-        <v>17.52403159933173</v>
+        <v>17.52403351722407</v>
       </c>
       <c r="F368" t="n">
         <v>4828900</v>
@@ -7792,16 +7792,16 @@
         <v>44790</v>
       </c>
       <c r="B369" t="n">
-        <v>17.27355003356934</v>
+        <v>17.27355194091797</v>
       </c>
       <c r="C369" t="n">
-        <v>17.52403117611753</v>
+        <v>17.52403311112434</v>
       </c>
       <c r="D369" t="n">
-        <v>17.16757674777512</v>
+        <v>17.16757864342216</v>
       </c>
       <c r="E369" t="n">
-        <v>17.31208460452908</v>
+        <v>17.31208651613271</v>
       </c>
       <c r="F369" t="n">
         <v>8548600</v>
@@ -7812,16 +7812,16 @@
         <v>44791</v>
       </c>
       <c r="B370" t="n">
-        <v>17.45659637451172</v>
+        <v>17.45659446716309</v>
       </c>
       <c r="C370" t="n">
-        <v>17.59147014518392</v>
+        <v>17.59146822309866</v>
       </c>
       <c r="D370" t="n">
-        <v>17.2928202940452</v>
+        <v>17.29281840459113</v>
       </c>
       <c r="E370" t="n">
-        <v>17.34098897285176</v>
+        <v>17.34098707813466</v>
       </c>
       <c r="F370" t="n">
         <v>13968800</v>
@@ -7832,16 +7832,16 @@
         <v>44792</v>
       </c>
       <c r="B371" t="n">
-        <v>17.12904357910156</v>
+        <v>17.12904167175293</v>
       </c>
       <c r="C371" t="n">
-        <v>17.57220128776223</v>
+        <v>17.57219933106722</v>
       </c>
       <c r="D371" t="n">
-        <v>17.07123896165407</v>
+        <v>17.07123706074208</v>
       </c>
       <c r="E371" t="n">
-        <v>17.45659572790173</v>
+        <v>17.4565937840796</v>
       </c>
       <c r="F371" t="n">
         <v>7571900</v>
@@ -7892,16 +7892,16 @@
         <v>44797</v>
       </c>
       <c r="B374" t="n">
-        <v>17.14831161499023</v>
+        <v>17.1483097076416</v>
       </c>
       <c r="C374" t="n">
-        <v>17.26391902361024</v>
+        <v>17.26391710340299</v>
       </c>
       <c r="D374" t="n">
-        <v>16.99416962850851</v>
+        <v>16.99416773830457</v>
       </c>
       <c r="E374" t="n">
-        <v>17.14831161499023</v>
+        <v>17.1483097076416</v>
       </c>
       <c r="F374" t="n">
         <v>5807100</v>
@@ -7912,16 +7912,16 @@
         <v>44798</v>
       </c>
       <c r="B375" t="n">
-        <v>17.29281806945801</v>
+        <v>17.29281616210938</v>
       </c>
       <c r="C375" t="n">
-        <v>17.32171853801719</v>
+        <v>17.32171662748092</v>
       </c>
       <c r="D375" t="n">
-        <v>16.98453231719579</v>
+        <v>16.9845304438502</v>
       </c>
       <c r="E375" t="n">
-        <v>17.19647888672088</v>
+        <v>17.19647698999819</v>
       </c>
       <c r="F375" t="n">
         <v>6074000</v>
@@ -7932,16 +7932,16 @@
         <v>44799</v>
       </c>
       <c r="B376" t="n">
-        <v>17.29281806945801</v>
+        <v>17.29281616210938</v>
       </c>
       <c r="C376" t="n">
-        <v>17.41805772075432</v>
+        <v>17.41805579959211</v>
       </c>
       <c r="D376" t="n">
-        <v>17.10977380600918</v>
+        <v>17.10977191884981</v>
       </c>
       <c r="E376" t="n">
-        <v>17.30245033396635</v>
+        <v>17.30244842555531</v>
       </c>
       <c r="F376" t="n">
         <v>3647900</v>
@@ -7972,16 +7972,16 @@
         <v>44803</v>
       </c>
       <c r="B378" t="n">
-        <v>17.63000297546387</v>
+        <v>17.6300048828125</v>
       </c>
       <c r="C378" t="n">
-        <v>17.95755510397125</v>
+        <v>17.95755704675698</v>
       </c>
       <c r="D378" t="n">
-        <v>17.55293199449255</v>
+        <v>17.55293389350305</v>
       </c>
       <c r="E378" t="n">
-        <v>17.6878075893302</v>
+        <v>17.68780950293258</v>
       </c>
       <c r="F378" t="n">
         <v>6440300</v>
@@ -8092,16 +8092,16 @@
         <v>44812</v>
       </c>
       <c r="B384" t="n">
-        <v>18.40071678161621</v>
+        <v>18.40071487426758</v>
       </c>
       <c r="C384" t="n">
-        <v>18.94984781515502</v>
+        <v>18.94984585088554</v>
       </c>
       <c r="D384" t="n">
-        <v>18.34291399848511</v>
+        <v>18.3429120971281</v>
       </c>
       <c r="E384" t="n">
-        <v>18.91131140138939</v>
+        <v>18.91130944111445</v>
       </c>
       <c r="F384" t="n">
         <v>6653400</v>
@@ -8112,16 +8112,16 @@
         <v>44813</v>
       </c>
       <c r="B385" t="n">
-        <v>18.15986824035645</v>
+        <v>18.15987014770508</v>
       </c>
       <c r="C385" t="n">
-        <v>18.62229414306423</v>
+        <v>18.6222960989819</v>
       </c>
       <c r="D385" t="n">
-        <v>18.08279725657182</v>
+        <v>18.08279915582561</v>
       </c>
       <c r="E385" t="n">
-        <v>18.47778627815769</v>
+        <v>18.47778821889757</v>
       </c>
       <c r="F385" t="n">
         <v>8752700</v>
@@ -8152,16 +8152,16 @@
         <v>44817</v>
       </c>
       <c r="B387" t="n">
-        <v>17.48549652099609</v>
+        <v>17.48549461364746</v>
       </c>
       <c r="C387" t="n">
-        <v>17.84195098508192</v>
+        <v>17.84194903885061</v>
       </c>
       <c r="D387" t="n">
-        <v>17.32172044358108</v>
+        <v>17.32171855409743</v>
       </c>
       <c r="E387" t="n">
-        <v>17.64927259841111</v>
+        <v>17.64927067319749</v>
       </c>
       <c r="F387" t="n">
         <v>10161300</v>
@@ -8212,16 +8212,16 @@
         <v>44820</v>
       </c>
       <c r="B390" t="n">
-        <v>17.2446460723877</v>
+        <v>17.24465179443359</v>
       </c>
       <c r="C390" t="n">
-        <v>17.62036866891358</v>
+        <v>17.62037451563017</v>
       </c>
       <c r="D390" t="n">
-        <v>17.0616018247221</v>
+        <v>17.06160748603103</v>
       </c>
       <c r="E390" t="n">
-        <v>17.49512719089932</v>
+        <v>17.4951329960588</v>
       </c>
       <c r="F390" t="n">
         <v>10140200</v>
@@ -8232,16 +8232,16 @@
         <v>44823</v>
       </c>
       <c r="B391" t="n">
-        <v>17.46622848510742</v>
+        <v>17.46623039245605</v>
       </c>
       <c r="C391" t="n">
-        <v>17.58183588574045</v>
+        <v>17.58183780571365</v>
       </c>
       <c r="D391" t="n">
-        <v>17.14831043026322</v>
+        <v>17.14831230289454</v>
       </c>
       <c r="E391" t="n">
-        <v>17.14831043026322</v>
+        <v>17.14831230289454</v>
       </c>
       <c r="F391" t="n">
         <v>7719100</v>
@@ -8252,16 +8252,16 @@
         <v>44824</v>
       </c>
       <c r="B392" t="n">
-        <v>17.60110092163086</v>
+        <v>17.60110282897949</v>
       </c>
       <c r="C392" t="n">
-        <v>17.83231384373147</v>
+        <v>17.83231577613557</v>
       </c>
       <c r="D392" t="n">
-        <v>17.43732487211997</v>
+        <v>17.43732676172096</v>
       </c>
       <c r="E392" t="n">
-        <v>17.55293041441179</v>
+        <v>17.55293231654042</v>
       </c>
       <c r="F392" t="n">
         <v>8039000</v>
@@ -8272,16 +8272,16 @@
         <v>44825</v>
       </c>
       <c r="B393" t="n">
-        <v>17.63000297546387</v>
+        <v>17.6300048828125</v>
       </c>
       <c r="C393" t="n">
-        <v>17.95755510397125</v>
+        <v>17.95755704675698</v>
       </c>
       <c r="D393" t="n">
-        <v>17.54329789218149</v>
+        <v>17.54329979014971</v>
       </c>
       <c r="E393" t="n">
-        <v>17.63000297546387</v>
+        <v>17.6300048828125</v>
       </c>
       <c r="F393" t="n">
         <v>11282800</v>
@@ -8332,16 +8332,16 @@
         <v>44830</v>
       </c>
       <c r="B396" t="n">
-        <v>17.09050559997559</v>
+        <v>17.09050750732422</v>
       </c>
       <c r="C396" t="n">
-        <v>17.20611298675014</v>
+        <v>17.20611490700088</v>
       </c>
       <c r="D396" t="n">
-        <v>16.71478480861316</v>
+        <v>16.7147866740303</v>
       </c>
       <c r="E396" t="n">
-        <v>16.89782907204076</v>
+        <v>16.89783095788615</v>
       </c>
       <c r="F396" t="n">
         <v>7980700</v>
@@ -8352,16 +8352,16 @@
         <v>44831</v>
       </c>
       <c r="B397" t="n">
-        <v>17.12904357910156</v>
+        <v>17.12904167175293</v>
       </c>
       <c r="C397" t="n">
-        <v>17.49513030201615</v>
+        <v>17.49512835390313</v>
       </c>
       <c r="D397" t="n">
-        <v>16.86892831313957</v>
+        <v>16.86892643475522</v>
       </c>
       <c r="E397" t="n">
-        <v>17.25428324186998</v>
+        <v>17.2542813205757</v>
       </c>
       <c r="F397" t="n">
         <v>9260100</v>
@@ -8372,16 +8372,16 @@
         <v>44832</v>
       </c>
       <c r="B398" t="n">
-        <v>17.29281806945801</v>
+        <v>17.29281616210938</v>
       </c>
       <c r="C398" t="n">
-        <v>17.36025494611888</v>
+        <v>17.36025303133215</v>
       </c>
       <c r="D398" t="n">
-        <v>16.97490005268744</v>
+        <v>16.97489818040426</v>
       </c>
       <c r="E398" t="n">
-        <v>17.13867611208543</v>
+        <v>17.13867422173822</v>
       </c>
       <c r="F398" t="n">
         <v>11092900</v>
@@ -8392,16 +8392,16 @@
         <v>44833</v>
       </c>
       <c r="B399" t="n">
-        <v>17.29281806945801</v>
+        <v>17.29281616210938</v>
       </c>
       <c r="C399" t="n">
-        <v>17.456594128856</v>
+        <v>17.45659220344334</v>
       </c>
       <c r="D399" t="n">
-        <v>16.9556318486366</v>
+        <v>16.95562997847865</v>
       </c>
       <c r="E399" t="n">
-        <v>17.1194079080346</v>
+        <v>17.11940601981261</v>
       </c>
       <c r="F399" t="n">
         <v>8404000</v>
@@ -8412,16 +8412,16 @@
         <v>44834</v>
       </c>
       <c r="B400" t="n">
-        <v>16.90746116638184</v>
+        <v>16.90746307373047</v>
       </c>
       <c r="C400" t="n">
-        <v>17.28318379147985</v>
+        <v>17.28318574121415</v>
       </c>
       <c r="D400" t="n">
-        <v>16.8592924942622</v>
+        <v>16.85929439617687</v>
       </c>
       <c r="E400" t="n">
-        <v>17.24464738377049</v>
+        <v>17.24464932915746</v>
       </c>
       <c r="F400" t="n">
         <v>11790900</v>
@@ -8432,16 +8432,16 @@
         <v>44837</v>
       </c>
       <c r="B401" t="n">
-        <v>17.75524520874023</v>
+        <v>17.75524711608887</v>
       </c>
       <c r="C401" t="n">
-        <v>17.81304798750098</v>
+        <v>17.81304990105905</v>
       </c>
       <c r="D401" t="n">
-        <v>16.96526716144702</v>
+        <v>16.96526898393264</v>
       </c>
       <c r="E401" t="n">
-        <v>17.24464879005494</v>
+        <v>17.244650642553</v>
       </c>
       <c r="F401" t="n">
         <v>18011200</v>
@@ -8452,16 +8452,16 @@
         <v>44838</v>
       </c>
       <c r="B402" t="n">
-        <v>17.41805839538574</v>
+        <v>17.41806030273438</v>
       </c>
       <c r="C402" t="n">
-        <v>18.07316265835103</v>
+        <v>18.07316463743626</v>
       </c>
       <c r="D402" t="n">
-        <v>17.3313533113158</v>
+        <v>17.33135520916987</v>
       </c>
       <c r="E402" t="n">
-        <v>17.98645757428108</v>
+        <v>17.98645954387175</v>
       </c>
       <c r="F402" t="n">
         <v>18594600</v>
@@ -8472,16 +8472,16 @@
         <v>44839</v>
       </c>
       <c r="B403" t="n">
-        <v>17.45659637451172</v>
+        <v>17.45659446716309</v>
       </c>
       <c r="C403" t="n">
-        <v>17.74561212238566</v>
+        <v>17.74561018345848</v>
       </c>
       <c r="D403" t="n">
-        <v>17.14831058259092</v>
+        <v>17.14830870892632</v>
       </c>
       <c r="E403" t="n">
-        <v>17.4276940647174</v>
+        <v>17.4276921605267</v>
       </c>
       <c r="F403" t="n">
         <v>8852300</v>
@@ -8492,16 +8492,16 @@
         <v>44840</v>
       </c>
       <c r="B404" t="n">
-        <v>17.44696044921875</v>
+        <v>17.44696235656738</v>
       </c>
       <c r="C404" t="n">
-        <v>17.6396369818406</v>
+        <v>17.63963891025314</v>
       </c>
       <c r="D404" t="n">
-        <v>17.30245075285597</v>
+        <v>17.30245264440641</v>
       </c>
       <c r="E404" t="n">
-        <v>17.63000287958194</v>
+        <v>17.63000480694126</v>
       </c>
       <c r="F404" t="n">
         <v>6691000</v>
@@ -8532,16 +8532,16 @@
         <v>44844</v>
       </c>
       <c r="B406" t="n">
-        <v>18.10206604003906</v>
+        <v>18.1020679473877</v>
       </c>
       <c r="C406" t="n">
-        <v>18.12133240846265</v>
+        <v>18.12133431784131</v>
       </c>
       <c r="D406" t="n">
-        <v>17.58183550473985</v>
+        <v>17.58183735727369</v>
       </c>
       <c r="E406" t="n">
-        <v>17.73597747723208</v>
+        <v>17.73597934600729</v>
       </c>
       <c r="F406" t="n">
         <v>7333800</v>
@@ -8552,16 +8552,16 @@
         <v>44845</v>
       </c>
       <c r="B407" t="n">
-        <v>18.32364463806152</v>
+        <v>18.32364654541016</v>
       </c>
       <c r="C407" t="n">
-        <v>18.59339216736995</v>
+        <v>18.5933941027972</v>
       </c>
       <c r="D407" t="n">
-        <v>17.85158462425454</v>
+        <v>17.8515864824654</v>
       </c>
       <c r="E407" t="n">
-        <v>18.15023446206769</v>
+        <v>18.15023635136567</v>
       </c>
       <c r="F407" t="n">
         <v>12287200</v>
@@ -8592,16 +8592,16 @@
         <v>44848</v>
       </c>
       <c r="B409" t="n">
-        <v>18.39108276367188</v>
+        <v>18.39108085632324</v>
       </c>
       <c r="C409" t="n">
-        <v>18.9402137997635</v>
+        <v>18.94021183546421</v>
       </c>
       <c r="D409" t="n">
-        <v>18.29474356632728</v>
+        <v>18.29474166897004</v>
       </c>
       <c r="E409" t="n">
-        <v>18.80534002599148</v>
+        <v>18.80533807568002</v>
       </c>
       <c r="F409" t="n">
         <v>11391600</v>
@@ -8612,16 +8612,16 @@
         <v>44851</v>
       </c>
       <c r="B410" t="n">
-        <v>19.01728248596191</v>
+        <v>19.01728439331055</v>
       </c>
       <c r="C410" t="n">
-        <v>19.06545299755645</v>
+        <v>19.06545490973637</v>
       </c>
       <c r="D410" t="n">
-        <v>18.3621782284133</v>
+        <v>18.3621800700579</v>
       </c>
       <c r="E410" t="n">
-        <v>18.49705382336087</v>
+        <v>18.49705567853288</v>
       </c>
       <c r="F410" t="n">
         <v>20683400</v>
@@ -8632,16 +8632,16 @@
         <v>44852</v>
       </c>
       <c r="B411" t="n">
-        <v>17.263916015625</v>
+        <v>17.26391792297363</v>
       </c>
       <c r="C411" t="n">
-        <v>19.16179004195282</v>
+        <v>19.16179215898201</v>
       </c>
       <c r="D411" t="n">
-        <v>17.263916015625</v>
+        <v>17.26391792297363</v>
       </c>
       <c r="E411" t="n">
-        <v>19.10398726647282</v>
+        <v>19.10398937711585</v>
       </c>
       <c r="F411" t="n">
         <v>33355700</v>
@@ -8652,16 +8652,16 @@
         <v>44853</v>
       </c>
       <c r="B412" t="n">
-        <v>17.67817687988281</v>
+        <v>17.67817306518555</v>
       </c>
       <c r="C412" t="n">
-        <v>17.97682675877506</v>
+        <v>17.97682287963343</v>
       </c>
       <c r="D412" t="n">
-        <v>17.28318779690735</v>
+        <v>17.28318406744306</v>
       </c>
       <c r="E412" t="n">
-        <v>17.4758643675563</v>
+        <v>17.47586059651518</v>
       </c>
       <c r="F412" t="n">
         <v>27062400</v>
@@ -8672,16 +8672,16 @@
         <v>44854</v>
       </c>
       <c r="B413" t="n">
-        <v>17.35062408447266</v>
+        <v>17.35062217712402</v>
       </c>
       <c r="C413" t="n">
-        <v>18.11169991144759</v>
+        <v>18.11169792043414</v>
       </c>
       <c r="D413" t="n">
-        <v>17.19648209831274</v>
+        <v>17.19648020790888</v>
       </c>
       <c r="E413" t="n">
-        <v>17.73597904987246</v>
+        <v>17.73597710016188</v>
       </c>
       <c r="F413" t="n">
         <v>15810900</v>
@@ -8712,16 +8712,16 @@
         <v>44858</v>
       </c>
       <c r="B415" t="n">
-        <v>18.00572776794434</v>
+        <v>18.0057258605957</v>
       </c>
       <c r="C415" t="n">
-        <v>18.36218040847837</v>
+        <v>18.36217846337067</v>
       </c>
       <c r="D415" t="n">
-        <v>17.54329998932035</v>
+        <v>17.54329813095674</v>
       </c>
       <c r="E415" t="n">
-        <v>17.91902267429717</v>
+        <v>17.91902077613322</v>
       </c>
       <c r="F415" t="n">
         <v>16227000</v>
@@ -8772,16 +8772,16 @@
         <v>44861</v>
       </c>
       <c r="B418" t="n">
-        <v>17.47586250305176</v>
+        <v>17.47586059570312</v>
       </c>
       <c r="C418" t="n">
-        <v>17.74561187820164</v>
+        <v>17.74560994141206</v>
       </c>
       <c r="D418" t="n">
-        <v>15.9922455335206</v>
+        <v>15.99224378809673</v>
       </c>
       <c r="E418" t="n">
-        <v>16.13675340546911</v>
+        <v>16.13675164427337</v>
       </c>
       <c r="F418" t="n">
         <v>30122400</v>
@@ -8812,16 +8812,16 @@
         <v>44865</v>
       </c>
       <c r="B420" t="n">
-        <v>19.09435653686523</v>
+        <v>19.0943546295166</v>
       </c>
       <c r="C420" t="n">
-        <v>19.24849852371545</v>
+        <v>19.24849660096946</v>
       </c>
       <c r="D420" t="n">
-        <v>18.13096820029268</v>
+        <v>18.13096638917758</v>
       </c>
       <c r="E420" t="n">
-        <v>18.29474429101071</v>
+        <v>18.2947424635359</v>
       </c>
       <c r="F420" t="n">
         <v>18379300</v>
@@ -8872,16 +8872,16 @@
         <v>44869</v>
       </c>
       <c r="B423" t="n">
-        <v>19.79762840270996</v>
+        <v>19.79762649536133</v>
       </c>
       <c r="C423" t="n">
-        <v>19.98067269026426</v>
+        <v>19.98067076528072</v>
       </c>
       <c r="D423" t="n">
-        <v>19.60495184937882</v>
+        <v>19.60494996059309</v>
       </c>
       <c r="E423" t="n">
-        <v>19.81689660929827</v>
+        <v>19.81689470009329</v>
       </c>
       <c r="F423" t="n">
         <v>15655600</v>
@@ -8932,16 +8932,16 @@
         <v>44874</v>
       </c>
       <c r="B426" t="n">
-        <v>19.65311813354492</v>
+        <v>19.65312194824219</v>
       </c>
       <c r="C426" t="n">
-        <v>20.09627764348921</v>
+        <v>20.09628154420435</v>
       </c>
       <c r="D426" t="n">
-        <v>19.13288948167312</v>
+        <v>19.13289319539329</v>
       </c>
       <c r="E426" t="n">
-        <v>19.13288948167312</v>
+        <v>19.13289319539329</v>
       </c>
       <c r="F426" t="n">
         <v>19633400</v>
@@ -8952,16 +8952,16 @@
         <v>44875</v>
       </c>
       <c r="B427" t="n">
-        <v>18.80533981323242</v>
+        <v>18.80533790588379</v>
       </c>
       <c r="C427" t="n">
-        <v>19.64348659435789</v>
+        <v>19.64348460199946</v>
       </c>
       <c r="D427" t="n">
-        <v>18.43925123496827</v>
+        <v>18.43924936475051</v>
       </c>
       <c r="E427" t="n">
-        <v>19.64348659435789</v>
+        <v>19.64348460199946</v>
       </c>
       <c r="F427" t="n">
         <v>13893700</v>
@@ -9032,16 +9032,16 @@
         <v>44882</v>
       </c>
       <c r="B431" t="n">
-        <v>18.78607177734375</v>
+        <v>18.78606986999512</v>
       </c>
       <c r="C431" t="n">
-        <v>18.90167918140427</v>
+        <v>18.90167726231802</v>
       </c>
       <c r="D431" t="n">
-        <v>18.0538964516734</v>
+        <v>18.05389461866248</v>
       </c>
       <c r="E431" t="n">
-        <v>18.66083210733576</v>
+        <v>18.6608302127027</v>
       </c>
       <c r="F431" t="n">
         <v>10826800</v>
@@ -9132,16 +9132,16 @@
         <v>44889</v>
       </c>
       <c r="B436" t="n">
-        <v>19.08472061157227</v>
+        <v>19.08471870422363</v>
       </c>
       <c r="C436" t="n">
-        <v>19.26776489255638</v>
+        <v>19.26776296691409</v>
       </c>
       <c r="D436" t="n">
-        <v>18.58376012087891</v>
+        <v>18.58375826359684</v>
       </c>
       <c r="E436" t="n">
-        <v>18.67046337237954</v>
+        <v>18.67046150643225</v>
       </c>
       <c r="F436" t="n">
         <v>7241600</v>
@@ -9192,16 +9192,16 @@
         <v>44894</v>
       </c>
       <c r="B439" t="n">
-        <v>18.68973159790039</v>
+        <v>18.68972969055176</v>
       </c>
       <c r="C439" t="n">
-        <v>18.98838143954377</v>
+        <v>18.98837950171693</v>
       </c>
       <c r="D439" t="n">
-        <v>18.29474256418963</v>
+        <v>18.29474069715092</v>
       </c>
       <c r="E439" t="n">
-        <v>18.53558962559947</v>
+        <v>18.53558773398153</v>
       </c>
       <c r="F439" t="n">
         <v>13403400</v>
@@ -9232,16 +9232,16 @@
         <v>44896</v>
       </c>
       <c r="B441" t="n">
-        <v>18.95948028564453</v>
+        <v>18.95948219299316</v>
       </c>
       <c r="C441" t="n">
-        <v>19.08471994456143</v>
+        <v>19.08472186450934</v>
       </c>
       <c r="D441" t="n">
-        <v>18.41998340201319</v>
+        <v>18.41998525508773</v>
       </c>
       <c r="E441" t="n">
-        <v>19.0750858419498</v>
+        <v>19.0750877609285</v>
       </c>
       <c r="F441" t="n">
         <v>25518700</v>
@@ -9252,16 +9252,16 @@
         <v>44897</v>
       </c>
       <c r="B442" t="n">
-        <v>19.78799438476562</v>
+        <v>19.78799247741699</v>
       </c>
       <c r="C442" t="n">
-        <v>19.97103681859475</v>
+        <v>19.97103489360281</v>
       </c>
       <c r="D442" t="n">
-        <v>19.01728272713333</v>
+        <v>19.01728089407297</v>
       </c>
       <c r="E442" t="n">
-        <v>19.11362191402701</v>
+        <v>19.11362007168059</v>
       </c>
       <c r="F442" t="n">
         <v>24428900</v>
@@ -9272,16 +9272,16 @@
         <v>44900</v>
       </c>
       <c r="B443" t="n">
-        <v>19.63385391235352</v>
+        <v>19.63385200500488</v>
       </c>
       <c r="C443" t="n">
-        <v>19.75909542780647</v>
+        <v>19.75909350829114</v>
       </c>
       <c r="D443" t="n">
-        <v>19.29666945732816</v>
+        <v>19.29666758273562</v>
       </c>
       <c r="E443" t="n">
-        <v>19.60495343764704</v>
+        <v>19.60495153310597</v>
       </c>
       <c r="F443" t="n">
         <v>17246700</v>
@@ -9372,16 +9372,16 @@
         <v>44907</v>
       </c>
       <c r="B448" t="n">
-        <v>18.25620651245117</v>
+        <v>18.2562084197998</v>
       </c>
       <c r="C448" t="n">
-        <v>18.67046188103712</v>
+        <v>18.6704638316658</v>
       </c>
       <c r="D448" t="n">
-        <v>17.87084977536743</v>
+        <v>17.87085164245525</v>
       </c>
       <c r="E448" t="n">
-        <v>18.45851714565475</v>
+        <v>18.45851907414013</v>
       </c>
       <c r="F448" t="n">
         <v>10851800</v>
@@ -9392,16 +9392,16 @@
         <v>44908</v>
       </c>
       <c r="B449" t="n">
-        <v>17.94792175292969</v>
+        <v>17.94792366027832</v>
       </c>
       <c r="C449" t="n">
-        <v>18.52595505316863</v>
+        <v>18.5259570219456</v>
       </c>
       <c r="D449" t="n">
-        <v>17.89975307687528</v>
+        <v>17.89975497910497</v>
       </c>
       <c r="E449" t="n">
-        <v>18.52595505316863</v>
+        <v>18.5259570219456</v>
       </c>
       <c r="F449" t="n">
         <v>13648600</v>
@@ -9452,16 +9452,16 @@
         <v>44911</v>
       </c>
       <c r="B452" t="n">
-        <v>18.02499580383301</v>
+        <v>18.02499389648438</v>
       </c>
       <c r="C452" t="n">
-        <v>18.69936840843323</v>
+        <v>18.69936642972459</v>
       </c>
       <c r="D452" t="n">
-        <v>17.55293571561986</v>
+        <v>17.55293385822315</v>
       </c>
       <c r="E452" t="n">
-        <v>18.38145031483998</v>
+        <v>18.38144836977245</v>
       </c>
       <c r="F452" t="n">
         <v>14090800</v>
@@ -9492,16 +9492,16 @@
         <v>44915</v>
       </c>
       <c r="B454" t="n">
-        <v>19.26776504516602</v>
+        <v>19.26776695251465</v>
       </c>
       <c r="C454" t="n">
-        <v>19.66275408159054</v>
+        <v>19.66275602803981</v>
       </c>
       <c r="D454" t="n">
-        <v>18.86314190571684</v>
+        <v>18.86314377301114</v>
       </c>
       <c r="E454" t="n">
-        <v>18.91131058332285</v>
+        <v>18.91131245538545</v>
       </c>
       <c r="F454" t="n">
         <v>10658900</v>
@@ -9552,16 +9552,16 @@
         <v>44918</v>
       </c>
       <c r="B457" t="n">
-        <v>19.28703308105469</v>
+        <v>19.28703117370605</v>
       </c>
       <c r="C457" t="n">
-        <v>20.03847473517549</v>
+        <v>20.03847275351469</v>
       </c>
       <c r="D457" t="n">
-        <v>19.06545422599431</v>
+        <v>19.06545234055823</v>
       </c>
       <c r="E457" t="n">
-        <v>19.47007552435644</v>
+        <v>19.47007359890622</v>
       </c>
       <c r="F457" t="n">
         <v>9067600</v>
@@ -9592,16 +9592,16 @@
         <v>44922</v>
       </c>
       <c r="B459" t="n">
-        <v>18.59339332580566</v>
+        <v>18.59339141845703</v>
       </c>
       <c r="C459" t="n">
-        <v>19.36410506296115</v>
+        <v>19.36410307655132</v>
       </c>
       <c r="D459" t="n">
-        <v>18.41998497652509</v>
+        <v>18.41998308696504</v>
       </c>
       <c r="E459" t="n">
-        <v>19.28703407299734</v>
+        <v>19.28703209449361</v>
       </c>
       <c r="F459" t="n">
         <v>8606100</v>
@@ -9612,16 +9612,16 @@
         <v>44923</v>
       </c>
       <c r="B460" t="n">
-        <v>18.71863555908203</v>
+        <v>18.7186336517334</v>
       </c>
       <c r="C460" t="n">
-        <v>18.94984853794273</v>
+        <v>18.94984660703449</v>
       </c>
       <c r="D460" t="n">
-        <v>18.26584186765209</v>
+        <v>18.26584000644119</v>
       </c>
       <c r="E460" t="n">
-        <v>18.68973324765541</v>
+        <v>18.6897313432518</v>
       </c>
       <c r="F460" t="n">
         <v>8329700</v>
@@ -9652,16 +9652,16 @@
         <v>44928</v>
       </c>
       <c r="B462" t="n">
-        <v>18.32970237731934</v>
+        <v>18.32970428466797</v>
       </c>
       <c r="C462" t="n">
-        <v>18.50344392873929</v>
+        <v>18.50344585416709</v>
       </c>
       <c r="D462" t="n">
-        <v>17.90500101174039</v>
+        <v>17.90500287489553</v>
       </c>
       <c r="E462" t="n">
-        <v>18.33935489029029</v>
+        <v>18.33935679864334</v>
       </c>
       <c r="F462" t="n">
         <v>4837200</v>
@@ -9772,16 +9772,16 @@
         <v>44936</v>
       </c>
       <c r="B468" t="n">
-        <v>18.57101249694824</v>
+        <v>18.57101058959961</v>
       </c>
       <c r="C468" t="n">
-        <v>18.68684082914984</v>
+        <v>18.68683890990498</v>
       </c>
       <c r="D468" t="n">
-        <v>18.14631106691423</v>
+        <v>18.14630920318485</v>
       </c>
       <c r="E468" t="n">
-        <v>18.29109694242345</v>
+        <v>18.29109506382374</v>
       </c>
       <c r="F468" t="n">
         <v>7152400</v>
@@ -9952,16 +9952,16 @@
         <v>44949</v>
       </c>
       <c r="B477" t="n">
-        <v>19.5651969909668</v>
+        <v>19.56519889831543</v>
       </c>
       <c r="C477" t="n">
-        <v>19.78719927266691</v>
+        <v>19.78720120165784</v>
       </c>
       <c r="D477" t="n">
-        <v>19.25632393103121</v>
+        <v>19.2563258082688</v>
       </c>
       <c r="E477" t="n">
-        <v>19.28527962975727</v>
+        <v>19.28528150981765</v>
       </c>
       <c r="F477" t="n">
         <v>3499900</v>
@@ -9992,16 +9992,16 @@
         <v>44951</v>
       </c>
       <c r="B479" t="n">
-        <v>20.37599182128906</v>
+        <v>20.37598991394043</v>
       </c>
       <c r="C479" t="n">
-        <v>20.61729915468745</v>
+        <v>20.6172972247506</v>
       </c>
       <c r="D479" t="n">
-        <v>20.12503197363128</v>
+        <v>20.12503008977441</v>
       </c>
       <c r="E479" t="n">
-        <v>20.57868909764986</v>
+        <v>20.57868717132721</v>
       </c>
       <c r="F479" t="n">
         <v>2807800</v>
@@ -10012,16 +10012,16 @@
         <v>44952</v>
       </c>
       <c r="B480" t="n">
-        <v>20.26981544494629</v>
+        <v>20.26981735229492</v>
       </c>
       <c r="C480" t="n">
-        <v>20.43390450076081</v>
+        <v>20.4339064235499</v>
       </c>
       <c r="D480" t="n">
-        <v>19.96094236130219</v>
+        <v>19.96094423958649</v>
       </c>
       <c r="E480" t="n">
-        <v>20.37599125783475</v>
+        <v>20.37599317517431</v>
       </c>
       <c r="F480" t="n">
         <v>7475700</v>
@@ -10132,16 +10132,16 @@
         <v>44960</v>
       </c>
       <c r="B486" t="n">
-        <v>18.45518493652344</v>
+        <v>18.4551830291748</v>
       </c>
       <c r="C486" t="n">
-        <v>18.82197125869143</v>
+        <v>18.82196931343532</v>
       </c>
       <c r="D486" t="n">
-        <v>18.35866163878593</v>
+        <v>18.35865974141301</v>
       </c>
       <c r="E486" t="n">
-        <v>18.69649226035282</v>
+        <v>18.696490328065</v>
       </c>
       <c r="F486" t="n">
         <v>6859200</v>
@@ -10172,16 +10172,16 @@
         <v>44964</v>
       </c>
       <c r="B488" t="n">
-        <v>18.19457244873047</v>
+        <v>18.19457054138184</v>
       </c>
       <c r="C488" t="n">
-        <v>18.68683960658058</v>
+        <v>18.68683764762727</v>
       </c>
       <c r="D488" t="n">
-        <v>17.77952356028652</v>
+        <v>17.77952169644773</v>
       </c>
       <c r="E488" t="n">
-        <v>18.12700669312867</v>
+        <v>18.12700479286299</v>
       </c>
       <c r="F488" t="n">
         <v>19883200</v>
@@ -10192,16 +10192,16 @@
         <v>44965</v>
       </c>
       <c r="B489" t="n">
-        <v>18.10770416259766</v>
+        <v>18.10770225524902</v>
       </c>
       <c r="C489" t="n">
-        <v>18.39727225254545</v>
+        <v>18.39727031469558</v>
       </c>
       <c r="D489" t="n">
-        <v>17.76987349697256</v>
+        <v>17.76987162520883</v>
       </c>
       <c r="E489" t="n">
-        <v>18.2910982681134</v>
+        <v>18.29109634144721</v>
       </c>
       <c r="F489" t="n">
         <v>14424900</v>
@@ -10212,16 +10212,16 @@
         <v>44966</v>
       </c>
       <c r="B490" t="n">
-        <v>17.87604713439941</v>
+        <v>17.87604522705078</v>
       </c>
       <c r="C490" t="n">
-        <v>18.04978870351367</v>
+        <v>18.04978677762706</v>
       </c>
       <c r="D490" t="n">
-        <v>17.69265305133117</v>
+        <v>17.69265116355042</v>
       </c>
       <c r="E490" t="n">
-        <v>17.91465534918659</v>
+        <v>17.91465343771851</v>
       </c>
       <c r="F490" t="n">
         <v>11653900</v>
@@ -10232,16 +10232,16 @@
         <v>44967</v>
       </c>
       <c r="B491" t="n">
-        <v>17.98221969604492</v>
+        <v>17.98222160339355</v>
       </c>
       <c r="C491" t="n">
-        <v>18.09804801338318</v>
+        <v>18.09804993301756</v>
       </c>
       <c r="D491" t="n">
-        <v>17.6250859128902</v>
+        <v>17.62508778235816</v>
       </c>
       <c r="E491" t="n">
-        <v>17.79882746838327</v>
+        <v>17.79882935627974</v>
       </c>
       <c r="F491" t="n">
         <v>6326900</v>
@@ -10272,16 +10272,16 @@
         <v>44971</v>
       </c>
       <c r="B493" t="n">
-        <v>17.80847930908203</v>
+        <v>17.80848121643066</v>
       </c>
       <c r="C493" t="n">
-        <v>18.11735235561527</v>
+        <v>18.11735429604525</v>
       </c>
       <c r="D493" t="n">
-        <v>17.71195602178325</v>
+        <v>17.71195791879391</v>
       </c>
       <c r="E493" t="n">
-        <v>18.02082906831649</v>
+        <v>18.0208309984085</v>
       </c>
       <c r="F493" t="n">
         <v>9612400</v>
@@ -10312,16 +10312,16 @@
         <v>44973</v>
       </c>
       <c r="B495" t="n">
-        <v>18.34900665283203</v>
+        <v>18.34900856018066</v>
       </c>
       <c r="C495" t="n">
-        <v>18.55170389384643</v>
+        <v>18.5517058222651</v>
       </c>
       <c r="D495" t="n">
-        <v>17.8856970953461</v>
+        <v>17.88569895453448</v>
       </c>
       <c r="E495" t="n">
-        <v>18.43587742498921</v>
+        <v>18.43587934136792</v>
       </c>
       <c r="F495" t="n">
         <v>33990600</v>
@@ -10332,16 +10332,16 @@
         <v>44974</v>
       </c>
       <c r="B496" t="n">
-        <v>18.45518493652344</v>
+        <v>18.4551830291748</v>
       </c>
       <c r="C496" t="n">
-        <v>18.62892466321642</v>
+        <v>18.62892273791173</v>
       </c>
       <c r="D496" t="n">
-        <v>18.01117850334242</v>
+        <v>18.01117664188198</v>
       </c>
       <c r="E496" t="n">
-        <v>18.24283331329517</v>
+        <v>18.24283142789314</v>
       </c>
       <c r="F496" t="n">
         <v>11362300</v>
@@ -10352,16 +10352,16 @@
         <v>44979</v>
       </c>
       <c r="B497" t="n">
-        <v>18.17526626586914</v>
+        <v>18.17526817321777</v>
       </c>
       <c r="C497" t="n">
-        <v>18.42622608574493</v>
+        <v>18.42622801942978</v>
       </c>
       <c r="D497" t="n">
-        <v>18.0304822500639</v>
+        <v>18.03048414221861</v>
       </c>
       <c r="E497" t="n">
-        <v>18.32970279486522</v>
+        <v>18.32970471842073</v>
       </c>
       <c r="F497" t="n">
         <v>5044700</v>
@@ -10392,16 +10392,16 @@
         <v>44981</v>
       </c>
       <c r="B499" t="n">
-        <v>18.04013633728027</v>
+        <v>18.04013442993164</v>
       </c>
       <c r="C499" t="n">
-        <v>18.16561533765205</v>
+        <v>18.16561341703677</v>
       </c>
       <c r="D499" t="n">
-        <v>17.82778471061123</v>
+        <v>17.82778282571412</v>
       </c>
       <c r="E499" t="n">
-        <v>18.10770209448268</v>
+        <v>18.10770017999045</v>
       </c>
       <c r="F499" t="n">
         <v>6522200</v>
@@ -10432,16 +10432,16 @@
         <v>44985</v>
       </c>
       <c r="B501" t="n">
-        <v>17.50925827026367</v>
+        <v>17.50925636291504</v>
       </c>
       <c r="C501" t="n">
-        <v>17.81813134036312</v>
+        <v>17.81812939936779</v>
       </c>
       <c r="D501" t="n">
-        <v>17.23899525444101</v>
+        <v>17.23899337653314</v>
       </c>
       <c r="E501" t="n">
-        <v>17.74091307283826</v>
+        <v>17.7409111402546</v>
       </c>
       <c r="F501" t="n">
         <v>18187200</v>
@@ -10532,16 +10532,16 @@
         <v>44992</v>
       </c>
       <c r="B506" t="n">
-        <v>17.13282012939453</v>
+        <v>17.13282203674316</v>
       </c>
       <c r="C506" t="n">
-        <v>17.22934342790674</v>
+        <v>17.22934534600104</v>
       </c>
       <c r="D506" t="n">
-        <v>16.85290274781201</v>
+        <v>16.85290462399823</v>
       </c>
       <c r="E506" t="n">
-        <v>17.06525437274463</v>
+        <v>17.06525627257135</v>
       </c>
       <c r="F506" t="n">
         <v>12726400</v>
@@ -10592,16 +10592,16 @@
         <v>44995</v>
       </c>
       <c r="B509" t="n">
-        <v>16.28341865539551</v>
+        <v>16.28341674804688</v>
       </c>
       <c r="C509" t="n">
-        <v>17.20038536068198</v>
+        <v>17.200383345925</v>
       </c>
       <c r="D509" t="n">
-        <v>16.10967709158599</v>
+        <v>16.10967520458848</v>
       </c>
       <c r="E509" t="n">
-        <v>17.11351457877723</v>
+        <v>17.1135125741958</v>
       </c>
       <c r="F509" t="n">
         <v>24597700</v>
@@ -10612,16 +10612,16 @@
         <v>44998</v>
       </c>
       <c r="B510" t="n">
-        <v>16.10967826843262</v>
+        <v>16.10967636108398</v>
       </c>
       <c r="C510" t="n">
-        <v>16.51507466659365</v>
+        <v>16.51507271124702</v>
       </c>
       <c r="D510" t="n">
-        <v>16.02280748018176</v>
+        <v>16.02280558311843</v>
       </c>
       <c r="E510" t="n">
-        <v>16.16759151359023</v>
+        <v>16.1675895993848</v>
       </c>
       <c r="F510" t="n">
         <v>7318300</v>
@@ -10772,16 +10772,16 @@
         <v>45008</v>
       </c>
       <c r="B518" t="n">
-        <v>14.71974563598633</v>
+        <v>14.71974658966064</v>
       </c>
       <c r="C518" t="n">
-        <v>15.01896709984251</v>
+        <v>15.01896807290302</v>
       </c>
       <c r="D518" t="n">
-        <v>14.25643605125789</v>
+        <v>14.25643697491495</v>
       </c>
       <c r="E518" t="n">
-        <v>14.74870225490328</v>
+        <v>14.74870321045366</v>
       </c>
       <c r="F518" t="n">
         <v>25394300</v>
@@ -10832,16 +10832,16 @@
         <v>45013</v>
       </c>
       <c r="B521" t="n">
-        <v>14.82592105865479</v>
+        <v>14.82592010498047</v>
       </c>
       <c r="C521" t="n">
-        <v>14.99001010601382</v>
+        <v>14.99000914178451</v>
       </c>
       <c r="D521" t="n">
-        <v>14.410873104024</v>
+        <v>14.41087217704756</v>
       </c>
       <c r="E521" t="n">
-        <v>14.57496215138304</v>
+        <v>14.5749612138516</v>
       </c>
       <c r="F521" t="n">
         <v>12984500</v>
@@ -10852,16 +10852,16 @@
         <v>45014</v>
       </c>
       <c r="B522" t="n">
-        <v>14.89348793029785</v>
+        <v>14.89348888397217</v>
       </c>
       <c r="C522" t="n">
-        <v>14.96105368463159</v>
+        <v>14.96105464263234</v>
       </c>
       <c r="D522" t="n">
-        <v>14.42052488841858</v>
+        <v>14.42052581180767</v>
       </c>
       <c r="E522" t="n">
-        <v>14.84522628269617</v>
+        <v>14.84522723328015</v>
       </c>
       <c r="F522" t="n">
         <v>19793200</v>
@@ -10892,16 +10892,16 @@
         <v>45016</v>
       </c>
       <c r="B524" t="n">
-        <v>14.99966239929199</v>
+        <v>14.99966144561768</v>
       </c>
       <c r="C524" t="n">
-        <v>15.60775693283936</v>
+        <v>15.60775594050256</v>
       </c>
       <c r="D524" t="n">
-        <v>14.90313910678695</v>
+        <v>14.90313815924955</v>
       </c>
       <c r="E524" t="n">
-        <v>15.53053866704106</v>
+        <v>15.53053767961378</v>
       </c>
       <c r="F524" t="n">
         <v>26076900</v>
@@ -10912,16 +10912,16 @@
         <v>45019</v>
       </c>
       <c r="B525" t="n">
-        <v>14.25643634796143</v>
+        <v>14.25643730163574</v>
       </c>
       <c r="C525" t="n">
-        <v>14.97070576620689</v>
+        <v>14.97070676766176</v>
       </c>
       <c r="D525" t="n">
-        <v>14.23713132127214</v>
+        <v>14.23713227365506</v>
       </c>
       <c r="E525" t="n">
-        <v>14.96105325286225</v>
+        <v>14.96105425367142</v>
       </c>
       <c r="F525" t="n">
         <v>17443100</v>
@@ -10972,16 +10972,16 @@
         <v>45022</v>
       </c>
       <c r="B528" t="n">
-        <v>13.1560754776001</v>
+        <v>13.15607452392578</v>
       </c>
       <c r="C528" t="n">
-        <v>13.57112437142145</v>
+        <v>13.57112338766055</v>
       </c>
       <c r="D528" t="n">
-        <v>13.00163893678686</v>
+        <v>13.00163799430754</v>
       </c>
       <c r="E528" t="n">
-        <v>13.33946863968721</v>
+        <v>13.33946767271886</v>
       </c>
       <c r="F528" t="n">
         <v>26117400</v>
@@ -11112,16 +11112,16 @@
         <v>45034</v>
       </c>
       <c r="B535" t="n">
-        <v>12.70241737365723</v>
+        <v>12.70241641998291</v>
       </c>
       <c r="C535" t="n">
-        <v>12.95337721125578</v>
+        <v>12.95337623873985</v>
       </c>
       <c r="D535" t="n">
-        <v>12.61554658983354</v>
+        <v>12.61554564268133</v>
       </c>
       <c r="E535" t="n">
-        <v>12.87615894130459</v>
+        <v>12.87615797458607</v>
       </c>
       <c r="F535" t="n">
         <v>12417000</v>
@@ -11132,16 +11132,16 @@
         <v>45035</v>
       </c>
       <c r="B536" t="n">
-        <v>12.44180583953857</v>
+        <v>12.44180488586426</v>
       </c>
       <c r="C536" t="n">
-        <v>12.69276475454189</v>
+        <v>12.69276378163138</v>
       </c>
       <c r="D536" t="n">
-        <v>12.27771678712426</v>
+        <v>12.2777158460275</v>
       </c>
       <c r="E536" t="n">
-        <v>12.58658986436797</v>
+        <v>12.58658889959584</v>
       </c>
       <c r="F536" t="n">
         <v>13110300</v>
@@ -11172,16 +11172,16 @@
         <v>45040</v>
       </c>
       <c r="B538" t="n">
-        <v>12.45145797729492</v>
+        <v>12.45145702362061</v>
       </c>
       <c r="C538" t="n">
-        <v>12.88581191180532</v>
+        <v>12.88581092486324</v>
       </c>
       <c r="D538" t="n">
-        <v>12.35493559669272</v>
+        <v>12.35493465041118</v>
       </c>
       <c r="E538" t="n">
-        <v>12.54798127841155</v>
+        <v>12.54798031734438</v>
       </c>
       <c r="F538" t="n">
         <v>8287100</v>
@@ -11192,16 +11192,16 @@
         <v>45041</v>
       </c>
       <c r="B539" t="n">
-        <v>12.04606056213379</v>
+        <v>12.04606151580811</v>
       </c>
       <c r="C539" t="n">
-        <v>12.48041445974649</v>
+        <v>12.48041544780816</v>
       </c>
       <c r="D539" t="n">
-        <v>11.79510165747509</v>
+        <v>11.79510259128125</v>
       </c>
       <c r="E539" t="n">
-        <v>12.46110943295733</v>
+        <v>12.46111041949064</v>
       </c>
       <c r="F539" t="n">
         <v>18435400</v>
@@ -11212,16 +11212,16 @@
         <v>45042</v>
       </c>
       <c r="B540" t="n">
-        <v>12.15223598480225</v>
+        <v>12.15223693847656</v>
       </c>
       <c r="C540" t="n">
-        <v>12.39354328896269</v>
+        <v>12.39354426157415</v>
       </c>
       <c r="D540" t="n">
-        <v>11.9495378124869</v>
+        <v>11.94953875025402</v>
       </c>
       <c r="E540" t="n">
-        <v>12.01710356308724</v>
+        <v>12.01710450615674</v>
       </c>
       <c r="F540" t="n">
         <v>19317300</v>
@@ -11232,16 +11232,16 @@
         <v>45043</v>
       </c>
       <c r="B541" t="n">
-        <v>11.87231922149658</v>
+        <v>11.8723201751709</v>
       </c>
       <c r="C541" t="n">
-        <v>12.16188816260904</v>
+        <v>12.16188913954372</v>
       </c>
       <c r="D541" t="n">
-        <v>11.65996854194554</v>
+        <v>11.65996947856225</v>
       </c>
       <c r="E541" t="n">
-        <v>12.00745071897192</v>
+        <v>12.00745168350102</v>
       </c>
       <c r="F541" t="n">
         <v>19434000</v>
@@ -11272,16 +11272,16 @@
         <v>45048</v>
       </c>
       <c r="B543" t="n">
-        <v>11.47497940063477</v>
+        <v>11.47497844696045</v>
       </c>
       <c r="C543" t="n">
-        <v>11.9595646731327</v>
+        <v>11.95956367918498</v>
       </c>
       <c r="D543" t="n">
-        <v>11.35867904614803</v>
+        <v>11.35867810213932</v>
       </c>
       <c r="E543" t="n">
-        <v>11.86264724892389</v>
+        <v>11.86264626303088</v>
       </c>
       <c r="F543" t="n">
         <v>17427900</v>
@@ -11292,16 +11292,16 @@
         <v>45049</v>
       </c>
       <c r="B544" t="n">
-        <v>11.11638641357422</v>
+        <v>11.1163854598999</v>
       </c>
       <c r="C544" t="n">
-        <v>11.29083648322547</v>
+        <v>11.29083551458509</v>
       </c>
       <c r="D544" t="n">
-        <v>10.59303435607435</v>
+        <v>10.59303344729838</v>
       </c>
       <c r="E544" t="n">
-        <v>11.02916091661206</v>
+        <v>11.02915997042082</v>
       </c>
       <c r="F544" t="n">
         <v>30544100</v>
@@ -11312,16 +11312,16 @@
         <v>45050</v>
       </c>
       <c r="B545" t="n">
-        <v>11.12607669830322</v>
+        <v>11.12607765197754</v>
       </c>
       <c r="C545" t="n">
-        <v>11.50405351931347</v>
+        <v>11.50405450538616</v>
       </c>
       <c r="D545" t="n">
-        <v>10.64149145692891</v>
+        <v>10.64149236906689</v>
       </c>
       <c r="E545" t="n">
-        <v>11.31991153427135</v>
+        <v>11.31991250456026</v>
       </c>
       <c r="F545" t="n">
         <v>26954400</v>
@@ -11452,16 +11452,16 @@
         <v>45061</v>
       </c>
       <c r="B552" t="n">
-        <v>11.36836910247803</v>
+        <v>11.36837005615234</v>
       </c>
       <c r="C552" t="n">
-        <v>11.40713680835171</v>
+        <v>11.40713776527819</v>
       </c>
       <c r="D552" t="n">
-        <v>11.10669355774151</v>
+        <v>11.10669448946428</v>
       </c>
       <c r="E552" t="n">
-        <v>11.26176068414433</v>
+        <v>11.26176162887544</v>
       </c>
       <c r="F552" t="n">
         <v>12238900</v>
@@ -11512,16 +11512,16 @@
         <v>45064</v>
       </c>
       <c r="B555" t="n">
-        <v>10.95162582397461</v>
+        <v>10.95162677764893</v>
       </c>
       <c r="C555" t="n">
-        <v>10.96131774990553</v>
+        <v>10.96131870442382</v>
       </c>
       <c r="D555" t="n">
-        <v>10.65118259002663</v>
+        <v>10.65118351753816</v>
       </c>
       <c r="E555" t="n">
-        <v>10.79655870617162</v>
+        <v>10.7965596463426</v>
       </c>
       <c r="F555" t="n">
         <v>10867600</v>
@@ -11572,16 +11572,16 @@
         <v>45069</v>
       </c>
       <c r="B558" t="n">
-        <v>11.21330261230469</v>
+        <v>11.21330165863037</v>
       </c>
       <c r="C558" t="n">
-        <v>11.89172271521926</v>
+        <v>11.89172170384635</v>
       </c>
       <c r="D558" t="n">
-        <v>11.1745358285044</v>
+        <v>11.17453487812714</v>
       </c>
       <c r="E558" t="n">
-        <v>11.76573043680007</v>
+        <v>11.76572943614261</v>
       </c>
       <c r="F558" t="n">
         <v>12722500</v>
@@ -11592,16 +11592,16 @@
         <v>45070</v>
       </c>
       <c r="B559" t="n">
-        <v>10.86440086364746</v>
+        <v>10.86440181732178</v>
       </c>
       <c r="C559" t="n">
-        <v>11.05823477025899</v>
+        <v>11.058235740948</v>
       </c>
       <c r="D559" t="n">
-        <v>10.68025888343475</v>
+        <v>10.68025982094513</v>
       </c>
       <c r="E559" t="n">
-        <v>11.02915991533551</v>
+        <v>11.02916088347233</v>
       </c>
       <c r="F559" t="n">
         <v>30388700</v>
@@ -11612,16 +11612,16 @@
         <v>45071</v>
       </c>
       <c r="B560" t="n">
-        <v>11.27145290374756</v>
+        <v>11.27145195007324</v>
       </c>
       <c r="C560" t="n">
-        <v>11.51374552612148</v>
+        <v>11.51374455194686</v>
       </c>
       <c r="D560" t="n">
-        <v>11.00008542548521</v>
+        <v>11.00008449477122</v>
       </c>
       <c r="E560" t="n">
-        <v>11.00977642793268</v>
+        <v>11.00977549639874</v>
       </c>
       <c r="F560" t="n">
         <v>17432300</v>
@@ -11652,16 +11652,16 @@
         <v>45075</v>
       </c>
       <c r="B562" t="n">
-        <v>11.16484451293945</v>
+        <v>11.16484546661377</v>
       </c>
       <c r="C562" t="n">
-        <v>11.32960264626966</v>
+        <v>11.32960361401722</v>
       </c>
       <c r="D562" t="n">
-        <v>10.99039352858946</v>
+        <v>10.99039446736259</v>
       </c>
       <c r="E562" t="n">
-        <v>10.99039352858946</v>
+        <v>10.99039446736259</v>
       </c>
       <c r="F562" t="n">
         <v>13598300</v>
@@ -11692,16 +11692,16 @@
         <v>45077</v>
       </c>
       <c r="B564" t="n">
-        <v>10.41858196258545</v>
+        <v>10.41858291625977</v>
       </c>
       <c r="C564" t="n">
-        <v>10.89347524417082</v>
+        <v>10.89347624131492</v>
       </c>
       <c r="D564" t="n">
-        <v>10.3604313309979</v>
+        <v>10.36043227934935</v>
       </c>
       <c r="E564" t="n">
-        <v>10.89347524417082</v>
+        <v>10.89347624131492</v>
       </c>
       <c r="F564" t="n">
         <v>32506900</v>
@@ -11712,16 +11712,16 @@
         <v>45078</v>
       </c>
       <c r="B565" t="n">
-        <v>10.67056751251221</v>
+        <v>10.67056655883789</v>
       </c>
       <c r="C565" t="n">
-        <v>10.70933429585259</v>
+        <v>10.70933333871352</v>
       </c>
       <c r="D565" t="n">
-        <v>10.21505711505793</v>
+        <v>10.21505620209453</v>
       </c>
       <c r="E565" t="n">
-        <v>10.51550037915067</v>
+        <v>10.51549943933537</v>
       </c>
       <c r="F565" t="n">
         <v>22690400</v>
@@ -11772,16 +11772,16 @@
         <v>45083</v>
       </c>
       <c r="B568" t="n">
-        <v>12.40538215637207</v>
+        <v>12.40538311004639</v>
       </c>
       <c r="C568" t="n">
-        <v>12.42476508508062</v>
+        <v>12.42476604024501</v>
       </c>
       <c r="D568" t="n">
-        <v>10.85470904022319</v>
+        <v>10.85470987468819</v>
       </c>
       <c r="E568" t="n">
-        <v>10.91285967489479</v>
+        <v>10.91286051383017</v>
       </c>
       <c r="F568" t="n">
         <v>56145900</v>
@@ -11972,16 +11972,16 @@
         <v>45098</v>
       </c>
       <c r="B578" t="n">
-        <v>12.98688507080078</v>
+        <v>12.98688411712646</v>
       </c>
       <c r="C578" t="n">
-        <v>13.03534378341849</v>
+        <v>13.03534282618567</v>
       </c>
       <c r="D578" t="n">
-        <v>12.70582564674574</v>
+        <v>12.70582471371064</v>
       </c>
       <c r="E578" t="n">
-        <v>12.99657699817894</v>
+        <v>12.99657604379291</v>
       </c>
       <c r="F578" t="n">
         <v>18033300</v>
@@ -11992,16 +11992,16 @@
         <v>45099</v>
       </c>
       <c r="B579" t="n">
-        <v>12.94811820983887</v>
+        <v>12.94811725616455</v>
       </c>
       <c r="C579" t="n">
-        <v>13.14195305917614</v>
+        <v>13.1419520912252</v>
       </c>
       <c r="D579" t="n">
-        <v>12.51199164737614</v>
+        <v>12.51199072582407</v>
       </c>
       <c r="E579" t="n">
-        <v>12.70582557244034</v>
+        <v>12.70582463661173</v>
       </c>
       <c r="F579" t="n">
         <v>34919500</v>
@@ -12052,16 +12052,16 @@
         <v>45104</v>
       </c>
       <c r="B582" t="n">
-        <v>12.68644237518311</v>
+        <v>12.68644142150879</v>
       </c>
       <c r="C582" t="n">
-        <v>13.85913875249263</v>
+        <v>13.85913771066354</v>
       </c>
       <c r="D582" t="n">
-        <v>12.56045009547363</v>
+        <v>12.5604491512705</v>
       </c>
       <c r="E582" t="n">
-        <v>13.77191325698045</v>
+        <v>13.77191222170834</v>
       </c>
       <c r="F582" t="n">
         <v>64278500</v>
@@ -12072,16 +12072,16 @@
         <v>45105</v>
       </c>
       <c r="B583" t="n">
-        <v>12.66705894470215</v>
+        <v>12.66705799102783</v>
       </c>
       <c r="C583" t="n">
-        <v>12.97719415292859</v>
+        <v>12.9771931759049</v>
       </c>
       <c r="D583" t="n">
-        <v>12.45384208662074</v>
+        <v>12.45384114899904</v>
       </c>
       <c r="E583" t="n">
-        <v>12.74459251569049</v>
+        <v>12.74459155617885</v>
       </c>
       <c r="F583" t="n">
         <v>61575500</v>
@@ -12092,16 +12092,16 @@
         <v>45106</v>
       </c>
       <c r="B584" t="n">
-        <v>12.93842601776123</v>
+        <v>12.93842697143555</v>
       </c>
       <c r="C584" t="n">
-        <v>13.19040963505111</v>
+        <v>13.19041060729881</v>
       </c>
       <c r="D584" t="n">
-        <v>12.57983213400556</v>
+        <v>12.5798330612484</v>
       </c>
       <c r="E584" t="n">
-        <v>12.7445911862372</v>
+        <v>12.74459212562421</v>
       </c>
       <c r="F584" t="n">
         <v>22969900</v>
@@ -12132,16 +12132,16 @@
         <v>45110</v>
       </c>
       <c r="B586" t="n">
-        <v>13.20010280609131</v>
+        <v>13.20010185241699</v>
       </c>
       <c r="C586" t="n">
-        <v>13.46177929875788</v>
+        <v>13.46177832617809</v>
       </c>
       <c r="D586" t="n">
-        <v>13.09349437811959</v>
+        <v>13.09349343214747</v>
       </c>
       <c r="E586" t="n">
-        <v>13.46177929875788</v>
+        <v>13.46177832617809</v>
       </c>
       <c r="F586" t="n">
         <v>9654100</v>
@@ -12212,16 +12212,16 @@
         <v>45114</v>
       </c>
       <c r="B590" t="n">
-        <v>13.56838607788086</v>
+        <v>13.56838703155518</v>
       </c>
       <c r="C590" t="n">
-        <v>13.88821224720336</v>
+        <v>13.88821322335713</v>
       </c>
       <c r="D590" t="n">
-        <v>13.13225956737499</v>
+        <v>13.1322604903955</v>
       </c>
       <c r="E590" t="n">
-        <v>13.28732668895282</v>
+        <v>13.28732762287245</v>
       </c>
       <c r="F590" t="n">
         <v>12191300</v>
@@ -12232,16 +12232,16 @@
         <v>45117</v>
       </c>
       <c r="B591" t="n">
-        <v>13.28732776641846</v>
+        <v>13.28732681274414</v>
       </c>
       <c r="C591" t="n">
-        <v>13.70407138265719</v>
+        <v>13.70407039907184</v>
       </c>
       <c r="D591" t="n">
-        <v>13.21948612629514</v>
+        <v>13.21948517749003</v>
       </c>
       <c r="E591" t="n">
-        <v>13.55869525118476</v>
+        <v>13.55869427803353</v>
       </c>
       <c r="F591" t="n">
         <v>9043800</v>
@@ -12312,16 +12312,16 @@
         <v>45121</v>
       </c>
       <c r="B595" t="n">
-        <v>12.18247318267822</v>
+        <v>12.18247222900391</v>
       </c>
       <c r="C595" t="n">
-        <v>12.62829166038781</v>
+        <v>12.62829067181371</v>
       </c>
       <c r="D595" t="n">
-        <v>12.0370979738857</v>
+        <v>12.03709703159172</v>
       </c>
       <c r="E595" t="n">
-        <v>12.60890873054289</v>
+        <v>12.60890774348613</v>
       </c>
       <c r="F595" t="n">
         <v>15603200</v>
@@ -12452,16 +12452,16 @@
         <v>45132</v>
       </c>
       <c r="B602" t="n">
-        <v>12.27939033508301</v>
+        <v>12.27938938140869</v>
       </c>
       <c r="C602" t="n">
-        <v>12.7058249493107</v>
+        <v>12.7058239625175</v>
       </c>
       <c r="D602" t="n">
-        <v>12.19216484201363</v>
+        <v>12.19216389511365</v>
       </c>
       <c r="E602" t="n">
-        <v>12.66705816619909</v>
+        <v>12.6670571824167</v>
       </c>
       <c r="F602" t="n">
         <v>13780600</v>
@@ -12492,16 +12492,16 @@
         <v>45134</v>
       </c>
       <c r="B604" t="n">
-        <v>13.08380222320557</v>
+        <v>13.08380126953125</v>
       </c>
       <c r="C604" t="n">
-        <v>13.55869556355564</v>
+        <v>13.5586945752665</v>
       </c>
       <c r="D604" t="n">
-        <v>12.88027637387367</v>
+        <v>12.88027543503429</v>
       </c>
       <c r="E604" t="n">
-        <v>13.13226093481279</v>
+        <v>13.13225997760633</v>
       </c>
       <c r="F604" t="n">
         <v>67544900</v>
@@ -12532,16 +12532,16 @@
         <v>45138</v>
       </c>
       <c r="B606" t="n">
-        <v>13.05472660064697</v>
+        <v>13.05472564697266</v>
       </c>
       <c r="C606" t="n">
-        <v>13.18071887373052</v>
+        <v>13.18071791085222</v>
       </c>
       <c r="D606" t="n">
-        <v>12.72520849016276</v>
+        <v>12.72520756056041</v>
       </c>
       <c r="E606" t="n">
-        <v>12.89965947201275</v>
+        <v>12.89965852966641</v>
       </c>
       <c r="F606" t="n">
         <v>32856600</v>
@@ -12612,16 +12612,16 @@
         <v>45142</v>
       </c>
       <c r="B610" t="n">
-        <v>13.26794338226318</v>
+        <v>13.2679443359375</v>
       </c>
       <c r="C610" t="n">
-        <v>13.64592019985814</v>
+        <v>13.6459211807007</v>
       </c>
       <c r="D610" t="n">
-        <v>13.01595976147287</v>
+        <v>13.01596069703509</v>
       </c>
       <c r="E610" t="n">
-        <v>13.37455272593696</v>
+        <v>13.37455368727415</v>
       </c>
       <c r="F610" t="n">
         <v>25269600</v>
@@ -12632,16 +12632,16 @@
         <v>45145</v>
       </c>
       <c r="B611" t="n">
-        <v>13.4423942565918</v>
+        <v>13.44239521026611</v>
       </c>
       <c r="C611" t="n">
-        <v>13.85913785286578</v>
+        <v>13.85913883610609</v>
       </c>
       <c r="D611" t="n">
-        <v>13.384244546207</v>
+        <v>13.38424549575587</v>
       </c>
       <c r="E611" t="n">
-        <v>13.58777038109976</v>
+        <v>13.58777134508783</v>
       </c>
       <c r="F611" t="n">
         <v>31957200</v>
@@ -12652,16 +12652,16 @@
         <v>45146</v>
       </c>
       <c r="B612" t="n">
-        <v>13.6846866607666</v>
+        <v>13.68468761444092</v>
       </c>
       <c r="C612" t="n">
-        <v>13.7525282965869</v>
+        <v>13.75252925498904</v>
       </c>
       <c r="D612" t="n">
-        <v>13.05472623716194</v>
+        <v>13.05472714693484</v>
       </c>
       <c r="E612" t="n">
-        <v>13.34547755739215</v>
+        <v>13.34547848742727</v>
       </c>
       <c r="F612" t="n">
         <v>19992600</v>
@@ -12712,16 +12712,16 @@
         <v>45149</v>
       </c>
       <c r="B615" t="n">
-        <v>13.08380222320557</v>
+        <v>13.08380126953125</v>
       </c>
       <c r="C615" t="n">
-        <v>13.61684620233892</v>
+        <v>13.61684520981119</v>
       </c>
       <c r="D615" t="n">
-        <v>12.94811801555995</v>
+        <v>12.94811707177562</v>
       </c>
       <c r="E615" t="n">
-        <v>13.38424549575191</v>
+        <v>13.38424452017838</v>
       </c>
       <c r="F615" t="n">
         <v>15622100</v>
@@ -12732,16 +12732,16 @@
         <v>45152</v>
       </c>
       <c r="B616" t="n">
-        <v>12.74459075927734</v>
+        <v>12.74459171295166</v>
       </c>
       <c r="C616" t="n">
-        <v>13.11287563285283</v>
+        <v>13.1128766140858</v>
       </c>
       <c r="D616" t="n">
-        <v>12.66705719897439</v>
+        <v>12.66705814684689</v>
       </c>
       <c r="E616" t="n">
-        <v>13.02565014644377</v>
+        <v>13.02565112114969</v>
       </c>
       <c r="F616" t="n">
         <v>20429600</v>
@@ -12752,16 +12752,16 @@
         <v>45153</v>
       </c>
       <c r="B617" t="n">
-        <v>12.70582485198975</v>
+        <v>12.70582580566406</v>
       </c>
       <c r="C617" t="n">
-        <v>12.87058391002036</v>
+        <v>12.87058487606116</v>
       </c>
       <c r="D617" t="n">
-        <v>12.5701415742749</v>
+        <v>12.57014251776509</v>
       </c>
       <c r="E617" t="n">
-        <v>12.78335841761909</v>
+        <v>12.78335937711292</v>
       </c>
       <c r="F617" t="n">
         <v>15018500</v>
@@ -12832,16 +12832,16 @@
         <v>45159</v>
       </c>
       <c r="B621" t="n">
-        <v>12.68644237518311</v>
+        <v>12.68644142150879</v>
       </c>
       <c r="C621" t="n">
-        <v>13.07411021715607</v>
+        <v>13.07410923433971</v>
       </c>
       <c r="D621" t="n">
-        <v>12.68644237518311</v>
+        <v>12.68644142150879</v>
       </c>
       <c r="E621" t="n">
-        <v>13.03534343295877</v>
+        <v>13.03534245305662</v>
       </c>
       <c r="F621" t="n">
         <v>19861900</v>
@@ -12932,16 +12932,16 @@
         <v>45166</v>
       </c>
       <c r="B626" t="n">
-        <v>11.77542114257812</v>
+        <v>11.77542018890381</v>
       </c>
       <c r="C626" t="n">
-        <v>12.05648054911036</v>
+        <v>12.05647957267345</v>
       </c>
       <c r="D626" t="n">
-        <v>11.63004593806156</v>
+        <v>11.63004499616097</v>
       </c>
       <c r="E626" t="n">
-        <v>12.02740569306165</v>
+        <v>12.02740471897947</v>
       </c>
       <c r="F626" t="n">
         <v>17568500</v>
@@ -13172,16 +13172,16 @@
         <v>45183</v>
       </c>
       <c r="B638" t="n">
-        <v>12.23093128204346</v>
+        <v>12.23093223571777</v>
       </c>
       <c r="C638" t="n">
-        <v>12.63798295543392</v>
+        <v>12.63798394084701</v>
       </c>
       <c r="D638" t="n">
-        <v>11.89172217040007</v>
+        <v>11.89172309762546</v>
       </c>
       <c r="E638" t="n">
-        <v>12.47322390076287</v>
+        <v>12.47322487332931</v>
       </c>
       <c r="F638" t="n">
         <v>24212200</v>
@@ -13192,16 +13192,16 @@
         <v>45184</v>
       </c>
       <c r="B639" t="n">
-        <v>12.03709697723389</v>
+        <v>12.0370979309082</v>
       </c>
       <c r="C639" t="n">
-        <v>12.26969766175218</v>
+        <v>12.26969863385497</v>
       </c>
       <c r="D639" t="n">
-        <v>11.88202985422169</v>
+        <v>11.88203079561036</v>
       </c>
       <c r="E639" t="n">
-        <v>12.23093088099913</v>
+        <v>12.23093185003051</v>
       </c>
       <c r="F639" t="n">
         <v>12780600</v>
@@ -13212,16 +13212,16 @@
         <v>45187</v>
       </c>
       <c r="B640" t="n">
-        <v>11.88203144073486</v>
+        <v>11.88203048706055</v>
       </c>
       <c r="C640" t="n">
-        <v>12.11463215631048</v>
+        <v>12.11463118396719</v>
       </c>
       <c r="D640" t="n">
-        <v>11.82388079970442</v>
+        <v>11.82387985069738</v>
       </c>
       <c r="E640" t="n">
-        <v>12.00802372607326</v>
+        <v>12.00802276228657</v>
       </c>
       <c r="F640" t="n">
         <v>10083800</v>
@@ -13232,16 +13232,16 @@
         <v>45188</v>
       </c>
       <c r="B641" t="n">
-        <v>11.68819713592529</v>
+        <v>11.68819618225098</v>
       </c>
       <c r="C641" t="n">
-        <v>11.94987270148044</v>
+        <v>11.94987172645524</v>
       </c>
       <c r="D641" t="n">
-        <v>11.56220485463095</v>
+        <v>11.56220391123671</v>
       </c>
       <c r="E641" t="n">
-        <v>11.83357234742559</v>
+        <v>11.83357138188968</v>
       </c>
       <c r="F641" t="n">
         <v>9202900</v>
@@ -13272,16 +13272,16 @@
         <v>45190</v>
       </c>
       <c r="B643" t="n">
-        <v>11.4265193939209</v>
+        <v>11.42652034759521</v>
       </c>
       <c r="C643" t="n">
-        <v>11.69788685697771</v>
+        <v>11.69788783330076</v>
       </c>
       <c r="D643" t="n">
-        <v>11.33929390687011</v>
+        <v>11.33929485326446</v>
       </c>
       <c r="E643" t="n">
-        <v>11.52343680714909</v>
+        <v>11.52343776891228</v>
       </c>
       <c r="F643" t="n">
         <v>16782800</v>
@@ -13332,16 +13332,16 @@
         <v>45195</v>
       </c>
       <c r="B646" t="n">
-        <v>10.94193553924561</v>
+        <v>10.94193458557129</v>
       </c>
       <c r="C646" t="n">
-        <v>11.18422817822294</v>
+        <v>11.18422720343095</v>
       </c>
       <c r="D646" t="n">
-        <v>10.90316875398015</v>
+        <v>10.90316780368466</v>
       </c>
       <c r="E646" t="n">
-        <v>10.92255260874941</v>
+        <v>10.92255165676447</v>
       </c>
       <c r="F646" t="n">
         <v>10375300</v>
@@ -13412,16 +13412,16 @@
         <v>45201</v>
       </c>
       <c r="B650" t="n">
-        <v>11.63004589080811</v>
+        <v>11.63004684448242</v>
       </c>
       <c r="C650" t="n">
-        <v>11.84326365760269</v>
+        <v>11.84326462876106</v>
       </c>
       <c r="D650" t="n">
-        <v>11.61066203733905</v>
+        <v>11.61066298942387</v>
       </c>
       <c r="E650" t="n">
-        <v>11.82387980413364</v>
+        <v>11.82388077370251</v>
       </c>
       <c r="F650" t="n">
         <v>7262700</v>
@@ -13432,16 +13432,16 @@
         <v>45202</v>
       </c>
       <c r="B651" t="n">
-        <v>11.13576984405518</v>
+        <v>11.13576889038086</v>
       </c>
       <c r="C651" t="n">
-        <v>11.67850578049106</v>
+        <v>11.67850478033649</v>
       </c>
       <c r="D651" t="n">
-        <v>11.0679281986031</v>
+        <v>11.06792725073879</v>
       </c>
       <c r="E651" t="n">
-        <v>11.48467184757578</v>
+        <v>11.48467086402128</v>
       </c>
       <c r="F651" t="n">
         <v>18442400</v>
@@ -13452,16 +13452,16 @@
         <v>45203</v>
       </c>
       <c r="B652" t="n">
-        <v>11.27145290374756</v>
+        <v>11.27145195007324</v>
       </c>
       <c r="C652" t="n">
-        <v>11.45559489007162</v>
+        <v>11.4555939208171</v>
       </c>
       <c r="D652" t="n">
-        <v>11.14546062920036</v>
+        <v>11.14545968618621</v>
       </c>
       <c r="E652" t="n">
-        <v>11.17453548508879</v>
+        <v>11.17453453961463</v>
       </c>
       <c r="F652" t="n">
         <v>10408400</v>
@@ -13472,16 +13472,16 @@
         <v>45204</v>
       </c>
       <c r="B653" t="n">
-        <v>11.27145290374756</v>
+        <v>11.27145195007324</v>
       </c>
       <c r="C653" t="n">
-        <v>11.43621196090366</v>
+        <v>11.43621099328913</v>
       </c>
       <c r="D653" t="n">
-        <v>11.11638577331193</v>
+        <v>11.1163848327578</v>
       </c>
       <c r="E653" t="n">
-        <v>11.2520690503066</v>
+        <v>11.25206809827235</v>
       </c>
       <c r="F653" t="n">
         <v>7593000</v>
@@ -13532,16 +13532,16 @@
         <v>45209</v>
       </c>
       <c r="B656" t="n">
-        <v>11.73665332794189</v>
+        <v>11.73665428161621</v>
       </c>
       <c r="C656" t="n">
-        <v>11.73665332794189</v>
+        <v>11.73665428161621</v>
       </c>
       <c r="D656" t="n">
-        <v>11.2326851955536</v>
+        <v>11.23268610827745</v>
       </c>
       <c r="E656" t="n">
-        <v>11.25206812312438</v>
+        <v>11.25206903742321</v>
       </c>
       <c r="F656" t="n">
         <v>12462900</v>
@@ -13612,16 +13612,16 @@
         <v>45216</v>
       </c>
       <c r="B660" t="n">
-        <v>11.21330261230469</v>
+        <v>11.21330165863037</v>
       </c>
       <c r="C660" t="n">
-        <v>11.67850494218117</v>
+        <v>11.6785039489421</v>
       </c>
       <c r="D660" t="n">
-        <v>11.1745358285044</v>
+        <v>11.17453487812714</v>
       </c>
       <c r="E660" t="n">
-        <v>11.33929489072388</v>
+        <v>11.33929392633411</v>
       </c>
       <c r="F660" t="n">
         <v>9846900</v>
@@ -13652,16 +13652,16 @@
         <v>45218</v>
       </c>
       <c r="B662" t="n">
-        <v>10.65118312835693</v>
+        <v>10.65118408203125</v>
       </c>
       <c r="C662" t="n">
-        <v>10.91285959607978</v>
+        <v>10.9128605731838</v>
       </c>
       <c r="D662" t="n">
-        <v>10.38950758490707</v>
+        <v>10.38950851515176</v>
       </c>
       <c r="E662" t="n">
-        <v>10.41858243989639</v>
+        <v>10.41858337274435</v>
       </c>
       <c r="F662" t="n">
         <v>8209500</v>
@@ -13692,16 +13692,16 @@
         <v>45222</v>
       </c>
       <c r="B664" t="n">
-        <v>11.16484451293945</v>
+        <v>11.16484546661377</v>
       </c>
       <c r="C664" t="n">
-        <v>11.31991164379589</v>
+        <v>11.31991261071567</v>
       </c>
       <c r="D664" t="n">
-        <v>10.58334184795481</v>
+        <v>10.58334275195856</v>
       </c>
       <c r="E664" t="n">
-        <v>10.58334184795481</v>
+        <v>10.58334275195856</v>
       </c>
       <c r="F664" t="n">
         <v>7677200</v>
@@ -13792,16 +13792,16 @@
         <v>45229</v>
       </c>
       <c r="B669" t="n">
-        <v>10.62210845947266</v>
+        <v>10.62210941314697</v>
       </c>
       <c r="C669" t="n">
-        <v>11.0970017711349</v>
+        <v>11.09700276744609</v>
       </c>
       <c r="D669" t="n">
-        <v>10.53488296870347</v>
+        <v>10.53488391454651</v>
       </c>
       <c r="E669" t="n">
-        <v>10.95162656936825</v>
+        <v>10.95162755262737</v>
       </c>
       <c r="F669" t="n">
         <v>14902100</v>
@@ -13912,16 +13912,16 @@
         <v>45238</v>
       </c>
       <c r="B675" t="n">
-        <v>11.94018077850342</v>
+        <v>11.9401798248291</v>
       </c>
       <c r="C675" t="n">
-        <v>12.30846569527843</v>
+        <v>12.30846471218883</v>
       </c>
       <c r="D675" t="n">
-        <v>11.68819714009782</v>
+        <v>11.68819620654969</v>
       </c>
       <c r="E675" t="n">
-        <v>11.83357235165001</v>
+        <v>11.83357140649062</v>
       </c>
       <c r="F675" t="n">
         <v>13850200</v>
@@ -13952,16 +13952,16 @@
         <v>45240</v>
       </c>
       <c r="B677" t="n">
-        <v>12.22124004364014</v>
+        <v>12.22123908996582</v>
       </c>
       <c r="C677" t="n">
-        <v>12.66705852415857</v>
+        <v>12.66705753569518</v>
       </c>
       <c r="D677" t="n">
-        <v>12.11463161813881</v>
+        <v>12.11463067278359</v>
       </c>
       <c r="E677" t="n">
-        <v>12.19216518655305</v>
+        <v>12.19216423514757</v>
       </c>
       <c r="F677" t="n">
         <v>17847100</v>
@@ -14032,16 +14032,16 @@
         <v>45247</v>
       </c>
       <c r="B681" t="n">
-        <v>12.70582485198975</v>
+        <v>12.70582580566406</v>
       </c>
       <c r="C681" t="n">
-        <v>13.03534296805097</v>
+        <v>13.03534394645827</v>
       </c>
       <c r="D681" t="n">
-        <v>12.63798321313232</v>
+        <v>12.63798416171458</v>
       </c>
       <c r="E681" t="n">
-        <v>13.02565104127905</v>
+        <v>13.02565201895889</v>
       </c>
       <c r="F681" t="n">
         <v>13810400</v>
@@ -14132,16 +14132,16 @@
         <v>45254</v>
       </c>
       <c r="B686" t="n">
-        <v>12.74459075927734</v>
+        <v>12.74459171295166</v>
       </c>
       <c r="C686" t="n">
-        <v>13.23886789941336</v>
+        <v>13.2388688900743</v>
       </c>
       <c r="D686" t="n">
-        <v>12.66705719897439</v>
+        <v>12.66705814684689</v>
       </c>
       <c r="E686" t="n">
-        <v>13.20010111926188</v>
+        <v>13.20010210702191</v>
       </c>
       <c r="F686" t="n">
         <v>7056600</v>
@@ -14192,16 +14192,16 @@
         <v>45259</v>
       </c>
       <c r="B689" t="n">
-        <v>12.76397514343262</v>
+        <v>12.76397609710693</v>
       </c>
       <c r="C689" t="n">
-        <v>13.45208621300327</v>
+        <v>13.45208721809055</v>
       </c>
       <c r="D689" t="n">
-        <v>12.72520836166552</v>
+        <v>12.72520931244334</v>
       </c>
       <c r="E689" t="n">
-        <v>13.22917652463774</v>
+        <v>13.22917751307009</v>
       </c>
       <c r="F689" t="n">
         <v>13863800</v>
@@ -14232,16 +14232,16 @@
         <v>45261</v>
       </c>
       <c r="B691" t="n">
-        <v>12.51199150085449</v>
+        <v>12.51199054718018</v>
       </c>
       <c r="C691" t="n">
-        <v>12.63798378173906</v>
+        <v>12.63798281846151</v>
       </c>
       <c r="D691" t="n">
-        <v>12.13401558247384</v>
+        <v>12.13401465760916</v>
       </c>
       <c r="E691" t="n">
-        <v>12.52168342806247</v>
+        <v>12.52168247364943</v>
       </c>
       <c r="F691" t="n">
         <v>20043200</v>
@@ -14252,16 +14252,16 @@
         <v>45264</v>
       </c>
       <c r="B692" t="n">
-        <v>12.28908157348633</v>
+        <v>12.28908252716064</v>
       </c>
       <c r="C692" t="n">
-        <v>12.71551616382486</v>
+        <v>12.71551715059195</v>
       </c>
       <c r="D692" t="n">
-        <v>12.28908157348633</v>
+        <v>12.28908252716064</v>
       </c>
       <c r="E692" t="n">
-        <v>12.53137418542874</v>
+        <v>12.53137515790578</v>
       </c>
       <c r="F692" t="n">
         <v>9929700</v>
@@ -14372,16 +14372,16 @@
         <v>45272</v>
       </c>
       <c r="B698" t="n">
-        <v>11.6978874206543</v>
+        <v>11.69788837432861</v>
       </c>
       <c r="C698" t="n">
-        <v>11.98863875007613</v>
+        <v>11.98863972745405</v>
       </c>
       <c r="D698" t="n">
-        <v>11.54282029143545</v>
+        <v>11.54282123246787</v>
       </c>
       <c r="E698" t="n">
-        <v>11.54282029143545</v>
+        <v>11.54282123246787</v>
       </c>
       <c r="F698" t="n">
         <v>12668100</v>
@@ -14412,16 +14412,16 @@
         <v>45274</v>
       </c>
       <c r="B700" t="n">
-        <v>12.94811820983887</v>
+        <v>12.94811725616455</v>
       </c>
       <c r="C700" t="n">
-        <v>13.41332055426603</v>
+        <v>13.41331956632793</v>
       </c>
       <c r="D700" t="n">
-        <v>12.61860099936625</v>
+        <v>12.61860006996203</v>
       </c>
       <c r="E700" t="n">
-        <v>12.62829200241466</v>
+        <v>12.62829107229667</v>
       </c>
       <c r="F700" t="n">
         <v>27002600</v>
@@ -14452,16 +14452,16 @@
         <v>45278</v>
       </c>
       <c r="B702" t="n">
-        <v>12.80274105072021</v>
+        <v>12.80274200439453</v>
       </c>
       <c r="C702" t="n">
-        <v>12.97719201889291</v>
+        <v>12.97719298556206</v>
       </c>
       <c r="D702" t="n">
-        <v>12.34723070286534</v>
+        <v>12.34723162260876</v>
       </c>
       <c r="E702" t="n">
-        <v>12.55075652430919</v>
+        <v>12.55075745921321</v>
       </c>
       <c r="F702" t="n">
         <v>9094600</v>
@@ -14472,16 +14472,16 @@
         <v>45279</v>
       </c>
       <c r="B703" t="n">
-        <v>12.98688507080078</v>
+        <v>12.98688411712646</v>
       </c>
       <c r="C703" t="n">
-        <v>13.0547276381748</v>
+        <v>13.05472667951856</v>
       </c>
       <c r="D703" t="n">
-        <v>12.87058471508212</v>
+        <v>12.87058376994816</v>
       </c>
       <c r="E703" t="n">
-        <v>12.98688507080078</v>
+        <v>12.98688411712646</v>
       </c>
       <c r="F703" t="n">
         <v>5248800</v>
@@ -14492,16 +14492,16 @@
         <v>45280</v>
       </c>
       <c r="B704" t="n">
-        <v>12.94811820983887</v>
+        <v>12.94811725616455</v>
       </c>
       <c r="C704" t="n">
-        <v>13.22917763225023</v>
+        <v>13.22917665787491</v>
       </c>
       <c r="D704" t="n">
-        <v>12.88027656713466</v>
+        <v>12.88027561845712</v>
       </c>
       <c r="E704" t="n">
-        <v>12.94811820983887</v>
+        <v>12.94811725616455</v>
       </c>
       <c r="F704" t="n">
         <v>7030200</v>
@@ -14532,16 +14532,16 @@
         <v>45282</v>
       </c>
       <c r="B706" t="n">
-        <v>12.99657535552979</v>
+        <v>12.9965763092041</v>
       </c>
       <c r="C706" t="n">
-        <v>13.18071825534848</v>
+        <v>13.180719222535</v>
       </c>
       <c r="D706" t="n">
-        <v>12.81243337998404</v>
+        <v>12.81243432014622</v>
       </c>
       <c r="E706" t="n">
-        <v>12.83181630801746</v>
+        <v>12.83181724960194</v>
       </c>
       <c r="F706" t="n">
         <v>4433600</v>
@@ -14652,16 +14652,16 @@
         <v>45295</v>
       </c>
       <c r="B712" t="n">
-        <v>12.80274105072021</v>
+        <v>12.80274200439453</v>
       </c>
       <c r="C712" t="n">
-        <v>12.91904138807771</v>
+        <v>12.91904235041522</v>
       </c>
       <c r="D712" t="n">
-        <v>12.44414811279971</v>
+        <v>12.44414903976249</v>
       </c>
       <c r="E712" t="n">
-        <v>12.502297819342</v>
+        <v>12.50229875063634</v>
       </c>
       <c r="F712" t="n">
         <v>8604100</v>
@@ -14692,16 +14692,16 @@
         <v>45299</v>
       </c>
       <c r="B714" t="n">
-        <v>13.73314666748047</v>
+        <v>13.73314571380615</v>
       </c>
       <c r="C714" t="n">
-        <v>13.73314666748047</v>
+        <v>13.73314571380615</v>
       </c>
       <c r="D714" t="n">
-        <v>13.09349425702008</v>
+        <v>13.09349334776531</v>
       </c>
       <c r="E714" t="n">
-        <v>13.15164397200391</v>
+        <v>13.15164305871103</v>
       </c>
       <c r="F714" t="n">
         <v>17538900</v>
@@ -14712,16 +14712,16 @@
         <v>45300</v>
       </c>
       <c r="B715" t="n">
-        <v>13.51023578643799</v>
+        <v>13.5102367401123</v>
       </c>
       <c r="C715" t="n">
-        <v>13.85913774307474</v>
+        <v>13.8591387213777</v>
       </c>
       <c r="D715" t="n">
-        <v>13.35516866094298</v>
+        <v>13.35516960367126</v>
       </c>
       <c r="E715" t="n">
-        <v>13.72345354613012</v>
+        <v>13.72345451485526</v>
       </c>
       <c r="F715" t="n">
         <v>9819500</v>
@@ -14752,16 +14752,16 @@
         <v>45302</v>
       </c>
       <c r="B717" t="n">
-        <v>13.4423942565918</v>
+        <v>13.44239521026611</v>
       </c>
       <c r="C717" t="n">
-        <v>13.71376172835782</v>
+        <v>13.71376270128438</v>
       </c>
       <c r="D717" t="n">
-        <v>13.20979356650663</v>
+        <v>13.20979450367903</v>
       </c>
       <c r="E717" t="n">
-        <v>13.20979356650663</v>
+        <v>13.20979450367903</v>
       </c>
       <c r="F717" t="n">
         <v>14967000</v>
@@ -14792,16 +14792,16 @@
         <v>45306</v>
       </c>
       <c r="B719" t="n">
-        <v>14.24680614471436</v>
+        <v>14.24680709838867</v>
       </c>
       <c r="C719" t="n">
-        <v>14.33403163747295</v>
+        <v>14.3340325969861</v>
       </c>
       <c r="D719" t="n">
-        <v>13.70407118308557</v>
+        <v>13.70407210042947</v>
       </c>
       <c r="E719" t="n">
-        <v>13.80098767838277</v>
+        <v>13.80098860221422</v>
       </c>
       <c r="F719" t="n">
         <v>8029800</v>
@@ -14812,16 +14812,16 @@
         <v>45307</v>
       </c>
       <c r="B720" t="n">
-        <v>14.03358840942383</v>
+        <v>14.03358745574951</v>
       </c>
       <c r="C720" t="n">
-        <v>14.30495681515323</v>
+        <v>14.30495584303765</v>
       </c>
       <c r="D720" t="n">
-        <v>13.93667191389734</v>
+        <v>13.93667096680914</v>
       </c>
       <c r="E720" t="n">
-        <v>14.30495681515323</v>
+        <v>14.30495584303765</v>
       </c>
       <c r="F720" t="n">
         <v>11210600</v>
@@ -14912,16 +14912,16 @@
         <v>45314</v>
       </c>
       <c r="B725" t="n">
-        <v>13.21948623657227</v>
+        <v>13.21948528289795</v>
       </c>
       <c r="C725" t="n">
-        <v>13.4811617965687</v>
+        <v>13.4811608240167</v>
       </c>
       <c r="D725" t="n">
-        <v>13.18071945271083</v>
+        <v>13.18071850183321</v>
       </c>
       <c r="E725" t="n">
-        <v>13.24856109340008</v>
+        <v>13.24856013762826</v>
       </c>
       <c r="F725" t="n">
         <v>9537600</v>
@@ -14932,16 +14932,16 @@
         <v>45315</v>
       </c>
       <c r="B726" t="n">
-        <v>12.93842601776123</v>
+        <v>12.93842697143555</v>
       </c>
       <c r="C726" t="n">
-        <v>13.43270225018317</v>
+        <v>13.43270324028994</v>
       </c>
       <c r="D726" t="n">
-        <v>12.93842601776123</v>
+        <v>12.93842697143555</v>
       </c>
       <c r="E726" t="n">
-        <v>13.27763512438233</v>
+        <v>13.2776361030593</v>
       </c>
       <c r="F726" t="n">
         <v>9089400</v>
@@ -14952,16 +14952,16 @@
         <v>45316</v>
       </c>
       <c r="B727" t="n">
-        <v>13.56838607788086</v>
+        <v>13.56838703155518</v>
       </c>
       <c r="C727" t="n">
-        <v>13.60715285827531</v>
+        <v>13.60715381467441</v>
       </c>
       <c r="D727" t="n">
-        <v>12.93842566540271</v>
+        <v>12.93842657479932</v>
       </c>
       <c r="E727" t="n">
-        <v>12.93842566540271</v>
+        <v>12.93842657479932</v>
       </c>
       <c r="F727" t="n">
         <v>8608700</v>
@@ -14992,16 +14992,16 @@
         <v>45320</v>
       </c>
       <c r="B729" t="n">
-        <v>14.01420497894287</v>
+        <v>14.01420593261719</v>
       </c>
       <c r="C729" t="n">
-        <v>14.03358790764592</v>
+        <v>14.03358886263925</v>
       </c>
       <c r="D729" t="n">
-        <v>13.28732712925553</v>
+        <v>13.28732803346541</v>
       </c>
       <c r="E729" t="n">
-        <v>13.28732712925553</v>
+        <v>13.28732803346541</v>
       </c>
       <c r="F729" t="n">
         <v>11897100</v>
@@ -15172,16 +15172,16 @@
         <v>45331</v>
       </c>
       <c r="B738" t="n">
-        <v>12.93842601776123</v>
+        <v>12.93842697143555</v>
       </c>
       <c r="C738" t="n">
-        <v>13.40362739516376</v>
+        <v>13.40362838312745</v>
       </c>
       <c r="D738" t="n">
-        <v>12.90935023846884</v>
+        <v>12.90935119000002</v>
       </c>
       <c r="E738" t="n">
-        <v>13.40362739516376</v>
+        <v>13.40362838312745</v>
       </c>
       <c r="F738" t="n">
         <v>18553100</v>
@@ -15192,16 +15192,16 @@
         <v>45336</v>
       </c>
       <c r="B739" t="n">
-        <v>12.7542839050293</v>
+        <v>12.75428295135498</v>
       </c>
       <c r="C739" t="n">
-        <v>12.9481178243223</v>
+        <v>12.94811685615447</v>
       </c>
       <c r="D739" t="n">
-        <v>12.67675033731209</v>
+        <v>12.67674938943519</v>
       </c>
       <c r="E739" t="n">
-        <v>12.85120132681232</v>
+        <v>12.85120036589121</v>
       </c>
       <c r="F739" t="n">
         <v>7875600</v>
@@ -15212,16 +15212,16 @@
         <v>45337</v>
       </c>
       <c r="B740" t="n">
-        <v>12.97719287872314</v>
+        <v>12.97719383239746</v>
       </c>
       <c r="C740" t="n">
-        <v>13.180718713652</v>
+        <v>13.18071968228313</v>
       </c>
       <c r="D740" t="n">
-        <v>12.65736669873108</v>
+        <v>12.65736762890185</v>
       </c>
       <c r="E740" t="n">
-        <v>12.80274189899184</v>
+        <v>12.80274283984602</v>
       </c>
       <c r="F740" t="n">
         <v>6962800</v>
@@ -15272,16 +15272,16 @@
         <v>45342</v>
       </c>
       <c r="B743" t="n">
-        <v>13.55869483947754</v>
+        <v>13.55869388580322</v>
       </c>
       <c r="C743" t="n">
-        <v>13.70407096653565</v>
+        <v>13.70407000263605</v>
       </c>
       <c r="D743" t="n">
-        <v>13.02565088881045</v>
+        <v>13.02564997262871</v>
       </c>
       <c r="E743" t="n">
-        <v>13.0450347421274</v>
+        <v>13.04503382458226</v>
       </c>
       <c r="F743" t="n">
         <v>16895700</v>
@@ -15332,16 +15332,16 @@
         <v>45345</v>
       </c>
       <c r="B746" t="n">
-        <v>14.26619052886963</v>
+        <v>14.26618957519531</v>
       </c>
       <c r="C746" t="n">
-        <v>14.46002445094536</v>
+        <v>14.46002348431353</v>
       </c>
       <c r="D746" t="n">
-        <v>13.98513111079155</v>
+        <v>13.98513017590566</v>
       </c>
       <c r="E746" t="n">
-        <v>14.46002445094536</v>
+        <v>14.46002348431353</v>
       </c>
       <c r="F746" t="n">
         <v>7821200</v>
@@ -15372,16 +15372,16 @@
         <v>45349</v>
       </c>
       <c r="B748" t="n">
-        <v>14.25649738311768</v>
+        <v>14.25649833679199</v>
       </c>
       <c r="C748" t="n">
-        <v>14.36310580007867</v>
+        <v>14.36310676088445</v>
       </c>
       <c r="D748" t="n">
-        <v>14.08204640602426</v>
+        <v>14.08204734802885</v>
       </c>
       <c r="E748" t="n">
-        <v>14.2661893094613</v>
+        <v>14.26619026378395</v>
       </c>
       <c r="F748" t="n">
         <v>8891500</v>
@@ -15472,16 +15472,16 @@
         <v>45356</v>
       </c>
       <c r="B753" t="n">
-        <v>14.02389812469482</v>
+        <v>14.02389717102051</v>
       </c>
       <c r="C753" t="n">
-        <v>14.13050655251276</v>
+        <v>14.1305055915887</v>
       </c>
       <c r="D753" t="n">
-        <v>13.58777156181936</v>
+        <v>13.58777063780318</v>
       </c>
       <c r="E753" t="n">
-        <v>13.64592127725712</v>
+        <v>13.64592034928656</v>
       </c>
       <c r="F753" t="n">
         <v>16007800</v>
@@ -15512,16 +15512,16 @@
         <v>45358</v>
       </c>
       <c r="B755" t="n">
-        <v>14.00451374053955</v>
+        <v>14.00451278686523</v>
       </c>
       <c r="C755" t="n">
-        <v>14.09173923467137</v>
+        <v>14.0917382750572</v>
       </c>
       <c r="D755" t="n">
-        <v>13.70407139883333</v>
+        <v>13.70407046561843</v>
       </c>
       <c r="E755" t="n">
-        <v>13.97543888391995</v>
+        <v>13.97543793222557</v>
       </c>
       <c r="F755" t="n">
         <v>6452500</v>
@@ -15532,16 +15532,16 @@
         <v>45359</v>
       </c>
       <c r="B756" t="n">
-        <v>13.96574687957764</v>
+        <v>13.96574592590332</v>
       </c>
       <c r="C756" t="n">
-        <v>14.09173915659519</v>
+        <v>14.09173819431728</v>
       </c>
       <c r="D756" t="n">
-        <v>13.70407132290505</v>
+        <v>13.70407038709969</v>
       </c>
       <c r="E756" t="n">
-        <v>13.86883038329161</v>
+        <v>13.8688294362354</v>
       </c>
       <c r="F756" t="n">
         <v>9093700</v>
@@ -15572,16 +15572,16 @@
         <v>45363</v>
       </c>
       <c r="B758" t="n">
-        <v>14.26619052886963</v>
+        <v>14.26618957519531</v>
       </c>
       <c r="C758" t="n">
-        <v>14.37279895494302</v>
+        <v>14.37279799414208</v>
       </c>
       <c r="D758" t="n">
-        <v>13.74283847712863</v>
+        <v>13.74283755843964</v>
       </c>
       <c r="E758" t="n">
-        <v>14.0045140408626</v>
+        <v>14.00451310468098</v>
       </c>
       <c r="F758" t="n">
         <v>5196700</v>
@@ -15592,16 +15592,16 @@
         <v>45364</v>
       </c>
       <c r="B759" t="n">
-        <v>14.24680614471436</v>
+        <v>14.24680709838867</v>
       </c>
       <c r="C759" t="n">
-        <v>14.47940684255526</v>
+        <v>14.47940781179976</v>
       </c>
       <c r="D759" t="n">
-        <v>14.16927257876739</v>
+        <v>14.16927352725164</v>
       </c>
       <c r="E759" t="n">
-        <v>14.19834743492925</v>
+        <v>14.19834838535976</v>
       </c>
       <c r="F759" t="n">
         <v>5340300</v>
@@ -15612,16 +15612,16 @@
         <v>45365</v>
       </c>
       <c r="B760" t="n">
-        <v>14.0917387008667</v>
+        <v>14.09173774719238</v>
       </c>
       <c r="C760" t="n">
-        <v>14.38249002886788</v>
+        <v>14.38248905551664</v>
       </c>
       <c r="D760" t="n">
-        <v>13.80098737286552</v>
+        <v>13.80098643886813</v>
       </c>
       <c r="E760" t="n">
-        <v>14.24680582932786</v>
+        <v>14.2468048651592</v>
       </c>
       <c r="F760" t="n">
         <v>10904800</v>
@@ -15652,16 +15652,16 @@
         <v>45369</v>
       </c>
       <c r="B762" t="n">
-        <v>14.01420497894287</v>
+        <v>14.01420593261719</v>
       </c>
       <c r="C762" t="n">
-        <v>14.28557245069638</v>
+        <v>14.2855734228374</v>
       </c>
       <c r="D762" t="n">
-        <v>13.95605434428777</v>
+        <v>13.9560552940049</v>
       </c>
       <c r="E762" t="n">
-        <v>14.21773081382625</v>
+        <v>14.21773178135061</v>
       </c>
       <c r="F762" t="n">
         <v>3894300</v>
@@ -15672,16 +15672,16 @@
         <v>45370</v>
       </c>
       <c r="B763" t="n">
-        <v>14.27588081359863</v>
+        <v>14.27588176727295</v>
       </c>
       <c r="C763" t="n">
-        <v>14.35341530280148</v>
+        <v>14.35341626165535</v>
       </c>
       <c r="D763" t="n">
-        <v>14.00451333634416</v>
+        <v>14.00451427189027</v>
       </c>
       <c r="E763" t="n">
-        <v>14.09173882795849</v>
+        <v>14.09173976933154</v>
       </c>
       <c r="F763" t="n">
         <v>3066400</v>
@@ -15732,16 +15732,16 @@
         <v>45373</v>
       </c>
       <c r="B766" t="n">
-        <v>13.92698097229004</v>
+        <v>13.92698001861572</v>
       </c>
       <c r="C766" t="n">
-        <v>14.37279947121457</v>
+        <v>14.37279848701205</v>
       </c>
       <c r="D766" t="n">
-        <v>13.92698097229004</v>
+        <v>13.92698001861572</v>
       </c>
       <c r="E766" t="n">
-        <v>14.25649911379161</v>
+        <v>14.25649813755297</v>
       </c>
       <c r="F766" t="n">
         <v>3379700</v>
@@ -15772,16 +15772,16 @@
         <v>45377</v>
       </c>
       <c r="B768" t="n">
-        <v>14.00451374053955</v>
+        <v>14.00451278686523</v>
       </c>
       <c r="C768" t="n">
-        <v>14.24680636900658</v>
+        <v>14.24680539883271</v>
       </c>
       <c r="D768" t="n">
-        <v>13.88821338978814</v>
+        <v>13.8882124440336</v>
       </c>
       <c r="E768" t="n">
-        <v>13.94636402730036</v>
+        <v>13.9463630775859</v>
       </c>
       <c r="F768" t="n">
         <v>4898500</v>
@@ -15812,16 +15812,16 @@
         <v>45379</v>
       </c>
       <c r="B770" t="n">
-        <v>14.25649738311768</v>
+        <v>14.25649833679199</v>
       </c>
       <c r="C770" t="n">
-        <v>14.73139068267979</v>
+        <v>14.73139166812162</v>
       </c>
       <c r="D770" t="n">
-        <v>14.25649738311768</v>
+        <v>14.25649833679199</v>
       </c>
       <c r="E770" t="n">
-        <v>14.45033128862538</v>
+        <v>14.45033225526602</v>
       </c>
       <c r="F770" t="n">
         <v>7122000</v>
@@ -15832,16 +15832,16 @@
         <v>45383</v>
       </c>
       <c r="B771" t="n">
-        <v>13.74283790588379</v>
+        <v>13.74283885955811</v>
       </c>
       <c r="C771" t="n">
-        <v>14.25649800910157</v>
+        <v>14.25649899842096</v>
       </c>
       <c r="D771" t="n">
-        <v>13.65561241350713</v>
+        <v>13.65561336112849</v>
       </c>
       <c r="E771" t="n">
-        <v>14.20803929952865</v>
+        <v>14.20804028548528</v>
       </c>
       <c r="F771" t="n">
         <v>14371700</v>
@@ -15872,16 +15872,16 @@
         <v>45385</v>
       </c>
       <c r="B773" t="n">
-        <v>13.56838607788086</v>
+        <v>13.56838703155518</v>
       </c>
       <c r="C773" t="n">
-        <v>13.70407027139793</v>
+        <v>13.70407123460901</v>
       </c>
       <c r="D773" t="n">
-        <v>13.31640154318042</v>
+        <v>13.31640247914363</v>
       </c>
       <c r="E773" t="n">
-        <v>13.63622771250292</v>
+        <v>13.63622867094559</v>
       </c>
       <c r="F773" t="n">
         <v>11886900</v>
@@ -15932,16 +15932,16 @@
         <v>45390</v>
       </c>
       <c r="B776" t="n">
-        <v>13.6846866607666</v>
+        <v>13.68468761444092</v>
       </c>
       <c r="C776" t="n">
-        <v>13.81067893034213</v>
+        <v>13.81067989279674</v>
       </c>
       <c r="D776" t="n">
-        <v>13.0450343108239</v>
+        <v>13.04503521992138</v>
       </c>
       <c r="E776" t="n">
-        <v>13.30670985204002</v>
+        <v>13.30671077937345</v>
       </c>
       <c r="F776" t="n">
         <v>17208100</v>
@@ -15972,16 +15972,16 @@
         <v>45392</v>
       </c>
       <c r="B778" t="n">
-        <v>13.80098724365234</v>
+        <v>13.80098819732666</v>
       </c>
       <c r="C778" t="n">
-        <v>14.17896405894233</v>
+        <v>14.17896503873556</v>
       </c>
       <c r="D778" t="n">
-        <v>13.79129531714601</v>
+        <v>13.7912962701506</v>
       </c>
       <c r="E778" t="n">
-        <v>14.04327986067267</v>
+        <v>14.04328083108987</v>
       </c>
       <c r="F778" t="n">
         <v>7408300</v>
@@ -15992,16 +15992,16 @@
         <v>45393</v>
       </c>
       <c r="B779" t="n">
-        <v>13.74283790588379</v>
+        <v>13.74283885955811</v>
       </c>
       <c r="C779" t="n">
-        <v>13.83975440075663</v>
+        <v>13.8397553611564</v>
       </c>
       <c r="D779" t="n">
-        <v>13.62653755747257</v>
+        <v>13.62653850307631</v>
       </c>
       <c r="E779" t="n">
-        <v>13.74283790588379</v>
+        <v>13.74283885955811</v>
       </c>
       <c r="F779" t="n">
         <v>5563300</v>
@@ -16012,16 +16012,16 @@
         <v>45394</v>
       </c>
       <c r="B780" t="n">
-        <v>13.5490026473999</v>
+        <v>13.54900360107422</v>
       </c>
       <c r="C780" t="n">
-        <v>13.8300629693518</v>
+        <v>13.83006394280913</v>
       </c>
       <c r="D780" t="n">
-        <v>13.51023586579843</v>
+        <v>13.51023681674407</v>
       </c>
       <c r="E780" t="n">
-        <v>13.6071532819386</v>
+        <v>13.60715423970597</v>
       </c>
       <c r="F780" t="n">
         <v>8459200</v>
@@ -16212,16 +16212,16 @@
         <v>45408</v>
       </c>
       <c r="B790" t="n">
-        <v>12.90935039520264</v>
+        <v>12.90935134887695</v>
       </c>
       <c r="C790" t="n">
-        <v>13.10318522908003</v>
+        <v>13.10318619707384</v>
       </c>
       <c r="D790" t="n">
-        <v>12.77366712061604</v>
+        <v>12.7736680642668</v>
       </c>
       <c r="E790" t="n">
-        <v>13.03534266751375</v>
+        <v>13.03534363049571</v>
       </c>
       <c r="F790" t="n">
         <v>14489900</v>
@@ -16372,16 +16372,16 @@
         <v>45421</v>
       </c>
       <c r="B798" t="n">
-        <v>13.0353422164917</v>
+        <v>13.03534317016602</v>
       </c>
       <c r="C798" t="n">
-        <v>13.07410899707125</v>
+        <v>13.07410995358177</v>
       </c>
       <c r="D798" t="n">
-        <v>12.72520797185527</v>
+        <v>12.72520890283996</v>
       </c>
       <c r="E798" t="n">
-        <v>12.88996702038661</v>
+        <v>12.88996796342518</v>
       </c>
       <c r="F798" t="n">
         <v>8332000</v>
@@ -16392,16 +16392,16 @@
         <v>45422</v>
       </c>
       <c r="B799" t="n">
-        <v>12.99657535552979</v>
+        <v>12.9965763092041</v>
       </c>
       <c r="C799" t="n">
-        <v>13.13225954885551</v>
+        <v>13.13226051248618</v>
       </c>
       <c r="D799" t="n">
-        <v>12.82212438186427</v>
+        <v>12.82212532273757</v>
       </c>
       <c r="E799" t="n">
-        <v>12.9868834293766</v>
+        <v>12.98688438233973</v>
       </c>
       <c r="F799" t="n">
         <v>9643100</v>
@@ -16432,16 +16432,16 @@
         <v>45426</v>
       </c>
       <c r="B801" t="n">
-        <v>12.7542839050293</v>
+        <v>12.75428295135498</v>
       </c>
       <c r="C801" t="n">
-        <v>12.96750167838812</v>
+        <v>12.9675007087709</v>
       </c>
       <c r="D801" t="n">
-        <v>12.66705841027919</v>
+        <v>12.66705746312697</v>
       </c>
       <c r="E801" t="n">
-        <v>12.84150939977941</v>
+        <v>12.84150843958299</v>
       </c>
       <c r="F801" t="n">
         <v>10701800</v>
@@ -16472,16 +16472,16 @@
         <v>45428</v>
       </c>
       <c r="B803" t="n">
-        <v>13.05472660064697</v>
+        <v>13.05472564697266</v>
       </c>
       <c r="C803" t="n">
-        <v>13.21948565588908</v>
+        <v>13.21948469017878</v>
       </c>
       <c r="D803" t="n">
-        <v>12.9481172565062</v>
+        <v>12.94811631061992</v>
       </c>
       <c r="E803" t="n">
-        <v>13.2001018026733</v>
+        <v>13.20010083837903</v>
       </c>
       <c r="F803" t="n">
         <v>4347100</v>
@@ -16492,16 +16492,16 @@
         <v>45429</v>
       </c>
       <c r="B804" t="n">
-        <v>13.20979404449463</v>
+        <v>13.20979499816895</v>
       </c>
       <c r="C804" t="n">
-        <v>13.2582527544174</v>
+        <v>13.25825371159017</v>
       </c>
       <c r="D804" t="n">
-        <v>12.97719334599296</v>
+        <v>12.97719428287479</v>
       </c>
       <c r="E804" t="n">
-        <v>12.99657627539826</v>
+        <v>12.99657721367943</v>
       </c>
       <c r="F804" t="n">
         <v>6205200</v>
@@ -16512,16 +16512,16 @@
         <v>45432</v>
       </c>
       <c r="B805" t="n">
-        <v>13.02565097808838</v>
+        <v>13.02565002441406</v>
       </c>
       <c r="C805" t="n">
-        <v>13.29701938074762</v>
+        <v>13.29701840720504</v>
       </c>
       <c r="D805" t="n">
-        <v>12.96750126628497</v>
+        <v>12.96750031686809</v>
       </c>
       <c r="E805" t="n">
-        <v>13.1516432526931</v>
+        <v>13.15164228979424</v>
       </c>
       <c r="F805" t="n">
         <v>6307000</v>
@@ -16732,16 +16732,16 @@
         <v>45448</v>
       </c>
       <c r="B816" t="n">
-        <v>11.70757961273193</v>
+        <v>11.70757865905762</v>
       </c>
       <c r="C816" t="n">
-        <v>12.07586451511291</v>
+        <v>12.0758635314389</v>
       </c>
       <c r="D816" t="n">
-        <v>11.63973797322884</v>
+        <v>11.63973702508076</v>
       </c>
       <c r="E816" t="n">
-        <v>11.67850475641247</v>
+        <v>11.67850380510653</v>
       </c>
       <c r="F816" t="n">
         <v>8966900</v>
@@ -16772,16 +16772,16 @@
         <v>45450</v>
       </c>
       <c r="B818" t="n">
-        <v>11.63004589080811</v>
+        <v>11.63004684448242</v>
       </c>
       <c r="C818" t="n">
-        <v>11.83357173086817</v>
+        <v>11.83357270123179</v>
       </c>
       <c r="D818" t="n">
-        <v>11.50405361607826</v>
+        <v>11.50405455942109</v>
       </c>
       <c r="E818" t="n">
-        <v>11.7366543120689</v>
+        <v>11.7366552744852</v>
       </c>
       <c r="F818" t="n">
         <v>7620600</v>
@@ -16812,16 +16812,16 @@
         <v>45454</v>
       </c>
       <c r="B820" t="n">
-        <v>11.63004589080811</v>
+        <v>11.63004684448242</v>
       </c>
       <c r="C820" t="n">
-        <v>11.69788752940379</v>
+        <v>11.69788848864118</v>
       </c>
       <c r="D820" t="n">
-        <v>11.47497876014768</v>
+        <v>11.47497970110635</v>
       </c>
       <c r="E820" t="n">
-        <v>11.56220425221242</v>
+        <v>11.56220520032366</v>
       </c>
       <c r="F820" t="n">
         <v>6029300</v>
@@ -16832,16 +16832,16 @@
         <v>45455</v>
       </c>
       <c r="B821" t="n">
-        <v>11.43621253967285</v>
+        <v>11.43621158599854</v>
       </c>
       <c r="C821" t="n">
-        <v>11.84326423980314</v>
+        <v>11.84326325218448</v>
       </c>
       <c r="D821" t="n">
-        <v>11.34898704332021</v>
+        <v>11.34898609691969</v>
       </c>
       <c r="E821" t="n">
-        <v>11.77542167359939</v>
+        <v>11.77542069163817</v>
       </c>
       <c r="F821" t="n">
         <v>19599700</v>
@@ -16852,16 +16852,16 @@
         <v>45456</v>
       </c>
       <c r="B822" t="n">
-        <v>11.21330261230469</v>
+        <v>11.21330165863037</v>
       </c>
       <c r="C822" t="n">
-        <v>11.48467102317973</v>
+        <v>11.48467004642594</v>
       </c>
       <c r="D822" t="n">
-        <v>11.18422775552273</v>
+        <v>11.18422680432119</v>
       </c>
       <c r="E822" t="n">
-        <v>11.3877536015425</v>
+        <v>11.38775263303139</v>
       </c>
       <c r="F822" t="n">
         <v>6392900</v>
@@ -17032,16 +17032,16 @@
         <v>45469</v>
       </c>
       <c r="B831" t="n">
-        <v>10.35074234008789</v>
+        <v>10.35074138641357</v>
       </c>
       <c r="C831" t="n">
-        <v>10.58334306307854</v>
+        <v>10.58334208797336</v>
       </c>
       <c r="D831" t="n">
-        <v>10.25382491003857</v>
+        <v>10.25382396529382</v>
       </c>
       <c r="E831" t="n">
-        <v>10.57365113521898</v>
+        <v>10.57365016100677</v>
       </c>
       <c r="F831" t="n">
         <v>18723900</v>
@@ -17052,16 +17052,16 @@
         <v>45470</v>
       </c>
       <c r="B832" t="n">
-        <v>10.49611663818359</v>
+        <v>10.49611568450928</v>
       </c>
       <c r="C832" t="n">
-        <v>10.49611663818359</v>
+        <v>10.49611568450928</v>
       </c>
       <c r="D832" t="n">
-        <v>10.12783173035415</v>
+        <v>10.1278308101421</v>
       </c>
       <c r="E832" t="n">
-        <v>10.34104950315499</v>
+        <v>10.34104856357003</v>
       </c>
       <c r="F832" t="n">
         <v>16356000</v>
@@ -17092,16 +17092,16 @@
         <v>45474</v>
       </c>
       <c r="B834" t="n">
-        <v>9.691705703735352</v>
+        <v>9.691704750061035</v>
       </c>
       <c r="C834" t="n">
-        <v>10.08906548970481</v>
+        <v>10.08906449692986</v>
       </c>
       <c r="D834" t="n">
-        <v>9.594788276988766</v>
+        <v>9.594787332851229</v>
       </c>
       <c r="E834" t="n">
-        <v>9.982457059702028</v>
+        <v>9.982456077417465</v>
       </c>
       <c r="F834" t="n">
         <v>19240000</v>
@@ -17192,16 +17192,16 @@
         <v>45481</v>
       </c>
       <c r="B839" t="n">
-        <v>11.27145290374756</v>
+        <v>11.27145195007324</v>
       </c>
       <c r="C839" t="n">
-        <v>11.33929454224489</v>
+        <v>11.33929358283052</v>
       </c>
       <c r="D839" t="n">
-        <v>10.9613186428763</v>
+        <v>10.96131771544235</v>
       </c>
       <c r="E839" t="n">
-        <v>10.9613186428763</v>
+        <v>10.96131771544235</v>
       </c>
       <c r="F839" t="n">
         <v>12616400</v>
@@ -17212,16 +17212,16 @@
         <v>45482</v>
       </c>
       <c r="B840" t="n">
-        <v>11.12607669830322</v>
+        <v>11.12607765197754</v>
       </c>
       <c r="C840" t="n">
-        <v>11.36836931899038</v>
+        <v>11.36837029343287</v>
       </c>
       <c r="D840" t="n">
-        <v>11.0970018426172</v>
+        <v>11.09700279379936</v>
       </c>
       <c r="E840" t="n">
-        <v>11.26176089862631</v>
+        <v>11.26176186393083</v>
       </c>
       <c r="F840" t="n">
         <v>14484000</v>
@@ -17232,16 +17232,16 @@
         <v>45483</v>
       </c>
       <c r="B841" t="n">
-        <v>10.95162582397461</v>
+        <v>10.95162677764893</v>
       </c>
       <c r="C841" t="n">
-        <v>11.24237713199167</v>
+        <v>11.24237811098479</v>
       </c>
       <c r="D841" t="n">
-        <v>10.91285904452386</v>
+        <v>10.91285999482234</v>
       </c>
       <c r="E841" t="n">
-        <v>11.19391842661001</v>
+        <v>11.19391940138331</v>
       </c>
       <c r="F841" t="n">
         <v>14212100</v>
@@ -17252,16 +17252,16 @@
         <v>45484</v>
       </c>
       <c r="B842" t="n">
-        <v>10.90316867828369</v>
+        <v>10.90316772460938</v>
       </c>
       <c r="C842" t="n">
-        <v>11.2229948855715</v>
+        <v>11.22299390392275</v>
       </c>
       <c r="D842" t="n">
-        <v>10.72871768366377</v>
+        <v>10.72871674524827</v>
       </c>
       <c r="E842" t="n">
-        <v>11.09700260326523</v>
+        <v>11.09700163263672</v>
       </c>
       <c r="F842" t="n">
         <v>13851900</v>
@@ -17272,16 +17272,16 @@
         <v>45485</v>
       </c>
       <c r="B843" t="n">
-        <v>10.89347553253174</v>
+        <v>10.89347648620605</v>
       </c>
       <c r="C843" t="n">
-        <v>11.00977587451248</v>
+        <v>11.00977683836836</v>
       </c>
       <c r="D843" t="n">
-        <v>10.7868671167843</v>
+        <v>10.78686806112553</v>
       </c>
       <c r="E843" t="n">
-        <v>10.90316745876504</v>
+        <v>10.90316841328784</v>
       </c>
       <c r="F843" t="n">
         <v>11713600</v>
@@ -17312,16 +17312,16 @@
         <v>45489</v>
       </c>
       <c r="B845" t="n">
-        <v>10.76748371124268</v>
+        <v>10.76748275756836</v>
       </c>
       <c r="C845" t="n">
-        <v>10.90316791132185</v>
+        <v>10.90316694563</v>
       </c>
       <c r="D845" t="n">
-        <v>10.69964207333959</v>
+        <v>10.69964112567399</v>
       </c>
       <c r="E845" t="n">
-        <v>10.76748371124268</v>
+        <v>10.76748275756836</v>
       </c>
       <c r="F845" t="n">
         <v>9437300</v>
@@ -17332,16 +17332,16 @@
         <v>45490</v>
       </c>
       <c r="B846" t="n">
-        <v>10.41858196258545</v>
+        <v>10.41858291625977</v>
       </c>
       <c r="C846" t="n">
-        <v>10.82563361087946</v>
+        <v>10.82563460181362</v>
       </c>
       <c r="D846" t="n">
-        <v>10.41858196258545</v>
+        <v>10.41858291625977</v>
       </c>
       <c r="E846" t="n">
-        <v>10.7577919775881</v>
+        <v>10.75779296231231</v>
       </c>
       <c r="F846" t="n">
         <v>8121300</v>
@@ -17352,16 +17352,16 @@
         <v>45491</v>
       </c>
       <c r="B847" t="n">
-        <v>10.0890645980835</v>
+        <v>10.08906555175781</v>
       </c>
       <c r="C847" t="n">
-        <v>10.41858271077302</v>
+        <v>10.41858369559522</v>
       </c>
       <c r="D847" t="n">
-        <v>10.05029781566549</v>
+        <v>10.05029876567536</v>
       </c>
       <c r="E847" t="n">
-        <v>10.41858271077302</v>
+        <v>10.41858369559522</v>
       </c>
       <c r="F847" t="n">
         <v>10952400</v>
@@ -17392,16 +17392,16 @@
         <v>45495</v>
       </c>
       <c r="B849" t="n">
-        <v>10.37012481689453</v>
+        <v>10.37012386322021</v>
       </c>
       <c r="C849" t="n">
-        <v>10.44765838782558</v>
+        <v>10.44765742702099</v>
       </c>
       <c r="D849" t="n">
-        <v>10.22474960246709</v>
+        <v>10.22474866216201</v>
       </c>
       <c r="E849" t="n">
-        <v>10.22474960246709</v>
+        <v>10.22474866216201</v>
       </c>
       <c r="F849" t="n">
         <v>6418700</v>
@@ -17432,16 +17432,16 @@
         <v>45497</v>
       </c>
       <c r="B851" t="n">
-        <v>9.691705703735352</v>
+        <v>9.691704750061035</v>
       </c>
       <c r="C851" t="n">
-        <v>10.26351648813943</v>
+        <v>10.26351547819831</v>
       </c>
       <c r="D851" t="n">
-        <v>9.691705703735352</v>
+        <v>9.691704750061035</v>
       </c>
       <c r="E851" t="n">
-        <v>10.09875741723408</v>
+        <v>10.09875642350544</v>
       </c>
       <c r="F851" t="n">
         <v>20101500</v>
@@ -17552,16 +17552,16 @@
         <v>45505</v>
       </c>
       <c r="B857" t="n">
-        <v>9.604479789733887</v>
+        <v>9.60447883605957</v>
       </c>
       <c r="C857" t="n">
-        <v>9.769238853523861</v>
+        <v>9.769237883489836</v>
       </c>
       <c r="D857" t="n">
-        <v>9.517254294283541</v>
+        <v>9.517253349270259</v>
       </c>
       <c r="E857" t="n">
-        <v>9.565713005564071</v>
+        <v>9.565712055739093</v>
       </c>
       <c r="F857" t="n">
         <v>16979700</v>
@@ -17572,16 +17572,16 @@
         <v>45506</v>
       </c>
       <c r="B858" t="n">
-        <v>9.885538101196289</v>
+        <v>9.885539054870605</v>
       </c>
       <c r="C858" t="n">
-        <v>9.953380659115961</v>
+        <v>9.953381619335163</v>
       </c>
       <c r="D858" t="n">
-        <v>9.585095788526804</v>
+        <v>9.58509671321695</v>
       </c>
       <c r="E858" t="n">
-        <v>9.604478716308897</v>
+        <v>9.604479642868947</v>
       </c>
       <c r="F858" t="n">
         <v>10117700</v>
@@ -17672,16 +17672,16 @@
         <v>45513</v>
       </c>
       <c r="B863" t="n">
-        <v>9.953380584716797</v>
+        <v>9.953381538391113</v>
       </c>
       <c r="C863" t="n">
-        <v>10.13752255649849</v>
+        <v>10.1375235278162</v>
       </c>
       <c r="D863" t="n">
-        <v>9.662629275975187</v>
+        <v>9.662630201791425</v>
       </c>
       <c r="E863" t="n">
-        <v>10.12783063054342</v>
+        <v>10.12783160093251</v>
       </c>
       <c r="F863" t="n">
         <v>24889300</v>
@@ -17812,16 +17812,16 @@
         <v>45524</v>
       </c>
       <c r="B870" t="n">
-        <v>9.904923439025879</v>
+        <v>9.904922485351562</v>
       </c>
       <c r="C870" t="n">
-        <v>10.38950872181597</v>
+        <v>10.3895077214844</v>
       </c>
       <c r="D870" t="n">
-        <v>9.904923439025879</v>
+        <v>9.904922485351562</v>
       </c>
       <c r="E870" t="n">
-        <v>10.37981679433463</v>
+        <v>10.37981579493622</v>
       </c>
       <c r="F870" t="n">
         <v>10092800</v>
@@ -17872,16 +17872,16 @@
         <v>45527</v>
       </c>
       <c r="B873" t="n">
-        <v>9.430028915405273</v>
+        <v>9.430027961730957</v>
       </c>
       <c r="C873" t="n">
-        <v>9.633554765881009</v>
+        <v>9.633553791623788</v>
       </c>
       <c r="D873" t="n">
-        <v>9.381571127798761</v>
+        <v>9.38157017902506</v>
       </c>
       <c r="E873" t="n">
-        <v>9.517254411933882</v>
+        <v>9.517253449438307</v>
       </c>
       <c r="F873" t="n">
         <v>14322600</v>
@@ -17952,16 +17952,16 @@
         <v>45533</v>
       </c>
       <c r="B877" t="n">
-        <v>9.071435928344727</v>
+        <v>9.07143497467041</v>
       </c>
       <c r="C877" t="n">
-        <v>9.294345633330934</v>
+        <v>9.294344656222261</v>
       </c>
       <c r="D877" t="n">
-        <v>8.838835220398899</v>
+        <v>8.838834291177749</v>
       </c>
       <c r="E877" t="n">
-        <v>9.294345633330934</v>
+        <v>9.294344656222261</v>
       </c>
       <c r="F877" t="n">
         <v>21733300</v>
@@ -18012,16 +18012,16 @@
         <v>45538</v>
       </c>
       <c r="B880" t="n">
-        <v>9.691705703735352</v>
+        <v>9.691704750061035</v>
       </c>
       <c r="C880" t="n">
-        <v>9.817697988796681</v>
+        <v>9.817697022724587</v>
       </c>
       <c r="D880" t="n">
-        <v>9.497871774515261</v>
+        <v>9.497870839914412</v>
       </c>
       <c r="E880" t="n">
-        <v>9.556021491144747</v>
+        <v>9.556020550821904</v>
       </c>
       <c r="F880" t="n">
         <v>16401400</v>
@@ -18032,16 +18032,16 @@
         <v>45539</v>
       </c>
       <c r="B881" t="n">
-        <v>9.672320365905762</v>
+        <v>9.672321319580078</v>
       </c>
       <c r="C881" t="n">
-        <v>10.05029716314574</v>
+        <v>10.05029815408792</v>
       </c>
       <c r="D881" t="n">
-        <v>9.652937438091705</v>
+        <v>9.652938389854897</v>
       </c>
       <c r="E881" t="n">
-        <v>9.730470997893812</v>
+        <v>9.730471957301681</v>
       </c>
       <c r="F881" t="n">
         <v>19605600</v>
@@ -18072,16 +18072,16 @@
         <v>45541</v>
       </c>
       <c r="B883" t="n">
-        <v>9.158660888671875</v>
+        <v>9.158659934997559</v>
       </c>
       <c r="C883" t="n">
-        <v>9.352494800611487</v>
+        <v>9.352493826753605</v>
       </c>
       <c r="D883" t="n">
-        <v>9.09081925056126</v>
+        <v>9.090818303951167</v>
       </c>
       <c r="E883" t="n">
-        <v>9.304037015831332</v>
+        <v>9.30403604701927</v>
       </c>
       <c r="F883" t="n">
         <v>16796100</v>
@@ -18112,16 +18112,16 @@
         <v>45545</v>
       </c>
       <c r="B885" t="n">
-        <v>8.625617027282715</v>
+        <v>8.625616073608398</v>
       </c>
       <c r="C885" t="n">
-        <v>8.896985431091611</v>
+        <v>8.896984447413983</v>
       </c>
       <c r="D885" t="n">
-        <v>8.528700532442116</v>
+        <v>8.52869958948318</v>
       </c>
       <c r="E885" t="n">
-        <v>8.896985431091611</v>
+        <v>8.896984447413983</v>
       </c>
       <c r="F885" t="n">
         <v>19808800</v>
@@ -18192,16 +18192,16 @@
         <v>45551</v>
       </c>
       <c r="B889" t="n">
-        <v>8.480240821838379</v>
+        <v>8.480241775512695</v>
       </c>
       <c r="C889" t="n">
-        <v>8.703149565504281</v>
+        <v>8.703150544246558</v>
       </c>
       <c r="D889" t="n">
-        <v>8.480240821838379</v>
+        <v>8.480241775512695</v>
       </c>
       <c r="E889" t="n">
-        <v>8.567466303889523</v>
+        <v>8.567467267373077</v>
       </c>
       <c r="F889" t="n">
         <v>13539000</v>
@@ -18332,16 +18332,16 @@
         <v>45560</v>
       </c>
       <c r="B896" t="n">
-        <v>7.540146350860596</v>
+        <v>7.540146827697754</v>
       </c>
       <c r="C896" t="n">
-        <v>7.850281063143172</v>
+        <v>7.85028155959318</v>
       </c>
       <c r="D896" t="n">
-        <v>7.472304252572895</v>
+        <v>7.472304725119734</v>
       </c>
       <c r="E896" t="n">
-        <v>7.801822355489603</v>
+        <v>7.801822848875092</v>
       </c>
       <c r="F896" t="n">
         <v>30722700</v>
@@ -18352,16 +18352,16 @@
         <v>45561</v>
       </c>
       <c r="B897" t="n">
-        <v>7.801822662353516</v>
+        <v>7.801822185516357</v>
       </c>
       <c r="C897" t="n">
-        <v>7.8696643011731</v>
+        <v>7.86966382018955</v>
       </c>
       <c r="D897" t="n">
-        <v>7.54983811206219</v>
+        <v>7.549837650625997</v>
       </c>
       <c r="E897" t="n">
-        <v>7.559530038828704</v>
+        <v>7.559529576800154</v>
       </c>
       <c r="F897" t="n">
         <v>14720200</v>
@@ -18372,16 +18372,16 @@
         <v>45562</v>
       </c>
       <c r="B898" t="n">
-        <v>7.869663715362549</v>
+        <v>7.869664192199707</v>
       </c>
       <c r="C898" t="n">
-        <v>7.966581127267234</v>
+        <v>7.966581609976793</v>
       </c>
       <c r="D898" t="n">
-        <v>7.753363375640691</v>
+        <v>7.753363845431002</v>
       </c>
       <c r="E898" t="n">
-        <v>7.753363375640691</v>
+        <v>7.753363845431002</v>
       </c>
       <c r="F898" t="n">
         <v>13583900</v>
@@ -18392,16 +18392,16 @@
         <v>45565</v>
       </c>
       <c r="B899" t="n">
-        <v>7.23970365524292</v>
+        <v>7.239703178405762</v>
       </c>
       <c r="C899" t="n">
-        <v>7.666138743868849</v>
+        <v>7.666138238944893</v>
       </c>
       <c r="D899" t="n">
-        <v>7.055561661236209</v>
+        <v>7.055561196527413</v>
       </c>
       <c r="E899" t="n">
-        <v>7.569221783303075</v>
+        <v>7.569221284762475</v>
       </c>
       <c r="F899" t="n">
         <v>49266200</v>
@@ -18412,16 +18412,16 @@
         <v>45566</v>
       </c>
       <c r="B900" t="n">
-        <v>6.900493621826172</v>
+        <v>6.90049409866333</v>
       </c>
       <c r="C900" t="n">
-        <v>7.356004000620823</v>
+        <v>7.35600450893461</v>
       </c>
       <c r="D900" t="n">
-        <v>6.900493621826172</v>
+        <v>6.90049409866333</v>
       </c>
       <c r="E900" t="n">
-        <v>7.288161901485994</v>
+        <v>7.288162405111764</v>
       </c>
       <c r="F900" t="n">
         <v>31533300</v>
@@ -18472,16 +18472,16 @@
         <v>45569</v>
       </c>
       <c r="B903" t="n">
-        <v>6.755117893218994</v>
+        <v>6.755118370056152</v>
       </c>
       <c r="C903" t="n">
-        <v>6.813268527416111</v>
+        <v>6.813269008358065</v>
       </c>
       <c r="D903" t="n">
-        <v>6.464367032915849</v>
+        <v>6.464367489229188</v>
       </c>
       <c r="E903" t="n">
-        <v>6.512825278564796</v>
+        <v>6.512825738298756</v>
       </c>
       <c r="F903" t="n">
         <v>23862600</v>
@@ -18512,16 +18512,16 @@
         <v>45573</v>
       </c>
       <c r="B905" t="n">
-        <v>6.609743118286133</v>
+        <v>6.609742641448975</v>
       </c>
       <c r="C905" t="n">
-        <v>6.648509902147569</v>
+        <v>6.648509422513715</v>
       </c>
       <c r="D905" t="n">
-        <v>6.512825696496025</v>
+        <v>6.512825226650641</v>
       </c>
       <c r="E905" t="n">
-        <v>6.551592942493978</v>
+        <v>6.551592469851864</v>
       </c>
       <c r="F905" t="n">
         <v>17971800</v>
@@ -18572,16 +18572,16 @@
         <v>45576</v>
       </c>
       <c r="B908" t="n">
-        <v>6.512825489044189</v>
+        <v>6.512825012207031</v>
       </c>
       <c r="C908" t="n">
-        <v>6.541900807082394</v>
+        <v>6.541900328116484</v>
       </c>
       <c r="D908" t="n">
-        <v>6.231766083933051</v>
+        <v>6.231765627673685</v>
       </c>
       <c r="E908" t="n">
-        <v>6.435291923790979</v>
+        <v>6.435291452630448</v>
       </c>
       <c r="F908" t="n">
         <v>16985100</v>
@@ -18632,16 +18632,16 @@
         <v>45581</v>
       </c>
       <c r="B911" t="n">
-        <v>6.900493621826172</v>
+        <v>6.90049409866333</v>
       </c>
       <c r="C911" t="n">
-        <v>6.939260403578505</v>
+        <v>6.939260883094521</v>
       </c>
       <c r="D911" t="n">
-        <v>6.667892931312173</v>
+        <v>6.667893392076184</v>
       </c>
       <c r="E911" t="n">
-        <v>6.822960058321506</v>
+        <v>6.822960529800948</v>
       </c>
       <c r="F911" t="n">
         <v>22035800</v>
@@ -18652,16 +18652,16 @@
         <v>45582</v>
       </c>
       <c r="B912" t="n">
-        <v>6.842343330383301</v>
+        <v>6.842343807220459</v>
       </c>
       <c r="C912" t="n">
-        <v>6.852035256721334</v>
+        <v>6.852035734233914</v>
       </c>
       <c r="D912" t="n">
-        <v>6.687276206066643</v>
+        <v>6.687276672097303</v>
       </c>
       <c r="E912" t="n">
-        <v>6.764809768224971</v>
+        <v>6.764810239658881</v>
       </c>
       <c r="F912" t="n">
         <v>17844000</v>
@@ -18672,16 +18672,16 @@
         <v>45583</v>
       </c>
       <c r="B913" t="n">
-        <v>6.871418952941895</v>
+        <v>6.871419429779053</v>
       </c>
       <c r="C913" t="n">
-        <v>7.007102692754978</v>
+        <v>7.007103179007811</v>
       </c>
       <c r="D913" t="n">
-        <v>6.755118142394176</v>
+        <v>6.755118611160723</v>
       </c>
       <c r="E913" t="n">
-        <v>6.881110417574576</v>
+        <v>6.881110895084267</v>
       </c>
       <c r="F913" t="n">
         <v>25498900</v>
@@ -18692,16 +18692,16 @@
         <v>45586</v>
       </c>
       <c r="B914" t="n">
-        <v>7.007102489471436</v>
+        <v>7.007102966308594</v>
       </c>
       <c r="C914" t="n">
-        <v>7.11371137015713</v>
+        <v>7.113711854249081</v>
       </c>
       <c r="D914" t="n">
-        <v>6.83265197191561</v>
+        <v>6.832652436881316</v>
       </c>
       <c r="E914" t="n">
-        <v>6.900493608785741</v>
+        <v>6.900494078368107</v>
       </c>
       <c r="F914" t="n">
         <v>20497200</v>
@@ -18732,16 +18732,16 @@
         <v>45588</v>
       </c>
       <c r="B916" t="n">
-        <v>7.04586935043335</v>
+        <v>7.045868873596191</v>
       </c>
       <c r="C916" t="n">
-        <v>7.239703261009804</v>
+        <v>7.239702771054718</v>
       </c>
       <c r="D916" t="n">
-        <v>6.929569004087476</v>
+        <v>6.929568535121075</v>
       </c>
       <c r="E916" t="n">
-        <v>7.007102568318058</v>
+        <v>7.007102094104486</v>
       </c>
       <c r="F916" t="n">
         <v>16495300</v>
@@ -18752,16 +18752,16 @@
         <v>45589</v>
       </c>
       <c r="B917" t="n">
-        <v>7.23970365524292</v>
+        <v>7.239703178405762</v>
       </c>
       <c r="C917" t="n">
-        <v>7.259087047356075</v>
+        <v>7.259086569242245</v>
       </c>
       <c r="D917" t="n">
-        <v>6.929569381432441</v>
+        <v>6.929568925022024</v>
       </c>
       <c r="E917" t="n">
-        <v>7.00710294988506</v>
+        <v>7.007102488367958</v>
       </c>
       <c r="F917" t="n">
         <v>17525100</v>
@@ -18772,16 +18772,16 @@
         <v>45590</v>
       </c>
       <c r="B918" t="n">
-        <v>7.04586935043335</v>
+        <v>7.045868873596191</v>
       </c>
       <c r="C918" t="n">
-        <v>7.297853896319237</v>
+        <v>7.297853402428741</v>
       </c>
       <c r="D918" t="n">
-        <v>7.026485959375703</v>
+        <v>7.026485483850339</v>
       </c>
       <c r="E918" t="n">
-        <v>7.278470505261592</v>
+        <v>7.278470012682888</v>
       </c>
       <c r="F918" t="n">
         <v>15271300</v>
@@ -18832,16 +18832,16 @@
         <v>45595</v>
       </c>
       <c r="B921" t="n">
-        <v>7.443228721618652</v>
+        <v>7.443229198455811</v>
       </c>
       <c r="C921" t="n">
-        <v>7.598296304371199</v>
+        <v>7.598296791142485</v>
       </c>
       <c r="D921" t="n">
-        <v>7.249394820848559</v>
+        <v>7.249395285268095</v>
       </c>
       <c r="E921" t="n">
-        <v>7.317236917186328</v>
+        <v>7.317237385952047</v>
       </c>
       <c r="F921" t="n">
         <v>17976200</v>
@@ -18912,16 +18912,16 @@
         <v>45601</v>
       </c>
       <c r="B925" t="n">
-        <v>7.443228721618652</v>
+        <v>7.443229198455811</v>
       </c>
       <c r="C925" t="n">
-        <v>7.569220988187449</v>
+        <v>7.569221473096077</v>
       </c>
       <c r="D925" t="n">
-        <v>7.191244650617532</v>
+        <v>7.191245111311781</v>
       </c>
       <c r="E925" t="n">
-        <v>7.472304037802402</v>
+        <v>7.472304516502219</v>
       </c>
       <c r="F925" t="n">
         <v>13215900</v>
@@ -19052,16 +19052,16 @@
         <v>45610</v>
       </c>
       <c r="B932" t="n">
-        <v>6.842343330383301</v>
+        <v>6.842343807220459</v>
       </c>
       <c r="C932" t="n">
-        <v>6.948952209419245</v>
+        <v>6.948952693685886</v>
       </c>
       <c r="D932" t="n">
-        <v>6.726042987145807</v>
+        <v>6.726043455878092</v>
       </c>
       <c r="E932" t="n">
-        <v>6.793885085102587</v>
+        <v>6.793885558562731</v>
       </c>
       <c r="F932" t="n">
         <v>20675000</v>
@@ -19092,16 +19092,16 @@
         <v>45615</v>
       </c>
       <c r="B934" t="n">
-        <v>6.755117893218994</v>
+        <v>6.755118370056152</v>
       </c>
       <c r="C934" t="n">
-        <v>7.123402778406132</v>
+        <v>7.12340328124016</v>
       </c>
       <c r="D934" t="n">
-        <v>6.755117893218994</v>
+        <v>6.755118370056152</v>
       </c>
       <c r="E934" t="n">
-        <v>6.968335652911121</v>
+        <v>6.968336144799112</v>
       </c>
       <c r="F934" t="n">
         <v>23825500</v>
@@ -19172,16 +19172,16 @@
         <v>45622</v>
       </c>
       <c r="B938" t="n">
-        <v>7.646754741668701</v>
+        <v>7.646755218505859</v>
       </c>
       <c r="C938" t="n">
-        <v>7.724288303935401</v>
+        <v>7.724288785607405</v>
       </c>
       <c r="D938" t="n">
-        <v>7.239703077632047</v>
+        <v>7.239703529086233</v>
       </c>
       <c r="E938" t="n">
-        <v>7.239703077632047</v>
+        <v>7.239703529086233</v>
       </c>
       <c r="F938" t="n">
         <v>34068500</v>
@@ -19272,16 +19272,16 @@
         <v>45629</v>
       </c>
       <c r="B943" t="n">
-        <v>6.231765747070312</v>
+        <v>6.231766223907471</v>
       </c>
       <c r="C943" t="n">
-        <v>6.444983502127498</v>
+        <v>6.444983995279478</v>
       </c>
       <c r="D943" t="n">
-        <v>6.134848795742718</v>
+        <v>6.134849265164064</v>
       </c>
       <c r="E943" t="n">
-        <v>6.309299770268865</v>
+        <v>6.309300253038709</v>
       </c>
       <c r="F943" t="n">
         <v>16180200</v>
@@ -19332,16 +19332,16 @@
         <v>45632</v>
       </c>
       <c r="B946" t="n">
-        <v>5.970090389251709</v>
+        <v>5.970089912414551</v>
       </c>
       <c r="C946" t="n">
-        <v>6.464367587366049</v>
+        <v>6.464367071050471</v>
       </c>
       <c r="D946" t="n">
-        <v>5.970090389251709</v>
+        <v>5.970089912414551</v>
       </c>
       <c r="E946" t="n">
-        <v>6.31899191367733</v>
+        <v>6.318991408973054</v>
       </c>
       <c r="F946" t="n">
         <v>18084600</v>
@@ -19352,16 +19352,16 @@
         <v>45635</v>
       </c>
       <c r="B947" t="n">
-        <v>5.873173236846924</v>
+        <v>5.873172760009766</v>
       </c>
       <c r="C947" t="n">
-        <v>6.008856978888051</v>
+        <v>6.008856491034863</v>
       </c>
       <c r="D947" t="n">
-        <v>5.776256278246119</v>
+        <v>5.776255809277553</v>
       </c>
       <c r="E947" t="n">
-        <v>5.98947358716789</v>
+        <v>5.989473100888421</v>
       </c>
       <c r="F947" t="n">
         <v>18041800</v>
@@ -19372,16 +19372,16 @@
         <v>45636</v>
       </c>
       <c r="B948" t="n">
-        <v>6.144540786743164</v>
+        <v>6.144541263580322</v>
       </c>
       <c r="C948" t="n">
-        <v>6.202690958152964</v>
+        <v>6.202691439502773</v>
       </c>
       <c r="D948" t="n">
-        <v>5.911939638967481</v>
+        <v>5.911940097754003</v>
       </c>
       <c r="E948" t="n">
-        <v>5.960398346210555</v>
+        <v>5.960398808757637</v>
       </c>
       <c r="F948" t="n">
         <v>21640400</v>
@@ -19412,16 +19412,16 @@
         <v>45638</v>
       </c>
       <c r="B950" t="n">
-        <v>5.873173236846924</v>
+        <v>5.873172760009766</v>
       </c>
       <c r="C950" t="n">
-        <v>6.086391007905207</v>
+        <v>6.086390513757107</v>
       </c>
       <c r="D950" t="n">
-        <v>5.737489494805797</v>
+        <v>5.737489028984668</v>
       </c>
       <c r="E950" t="n">
-        <v>6.047623762328373</v>
+        <v>6.047623271327748</v>
       </c>
       <c r="F950" t="n">
         <v>28228300</v>
@@ -19452,16 +19452,16 @@
         <v>45642</v>
       </c>
       <c r="B952" t="n">
-        <v>5.233520984649658</v>
+        <v>5.2335205078125</v>
       </c>
       <c r="C952" t="n">
-        <v>5.630880756360631</v>
+        <v>5.630880243319184</v>
       </c>
       <c r="D952" t="n">
-        <v>5.233520984649658</v>
+        <v>5.2335205078125</v>
       </c>
       <c r="E952" t="n">
-        <v>5.592113971907684</v>
+        <v>5.592113462398361</v>
       </c>
       <c r="F952" t="n">
         <v>32238500</v>
@@ -19472,16 +19472,16 @@
         <v>45643</v>
       </c>
       <c r="B953" t="n">
-        <v>5.340129375457764</v>
+        <v>5.340129852294922</v>
       </c>
       <c r="C953" t="n">
-        <v>5.398279546719705</v>
+        <v>5.398280028749276</v>
       </c>
       <c r="D953" t="n">
-        <v>5.146295009114813</v>
+        <v>5.146295468643883</v>
       </c>
       <c r="E953" t="n">
-        <v>5.243211961218048</v>
+        <v>5.243212429401142</v>
       </c>
       <c r="F953" t="n">
         <v>32812100</v>
@@ -19492,16 +19492,16 @@
         <v>45644</v>
       </c>
       <c r="B954" t="n">
-        <v>4.981536388397217</v>
+        <v>4.981535911560059</v>
       </c>
       <c r="C954" t="n">
-        <v>5.340129835259944</v>
+        <v>5.340129324097897</v>
       </c>
       <c r="D954" t="n">
-        <v>4.894311355062193</v>
+        <v>4.894310886574293</v>
       </c>
       <c r="E954" t="n">
-        <v>5.23352094769878</v>
+        <v>5.233520446741433</v>
       </c>
       <c r="F954" t="n">
         <v>36135800</v>
@@ -19632,16 +19632,16 @@
         <v>45659</v>
       </c>
       <c r="B961" t="n">
-        <v>5.281979560852051</v>
+        <v>5.281979084014893</v>
       </c>
       <c r="C961" t="n">
-        <v>5.437047170391708</v>
+        <v>5.437046679555632</v>
       </c>
       <c r="D961" t="n">
-        <v>5.194754521506081</v>
+        <v>5.194754052543269</v>
       </c>
       <c r="E961" t="n">
-        <v>5.427355242610738</v>
+        <v>5.427354752649612</v>
       </c>
       <c r="F961" t="n">
         <v>15340600</v>
@@ -19692,16 +19692,16 @@
         <v>45664</v>
       </c>
       <c r="B964" t="n">
-        <v>5.714285850524902</v>
+        <v>5.714285373687744</v>
       </c>
       <c r="C964" t="n">
-        <v>5.793103508635817</v>
+        <v>5.793103025221601</v>
       </c>
       <c r="D964" t="n">
-        <v>5.566502506671788</v>
+        <v>5.566502042166633</v>
       </c>
       <c r="E964" t="n">
-        <v>5.704433408365889</v>
+        <v>5.704432932350882</v>
       </c>
       <c r="F964" t="n">
         <v>22063000</v>
@@ -19752,16 +19752,16 @@
         <v>45667</v>
       </c>
       <c r="B967" t="n">
-        <v>5.536945343017578</v>
+        <v>5.536945819854736</v>
       </c>
       <c r="C967" t="n">
-        <v>5.60591102493633</v>
+        <v>5.605911507712756</v>
       </c>
       <c r="D967" t="n">
-        <v>5.399014448970347</v>
+        <v>5.399014913929011</v>
       </c>
       <c r="E967" t="n">
-        <v>5.536945343017578</v>
+        <v>5.536945819854736</v>
       </c>
       <c r="F967" t="n">
         <v>14811000</v>
@@ -19792,16 +19792,16 @@
         <v>45671</v>
       </c>
       <c r="B969" t="n">
-        <v>5.320197105407715</v>
+        <v>5.320196628570557</v>
       </c>
       <c r="C969" t="n">
-        <v>5.477832422080734</v>
+        <v>5.477831931115081</v>
       </c>
       <c r="D969" t="n">
-        <v>5.211822590299863</v>
+        <v>5.211822123176066</v>
       </c>
       <c r="E969" t="n">
-        <v>5.448276035099693</v>
+        <v>5.448275546783112</v>
       </c>
       <c r="F969" t="n">
         <v>30338700</v>
@@ -19812,16 +19812,16 @@
         <v>45672</v>
       </c>
       <c r="B970" t="n">
-        <v>5.655171871185303</v>
+        <v>5.655172348022461</v>
       </c>
       <c r="C970" t="n">
-        <v>5.714285581778635</v>
+        <v>5.714286063600189</v>
       </c>
       <c r="D970" t="n">
-        <v>5.408866466277436</v>
+        <v>5.408866922346424</v>
       </c>
       <c r="E970" t="n">
-        <v>5.418718907973084</v>
+        <v>5.418719364872818</v>
       </c>
       <c r="F970" t="n">
         <v>28010800</v>
@@ -19832,16 +19832,16 @@
         <v>45673</v>
       </c>
       <c r="B971" t="n">
-        <v>5.566502094268799</v>
+        <v>5.566502571105957</v>
       </c>
       <c r="C971" t="n">
-        <v>5.635467305111304</v>
+        <v>5.635467787856154</v>
       </c>
       <c r="D971" t="n">
-        <v>5.399014348296546</v>
+        <v>5.399014810786386</v>
       </c>
       <c r="E971" t="n">
-        <v>5.615762892043408</v>
+        <v>5.615763373100339</v>
       </c>
       <c r="F971" t="n">
         <v>13042600</v>
@@ -19892,16 +19892,16 @@
         <v>45678</v>
       </c>
       <c r="B974" t="n">
-        <v>6.029556751251221</v>
+        <v>6.029556274414062</v>
       </c>
       <c r="C974" t="n">
-        <v>6.197044517084364</v>
+        <v>6.197044027001723</v>
       </c>
       <c r="D974" t="n">
-        <v>5.911330258824409</v>
+        <v>5.911329791336991</v>
       </c>
       <c r="E974" t="n">
-        <v>5.970443505037815</v>
+        <v>5.970443032875527</v>
       </c>
       <c r="F974" t="n">
         <v>19059500</v>
@@ -19912,16 +19912,16 @@
         <v>45679</v>
       </c>
       <c r="B975" t="n">
-        <v>6.236452579498291</v>
+        <v>6.236453056335449</v>
       </c>
       <c r="C975" t="n">
-        <v>6.325122672788494</v>
+        <v>6.325123156405338</v>
       </c>
       <c r="D975" t="n">
-        <v>5.931033943464581</v>
+        <v>5.931034396949529</v>
       </c>
       <c r="E975" t="n">
-        <v>6.068964834301359</v>
+        <v>6.068965298332458</v>
       </c>
       <c r="F975" t="n">
         <v>18324700</v>
@@ -19932,16 +19932,16 @@
         <v>45680</v>
       </c>
       <c r="B976" t="n">
-        <v>6.108373641967773</v>
+        <v>6.108374118804932</v>
       </c>
       <c r="C976" t="n">
-        <v>6.315270212498674</v>
+        <v>6.315270705486772</v>
       </c>
       <c r="D976" t="n">
-        <v>6.029555990297004</v>
+        <v>6.02955646098143</v>
       </c>
       <c r="E976" t="n">
-        <v>6.256156973745597</v>
+        <v>6.256157462119146</v>
       </c>
       <c r="F976" t="n">
         <v>32962200</v>
@@ -19952,16 +19952,16 @@
         <v>45681</v>
       </c>
       <c r="B977" t="n">
-        <v>6.059113502502441</v>
+        <v>6.059113025665283</v>
       </c>
       <c r="C977" t="n">
-        <v>6.364532170785939</v>
+        <v>6.364531669913091</v>
       </c>
       <c r="D977" t="n">
-        <v>6.039409087445129</v>
+        <v>6.03940861215866</v>
       </c>
       <c r="E977" t="n">
-        <v>6.108374305250566</v>
+        <v>6.108373824536706</v>
       </c>
       <c r="F977" t="n">
         <v>10904000</v>
@@ -20032,16 +20032,16 @@
         <v>45687</v>
       </c>
       <c r="B981" t="n">
-        <v>6.738916397094727</v>
+        <v>6.738915920257568</v>
       </c>
       <c r="C981" t="n">
-        <v>6.817734055808534</v>
+        <v>6.817733573394338</v>
       </c>
       <c r="D981" t="n">
-        <v>6.403940877770744</v>
+        <v>6.403940424636028</v>
       </c>
       <c r="E981" t="n">
-        <v>6.403940877770744</v>
+        <v>6.403940424636028</v>
       </c>
       <c r="F981" t="n">
         <v>22177900</v>
@@ -20112,16 +20112,16 @@
         <v>45693</v>
       </c>
       <c r="B985" t="n">
-        <v>6.738916397094727</v>
+        <v>6.738915920257568</v>
       </c>
       <c r="C985" t="n">
-        <v>6.827586028252608</v>
+        <v>6.827585545141299</v>
       </c>
       <c r="D985" t="n">
-        <v>6.532019808075832</v>
+        <v>6.532019345878414</v>
       </c>
       <c r="E985" t="n">
-        <v>6.650246296146542</v>
+        <v>6.650245825583568</v>
       </c>
       <c r="F985" t="n">
         <v>12476200</v>
@@ -20152,16 +20152,16 @@
         <v>45695</v>
       </c>
       <c r="B987" t="n">
-        <v>6.95566463470459</v>
+        <v>6.955665111541748</v>
       </c>
       <c r="C987" t="n">
-        <v>7.004925904002285</v>
+        <v>7.00492638421649</v>
       </c>
       <c r="D987" t="n">
-        <v>6.827585710362809</v>
+        <v>6.827586178419671</v>
       </c>
       <c r="E987" t="n">
-        <v>6.876846979660503</v>
+        <v>6.876847451094413</v>
       </c>
       <c r="F987" t="n">
         <v>23962500</v>
@@ -20172,16 +20172,16 @@
         <v>45698</v>
       </c>
       <c r="B988" t="n">
-        <v>6.896551132202148</v>
+        <v>6.896551609039307</v>
       </c>
       <c r="C988" t="n">
-        <v>7.182265355810159</v>
+        <v>7.182265852401997</v>
       </c>
       <c r="D988" t="n">
-        <v>6.876846719187467</v>
+        <v>6.876847194662234</v>
       </c>
       <c r="E988" t="n">
-        <v>7.024630051692709</v>
+        <v>7.024630537385422</v>
       </c>
       <c r="F988" t="n">
         <v>17122200</v>
@@ -20192,16 +20192,16 @@
         <v>45699</v>
       </c>
       <c r="B989" t="n">
-        <v>7.024630546569824</v>
+        <v>7.024630069732666</v>
       </c>
       <c r="C989" t="n">
-        <v>7.428571276723081</v>
+        <v>7.428570772466125</v>
       </c>
       <c r="D989" t="n">
-        <v>6.866994761556851</v>
+        <v>6.866994295420128</v>
       </c>
       <c r="E989" t="n">
-        <v>6.896551618056251</v>
+        <v>6.896551149913186</v>
       </c>
       <c r="F989" t="n">
         <v>37544600</v>
@@ -20212,16 +20212,16 @@
         <v>45700</v>
       </c>
       <c r="B990" t="n">
-        <v>7.024630546569824</v>
+        <v>7.024630069732666</v>
       </c>
       <c r="C990" t="n">
-        <v>7.113300176487432</v>
+        <v>7.113299693631313</v>
       </c>
       <c r="D990" t="n">
-        <v>6.896551618056251</v>
+        <v>6.896551149913186</v>
       </c>
       <c r="E990" t="n">
-        <v>6.96551730336132</v>
+        <v>6.965516830536814</v>
       </c>
       <c r="F990" t="n">
         <v>32300000</v>
@@ -20252,16 +20252,16 @@
         <v>45702</v>
       </c>
       <c r="B992" t="n">
-        <v>7.369458198547363</v>
+        <v>7.369457721710205</v>
       </c>
       <c r="C992" t="n">
-        <v>7.418719470552762</v>
+        <v>7.418718990528178</v>
       </c>
       <c r="D992" t="n">
-        <v>7.241379267165571</v>
+        <v>7.241378798615696</v>
       </c>
       <c r="E992" t="n">
-        <v>7.29064053917097</v>
+        <v>7.29064006743367</v>
       </c>
       <c r="F992" t="n">
         <v>14556600</v>
@@ -20272,16 +20272,16 @@
         <v>45705</v>
       </c>
       <c r="B993" t="n">
-        <v>7.665024280548096</v>
+        <v>7.665024757385254</v>
       </c>
       <c r="C993" t="n">
-        <v>7.871920385038538</v>
+        <v>7.871920874746595</v>
       </c>
       <c r="D993" t="n">
-        <v>7.349753198360755</v>
+        <v>7.349753655585064</v>
       </c>
       <c r="E993" t="n">
-        <v>7.408866438185206</v>
+        <v>7.408866899086918</v>
       </c>
       <c r="F993" t="n">
         <v>15107600</v>
@@ -20392,16 +20392,16 @@
         <v>45713</v>
       </c>
       <c r="B999" t="n">
-        <v>7.014777660369873</v>
+        <v>7.014778137207031</v>
       </c>
       <c r="C999" t="n">
-        <v>7.073890899835936</v>
+        <v>7.073891380691381</v>
       </c>
       <c r="D999" t="n">
-        <v>6.669950195256039</v>
+        <v>6.669950648653175</v>
       </c>
       <c r="E999" t="n">
-        <v>6.719211463039558</v>
+        <v>6.719211919785282</v>
       </c>
       <c r="F999" t="n">
         <v>14319100</v>
@@ -20752,16 +20752,16 @@
         <v>45741</v>
       </c>
       <c r="B1017" t="n">
-        <v>7.487684726715088</v>
+        <v>7.48768424987793</v>
       </c>
       <c r="C1017" t="n">
-        <v>7.921182325339423</v>
+        <v>7.921181820895899</v>
       </c>
       <c r="D1017" t="n">
-        <v>7.438423924242739</v>
+        <v>7.43842345054265</v>
       </c>
       <c r="E1017" t="n">
-        <v>7.448275896821086</v>
+        <v>7.448275422493594</v>
       </c>
       <c r="F1017" t="n">
         <v>12850900</v>
@@ -20892,16 +20892,16 @@
         <v>45750</v>
       </c>
       <c r="B1024" t="n">
-        <v>8.31527042388916</v>
+        <v>8.315269470214844</v>
       </c>
       <c r="C1024" t="n">
-        <v>8.45320179498446</v>
+        <v>8.453200825490862</v>
       </c>
       <c r="D1024" t="n">
-        <v>7.832512034426506</v>
+        <v>7.832511136119513</v>
       </c>
       <c r="E1024" t="n">
-        <v>7.881773305502012</v>
+        <v>7.881772401545269</v>
       </c>
       <c r="F1024" t="n">
         <v>17671400</v>
@@ -20932,16 +20932,16 @@
         <v>45754</v>
       </c>
       <c r="B1026" t="n">
-        <v>7.89162540435791</v>
+        <v>7.891625881195068</v>
       </c>
       <c r="C1026" t="n">
-        <v>8.08866954050818</v>
+        <v>8.088670029251373</v>
       </c>
       <c r="D1026" t="n">
-        <v>7.527093047794494</v>
+        <v>7.527093502605445</v>
       </c>
       <c r="E1026" t="n">
-        <v>7.655171971187308</v>
+        <v>7.655172433737196</v>
       </c>
       <c r="F1026" t="n">
         <v>17470600</v>
@@ -21172,16 +21172,16 @@
         <v>45772</v>
       </c>
       <c r="B1038" t="n">
-        <v>9.103447914123535</v>
+        <v>9.103446960449219</v>
       </c>
       <c r="C1038" t="n">
-        <v>9.251231726891742</v>
+        <v>9.251230757735641</v>
       </c>
       <c r="D1038" t="n">
-        <v>8.965517483036587</v>
+        <v>8.965516543811818</v>
       </c>
       <c r="E1038" t="n">
-        <v>9.044335140680726</v>
+        <v>9.044334193199045</v>
       </c>
       <c r="F1038" t="n">
         <v>7962500</v>
@@ -27472,19 +27472,39 @@
         <v>46232</v>
       </c>
       <c r="B1353" t="n">
-        <v>8.300000000000001</v>
+        <v>8.300000190734863</v>
       </c>
       <c r="C1353" t="n">
-        <v>8.43</v>
+        <v>8.430000305175781</v>
       </c>
       <c r="D1353" t="n">
-        <v>8.18</v>
+        <v>8.180000305175781</v>
       </c>
       <c r="E1353" t="n">
-        <v>8.26</v>
+        <v>8.260000228881836</v>
       </c>
       <c r="F1353" t="n">
         <v>9145900</v>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B1354" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="C1354" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="D1354" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="E1354" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="F1354" t="n">
+        <v>5160500</v>
       </c>
     </row>
   </sheetData>

--- a/database/ASAI3.xlsx
+++ b/database/ASAI3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1355"/>
+  <dimension ref="A1:F1356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44256</v>
       </c>
       <c r="B2" t="n">
-        <v>13.55914783477783</v>
+        <v>13.55914878845215</v>
       </c>
       <c r="C2" t="n">
-        <v>14.43840408118833</v>
+        <v>14.43840509670459</v>
       </c>
       <c r="D2" t="n">
-        <v>13.17554232187502</v>
+        <v>13.17554324856868</v>
       </c>
       <c r="E2" t="n">
-        <v>13.67498995526467</v>
+        <v>13.67499091708668</v>
       </c>
       <c r="F2" t="n">
         <v>64088000</v>
@@ -472,16 +472,16 @@
         <v>44257</v>
       </c>
       <c r="B3" t="n">
-        <v>13.76804256439209</v>
+        <v>13.76804351806641</v>
       </c>
       <c r="C3" t="n">
-        <v>14.05289879855508</v>
+        <v>14.0528997719606</v>
       </c>
       <c r="D3" t="n">
-        <v>13.0046284363764</v>
+        <v>13.00462933717113</v>
       </c>
       <c r="E3" t="n">
-        <v>13.3711429203832</v>
+        <v>13.37114384656537</v>
       </c>
       <c r="F3" t="n">
         <v>14717000</v>
@@ -512,16 +512,16 @@
         <v>44259</v>
       </c>
       <c r="B5" t="n">
-        <v>13.90097713470459</v>
+        <v>13.90097618103027</v>
       </c>
       <c r="C5" t="n">
-        <v>14.04340481356423</v>
+        <v>14.04340385011868</v>
       </c>
       <c r="D5" t="n">
-        <v>13.44330802948757</v>
+        <v>13.44330710721157</v>
       </c>
       <c r="E5" t="n">
-        <v>13.53256280482981</v>
+        <v>13.53256187643049</v>
       </c>
       <c r="F5" t="n">
         <v>12300000</v>
@@ -552,16 +552,16 @@
         <v>44263</v>
       </c>
       <c r="B7" t="n">
-        <v>13.48508548736572</v>
+        <v>13.48508644104004</v>
       </c>
       <c r="C7" t="n">
-        <v>14.29787472337838</v>
+        <v>14.2978757345337</v>
       </c>
       <c r="D7" t="n">
-        <v>13.05210487258059</v>
+        <v>13.05210579563423</v>
       </c>
       <c r="E7" t="n">
-        <v>14.21051885821534</v>
+        <v>14.21051986319279</v>
       </c>
       <c r="F7" t="n">
         <v>12366000</v>
@@ -572,16 +572,16 @@
         <v>44264</v>
       </c>
       <c r="B8" t="n">
-        <v>13.44520664215088</v>
+        <v>13.44520568847656</v>
       </c>
       <c r="C8" t="n">
-        <v>13.44520664215088</v>
+        <v>13.44520568847656</v>
       </c>
       <c r="D8" t="n">
-        <v>13.01032619226716</v>
+        <v>13.0103252694391</v>
       </c>
       <c r="E8" t="n">
-        <v>13.29138464363907</v>
+        <v>13.29138370087542</v>
       </c>
       <c r="F8" t="n">
         <v>10167000</v>
@@ -592,16 +592,16 @@
         <v>44265</v>
       </c>
       <c r="B9" t="n">
-        <v>13.48318576812744</v>
+        <v>13.48318862915039</v>
       </c>
       <c r="C9" t="n">
-        <v>13.95794583676244</v>
+        <v>13.95794879852564</v>
       </c>
       <c r="D9" t="n">
-        <v>13.23631031510933</v>
+        <v>13.2363131237473</v>
       </c>
       <c r="E9" t="n">
-        <v>13.48508467076097</v>
+        <v>13.48508753218685</v>
       </c>
       <c r="F9" t="n">
         <v>15699500</v>
@@ -612,16 +612,16 @@
         <v>44266</v>
       </c>
       <c r="B10" t="n">
-        <v>13.9560489654541</v>
+        <v>13.95604705810547</v>
       </c>
       <c r="C10" t="n">
-        <v>14.15544825952501</v>
+        <v>14.15544632492482</v>
       </c>
       <c r="D10" t="n">
-        <v>13.6351108298175</v>
+        <v>13.63510896633091</v>
       </c>
       <c r="E10" t="n">
-        <v>13.7129721878558</v>
+        <v>13.71297031372804</v>
       </c>
       <c r="F10" t="n">
         <v>16646000</v>
@@ -672,16 +672,16 @@
         <v>44271</v>
       </c>
       <c r="B13" t="n">
-        <v>13.58763408660889</v>
+        <v>13.5876350402832</v>
       </c>
       <c r="C13" t="n">
-        <v>13.91047018507921</v>
+        <v>13.9104711614124</v>
       </c>
       <c r="D13" t="n">
-        <v>13.49458060971476</v>
+        <v>13.49458155685794</v>
       </c>
       <c r="E13" t="n">
-        <v>13.84400406267841</v>
+        <v>13.84400503434655</v>
       </c>
       <c r="F13" t="n">
         <v>7789500</v>
@@ -712,16 +712,16 @@
         <v>44273</v>
       </c>
       <c r="B15" t="n">
-        <v>13.91047096252441</v>
+        <v>13.91047191619873</v>
       </c>
       <c r="C15" t="n">
-        <v>14.0130198642166</v>
+        <v>14.01302082492147</v>
       </c>
       <c r="D15" t="n">
-        <v>13.69018284217017</v>
+        <v>13.69018378074197</v>
       </c>
       <c r="E15" t="n">
-        <v>13.69018284217017</v>
+        <v>13.69018378074197</v>
       </c>
       <c r="F15" t="n">
         <v>2304000</v>
@@ -732,16 +732,16 @@
         <v>44274</v>
       </c>
       <c r="B16" t="n">
-        <v>13.54775428771973</v>
+        <v>13.54775333404541</v>
       </c>
       <c r="C16" t="n">
-        <v>14.03580762724047</v>
+        <v>14.03580663921036</v>
       </c>
       <c r="D16" t="n">
-        <v>13.46419713061404</v>
+        <v>13.46419618282161</v>
       </c>
       <c r="E16" t="n">
-        <v>13.95414937295086</v>
+        <v>13.95414839066896</v>
       </c>
       <c r="F16" t="n">
         <v>14098000</v>
@@ -772,16 +772,16 @@
         <v>44278</v>
       </c>
       <c r="B18" t="n">
-        <v>13.44140720367432</v>
+        <v>13.44140911102295</v>
       </c>
       <c r="C18" t="n">
-        <v>13.44140720367432</v>
+        <v>13.44140911102295</v>
       </c>
       <c r="D18" t="n">
-        <v>13.01982003059373</v>
+        <v>13.01982187811874</v>
       </c>
       <c r="E18" t="n">
-        <v>13.29328193175233</v>
+        <v>13.29328381808184</v>
       </c>
       <c r="F18" t="n">
         <v>7916000</v>
@@ -792,16 +792,16 @@
         <v>44279</v>
       </c>
       <c r="B19" t="n">
-        <v>13.00842571258545</v>
+        <v>13.00842761993408</v>
       </c>
       <c r="C19" t="n">
-        <v>13.47179146035269</v>
+        <v>13.4717934356419</v>
       </c>
       <c r="D19" t="n">
-        <v>12.86599805406478</v>
+        <v>12.86599994053009</v>
       </c>
       <c r="E19" t="n">
-        <v>13.31417167521553</v>
+        <v>13.31417362739389</v>
       </c>
       <c r="F19" t="n">
         <v>12174500</v>
@@ -812,16 +812,16 @@
         <v>44280</v>
       </c>
       <c r="B20" t="n">
-        <v>13.64840316772461</v>
+        <v>13.64840412139893</v>
       </c>
       <c r="C20" t="n">
-        <v>13.67309071501351</v>
+        <v>13.67309167041285</v>
       </c>
       <c r="D20" t="n">
-        <v>12.83941262661621</v>
+        <v>12.83941352376278</v>
       </c>
       <c r="E20" t="n">
-        <v>12.9134752684829</v>
+        <v>12.91347617080455</v>
       </c>
       <c r="F20" t="n">
         <v>6602000</v>
@@ -832,16 +832,16 @@
         <v>44281</v>
       </c>
       <c r="B21" t="n">
-        <v>13.80602550506592</v>
+        <v>13.8060245513916</v>
       </c>
       <c r="C21" t="n">
-        <v>14.12696365780925</v>
+        <v>14.1269626819656</v>
       </c>
       <c r="D21" t="n">
-        <v>13.488886063878</v>
+        <v>13.48888513211062</v>
       </c>
       <c r="E21" t="n">
-        <v>13.54965548789999</v>
+        <v>13.54965455193487</v>
       </c>
       <c r="F21" t="n">
         <v>4396500</v>
@@ -852,16 +852,16 @@
         <v>44284</v>
       </c>
       <c r="B22" t="n">
-        <v>13.95794677734375</v>
+        <v>13.95794773101807</v>
       </c>
       <c r="C22" t="n">
-        <v>13.95794677734375</v>
+        <v>13.95794773101807</v>
       </c>
       <c r="D22" t="n">
-        <v>13.4869853877722</v>
+        <v>13.48698630926816</v>
       </c>
       <c r="E22" t="n">
-        <v>13.7148700187455</v>
+        <v>13.71487095581164</v>
       </c>
       <c r="F22" t="n">
         <v>6557000</v>
@@ -872,16 +872,16 @@
         <v>44285</v>
       </c>
       <c r="B23" t="n">
-        <v>13.95794677734375</v>
+        <v>13.95794773101807</v>
       </c>
       <c r="C23" t="n">
-        <v>14.08138451217088</v>
+        <v>14.08138547427906</v>
       </c>
       <c r="D23" t="n">
-        <v>13.76804291819933</v>
+        <v>13.7680438588985</v>
       </c>
       <c r="E23" t="n">
-        <v>13.76804291819933</v>
+        <v>13.7680438588985</v>
       </c>
       <c r="F23" t="n">
         <v>8433000</v>
@@ -892,16 +892,16 @@
         <v>44286</v>
       </c>
       <c r="B24" t="n">
-        <v>14.02251529693604</v>
+        <v>14.02251434326172</v>
       </c>
       <c r="C24" t="n">
-        <v>14.04150613737493</v>
+        <v>14.04150518240905</v>
       </c>
       <c r="D24" t="n">
-        <v>13.67499161002203</v>
+        <v>13.67499067998287</v>
       </c>
       <c r="E24" t="n">
-        <v>13.96744348962283</v>
+        <v>13.96744253969395</v>
       </c>
       <c r="F24" t="n">
         <v>3663000</v>
@@ -932,16 +932,16 @@
         <v>44291</v>
       </c>
       <c r="B26" t="n">
-        <v>14.71756458282471</v>
+        <v>14.71756362915039</v>
       </c>
       <c r="C26" t="n">
-        <v>14.88657962286491</v>
+        <v>14.88657865823869</v>
       </c>
       <c r="D26" t="n">
-        <v>14.29977605116619</v>
+        <v>14.29977512456389</v>
       </c>
       <c r="E26" t="n">
-        <v>14.29977605116619</v>
+        <v>14.29977512456389</v>
       </c>
       <c r="F26" t="n">
         <v>6073500</v>
@@ -952,16 +952,16 @@
         <v>44292</v>
       </c>
       <c r="B27" t="n">
-        <v>14.5865306854248</v>
+        <v>14.58652973175049</v>
       </c>
       <c r="C27" t="n">
-        <v>14.72136184524953</v>
+        <v>14.72136088275989</v>
       </c>
       <c r="D27" t="n">
-        <v>14.52766016847332</v>
+        <v>14.52765921864798</v>
       </c>
       <c r="E27" t="n">
-        <v>14.71756403948914</v>
+        <v>14.7175630772478</v>
       </c>
       <c r="F27" t="n">
         <v>5821500</v>
@@ -992,16 +992,16 @@
         <v>44294</v>
       </c>
       <c r="B29" t="n">
-        <v>14.70237255096436</v>
+        <v>14.70237064361572</v>
       </c>
       <c r="C29" t="n">
-        <v>14.74035332682097</v>
+        <v>14.74035141454506</v>
       </c>
       <c r="D29" t="n">
-        <v>14.26559317584676</v>
+        <v>14.26559132516181</v>
       </c>
       <c r="E29" t="n">
-        <v>14.43270840850923</v>
+        <v>14.4327065361443</v>
       </c>
       <c r="F29" t="n">
         <v>6395000</v>
@@ -1012,16 +1012,16 @@
         <v>44295</v>
       </c>
       <c r="B30" t="n">
-        <v>14.71756458282471</v>
+        <v>14.71756362915039</v>
       </c>
       <c r="C30" t="n">
-        <v>14.73655542339393</v>
+        <v>14.73655446848903</v>
       </c>
       <c r="D30" t="n">
-        <v>14.40802076359814</v>
+        <v>14.40801982998176</v>
       </c>
       <c r="E30" t="n">
-        <v>14.63210761132946</v>
+        <v>14.63210666319261</v>
       </c>
       <c r="F30" t="n">
         <v>7012500</v>
@@ -1052,16 +1052,16 @@
         <v>44299</v>
       </c>
       <c r="B32" t="n">
-        <v>14.67008590698242</v>
+        <v>14.67008876800537</v>
       </c>
       <c r="C32" t="n">
-        <v>14.81251447057491</v>
+        <v>14.81251735937489</v>
       </c>
       <c r="D32" t="n">
-        <v>14.5276582489229</v>
+        <v>14.527661082169</v>
       </c>
       <c r="E32" t="n">
-        <v>14.69667235485844</v>
+        <v>14.69667522106639</v>
       </c>
       <c r="F32" t="n">
         <v>5449500</v>
@@ -1072,16 +1072,16 @@
         <v>44300</v>
       </c>
       <c r="B33" t="n">
-        <v>14.93785285949707</v>
+        <v>14.93785190582275</v>
       </c>
       <c r="C33" t="n">
-        <v>14.9454484709092</v>
+        <v>14.94544751674995</v>
       </c>
       <c r="D33" t="n">
-        <v>14.62261144203403</v>
+        <v>14.62261050848561</v>
       </c>
       <c r="E33" t="n">
-        <v>14.65109770142871</v>
+        <v>14.65109676606165</v>
       </c>
       <c r="F33" t="n">
         <v>5841000</v>
@@ -1092,16 +1092,16 @@
         <v>44301</v>
       </c>
       <c r="B34" t="n">
-        <v>15.18662738800049</v>
+        <v>15.1866283416748</v>
       </c>
       <c r="C34" t="n">
-        <v>15.20371751383992</v>
+        <v>15.20371846858745</v>
       </c>
       <c r="D34" t="n">
-        <v>14.84100171054341</v>
+        <v>14.84100264251348</v>
       </c>
       <c r="E34" t="n">
-        <v>14.84100171054341</v>
+        <v>14.84100264251348</v>
       </c>
       <c r="F34" t="n">
         <v>11554500</v>
@@ -1112,16 +1112,16 @@
         <v>44302</v>
       </c>
       <c r="B35" t="n">
-        <v>15.14484691619873</v>
+        <v>15.14484786987305</v>
       </c>
       <c r="C35" t="n">
-        <v>15.7278517141565</v>
+        <v>15.72785270454275</v>
       </c>
       <c r="D35" t="n">
-        <v>15.00052034653632</v>
+        <v>15.00052129112236</v>
       </c>
       <c r="E35" t="n">
-        <v>15.7278517141565</v>
+        <v>15.72785270454275</v>
       </c>
       <c r="F35" t="n">
         <v>13035000</v>
@@ -1132,16 +1132,16 @@
         <v>44305</v>
       </c>
       <c r="B36" t="n">
-        <v>15.28727722167969</v>
+        <v>15.28727531433105</v>
       </c>
       <c r="C36" t="n">
-        <v>15.50756626494049</v>
+        <v>15.50756433010704</v>
       </c>
       <c r="D36" t="n">
-        <v>15.00431985298662</v>
+        <v>15.00431798094175</v>
       </c>
       <c r="E36" t="n">
-        <v>15.14484863308528</v>
+        <v>15.14484674350704</v>
       </c>
       <c r="F36" t="n">
         <v>5017000</v>
@@ -1172,16 +1172,16 @@
         <v>44308</v>
       </c>
       <c r="B38" t="n">
-        <v>15.27967739105225</v>
+        <v>15.27967834472656</v>
       </c>
       <c r="C38" t="n">
-        <v>15.75253947002613</v>
+        <v>15.75254045321392</v>
       </c>
       <c r="D38" t="n">
-        <v>15.19422224353416</v>
+        <v>15.19422319187483</v>
       </c>
       <c r="E38" t="n">
-        <v>15.50376420492759</v>
+        <v>15.50376517258819</v>
       </c>
       <c r="F38" t="n">
         <v>8470500</v>
@@ -1192,16 +1192,16 @@
         <v>44309</v>
       </c>
       <c r="B39" t="n">
-        <v>15.41261291503906</v>
+        <v>15.41261386871338</v>
       </c>
       <c r="C39" t="n">
-        <v>15.53794955811708</v>
+        <v>15.53795051954675</v>
       </c>
       <c r="D39" t="n">
-        <v>15.218910336355</v>
+        <v>15.21891127804373</v>
       </c>
       <c r="E39" t="n">
-        <v>15.45819020544309</v>
+        <v>15.45819116193756</v>
       </c>
       <c r="F39" t="n">
         <v>4653000</v>
@@ -1212,16 +1212,16 @@
         <v>44312</v>
       </c>
       <c r="B40" t="n">
-        <v>15.2606897354126</v>
+        <v>15.26069068908691</v>
       </c>
       <c r="C40" t="n">
-        <v>15.51705882313055</v>
+        <v>15.51705979282594</v>
       </c>
       <c r="D40" t="n">
-        <v>15.16573734944818</v>
+        <v>15.16573829718871</v>
       </c>
       <c r="E40" t="n">
-        <v>15.48477656941952</v>
+        <v>15.48477753709752</v>
       </c>
       <c r="F40" t="n">
         <v>3662000</v>
@@ -1232,16 +1232,16 @@
         <v>44313</v>
       </c>
       <c r="B41" t="n">
-        <v>15.1277551651001</v>
+        <v>15.12775611877441</v>
       </c>
       <c r="C41" t="n">
-        <v>15.29677017902364</v>
+        <v>15.29677114335289</v>
       </c>
       <c r="D41" t="n">
-        <v>15.1011687168379</v>
+        <v>15.10116966883617</v>
       </c>
       <c r="E41" t="n">
-        <v>15.24929308493688</v>
+        <v>15.24929404627311</v>
       </c>
       <c r="F41" t="n">
         <v>4986500</v>
@@ -1252,16 +1252,16 @@
         <v>44314</v>
       </c>
       <c r="B42" t="n">
-        <v>15.18852519989014</v>
+        <v>15.18852710723877</v>
       </c>
       <c r="C42" t="n">
-        <v>15.35564131800169</v>
+        <v>15.35564324633648</v>
       </c>
       <c r="D42" t="n">
-        <v>15.04799553112973</v>
+        <v>15.04799742083089</v>
       </c>
       <c r="E42" t="n">
-        <v>15.14864552586341</v>
+        <v>15.14864742820402</v>
       </c>
       <c r="F42" t="n">
         <v>5371500</v>
@@ -1272,16 +1272,16 @@
         <v>44315</v>
       </c>
       <c r="B43" t="n">
-        <v>15.21646499633789</v>
+        <v>15.21646595001221</v>
       </c>
       <c r="C43" t="n">
-        <v>15.32323336252505</v>
+        <v>15.32323432289095</v>
       </c>
       <c r="D43" t="n">
-        <v>14.90950503441863</v>
+        <v>14.90950596885459</v>
       </c>
       <c r="E43" t="n">
-        <v>15.26222338706449</v>
+        <v>15.26222434360666</v>
       </c>
       <c r="F43" t="n">
         <v>5343000</v>
@@ -1292,16 +1292,16 @@
         <v>44316</v>
       </c>
       <c r="B44" t="n">
-        <v>15.4223747253418</v>
+        <v>15.42237663269043</v>
       </c>
       <c r="C44" t="n">
-        <v>15.46813311247533</v>
+        <v>15.46813502548309</v>
       </c>
       <c r="D44" t="n">
-        <v>14.92856925223867</v>
+        <v>14.92857109851635</v>
       </c>
       <c r="E44" t="n">
-        <v>15.10016229485833</v>
+        <v>15.10016416235762</v>
       </c>
       <c r="F44" t="n">
         <v>22683000</v>
@@ -1312,16 +1312,16 @@
         <v>44319</v>
       </c>
       <c r="B45" t="n">
-        <v>15.53295993804932</v>
+        <v>15.532958984375</v>
       </c>
       <c r="C45" t="n">
-        <v>15.67023330010677</v>
+        <v>15.6702323380043</v>
       </c>
       <c r="D45" t="n">
-        <v>15.29463663895672</v>
+        <v>15.29463569991469</v>
       </c>
       <c r="E45" t="n">
-        <v>15.4433505085054</v>
+        <v>15.44334956033281</v>
       </c>
       <c r="F45" t="n">
         <v>8474000</v>
@@ -1332,16 +1332,16 @@
         <v>44320</v>
       </c>
       <c r="B46" t="n">
-        <v>15.72933769226074</v>
+        <v>15.72933673858643</v>
       </c>
       <c r="C46" t="n">
-        <v>15.74840399251314</v>
+        <v>15.74840303768283</v>
       </c>
       <c r="D46" t="n">
-        <v>15.35945946771906</v>
+        <v>15.35945853647056</v>
       </c>
       <c r="E46" t="n">
-        <v>15.63400800926121</v>
+        <v>15.63400706136676</v>
       </c>
       <c r="F46" t="n">
         <v>9407500</v>
@@ -1412,16 +1412,16 @@
         <v>44326</v>
       </c>
       <c r="B50" t="n">
-        <v>16.81418609619141</v>
+        <v>16.81418418884277</v>
       </c>
       <c r="C50" t="n">
-        <v>17.0162841548014</v>
+        <v>17.01628222452739</v>
       </c>
       <c r="D50" t="n">
-        <v>16.55298359675715</v>
+        <v>16.55298171903851</v>
       </c>
       <c r="E50" t="n">
-        <v>16.97052576072697</v>
+        <v>16.97052383564365</v>
       </c>
       <c r="F50" t="n">
         <v>7669500</v>
@@ -1432,16 +1432,16 @@
         <v>44327</v>
       </c>
       <c r="B51" t="n">
-        <v>16.58730125427246</v>
+        <v>16.58729934692383</v>
       </c>
       <c r="C51" t="n">
-        <v>16.78368087460993</v>
+        <v>16.78367894467991</v>
       </c>
       <c r="D51" t="n">
-        <v>16.49197157097672</v>
+        <v>16.4919696745899</v>
       </c>
       <c r="E51" t="n">
-        <v>16.62543385489575</v>
+        <v>16.6254319431623</v>
       </c>
       <c r="F51" t="n">
         <v>6191000</v>
@@ -1452,16 +1452,16 @@
         <v>44328</v>
       </c>
       <c r="B52" t="n">
-        <v>16.12590789794922</v>
+        <v>16.12590599060059</v>
       </c>
       <c r="C52" t="n">
-        <v>16.57776793756821</v>
+        <v>16.57776597677424</v>
       </c>
       <c r="D52" t="n">
-        <v>16.04201690472579</v>
+        <v>16.04201500729966</v>
       </c>
       <c r="E52" t="n">
-        <v>16.49006586623571</v>
+        <v>16.49006391581501</v>
       </c>
       <c r="F52" t="n">
         <v>6728500</v>
@@ -1492,16 +1492,16 @@
         <v>44330</v>
       </c>
       <c r="B54" t="n">
-        <v>16.52629089355469</v>
+        <v>16.52628898620605</v>
       </c>
       <c r="C54" t="n">
-        <v>16.66356425245107</v>
+        <v>16.66356232925931</v>
       </c>
       <c r="D54" t="n">
-        <v>16.13734637653381</v>
+        <v>16.13734451407442</v>
       </c>
       <c r="E54" t="n">
-        <v>16.54726273245572</v>
+        <v>16.54726082268666</v>
       </c>
       <c r="F54" t="n">
         <v>5923000</v>
@@ -1552,16 +1552,16 @@
         <v>44335</v>
       </c>
       <c r="B57" t="n">
-        <v>15.8284797668457</v>
+        <v>15.82847881317139</v>
       </c>
       <c r="C57" t="n">
-        <v>16.36804368259568</v>
+        <v>16.36804269641236</v>
       </c>
       <c r="D57" t="n">
-        <v>15.67595300621593</v>
+        <v>15.67595206173143</v>
       </c>
       <c r="E57" t="n">
-        <v>15.98481942375186</v>
+        <v>15.98481846065799</v>
       </c>
       <c r="F57" t="n">
         <v>6358000</v>
@@ -1572,16 +1572,16 @@
         <v>44336</v>
       </c>
       <c r="B58" t="n">
-        <v>16.03248596191406</v>
+        <v>16.03248405456543</v>
       </c>
       <c r="C58" t="n">
-        <v>16.03248596191406</v>
+        <v>16.03248405456543</v>
       </c>
       <c r="D58" t="n">
-        <v>15.69692561740377</v>
+        <v>15.69692374997599</v>
       </c>
       <c r="E58" t="n">
-        <v>15.90283657256179</v>
+        <v>15.90283468063725</v>
       </c>
       <c r="F58" t="n">
         <v>7278000</v>
@@ -1592,16 +1592,16 @@
         <v>44337</v>
       </c>
       <c r="B59" t="n">
-        <v>16.43477439880371</v>
+        <v>16.43477249145508</v>
       </c>
       <c r="C59" t="n">
-        <v>16.6254337643569</v>
+        <v>16.62543183488117</v>
       </c>
       <c r="D59" t="n">
-        <v>15.75984264485187</v>
+        <v>15.75984081583289</v>
       </c>
       <c r="E59" t="n">
-        <v>16.03439118575198</v>
+        <v>16.03438932487009</v>
       </c>
       <c r="F59" t="n">
         <v>10145000</v>
@@ -1632,16 +1632,16 @@
         <v>44341</v>
       </c>
       <c r="B61" t="n">
-        <v>16.88472557067871</v>
+        <v>16.88472747802734</v>
       </c>
       <c r="C61" t="n">
-        <v>17.06394439344869</v>
+        <v>17.06394632104241</v>
       </c>
       <c r="D61" t="n">
-        <v>16.77986275848394</v>
+        <v>16.77986465398696</v>
       </c>
       <c r="E61" t="n">
-        <v>17.01628047059403</v>
+        <v>17.0162823928035</v>
       </c>
       <c r="F61" t="n">
         <v>5307000</v>
@@ -1652,16 +1652,16 @@
         <v>44342</v>
       </c>
       <c r="B62" t="n">
-        <v>16.94192504882812</v>
+        <v>16.94192314147949</v>
       </c>
       <c r="C62" t="n">
-        <v>17.11161256574568</v>
+        <v>17.11161063929336</v>
       </c>
       <c r="D62" t="n">
-        <v>16.65975073072218</v>
+        <v>16.65974885514118</v>
       </c>
       <c r="E62" t="n">
-        <v>17.02390868058733</v>
+        <v>17.02390676400885</v>
       </c>
       <c r="F62" t="n">
         <v>5462000</v>
@@ -1672,16 +1672,16 @@
         <v>44343</v>
       </c>
       <c r="B63" t="n">
-        <v>16.94955253601074</v>
+        <v>16.94955444335938</v>
       </c>
       <c r="C63" t="n">
-        <v>17.26223183953111</v>
+        <v>17.26223378206583</v>
       </c>
       <c r="D63" t="n">
-        <v>16.70550899973091</v>
+        <v>16.7055108796171</v>
       </c>
       <c r="E63" t="n">
-        <v>16.94955253601074</v>
+        <v>16.94955444335938</v>
       </c>
       <c r="F63" t="n">
         <v>5669000</v>
@@ -1692,16 +1692,16 @@
         <v>44344</v>
       </c>
       <c r="B64" t="n">
-        <v>16.98577690124512</v>
+        <v>16.98577880859375</v>
       </c>
       <c r="C64" t="n">
-        <v>17.14974233685488</v>
+        <v>17.14974426261534</v>
       </c>
       <c r="D64" t="n">
-        <v>16.56442007870208</v>
+        <v>16.56442193873616</v>
       </c>
       <c r="E64" t="n">
-        <v>16.91141906621777</v>
+        <v>16.91142096521669</v>
       </c>
       <c r="F64" t="n">
         <v>4590500</v>
@@ -1712,16 +1712,16 @@
         <v>44347</v>
       </c>
       <c r="B65" t="n">
-        <v>17.05441474914551</v>
+        <v>17.05441284179688</v>
       </c>
       <c r="C65" t="n">
-        <v>17.25460726644232</v>
+        <v>17.25460533670436</v>
       </c>
       <c r="D65" t="n">
-        <v>16.87138299313376</v>
+        <v>16.87138110625522</v>
       </c>
       <c r="E65" t="n">
-        <v>17.09254734987347</v>
+        <v>17.09254543826012</v>
       </c>
       <c r="F65" t="n">
         <v>4641000</v>
@@ -1752,16 +1752,16 @@
         <v>44349</v>
       </c>
       <c r="B67" t="n">
-        <v>16.76651763916016</v>
+        <v>16.76651954650879</v>
       </c>
       <c r="C67" t="n">
-        <v>17.26032492574389</v>
+        <v>17.26032688926774</v>
       </c>
       <c r="D67" t="n">
-        <v>16.73982554996776</v>
+        <v>16.73982745427992</v>
       </c>
       <c r="E67" t="n">
-        <v>17.06394533438589</v>
+        <v>17.06394727556971</v>
       </c>
       <c r="F67" t="n">
         <v>9352500</v>
@@ -1832,16 +1832,16 @@
         <v>44356</v>
       </c>
       <c r="B71" t="n">
-        <v>16.16403961181641</v>
+        <v>16.16403770446777</v>
       </c>
       <c r="C71" t="n">
-        <v>16.39664448651429</v>
+        <v>16.39664255171839</v>
       </c>
       <c r="D71" t="n">
-        <v>15.82466817777308</v>
+        <v>15.82466631047011</v>
       </c>
       <c r="E71" t="n">
-        <v>16.08205778944601</v>
+        <v>16.08205589177119</v>
       </c>
       <c r="F71" t="n">
         <v>10294500</v>
@@ -1852,16 +1852,16 @@
         <v>44357</v>
       </c>
       <c r="B72" t="n">
-        <v>16.30321884155273</v>
+        <v>16.30322074890137</v>
       </c>
       <c r="C72" t="n">
-        <v>16.34707169398488</v>
+        <v>16.34707360646395</v>
       </c>
       <c r="D72" t="n">
-        <v>15.97719348463267</v>
+        <v>15.97719535383889</v>
       </c>
       <c r="E72" t="n">
-        <v>16.15641233581547</v>
+        <v>16.15641422598889</v>
       </c>
       <c r="F72" t="n">
         <v>4720000</v>
@@ -1872,16 +1872,16 @@
         <v>44358</v>
       </c>
       <c r="B73" t="n">
-        <v>16.07061576843262</v>
+        <v>16.07061386108398</v>
       </c>
       <c r="C73" t="n">
-        <v>16.30512616021678</v>
+        <v>16.30512422503518</v>
       </c>
       <c r="D73" t="n">
-        <v>15.87423797549705</v>
+        <v>15.8742360914556</v>
       </c>
       <c r="E73" t="n">
-        <v>16.3032188029694</v>
+        <v>16.30321686801416</v>
       </c>
       <c r="F73" t="n">
         <v>5133000</v>
@@ -1912,16 +1912,16 @@
         <v>44362</v>
       </c>
       <c r="B75" t="n">
-        <v>15.85898494720459</v>
+        <v>15.85898780822754</v>
       </c>
       <c r="C75" t="n">
-        <v>16.02676511323235</v>
+        <v>16.0267680045235</v>
       </c>
       <c r="D75" t="n">
-        <v>15.48720119095393</v>
+        <v>15.48720398490564</v>
       </c>
       <c r="E75" t="n">
-        <v>16.01532460600237</v>
+        <v>16.01532749522961</v>
       </c>
       <c r="F75" t="n">
         <v>8432500</v>
@@ -1932,16 +1932,16 @@
         <v>44363</v>
       </c>
       <c r="B76" t="n">
-        <v>15.89902114868164</v>
+        <v>15.89902400970459</v>
       </c>
       <c r="C76" t="n">
-        <v>16.11446521988256</v>
+        <v>16.11446811967458</v>
       </c>
       <c r="D76" t="n">
-        <v>15.6626052411311</v>
+        <v>15.66260805961109</v>
       </c>
       <c r="E76" t="n">
-        <v>15.70264337503251</v>
+        <v>15.70264620071735</v>
       </c>
       <c r="F76" t="n">
         <v>10606500</v>
@@ -1952,16 +1952,16 @@
         <v>44364</v>
       </c>
       <c r="B77" t="n">
-        <v>15.97719287872314</v>
+        <v>15.97719478607178</v>
       </c>
       <c r="C77" t="n">
-        <v>16.00769786575993</v>
+        <v>16.00769977675023</v>
       </c>
       <c r="D77" t="n">
-        <v>15.6912038523147</v>
+        <v>15.69120572552212</v>
       </c>
       <c r="E77" t="n">
-        <v>15.89711660590322</v>
+        <v>15.89711850369239</v>
       </c>
       <c r="F77" t="n">
         <v>7246000</v>
@@ -1972,16 +1972,16 @@
         <v>44365</v>
       </c>
       <c r="B78" t="n">
-        <v>16.20789337158203</v>
+        <v>16.20788955688477</v>
       </c>
       <c r="C78" t="n">
-        <v>16.36423305011592</v>
+        <v>16.36422919862247</v>
       </c>
       <c r="D78" t="n">
-        <v>15.67976807160136</v>
+        <v>15.67976438120391</v>
       </c>
       <c r="E78" t="n">
-        <v>15.98863453186528</v>
+        <v>15.98863076877287</v>
       </c>
       <c r="F78" t="n">
         <v>12012000</v>
@@ -2012,16 +2012,16 @@
         <v>44369</v>
       </c>
       <c r="B80" t="n">
-        <v>16.4729061126709</v>
+        <v>16.47290420532227</v>
       </c>
       <c r="C80" t="n">
-        <v>16.49578530803645</v>
+        <v>16.49578339803871</v>
       </c>
       <c r="D80" t="n">
-        <v>16.13162735767305</v>
+        <v>16.13162548984007</v>
       </c>
       <c r="E80" t="n">
-        <v>16.46718585926392</v>
+        <v>16.46718395257762</v>
       </c>
       <c r="F80" t="n">
         <v>6518000</v>
@@ -2072,16 +2072,16 @@
         <v>44372</v>
       </c>
       <c r="B83" t="n">
-        <v>16.18501281738281</v>
+        <v>16.18501091003418</v>
       </c>
       <c r="C83" t="n">
-        <v>16.74745595976945</v>
+        <v>16.74745398613881</v>
       </c>
       <c r="D83" t="n">
-        <v>16.05345788821992</v>
+        <v>16.05345599637458</v>
       </c>
       <c r="E83" t="n">
-        <v>16.64640602074596</v>
+        <v>16.64640405902371</v>
       </c>
       <c r="F83" t="n">
         <v>6078000</v>
@@ -2192,16 +2192,16 @@
         <v>44382</v>
       </c>
       <c r="B89" t="n">
-        <v>16.41570663452148</v>
+        <v>16.41570472717285</v>
       </c>
       <c r="C89" t="n">
-        <v>16.54726154865489</v>
+        <v>16.54725962602083</v>
       </c>
       <c r="D89" t="n">
-        <v>16.25174119484036</v>
+        <v>16.25173930654295</v>
       </c>
       <c r="E89" t="n">
-        <v>16.40808084242347</v>
+        <v>16.40807893596088</v>
       </c>
       <c r="F89" t="n">
         <v>3871000</v>
@@ -2232,16 +2232,16 @@
         <v>44384</v>
       </c>
       <c r="B91" t="n">
-        <v>16.44430732727051</v>
+        <v>16.44430351257324</v>
       </c>
       <c r="C91" t="n">
-        <v>16.58348804403921</v>
+        <v>16.58348419705526</v>
       </c>
       <c r="D91" t="n">
-        <v>16.15069249011994</v>
+        <v>16.15068874353449</v>
       </c>
       <c r="E91" t="n">
-        <v>16.39664339565586</v>
+        <v>16.39663959201552</v>
       </c>
       <c r="F91" t="n">
         <v>12086500</v>
@@ -2252,16 +2252,16 @@
         <v>44385</v>
       </c>
       <c r="B92" t="n">
-        <v>16.43477439880371</v>
+        <v>16.43477249145508</v>
       </c>
       <c r="C92" t="n">
-        <v>16.79893236876558</v>
+        <v>16.79893041915436</v>
       </c>
       <c r="D92" t="n">
-        <v>16.24411685151298</v>
+        <v>16.24411496629124</v>
       </c>
       <c r="E92" t="n">
-        <v>16.26318133345833</v>
+        <v>16.26317944602405</v>
       </c>
       <c r="F92" t="n">
         <v>7435000</v>
@@ -2272,16 +2272,16 @@
         <v>44389</v>
       </c>
       <c r="B93" t="n">
-        <v>16.50150489807129</v>
+        <v>16.50150108337402</v>
       </c>
       <c r="C93" t="n">
-        <v>16.60255483619654</v>
+        <v>16.60255099813928</v>
       </c>
       <c r="D93" t="n">
-        <v>16.27462210402238</v>
+        <v>16.27461834177422</v>
       </c>
       <c r="E93" t="n">
-        <v>16.43096176807677</v>
+        <v>16.43095796968715</v>
       </c>
       <c r="F93" t="n">
         <v>4327500</v>
@@ -2292,16 +2292,16 @@
         <v>44390</v>
       </c>
       <c r="B94" t="n">
-        <v>16.7874927520752</v>
+        <v>16.78749465942383</v>
       </c>
       <c r="C94" t="n">
-        <v>16.91142006005396</v>
+        <v>16.91142198148287</v>
       </c>
       <c r="D94" t="n">
-        <v>16.43096059459017</v>
+        <v>16.4309624614306</v>
       </c>
       <c r="E94" t="n">
-        <v>16.45383978992295</v>
+        <v>16.45384165936285</v>
       </c>
       <c r="F94" t="n">
         <v>6446000</v>
@@ -2332,16 +2332,16 @@
         <v>44392</v>
       </c>
       <c r="B96" t="n">
-        <v>16.45002937316895</v>
+        <v>16.45002555847168</v>
       </c>
       <c r="C96" t="n">
-        <v>16.86375867221395</v>
+        <v>16.86375476157448</v>
       </c>
       <c r="D96" t="n">
-        <v>16.44049622215487</v>
+        <v>16.44049240966831</v>
       </c>
       <c r="E96" t="n">
-        <v>16.72267058277338</v>
+        <v>16.72266670485169</v>
       </c>
       <c r="F96" t="n">
         <v>3746000</v>
@@ -2352,16 +2352,16 @@
         <v>44393</v>
       </c>
       <c r="B97" t="n">
-        <v>16.67119216918945</v>
+        <v>16.67118835449219</v>
       </c>
       <c r="C97" t="n">
-        <v>16.86947550939675</v>
+        <v>16.86947164932835</v>
       </c>
       <c r="D97" t="n">
-        <v>16.52247830033713</v>
+        <v>16.52247451966853</v>
       </c>
       <c r="E97" t="n">
-        <v>16.54154278229579</v>
+        <v>16.54153899726486</v>
       </c>
       <c r="F97" t="n">
         <v>7965000</v>
@@ -2372,16 +2372,16 @@
         <v>44396</v>
       </c>
       <c r="B98" t="n">
-        <v>16.65402984619141</v>
+        <v>16.65403175354004</v>
       </c>
       <c r="C98" t="n">
-        <v>16.79702526617702</v>
+        <v>16.7970271899026</v>
       </c>
       <c r="D98" t="n">
-        <v>16.40426788246265</v>
+        <v>16.40426976120661</v>
       </c>
       <c r="E98" t="n">
-        <v>16.58539408105208</v>
+        <v>16.58539598054001</v>
       </c>
       <c r="F98" t="n">
         <v>7763500</v>
@@ -2392,16 +2392,16 @@
         <v>44397</v>
       </c>
       <c r="B99" t="n">
-        <v>16.51103591918945</v>
+        <v>16.51103401184082</v>
       </c>
       <c r="C99" t="n">
-        <v>16.71694684707543</v>
+        <v>16.71694491594005</v>
       </c>
       <c r="D99" t="n">
-        <v>16.45955909634909</v>
+        <v>16.45955719494704</v>
       </c>
       <c r="E99" t="n">
-        <v>16.6540295180957</v>
+        <v>16.65402759422851</v>
       </c>
       <c r="F99" t="n">
         <v>3835500</v>
@@ -2432,16 +2432,16 @@
         <v>44399</v>
       </c>
       <c r="B101" t="n">
-        <v>16.64449501037598</v>
+        <v>16.64449882507324</v>
       </c>
       <c r="C101" t="n">
-        <v>16.68072024642313</v>
+        <v>16.68072406942274</v>
       </c>
       <c r="D101" t="n">
-        <v>16.44430435190125</v>
+        <v>16.44430812071748</v>
       </c>
       <c r="E101" t="n">
-        <v>16.58729793913493</v>
+        <v>16.58730174072338</v>
       </c>
       <c r="F101" t="n">
         <v>2829500</v>
@@ -2452,16 +2452,16 @@
         <v>44400</v>
       </c>
       <c r="B102" t="n">
-        <v>16.6826286315918</v>
+        <v>16.68263053894043</v>
       </c>
       <c r="C102" t="n">
-        <v>16.73029255752003</v>
+        <v>16.73029447031815</v>
       </c>
       <c r="D102" t="n">
-        <v>16.56060687203135</v>
+        <v>16.56060876542906</v>
       </c>
       <c r="E102" t="n">
-        <v>16.64449603623943</v>
+        <v>16.64449793922831</v>
       </c>
       <c r="F102" t="n">
         <v>4154500</v>
@@ -2472,16 +2472,16 @@
         <v>44403</v>
       </c>
       <c r="B103" t="n">
-        <v>17.19741058349609</v>
+        <v>17.19740676879883</v>
       </c>
       <c r="C103" t="n">
-        <v>17.21647506604089</v>
+        <v>17.21647124711478</v>
       </c>
       <c r="D103" t="n">
-        <v>16.56060959167434</v>
+        <v>16.56060591823107</v>
       </c>
       <c r="E103" t="n">
-        <v>16.75126896322247</v>
+        <v>16.7512652474875</v>
       </c>
       <c r="F103" t="n">
         <v>9987000</v>
@@ -2532,16 +2532,16 @@
         <v>44406</v>
       </c>
       <c r="B106" t="n">
-        <v>16.62543487548828</v>
+        <v>16.62543296813965</v>
       </c>
       <c r="C106" t="n">
-        <v>16.7779616508197</v>
+        <v>16.77795972597248</v>
       </c>
       <c r="D106" t="n">
-        <v>16.27462292857349</v>
+        <v>16.27462106147167</v>
       </c>
       <c r="E106" t="n">
-        <v>16.7779616508197</v>
+        <v>16.77795972597248</v>
       </c>
       <c r="F106" t="n">
         <v>12625000</v>
@@ -2552,16 +2552,16 @@
         <v>44407</v>
       </c>
       <c r="B107" t="n">
-        <v>16.52629089355469</v>
+        <v>16.52628898620605</v>
       </c>
       <c r="C107" t="n">
-        <v>16.73220184103048</v>
+        <v>16.73219990991705</v>
       </c>
       <c r="D107" t="n">
-        <v>16.30893943885111</v>
+        <v>16.30893755658766</v>
       </c>
       <c r="E107" t="n">
-        <v>16.6254334709708</v>
+        <v>16.62543155217983</v>
       </c>
       <c r="F107" t="n">
         <v>16469000</v>
@@ -2592,16 +2592,16 @@
         <v>44411</v>
       </c>
       <c r="B109" t="n">
-        <v>16.53009986877441</v>
+        <v>16.53010177612305</v>
       </c>
       <c r="C109" t="n">
-        <v>16.68071923819987</v>
+        <v>16.68072116292792</v>
       </c>
       <c r="D109" t="n">
-        <v>16.2612716501018</v>
+        <v>16.26127352643131</v>
       </c>
       <c r="E109" t="n">
-        <v>16.68071923819987</v>
+        <v>16.68072116292792</v>
       </c>
       <c r="F109" t="n">
         <v>5450500</v>
@@ -2612,16 +2612,16 @@
         <v>44412</v>
       </c>
       <c r="B110" t="n">
-        <v>16.60255432128906</v>
+        <v>16.6025562286377</v>
       </c>
       <c r="C110" t="n">
-        <v>16.83134446559894</v>
+        <v>16.83134639923163</v>
       </c>
       <c r="D110" t="n">
-        <v>16.3489776234245</v>
+        <v>16.34897950164152</v>
       </c>
       <c r="E110" t="n">
-        <v>16.48243990463543</v>
+        <v>16.48244179818497</v>
       </c>
       <c r="F110" t="n">
         <v>6533500</v>
@@ -2632,16 +2632,16 @@
         <v>44413</v>
       </c>
       <c r="B111" t="n">
-        <v>16.58730125427246</v>
+        <v>16.58729934692383</v>
       </c>
       <c r="C111" t="n">
-        <v>16.93811317965181</v>
+        <v>16.93811123196384</v>
       </c>
       <c r="D111" t="n">
-        <v>16.47481262800123</v>
+        <v>16.47481073358749</v>
       </c>
       <c r="E111" t="n">
-        <v>16.59302150801845</v>
+        <v>16.59301960001205</v>
       </c>
       <c r="F111" t="n">
         <v>13427000</v>
@@ -2692,16 +2692,16 @@
         <v>44418</v>
       </c>
       <c r="B114" t="n">
-        <v>17.55012893676758</v>
+        <v>17.55012702941895</v>
       </c>
       <c r="C114" t="n">
-        <v>17.66452492908273</v>
+        <v>17.66452300930153</v>
       </c>
       <c r="D114" t="n">
-        <v>17.10589465161376</v>
+        <v>17.10589279254452</v>
       </c>
       <c r="E114" t="n">
-        <v>17.22219618314763</v>
+        <v>17.22219431143875</v>
       </c>
       <c r="F114" t="n">
         <v>10281500</v>
@@ -2712,16 +2712,16 @@
         <v>44419</v>
       </c>
       <c r="B115" t="n">
-        <v>17.20884704589844</v>
+        <v>17.20884895324707</v>
       </c>
       <c r="C115" t="n">
-        <v>17.57872523333663</v>
+        <v>17.57872718168084</v>
       </c>
       <c r="D115" t="n">
-        <v>17.19740835785192</v>
+        <v>17.19741026393275</v>
       </c>
       <c r="E115" t="n">
-        <v>17.57872523333663</v>
+        <v>17.57872718168084</v>
       </c>
       <c r="F115" t="n">
         <v>6265000</v>
@@ -2732,16 +2732,16 @@
         <v>44420</v>
       </c>
       <c r="B116" t="n">
-        <v>16.92095375061035</v>
+        <v>16.92095184326172</v>
       </c>
       <c r="C116" t="n">
-        <v>17.24507357354782</v>
+        <v>17.24507162966405</v>
       </c>
       <c r="D116" t="n">
-        <v>16.68263045834824</v>
+        <v>16.68262857786367</v>
       </c>
       <c r="E116" t="n">
-        <v>16.98768398152176</v>
+        <v>16.98768206665122</v>
       </c>
       <c r="F116" t="n">
         <v>14059400</v>
@@ -2772,16 +2772,16 @@
         <v>44424</v>
       </c>
       <c r="B118" t="n">
-        <v>16.44430732727051</v>
+        <v>16.44430351257324</v>
       </c>
       <c r="C118" t="n">
-        <v>17.04488122962231</v>
+        <v>17.04487727560585</v>
       </c>
       <c r="D118" t="n">
-        <v>16.27271426423787</v>
+        <v>16.27271048934621</v>
       </c>
       <c r="E118" t="n">
-        <v>16.86375683487669</v>
+        <v>16.86375292287688</v>
       </c>
       <c r="F118" t="n">
         <v>7814500</v>
@@ -2792,16 +2792,16 @@
         <v>44425</v>
       </c>
       <c r="B119" t="n">
-        <v>16.16785049438477</v>
+        <v>16.1678524017334</v>
       </c>
       <c r="C119" t="n">
-        <v>16.39664244399077</v>
+        <v>16.39664437833038</v>
       </c>
       <c r="D119" t="n">
-        <v>15.70073708227531</v>
+        <v>15.70073893451779</v>
       </c>
       <c r="E119" t="n">
-        <v>16.16785049438477</v>
+        <v>16.1678524017334</v>
       </c>
       <c r="F119" t="n">
         <v>9967800</v>
@@ -2812,16 +2812,16 @@
         <v>44426</v>
       </c>
       <c r="B120" t="n">
-        <v>15.88186359405518</v>
+        <v>15.88186550140381</v>
       </c>
       <c r="C120" t="n">
-        <v>16.30131308548479</v>
+        <v>16.30131504320764</v>
       </c>
       <c r="D120" t="n">
-        <v>15.64354030864827</v>
+        <v>15.64354218737522</v>
       </c>
       <c r="E120" t="n">
-        <v>16.16785080923852</v>
+        <v>16.16785275093307</v>
       </c>
       <c r="F120" t="n">
         <v>10736900</v>
@@ -2832,16 +2832,16 @@
         <v>44427</v>
       </c>
       <c r="B121" t="n">
-        <v>16.6635627746582</v>
+        <v>16.66356468200684</v>
       </c>
       <c r="C121" t="n">
-        <v>16.87328841811889</v>
+        <v>16.87329034947318</v>
       </c>
       <c r="D121" t="n">
-        <v>15.57680923404292</v>
+        <v>15.57681101699932</v>
       </c>
       <c r="E121" t="n">
-        <v>15.71026968478171</v>
+        <v>15.71027148301428</v>
       </c>
       <c r="F121" t="n">
         <v>14455000</v>
@@ -2852,16 +2852,16 @@
         <v>44428</v>
       </c>
       <c r="B122" t="n">
-        <v>16.94955253601074</v>
+        <v>16.94955444335938</v>
       </c>
       <c r="C122" t="n">
-        <v>17.41666595234703</v>
+        <v>17.41666791226037</v>
       </c>
       <c r="D122" t="n">
-        <v>16.37757629334467</v>
+        <v>16.3775781363283</v>
       </c>
       <c r="E122" t="n">
-        <v>16.53963619846235</v>
+        <v>16.53963805968273</v>
       </c>
       <c r="F122" t="n">
         <v>9513400</v>
@@ -2912,16 +2912,16 @@
         <v>44433</v>
       </c>
       <c r="B125" t="n">
-        <v>17.01628303527832</v>
+        <v>17.01628494262695</v>
       </c>
       <c r="C125" t="n">
-        <v>17.19740924229705</v>
+        <v>17.19741116994805</v>
       </c>
       <c r="D125" t="n">
-        <v>16.78749289822105</v>
+        <v>16.78749477992469</v>
       </c>
       <c r="E125" t="n">
-        <v>17.0258161849385</v>
+        <v>17.0258180933557</v>
       </c>
       <c r="F125" t="n">
         <v>4269900</v>
@@ -2952,16 +2952,16 @@
         <v>44435</v>
       </c>
       <c r="B127" t="n">
-        <v>16.58730125427246</v>
+        <v>16.58729934692383</v>
       </c>
       <c r="C127" t="n">
-        <v>16.72076353819149</v>
+        <v>16.72076161549623</v>
       </c>
       <c r="D127" t="n">
-        <v>16.39664370594345</v>
+        <v>16.39664182051824</v>
       </c>
       <c r="E127" t="n">
-        <v>16.55870362206747</v>
+        <v>16.55870171800724</v>
       </c>
       <c r="F127" t="n">
         <v>5662600</v>
@@ -2992,16 +2992,16 @@
         <v>44439</v>
       </c>
       <c r="B129" t="n">
-        <v>16.02485466003418</v>
+        <v>16.02485656738281</v>
       </c>
       <c r="C129" t="n">
-        <v>16.63496341032833</v>
+        <v>16.63496539029478</v>
       </c>
       <c r="D129" t="n">
-        <v>16.02485466003418</v>
+        <v>16.02485656738281</v>
       </c>
       <c r="E129" t="n">
-        <v>16.37757386652902</v>
+        <v>16.37757581585984</v>
       </c>
       <c r="F129" t="n">
         <v>8477100</v>
@@ -3012,16 +3012,16 @@
         <v>44440</v>
       </c>
       <c r="B130" t="n">
-        <v>16.23458480834961</v>
+        <v>16.23458290100098</v>
       </c>
       <c r="C130" t="n">
-        <v>16.77796167348466</v>
+        <v>16.77795970229644</v>
       </c>
       <c r="D130" t="n">
-        <v>15.89139865425901</v>
+        <v>15.89139678723021</v>
       </c>
       <c r="E130" t="n">
-        <v>16.30131504536443</v>
+        <v>16.30131313017587</v>
       </c>
       <c r="F130" t="n">
         <v>7651500</v>
@@ -3052,16 +3052,16 @@
         <v>44442</v>
       </c>
       <c r="B132" t="n">
-        <v>17.31180191040039</v>
+        <v>17.31180000305176</v>
       </c>
       <c r="C132" t="n">
-        <v>17.359465836333</v>
+        <v>17.35946392373294</v>
       </c>
       <c r="D132" t="n">
-        <v>16.69216178196529</v>
+        <v>16.69215994288625</v>
       </c>
       <c r="E132" t="n">
-        <v>16.9018856016359</v>
+        <v>16.90188373945029</v>
       </c>
       <c r="F132" t="n">
         <v>19565300</v>
@@ -3072,16 +3072,16 @@
         <v>44445</v>
       </c>
       <c r="B133" t="n">
-        <v>17.4929313659668</v>
+        <v>17.49292945861816</v>
       </c>
       <c r="C133" t="n">
-        <v>17.66452444056273</v>
+        <v>17.66452251450438</v>
       </c>
       <c r="D133" t="n">
-        <v>17.04488237824128</v>
+        <v>17.04488051974584</v>
       </c>
       <c r="E133" t="n">
-        <v>17.30227199013519</v>
+        <v>17.30227010357517</v>
       </c>
       <c r="F133" t="n">
         <v>6471000</v>
@@ -3112,16 +3112,16 @@
         <v>44448</v>
       </c>
       <c r="B135" t="n">
-        <v>17.34993553161621</v>
+        <v>17.34993934631348</v>
       </c>
       <c r="C135" t="n">
-        <v>17.44526338911795</v>
+        <v>17.44526722477477</v>
       </c>
       <c r="D135" t="n">
-        <v>16.92095289980908</v>
+        <v>16.92095662018675</v>
       </c>
       <c r="E135" t="n">
-        <v>17.07347965372665</v>
+        <v>17.07348340764009</v>
       </c>
       <c r="F135" t="n">
         <v>12544000</v>
@@ -3132,16 +3132,16 @@
         <v>44449</v>
       </c>
       <c r="B136" t="n">
-        <v>17.33087348937988</v>
+        <v>17.33086967468262</v>
       </c>
       <c r="C136" t="n">
-        <v>17.60732761690594</v>
+        <v>17.60732374135838</v>
       </c>
       <c r="D136" t="n">
-        <v>17.01628675487766</v>
+        <v>17.01628300942406</v>
       </c>
       <c r="E136" t="n">
-        <v>17.33087348937988</v>
+        <v>17.33086967468262</v>
       </c>
       <c r="F136" t="n">
         <v>19125200</v>
@@ -3152,16 +3152,16 @@
         <v>44452</v>
       </c>
       <c r="B137" t="n">
-        <v>17.79798316955566</v>
+        <v>17.79798126220703</v>
       </c>
       <c r="C137" t="n">
-        <v>17.9695762273458</v>
+        <v>17.96957430160813</v>
       </c>
       <c r="D137" t="n">
-        <v>17.49292965271203</v>
+        <v>17.49292777805493</v>
       </c>
       <c r="E137" t="n">
-        <v>17.5787261816071</v>
+        <v>17.57872429775548</v>
       </c>
       <c r="F137" t="n">
         <v>17075500</v>
@@ -3212,16 +3212,16 @@
         <v>44455</v>
       </c>
       <c r="B140" t="n">
-        <v>18.26509475708008</v>
+        <v>18.26509666442871</v>
       </c>
       <c r="C140" t="n">
-        <v>18.33182497989392</v>
+        <v>18.33182689421092</v>
       </c>
       <c r="D140" t="n">
-        <v>17.72171800758197</v>
+        <v>17.72171985818801</v>
       </c>
       <c r="E140" t="n">
-        <v>17.72171800758197</v>
+        <v>17.72171985818801</v>
       </c>
       <c r="F140" t="n">
         <v>17281800</v>
@@ -3292,16 +3292,16 @@
         <v>44461</v>
       </c>
       <c r="B144" t="n">
-        <v>18.38902854919434</v>
+        <v>18.38902473449707</v>
       </c>
       <c r="C144" t="n">
-        <v>18.68454896178596</v>
+        <v>18.6845450857847</v>
       </c>
       <c r="D144" t="n">
-        <v>18.21743546502415</v>
+        <v>18.21743168592287</v>
       </c>
       <c r="E144" t="n">
-        <v>18.61781872200037</v>
+        <v>18.61781485984191</v>
       </c>
       <c r="F144" t="n">
         <v>5973600</v>
@@ -3312,16 +3312,16 @@
         <v>44462</v>
       </c>
       <c r="B145" t="n">
-        <v>18.29369735717773</v>
+        <v>18.2936954498291</v>
       </c>
       <c r="C145" t="n">
-        <v>18.53202066160796</v>
+        <v>18.53201872941112</v>
       </c>
       <c r="D145" t="n">
-        <v>18.07443853522241</v>
+        <v>18.07443665073428</v>
       </c>
       <c r="E145" t="n">
-        <v>18.34136129075877</v>
+        <v>18.34135937844058</v>
       </c>
       <c r="F145" t="n">
         <v>20822300</v>
@@ -3332,16 +3332,16 @@
         <v>44463</v>
       </c>
       <c r="B146" t="n">
-        <v>18.09350204467773</v>
+        <v>18.09350395202637</v>
       </c>
       <c r="C146" t="n">
-        <v>18.26509508831786</v>
+        <v>18.26509701375519</v>
       </c>
       <c r="D146" t="n">
-        <v>17.87424507480967</v>
+        <v>17.87424695904506</v>
       </c>
       <c r="E146" t="n">
-        <v>18.13163464026987</v>
+        <v>18.13163655163829</v>
       </c>
       <c r="F146" t="n">
         <v>18657800</v>
@@ -3392,16 +3392,16 @@
         <v>44468</v>
       </c>
       <c r="B149" t="n">
-        <v>18.08396911621094</v>
+        <v>18.08397102355957</v>
       </c>
       <c r="C149" t="n">
-        <v>18.4271552076744</v>
+        <v>18.42715715121949</v>
       </c>
       <c r="D149" t="n">
-        <v>17.96957496456462</v>
+        <v>17.9695768598479</v>
       </c>
       <c r="E149" t="n">
-        <v>18.29369475799961</v>
+        <v>18.29369668746839</v>
       </c>
       <c r="F149" t="n">
         <v>10203400</v>
@@ -3432,16 +3432,16 @@
         <v>44470</v>
       </c>
       <c r="B151" t="n">
-        <v>18.45575714111328</v>
+        <v>18.45575523376465</v>
       </c>
       <c r="C151" t="n">
-        <v>18.56061815787245</v>
+        <v>18.56061623968673</v>
       </c>
       <c r="D151" t="n">
-        <v>18.00770816839343</v>
+        <v>18.00770630734936</v>
       </c>
       <c r="E151" t="n">
-        <v>18.19836753783964</v>
+        <v>18.19836565709148</v>
       </c>
       <c r="F151" t="n">
         <v>5841800</v>
@@ -3452,16 +3452,16 @@
         <v>44473</v>
       </c>
       <c r="B152" t="n">
-        <v>18.41762351989746</v>
+        <v>18.41762161254883</v>
       </c>
       <c r="C152" t="n">
-        <v>18.49388689979976</v>
+        <v>18.49388498455321</v>
       </c>
       <c r="D152" t="n">
-        <v>18.07443740120593</v>
+        <v>18.07443552939801</v>
       </c>
       <c r="E152" t="n">
-        <v>18.3890258888481</v>
+        <v>18.38902398446107</v>
       </c>
       <c r="F152" t="n">
         <v>9789400</v>
@@ -3492,16 +3492,16 @@
         <v>44475</v>
       </c>
       <c r="B154" t="n">
-        <v>18.27167892456055</v>
+        <v>18.27167701721191</v>
       </c>
       <c r="C154" t="n">
-        <v>18.63481816893143</v>
+        <v>18.63481622367532</v>
       </c>
       <c r="D154" t="n">
-        <v>18.06143878380436</v>
+        <v>18.06143689840233</v>
       </c>
       <c r="E154" t="n">
-        <v>18.11877617550022</v>
+        <v>18.11877428411284</v>
       </c>
       <c r="F154" t="n">
         <v>10611600</v>
@@ -3512,16 +3512,16 @@
         <v>44476</v>
       </c>
       <c r="B155" t="n">
-        <v>18.08055114746094</v>
+        <v>18.0805492401123</v>
       </c>
       <c r="C155" t="n">
-        <v>18.36723991743979</v>
+        <v>18.36723797984786</v>
       </c>
       <c r="D155" t="n">
-        <v>17.99454415192273</v>
+        <v>17.99454225364713</v>
       </c>
       <c r="E155" t="n">
-        <v>18.271678209262</v>
+        <v>18.27167628175104</v>
       </c>
       <c r="F155" t="n">
         <v>7169200</v>
@@ -3532,16 +3532,16 @@
         <v>44477</v>
       </c>
       <c r="B156" t="n">
-        <v>17.48805999755859</v>
+        <v>17.48805809020996</v>
       </c>
       <c r="C156" t="n">
-        <v>18.32901694393641</v>
+        <v>18.32901494486817</v>
       </c>
       <c r="D156" t="n">
-        <v>17.3638286741761</v>
+        <v>17.36382678037685</v>
       </c>
       <c r="E156" t="n">
-        <v>18.06143940232113</v>
+        <v>18.06143743243643</v>
       </c>
       <c r="F156" t="n">
         <v>14612800</v>
@@ -3552,16 +3552,16 @@
         <v>44480</v>
       </c>
       <c r="B157" t="n">
-        <v>16.62799263000488</v>
+        <v>16.62799072265625</v>
       </c>
       <c r="C157" t="n">
-        <v>17.52628701478551</v>
+        <v>17.52628500439614</v>
       </c>
       <c r="D157" t="n">
-        <v>16.47509169081537</v>
+        <v>16.47508980100556</v>
       </c>
       <c r="E157" t="n">
-        <v>17.4211669355716</v>
+        <v>17.42116493724025</v>
       </c>
       <c r="F157" t="n">
         <v>31512800</v>
@@ -3612,16 +3612,16 @@
         <v>44484</v>
       </c>
       <c r="B160" t="n">
-        <v>16.76177978515625</v>
+        <v>16.76177787780762</v>
       </c>
       <c r="C160" t="n">
-        <v>16.93379194870116</v>
+        <v>16.933790021779</v>
       </c>
       <c r="D160" t="n">
-        <v>15.86348553616024</v>
+        <v>15.86348373102988</v>
       </c>
       <c r="E160" t="n">
-        <v>15.95904906438921</v>
+        <v>15.95904724838453</v>
       </c>
       <c r="F160" t="n">
         <v>78021300</v>
@@ -3672,16 +3672,16 @@
         <v>44489</v>
       </c>
       <c r="B163" t="n">
-        <v>15.98771667480469</v>
+        <v>15.98771953582764</v>
       </c>
       <c r="C163" t="n">
-        <v>16.21706804645106</v>
+        <v>16.21707094851675</v>
       </c>
       <c r="D163" t="n">
-        <v>15.71058445091965</v>
+        <v>15.71058726234942</v>
       </c>
       <c r="E163" t="n">
-        <v>15.93993582256603</v>
+        <v>15.93993867503853</v>
       </c>
       <c r="F163" t="n">
         <v>11472200</v>
@@ -3732,16 +3732,16 @@
         <v>44494</v>
       </c>
       <c r="B166" t="n">
-        <v>15.41433811187744</v>
+        <v>15.41433715820312</v>
       </c>
       <c r="C166" t="n">
-        <v>15.66280256604172</v>
+        <v>15.66280159699508</v>
       </c>
       <c r="D166" t="n">
-        <v>15.13720587401294</v>
+        <v>15.1372049374846</v>
       </c>
       <c r="E166" t="n">
-        <v>15.39522686365155</v>
+        <v>15.39522591115963</v>
       </c>
       <c r="F166" t="n">
         <v>20484500</v>
@@ -3792,16 +3792,16 @@
         <v>44497</v>
       </c>
       <c r="B169" t="n">
-        <v>14.95563411712646</v>
+        <v>14.95563507080078</v>
       </c>
       <c r="C169" t="n">
-        <v>15.13720463078065</v>
+        <v>15.13720559603315</v>
       </c>
       <c r="D169" t="n">
-        <v>14.69761406004066</v>
+        <v>14.69761499726184</v>
       </c>
       <c r="E169" t="n">
-        <v>15.02252894859126</v>
+        <v>15.02252990653125</v>
       </c>
       <c r="F169" t="n">
         <v>8208600</v>
@@ -3812,16 +3812,16 @@
         <v>44498</v>
       </c>
       <c r="B170" t="n">
-        <v>14.61160850524902</v>
+        <v>14.61160755157471</v>
       </c>
       <c r="C170" t="n">
-        <v>15.21365657937846</v>
+        <v>15.21365558640951</v>
       </c>
       <c r="D170" t="n">
-        <v>14.50648934742759</v>
+        <v>14.50648840061422</v>
       </c>
       <c r="E170" t="n">
-        <v>15.0034173523742</v>
+        <v>15.0034163731272</v>
       </c>
       <c r="F170" t="n">
         <v>13706000</v>
@@ -3832,16 +3832,16 @@
         <v>44501</v>
       </c>
       <c r="B171" t="n">
-        <v>14.31536197662354</v>
+        <v>14.31536102294922</v>
       </c>
       <c r="C171" t="n">
-        <v>14.77406565205061</v>
+        <v>14.77406466781794</v>
       </c>
       <c r="D171" t="n">
-        <v>14.20068628560711</v>
+        <v>14.20068533957237</v>
       </c>
       <c r="E171" t="n">
-        <v>14.76450911662556</v>
+        <v>14.76450813302954</v>
       </c>
       <c r="F171" t="n">
         <v>10277500</v>
@@ -3852,16 +3852,16 @@
         <v>44503</v>
       </c>
       <c r="B172" t="n">
-        <v>14.74539566040039</v>
+        <v>14.74539661407471</v>
       </c>
       <c r="C172" t="n">
-        <v>14.86962787591666</v>
+        <v>14.86962883762583</v>
       </c>
       <c r="D172" t="n">
-        <v>14.07645282125721</v>
+        <v>14.07645373166693</v>
       </c>
       <c r="E172" t="n">
-        <v>14.14334765198831</v>
+        <v>14.14334856672452</v>
       </c>
       <c r="F172" t="n">
         <v>21906500</v>
@@ -3912,16 +3912,16 @@
         <v>44508</v>
       </c>
       <c r="B175" t="n">
-        <v>14.73583793640137</v>
+        <v>14.73584079742432</v>
       </c>
       <c r="C175" t="n">
-        <v>14.89829536578197</v>
+        <v>14.89829825834669</v>
       </c>
       <c r="D175" t="n">
-        <v>14.28669087215139</v>
+        <v>14.28669364597061</v>
       </c>
       <c r="E175" t="n">
-        <v>14.39181092137485</v>
+        <v>14.39181371560356</v>
       </c>
       <c r="F175" t="n">
         <v>8290300</v>
@@ -3932,16 +3932,16 @@
         <v>44509</v>
       </c>
       <c r="B176" t="n">
-        <v>14.81229114532471</v>
+        <v>14.81229019165039</v>
       </c>
       <c r="C176" t="n">
-        <v>15.08942429804084</v>
+        <v>15.08942332652359</v>
       </c>
       <c r="D176" t="n">
-        <v>14.66894675684999</v>
+        <v>14.66894581240476</v>
       </c>
       <c r="E176" t="n">
-        <v>14.80273460973002</v>
+        <v>14.80273365667099</v>
       </c>
       <c r="F176" t="n">
         <v>6124400</v>
@@ -3952,16 +3952,16 @@
         <v>44510</v>
       </c>
       <c r="B177" t="n">
-        <v>15.26143646240234</v>
+        <v>15.26143741607666</v>
       </c>
       <c r="C177" t="n">
-        <v>15.38566867614508</v>
+        <v>15.38566963758256</v>
       </c>
       <c r="D177" t="n">
-        <v>14.71672584655168</v>
+        <v>14.71672676618749</v>
       </c>
       <c r="E177" t="n">
-        <v>14.84095806029442</v>
+        <v>14.84095898769339</v>
       </c>
       <c r="F177" t="n">
         <v>10223900</v>
@@ -4052,16 +4052,16 @@
         <v>44518</v>
       </c>
       <c r="B182" t="n">
-        <v>13.35972881317139</v>
+        <v>13.3597297668457</v>
       </c>
       <c r="C182" t="n">
-        <v>13.69420022476301</v>
+        <v>13.69420120231332</v>
       </c>
       <c r="D182" t="n">
-        <v>13.1399339911367</v>
+        <v>13.13993492912112</v>
       </c>
       <c r="E182" t="n">
-        <v>13.6559749986978</v>
+        <v>13.65597597351942</v>
       </c>
       <c r="F182" t="n">
         <v>21252300</v>
@@ -4072,16 +4072,16 @@
         <v>44519</v>
       </c>
       <c r="B183" t="n">
-        <v>13.45529270172119</v>
+        <v>13.45529365539551</v>
       </c>
       <c r="C183" t="n">
-        <v>13.74198236072563</v>
+        <v>13.74198333471972</v>
       </c>
       <c r="D183" t="n">
-        <v>13.28327872404627</v>
+        <v>13.28327966552871</v>
       </c>
       <c r="E183" t="n">
-        <v>13.35017355500946</v>
+        <v>13.35017450123322</v>
       </c>
       <c r="F183" t="n">
         <v>11060800</v>
@@ -4092,16 +4092,16 @@
         <v>44522</v>
       </c>
       <c r="B184" t="n">
-        <v>13.17816066741943</v>
+        <v>13.17815971374512</v>
       </c>
       <c r="C184" t="n">
-        <v>13.56996950554565</v>
+        <v>13.569968523517</v>
       </c>
       <c r="D184" t="n">
-        <v>13.12082236633105</v>
+        <v>13.12082141680619</v>
       </c>
       <c r="E184" t="n">
-        <v>13.52218773986557</v>
+        <v>13.52218676129477</v>
       </c>
       <c r="F184" t="n">
         <v>12046100</v>
@@ -4112,16 +4112,16 @@
         <v>44523</v>
       </c>
       <c r="B185" t="n">
-        <v>13.24505233764648</v>
+        <v>13.24505424499512</v>
       </c>
       <c r="C185" t="n">
-        <v>13.41706630026567</v>
+        <v>13.4170682323851</v>
       </c>
       <c r="D185" t="n">
-        <v>12.99658883886027</v>
+        <v>12.99659071042901</v>
       </c>
       <c r="E185" t="n">
-        <v>13.23549671522637</v>
+        <v>13.23549862119895</v>
       </c>
       <c r="F185" t="n">
         <v>3755200</v>
@@ -4132,16 +4132,16 @@
         <v>44524</v>
       </c>
       <c r="B186" t="n">
-        <v>13.11126518249512</v>
+        <v>13.11126613616943</v>
       </c>
       <c r="C186" t="n">
-        <v>13.38839829683666</v>
+        <v>13.38839927066881</v>
       </c>
       <c r="D186" t="n">
-        <v>12.97747643677941</v>
+        <v>12.97747738072233</v>
       </c>
       <c r="E186" t="n">
-        <v>13.09215211395233</v>
+        <v>13.09215306623642</v>
       </c>
       <c r="F186" t="n">
         <v>5705900</v>
@@ -4152,16 +4152,16 @@
         <v>44525</v>
       </c>
       <c r="B187" t="n">
-        <v>13.23549842834473</v>
+        <v>13.23549938201904</v>
       </c>
       <c r="C187" t="n">
-        <v>13.27372365705648</v>
+        <v>13.27372461348509</v>
       </c>
       <c r="D187" t="n">
-        <v>12.89147045857758</v>
+        <v>12.89147138746321</v>
       </c>
       <c r="E187" t="n">
-        <v>13.13037836586639</v>
+        <v>13.13037931196636</v>
       </c>
       <c r="F187" t="n">
         <v>5547700</v>
@@ -4192,16 +4192,16 @@
         <v>44529</v>
       </c>
       <c r="B189" t="n">
-        <v>12.4709939956665</v>
+        <v>12.47099304199219</v>
       </c>
       <c r="C189" t="n">
-        <v>13.1112673141673</v>
+        <v>13.11126631153039</v>
       </c>
       <c r="D189" t="n">
-        <v>12.42321222790229</v>
+        <v>12.42321127788191</v>
       </c>
       <c r="E189" t="n">
-        <v>12.88191501117135</v>
+        <v>12.88191402607333</v>
       </c>
       <c r="F189" t="n">
         <v>13464500</v>
@@ -4212,16 +4212,16 @@
         <v>44530</v>
       </c>
       <c r="B190" t="n">
-        <v>12.18430233001709</v>
+        <v>12.18430328369141</v>
       </c>
       <c r="C190" t="n">
-        <v>12.44232328740027</v>
+        <v>12.44232426127008</v>
       </c>
       <c r="D190" t="n">
-        <v>11.84027529820078</v>
+        <v>11.84027622494785</v>
       </c>
       <c r="E190" t="n">
-        <v>12.38498499308359</v>
+        <v>12.38498596246548</v>
       </c>
       <c r="F190" t="n">
         <v>16793700</v>
@@ -4252,16 +4252,16 @@
         <v>44532</v>
       </c>
       <c r="B192" t="n">
-        <v>11.89761447906494</v>
+        <v>11.89761257171631</v>
       </c>
       <c r="C192" t="n">
-        <v>12.14607893971519</v>
+        <v>12.14607699253434</v>
       </c>
       <c r="D192" t="n">
-        <v>11.71604485711986</v>
+        <v>11.71604297887929</v>
       </c>
       <c r="E192" t="n">
-        <v>12.14607893971519</v>
+        <v>12.14607699253434</v>
       </c>
       <c r="F192" t="n">
         <v>7306700</v>
@@ -4272,16 +4272,16 @@
         <v>44533</v>
       </c>
       <c r="B193" t="n">
-        <v>12.70989990234375</v>
+        <v>12.70990085601807</v>
       </c>
       <c r="C193" t="n">
-        <v>12.7481251282053</v>
+        <v>12.74812608474781</v>
       </c>
       <c r="D193" t="n">
-        <v>11.95495100805711</v>
+        <v>11.95495190508461</v>
       </c>
       <c r="E193" t="n">
-        <v>11.99317623391867</v>
+        <v>11.99317713381436</v>
       </c>
       <c r="F193" t="n">
         <v>16852000</v>
@@ -4312,16 +4312,16 @@
         <v>44537</v>
       </c>
       <c r="B195" t="n">
-        <v>13.4266242980957</v>
+        <v>13.42662525177002</v>
       </c>
       <c r="C195" t="n">
-        <v>13.76109481466241</v>
+        <v>13.7610957920937</v>
       </c>
       <c r="D195" t="n">
-        <v>13.40751122844893</v>
+        <v>13.40751218076567</v>
       </c>
       <c r="E195" t="n">
-        <v>13.56996867500125</v>
+        <v>13.56996963885711</v>
       </c>
       <c r="F195" t="n">
         <v>14090400</v>
@@ -4332,16 +4332,16 @@
         <v>44538</v>
       </c>
       <c r="B196" t="n">
-        <v>13.751540184021</v>
+        <v>13.75153923034668</v>
       </c>
       <c r="C196" t="n">
-        <v>14.02867333437821</v>
+        <v>14.02867236148461</v>
       </c>
       <c r="D196" t="n">
-        <v>13.27372434469053</v>
+        <v>13.27372342415291</v>
       </c>
       <c r="E196" t="n">
-        <v>13.42662526745845</v>
+        <v>13.42662433631711</v>
       </c>
       <c r="F196" t="n">
         <v>14295000</v>
@@ -4352,16 +4352,16 @@
         <v>44539</v>
       </c>
       <c r="B197" t="n">
-        <v>13.58908176422119</v>
+        <v>13.58908271789551</v>
       </c>
       <c r="C197" t="n">
-        <v>13.74198267617036</v>
+        <v>13.74198364057517</v>
       </c>
       <c r="D197" t="n">
-        <v>13.43618085227203</v>
+        <v>13.43618179521584</v>
       </c>
       <c r="E197" t="n">
-        <v>13.74198267617036</v>
+        <v>13.74198364057517</v>
       </c>
       <c r="F197" t="n">
         <v>9843600</v>
@@ -4372,16 +4372,16 @@
         <v>44540</v>
       </c>
       <c r="B198" t="n">
-        <v>13.91399765014648</v>
+        <v>13.91399574279785</v>
       </c>
       <c r="C198" t="n">
-        <v>14.19113080065994</v>
+        <v>14.19112885532154</v>
       </c>
       <c r="D198" t="n">
-        <v>13.7419836562549</v>
+        <v>13.74198177248616</v>
       </c>
       <c r="E198" t="n">
-        <v>13.7419836562549</v>
+        <v>13.74198177248616</v>
       </c>
       <c r="F198" t="n">
         <v>8247400</v>
@@ -4452,16 +4452,16 @@
         <v>44546</v>
       </c>
       <c r="B202" t="n">
-        <v>13.89488410949707</v>
+        <v>13.89488315582275</v>
       </c>
       <c r="C202" t="n">
-        <v>14.28669293890897</v>
+        <v>14.28669195834289</v>
       </c>
       <c r="D202" t="n">
-        <v>13.82799018584958</v>
+        <v>13.82798923676653</v>
       </c>
       <c r="E202" t="n">
-        <v>14.21024248006574</v>
+        <v>14.21024150474683</v>
       </c>
       <c r="F202" t="n">
         <v>5287600</v>
@@ -4472,16 +4472,16 @@
         <v>44547</v>
       </c>
       <c r="B203" t="n">
-        <v>13.81843376159668</v>
+        <v>13.81843280792236</v>
       </c>
       <c r="C203" t="n">
-        <v>14.00955991023924</v>
+        <v>14.00955894337442</v>
       </c>
       <c r="D203" t="n">
-        <v>13.6464197721377</v>
+        <v>13.64641883033486</v>
       </c>
       <c r="E203" t="n">
-        <v>13.84710245605272</v>
+        <v>13.84710150039985</v>
       </c>
       <c r="F203" t="n">
         <v>8250000</v>
@@ -4492,16 +4492,16 @@
         <v>44550</v>
       </c>
       <c r="B204" t="n">
-        <v>13.47440528869629</v>
+        <v>13.47440624237061</v>
       </c>
       <c r="C204" t="n">
-        <v>13.86621408038928</v>
+        <v>13.86621506179454</v>
       </c>
       <c r="D204" t="n">
-        <v>13.29283478290215</v>
+        <v>13.29283572372549</v>
       </c>
       <c r="E204" t="n">
-        <v>13.81843232037181</v>
+        <v>13.81843329839523</v>
       </c>
       <c r="F204" t="n">
         <v>6680500</v>
@@ -4512,16 +4512,16 @@
         <v>44551</v>
       </c>
       <c r="B205" t="n">
-        <v>13.617751121521</v>
+        <v>13.61775016784668</v>
       </c>
       <c r="C205" t="n">
-        <v>13.6655328866758</v>
+        <v>13.66553192965524</v>
       </c>
       <c r="D205" t="n">
-        <v>13.36928667180511</v>
+        <v>13.36928573553119</v>
       </c>
       <c r="E205" t="n">
-        <v>13.48396236135982</v>
+        <v>13.48396141705496</v>
       </c>
       <c r="F205" t="n">
         <v>4083800</v>
@@ -4532,16 +4532,16 @@
         <v>44552</v>
       </c>
       <c r="B206" t="n">
-        <v>13.5317440032959</v>
+        <v>13.53174304962158</v>
       </c>
       <c r="C206" t="n">
-        <v>13.66553276223881</v>
+        <v>13.66553179913548</v>
       </c>
       <c r="D206" t="n">
-        <v>13.29283609105872</v>
+        <v>13.29283515422187</v>
       </c>
       <c r="E206" t="n">
-        <v>13.58908230323182</v>
+        <v>13.58908134551648</v>
       </c>
       <c r="F206" t="n">
         <v>6990400</v>
@@ -4552,16 +4552,16 @@
         <v>44553</v>
       </c>
       <c r="B207" t="n">
-        <v>13.4648494720459</v>
+        <v>13.46484851837158</v>
       </c>
       <c r="C207" t="n">
-        <v>13.65597561094082</v>
+        <v>13.65597464372962</v>
       </c>
       <c r="D207" t="n">
-        <v>13.32150418435372</v>
+        <v>13.32150324083211</v>
       </c>
       <c r="E207" t="n">
-        <v>13.41706770948184</v>
+        <v>13.41706675919176</v>
       </c>
       <c r="F207" t="n">
         <v>4198000</v>
@@ -4592,16 +4592,16 @@
         <v>44558</v>
       </c>
       <c r="B209" t="n">
-        <v>12.51877593994141</v>
+        <v>12.51877403259277</v>
       </c>
       <c r="C209" t="n">
-        <v>13.12082312363037</v>
+        <v>13.12082112455441</v>
       </c>
       <c r="D209" t="n">
-        <v>12.31809324159127</v>
+        <v>12.31809136481846</v>
       </c>
       <c r="E209" t="n">
-        <v>13.12082312363037</v>
+        <v>13.12082112455441</v>
       </c>
       <c r="F209" t="n">
         <v>22962600</v>
@@ -4632,16 +4632,16 @@
         <v>44560</v>
       </c>
       <c r="B211" t="n">
-        <v>12.38498497009277</v>
+        <v>12.38498687744141</v>
       </c>
       <c r="C211" t="n">
-        <v>12.499660647152</v>
+        <v>12.49966257216125</v>
       </c>
       <c r="D211" t="n">
-        <v>12.25119622450971</v>
+        <v>12.25119811125422</v>
       </c>
       <c r="E211" t="n">
-        <v>12.32764667588253</v>
+        <v>12.32764857440078</v>
       </c>
       <c r="F211" t="n">
         <v>5913100</v>
@@ -4712,16 +4712,16 @@
         <v>44567</v>
       </c>
       <c r="B215" t="n">
-        <v>11.07577037811279</v>
+        <v>11.07577133178711</v>
       </c>
       <c r="C215" t="n">
-        <v>11.62048009790152</v>
+        <v>11.62048109847782</v>
       </c>
       <c r="D215" t="n">
-        <v>11.02798861589103</v>
+        <v>11.02798956545112</v>
       </c>
       <c r="E215" t="n">
-        <v>11.56314271232445</v>
+        <v>11.56314370796374</v>
       </c>
       <c r="F215" t="n">
         <v>15779400</v>
@@ -4752,16 +4752,16 @@
         <v>44571</v>
       </c>
       <c r="B217" t="n">
-        <v>10.79863834381104</v>
+        <v>10.79863739013672</v>
       </c>
       <c r="C217" t="n">
-        <v>10.85597573519133</v>
+        <v>10.8559747764533</v>
       </c>
       <c r="D217" t="n">
-        <v>10.54061734851548</v>
+        <v>10.54061641762812</v>
       </c>
       <c r="E217" t="n">
-        <v>10.76041311243704</v>
+        <v>10.76041216213855</v>
       </c>
       <c r="F217" t="n">
         <v>8755800</v>
@@ -4792,16 +4792,16 @@
         <v>44573</v>
       </c>
       <c r="B219" t="n">
-        <v>11.27645301818848</v>
+        <v>11.27645206451416</v>
       </c>
       <c r="C219" t="n">
-        <v>11.28600955287783</v>
+        <v>11.2860085983953</v>
       </c>
       <c r="D219" t="n">
-        <v>10.80819375474579</v>
+        <v>10.80819284067318</v>
       </c>
       <c r="E219" t="n">
-        <v>10.94198159495152</v>
+        <v>10.94198066956419</v>
       </c>
       <c r="F219" t="n">
         <v>7862000</v>
@@ -4812,16 +4812,16 @@
         <v>44574</v>
       </c>
       <c r="B220" t="n">
-        <v>11.48669147491455</v>
+        <v>11.48669242858887</v>
       </c>
       <c r="C220" t="n">
-        <v>11.57269754742197</v>
+        <v>11.57269850823688</v>
       </c>
       <c r="D220" t="n">
-        <v>11.15222007350554</v>
+        <v>11.15222099941061</v>
       </c>
       <c r="E220" t="n">
-        <v>11.27645228227571</v>
+        <v>11.27645321849507</v>
       </c>
       <c r="F220" t="n">
         <v>9668300</v>
@@ -4832,16 +4832,16 @@
         <v>44575</v>
       </c>
       <c r="B221" t="n">
-        <v>11.59181118011475</v>
+        <v>11.59181308746338</v>
       </c>
       <c r="C221" t="n">
-        <v>11.65870509911001</v>
+        <v>11.65870701746556</v>
       </c>
       <c r="D221" t="n">
-        <v>11.39112851176765</v>
+        <v>11.3911303860954</v>
       </c>
       <c r="E221" t="n">
-        <v>11.4102406694686</v>
+        <v>11.41024254694112</v>
       </c>
       <c r="F221" t="n">
         <v>7586600</v>
@@ -4852,16 +4852,16 @@
         <v>44578</v>
       </c>
       <c r="B222" t="n">
-        <v>11.47713565826416</v>
+        <v>11.47713661193848</v>
       </c>
       <c r="C222" t="n">
-        <v>11.6109234981016</v>
+        <v>11.61092446289281</v>
       </c>
       <c r="D222" t="n">
-        <v>11.41024082698413</v>
+        <v>11.41024177509993</v>
       </c>
       <c r="E222" t="n">
-        <v>11.59181134013681</v>
+        <v>11.59181230333992</v>
       </c>
       <c r="F222" t="n">
         <v>4569300</v>
@@ -4872,16 +4872,16 @@
         <v>44579</v>
       </c>
       <c r="B223" t="n">
-        <v>11.39112854003906</v>
+        <v>11.39112949371338</v>
       </c>
       <c r="C223" t="n">
-        <v>11.49624768605842</v>
+        <v>11.49624864853339</v>
       </c>
       <c r="D223" t="n">
-        <v>11.29556501721325</v>
+        <v>11.29556596288691</v>
       </c>
       <c r="E223" t="n">
-        <v>11.47713552831003</v>
+        <v>11.47713648918492</v>
       </c>
       <c r="F223" t="n">
         <v>7771300</v>
@@ -4892,16 +4892,16 @@
         <v>44580</v>
       </c>
       <c r="B224" t="n">
-        <v>11.49624824523926</v>
+        <v>11.49624919891357</v>
       </c>
       <c r="C224" t="n">
-        <v>11.69693092384569</v>
+        <v>11.69693189416769</v>
       </c>
       <c r="D224" t="n">
-        <v>11.41979778780455</v>
+        <v>11.4197987351369</v>
       </c>
       <c r="E224" t="n">
-        <v>11.41979778780455</v>
+        <v>11.4197987351369</v>
       </c>
       <c r="F224" t="n">
         <v>5074700</v>
@@ -4932,16 +4932,16 @@
         <v>44582</v>
       </c>
       <c r="B226" t="n">
-        <v>11.48669147491455</v>
+        <v>11.48669242858887</v>
       </c>
       <c r="C226" t="n">
-        <v>11.63003584045484</v>
+        <v>11.63003680603022</v>
       </c>
       <c r="D226" t="n">
-        <v>11.21911398924284</v>
+        <v>11.21911492070173</v>
       </c>
       <c r="E226" t="n">
-        <v>11.37201488884882</v>
+        <v>11.37201583300219</v>
       </c>
       <c r="F226" t="n">
         <v>8537100</v>
@@ -5012,16 +5012,16 @@
         <v>44588</v>
       </c>
       <c r="B230" t="n">
-        <v>11.99317741394043</v>
+        <v>11.99317646026611</v>
       </c>
       <c r="C230" t="n">
-        <v>12.13652179718475</v>
+        <v>12.13652083211196</v>
       </c>
       <c r="D230" t="n">
-        <v>11.66826250646786</v>
+        <v>11.66826157863015</v>
       </c>
       <c r="E230" t="n">
-        <v>11.85938865458074</v>
+        <v>11.85938771154504</v>
       </c>
       <c r="F230" t="n">
         <v>13761300</v>
@@ -5032,16 +5032,16 @@
         <v>44589</v>
       </c>
       <c r="B231" t="n">
-        <v>11.83071994781494</v>
+        <v>11.83071899414062</v>
       </c>
       <c r="C231" t="n">
-        <v>12.04095916619962</v>
+        <v>12.04095819557792</v>
       </c>
       <c r="D231" t="n">
-        <v>11.4580232758641</v>
+        <v>11.45802235223286</v>
       </c>
       <c r="E231" t="n">
-        <v>11.94539563656258</v>
+        <v>11.94539467364426</v>
       </c>
       <c r="F231" t="n">
         <v>14924100</v>
@@ -5052,16 +5052,16 @@
         <v>44592</v>
       </c>
       <c r="B232" t="n">
-        <v>11.9740629196167</v>
+        <v>11.97406387329102</v>
       </c>
       <c r="C232" t="n">
-        <v>12.12696381992561</v>
+        <v>12.12696478577772</v>
       </c>
       <c r="D232" t="n">
-        <v>11.76382463737258</v>
+        <v>11.76382557430247</v>
       </c>
       <c r="E232" t="n">
-        <v>11.81160548519817</v>
+        <v>11.81160642593357</v>
       </c>
       <c r="F232" t="n">
         <v>12073700</v>
@@ -5092,16 +5092,16 @@
         <v>44594</v>
       </c>
       <c r="B234" t="n">
-        <v>11.94539642333984</v>
+        <v>11.94539546966553</v>
       </c>
       <c r="C234" t="n">
-        <v>12.27986788773793</v>
+        <v>12.2798669073607</v>
       </c>
       <c r="D234" t="n">
-        <v>11.81160765530833</v>
+        <v>11.81160671231519</v>
       </c>
       <c r="E234" t="n">
-        <v>12.0218468875403</v>
+        <v>12.02184592776248</v>
       </c>
       <c r="F234" t="n">
         <v>9442200</v>
@@ -5112,16 +5112,16 @@
         <v>44595</v>
       </c>
       <c r="B235" t="n">
-        <v>11.94539642333984</v>
+        <v>11.94539546966553</v>
       </c>
       <c r="C235" t="n">
-        <v>12.21297304804146</v>
+        <v>12.21297207300486</v>
       </c>
       <c r="D235" t="n">
-        <v>11.8976146553742</v>
+        <v>11.8976137055146</v>
       </c>
       <c r="E235" t="n">
-        <v>12.04095995927113</v>
+        <v>12.04095899796739</v>
       </c>
       <c r="F235" t="n">
         <v>8796800</v>
@@ -5172,16 +5172,16 @@
         <v>44600</v>
       </c>
       <c r="B238" t="n">
-        <v>11.95495223999023</v>
+        <v>11.95495128631592</v>
       </c>
       <c r="C238" t="n">
-        <v>12.20341668937472</v>
+        <v>12.20341571587981</v>
       </c>
       <c r="D238" t="n">
-        <v>11.83072001529799</v>
+        <v>11.83071907153397</v>
       </c>
       <c r="E238" t="n">
-        <v>12.14607838899316</v>
+        <v>12.14607742007226</v>
       </c>
       <c r="F238" t="n">
         <v>8002100</v>
@@ -5212,16 +5212,16 @@
         <v>44602</v>
       </c>
       <c r="B240" t="n">
-        <v>12.11740970611572</v>
+        <v>12.11740875244141</v>
       </c>
       <c r="C240" t="n">
-        <v>12.29897932000246</v>
+        <v>12.29897835203811</v>
       </c>
       <c r="D240" t="n">
-        <v>11.88805741573067</v>
+        <v>11.88805648010703</v>
       </c>
       <c r="E240" t="n">
-        <v>11.95495225146694</v>
+        <v>11.95495131057848</v>
       </c>
       <c r="F240" t="n">
         <v>4310600</v>
@@ -5232,16 +5232,16 @@
         <v>44603</v>
       </c>
       <c r="B241" t="n">
-        <v>11.79249572753906</v>
+        <v>11.79249382019043</v>
       </c>
       <c r="C241" t="n">
-        <v>12.21297328893528</v>
+        <v>12.21297131357752</v>
       </c>
       <c r="D241" t="n">
-        <v>11.74471395863095</v>
+        <v>11.74471205901066</v>
       </c>
       <c r="E241" t="n">
-        <v>12.18430459213499</v>
+        <v>12.18430262141418</v>
       </c>
       <c r="F241" t="n">
         <v>7316000</v>
@@ -5252,16 +5252,16 @@
         <v>44606</v>
       </c>
       <c r="B242" t="n">
-        <v>11.78293800354004</v>
+        <v>11.78293895721436</v>
       </c>
       <c r="C242" t="n">
-        <v>11.97406414854188</v>
+        <v>11.97406511768535</v>
       </c>
       <c r="D242" t="n">
-        <v>11.639593622629</v>
+        <v>11.63959456470146</v>
       </c>
       <c r="E242" t="n">
-        <v>11.79249453863047</v>
+        <v>11.79249549307826</v>
       </c>
       <c r="F242" t="n">
         <v>5445000</v>
@@ -5292,16 +5292,16 @@
         <v>44608</v>
       </c>
       <c r="B244" t="n">
-        <v>12.4709939956665</v>
+        <v>12.47099304199219</v>
       </c>
       <c r="C244" t="n">
-        <v>12.64300708371169</v>
+        <v>12.6430061168833</v>
       </c>
       <c r="D244" t="n">
-        <v>11.56314405359208</v>
+        <v>11.56314316934232</v>
       </c>
       <c r="E244" t="n">
-        <v>11.65870667775909</v>
+        <v>11.65870578620152</v>
       </c>
       <c r="F244" t="n">
         <v>21489000</v>
@@ -5352,16 +5352,16 @@
         <v>44613</v>
       </c>
       <c r="B247" t="n">
-        <v>11.90717124938965</v>
+        <v>11.90717029571533</v>
       </c>
       <c r="C247" t="n">
-        <v>12.27986794770807</v>
+        <v>12.27986696418357</v>
       </c>
       <c r="D247" t="n">
-        <v>11.72560162386719</v>
+        <v>11.72560068473523</v>
       </c>
       <c r="E247" t="n">
-        <v>12.1365226431111</v>
+        <v>12.13652167106747</v>
       </c>
       <c r="F247" t="n">
         <v>4718800</v>
@@ -5372,16 +5372,16 @@
         <v>44614</v>
       </c>
       <c r="B248" t="n">
-        <v>12.51877593994141</v>
+        <v>12.51877403259277</v>
       </c>
       <c r="C248" t="n">
-        <v>12.63345163737556</v>
+        <v>12.63344971255505</v>
       </c>
       <c r="D248" t="n">
-        <v>12.08874093536153</v>
+        <v>12.08873909353262</v>
       </c>
       <c r="E248" t="n">
-        <v>12.14607923975932</v>
+        <v>12.1460773891944</v>
       </c>
       <c r="F248" t="n">
         <v>15416600</v>
@@ -5392,16 +5392,16 @@
         <v>44615</v>
       </c>
       <c r="B249" t="n">
-        <v>12.73856830596924</v>
+        <v>12.73856925964355</v>
       </c>
       <c r="C249" t="n">
-        <v>12.87235704914128</v>
+        <v>12.87235801283171</v>
       </c>
       <c r="D249" t="n">
-        <v>12.51877349007365</v>
+        <v>12.51877442729301</v>
       </c>
       <c r="E249" t="n">
-        <v>12.51877349007365</v>
+        <v>12.51877442729301</v>
       </c>
       <c r="F249" t="n">
         <v>5598100</v>
@@ -5412,16 +5412,16 @@
         <v>44616</v>
       </c>
       <c r="B250" t="n">
-        <v>12.93925189971924</v>
+        <v>12.93925285339355</v>
       </c>
       <c r="C250" t="n">
-        <v>13.04437104821551</v>
+        <v>13.04437200963752</v>
       </c>
       <c r="D250" t="n">
-        <v>12.21297166094141</v>
+        <v>12.21297256108599</v>
       </c>
       <c r="E250" t="n">
-        <v>12.41365433451525</v>
+        <v>12.41365524945094</v>
       </c>
       <c r="F250" t="n">
         <v>6603100</v>
@@ -5432,16 +5432,16 @@
         <v>44617</v>
       </c>
       <c r="B251" t="n">
-        <v>12.86280250549316</v>
+        <v>12.86280155181885</v>
       </c>
       <c r="C251" t="n">
-        <v>13.13993565745039</v>
+        <v>13.13993468322886</v>
       </c>
       <c r="D251" t="n">
-        <v>12.72901374161811</v>
+        <v>12.72901279786317</v>
       </c>
       <c r="E251" t="n">
-        <v>12.83413381014901</v>
+        <v>12.83413285860025</v>
       </c>
       <c r="F251" t="n">
         <v>8089600</v>
@@ -5452,16 +5452,16 @@
         <v>44622</v>
       </c>
       <c r="B252" t="n">
-        <v>12.68123149871826</v>
+        <v>12.68123245239258</v>
       </c>
       <c r="C252" t="n">
-        <v>12.95836462034722</v>
+        <v>12.95836559486294</v>
       </c>
       <c r="D252" t="n">
-        <v>12.6430053606275</v>
+        <v>12.64300631142708</v>
       </c>
       <c r="E252" t="n">
-        <v>12.8628010978429</v>
+        <v>12.86280206517191</v>
       </c>
       <c r="F252" t="n">
         <v>4196000</v>
@@ -5552,16 +5552,16 @@
         <v>44629</v>
       </c>
       <c r="B257" t="n">
-        <v>12.80546474456787</v>
+        <v>12.80546379089355</v>
       </c>
       <c r="C257" t="n">
-        <v>13.03481705109711</v>
+        <v>13.03481608034201</v>
       </c>
       <c r="D257" t="n">
-        <v>11.75427039436804</v>
+        <v>11.75426951898038</v>
       </c>
       <c r="E257" t="n">
-        <v>11.89761478850756</v>
+        <v>11.89761390244447</v>
       </c>
       <c r="F257" t="n">
         <v>14771600</v>
@@ -5572,16 +5572,16 @@
         <v>44630</v>
       </c>
       <c r="B258" t="n">
-        <v>12.71945762634277</v>
+        <v>12.71945858001709</v>
       </c>
       <c r="C258" t="n">
-        <v>13.02525946183787</v>
+        <v>13.02526043844047</v>
       </c>
       <c r="D258" t="n">
-        <v>12.24164180270101</v>
+        <v>12.24164272054984</v>
       </c>
       <c r="E258" t="n">
-        <v>12.67167586170632</v>
+        <v>12.67167681179808</v>
       </c>
       <c r="F258" t="n">
         <v>9185900</v>
@@ -5592,16 +5592,16 @@
         <v>44631</v>
       </c>
       <c r="B259" t="n">
-        <v>12.40409755706787</v>
+        <v>12.40409851074219</v>
       </c>
       <c r="C259" t="n">
-        <v>12.92969511198934</v>
+        <v>12.9296961060736</v>
       </c>
       <c r="D259" t="n">
-        <v>12.20341579878139</v>
+        <v>12.20341673702652</v>
       </c>
       <c r="E259" t="n">
-        <v>12.92969511198934</v>
+        <v>12.9296961060736</v>
       </c>
       <c r="F259" t="n">
         <v>7293900</v>
@@ -5612,16 +5612,16 @@
         <v>44634</v>
       </c>
       <c r="B260" t="n">
-        <v>12.51877593994141</v>
+        <v>12.51877403259277</v>
       </c>
       <c r="C260" t="n">
-        <v>12.74812733480972</v>
+        <v>12.74812539251733</v>
       </c>
       <c r="D260" t="n">
-        <v>12.38498717058751</v>
+        <v>12.3849852836228</v>
       </c>
       <c r="E260" t="n">
-        <v>12.43276893902543</v>
+        <v>12.43276704478074</v>
       </c>
       <c r="F260" t="n">
         <v>4274300</v>
@@ -5632,16 +5632,16 @@
         <v>44635</v>
       </c>
       <c r="B261" t="n">
-        <v>12.82457637786865</v>
+        <v>12.82457542419434</v>
       </c>
       <c r="C261" t="n">
-        <v>12.90102683434848</v>
+        <v>12.90102587498907</v>
       </c>
       <c r="D261" t="n">
-        <v>12.29897880604886</v>
+        <v>12.29897789145957</v>
       </c>
       <c r="E261" t="n">
-        <v>12.29897880604886</v>
+        <v>12.29897789145957</v>
       </c>
       <c r="F261" t="n">
         <v>8181800</v>
@@ -5672,16 +5672,16 @@
         <v>44637</v>
       </c>
       <c r="B263" t="n">
-        <v>13.12082099914551</v>
+        <v>13.12082195281982</v>
       </c>
       <c r="C263" t="n">
-        <v>13.24505321242422</v>
+        <v>13.24505417512824</v>
       </c>
       <c r="D263" t="n">
-        <v>12.87235748394937</v>
+        <v>12.87235841956435</v>
       </c>
       <c r="E263" t="n">
-        <v>13.09215230726928</v>
+        <v>13.09215325885984</v>
       </c>
       <c r="F263" t="n">
         <v>6159800</v>
@@ -5692,16 +5692,16 @@
         <v>44638</v>
       </c>
       <c r="B264" t="n">
-        <v>13.58908176422119</v>
+        <v>13.58908271789551</v>
       </c>
       <c r="C264" t="n">
-        <v>13.78020790415765</v>
+        <v>13.78020887124509</v>
       </c>
       <c r="D264" t="n">
-        <v>12.98703373990036</v>
+        <v>12.98703465132328</v>
       </c>
       <c r="E264" t="n">
-        <v>13.04437112620064</v>
+        <v>13.04437204164746</v>
       </c>
       <c r="F264" t="n">
         <v>10366600</v>
@@ -5712,16 +5712,16 @@
         <v>44641</v>
       </c>
       <c r="B265" t="n">
-        <v>13.5604133605957</v>
+        <v>13.56041145324707</v>
       </c>
       <c r="C265" t="n">
-        <v>13.62730819901854</v>
+        <v>13.62730628226077</v>
       </c>
       <c r="D265" t="n">
-        <v>13.18771758255467</v>
+        <v>13.1877157276278</v>
       </c>
       <c r="E265" t="n">
-        <v>13.58908296764609</v>
+        <v>13.58908105626492</v>
       </c>
       <c r="F265" t="n">
         <v>3916100</v>
@@ -5732,16 +5732,16 @@
         <v>44642</v>
       </c>
       <c r="B266" t="n">
-        <v>14.08601093292236</v>
+        <v>14.08600997924805</v>
       </c>
       <c r="C266" t="n">
-        <v>14.26758146491387</v>
+        <v>14.26758049894657</v>
       </c>
       <c r="D266" t="n">
-        <v>13.62730815783909</v>
+        <v>13.62730723522063</v>
       </c>
       <c r="E266" t="n">
-        <v>13.66553338909603</v>
+        <v>13.66553246388958</v>
       </c>
       <c r="F266" t="n">
         <v>13737200</v>
@@ -5752,16 +5752,16 @@
         <v>44643</v>
       </c>
       <c r="B267" t="n">
-        <v>14.38225555419922</v>
+        <v>14.38225650787354</v>
       </c>
       <c r="C267" t="n">
-        <v>14.59249475833878</v>
+        <v>14.59249572595387</v>
       </c>
       <c r="D267" t="n">
-        <v>13.87577106870787</v>
+        <v>13.87577198879766</v>
       </c>
       <c r="E267" t="n">
-        <v>14.02867197667799</v>
+        <v>14.0286729069065</v>
       </c>
       <c r="F267" t="n">
         <v>8813400</v>
@@ -5772,16 +5772,16 @@
         <v>44644</v>
       </c>
       <c r="B268" t="n">
-        <v>14.63071918487549</v>
+        <v>14.6307201385498</v>
       </c>
       <c r="C268" t="n">
-        <v>14.7453948595791</v>
+        <v>14.74539582072832</v>
       </c>
       <c r="D268" t="n">
-        <v>14.35358607650145</v>
+        <v>14.35358701211139</v>
       </c>
       <c r="E268" t="n">
-        <v>14.39181130140265</v>
+        <v>14.39181223950423</v>
       </c>
       <c r="F268" t="n">
         <v>7986800</v>
@@ -5792,16 +5792,16 @@
         <v>44645</v>
       </c>
       <c r="B269" t="n">
-        <v>15.13720512390137</v>
+        <v>15.13720321655273</v>
       </c>
       <c r="C269" t="n">
-        <v>15.24232427482575</v>
+        <v>15.24232235423169</v>
       </c>
       <c r="D269" t="n">
-        <v>14.64027624019771</v>
+        <v>14.64027439546411</v>
       </c>
       <c r="E269" t="n">
-        <v>14.71672669748114</v>
+        <v>14.71672484311448</v>
       </c>
       <c r="F269" t="n">
         <v>8426200</v>
@@ -5832,16 +5832,16 @@
         <v>44649</v>
       </c>
       <c r="B271" t="n">
-        <v>15.50034427642822</v>
+        <v>15.50034332275391</v>
       </c>
       <c r="C271" t="n">
-        <v>15.93037923607671</v>
+        <v>15.93037825594406</v>
       </c>
       <c r="D271" t="n">
-        <v>15.43345035442127</v>
+        <v>15.43344940486267</v>
       </c>
       <c r="E271" t="n">
-        <v>15.72969564733319</v>
+        <v>15.7296946795478</v>
       </c>
       <c r="F271" t="n">
         <v>7323700</v>
@@ -5852,16 +5852,16 @@
         <v>44650</v>
       </c>
       <c r="B272" t="n">
-        <v>15.45256328582764</v>
+        <v>15.45256423950195</v>
       </c>
       <c r="C272" t="n">
-        <v>15.82525903236704</v>
+        <v>15.82526000904275</v>
       </c>
       <c r="D272" t="n">
-        <v>15.39522589929603</v>
+        <v>15.3952268494317</v>
       </c>
       <c r="E272" t="n">
-        <v>15.51945720723495</v>
+        <v>15.51945816503771</v>
       </c>
       <c r="F272" t="n">
         <v>8944100</v>
@@ -5872,16 +5872,16 @@
         <v>44651</v>
       </c>
       <c r="B273" t="n">
-        <v>15.56723880767822</v>
+        <v>15.56723976135254</v>
       </c>
       <c r="C273" t="n">
-        <v>15.8157014064154</v>
+        <v>15.81570237531094</v>
       </c>
       <c r="D273" t="n">
-        <v>15.42389261715424</v>
+        <v>15.42389356204693</v>
       </c>
       <c r="E273" t="n">
-        <v>15.42389261715424</v>
+        <v>15.42389356204693</v>
       </c>
       <c r="F273" t="n">
         <v>17319900</v>
@@ -5912,16 +5912,16 @@
         <v>44655</v>
       </c>
       <c r="B275" t="n">
-        <v>15.56723880767822</v>
+        <v>15.56723976135254</v>
       </c>
       <c r="C275" t="n">
-        <v>15.86348407749757</v>
+        <v>15.86348504932035</v>
       </c>
       <c r="D275" t="n">
-        <v>15.52901267081248</v>
+        <v>15.52901362214501</v>
       </c>
       <c r="E275" t="n">
-        <v>15.75836402383932</v>
+        <v>15.75836498922228</v>
       </c>
       <c r="F275" t="n">
         <v>2672100</v>
@@ -5932,16 +5932,16 @@
         <v>44656</v>
       </c>
       <c r="B276" t="n">
-        <v>15.45256328582764</v>
+        <v>15.45256423950195</v>
       </c>
       <c r="C276" t="n">
-        <v>15.65324505004958</v>
+        <v>15.65324601610922</v>
       </c>
       <c r="D276" t="n">
-        <v>15.35699975979319</v>
+        <v>15.35700070756969</v>
       </c>
       <c r="E276" t="n">
-        <v>15.57679459376655</v>
+        <v>15.57679555510796</v>
       </c>
       <c r="F276" t="n">
         <v>10716200</v>
@@ -5952,16 +5952,16 @@
         <v>44657</v>
       </c>
       <c r="B277" t="n">
-        <v>15.56723880767822</v>
+        <v>15.56723976135254</v>
       </c>
       <c r="C277" t="n">
-        <v>15.70102664126324</v>
+        <v>15.70102760313362</v>
       </c>
       <c r="D277" t="n">
-        <v>15.13720388155133</v>
+        <v>15.13720480888101</v>
       </c>
       <c r="E277" t="n">
-        <v>15.38566830301103</v>
+        <v>15.38566924556204</v>
       </c>
       <c r="F277" t="n">
         <v>10924400</v>
@@ -6012,16 +6012,16 @@
         <v>44662</v>
       </c>
       <c r="B280" t="n">
-        <v>15.29010677337646</v>
+        <v>15.29010581970215</v>
       </c>
       <c r="C280" t="n">
-        <v>15.4907885498701</v>
+        <v>15.49078758367887</v>
       </c>
       <c r="D280" t="n">
-        <v>15.21365631241849</v>
+        <v>15.21365536351254</v>
       </c>
       <c r="E280" t="n">
-        <v>15.38567030525462</v>
+        <v>15.38566934561982</v>
       </c>
       <c r="F280" t="n">
         <v>10289300</v>
@@ -6032,16 +6032,16 @@
         <v>44663</v>
       </c>
       <c r="B281" t="n">
-        <v>15.72014141082764</v>
+        <v>15.72014236450195</v>
       </c>
       <c r="C281" t="n">
-        <v>15.82525965313857</v>
+        <v>15.82526061318996</v>
       </c>
       <c r="D281" t="n">
-        <v>15.39522650319881</v>
+        <v>15.39522743716192</v>
       </c>
       <c r="E281" t="n">
-        <v>15.48123349773131</v>
+        <v>15.48123443691209</v>
       </c>
       <c r="F281" t="n">
         <v>9798400</v>
@@ -6052,16 +6052,16 @@
         <v>44664</v>
       </c>
       <c r="B282" t="n">
-        <v>15.76792240142822</v>
+        <v>15.76792144775391</v>
       </c>
       <c r="C282" t="n">
-        <v>16.02594338726869</v>
+        <v>16.02594241798877</v>
       </c>
       <c r="D282" t="n">
-        <v>15.69147194148172</v>
+        <v>15.69147099243128</v>
       </c>
       <c r="E282" t="n">
-        <v>15.78703547209553</v>
+        <v>15.78703451726522</v>
       </c>
       <c r="F282" t="n">
         <v>7212700</v>
@@ -6072,16 +6072,16 @@
         <v>44665</v>
       </c>
       <c r="B283" t="n">
-        <v>15.64369010925293</v>
+        <v>15.64369106292725</v>
       </c>
       <c r="C283" t="n">
-        <v>15.79659101958422</v>
+        <v>15.79659198257972</v>
       </c>
       <c r="D283" t="n">
-        <v>15.4812326641856</v>
+        <v>15.48123360795615</v>
       </c>
       <c r="E283" t="n">
-        <v>15.72014056441858</v>
+        <v>15.72014152275348</v>
       </c>
       <c r="F283" t="n">
         <v>4607000</v>
@@ -6112,16 +6112,16 @@
         <v>44670</v>
       </c>
       <c r="B285" t="n">
-        <v>15.61502170562744</v>
+        <v>15.61502265930176</v>
       </c>
       <c r="C285" t="n">
-        <v>15.77747916318553</v>
+        <v>15.7774801267818</v>
       </c>
       <c r="D285" t="n">
-        <v>15.18498763441659</v>
+        <v>15.18498856182694</v>
       </c>
       <c r="E285" t="n">
-        <v>15.32833293239446</v>
+        <v>15.3283338685595</v>
       </c>
       <c r="F285" t="n">
         <v>7756800</v>
@@ -6192,16 +6192,16 @@
         <v>44677</v>
       </c>
       <c r="B289" t="n">
-        <v>15.12764930725098</v>
+        <v>15.12764835357666</v>
       </c>
       <c r="C289" t="n">
-        <v>15.30921983544218</v>
+        <v>15.30921887032133</v>
       </c>
       <c r="D289" t="n">
-        <v>15.02253015133491</v>
+        <v>15.02252920428749</v>
       </c>
       <c r="E289" t="n">
-        <v>15.2136563036193</v>
+        <v>15.21365534452294</v>
       </c>
       <c r="F289" t="n">
         <v>9387600</v>
@@ -6252,16 +6252,16 @@
         <v>44680</v>
       </c>
       <c r="B292" t="n">
-        <v>14.72057247161865</v>
+        <v>14.72057151794434</v>
       </c>
       <c r="C292" t="n">
-        <v>15.13482972068782</v>
+        <v>15.13482874017579</v>
       </c>
       <c r="D292" t="n">
-        <v>14.72057247161865</v>
+        <v>14.72057151794434</v>
       </c>
       <c r="E292" t="n">
-        <v>15.06739283595885</v>
+        <v>15.06739185981573</v>
       </c>
       <c r="F292" t="n">
         <v>7651000</v>
@@ -6272,16 +6272,16 @@
         <v>44683</v>
       </c>
       <c r="B293" t="n">
-        <v>14.69167041778564</v>
+        <v>14.69167137145996</v>
       </c>
       <c r="C293" t="n">
-        <v>14.97105296602926</v>
+        <v>14.97105393783902</v>
       </c>
       <c r="D293" t="n">
-        <v>14.44118925901314</v>
+        <v>14.44119019642807</v>
       </c>
       <c r="E293" t="n">
-        <v>14.54716255167152</v>
+        <v>14.54716349596546</v>
       </c>
       <c r="F293" t="n">
         <v>5536000</v>
@@ -6292,16 +6292,16 @@
         <v>44684</v>
       </c>
       <c r="B294" t="n">
-        <v>14.62423324584961</v>
+        <v>14.62423419952393</v>
       </c>
       <c r="C294" t="n">
-        <v>14.85544619454671</v>
+        <v>14.85544716329886</v>
       </c>
       <c r="D294" t="n">
-        <v>14.47972446384498</v>
+        <v>14.4797254080956</v>
       </c>
       <c r="E294" t="n">
-        <v>14.70130422874864</v>
+        <v>14.70130518744891</v>
       </c>
       <c r="F294" t="n">
         <v>5388000</v>
@@ -6312,16 +6312,16 @@
         <v>44685</v>
       </c>
       <c r="B295" t="n">
-        <v>14.79764175415039</v>
+        <v>14.79764270782471</v>
       </c>
       <c r="C295" t="n">
-        <v>14.95178463095864</v>
+        <v>14.95178559456712</v>
       </c>
       <c r="D295" t="n">
-        <v>14.2581449009764</v>
+        <v>14.25814581988137</v>
       </c>
       <c r="E295" t="n">
-        <v>14.43155414440306</v>
+        <v>14.43155507448386</v>
       </c>
       <c r="F295" t="n">
         <v>5127000</v>
@@ -6332,16 +6332,16 @@
         <v>44686</v>
       </c>
       <c r="B296" t="n">
-        <v>14.4700927734375</v>
+        <v>14.47009181976318</v>
       </c>
       <c r="C296" t="n">
-        <v>14.74947534496982</v>
+        <v>14.74947437288235</v>
       </c>
       <c r="D296" t="n">
-        <v>14.32558397651884</v>
+        <v>14.32558303236861</v>
       </c>
       <c r="E296" t="n">
-        <v>14.54716376429064</v>
+        <v>14.54716280553684</v>
       </c>
       <c r="F296" t="n">
         <v>6151000</v>
@@ -6412,16 +6412,16 @@
         <v>44692</v>
       </c>
       <c r="B300" t="n">
-        <v>14.60496616363525</v>
+        <v>14.60496520996094</v>
       </c>
       <c r="C300" t="n">
-        <v>14.7880104511626</v>
+        <v>14.78800948553586</v>
       </c>
       <c r="D300" t="n">
-        <v>14.4026545882811</v>
+        <v>14.40265364781732</v>
       </c>
       <c r="E300" t="n">
-        <v>14.45082418598612</v>
+        <v>14.45082324237696</v>
       </c>
       <c r="F300" t="n">
         <v>6181500</v>
@@ -6432,16 +6432,16 @@
         <v>44693</v>
       </c>
       <c r="B301" t="n">
-        <v>14.68203544616699</v>
+        <v>14.68203639984131</v>
       </c>
       <c r="C301" t="n">
-        <v>15.07702444767837</v>
+        <v>15.07702542700927</v>
       </c>
       <c r="D301" t="n">
-        <v>14.42192111880329</v>
+        <v>14.42192205558183</v>
       </c>
       <c r="E301" t="n">
-        <v>14.42192111880329</v>
+        <v>14.42192205558183</v>
       </c>
       <c r="F301" t="n">
         <v>8258700</v>
@@ -6452,16 +6452,16 @@
         <v>44694</v>
       </c>
       <c r="B302" t="n">
-        <v>14.91324901580811</v>
+        <v>14.91325092315674</v>
       </c>
       <c r="C302" t="n">
-        <v>15.09629328979575</v>
+        <v>15.09629522055506</v>
       </c>
       <c r="D302" t="n">
-        <v>14.62423328847366</v>
+        <v>14.62423515885826</v>
       </c>
       <c r="E302" t="n">
-        <v>14.72057155799894</v>
+        <v>14.72057344070485</v>
       </c>
       <c r="F302" t="n">
         <v>5016200</v>
@@ -6492,16 +6492,16 @@
         <v>44698</v>
       </c>
       <c r="B304" t="n">
-        <v>15.25043678283691</v>
+        <v>15.2504358291626</v>
       </c>
       <c r="C304" t="n">
-        <v>15.26970498992616</v>
+        <v>15.26970403504692</v>
       </c>
       <c r="D304" t="n">
-        <v>14.84581362154963</v>
+        <v>14.84581269317811</v>
       </c>
       <c r="E304" t="n">
-        <v>14.84581362154963</v>
+        <v>14.84581269317811</v>
       </c>
       <c r="F304" t="n">
         <v>7407200</v>
@@ -6512,16 +6512,16 @@
         <v>44699</v>
       </c>
       <c r="B305" t="n">
-        <v>14.83617782592773</v>
+        <v>14.83617973327637</v>
       </c>
       <c r="C305" t="n">
-        <v>15.2504350435133</v>
+        <v>15.25043700411911</v>
       </c>
       <c r="D305" t="n">
-        <v>14.81691053979462</v>
+        <v>14.81691244466624</v>
       </c>
       <c r="E305" t="n">
-        <v>15.23116775738018</v>
+        <v>15.23116971550898</v>
       </c>
       <c r="F305" t="n">
         <v>6842800</v>
@@ -6532,16 +6532,16 @@
         <v>44700</v>
       </c>
       <c r="B306" t="n">
-        <v>14.88434886932373</v>
+        <v>14.88434791564941</v>
       </c>
       <c r="C306" t="n">
-        <v>14.95178667425537</v>
+        <v>14.95178571626016</v>
       </c>
       <c r="D306" t="n">
-        <v>14.66277000403615</v>
+        <v>14.6627690645589</v>
       </c>
       <c r="E306" t="n">
-        <v>14.92288436410238</v>
+        <v>14.92288340795901</v>
       </c>
       <c r="F306" t="n">
         <v>6219800</v>
@@ -6612,16 +6612,16 @@
         <v>44706</v>
       </c>
       <c r="B310" t="n">
-        <v>15.14446258544922</v>
+        <v>15.14446353912354</v>
       </c>
       <c r="C310" t="n">
-        <v>15.44311332823613</v>
+        <v>15.44311430071703</v>
       </c>
       <c r="D310" t="n">
-        <v>14.94215102904739</v>
+        <v>14.94215196998178</v>
       </c>
       <c r="E310" t="n">
-        <v>15.16372987147109</v>
+        <v>15.16373082635871</v>
       </c>
       <c r="F310" t="n">
         <v>8129200</v>
@@ -6632,16 +6632,16 @@
         <v>44707</v>
       </c>
       <c r="B311" t="n">
-        <v>15.50091648101807</v>
+        <v>15.50091743469238</v>
       </c>
       <c r="C311" t="n">
-        <v>15.60688977236364</v>
+        <v>15.60689073255783</v>
       </c>
       <c r="D311" t="n">
-        <v>15.03848966141599</v>
+        <v>15.03849058664008</v>
       </c>
       <c r="E311" t="n">
-        <v>15.07702515315295</v>
+        <v>15.07702608074788</v>
       </c>
       <c r="F311" t="n">
         <v>6641000</v>
@@ -6652,16 +6652,16 @@
         <v>44708</v>
       </c>
       <c r="B312" t="n">
-        <v>15.22153472900391</v>
+        <v>15.22153377532959</v>
       </c>
       <c r="C312" t="n">
-        <v>15.51055139146295</v>
+        <v>15.51055041968089</v>
       </c>
       <c r="D312" t="n">
-        <v>15.13482963839033</v>
+        <v>15.13482869014834</v>
       </c>
       <c r="E312" t="n">
-        <v>15.43348040397503</v>
+        <v>15.43347943702168</v>
       </c>
       <c r="F312" t="n">
         <v>3408100</v>
@@ -6712,16 +6712,16 @@
         <v>44713</v>
       </c>
       <c r="B315" t="n">
-        <v>14.85544586181641</v>
+        <v>14.85544681549072</v>
       </c>
       <c r="C315" t="n">
-        <v>15.53945059003543</v>
+        <v>15.53945158762076</v>
       </c>
       <c r="D315" t="n">
-        <v>14.73020528772095</v>
+        <v>14.73020623335521</v>
       </c>
       <c r="E315" t="n">
-        <v>15.39494273002606</v>
+        <v>15.39494371833443</v>
       </c>
       <c r="F315" t="n">
         <v>6096700</v>
@@ -6752,16 +6752,16 @@
         <v>44715</v>
       </c>
       <c r="B317" t="n">
-        <v>14.88434886932373</v>
+        <v>14.88434791564941</v>
       </c>
       <c r="C317" t="n">
-        <v>15.23116924109026</v>
+        <v>15.23116826519437</v>
       </c>
       <c r="D317" t="n">
-        <v>14.78801059175644</v>
+        <v>14.78800964425473</v>
       </c>
       <c r="E317" t="n">
-        <v>15.17336553954295</v>
+        <v>15.17336456735067</v>
       </c>
       <c r="F317" t="n">
         <v>4184100</v>
@@ -6772,16 +6772,16 @@
         <v>44718</v>
       </c>
       <c r="B318" t="n">
-        <v>14.9036169052124</v>
+        <v>14.90361595153809</v>
       </c>
       <c r="C318" t="n">
-        <v>15.1348298712333</v>
+        <v>15.13482890276379</v>
       </c>
       <c r="D318" t="n">
-        <v>14.84581320432785</v>
+        <v>14.84581225435236</v>
       </c>
       <c r="E318" t="n">
-        <v>15.01922338822285</v>
+        <v>15.01922242715094</v>
       </c>
       <c r="F318" t="n">
         <v>2626600</v>
@@ -6792,16 +6792,16 @@
         <v>44719</v>
       </c>
       <c r="B319" t="n">
-        <v>15.12519550323486</v>
+        <v>15.12519645690918</v>
       </c>
       <c r="C319" t="n">
-        <v>15.31787297154666</v>
+        <v>15.31787393736968</v>
       </c>
       <c r="D319" t="n">
-        <v>14.70130507294891</v>
+        <v>14.70130599989608</v>
       </c>
       <c r="E319" t="n">
-        <v>14.82654565704124</v>
+        <v>14.82654659188508</v>
       </c>
       <c r="F319" t="n">
         <v>7316900</v>
@@ -6832,16 +6832,16 @@
         <v>44721</v>
       </c>
       <c r="B321" t="n">
-        <v>15.02885627746582</v>
+        <v>15.02885723114014</v>
       </c>
       <c r="C321" t="n">
-        <v>15.50091627464848</v>
+        <v>15.50091725827793</v>
       </c>
       <c r="D321" t="n">
-        <v>14.76874102263543</v>
+        <v>14.76874195980382</v>
       </c>
       <c r="E321" t="n">
-        <v>15.38530980097672</v>
+        <v>15.38531077727023</v>
       </c>
       <c r="F321" t="n">
         <v>9688900</v>
@@ -6852,16 +6852,16 @@
         <v>44722</v>
       </c>
       <c r="B322" t="n">
-        <v>14.48935890197754</v>
+        <v>14.48935985565186</v>
       </c>
       <c r="C322" t="n">
-        <v>15.01922261074923</v>
+        <v>15.01922359929862</v>
       </c>
       <c r="D322" t="n">
-        <v>14.22924455835858</v>
+        <v>14.22924549491244</v>
       </c>
       <c r="E322" t="n">
-        <v>14.85544653860601</v>
+        <v>14.85544751637582</v>
       </c>
       <c r="F322" t="n">
         <v>15101900</v>
@@ -6912,16 +6912,16 @@
         <v>44727</v>
       </c>
       <c r="B325" t="n">
-        <v>14.91324901580811</v>
+        <v>14.91325092315674</v>
       </c>
       <c r="C325" t="n">
-        <v>15.06739190081403</v>
+        <v>15.06739382787696</v>
       </c>
       <c r="D325" t="n">
-        <v>14.25814565925695</v>
+        <v>14.25814748282032</v>
       </c>
       <c r="E325" t="n">
-        <v>14.34485074496072</v>
+        <v>14.34485257961335</v>
       </c>
       <c r="F325" t="n">
         <v>25461900</v>
@@ -6992,16 +6992,16 @@
         <v>44734</v>
       </c>
       <c r="B329" t="n">
-        <v>14.44118976593018</v>
+        <v>14.44119071960449</v>
       </c>
       <c r="C329" t="n">
-        <v>15.13482956889515</v>
+        <v>15.13483056837639</v>
       </c>
       <c r="D329" t="n">
-        <v>14.32558328522912</v>
+        <v>14.32558423126896</v>
       </c>
       <c r="E329" t="n">
-        <v>14.6820368304137</v>
+        <v>14.68203779999319</v>
       </c>
       <c r="F329" t="n">
         <v>8791300</v>
@@ -7012,16 +7012,16 @@
         <v>44735</v>
       </c>
       <c r="B330" t="n">
-        <v>14.72057247161865</v>
+        <v>14.72057151794434</v>
       </c>
       <c r="C330" t="n">
-        <v>14.90361675696679</v>
+        <v>14.90361579143392</v>
       </c>
       <c r="D330" t="n">
-        <v>14.39302031363454</v>
+        <v>14.39301938118073</v>
       </c>
       <c r="E330" t="n">
-        <v>14.39302031363454</v>
+        <v>14.39301938118073</v>
       </c>
       <c r="F330" t="n">
         <v>3851900</v>
@@ -7032,16 +7032,16 @@
         <v>44736</v>
       </c>
       <c r="B331" t="n">
-        <v>14.4219217300415</v>
+        <v>14.42192268371582</v>
       </c>
       <c r="C331" t="n">
-        <v>14.86508034244202</v>
+        <v>14.86508132542095</v>
       </c>
       <c r="D331" t="n">
-        <v>14.25814566119184</v>
+        <v>14.25814660403618</v>
       </c>
       <c r="E331" t="n">
-        <v>14.86508034244202</v>
+        <v>14.86508132542095</v>
       </c>
       <c r="F331" t="n">
         <v>5803600</v>
@@ -7112,16 +7112,16 @@
         <v>44742</v>
       </c>
       <c r="B335" t="n">
-        <v>13.74755001068115</v>
+        <v>13.74755096435547</v>
       </c>
       <c r="C335" t="n">
-        <v>13.88242377024082</v>
+        <v>13.88242473327139</v>
       </c>
       <c r="D335" t="n">
-        <v>13.34292689448499</v>
+        <v>13.34292782009041</v>
       </c>
       <c r="E335" t="n">
-        <v>13.58377394370849</v>
+        <v>13.58377488602158</v>
       </c>
       <c r="F335" t="n">
         <v>10650900</v>
@@ -7132,16 +7132,16 @@
         <v>44743</v>
       </c>
       <c r="B336" t="n">
-        <v>14.06546974182129</v>
+        <v>14.06546878814697</v>
       </c>
       <c r="C336" t="n">
-        <v>14.28704861287829</v>
+        <v>14.28704764418037</v>
       </c>
       <c r="D336" t="n">
-        <v>13.54524008938454</v>
+        <v>13.54523917098311</v>
       </c>
       <c r="E336" t="n">
-        <v>13.64157836946027</v>
+        <v>13.64157744452686</v>
       </c>
       <c r="F336" t="n">
         <v>10271400</v>
@@ -7152,16 +7152,16 @@
         <v>44746</v>
       </c>
       <c r="B337" t="n">
-        <v>13.87279033660889</v>
+        <v>13.8727912902832</v>
       </c>
       <c r="C337" t="n">
-        <v>14.14253970625061</v>
+        <v>14.14254067846864</v>
       </c>
       <c r="D337" t="n">
-        <v>13.76681796059447</v>
+        <v>13.76681890698379</v>
       </c>
       <c r="E337" t="n">
-        <v>13.95949542551097</v>
+        <v>13.95949638514576</v>
       </c>
       <c r="F337" t="n">
         <v>1980900</v>
@@ -7172,16 +7172,16 @@
         <v>44747</v>
       </c>
       <c r="B338" t="n">
-        <v>14.17144012451172</v>
+        <v>14.17144107818604</v>
       </c>
       <c r="C338" t="n">
-        <v>14.19070741030283</v>
+        <v>14.19070836527375</v>
       </c>
       <c r="D338" t="n">
-        <v>13.46816627734423</v>
+        <v>13.46816718369137</v>
       </c>
       <c r="E338" t="n">
-        <v>13.67047783132298</v>
+        <v>13.67047875128478</v>
       </c>
       <c r="F338" t="n">
         <v>7354200</v>
@@ -7192,16 +7192,16 @@
         <v>44748</v>
       </c>
       <c r="B339" t="n">
-        <v>14.35448551177979</v>
+        <v>14.35448455810547</v>
       </c>
       <c r="C339" t="n">
-        <v>14.63386808610274</v>
+        <v>14.63386711386697</v>
       </c>
       <c r="D339" t="n">
-        <v>13.92096095421089</v>
+        <v>13.9209600293388</v>
       </c>
       <c r="E339" t="n">
-        <v>13.96913055366492</v>
+        <v>13.96912962559257</v>
       </c>
       <c r="F339" t="n">
         <v>11107300</v>
@@ -7232,16 +7232,16 @@
         <v>44750</v>
       </c>
       <c r="B341" t="n">
-        <v>14.72057247161865</v>
+        <v>14.72057151794434</v>
       </c>
       <c r="C341" t="n">
-        <v>14.82654576905978</v>
+        <v>14.82654480851997</v>
       </c>
       <c r="D341" t="n">
-        <v>14.41228851999061</v>
+        <v>14.41228758628851</v>
       </c>
       <c r="E341" t="n">
-        <v>14.73984067797473</v>
+        <v>14.73983972305212</v>
       </c>
       <c r="F341" t="n">
         <v>3792400</v>
@@ -7272,16 +7272,16 @@
         <v>44754</v>
       </c>
       <c r="B343" t="n">
-        <v>14.68203544616699</v>
+        <v>14.68203639984131</v>
       </c>
       <c r="C343" t="n">
-        <v>14.97105208004998</v>
+        <v>14.97105305249743</v>
       </c>
       <c r="D343" t="n">
-        <v>14.59533036412624</v>
+        <v>14.59533131216861</v>
       </c>
       <c r="E343" t="n">
-        <v>14.79764191596848</v>
+        <v>14.79764287715203</v>
       </c>
       <c r="F343" t="n">
         <v>4929100</v>
@@ -7292,16 +7292,16 @@
         <v>44755</v>
       </c>
       <c r="B344" t="n">
-        <v>14.77837562561035</v>
+        <v>14.77837657928467</v>
       </c>
       <c r="C344" t="n">
-        <v>15.01922268360593</v>
+        <v>15.01922365282253</v>
       </c>
       <c r="D344" t="n">
-        <v>14.44118937691309</v>
+        <v>14.44119030882819</v>
       </c>
       <c r="E344" t="n">
-        <v>14.58569816296561</v>
+        <v>14.58569910420611</v>
       </c>
       <c r="F344" t="n">
         <v>3964800</v>
@@ -7312,16 +7312,16 @@
         <v>44756</v>
       </c>
       <c r="B345" t="n">
-        <v>14.759108543396</v>
+        <v>14.75910758972168</v>
       </c>
       <c r="C345" t="n">
-        <v>14.99995561972431</v>
+        <v>14.99995465048742</v>
       </c>
       <c r="D345" t="n">
-        <v>14.51826146706769</v>
+        <v>14.51826052895594</v>
       </c>
       <c r="E345" t="n">
-        <v>14.5278955706229</v>
+        <v>14.52789463188864</v>
       </c>
       <c r="F345" t="n">
         <v>8175300</v>
@@ -7352,16 +7352,16 @@
         <v>44760</v>
       </c>
       <c r="B347" t="n">
-        <v>14.87471580505371</v>
+        <v>14.87471389770508</v>
       </c>
       <c r="C347" t="n">
-        <v>15.19263480763503</v>
+        <v>15.19263285952041</v>
       </c>
       <c r="D347" t="n">
-        <v>14.80727891416975</v>
+        <v>14.80727701546838</v>
       </c>
       <c r="E347" t="n">
-        <v>15.07702739646433</v>
+        <v>15.07702546317377</v>
       </c>
       <c r="F347" t="n">
         <v>3805700</v>
@@ -7492,16 +7492,16 @@
         <v>44769</v>
       </c>
       <c r="B354" t="n">
-        <v>15.76103115081787</v>
+        <v>15.76103210449219</v>
       </c>
       <c r="C354" t="n">
-        <v>15.9344413165386</v>
+        <v>15.93444228070568</v>
       </c>
       <c r="D354" t="n">
-        <v>15.03848909990104</v>
+        <v>15.03849000985551</v>
       </c>
       <c r="E354" t="n">
-        <v>15.04812320216521</v>
+        <v>15.04812411270262</v>
       </c>
       <c r="F354" t="n">
         <v>22102600</v>
@@ -7552,16 +7552,16 @@
         <v>44774</v>
       </c>
       <c r="B357" t="n">
-        <v>15.05775833129883</v>
+        <v>15.05775928497314</v>
       </c>
       <c r="C357" t="n">
-        <v>15.4045777676332</v>
+        <v>15.40457874327312</v>
       </c>
       <c r="D357" t="n">
-        <v>14.85544676374746</v>
+        <v>14.85544770460849</v>
       </c>
       <c r="E357" t="n">
-        <v>14.96141913960441</v>
+        <v>14.96142008717714</v>
       </c>
       <c r="F357" t="n">
         <v>9649400</v>
@@ -7592,16 +7592,16 @@
         <v>44776</v>
       </c>
       <c r="B359" t="n">
-        <v>15.95370769500732</v>
+        <v>15.95370960235596</v>
       </c>
       <c r="C359" t="n">
-        <v>16.00187820636274</v>
+        <v>16.00188011947041</v>
       </c>
       <c r="D359" t="n">
-        <v>15.06739141751453</v>
+        <v>15.06739321889945</v>
       </c>
       <c r="E359" t="n">
-        <v>15.12519419362391</v>
+        <v>15.12519600191945</v>
       </c>
       <c r="F359" t="n">
         <v>9465300</v>
@@ -7612,16 +7612,16 @@
         <v>44777</v>
       </c>
       <c r="B360" t="n">
-        <v>16.21382522583008</v>
+        <v>16.21382331848145</v>
       </c>
       <c r="C360" t="n">
-        <v>16.42576999307324</v>
+        <v>16.42576806079203</v>
       </c>
       <c r="D360" t="n">
-        <v>15.92480946708782</v>
+        <v>15.92480759373818</v>
       </c>
       <c r="E360" t="n">
-        <v>16.02114682832365</v>
+        <v>16.02114494364116</v>
       </c>
       <c r="F360" t="n">
         <v>10048700</v>
@@ -7652,16 +7652,16 @@
         <v>44781</v>
       </c>
       <c r="B362" t="n">
-        <v>16.68588447570801</v>
+        <v>16.68588638305664</v>
       </c>
       <c r="C362" t="n">
-        <v>16.88819696710841</v>
+        <v>16.88819889758321</v>
       </c>
       <c r="D362" t="n">
-        <v>16.26199312409735</v>
+        <v>16.26199498299134</v>
       </c>
       <c r="E362" t="n">
-        <v>16.53174250012546</v>
+        <v>16.53174438985426</v>
       </c>
       <c r="F362" t="n">
         <v>10381400</v>
@@ -7712,16 +7712,16 @@
         <v>44784</v>
       </c>
       <c r="B365" t="n">
-        <v>16.99416923522949</v>
+        <v>16.99417114257812</v>
       </c>
       <c r="C365" t="n">
-        <v>17.34098961554597</v>
+        <v>17.34099156182016</v>
       </c>
       <c r="D365" t="n">
-        <v>16.86892956318042</v>
+        <v>16.86893145647272</v>
       </c>
       <c r="E365" t="n">
-        <v>16.91709824377221</v>
+        <v>16.91710014247074</v>
       </c>
       <c r="F365" t="n">
         <v>8667500</v>
@@ -7732,16 +7732,16 @@
         <v>44785</v>
       </c>
       <c r="B366" t="n">
-        <v>17.34098625183105</v>
+        <v>17.34098815917969</v>
       </c>
       <c r="C366" t="n">
-        <v>17.64927015786088</v>
+        <v>17.6492720991179</v>
       </c>
       <c r="D366" t="n">
-        <v>17.06160281354338</v>
+        <v>17.06160469016241</v>
       </c>
       <c r="E366" t="n">
-        <v>17.16757609531002</v>
+        <v>17.16757798358513</v>
       </c>
       <c r="F366" t="n">
         <v>11729000</v>
@@ -7752,16 +7752,16 @@
         <v>44788</v>
       </c>
       <c r="B367" t="n">
-        <v>17.53366851806641</v>
+        <v>17.53366661071777</v>
       </c>
       <c r="C367" t="n">
-        <v>17.66854229762282</v>
+        <v>17.66854037560234</v>
       </c>
       <c r="D367" t="n">
-        <v>17.06160661458408</v>
+        <v>17.06160475858731</v>
       </c>
       <c r="E367" t="n">
-        <v>17.20611633555731</v>
+        <v>17.20611446384048</v>
       </c>
       <c r="F367" t="n">
         <v>7999500</v>
@@ -7772,16 +7772,16 @@
         <v>44789</v>
       </c>
       <c r="B368" t="n">
-        <v>17.42769050598145</v>
+        <v>17.42769241333008</v>
       </c>
       <c r="C368" t="n">
-        <v>17.6300011206779</v>
+        <v>17.63000305016812</v>
       </c>
       <c r="D368" t="n">
-        <v>17.19647758739253</v>
+        <v>17.1964794694364</v>
       </c>
       <c r="E368" t="n">
-        <v>17.52402968143939</v>
+        <v>17.52403159933173</v>
       </c>
       <c r="F368" t="n">
         <v>4828900</v>
@@ -7832,16 +7832,16 @@
         <v>44792</v>
       </c>
       <c r="B371" t="n">
-        <v>17.12904357910156</v>
+        <v>17.1290454864502</v>
       </c>
       <c r="C371" t="n">
-        <v>17.57220128776223</v>
+        <v>17.57220324445724</v>
       </c>
       <c r="D371" t="n">
-        <v>17.07123896165407</v>
+        <v>17.07124086256606</v>
       </c>
       <c r="E371" t="n">
-        <v>17.45659572790173</v>
+        <v>17.45659767172386</v>
       </c>
       <c r="F371" t="n">
         <v>7571900</v>
@@ -7852,16 +7852,16 @@
         <v>44795</v>
       </c>
       <c r="B372" t="n">
-        <v>17.36025428771973</v>
+        <v>17.36025619506836</v>
       </c>
       <c r="C372" t="n">
-        <v>17.45659346680312</v>
+        <v>17.45659538473642</v>
       </c>
       <c r="D372" t="n">
-        <v>16.82075561985949</v>
+        <v>16.82075746793411</v>
       </c>
       <c r="E372" t="n">
-        <v>16.98453167304617</v>
+        <v>16.98453353911465</v>
       </c>
       <c r="F372" t="n">
         <v>10077700</v>
@@ -7872,16 +7872,16 @@
         <v>44796</v>
       </c>
       <c r="B373" t="n">
-        <v>17.20611572265625</v>
+        <v>17.20611381530762</v>
       </c>
       <c r="C373" t="n">
-        <v>17.7937813394455</v>
+        <v>17.7937793669524</v>
       </c>
       <c r="D373" t="n">
-        <v>17.10977652461162</v>
+        <v>17.10977462794247</v>
       </c>
       <c r="E373" t="n">
-        <v>17.49513147927278</v>
+        <v>17.49512953988589</v>
       </c>
       <c r="F373" t="n">
         <v>12142000</v>
@@ -7892,16 +7892,16 @@
         <v>44797</v>
       </c>
       <c r="B374" t="n">
-        <v>17.14831161499023</v>
+        <v>17.1483097076416</v>
       </c>
       <c r="C374" t="n">
-        <v>17.26391902361024</v>
+        <v>17.26391710340299</v>
       </c>
       <c r="D374" t="n">
-        <v>16.99416962850851</v>
+        <v>16.99416773830457</v>
       </c>
       <c r="E374" t="n">
-        <v>17.14831161499023</v>
+        <v>17.1483097076416</v>
       </c>
       <c r="F374" t="n">
         <v>5807100</v>
@@ -7952,16 +7952,16 @@
         <v>44802</v>
       </c>
       <c r="B377" t="n">
-        <v>17.68780708312988</v>
+        <v>17.68780899047852</v>
       </c>
       <c r="C377" t="n">
-        <v>17.98645689615716</v>
+        <v>17.98645883571042</v>
       </c>
       <c r="D377" t="n">
-        <v>17.19647890442993</v>
+        <v>17.19648075879664</v>
       </c>
       <c r="E377" t="n">
-        <v>17.29281808726627</v>
+        <v>17.29281995202162</v>
       </c>
       <c r="F377" t="n">
         <v>7263100</v>
@@ -7972,16 +7972,16 @@
         <v>44803</v>
       </c>
       <c r="B378" t="n">
-        <v>17.63000297546387</v>
+        <v>17.6300048828125</v>
       </c>
       <c r="C378" t="n">
-        <v>17.95755510397125</v>
+        <v>17.95755704675698</v>
       </c>
       <c r="D378" t="n">
-        <v>17.55293199449255</v>
+        <v>17.55293389350305</v>
       </c>
       <c r="E378" t="n">
-        <v>17.6878075893302</v>
+        <v>17.68780950293258</v>
       </c>
       <c r="F378" t="n">
         <v>6440300</v>
@@ -7992,16 +7992,16 @@
         <v>44804</v>
       </c>
       <c r="B379" t="n">
-        <v>17.71670913696289</v>
+        <v>17.71671104431152</v>
       </c>
       <c r="C379" t="n">
-        <v>17.98645850553768</v>
+        <v>17.98646044192704</v>
       </c>
       <c r="D379" t="n">
-        <v>17.51439848866973</v>
+        <v>17.51440037423797</v>
       </c>
       <c r="E379" t="n">
-        <v>17.74561144565502</v>
+        <v>17.74561335611522</v>
       </c>
       <c r="F379" t="n">
         <v>9759800</v>
@@ -8052,16 +8052,16 @@
         <v>44809</v>
       </c>
       <c r="B382" t="n">
-        <v>18.73790168762207</v>
+        <v>18.7379035949707</v>
       </c>
       <c r="C382" t="n">
-        <v>18.91131002438889</v>
+        <v>18.91131194938891</v>
       </c>
       <c r="D382" t="n">
-        <v>18.12133197488807</v>
+        <v>18.12133381947549</v>
       </c>
       <c r="E382" t="n">
-        <v>18.39108133905402</v>
+        <v>18.39108321109948</v>
       </c>
       <c r="F382" t="n">
         <v>11861400</v>
@@ -8072,16 +8072,16 @@
         <v>44810</v>
       </c>
       <c r="B383" t="n">
-        <v>18.75716781616211</v>
+        <v>18.75716972351074</v>
       </c>
       <c r="C383" t="n">
-        <v>18.83423879958045</v>
+        <v>18.83424071476615</v>
       </c>
       <c r="D383" t="n">
-        <v>18.33327832611984</v>
+        <v>18.33328019036468</v>
       </c>
       <c r="E383" t="n">
-        <v>18.68973093536071</v>
+        <v>18.68973283585193</v>
       </c>
       <c r="F383" t="n">
         <v>7863100</v>
@@ -8112,16 +8112,16 @@
         <v>44813</v>
       </c>
       <c r="B385" t="n">
-        <v>18.15986824035645</v>
+        <v>18.15987014770508</v>
       </c>
       <c r="C385" t="n">
-        <v>18.62229414306423</v>
+        <v>18.6222960989819</v>
       </c>
       <c r="D385" t="n">
-        <v>18.08279725657182</v>
+        <v>18.08279915582561</v>
       </c>
       <c r="E385" t="n">
-        <v>18.47778627815769</v>
+        <v>18.47778821889757</v>
       </c>
       <c r="F385" t="n">
         <v>8752700</v>
@@ -8132,16 +8132,16 @@
         <v>44816</v>
       </c>
       <c r="B386" t="n">
-        <v>17.78414535522461</v>
+        <v>17.78414726257324</v>
       </c>
       <c r="C386" t="n">
-        <v>18.38144684992308</v>
+        <v>18.38144882133227</v>
       </c>
       <c r="D386" t="n">
-        <v>17.7070743724426</v>
+        <v>17.70707627152537</v>
       </c>
       <c r="E386" t="n">
-        <v>18.25620719197125</v>
+        <v>18.25620914994849</v>
       </c>
       <c r="F386" t="n">
         <v>10149200</v>
@@ -8252,16 +8252,16 @@
         <v>44824</v>
       </c>
       <c r="B392" t="n">
-        <v>17.60110282897949</v>
+        <v>17.60110473632812</v>
       </c>
       <c r="C392" t="n">
-        <v>17.83231577613557</v>
+        <v>17.83231770853966</v>
       </c>
       <c r="D392" t="n">
-        <v>17.43732676172096</v>
+        <v>17.43732865132195</v>
       </c>
       <c r="E392" t="n">
-        <v>17.55293231654042</v>
+        <v>17.55293421866904</v>
       </c>
       <c r="F392" t="n">
         <v>8039000</v>
@@ -8272,16 +8272,16 @@
         <v>44825</v>
       </c>
       <c r="B393" t="n">
-        <v>17.63000297546387</v>
+        <v>17.6300048828125</v>
       </c>
       <c r="C393" t="n">
-        <v>17.95755510397125</v>
+        <v>17.95755704675698</v>
       </c>
       <c r="D393" t="n">
-        <v>17.54329789218149</v>
+        <v>17.54329979014971</v>
       </c>
       <c r="E393" t="n">
-        <v>17.63000297546387</v>
+        <v>17.6300048828125</v>
       </c>
       <c r="F393" t="n">
         <v>11282800</v>
@@ -8292,16 +8292,16 @@
         <v>44826</v>
       </c>
       <c r="B394" t="n">
-        <v>17.36025428771973</v>
+        <v>17.36025619506836</v>
       </c>
       <c r="C394" t="n">
-        <v>17.88048291474287</v>
+        <v>17.88048487924835</v>
       </c>
       <c r="D394" t="n">
-        <v>16.94599710392301</v>
+        <v>16.94599896575775</v>
       </c>
       <c r="E394" t="n">
-        <v>17.668538190773</v>
+        <v>17.66854013199238</v>
       </c>
       <c r="F394" t="n">
         <v>12903600</v>
@@ -8312,16 +8312,16 @@
         <v>44827</v>
       </c>
       <c r="B395" t="n">
-        <v>17.1386775970459</v>
+        <v>17.13867950439453</v>
       </c>
       <c r="C395" t="n">
-        <v>17.42769333278163</v>
+        <v>17.42769527229457</v>
       </c>
       <c r="D395" t="n">
-        <v>16.96526742059757</v>
+        <v>16.96526930864753</v>
       </c>
       <c r="E395" t="n">
-        <v>17.10977528846543</v>
+        <v>17.10977719259755</v>
       </c>
       <c r="F395" t="n">
         <v>12048200</v>
@@ -8332,16 +8332,16 @@
         <v>44830</v>
       </c>
       <c r="B396" t="n">
-        <v>17.09050559997559</v>
+        <v>17.09050750732422</v>
       </c>
       <c r="C396" t="n">
-        <v>17.20611298675014</v>
+        <v>17.20611490700088</v>
       </c>
       <c r="D396" t="n">
-        <v>16.71478480861316</v>
+        <v>16.7147866740303</v>
       </c>
       <c r="E396" t="n">
-        <v>16.89782907204076</v>
+        <v>16.89783095788615</v>
       </c>
       <c r="F396" t="n">
         <v>7980700</v>
@@ -8352,16 +8352,16 @@
         <v>44831</v>
       </c>
       <c r="B397" t="n">
-        <v>17.12904357910156</v>
+        <v>17.1290454864502</v>
       </c>
       <c r="C397" t="n">
-        <v>17.49513030201615</v>
+        <v>17.49513225012917</v>
       </c>
       <c r="D397" t="n">
-        <v>16.86892831313957</v>
+        <v>16.86893019152391</v>
       </c>
       <c r="E397" t="n">
-        <v>17.25428324186998</v>
+        <v>17.25428516316427</v>
       </c>
       <c r="F397" t="n">
         <v>9260100</v>
@@ -8412,16 +8412,16 @@
         <v>44834</v>
       </c>
       <c r="B400" t="n">
-        <v>16.9074649810791</v>
+        <v>16.90746307373047</v>
       </c>
       <c r="C400" t="n">
-        <v>17.28318769094845</v>
+        <v>17.28318574121415</v>
       </c>
       <c r="D400" t="n">
-        <v>16.85929629809154</v>
+        <v>16.85929439617687</v>
       </c>
       <c r="E400" t="n">
-        <v>17.24465127454443</v>
+        <v>17.24464932915746</v>
       </c>
       <c r="F400" t="n">
         <v>11790900</v>
@@ -8432,16 +8432,16 @@
         <v>44837</v>
       </c>
       <c r="B401" t="n">
-        <v>17.75524520874023</v>
+        <v>17.75524711608887</v>
       </c>
       <c r="C401" t="n">
-        <v>17.81304798750098</v>
+        <v>17.81304990105905</v>
       </c>
       <c r="D401" t="n">
-        <v>16.96526716144702</v>
+        <v>16.96526898393264</v>
       </c>
       <c r="E401" t="n">
-        <v>17.24464879005494</v>
+        <v>17.244650642553</v>
       </c>
       <c r="F401" t="n">
         <v>18011200</v>
@@ -8512,16 +8512,16 @@
         <v>44841</v>
       </c>
       <c r="B405" t="n">
-        <v>17.49513244628906</v>
+        <v>17.4951286315918</v>
       </c>
       <c r="C405" t="n">
-        <v>17.68781085302832</v>
+        <v>17.68780699631881</v>
       </c>
       <c r="D405" t="n">
-        <v>17.32172224772722</v>
+        <v>17.3217184708409</v>
       </c>
       <c r="E405" t="n">
-        <v>17.44696376336298</v>
+        <v>17.44695995916858</v>
       </c>
       <c r="F405" t="n">
         <v>11897600</v>
@@ -8532,16 +8532,16 @@
         <v>44844</v>
       </c>
       <c r="B406" t="n">
-        <v>18.10206604003906</v>
+        <v>18.10206413269043</v>
       </c>
       <c r="C406" t="n">
-        <v>18.12133240846265</v>
+        <v>18.12133049908399</v>
       </c>
       <c r="D406" t="n">
-        <v>17.58183550473985</v>
+        <v>17.58183365220601</v>
       </c>
       <c r="E406" t="n">
-        <v>17.73597747723208</v>
+        <v>17.73597560845686</v>
       </c>
       <c r="F406" t="n">
         <v>7333800</v>
@@ -8552,16 +8552,16 @@
         <v>44845</v>
       </c>
       <c r="B407" t="n">
-        <v>18.32364463806152</v>
+        <v>18.32364654541016</v>
       </c>
       <c r="C407" t="n">
-        <v>18.59339216736995</v>
+        <v>18.5933941027972</v>
       </c>
       <c r="D407" t="n">
-        <v>17.85158462425454</v>
+        <v>17.8515864824654</v>
       </c>
       <c r="E407" t="n">
-        <v>18.15023446206769</v>
+        <v>18.15023635136567</v>
       </c>
       <c r="F407" t="n">
         <v>12287200</v>
@@ -8572,16 +8572,16 @@
         <v>44847</v>
       </c>
       <c r="B408" t="n">
-        <v>18.75716781616211</v>
+        <v>18.75716972351074</v>
       </c>
       <c r="C408" t="n">
-        <v>18.99801486903407</v>
+        <v>18.99801680087357</v>
       </c>
       <c r="D408" t="n">
-        <v>17.93828930641119</v>
+        <v>17.93829113049103</v>
       </c>
       <c r="E408" t="n">
-        <v>18.17913635928316</v>
+        <v>18.17913820785386</v>
       </c>
       <c r="F408" t="n">
         <v>20665700</v>
@@ -8592,16 +8592,16 @@
         <v>44848</v>
       </c>
       <c r="B409" t="n">
-        <v>18.39108276367188</v>
+        <v>18.39108085632324</v>
       </c>
       <c r="C409" t="n">
-        <v>18.9402137997635</v>
+        <v>18.94021183546421</v>
       </c>
       <c r="D409" t="n">
-        <v>18.29474356632728</v>
+        <v>18.29474166897004</v>
       </c>
       <c r="E409" t="n">
-        <v>18.80534002599148</v>
+        <v>18.80533807568002</v>
       </c>
       <c r="F409" t="n">
         <v>11391600</v>
@@ -8612,16 +8612,16 @@
         <v>44851</v>
       </c>
       <c r="B410" t="n">
-        <v>19.01728248596191</v>
+        <v>19.01728439331055</v>
       </c>
       <c r="C410" t="n">
-        <v>19.06545299755645</v>
+        <v>19.06545490973637</v>
       </c>
       <c r="D410" t="n">
-        <v>18.3621782284133</v>
+        <v>18.3621800700579</v>
       </c>
       <c r="E410" t="n">
-        <v>18.49705382336087</v>
+        <v>18.49705567853288</v>
       </c>
       <c r="F410" t="n">
         <v>20683400</v>
@@ -8632,16 +8632,16 @@
         <v>44852</v>
       </c>
       <c r="B411" t="n">
-        <v>17.26391983032227</v>
+        <v>17.26391792297363</v>
       </c>
       <c r="C411" t="n">
-        <v>19.16179427601119</v>
+        <v>19.16179215898201</v>
       </c>
       <c r="D411" t="n">
-        <v>17.26391983032227</v>
+        <v>17.26391792297363</v>
       </c>
       <c r="E411" t="n">
-        <v>19.10399148775888</v>
+        <v>19.10398937711585</v>
       </c>
       <c r="F411" t="n">
         <v>33355700</v>
@@ -8692,16 +8692,16 @@
         <v>44855</v>
       </c>
       <c r="B414" t="n">
-        <v>17.91901969909668</v>
+        <v>17.91902160644531</v>
       </c>
       <c r="C414" t="n">
-        <v>18.2562059142376</v>
+        <v>18.25620785747724</v>
       </c>
       <c r="D414" t="n">
-        <v>17.34098644992897</v>
+        <v>17.34098829575019</v>
       </c>
       <c r="E414" t="n">
-        <v>17.53366481215722</v>
+        <v>17.53366667848764</v>
       </c>
       <c r="F414" t="n">
         <v>27105700</v>
@@ -8712,16 +8712,16 @@
         <v>44858</v>
       </c>
       <c r="B415" t="n">
-        <v>18.0057258605957</v>
+        <v>18.00572776794434</v>
       </c>
       <c r="C415" t="n">
-        <v>18.36217846337067</v>
+        <v>18.36218040847837</v>
       </c>
       <c r="D415" t="n">
-        <v>17.54329813095674</v>
+        <v>17.54329998932035</v>
       </c>
       <c r="E415" t="n">
-        <v>17.91902077613322</v>
+        <v>17.91902267429717</v>
       </c>
       <c r="F415" t="n">
         <v>16227000</v>
@@ -8752,16 +8752,16 @@
         <v>44860</v>
       </c>
       <c r="B417" t="n">
-        <v>16.45467376708984</v>
+        <v>16.45467185974121</v>
       </c>
       <c r="C417" t="n">
-        <v>17.07124175390729</v>
+        <v>17.07123977508899</v>
       </c>
       <c r="D417" t="n">
-        <v>16.36796866425395</v>
+        <v>16.36796676695576</v>
       </c>
       <c r="E417" t="n">
-        <v>17.04234127797369</v>
+        <v>17.0423393025054</v>
       </c>
       <c r="F417" t="n">
         <v>12823000</v>
@@ -8772,16 +8772,16 @@
         <v>44861</v>
       </c>
       <c r="B418" t="n">
-        <v>17.47586059570312</v>
+        <v>17.47586250305176</v>
       </c>
       <c r="C418" t="n">
-        <v>17.74560994141206</v>
+        <v>17.74561187820164</v>
       </c>
       <c r="D418" t="n">
-        <v>15.99224378809673</v>
+        <v>15.9922455335206</v>
       </c>
       <c r="E418" t="n">
-        <v>16.13675164427337</v>
+        <v>16.13675340546911</v>
       </c>
       <c r="F418" t="n">
         <v>30122400</v>
@@ -8792,16 +8792,16 @@
         <v>44862</v>
       </c>
       <c r="B419" t="n">
-        <v>18.12133026123047</v>
+        <v>18.1213321685791</v>
       </c>
       <c r="C419" t="n">
-        <v>18.21766944200201</v>
+        <v>18.21767135949075</v>
       </c>
       <c r="D419" t="n">
-        <v>17.27354951297842</v>
+        <v>17.27355133109445</v>
       </c>
       <c r="E419" t="n">
-        <v>17.40842326354835</v>
+        <v>17.40842509586043</v>
       </c>
       <c r="F419" t="n">
         <v>12193800</v>
@@ -8812,16 +8812,16 @@
         <v>44865</v>
       </c>
       <c r="B420" t="n">
-        <v>19.0943546295166</v>
+        <v>19.09435272216797</v>
       </c>
       <c r="C420" t="n">
-        <v>19.24849660096946</v>
+        <v>19.24849467822348</v>
       </c>
       <c r="D420" t="n">
-        <v>18.13096638917758</v>
+        <v>18.13096457806249</v>
       </c>
       <c r="E420" t="n">
-        <v>18.2947424635359</v>
+        <v>18.2947406360611</v>
       </c>
       <c r="F420" t="n">
         <v>18379300</v>
@@ -8832,16 +8832,16 @@
         <v>44866</v>
       </c>
       <c r="B421" t="n">
-        <v>19.16178894042969</v>
+        <v>19.16179275512695</v>
       </c>
       <c r="C421" t="n">
-        <v>19.48934104518208</v>
+        <v>19.48934492508787</v>
       </c>
       <c r="D421" t="n">
-        <v>18.67046078330111</v>
+        <v>18.67046450018557</v>
       </c>
       <c r="E421" t="n">
-        <v>18.88240734373912</v>
+        <v>18.88241110281756</v>
       </c>
       <c r="F421" t="n">
         <v>15316600</v>
@@ -8872,16 +8872,16 @@
         <v>44869</v>
       </c>
       <c r="B423" t="n">
-        <v>19.79762649536133</v>
+        <v>19.79762840270996</v>
       </c>
       <c r="C423" t="n">
-        <v>19.98067076528072</v>
+        <v>19.98067269026426</v>
       </c>
       <c r="D423" t="n">
-        <v>19.60494996059309</v>
+        <v>19.60495184937882</v>
       </c>
       <c r="E423" t="n">
-        <v>19.81689470009329</v>
+        <v>19.81689660929827</v>
       </c>
       <c r="F423" t="n">
         <v>15655600</v>
@@ -8952,16 +8952,16 @@
         <v>44875</v>
       </c>
       <c r="B427" t="n">
-        <v>18.80533981323242</v>
+        <v>18.80533790588379</v>
       </c>
       <c r="C427" t="n">
-        <v>19.64348659435789</v>
+        <v>19.64348460199946</v>
       </c>
       <c r="D427" t="n">
-        <v>18.43925123496827</v>
+        <v>18.43924936475051</v>
       </c>
       <c r="E427" t="n">
-        <v>19.64348659435789</v>
+        <v>19.64348460199946</v>
       </c>
       <c r="F427" t="n">
         <v>13893700</v>
@@ -8992,16 +8992,16 @@
         <v>44879</v>
       </c>
       <c r="B429" t="n">
-        <v>18.88241004943848</v>
+        <v>18.88241195678711</v>
       </c>
       <c r="C429" t="n">
-        <v>19.19069399514078</v>
+        <v>19.19069593362977</v>
       </c>
       <c r="D429" t="n">
-        <v>18.47778691132489</v>
+        <v>18.47778877780176</v>
       </c>
       <c r="E429" t="n">
-        <v>18.87277594644562</v>
+        <v>18.87277785282109</v>
       </c>
       <c r="F429" t="n">
         <v>8802100</v>
@@ -9032,16 +9032,16 @@
         <v>44882</v>
       </c>
       <c r="B431" t="n">
-        <v>18.78607177734375</v>
+        <v>18.78606986999512</v>
       </c>
       <c r="C431" t="n">
-        <v>18.90167918140427</v>
+        <v>18.90167726231802</v>
       </c>
       <c r="D431" t="n">
-        <v>18.0538964516734</v>
+        <v>18.05389461866248</v>
       </c>
       <c r="E431" t="n">
-        <v>18.66083210733576</v>
+        <v>18.6608302127027</v>
       </c>
       <c r="F431" t="n">
         <v>10826800</v>
@@ -9052,16 +9052,16 @@
         <v>44883</v>
       </c>
       <c r="B432" t="n">
-        <v>18.44888305664062</v>
+        <v>18.44888496398926</v>
       </c>
       <c r="C432" t="n">
-        <v>19.02691632516161</v>
+        <v>19.02691829227056</v>
       </c>
       <c r="D432" t="n">
-        <v>18.44888305664062</v>
+        <v>18.44888496398926</v>
       </c>
       <c r="E432" t="n">
-        <v>18.78606928307096</v>
+        <v>18.78607122527979</v>
       </c>
       <c r="F432" t="n">
         <v>9969800</v>
@@ -9072,16 +9072,16 @@
         <v>44886</v>
       </c>
       <c r="B433" t="n">
-        <v>18.98838043212891</v>
+        <v>18.98838233947754</v>
       </c>
       <c r="C433" t="n">
-        <v>19.02691684191824</v>
+        <v>19.02691875313779</v>
       </c>
       <c r="D433" t="n">
-        <v>18.58375915444382</v>
+        <v>18.58376102114898</v>
       </c>
       <c r="E433" t="n">
-        <v>18.60302552182134</v>
+        <v>18.60302739046176</v>
       </c>
       <c r="F433" t="n">
         <v>10461100</v>
@@ -9092,16 +9092,16 @@
         <v>44887</v>
       </c>
       <c r="B434" t="n">
-        <v>18.75716781616211</v>
+        <v>18.75716972351074</v>
       </c>
       <c r="C434" t="n">
-        <v>19.39300388874271</v>
+        <v>19.39300586074722</v>
       </c>
       <c r="D434" t="n">
-        <v>18.62229405455931</v>
+        <v>18.62229594819312</v>
       </c>
       <c r="E434" t="n">
-        <v>19.07508585245241</v>
+        <v>19.07508779212898</v>
       </c>
       <c r="F434" t="n">
         <v>9653000</v>
@@ -9132,16 +9132,16 @@
         <v>44889</v>
       </c>
       <c r="B436" t="n">
-        <v>19.0847225189209</v>
+        <v>19.08472061157227</v>
       </c>
       <c r="C436" t="n">
-        <v>19.26776681819867</v>
+        <v>19.26776489255638</v>
       </c>
       <c r="D436" t="n">
-        <v>18.58376197816099</v>
+        <v>18.58376012087891</v>
       </c>
       <c r="E436" t="n">
-        <v>18.67046523832684</v>
+        <v>18.67046337237954</v>
       </c>
       <c r="F436" t="n">
         <v>7241600</v>
@@ -9172,16 +9172,16 @@
         <v>44893</v>
       </c>
       <c r="B438" t="n">
-        <v>18.6126594543457</v>
+        <v>18.61266136169434</v>
       </c>
       <c r="C438" t="n">
-        <v>19.0461848729321</v>
+        <v>19.04618682470663</v>
       </c>
       <c r="D438" t="n">
-        <v>18.21767044519682</v>
+        <v>18.21767231206861</v>
       </c>
       <c r="E438" t="n">
-        <v>18.35254420319387</v>
+        <v>18.35254608388696</v>
       </c>
       <c r="F438" t="n">
         <v>12132600</v>
@@ -9192,16 +9192,16 @@
         <v>44894</v>
       </c>
       <c r="B439" t="n">
-        <v>18.68973159790039</v>
+        <v>18.68972969055176</v>
       </c>
       <c r="C439" t="n">
-        <v>18.98838143954377</v>
+        <v>18.98837950171693</v>
       </c>
       <c r="D439" t="n">
-        <v>18.29474256418963</v>
+        <v>18.29474069715092</v>
       </c>
       <c r="E439" t="n">
-        <v>18.53558962559947</v>
+        <v>18.53558773398153</v>
       </c>
       <c r="F439" t="n">
         <v>13403400</v>
@@ -9212,16 +9212,16 @@
         <v>44895</v>
       </c>
       <c r="B440" t="n">
-        <v>19.31593704223633</v>
+        <v>19.31593322753906</v>
       </c>
       <c r="C440" t="n">
-        <v>19.38337577499833</v>
+        <v>19.38337194698261</v>
       </c>
       <c r="D440" t="n">
-        <v>18.15987204336573</v>
+        <v>18.15986845697931</v>
       </c>
       <c r="E440" t="n">
-        <v>18.30437993853485</v>
+        <v>18.30437632360963</v>
       </c>
       <c r="F440" t="n">
         <v>128079800</v>
@@ -9312,16 +9312,16 @@
         <v>44902</v>
       </c>
       <c r="B445" t="n">
-        <v>19.36410522460938</v>
+        <v>19.36410331726074</v>
       </c>
       <c r="C445" t="n">
-        <v>19.48934489527705</v>
+        <v>19.48934297559241</v>
       </c>
       <c r="D445" t="n">
-        <v>18.82460829035904</v>
+        <v>18.82460643615043</v>
       </c>
       <c r="E445" t="n">
-        <v>19.17142682933272</v>
+        <v>19.17142494096275</v>
       </c>
       <c r="F445" t="n">
         <v>7439200</v>
@@ -9372,16 +9372,16 @@
         <v>44907</v>
       </c>
       <c r="B448" t="n">
-        <v>18.25621032714844</v>
+        <v>18.25620651245117</v>
       </c>
       <c r="C448" t="n">
-        <v>18.67046578229448</v>
+        <v>18.67046188103712</v>
       </c>
       <c r="D448" t="n">
-        <v>17.87085350954307</v>
+        <v>17.87084977536743</v>
       </c>
       <c r="E448" t="n">
-        <v>18.45852100262552</v>
+        <v>18.45851714565475</v>
       </c>
       <c r="F448" t="n">
         <v>10851800</v>
@@ -9412,16 +9412,16 @@
         <v>44909</v>
       </c>
       <c r="B450" t="n">
-        <v>18.3718147277832</v>
+        <v>18.37181091308594</v>
       </c>
       <c r="C450" t="n">
-        <v>18.46815392602494</v>
+        <v>18.46815009132394</v>
       </c>
       <c r="D450" t="n">
-        <v>17.64927349724626</v>
+        <v>17.64926983257642</v>
       </c>
       <c r="E450" t="n">
-        <v>17.86122010088155</v>
+        <v>17.86121639220342</v>
       </c>
       <c r="F450" t="n">
         <v>10673700</v>
@@ -9452,16 +9452,16 @@
         <v>44911</v>
       </c>
       <c r="B452" t="n">
-        <v>18.02499389648438</v>
+        <v>18.02499198913574</v>
       </c>
       <c r="C452" t="n">
-        <v>18.69936642972459</v>
+        <v>18.69936445101596</v>
       </c>
       <c r="D452" t="n">
-        <v>17.55293385822315</v>
+        <v>17.55293200082644</v>
       </c>
       <c r="E452" t="n">
-        <v>18.38144836977245</v>
+        <v>18.38144642470492</v>
       </c>
       <c r="F452" t="n">
         <v>14090800</v>
@@ -9472,16 +9472,16 @@
         <v>44914</v>
       </c>
       <c r="B453" t="n">
-        <v>18.8342399597168</v>
+        <v>18.83423805236816</v>
       </c>
       <c r="C453" t="n">
-        <v>18.90167868218942</v>
+        <v>18.90167676801125</v>
       </c>
       <c r="D453" t="n">
-        <v>18.13096696301515</v>
+        <v>18.13096512688717</v>
       </c>
       <c r="E453" t="n">
-        <v>18.1502351694359</v>
+        <v>18.15023333135662</v>
       </c>
       <c r="F453" t="n">
         <v>7150400</v>
@@ -9492,16 +9492,16 @@
         <v>44915</v>
       </c>
       <c r="B454" t="n">
-        <v>19.26776313781738</v>
+        <v>19.26776504516602</v>
       </c>
       <c r="C454" t="n">
-        <v>19.66275213514127</v>
+        <v>19.66275408159054</v>
       </c>
       <c r="D454" t="n">
-        <v>18.86314003842253</v>
+        <v>18.86314190571684</v>
       </c>
       <c r="E454" t="n">
-        <v>18.91130871126024</v>
+        <v>18.91131058332285</v>
       </c>
       <c r="F454" t="n">
         <v>10658900</v>
@@ -9572,16 +9572,16 @@
         <v>44921</v>
       </c>
       <c r="B458" t="n">
-        <v>19.2003288269043</v>
+        <v>19.20032691955566</v>
       </c>
       <c r="C458" t="n">
-        <v>19.3255684955305</v>
+        <v>19.32556657574064</v>
       </c>
       <c r="D458" t="n">
-        <v>18.84387435270808</v>
+        <v>18.84387248076942</v>
       </c>
       <c r="E458" t="n">
-        <v>19.07508732076077</v>
+        <v>19.07508542585354</v>
       </c>
       <c r="F458" t="n">
         <v>2369600</v>
@@ -9592,16 +9592,16 @@
         <v>44922</v>
       </c>
       <c r="B459" t="n">
-        <v>18.59339332580566</v>
+        <v>18.59339141845703</v>
       </c>
       <c r="C459" t="n">
-        <v>19.36410506296115</v>
+        <v>19.36410307655132</v>
       </c>
       <c r="D459" t="n">
-        <v>18.41998497652509</v>
+        <v>18.41998308696504</v>
       </c>
       <c r="E459" t="n">
-        <v>19.28703407299734</v>
+        <v>19.28703209449361</v>
       </c>
       <c r="F459" t="n">
         <v>8606100</v>
@@ -9672,16 +9672,16 @@
         <v>44929</v>
       </c>
       <c r="B463" t="n">
-        <v>17.96291732788086</v>
+        <v>17.96291923522949</v>
       </c>
       <c r="C463" t="n">
-        <v>18.3972693953452</v>
+        <v>18.39727134881445</v>
       </c>
       <c r="D463" t="n">
-        <v>17.73126252369413</v>
+        <v>17.73126440644506</v>
       </c>
       <c r="E463" t="n">
-        <v>18.26213788649346</v>
+        <v>18.2621398256141</v>
       </c>
       <c r="F463" t="n">
         <v>7978600</v>
@@ -9732,16 +9732,16 @@
         <v>44932</v>
       </c>
       <c r="B466" t="n">
-        <v>18.37796783447266</v>
+        <v>18.37796592712402</v>
       </c>
       <c r="C466" t="n">
-        <v>18.85092999831188</v>
+        <v>18.85092804187709</v>
       </c>
       <c r="D466" t="n">
-        <v>18.20422625570949</v>
+        <v>18.20422436639255</v>
       </c>
       <c r="E466" t="n">
-        <v>18.33935777651244</v>
+        <v>18.33935587317094</v>
       </c>
       <c r="F466" t="n">
         <v>4999100</v>
@@ -9772,16 +9772,16 @@
         <v>44936</v>
       </c>
       <c r="B468" t="n">
-        <v>18.57101058959961</v>
+        <v>18.57101249694824</v>
       </c>
       <c r="C468" t="n">
-        <v>18.68683890990498</v>
+        <v>18.68684082914984</v>
       </c>
       <c r="D468" t="n">
-        <v>18.14630920318485</v>
+        <v>18.14631106691423</v>
       </c>
       <c r="E468" t="n">
-        <v>18.29109506382374</v>
+        <v>18.29109694242345</v>
       </c>
       <c r="F468" t="n">
         <v>7152400</v>
@@ -9832,16 +9832,16 @@
         <v>44939</v>
       </c>
       <c r="B471" t="n">
-        <v>19.26597595214844</v>
+        <v>19.2659740447998</v>
       </c>
       <c r="C471" t="n">
-        <v>19.60380657549171</v>
+        <v>19.60380463469755</v>
       </c>
       <c r="D471" t="n">
-        <v>18.94745035665993</v>
+        <v>18.94744848084562</v>
       </c>
       <c r="E471" t="n">
-        <v>19.23702025139507</v>
+        <v>19.23701834691308</v>
       </c>
       <c r="F471" t="n">
         <v>6794900</v>
@@ -9992,16 +9992,16 @@
         <v>44951</v>
       </c>
       <c r="B479" t="n">
-        <v>20.37598991394043</v>
+        <v>20.37599182128906</v>
       </c>
       <c r="C479" t="n">
-        <v>20.6172972247506</v>
+        <v>20.61729915468745</v>
       </c>
       <c r="D479" t="n">
-        <v>20.12503008977441</v>
+        <v>20.12503197363128</v>
       </c>
       <c r="E479" t="n">
-        <v>20.57868717132721</v>
+        <v>20.57868909764986</v>
       </c>
       <c r="F479" t="n">
         <v>2807800</v>
@@ -10052,16 +10052,16 @@
         <v>44956</v>
       </c>
       <c r="B482" t="n">
-        <v>20.05746650695801</v>
+        <v>20.05746459960938</v>
       </c>
       <c r="C482" t="n">
-        <v>20.5014711231836</v>
+        <v>20.50146917361271</v>
       </c>
       <c r="D482" t="n">
-        <v>19.85476738661628</v>
+        <v>19.85476549854316</v>
       </c>
       <c r="E482" t="n">
-        <v>20.35668708924173</v>
+        <v>20.35668515343896</v>
       </c>
       <c r="F482" t="n">
         <v>14094800</v>
@@ -10132,16 +10132,16 @@
         <v>44960</v>
       </c>
       <c r="B486" t="n">
-        <v>18.45518493652344</v>
+        <v>18.45518684387207</v>
       </c>
       <c r="C486" t="n">
-        <v>18.82197125869143</v>
+        <v>18.82197320394753</v>
       </c>
       <c r="D486" t="n">
-        <v>18.35866163878593</v>
+        <v>18.35866353615885</v>
       </c>
       <c r="E486" t="n">
-        <v>18.69649226035282</v>
+        <v>18.69649419264063</v>
       </c>
       <c r="F486" t="n">
         <v>6859200</v>
@@ -10252,16 +10252,16 @@
         <v>44970</v>
       </c>
       <c r="B492" t="n">
-        <v>18.02083015441895</v>
+        <v>18.02083206176758</v>
       </c>
       <c r="C492" t="n">
-        <v>18.13665847436409</v>
+        <v>18.13666039397214</v>
       </c>
       <c r="D492" t="n">
-        <v>17.76021781531389</v>
+        <v>17.76021969507897</v>
       </c>
       <c r="E492" t="n">
-        <v>17.91465434788829</v>
+        <v>17.91465624399913</v>
       </c>
       <c r="F492" t="n">
         <v>6817800</v>
@@ -10312,16 +10312,16 @@
         <v>44973</v>
       </c>
       <c r="B495" t="n">
-        <v>18.34900856018066</v>
+        <v>18.3490104675293</v>
       </c>
       <c r="C495" t="n">
-        <v>18.5517058222651</v>
+        <v>18.55170775068378</v>
       </c>
       <c r="D495" t="n">
-        <v>17.88569895453448</v>
+        <v>17.88570081372285</v>
       </c>
       <c r="E495" t="n">
-        <v>18.43587934136792</v>
+        <v>18.43588125774662</v>
       </c>
       <c r="F495" t="n">
         <v>33990600</v>
@@ -10332,16 +10332,16 @@
         <v>44974</v>
       </c>
       <c r="B496" t="n">
-        <v>18.45518493652344</v>
+        <v>18.45518684387207</v>
       </c>
       <c r="C496" t="n">
-        <v>18.62892466321642</v>
+        <v>18.6289265885211</v>
       </c>
       <c r="D496" t="n">
-        <v>18.01117850334242</v>
+        <v>18.01118036480286</v>
       </c>
       <c r="E496" t="n">
-        <v>18.24283331329517</v>
+        <v>18.2428351986972</v>
       </c>
       <c r="F496" t="n">
         <v>11362300</v>
@@ -10352,16 +10352,16 @@
         <v>44979</v>
       </c>
       <c r="B497" t="n">
-        <v>18.17526817321777</v>
+        <v>18.17526626586914</v>
       </c>
       <c r="C497" t="n">
-        <v>18.42622801942978</v>
+        <v>18.42622608574493</v>
       </c>
       <c r="D497" t="n">
-        <v>18.03048414221861</v>
+        <v>18.0304822500639</v>
       </c>
       <c r="E497" t="n">
-        <v>18.32970471842073</v>
+        <v>18.32970279486522</v>
       </c>
       <c r="F497" t="n">
         <v>5044700</v>
@@ -10452,16 +10452,16 @@
         <v>44986</v>
       </c>
       <c r="B502" t="n">
-        <v>17.02664375305176</v>
+        <v>17.02664184570312</v>
       </c>
       <c r="C502" t="n">
-        <v>17.77952324727908</v>
+        <v>17.77952125559183</v>
       </c>
       <c r="D502" t="n">
-        <v>16.67916246735577</v>
+        <v>16.67916059893248</v>
       </c>
       <c r="E502" t="n">
-        <v>17.5092583886011</v>
+        <v>17.5092564271893</v>
       </c>
       <c r="F502" t="n">
         <v>19714300</v>
@@ -10492,16 +10492,16 @@
         <v>44988</v>
       </c>
       <c r="B504" t="n">
-        <v>16.92047119140625</v>
+        <v>16.92046928405762</v>
       </c>
       <c r="C504" t="n">
-        <v>17.22934428926396</v>
+        <v>17.22934234709782</v>
       </c>
       <c r="D504" t="n">
-        <v>16.72742458473074</v>
+        <v>16.72742269914315</v>
       </c>
       <c r="E504" t="n">
-        <v>16.92047119140625</v>
+        <v>16.92046928405762</v>
       </c>
       <c r="F504" t="n">
         <v>8320600</v>
@@ -10592,16 +10592,16 @@
         <v>44995</v>
       </c>
       <c r="B509" t="n">
-        <v>16.28341674804688</v>
+        <v>16.28341865539551</v>
       </c>
       <c r="C509" t="n">
-        <v>17.200383345925</v>
+        <v>17.20038536068198</v>
       </c>
       <c r="D509" t="n">
-        <v>16.10967520458848</v>
+        <v>16.10967709158599</v>
       </c>
       <c r="E509" t="n">
-        <v>17.1135125741958</v>
+        <v>17.11351457877723</v>
       </c>
       <c r="F509" t="n">
         <v>24597700</v>
@@ -10632,16 +10632,16 @@
         <v>44999</v>
       </c>
       <c r="B511" t="n">
-        <v>15.9841947555542</v>
+        <v>15.98419570922852</v>
       </c>
       <c r="C511" t="n">
-        <v>16.40889611157714</v>
+        <v>16.40889709059065</v>
       </c>
       <c r="D511" t="n">
-        <v>15.80080253631832</v>
+        <v>15.80080347905079</v>
       </c>
       <c r="E511" t="n">
-        <v>16.17724132857241</v>
+        <v>16.17724229376458</v>
       </c>
       <c r="F511" t="n">
         <v>10544400</v>
@@ -10752,16 +10752,16 @@
         <v>45007</v>
       </c>
       <c r="B517" t="n">
-        <v>14.68113708496094</v>
+        <v>14.68113803863525</v>
       </c>
       <c r="C517" t="n">
-        <v>15.4919288903244</v>
+        <v>15.49192989666707</v>
       </c>
       <c r="D517" t="n">
-        <v>14.54600465714318</v>
+        <v>14.54600560203941</v>
       </c>
       <c r="E517" t="n">
-        <v>15.38575400308397</v>
+        <v>15.3857550025296</v>
       </c>
       <c r="F517" t="n">
         <v>42950800</v>
@@ -10792,16 +10792,16 @@
         <v>45009</v>
       </c>
       <c r="B519" t="n">
-        <v>14.43017768859863</v>
+        <v>14.43017673492432</v>
       </c>
       <c r="C519" t="n">
-        <v>14.95140146791577</v>
+        <v>14.95140047979436</v>
       </c>
       <c r="D519" t="n">
-        <v>14.01512972021653</v>
+        <v>14.01512879397227</v>
       </c>
       <c r="E519" t="n">
-        <v>14.74870328037497</v>
+        <v>14.74870230564966</v>
       </c>
       <c r="F519" t="n">
         <v>32819700</v>
@@ -10832,16 +10832,16 @@
         <v>45013</v>
       </c>
       <c r="B521" t="n">
-        <v>14.82592010498047</v>
+        <v>14.82592105865479</v>
       </c>
       <c r="C521" t="n">
-        <v>14.99000914178451</v>
+        <v>14.99001010601382</v>
       </c>
       <c r="D521" t="n">
-        <v>14.41087217704756</v>
+        <v>14.410873104024</v>
       </c>
       <c r="E521" t="n">
-        <v>14.5749612138516</v>
+        <v>14.57496215138304</v>
       </c>
       <c r="F521" t="n">
         <v>12984500</v>
@@ -10972,16 +10972,16 @@
         <v>45022</v>
       </c>
       <c r="B528" t="n">
-        <v>13.15607452392578</v>
+        <v>13.1560754776001</v>
       </c>
       <c r="C528" t="n">
-        <v>13.57112338766055</v>
+        <v>13.57112437142145</v>
       </c>
       <c r="D528" t="n">
-        <v>13.00163799430754</v>
+        <v>13.00163893678686</v>
       </c>
       <c r="E528" t="n">
-        <v>13.33946767271886</v>
+        <v>13.33946863968721</v>
       </c>
       <c r="F528" t="n">
         <v>26117400</v>
@@ -10992,16 +10992,16 @@
         <v>45026</v>
       </c>
       <c r="B529" t="n">
-        <v>13.43599033355713</v>
+        <v>13.43599128723145</v>
       </c>
       <c r="C529" t="n">
-        <v>13.47459946415011</v>
+        <v>13.47460042056487</v>
       </c>
       <c r="D529" t="n">
-        <v>13.08850815822031</v>
+        <v>13.08850908723065</v>
       </c>
       <c r="E529" t="n">
-        <v>13.20433554999925</v>
+        <v>13.20433648723092</v>
       </c>
       <c r="F529" t="n">
         <v>12159600</v>
@@ -11032,16 +11032,16 @@
         <v>45028</v>
       </c>
       <c r="B531" t="n">
-        <v>13.93791103363037</v>
+        <v>13.93791007995605</v>
       </c>
       <c r="C531" t="n">
-        <v>14.46878734593694</v>
+        <v>14.46878635593845</v>
       </c>
       <c r="D531" t="n">
-        <v>13.84138865353835</v>
+        <v>13.84138770646839</v>
       </c>
       <c r="E531" t="n">
-        <v>14.28539417940201</v>
+        <v>14.28539320195184</v>
       </c>
       <c r="F531" t="n">
         <v>21392400</v>
@@ -11072,16 +11072,16 @@
         <v>45030</v>
       </c>
       <c r="B533" t="n">
-        <v>12.76033115386963</v>
+        <v>12.76033210754395</v>
       </c>
       <c r="C533" t="n">
-        <v>13.29120743425609</v>
+        <v>13.29120842760674</v>
       </c>
       <c r="D533" t="n">
-        <v>12.59624210501355</v>
+        <v>12.59624304642427</v>
       </c>
       <c r="E533" t="n">
-        <v>13.20433665303648</v>
+        <v>13.20433763989463</v>
       </c>
       <c r="F533" t="n">
         <v>26653800</v>
@@ -11132,16 +11132,16 @@
         <v>45035</v>
       </c>
       <c r="B536" t="n">
-        <v>12.44180583953857</v>
+        <v>12.44180488586426</v>
       </c>
       <c r="C536" t="n">
-        <v>12.69276475454189</v>
+        <v>12.69276378163138</v>
       </c>
       <c r="D536" t="n">
-        <v>12.27771678712426</v>
+        <v>12.2777158460275</v>
       </c>
       <c r="E536" t="n">
-        <v>12.58658986436797</v>
+        <v>12.58658889959584</v>
       </c>
       <c r="F536" t="n">
         <v>13110300</v>
@@ -11252,16 +11252,16 @@
         <v>45044</v>
       </c>
       <c r="B542" t="n">
-        <v>11.91110515594482</v>
+        <v>11.91110610961914</v>
       </c>
       <c r="C542" t="n">
-        <v>12.04678935581152</v>
+        <v>12.04679032034952</v>
       </c>
       <c r="D542" t="n">
-        <v>11.70757931828128</v>
+        <v>11.7075802556601</v>
       </c>
       <c r="E542" t="n">
-        <v>11.8723383737362</v>
+        <v>11.87233932430661</v>
       </c>
       <c r="F542" t="n">
         <v>15072900</v>
@@ -11312,16 +11312,16 @@
         <v>45050</v>
       </c>
       <c r="B545" t="n">
-        <v>11.12607669830322</v>
+        <v>11.12607765197754</v>
       </c>
       <c r="C545" t="n">
-        <v>11.50405351931347</v>
+        <v>11.50405450538616</v>
       </c>
       <c r="D545" t="n">
-        <v>10.64149145692891</v>
+        <v>10.64149236906689</v>
       </c>
       <c r="E545" t="n">
-        <v>11.31991153427135</v>
+        <v>11.31991250456026</v>
       </c>
       <c r="F545" t="n">
         <v>26954400</v>
@@ -11332,16 +11332,16 @@
         <v>45051</v>
       </c>
       <c r="B546" t="n">
-        <v>10.17629051208496</v>
+        <v>10.17628955841064</v>
       </c>
       <c r="C546" t="n">
-        <v>10.95162711690795</v>
+        <v>10.95162609057271</v>
       </c>
       <c r="D546" t="n">
-        <v>10.05999016000247</v>
+        <v>10.05998921722728</v>
       </c>
       <c r="E546" t="n">
-        <v>10.84501776762755</v>
+        <v>10.84501675128325</v>
       </c>
       <c r="F546" t="n">
         <v>52976300</v>
@@ -11372,16 +11372,16 @@
         <v>45055</v>
       </c>
       <c r="B548" t="n">
-        <v>11.26176071166992</v>
+        <v>11.26176166534424</v>
       </c>
       <c r="C548" t="n">
-        <v>11.59127881821781</v>
+        <v>11.59127979979655</v>
       </c>
       <c r="D548" t="n">
-        <v>10.59303349635502</v>
+        <v>10.59303439339983</v>
       </c>
       <c r="E548" t="n">
-        <v>10.80625033354355</v>
+        <v>10.8062512486441</v>
       </c>
       <c r="F548" t="n">
         <v>38878100</v>
@@ -11512,16 +11512,16 @@
         <v>45064</v>
       </c>
       <c r="B555" t="n">
-        <v>10.95162773132324</v>
+        <v>10.95162677764893</v>
       </c>
       <c r="C555" t="n">
-        <v>10.96131965894212</v>
+        <v>10.96131870442382</v>
       </c>
       <c r="D555" t="n">
-        <v>10.6511844450497</v>
+        <v>10.65118351753816</v>
       </c>
       <c r="E555" t="n">
-        <v>10.79656058651357</v>
+        <v>10.7965596463426</v>
       </c>
       <c r="F555" t="n">
         <v>10867600</v>
@@ -11572,16 +11572,16 @@
         <v>45069</v>
       </c>
       <c r="B558" t="n">
-        <v>11.21330165863037</v>
+        <v>11.21330261230469</v>
       </c>
       <c r="C558" t="n">
-        <v>11.89172170384635</v>
+        <v>11.89172271521926</v>
       </c>
       <c r="D558" t="n">
-        <v>11.17453487812714</v>
+        <v>11.1745358285044</v>
       </c>
       <c r="E558" t="n">
-        <v>11.76572943614261</v>
+        <v>11.76573043680007</v>
       </c>
       <c r="F558" t="n">
         <v>12722500</v>
@@ -11792,16 +11792,16 @@
         <v>45084</v>
       </c>
       <c r="B569" t="n">
-        <v>12.3859977722168</v>
+        <v>12.38599872589111</v>
       </c>
       <c r="C569" t="n">
-        <v>13.10318458913605</v>
+        <v>13.103185598031</v>
       </c>
       <c r="D569" t="n">
-        <v>12.09524645987364</v>
+        <v>12.09524739116122</v>
       </c>
       <c r="E569" t="n">
-        <v>12.42476455224435</v>
+        <v>12.42476550890357</v>
       </c>
       <c r="F569" t="n">
         <v>35775900</v>
@@ -11832,16 +11832,16 @@
         <v>45089</v>
       </c>
       <c r="B571" t="n">
-        <v>13.29701900482178</v>
+        <v>13.29701995849609</v>
       </c>
       <c r="C571" t="n">
-        <v>13.52961969400545</v>
+        <v>13.5296206643621</v>
       </c>
       <c r="D571" t="n">
-        <v>12.72520828404051</v>
+        <v>12.72520919670404</v>
       </c>
       <c r="E571" t="n">
-        <v>12.80274184710173</v>
+        <v>12.80274276532604</v>
       </c>
       <c r="F571" t="n">
         <v>31653900</v>
@@ -11892,16 +11892,16 @@
         <v>45092</v>
       </c>
       <c r="B574" t="n">
-        <v>13.66530418395996</v>
+        <v>13.66530323028564</v>
       </c>
       <c r="C574" t="n">
-        <v>13.89790487812169</v>
+        <v>13.89790390821463</v>
       </c>
       <c r="D574" t="n">
-        <v>13.14195215995957</v>
+        <v>13.14195124280895</v>
       </c>
       <c r="E574" t="n">
-        <v>13.27763543608408</v>
+        <v>13.2776345094644</v>
       </c>
       <c r="F574" t="n">
         <v>25113500</v>
@@ -11952,16 +11952,16 @@
         <v>45097</v>
       </c>
       <c r="B577" t="n">
-        <v>12.91904163360596</v>
+        <v>12.91904258728027</v>
       </c>
       <c r="C577" t="n">
-        <v>13.00626711935004</v>
+        <v>13.00626807946328</v>
       </c>
       <c r="D577" t="n">
-        <v>12.6089073947585</v>
+        <v>12.60890832553893</v>
       </c>
       <c r="E577" t="n">
-        <v>12.77366644021444</v>
+        <v>12.77366738315727</v>
       </c>
       <c r="F577" t="n">
         <v>13900100</v>
@@ -11972,16 +11972,16 @@
         <v>45098</v>
       </c>
       <c r="B578" t="n">
-        <v>12.98688507080078</v>
+        <v>12.98688411712646</v>
       </c>
       <c r="C578" t="n">
-        <v>13.03534378341849</v>
+        <v>13.03534282618567</v>
       </c>
       <c r="D578" t="n">
-        <v>12.70582564674574</v>
+        <v>12.70582471371064</v>
       </c>
       <c r="E578" t="n">
-        <v>12.99657699817894</v>
+        <v>12.99657604379291</v>
       </c>
       <c r="F578" t="n">
         <v>18033300</v>
@@ -12032,16 +12032,16 @@
         <v>45103</v>
       </c>
       <c r="B581" t="n">
-        <v>13.47146987915039</v>
+        <v>13.47146892547607</v>
       </c>
       <c r="C581" t="n">
-        <v>14.14019805657877</v>
+        <v>14.14019705556374</v>
       </c>
       <c r="D581" t="n">
-        <v>13.35516952748307</v>
+        <v>13.35516858204191</v>
       </c>
       <c r="E581" t="n">
-        <v>13.85913864231449</v>
+        <v>13.85913766119627</v>
       </c>
       <c r="F581" t="n">
         <v>23023000</v>
@@ -12052,16 +12052,16 @@
         <v>45104</v>
       </c>
       <c r="B582" t="n">
-        <v>12.68644142150879</v>
+        <v>12.68644237518311</v>
       </c>
       <c r="C582" t="n">
-        <v>13.85913771066354</v>
+        <v>13.85913875249263</v>
       </c>
       <c r="D582" t="n">
-        <v>12.5604491512705</v>
+        <v>12.56045009547363</v>
       </c>
       <c r="E582" t="n">
-        <v>13.77191222170834</v>
+        <v>13.77191325698045</v>
       </c>
       <c r="F582" t="n">
         <v>64278500</v>
@@ -12092,16 +12092,16 @@
         <v>45106</v>
       </c>
       <c r="B584" t="n">
-        <v>12.93842697143555</v>
+        <v>12.93842601776123</v>
       </c>
       <c r="C584" t="n">
-        <v>13.19041060729881</v>
+        <v>13.19040963505111</v>
       </c>
       <c r="D584" t="n">
-        <v>12.5798330612484</v>
+        <v>12.57983213400556</v>
       </c>
       <c r="E584" t="n">
-        <v>12.74459212562421</v>
+        <v>12.7445911862372</v>
       </c>
       <c r="F584" t="n">
         <v>22969900</v>
@@ -12132,16 +12132,16 @@
         <v>45110</v>
       </c>
       <c r="B586" t="n">
-        <v>13.20010089874268</v>
+        <v>13.20010185241699</v>
       </c>
       <c r="C586" t="n">
-        <v>13.46177735359831</v>
+        <v>13.46177832617809</v>
       </c>
       <c r="D586" t="n">
-        <v>13.09349248617534</v>
+        <v>13.09349343214747</v>
       </c>
       <c r="E586" t="n">
-        <v>13.46177735359831</v>
+        <v>13.46177832617809</v>
       </c>
       <c r="F586" t="n">
         <v>9654100</v>
@@ -12172,16 +12172,16 @@
         <v>45112</v>
       </c>
       <c r="B588" t="n">
-        <v>13.29701900482178</v>
+        <v>13.29701995849609</v>
       </c>
       <c r="C588" t="n">
-        <v>13.59746133061578</v>
+        <v>13.59746230583809</v>
       </c>
       <c r="D588" t="n">
-        <v>13.14195187869933</v>
+        <v>13.14195282125209</v>
       </c>
       <c r="E588" t="n">
-        <v>13.17102673377904</v>
+        <v>13.17102767841708</v>
       </c>
       <c r="F588" t="n">
         <v>9442900</v>
@@ -12192,16 +12192,16 @@
         <v>45113</v>
       </c>
       <c r="B589" t="n">
-        <v>13.17102718353271</v>
+        <v>13.17102813720703</v>
       </c>
       <c r="C589" t="n">
-        <v>13.32609431495027</v>
+        <v>13.32609527985253</v>
       </c>
       <c r="D589" t="n">
-        <v>13.03534298140585</v>
+        <v>13.03534392525568</v>
       </c>
       <c r="E589" t="n">
-        <v>13.22917689567779</v>
+        <v>13.22917785356256</v>
       </c>
       <c r="F589" t="n">
         <v>10770700</v>
@@ -12212,16 +12212,16 @@
         <v>45114</v>
       </c>
       <c r="B590" t="n">
-        <v>13.56838798522949</v>
+        <v>13.56838703155518</v>
       </c>
       <c r="C590" t="n">
-        <v>13.88821419951091</v>
+        <v>13.88821322335713</v>
       </c>
       <c r="D590" t="n">
-        <v>13.13226141341602</v>
+        <v>13.1322604903955</v>
       </c>
       <c r="E590" t="n">
-        <v>13.28732855679209</v>
+        <v>13.28732762287245</v>
       </c>
       <c r="F590" t="n">
         <v>12191300</v>
@@ -12412,16 +12412,16 @@
         <v>45128</v>
       </c>
       <c r="B600" t="n">
-        <v>12.15339756011963</v>
+        <v>12.15339851379395</v>
       </c>
       <c r="C600" t="n">
-        <v>12.16308948656802</v>
+        <v>12.16309044100286</v>
       </c>
       <c r="D600" t="n">
-        <v>11.80449652643425</v>
+        <v>11.80449745273038</v>
       </c>
       <c r="E600" t="n">
-        <v>11.88203008947544</v>
+        <v>11.88203102185562</v>
       </c>
       <c r="F600" t="n">
         <v>8594300</v>
@@ -12432,16 +12432,16 @@
         <v>45131</v>
       </c>
       <c r="B601" t="n">
-        <v>12.3859977722168</v>
+        <v>12.38599872589111</v>
       </c>
       <c r="C601" t="n">
-        <v>12.54106489232703</v>
+        <v>12.54106585794092</v>
       </c>
       <c r="D601" t="n">
-        <v>12.03709675196877</v>
+        <v>12.03709767877904</v>
       </c>
       <c r="E601" t="n">
-        <v>12.192163872079</v>
+        <v>12.19216481082885</v>
       </c>
       <c r="F601" t="n">
         <v>10834500</v>
@@ -12532,16 +12532,16 @@
         <v>45138</v>
       </c>
       <c r="B606" t="n">
-        <v>13.05472755432129</v>
+        <v>13.05472660064697</v>
       </c>
       <c r="C606" t="n">
-        <v>13.18071983660883</v>
+        <v>13.18071887373052</v>
       </c>
       <c r="D606" t="n">
-        <v>12.72520941976511</v>
+        <v>12.72520849016276</v>
       </c>
       <c r="E606" t="n">
-        <v>12.8996604143591</v>
+        <v>12.89965947201275</v>
       </c>
       <c r="F606" t="n">
         <v>32856600</v>
@@ -12752,16 +12752,16 @@
         <v>45153</v>
       </c>
       <c r="B617" t="n">
-        <v>12.70582580566406</v>
+        <v>12.70582485198975</v>
       </c>
       <c r="C617" t="n">
-        <v>12.87058487606116</v>
+        <v>12.87058391002036</v>
       </c>
       <c r="D617" t="n">
-        <v>12.57014251776509</v>
+        <v>12.5701415742749</v>
       </c>
       <c r="E617" t="n">
-        <v>12.78335937711292</v>
+        <v>12.78335841761909</v>
       </c>
       <c r="F617" t="n">
         <v>15018500</v>
@@ -12792,16 +12792,16 @@
         <v>45155</v>
       </c>
       <c r="B619" t="n">
-        <v>12.60890865325928</v>
+        <v>12.60890769958496</v>
       </c>
       <c r="C619" t="n">
-        <v>12.81243449888516</v>
+        <v>12.81243352981718</v>
       </c>
       <c r="D619" t="n">
-        <v>12.45384151835823</v>
+        <v>12.45384057641241</v>
       </c>
       <c r="E619" t="n">
-        <v>12.67675029371023</v>
+        <v>12.67674933490471</v>
       </c>
       <c r="F619" t="n">
         <v>17965700</v>
@@ -12832,16 +12832,16 @@
         <v>45159</v>
       </c>
       <c r="B621" t="n">
-        <v>12.68644142150879</v>
+        <v>12.68644237518311</v>
       </c>
       <c r="C621" t="n">
-        <v>13.07410923433971</v>
+        <v>13.07411021715607</v>
       </c>
       <c r="D621" t="n">
-        <v>12.68644142150879</v>
+        <v>12.68644237518311</v>
       </c>
       <c r="E621" t="n">
-        <v>13.03534245305662</v>
+        <v>13.03534343295877</v>
       </c>
       <c r="F621" t="n">
         <v>19861900</v>
@@ -12872,16 +12872,16 @@
         <v>45161</v>
       </c>
       <c r="B623" t="n">
-        <v>12.65736770629883</v>
+        <v>12.65736675262451</v>
       </c>
       <c r="C623" t="n">
-        <v>12.66705870928746</v>
+        <v>12.66705775488297</v>
       </c>
       <c r="D623" t="n">
-        <v>12.32784957358586</v>
+        <v>12.32784864473922</v>
       </c>
       <c r="E623" t="n">
-        <v>12.57014220948974</v>
+        <v>12.57014126238746</v>
       </c>
       <c r="F623" t="n">
         <v>19525000</v>
@@ -12912,16 +12912,16 @@
         <v>45163</v>
       </c>
       <c r="B625" t="n">
-        <v>11.98863792419434</v>
+        <v>11.98863887786865</v>
       </c>
       <c r="C625" t="n">
-        <v>12.50229798541463</v>
+        <v>12.50229897994967</v>
       </c>
       <c r="D625" t="n">
-        <v>11.94017921858345</v>
+        <v>11.94018016840297</v>
       </c>
       <c r="E625" t="n">
-        <v>12.4053814984658</v>
+        <v>12.40538248529131</v>
       </c>
       <c r="F625" t="n">
         <v>23324500</v>
@@ -13012,16 +13012,16 @@
         <v>45170</v>
       </c>
       <c r="B630" t="n">
-        <v>11.49436092376709</v>
+        <v>11.49436187744141</v>
       </c>
       <c r="C630" t="n">
-        <v>11.68819574845535</v>
+        <v>11.68819671821193</v>
       </c>
       <c r="D630" t="n">
-        <v>11.30052702335177</v>
+        <v>11.30052796094391</v>
       </c>
       <c r="E630" t="n">
-        <v>11.33929380343484</v>
+        <v>11.33929474424341</v>
       </c>
       <c r="F630" t="n">
         <v>20778900</v>
@@ -13212,16 +13212,16 @@
         <v>45187</v>
       </c>
       <c r="B640" t="n">
-        <v>11.88203144073486</v>
+        <v>11.88203048706055</v>
       </c>
       <c r="C640" t="n">
-        <v>12.11463215631048</v>
+        <v>12.11463118396719</v>
       </c>
       <c r="D640" t="n">
-        <v>11.82388079970442</v>
+        <v>11.82387985069738</v>
       </c>
       <c r="E640" t="n">
-        <v>12.00802372607326</v>
+        <v>12.00802276228657</v>
       </c>
       <c r="F640" t="n">
         <v>10083800</v>
@@ -13312,16 +13312,16 @@
         <v>45194</v>
       </c>
       <c r="B645" t="n">
-        <v>11.03885269165039</v>
+        <v>11.03885173797607</v>
       </c>
       <c r="C645" t="n">
-        <v>11.03885269165039</v>
+        <v>11.03885173797607</v>
       </c>
       <c r="D645" t="n">
-        <v>10.83532684296994</v>
+        <v>10.83532590687873</v>
       </c>
       <c r="E645" t="n">
-        <v>11.03885269165039</v>
+        <v>11.03885173797607</v>
       </c>
       <c r="F645" t="n">
         <v>6587600</v>
@@ -13412,16 +13412,16 @@
         <v>45201</v>
       </c>
       <c r="B650" t="n">
-        <v>11.63004589080811</v>
+        <v>11.63004493713379</v>
       </c>
       <c r="C650" t="n">
-        <v>11.84326365760269</v>
+        <v>11.84326268644433</v>
       </c>
       <c r="D650" t="n">
-        <v>11.61066203733905</v>
+        <v>11.61066108525423</v>
       </c>
       <c r="E650" t="n">
-        <v>11.82387980413364</v>
+        <v>11.82387883456477</v>
       </c>
       <c r="F650" t="n">
         <v>7262700</v>
@@ -13492,16 +13492,16 @@
         <v>45205</v>
       </c>
       <c r="B654" t="n">
-        <v>11.3877534866333</v>
+        <v>11.38775253295898</v>
       </c>
       <c r="C654" t="n">
-        <v>11.52343769070169</v>
+        <v>11.52343672566442</v>
       </c>
       <c r="D654" t="n">
-        <v>10.70933431483741</v>
+        <v>10.70933341797772</v>
       </c>
       <c r="E654" t="n">
-        <v>11.01946858211027</v>
+        <v>11.0194676592782</v>
       </c>
       <c r="F654" t="n">
         <v>19863000</v>
@@ -13552,16 +13552,16 @@
         <v>45210</v>
       </c>
       <c r="B657" t="n">
-        <v>11.7948055267334</v>
+        <v>11.79480457305908</v>
       </c>
       <c r="C657" t="n">
-        <v>12.01771430692309</v>
+        <v>12.01771333522539</v>
       </c>
       <c r="D657" t="n">
-        <v>11.70758003039028</v>
+        <v>11.70757908376862</v>
       </c>
       <c r="E657" t="n">
-        <v>11.77542167231357</v>
+        <v>11.77542072020655</v>
       </c>
       <c r="F657" t="n">
         <v>11967500</v>
@@ -13572,16 +13572,16 @@
         <v>45212</v>
       </c>
       <c r="B658" t="n">
-        <v>11.26176071166992</v>
+        <v>11.26176166534424</v>
       </c>
       <c r="C658" t="n">
-        <v>11.79480465318721</v>
+        <v>11.79480565200103</v>
       </c>
       <c r="D658" t="n">
-        <v>11.21330200348235</v>
+        <v>11.21330295305306</v>
       </c>
       <c r="E658" t="n">
-        <v>11.7851127266951</v>
+        <v>11.78511372468819</v>
       </c>
       <c r="F658" t="n">
         <v>9170200</v>
@@ -13612,16 +13612,16 @@
         <v>45216</v>
       </c>
       <c r="B660" t="n">
-        <v>11.21330165863037</v>
+        <v>11.21330261230469</v>
       </c>
       <c r="C660" t="n">
-        <v>11.6785039489421</v>
+        <v>11.67850494218117</v>
       </c>
       <c r="D660" t="n">
-        <v>11.17453487812714</v>
+        <v>11.1745358285044</v>
       </c>
       <c r="E660" t="n">
-        <v>11.33929392633411</v>
+        <v>11.33929489072388</v>
       </c>
       <c r="F660" t="n">
         <v>9846900</v>
@@ -13652,16 +13652,16 @@
         <v>45218</v>
       </c>
       <c r="B662" t="n">
-        <v>10.65118312835693</v>
+        <v>10.65118217468262</v>
       </c>
       <c r="C662" t="n">
-        <v>10.91285959607978</v>
+        <v>10.91285861897575</v>
       </c>
       <c r="D662" t="n">
-        <v>10.38950758490707</v>
+        <v>10.38950665466237</v>
       </c>
       <c r="E662" t="n">
-        <v>10.41858243989639</v>
+        <v>10.41858150704843</v>
       </c>
       <c r="F662" t="n">
         <v>8209500</v>
@@ -13732,16 +13732,16 @@
         <v>45224</v>
       </c>
       <c r="B666" t="n">
-        <v>10.68994998931885</v>
+        <v>10.68995094299316</v>
       </c>
       <c r="C666" t="n">
-        <v>11.09700165929046</v>
+        <v>11.09700264927877</v>
       </c>
       <c r="D666" t="n">
-        <v>10.60272449942879</v>
+        <v>10.60272544532153</v>
       </c>
       <c r="E666" t="n">
-        <v>11.02916002238619</v>
+        <v>11.02916100632219</v>
       </c>
       <c r="F666" t="n">
         <v>7670100</v>
@@ -13792,16 +13792,16 @@
         <v>45229</v>
       </c>
       <c r="B669" t="n">
-        <v>10.62210941314697</v>
+        <v>10.62210845947266</v>
       </c>
       <c r="C669" t="n">
-        <v>11.09700276744609</v>
+        <v>11.0970017711349</v>
       </c>
       <c r="D669" t="n">
-        <v>10.53488391454651</v>
+        <v>10.53488296870347</v>
       </c>
       <c r="E669" t="n">
-        <v>10.95162755262737</v>
+        <v>10.95162656936825</v>
       </c>
       <c r="F669" t="n">
         <v>14902100</v>
@@ -13812,16 +13812,16 @@
         <v>45230</v>
       </c>
       <c r="B670" t="n">
-        <v>10.60272598266602</v>
+        <v>10.6027250289917</v>
       </c>
       <c r="C670" t="n">
-        <v>11.1357699987949</v>
+        <v>11.13576899717533</v>
       </c>
       <c r="D670" t="n">
-        <v>10.52519240842252</v>
+        <v>10.52519146172205</v>
       </c>
       <c r="E670" t="n">
-        <v>10.77717698685044</v>
+        <v>10.77717601748493</v>
       </c>
       <c r="F670" t="n">
         <v>15178600</v>
@@ -13852,16 +13852,16 @@
         <v>45233</v>
       </c>
       <c r="B672" t="n">
-        <v>11.57189464569092</v>
+        <v>11.57189559936523</v>
       </c>
       <c r="C672" t="n">
-        <v>11.61066142631588</v>
+        <v>11.61066238318509</v>
       </c>
       <c r="D672" t="n">
-        <v>11.2423774725152</v>
+        <v>11.24237839903302</v>
       </c>
       <c r="E672" t="n">
-        <v>11.25206847446672</v>
+        <v>11.25206940178321</v>
       </c>
       <c r="F672" t="n">
         <v>16636800</v>
@@ -13872,16 +13872,16 @@
         <v>45236</v>
       </c>
       <c r="B673" t="n">
-        <v>11.3877534866333</v>
+        <v>11.38775253295898</v>
       </c>
       <c r="C673" t="n">
-        <v>11.77542132072437</v>
+        <v>11.77542033458458</v>
       </c>
       <c r="D673" t="n">
-        <v>11.35867863014473</v>
+        <v>11.3586776789053</v>
       </c>
       <c r="E673" t="n">
-        <v>11.64942996784954</v>
+        <v>11.64942899226097</v>
       </c>
       <c r="F673" t="n">
         <v>11056500</v>
@@ -13912,16 +13912,16 @@
         <v>45238</v>
       </c>
       <c r="B675" t="n">
-        <v>11.9401798248291</v>
+        <v>11.94018077850342</v>
       </c>
       <c r="C675" t="n">
-        <v>12.30846471218883</v>
+        <v>12.30846569527843</v>
       </c>
       <c r="D675" t="n">
-        <v>11.68819620654969</v>
+        <v>11.68819714009782</v>
       </c>
       <c r="E675" t="n">
-        <v>11.83357140649062</v>
+        <v>11.83357235165001</v>
       </c>
       <c r="F675" t="n">
         <v>13850200</v>
@@ -13972,16 +13972,16 @@
         <v>45243</v>
       </c>
       <c r="B678" t="n">
-        <v>12.15339756011963</v>
+        <v>12.15339851379395</v>
       </c>
       <c r="C678" t="n">
-        <v>12.42476503076381</v>
+        <v>12.42476600573227</v>
       </c>
       <c r="D678" t="n">
-        <v>12.07586399707843</v>
+        <v>12.07586494466871</v>
       </c>
       <c r="E678" t="n">
-        <v>12.13401463149582</v>
+        <v>12.13401558364916</v>
       </c>
       <c r="F678" t="n">
         <v>9434300</v>
@@ -13992,16 +13992,16 @@
         <v>45244</v>
       </c>
       <c r="B679" t="n">
-        <v>12.16308975219727</v>
+        <v>12.16308879852295</v>
       </c>
       <c r="C679" t="n">
-        <v>12.50229886684223</v>
+        <v>12.50229788657146</v>
       </c>
       <c r="D679" t="n">
-        <v>12.11463104316999</v>
+        <v>12.11463009329518</v>
       </c>
       <c r="E679" t="n">
-        <v>12.24062331693171</v>
+        <v>12.24062235717821</v>
       </c>
       <c r="F679" t="n">
         <v>21179500</v>
@@ -14012,16 +14012,16 @@
         <v>45246</v>
       </c>
       <c r="B680" t="n">
-        <v>12.92873477935791</v>
+        <v>12.92873573303223</v>
       </c>
       <c r="C680" t="n">
-        <v>13.13226062387078</v>
+        <v>13.13226159255796</v>
       </c>
       <c r="D680" t="n">
-        <v>12.16309011176626</v>
+        <v>12.16309100896362</v>
       </c>
       <c r="E680" t="n">
-        <v>12.40538273979239</v>
+        <v>12.40538365486221</v>
       </c>
       <c r="F680" t="n">
         <v>22426900</v>
@@ -14032,16 +14032,16 @@
         <v>45247</v>
       </c>
       <c r="B681" t="n">
-        <v>12.70582580566406</v>
+        <v>12.70582485198975</v>
       </c>
       <c r="C681" t="n">
-        <v>13.03534394645827</v>
+        <v>13.03534296805097</v>
       </c>
       <c r="D681" t="n">
-        <v>12.63798416171458</v>
+        <v>12.63798321313232</v>
       </c>
       <c r="E681" t="n">
-        <v>13.02565201895889</v>
+        <v>13.02565104127905</v>
       </c>
       <c r="F681" t="n">
         <v>13810400</v>
@@ -14072,16 +14072,16 @@
         <v>45251</v>
       </c>
       <c r="B683" t="n">
-        <v>12.3859977722168</v>
+        <v>12.38599872589111</v>
       </c>
       <c r="C683" t="n">
-        <v>12.48291518442216</v>
+        <v>12.48291614555875</v>
       </c>
       <c r="D683" t="n">
-        <v>12.22123872603144</v>
+        <v>12.22123966701994</v>
       </c>
       <c r="E683" t="n">
-        <v>12.44414840439461</v>
+        <v>12.4441493625463</v>
       </c>
       <c r="F683" t="n">
         <v>9484000</v>
@@ -14172,16 +14172,16 @@
         <v>45258</v>
       </c>
       <c r="B688" t="n">
-        <v>13.10318660736084</v>
+        <v>13.10318565368652</v>
       </c>
       <c r="C688" t="n">
-        <v>13.48116253977923</v>
+        <v>13.48116155859512</v>
       </c>
       <c r="D688" t="n">
-        <v>12.98688532509186</v>
+        <v>12.98688437988217</v>
       </c>
       <c r="E688" t="n">
-        <v>13.14195339335947</v>
+        <v>13.14195243686364</v>
       </c>
       <c r="F688" t="n">
         <v>17069200</v>
@@ -14192,16 +14192,16 @@
         <v>45259</v>
       </c>
       <c r="B689" t="n">
-        <v>12.76397514343262</v>
+        <v>12.76397609710693</v>
       </c>
       <c r="C689" t="n">
-        <v>13.45208621300327</v>
+        <v>13.45208721809055</v>
       </c>
       <c r="D689" t="n">
-        <v>12.72520836166552</v>
+        <v>12.72520931244334</v>
       </c>
       <c r="E689" t="n">
-        <v>13.22917652463774</v>
+        <v>13.22917751307009</v>
       </c>
       <c r="F689" t="n">
         <v>13863800</v>
@@ -14272,16 +14272,16 @@
         <v>45265</v>
       </c>
       <c r="B693" t="n">
-        <v>12.3084659576416</v>
+        <v>12.30846500396729</v>
       </c>
       <c r="C693" t="n">
-        <v>12.65736795164083</v>
+        <v>12.65736697093318</v>
       </c>
       <c r="D693" t="n">
-        <v>12.23093238659134</v>
+        <v>12.23093143892442</v>
       </c>
       <c r="E693" t="n">
-        <v>12.33754081571718</v>
+        <v>12.33753985979011</v>
       </c>
       <c r="F693" t="n">
         <v>12428700</v>
@@ -14332,16 +14332,16 @@
         <v>45268</v>
       </c>
       <c r="B696" t="n">
-        <v>11.61066150665283</v>
+        <v>11.61066246032715</v>
       </c>
       <c r="C696" t="n">
-        <v>11.96925538525615</v>
+        <v>11.96925636838458</v>
       </c>
       <c r="D696" t="n">
-        <v>11.58158665205117</v>
+        <v>11.58158760333734</v>
       </c>
       <c r="E696" t="n">
-        <v>11.85295411830358</v>
+        <v>11.85295509187928</v>
       </c>
       <c r="F696" t="n">
         <v>16929900</v>
@@ -14352,16 +14352,16 @@
         <v>45271</v>
       </c>
       <c r="B697" t="n">
-        <v>11.54281997680664</v>
+        <v>11.54282093048096</v>
       </c>
       <c r="C697" t="n">
-        <v>11.64942931844344</v>
+        <v>11.64943028092588</v>
       </c>
       <c r="D697" t="n">
-        <v>11.40713670457504</v>
+        <v>11.40713764703913</v>
       </c>
       <c r="E697" t="n">
-        <v>11.63004546568294</v>
+        <v>11.63004642656387</v>
       </c>
       <c r="F697" t="n">
         <v>10547700</v>
@@ -14452,16 +14452,16 @@
         <v>45278</v>
       </c>
       <c r="B702" t="n">
-        <v>12.80274105072021</v>
+        <v>12.80274200439453</v>
       </c>
       <c r="C702" t="n">
-        <v>12.97719201889291</v>
+        <v>12.97719298556206</v>
       </c>
       <c r="D702" t="n">
-        <v>12.34723070286534</v>
+        <v>12.34723162260876</v>
       </c>
       <c r="E702" t="n">
-        <v>12.55075652430919</v>
+        <v>12.55075745921321</v>
       </c>
       <c r="F702" t="n">
         <v>9094600</v>
@@ -14472,16 +14472,16 @@
         <v>45279</v>
       </c>
       <c r="B703" t="n">
-        <v>12.98688507080078</v>
+        <v>12.98688411712646</v>
       </c>
       <c r="C703" t="n">
-        <v>13.0547276381748</v>
+        <v>13.05472667951856</v>
       </c>
       <c r="D703" t="n">
-        <v>12.87058471508212</v>
+        <v>12.87058376994816</v>
       </c>
       <c r="E703" t="n">
-        <v>12.98688507080078</v>
+        <v>12.98688411712646</v>
       </c>
       <c r="F703" t="n">
         <v>5248800</v>
@@ -14512,16 +14512,16 @@
         <v>45281</v>
       </c>
       <c r="B705" t="n">
-        <v>12.83181667327881</v>
+        <v>12.83181762695312</v>
       </c>
       <c r="C705" t="n">
-        <v>13.13225992266906</v>
+        <v>13.13226089867264</v>
       </c>
       <c r="D705" t="n">
-        <v>12.75428311039222</v>
+        <v>12.75428405830416</v>
       </c>
       <c r="E705" t="n">
-        <v>13.13225992266906</v>
+        <v>13.13226089867264</v>
       </c>
       <c r="F705" t="n">
         <v>7705900</v>
@@ -14652,16 +14652,16 @@
         <v>45295</v>
       </c>
       <c r="B712" t="n">
-        <v>12.80274105072021</v>
+        <v>12.80274200439453</v>
       </c>
       <c r="C712" t="n">
-        <v>12.91904138807771</v>
+        <v>12.91904235041522</v>
       </c>
       <c r="D712" t="n">
-        <v>12.44414811279971</v>
+        <v>12.44414903976249</v>
       </c>
       <c r="E712" t="n">
-        <v>12.502297819342</v>
+        <v>12.50229875063634</v>
       </c>
       <c r="F712" t="n">
         <v>8604100</v>
@@ -14672,16 +14672,16 @@
         <v>45296</v>
       </c>
       <c r="B713" t="n">
-        <v>13.16133499145508</v>
+        <v>13.16133594512939</v>
       </c>
       <c r="C713" t="n">
-        <v>13.61684537401709</v>
+        <v>13.61684636069783</v>
       </c>
       <c r="D713" t="n">
-        <v>12.74459139096602</v>
+        <v>12.74459231444297</v>
       </c>
       <c r="E713" t="n">
-        <v>12.80274202621196</v>
+        <v>12.80274295390252</v>
       </c>
       <c r="F713" t="n">
         <v>12696400</v>
@@ -14732,16 +14732,16 @@
         <v>45301</v>
       </c>
       <c r="B716" t="n">
-        <v>13.16133499145508</v>
+        <v>13.16133594512939</v>
       </c>
       <c r="C716" t="n">
-        <v>13.56838666535765</v>
+        <v>13.56838764852705</v>
       </c>
       <c r="D716" t="n">
-        <v>13.0450346452362</v>
+        <v>13.04503559048336</v>
       </c>
       <c r="E716" t="n">
-        <v>13.56838666535765</v>
+        <v>13.56838764852705</v>
       </c>
       <c r="F716" t="n">
         <v>19324800</v>
@@ -14792,16 +14792,16 @@
         <v>45306</v>
       </c>
       <c r="B719" t="n">
-        <v>14.24680614471436</v>
+        <v>14.24680519104004</v>
       </c>
       <c r="C719" t="n">
-        <v>14.33403163747295</v>
+        <v>14.3340306779598</v>
       </c>
       <c r="D719" t="n">
-        <v>13.70407118308557</v>
+        <v>13.70407026574167</v>
       </c>
       <c r="E719" t="n">
-        <v>13.80098767838277</v>
+        <v>13.80098675455133</v>
       </c>
       <c r="F719" t="n">
         <v>8029800</v>
@@ -14832,16 +14832,16 @@
         <v>45308</v>
       </c>
       <c r="B721" t="n">
-        <v>13.65561199188232</v>
+        <v>13.65561294555664</v>
       </c>
       <c r="C721" t="n">
-        <v>14.28557242406093</v>
+        <v>14.28557342173013</v>
       </c>
       <c r="D721" t="n">
-        <v>13.29701903095126</v>
+        <v>13.29701995958232</v>
       </c>
       <c r="E721" t="n">
-        <v>14.04327980795024</v>
+        <v>14.04328078869832</v>
       </c>
       <c r="F721" t="n">
         <v>14787300</v>
@@ -14852,16 +14852,16 @@
         <v>45309</v>
       </c>
       <c r="B722" t="n">
-        <v>13.36486053466797</v>
+        <v>13.36486148834229</v>
       </c>
       <c r="C722" t="n">
-        <v>13.85913768843952</v>
+        <v>13.85913867738389</v>
       </c>
       <c r="D722" t="n">
-        <v>13.24856019100519</v>
+        <v>13.24856113638068</v>
       </c>
       <c r="E722" t="n">
-        <v>13.71376156565631</v>
+        <v>13.71376254422711</v>
       </c>
       <c r="F722" t="n">
         <v>8302800</v>
@@ -14932,16 +14932,16 @@
         <v>45315</v>
       </c>
       <c r="B726" t="n">
-        <v>12.93842697143555</v>
+        <v>12.93842601776123</v>
       </c>
       <c r="C726" t="n">
-        <v>13.43270324028994</v>
+        <v>13.43270225018317</v>
       </c>
       <c r="D726" t="n">
-        <v>12.93842697143555</v>
+        <v>12.93842601776123</v>
       </c>
       <c r="E726" t="n">
-        <v>13.2776361030593</v>
+        <v>13.27763512438233</v>
       </c>
       <c r="F726" t="n">
         <v>9089400</v>
@@ -14952,16 +14952,16 @@
         <v>45316</v>
       </c>
       <c r="B727" t="n">
-        <v>13.56838798522949</v>
+        <v>13.56838703155518</v>
       </c>
       <c r="C727" t="n">
-        <v>13.60715477107351</v>
+        <v>13.60715381467441</v>
       </c>
       <c r="D727" t="n">
-        <v>12.93842748419593</v>
+        <v>12.93842657479932</v>
       </c>
       <c r="E727" t="n">
-        <v>12.93842748419593</v>
+        <v>12.93842657479932</v>
       </c>
       <c r="F727" t="n">
         <v>8608700</v>
@@ -15052,16 +15052,16 @@
         <v>45323</v>
       </c>
       <c r="B732" t="n">
-        <v>13.16133499145508</v>
+        <v>13.16133594512939</v>
       </c>
       <c r="C732" t="n">
-        <v>13.45208631913877</v>
+        <v>13.45208729388101</v>
       </c>
       <c r="D732" t="n">
-        <v>13.0450346452362</v>
+        <v>13.04503559048336</v>
       </c>
       <c r="E732" t="n">
-        <v>13.19040984694155</v>
+        <v>13.19041080272264</v>
       </c>
       <c r="F732" t="n">
         <v>12981400</v>
@@ -15072,16 +15072,16 @@
         <v>45324</v>
       </c>
       <c r="B733" t="n">
-        <v>13.10318660736084</v>
+        <v>13.10318565368652</v>
       </c>
       <c r="C733" t="n">
-        <v>13.28732860978607</v>
+        <v>13.28732764270956</v>
       </c>
       <c r="D733" t="n">
-        <v>12.85120203623319</v>
+        <v>12.85120110089878</v>
       </c>
       <c r="E733" t="n">
-        <v>13.11287761065569</v>
+        <v>13.11287665627604</v>
       </c>
       <c r="F733" t="n">
         <v>9537000</v>
@@ -15112,16 +15112,16 @@
         <v>45328</v>
       </c>
       <c r="B735" t="n">
-        <v>13.36486053466797</v>
+        <v>13.36486148834229</v>
       </c>
       <c r="C735" t="n">
-        <v>13.4520860234833</v>
+        <v>13.45208698338175</v>
       </c>
       <c r="D735" t="n">
-        <v>12.96750079608522</v>
+        <v>12.9675017214052</v>
       </c>
       <c r="E735" t="n">
-        <v>13.05472628490055</v>
+        <v>13.05472721644466</v>
       </c>
       <c r="F735" t="n">
         <v>13604000</v>
@@ -15132,16 +15132,16 @@
         <v>45329</v>
       </c>
       <c r="B736" t="n">
-        <v>13.38424491882324</v>
+        <v>13.38424396514893</v>
       </c>
       <c r="C736" t="n">
-        <v>13.54900305234901</v>
+        <v>13.5490020869351</v>
       </c>
       <c r="D736" t="n">
-        <v>13.13226036874593</v>
+        <v>13.1322594330264</v>
       </c>
       <c r="E736" t="n">
-        <v>13.36486106530668</v>
+        <v>13.36486011301353</v>
       </c>
       <c r="F736" t="n">
         <v>10806100</v>
@@ -15172,16 +15172,16 @@
         <v>45331</v>
       </c>
       <c r="B738" t="n">
-        <v>12.93842697143555</v>
+        <v>12.93842601776123</v>
       </c>
       <c r="C738" t="n">
-        <v>13.40362838312745</v>
+        <v>13.40362739516376</v>
       </c>
       <c r="D738" t="n">
-        <v>12.90935119000002</v>
+        <v>12.90935023846884</v>
       </c>
       <c r="E738" t="n">
-        <v>13.40362838312745</v>
+        <v>13.40362739516376</v>
       </c>
       <c r="F738" t="n">
         <v>18553100</v>
@@ -15392,16 +15392,16 @@
         <v>45350</v>
       </c>
       <c r="B749" t="n">
-        <v>13.5780782699585</v>
+        <v>13.57807922363281</v>
       </c>
       <c r="C749" t="n">
-        <v>14.22742254748699</v>
+        <v>14.22742354676887</v>
       </c>
       <c r="D749" t="n">
-        <v>13.30670987760992</v>
+        <v>13.30671081222432</v>
       </c>
       <c r="E749" t="n">
-        <v>14.15957998726337</v>
+        <v>14.15958098178023</v>
       </c>
       <c r="F749" t="n">
         <v>16650200</v>
@@ -15452,16 +15452,16 @@
         <v>45355</v>
       </c>
       <c r="B752" t="n">
-        <v>13.59746074676514</v>
+        <v>13.59746170043945</v>
       </c>
       <c r="C752" t="n">
-        <v>13.77191171829877</v>
+        <v>13.77191268420841</v>
       </c>
       <c r="D752" t="n">
-        <v>13.48116040716703</v>
+        <v>13.48116135268448</v>
       </c>
       <c r="E752" t="n">
-        <v>13.67499430649721</v>
+        <v>13.67499526560944</v>
       </c>
       <c r="F752" t="n">
         <v>6926800</v>
@@ -15472,16 +15472,16 @@
         <v>45356</v>
       </c>
       <c r="B753" t="n">
-        <v>14.02389621734619</v>
+        <v>14.02389717102051</v>
       </c>
       <c r="C753" t="n">
-        <v>14.13050463066464</v>
+        <v>14.1305055915887</v>
       </c>
       <c r="D753" t="n">
-        <v>13.587769713787</v>
+        <v>13.58777063780318</v>
       </c>
       <c r="E753" t="n">
-        <v>13.64591942131599</v>
+        <v>13.64592034928656</v>
       </c>
       <c r="F753" t="n">
         <v>16007800</v>
@@ -15532,16 +15532,16 @@
         <v>45359</v>
       </c>
       <c r="B756" t="n">
-        <v>13.96574687957764</v>
+        <v>13.96574592590332</v>
       </c>
       <c r="C756" t="n">
-        <v>14.09173915659519</v>
+        <v>14.09173819431728</v>
       </c>
       <c r="D756" t="n">
-        <v>13.70407132290505</v>
+        <v>13.70407038709969</v>
       </c>
       <c r="E756" t="n">
-        <v>13.86883038329161</v>
+        <v>13.8688294362354</v>
       </c>
       <c r="F756" t="n">
         <v>9093700</v>
@@ -15592,16 +15592,16 @@
         <v>45364</v>
       </c>
       <c r="B759" t="n">
-        <v>14.24680614471436</v>
+        <v>14.24680519104004</v>
       </c>
       <c r="C759" t="n">
-        <v>14.47940684255526</v>
+        <v>14.47940587331077</v>
       </c>
       <c r="D759" t="n">
-        <v>14.16927257876739</v>
+        <v>14.16927163028313</v>
       </c>
       <c r="E759" t="n">
-        <v>14.19834743492925</v>
+        <v>14.19834648449873</v>
       </c>
       <c r="F759" t="n">
         <v>5340300</v>
@@ -15612,16 +15612,16 @@
         <v>45365</v>
       </c>
       <c r="B760" t="n">
-        <v>14.0917387008667</v>
+        <v>14.09173965454102</v>
       </c>
       <c r="C760" t="n">
-        <v>14.38249002886788</v>
+        <v>14.38249100221912</v>
       </c>
       <c r="D760" t="n">
-        <v>13.80098737286552</v>
+        <v>13.80098830686291</v>
       </c>
       <c r="E760" t="n">
-        <v>14.24680582932786</v>
+        <v>14.24680679349652</v>
       </c>
       <c r="F760" t="n">
         <v>10904800</v>
@@ -15672,16 +15672,16 @@
         <v>45370</v>
       </c>
       <c r="B763" t="n">
-        <v>14.27588081359863</v>
+        <v>14.27588176727295</v>
       </c>
       <c r="C763" t="n">
-        <v>14.35341530280148</v>
+        <v>14.35341626165535</v>
       </c>
       <c r="D763" t="n">
-        <v>14.00451333634416</v>
+        <v>14.00451427189027</v>
       </c>
       <c r="E763" t="n">
-        <v>14.09173882795849</v>
+        <v>14.09173976933154</v>
       </c>
       <c r="F763" t="n">
         <v>3066400</v>
@@ -15692,16 +15692,16 @@
         <v>45371</v>
       </c>
       <c r="B764" t="n">
-        <v>14.4697151184082</v>
+        <v>14.46971607208252</v>
       </c>
       <c r="C764" t="n">
-        <v>14.58601546152873</v>
+        <v>14.5860164228682</v>
       </c>
       <c r="D764" t="n">
-        <v>14.15957994581383</v>
+        <v>14.15958087904767</v>
       </c>
       <c r="E764" t="n">
-        <v>14.28557221526265</v>
+        <v>14.28557315680042</v>
       </c>
       <c r="F764" t="n">
         <v>13419100</v>
@@ -15712,16 +15712,16 @@
         <v>45372</v>
       </c>
       <c r="B765" t="n">
-        <v>14.3631067276001</v>
+        <v>14.36310577392578</v>
       </c>
       <c r="C765" t="n">
-        <v>14.47940707841501</v>
+        <v>14.47940611701864</v>
       </c>
       <c r="D765" t="n">
-        <v>14.19834766621072</v>
+        <v>14.19834672347599</v>
       </c>
       <c r="E765" t="n">
-        <v>14.46002414874904</v>
+        <v>14.46002318863964</v>
       </c>
       <c r="F765" t="n">
         <v>19402800</v>
@@ -15792,16 +15792,16 @@
         <v>45378</v>
       </c>
       <c r="B769" t="n">
-        <v>14.42125606536865</v>
+        <v>14.42125701904297</v>
       </c>
       <c r="C769" t="n">
-        <v>14.57632318581246</v>
+        <v>14.57632414974133</v>
       </c>
       <c r="D769" t="n">
-        <v>14.0045124859712</v>
+        <v>14.00451341208636</v>
       </c>
       <c r="E769" t="n">
-        <v>14.04327926608215</v>
+        <v>14.04328019476095</v>
       </c>
       <c r="F769" t="n">
         <v>11710900</v>
@@ -15832,16 +15832,16 @@
         <v>45383</v>
       </c>
       <c r="B771" t="n">
-        <v>13.74283790588379</v>
+        <v>13.74283885955811</v>
       </c>
       <c r="C771" t="n">
-        <v>14.25649800910157</v>
+        <v>14.25649899842096</v>
       </c>
       <c r="D771" t="n">
-        <v>13.65561241350713</v>
+        <v>13.65561336112849</v>
       </c>
       <c r="E771" t="n">
-        <v>14.20803929952865</v>
+        <v>14.20804028548528</v>
       </c>
       <c r="F771" t="n">
         <v>14371700</v>
@@ -15872,16 +15872,16 @@
         <v>45385</v>
       </c>
       <c r="B773" t="n">
-        <v>13.56838798522949</v>
+        <v>13.56838703155518</v>
       </c>
       <c r="C773" t="n">
-        <v>13.7040721978201</v>
+        <v>13.70407123460901</v>
       </c>
       <c r="D773" t="n">
-        <v>13.31640341510683</v>
+        <v>13.31640247914363</v>
       </c>
       <c r="E773" t="n">
-        <v>13.63622962938825</v>
+        <v>13.63622867094559</v>
       </c>
       <c r="F773" t="n">
         <v>11886900</v>
@@ -15992,16 +15992,16 @@
         <v>45393</v>
       </c>
       <c r="B779" t="n">
-        <v>13.74283790588379</v>
+        <v>13.74283885955811</v>
       </c>
       <c r="C779" t="n">
-        <v>13.83975440075663</v>
+        <v>13.8397553611564</v>
       </c>
       <c r="D779" t="n">
-        <v>13.62653755747257</v>
+        <v>13.62653850307631</v>
       </c>
       <c r="E779" t="n">
-        <v>13.74283790588379</v>
+        <v>13.74283885955811</v>
       </c>
       <c r="F779" t="n">
         <v>5563300</v>
@@ -16012,16 +16012,16 @@
         <v>45394</v>
       </c>
       <c r="B780" t="n">
-        <v>13.54900360107422</v>
+        <v>13.5490026473999</v>
       </c>
       <c r="C780" t="n">
-        <v>13.83006394280913</v>
+        <v>13.8300629693518</v>
       </c>
       <c r="D780" t="n">
-        <v>13.51023681674407</v>
+        <v>13.51023586579843</v>
       </c>
       <c r="E780" t="n">
-        <v>13.60715423970597</v>
+        <v>13.6071532819386</v>
       </c>
       <c r="F780" t="n">
         <v>8459200</v>
@@ -16112,16 +16112,16 @@
         <v>45401</v>
       </c>
       <c r="B785" t="n">
-        <v>12.96750068664551</v>
+        <v>12.96750164031982</v>
       </c>
       <c r="C785" t="n">
-        <v>13.20979329829971</v>
+        <v>13.20979426979305</v>
       </c>
       <c r="D785" t="n">
-        <v>12.77366678217674</v>
+        <v>12.77366772159585</v>
       </c>
       <c r="E785" t="n">
-        <v>12.80274163677882</v>
+        <v>12.80274257833619</v>
       </c>
       <c r="F785" t="n">
         <v>12837800</v>
@@ -16132,16 +16132,16 @@
         <v>45404</v>
       </c>
       <c r="B786" t="n">
-        <v>13.14195251464844</v>
+        <v>13.14195156097412</v>
       </c>
       <c r="C786" t="n">
-        <v>13.19041030070188</v>
+        <v>13.19040934351112</v>
       </c>
       <c r="D786" t="n">
-        <v>12.83181732312288</v>
+        <v>12.8318163919542</v>
       </c>
       <c r="E786" t="n">
-        <v>13.01596023750884</v>
+        <v>13.01595929297743</v>
       </c>
       <c r="F786" t="n">
         <v>6410200</v>
@@ -16232,16 +16232,16 @@
         <v>45411</v>
       </c>
       <c r="B791" t="n">
-        <v>13.17102718353271</v>
+        <v>13.17102813720703</v>
       </c>
       <c r="C791" t="n">
-        <v>13.21948589316895</v>
+        <v>13.21948685035202</v>
       </c>
       <c r="D791" t="n">
-        <v>12.89965970355199</v>
+        <v>12.8996606375774</v>
       </c>
       <c r="E791" t="n">
-        <v>12.98688427176961</v>
+        <v>12.98688521211069</v>
       </c>
       <c r="F791" t="n">
         <v>6604200</v>
@@ -16312,16 +16312,16 @@
         <v>45418</v>
       </c>
       <c r="B795" t="n">
-        <v>12.92873477935791</v>
+        <v>12.92873573303223</v>
       </c>
       <c r="C795" t="n">
-        <v>13.2097941908973</v>
+        <v>13.20979516530366</v>
       </c>
       <c r="D795" t="n">
-        <v>12.81243442881813</v>
+        <v>12.81243537391368</v>
       </c>
       <c r="E795" t="n">
-        <v>13.11287676997764</v>
+        <v>13.11287773723499</v>
       </c>
       <c r="F795" t="n">
         <v>7469100</v>
@@ -16352,16 +16352,16 @@
         <v>45420</v>
       </c>
       <c r="B797" t="n">
-        <v>13.10318660736084</v>
+        <v>13.10318565368652</v>
       </c>
       <c r="C797" t="n">
-        <v>13.20010311022088</v>
+        <v>13.2001021494928</v>
       </c>
       <c r="D797" t="n">
-        <v>12.97719432179701</v>
+        <v>12.97719337729265</v>
       </c>
       <c r="E797" t="n">
-        <v>13.00626918022772</v>
+        <v>13.00626823360723</v>
       </c>
       <c r="F797" t="n">
         <v>4964400</v>
@@ -16372,16 +16372,16 @@
         <v>45421</v>
       </c>
       <c r="B798" t="n">
-        <v>13.03534317016602</v>
+        <v>13.0353422164917</v>
       </c>
       <c r="C798" t="n">
-        <v>13.07410995358177</v>
+        <v>13.07410899707125</v>
       </c>
       <c r="D798" t="n">
-        <v>12.72520890283996</v>
+        <v>12.72520797185527</v>
       </c>
       <c r="E798" t="n">
-        <v>12.88996796342518</v>
+        <v>12.88996702038661</v>
       </c>
       <c r="F798" t="n">
         <v>8332000</v>
@@ -16412,16 +16412,16 @@
         <v>45425</v>
       </c>
       <c r="B800" t="n">
-        <v>12.92873477935791</v>
+        <v>12.92873573303223</v>
       </c>
       <c r="C800" t="n">
-        <v>13.1516435534909</v>
+        <v>13.15164452360784</v>
       </c>
       <c r="D800" t="n">
-        <v>12.79305057492499</v>
+        <v>12.7930515185907</v>
       </c>
       <c r="E800" t="n">
-        <v>12.98688449249129</v>
+        <v>12.98688545045495</v>
       </c>
       <c r="F800" t="n">
         <v>6951300</v>
@@ -16472,16 +16472,16 @@
         <v>45428</v>
       </c>
       <c r="B803" t="n">
-        <v>13.05472755432129</v>
+        <v>13.05472660064697</v>
       </c>
       <c r="C803" t="n">
-        <v>13.21948662159938</v>
+        <v>13.21948565588908</v>
       </c>
       <c r="D803" t="n">
-        <v>12.94811820239249</v>
+        <v>12.9481172565062</v>
       </c>
       <c r="E803" t="n">
-        <v>13.20010276696758</v>
+        <v>13.2001018026733</v>
       </c>
       <c r="F803" t="n">
         <v>4347100</v>
@@ -16492,16 +16492,16 @@
         <v>45429</v>
       </c>
       <c r="B804" t="n">
-        <v>13.20979309082031</v>
+        <v>13.20979404449463</v>
       </c>
       <c r="C804" t="n">
-        <v>13.25825179724463</v>
+        <v>13.2582527544174</v>
       </c>
       <c r="D804" t="n">
-        <v>12.97719240911113</v>
+        <v>12.97719334599296</v>
       </c>
       <c r="E804" t="n">
-        <v>12.99657533711709</v>
+        <v>12.99657627539826</v>
       </c>
       <c r="F804" t="n">
         <v>6205200</v>
@@ -16632,16 +16632,16 @@
         <v>45440</v>
       </c>
       <c r="B811" t="n">
-        <v>12.3084659576416</v>
+        <v>12.30846500396729</v>
       </c>
       <c r="C811" t="n">
-        <v>12.75428445331711</v>
+        <v>12.75428346510026</v>
       </c>
       <c r="D811" t="n">
-        <v>12.17278267044019</v>
+        <v>12.17278172727877</v>
       </c>
       <c r="E811" t="n">
-        <v>12.72520959524153</v>
+        <v>12.72520860927743</v>
       </c>
       <c r="F811" t="n">
         <v>7568500</v>
@@ -16692,16 +16692,16 @@
         <v>45446</v>
       </c>
       <c r="B814" t="n">
-        <v>11.91110515594482</v>
+        <v>11.91110610961914</v>
       </c>
       <c r="C814" t="n">
-        <v>11.99833064698248</v>
+        <v>11.99833160764059</v>
       </c>
       <c r="D814" t="n">
-        <v>11.69788739166088</v>
+        <v>11.6978883282637</v>
       </c>
       <c r="E814" t="n">
-        <v>11.74634610048991</v>
+        <v>11.74634704097263</v>
       </c>
       <c r="F814" t="n">
         <v>7880700</v>
@@ -16732,16 +16732,16 @@
         <v>45448</v>
       </c>
       <c r="B816" t="n">
-        <v>11.70757961273193</v>
+        <v>11.70758056640625</v>
       </c>
       <c r="C816" t="n">
-        <v>12.07586451511291</v>
+        <v>12.07586549878692</v>
       </c>
       <c r="D816" t="n">
-        <v>11.63973797322884</v>
+        <v>11.63973892137692</v>
       </c>
       <c r="E816" t="n">
-        <v>11.67850475641247</v>
+        <v>11.67850570771841</v>
       </c>
       <c r="F816" t="n">
         <v>8966900</v>
@@ -16772,16 +16772,16 @@
         <v>45450</v>
       </c>
       <c r="B818" t="n">
-        <v>11.63004589080811</v>
+        <v>11.63004493713379</v>
       </c>
       <c r="C818" t="n">
-        <v>11.83357173086817</v>
+        <v>11.83357076050455</v>
       </c>
       <c r="D818" t="n">
-        <v>11.50405361607826</v>
+        <v>11.50405267273542</v>
       </c>
       <c r="E818" t="n">
-        <v>11.7366543120689</v>
+        <v>11.7366533496526</v>
       </c>
       <c r="F818" t="n">
         <v>7620600</v>
@@ -16812,16 +16812,16 @@
         <v>45454</v>
       </c>
       <c r="B820" t="n">
-        <v>11.63004589080811</v>
+        <v>11.63004493713379</v>
       </c>
       <c r="C820" t="n">
-        <v>11.69788752940379</v>
+        <v>11.6978865701664</v>
       </c>
       <c r="D820" t="n">
-        <v>11.47497876014768</v>
+        <v>11.47497781918901</v>
       </c>
       <c r="E820" t="n">
-        <v>11.56220425221242</v>
+        <v>11.56220330410118</v>
       </c>
       <c r="F820" t="n">
         <v>6029300</v>
@@ -16832,16 +16832,16 @@
         <v>45455</v>
       </c>
       <c r="B821" t="n">
-        <v>11.43621253967285</v>
+        <v>11.43621158599854</v>
       </c>
       <c r="C821" t="n">
-        <v>11.84326423980314</v>
+        <v>11.84326325218448</v>
       </c>
       <c r="D821" t="n">
-        <v>11.34898704332021</v>
+        <v>11.34898609691969</v>
       </c>
       <c r="E821" t="n">
-        <v>11.77542167359939</v>
+        <v>11.77542069163817</v>
       </c>
       <c r="F821" t="n">
         <v>19599700</v>
@@ -16852,16 +16852,16 @@
         <v>45456</v>
       </c>
       <c r="B822" t="n">
-        <v>11.21330165863037</v>
+        <v>11.21330261230469</v>
       </c>
       <c r="C822" t="n">
-        <v>11.48467004642594</v>
+        <v>11.48467102317973</v>
       </c>
       <c r="D822" t="n">
-        <v>11.18422680432119</v>
+        <v>11.18422775552273</v>
       </c>
       <c r="E822" t="n">
-        <v>11.38775263303139</v>
+        <v>11.3877536015425</v>
       </c>
       <c r="F822" t="n">
         <v>6392900</v>
@@ -16972,16 +16972,16 @@
         <v>45464</v>
       </c>
       <c r="B828" t="n">
-        <v>10.45734977722168</v>
+        <v>10.45734882354736</v>
       </c>
       <c r="C828" t="n">
-        <v>10.59303398150649</v>
+        <v>10.59303301545824</v>
       </c>
       <c r="D828" t="n">
-        <v>10.34104942680885</v>
+        <v>10.34104848374073</v>
       </c>
       <c r="E828" t="n">
-        <v>10.49611656069262</v>
+        <v>10.49611560348291</v>
       </c>
       <c r="F828" t="n">
         <v>14565700</v>
@@ -16992,16 +16992,16 @@
         <v>45467</v>
       </c>
       <c r="B829" t="n">
-        <v>10.72871685028076</v>
+        <v>10.72871780395508</v>
       </c>
       <c r="C829" t="n">
-        <v>10.80625041425074</v>
+        <v>10.80625137481701</v>
       </c>
       <c r="D829" t="n">
-        <v>10.38950773898034</v>
+        <v>10.3895086625024</v>
       </c>
       <c r="E829" t="n">
-        <v>10.53488294035581</v>
+        <v>10.53488387680025</v>
       </c>
       <c r="F829" t="n">
         <v>12559000</v>
@@ -17012,16 +17012,16 @@
         <v>45468</v>
       </c>
       <c r="B830" t="n">
-        <v>10.55426788330078</v>
+        <v>10.55426692962646</v>
       </c>
       <c r="C830" t="n">
-        <v>10.85471024363938</v>
+        <v>10.85470926281736</v>
       </c>
       <c r="D830" t="n">
-        <v>10.52519210060498</v>
+        <v>10.52519114955792</v>
       </c>
       <c r="E830" t="n">
-        <v>10.68995117212218</v>
+        <v>10.68995020618764</v>
       </c>
       <c r="F830" t="n">
         <v>9834800</v>
@@ -17032,16 +17032,16 @@
         <v>45469</v>
       </c>
       <c r="B831" t="n">
-        <v>10.35074043273926</v>
+        <v>10.35074138641357</v>
       </c>
       <c r="C831" t="n">
-        <v>10.58334111286818</v>
+        <v>10.58334208797336</v>
       </c>
       <c r="D831" t="n">
-        <v>10.25382302054907</v>
+        <v>10.25382396529382</v>
       </c>
       <c r="E831" t="n">
-        <v>10.57364918679457</v>
+        <v>10.57365016100677</v>
       </c>
       <c r="F831" t="n">
         <v>18723900</v>
@@ -17092,16 +17092,16 @@
         <v>45474</v>
       </c>
       <c r="B834" t="n">
-        <v>9.691705703735352</v>
+        <v>9.691704750061035</v>
       </c>
       <c r="C834" t="n">
-        <v>10.08906548970481</v>
+        <v>10.08906449692986</v>
       </c>
       <c r="D834" t="n">
-        <v>9.594788276988766</v>
+        <v>9.594787332851229</v>
       </c>
       <c r="E834" t="n">
-        <v>9.982457059702028</v>
+        <v>9.982456077417465</v>
       </c>
       <c r="F834" t="n">
         <v>19240000</v>
@@ -17112,16 +17112,16 @@
         <v>45475</v>
       </c>
       <c r="B835" t="n">
-        <v>9.59478759765625</v>
+        <v>9.594786643981934</v>
       </c>
       <c r="C835" t="n">
-        <v>9.730471800640107</v>
+        <v>9.730470833479455</v>
       </c>
       <c r="D835" t="n">
-        <v>9.478487248358521</v>
+        <v>9.478486306243884</v>
       </c>
       <c r="E835" t="n">
-        <v>9.672321163854736</v>
+        <v>9.672320202473967</v>
       </c>
       <c r="F835" t="n">
         <v>21630700</v>
@@ -17132,16 +17132,16 @@
         <v>45476</v>
       </c>
       <c r="B836" t="n">
-        <v>10.17629051208496</v>
+        <v>10.17628955841064</v>
       </c>
       <c r="C836" t="n">
-        <v>10.31197471831772</v>
+        <v>10.31197375192772</v>
       </c>
       <c r="D836" t="n">
-        <v>9.691705249604725</v>
+        <v>9.69170434134347</v>
       </c>
       <c r="E836" t="n">
-        <v>9.691705249604725</v>
+        <v>9.69170434134347</v>
       </c>
       <c r="F836" t="n">
         <v>29182300</v>
@@ -17152,16 +17152,16 @@
         <v>45477</v>
       </c>
       <c r="B837" t="n">
-        <v>10.68994998931885</v>
+        <v>10.68995094299316</v>
       </c>
       <c r="C837" t="n">
-        <v>10.7868674057018</v>
+        <v>10.78686836802233</v>
       </c>
       <c r="D837" t="n">
-        <v>10.40889059093587</v>
+        <v>10.40889151953625</v>
       </c>
       <c r="E837" t="n">
-        <v>10.50580800731882</v>
+        <v>10.50580894456542</v>
       </c>
       <c r="F837" t="n">
         <v>16102500</v>
@@ -17172,16 +17172,16 @@
         <v>45478</v>
       </c>
       <c r="B838" t="n">
-        <v>11.09700107574463</v>
+        <v>11.09700202941895</v>
       </c>
       <c r="C838" t="n">
-        <v>11.18422656104786</v>
+        <v>11.18422752221831</v>
       </c>
       <c r="D838" t="n">
-        <v>10.66087457350143</v>
+        <v>10.66087548969511</v>
       </c>
       <c r="E838" t="n">
-        <v>10.73840813282142</v>
+        <v>10.73840905567833</v>
       </c>
       <c r="F838" t="n">
         <v>25549700</v>
@@ -17212,16 +17212,16 @@
         <v>45482</v>
       </c>
       <c r="B840" t="n">
-        <v>11.12607669830322</v>
+        <v>11.12607765197754</v>
       </c>
       <c r="C840" t="n">
-        <v>11.36836931899038</v>
+        <v>11.36837029343287</v>
       </c>
       <c r="D840" t="n">
-        <v>11.0970018426172</v>
+        <v>11.09700279379936</v>
       </c>
       <c r="E840" t="n">
-        <v>11.26176089862631</v>
+        <v>11.26176186393083</v>
       </c>
       <c r="F840" t="n">
         <v>14484000</v>
@@ -17232,16 +17232,16 @@
         <v>45483</v>
       </c>
       <c r="B841" t="n">
-        <v>10.95162773132324</v>
+        <v>10.95162677764893</v>
       </c>
       <c r="C841" t="n">
-        <v>11.24237908997791</v>
+        <v>11.24237811098479</v>
       </c>
       <c r="D841" t="n">
-        <v>10.91286094512083</v>
+        <v>10.91285999482234</v>
       </c>
       <c r="E841" t="n">
-        <v>11.19392037615662</v>
+        <v>11.19391940138331</v>
       </c>
       <c r="F841" t="n">
         <v>14212100</v>
@@ -17252,16 +17252,16 @@
         <v>45484</v>
       </c>
       <c r="B842" t="n">
-        <v>10.90316867828369</v>
+        <v>10.90316772460938</v>
       </c>
       <c r="C842" t="n">
-        <v>11.2229948855715</v>
+        <v>11.22299390392275</v>
       </c>
       <c r="D842" t="n">
-        <v>10.72871768366377</v>
+        <v>10.72871674524827</v>
       </c>
       <c r="E842" t="n">
-        <v>11.09700260326523</v>
+        <v>11.09700163263672</v>
       </c>
       <c r="F842" t="n">
         <v>13851900</v>
@@ -17352,16 +17352,16 @@
         <v>45491</v>
       </c>
       <c r="B847" t="n">
-        <v>10.08906555175781</v>
+        <v>10.0890645980835</v>
       </c>
       <c r="C847" t="n">
-        <v>10.41858369559522</v>
+        <v>10.41858271077302</v>
       </c>
       <c r="D847" t="n">
-        <v>10.05029876567536</v>
+        <v>10.05029781566549</v>
       </c>
       <c r="E847" t="n">
-        <v>10.41858369559522</v>
+        <v>10.41858271077302</v>
       </c>
       <c r="F847" t="n">
         <v>10952400</v>
@@ -17372,16 +17372,16 @@
         <v>45492</v>
       </c>
       <c r="B848" t="n">
-        <v>10.21505737304688</v>
+        <v>10.21505641937256</v>
       </c>
       <c r="C848" t="n">
-        <v>10.34104965315341</v>
+        <v>10.34104868771649</v>
       </c>
       <c r="D848" t="n">
-        <v>10.09875702008847</v>
+        <v>10.09875607727191</v>
       </c>
       <c r="E848" t="n">
-        <v>10.11813995011168</v>
+        <v>10.11813900548554</v>
       </c>
       <c r="F848" t="n">
         <v>9806100</v>
@@ -17432,16 +17432,16 @@
         <v>45497</v>
       </c>
       <c r="B851" t="n">
-        <v>9.691705703735352</v>
+        <v>9.691704750061035</v>
       </c>
       <c r="C851" t="n">
-        <v>10.26351648813943</v>
+        <v>10.26351547819831</v>
       </c>
       <c r="D851" t="n">
-        <v>9.691705703735352</v>
+        <v>9.691704750061035</v>
       </c>
       <c r="E851" t="n">
-        <v>10.09875741723408</v>
+        <v>10.09875642350544</v>
       </c>
       <c r="F851" t="n">
         <v>20101500</v>
@@ -17452,16 +17452,16 @@
         <v>45498</v>
       </c>
       <c r="B852" t="n">
-        <v>9.59478759765625</v>
+        <v>9.594786643981934</v>
       </c>
       <c r="C852" t="n">
-        <v>9.817697293681658</v>
+        <v>9.817696317851222</v>
       </c>
       <c r="D852" t="n">
-        <v>9.585096595086201</v>
+        <v>9.585095642375123</v>
       </c>
       <c r="E852" t="n">
-        <v>9.682013090697801</v>
+        <v>9.682012128353703</v>
       </c>
       <c r="F852" t="n">
         <v>20234100</v>
@@ -17512,16 +17512,16 @@
         <v>45503</v>
       </c>
       <c r="B855" t="n">
-        <v>9.148969650268555</v>
+        <v>9.148968696594238</v>
       </c>
       <c r="C855" t="n">
-        <v>9.439721002187216</v>
+        <v>9.439720018205433</v>
       </c>
       <c r="D855" t="n">
-        <v>9.139278647147284</v>
+        <v>9.139277694483143</v>
       </c>
       <c r="E855" t="n">
-        <v>9.207120290361514</v>
+        <v>9.207119330625666</v>
       </c>
       <c r="F855" t="n">
         <v>13878900</v>
@@ -17612,16 +17612,16 @@
         <v>45510</v>
       </c>
       <c r="B860" t="n">
-        <v>9.643246650695801</v>
+        <v>9.643245697021484</v>
       </c>
       <c r="C860" t="n">
-        <v>10.01153156537833</v>
+        <v>10.01153057528227</v>
       </c>
       <c r="D860" t="n">
-        <v>9.643246650695801</v>
+        <v>9.643245697021484</v>
       </c>
       <c r="E860" t="n">
-        <v>9.904923139130645</v>
+        <v>9.904922159577684</v>
       </c>
       <c r="F860" t="n">
         <v>9331400</v>
@@ -17652,16 +17652,16 @@
         <v>45512</v>
       </c>
       <c r="B862" t="n">
-        <v>10.12783145904541</v>
+        <v>10.12783050537109</v>
       </c>
       <c r="C862" t="n">
-        <v>10.1956740220078</v>
+        <v>10.19567306194518</v>
       </c>
       <c r="D862" t="n">
-        <v>9.963072401422901</v>
+        <v>9.96307146326291</v>
       </c>
       <c r="E862" t="n">
-        <v>9.982456254918727</v>
+        <v>9.982455314933482</v>
       </c>
       <c r="F862" t="n">
         <v>7383500</v>
@@ -17672,16 +17672,16 @@
         <v>45513</v>
       </c>
       <c r="B863" t="n">
-        <v>9.953380584716797</v>
+        <v>9.953381538391113</v>
       </c>
       <c r="C863" t="n">
-        <v>10.13752255649849</v>
+        <v>10.1375235278162</v>
       </c>
       <c r="D863" t="n">
-        <v>9.662629275975187</v>
+        <v>9.662630201791425</v>
       </c>
       <c r="E863" t="n">
-        <v>10.12783063054342</v>
+        <v>10.12783160093251</v>
       </c>
       <c r="F863" t="n">
         <v>24889300</v>
@@ -17812,16 +17812,16 @@
         <v>45524</v>
       </c>
       <c r="B870" t="n">
-        <v>9.904922485351562</v>
+        <v>9.904923439025879</v>
       </c>
       <c r="C870" t="n">
-        <v>10.3895077214844</v>
+        <v>10.38950872181597</v>
       </c>
       <c r="D870" t="n">
-        <v>9.904922485351562</v>
+        <v>9.904923439025879</v>
       </c>
       <c r="E870" t="n">
-        <v>10.37981579493622</v>
+        <v>10.37981679433463</v>
       </c>
       <c r="F870" t="n">
         <v>10092800</v>
@@ -17892,16 +17892,16 @@
         <v>45530</v>
       </c>
       <c r="B874" t="n">
-        <v>9.362187385559082</v>
+        <v>9.362186431884766</v>
       </c>
       <c r="C874" t="n">
-        <v>9.478487740900261</v>
+        <v>9.47848677537907</v>
       </c>
       <c r="D874" t="n">
-        <v>9.216812172450874</v>
+        <v>9.216811233585126</v>
       </c>
       <c r="E874" t="n">
-        <v>9.478487740900261</v>
+        <v>9.47848677537907</v>
       </c>
       <c r="F874" t="n">
         <v>15789500</v>
@@ -18012,16 +18012,16 @@
         <v>45538</v>
       </c>
       <c r="B880" t="n">
-        <v>9.691705703735352</v>
+        <v>9.691704750061035</v>
       </c>
       <c r="C880" t="n">
-        <v>9.817697988796681</v>
+        <v>9.817697022724587</v>
       </c>
       <c r="D880" t="n">
-        <v>9.497871774515261</v>
+        <v>9.497870839914412</v>
       </c>
       <c r="E880" t="n">
-        <v>9.556021491144747</v>
+        <v>9.556020550821904</v>
       </c>
       <c r="F880" t="n">
         <v>16401400</v>
@@ -18032,16 +18032,16 @@
         <v>45539</v>
       </c>
       <c r="B881" t="n">
-        <v>9.672321319580078</v>
+        <v>9.672322273254395</v>
       </c>
       <c r="C881" t="n">
-        <v>10.05029815408792</v>
+        <v>10.05029914503011</v>
       </c>
       <c r="D881" t="n">
-        <v>9.652938389854897</v>
+        <v>9.65293934161809</v>
       </c>
       <c r="E881" t="n">
-        <v>9.730471957301681</v>
+        <v>9.730472916709552</v>
       </c>
       <c r="F881" t="n">
         <v>19605600</v>
@@ -18052,16 +18052,16 @@
         <v>45540</v>
       </c>
       <c r="B882" t="n">
-        <v>9.294345855712891</v>
+        <v>9.294344902038574</v>
       </c>
       <c r="C882" t="n">
-        <v>9.711089493958539</v>
+        <v>9.711088497522988</v>
       </c>
       <c r="D882" t="n">
-        <v>9.255579070127697</v>
+        <v>9.255578120431162</v>
       </c>
       <c r="E882" t="n">
-        <v>9.623863995323582</v>
+        <v>9.623863007838066</v>
       </c>
       <c r="F882" t="n">
         <v>22096900</v>
@@ -18092,16 +18092,16 @@
         <v>45544</v>
       </c>
       <c r="B884" t="n">
-        <v>8.964827537536621</v>
+        <v>8.964826583862305</v>
       </c>
       <c r="C884" t="n">
-        <v>9.12958660406022</v>
+        <v>9.129585632858907</v>
       </c>
       <c r="D884" t="n">
-        <v>8.664384262030925</v>
+        <v>8.664383340317629</v>
       </c>
       <c r="E884" t="n">
-        <v>8.790376543741504</v>
+        <v>8.790375608625205</v>
       </c>
       <c r="F884" t="n">
         <v>20755700</v>
@@ -18232,16 +18232,16 @@
         <v>45553</v>
       </c>
       <c r="B891" t="n">
-        <v>8.470550537109375</v>
+        <v>8.470549583435059</v>
       </c>
       <c r="C891" t="n">
-        <v>8.761301892179148</v>
+        <v>8.761300905769993</v>
       </c>
       <c r="D891" t="n">
-        <v>8.470550537109375</v>
+        <v>8.470549583435059</v>
       </c>
       <c r="E891" t="n">
-        <v>8.548084108558237</v>
+        <v>8.548083146154644</v>
       </c>
       <c r="F891" t="n">
         <v>22128100</v>
@@ -18352,16 +18352,16 @@
         <v>45561</v>
       </c>
       <c r="B897" t="n">
-        <v>7.801823139190674</v>
+        <v>7.801822662353516</v>
       </c>
       <c r="C897" t="n">
-        <v>7.869664782156651</v>
+        <v>7.8696643011731</v>
       </c>
       <c r="D897" t="n">
-        <v>7.549838573498384</v>
+        <v>7.54983811206219</v>
       </c>
       <c r="E897" t="n">
-        <v>7.559530500857256</v>
+        <v>7.559530038828704</v>
       </c>
       <c r="F897" t="n">
         <v>14720200</v>
@@ -18372,16 +18372,16 @@
         <v>45562</v>
       </c>
       <c r="B898" t="n">
-        <v>7.869664192199707</v>
+        <v>7.869664669036865</v>
       </c>
       <c r="C898" t="n">
-        <v>7.966581609976793</v>
+        <v>7.966582092686352</v>
       </c>
       <c r="D898" t="n">
-        <v>7.753363845431002</v>
+        <v>7.753364315221312</v>
       </c>
       <c r="E898" t="n">
-        <v>7.753363845431002</v>
+        <v>7.753364315221312</v>
       </c>
       <c r="F898" t="n">
         <v>13583900</v>
@@ -18392,16 +18392,16 @@
         <v>45565</v>
       </c>
       <c r="B899" t="n">
-        <v>7.239703178405762</v>
+        <v>7.23970365524292</v>
       </c>
       <c r="C899" t="n">
-        <v>7.666138238944893</v>
+        <v>7.666138743868849</v>
       </c>
       <c r="D899" t="n">
-        <v>7.055561196527413</v>
+        <v>7.055561661236209</v>
       </c>
       <c r="E899" t="n">
-        <v>7.569221284762475</v>
+        <v>7.569221783303075</v>
       </c>
       <c r="F899" t="n">
         <v>49266200</v>
@@ -18672,16 +18672,16 @@
         <v>45583</v>
       </c>
       <c r="B913" t="n">
-        <v>6.871418952941895</v>
+        <v>6.871419429779053</v>
       </c>
       <c r="C913" t="n">
-        <v>7.007102692754978</v>
+        <v>7.007103179007811</v>
       </c>
       <c r="D913" t="n">
-        <v>6.755118142394176</v>
+        <v>6.755118611160723</v>
       </c>
       <c r="E913" t="n">
-        <v>6.881110417574576</v>
+        <v>6.881110895084267</v>
       </c>
       <c r="F913" t="n">
         <v>25498900</v>
@@ -18732,16 +18732,16 @@
         <v>45588</v>
       </c>
       <c r="B916" t="n">
-        <v>7.04586935043335</v>
+        <v>7.045869827270508</v>
       </c>
       <c r="C916" t="n">
-        <v>7.239703261009804</v>
+        <v>7.239703750964892</v>
       </c>
       <c r="D916" t="n">
-        <v>6.929569004087476</v>
+        <v>6.929569473053877</v>
       </c>
       <c r="E916" t="n">
-        <v>7.007102568318058</v>
+        <v>7.007103042531631</v>
       </c>
       <c r="F916" t="n">
         <v>16495300</v>
@@ -18752,16 +18752,16 @@
         <v>45589</v>
       </c>
       <c r="B917" t="n">
-        <v>7.239703178405762</v>
+        <v>7.23970365524292</v>
       </c>
       <c r="C917" t="n">
-        <v>7.259086569242245</v>
+        <v>7.259087047356075</v>
       </c>
       <c r="D917" t="n">
-        <v>6.929568925022024</v>
+        <v>6.929569381432441</v>
       </c>
       <c r="E917" t="n">
-        <v>7.007102488367958</v>
+        <v>7.00710294988506</v>
       </c>
       <c r="F917" t="n">
         <v>17525100</v>
@@ -18772,16 +18772,16 @@
         <v>45590</v>
       </c>
       <c r="B918" t="n">
-        <v>7.04586935043335</v>
+        <v>7.045869827270508</v>
       </c>
       <c r="C918" t="n">
-        <v>7.297853896319237</v>
+        <v>7.297854390209734</v>
       </c>
       <c r="D918" t="n">
-        <v>7.026485959375703</v>
+        <v>7.026486434901069</v>
       </c>
       <c r="E918" t="n">
-        <v>7.278470505261592</v>
+        <v>7.278470997840296</v>
       </c>
       <c r="F918" t="n">
         <v>15271300</v>
@@ -18832,16 +18832,16 @@
         <v>45595</v>
       </c>
       <c r="B921" t="n">
-        <v>7.443228721618652</v>
+        <v>7.443229198455811</v>
       </c>
       <c r="C921" t="n">
-        <v>7.598296304371199</v>
+        <v>7.598296791142485</v>
       </c>
       <c r="D921" t="n">
-        <v>7.249394820848559</v>
+        <v>7.249395285268095</v>
       </c>
       <c r="E921" t="n">
-        <v>7.317236917186328</v>
+        <v>7.317237385952047</v>
       </c>
       <c r="F921" t="n">
         <v>17976200</v>
@@ -18852,16 +18852,16 @@
         <v>45596</v>
       </c>
       <c r="B922" t="n">
-        <v>7.259086608886719</v>
+        <v>7.259087085723877</v>
       </c>
       <c r="C922" t="n">
-        <v>7.511071153273676</v>
+        <v>7.511071646663273</v>
       </c>
       <c r="D922" t="n">
-        <v>7.249395144483795</v>
+        <v>7.249395620684336</v>
       </c>
       <c r="E922" t="n">
-        <v>7.385078881080197</v>
+        <v>7.385079366193574</v>
       </c>
       <c r="F922" t="n">
         <v>15084800</v>
@@ -18892,16 +18892,16 @@
         <v>45600</v>
       </c>
       <c r="B924" t="n">
-        <v>7.481996059417725</v>
+        <v>7.481996536254883</v>
       </c>
       <c r="C924" t="n">
-        <v>7.549838160811873</v>
+        <v>7.549838641972695</v>
       </c>
       <c r="D924" t="n">
-        <v>7.171861795070777</v>
+        <v>7.171862252142683</v>
       </c>
       <c r="E924" t="n">
-        <v>7.191245186592461</v>
+        <v>7.191245644899695</v>
       </c>
       <c r="F924" t="n">
         <v>18988900</v>
@@ -18912,16 +18912,16 @@
         <v>45601</v>
       </c>
       <c r="B925" t="n">
-        <v>7.443228721618652</v>
+        <v>7.443229198455811</v>
       </c>
       <c r="C925" t="n">
-        <v>7.569220988187449</v>
+        <v>7.569221473096077</v>
       </c>
       <c r="D925" t="n">
-        <v>7.191244650617532</v>
+        <v>7.191245111311781</v>
       </c>
       <c r="E925" t="n">
-        <v>7.472304037802402</v>
+        <v>7.472304516502219</v>
       </c>
       <c r="F925" t="n">
         <v>13215900</v>
@@ -19132,16 +19132,16 @@
         <v>45618</v>
       </c>
       <c r="B936" t="n">
-        <v>6.97802734375</v>
+        <v>6.978026866912842</v>
       </c>
       <c r="C936" t="n">
-        <v>7.045869444425019</v>
+        <v>7.045868962951932</v>
       </c>
       <c r="D936" t="n">
-        <v>6.726043256639149</v>
+        <v>6.726042797021093</v>
       </c>
       <c r="E936" t="n">
-        <v>6.774501503861446</v>
+        <v>6.774501040932041</v>
       </c>
       <c r="F936" t="n">
         <v>20807700</v>
@@ -19172,16 +19172,16 @@
         <v>45622</v>
       </c>
       <c r="B938" t="n">
-        <v>7.646754741668701</v>
+        <v>7.646755218505859</v>
       </c>
       <c r="C938" t="n">
-        <v>7.724288303935401</v>
+        <v>7.724288785607405</v>
       </c>
       <c r="D938" t="n">
-        <v>7.239703077632047</v>
+        <v>7.239703529086233</v>
       </c>
       <c r="E938" t="n">
-        <v>7.239703077632047</v>
+        <v>7.239703529086233</v>
       </c>
       <c r="F938" t="n">
         <v>34068500</v>
@@ -19192,16 +19192,16 @@
         <v>45623</v>
       </c>
       <c r="B939" t="n">
-        <v>7.181553363800049</v>
+        <v>7.181552886962891</v>
       </c>
       <c r="C939" t="n">
-        <v>7.801822825752589</v>
+        <v>7.801822307731091</v>
       </c>
       <c r="D939" t="n">
-        <v>7.133095115362094</v>
+        <v>7.133094641742442</v>
       </c>
       <c r="E939" t="n">
-        <v>7.675830547968181</v>
+        <v>7.675830038312255</v>
       </c>
       <c r="F939" t="n">
         <v>36141700</v>
@@ -19332,16 +19332,16 @@
         <v>45632</v>
       </c>
       <c r="B946" t="n">
-        <v>5.970089912414551</v>
+        <v>5.970090389251709</v>
       </c>
       <c r="C946" t="n">
-        <v>6.464367071050471</v>
+        <v>6.464367587366049</v>
       </c>
       <c r="D946" t="n">
-        <v>5.970089912414551</v>
+        <v>5.970090389251709</v>
       </c>
       <c r="E946" t="n">
-        <v>6.318991408973054</v>
+        <v>6.31899191367733</v>
       </c>
       <c r="F946" t="n">
         <v>18084600</v>
@@ -19472,16 +19472,16 @@
         <v>45643</v>
       </c>
       <c r="B953" t="n">
-        <v>5.340129375457764</v>
+        <v>5.340129852294922</v>
       </c>
       <c r="C953" t="n">
-        <v>5.398279546719705</v>
+        <v>5.398280028749276</v>
       </c>
       <c r="D953" t="n">
-        <v>5.146295009114813</v>
+        <v>5.146295468643883</v>
       </c>
       <c r="E953" t="n">
-        <v>5.243211961218048</v>
+        <v>5.243212429401142</v>
       </c>
       <c r="F953" t="n">
         <v>32812100</v>
@@ -19532,16 +19532,16 @@
         <v>45646</v>
       </c>
       <c r="B956" t="n">
-        <v>5.592113971710205</v>
+        <v>5.592113494873047</v>
       </c>
       <c r="C956" t="n">
-        <v>5.659956075568729</v>
+        <v>5.659955592946704</v>
       </c>
       <c r="D956" t="n">
-        <v>5.165678880606319</v>
+        <v>5.165678440131098</v>
       </c>
       <c r="E956" t="n">
-        <v>5.223829057283687</v>
+        <v>5.223828611850025</v>
       </c>
       <c r="F956" t="n">
         <v>45865200</v>
@@ -19652,16 +19652,16 @@
         <v>45660</v>
       </c>
       <c r="B962" t="n">
-        <v>5.252904415130615</v>
+        <v>5.252903938293457</v>
       </c>
       <c r="C962" t="n">
-        <v>5.340129911853232</v>
+        <v>5.3401294270981</v>
       </c>
       <c r="D962" t="n">
-        <v>5.165678918407998</v>
+        <v>5.165678449488814</v>
       </c>
       <c r="E962" t="n">
-        <v>5.301362664981436</v>
+        <v>5.301362183745437</v>
       </c>
       <c r="F962" t="n">
         <v>13594200</v>
@@ -19692,16 +19692,16 @@
         <v>45664</v>
       </c>
       <c r="B964" t="n">
-        <v>5.714285373687744</v>
+        <v>5.714285850524902</v>
       </c>
       <c r="C964" t="n">
-        <v>5.793103025221601</v>
+        <v>5.793103508635817</v>
       </c>
       <c r="D964" t="n">
-        <v>5.566502042166633</v>
+        <v>5.566502506671788</v>
       </c>
       <c r="E964" t="n">
-        <v>5.704432932350882</v>
+        <v>5.704433408365889</v>
       </c>
       <c r="F964" t="n">
         <v>22063000</v>
@@ -19752,16 +19752,16 @@
         <v>45667</v>
       </c>
       <c r="B967" t="n">
-        <v>5.536945819854736</v>
+        <v>5.536945343017578</v>
       </c>
       <c r="C967" t="n">
-        <v>5.605911507712756</v>
+        <v>5.60591102493633</v>
       </c>
       <c r="D967" t="n">
-        <v>5.399014913929011</v>
+        <v>5.399014448970347</v>
       </c>
       <c r="E967" t="n">
-        <v>5.536945819854736</v>
+        <v>5.536945343017578</v>
       </c>
       <c r="F967" t="n">
         <v>14811000</v>
@@ -19792,16 +19792,16 @@
         <v>45671</v>
       </c>
       <c r="B969" t="n">
-        <v>5.320196628570557</v>
+        <v>5.320197105407715</v>
       </c>
       <c r="C969" t="n">
-        <v>5.477831931115081</v>
+        <v>5.477832422080734</v>
       </c>
       <c r="D969" t="n">
-        <v>5.211822123176066</v>
+        <v>5.211822590299863</v>
       </c>
       <c r="E969" t="n">
-        <v>5.448275546783112</v>
+        <v>5.448276035099693</v>
       </c>
       <c r="F969" t="n">
         <v>30338700</v>
@@ -19812,16 +19812,16 @@
         <v>45672</v>
       </c>
       <c r="B970" t="n">
-        <v>5.655172348022461</v>
+        <v>5.655171871185303</v>
       </c>
       <c r="C970" t="n">
-        <v>5.714286063600189</v>
+        <v>5.714285581778635</v>
       </c>
       <c r="D970" t="n">
-        <v>5.408866922346424</v>
+        <v>5.408866466277436</v>
       </c>
       <c r="E970" t="n">
-        <v>5.418719364872818</v>
+        <v>5.418718907973084</v>
       </c>
       <c r="F970" t="n">
         <v>28010800</v>
@@ -19832,16 +19832,16 @@
         <v>45673</v>
       </c>
       <c r="B971" t="n">
-        <v>5.566502571105957</v>
+        <v>5.566502094268799</v>
       </c>
       <c r="C971" t="n">
-        <v>5.635467787856154</v>
+        <v>5.635467305111304</v>
       </c>
       <c r="D971" t="n">
-        <v>5.399014810786386</v>
+        <v>5.399014348296546</v>
       </c>
       <c r="E971" t="n">
-        <v>5.615763373100339</v>
+        <v>5.615762892043408</v>
       </c>
       <c r="F971" t="n">
         <v>13042600</v>
@@ -19892,16 +19892,16 @@
         <v>45678</v>
       </c>
       <c r="B974" t="n">
-        <v>6.029556274414062</v>
+        <v>6.029556751251221</v>
       </c>
       <c r="C974" t="n">
-        <v>6.197044027001723</v>
+        <v>6.197044517084364</v>
       </c>
       <c r="D974" t="n">
-        <v>5.911329791336991</v>
+        <v>5.911330258824409</v>
       </c>
       <c r="E974" t="n">
-        <v>5.970443032875527</v>
+        <v>5.970443505037815</v>
       </c>
       <c r="F974" t="n">
         <v>19059500</v>
@@ -19912,16 +19912,16 @@
         <v>45679</v>
       </c>
       <c r="B975" t="n">
-        <v>6.236453056335449</v>
+        <v>6.236452579498291</v>
       </c>
       <c r="C975" t="n">
-        <v>6.325123156405338</v>
+        <v>6.325122672788494</v>
       </c>
       <c r="D975" t="n">
-        <v>5.931034396949529</v>
+        <v>5.931033943464581</v>
       </c>
       <c r="E975" t="n">
-        <v>6.068965298332458</v>
+        <v>6.068964834301359</v>
       </c>
       <c r="F975" t="n">
         <v>18324700</v>
@@ -19932,16 +19932,16 @@
         <v>45680</v>
       </c>
       <c r="B976" t="n">
-        <v>6.108374118804932</v>
+        <v>6.108373641967773</v>
       </c>
       <c r="C976" t="n">
-        <v>6.315270705486772</v>
+        <v>6.315270212498674</v>
       </c>
       <c r="D976" t="n">
-        <v>6.02955646098143</v>
+        <v>6.029555990297004</v>
       </c>
       <c r="E976" t="n">
-        <v>6.256157462119146</v>
+        <v>6.256156973745597</v>
       </c>
       <c r="F976" t="n">
         <v>32962200</v>
@@ -19952,16 +19952,16 @@
         <v>45681</v>
       </c>
       <c r="B977" t="n">
-        <v>6.059113025665283</v>
+        <v>6.059113502502441</v>
       </c>
       <c r="C977" t="n">
-        <v>6.364531669913091</v>
+        <v>6.364532170785939</v>
       </c>
       <c r="D977" t="n">
-        <v>6.03940861215866</v>
+        <v>6.039409087445129</v>
       </c>
       <c r="E977" t="n">
-        <v>6.108373824536706</v>
+        <v>6.108374305250566</v>
       </c>
       <c r="F977" t="n">
         <v>10904000</v>
@@ -20032,16 +20032,16 @@
         <v>45687</v>
       </c>
       <c r="B981" t="n">
-        <v>6.738915920257568</v>
+        <v>6.738916397094727</v>
       </c>
       <c r="C981" t="n">
-        <v>6.817733573394338</v>
+        <v>6.817734055808534</v>
       </c>
       <c r="D981" t="n">
-        <v>6.403940424636028</v>
+        <v>6.403940877770744</v>
       </c>
       <c r="E981" t="n">
-        <v>6.403940424636028</v>
+        <v>6.403940877770744</v>
       </c>
       <c r="F981" t="n">
         <v>22177900</v>
@@ -20112,16 +20112,16 @@
         <v>45693</v>
       </c>
       <c r="B985" t="n">
-        <v>6.738915920257568</v>
+        <v>6.738916397094727</v>
       </c>
       <c r="C985" t="n">
-        <v>6.827585545141299</v>
+        <v>6.827586028252608</v>
       </c>
       <c r="D985" t="n">
-        <v>6.532019345878414</v>
+        <v>6.532019808075832</v>
       </c>
       <c r="E985" t="n">
-        <v>6.650245825583568</v>
+        <v>6.650246296146542</v>
       </c>
       <c r="F985" t="n">
         <v>12476200</v>
@@ -20152,16 +20152,16 @@
         <v>45695</v>
       </c>
       <c r="B987" t="n">
-        <v>6.955665111541748</v>
+        <v>6.95566463470459</v>
       </c>
       <c r="C987" t="n">
-        <v>7.00492638421649</v>
+        <v>7.004925904002285</v>
       </c>
       <c r="D987" t="n">
-        <v>6.827586178419671</v>
+        <v>6.827585710362809</v>
       </c>
       <c r="E987" t="n">
-        <v>6.876847451094413</v>
+        <v>6.876846979660503</v>
       </c>
       <c r="F987" t="n">
         <v>23962500</v>
@@ -20172,16 +20172,16 @@
         <v>45698</v>
       </c>
       <c r="B988" t="n">
-        <v>6.896551609039307</v>
+        <v>6.896551132202148</v>
       </c>
       <c r="C988" t="n">
-        <v>7.182265852401997</v>
+        <v>7.182265355810159</v>
       </c>
       <c r="D988" t="n">
-        <v>6.876847194662234</v>
+        <v>6.876846719187467</v>
       </c>
       <c r="E988" t="n">
-        <v>7.024630537385422</v>
+        <v>7.024630051692709</v>
       </c>
       <c r="F988" t="n">
         <v>17122200</v>
@@ -20192,16 +20192,16 @@
         <v>45699</v>
       </c>
       <c r="B989" t="n">
-        <v>7.024630069732666</v>
+        <v>7.024630546569824</v>
       </c>
       <c r="C989" t="n">
-        <v>7.428570772466125</v>
+        <v>7.428571276723081</v>
       </c>
       <c r="D989" t="n">
-        <v>6.866994295420128</v>
+        <v>6.866994761556851</v>
       </c>
       <c r="E989" t="n">
-        <v>6.896551149913186</v>
+        <v>6.896551618056251</v>
       </c>
       <c r="F989" t="n">
         <v>37544600</v>
@@ -20212,16 +20212,16 @@
         <v>45700</v>
       </c>
       <c r="B990" t="n">
-        <v>7.024630069732666</v>
+        <v>7.024630546569824</v>
       </c>
       <c r="C990" t="n">
-        <v>7.113299693631313</v>
+        <v>7.113300176487432</v>
       </c>
       <c r="D990" t="n">
-        <v>6.896551149913186</v>
+        <v>6.896551618056251</v>
       </c>
       <c r="E990" t="n">
-        <v>6.965516830536814</v>
+        <v>6.96551730336132</v>
       </c>
       <c r="F990" t="n">
         <v>32300000</v>
@@ -20252,16 +20252,16 @@
         <v>45702</v>
       </c>
       <c r="B992" t="n">
-        <v>7.369457721710205</v>
+        <v>7.369458198547363</v>
       </c>
       <c r="C992" t="n">
-        <v>7.418718990528178</v>
+        <v>7.418719470552762</v>
       </c>
       <c r="D992" t="n">
-        <v>7.241378798615696</v>
+        <v>7.241379267165571</v>
       </c>
       <c r="E992" t="n">
-        <v>7.29064006743367</v>
+        <v>7.29064053917097</v>
       </c>
       <c r="F992" t="n">
         <v>14556600</v>
@@ -20272,16 +20272,16 @@
         <v>45705</v>
       </c>
       <c r="B993" t="n">
-        <v>7.665024757385254</v>
+        <v>7.665024280548096</v>
       </c>
       <c r="C993" t="n">
-        <v>7.871920874746595</v>
+        <v>7.871920385038538</v>
       </c>
       <c r="D993" t="n">
-        <v>7.349753655585064</v>
+        <v>7.349753198360755</v>
       </c>
       <c r="E993" t="n">
-        <v>7.408866899086918</v>
+        <v>7.408866438185206</v>
       </c>
       <c r="F993" t="n">
         <v>15107600</v>
@@ -20392,16 +20392,16 @@
         <v>45713</v>
       </c>
       <c r="B999" t="n">
-        <v>7.014778137207031</v>
+        <v>7.014777660369873</v>
       </c>
       <c r="C999" t="n">
-        <v>7.073891380691381</v>
+        <v>7.073890899835936</v>
       </c>
       <c r="D999" t="n">
-        <v>6.669950648653175</v>
+        <v>6.669950195256039</v>
       </c>
       <c r="E999" t="n">
-        <v>6.719211919785282</v>
+        <v>6.719211463039558</v>
       </c>
       <c r="F999" t="n">
         <v>14319100</v>
@@ -20752,16 +20752,16 @@
         <v>45741</v>
       </c>
       <c r="B1017" t="n">
-        <v>7.48768424987793</v>
+        <v>7.487684726715088</v>
       </c>
       <c r="C1017" t="n">
-        <v>7.921181820895899</v>
+        <v>7.921182325339423</v>
       </c>
       <c r="D1017" t="n">
-        <v>7.43842345054265</v>
+        <v>7.438423924242739</v>
       </c>
       <c r="E1017" t="n">
-        <v>7.448275422493594</v>
+        <v>7.448275896821086</v>
       </c>
       <c r="F1017" t="n">
         <v>12850900</v>
@@ -20892,16 +20892,16 @@
         <v>45750</v>
       </c>
       <c r="B1024" t="n">
-        <v>8.315269470214844</v>
+        <v>8.31527042388916</v>
       </c>
       <c r="C1024" t="n">
-        <v>8.453200825490862</v>
+        <v>8.45320179498446</v>
       </c>
       <c r="D1024" t="n">
-        <v>7.832511136119513</v>
+        <v>7.832512034426506</v>
       </c>
       <c r="E1024" t="n">
-        <v>7.881772401545269</v>
+        <v>7.881773305502012</v>
       </c>
       <c r="F1024" t="n">
         <v>17671400</v>
@@ -20932,16 +20932,16 @@
         <v>45754</v>
       </c>
       <c r="B1026" t="n">
-        <v>7.891625881195068</v>
+        <v>7.89162540435791</v>
       </c>
       <c r="C1026" t="n">
-        <v>8.088670029251373</v>
+        <v>8.08866954050818</v>
       </c>
       <c r="D1026" t="n">
-        <v>7.527093502605445</v>
+        <v>7.527093047794494</v>
       </c>
       <c r="E1026" t="n">
-        <v>7.655172433737196</v>
+        <v>7.655171971187308</v>
       </c>
       <c r="F1026" t="n">
         <v>17470600</v>
@@ -21172,16 +21172,16 @@
         <v>45772</v>
       </c>
       <c r="B1038" t="n">
-        <v>9.103446960449219</v>
+        <v>9.103447914123535</v>
       </c>
       <c r="C1038" t="n">
-        <v>9.251230757735641</v>
+        <v>9.251231726891742</v>
       </c>
       <c r="D1038" t="n">
-        <v>8.965516543811818</v>
+        <v>8.965517483036587</v>
       </c>
       <c r="E1038" t="n">
-        <v>9.044334193199045</v>
+        <v>9.044335140680726</v>
       </c>
       <c r="F1038" t="n">
         <v>7962500</v>
@@ -27515,16 +27515,36 @@
         <v>8.5</v>
       </c>
       <c r="C1355" t="n">
-        <v>8.51</v>
+        <v>8.510000228881836</v>
       </c>
       <c r="D1355" t="n">
-        <v>8.34</v>
+        <v>8.340000152587891</v>
       </c>
       <c r="E1355" t="n">
-        <v>8.51</v>
+        <v>8.510000228881836</v>
       </c>
       <c r="F1355" t="n">
         <v>3774300</v>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B1356" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="C1356" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="D1356" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="E1356" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="F1356" t="n">
+        <v>5991300</v>
       </c>
     </row>
   </sheetData>

--- a/database/ASAI3.xlsx
+++ b/database/ASAI3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1362"/>
+  <dimension ref="A1:F1361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -552,16 +552,16 @@
         <v>44263</v>
       </c>
       <c r="B7" t="n">
-        <v>13.48508644104004</v>
+        <v>13.48508548736572</v>
       </c>
       <c r="C7" t="n">
-        <v>14.2978757345337</v>
+        <v>14.29787472337838</v>
       </c>
       <c r="D7" t="n">
-        <v>13.05210579563423</v>
+        <v>13.05210487258059</v>
       </c>
       <c r="E7" t="n">
-        <v>14.21051986319279</v>
+        <v>14.21051885821534</v>
       </c>
       <c r="F7" t="n">
         <v>12366000</v>
@@ -572,16 +572,16 @@
         <v>44264</v>
       </c>
       <c r="B8" t="n">
-        <v>13.44520568847656</v>
+        <v>13.44520664215088</v>
       </c>
       <c r="C8" t="n">
-        <v>13.44520568847656</v>
+        <v>13.44520664215088</v>
       </c>
       <c r="D8" t="n">
-        <v>13.0103252694391</v>
+        <v>13.01032619226716</v>
       </c>
       <c r="E8" t="n">
-        <v>13.29138370087542</v>
+        <v>13.29138464363907</v>
       </c>
       <c r="F8" t="n">
         <v>10167000</v>
@@ -592,16 +592,16 @@
         <v>44265</v>
       </c>
       <c r="B9" t="n">
-        <v>13.48318672180176</v>
+        <v>13.48318767547607</v>
       </c>
       <c r="C9" t="n">
-        <v>13.95794682401684</v>
+        <v>13.95794781127124</v>
       </c>
       <c r="D9" t="n">
-        <v>13.23631125132199</v>
+        <v>13.23631218753465</v>
       </c>
       <c r="E9" t="n">
-        <v>13.4850856245696</v>
+        <v>13.48508657837822</v>
       </c>
       <c r="F9" t="n">
         <v>15699500</v>
@@ -652,16 +652,16 @@
         <v>44270</v>
       </c>
       <c r="B12" t="n">
-        <v>13.83451080322266</v>
+        <v>13.83450794219971</v>
       </c>
       <c r="C12" t="n">
-        <v>14.01681907452333</v>
+        <v>14.01681617579842</v>
       </c>
       <c r="D12" t="n">
-        <v>13.62181827280511</v>
+        <v>13.62181545576768</v>
       </c>
       <c r="E12" t="n">
-        <v>13.81931867366422</v>
+        <v>13.81931581578305</v>
       </c>
       <c r="F12" t="n">
         <v>11593000</v>
@@ -672,16 +672,16 @@
         <v>44271</v>
       </c>
       <c r="B13" t="n">
-        <v>13.58763408660889</v>
+        <v>13.5876350402832</v>
       </c>
       <c r="C13" t="n">
-        <v>13.91047018507921</v>
+        <v>13.9104711614124</v>
       </c>
       <c r="D13" t="n">
-        <v>13.49458060971476</v>
+        <v>13.49458155685794</v>
       </c>
       <c r="E13" t="n">
-        <v>13.84400406267841</v>
+        <v>13.84400503434655</v>
       </c>
       <c r="F13" t="n">
         <v>7789500</v>
@@ -732,16 +732,16 @@
         <v>44274</v>
       </c>
       <c r="B16" t="n">
-        <v>13.54775333404541</v>
+        <v>13.54775524139404</v>
       </c>
       <c r="C16" t="n">
-        <v>14.03580663921036</v>
+        <v>14.03580861527059</v>
       </c>
       <c r="D16" t="n">
-        <v>13.46419618282161</v>
+        <v>13.46419807840647</v>
       </c>
       <c r="E16" t="n">
-        <v>13.95414839066896</v>
+        <v>13.95415035523277</v>
       </c>
       <c r="F16" t="n">
         <v>14098000</v>
@@ -812,16 +812,16 @@
         <v>44280</v>
       </c>
       <c r="B20" t="n">
-        <v>13.64840221405029</v>
+        <v>13.64840316772461</v>
       </c>
       <c r="C20" t="n">
-        <v>13.67308975961416</v>
+        <v>13.67309071501351</v>
       </c>
       <c r="D20" t="n">
-        <v>12.83941172946964</v>
+        <v>12.83941262661621</v>
       </c>
       <c r="E20" t="n">
-        <v>12.91347436616125</v>
+        <v>12.9134752684829</v>
       </c>
       <c r="F20" t="n">
         <v>6602000</v>
@@ -832,16 +832,16 @@
         <v>44281</v>
       </c>
       <c r="B21" t="n">
-        <v>13.80602359771729</v>
+        <v>13.8060245513916</v>
       </c>
       <c r="C21" t="n">
-        <v>14.12696170612194</v>
+        <v>14.1269626819656</v>
       </c>
       <c r="D21" t="n">
-        <v>13.48888420034324</v>
+        <v>13.48888513211062</v>
       </c>
       <c r="E21" t="n">
-        <v>13.54965361596974</v>
+        <v>13.54965455193487</v>
       </c>
       <c r="F21" t="n">
         <v>4396500</v>
@@ -852,16 +852,16 @@
         <v>44284</v>
       </c>
       <c r="B22" t="n">
-        <v>13.95794677734375</v>
+        <v>13.95794773101807</v>
       </c>
       <c r="C22" t="n">
-        <v>13.95794677734375</v>
+        <v>13.95794773101807</v>
       </c>
       <c r="D22" t="n">
-        <v>13.4869853877722</v>
+        <v>13.48698630926816</v>
       </c>
       <c r="E22" t="n">
-        <v>13.7148700187455</v>
+        <v>13.71487095581164</v>
       </c>
       <c r="F22" t="n">
         <v>6557000</v>
@@ -872,16 +872,16 @@
         <v>44285</v>
       </c>
       <c r="B23" t="n">
-        <v>13.95794677734375</v>
+        <v>13.95794773101807</v>
       </c>
       <c r="C23" t="n">
-        <v>14.08138451217088</v>
+        <v>14.08138547427906</v>
       </c>
       <c r="D23" t="n">
-        <v>13.76804291819933</v>
+        <v>13.7680438588985</v>
       </c>
       <c r="E23" t="n">
-        <v>13.76804291819933</v>
+        <v>13.7680438588985</v>
       </c>
       <c r="F23" t="n">
         <v>8433000</v>
@@ -912,16 +912,16 @@
         <v>44287</v>
       </c>
       <c r="B25" t="n">
-        <v>14.2541971206665</v>
+        <v>14.25419807434082</v>
       </c>
       <c r="C25" t="n">
-        <v>14.40232240017016</v>
+        <v>14.40232336375477</v>
       </c>
       <c r="D25" t="n">
-        <v>14.02631249321458</v>
+        <v>14.02631343164232</v>
       </c>
       <c r="E25" t="n">
-        <v>14.09087971377266</v>
+        <v>14.09088065652025</v>
       </c>
       <c r="F25" t="n">
         <v>9940000</v>
@@ -932,16 +932,16 @@
         <v>44291</v>
       </c>
       <c r="B26" t="n">
-        <v>14.71756362915039</v>
+        <v>14.71756267547607</v>
       </c>
       <c r="C26" t="n">
-        <v>14.88657865823869</v>
+        <v>14.88657769361247</v>
       </c>
       <c r="D26" t="n">
-        <v>14.29977512456389</v>
+        <v>14.2997741979616</v>
       </c>
       <c r="E26" t="n">
-        <v>14.29977512456389</v>
+        <v>14.2997741979616</v>
       </c>
       <c r="F26" t="n">
         <v>6073500</v>
@@ -952,16 +952,16 @@
         <v>44292</v>
       </c>
       <c r="B27" t="n">
-        <v>14.58652877807617</v>
+        <v>14.58652973175049</v>
       </c>
       <c r="C27" t="n">
-        <v>14.72135992027025</v>
+        <v>14.72136088275989</v>
       </c>
       <c r="D27" t="n">
-        <v>14.52765826882265</v>
+        <v>14.52765921864798</v>
       </c>
       <c r="E27" t="n">
-        <v>14.71756211500646</v>
+        <v>14.7175630772478</v>
       </c>
       <c r="F27" t="n">
         <v>5821500</v>
@@ -992,16 +992,16 @@
         <v>44294</v>
       </c>
       <c r="B29" t="n">
-        <v>14.70237064361572</v>
+        <v>14.70237255096436</v>
       </c>
       <c r="C29" t="n">
-        <v>14.74035141454506</v>
+        <v>14.74035332682097</v>
       </c>
       <c r="D29" t="n">
-        <v>14.26559132516181</v>
+        <v>14.26559317584676</v>
       </c>
       <c r="E29" t="n">
-        <v>14.4327065361443</v>
+        <v>14.43270840850923</v>
       </c>
       <c r="F29" t="n">
         <v>6395000</v>
@@ -1012,16 +1012,16 @@
         <v>44295</v>
       </c>
       <c r="B30" t="n">
-        <v>14.71756362915039</v>
+        <v>14.71756267547607</v>
       </c>
       <c r="C30" t="n">
-        <v>14.73655446848903</v>
+        <v>14.73655351358414</v>
       </c>
       <c r="D30" t="n">
-        <v>14.40801982998176</v>
+        <v>14.40801889636538</v>
       </c>
       <c r="E30" t="n">
-        <v>14.63210666319261</v>
+        <v>14.63210571505577</v>
       </c>
       <c r="F30" t="n">
         <v>7012500</v>
@@ -1072,16 +1072,16 @@
         <v>44300</v>
       </c>
       <c r="B33" t="n">
-        <v>14.93785095214844</v>
+        <v>14.93785381317139</v>
       </c>
       <c r="C33" t="n">
-        <v>14.94544656259071</v>
+        <v>14.94544942506844</v>
       </c>
       <c r="D33" t="n">
-        <v>14.62260957493718</v>
+        <v>14.62261237558245</v>
       </c>
       <c r="E33" t="n">
-        <v>14.65109583069458</v>
+        <v>14.65109863679578</v>
       </c>
       <c r="F33" t="n">
         <v>5841000</v>
@@ -1092,16 +1092,16 @@
         <v>44301</v>
       </c>
       <c r="B34" t="n">
-        <v>15.18662643432617</v>
+        <v>15.18662738800049</v>
       </c>
       <c r="C34" t="n">
-        <v>15.2037165590924</v>
+        <v>15.20371751383992</v>
       </c>
       <c r="D34" t="n">
-        <v>14.84100077857334</v>
+        <v>14.84100171054341</v>
       </c>
       <c r="E34" t="n">
-        <v>14.84100077857334</v>
+        <v>14.84100171054341</v>
       </c>
       <c r="F34" t="n">
         <v>11554500</v>
@@ -1132,16 +1132,16 @@
         <v>44305</v>
       </c>
       <c r="B36" t="n">
-        <v>15.28727436065674</v>
+        <v>15.28727531433105</v>
       </c>
       <c r="C36" t="n">
-        <v>15.50756336269031</v>
+        <v>15.50756433010704</v>
       </c>
       <c r="D36" t="n">
-        <v>15.00431704491931</v>
+        <v>15.00431798094175</v>
       </c>
       <c r="E36" t="n">
-        <v>15.14484579871793</v>
+        <v>15.14484674350704</v>
       </c>
       <c r="F36" t="n">
         <v>5017000</v>
@@ -1152,16 +1152,16 @@
         <v>44306</v>
       </c>
       <c r="B37" t="n">
-        <v>15.47718048095703</v>
+        <v>15.47718143463135</v>
       </c>
       <c r="C37" t="n">
-        <v>15.65569185126732</v>
+        <v>15.65569281594117</v>
       </c>
       <c r="D37" t="n">
-        <v>15.06698845640197</v>
+        <v>15.06698938480104</v>
       </c>
       <c r="E37" t="n">
-        <v>15.35944125083699</v>
+        <v>15.35944219725644</v>
       </c>
       <c r="F37" t="n">
         <v>6029000</v>
@@ -1172,16 +1172,16 @@
         <v>44308</v>
       </c>
       <c r="B38" t="n">
-        <v>15.27967834472656</v>
+        <v>15.27967929840088</v>
       </c>
       <c r="C38" t="n">
-        <v>15.75254045321392</v>
+        <v>15.75254143640172</v>
       </c>
       <c r="D38" t="n">
-        <v>15.19422319187483</v>
+        <v>15.1942241402155</v>
       </c>
       <c r="E38" t="n">
-        <v>15.50376517258819</v>
+        <v>15.50376614024878</v>
       </c>
       <c r="F38" t="n">
         <v>8470500</v>
@@ -1192,16 +1192,16 @@
         <v>44309</v>
       </c>
       <c r="B39" t="n">
-        <v>15.41261386871338</v>
+        <v>15.41261196136475</v>
       </c>
       <c r="C39" t="n">
-        <v>15.53795051954675</v>
+        <v>15.53794859668741</v>
       </c>
       <c r="D39" t="n">
-        <v>15.21891127804373</v>
+        <v>15.21890939466627</v>
       </c>
       <c r="E39" t="n">
-        <v>15.45819116193756</v>
+        <v>15.45818924894863</v>
       </c>
       <c r="F39" t="n">
         <v>4653000</v>
@@ -1212,16 +1212,16 @@
         <v>44312</v>
       </c>
       <c r="B40" t="n">
-        <v>15.2606897354126</v>
+        <v>15.26068878173828</v>
       </c>
       <c r="C40" t="n">
-        <v>15.51705882313055</v>
+        <v>15.51705785343516</v>
       </c>
       <c r="D40" t="n">
-        <v>15.16573734944818</v>
+        <v>15.16573640170765</v>
       </c>
       <c r="E40" t="n">
-        <v>15.48477656941952</v>
+        <v>15.48477560174152</v>
       </c>
       <c r="F40" t="n">
         <v>3662000</v>
@@ -1252,16 +1252,16 @@
         <v>44314</v>
       </c>
       <c r="B42" t="n">
-        <v>15.18852519989014</v>
+        <v>15.18852615356445</v>
       </c>
       <c r="C42" t="n">
-        <v>15.35564131800169</v>
+        <v>15.35564228216909</v>
       </c>
       <c r="D42" t="n">
-        <v>15.04799553112973</v>
+        <v>15.04799647598031</v>
       </c>
       <c r="E42" t="n">
-        <v>15.14864552586341</v>
+        <v>15.14864647703371</v>
       </c>
       <c r="F42" t="n">
         <v>5371500</v>
@@ -1312,16 +1312,16 @@
         <v>44319</v>
       </c>
       <c r="B45" t="n">
-        <v>15.53295993804932</v>
+        <v>15.53295803070068</v>
       </c>
       <c r="C45" t="n">
-        <v>15.67023330010677</v>
+        <v>15.67023137590184</v>
       </c>
       <c r="D45" t="n">
-        <v>15.29463663895672</v>
+        <v>15.29463476087267</v>
       </c>
       <c r="E45" t="n">
-        <v>15.4433505085054</v>
+        <v>15.44334861216023</v>
       </c>
       <c r="F45" t="n">
         <v>8474000</v>
@@ -1332,16 +1332,16 @@
         <v>44320</v>
       </c>
       <c r="B46" t="n">
-        <v>15.72933864593506</v>
+        <v>15.72933769226074</v>
       </c>
       <c r="C46" t="n">
-        <v>15.74840494734345</v>
+        <v>15.74840399251314</v>
       </c>
       <c r="D46" t="n">
-        <v>15.35946039896755</v>
+        <v>15.35945946771906</v>
       </c>
       <c r="E46" t="n">
-        <v>15.63400895715566</v>
+        <v>15.63400800926121</v>
       </c>
       <c r="F46" t="n">
         <v>9407500</v>
@@ -1352,16 +1352,16 @@
         <v>44321</v>
       </c>
       <c r="B47" t="n">
-        <v>16.32228469848633</v>
+        <v>16.32228660583496</v>
       </c>
       <c r="C47" t="n">
-        <v>16.58730007183393</v>
+        <v>16.58730201015107</v>
       </c>
       <c r="D47" t="n">
-        <v>16.01532383109572</v>
+        <v>16.01532570257429</v>
       </c>
       <c r="E47" t="n">
-        <v>16.08396141636727</v>
+        <v>16.08396329586652</v>
       </c>
       <c r="F47" t="n">
         <v>17262500</v>
@@ -1412,16 +1412,16 @@
         <v>44326</v>
       </c>
       <c r="B50" t="n">
-        <v>16.81418418884277</v>
+        <v>16.81418609619141</v>
       </c>
       <c r="C50" t="n">
-        <v>17.01628222452739</v>
+        <v>17.0162841548014</v>
       </c>
       <c r="D50" t="n">
-        <v>16.55298171903851</v>
+        <v>16.55298359675715</v>
       </c>
       <c r="E50" t="n">
-        <v>16.97052383564365</v>
+        <v>16.97052576072697</v>
       </c>
       <c r="F50" t="n">
         <v>7669500</v>
@@ -1452,16 +1452,16 @@
         <v>44328</v>
       </c>
       <c r="B52" t="n">
-        <v>16.12590408325195</v>
+        <v>16.12590599060059</v>
       </c>
       <c r="C52" t="n">
-        <v>16.57776401598027</v>
+        <v>16.57776597677424</v>
       </c>
       <c r="D52" t="n">
-        <v>16.04201310987353</v>
+        <v>16.04201500729966</v>
       </c>
       <c r="E52" t="n">
-        <v>16.49006196539431</v>
+        <v>16.49006391581501</v>
       </c>
       <c r="F52" t="n">
         <v>6728500</v>
@@ -1472,16 +1472,16 @@
         <v>44329</v>
       </c>
       <c r="B53" t="n">
-        <v>16.43286895751953</v>
+        <v>16.43287086486816</v>
       </c>
       <c r="C53" t="n">
-        <v>16.51866367244025</v>
+        <v>16.518665589747</v>
       </c>
       <c r="D53" t="n">
-        <v>16.12781360716679</v>
+        <v>16.12781547910792</v>
       </c>
       <c r="E53" t="n">
-        <v>16.17547935796994</v>
+        <v>16.17548123544359</v>
       </c>
       <c r="F53" t="n">
         <v>6595000</v>
@@ -1492,16 +1492,16 @@
         <v>44330</v>
       </c>
       <c r="B54" t="n">
-        <v>16.52628898620605</v>
+        <v>16.52629089355469</v>
       </c>
       <c r="C54" t="n">
-        <v>16.66356232925931</v>
+        <v>16.66356425245107</v>
       </c>
       <c r="D54" t="n">
-        <v>16.13734451407442</v>
+        <v>16.13734637653381</v>
       </c>
       <c r="E54" t="n">
-        <v>16.54726082268666</v>
+        <v>16.54726273245572</v>
       </c>
       <c r="F54" t="n">
         <v>5923000</v>
@@ -1532,16 +1532,16 @@
         <v>44334</v>
       </c>
       <c r="B56" t="n">
-        <v>16.06108474731445</v>
+        <v>16.06108283996582</v>
       </c>
       <c r="C56" t="n">
-        <v>16.39092486167181</v>
+        <v>16.39092291515271</v>
       </c>
       <c r="D56" t="n">
-        <v>15.88758612704159</v>
+        <v>15.88758424029694</v>
       </c>
       <c r="E56" t="n">
-        <v>16.34897936103174</v>
+        <v>16.34897741949393</v>
       </c>
       <c r="F56" t="n">
         <v>6527500</v>
@@ -1552,16 +1552,16 @@
         <v>44335</v>
       </c>
       <c r="B57" t="n">
-        <v>15.82848262786865</v>
+        <v>15.82848072052002</v>
       </c>
       <c r="C57" t="n">
-        <v>16.36804664114567</v>
+        <v>16.36804466877901</v>
       </c>
       <c r="D57" t="n">
-        <v>15.67595583966943</v>
+        <v>15.67595395070043</v>
       </c>
       <c r="E57" t="n">
-        <v>15.98482231303345</v>
+        <v>15.98482038684572</v>
       </c>
       <c r="F57" t="n">
         <v>6358000</v>
@@ -1592,16 +1592,16 @@
         <v>44337</v>
       </c>
       <c r="B59" t="n">
-        <v>16.43477439880371</v>
+        <v>16.43477249145508</v>
       </c>
       <c r="C59" t="n">
-        <v>16.6254337643569</v>
+        <v>16.62543183488117</v>
       </c>
       <c r="D59" t="n">
-        <v>15.75984264485187</v>
+        <v>15.75984081583289</v>
       </c>
       <c r="E59" t="n">
-        <v>16.03439118575198</v>
+        <v>16.03438932487009</v>
       </c>
       <c r="F59" t="n">
         <v>10145000</v>
@@ -1652,16 +1652,16 @@
         <v>44342</v>
       </c>
       <c r="B62" t="n">
-        <v>16.94192695617676</v>
+        <v>16.94192504882812</v>
       </c>
       <c r="C62" t="n">
-        <v>17.11161449219801</v>
+        <v>17.11161256574568</v>
       </c>
       <c r="D62" t="n">
-        <v>16.65975260630318</v>
+        <v>16.65975073072218</v>
       </c>
       <c r="E62" t="n">
-        <v>17.02391059716581</v>
+        <v>17.02390868058733</v>
       </c>
       <c r="F62" t="n">
         <v>5462000</v>
@@ -1752,16 +1752,16 @@
         <v>44349</v>
       </c>
       <c r="B67" t="n">
-        <v>16.76651763916016</v>
+        <v>16.76651954650879</v>
       </c>
       <c r="C67" t="n">
-        <v>17.26032492574389</v>
+        <v>17.26032688926774</v>
       </c>
       <c r="D67" t="n">
-        <v>16.73982554996776</v>
+        <v>16.73982745427992</v>
       </c>
       <c r="E67" t="n">
-        <v>17.06394533438589</v>
+        <v>17.06394727556971</v>
       </c>
       <c r="F67" t="n">
         <v>9352500</v>
@@ -1772,16 +1772,16 @@
         <v>44351</v>
       </c>
       <c r="B68" t="n">
-        <v>16.77223968505859</v>
+        <v>16.77223777770996</v>
       </c>
       <c r="C68" t="n">
-        <v>16.81609071938215</v>
+        <v>16.81608880704675</v>
       </c>
       <c r="D68" t="n">
-        <v>16.40617437066384</v>
+        <v>16.40617250494436</v>
       </c>
       <c r="E68" t="n">
-        <v>16.72266839722167</v>
+        <v>16.72266649551031</v>
       </c>
       <c r="F68" t="n">
         <v>8097000</v>
@@ -1812,16 +1812,16 @@
         <v>44355</v>
       </c>
       <c r="B70" t="n">
-        <v>16.08205604553223</v>
+        <v>16.08205795288086</v>
       </c>
       <c r="C70" t="n">
-        <v>16.61017944054762</v>
+        <v>16.61018141053224</v>
       </c>
       <c r="D70" t="n">
-        <v>15.92952747058032</v>
+        <v>15.9295293598389</v>
       </c>
       <c r="E70" t="n">
-        <v>16.60064629097173</v>
+        <v>16.60064825982571</v>
       </c>
       <c r="F70" t="n">
         <v>9246000</v>
@@ -1832,16 +1832,16 @@
         <v>44356</v>
       </c>
       <c r="B71" t="n">
-        <v>16.16403961181641</v>
+        <v>16.16403770446777</v>
       </c>
       <c r="C71" t="n">
-        <v>16.39664448651429</v>
+        <v>16.39664255171839</v>
       </c>
       <c r="D71" t="n">
-        <v>15.82466817777308</v>
+        <v>15.82466631047011</v>
       </c>
       <c r="E71" t="n">
-        <v>16.08205778944601</v>
+        <v>16.08205589177119</v>
       </c>
       <c r="F71" t="n">
         <v>10294500</v>
@@ -1912,16 +1912,16 @@
         <v>44362</v>
       </c>
       <c r="B75" t="n">
-        <v>15.85898780822754</v>
+        <v>15.85898590087891</v>
       </c>
       <c r="C75" t="n">
-        <v>16.0267680045235</v>
+        <v>16.02676607699607</v>
       </c>
       <c r="D75" t="n">
-        <v>15.48720398490564</v>
+        <v>15.48720212227117</v>
       </c>
       <c r="E75" t="n">
-        <v>16.01532749522961</v>
+        <v>16.01532556907812</v>
       </c>
       <c r="F75" t="n">
         <v>8432500</v>
@@ -1932,16 +1932,16 @@
         <v>44363</v>
       </c>
       <c r="B76" t="n">
-        <v>15.89902400970459</v>
+        <v>15.89902210235596</v>
       </c>
       <c r="C76" t="n">
-        <v>16.11446811967458</v>
+        <v>16.1144661864799</v>
       </c>
       <c r="D76" t="n">
-        <v>15.66260805961109</v>
+        <v>15.66260618062443</v>
       </c>
       <c r="E76" t="n">
-        <v>15.70264620071735</v>
+        <v>15.70264431692745</v>
       </c>
       <c r="F76" t="n">
         <v>10606500</v>
@@ -1992,16 +1992,16 @@
         <v>44368</v>
       </c>
       <c r="B79" t="n">
-        <v>16.48434448242188</v>
+        <v>16.48434638977051</v>
       </c>
       <c r="C79" t="n">
-        <v>16.59302020374093</v>
+        <v>16.59302212366407</v>
       </c>
       <c r="D79" t="n">
-        <v>16.00007212945171</v>
+        <v>16.0000739807668</v>
       </c>
       <c r="E79" t="n">
-        <v>16.20789042268334</v>
+        <v>16.20789229804439</v>
       </c>
       <c r="F79" t="n">
         <v>6798000</v>
@@ -2012,16 +2012,16 @@
         <v>44369</v>
       </c>
       <c r="B80" t="n">
-        <v>16.47290420532227</v>
+        <v>16.4729061126709</v>
       </c>
       <c r="C80" t="n">
-        <v>16.49578339803871</v>
+        <v>16.49578530803645</v>
       </c>
       <c r="D80" t="n">
-        <v>16.13162548984007</v>
+        <v>16.13162735767305</v>
       </c>
       <c r="E80" t="n">
-        <v>16.46718395257762</v>
+        <v>16.46718585926392</v>
       </c>
       <c r="F80" t="n">
         <v>6518000</v>
@@ -2032,16 +2032,16 @@
         <v>44370</v>
       </c>
       <c r="B81" t="n">
-        <v>16.39664459228516</v>
+        <v>16.39664268493652</v>
       </c>
       <c r="C81" t="n">
-        <v>16.45574721722616</v>
+        <v>16.45574530300238</v>
       </c>
       <c r="D81" t="n">
-        <v>16.20979811200328</v>
+        <v>16.20979622638967</v>
       </c>
       <c r="E81" t="n">
-        <v>16.4004574889011</v>
+        <v>16.40045558110893</v>
       </c>
       <c r="F81" t="n">
         <v>5819500</v>
@@ -2052,16 +2052,16 @@
         <v>44371</v>
       </c>
       <c r="B82" t="n">
-        <v>16.64640235900879</v>
+        <v>16.64640426635742</v>
       </c>
       <c r="C82" t="n">
-        <v>16.72647862235864</v>
+        <v>16.72648053888243</v>
       </c>
       <c r="D82" t="n">
-        <v>16.39664042071346</v>
+        <v>16.39664229944431</v>
       </c>
       <c r="E82" t="n">
-        <v>16.46908907450944</v>
+        <v>16.46909096154148</v>
       </c>
       <c r="F82" t="n">
         <v>8527500</v>
@@ -2092,16 +2092,16 @@
         <v>44375</v>
       </c>
       <c r="B84" t="n">
-        <v>16.3737621307373</v>
+        <v>16.37376403808594</v>
       </c>
       <c r="C84" t="n">
-        <v>16.37948056539015</v>
+        <v>16.37948247340491</v>
       </c>
       <c r="D84" t="n">
-        <v>15.9390592744375</v>
+        <v>15.93906113114842</v>
       </c>
       <c r="E84" t="n">
-        <v>16.2250482827814</v>
+        <v>16.22505017280664</v>
       </c>
       <c r="F84" t="n">
         <v>6202500</v>
@@ -2112,16 +2112,16 @@
         <v>44376</v>
       </c>
       <c r="B85" t="n">
-        <v>16.42333602905273</v>
+        <v>16.42333793640137</v>
       </c>
       <c r="C85" t="n">
-        <v>16.53963755336238</v>
+        <v>16.53963947421787</v>
       </c>
       <c r="D85" t="n">
-        <v>16.120188031945</v>
+        <v>16.12018990408709</v>
       </c>
       <c r="E85" t="n">
-        <v>16.3680444846797</v>
+        <v>16.36804638560697</v>
       </c>
       <c r="F85" t="n">
         <v>8958000</v>
@@ -2132,16 +2132,16 @@
         <v>44377</v>
       </c>
       <c r="B86" t="n">
-        <v>16.49959945678711</v>
+        <v>16.49959754943848</v>
       </c>
       <c r="C86" t="n">
-        <v>16.49959945678711</v>
+        <v>16.49959754943848</v>
       </c>
       <c r="D86" t="n">
-        <v>16.19073120503556</v>
+        <v>16.19072933339201</v>
       </c>
       <c r="E86" t="n">
-        <v>16.38901636774828</v>
+        <v>16.38901447318302</v>
       </c>
       <c r="F86" t="n">
         <v>6685000</v>
@@ -2172,16 +2172,16 @@
         <v>44379</v>
       </c>
       <c r="B88" t="n">
-        <v>16.39664459228516</v>
+        <v>16.39664268493652</v>
       </c>
       <c r="C88" t="n">
-        <v>16.45765457466542</v>
+        <v>16.45765266021977</v>
       </c>
       <c r="D88" t="n">
-        <v>16.21551836605848</v>
+        <v>16.21551647977946</v>
       </c>
       <c r="E88" t="n">
-        <v>16.36804514027171</v>
+        <v>16.36804323624992</v>
       </c>
       <c r="F88" t="n">
         <v>5948000</v>
@@ -2192,16 +2192,16 @@
         <v>44382</v>
       </c>
       <c r="B89" t="n">
-        <v>16.41570663452148</v>
+        <v>16.41570854187012</v>
       </c>
       <c r="C89" t="n">
-        <v>16.54726154865489</v>
+        <v>16.54726347128895</v>
       </c>
       <c r="D89" t="n">
-        <v>16.25174119484036</v>
+        <v>16.25174308313778</v>
       </c>
       <c r="E89" t="n">
-        <v>16.40808084242347</v>
+        <v>16.40808274888606</v>
       </c>
       <c r="F89" t="n">
         <v>3871000</v>
@@ -2212,16 +2212,16 @@
         <v>44383</v>
       </c>
       <c r="B90" t="n">
-        <v>16.33944320678711</v>
+        <v>16.33944511413574</v>
       </c>
       <c r="C90" t="n">
-        <v>16.38901449179115</v>
+        <v>16.38901640492637</v>
       </c>
       <c r="D90" t="n">
-        <v>16.11256043736321</v>
+        <v>16.11256231822719</v>
       </c>
       <c r="E90" t="n">
-        <v>16.38901449179115</v>
+        <v>16.38901640492637</v>
       </c>
       <c r="F90" t="n">
         <v>3828000</v>
@@ -2252,16 +2252,16 @@
         <v>44385</v>
       </c>
       <c r="B92" t="n">
-        <v>16.43477439880371</v>
+        <v>16.43477249145508</v>
       </c>
       <c r="C92" t="n">
-        <v>16.79893236876558</v>
+        <v>16.79893041915436</v>
       </c>
       <c r="D92" t="n">
-        <v>16.24411685151298</v>
+        <v>16.24411496629124</v>
       </c>
       <c r="E92" t="n">
-        <v>16.26318133345833</v>
+        <v>16.26317944602405</v>
       </c>
       <c r="F92" t="n">
         <v>7435000</v>
@@ -2312,16 +2312,16 @@
         <v>44391</v>
       </c>
       <c r="B95" t="n">
-        <v>16.72266960144043</v>
+        <v>16.7226676940918</v>
       </c>
       <c r="C95" t="n">
-        <v>17.08873494219598</v>
+        <v>17.08873299309478</v>
       </c>
       <c r="D95" t="n">
-        <v>16.67309831003382</v>
+        <v>16.67309640833917</v>
       </c>
       <c r="E95" t="n">
-        <v>16.93048791752151</v>
+        <v>16.9304859864696</v>
       </c>
       <c r="F95" t="n">
         <v>5548000</v>
@@ -2332,16 +2332,16 @@
         <v>44392</v>
       </c>
       <c r="B96" t="n">
-        <v>16.45002555847168</v>
+        <v>16.45002746582031</v>
       </c>
       <c r="C96" t="n">
-        <v>16.86375476157448</v>
+        <v>16.86375671689422</v>
       </c>
       <c r="D96" t="n">
-        <v>16.44049240966831</v>
+        <v>16.44049431591159</v>
       </c>
       <c r="E96" t="n">
-        <v>16.72266670485169</v>
+        <v>16.72266864381253</v>
       </c>
       <c r="F96" t="n">
         <v>3746000</v>
@@ -2372,16 +2372,16 @@
         <v>44396</v>
       </c>
       <c r="B98" t="n">
-        <v>16.65402984619141</v>
+        <v>16.65403175354004</v>
       </c>
       <c r="C98" t="n">
-        <v>16.79702526617702</v>
+        <v>16.7970271899026</v>
       </c>
       <c r="D98" t="n">
-        <v>16.40426788246265</v>
+        <v>16.40426976120661</v>
       </c>
       <c r="E98" t="n">
-        <v>16.58539408105208</v>
+        <v>16.58539598054001</v>
       </c>
       <c r="F98" t="n">
         <v>7763500</v>
@@ -2392,16 +2392,16 @@
         <v>44397</v>
       </c>
       <c r="B99" t="n">
-        <v>16.51103401184082</v>
+        <v>16.51103782653809</v>
       </c>
       <c r="C99" t="n">
-        <v>16.71694491594005</v>
+        <v>16.71694877821082</v>
       </c>
       <c r="D99" t="n">
-        <v>16.45955719494704</v>
+        <v>16.45956099775114</v>
       </c>
       <c r="E99" t="n">
-        <v>16.65402759422851</v>
+        <v>16.6540314419629</v>
       </c>
       <c r="F99" t="n">
         <v>3835500</v>
@@ -2432,16 +2432,16 @@
         <v>44399</v>
       </c>
       <c r="B101" t="n">
-        <v>16.64449501037598</v>
+        <v>16.64449691772461</v>
       </c>
       <c r="C101" t="n">
-        <v>16.68072024642313</v>
+        <v>16.68072215792294</v>
       </c>
       <c r="D101" t="n">
-        <v>16.44430435190125</v>
+        <v>16.44430623630937</v>
       </c>
       <c r="E101" t="n">
-        <v>16.58729793913493</v>
+        <v>16.58729983992916</v>
       </c>
       <c r="F101" t="n">
         <v>2829500</v>
@@ -2472,16 +2472,16 @@
         <v>44403</v>
       </c>
       <c r="B103" t="n">
-        <v>17.19741058349609</v>
+        <v>17.19740867614746</v>
       </c>
       <c r="C103" t="n">
-        <v>17.21647506604089</v>
+        <v>17.21647315657783</v>
       </c>
       <c r="D103" t="n">
-        <v>16.56060959167434</v>
+        <v>16.5606077549527</v>
       </c>
       <c r="E103" t="n">
-        <v>16.75126896322247</v>
+        <v>16.75126710535498</v>
       </c>
       <c r="F103" t="n">
         <v>9987000</v>
@@ -2512,16 +2512,16 @@
         <v>44405</v>
       </c>
       <c r="B105" t="n">
-        <v>16.793212890625</v>
+        <v>16.79321479797363</v>
       </c>
       <c r="C105" t="n">
-        <v>17.38044259996134</v>
+        <v>17.38044457400667</v>
       </c>
       <c r="D105" t="n">
-        <v>16.42333646812846</v>
+        <v>16.42333833346707</v>
       </c>
       <c r="E105" t="n">
-        <v>17.34993760917749</v>
+        <v>17.3499395797581</v>
       </c>
       <c r="F105" t="n">
         <v>14614500</v>
@@ -2552,16 +2552,16 @@
         <v>44407</v>
       </c>
       <c r="B107" t="n">
-        <v>16.52628898620605</v>
+        <v>16.52629089355469</v>
       </c>
       <c r="C107" t="n">
-        <v>16.73219990991705</v>
+        <v>16.73220184103048</v>
       </c>
       <c r="D107" t="n">
-        <v>16.30893755658766</v>
+        <v>16.30893943885111</v>
       </c>
       <c r="E107" t="n">
-        <v>16.62543155217983</v>
+        <v>16.6254334709708</v>
       </c>
       <c r="F107" t="n">
         <v>16469000</v>
@@ -2592,16 +2592,16 @@
         <v>44411</v>
       </c>
       <c r="B109" t="n">
-        <v>16.53010368347168</v>
+        <v>16.53010177612305</v>
       </c>
       <c r="C109" t="n">
-        <v>16.68072308765598</v>
+        <v>16.68072116292792</v>
       </c>
       <c r="D109" t="n">
-        <v>16.26127540276083</v>
+        <v>16.26127352643131</v>
       </c>
       <c r="E109" t="n">
-        <v>16.68072308765598</v>
+        <v>16.68072116292792</v>
       </c>
       <c r="F109" t="n">
         <v>5450500</v>
@@ -2652,16 +2652,16 @@
         <v>44414</v>
       </c>
       <c r="B112" t="n">
-        <v>16.73982810974121</v>
+        <v>16.73982620239258</v>
       </c>
       <c r="C112" t="n">
-        <v>16.78368096434495</v>
+        <v>16.78367905199969</v>
       </c>
       <c r="D112" t="n">
-        <v>16.37567013584921</v>
+        <v>16.37566826999301</v>
       </c>
       <c r="E112" t="n">
-        <v>16.63115237929877</v>
+        <v>16.63115048433273</v>
       </c>
       <c r="F112" t="n">
         <v>15424500</v>
@@ -2672,16 +2672,16 @@
         <v>44417</v>
       </c>
       <c r="B113" t="n">
-        <v>17.31942749023438</v>
+        <v>17.31942939758301</v>
       </c>
       <c r="C113" t="n">
-        <v>17.35756008512363</v>
+        <v>17.35756199667172</v>
       </c>
       <c r="D113" t="n">
-        <v>16.61780374497947</v>
+        <v>16.6178055750599</v>
       </c>
       <c r="E113" t="n">
-        <v>16.61780374497947</v>
+        <v>16.6178055750599</v>
       </c>
       <c r="F113" t="n">
         <v>10558500</v>
@@ -2712,16 +2712,16 @@
         <v>44419</v>
       </c>
       <c r="B115" t="n">
-        <v>17.20884895324707</v>
+        <v>17.20884704589844</v>
       </c>
       <c r="C115" t="n">
-        <v>17.57872718168084</v>
+        <v>17.57872523333663</v>
       </c>
       <c r="D115" t="n">
-        <v>17.19741026393275</v>
+        <v>17.19740835785192</v>
       </c>
       <c r="E115" t="n">
-        <v>17.57872718168084</v>
+        <v>17.57872523333663</v>
       </c>
       <c r="F115" t="n">
         <v>6265000</v>
@@ -2732,16 +2732,16 @@
         <v>44420</v>
       </c>
       <c r="B116" t="n">
-        <v>16.92095184326172</v>
+        <v>16.92095375061035</v>
       </c>
       <c r="C116" t="n">
-        <v>17.24507162966405</v>
+        <v>17.24507357354782</v>
       </c>
       <c r="D116" t="n">
-        <v>16.68262857786367</v>
+        <v>16.68263045834824</v>
       </c>
       <c r="E116" t="n">
-        <v>16.98768206665122</v>
+        <v>16.98768398152176</v>
       </c>
       <c r="F116" t="n">
         <v>14059400</v>
@@ -2752,16 +2752,16 @@
         <v>44421</v>
       </c>
       <c r="B117" t="n">
-        <v>16.91141891479492</v>
+        <v>16.91142082214355</v>
       </c>
       <c r="C117" t="n">
-        <v>17.27367130114663</v>
+        <v>17.27367324935177</v>
       </c>
       <c r="D117" t="n">
-        <v>16.53010204884227</v>
+        <v>16.53010391318421</v>
       </c>
       <c r="E117" t="n">
-        <v>16.82562239267279</v>
+        <v>16.82562429034489</v>
       </c>
       <c r="F117" t="n">
         <v>5547600</v>
@@ -2832,16 +2832,16 @@
         <v>44427</v>
       </c>
       <c r="B121" t="n">
-        <v>16.6635627746582</v>
+        <v>16.66356658935547</v>
       </c>
       <c r="C121" t="n">
-        <v>16.87328841811889</v>
+        <v>16.87329228082749</v>
       </c>
       <c r="D121" t="n">
-        <v>15.57680923404292</v>
+        <v>15.57681279995571</v>
       </c>
       <c r="E121" t="n">
-        <v>15.71026968478171</v>
+        <v>15.71027328124686</v>
       </c>
       <c r="F121" t="n">
         <v>14455000</v>
@@ -2872,16 +2872,16 @@
         <v>44431</v>
       </c>
       <c r="B123" t="n">
-        <v>16.69216537475586</v>
+        <v>16.69216346740723</v>
       </c>
       <c r="C123" t="n">
-        <v>17.16881200972343</v>
+        <v>17.16881004791025</v>
       </c>
       <c r="D123" t="n">
-        <v>16.52057229524551</v>
+        <v>16.52057040750415</v>
       </c>
       <c r="E123" t="n">
-        <v>16.97815262843136</v>
+        <v>16.97815068840407</v>
       </c>
       <c r="F123" t="n">
         <v>5050600</v>
@@ -2892,16 +2892,16 @@
         <v>44432</v>
       </c>
       <c r="B124" t="n">
-        <v>16.91141891479492</v>
+        <v>16.91142082214355</v>
       </c>
       <c r="C124" t="n">
-        <v>17.05441251224439</v>
+        <v>17.05441443572051</v>
       </c>
       <c r="D124" t="n">
-        <v>16.66356249736014</v>
+        <v>16.66356437675437</v>
       </c>
       <c r="E124" t="n">
-        <v>16.78749161520865</v>
+        <v>16.78749350858018</v>
       </c>
       <c r="F124" t="n">
         <v>4198100</v>
@@ -3012,16 +3012,16 @@
         <v>44440</v>
       </c>
       <c r="B130" t="n">
-        <v>16.23458290100098</v>
+        <v>16.23458099365234</v>
       </c>
       <c r="C130" t="n">
-        <v>16.77795970229644</v>
+        <v>16.77795773110823</v>
       </c>
       <c r="D130" t="n">
-        <v>15.89139678723021</v>
+        <v>15.8913949202014</v>
       </c>
       <c r="E130" t="n">
-        <v>16.30131313017587</v>
+        <v>16.30131121498732</v>
       </c>
       <c r="F130" t="n">
         <v>7651500</v>
@@ -3032,16 +3032,16 @@
         <v>44441</v>
       </c>
       <c r="B131" t="n">
-        <v>16.72076225280762</v>
+        <v>16.72076416015625</v>
       </c>
       <c r="C131" t="n">
-        <v>17.03534891071645</v>
+        <v>17.03535085395019</v>
       </c>
       <c r="D131" t="n">
-        <v>16.10112026815059</v>
+        <v>16.10112210481625</v>
       </c>
       <c r="E131" t="n">
-        <v>16.16785049584908</v>
+        <v>16.1678523401267</v>
       </c>
       <c r="F131" t="n">
         <v>17566400</v>
@@ -3052,16 +3052,16 @@
         <v>44442</v>
       </c>
       <c r="B132" t="n">
-        <v>17.31180381774902</v>
+        <v>17.31180572509766</v>
       </c>
       <c r="C132" t="n">
-        <v>17.35946774893307</v>
+        <v>17.35946966153313</v>
       </c>
       <c r="D132" t="n">
-        <v>16.69216362104432</v>
+        <v>16.69216546012336</v>
       </c>
       <c r="E132" t="n">
-        <v>16.90188746382151</v>
+        <v>16.90188932600712</v>
       </c>
       <c r="F132" t="n">
         <v>19565300</v>
@@ -3092,16 +3092,16 @@
         <v>44447</v>
       </c>
       <c r="B134" t="n">
-        <v>17.0734806060791</v>
+        <v>17.07347869873047</v>
       </c>
       <c r="C134" t="n">
-        <v>17.55012719322427</v>
+        <v>17.55012523262749</v>
       </c>
       <c r="D134" t="n">
-        <v>16.84469046244091</v>
+        <v>16.84468858065136</v>
       </c>
       <c r="E134" t="n">
-        <v>17.49293011188033</v>
+        <v>17.49292815767328</v>
       </c>
       <c r="F134" t="n">
         <v>11069100</v>
@@ -3112,16 +3112,16 @@
         <v>44448</v>
       </c>
       <c r="B135" t="n">
-        <v>17.34993934631348</v>
+        <v>17.34993553161621</v>
       </c>
       <c r="C135" t="n">
-        <v>17.44526722477477</v>
+        <v>17.44526338911795</v>
       </c>
       <c r="D135" t="n">
-        <v>16.92095662018675</v>
+        <v>16.92095289980908</v>
       </c>
       <c r="E135" t="n">
-        <v>17.07348340764009</v>
+        <v>17.07347965372665</v>
       </c>
       <c r="F135" t="n">
         <v>12544000</v>
@@ -3152,16 +3152,16 @@
         <v>44452</v>
       </c>
       <c r="B137" t="n">
-        <v>17.79798316955566</v>
+        <v>17.79798126220703</v>
       </c>
       <c r="C137" t="n">
-        <v>17.9695762273458</v>
+        <v>17.96957430160813</v>
       </c>
       <c r="D137" t="n">
-        <v>17.49292965271203</v>
+        <v>17.49292777805493</v>
       </c>
       <c r="E137" t="n">
-        <v>17.5787261816071</v>
+        <v>17.57872429775548</v>
       </c>
       <c r="F137" t="n">
         <v>17075500</v>
@@ -3172,16 +3172,16 @@
         <v>44453</v>
       </c>
       <c r="B138" t="n">
-        <v>17.47386360168457</v>
+        <v>17.47386169433594</v>
       </c>
       <c r="C138" t="n">
-        <v>18.1507026927803</v>
+        <v>18.15070071155172</v>
       </c>
       <c r="D138" t="n">
-        <v>17.3976002213898</v>
+        <v>17.39759832236565</v>
       </c>
       <c r="E138" t="n">
-        <v>17.82658287196191</v>
+        <v>17.82658092611242</v>
       </c>
       <c r="F138" t="n">
         <v>6594500</v>
@@ -3272,16 +3272,16 @@
         <v>44460</v>
       </c>
       <c r="B143" t="n">
-        <v>18.57968139648438</v>
+        <v>18.57968330383301</v>
       </c>
       <c r="C143" t="n">
-        <v>18.74174128832697</v>
+        <v>18.7417432123123</v>
       </c>
       <c r="D143" t="n">
-        <v>17.82658082963624</v>
+        <v>17.82658265967325</v>
       </c>
       <c r="E143" t="n">
-        <v>18.06490409303639</v>
+        <v>18.06490594753913</v>
       </c>
       <c r="F143" t="n">
         <v>17756900</v>
@@ -3332,16 +3332,16 @@
         <v>44463</v>
       </c>
       <c r="B146" t="n">
-        <v>18.09350395202637</v>
+        <v>18.09350204467773</v>
       </c>
       <c r="C146" t="n">
-        <v>18.26509701375519</v>
+        <v>18.26509508831786</v>
       </c>
       <c r="D146" t="n">
-        <v>17.87424695904506</v>
+        <v>17.87424507480967</v>
       </c>
       <c r="E146" t="n">
-        <v>18.13163655163829</v>
+        <v>18.13163464026987</v>
       </c>
       <c r="F146" t="n">
         <v>18657800</v>
@@ -3372,16 +3372,16 @@
         <v>44467</v>
       </c>
       <c r="B148" t="n">
-        <v>18.2841625213623</v>
+        <v>18.28416061401367</v>
       </c>
       <c r="C148" t="n">
-        <v>18.29369567085224</v>
+        <v>18.29369376250914</v>
       </c>
       <c r="D148" t="n">
-        <v>18.01723979043107</v>
+        <v>18.01723791092701</v>
       </c>
       <c r="E148" t="n">
-        <v>18.23649677391261</v>
+        <v>18.23649487153633</v>
       </c>
       <c r="F148" t="n">
         <v>11310100</v>
@@ -3392,16 +3392,16 @@
         <v>44468</v>
       </c>
       <c r="B149" t="n">
-        <v>18.08396911621094</v>
+        <v>18.08397102355957</v>
       </c>
       <c r="C149" t="n">
-        <v>18.4271552076744</v>
+        <v>18.42715715121949</v>
       </c>
       <c r="D149" t="n">
-        <v>17.96957496456462</v>
+        <v>17.9695768598479</v>
       </c>
       <c r="E149" t="n">
-        <v>18.29369475799961</v>
+        <v>18.29369668746839</v>
       </c>
       <c r="F149" t="n">
         <v>10203400</v>
@@ -3412,16 +3412,16 @@
         <v>44469</v>
       </c>
       <c r="B150" t="n">
-        <v>18.15070343017578</v>
+        <v>18.15070152282715</v>
       </c>
       <c r="C150" t="n">
-        <v>18.6273500309481</v>
+        <v>18.62734807351153</v>
       </c>
       <c r="D150" t="n">
-        <v>18.04584059616188</v>
+        <v>18.04583869983265</v>
       </c>
       <c r="E150" t="n">
-        <v>18.30323019696192</v>
+        <v>18.30322827358517</v>
       </c>
       <c r="F150" t="n">
         <v>10293000</v>
@@ -3432,16 +3432,16 @@
         <v>44470</v>
       </c>
       <c r="B151" t="n">
-        <v>18.45575714111328</v>
+        <v>18.45575523376465</v>
       </c>
       <c r="C151" t="n">
-        <v>18.56061815787245</v>
+        <v>18.56061623968673</v>
       </c>
       <c r="D151" t="n">
-        <v>18.00770816839343</v>
+        <v>18.00770630734936</v>
       </c>
       <c r="E151" t="n">
-        <v>18.19836753783964</v>
+        <v>18.19836565709148</v>
       </c>
       <c r="F151" t="n">
         <v>5841800</v>
@@ -3452,16 +3452,16 @@
         <v>44473</v>
       </c>
       <c r="B152" t="n">
-        <v>18.4176197052002</v>
+        <v>18.41762351989746</v>
       </c>
       <c r="C152" t="n">
-        <v>18.49388306930666</v>
+        <v>18.49388689979976</v>
       </c>
       <c r="D152" t="n">
-        <v>18.0744336575901</v>
+        <v>18.07443740120593</v>
       </c>
       <c r="E152" t="n">
-        <v>18.38902208007404</v>
+        <v>18.3890258888481</v>
       </c>
       <c r="F152" t="n">
         <v>9789400</v>
@@ -3592,16 +3592,16 @@
         <v>44483</v>
       </c>
       <c r="B159" t="n">
-        <v>17.06758308410645</v>
+        <v>17.06758117675781</v>
       </c>
       <c r="C159" t="n">
-        <v>17.14403354871527</v>
+        <v>17.14403163282309</v>
       </c>
       <c r="D159" t="n">
-        <v>16.60887847373064</v>
+        <v>16.6088766176435</v>
       </c>
       <c r="E159" t="n">
-        <v>16.96246301174824</v>
+        <v>16.96246111614706</v>
       </c>
       <c r="F159" t="n">
         <v>10051300</v>
@@ -3772,16 +3772,16 @@
         <v>44496</v>
       </c>
       <c r="B168" t="n">
-        <v>14.94607830047607</v>
+        <v>14.94607734680176</v>
       </c>
       <c r="C168" t="n">
-        <v>15.38566886553011</v>
+        <v>15.38566788380655</v>
       </c>
       <c r="D168" t="n">
-        <v>14.81228955063831</v>
+        <v>14.81228860550074</v>
       </c>
       <c r="E168" t="n">
-        <v>15.38566886553011</v>
+        <v>15.38566788380655</v>
       </c>
       <c r="F168" t="n">
         <v>9783700</v>
@@ -3812,16 +3812,16 @@
         <v>44498</v>
       </c>
       <c r="B170" t="n">
-        <v>14.61160850524902</v>
+        <v>14.61160755157471</v>
       </c>
       <c r="C170" t="n">
-        <v>15.21365657937846</v>
+        <v>15.21365558640951</v>
       </c>
       <c r="D170" t="n">
-        <v>14.50648934742759</v>
+        <v>14.50648840061422</v>
       </c>
       <c r="E170" t="n">
-        <v>15.0034173523742</v>
+        <v>15.0034163731272</v>
       </c>
       <c r="F170" t="n">
         <v>13706000</v>
@@ -3832,16 +3832,16 @@
         <v>44501</v>
       </c>
       <c r="B171" t="n">
-        <v>14.31536197662354</v>
+        <v>14.31536102294922</v>
       </c>
       <c r="C171" t="n">
-        <v>14.77406565205061</v>
+        <v>14.77406466781794</v>
       </c>
       <c r="D171" t="n">
-        <v>14.20068628560711</v>
+        <v>14.20068533957237</v>
       </c>
       <c r="E171" t="n">
-        <v>14.76450911662556</v>
+        <v>14.76450813302954</v>
       </c>
       <c r="F171" t="n">
         <v>10277500</v>
@@ -3912,16 +3912,16 @@
         <v>44508</v>
       </c>
       <c r="B175" t="n">
-        <v>14.73583889007568</v>
+        <v>14.73583984375</v>
       </c>
       <c r="C175" t="n">
-        <v>14.89829632997021</v>
+        <v>14.89829729415845</v>
       </c>
       <c r="D175" t="n">
-        <v>14.28669179675779</v>
+        <v>14.2866927213642</v>
       </c>
       <c r="E175" t="n">
-        <v>14.39181185278442</v>
+        <v>14.39181278419399</v>
       </c>
       <c r="F175" t="n">
         <v>8290300</v>
@@ -3952,16 +3952,16 @@
         <v>44510</v>
       </c>
       <c r="B177" t="n">
-        <v>15.26143836975098</v>
+        <v>15.26143932342529</v>
       </c>
       <c r="C177" t="n">
-        <v>15.38567059902005</v>
+        <v>15.38567156045753</v>
       </c>
       <c r="D177" t="n">
-        <v>14.7167276858233</v>
+        <v>14.71672860545911</v>
       </c>
       <c r="E177" t="n">
-        <v>14.84095991509237</v>
+        <v>14.84096084249134</v>
       </c>
       <c r="F177" t="n">
         <v>10223900</v>
@@ -3992,16 +3992,16 @@
         <v>44512</v>
       </c>
       <c r="B179" t="n">
-        <v>14.84096050262451</v>
+        <v>14.8409595489502</v>
       </c>
       <c r="C179" t="n">
-        <v>15.23276936586659</v>
+        <v>15.23276838701479</v>
       </c>
       <c r="D179" t="n">
-        <v>14.82184834194417</v>
+        <v>14.82184738949799</v>
       </c>
       <c r="E179" t="n">
-        <v>15.089424970999</v>
+        <v>15.08942400135846</v>
       </c>
       <c r="F179" t="n">
         <v>7831400</v>
@@ -4012,16 +4012,16 @@
         <v>44516</v>
       </c>
       <c r="B180" t="n">
-        <v>14.18157386779785</v>
+        <v>14.18157482147217</v>
       </c>
       <c r="C180" t="n">
-        <v>14.86007237747372</v>
+        <v>14.86007337677532</v>
       </c>
       <c r="D180" t="n">
-        <v>14.00000334347483</v>
+        <v>14.00000428493899</v>
       </c>
       <c r="E180" t="n">
-        <v>14.81229061258022</v>
+        <v>14.81229160866862</v>
       </c>
       <c r="F180" t="n">
         <v>11424100</v>
@@ -4052,16 +4052,16 @@
         <v>44518</v>
       </c>
       <c r="B182" t="n">
-        <v>13.3597297668457</v>
+        <v>13.35973072052002</v>
       </c>
       <c r="C182" t="n">
-        <v>13.69420120231332</v>
+        <v>13.69420217986363</v>
       </c>
       <c r="D182" t="n">
-        <v>13.13993492912112</v>
+        <v>13.13993586710555</v>
       </c>
       <c r="E182" t="n">
-        <v>13.65597597351942</v>
+        <v>13.65597694834105</v>
       </c>
       <c r="F182" t="n">
         <v>21252300</v>
@@ -4112,16 +4112,16 @@
         <v>44523</v>
       </c>
       <c r="B185" t="n">
-        <v>13.24505424499512</v>
+        <v>13.2450532913208</v>
       </c>
       <c r="C185" t="n">
-        <v>13.4170682323851</v>
+        <v>13.41706726632538</v>
       </c>
       <c r="D185" t="n">
-        <v>12.99659071042901</v>
+        <v>12.99658977464464</v>
       </c>
       <c r="E185" t="n">
-        <v>13.23549862119895</v>
+        <v>13.23549766821266</v>
       </c>
       <c r="F185" t="n">
         <v>3755200</v>
@@ -4212,16 +4212,16 @@
         <v>44530</v>
       </c>
       <c r="B190" t="n">
-        <v>12.18430328369141</v>
+        <v>12.18430423736572</v>
       </c>
       <c r="C190" t="n">
-        <v>12.44232426127008</v>
+        <v>12.44232523513989</v>
       </c>
       <c r="D190" t="n">
-        <v>11.84027622494785</v>
+        <v>11.84027715169492</v>
       </c>
       <c r="E190" t="n">
-        <v>12.38498596246548</v>
+        <v>12.38498693184738</v>
       </c>
       <c r="F190" t="n">
         <v>16793700</v>
@@ -4232,16 +4232,16 @@
         <v>44531</v>
       </c>
       <c r="B191" t="n">
-        <v>11.91672706604004</v>
+        <v>11.91672801971436</v>
       </c>
       <c r="C191" t="n">
-        <v>12.37542982579687</v>
+        <v>12.37543081618034</v>
       </c>
       <c r="D191" t="n">
-        <v>11.81160700007474</v>
+        <v>11.81160794533648</v>
       </c>
       <c r="E191" t="n">
-        <v>12.2989793658374</v>
+        <v>12.29898035010268</v>
       </c>
       <c r="F191" t="n">
         <v>5991300</v>
@@ -4252,16 +4252,16 @@
         <v>44532</v>
       </c>
       <c r="B192" t="n">
-        <v>11.89761447906494</v>
+        <v>11.89761352539062</v>
       </c>
       <c r="C192" t="n">
-        <v>12.14607893971519</v>
+        <v>12.14607796612476</v>
       </c>
       <c r="D192" t="n">
-        <v>11.71604485711986</v>
+        <v>11.71604391799958</v>
       </c>
       <c r="E192" t="n">
-        <v>12.14607893971519</v>
+        <v>12.14607796612476</v>
       </c>
       <c r="F192" t="n">
         <v>7306700</v>
@@ -4392,16 +4392,16 @@
         <v>44543</v>
       </c>
       <c r="B199" t="n">
-        <v>13.74198341369629</v>
+        <v>13.74198246002197</v>
       </c>
       <c r="C199" t="n">
-        <v>14.12423571408451</v>
+        <v>14.12423473388242</v>
       </c>
       <c r="D199" t="n">
-        <v>13.66553295361865</v>
+        <v>13.66553200524988</v>
       </c>
       <c r="E199" t="n">
-        <v>13.96177825857917</v>
+        <v>13.9617772896514</v>
       </c>
       <c r="F199" t="n">
         <v>11783000</v>
@@ -4432,16 +4432,16 @@
         <v>44545</v>
       </c>
       <c r="B201" t="n">
-        <v>14.03822898864746</v>
+        <v>14.03822803497314</v>
       </c>
       <c r="C201" t="n">
-        <v>14.05734205971515</v>
+        <v>14.0573411047424</v>
       </c>
       <c r="D201" t="n">
-        <v>13.73242714245554</v>
+        <v>13.7324262095556</v>
       </c>
       <c r="E201" t="n">
-        <v>13.92355329632549</v>
+        <v>13.92355235044156</v>
       </c>
       <c r="F201" t="n">
         <v>6373000</v>
@@ -4492,16 +4492,16 @@
         <v>44550</v>
       </c>
       <c r="B204" t="n">
-        <v>13.47440528869629</v>
+        <v>13.47440624237061</v>
       </c>
       <c r="C204" t="n">
-        <v>13.86621408038928</v>
+        <v>13.86621506179454</v>
       </c>
       <c r="D204" t="n">
-        <v>13.29283478290215</v>
+        <v>13.29283572372549</v>
       </c>
       <c r="E204" t="n">
-        <v>13.81843232037181</v>
+        <v>13.81843329839523</v>
       </c>
       <c r="F204" t="n">
         <v>6680500</v>
@@ -4592,16 +4592,16 @@
         <v>44558</v>
       </c>
       <c r="B209" t="n">
-        <v>12.51877498626709</v>
+        <v>12.51877403259277</v>
       </c>
       <c r="C209" t="n">
-        <v>13.12082212409239</v>
+        <v>13.12082112455441</v>
       </c>
       <c r="D209" t="n">
-        <v>12.31809230320487</v>
+        <v>12.31809136481846</v>
       </c>
       <c r="E209" t="n">
-        <v>13.12082212409239</v>
+        <v>13.12082112455441</v>
       </c>
       <c r="F209" t="n">
         <v>22962600</v>
@@ -4632,16 +4632,16 @@
         <v>44560</v>
       </c>
       <c r="B211" t="n">
-        <v>12.38498592376709</v>
+        <v>12.38498497009277</v>
       </c>
       <c r="C211" t="n">
-        <v>12.49966160965662</v>
+        <v>12.499660647152</v>
       </c>
       <c r="D211" t="n">
-        <v>12.25119716788196</v>
+        <v>12.25119622450971</v>
       </c>
       <c r="E211" t="n">
-        <v>12.32764762514165</v>
+        <v>12.32764667588253</v>
       </c>
       <c r="F211" t="n">
         <v>5913100</v>
@@ -4752,16 +4752,16 @@
         <v>44571</v>
       </c>
       <c r="B217" t="n">
-        <v>10.7986364364624</v>
+        <v>10.79863739013672</v>
       </c>
       <c r="C217" t="n">
-        <v>10.85597381771528</v>
+        <v>10.8559747764533</v>
       </c>
       <c r="D217" t="n">
-        <v>10.54061548674074</v>
+        <v>10.54061641762812</v>
       </c>
       <c r="E217" t="n">
-        <v>10.76041121184007</v>
+        <v>10.76041216213855</v>
       </c>
       <c r="F217" t="n">
         <v>8755800</v>
@@ -4872,16 +4872,16 @@
         <v>44579</v>
       </c>
       <c r="B223" t="n">
-        <v>11.39112854003906</v>
+        <v>11.39112949371338</v>
       </c>
       <c r="C223" t="n">
-        <v>11.49624768605842</v>
+        <v>11.49624864853339</v>
       </c>
       <c r="D223" t="n">
-        <v>11.29556501721325</v>
+        <v>11.29556596288691</v>
       </c>
       <c r="E223" t="n">
-        <v>11.47713552831003</v>
+        <v>11.47713648918492</v>
       </c>
       <c r="F223" t="n">
         <v>7771300</v>
@@ -4892,16 +4892,16 @@
         <v>44580</v>
       </c>
       <c r="B224" t="n">
-        <v>11.49624824523926</v>
+        <v>11.49624919891357</v>
       </c>
       <c r="C224" t="n">
-        <v>11.69693092384569</v>
+        <v>11.69693189416769</v>
       </c>
       <c r="D224" t="n">
-        <v>11.41979778780455</v>
+        <v>11.4197987351369</v>
       </c>
       <c r="E224" t="n">
-        <v>11.41979778780455</v>
+        <v>11.4197987351369</v>
       </c>
       <c r="F224" t="n">
         <v>5074700</v>
@@ -4952,16 +4952,16 @@
         <v>44585</v>
       </c>
       <c r="B227" t="n">
-        <v>11.50580501556396</v>
+        <v>11.50580406188965</v>
       </c>
       <c r="C227" t="n">
-        <v>11.63959377449148</v>
+        <v>11.6395928097279</v>
       </c>
       <c r="D227" t="n">
-        <v>11.3242354032836</v>
+        <v>11.32423446465893</v>
       </c>
       <c r="E227" t="n">
-        <v>11.46757978606487</v>
+        <v>11.4675788355589</v>
       </c>
       <c r="F227" t="n">
         <v>6551900</v>
@@ -4972,16 +4972,16 @@
         <v>44586</v>
       </c>
       <c r="B228" t="n">
-        <v>11.75427055358887</v>
+        <v>11.75426959991455</v>
       </c>
       <c r="C228" t="n">
-        <v>11.8880584135683</v>
+        <v>11.8880574490392</v>
       </c>
       <c r="D228" t="n">
-        <v>10.98020844521045</v>
+        <v>10.98020755433911</v>
       </c>
       <c r="E228" t="n">
-        <v>11.4293556170192</v>
+        <v>11.42935468970662</v>
       </c>
       <c r="F228" t="n">
         <v>40426700</v>
@@ -4992,16 +4992,16 @@
         <v>44587</v>
       </c>
       <c r="B229" t="n">
-        <v>11.73515701293945</v>
+        <v>11.73515605926514</v>
       </c>
       <c r="C229" t="n">
-        <v>12.21297286261863</v>
+        <v>12.21297187011393</v>
       </c>
       <c r="D229" t="n">
-        <v>11.73515701293945</v>
+        <v>11.73515605926514</v>
       </c>
       <c r="E229" t="n">
-        <v>11.81160747597921</v>
+        <v>11.81160651609204</v>
       </c>
       <c r="F229" t="n">
         <v>11052300</v>
@@ -5032,16 +5032,16 @@
         <v>44589</v>
       </c>
       <c r="B231" t="n">
-        <v>11.83071994781494</v>
+        <v>11.83071899414062</v>
       </c>
       <c r="C231" t="n">
-        <v>12.04095916619962</v>
+        <v>12.04095819557792</v>
       </c>
       <c r="D231" t="n">
-        <v>11.4580232758641</v>
+        <v>11.45802235223286</v>
       </c>
       <c r="E231" t="n">
-        <v>11.94539563656258</v>
+        <v>11.94539467364426</v>
       </c>
       <c r="F231" t="n">
         <v>14924100</v>
@@ -5072,16 +5072,16 @@
         <v>44593</v>
       </c>
       <c r="B233" t="n">
-        <v>12.0218448638916</v>
+        <v>12.02184581756592</v>
       </c>
       <c r="C233" t="n">
-        <v>12.09829531522309</v>
+        <v>12.0982962749621</v>
       </c>
       <c r="D233" t="n">
-        <v>11.83071873556289</v>
+        <v>11.83071967407547</v>
       </c>
       <c r="E233" t="n">
-        <v>11.93583787830337</v>
+        <v>11.93583882515488</v>
       </c>
       <c r="F233" t="n">
         <v>5991900</v>
@@ -5172,16 +5172,16 @@
         <v>44600</v>
       </c>
       <c r="B238" t="n">
-        <v>11.9549503326416</v>
+        <v>11.95495223999023</v>
       </c>
       <c r="C238" t="n">
-        <v>12.20341474238491</v>
+        <v>12.20341668937472</v>
       </c>
       <c r="D238" t="n">
-        <v>11.83071812776995</v>
+        <v>11.83072001529799</v>
       </c>
       <c r="E238" t="n">
-        <v>12.14607645115137</v>
+        <v>12.14607838899316</v>
       </c>
       <c r="F238" t="n">
         <v>8002100</v>
@@ -5192,16 +5192,16 @@
         <v>44601</v>
       </c>
       <c r="B239" t="n">
-        <v>12.05051517486572</v>
+        <v>12.05051422119141</v>
       </c>
       <c r="C239" t="n">
-        <v>12.28942309522567</v>
+        <v>12.28942212264425</v>
       </c>
       <c r="D239" t="n">
-        <v>11.91672732273544</v>
+        <v>11.91672637964906</v>
       </c>
       <c r="E239" t="n">
-        <v>11.95495255353858</v>
+        <v>11.95495160742706</v>
       </c>
       <c r="F239" t="n">
         <v>9060800</v>
@@ -5232,16 +5232,16 @@
         <v>44603</v>
       </c>
       <c r="B241" t="n">
-        <v>11.79249382019043</v>
+        <v>11.79249477386475</v>
       </c>
       <c r="C241" t="n">
-        <v>12.21297131357752</v>
+        <v>12.2129723012564</v>
       </c>
       <c r="D241" t="n">
-        <v>11.74471205901066</v>
+        <v>11.74471300882081</v>
       </c>
       <c r="E241" t="n">
-        <v>12.18430262141418</v>
+        <v>12.18430360677458</v>
       </c>
       <c r="F241" t="n">
         <v>7316000</v>
@@ -5252,16 +5252,16 @@
         <v>44606</v>
       </c>
       <c r="B242" t="n">
-        <v>11.78293800354004</v>
+        <v>11.78293895721436</v>
       </c>
       <c r="C242" t="n">
-        <v>11.97406414854188</v>
+        <v>11.97406511768535</v>
       </c>
       <c r="D242" t="n">
-        <v>11.639593622629</v>
+        <v>11.63959456470146</v>
       </c>
       <c r="E242" t="n">
-        <v>11.79249453863047</v>
+        <v>11.79249549307826</v>
       </c>
       <c r="F242" t="n">
         <v>5445000</v>
@@ -5272,16 +5272,16 @@
         <v>44607</v>
       </c>
       <c r="B243" t="n">
-        <v>11.63959503173828</v>
+        <v>11.63959312438965</v>
       </c>
       <c r="C243" t="n">
-        <v>11.95495343700949</v>
+        <v>11.95495147798393</v>
       </c>
       <c r="D243" t="n">
-        <v>11.53447495574024</v>
+        <v>11.53447306561735</v>
       </c>
       <c r="E243" t="n">
-        <v>11.92628382826741</v>
+        <v>11.92628187393986</v>
       </c>
       <c r="F243" t="n">
         <v>11329100</v>
@@ -5312,16 +5312,16 @@
         <v>44609</v>
       </c>
       <c r="B245" t="n">
-        <v>12.66211700439453</v>
+        <v>12.66211795806885</v>
       </c>
       <c r="C245" t="n">
-        <v>12.9488066282757</v>
+        <v>12.94880760354266</v>
       </c>
       <c r="D245" t="n">
-        <v>12.46143435881383</v>
+        <v>12.46143529737331</v>
       </c>
       <c r="E245" t="n">
-        <v>12.46143435881383</v>
+        <v>12.46143529737331</v>
       </c>
       <c r="F245" t="n">
         <v>10362100</v>
@@ -5372,16 +5372,16 @@
         <v>44614</v>
       </c>
       <c r="B248" t="n">
-        <v>12.51877498626709</v>
+        <v>12.51877403259277</v>
       </c>
       <c r="C248" t="n">
-        <v>12.63345067496531</v>
+        <v>12.63344971255505</v>
       </c>
       <c r="D248" t="n">
-        <v>12.08874001444707</v>
+        <v>12.08873909353262</v>
       </c>
       <c r="E248" t="n">
-        <v>12.14607831447686</v>
+        <v>12.1460773891944</v>
       </c>
       <c r="F248" t="n">
         <v>15416600</v>
@@ -5392,16 +5392,16 @@
         <v>44615</v>
       </c>
       <c r="B249" t="n">
-        <v>12.73856925964355</v>
+        <v>12.73857021331787</v>
       </c>
       <c r="C249" t="n">
-        <v>12.87235801283171</v>
+        <v>12.87235897652213</v>
       </c>
       <c r="D249" t="n">
-        <v>12.51877442729301</v>
+        <v>12.51877536451236</v>
       </c>
       <c r="E249" t="n">
-        <v>12.51877442729301</v>
+        <v>12.51877536451236</v>
       </c>
       <c r="F249" t="n">
         <v>5598100</v>
@@ -5472,16 +5472,16 @@
         <v>44623</v>
       </c>
       <c r="B253" t="n">
-        <v>12.56655406951904</v>
+        <v>12.56655502319336</v>
       </c>
       <c r="C253" t="n">
-        <v>12.95836375658081</v>
+        <v>12.95836473998952</v>
       </c>
       <c r="D253" t="n">
-        <v>12.33720272443013</v>
+        <v>12.337203660699</v>
       </c>
       <c r="E253" t="n">
-        <v>12.80546194849363</v>
+        <v>12.80546292029864</v>
       </c>
       <c r="F253" t="n">
         <v>12631200</v>
@@ -5512,16 +5512,16 @@
         <v>44627</v>
       </c>
       <c r="B255" t="n">
-        <v>11.73515701293945</v>
+        <v>11.73515605926514</v>
       </c>
       <c r="C255" t="n">
-        <v>12.17474763109875</v>
+        <v>12.17474664170048</v>
       </c>
       <c r="D255" t="n">
-        <v>11.68737524569925</v>
+        <v>11.68737429590799</v>
       </c>
       <c r="E255" t="n">
-        <v>12.08874063233868</v>
+        <v>12.08873964992988</v>
       </c>
       <c r="F255" t="n">
         <v>12255900</v>
@@ -5532,16 +5532,16 @@
         <v>44628</v>
       </c>
       <c r="B256" t="n">
-        <v>11.75427055358887</v>
+        <v>11.75426959991455</v>
       </c>
       <c r="C256" t="n">
-        <v>11.99317848796522</v>
+        <v>11.99317751490728</v>
       </c>
       <c r="D256" t="n">
-        <v>11.52491915531431</v>
+        <v>11.52491822024826</v>
       </c>
       <c r="E256" t="n">
-        <v>11.74471401748707</v>
+        <v>11.74471306458811</v>
       </c>
       <c r="F256" t="n">
         <v>10151100</v>
@@ -5612,16 +5612,16 @@
         <v>44634</v>
       </c>
       <c r="B260" t="n">
-        <v>12.51877498626709</v>
+        <v>12.51877403259277</v>
       </c>
       <c r="C260" t="n">
-        <v>12.74812636366353</v>
+        <v>12.74812539251733</v>
       </c>
       <c r="D260" t="n">
-        <v>12.38498622710516</v>
+        <v>12.3849852836228</v>
       </c>
       <c r="E260" t="n">
-        <v>12.43276799190309</v>
+        <v>12.43276704478074</v>
       </c>
       <c r="F260" t="n">
         <v>4274300</v>
@@ -5632,16 +5632,16 @@
         <v>44635</v>
       </c>
       <c r="B261" t="n">
-        <v>12.82457542419434</v>
+        <v>12.82457637786865</v>
       </c>
       <c r="C261" t="n">
-        <v>12.90102587498907</v>
+        <v>12.90102683434848</v>
       </c>
       <c r="D261" t="n">
-        <v>12.29897789145957</v>
+        <v>12.29897880604886</v>
       </c>
       <c r="E261" t="n">
-        <v>12.29897789145957</v>
+        <v>12.29897880604886</v>
       </c>
       <c r="F261" t="n">
         <v>8181800</v>
@@ -5652,16 +5652,16 @@
         <v>44636</v>
       </c>
       <c r="B262" t="n">
-        <v>12.99659156799316</v>
+        <v>12.99659061431885</v>
       </c>
       <c r="C262" t="n">
-        <v>13.09215419178991</v>
+        <v>13.09215323110332</v>
       </c>
       <c r="D262" t="n">
-        <v>12.73857056988299</v>
+        <v>12.73856963514194</v>
       </c>
       <c r="E262" t="n">
-        <v>12.91058456862311</v>
+        <v>12.91058362125988</v>
       </c>
       <c r="F262" t="n">
         <v>7731200</v>
@@ -5672,16 +5672,16 @@
         <v>44637</v>
       </c>
       <c r="B263" t="n">
-        <v>13.12082099914551</v>
+        <v>13.12082195281982</v>
       </c>
       <c r="C263" t="n">
-        <v>13.24505321242422</v>
+        <v>13.24505417512824</v>
       </c>
       <c r="D263" t="n">
-        <v>12.87235748394937</v>
+        <v>12.87235841956435</v>
       </c>
       <c r="E263" t="n">
-        <v>13.09215230726928</v>
+        <v>13.09215325885984</v>
       </c>
       <c r="F263" t="n">
         <v>6159800</v>
@@ -5752,16 +5752,16 @@
         <v>44643</v>
       </c>
       <c r="B267" t="n">
-        <v>14.38225650787354</v>
+        <v>14.38225555419922</v>
       </c>
       <c r="C267" t="n">
-        <v>14.59249572595387</v>
+        <v>14.59249475833878</v>
       </c>
       <c r="D267" t="n">
-        <v>13.87577198879766</v>
+        <v>13.87577106870787</v>
       </c>
       <c r="E267" t="n">
-        <v>14.0286729069065</v>
+        <v>14.02867197667799</v>
       </c>
       <c r="F267" t="n">
         <v>8813400</v>
@@ -5832,16 +5832,16 @@
         <v>44649</v>
       </c>
       <c r="B271" t="n">
-        <v>15.50034523010254</v>
+        <v>15.50034427642822</v>
       </c>
       <c r="C271" t="n">
-        <v>15.93038021620936</v>
+        <v>15.93037923607671</v>
       </c>
       <c r="D271" t="n">
-        <v>15.43345130397987</v>
+        <v>15.43345035442127</v>
       </c>
       <c r="E271" t="n">
-        <v>15.72969661511858</v>
+        <v>15.72969564733319</v>
       </c>
       <c r="F271" t="n">
         <v>7323700</v>
@@ -5892,16 +5892,16 @@
         <v>44652</v>
       </c>
       <c r="B274" t="n">
-        <v>15.74880695343018</v>
+        <v>15.74880599975586</v>
       </c>
       <c r="C274" t="n">
-        <v>15.97815829864838</v>
+        <v>15.97815733108562</v>
       </c>
       <c r="D274" t="n">
-        <v>15.4716747614791</v>
+        <v>15.47167382458661</v>
       </c>
       <c r="E274" t="n">
-        <v>15.72013917447944</v>
+        <v>15.72013822254111</v>
       </c>
       <c r="F274" t="n">
         <v>8302400</v>
@@ -5992,16 +5992,16 @@
         <v>44659</v>
       </c>
       <c r="B279" t="n">
-        <v>15.40478229522705</v>
+        <v>15.40478134155273</v>
       </c>
       <c r="C279" t="n">
-        <v>15.57679445327038</v>
+        <v>15.5767934889472</v>
       </c>
       <c r="D279" t="n">
-        <v>15.07031086848462</v>
+        <v>15.07030993551665</v>
       </c>
       <c r="E279" t="n">
-        <v>15.32833183963358</v>
+        <v>15.32833089069213</v>
       </c>
       <c r="F279" t="n">
         <v>3069100</v>
@@ -6012,16 +6012,16 @@
         <v>44662</v>
       </c>
       <c r="B280" t="n">
-        <v>15.29010581970215</v>
+        <v>15.29010677337646</v>
       </c>
       <c r="C280" t="n">
-        <v>15.49078758367887</v>
+        <v>15.4907885498701</v>
       </c>
       <c r="D280" t="n">
-        <v>15.21365536351254</v>
+        <v>15.21365631241849</v>
       </c>
       <c r="E280" t="n">
-        <v>15.38566934561982</v>
+        <v>15.38567030525462</v>
       </c>
       <c r="F280" t="n">
         <v>10289300</v>
@@ -6032,16 +6032,16 @@
         <v>44663</v>
       </c>
       <c r="B281" t="n">
-        <v>15.720139503479</v>
+        <v>15.72014141082764</v>
       </c>
       <c r="C281" t="n">
-        <v>15.82525773303578</v>
+        <v>15.82525965313857</v>
       </c>
       <c r="D281" t="n">
-        <v>15.3952246352726</v>
+        <v>15.39522650319881</v>
       </c>
       <c r="E281" t="n">
-        <v>15.48123161936973</v>
+        <v>15.48123349773131</v>
       </c>
       <c r="F281" t="n">
         <v>9798400</v>
@@ -6052,16 +6052,16 @@
         <v>44664</v>
       </c>
       <c r="B282" t="n">
-        <v>15.76792335510254</v>
+        <v>15.76792144775391</v>
       </c>
       <c r="C282" t="n">
-        <v>16.02594435654861</v>
+        <v>16.02594241798877</v>
       </c>
       <c r="D282" t="n">
-        <v>15.69147289053217</v>
+        <v>15.69147099243128</v>
       </c>
       <c r="E282" t="n">
-        <v>15.78703642692584</v>
+        <v>15.78703451726522</v>
       </c>
       <c r="F282" t="n">
         <v>7212700</v>
@@ -6072,16 +6072,16 @@
         <v>44665</v>
       </c>
       <c r="B283" t="n">
-        <v>15.64369106292725</v>
+        <v>15.64369201660156</v>
       </c>
       <c r="C283" t="n">
-        <v>15.79659198257972</v>
+        <v>15.79659294557522</v>
       </c>
       <c r="D283" t="n">
-        <v>15.48123360795615</v>
+        <v>15.4812345517267</v>
       </c>
       <c r="E283" t="n">
-        <v>15.72014152275348</v>
+        <v>15.72014248108839</v>
       </c>
       <c r="F283" t="n">
         <v>4607000</v>
@@ -6092,16 +6092,16 @@
         <v>44669</v>
       </c>
       <c r="B284" t="n">
-        <v>15.3187780380249</v>
+        <v>15.31877708435059</v>
       </c>
       <c r="C284" t="n">
-        <v>15.67236077471006</v>
+        <v>15.67235979902336</v>
       </c>
       <c r="D284" t="n">
-        <v>15.3187780380249</v>
+        <v>15.31877708435059</v>
       </c>
       <c r="E284" t="n">
-        <v>15.56724251871545</v>
+        <v>15.56724154957292</v>
       </c>
       <c r="F284" t="n">
         <v>3539900</v>
@@ -6112,16 +6112,16 @@
         <v>44670</v>
       </c>
       <c r="B285" t="n">
-        <v>15.61502170562744</v>
+        <v>15.61502075195312</v>
       </c>
       <c r="C285" t="n">
-        <v>15.77747916318553</v>
+        <v>15.77747819958926</v>
       </c>
       <c r="D285" t="n">
-        <v>15.18498763441659</v>
+        <v>15.18498670700624</v>
       </c>
       <c r="E285" t="n">
-        <v>15.32833293239446</v>
+        <v>15.32833199622942</v>
       </c>
       <c r="F285" t="n">
         <v>7756800</v>
@@ -6152,16 +6152,16 @@
         <v>44673</v>
       </c>
       <c r="B287" t="n">
-        <v>15.3187780380249</v>
+        <v>15.31877708435059</v>
       </c>
       <c r="C287" t="n">
-        <v>15.74881124394384</v>
+        <v>15.7488102634977</v>
       </c>
       <c r="D287" t="n">
-        <v>15.14676402656814</v>
+        <v>15.1467630836026</v>
       </c>
       <c r="E287" t="n">
-        <v>15.74881124394384</v>
+        <v>15.7488102634977</v>
       </c>
       <c r="F287" t="n">
         <v>8878800</v>
@@ -6192,16 +6192,16 @@
         <v>44677</v>
       </c>
       <c r="B289" t="n">
-        <v>15.12764930725098</v>
+        <v>15.12765026092529</v>
       </c>
       <c r="C289" t="n">
-        <v>15.30921983544218</v>
+        <v>15.30922080056303</v>
       </c>
       <c r="D289" t="n">
-        <v>15.02253015133491</v>
+        <v>15.02253109838233</v>
       </c>
       <c r="E289" t="n">
-        <v>15.2136563036193</v>
+        <v>15.21365726271565</v>
       </c>
       <c r="F289" t="n">
         <v>9387600</v>
@@ -6232,16 +6232,16 @@
         <v>44679</v>
       </c>
       <c r="B291" t="n">
-        <v>14.84096050262451</v>
+        <v>14.8409595489502</v>
       </c>
       <c r="C291" t="n">
-        <v>15.3856712081165</v>
+        <v>15.38567021943929</v>
       </c>
       <c r="D291" t="n">
-        <v>14.84096050262451</v>
+        <v>14.8409595489502</v>
       </c>
       <c r="E291" t="n">
-        <v>15.32833381471404</v>
+        <v>15.3283328297213</v>
       </c>
       <c r="F291" t="n">
         <v>5384600</v>
@@ -6272,16 +6272,16 @@
         <v>44683</v>
       </c>
       <c r="B293" t="n">
-        <v>14.69167137145996</v>
+        <v>14.69167041778564</v>
       </c>
       <c r="C293" t="n">
-        <v>14.97105393783902</v>
+        <v>14.97105296602926</v>
       </c>
       <c r="D293" t="n">
-        <v>14.44119019642807</v>
+        <v>14.44118925901314</v>
       </c>
       <c r="E293" t="n">
-        <v>14.54716349596546</v>
+        <v>14.54716255167152</v>
       </c>
       <c r="F293" t="n">
         <v>5536000</v>
@@ -6292,16 +6292,16 @@
         <v>44684</v>
       </c>
       <c r="B294" t="n">
-        <v>14.62423419952393</v>
+        <v>14.62423324584961</v>
       </c>
       <c r="C294" t="n">
-        <v>14.85544716329886</v>
+        <v>14.85544619454671</v>
       </c>
       <c r="D294" t="n">
-        <v>14.4797254080956</v>
+        <v>14.47972446384498</v>
       </c>
       <c r="E294" t="n">
-        <v>14.70130518744891</v>
+        <v>14.70130422874864</v>
       </c>
       <c r="F294" t="n">
         <v>5388000</v>
@@ -6372,16 +6372,16 @@
         <v>44690</v>
       </c>
       <c r="B298" t="n">
-        <v>14.21961116790771</v>
+        <v>14.21961212158203</v>
       </c>
       <c r="C298" t="n">
-        <v>14.32558354746724</v>
+        <v>14.32558450824887</v>
       </c>
       <c r="D298" t="n">
-        <v>13.92096039822737</v>
+        <v>13.92096133187191</v>
       </c>
       <c r="E298" t="n">
-        <v>14.04620098430244</v>
+        <v>14.04620192634656</v>
       </c>
       <c r="F298" t="n">
         <v>11844800</v>
@@ -6392,16 +6392,16 @@
         <v>44691</v>
       </c>
       <c r="B299" t="n">
-        <v>14.71093845367432</v>
+        <v>14.71093940734863</v>
       </c>
       <c r="C299" t="n">
-        <v>14.97105279343268</v>
+        <v>14.97105376396958</v>
       </c>
       <c r="D299" t="n">
-        <v>14.14253926099675</v>
+        <v>14.14254017782313</v>
       </c>
       <c r="E299" t="n">
-        <v>14.2196102445369</v>
+        <v>14.21961116635961</v>
       </c>
       <c r="F299" t="n">
         <v>13119700</v>
@@ -6452,16 +6452,16 @@
         <v>44694</v>
       </c>
       <c r="B302" t="n">
-        <v>14.91324996948242</v>
+        <v>14.91324901580811</v>
       </c>
       <c r="C302" t="n">
-        <v>15.09629425517541</v>
+        <v>15.09629328979575</v>
       </c>
       <c r="D302" t="n">
-        <v>14.62423422366596</v>
+        <v>14.62423328847366</v>
       </c>
       <c r="E302" t="n">
-        <v>14.7205724993519</v>
+        <v>14.72057155799894</v>
       </c>
       <c r="F302" t="n">
         <v>5016200</v>
@@ -6572,16 +6572,16 @@
         <v>44704</v>
       </c>
       <c r="B308" t="n">
-        <v>15.28897285461426</v>
+        <v>15.28897190093994</v>
       </c>
       <c r="C308" t="n">
-        <v>15.63579232646676</v>
+        <v>15.63579135115902</v>
       </c>
       <c r="D308" t="n">
-        <v>15.17336636399676</v>
+        <v>15.17336541753358</v>
       </c>
       <c r="E308" t="n">
-        <v>15.52982085851578</v>
+        <v>15.52981988981818</v>
       </c>
       <c r="F308" t="n">
         <v>8474400</v>
@@ -6612,16 +6612,16 @@
         <v>44706</v>
       </c>
       <c r="B310" t="n">
-        <v>15.14446258544922</v>
+        <v>15.1444616317749</v>
       </c>
       <c r="C310" t="n">
-        <v>15.44311332823613</v>
+        <v>15.44311235575524</v>
       </c>
       <c r="D310" t="n">
-        <v>14.94215102904739</v>
+        <v>14.942150088113</v>
       </c>
       <c r="E310" t="n">
-        <v>15.16372987147109</v>
+        <v>15.16372891658348</v>
       </c>
       <c r="F310" t="n">
         <v>8129200</v>
@@ -6652,16 +6652,16 @@
         <v>44708</v>
       </c>
       <c r="B312" t="n">
-        <v>15.22153472900391</v>
+        <v>15.22153377532959</v>
       </c>
       <c r="C312" t="n">
-        <v>15.51055139146295</v>
+        <v>15.51055041968089</v>
       </c>
       <c r="D312" t="n">
-        <v>15.13482963839033</v>
+        <v>15.13482869014834</v>
       </c>
       <c r="E312" t="n">
-        <v>15.43348040397503</v>
+        <v>15.43347943702168</v>
       </c>
       <c r="F312" t="n">
         <v>3408100</v>
@@ -6692,16 +6692,16 @@
         <v>44712</v>
       </c>
       <c r="B314" t="n">
-        <v>15.26006984710693</v>
+        <v>15.26007080078125</v>
       </c>
       <c r="C314" t="n">
-        <v>15.39494361251144</v>
+        <v>15.39494457461466</v>
       </c>
       <c r="D314" t="n">
-        <v>15.05775828024155</v>
+        <v>15.05775922127246</v>
       </c>
       <c r="E314" t="n">
-        <v>15.29860533990231</v>
+        <v>15.29860629598489</v>
       </c>
       <c r="F314" t="n">
         <v>5708500</v>
@@ -6712,16 +6712,16 @@
         <v>44713</v>
       </c>
       <c r="B315" t="n">
-        <v>14.85544586181641</v>
+        <v>14.85544681549072</v>
       </c>
       <c r="C315" t="n">
-        <v>15.53945059003543</v>
+        <v>15.53945158762076</v>
       </c>
       <c r="D315" t="n">
-        <v>14.73020528772095</v>
+        <v>14.73020623335521</v>
       </c>
       <c r="E315" t="n">
-        <v>15.39494273002606</v>
+        <v>15.39494371833443</v>
       </c>
       <c r="F315" t="n">
         <v>6096700</v>
@@ -6732,16 +6732,16 @@
         <v>44714</v>
       </c>
       <c r="B316" t="n">
-        <v>15.30823993682861</v>
+        <v>15.30824089050293</v>
       </c>
       <c r="C316" t="n">
-        <v>15.41421231574625</v>
+        <v>15.41421327602245</v>
       </c>
       <c r="D316" t="n">
-        <v>14.88434858364075</v>
+        <v>14.88434951090744</v>
       </c>
       <c r="E316" t="n">
-        <v>15.06739286939508</v>
+        <v>15.06739380806508</v>
       </c>
       <c r="F316" t="n">
         <v>5285700</v>
@@ -6852,16 +6852,16 @@
         <v>44722</v>
       </c>
       <c r="B322" t="n">
-        <v>14.48935985565186</v>
+        <v>14.48936080932617</v>
       </c>
       <c r="C322" t="n">
-        <v>15.01922359929862</v>
+        <v>15.019224587848</v>
       </c>
       <c r="D322" t="n">
-        <v>14.22924549491244</v>
+        <v>14.22924643146631</v>
       </c>
       <c r="E322" t="n">
-        <v>14.85544751637582</v>
+        <v>14.85544849414564</v>
       </c>
       <c r="F322" t="n">
         <v>15101900</v>
@@ -6872,16 +6872,16 @@
         <v>44725</v>
       </c>
       <c r="B323" t="n">
-        <v>14.03656578063965</v>
+        <v>14.03656673431396</v>
       </c>
       <c r="C323" t="n">
-        <v>14.35448381315351</v>
+        <v>14.35448478842786</v>
       </c>
       <c r="D323" t="n">
-        <v>13.89205791813647</v>
+        <v>13.89205886199261</v>
       </c>
       <c r="E323" t="n">
-        <v>14.25814554440425</v>
+        <v>14.25814651313317</v>
       </c>
       <c r="F323" t="n">
         <v>9104400</v>
@@ -6912,16 +6912,16 @@
         <v>44727</v>
       </c>
       <c r="B325" t="n">
-        <v>14.91324996948242</v>
+        <v>14.91324901580811</v>
       </c>
       <c r="C325" t="n">
-        <v>15.06739286434549</v>
+        <v>15.06739190081403</v>
       </c>
       <c r="D325" t="n">
-        <v>14.25814657103863</v>
+        <v>14.25814565925695</v>
       </c>
       <c r="E325" t="n">
-        <v>14.34485166228703</v>
+        <v>14.34485074496072</v>
       </c>
       <c r="F325" t="n">
         <v>25461900</v>
@@ -6932,16 +6932,16 @@
         <v>44729</v>
       </c>
       <c r="B326" t="n">
-        <v>14.94215202331543</v>
+        <v>14.94215297698975</v>
       </c>
       <c r="C326" t="n">
-        <v>15.18299908654582</v>
+        <v>15.18300005559206</v>
       </c>
       <c r="D326" t="n">
-        <v>14.56643027392291</v>
+        <v>14.56643120361701</v>
       </c>
       <c r="E326" t="n">
-        <v>14.63386715762466</v>
+        <v>14.63386809162287</v>
       </c>
       <c r="F326" t="n">
         <v>14099900</v>
@@ -6972,16 +6972,16 @@
         <v>44733</v>
       </c>
       <c r="B328" t="n">
-        <v>14.84581279754639</v>
+        <v>14.84581184387207</v>
       </c>
       <c r="C328" t="n">
-        <v>15.6454249721946</v>
+        <v>15.64542396715431</v>
       </c>
       <c r="D328" t="n">
-        <v>14.81691140727535</v>
+        <v>14.81691045545762</v>
       </c>
       <c r="E328" t="n">
-        <v>15.37567651922811</v>
+        <v>15.37567553151609</v>
       </c>
       <c r="F328" t="n">
         <v>9398400</v>
@@ -7032,16 +7032,16 @@
         <v>44736</v>
       </c>
       <c r="B331" t="n">
-        <v>14.4219217300415</v>
+        <v>14.42192268371582</v>
       </c>
       <c r="C331" t="n">
-        <v>14.86508034244202</v>
+        <v>14.86508132542095</v>
       </c>
       <c r="D331" t="n">
-        <v>14.25814566119184</v>
+        <v>14.25814660403618</v>
       </c>
       <c r="E331" t="n">
-        <v>14.86508034244202</v>
+        <v>14.86508132542095</v>
       </c>
       <c r="F331" t="n">
         <v>5803600</v>
@@ -7052,16 +7052,16 @@
         <v>44739</v>
       </c>
       <c r="B332" t="n">
-        <v>14.16180801391602</v>
+        <v>14.1618070602417</v>
       </c>
       <c r="C332" t="n">
-        <v>14.49899429088777</v>
+        <v>14.4989933145069</v>
       </c>
       <c r="D332" t="n">
-        <v>14.10400522965489</v>
+        <v>14.10400427987309</v>
       </c>
       <c r="E332" t="n">
-        <v>14.47972608362827</v>
+        <v>14.47972510854494</v>
       </c>
       <c r="F332" t="n">
         <v>8041800</v>
@@ -7092,16 +7092,16 @@
         <v>44741</v>
       </c>
       <c r="B334" t="n">
-        <v>13.85352325439453</v>
+        <v>13.85352230072021</v>
       </c>
       <c r="C334" t="n">
-        <v>14.1810754089765</v>
+        <v>14.18107443275354</v>
       </c>
       <c r="D334" t="n">
-        <v>13.5934079838411</v>
+        <v>13.59340704807308</v>
       </c>
       <c r="E334" t="n">
-        <v>14.1810754089765</v>
+        <v>14.18107443275354</v>
       </c>
       <c r="F334" t="n">
         <v>8408900</v>
@@ -7132,16 +7132,16 @@
         <v>44743</v>
       </c>
       <c r="B336" t="n">
-        <v>14.06546878814697</v>
+        <v>14.06546974182129</v>
       </c>
       <c r="C336" t="n">
-        <v>14.28704764418037</v>
+        <v>14.28704861287829</v>
       </c>
       <c r="D336" t="n">
-        <v>13.54523917098311</v>
+        <v>13.54524008938454</v>
       </c>
       <c r="E336" t="n">
-        <v>13.64157744452686</v>
+        <v>13.64157836946027</v>
       </c>
       <c r="F336" t="n">
         <v>10271400</v>
@@ -7152,16 +7152,16 @@
         <v>44746</v>
       </c>
       <c r="B337" t="n">
-        <v>13.8727912902832</v>
+        <v>13.87279033660889</v>
       </c>
       <c r="C337" t="n">
-        <v>14.14254067846864</v>
+        <v>14.14253970625061</v>
       </c>
       <c r="D337" t="n">
-        <v>13.76681890698379</v>
+        <v>13.76681796059447</v>
       </c>
       <c r="E337" t="n">
-        <v>13.95949638514576</v>
+        <v>13.95949542551097</v>
       </c>
       <c r="F337" t="n">
         <v>1980900</v>
@@ -7172,16 +7172,16 @@
         <v>44747</v>
       </c>
       <c r="B338" t="n">
-        <v>14.17144107818604</v>
+        <v>14.17144012451172</v>
       </c>
       <c r="C338" t="n">
-        <v>14.19070836527375</v>
+        <v>14.19070741030283</v>
       </c>
       <c r="D338" t="n">
-        <v>13.46816718369137</v>
+        <v>13.46816627734423</v>
       </c>
       <c r="E338" t="n">
-        <v>13.67047875128478</v>
+        <v>13.67047783132298</v>
       </c>
       <c r="F338" t="n">
         <v>7354200</v>
@@ -7192,16 +7192,16 @@
         <v>44748</v>
       </c>
       <c r="B339" t="n">
-        <v>14.35448455810547</v>
+        <v>14.35448551177979</v>
       </c>
       <c r="C339" t="n">
-        <v>14.63386711386697</v>
+        <v>14.63386808610274</v>
       </c>
       <c r="D339" t="n">
-        <v>13.9209600293388</v>
+        <v>13.92096095421089</v>
       </c>
       <c r="E339" t="n">
-        <v>13.96912962559257</v>
+        <v>13.96913055366492</v>
       </c>
       <c r="F339" t="n">
         <v>11107300</v>
@@ -7252,16 +7252,16 @@
         <v>44753</v>
       </c>
       <c r="B342" t="n">
-        <v>14.78800964355469</v>
+        <v>14.788010597229</v>
       </c>
       <c r="C342" t="n">
-        <v>14.8939820177114</v>
+        <v>14.89398297821984</v>
       </c>
       <c r="D342" t="n">
-        <v>14.52789438140829</v>
+        <v>14.52789531830785</v>
       </c>
       <c r="E342" t="n">
-        <v>14.57606397648265</v>
+        <v>14.57606491648865</v>
       </c>
       <c r="F342" t="n">
         <v>3654100</v>
@@ -7312,16 +7312,16 @@
         <v>44756</v>
       </c>
       <c r="B345" t="n">
-        <v>14.75910758972168</v>
+        <v>14.75910663604736</v>
       </c>
       <c r="C345" t="n">
-        <v>14.99995465048742</v>
+        <v>14.99995368125053</v>
       </c>
       <c r="D345" t="n">
-        <v>14.51826052895594</v>
+        <v>14.5182595908442</v>
       </c>
       <c r="E345" t="n">
-        <v>14.52789463188864</v>
+        <v>14.52789369315438</v>
       </c>
       <c r="F345" t="n">
         <v>8175300</v>
@@ -7332,16 +7332,16 @@
         <v>44757</v>
       </c>
       <c r="B346" t="n">
-        <v>15.00958824157715</v>
+        <v>15.00958919525146</v>
       </c>
       <c r="C346" t="n">
-        <v>15.16373020820944</v>
+        <v>15.16373117167757</v>
       </c>
       <c r="D346" t="n">
-        <v>14.56642962813003</v>
+        <v>14.56643055364708</v>
       </c>
       <c r="E346" t="n">
-        <v>14.83617806973653</v>
+        <v>14.83617901239277</v>
       </c>
       <c r="F346" t="n">
         <v>3973400</v>
@@ -7352,16 +7352,16 @@
         <v>44760</v>
       </c>
       <c r="B347" t="n">
-        <v>14.87471294403076</v>
+        <v>14.87471389770508</v>
       </c>
       <c r="C347" t="n">
-        <v>15.19263188546311</v>
+        <v>15.19263285952041</v>
       </c>
       <c r="D347" t="n">
-        <v>14.8072760661177</v>
+        <v>14.80727701546838</v>
       </c>
       <c r="E347" t="n">
-        <v>15.0770244965285</v>
+        <v>15.07702546317377</v>
       </c>
       <c r="F347" t="n">
         <v>3805700</v>
@@ -7392,16 +7392,16 @@
         <v>44762</v>
       </c>
       <c r="B349" t="n">
-        <v>14.82654571533203</v>
+        <v>14.82654476165771</v>
       </c>
       <c r="C349" t="n">
-        <v>15.10592827517219</v>
+        <v>15.10592730352741</v>
       </c>
       <c r="D349" t="n">
-        <v>14.57606454616261</v>
+        <v>14.57606360859976</v>
       </c>
       <c r="E349" t="n">
-        <v>14.89398259981663</v>
+        <v>14.89398164180463</v>
       </c>
       <c r="F349" t="n">
         <v>5599700</v>
@@ -7412,16 +7412,16 @@
         <v>44763</v>
       </c>
       <c r="B350" t="n">
-        <v>14.84581279754639</v>
+        <v>14.84581184387207</v>
       </c>
       <c r="C350" t="n">
-        <v>14.95178609313791</v>
+        <v>14.95178513265602</v>
       </c>
       <c r="D350" t="n">
-        <v>14.60496573485093</v>
+        <v>14.6049647966483</v>
       </c>
       <c r="E350" t="n">
-        <v>14.74947452372338</v>
+        <v>14.7494735762377</v>
       </c>
       <c r="F350" t="n">
         <v>4662200</v>
@@ -7472,16 +7472,16 @@
         <v>44768</v>
       </c>
       <c r="B353" t="n">
-        <v>14.95178508758545</v>
+        <v>14.95178604125977</v>
       </c>
       <c r="C353" t="n">
-        <v>15.03848925256745</v>
+        <v>15.03849021177204</v>
       </c>
       <c r="D353" t="n">
-        <v>14.76874081774235</v>
+        <v>14.76874175974149</v>
       </c>
       <c r="E353" t="n">
-        <v>14.82654451315558</v>
+        <v>14.82654545884164</v>
       </c>
       <c r="F353" t="n">
         <v>3874000</v>
@@ -7632,16 +7632,16 @@
         <v>44778</v>
       </c>
       <c r="B361" t="n">
-        <v>16.40650367736816</v>
+        <v>16.40650177001953</v>
       </c>
       <c r="C361" t="n">
-        <v>16.57027976453278</v>
+        <v>16.57027783814425</v>
       </c>
       <c r="D361" t="n">
-        <v>16.10785197649791</v>
+        <v>16.10785010386923</v>
       </c>
       <c r="E361" t="n">
-        <v>16.26199396000374</v>
+        <v>16.26199206945518</v>
       </c>
       <c r="F361" t="n">
         <v>6244900</v>
@@ -7652,16 +7652,16 @@
         <v>44781</v>
       </c>
       <c r="B362" t="n">
-        <v>16.68588256835938</v>
+        <v>16.68588447570801</v>
       </c>
       <c r="C362" t="n">
-        <v>16.88819503663362</v>
+        <v>16.88819696710841</v>
       </c>
       <c r="D362" t="n">
-        <v>16.26199126520336</v>
+        <v>16.26199312409735</v>
       </c>
       <c r="E362" t="n">
-        <v>16.53174061039666</v>
+        <v>16.53174250012546</v>
       </c>
       <c r="F362" t="n">
         <v>10381400</v>
@@ -7672,16 +7672,16 @@
         <v>44782</v>
       </c>
       <c r="B363" t="n">
-        <v>16.61844825744629</v>
+        <v>16.61845016479492</v>
       </c>
       <c r="C363" t="n">
-        <v>16.87856354074092</v>
+        <v>16.87856547794376</v>
       </c>
       <c r="D363" t="n">
-        <v>16.51247495591499</v>
+        <v>16.51247685110075</v>
       </c>
       <c r="E363" t="n">
-        <v>16.65698467164581</v>
+        <v>16.65698658341738</v>
       </c>
       <c r="F363" t="n">
         <v>6314800</v>
@@ -7712,16 +7712,16 @@
         <v>44784</v>
       </c>
       <c r="B365" t="n">
-        <v>16.99416732788086</v>
+        <v>16.99416923522949</v>
       </c>
       <c r="C365" t="n">
-        <v>17.34098766927179</v>
+        <v>17.34098961554597</v>
       </c>
       <c r="D365" t="n">
-        <v>16.86892766988812</v>
+        <v>16.86892956318042</v>
       </c>
       <c r="E365" t="n">
-        <v>16.91709634507367</v>
+        <v>16.91709824377221</v>
       </c>
       <c r="F365" t="n">
         <v>8667500</v>
@@ -7732,16 +7732,16 @@
         <v>44785</v>
       </c>
       <c r="B366" t="n">
-        <v>17.34099006652832</v>
+        <v>17.34098815917969</v>
       </c>
       <c r="C366" t="n">
-        <v>17.64927404037492</v>
+        <v>17.6492720991179</v>
       </c>
       <c r="D366" t="n">
-        <v>17.06160656678144</v>
+        <v>17.06160469016241</v>
       </c>
       <c r="E366" t="n">
-        <v>17.16757987186025</v>
+        <v>17.16757798358513</v>
       </c>
       <c r="F366" t="n">
         <v>11729000</v>
@@ -7832,16 +7832,16 @@
         <v>44792</v>
       </c>
       <c r="B371" t="n">
-        <v>17.12904167175293</v>
+        <v>17.12904357910156</v>
       </c>
       <c r="C371" t="n">
-        <v>17.57219933106722</v>
+        <v>17.57220128776223</v>
       </c>
       <c r="D371" t="n">
-        <v>17.07123706074208</v>
+        <v>17.07123896165407</v>
       </c>
       <c r="E371" t="n">
-        <v>17.4565937840796</v>
+        <v>17.45659572790173</v>
       </c>
       <c r="F371" t="n">
         <v>7571900</v>
@@ -8012,16 +8012,16 @@
         <v>44805</v>
       </c>
       <c r="B380" t="n">
-        <v>18.08279800415039</v>
+        <v>18.08279609680176</v>
       </c>
       <c r="C380" t="n">
-        <v>18.24657408115321</v>
+        <v>18.2465721565297</v>
       </c>
       <c r="D380" t="n">
-        <v>17.71670943790068</v>
+        <v>17.71670756916656</v>
       </c>
       <c r="E380" t="n">
-        <v>17.81304863099362</v>
+        <v>17.81304675209778</v>
       </c>
       <c r="F380" t="n">
         <v>12942800</v>
@@ -8032,16 +8032,16 @@
         <v>44806</v>
       </c>
       <c r="B381" t="n">
-        <v>18.20803833007812</v>
+        <v>18.20803642272949</v>
       </c>
       <c r="C381" t="n">
-        <v>18.54522459938866</v>
+        <v>18.54522265671872</v>
       </c>
       <c r="D381" t="n">
-        <v>17.95755715394794</v>
+        <v>17.95755527283799</v>
       </c>
       <c r="E381" t="n">
-        <v>18.20803833007812</v>
+        <v>18.20803642272949</v>
       </c>
       <c r="F381" t="n">
         <v>12423600</v>
@@ -8052,16 +8052,16 @@
         <v>44809</v>
       </c>
       <c r="B382" t="n">
-        <v>18.73790168762207</v>
+        <v>18.7379035949707</v>
       </c>
       <c r="C382" t="n">
-        <v>18.91131002438889</v>
+        <v>18.91131194938891</v>
       </c>
       <c r="D382" t="n">
-        <v>18.12133197488807</v>
+        <v>18.12133381947549</v>
       </c>
       <c r="E382" t="n">
-        <v>18.39108133905402</v>
+        <v>18.39108321109948</v>
       </c>
       <c r="F382" t="n">
         <v>11861400</v>
@@ -8092,16 +8092,16 @@
         <v>44812</v>
       </c>
       <c r="B384" t="n">
-        <v>18.40071487426758</v>
+        <v>18.40071678161621</v>
       </c>
       <c r="C384" t="n">
-        <v>18.94984585088554</v>
+        <v>18.94984781515502</v>
       </c>
       <c r="D384" t="n">
-        <v>18.3429120971281</v>
+        <v>18.34291399848511</v>
       </c>
       <c r="E384" t="n">
-        <v>18.91130944111445</v>
+        <v>18.91131140138939</v>
       </c>
       <c r="F384" t="n">
         <v>6653400</v>
@@ -8172,16 +8172,16 @@
         <v>44818</v>
       </c>
       <c r="B388" t="n">
-        <v>17.70707511901855</v>
+        <v>17.70707321166992</v>
       </c>
       <c r="C388" t="n">
-        <v>17.8708511940252</v>
+        <v>17.87084926903514</v>
       </c>
       <c r="D388" t="n">
-        <v>17.36989070357892</v>
+        <v>17.3698888325507</v>
       </c>
       <c r="E388" t="n">
-        <v>17.44696168961044</v>
+        <v>17.44695981028038</v>
       </c>
       <c r="F388" t="n">
         <v>7347400</v>
@@ -8352,16 +8352,16 @@
         <v>44831</v>
       </c>
       <c r="B397" t="n">
-        <v>17.12904167175293</v>
+        <v>17.12904357910156</v>
       </c>
       <c r="C397" t="n">
-        <v>17.49512835390313</v>
+        <v>17.49513030201615</v>
       </c>
       <c r="D397" t="n">
-        <v>16.86892643475522</v>
+        <v>16.86892831313957</v>
       </c>
       <c r="E397" t="n">
-        <v>17.2542813205757</v>
+        <v>17.25428324186998</v>
       </c>
       <c r="F397" t="n">
         <v>9260100</v>
@@ -8512,16 +8512,16 @@
         <v>44841</v>
       </c>
       <c r="B405" t="n">
-        <v>17.49513053894043</v>
+        <v>17.49513244628906</v>
       </c>
       <c r="C405" t="n">
-        <v>17.68780892467357</v>
+        <v>17.68781085302832</v>
       </c>
       <c r="D405" t="n">
-        <v>17.32172035928406</v>
+        <v>17.32172224772722</v>
       </c>
       <c r="E405" t="n">
-        <v>17.44696186126578</v>
+        <v>17.44696376336298</v>
       </c>
       <c r="F405" t="n">
         <v>11897600</v>
@@ -8532,16 +8532,16 @@
         <v>44844</v>
       </c>
       <c r="B406" t="n">
-        <v>18.10206604003906</v>
+        <v>18.1020679473877</v>
       </c>
       <c r="C406" t="n">
-        <v>18.12133240846265</v>
+        <v>18.12133431784131</v>
       </c>
       <c r="D406" t="n">
-        <v>17.58183550473985</v>
+        <v>17.58183735727369</v>
       </c>
       <c r="E406" t="n">
-        <v>17.73597747723208</v>
+        <v>17.73597934600729</v>
       </c>
       <c r="F406" t="n">
         <v>7333800</v>
@@ -8592,16 +8592,16 @@
         <v>44848</v>
       </c>
       <c r="B409" t="n">
-        <v>18.39108085632324</v>
+        <v>18.39108276367188</v>
       </c>
       <c r="C409" t="n">
-        <v>18.94021183546421</v>
+        <v>18.9402137997635</v>
       </c>
       <c r="D409" t="n">
-        <v>18.29474166897004</v>
+        <v>18.29474356632728</v>
       </c>
       <c r="E409" t="n">
-        <v>18.80533807568002</v>
+        <v>18.80534002599148</v>
       </c>
       <c r="F409" t="n">
         <v>11391600</v>
@@ -8632,16 +8632,16 @@
         <v>44852</v>
       </c>
       <c r="B411" t="n">
-        <v>17.263916015625</v>
+        <v>17.26391792297363</v>
       </c>
       <c r="C411" t="n">
-        <v>19.16179004195282</v>
+        <v>19.16179215898201</v>
       </c>
       <c r="D411" t="n">
-        <v>17.263916015625</v>
+        <v>17.26391792297363</v>
       </c>
       <c r="E411" t="n">
-        <v>19.10398726647282</v>
+        <v>19.10398937711585</v>
       </c>
       <c r="F411" t="n">
         <v>33355700</v>
@@ -8712,16 +8712,16 @@
         <v>44858</v>
       </c>
       <c r="B415" t="n">
-        <v>18.00572776794434</v>
+        <v>18.0057258605957</v>
       </c>
       <c r="C415" t="n">
-        <v>18.36218040847837</v>
+        <v>18.36217846337067</v>
       </c>
       <c r="D415" t="n">
-        <v>17.54329998932035</v>
+        <v>17.54329813095674</v>
       </c>
       <c r="E415" t="n">
-        <v>17.91902267429717</v>
+        <v>17.91902077613322</v>
       </c>
       <c r="F415" t="n">
         <v>16227000</v>
@@ -8732,16 +8732,16 @@
         <v>44859</v>
       </c>
       <c r="B416" t="n">
-        <v>17.04233932495117</v>
+        <v>17.04233741760254</v>
       </c>
       <c r="C416" t="n">
-        <v>18.00572761270958</v>
+        <v>18.00572559754023</v>
       </c>
       <c r="D416" t="n">
-        <v>16.80149225301157</v>
+        <v>16.80149037261812</v>
       </c>
       <c r="E416" t="n">
-        <v>18.00572761270958</v>
+        <v>18.00572559754023</v>
       </c>
       <c r="F416" t="n">
         <v>27810400</v>
@@ -8752,16 +8752,16 @@
         <v>44860</v>
       </c>
       <c r="B417" t="n">
-        <v>16.45466995239258</v>
+        <v>16.45467185974121</v>
       </c>
       <c r="C417" t="n">
-        <v>17.07123779627069</v>
+        <v>17.07123977508899</v>
       </c>
       <c r="D417" t="n">
-        <v>16.36796486965758</v>
+        <v>16.36796676695576</v>
       </c>
       <c r="E417" t="n">
-        <v>17.0423373270371</v>
+        <v>17.0423393025054</v>
       </c>
       <c r="F417" t="n">
         <v>12823000</v>
@@ -8792,16 +8792,16 @@
         <v>44862</v>
       </c>
       <c r="B419" t="n">
-        <v>18.12133026123047</v>
+        <v>18.1213321685791</v>
       </c>
       <c r="C419" t="n">
-        <v>18.21766944200201</v>
+        <v>18.21767135949075</v>
       </c>
       <c r="D419" t="n">
-        <v>17.27354951297842</v>
+        <v>17.27355133109445</v>
       </c>
       <c r="E419" t="n">
-        <v>17.40842326354835</v>
+        <v>17.40842509586043</v>
       </c>
       <c r="F419" t="n">
         <v>12193800</v>
@@ -8932,16 +8932,16 @@
         <v>44874</v>
       </c>
       <c r="B426" t="n">
-        <v>19.65312004089355</v>
+        <v>19.65311813354492</v>
       </c>
       <c r="C426" t="n">
-        <v>20.09627959384678</v>
+        <v>20.09627764348921</v>
       </c>
       <c r="D426" t="n">
-        <v>19.1328913385332</v>
+        <v>19.13288948167312</v>
       </c>
       <c r="E426" t="n">
-        <v>19.1328913385332</v>
+        <v>19.13288948167312</v>
       </c>
       <c r="F426" t="n">
         <v>19633400</v>
@@ -9032,16 +9032,16 @@
         <v>44882</v>
       </c>
       <c r="B431" t="n">
-        <v>18.78607368469238</v>
+        <v>18.78607177734375</v>
       </c>
       <c r="C431" t="n">
-        <v>18.90168110049051</v>
+        <v>18.90167918140427</v>
       </c>
       <c r="D431" t="n">
-        <v>18.05389828468432</v>
+        <v>18.0538964516734</v>
       </c>
       <c r="E431" t="n">
-        <v>18.66083400196882</v>
+        <v>18.66083210733576</v>
       </c>
       <c r="F431" t="n">
         <v>10826800</v>
@@ -9232,16 +9232,16 @@
         <v>44896</v>
       </c>
       <c r="B441" t="n">
-        <v>18.95948219299316</v>
+        <v>18.95948028564453</v>
       </c>
       <c r="C441" t="n">
-        <v>19.08472186450934</v>
+        <v>19.08471994456143</v>
       </c>
       <c r="D441" t="n">
-        <v>18.41998525508773</v>
+        <v>18.41998340201319</v>
       </c>
       <c r="E441" t="n">
-        <v>19.0750877609285</v>
+        <v>19.0750858419498</v>
       </c>
       <c r="F441" t="n">
         <v>25518700</v>
@@ -9252,16 +9252,16 @@
         <v>44897</v>
       </c>
       <c r="B442" t="n">
-        <v>19.78799438476562</v>
+        <v>19.78799247741699</v>
       </c>
       <c r="C442" t="n">
-        <v>19.97103681859475</v>
+        <v>19.97103489360281</v>
       </c>
       <c r="D442" t="n">
-        <v>19.01728272713333</v>
+        <v>19.01728089407297</v>
       </c>
       <c r="E442" t="n">
-        <v>19.11362191402701</v>
+        <v>19.11362007168059</v>
       </c>
       <c r="F442" t="n">
         <v>24428900</v>
@@ -9352,16 +9352,16 @@
         <v>44904</v>
       </c>
       <c r="B447" t="n">
-        <v>18.57412528991699</v>
+        <v>18.57412719726562</v>
       </c>
       <c r="C447" t="n">
-        <v>18.7571677262095</v>
+        <v>18.75716965235448</v>
       </c>
       <c r="D447" t="n">
-        <v>18.25620725515131</v>
+        <v>18.25620912985342</v>
       </c>
       <c r="E447" t="n">
-        <v>18.57412528991699</v>
+        <v>18.57412719726562</v>
       </c>
       <c r="F447" t="n">
         <v>14833900</v>
@@ -9372,16 +9372,16 @@
         <v>44907</v>
       </c>
       <c r="B448" t="n">
-        <v>18.2562084197998</v>
+        <v>18.25621032714844</v>
       </c>
       <c r="C448" t="n">
-        <v>18.6704638316658</v>
+        <v>18.67046578229448</v>
       </c>
       <c r="D448" t="n">
-        <v>17.87085164245525</v>
+        <v>17.87085350954307</v>
       </c>
       <c r="E448" t="n">
-        <v>18.45851907414013</v>
+        <v>18.45852100262552</v>
       </c>
       <c r="F448" t="n">
         <v>10851800</v>
@@ -9392,16 +9392,16 @@
         <v>44908</v>
       </c>
       <c r="B449" t="n">
-        <v>17.94792175292969</v>
+        <v>17.94792366027832</v>
       </c>
       <c r="C449" t="n">
-        <v>18.52595505316863</v>
+        <v>18.5259570219456</v>
       </c>
       <c r="D449" t="n">
-        <v>17.89975307687528</v>
+        <v>17.89975497910497</v>
       </c>
       <c r="E449" t="n">
-        <v>18.52595505316863</v>
+        <v>18.5259570219456</v>
       </c>
       <c r="F449" t="n">
         <v>13648600</v>
@@ -9472,16 +9472,16 @@
         <v>44914</v>
       </c>
       <c r="B453" t="n">
-        <v>18.8342399597168</v>
+        <v>18.83424186706543</v>
       </c>
       <c r="C453" t="n">
-        <v>18.90167868218942</v>
+        <v>18.90168059636759</v>
       </c>
       <c r="D453" t="n">
-        <v>18.13096696301515</v>
+        <v>18.13096879914314</v>
       </c>
       <c r="E453" t="n">
-        <v>18.1502351694359</v>
+        <v>18.15023700751518</v>
       </c>
       <c r="F453" t="n">
         <v>7150400</v>
@@ -9652,16 +9652,16 @@
         <v>44928</v>
       </c>
       <c r="B462" t="n">
-        <v>18.32970237731934</v>
+        <v>18.32970428466797</v>
       </c>
       <c r="C462" t="n">
-        <v>18.50344392873929</v>
+        <v>18.50344585416709</v>
       </c>
       <c r="D462" t="n">
-        <v>17.90500101174039</v>
+        <v>17.90500287489553</v>
       </c>
       <c r="E462" t="n">
-        <v>18.33935489029029</v>
+        <v>18.33935679864334</v>
       </c>
       <c r="F462" t="n">
         <v>4837200</v>
@@ -9692,16 +9692,16 @@
         <v>44930</v>
       </c>
       <c r="B464" t="n">
-        <v>18.41657447814941</v>
+        <v>18.41657257080078</v>
       </c>
       <c r="C464" t="n">
-        <v>18.54205347374314</v>
+        <v>18.54205155339903</v>
       </c>
       <c r="D464" t="n">
-        <v>17.87604660008386</v>
+        <v>17.87604474871605</v>
       </c>
       <c r="E464" t="n">
-        <v>18.1752671595987</v>
+        <v>18.17526527724153</v>
       </c>
       <c r="F464" t="n">
         <v>9017200</v>
@@ -9732,16 +9732,16 @@
         <v>44932</v>
       </c>
       <c r="B466" t="n">
-        <v>18.37796592712402</v>
+        <v>18.37796401977539</v>
       </c>
       <c r="C466" t="n">
-        <v>18.85092804187709</v>
+        <v>18.85092608544231</v>
       </c>
       <c r="D466" t="n">
-        <v>18.20422436639255</v>
+        <v>18.2042224770756</v>
       </c>
       <c r="E466" t="n">
-        <v>18.33935587317094</v>
+        <v>18.33935396982943</v>
       </c>
       <c r="F466" t="n">
         <v>4999100</v>
@@ -9752,16 +9752,16 @@
         <v>44935</v>
       </c>
       <c r="B467" t="n">
-        <v>18.56135940551758</v>
+        <v>18.56135749816895</v>
       </c>
       <c r="C467" t="n">
-        <v>18.77371103444791</v>
+        <v>18.77370910527821</v>
       </c>
       <c r="D467" t="n">
-        <v>18.20422558763648</v>
+        <v>18.20422371698659</v>
       </c>
       <c r="E467" t="n">
-        <v>18.29109637383</v>
+        <v>18.29109449425335</v>
       </c>
       <c r="F467" t="n">
         <v>4878500</v>
@@ -9772,16 +9772,16 @@
         <v>44936</v>
       </c>
       <c r="B468" t="n">
-        <v>18.57101058959961</v>
+        <v>18.57101249694824</v>
       </c>
       <c r="C468" t="n">
-        <v>18.68683890990498</v>
+        <v>18.68684082914984</v>
       </c>
       <c r="D468" t="n">
-        <v>18.14630920318485</v>
+        <v>18.14631106691423</v>
       </c>
       <c r="E468" t="n">
-        <v>18.29109506382374</v>
+        <v>18.29109694242345</v>
       </c>
       <c r="F468" t="n">
         <v>7152400</v>
@@ -9992,16 +9992,16 @@
         <v>44951</v>
       </c>
       <c r="B479" t="n">
-        <v>20.37598991394043</v>
+        <v>20.37599182128906</v>
       </c>
       <c r="C479" t="n">
-        <v>20.6172972247506</v>
+        <v>20.61729915468745</v>
       </c>
       <c r="D479" t="n">
-        <v>20.12503008977441</v>
+        <v>20.12503197363128</v>
       </c>
       <c r="E479" t="n">
-        <v>20.57868717132721</v>
+        <v>20.57868909764986</v>
       </c>
       <c r="F479" t="n">
         <v>2807800</v>
@@ -10052,16 +10052,16 @@
         <v>44956</v>
       </c>
       <c r="B482" t="n">
-        <v>20.05746459960938</v>
+        <v>20.05746269226074</v>
       </c>
       <c r="C482" t="n">
-        <v>20.50146917361271</v>
+        <v>20.50146722404181</v>
       </c>
       <c r="D482" t="n">
-        <v>19.85476549854316</v>
+        <v>19.85476361047004</v>
       </c>
       <c r="E482" t="n">
-        <v>20.35668515343896</v>
+        <v>20.35668321763618</v>
       </c>
       <c r="F482" t="n">
         <v>14094800</v>
@@ -10152,16 +10152,16 @@
         <v>44963</v>
       </c>
       <c r="B487" t="n">
-        <v>18.55170631408691</v>
+        <v>18.55170440673828</v>
       </c>
       <c r="C487" t="n">
-        <v>18.66753463908353</v>
+        <v>18.66753271982629</v>
       </c>
       <c r="D487" t="n">
-        <v>18.24283323546763</v>
+        <v>18.24283135987503</v>
       </c>
       <c r="E487" t="n">
-        <v>18.45518485778996</v>
+        <v>18.45518296036495</v>
       </c>
       <c r="F487" t="n">
         <v>7136600</v>
@@ -10192,16 +10192,16 @@
         <v>44965</v>
       </c>
       <c r="B489" t="n">
-        <v>18.10770225524902</v>
+        <v>18.10770034790039</v>
       </c>
       <c r="C489" t="n">
-        <v>18.39727031469558</v>
+        <v>18.39726837684571</v>
       </c>
       <c r="D489" t="n">
-        <v>17.76987162520883</v>
+        <v>17.76986975344509</v>
       </c>
       <c r="E489" t="n">
-        <v>18.29109634144721</v>
+        <v>18.29109441478103</v>
       </c>
       <c r="F489" t="n">
         <v>14424900</v>
@@ -10212,16 +10212,16 @@
         <v>44966</v>
       </c>
       <c r="B490" t="n">
-        <v>17.87604904174805</v>
+        <v>17.87604713439941</v>
       </c>
       <c r="C490" t="n">
-        <v>18.04979062940028</v>
+        <v>18.04978870351367</v>
       </c>
       <c r="D490" t="n">
-        <v>17.69265493911191</v>
+        <v>17.69265305133117</v>
       </c>
       <c r="E490" t="n">
-        <v>17.91465726065466</v>
+        <v>17.91465534918659</v>
       </c>
       <c r="F490" t="n">
         <v>11653900</v>
@@ -10232,16 +10232,16 @@
         <v>44967</v>
       </c>
       <c r="B491" t="n">
-        <v>17.98221969604492</v>
+        <v>17.98222160339355</v>
       </c>
       <c r="C491" t="n">
-        <v>18.09804801338318</v>
+        <v>18.09804993301756</v>
       </c>
       <c r="D491" t="n">
-        <v>17.6250859128902</v>
+        <v>17.62508778235816</v>
       </c>
       <c r="E491" t="n">
-        <v>17.79882746838327</v>
+        <v>17.79882935627974</v>
       </c>
       <c r="F491" t="n">
         <v>6326900</v>
@@ -10272,16 +10272,16 @@
         <v>44971</v>
       </c>
       <c r="B493" t="n">
-        <v>17.80848121643066</v>
+        <v>17.80847930908203</v>
       </c>
       <c r="C493" t="n">
-        <v>18.11735429604525</v>
+        <v>18.11735235561527</v>
       </c>
       <c r="D493" t="n">
-        <v>17.71195791879391</v>
+        <v>17.71195602178325</v>
       </c>
       <c r="E493" t="n">
-        <v>18.0208309984085</v>
+        <v>18.02082906831649</v>
       </c>
       <c r="F493" t="n">
         <v>9612400</v>
@@ -10292,16 +10292,16 @@
         <v>44972</v>
       </c>
       <c r="B494" t="n">
-        <v>18.55170631408691</v>
+        <v>18.55170440673828</v>
       </c>
       <c r="C494" t="n">
-        <v>18.7737104502447</v>
+        <v>18.77370852007125</v>
       </c>
       <c r="D494" t="n">
-        <v>17.7602185898678</v>
+        <v>17.76021676389406</v>
       </c>
       <c r="E494" t="n">
-        <v>17.80848115904505</v>
+        <v>17.8084793281093</v>
       </c>
       <c r="F494" t="n">
         <v>12677500</v>
@@ -10312,16 +10312,16 @@
         <v>44973</v>
       </c>
       <c r="B495" t="n">
-        <v>18.3490104675293</v>
+        <v>18.34900856018066</v>
       </c>
       <c r="C495" t="n">
-        <v>18.55170775068378</v>
+        <v>18.5517058222651</v>
       </c>
       <c r="D495" t="n">
-        <v>17.88570081372285</v>
+        <v>17.88569895453448</v>
       </c>
       <c r="E495" t="n">
-        <v>18.43588125774662</v>
+        <v>18.43587934136792</v>
       </c>
       <c r="F495" t="n">
         <v>33990600</v>
@@ -10372,16 +10372,16 @@
         <v>44980</v>
       </c>
       <c r="B498" t="n">
-        <v>18.11735343933105</v>
+        <v>18.11735153198242</v>
       </c>
       <c r="C498" t="n">
-        <v>18.27178997183552</v>
+        <v>18.2717880482282</v>
       </c>
       <c r="D498" t="n">
-        <v>17.8470885869339</v>
+        <v>17.84708670803806</v>
       </c>
       <c r="E498" t="n">
-        <v>18.17526667876306</v>
+        <v>18.17526476531746</v>
       </c>
       <c r="F498" t="n">
         <v>5103300</v>
@@ -10392,16 +10392,16 @@
         <v>44981</v>
       </c>
       <c r="B499" t="n">
-        <v>18.04013633728027</v>
+        <v>18.04013442993164</v>
       </c>
       <c r="C499" t="n">
-        <v>18.16561533765205</v>
+        <v>18.16561341703677</v>
       </c>
       <c r="D499" t="n">
-        <v>17.82778471061123</v>
+        <v>17.82778282571412</v>
       </c>
       <c r="E499" t="n">
-        <v>18.10770209448268</v>
+        <v>18.10770017999045</v>
       </c>
       <c r="F499" t="n">
         <v>6522200</v>
@@ -10452,16 +10452,16 @@
         <v>44986</v>
       </c>
       <c r="B502" t="n">
-        <v>17.02664184570312</v>
+        <v>17.02664375305176</v>
       </c>
       <c r="C502" t="n">
-        <v>17.77952125559183</v>
+        <v>17.77952324727908</v>
       </c>
       <c r="D502" t="n">
-        <v>16.67916059893248</v>
+        <v>16.67916246735577</v>
       </c>
       <c r="E502" t="n">
-        <v>17.5092564271893</v>
+        <v>17.5092583886011</v>
       </c>
       <c r="F502" t="n">
         <v>19714300</v>
@@ -10652,16 +10652,16 @@
         <v>45000</v>
       </c>
       <c r="B512" t="n">
-        <v>16.15793800354004</v>
+        <v>16.15793609619141</v>
       </c>
       <c r="C512" t="n">
-        <v>16.43785537977234</v>
+        <v>16.43785343938112</v>
       </c>
       <c r="D512" t="n">
-        <v>15.6077576058738</v>
+        <v>15.6077557634707</v>
       </c>
       <c r="E512" t="n">
-        <v>15.7911516854388</v>
+        <v>15.79114982138712</v>
       </c>
       <c r="F512" t="n">
         <v>24755700</v>
@@ -10672,16 +10672,16 @@
         <v>45001</v>
       </c>
       <c r="B513" t="n">
-        <v>15.68497467041016</v>
+        <v>15.68497562408447</v>
       </c>
       <c r="C513" t="n">
-        <v>16.33167831507744</v>
+        <v>16.33167930807249</v>
       </c>
       <c r="D513" t="n">
-        <v>15.64636461829695</v>
+        <v>15.64636556962371</v>
       </c>
       <c r="E513" t="n">
-        <v>16.03245777531455</v>
+        <v>16.03245875011646</v>
       </c>
       <c r="F513" t="n">
         <v>11501700</v>
@@ -10712,16 +10712,16 @@
         <v>45005</v>
       </c>
       <c r="B515" t="n">
-        <v>15.49192810058594</v>
+        <v>15.49192905426025</v>
       </c>
       <c r="C515" t="n">
-        <v>15.59810390292816</v>
+        <v>15.5981048631386</v>
       </c>
       <c r="D515" t="n">
-        <v>15.31818746855065</v>
+        <v>15.31818841152959</v>
       </c>
       <c r="E515" t="n">
-        <v>15.44366737644599</v>
+        <v>15.4436683271494</v>
       </c>
       <c r="F515" t="n">
         <v>20828100</v>
@@ -10772,16 +10772,16 @@
         <v>45008</v>
       </c>
       <c r="B518" t="n">
-        <v>14.71974658966064</v>
+        <v>14.71974563598633</v>
       </c>
       <c r="C518" t="n">
-        <v>15.01896807290302</v>
+        <v>15.01896709984251</v>
       </c>
       <c r="D518" t="n">
-        <v>14.25643697491495</v>
+        <v>14.25643605125789</v>
       </c>
       <c r="E518" t="n">
-        <v>14.74870321045366</v>
+        <v>14.74870225490328</v>
       </c>
       <c r="F518" t="n">
         <v>25394300</v>
@@ -10792,16 +10792,16 @@
         <v>45009</v>
       </c>
       <c r="B519" t="n">
-        <v>14.43017768859863</v>
+        <v>14.43017673492432</v>
       </c>
       <c r="C519" t="n">
-        <v>14.95140146791577</v>
+        <v>14.95140047979436</v>
       </c>
       <c r="D519" t="n">
-        <v>14.01512972021653</v>
+        <v>14.01512879397227</v>
       </c>
       <c r="E519" t="n">
-        <v>14.74870328037497</v>
+        <v>14.74870230564966</v>
       </c>
       <c r="F519" t="n">
         <v>32819700</v>
@@ -10812,16 +10812,16 @@
         <v>45012</v>
       </c>
       <c r="B520" t="n">
-        <v>14.65218162536621</v>
+        <v>14.65218067169189</v>
       </c>
       <c r="C520" t="n">
-        <v>14.72939989865945</v>
+        <v>14.72939893995919</v>
       </c>
       <c r="D520" t="n">
-        <v>14.23713271602922</v>
+        <v>14.23713178936941</v>
       </c>
       <c r="E520" t="n">
-        <v>14.48809256448947</v>
+        <v>14.4880916214953</v>
       </c>
       <c r="F520" t="n">
         <v>14200700</v>
@@ -10852,16 +10852,16 @@
         <v>45014</v>
       </c>
       <c r="B522" t="n">
-        <v>14.89348697662354</v>
+        <v>14.89348793029785</v>
       </c>
       <c r="C522" t="n">
-        <v>14.96105272663084</v>
+        <v>14.96105368463159</v>
       </c>
       <c r="D522" t="n">
-        <v>14.4205239650295</v>
+        <v>14.42052488841858</v>
       </c>
       <c r="E522" t="n">
-        <v>14.84522533211219</v>
+        <v>14.84522628269617</v>
       </c>
       <c r="F522" t="n">
         <v>19793200</v>
@@ -10932,16 +10932,16 @@
         <v>45020</v>
       </c>
       <c r="B526" t="n">
-        <v>14.15991306304932</v>
+        <v>14.15991401672363</v>
       </c>
       <c r="C526" t="n">
-        <v>14.57496193194557</v>
+        <v>14.57496291357355</v>
       </c>
       <c r="D526" t="n">
-        <v>14.05373817774498</v>
+        <v>14.05373912426839</v>
       </c>
       <c r="E526" t="n">
-        <v>14.37226375417232</v>
+        <v>14.37226472214852</v>
       </c>
       <c r="F526" t="n">
         <v>12462300</v>
@@ -10972,16 +10972,16 @@
         <v>45022</v>
       </c>
       <c r="B528" t="n">
-        <v>13.1560754776001</v>
+        <v>13.15607452392578</v>
       </c>
       <c r="C528" t="n">
-        <v>13.57112437142145</v>
+        <v>13.57112338766055</v>
       </c>
       <c r="D528" t="n">
-        <v>13.00163893678686</v>
+        <v>13.00163799430754</v>
       </c>
       <c r="E528" t="n">
-        <v>13.33946863968721</v>
+        <v>13.33946767271886</v>
       </c>
       <c r="F528" t="n">
         <v>26117400</v>
@@ -11012,16 +11012,16 @@
         <v>45027</v>
       </c>
       <c r="B530" t="n">
-        <v>14.19852256774902</v>
+        <v>14.19852161407471</v>
       </c>
       <c r="C530" t="n">
-        <v>14.3240024830388</v>
+        <v>14.32400152093636</v>
       </c>
       <c r="D530" t="n">
-        <v>13.51320975071368</v>
+        <v>13.51320884306988</v>
       </c>
       <c r="E530" t="n">
-        <v>13.52286226431621</v>
+        <v>13.52286135602407</v>
       </c>
       <c r="F530" t="n">
         <v>23105700</v>
@@ -11052,16 +11052,16 @@
         <v>45029</v>
       </c>
       <c r="B532" t="n">
-        <v>13.27190208435059</v>
+        <v>13.2719030380249</v>
       </c>
       <c r="C532" t="n">
-        <v>14.14060803439325</v>
+        <v>14.14060905048986</v>
       </c>
       <c r="D532" t="n">
-        <v>13.27190208435059</v>
+        <v>13.2719030380249</v>
       </c>
       <c r="E532" t="n">
-        <v>14.09234730867981</v>
+        <v>14.09234832130857</v>
       </c>
       <c r="F532" t="n">
         <v>20136100</v>
@@ -11112,16 +11112,16 @@
         <v>45034</v>
       </c>
       <c r="B535" t="n">
-        <v>12.70241737365723</v>
+        <v>12.70241641998291</v>
       </c>
       <c r="C535" t="n">
-        <v>12.95337721125578</v>
+        <v>12.95337623873985</v>
       </c>
       <c r="D535" t="n">
-        <v>12.61554658983354</v>
+        <v>12.61554564268133</v>
       </c>
       <c r="E535" t="n">
-        <v>12.87615894130459</v>
+        <v>12.87615797458607</v>
       </c>
       <c r="F535" t="n">
         <v>12417000</v>
@@ -27509,162 +27509,142 @@
     </row>
     <row r="1355">
       <c r="A1355" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B1355" t="n">
-        <v>8.5</v>
+        <v>8.550000190734863</v>
       </c>
       <c r="C1355" t="n">
-        <v>8.510000228881836</v>
+        <v>8.680000305175781</v>
       </c>
       <c r="D1355" t="n">
-        <v>8.340000152587891</v>
+        <v>8.439999580383301</v>
       </c>
       <c r="E1355" t="n">
-        <v>8.510000228881836</v>
+        <v>8.600000381469727</v>
       </c>
       <c r="F1355" t="n">
-        <v>3774300</v>
+        <v>5991300</v>
       </c>
     </row>
     <row r="1356">
       <c r="A1356" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B1356" t="n">
-        <v>8.550000190734863</v>
+        <v>8.659999847412109</v>
       </c>
       <c r="C1356" t="n">
-        <v>8.680000305175781</v>
+        <v>8.770000457763672</v>
       </c>
       <c r="D1356" t="n">
-        <v>8.439999580383301</v>
+        <v>8.590000152587891</v>
       </c>
       <c r="E1356" t="n">
-        <v>8.600000381469727</v>
+        <v>8.729999542236328</v>
       </c>
       <c r="F1356" t="n">
-        <v>5991300</v>
+        <v>5728800</v>
       </c>
     </row>
     <row r="1357">
       <c r="A1357" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B1357" t="n">
-        <v>8.659999847412109</v>
+        <v>8.829999923706055</v>
       </c>
       <c r="C1357" t="n">
-        <v>8.770000457763672</v>
+        <v>8.909999847412109</v>
       </c>
       <c r="D1357" t="n">
-        <v>8.590000152587891</v>
+        <v>8.670000076293945</v>
       </c>
       <c r="E1357" t="n">
-        <v>8.729999542236328</v>
+        <v>8.710000038146973</v>
       </c>
       <c r="F1357" t="n">
-        <v>5728800</v>
+        <v>8653300</v>
       </c>
     </row>
     <row r="1358">
       <c r="A1358" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B1358" t="n">
-        <v>8.829999923706055</v>
+        <v>8.489999771118164</v>
       </c>
       <c r="C1358" t="n">
-        <v>8.909999847412109</v>
+        <v>8.869999885559082</v>
       </c>
       <c r="D1358" t="n">
-        <v>8.670000076293945</v>
+        <v>8.489999771118164</v>
       </c>
       <c r="E1358" t="n">
-        <v>8.710000038146973</v>
+        <v>8.739999771118164</v>
       </c>
       <c r="F1358" t="n">
-        <v>8653300</v>
+        <v>9598300</v>
       </c>
     </row>
     <row r="1359">
       <c r="A1359" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B1359" t="n">
-        <v>8.489999771118164</v>
+        <v>8.239999771118164</v>
       </c>
       <c r="C1359" t="n">
-        <v>8.869999885559082</v>
+        <v>8.630000114440918</v>
       </c>
       <c r="D1359" t="n">
-        <v>8.489999771118164</v>
+        <v>7.929999828338623</v>
       </c>
       <c r="E1359" t="n">
-        <v>8.739999771118164</v>
+        <v>8.619999885559082</v>
       </c>
       <c r="F1359" t="n">
-        <v>9598300</v>
+        <v>15405900</v>
       </c>
     </row>
     <row r="1360">
       <c r="A1360" s="1" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B1360" t="n">
-        <v>8.239999771118164</v>
+        <v>8.079999923706055</v>
       </c>
       <c r="C1360" t="n">
-        <v>8.630000114440918</v>
+        <v>8.189999580383301</v>
       </c>
       <c r="D1360" t="n">
-        <v>7.929999828338623</v>
+        <v>7.949999809265137</v>
       </c>
       <c r="E1360" t="n">
-        <v>8.619999885559082</v>
+        <v>8.060000419616699</v>
       </c>
       <c r="F1360" t="n">
-        <v>15405900</v>
+        <v>14248700</v>
       </c>
     </row>
     <row r="1361">
       <c r="A1361" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B1361" t="n">
-        <v>8.060000419616699</v>
+        <v>8</v>
       </c>
       <c r="C1361" t="n">
-        <v>8.229999542236328</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D1361" t="n">
-        <v>7.960000038146973</v>
+        <v>7.95</v>
       </c>
       <c r="E1361" t="n">
-        <v>8.229999542236328</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="F1361" t="n">
-        <v>10741500</v>
-      </c>
-    </row>
-    <row r="1362">
-      <c r="A1362" s="1" t="n">
-        <v>46245</v>
-      </c>
-      <c r="B1362" t="n">
-        <v>8.08</v>
-      </c>
-      <c r="C1362" t="n">
-        <v>8.19</v>
-      </c>
-      <c r="D1362" t="n">
-        <v>7.95</v>
-      </c>
-      <c r="E1362" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="F1362" t="n">
-        <v>14248700</v>
+        <v>8426200</v>
       </c>
     </row>
   </sheetData>

--- a/database/ASAI3.xlsx
+++ b/database/ASAI3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1361"/>
+  <dimension ref="A1:F1362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44256</v>
       </c>
       <c r="B2" t="n">
-        <v>13.55914783477783</v>
+        <v>13.55914878845215</v>
       </c>
       <c r="C2" t="n">
-        <v>14.43840408118833</v>
+        <v>14.43840509670459</v>
       </c>
       <c r="D2" t="n">
-        <v>13.17554232187502</v>
+        <v>13.17554324856868</v>
       </c>
       <c r="E2" t="n">
-        <v>13.67498995526467</v>
+        <v>13.67499091708668</v>
       </c>
       <c r="F2" t="n">
         <v>64088000</v>
@@ -472,16 +472,16 @@
         <v>44257</v>
       </c>
       <c r="B3" t="n">
-        <v>13.76804447174072</v>
+        <v>13.76804256439209</v>
       </c>
       <c r="C3" t="n">
-        <v>14.05290074536612</v>
+        <v>14.05289879855508</v>
       </c>
       <c r="D3" t="n">
-        <v>13.00463023796586</v>
+        <v>13.0046284363764</v>
       </c>
       <c r="E3" t="n">
-        <v>13.37114477274755</v>
+        <v>13.3711429203832</v>
       </c>
       <c r="F3" t="n">
         <v>14717000</v>
@@ -492,16 +492,16 @@
         <v>44258</v>
       </c>
       <c r="B4" t="n">
-        <v>13.54015827178955</v>
+        <v>13.54015922546387</v>
       </c>
       <c r="C4" t="n">
-        <v>13.82881231846659</v>
+        <v>13.82881329247169</v>
       </c>
       <c r="D4" t="n">
-        <v>13.17934048705999</v>
+        <v>13.17934141532082</v>
       </c>
       <c r="E4" t="n">
-        <v>13.63321084572767</v>
+        <v>13.63321180595596</v>
       </c>
       <c r="F4" t="n">
         <v>17545000</v>
@@ -512,16 +512,16 @@
         <v>44259</v>
       </c>
       <c r="B5" t="n">
-        <v>13.90097713470459</v>
+        <v>13.90097618103027</v>
       </c>
       <c r="C5" t="n">
-        <v>14.04340481356423</v>
+        <v>14.04340385011868</v>
       </c>
       <c r="D5" t="n">
-        <v>13.44330802948757</v>
+        <v>13.44330710721157</v>
       </c>
       <c r="E5" t="n">
-        <v>13.53256280482981</v>
+        <v>13.53256187643049</v>
       </c>
       <c r="F5" t="n">
         <v>12300000</v>
@@ -532,16 +532,16 @@
         <v>44260</v>
       </c>
       <c r="B6" t="n">
-        <v>14.2428035736084</v>
+        <v>14.24280452728271</v>
       </c>
       <c r="C6" t="n">
-        <v>14.90746755927018</v>
+        <v>14.90746855744928</v>
       </c>
       <c r="D6" t="n">
-        <v>13.67309106845084</v>
+        <v>13.67309198397816</v>
       </c>
       <c r="E6" t="n">
-        <v>13.76994235732357</v>
+        <v>13.76994327933589</v>
       </c>
       <c r="F6" t="n">
         <v>18499500</v>
@@ -552,16 +552,16 @@
         <v>44263</v>
       </c>
       <c r="B7" t="n">
-        <v>13.48508548736572</v>
+        <v>13.48508644104004</v>
       </c>
       <c r="C7" t="n">
-        <v>14.29787472337838</v>
+        <v>14.2978757345337</v>
       </c>
       <c r="D7" t="n">
-        <v>13.05210487258059</v>
+        <v>13.05210579563423</v>
       </c>
       <c r="E7" t="n">
-        <v>14.21051885821534</v>
+        <v>14.21051986319279</v>
       </c>
       <c r="F7" t="n">
         <v>12366000</v>
@@ -652,16 +652,16 @@
         <v>44270</v>
       </c>
       <c r="B12" t="n">
-        <v>13.83450794219971</v>
+        <v>13.83450889587402</v>
       </c>
       <c r="C12" t="n">
-        <v>14.01681617579842</v>
+        <v>14.01681714204006</v>
       </c>
       <c r="D12" t="n">
-        <v>13.62181545576768</v>
+        <v>13.62181639478016</v>
       </c>
       <c r="E12" t="n">
-        <v>13.81931581578305</v>
+        <v>13.81931676841011</v>
       </c>
       <c r="F12" t="n">
         <v>11593000</v>
@@ -732,16 +732,16 @@
         <v>44274</v>
       </c>
       <c r="B16" t="n">
-        <v>13.54775524139404</v>
+        <v>13.54775428771973</v>
       </c>
       <c r="C16" t="n">
-        <v>14.03580861527059</v>
+        <v>14.03580762724047</v>
       </c>
       <c r="D16" t="n">
-        <v>13.46419807840647</v>
+        <v>13.46419713061404</v>
       </c>
       <c r="E16" t="n">
-        <v>13.95415035523277</v>
+        <v>13.95414937295086</v>
       </c>
       <c r="F16" t="n">
         <v>14098000</v>
@@ -772,16 +772,16 @@
         <v>44278</v>
       </c>
       <c r="B18" t="n">
-        <v>13.44140911102295</v>
+        <v>13.44140815734863</v>
       </c>
       <c r="C18" t="n">
-        <v>13.44140911102295</v>
+        <v>13.44140815734863</v>
       </c>
       <c r="D18" t="n">
-        <v>13.01982187811874</v>
+        <v>13.01982095435623</v>
       </c>
       <c r="E18" t="n">
-        <v>13.29328381808184</v>
+        <v>13.29328287491709</v>
       </c>
       <c r="F18" t="n">
         <v>7916000</v>
@@ -792,16 +792,16 @@
         <v>44279</v>
       </c>
       <c r="B19" t="n">
-        <v>13.00842761993408</v>
+        <v>13.00842666625977</v>
       </c>
       <c r="C19" t="n">
-        <v>13.4717934356419</v>
+        <v>13.4717924479973</v>
       </c>
       <c r="D19" t="n">
-        <v>12.86599994053009</v>
+        <v>12.86599899729744</v>
       </c>
       <c r="E19" t="n">
-        <v>13.31417362739389</v>
+        <v>13.31417265130471</v>
       </c>
       <c r="F19" t="n">
         <v>12174500</v>
@@ -812,16 +812,16 @@
         <v>44280</v>
       </c>
       <c r="B20" t="n">
-        <v>13.64840316772461</v>
+        <v>13.64840221405029</v>
       </c>
       <c r="C20" t="n">
-        <v>13.67309071501351</v>
+        <v>13.67308975961416</v>
       </c>
       <c r="D20" t="n">
-        <v>12.83941262661621</v>
+        <v>12.83941172946964</v>
       </c>
       <c r="E20" t="n">
-        <v>12.9134752684829</v>
+        <v>12.91347436616125</v>
       </c>
       <c r="F20" t="n">
         <v>6602000</v>
@@ -892,16 +892,16 @@
         <v>44286</v>
       </c>
       <c r="B24" t="n">
-        <v>14.02251434326172</v>
+        <v>14.02251529693604</v>
       </c>
       <c r="C24" t="n">
-        <v>14.04150518240905</v>
+        <v>14.04150613737493</v>
       </c>
       <c r="D24" t="n">
-        <v>13.67499067998287</v>
+        <v>13.67499161002203</v>
       </c>
       <c r="E24" t="n">
-        <v>13.96744253969395</v>
+        <v>13.96744348962283</v>
       </c>
       <c r="F24" t="n">
         <v>3663000</v>
@@ -932,16 +932,16 @@
         <v>44291</v>
       </c>
       <c r="B26" t="n">
-        <v>14.71756267547607</v>
+        <v>14.71756362915039</v>
       </c>
       <c r="C26" t="n">
-        <v>14.88657769361247</v>
+        <v>14.88657865823869</v>
       </c>
       <c r="D26" t="n">
-        <v>14.2997741979616</v>
+        <v>14.29977512456389</v>
       </c>
       <c r="E26" t="n">
-        <v>14.2997741979616</v>
+        <v>14.29977512456389</v>
       </c>
       <c r="F26" t="n">
         <v>6073500</v>
@@ -992,16 +992,16 @@
         <v>44294</v>
       </c>
       <c r="B29" t="n">
-        <v>14.70237255096436</v>
+        <v>14.70237159729004</v>
       </c>
       <c r="C29" t="n">
-        <v>14.74035332682097</v>
+        <v>14.74035237068301</v>
       </c>
       <c r="D29" t="n">
-        <v>14.26559317584676</v>
+        <v>14.26559225050429</v>
       </c>
       <c r="E29" t="n">
-        <v>14.43270840850923</v>
+        <v>14.43270747232676</v>
       </c>
       <c r="F29" t="n">
         <v>6395000</v>
@@ -1012,16 +1012,16 @@
         <v>44295</v>
       </c>
       <c r="B30" t="n">
-        <v>14.71756267547607</v>
+        <v>14.71756362915039</v>
       </c>
       <c r="C30" t="n">
-        <v>14.73655351358414</v>
+        <v>14.73655446848903</v>
       </c>
       <c r="D30" t="n">
-        <v>14.40801889636538</v>
+        <v>14.40801982998176</v>
       </c>
       <c r="E30" t="n">
-        <v>14.63210571505577</v>
+        <v>14.63210666319261</v>
       </c>
       <c r="F30" t="n">
         <v>7012500</v>
@@ -1032,16 +1032,16 @@
         <v>44298</v>
       </c>
       <c r="B31" t="n">
-        <v>14.69857311248779</v>
+        <v>14.69857215881348</v>
       </c>
       <c r="C31" t="n">
-        <v>14.8011220172082</v>
+        <v>14.8011210568803</v>
       </c>
       <c r="D31" t="n">
-        <v>14.52766008235327</v>
+        <v>14.52765913976815</v>
       </c>
       <c r="E31" t="n">
-        <v>14.69857311248779</v>
+        <v>14.69857215881348</v>
       </c>
       <c r="F31" t="n">
         <v>4711000</v>
@@ -1072,16 +1072,16 @@
         <v>44300</v>
       </c>
       <c r="B33" t="n">
-        <v>14.93785381317139</v>
+        <v>14.93785285949707</v>
       </c>
       <c r="C33" t="n">
-        <v>14.94544942506844</v>
+        <v>14.9454484709092</v>
       </c>
       <c r="D33" t="n">
-        <v>14.62261237558245</v>
+        <v>14.62261144203403</v>
       </c>
       <c r="E33" t="n">
-        <v>14.65109863679578</v>
+        <v>14.65109770142871</v>
       </c>
       <c r="F33" t="n">
         <v>5841000</v>
@@ -1092,16 +1092,16 @@
         <v>44301</v>
       </c>
       <c r="B34" t="n">
-        <v>15.18662738800049</v>
+        <v>15.18662643432617</v>
       </c>
       <c r="C34" t="n">
-        <v>15.20371751383992</v>
+        <v>15.2037165590924</v>
       </c>
       <c r="D34" t="n">
-        <v>14.84100171054341</v>
+        <v>14.84100077857334</v>
       </c>
       <c r="E34" t="n">
-        <v>14.84100171054341</v>
+        <v>14.84100077857334</v>
       </c>
       <c r="F34" t="n">
         <v>11554500</v>
@@ -1112,16 +1112,16 @@
         <v>44302</v>
       </c>
       <c r="B35" t="n">
-        <v>15.14484882354736</v>
+        <v>15.14484786987305</v>
       </c>
       <c r="C35" t="n">
-        <v>15.72785369492901</v>
+        <v>15.72785270454275</v>
       </c>
       <c r="D35" t="n">
-        <v>15.0005222357084</v>
+        <v>15.00052129112236</v>
       </c>
       <c r="E35" t="n">
-        <v>15.72785369492901</v>
+        <v>15.72785270454275</v>
       </c>
       <c r="F35" t="n">
         <v>13035000</v>
@@ -1132,16 +1132,16 @@
         <v>44305</v>
       </c>
       <c r="B36" t="n">
-        <v>15.28727531433105</v>
+        <v>15.28727436065674</v>
       </c>
       <c r="C36" t="n">
-        <v>15.50756433010704</v>
+        <v>15.50756336269031</v>
       </c>
       <c r="D36" t="n">
-        <v>15.00431798094175</v>
+        <v>15.00431704491931</v>
       </c>
       <c r="E36" t="n">
-        <v>15.14484674350704</v>
+        <v>15.14484579871793</v>
       </c>
       <c r="F36" t="n">
         <v>5017000</v>
@@ -1152,16 +1152,16 @@
         <v>44306</v>
       </c>
       <c r="B37" t="n">
-        <v>15.47718143463135</v>
+        <v>15.4771785736084</v>
       </c>
       <c r="C37" t="n">
-        <v>15.65569281594117</v>
+        <v>15.65568992191963</v>
       </c>
       <c r="D37" t="n">
-        <v>15.06698938480104</v>
+        <v>15.06698659960384</v>
       </c>
       <c r="E37" t="n">
-        <v>15.35944219725644</v>
+        <v>15.35943935799809</v>
       </c>
       <c r="F37" t="n">
         <v>6029000</v>
@@ -1172,16 +1172,16 @@
         <v>44308</v>
       </c>
       <c r="B38" t="n">
-        <v>15.27967929840088</v>
+        <v>15.27967834472656</v>
       </c>
       <c r="C38" t="n">
-        <v>15.75254143640172</v>
+        <v>15.75254045321392</v>
       </c>
       <c r="D38" t="n">
-        <v>15.1942241402155</v>
+        <v>15.19422319187483</v>
       </c>
       <c r="E38" t="n">
-        <v>15.50376614024878</v>
+        <v>15.50376517258819</v>
       </c>
       <c r="F38" t="n">
         <v>8470500</v>
@@ -1192,16 +1192,16 @@
         <v>44309</v>
       </c>
       <c r="B39" t="n">
-        <v>15.41261196136475</v>
+        <v>15.41261291503906</v>
       </c>
       <c r="C39" t="n">
-        <v>15.53794859668741</v>
+        <v>15.53794955811708</v>
       </c>
       <c r="D39" t="n">
-        <v>15.21890939466627</v>
+        <v>15.218910336355</v>
       </c>
       <c r="E39" t="n">
-        <v>15.45818924894863</v>
+        <v>15.45819020544309</v>
       </c>
       <c r="F39" t="n">
         <v>4653000</v>
@@ -1252,16 +1252,16 @@
         <v>44314</v>
       </c>
       <c r="B42" t="n">
-        <v>15.18852615356445</v>
+        <v>15.18852710723877</v>
       </c>
       <c r="C42" t="n">
-        <v>15.35564228216909</v>
+        <v>15.35564324633648</v>
       </c>
       <c r="D42" t="n">
-        <v>15.04799647598031</v>
+        <v>15.04799742083089</v>
       </c>
       <c r="E42" t="n">
-        <v>15.14864647703371</v>
+        <v>15.14864742820402</v>
       </c>
       <c r="F42" t="n">
         <v>5371500</v>
@@ -1272,16 +1272,16 @@
         <v>44315</v>
       </c>
       <c r="B43" t="n">
-        <v>15.21646499633789</v>
+        <v>15.21646595001221</v>
       </c>
       <c r="C43" t="n">
-        <v>15.32323336252505</v>
+        <v>15.32323432289095</v>
       </c>
       <c r="D43" t="n">
-        <v>14.90950503441863</v>
+        <v>14.90950596885459</v>
       </c>
       <c r="E43" t="n">
-        <v>15.26222338706449</v>
+        <v>15.26222434360666</v>
       </c>
       <c r="F43" t="n">
         <v>5343000</v>
@@ -1292,16 +1292,16 @@
         <v>44316</v>
       </c>
       <c r="B44" t="n">
-        <v>15.42237663269043</v>
+        <v>15.42237567901611</v>
       </c>
       <c r="C44" t="n">
-        <v>15.46813502548309</v>
+        <v>15.46813406897922</v>
       </c>
       <c r="D44" t="n">
-        <v>14.92857109851635</v>
+        <v>14.92857017537751</v>
       </c>
       <c r="E44" t="n">
-        <v>15.10016416235762</v>
+        <v>15.10016322860797</v>
       </c>
       <c r="F44" t="n">
         <v>22683000</v>
@@ -1332,16 +1332,16 @@
         <v>44320</v>
       </c>
       <c r="B46" t="n">
-        <v>15.72933769226074</v>
+        <v>15.72933578491211</v>
       </c>
       <c r="C46" t="n">
-        <v>15.74840399251314</v>
+        <v>15.74840208285252</v>
       </c>
       <c r="D46" t="n">
-        <v>15.35945946771906</v>
+        <v>15.35945760522207</v>
       </c>
       <c r="E46" t="n">
-        <v>15.63400800926121</v>
+        <v>15.63400611347231</v>
       </c>
       <c r="F46" t="n">
         <v>9407500</v>
@@ -1352,16 +1352,16 @@
         <v>44321</v>
       </c>
       <c r="B47" t="n">
-        <v>16.32228660583496</v>
+        <v>16.32228469848633</v>
       </c>
       <c r="C47" t="n">
-        <v>16.58730201015107</v>
+        <v>16.58730007183393</v>
       </c>
       <c r="D47" t="n">
-        <v>16.01532570257429</v>
+        <v>16.01532383109572</v>
       </c>
       <c r="E47" t="n">
-        <v>16.08396329586652</v>
+        <v>16.08396141636727</v>
       </c>
       <c r="F47" t="n">
         <v>17262500</v>
@@ -1372,16 +1372,16 @@
         <v>44322</v>
       </c>
       <c r="B48" t="n">
-        <v>16.61971282958984</v>
+        <v>16.61971092224121</v>
       </c>
       <c r="C48" t="n">
-        <v>16.64449756423438</v>
+        <v>16.64449565404135</v>
       </c>
       <c r="D48" t="n">
-        <v>16.16022519568053</v>
+        <v>16.16022334106464</v>
       </c>
       <c r="E48" t="n">
-        <v>16.31847220804819</v>
+        <v>16.31847033527121</v>
       </c>
       <c r="F48" t="n">
         <v>9404500</v>
@@ -1412,16 +1412,16 @@
         <v>44326</v>
       </c>
       <c r="B50" t="n">
-        <v>16.81418609619141</v>
+        <v>16.81418418884277</v>
       </c>
       <c r="C50" t="n">
-        <v>17.0162841548014</v>
+        <v>17.01628222452739</v>
       </c>
       <c r="D50" t="n">
-        <v>16.55298359675715</v>
+        <v>16.55298171903851</v>
       </c>
       <c r="E50" t="n">
-        <v>16.97052576072697</v>
+        <v>16.97052383564365</v>
       </c>
       <c r="F50" t="n">
         <v>7669500</v>
@@ -1432,16 +1432,16 @@
         <v>44327</v>
       </c>
       <c r="B51" t="n">
-        <v>16.58729934692383</v>
+        <v>16.5872974395752</v>
       </c>
       <c r="C51" t="n">
-        <v>16.78367894467991</v>
+        <v>16.78367701474988</v>
       </c>
       <c r="D51" t="n">
-        <v>16.4919696745899</v>
+        <v>16.49196777820309</v>
       </c>
       <c r="E51" t="n">
-        <v>16.6254319431623</v>
+        <v>16.62543003142886</v>
       </c>
       <c r="F51" t="n">
         <v>6191000</v>
@@ -1452,16 +1452,16 @@
         <v>44328</v>
       </c>
       <c r="B52" t="n">
-        <v>16.12590599060059</v>
+        <v>16.12590789794922</v>
       </c>
       <c r="C52" t="n">
-        <v>16.57776597677424</v>
+        <v>16.57776793756821</v>
       </c>
       <c r="D52" t="n">
-        <v>16.04201500729966</v>
+        <v>16.04201690472579</v>
       </c>
       <c r="E52" t="n">
-        <v>16.49006391581501</v>
+        <v>16.49006586623571</v>
       </c>
       <c r="F52" t="n">
         <v>6728500</v>
@@ -1472,16 +1472,16 @@
         <v>44329</v>
       </c>
       <c r="B53" t="n">
-        <v>16.43287086486816</v>
+        <v>16.4328670501709</v>
       </c>
       <c r="C53" t="n">
-        <v>16.518665589747</v>
+        <v>16.5186617551335</v>
       </c>
       <c r="D53" t="n">
-        <v>16.12781547910792</v>
+        <v>16.12781173522566</v>
       </c>
       <c r="E53" t="n">
-        <v>16.17548123544359</v>
+        <v>16.17547748049629</v>
       </c>
       <c r="F53" t="n">
         <v>6595000</v>
@@ -1492,16 +1492,16 @@
         <v>44330</v>
       </c>
       <c r="B54" t="n">
-        <v>16.52629089355469</v>
+        <v>16.52628898620605</v>
       </c>
       <c r="C54" t="n">
-        <v>16.66356425245107</v>
+        <v>16.66356232925931</v>
       </c>
       <c r="D54" t="n">
-        <v>16.13734637653381</v>
+        <v>16.13734451407442</v>
       </c>
       <c r="E54" t="n">
-        <v>16.54726273245572</v>
+        <v>16.54726082268666</v>
       </c>
       <c r="F54" t="n">
         <v>5923000</v>
@@ -1512,16 +1512,16 @@
         <v>44333</v>
       </c>
       <c r="B55" t="n">
-        <v>16.34707069396973</v>
+        <v>16.34707260131836</v>
       </c>
       <c r="C55" t="n">
-        <v>16.52819507306194</v>
+        <v>16.52819700154386</v>
       </c>
       <c r="D55" t="n">
-        <v>16.06108167421069</v>
+        <v>16.06108354819061</v>
       </c>
       <c r="E55" t="n">
-        <v>16.50531587875072</v>
+        <v>16.50531780456314</v>
       </c>
       <c r="F55" t="n">
         <v>4728000</v>
@@ -1552,16 +1552,16 @@
         <v>44335</v>
       </c>
       <c r="B57" t="n">
-        <v>15.82848072052002</v>
+        <v>15.82847690582275</v>
       </c>
       <c r="C57" t="n">
-        <v>16.36804466877901</v>
+        <v>16.3680407240457</v>
       </c>
       <c r="D57" t="n">
-        <v>15.67595395070043</v>
+        <v>15.67595017276244</v>
       </c>
       <c r="E57" t="n">
-        <v>15.98482038684572</v>
+        <v>15.98481653447027</v>
       </c>
       <c r="F57" t="n">
         <v>6358000</v>
@@ -1572,16 +1572,16 @@
         <v>44336</v>
       </c>
       <c r="B58" t="n">
-        <v>16.03248596191406</v>
+        <v>16.03248405456543</v>
       </c>
       <c r="C58" t="n">
-        <v>16.03248596191406</v>
+        <v>16.03248405456543</v>
       </c>
       <c r="D58" t="n">
-        <v>15.69692561740377</v>
+        <v>15.69692374997599</v>
       </c>
       <c r="E58" t="n">
-        <v>15.90283657256179</v>
+        <v>15.90283468063725</v>
       </c>
       <c r="F58" t="n">
         <v>7278000</v>
@@ -1612,16 +1612,16 @@
         <v>44340</v>
       </c>
       <c r="B60" t="n">
-        <v>17.00865364074707</v>
+        <v>17.0086555480957</v>
       </c>
       <c r="C60" t="n">
-        <v>17.06203963689752</v>
+        <v>17.06204155023285</v>
       </c>
       <c r="D60" t="n">
-        <v>16.39664113380684</v>
+        <v>16.39664297252445</v>
       </c>
       <c r="E60" t="n">
-        <v>16.5415402659626</v>
+        <v>16.54154212092919</v>
       </c>
       <c r="F60" t="n">
         <v>10386000</v>
@@ -1632,16 +1632,16 @@
         <v>44341</v>
       </c>
       <c r="B61" t="n">
-        <v>16.88472938537598</v>
+        <v>16.88472747802734</v>
       </c>
       <c r="C61" t="n">
-        <v>17.06394824863613</v>
+        <v>17.06394632104241</v>
       </c>
       <c r="D61" t="n">
-        <v>16.77986654948997</v>
+        <v>16.77986465398696</v>
       </c>
       <c r="E61" t="n">
-        <v>17.01628431501296</v>
+        <v>17.0162823928035</v>
       </c>
       <c r="F61" t="n">
         <v>5307000</v>
@@ -1652,16 +1652,16 @@
         <v>44342</v>
       </c>
       <c r="B62" t="n">
-        <v>16.94192504882812</v>
+        <v>16.94192695617676</v>
       </c>
       <c r="C62" t="n">
-        <v>17.11161256574568</v>
+        <v>17.11161449219801</v>
       </c>
       <c r="D62" t="n">
-        <v>16.65975073072218</v>
+        <v>16.65975260630318</v>
       </c>
       <c r="E62" t="n">
-        <v>17.02390868058733</v>
+        <v>17.02391059716581</v>
       </c>
       <c r="F62" t="n">
         <v>5462000</v>
@@ -1672,16 +1672,16 @@
         <v>44343</v>
       </c>
       <c r="B63" t="n">
-        <v>16.94955062866211</v>
+        <v>16.94955253601074</v>
       </c>
       <c r="C63" t="n">
-        <v>17.26222989699639</v>
+        <v>17.26223183953111</v>
       </c>
       <c r="D63" t="n">
-        <v>16.70550711984472</v>
+        <v>16.70550899973091</v>
       </c>
       <c r="E63" t="n">
-        <v>16.94955062866211</v>
+        <v>16.94955253601074</v>
       </c>
       <c r="F63" t="n">
         <v>5669000</v>
@@ -1752,16 +1752,16 @@
         <v>44349</v>
       </c>
       <c r="B67" t="n">
-        <v>16.76651954650879</v>
+        <v>16.76652145385742</v>
       </c>
       <c r="C67" t="n">
-        <v>17.26032688926774</v>
+        <v>17.26032885279158</v>
       </c>
       <c r="D67" t="n">
-        <v>16.73982745427992</v>
+        <v>16.73982935859208</v>
       </c>
       <c r="E67" t="n">
-        <v>17.06394727556971</v>
+        <v>17.06394921675354</v>
       </c>
       <c r="F67" t="n">
         <v>9352500</v>
@@ -1772,16 +1772,16 @@
         <v>44351</v>
       </c>
       <c r="B68" t="n">
-        <v>16.77223777770996</v>
+        <v>16.77223968505859</v>
       </c>
       <c r="C68" t="n">
-        <v>16.81608880704675</v>
+        <v>16.81609071938215</v>
       </c>
       <c r="D68" t="n">
-        <v>16.40617250494436</v>
+        <v>16.40617437066384</v>
       </c>
       <c r="E68" t="n">
-        <v>16.72266649551031</v>
+        <v>16.72266839722167</v>
       </c>
       <c r="F68" t="n">
         <v>8097000</v>
@@ -1792,16 +1792,16 @@
         <v>44354</v>
       </c>
       <c r="B69" t="n">
-        <v>16.5377311706543</v>
+        <v>16.53772926330566</v>
       </c>
       <c r="C69" t="n">
-        <v>16.77224159045738</v>
+        <v>16.77223965606192</v>
       </c>
       <c r="D69" t="n">
-        <v>16.03057954590612</v>
+        <v>16.03057769704888</v>
       </c>
       <c r="E69" t="n">
-        <v>16.77224159045738</v>
+        <v>16.77223965606192</v>
       </c>
       <c r="F69" t="n">
         <v>10336000</v>
@@ -1812,16 +1812,16 @@
         <v>44355</v>
       </c>
       <c r="B70" t="n">
-        <v>16.08205795288086</v>
+        <v>16.08205604553223</v>
       </c>
       <c r="C70" t="n">
-        <v>16.61018141053224</v>
+        <v>16.61017944054762</v>
       </c>
       <c r="D70" t="n">
-        <v>15.9295293598389</v>
+        <v>15.92952747058032</v>
       </c>
       <c r="E70" t="n">
-        <v>16.60064825982571</v>
+        <v>16.60064629097173</v>
       </c>
       <c r="F70" t="n">
         <v>9246000</v>
@@ -1852,16 +1852,16 @@
         <v>44357</v>
       </c>
       <c r="B72" t="n">
-        <v>16.30322074890137</v>
+        <v>16.3032169342041</v>
       </c>
       <c r="C72" t="n">
-        <v>16.34707360646395</v>
+        <v>16.34706978150581</v>
       </c>
       <c r="D72" t="n">
-        <v>15.97719535383889</v>
+        <v>15.97719161542644</v>
       </c>
       <c r="E72" t="n">
-        <v>16.15641422598889</v>
+        <v>16.15641044564205</v>
       </c>
       <c r="F72" t="n">
         <v>4720000</v>
@@ -1872,16 +1872,16 @@
         <v>44358</v>
       </c>
       <c r="B73" t="n">
-        <v>16.07061386108398</v>
+        <v>16.07061576843262</v>
       </c>
       <c r="C73" t="n">
-        <v>16.30512422503518</v>
+        <v>16.30512616021678</v>
       </c>
       <c r="D73" t="n">
-        <v>15.8742360914556</v>
+        <v>15.87423797549705</v>
       </c>
       <c r="E73" t="n">
-        <v>16.30321686801416</v>
+        <v>16.3032188029694</v>
       </c>
       <c r="F73" t="n">
         <v>5133000</v>
@@ -1912,16 +1912,16 @@
         <v>44362</v>
       </c>
       <c r="B75" t="n">
-        <v>15.85898590087891</v>
+        <v>15.85898399353027</v>
       </c>
       <c r="C75" t="n">
-        <v>16.02676607699607</v>
+        <v>16.02676414946864</v>
       </c>
       <c r="D75" t="n">
-        <v>15.48720212227117</v>
+        <v>15.4872002596367</v>
       </c>
       <c r="E75" t="n">
-        <v>16.01532556907812</v>
+        <v>16.01532364292663</v>
       </c>
       <c r="F75" t="n">
         <v>8432500</v>
@@ -1952,16 +1952,16 @@
         <v>44364</v>
       </c>
       <c r="B77" t="n">
-        <v>15.97719287872314</v>
+        <v>15.97719478607178</v>
       </c>
       <c r="C77" t="n">
-        <v>16.00769786575993</v>
+        <v>16.00769977675023</v>
       </c>
       <c r="D77" t="n">
-        <v>15.6912038523147</v>
+        <v>15.69120572552212</v>
       </c>
       <c r="E77" t="n">
-        <v>15.89711660590322</v>
+        <v>15.89711850369239</v>
       </c>
       <c r="F77" t="n">
         <v>7246000</v>
@@ -1992,16 +1992,16 @@
         <v>44368</v>
       </c>
       <c r="B79" t="n">
-        <v>16.48434638977051</v>
+        <v>16.48434448242188</v>
       </c>
       <c r="C79" t="n">
-        <v>16.59302212366407</v>
+        <v>16.59302020374093</v>
       </c>
       <c r="D79" t="n">
-        <v>16.0000739807668</v>
+        <v>16.00007212945171</v>
       </c>
       <c r="E79" t="n">
-        <v>16.20789229804439</v>
+        <v>16.20789042268334</v>
       </c>
       <c r="F79" t="n">
         <v>6798000</v>
@@ -2012,16 +2012,16 @@
         <v>44369</v>
       </c>
       <c r="B80" t="n">
-        <v>16.4729061126709</v>
+        <v>16.47290420532227</v>
       </c>
       <c r="C80" t="n">
-        <v>16.49578530803645</v>
+        <v>16.49578339803871</v>
       </c>
       <c r="D80" t="n">
-        <v>16.13162735767305</v>
+        <v>16.13162548984007</v>
       </c>
       <c r="E80" t="n">
-        <v>16.46718585926392</v>
+        <v>16.46718395257762</v>
       </c>
       <c r="F80" t="n">
         <v>6518000</v>
@@ -2052,16 +2052,16 @@
         <v>44371</v>
       </c>
       <c r="B82" t="n">
-        <v>16.64640426635742</v>
+        <v>16.64640235900879</v>
       </c>
       <c r="C82" t="n">
-        <v>16.72648053888243</v>
+        <v>16.72647862235864</v>
       </c>
       <c r="D82" t="n">
-        <v>16.39664229944431</v>
+        <v>16.39664042071346</v>
       </c>
       <c r="E82" t="n">
-        <v>16.46909096154148</v>
+        <v>16.46908907450944</v>
       </c>
       <c r="F82" t="n">
         <v>8527500</v>
@@ -2072,16 +2072,16 @@
         <v>44372</v>
       </c>
       <c r="B83" t="n">
-        <v>16.18501091003418</v>
+        <v>16.18501281738281</v>
       </c>
       <c r="C83" t="n">
-        <v>16.74745398613881</v>
+        <v>16.74745595976945</v>
       </c>
       <c r="D83" t="n">
-        <v>16.05345599637458</v>
+        <v>16.05345788821992</v>
       </c>
       <c r="E83" t="n">
-        <v>16.64640405902371</v>
+        <v>16.64640602074596</v>
       </c>
       <c r="F83" t="n">
         <v>6078000</v>
@@ -2092,16 +2092,16 @@
         <v>44375</v>
       </c>
       <c r="B84" t="n">
-        <v>16.37376403808594</v>
+        <v>16.3737621307373</v>
       </c>
       <c r="C84" t="n">
-        <v>16.37948247340491</v>
+        <v>16.37948056539015</v>
       </c>
       <c r="D84" t="n">
-        <v>15.93906113114842</v>
+        <v>15.9390592744375</v>
       </c>
       <c r="E84" t="n">
-        <v>16.22505017280664</v>
+        <v>16.2250482827814</v>
       </c>
       <c r="F84" t="n">
         <v>6202500</v>
@@ -2112,16 +2112,16 @@
         <v>44376</v>
       </c>
       <c r="B85" t="n">
-        <v>16.42333793640137</v>
+        <v>16.42333602905273</v>
       </c>
       <c r="C85" t="n">
-        <v>16.53963947421787</v>
+        <v>16.53963755336238</v>
       </c>
       <c r="D85" t="n">
-        <v>16.12018990408709</v>
+        <v>16.120188031945</v>
       </c>
       <c r="E85" t="n">
-        <v>16.36804638560697</v>
+        <v>16.3680444846797</v>
       </c>
       <c r="F85" t="n">
         <v>8958000</v>
@@ -2132,16 +2132,16 @@
         <v>44377</v>
       </c>
       <c r="B86" t="n">
-        <v>16.49959754943848</v>
+        <v>16.49959945678711</v>
       </c>
       <c r="C86" t="n">
-        <v>16.49959754943848</v>
+        <v>16.49959945678711</v>
       </c>
       <c r="D86" t="n">
-        <v>16.19072933339201</v>
+        <v>16.19073120503556</v>
       </c>
       <c r="E86" t="n">
-        <v>16.38901447318302</v>
+        <v>16.38901636774828</v>
       </c>
       <c r="F86" t="n">
         <v>6685000</v>
@@ -2152,16 +2152,16 @@
         <v>44378</v>
       </c>
       <c r="B87" t="n">
-        <v>16.35851097106934</v>
+        <v>16.3585090637207</v>
       </c>
       <c r="C87" t="n">
-        <v>16.66356450050222</v>
+        <v>16.66356255758535</v>
       </c>
       <c r="D87" t="n">
-        <v>16.14878712414984</v>
+        <v>16.14878524125432</v>
       </c>
       <c r="E87" t="n">
-        <v>16.66356450050222</v>
+        <v>16.66356255758535</v>
       </c>
       <c r="F87" t="n">
         <v>8503000</v>
@@ -2192,16 +2192,16 @@
         <v>44382</v>
       </c>
       <c r="B89" t="n">
-        <v>16.41570854187012</v>
+        <v>16.41570663452148</v>
       </c>
       <c r="C89" t="n">
-        <v>16.54726347128895</v>
+        <v>16.54726154865489</v>
       </c>
       <c r="D89" t="n">
-        <v>16.25174308313778</v>
+        <v>16.25174119484036</v>
       </c>
       <c r="E89" t="n">
-        <v>16.40808274888606</v>
+        <v>16.40808084242347</v>
       </c>
       <c r="F89" t="n">
         <v>3871000</v>
@@ -2212,16 +2212,16 @@
         <v>44383</v>
       </c>
       <c r="B90" t="n">
-        <v>16.33944511413574</v>
+        <v>16.33944702148438</v>
       </c>
       <c r="C90" t="n">
-        <v>16.38901640492637</v>
+        <v>16.3890183180616</v>
       </c>
       <c r="D90" t="n">
-        <v>16.11256231822719</v>
+        <v>16.11256419909116</v>
       </c>
       <c r="E90" t="n">
-        <v>16.38901640492637</v>
+        <v>16.3890183180616</v>
       </c>
       <c r="F90" t="n">
         <v>3828000</v>
@@ -2232,16 +2232,16 @@
         <v>44384</v>
       </c>
       <c r="B91" t="n">
-        <v>16.44430541992188</v>
+        <v>16.44430732727051</v>
       </c>
       <c r="C91" t="n">
-        <v>16.58348612054724</v>
+        <v>16.58348804403921</v>
       </c>
       <c r="D91" t="n">
-        <v>16.15069061682722</v>
+        <v>16.15069249011994</v>
       </c>
       <c r="E91" t="n">
-        <v>16.39664149383569</v>
+        <v>16.39664339565586</v>
       </c>
       <c r="F91" t="n">
         <v>12086500</v>
@@ -2272,16 +2272,16 @@
         <v>44389</v>
       </c>
       <c r="B93" t="n">
-        <v>16.50150299072266</v>
+        <v>16.50150108337402</v>
       </c>
       <c r="C93" t="n">
-        <v>16.60255291716791</v>
+        <v>16.60255099813928</v>
       </c>
       <c r="D93" t="n">
-        <v>16.2746202228983</v>
+        <v>16.27461834177422</v>
       </c>
       <c r="E93" t="n">
-        <v>16.43095986888196</v>
+        <v>16.43095796968715</v>
       </c>
       <c r="F93" t="n">
         <v>4327500</v>
@@ -2292,16 +2292,16 @@
         <v>44390</v>
       </c>
       <c r="B94" t="n">
-        <v>16.7874927520752</v>
+        <v>16.78749084472656</v>
       </c>
       <c r="C94" t="n">
-        <v>16.91142006005396</v>
+        <v>16.91141813862505</v>
       </c>
       <c r="D94" t="n">
-        <v>16.43096059459017</v>
+        <v>16.43095872774974</v>
       </c>
       <c r="E94" t="n">
-        <v>16.45383978992295</v>
+        <v>16.45383792048305</v>
       </c>
       <c r="F94" t="n">
         <v>6446000</v>
@@ -2332,16 +2332,16 @@
         <v>44392</v>
       </c>
       <c r="B96" t="n">
-        <v>16.45002746582031</v>
+        <v>16.45002555847168</v>
       </c>
       <c r="C96" t="n">
-        <v>16.86375671689422</v>
+        <v>16.86375476157448</v>
       </c>
       <c r="D96" t="n">
-        <v>16.44049431591159</v>
+        <v>16.44049240966831</v>
       </c>
       <c r="E96" t="n">
-        <v>16.72266864381253</v>
+        <v>16.72266670485169</v>
       </c>
       <c r="F96" t="n">
         <v>3746000</v>
@@ -2372,16 +2372,16 @@
         <v>44396</v>
       </c>
       <c r="B98" t="n">
-        <v>16.65403175354004</v>
+        <v>16.65402984619141</v>
       </c>
       <c r="C98" t="n">
-        <v>16.7970271899026</v>
+        <v>16.79702526617702</v>
       </c>
       <c r="D98" t="n">
-        <v>16.40426976120661</v>
+        <v>16.40426788246265</v>
       </c>
       <c r="E98" t="n">
-        <v>16.58539598054001</v>
+        <v>16.58539408105208</v>
       </c>
       <c r="F98" t="n">
         <v>7763500</v>
@@ -2452,16 +2452,16 @@
         <v>44400</v>
       </c>
       <c r="B102" t="n">
-        <v>16.6826286315918</v>
+        <v>16.68263053894043</v>
       </c>
       <c r="C102" t="n">
-        <v>16.73029255752003</v>
+        <v>16.73029447031815</v>
       </c>
       <c r="D102" t="n">
-        <v>16.56060687203135</v>
+        <v>16.56060876542906</v>
       </c>
       <c r="E102" t="n">
-        <v>16.64449603623943</v>
+        <v>16.64449793922831</v>
       </c>
       <c r="F102" t="n">
         <v>4154500</v>
@@ -2512,16 +2512,16 @@
         <v>44405</v>
       </c>
       <c r="B105" t="n">
-        <v>16.79321479797363</v>
+        <v>16.79320907592773</v>
       </c>
       <c r="C105" t="n">
-        <v>17.38044457400667</v>
+        <v>17.38043865187069</v>
       </c>
       <c r="D105" t="n">
-        <v>16.42333833346707</v>
+        <v>16.42333273745124</v>
       </c>
       <c r="E105" t="n">
-        <v>17.3499395797581</v>
+        <v>17.34993366801626</v>
       </c>
       <c r="F105" t="n">
         <v>14614500</v>
@@ -2532,16 +2532,16 @@
         <v>44406</v>
       </c>
       <c r="B106" t="n">
-        <v>16.62543296813965</v>
+        <v>16.62543106079102</v>
       </c>
       <c r="C106" t="n">
-        <v>16.77795972597248</v>
+        <v>16.77795780112525</v>
       </c>
       <c r="D106" t="n">
-        <v>16.27462106147167</v>
+        <v>16.27461919436984</v>
       </c>
       <c r="E106" t="n">
-        <v>16.77795972597248</v>
+        <v>16.77795780112525</v>
       </c>
       <c r="F106" t="n">
         <v>12625000</v>
@@ -2552,16 +2552,16 @@
         <v>44407</v>
       </c>
       <c r="B107" t="n">
-        <v>16.52629089355469</v>
+        <v>16.52628898620605</v>
       </c>
       <c r="C107" t="n">
-        <v>16.73220184103048</v>
+        <v>16.73219990991705</v>
       </c>
       <c r="D107" t="n">
-        <v>16.30893943885111</v>
+        <v>16.30893755658766</v>
       </c>
       <c r="E107" t="n">
-        <v>16.6254334709708</v>
+        <v>16.62543155217983</v>
       </c>
       <c r="F107" t="n">
         <v>16469000</v>
@@ -2612,16 +2612,16 @@
         <v>44412</v>
       </c>
       <c r="B110" t="n">
-        <v>16.60255432128906</v>
+        <v>16.60255241394043</v>
       </c>
       <c r="C110" t="n">
-        <v>16.83134446559894</v>
+        <v>16.83134253196625</v>
       </c>
       <c r="D110" t="n">
-        <v>16.3489776234245</v>
+        <v>16.34897574520748</v>
       </c>
       <c r="E110" t="n">
-        <v>16.48243990463543</v>
+        <v>16.48243801108588</v>
       </c>
       <c r="F110" t="n">
         <v>6533500</v>
@@ -2632,16 +2632,16 @@
         <v>44413</v>
       </c>
       <c r="B111" t="n">
-        <v>16.58729934692383</v>
+        <v>16.5872974395752</v>
       </c>
       <c r="C111" t="n">
-        <v>16.93811123196384</v>
+        <v>16.93810928427588</v>
       </c>
       <c r="D111" t="n">
-        <v>16.47481073358749</v>
+        <v>16.47480883917376</v>
       </c>
       <c r="E111" t="n">
-        <v>16.59301960001205</v>
+        <v>16.59301769200566</v>
       </c>
       <c r="F111" t="n">
         <v>13427000</v>
@@ -2652,16 +2652,16 @@
         <v>44414</v>
       </c>
       <c r="B112" t="n">
-        <v>16.73982620239258</v>
+        <v>16.73982810974121</v>
       </c>
       <c r="C112" t="n">
-        <v>16.78367905199969</v>
+        <v>16.78368096434495</v>
       </c>
       <c r="D112" t="n">
-        <v>16.37566826999301</v>
+        <v>16.37567013584921</v>
       </c>
       <c r="E112" t="n">
-        <v>16.63115048433273</v>
+        <v>16.63115237929877</v>
       </c>
       <c r="F112" t="n">
         <v>15424500</v>
@@ -2672,16 +2672,16 @@
         <v>44417</v>
       </c>
       <c r="B113" t="n">
-        <v>17.31942939758301</v>
+        <v>17.31942749023438</v>
       </c>
       <c r="C113" t="n">
-        <v>17.35756199667172</v>
+        <v>17.35756008512363</v>
       </c>
       <c r="D113" t="n">
-        <v>16.6178055750599</v>
+        <v>16.61780374497947</v>
       </c>
       <c r="E113" t="n">
-        <v>16.6178055750599</v>
+        <v>16.61780374497947</v>
       </c>
       <c r="F113" t="n">
         <v>10558500</v>
@@ -2692,16 +2692,16 @@
         <v>44418</v>
       </c>
       <c r="B114" t="n">
-        <v>17.55012702941895</v>
+        <v>17.55012512207031</v>
       </c>
       <c r="C114" t="n">
-        <v>17.66452300930153</v>
+        <v>17.66452108952034</v>
       </c>
       <c r="D114" t="n">
-        <v>17.10589279254452</v>
+        <v>17.10589093347529</v>
       </c>
       <c r="E114" t="n">
-        <v>17.22219431143875</v>
+        <v>17.22219243972985</v>
       </c>
       <c r="F114" t="n">
         <v>10281500</v>
@@ -2772,16 +2772,16 @@
         <v>44424</v>
       </c>
       <c r="B118" t="n">
-        <v>16.44430541992188</v>
+        <v>16.44430732727051</v>
       </c>
       <c r="C118" t="n">
-        <v>17.04487925261408</v>
+        <v>17.04488122962231</v>
       </c>
       <c r="D118" t="n">
-        <v>16.27271237679204</v>
+        <v>16.27271426423787</v>
       </c>
       <c r="E118" t="n">
-        <v>16.86375487887679</v>
+        <v>16.86375683487669</v>
       </c>
       <c r="F118" t="n">
         <v>7814500</v>
@@ -2792,16 +2792,16 @@
         <v>44425</v>
       </c>
       <c r="B119" t="n">
-        <v>16.16785049438477</v>
+        <v>16.1678524017334</v>
       </c>
       <c r="C119" t="n">
-        <v>16.39664244399077</v>
+        <v>16.39664437833038</v>
       </c>
       <c r="D119" t="n">
-        <v>15.70073708227531</v>
+        <v>15.70073893451779</v>
       </c>
       <c r="E119" t="n">
-        <v>16.16785049438477</v>
+        <v>16.1678524017334</v>
       </c>
       <c r="F119" t="n">
         <v>9967800</v>
@@ -2812,16 +2812,16 @@
         <v>44426</v>
       </c>
       <c r="B120" t="n">
-        <v>15.88186550140381</v>
+        <v>15.88186359405518</v>
       </c>
       <c r="C120" t="n">
-        <v>16.30131504320764</v>
+        <v>16.30131308548479</v>
       </c>
       <c r="D120" t="n">
-        <v>15.64354218737522</v>
+        <v>15.64354030864827</v>
       </c>
       <c r="E120" t="n">
-        <v>16.16785275093307</v>
+        <v>16.16785080923852</v>
       </c>
       <c r="F120" t="n">
         <v>10736900</v>
@@ -2832,16 +2832,16 @@
         <v>44427</v>
       </c>
       <c r="B121" t="n">
-        <v>16.66356658935547</v>
+        <v>16.66356468200684</v>
       </c>
       <c r="C121" t="n">
-        <v>16.87329228082749</v>
+        <v>16.87329034947318</v>
       </c>
       <c r="D121" t="n">
-        <v>15.57681279995571</v>
+        <v>15.57681101699932</v>
       </c>
       <c r="E121" t="n">
-        <v>15.71027328124686</v>
+        <v>15.71027148301428</v>
       </c>
       <c r="F121" t="n">
         <v>14455000</v>
@@ -2852,16 +2852,16 @@
         <v>44428</v>
       </c>
       <c r="B122" t="n">
-        <v>16.94955062866211</v>
+        <v>16.94955253601074</v>
       </c>
       <c r="C122" t="n">
-        <v>17.4166639924337</v>
+        <v>17.41666595234703</v>
       </c>
       <c r="D122" t="n">
-        <v>16.37757445036105</v>
+        <v>16.37757629334467</v>
       </c>
       <c r="E122" t="n">
-        <v>16.53963433724198</v>
+        <v>16.53963619846235</v>
       </c>
       <c r="F122" t="n">
         <v>9513400</v>
@@ -2932,16 +2932,16 @@
         <v>44434</v>
       </c>
       <c r="B126" t="n">
-        <v>16.55870056152344</v>
+        <v>16.55870246887207</v>
       </c>
       <c r="C126" t="n">
-        <v>17.00674762645968</v>
+        <v>17.00674958541756</v>
       </c>
       <c r="D126" t="n">
-        <v>16.55870056152344</v>
+        <v>16.55870246887207</v>
       </c>
       <c r="E126" t="n">
-        <v>16.93048425757134</v>
+        <v>16.93048620774466</v>
       </c>
       <c r="F126" t="n">
         <v>4969900</v>
@@ -2952,16 +2952,16 @@
         <v>44435</v>
       </c>
       <c r="B127" t="n">
-        <v>16.58729934692383</v>
+        <v>16.5872974395752</v>
       </c>
       <c r="C127" t="n">
-        <v>16.72076161549623</v>
+        <v>16.72075969280097</v>
       </c>
       <c r="D127" t="n">
-        <v>16.39664182051824</v>
+        <v>16.39663993509303</v>
       </c>
       <c r="E127" t="n">
-        <v>16.55870171800724</v>
+        <v>16.558699813947</v>
       </c>
       <c r="F127" t="n">
         <v>5662600</v>
@@ -2972,16 +2972,16 @@
         <v>44438</v>
       </c>
       <c r="B128" t="n">
-        <v>16.35851097106934</v>
+        <v>16.3585090637207</v>
       </c>
       <c r="C128" t="n">
-        <v>16.79702678332595</v>
+        <v>16.79702482484782</v>
       </c>
       <c r="D128" t="n">
-        <v>16.16785160604255</v>
+        <v>16.16784972092418</v>
       </c>
       <c r="E128" t="n">
-        <v>16.4729069537379</v>
+        <v>16.47290503305107</v>
       </c>
       <c r="F128" t="n">
         <v>16747200</v>
@@ -3032,16 +3032,16 @@
         <v>44441</v>
       </c>
       <c r="B131" t="n">
-        <v>16.72076416015625</v>
+        <v>16.72076225280762</v>
       </c>
       <c r="C131" t="n">
-        <v>17.03535085395019</v>
+        <v>17.03534891071645</v>
       </c>
       <c r="D131" t="n">
-        <v>16.10112210481625</v>
+        <v>16.10112026815059</v>
       </c>
       <c r="E131" t="n">
-        <v>16.1678523401267</v>
+        <v>16.16785049584908</v>
       </c>
       <c r="F131" t="n">
         <v>17566400</v>
@@ -3052,16 +3052,16 @@
         <v>44442</v>
       </c>
       <c r="B132" t="n">
-        <v>17.31180572509766</v>
+        <v>17.31180191040039</v>
       </c>
       <c r="C132" t="n">
-        <v>17.35946966153313</v>
+        <v>17.359465836333</v>
       </c>
       <c r="D132" t="n">
-        <v>16.69216546012336</v>
+        <v>16.69216178196529</v>
       </c>
       <c r="E132" t="n">
-        <v>16.90188932600712</v>
+        <v>16.9018856016359</v>
       </c>
       <c r="F132" t="n">
         <v>19565300</v>
@@ -3072,16 +3072,16 @@
         <v>44445</v>
       </c>
       <c r="B133" t="n">
-        <v>17.4929313659668</v>
+        <v>17.49292945861816</v>
       </c>
       <c r="C133" t="n">
-        <v>17.66452444056273</v>
+        <v>17.66452251450438</v>
       </c>
       <c r="D133" t="n">
-        <v>17.04488237824128</v>
+        <v>17.04488051974584</v>
       </c>
       <c r="E133" t="n">
-        <v>17.30227199013519</v>
+        <v>17.30227010357517</v>
       </c>
       <c r="F133" t="n">
         <v>6471000</v>
@@ -3092,16 +3092,16 @@
         <v>44447</v>
       </c>
       <c r="B134" t="n">
-        <v>17.07347869873047</v>
+        <v>17.0734806060791</v>
       </c>
       <c r="C134" t="n">
-        <v>17.55012523262749</v>
+        <v>17.55012719322427</v>
       </c>
       <c r="D134" t="n">
-        <v>16.84468858065136</v>
+        <v>16.84469046244091</v>
       </c>
       <c r="E134" t="n">
-        <v>17.49292815767328</v>
+        <v>17.49293011188033</v>
       </c>
       <c r="F134" t="n">
         <v>11069100</v>
@@ -3132,16 +3132,16 @@
         <v>44449</v>
       </c>
       <c r="B136" t="n">
-        <v>17.33086967468262</v>
+        <v>17.33086776733398</v>
       </c>
       <c r="C136" t="n">
-        <v>17.60732374135838</v>
+        <v>17.6073218035846</v>
       </c>
       <c r="D136" t="n">
-        <v>17.01628300942406</v>
+        <v>17.01628113669726</v>
       </c>
       <c r="E136" t="n">
-        <v>17.33086967468262</v>
+        <v>17.33086776733398</v>
       </c>
       <c r="F136" t="n">
         <v>19125200</v>
@@ -3152,16 +3152,16 @@
         <v>44452</v>
       </c>
       <c r="B137" t="n">
-        <v>17.79798126220703</v>
+        <v>17.79798316955566</v>
       </c>
       <c r="C137" t="n">
-        <v>17.96957430160813</v>
+        <v>17.9695762273458</v>
       </c>
       <c r="D137" t="n">
-        <v>17.49292777805493</v>
+        <v>17.49292965271203</v>
       </c>
       <c r="E137" t="n">
-        <v>17.57872429775548</v>
+        <v>17.5787261816071</v>
       </c>
       <c r="F137" t="n">
         <v>17075500</v>
@@ -3172,16 +3172,16 @@
         <v>44453</v>
       </c>
       <c r="B138" t="n">
-        <v>17.47386169433594</v>
+        <v>17.47386360168457</v>
       </c>
       <c r="C138" t="n">
-        <v>18.15070071155172</v>
+        <v>18.1507026927803</v>
       </c>
       <c r="D138" t="n">
-        <v>17.39759832236565</v>
+        <v>17.3976002213898</v>
       </c>
       <c r="E138" t="n">
-        <v>17.82658092611242</v>
+        <v>17.82658287196191</v>
       </c>
       <c r="F138" t="n">
         <v>6594500</v>
@@ -3192,16 +3192,16 @@
         <v>44454</v>
       </c>
       <c r="B139" t="n">
-        <v>17.72171783447266</v>
+        <v>17.72171974182129</v>
       </c>
       <c r="C139" t="n">
-        <v>17.82658065116278</v>
+        <v>17.82658256979756</v>
       </c>
       <c r="D139" t="n">
-        <v>17.27367075834045</v>
+        <v>17.27367261746679</v>
       </c>
       <c r="E139" t="n">
-        <v>17.46432827619446</v>
+        <v>17.46433015584083</v>
       </c>
       <c r="F139" t="n">
         <v>8756500</v>
@@ -3212,16 +3212,16 @@
         <v>44455</v>
       </c>
       <c r="B140" t="n">
-        <v>18.26509475708008</v>
+        <v>18.26509666442871</v>
       </c>
       <c r="C140" t="n">
-        <v>18.33182497989392</v>
+        <v>18.33182689421092</v>
       </c>
       <c r="D140" t="n">
-        <v>17.72171800758197</v>
+        <v>17.72171985818801</v>
       </c>
       <c r="E140" t="n">
-        <v>17.72171800758197</v>
+        <v>17.72171985818801</v>
       </c>
       <c r="F140" t="n">
         <v>17281800</v>
@@ -3252,16 +3252,16 @@
         <v>44459</v>
       </c>
       <c r="B142" t="n">
-        <v>17.94097709655762</v>
+        <v>17.94097900390625</v>
       </c>
       <c r="C142" t="n">
-        <v>18.12210330724501</v>
+        <v>18.12210523384961</v>
       </c>
       <c r="D142" t="n">
-        <v>17.63592357430248</v>
+        <v>17.63592544922014</v>
       </c>
       <c r="E142" t="n">
-        <v>18.02677362697468</v>
+        <v>18.02677554344455</v>
       </c>
       <c r="F142" t="n">
         <v>15522000</v>
@@ -3312,16 +3312,16 @@
         <v>44462</v>
       </c>
       <c r="B145" t="n">
-        <v>18.29369735717773</v>
+        <v>18.2936954498291</v>
       </c>
       <c r="C145" t="n">
-        <v>18.53202066160796</v>
+        <v>18.53201872941112</v>
       </c>
       <c r="D145" t="n">
-        <v>18.07443853522241</v>
+        <v>18.07443665073428</v>
       </c>
       <c r="E145" t="n">
-        <v>18.34136129075877</v>
+        <v>18.34135937844058</v>
       </c>
       <c r="F145" t="n">
         <v>20822300</v>
@@ -3332,16 +3332,16 @@
         <v>44463</v>
       </c>
       <c r="B146" t="n">
-        <v>18.09350204467773</v>
+        <v>18.09350395202637</v>
       </c>
       <c r="C146" t="n">
-        <v>18.26509508831786</v>
+        <v>18.26509701375519</v>
       </c>
       <c r="D146" t="n">
-        <v>17.87424507480967</v>
+        <v>17.87424695904506</v>
       </c>
       <c r="E146" t="n">
-        <v>18.13163464026987</v>
+        <v>18.13163655163829</v>
       </c>
       <c r="F146" t="n">
         <v>18657800</v>
@@ -3372,16 +3372,16 @@
         <v>44467</v>
       </c>
       <c r="B148" t="n">
-        <v>18.28416061401367</v>
+        <v>18.2841625213623</v>
       </c>
       <c r="C148" t="n">
-        <v>18.29369376250914</v>
+        <v>18.29369567085224</v>
       </c>
       <c r="D148" t="n">
-        <v>18.01723791092701</v>
+        <v>18.01723979043107</v>
       </c>
       <c r="E148" t="n">
-        <v>18.23649487153633</v>
+        <v>18.23649677391261</v>
       </c>
       <c r="F148" t="n">
         <v>11310100</v>
@@ -3392,16 +3392,16 @@
         <v>44468</v>
       </c>
       <c r="B149" t="n">
-        <v>18.08397102355957</v>
+        <v>18.08396911621094</v>
       </c>
       <c r="C149" t="n">
-        <v>18.42715715121949</v>
+        <v>18.4271552076744</v>
       </c>
       <c r="D149" t="n">
-        <v>17.9695768598479</v>
+        <v>17.96957496456462</v>
       </c>
       <c r="E149" t="n">
-        <v>18.29369668746839</v>
+        <v>18.29369475799961</v>
       </c>
       <c r="F149" t="n">
         <v>10203400</v>
@@ -3432,16 +3432,16 @@
         <v>44470</v>
       </c>
       <c r="B151" t="n">
-        <v>18.45575523376465</v>
+        <v>18.45575714111328</v>
       </c>
       <c r="C151" t="n">
-        <v>18.56061623968673</v>
+        <v>18.56061815787245</v>
       </c>
       <c r="D151" t="n">
-        <v>18.00770630734936</v>
+        <v>18.00770816839343</v>
       </c>
       <c r="E151" t="n">
-        <v>18.19836565709148</v>
+        <v>18.19836753783964</v>
       </c>
       <c r="F151" t="n">
         <v>5841800</v>
@@ -3472,16 +3472,16 @@
         <v>44474</v>
       </c>
       <c r="B153" t="n">
-        <v>18.32229423522949</v>
+        <v>18.32229232788086</v>
       </c>
       <c r="C153" t="n">
-        <v>18.49388729827244</v>
+        <v>18.49388537306099</v>
       </c>
       <c r="D153" t="n">
-        <v>18.04584015897554</v>
+        <v>18.04583828040574</v>
       </c>
       <c r="E153" t="n">
-        <v>18.34136053518147</v>
+        <v>18.34135862584804</v>
       </c>
       <c r="F153" t="n">
         <v>8000200</v>
@@ -3492,16 +3492,16 @@
         <v>44475</v>
       </c>
       <c r="B154" t="n">
-        <v>18.27167701721191</v>
+        <v>18.27167892456055</v>
       </c>
       <c r="C154" t="n">
-        <v>18.63481622367532</v>
+        <v>18.63481816893143</v>
       </c>
       <c r="D154" t="n">
-        <v>18.06143689840233</v>
+        <v>18.06143878380436</v>
       </c>
       <c r="E154" t="n">
-        <v>18.11877428411284</v>
+        <v>18.11877617550022</v>
       </c>
       <c r="F154" t="n">
         <v>10611600</v>
@@ -3512,16 +3512,16 @@
         <v>44476</v>
       </c>
       <c r="B155" t="n">
-        <v>18.0805492401123</v>
+        <v>18.08055114746094</v>
       </c>
       <c r="C155" t="n">
-        <v>18.36723797984786</v>
+        <v>18.36723991743979</v>
       </c>
       <c r="D155" t="n">
-        <v>17.99454225364713</v>
+        <v>17.99454415192273</v>
       </c>
       <c r="E155" t="n">
-        <v>18.27167628175104</v>
+        <v>18.271678209262</v>
       </c>
       <c r="F155" t="n">
         <v>7169200</v>
@@ -3552,16 +3552,16 @@
         <v>44480</v>
       </c>
       <c r="B157" t="n">
-        <v>16.62799072265625</v>
+        <v>16.62798690795898</v>
       </c>
       <c r="C157" t="n">
-        <v>17.52628500439614</v>
+        <v>17.5262809836174</v>
       </c>
       <c r="D157" t="n">
-        <v>16.47508980100556</v>
+        <v>16.47508602138593</v>
       </c>
       <c r="E157" t="n">
-        <v>17.42116493724025</v>
+        <v>17.42116094057755</v>
       </c>
       <c r="F157" t="n">
         <v>31512800</v>
@@ -3612,16 +3612,16 @@
         <v>44484</v>
       </c>
       <c r="B160" t="n">
-        <v>16.76177787780762</v>
+        <v>16.76177978515625</v>
       </c>
       <c r="C160" t="n">
-        <v>16.933790021779</v>
+        <v>16.93379194870116</v>
       </c>
       <c r="D160" t="n">
-        <v>15.86348373102988</v>
+        <v>15.86348553616024</v>
       </c>
       <c r="E160" t="n">
-        <v>15.95904724838453</v>
+        <v>15.95904906438921</v>
       </c>
       <c r="F160" t="n">
         <v>78021300</v>
@@ -3632,16 +3632,16 @@
         <v>44487</v>
       </c>
       <c r="B161" t="n">
-        <v>16.20751190185547</v>
+        <v>16.2075138092041</v>
       </c>
       <c r="C161" t="n">
-        <v>16.67577301414236</v>
+        <v>16.67577497659736</v>
       </c>
       <c r="D161" t="n">
-        <v>16.10239365985386</v>
+        <v>16.10239555483187</v>
       </c>
       <c r="E161" t="n">
-        <v>16.58976601986295</v>
+        <v>16.58976797219639</v>
       </c>
       <c r="F161" t="n">
         <v>13070300</v>
@@ -3652,16 +3652,16 @@
         <v>44488</v>
       </c>
       <c r="B162" t="n">
-        <v>15.81570434570312</v>
+        <v>15.81570243835449</v>
       </c>
       <c r="C162" t="n">
-        <v>16.07372534933147</v>
+        <v>16.07372341086592</v>
       </c>
       <c r="D162" t="n">
-        <v>15.63413563001462</v>
+        <v>15.63413374456288</v>
       </c>
       <c r="E162" t="n">
-        <v>16.05461227734651</v>
+        <v>16.05461034118597</v>
       </c>
       <c r="F162" t="n">
         <v>17605400</v>
@@ -3672,16 +3672,16 @@
         <v>44489</v>
       </c>
       <c r="B163" t="n">
-        <v>15.98771572113037</v>
+        <v>15.98771667480469</v>
       </c>
       <c r="C163" t="n">
-        <v>16.21706707909584</v>
+        <v>16.21706804645106</v>
       </c>
       <c r="D163" t="n">
-        <v>15.71058351377639</v>
+        <v>15.71058445091965</v>
       </c>
       <c r="E163" t="n">
-        <v>15.93993487174186</v>
+        <v>15.93993582256603</v>
       </c>
       <c r="F163" t="n">
         <v>11472200</v>
@@ -3692,16 +3692,16 @@
         <v>44490</v>
       </c>
       <c r="B164" t="n">
-        <v>15.70102882385254</v>
+        <v>15.70102596282959</v>
       </c>
       <c r="C164" t="n">
-        <v>16.21706898421667</v>
+        <v>16.2170660291615</v>
       </c>
       <c r="D164" t="n">
-        <v>15.31877651567118</v>
+        <v>15.3187737243018</v>
       </c>
       <c r="E164" t="n">
-        <v>15.81570360494555</v>
+        <v>15.8157007230267</v>
       </c>
       <c r="F164" t="n">
         <v>11995800</v>
@@ -3752,16 +3752,16 @@
         <v>44495</v>
       </c>
       <c r="B167" t="n">
-        <v>15.24232482910156</v>
+        <v>15.24232387542725</v>
       </c>
       <c r="C167" t="n">
-        <v>15.44300751460859</v>
+        <v>15.44300654837805</v>
       </c>
       <c r="D167" t="n">
-        <v>15.01297344891107</v>
+        <v>15.0129725095867</v>
       </c>
       <c r="E167" t="n">
-        <v>15.38567012524165</v>
+        <v>15.38566916259858</v>
       </c>
       <c r="F167" t="n">
         <v>7090300</v>
@@ -3772,16 +3772,16 @@
         <v>44496</v>
       </c>
       <c r="B168" t="n">
-        <v>14.94607734680176</v>
+        <v>14.94607925415039</v>
       </c>
       <c r="C168" t="n">
-        <v>15.38566788380655</v>
+        <v>15.38566984725368</v>
       </c>
       <c r="D168" t="n">
-        <v>14.81228860550074</v>
+        <v>14.81229049577588</v>
       </c>
       <c r="E168" t="n">
-        <v>15.38566788380655</v>
+        <v>15.38566984725368</v>
       </c>
       <c r="F168" t="n">
         <v>9783700</v>
@@ -3812,16 +3812,16 @@
         <v>44498</v>
       </c>
       <c r="B170" t="n">
-        <v>14.61160755157471</v>
+        <v>14.61160659790039</v>
       </c>
       <c r="C170" t="n">
-        <v>15.21365558640951</v>
+        <v>15.21365459344056</v>
       </c>
       <c r="D170" t="n">
-        <v>14.50648840061422</v>
+        <v>14.50648745380085</v>
       </c>
       <c r="E170" t="n">
-        <v>15.0034163731272</v>
+        <v>15.0034153938802</v>
       </c>
       <c r="F170" t="n">
         <v>13706000</v>
@@ -3832,16 +3832,16 @@
         <v>44501</v>
       </c>
       <c r="B171" t="n">
-        <v>14.31536102294922</v>
+        <v>14.31536197662354</v>
       </c>
       <c r="C171" t="n">
-        <v>14.77406466781794</v>
+        <v>14.77406565205061</v>
       </c>
       <c r="D171" t="n">
-        <v>14.20068533957237</v>
+        <v>14.20068628560711</v>
       </c>
       <c r="E171" t="n">
-        <v>14.76450813302954</v>
+        <v>14.76450911662556</v>
       </c>
       <c r="F171" t="n">
         <v>10277500</v>
@@ -3952,16 +3952,16 @@
         <v>44510</v>
       </c>
       <c r="B177" t="n">
-        <v>15.26143932342529</v>
+        <v>15.26143836975098</v>
       </c>
       <c r="C177" t="n">
-        <v>15.38567156045753</v>
+        <v>15.38567059902005</v>
       </c>
       <c r="D177" t="n">
-        <v>14.71672860545911</v>
+        <v>14.7167276858233</v>
       </c>
       <c r="E177" t="n">
-        <v>14.84096084249134</v>
+        <v>14.84095991509237</v>
       </c>
       <c r="F177" t="n">
         <v>10223900</v>
@@ -3972,16 +3972,16 @@
         <v>44511</v>
       </c>
       <c r="B178" t="n">
-        <v>15.19454288482666</v>
+        <v>15.19454193115234</v>
       </c>
       <c r="C178" t="n">
-        <v>15.51945779195179</v>
+        <v>15.51945681788442</v>
       </c>
       <c r="D178" t="n">
-        <v>15.07986719608156</v>
+        <v>15.07986624960478</v>
       </c>
       <c r="E178" t="n">
-        <v>15.43345079755262</v>
+        <v>15.43344982888343</v>
       </c>
       <c r="F178" t="n">
         <v>5555700</v>
@@ -3992,16 +3992,16 @@
         <v>44512</v>
       </c>
       <c r="B179" t="n">
-        <v>14.8409595489502</v>
+        <v>14.84095859527588</v>
       </c>
       <c r="C179" t="n">
-        <v>15.23276838701479</v>
+        <v>15.23276740816299</v>
       </c>
       <c r="D179" t="n">
-        <v>14.82184738949799</v>
+        <v>14.82184643705182</v>
       </c>
       <c r="E179" t="n">
-        <v>15.08942400135846</v>
+        <v>15.08942303171791</v>
       </c>
       <c r="F179" t="n">
         <v>7831400</v>
@@ -4012,16 +4012,16 @@
         <v>44516</v>
       </c>
       <c r="B180" t="n">
-        <v>14.18157482147217</v>
+        <v>14.18157386779785</v>
       </c>
       <c r="C180" t="n">
-        <v>14.86007337677532</v>
+        <v>14.86007237747372</v>
       </c>
       <c r="D180" t="n">
-        <v>14.00000428493899</v>
+        <v>14.00000334347483</v>
       </c>
       <c r="E180" t="n">
-        <v>14.81229160866862</v>
+        <v>14.81229061258022</v>
       </c>
       <c r="F180" t="n">
         <v>11424100</v>
@@ -4032,16 +4032,16 @@
         <v>44517</v>
       </c>
       <c r="B181" t="n">
-        <v>13.62730598449707</v>
+        <v>13.6273078918457</v>
       </c>
       <c r="C181" t="n">
-        <v>14.42048009010075</v>
+        <v>14.42048210846616</v>
       </c>
       <c r="D181" t="n">
-        <v>13.49351724075429</v>
+        <v>13.49351912937716</v>
       </c>
       <c r="E181" t="n">
-        <v>14.42048009010075</v>
+        <v>14.42048210846616</v>
       </c>
       <c r="F181" t="n">
         <v>10535200</v>
@@ -4052,16 +4052,16 @@
         <v>44518</v>
       </c>
       <c r="B182" t="n">
-        <v>13.35973072052002</v>
+        <v>13.3597297668457</v>
       </c>
       <c r="C182" t="n">
-        <v>13.69420217986363</v>
+        <v>13.69420120231332</v>
       </c>
       <c r="D182" t="n">
-        <v>13.13993586710555</v>
+        <v>13.13993492912112</v>
       </c>
       <c r="E182" t="n">
-        <v>13.65597694834105</v>
+        <v>13.65597597351942</v>
       </c>
       <c r="F182" t="n">
         <v>21252300</v>
@@ -4092,16 +4092,16 @@
         <v>44522</v>
       </c>
       <c r="B184" t="n">
-        <v>13.17815971374512</v>
+        <v>13.1781587600708</v>
       </c>
       <c r="C184" t="n">
-        <v>13.569968523517</v>
+        <v>13.56996754148834</v>
       </c>
       <c r="D184" t="n">
-        <v>13.12082141680619</v>
+        <v>13.12082046728131</v>
       </c>
       <c r="E184" t="n">
-        <v>13.52218676129477</v>
+        <v>13.52218578272398</v>
       </c>
       <c r="F184" t="n">
         <v>12046100</v>
@@ -4132,16 +4132,16 @@
         <v>44524</v>
       </c>
       <c r="B186" t="n">
-        <v>13.11126613616943</v>
+        <v>13.11126708984375</v>
       </c>
       <c r="C186" t="n">
-        <v>13.38839927066881</v>
+        <v>13.38840024450097</v>
       </c>
       <c r="D186" t="n">
-        <v>12.97747738072233</v>
+        <v>12.97747832466525</v>
       </c>
       <c r="E186" t="n">
-        <v>13.09215306623642</v>
+        <v>13.09215401852051</v>
       </c>
       <c r="F186" t="n">
         <v>5705900</v>
@@ -4192,16 +4192,16 @@
         <v>44529</v>
       </c>
       <c r="B189" t="n">
-        <v>12.47099304199219</v>
+        <v>12.4709939956665</v>
       </c>
       <c r="C189" t="n">
-        <v>13.11126631153039</v>
+        <v>13.1112673141673</v>
       </c>
       <c r="D189" t="n">
-        <v>12.42321127788191</v>
+        <v>12.42321222790229</v>
       </c>
       <c r="E189" t="n">
-        <v>12.88191402607333</v>
+        <v>12.88191501117135</v>
       </c>
       <c r="F189" t="n">
         <v>13464500</v>
@@ -4212,16 +4212,16 @@
         <v>44530</v>
       </c>
       <c r="B190" t="n">
-        <v>12.18430423736572</v>
+        <v>12.18430328369141</v>
       </c>
       <c r="C190" t="n">
-        <v>12.44232523513989</v>
+        <v>12.44232426127008</v>
       </c>
       <c r="D190" t="n">
-        <v>11.84027715169492</v>
+        <v>11.84027622494785</v>
       </c>
       <c r="E190" t="n">
-        <v>12.38498693184738</v>
+        <v>12.38498596246548</v>
       </c>
       <c r="F190" t="n">
         <v>16793700</v>
@@ -4232,16 +4232,16 @@
         <v>44531</v>
       </c>
       <c r="B191" t="n">
-        <v>11.91672801971436</v>
+        <v>11.91672515869141</v>
       </c>
       <c r="C191" t="n">
-        <v>12.37543081618034</v>
+        <v>12.37542784502991</v>
       </c>
       <c r="D191" t="n">
-        <v>11.81160794533648</v>
+        <v>11.81160510955125</v>
       </c>
       <c r="E191" t="n">
-        <v>12.29898035010268</v>
+        <v>12.29897739730683</v>
       </c>
       <c r="F191" t="n">
         <v>5991300</v>
@@ -4312,16 +4312,16 @@
         <v>44537</v>
       </c>
       <c r="B195" t="n">
-        <v>13.42662525177002</v>
+        <v>13.4266242980957</v>
       </c>
       <c r="C195" t="n">
-        <v>13.7610957920937</v>
+        <v>13.76109481466241</v>
       </c>
       <c r="D195" t="n">
-        <v>13.40751218076567</v>
+        <v>13.40751122844893</v>
       </c>
       <c r="E195" t="n">
-        <v>13.56996963885711</v>
+        <v>13.56996867500125</v>
       </c>
       <c r="F195" t="n">
         <v>14090400</v>
@@ -4352,16 +4352,16 @@
         <v>44539</v>
       </c>
       <c r="B197" t="n">
-        <v>13.58908271789551</v>
+        <v>13.58908176422119</v>
       </c>
       <c r="C197" t="n">
-        <v>13.74198364057517</v>
+        <v>13.74198267617036</v>
       </c>
       <c r="D197" t="n">
-        <v>13.43618179521584</v>
+        <v>13.43618085227203</v>
       </c>
       <c r="E197" t="n">
-        <v>13.74198364057517</v>
+        <v>13.74198267617036</v>
       </c>
       <c r="F197" t="n">
         <v>9843600</v>
@@ -4452,16 +4452,16 @@
         <v>44546</v>
       </c>
       <c r="B202" t="n">
-        <v>13.89488410949707</v>
+        <v>13.89488315582275</v>
       </c>
       <c r="C202" t="n">
-        <v>14.28669293890897</v>
+        <v>14.28669195834289</v>
       </c>
       <c r="D202" t="n">
-        <v>13.82799018584958</v>
+        <v>13.82798923676653</v>
       </c>
       <c r="E202" t="n">
-        <v>14.21024248006574</v>
+        <v>14.21024150474683</v>
       </c>
       <c r="F202" t="n">
         <v>5287600</v>
@@ -4472,16 +4472,16 @@
         <v>44547</v>
       </c>
       <c r="B203" t="n">
-        <v>13.81843280792236</v>
+        <v>13.81843376159668</v>
       </c>
       <c r="C203" t="n">
-        <v>14.00955894337442</v>
+        <v>14.00955991023924</v>
       </c>
       <c r="D203" t="n">
-        <v>13.64641883033486</v>
+        <v>13.6464197721377</v>
       </c>
       <c r="E203" t="n">
-        <v>13.84710150039985</v>
+        <v>13.84710245605272</v>
       </c>
       <c r="F203" t="n">
         <v>8250000</v>
@@ -4532,16 +4532,16 @@
         <v>44552</v>
       </c>
       <c r="B206" t="n">
-        <v>13.53174209594727</v>
+        <v>13.5317440032959</v>
       </c>
       <c r="C206" t="n">
-        <v>13.66553083603216</v>
+        <v>13.66553276223881</v>
       </c>
       <c r="D206" t="n">
-        <v>13.29283421738503</v>
+        <v>13.29283609105872</v>
       </c>
       <c r="E206" t="n">
-        <v>13.58908038780114</v>
+        <v>13.58908230323182</v>
       </c>
       <c r="F206" t="n">
         <v>6990400</v>
@@ -4552,16 +4552,16 @@
         <v>44553</v>
       </c>
       <c r="B207" t="n">
-        <v>13.46484851837158</v>
+        <v>13.4648494720459</v>
       </c>
       <c r="C207" t="n">
-        <v>13.65597464372962</v>
+        <v>13.65597561094082</v>
       </c>
       <c r="D207" t="n">
-        <v>13.32150324083211</v>
+        <v>13.32150418435372</v>
       </c>
       <c r="E207" t="n">
-        <v>13.41706675919176</v>
+        <v>13.41706770948184</v>
       </c>
       <c r="F207" t="n">
         <v>4198000</v>
@@ -4632,16 +4632,16 @@
         <v>44560</v>
       </c>
       <c r="B211" t="n">
-        <v>12.38498497009277</v>
+        <v>12.38498592376709</v>
       </c>
       <c r="C211" t="n">
-        <v>12.499660647152</v>
+        <v>12.49966160965662</v>
       </c>
       <c r="D211" t="n">
-        <v>12.25119622450971</v>
+        <v>12.25119716788196</v>
       </c>
       <c r="E211" t="n">
-        <v>12.32764667588253</v>
+        <v>12.32764762514165</v>
       </c>
       <c r="F211" t="n">
         <v>5913100</v>
@@ -4652,16 +4652,16 @@
         <v>44564</v>
       </c>
       <c r="B212" t="n">
-        <v>12.1556339263916</v>
+        <v>12.15563488006592</v>
       </c>
       <c r="C212" t="n">
-        <v>12.49966096635466</v>
+        <v>12.49966194701974</v>
       </c>
       <c r="D212" t="n">
-        <v>11.84983120172981</v>
+        <v>11.84983213141227</v>
       </c>
       <c r="E212" t="n">
-        <v>12.49966096635466</v>
+        <v>12.49966194701974</v>
       </c>
       <c r="F212" t="n">
         <v>16124600</v>
@@ -4672,16 +4672,16 @@
         <v>44565</v>
       </c>
       <c r="B213" t="n">
-        <v>12.1556339263916</v>
+        <v>12.15563488006592</v>
       </c>
       <c r="C213" t="n">
-        <v>12.25119653736736</v>
+        <v>12.25119749853907</v>
       </c>
       <c r="D213" t="n">
-        <v>11.89761296289834</v>
+        <v>11.89761389632953</v>
       </c>
       <c r="E213" t="n">
-        <v>12.20341568756013</v>
+        <v>12.20341664498318</v>
       </c>
       <c r="F213" t="n">
         <v>9389900</v>
@@ -4752,16 +4752,16 @@
         <v>44571</v>
       </c>
       <c r="B217" t="n">
-        <v>10.79863739013672</v>
+        <v>10.79863834381104</v>
       </c>
       <c r="C217" t="n">
-        <v>10.8559747764533</v>
+        <v>10.85597573519133</v>
       </c>
       <c r="D217" t="n">
-        <v>10.54061641762812</v>
+        <v>10.54061734851548</v>
       </c>
       <c r="E217" t="n">
-        <v>10.76041216213855</v>
+        <v>10.76041311243704</v>
       </c>
       <c r="F217" t="n">
         <v>8755800</v>
@@ -4772,16 +4772,16 @@
         <v>44572</v>
       </c>
       <c r="B218" t="n">
-        <v>10.94198226928711</v>
+        <v>10.94198322296143</v>
       </c>
       <c r="C218" t="n">
-        <v>10.96109533984372</v>
+        <v>10.96109629518389</v>
       </c>
       <c r="D218" t="n">
-        <v>10.66484912574574</v>
+        <v>10.66485005526586</v>
       </c>
       <c r="E218" t="n">
-        <v>10.7030743554976</v>
+        <v>10.70307528834934</v>
       </c>
       <c r="F218" t="n">
         <v>6045500</v>
@@ -4832,16 +4832,16 @@
         <v>44575</v>
       </c>
       <c r="B221" t="n">
-        <v>11.59181213378906</v>
+        <v>11.59181118011475</v>
       </c>
       <c r="C221" t="n">
-        <v>11.65870605828779</v>
+        <v>11.65870509911001</v>
       </c>
       <c r="D221" t="n">
-        <v>11.39112944893152</v>
+        <v>11.39112851176765</v>
       </c>
       <c r="E221" t="n">
-        <v>11.41024160820486</v>
+        <v>11.4102406694686</v>
       </c>
       <c r="F221" t="n">
         <v>7586600</v>
@@ -4852,16 +4852,16 @@
         <v>44578</v>
       </c>
       <c r="B222" t="n">
-        <v>11.47713565826416</v>
+        <v>11.47713661193848</v>
       </c>
       <c r="C222" t="n">
-        <v>11.6109234981016</v>
+        <v>11.61092446289281</v>
       </c>
       <c r="D222" t="n">
-        <v>11.41024082698413</v>
+        <v>11.41024177509993</v>
       </c>
       <c r="E222" t="n">
-        <v>11.59181134013681</v>
+        <v>11.59181230333992</v>
       </c>
       <c r="F222" t="n">
         <v>4569300</v>
@@ -4872,16 +4872,16 @@
         <v>44579</v>
       </c>
       <c r="B223" t="n">
-        <v>11.39112949371338</v>
+        <v>11.39112854003906</v>
       </c>
       <c r="C223" t="n">
-        <v>11.49624864853339</v>
+        <v>11.49624768605842</v>
       </c>
       <c r="D223" t="n">
-        <v>11.29556596288691</v>
+        <v>11.29556501721325</v>
       </c>
       <c r="E223" t="n">
-        <v>11.47713648918492</v>
+        <v>11.47713552831003</v>
       </c>
       <c r="F223" t="n">
         <v>7771300</v>
@@ -4892,16 +4892,16 @@
         <v>44580</v>
       </c>
       <c r="B224" t="n">
-        <v>11.49624919891357</v>
+        <v>11.49624729156494</v>
       </c>
       <c r="C224" t="n">
-        <v>11.69693189416769</v>
+        <v>11.69692995352369</v>
       </c>
       <c r="D224" t="n">
-        <v>11.4197987351369</v>
+        <v>11.41979684047221</v>
       </c>
       <c r="E224" t="n">
-        <v>11.4197987351369</v>
+        <v>11.41979684047221</v>
       </c>
       <c r="F224" t="n">
         <v>5074700</v>
@@ -4952,16 +4952,16 @@
         <v>44585</v>
       </c>
       <c r="B227" t="n">
-        <v>11.50580406188965</v>
+        <v>11.50580596923828</v>
       </c>
       <c r="C227" t="n">
-        <v>11.6395928097279</v>
+        <v>11.63959473925506</v>
       </c>
       <c r="D227" t="n">
-        <v>11.32423446465893</v>
+        <v>11.32423634190827</v>
       </c>
       <c r="E227" t="n">
-        <v>11.4675788355589</v>
+        <v>11.46758073657084</v>
       </c>
       <c r="F227" t="n">
         <v>6551900</v>
@@ -4992,16 +4992,16 @@
         <v>44587</v>
       </c>
       <c r="B229" t="n">
-        <v>11.73515605926514</v>
+        <v>11.73515701293945</v>
       </c>
       <c r="C229" t="n">
-        <v>12.21297187011393</v>
+        <v>12.21297286261863</v>
       </c>
       <c r="D229" t="n">
-        <v>11.73515605926514</v>
+        <v>11.73515701293945</v>
       </c>
       <c r="E229" t="n">
-        <v>11.81160651609204</v>
+        <v>11.81160747597921</v>
       </c>
       <c r="F229" t="n">
         <v>11052300</v>
@@ -5012,16 +5012,16 @@
         <v>44588</v>
       </c>
       <c r="B230" t="n">
-        <v>11.99317741394043</v>
+        <v>11.99317646026611</v>
       </c>
       <c r="C230" t="n">
-        <v>12.13652179718475</v>
+        <v>12.13652083211196</v>
       </c>
       <c r="D230" t="n">
-        <v>11.66826250646786</v>
+        <v>11.66826157863015</v>
       </c>
       <c r="E230" t="n">
-        <v>11.85938865458074</v>
+        <v>11.85938771154504</v>
       </c>
       <c r="F230" t="n">
         <v>13761300</v>
@@ -5052,16 +5052,16 @@
         <v>44592</v>
       </c>
       <c r="B232" t="n">
-        <v>11.97406482696533</v>
+        <v>11.9740629196167</v>
       </c>
       <c r="C232" t="n">
-        <v>12.12696575162983</v>
+        <v>12.12696381992561</v>
       </c>
       <c r="D232" t="n">
-        <v>11.76382651123235</v>
+        <v>11.76382463737258</v>
       </c>
       <c r="E232" t="n">
-        <v>11.81160736666896</v>
+        <v>11.81160548519817</v>
       </c>
       <c r="F232" t="n">
         <v>12073700</v>
@@ -5152,16 +5152,16 @@
         <v>44599</v>
       </c>
       <c r="B237" t="n">
-        <v>12.20341777801514</v>
+        <v>12.20341682434082</v>
       </c>
       <c r="C237" t="n">
-        <v>12.60478227104545</v>
+        <v>12.60478128600524</v>
       </c>
       <c r="D237" t="n">
-        <v>12.20341777801514</v>
+        <v>12.20341682434082</v>
       </c>
       <c r="E237" t="n">
-        <v>12.29898040536085</v>
+        <v>12.29897944421849</v>
       </c>
       <c r="F237" t="n">
         <v>7212000</v>
@@ -5172,16 +5172,16 @@
         <v>44600</v>
       </c>
       <c r="B238" t="n">
-        <v>11.95495223999023</v>
+        <v>11.95495128631592</v>
       </c>
       <c r="C238" t="n">
-        <v>12.20341668937472</v>
+        <v>12.20341571587981</v>
       </c>
       <c r="D238" t="n">
-        <v>11.83072001529799</v>
+        <v>11.83071907153397</v>
       </c>
       <c r="E238" t="n">
-        <v>12.14607838899316</v>
+        <v>12.14607742007226</v>
       </c>
       <c r="F238" t="n">
         <v>8002100</v>
@@ -5192,16 +5192,16 @@
         <v>44601</v>
       </c>
       <c r="B239" t="n">
-        <v>12.05051422119141</v>
+        <v>12.05051517486572</v>
       </c>
       <c r="C239" t="n">
-        <v>12.28942212264425</v>
+        <v>12.28942309522567</v>
       </c>
       <c r="D239" t="n">
-        <v>11.91672637964906</v>
+        <v>11.91672732273544</v>
       </c>
       <c r="E239" t="n">
-        <v>11.95495160742706</v>
+        <v>11.95495255353858</v>
       </c>
       <c r="F239" t="n">
         <v>9060800</v>
@@ -5252,16 +5252,16 @@
         <v>44606</v>
       </c>
       <c r="B242" t="n">
-        <v>11.78293895721436</v>
+        <v>11.78293800354004</v>
       </c>
       <c r="C242" t="n">
-        <v>11.97406511768535</v>
+        <v>11.97406414854188</v>
       </c>
       <c r="D242" t="n">
-        <v>11.63959456470146</v>
+        <v>11.639593622629</v>
       </c>
       <c r="E242" t="n">
-        <v>11.79249549307826</v>
+        <v>11.79249453863047</v>
       </c>
       <c r="F242" t="n">
         <v>5445000</v>
@@ -5292,16 +5292,16 @@
         <v>44608</v>
       </c>
       <c r="B244" t="n">
-        <v>12.47099304199219</v>
+        <v>12.4709939956665</v>
       </c>
       <c r="C244" t="n">
-        <v>12.6430061168833</v>
+        <v>12.64300708371169</v>
       </c>
       <c r="D244" t="n">
-        <v>11.56314316934232</v>
+        <v>11.56314405359208</v>
       </c>
       <c r="E244" t="n">
-        <v>11.65870578620152</v>
+        <v>11.65870667775909</v>
       </c>
       <c r="F244" t="n">
         <v>21489000</v>
@@ -5312,16 +5312,16 @@
         <v>44609</v>
       </c>
       <c r="B245" t="n">
-        <v>12.66211795806885</v>
+        <v>12.66211891174316</v>
       </c>
       <c r="C245" t="n">
-        <v>12.94880760354266</v>
+        <v>12.94880857880961</v>
       </c>
       <c r="D245" t="n">
-        <v>12.46143529737331</v>
+        <v>12.46143623593278</v>
       </c>
       <c r="E245" t="n">
-        <v>12.46143529737331</v>
+        <v>12.46143623593278</v>
       </c>
       <c r="F245" t="n">
         <v>10362100</v>
@@ -5352,16 +5352,16 @@
         <v>44613</v>
       </c>
       <c r="B247" t="n">
-        <v>11.90716934204102</v>
+        <v>11.90717124938965</v>
       </c>
       <c r="C247" t="n">
-        <v>12.27986598065907</v>
+        <v>12.27986794770807</v>
       </c>
       <c r="D247" t="n">
-        <v>11.72559974560327</v>
+        <v>11.72560162386719</v>
       </c>
       <c r="E247" t="n">
-        <v>12.13652069902384</v>
+        <v>12.1365226431111</v>
       </c>
       <c r="F247" t="n">
         <v>4718800</v>
@@ -5392,16 +5392,16 @@
         <v>44615</v>
       </c>
       <c r="B249" t="n">
-        <v>12.73857021331787</v>
+        <v>12.73856925964355</v>
       </c>
       <c r="C249" t="n">
-        <v>12.87235897652213</v>
+        <v>12.87235801283171</v>
       </c>
       <c r="D249" t="n">
-        <v>12.51877536451236</v>
+        <v>12.51877442729301</v>
       </c>
       <c r="E249" t="n">
-        <v>12.51877536451236</v>
+        <v>12.51877442729301</v>
       </c>
       <c r="F249" t="n">
         <v>5598100</v>
@@ -5432,16 +5432,16 @@
         <v>44617</v>
       </c>
       <c r="B251" t="n">
-        <v>12.86280250549316</v>
+        <v>12.86280155181885</v>
       </c>
       <c r="C251" t="n">
-        <v>13.13993565745039</v>
+        <v>13.13993468322886</v>
       </c>
       <c r="D251" t="n">
-        <v>12.72901374161811</v>
+        <v>12.72901279786317</v>
       </c>
       <c r="E251" t="n">
-        <v>12.83413381014901</v>
+        <v>12.83413285860025</v>
       </c>
       <c r="F251" t="n">
         <v>8089600</v>
@@ -5472,16 +5472,16 @@
         <v>44623</v>
       </c>
       <c r="B253" t="n">
-        <v>12.56655502319336</v>
+        <v>12.56655597686768</v>
       </c>
       <c r="C253" t="n">
-        <v>12.95836473998952</v>
+        <v>12.95836572339823</v>
       </c>
       <c r="D253" t="n">
-        <v>12.337203660699</v>
+        <v>12.33720459696787</v>
       </c>
       <c r="E253" t="n">
-        <v>12.80546292029864</v>
+        <v>12.80546389210365</v>
       </c>
       <c r="F253" t="n">
         <v>12631200</v>
@@ -5492,16 +5492,16 @@
         <v>44624</v>
       </c>
       <c r="B254" t="n">
-        <v>12.14607810974121</v>
+        <v>12.14607715606689</v>
       </c>
       <c r="C254" t="n">
-        <v>12.64300608572388</v>
+        <v>12.64300509303224</v>
       </c>
       <c r="D254" t="n">
-        <v>12.13652157467044</v>
+        <v>12.13652062174647</v>
       </c>
       <c r="E254" t="n">
-        <v>12.64300608572388</v>
+        <v>12.64300509303224</v>
       </c>
       <c r="F254" t="n">
         <v>6563400</v>
@@ -5512,16 +5512,16 @@
         <v>44627</v>
       </c>
       <c r="B255" t="n">
-        <v>11.73515605926514</v>
+        <v>11.73515701293945</v>
       </c>
       <c r="C255" t="n">
-        <v>12.17474664170048</v>
+        <v>12.17474763109875</v>
       </c>
       <c r="D255" t="n">
-        <v>11.68737429590799</v>
+        <v>11.68737524569925</v>
       </c>
       <c r="E255" t="n">
-        <v>12.08873964992988</v>
+        <v>12.08874063233868</v>
       </c>
       <c r="F255" t="n">
         <v>12255900</v>
@@ -5552,16 +5552,16 @@
         <v>44629</v>
       </c>
       <c r="B257" t="n">
-        <v>12.80546379089355</v>
+        <v>12.80546283721924</v>
       </c>
       <c r="C257" t="n">
-        <v>13.03481608034201</v>
+        <v>13.0348151095869</v>
       </c>
       <c r="D257" t="n">
-        <v>11.75426951898038</v>
+        <v>11.75426864359272</v>
       </c>
       <c r="E257" t="n">
-        <v>11.89761390244447</v>
+        <v>11.89761301638138</v>
       </c>
       <c r="F257" t="n">
         <v>14771600</v>
@@ -5572,16 +5572,16 @@
         <v>44630</v>
       </c>
       <c r="B258" t="n">
-        <v>12.71945762634277</v>
+        <v>12.71945667266846</v>
       </c>
       <c r="C258" t="n">
-        <v>13.02525946183787</v>
+        <v>13.02525848523527</v>
       </c>
       <c r="D258" t="n">
-        <v>12.24164180270101</v>
+        <v>12.24164088485217</v>
       </c>
       <c r="E258" t="n">
-        <v>12.67167586170632</v>
+        <v>12.67167491161457</v>
       </c>
       <c r="F258" t="n">
         <v>9185900</v>
@@ -5672,16 +5672,16 @@
         <v>44637</v>
       </c>
       <c r="B263" t="n">
-        <v>13.12082195281982</v>
+        <v>13.12082099914551</v>
       </c>
       <c r="C263" t="n">
-        <v>13.24505417512824</v>
+        <v>13.24505321242422</v>
       </c>
       <c r="D263" t="n">
-        <v>12.87235841956435</v>
+        <v>12.87235748394937</v>
       </c>
       <c r="E263" t="n">
-        <v>13.09215325885984</v>
+        <v>13.09215230726928</v>
       </c>
       <c r="F263" t="n">
         <v>6159800</v>
@@ -5692,16 +5692,16 @@
         <v>44638</v>
       </c>
       <c r="B264" t="n">
-        <v>13.58908271789551</v>
+        <v>13.58908176422119</v>
       </c>
       <c r="C264" t="n">
-        <v>13.78020887124509</v>
+        <v>13.78020790415765</v>
       </c>
       <c r="D264" t="n">
-        <v>12.98703465132328</v>
+        <v>12.98703373990036</v>
       </c>
       <c r="E264" t="n">
-        <v>13.04437204164746</v>
+        <v>13.04437112620064</v>
       </c>
       <c r="F264" t="n">
         <v>10366600</v>
@@ -5732,16 +5732,16 @@
         <v>44642</v>
       </c>
       <c r="B266" t="n">
-        <v>14.08600997924805</v>
+        <v>14.08600902557373</v>
       </c>
       <c r="C266" t="n">
-        <v>14.26758049894657</v>
+        <v>14.26757953297927</v>
       </c>
       <c r="D266" t="n">
-        <v>13.62730723522063</v>
+        <v>13.62730631260216</v>
       </c>
       <c r="E266" t="n">
-        <v>13.66553246388958</v>
+        <v>13.66553153868313</v>
       </c>
       <c r="F266" t="n">
         <v>13737200</v>
@@ -5772,16 +5772,16 @@
         <v>44644</v>
       </c>
       <c r="B268" t="n">
-        <v>14.63072109222412</v>
+        <v>14.6307201385498</v>
       </c>
       <c r="C268" t="n">
-        <v>14.74539678187754</v>
+        <v>14.74539582072832</v>
       </c>
       <c r="D268" t="n">
-        <v>14.35358794772134</v>
+        <v>14.35358701211139</v>
       </c>
       <c r="E268" t="n">
-        <v>14.39181317760581</v>
+        <v>14.39181223950423</v>
       </c>
       <c r="F268" t="n">
         <v>7986800</v>
@@ -5792,16 +5792,16 @@
         <v>44645</v>
       </c>
       <c r="B269" t="n">
-        <v>15.13720417022705</v>
+        <v>15.13720512390137</v>
       </c>
       <c r="C269" t="n">
-        <v>15.24232331452872</v>
+        <v>15.24232427482575</v>
       </c>
       <c r="D269" t="n">
-        <v>14.64027531783091</v>
+        <v>14.64027624019771</v>
       </c>
       <c r="E269" t="n">
-        <v>14.71672577029781</v>
+        <v>14.71672669748114</v>
       </c>
       <c r="F269" t="n">
         <v>8426200</v>
@@ -5812,16 +5812,16 @@
         <v>44648</v>
       </c>
       <c r="B270" t="n">
-        <v>15.51945686340332</v>
+        <v>15.51945781707764</v>
       </c>
       <c r="C270" t="n">
-        <v>15.7774778311631</v>
+        <v>15.77747880069286</v>
       </c>
       <c r="D270" t="n">
-        <v>14.97474714661442</v>
+        <v>14.9747480668162</v>
       </c>
       <c r="E270" t="n">
-        <v>15.19454197571826</v>
+        <v>15.19454290942648</v>
       </c>
       <c r="F270" t="n">
         <v>14496800</v>
@@ -5832,16 +5832,16 @@
         <v>44649</v>
       </c>
       <c r="B271" t="n">
-        <v>15.50034427642822</v>
+        <v>15.50034236907959</v>
       </c>
       <c r="C271" t="n">
-        <v>15.93037923607671</v>
+        <v>15.93037727581141</v>
       </c>
       <c r="D271" t="n">
-        <v>15.43345035442127</v>
+        <v>15.43344845530407</v>
       </c>
       <c r="E271" t="n">
-        <v>15.72969564733319</v>
+        <v>15.72969371176241</v>
       </c>
       <c r="F271" t="n">
         <v>7323700</v>
@@ -5852,16 +5852,16 @@
         <v>44650</v>
       </c>
       <c r="B272" t="n">
-        <v>15.45256423950195</v>
+        <v>15.45256328582764</v>
       </c>
       <c r="C272" t="n">
-        <v>15.82526000904275</v>
+        <v>15.82525903236704</v>
       </c>
       <c r="D272" t="n">
-        <v>15.3952268494317</v>
+        <v>15.39522589929603</v>
       </c>
       <c r="E272" t="n">
-        <v>15.51945816503771</v>
+        <v>15.51945720723495</v>
       </c>
       <c r="F272" t="n">
         <v>8944100</v>
@@ -5872,16 +5872,16 @@
         <v>44651</v>
       </c>
       <c r="B273" t="n">
-        <v>15.56724071502686</v>
+        <v>15.56724166870117</v>
       </c>
       <c r="C273" t="n">
-        <v>15.81570334420647</v>
+        <v>15.81570431310201</v>
       </c>
       <c r="D273" t="n">
-        <v>15.42389450693963</v>
+        <v>15.42389545183233</v>
       </c>
       <c r="E273" t="n">
-        <v>15.42389450693963</v>
+        <v>15.42389545183233</v>
       </c>
       <c r="F273" t="n">
         <v>17319900</v>
@@ -5892,16 +5892,16 @@
         <v>44652</v>
       </c>
       <c r="B274" t="n">
-        <v>15.74880599975586</v>
+        <v>15.74880886077881</v>
       </c>
       <c r="C274" t="n">
-        <v>15.97815733108562</v>
+        <v>15.97816023377391</v>
       </c>
       <c r="D274" t="n">
-        <v>15.47167382458661</v>
+        <v>15.47167663526406</v>
       </c>
       <c r="E274" t="n">
-        <v>15.72013822254111</v>
+        <v>15.7201410783561</v>
       </c>
       <c r="F274" t="n">
         <v>8302400</v>
@@ -5912,16 +5912,16 @@
         <v>44655</v>
       </c>
       <c r="B275" t="n">
-        <v>15.56724071502686</v>
+        <v>15.56724166870117</v>
       </c>
       <c r="C275" t="n">
-        <v>15.86348602114313</v>
+        <v>15.86348699296592</v>
       </c>
       <c r="D275" t="n">
-        <v>15.52901457347753</v>
+        <v>15.52901552481005</v>
       </c>
       <c r="E275" t="n">
-        <v>15.75836595460524</v>
+        <v>15.75836691998819</v>
       </c>
       <c r="F275" t="n">
         <v>2672100</v>
@@ -5932,16 +5932,16 @@
         <v>44656</v>
       </c>
       <c r="B276" t="n">
-        <v>15.45256423950195</v>
+        <v>15.45256328582764</v>
       </c>
       <c r="C276" t="n">
-        <v>15.65324601610922</v>
+        <v>15.65324505004958</v>
       </c>
       <c r="D276" t="n">
-        <v>15.35700070756969</v>
+        <v>15.35699975979319</v>
       </c>
       <c r="E276" t="n">
-        <v>15.57679555510796</v>
+        <v>15.57679459376655</v>
       </c>
       <c r="F276" t="n">
         <v>10716200</v>
@@ -5952,16 +5952,16 @@
         <v>44657</v>
       </c>
       <c r="B277" t="n">
-        <v>15.56724071502686</v>
+        <v>15.56724166870117</v>
       </c>
       <c r="C277" t="n">
-        <v>15.701028565004</v>
+        <v>15.70102952687437</v>
       </c>
       <c r="D277" t="n">
-        <v>15.13720573621069</v>
+        <v>15.13720666354036</v>
       </c>
       <c r="E277" t="n">
-        <v>15.38567018811306</v>
+        <v>15.38567113066407</v>
       </c>
       <c r="F277" t="n">
         <v>10924400</v>
@@ -5972,16 +5972,16 @@
         <v>44658</v>
       </c>
       <c r="B278" t="n">
-        <v>15.38567066192627</v>
+        <v>15.38566875457764</v>
       </c>
       <c r="C278" t="n">
-        <v>15.52901505170514</v>
+        <v>15.52901312658622</v>
       </c>
       <c r="D278" t="n">
-        <v>15.25188189646763</v>
+        <v>15.25188000570468</v>
       </c>
       <c r="E278" t="n">
-        <v>15.366557590563</v>
+        <v>15.3665556855838</v>
       </c>
       <c r="F278" t="n">
         <v>6566700</v>
@@ -5992,16 +5992,16 @@
         <v>44659</v>
       </c>
       <c r="B279" t="n">
-        <v>15.40478134155273</v>
+        <v>15.40478229522705</v>
       </c>
       <c r="C279" t="n">
-        <v>15.5767934889472</v>
+        <v>15.57679445327038</v>
       </c>
       <c r="D279" t="n">
-        <v>15.07030993551665</v>
+        <v>15.07031086848462</v>
       </c>
       <c r="E279" t="n">
-        <v>15.32833089069213</v>
+        <v>15.32833183963358</v>
       </c>
       <c r="F279" t="n">
         <v>3069100</v>
@@ -6012,16 +6012,16 @@
         <v>44662</v>
       </c>
       <c r="B280" t="n">
-        <v>15.29010677337646</v>
+        <v>15.29010581970215</v>
       </c>
       <c r="C280" t="n">
-        <v>15.4907885498701</v>
+        <v>15.49078758367887</v>
       </c>
       <c r="D280" t="n">
-        <v>15.21365631241849</v>
+        <v>15.21365536351254</v>
       </c>
       <c r="E280" t="n">
-        <v>15.38567030525462</v>
+        <v>15.38566934561982</v>
       </c>
       <c r="F280" t="n">
         <v>10289300</v>
@@ -6072,16 +6072,16 @@
         <v>44665</v>
       </c>
       <c r="B283" t="n">
-        <v>15.64369201660156</v>
+        <v>15.64369106292725</v>
       </c>
       <c r="C283" t="n">
-        <v>15.79659294557522</v>
+        <v>15.79659198257972</v>
       </c>
       <c r="D283" t="n">
-        <v>15.4812345517267</v>
+        <v>15.48123360795615</v>
       </c>
       <c r="E283" t="n">
-        <v>15.72014248108839</v>
+        <v>15.72014152275348</v>
       </c>
       <c r="F283" t="n">
         <v>4607000</v>
@@ -6092,16 +6092,16 @@
         <v>44669</v>
       </c>
       <c r="B284" t="n">
-        <v>15.31877708435059</v>
+        <v>15.31877613067627</v>
       </c>
       <c r="C284" t="n">
-        <v>15.67235979902336</v>
+        <v>15.67235882333666</v>
       </c>
       <c r="D284" t="n">
-        <v>15.31877708435059</v>
+        <v>15.31877613067627</v>
       </c>
       <c r="E284" t="n">
-        <v>15.56724154957292</v>
+        <v>15.56724058043038</v>
       </c>
       <c r="F284" t="n">
         <v>3539900</v>
@@ -6132,16 +6132,16 @@
         <v>44671</v>
       </c>
       <c r="B286" t="n">
-        <v>15.85393047332764</v>
+        <v>15.85392951965332</v>
       </c>
       <c r="C286" t="n">
-        <v>16.33174633612178</v>
+        <v>16.33174535370502</v>
       </c>
       <c r="D286" t="n">
-        <v>15.72014261501659</v>
+        <v>15.72014166939012</v>
       </c>
       <c r="E286" t="n">
-        <v>15.74881040024161</v>
+        <v>15.74880945289066</v>
       </c>
       <c r="F286" t="n">
         <v>12326800</v>
@@ -6152,16 +6152,16 @@
         <v>44673</v>
       </c>
       <c r="B287" t="n">
-        <v>15.31877708435059</v>
+        <v>15.31877613067627</v>
       </c>
       <c r="C287" t="n">
-        <v>15.7488102634977</v>
+        <v>15.74880928305156</v>
       </c>
       <c r="D287" t="n">
-        <v>15.1467630836026</v>
+        <v>15.14676214063706</v>
       </c>
       <c r="E287" t="n">
-        <v>15.7488102634977</v>
+        <v>15.74880928305156</v>
       </c>
       <c r="F287" t="n">
         <v>8878800</v>
@@ -6172,16 +6172,16 @@
         <v>44676</v>
       </c>
       <c r="B288" t="n">
-        <v>15.29966163635254</v>
+        <v>15.29966259002686</v>
       </c>
       <c r="C288" t="n">
-        <v>15.46211907596952</v>
+        <v>15.4621200397703</v>
       </c>
       <c r="D288" t="n">
-        <v>15.01297198341896</v>
+        <v>15.01297291922304</v>
       </c>
       <c r="E288" t="n">
-        <v>15.2805485675217</v>
+        <v>15.28054952000464</v>
       </c>
       <c r="F288" t="n">
         <v>6454900</v>
@@ -6192,16 +6192,16 @@
         <v>44677</v>
       </c>
       <c r="B289" t="n">
-        <v>15.12765026092529</v>
+        <v>15.12764835357666</v>
       </c>
       <c r="C289" t="n">
-        <v>15.30922080056303</v>
+        <v>15.30921887032133</v>
       </c>
       <c r="D289" t="n">
-        <v>15.02253109838233</v>
+        <v>15.02252920428749</v>
       </c>
       <c r="E289" t="n">
-        <v>15.21365726271565</v>
+        <v>15.21365534452294</v>
       </c>
       <c r="F289" t="n">
         <v>9387600</v>
@@ -6232,16 +6232,16 @@
         <v>44679</v>
       </c>
       <c r="B291" t="n">
-        <v>14.8409595489502</v>
+        <v>14.84095859527588</v>
       </c>
       <c r="C291" t="n">
-        <v>15.38567021943929</v>
+        <v>15.38566923076207</v>
       </c>
       <c r="D291" t="n">
-        <v>14.8409595489502</v>
+        <v>14.84095859527588</v>
       </c>
       <c r="E291" t="n">
-        <v>15.3283328297213</v>
+        <v>15.32833184472857</v>
       </c>
       <c r="F291" t="n">
         <v>5384600</v>
@@ -6252,16 +6252,16 @@
         <v>44680</v>
       </c>
       <c r="B292" t="n">
-        <v>14.72057151794434</v>
+        <v>14.72057247161865</v>
       </c>
       <c r="C292" t="n">
-        <v>15.13482874017579</v>
+        <v>15.13482972068782</v>
       </c>
       <c r="D292" t="n">
-        <v>14.72057151794434</v>
+        <v>14.72057247161865</v>
       </c>
       <c r="E292" t="n">
-        <v>15.06739185981573</v>
+        <v>15.06739283595885</v>
       </c>
       <c r="F292" t="n">
         <v>7651000</v>
@@ -6352,16 +6352,16 @@
         <v>44687</v>
       </c>
       <c r="B297" t="n">
-        <v>14.15217208862305</v>
+        <v>14.15217304229736</v>
       </c>
       <c r="C297" t="n">
-        <v>14.51825971060268</v>
+        <v>14.51826068894659</v>
       </c>
       <c r="D297" t="n">
-        <v>14.05583382100224</v>
+        <v>14.0558347681846</v>
       </c>
       <c r="E297" t="n">
-        <v>14.45082283139226</v>
+        <v>14.45082380519179</v>
       </c>
       <c r="F297" t="n">
         <v>6832100</v>
@@ -6372,16 +6372,16 @@
         <v>44690</v>
       </c>
       <c r="B298" t="n">
-        <v>14.21961212158203</v>
+        <v>14.2196102142334</v>
       </c>
       <c r="C298" t="n">
-        <v>14.32558450824887</v>
+        <v>14.32558258668562</v>
       </c>
       <c r="D298" t="n">
-        <v>13.92096133187191</v>
+        <v>13.92095946458282</v>
       </c>
       <c r="E298" t="n">
-        <v>14.04620192634656</v>
+        <v>14.04620004225831</v>
       </c>
       <c r="F298" t="n">
         <v>11844800</v>
@@ -6392,16 +6392,16 @@
         <v>44691</v>
       </c>
       <c r="B299" t="n">
-        <v>14.71093940734863</v>
+        <v>14.71093845367432</v>
       </c>
       <c r="C299" t="n">
-        <v>14.97105376396958</v>
+        <v>14.97105279343268</v>
       </c>
       <c r="D299" t="n">
-        <v>14.14254017782313</v>
+        <v>14.14253926099675</v>
       </c>
       <c r="E299" t="n">
-        <v>14.21961116635961</v>
+        <v>14.2196102445369</v>
       </c>
       <c r="F299" t="n">
         <v>13119700</v>
@@ -6412,16 +6412,16 @@
         <v>44692</v>
       </c>
       <c r="B300" t="n">
-        <v>14.60496616363525</v>
+        <v>14.60496520996094</v>
       </c>
       <c r="C300" t="n">
-        <v>14.7880104511626</v>
+        <v>14.78800948553586</v>
       </c>
       <c r="D300" t="n">
-        <v>14.4026545882811</v>
+        <v>14.40265364781732</v>
       </c>
       <c r="E300" t="n">
-        <v>14.45082418598612</v>
+        <v>14.45082324237696</v>
       </c>
       <c r="F300" t="n">
         <v>6181500</v>
@@ -6452,16 +6452,16 @@
         <v>44694</v>
       </c>
       <c r="B302" t="n">
-        <v>14.91324901580811</v>
+        <v>14.91324996948242</v>
       </c>
       <c r="C302" t="n">
-        <v>15.09629328979575</v>
+        <v>15.09629425517541</v>
       </c>
       <c r="D302" t="n">
-        <v>14.62423328847366</v>
+        <v>14.62423422366596</v>
       </c>
       <c r="E302" t="n">
-        <v>14.72057155799894</v>
+        <v>14.7205724993519</v>
       </c>
       <c r="F302" t="n">
         <v>5016200</v>
@@ -6472,16 +6472,16 @@
         <v>44697</v>
       </c>
       <c r="B303" t="n">
-        <v>14.80727767944336</v>
+        <v>14.80727672576904</v>
       </c>
       <c r="C303" t="n">
-        <v>14.9325182654693</v>
+        <v>14.93251730372877</v>
       </c>
       <c r="D303" t="n">
-        <v>14.6435015991601</v>
+        <v>14.64350065603391</v>
       </c>
       <c r="E303" t="n">
-        <v>14.9325182654693</v>
+        <v>14.93251730372877</v>
       </c>
       <c r="F303" t="n">
         <v>6824600</v>
@@ -6552,16 +6552,16 @@
         <v>44701</v>
       </c>
       <c r="B307" t="n">
-        <v>15.37567710876465</v>
+        <v>15.37567615509033</v>
       </c>
       <c r="C307" t="n">
-        <v>15.49128359304003</v>
+        <v>15.49128263219524</v>
       </c>
       <c r="D307" t="n">
-        <v>14.93251845966301</v>
+        <v>14.93251753347555</v>
       </c>
       <c r="E307" t="n">
-        <v>15.0288576559385</v>
+        <v>15.02885672377561</v>
       </c>
       <c r="F307" t="n">
         <v>8142900</v>
@@ -6572,16 +6572,16 @@
         <v>44704</v>
       </c>
       <c r="B308" t="n">
-        <v>15.28897190093994</v>
+        <v>15.28897285461426</v>
       </c>
       <c r="C308" t="n">
-        <v>15.63579135115902</v>
+        <v>15.63579232646676</v>
       </c>
       <c r="D308" t="n">
-        <v>15.17336541753358</v>
+        <v>15.17336636399676</v>
       </c>
       <c r="E308" t="n">
-        <v>15.52981988981818</v>
+        <v>15.52982085851578</v>
       </c>
       <c r="F308" t="n">
         <v>8474400</v>
@@ -6612,16 +6612,16 @@
         <v>44706</v>
       </c>
       <c r="B310" t="n">
-        <v>15.1444616317749</v>
+        <v>15.14446353912354</v>
       </c>
       <c r="C310" t="n">
-        <v>15.44311235575524</v>
+        <v>15.44311430071703</v>
       </c>
       <c r="D310" t="n">
-        <v>14.942150088113</v>
+        <v>14.94215196998178</v>
       </c>
       <c r="E310" t="n">
-        <v>15.16372891658348</v>
+        <v>15.16373082635871</v>
       </c>
       <c r="F310" t="n">
         <v>8129200</v>
@@ -6632,16 +6632,16 @@
         <v>44707</v>
       </c>
       <c r="B311" t="n">
-        <v>15.50091648101807</v>
+        <v>15.5009183883667</v>
       </c>
       <c r="C311" t="n">
-        <v>15.60688977236364</v>
+        <v>15.60689169275202</v>
       </c>
       <c r="D311" t="n">
-        <v>15.03848966141599</v>
+        <v>15.03849151186417</v>
       </c>
       <c r="E311" t="n">
-        <v>15.07702515315295</v>
+        <v>15.07702700834282</v>
       </c>
       <c r="F311" t="n">
         <v>6641000</v>
@@ -6672,16 +6672,16 @@
         <v>44711</v>
       </c>
       <c r="B313" t="n">
-        <v>15.26970386505127</v>
+        <v>15.26970481872559</v>
       </c>
       <c r="C313" t="n">
-        <v>15.4912827177024</v>
+        <v>15.4912836852155</v>
       </c>
       <c r="D313" t="n">
-        <v>15.16373057138454</v>
+        <v>15.16373151844026</v>
       </c>
       <c r="E313" t="n">
-        <v>15.23116837247026</v>
+        <v>15.23116932373783</v>
       </c>
       <c r="F313" t="n">
         <v>1706700</v>
@@ -6692,16 +6692,16 @@
         <v>44712</v>
       </c>
       <c r="B314" t="n">
-        <v>15.26007080078125</v>
+        <v>15.26006984710693</v>
       </c>
       <c r="C314" t="n">
-        <v>15.39494457461466</v>
+        <v>15.39494361251144</v>
       </c>
       <c r="D314" t="n">
-        <v>15.05775922127246</v>
+        <v>15.05775828024155</v>
       </c>
       <c r="E314" t="n">
-        <v>15.29860629598489</v>
+        <v>15.29860533990231</v>
       </c>
       <c r="F314" t="n">
         <v>5708500</v>
@@ -6732,16 +6732,16 @@
         <v>44714</v>
       </c>
       <c r="B316" t="n">
-        <v>15.30824089050293</v>
+        <v>15.30823993682861</v>
       </c>
       <c r="C316" t="n">
-        <v>15.41421327602245</v>
+        <v>15.41421231574625</v>
       </c>
       <c r="D316" t="n">
-        <v>14.88434951090744</v>
+        <v>14.88434858364075</v>
       </c>
       <c r="E316" t="n">
-        <v>15.06739380806508</v>
+        <v>15.06739286939508</v>
       </c>
       <c r="F316" t="n">
         <v>5285700</v>
@@ -6772,16 +6772,16 @@
         <v>44718</v>
       </c>
       <c r="B318" t="n">
-        <v>14.9036169052124</v>
+        <v>14.90361595153809</v>
       </c>
       <c r="C318" t="n">
-        <v>15.1348298712333</v>
+        <v>15.13482890276379</v>
       </c>
       <c r="D318" t="n">
-        <v>14.84581320432785</v>
+        <v>14.84581225435236</v>
       </c>
       <c r="E318" t="n">
-        <v>15.01922338822285</v>
+        <v>15.01922242715094</v>
       </c>
       <c r="F318" t="n">
         <v>2626600</v>
@@ -6852,16 +6852,16 @@
         <v>44722</v>
       </c>
       <c r="B322" t="n">
-        <v>14.48936080932617</v>
+        <v>14.48935985565186</v>
       </c>
       <c r="C322" t="n">
-        <v>15.019224587848</v>
+        <v>15.01922359929862</v>
       </c>
       <c r="D322" t="n">
-        <v>14.22924643146631</v>
+        <v>14.22924549491244</v>
       </c>
       <c r="E322" t="n">
-        <v>14.85544849414564</v>
+        <v>14.85544751637582</v>
       </c>
       <c r="F322" t="n">
         <v>15101900</v>
@@ -6892,16 +6892,16 @@
         <v>44726</v>
       </c>
       <c r="B324" t="n">
-        <v>14.05583381652832</v>
+        <v>14.05583477020264</v>
       </c>
       <c r="C324" t="n">
-        <v>14.2099757796794</v>
+        <v>14.2099767438121</v>
       </c>
       <c r="D324" t="n">
-        <v>13.84388815781629</v>
+        <v>13.84388909711031</v>
       </c>
       <c r="E324" t="n">
-        <v>14.01729832574055</v>
+        <v>14.01729927680027</v>
       </c>
       <c r="F324" t="n">
         <v>10130900</v>
@@ -6912,16 +6912,16 @@
         <v>44727</v>
       </c>
       <c r="B325" t="n">
-        <v>14.91324901580811</v>
+        <v>14.91324996948242</v>
       </c>
       <c r="C325" t="n">
-        <v>15.06739190081403</v>
+        <v>15.06739286434549</v>
       </c>
       <c r="D325" t="n">
-        <v>14.25814565925695</v>
+        <v>14.25814657103863</v>
       </c>
       <c r="E325" t="n">
-        <v>14.34485074496072</v>
+        <v>14.34485166228703</v>
       </c>
       <c r="F325" t="n">
         <v>25461900</v>
@@ -6932,16 +6932,16 @@
         <v>44729</v>
       </c>
       <c r="B326" t="n">
-        <v>14.94215297698975</v>
+        <v>14.94215202331543</v>
       </c>
       <c r="C326" t="n">
-        <v>15.18300005559206</v>
+        <v>15.18299908654582</v>
       </c>
       <c r="D326" t="n">
-        <v>14.56643120361701</v>
+        <v>14.56643027392291</v>
       </c>
       <c r="E326" t="n">
-        <v>14.63386809162287</v>
+        <v>14.63386715762466</v>
       </c>
       <c r="F326" t="n">
         <v>14099900</v>
@@ -7012,16 +7012,16 @@
         <v>44735</v>
       </c>
       <c r="B330" t="n">
-        <v>14.72057151794434</v>
+        <v>14.72057247161865</v>
       </c>
       <c r="C330" t="n">
-        <v>14.90361579143392</v>
+        <v>14.90361675696679</v>
       </c>
       <c r="D330" t="n">
-        <v>14.39301938118073</v>
+        <v>14.39302031363454</v>
       </c>
       <c r="E330" t="n">
-        <v>14.39301938118073</v>
+        <v>14.39302031363454</v>
       </c>
       <c r="F330" t="n">
         <v>3851900</v>
@@ -7032,16 +7032,16 @@
         <v>44736</v>
       </c>
       <c r="B331" t="n">
-        <v>14.42192268371582</v>
+        <v>14.4219217300415</v>
       </c>
       <c r="C331" t="n">
-        <v>14.86508132542095</v>
+        <v>14.86508034244202</v>
       </c>
       <c r="D331" t="n">
-        <v>14.25814660403618</v>
+        <v>14.25814566119184</v>
       </c>
       <c r="E331" t="n">
-        <v>14.86508132542095</v>
+        <v>14.86508034244202</v>
       </c>
       <c r="F331" t="n">
         <v>5803600</v>
@@ -7132,16 +7132,16 @@
         <v>44743</v>
       </c>
       <c r="B336" t="n">
-        <v>14.06546974182129</v>
+        <v>14.06546878814697</v>
       </c>
       <c r="C336" t="n">
-        <v>14.28704861287829</v>
+        <v>14.28704764418037</v>
       </c>
       <c r="D336" t="n">
-        <v>13.54524008938454</v>
+        <v>13.54523917098311</v>
       </c>
       <c r="E336" t="n">
-        <v>13.64157836946027</v>
+        <v>13.64157744452686</v>
       </c>
       <c r="F336" t="n">
         <v>10271400</v>
@@ -7172,16 +7172,16 @@
         <v>44747</v>
       </c>
       <c r="B338" t="n">
-        <v>14.17144012451172</v>
+        <v>14.17144107818604</v>
       </c>
       <c r="C338" t="n">
-        <v>14.19070741030283</v>
+        <v>14.19070836527375</v>
       </c>
       <c r="D338" t="n">
-        <v>13.46816627734423</v>
+        <v>13.46816718369137</v>
       </c>
       <c r="E338" t="n">
-        <v>13.67047783132298</v>
+        <v>13.67047875128478</v>
       </c>
       <c r="F338" t="n">
         <v>7354200</v>
@@ -7232,16 +7232,16 @@
         <v>44750</v>
       </c>
       <c r="B341" t="n">
-        <v>14.72057151794434</v>
+        <v>14.72057247161865</v>
       </c>
       <c r="C341" t="n">
-        <v>14.82654480851997</v>
+        <v>14.82654576905978</v>
       </c>
       <c r="D341" t="n">
-        <v>14.41228758628851</v>
+        <v>14.41228851999061</v>
       </c>
       <c r="E341" t="n">
-        <v>14.73983972305212</v>
+        <v>14.73984067797473</v>
       </c>
       <c r="F341" t="n">
         <v>3792400</v>
@@ -7252,16 +7252,16 @@
         <v>44753</v>
       </c>
       <c r="B342" t="n">
-        <v>14.788010597229</v>
+        <v>14.78800964355469</v>
       </c>
       <c r="C342" t="n">
-        <v>14.89398297821984</v>
+        <v>14.8939820177114</v>
       </c>
       <c r="D342" t="n">
-        <v>14.52789531830785</v>
+        <v>14.52789438140829</v>
       </c>
       <c r="E342" t="n">
-        <v>14.57606491648865</v>
+        <v>14.57606397648265</v>
       </c>
       <c r="F342" t="n">
         <v>3654100</v>
@@ -7292,16 +7292,16 @@
         <v>44755</v>
       </c>
       <c r="B344" t="n">
-        <v>14.77837562561035</v>
+        <v>14.77837657928467</v>
       </c>
       <c r="C344" t="n">
-        <v>15.01922268360593</v>
+        <v>15.01922365282253</v>
       </c>
       <c r="D344" t="n">
-        <v>14.44118937691309</v>
+        <v>14.44119030882819</v>
       </c>
       <c r="E344" t="n">
-        <v>14.58569816296561</v>
+        <v>14.58569910420611</v>
       </c>
       <c r="F344" t="n">
         <v>3964800</v>
@@ -7312,16 +7312,16 @@
         <v>44756</v>
       </c>
       <c r="B345" t="n">
-        <v>14.75910663604736</v>
+        <v>14.759108543396</v>
       </c>
       <c r="C345" t="n">
-        <v>14.99995368125053</v>
+        <v>14.99995561972431</v>
       </c>
       <c r="D345" t="n">
-        <v>14.5182595908442</v>
+        <v>14.51826146706769</v>
       </c>
       <c r="E345" t="n">
-        <v>14.52789369315438</v>
+        <v>14.5278955706229</v>
       </c>
       <c r="F345" t="n">
         <v>8175300</v>
@@ -7332,16 +7332,16 @@
         <v>44757</v>
       </c>
       <c r="B346" t="n">
-        <v>15.00958919525146</v>
+        <v>15.00958824157715</v>
       </c>
       <c r="C346" t="n">
-        <v>15.16373117167757</v>
+        <v>15.16373020820944</v>
       </c>
       <c r="D346" t="n">
-        <v>14.56643055364708</v>
+        <v>14.56642962813003</v>
       </c>
       <c r="E346" t="n">
-        <v>14.83617901239277</v>
+        <v>14.83617806973653</v>
       </c>
       <c r="F346" t="n">
         <v>3973400</v>
@@ -7432,16 +7432,16 @@
         <v>44764</v>
       </c>
       <c r="B351" t="n">
-        <v>15.07702541351318</v>
+        <v>15.0770263671875</v>
       </c>
       <c r="C351" t="n">
-        <v>15.14446321428636</v>
+        <v>15.14446417222636</v>
       </c>
       <c r="D351" t="n">
-        <v>14.78800967987438</v>
+        <v>14.78801061526745</v>
       </c>
       <c r="E351" t="n">
-        <v>14.8458124590987</v>
+        <v>14.84581339814799</v>
       </c>
       <c r="F351" t="n">
         <v>3071000</v>
@@ -7492,16 +7492,16 @@
         <v>44769</v>
       </c>
       <c r="B354" t="n">
-        <v>15.76103115081787</v>
+        <v>15.7610330581665</v>
       </c>
       <c r="C354" t="n">
-        <v>15.9344413165386</v>
+        <v>15.93444324487276</v>
       </c>
       <c r="D354" t="n">
-        <v>15.03848909990104</v>
+        <v>15.03849091980999</v>
       </c>
       <c r="E354" t="n">
-        <v>15.04812320216521</v>
+        <v>15.04812502324004</v>
       </c>
       <c r="F354" t="n">
         <v>22102600</v>
@@ -7512,16 +7512,16 @@
         <v>44770</v>
       </c>
       <c r="B355" t="n">
-        <v>15.59725666046143</v>
+        <v>15.59725570678711</v>
       </c>
       <c r="C355" t="n">
-        <v>16.13675357904711</v>
+        <v>16.13675259238595</v>
       </c>
       <c r="D355" t="n">
-        <v>15.31787317917409</v>
+        <v>15.31787224258232</v>
       </c>
       <c r="E355" t="n">
-        <v>15.9151747171748</v>
+        <v>15.91517374406179</v>
       </c>
       <c r="F355" t="n">
         <v>25902000</v>
@@ -7532,16 +7532,16 @@
         <v>44771</v>
       </c>
       <c r="B356" t="n">
-        <v>15.26970386505127</v>
+        <v>15.26970481872559</v>
       </c>
       <c r="C356" t="n">
-        <v>15.66469289369624</v>
+        <v>15.66469387203972</v>
       </c>
       <c r="D356" t="n">
-        <v>15.26970386505127</v>
+        <v>15.26970481872559</v>
       </c>
       <c r="E356" t="n">
-        <v>15.59725601136913</v>
+        <v>15.59725698550082</v>
       </c>
       <c r="F356" t="n">
         <v>15825800</v>
@@ -7572,16 +7572,16 @@
         <v>44775</v>
       </c>
       <c r="B358" t="n">
-        <v>15.09629344940186</v>
+        <v>15.09629440307617</v>
       </c>
       <c r="C358" t="n">
-        <v>15.21189992530961</v>
+        <v>15.2119008862871</v>
       </c>
       <c r="D358" t="n">
-        <v>14.80727680025318</v>
+        <v>14.80727773566952</v>
       </c>
       <c r="E358" t="n">
-        <v>15.04812385475064</v>
+        <v>15.04812480538195</v>
       </c>
       <c r="F358" t="n">
         <v>7865200</v>
@@ -7592,16 +7592,16 @@
         <v>44776</v>
       </c>
       <c r="B359" t="n">
-        <v>15.95370960235596</v>
+        <v>15.95370769500732</v>
       </c>
       <c r="C359" t="n">
-        <v>16.00188011947041</v>
+        <v>16.00187820636274</v>
       </c>
       <c r="D359" t="n">
-        <v>15.06739321889945</v>
+        <v>15.06739141751453</v>
       </c>
       <c r="E359" t="n">
-        <v>15.12519600191945</v>
+        <v>15.12519419362391</v>
       </c>
       <c r="F359" t="n">
         <v>9465300</v>
@@ -7612,16 +7612,16 @@
         <v>44777</v>
       </c>
       <c r="B360" t="n">
-        <v>16.21382331848145</v>
+        <v>16.21382522583008</v>
       </c>
       <c r="C360" t="n">
-        <v>16.42576806079203</v>
+        <v>16.42576999307324</v>
       </c>
       <c r="D360" t="n">
-        <v>15.92480759373818</v>
+        <v>15.92480946708782</v>
       </c>
       <c r="E360" t="n">
-        <v>16.02114494364116</v>
+        <v>16.02114682832365</v>
       </c>
       <c r="F360" t="n">
         <v>10048700</v>
@@ -7672,16 +7672,16 @@
         <v>44782</v>
       </c>
       <c r="B363" t="n">
-        <v>16.61845016479492</v>
+        <v>16.61844825744629</v>
       </c>
       <c r="C363" t="n">
-        <v>16.87856547794376</v>
+        <v>16.87856354074092</v>
       </c>
       <c r="D363" t="n">
-        <v>16.51247685110075</v>
+        <v>16.51247495591499</v>
       </c>
       <c r="E363" t="n">
-        <v>16.65698658341738</v>
+        <v>16.65698467164581</v>
       </c>
       <c r="F363" t="n">
         <v>6314800</v>
@@ -7692,16 +7692,16 @@
         <v>44783</v>
       </c>
       <c r="B364" t="n">
-        <v>16.89782905578613</v>
+        <v>16.89783096313477</v>
       </c>
       <c r="C364" t="n">
-        <v>17.20611297019896</v>
+        <v>17.20611491234526</v>
       </c>
       <c r="D364" t="n">
-        <v>16.73405299656468</v>
+        <v>16.73405488542704</v>
       </c>
       <c r="E364" t="n">
-        <v>17.16757656213882</v>
+        <v>17.1675784999353</v>
       </c>
       <c r="F364" t="n">
         <v>6533000</v>
@@ -7752,16 +7752,16 @@
         <v>44788</v>
       </c>
       <c r="B367" t="n">
-        <v>17.53366851806641</v>
+        <v>17.53366661071777</v>
       </c>
       <c r="C367" t="n">
-        <v>17.66854229762282</v>
+        <v>17.66854037560234</v>
       </c>
       <c r="D367" t="n">
-        <v>17.06160661458408</v>
+        <v>17.06160475858731</v>
       </c>
       <c r="E367" t="n">
-        <v>17.20611633555731</v>
+        <v>17.20611446384048</v>
       </c>
       <c r="F367" t="n">
         <v>7999500</v>
@@ -7772,16 +7772,16 @@
         <v>44789</v>
       </c>
       <c r="B368" t="n">
-        <v>17.42769432067871</v>
+        <v>17.42769241333008</v>
       </c>
       <c r="C368" t="n">
-        <v>17.63000497965835</v>
+        <v>17.63000305016812</v>
       </c>
       <c r="D368" t="n">
-        <v>17.19648135148026</v>
+        <v>17.1964794694364</v>
       </c>
       <c r="E368" t="n">
-        <v>17.52403351722407</v>
+        <v>17.52403159933173</v>
       </c>
       <c r="F368" t="n">
         <v>4828900</v>
@@ -7812,16 +7812,16 @@
         <v>44791</v>
       </c>
       <c r="B370" t="n">
-        <v>17.45659637451172</v>
+        <v>17.45659446716309</v>
       </c>
       <c r="C370" t="n">
-        <v>17.59147014518392</v>
+        <v>17.59146822309866</v>
       </c>
       <c r="D370" t="n">
-        <v>17.2928202940452</v>
+        <v>17.29281840459113</v>
       </c>
       <c r="E370" t="n">
-        <v>17.34098897285176</v>
+        <v>17.34098707813466</v>
       </c>
       <c r="F370" t="n">
         <v>13968800</v>
@@ -7852,16 +7852,16 @@
         <v>44795</v>
       </c>
       <c r="B372" t="n">
-        <v>17.36025619506836</v>
+        <v>17.36025810241699</v>
       </c>
       <c r="C372" t="n">
-        <v>17.45659538473642</v>
+        <v>17.45659730266971</v>
       </c>
       <c r="D372" t="n">
-        <v>16.82075746793411</v>
+        <v>16.82075931600872</v>
       </c>
       <c r="E372" t="n">
-        <v>16.98453353911465</v>
+        <v>16.98453540518312</v>
       </c>
       <c r="F372" t="n">
         <v>10077700</v>
@@ -7952,16 +7952,16 @@
         <v>44802</v>
       </c>
       <c r="B377" t="n">
-        <v>17.68781089782715</v>
+        <v>17.68780899047852</v>
       </c>
       <c r="C377" t="n">
-        <v>17.98646077526369</v>
+        <v>17.98645883571042</v>
       </c>
       <c r="D377" t="n">
-        <v>17.19648261316334</v>
+        <v>17.19648075879664</v>
       </c>
       <c r="E377" t="n">
-        <v>17.29282181677697</v>
+        <v>17.29281995202162</v>
       </c>
       <c r="F377" t="n">
         <v>7263100</v>
@@ -8012,16 +8012,16 @@
         <v>44805</v>
       </c>
       <c r="B380" t="n">
-        <v>18.08279609680176</v>
+        <v>18.08279800415039</v>
       </c>
       <c r="C380" t="n">
-        <v>18.2465721565297</v>
+        <v>18.24657408115321</v>
       </c>
       <c r="D380" t="n">
-        <v>17.71670756916656</v>
+        <v>17.71670943790068</v>
       </c>
       <c r="E380" t="n">
-        <v>17.81304675209778</v>
+        <v>17.81304863099362</v>
       </c>
       <c r="F380" t="n">
         <v>12942800</v>
@@ -8072,16 +8072,16 @@
         <v>44810</v>
       </c>
       <c r="B383" t="n">
-        <v>18.75716972351074</v>
+        <v>18.75716781616211</v>
       </c>
       <c r="C383" t="n">
-        <v>18.83424071476615</v>
+        <v>18.83423879958045</v>
       </c>
       <c r="D383" t="n">
-        <v>18.33328019036468</v>
+        <v>18.33327832611984</v>
       </c>
       <c r="E383" t="n">
-        <v>18.68973283585193</v>
+        <v>18.68973093536071</v>
       </c>
       <c r="F383" t="n">
         <v>7863100</v>
@@ -8092,16 +8092,16 @@
         <v>44812</v>
       </c>
       <c r="B384" t="n">
-        <v>18.40071678161621</v>
+        <v>18.40071487426758</v>
       </c>
       <c r="C384" t="n">
-        <v>18.94984781515502</v>
+        <v>18.94984585088554</v>
       </c>
       <c r="D384" t="n">
-        <v>18.34291399848511</v>
+        <v>18.3429120971281</v>
       </c>
       <c r="E384" t="n">
-        <v>18.91131140138939</v>
+        <v>18.91130944111445</v>
       </c>
       <c r="F384" t="n">
         <v>6653400</v>
@@ -8112,16 +8112,16 @@
         <v>44813</v>
       </c>
       <c r="B385" t="n">
-        <v>18.15987014770508</v>
+        <v>18.15986824035645</v>
       </c>
       <c r="C385" t="n">
-        <v>18.6222960989819</v>
+        <v>18.62229414306423</v>
       </c>
       <c r="D385" t="n">
-        <v>18.08279915582561</v>
+        <v>18.08279725657182</v>
       </c>
       <c r="E385" t="n">
-        <v>18.47778821889757</v>
+        <v>18.47778627815769</v>
       </c>
       <c r="F385" t="n">
         <v>8752700</v>
@@ -8132,16 +8132,16 @@
         <v>44816</v>
       </c>
       <c r="B386" t="n">
-        <v>17.78414535522461</v>
+        <v>17.78414726257324</v>
       </c>
       <c r="C386" t="n">
-        <v>18.38144684992308</v>
+        <v>18.38144882133227</v>
       </c>
       <c r="D386" t="n">
-        <v>17.7070743724426</v>
+        <v>17.70707627152537</v>
       </c>
       <c r="E386" t="n">
-        <v>18.25620719197125</v>
+        <v>18.25620914994849</v>
       </c>
       <c r="F386" t="n">
         <v>10149200</v>
@@ -8152,16 +8152,16 @@
         <v>44817</v>
       </c>
       <c r="B387" t="n">
-        <v>17.48549461364746</v>
+        <v>17.48549652099609</v>
       </c>
       <c r="C387" t="n">
-        <v>17.84194903885061</v>
+        <v>17.84195098508192</v>
       </c>
       <c r="D387" t="n">
-        <v>17.32171855409743</v>
+        <v>17.32172044358108</v>
       </c>
       <c r="E387" t="n">
-        <v>17.64927067319749</v>
+        <v>17.64927259841111</v>
       </c>
       <c r="F387" t="n">
         <v>10161300</v>
@@ -8172,16 +8172,16 @@
         <v>44818</v>
       </c>
       <c r="B388" t="n">
-        <v>17.70707321166992</v>
+        <v>17.70707511901855</v>
       </c>
       <c r="C388" t="n">
-        <v>17.87084926903514</v>
+        <v>17.8708511940252</v>
       </c>
       <c r="D388" t="n">
-        <v>17.3698888325507</v>
+        <v>17.36989070357892</v>
       </c>
       <c r="E388" t="n">
-        <v>17.44695981028038</v>
+        <v>17.44696168961044</v>
       </c>
       <c r="F388" t="n">
         <v>7347400</v>
@@ -8192,16 +8192,16 @@
         <v>44819</v>
       </c>
       <c r="B389" t="n">
-        <v>17.62036895751953</v>
+        <v>17.62037086486816</v>
       </c>
       <c r="C389" t="n">
-        <v>17.8419477760763</v>
+        <v>17.84194970741013</v>
       </c>
       <c r="D389" t="n">
-        <v>17.48549337610141</v>
+        <v>17.4854952688502</v>
       </c>
       <c r="E389" t="n">
-        <v>17.69743993082262</v>
+        <v>17.69744184651394</v>
       </c>
       <c r="F389" t="n">
         <v>7203900</v>
@@ -8232,16 +8232,16 @@
         <v>44823</v>
       </c>
       <c r="B391" t="n">
-        <v>17.46623039245605</v>
+        <v>17.46622848510742</v>
       </c>
       <c r="C391" t="n">
-        <v>17.58183780571365</v>
+        <v>17.58183588574045</v>
       </c>
       <c r="D391" t="n">
-        <v>17.14831230289454</v>
+        <v>17.14831043026322</v>
       </c>
       <c r="E391" t="n">
-        <v>17.14831230289454</v>
+        <v>17.14831043026322</v>
       </c>
       <c r="F391" t="n">
         <v>7719100</v>
@@ -8292,16 +8292,16 @@
         <v>44826</v>
       </c>
       <c r="B394" t="n">
-        <v>17.36025619506836</v>
+        <v>17.36025810241699</v>
       </c>
       <c r="C394" t="n">
-        <v>17.88048487924835</v>
+        <v>17.88048684375383</v>
       </c>
       <c r="D394" t="n">
-        <v>16.94599896575775</v>
+        <v>16.94600082759248</v>
       </c>
       <c r="E394" t="n">
-        <v>17.66854013199238</v>
+        <v>17.66854207321177</v>
       </c>
       <c r="F394" t="n">
         <v>12903600</v>
@@ -8312,16 +8312,16 @@
         <v>44827</v>
       </c>
       <c r="B395" t="n">
-        <v>17.13867568969727</v>
+        <v>17.1386775970459</v>
       </c>
       <c r="C395" t="n">
-        <v>17.42769139326868</v>
+        <v>17.42769333278163</v>
       </c>
       <c r="D395" t="n">
-        <v>16.9652655325476</v>
+        <v>16.96526742059757</v>
       </c>
       <c r="E395" t="n">
-        <v>17.10977338433331</v>
+        <v>17.10977528846543</v>
       </c>
       <c r="F395" t="n">
         <v>12048200</v>
@@ -8432,16 +8432,16 @@
         <v>44837</v>
       </c>
       <c r="B401" t="n">
-        <v>17.75524520874023</v>
+        <v>17.75524711608887</v>
       </c>
       <c r="C401" t="n">
-        <v>17.81304798750098</v>
+        <v>17.81304990105905</v>
       </c>
       <c r="D401" t="n">
-        <v>16.96526716144702</v>
+        <v>16.96526898393264</v>
       </c>
       <c r="E401" t="n">
-        <v>17.24464879005494</v>
+        <v>17.244650642553</v>
       </c>
       <c r="F401" t="n">
         <v>18011200</v>
@@ -8452,16 +8452,16 @@
         <v>44838</v>
       </c>
       <c r="B402" t="n">
-        <v>17.41806030273438</v>
+        <v>17.41805839538574</v>
       </c>
       <c r="C402" t="n">
-        <v>18.07316463743626</v>
+        <v>18.07316265835103</v>
       </c>
       <c r="D402" t="n">
-        <v>17.33135520916987</v>
+        <v>17.3313533113158</v>
       </c>
       <c r="E402" t="n">
-        <v>17.98645954387175</v>
+        <v>17.98645757428108</v>
       </c>
       <c r="F402" t="n">
         <v>18594600</v>
@@ -8472,16 +8472,16 @@
         <v>44839</v>
       </c>
       <c r="B403" t="n">
-        <v>17.45659637451172</v>
+        <v>17.45659446716309</v>
       </c>
       <c r="C403" t="n">
-        <v>17.74561212238566</v>
+        <v>17.74561018345848</v>
       </c>
       <c r="D403" t="n">
-        <v>17.14831058259092</v>
+        <v>17.14830870892632</v>
       </c>
       <c r="E403" t="n">
-        <v>17.4276940647174</v>
+        <v>17.4276921605267</v>
       </c>
       <c r="F403" t="n">
         <v>8852300</v>
@@ -8492,16 +8492,16 @@
         <v>44840</v>
       </c>
       <c r="B404" t="n">
-        <v>17.44696044921875</v>
+        <v>17.44696426391602</v>
       </c>
       <c r="C404" t="n">
-        <v>17.6396369818406</v>
+        <v>17.6396408386657</v>
       </c>
       <c r="D404" t="n">
-        <v>17.30245075285597</v>
+        <v>17.30245453595685</v>
       </c>
       <c r="E404" t="n">
-        <v>17.63000287958194</v>
+        <v>17.63000673430058</v>
       </c>
       <c r="F404" t="n">
         <v>6691000</v>
@@ -8512,16 +8512,16 @@
         <v>44841</v>
       </c>
       <c r="B405" t="n">
-        <v>17.49513244628906</v>
+        <v>17.4951286315918</v>
       </c>
       <c r="C405" t="n">
-        <v>17.68781085302832</v>
+        <v>17.68780699631881</v>
       </c>
       <c r="D405" t="n">
-        <v>17.32172224772722</v>
+        <v>17.3217184708409</v>
       </c>
       <c r="E405" t="n">
-        <v>17.44696376336298</v>
+        <v>17.44695995916858</v>
       </c>
       <c r="F405" t="n">
         <v>11897600</v>
@@ -8532,16 +8532,16 @@
         <v>44844</v>
       </c>
       <c r="B406" t="n">
-        <v>18.1020679473877</v>
+        <v>18.10206604003906</v>
       </c>
       <c r="C406" t="n">
-        <v>18.12133431784131</v>
+        <v>18.12133240846265</v>
       </c>
       <c r="D406" t="n">
-        <v>17.58183735727369</v>
+        <v>17.58183550473985</v>
       </c>
       <c r="E406" t="n">
-        <v>17.73597934600729</v>
+        <v>17.73597747723208</v>
       </c>
       <c r="F406" t="n">
         <v>7333800</v>
@@ -8572,16 +8572,16 @@
         <v>44847</v>
       </c>
       <c r="B408" t="n">
-        <v>18.75716972351074</v>
+        <v>18.75716781616211</v>
       </c>
       <c r="C408" t="n">
-        <v>18.99801680087357</v>
+        <v>18.99801486903407</v>
       </c>
       <c r="D408" t="n">
-        <v>17.93829113049103</v>
+        <v>17.93828930641119</v>
       </c>
       <c r="E408" t="n">
-        <v>18.17913820785386</v>
+        <v>18.17913635928316</v>
       </c>
       <c r="F408" t="n">
         <v>20665700</v>
@@ -8632,16 +8632,16 @@
         <v>44852</v>
       </c>
       <c r="B411" t="n">
-        <v>17.26391792297363</v>
+        <v>17.263916015625</v>
       </c>
       <c r="C411" t="n">
-        <v>19.16179215898201</v>
+        <v>19.16179004195282</v>
       </c>
       <c r="D411" t="n">
-        <v>17.26391792297363</v>
+        <v>17.263916015625</v>
       </c>
       <c r="E411" t="n">
-        <v>19.10398937711585</v>
+        <v>19.10398726647282</v>
       </c>
       <c r="F411" t="n">
         <v>33355700</v>
@@ -8672,16 +8672,16 @@
         <v>44854</v>
       </c>
       <c r="B413" t="n">
-        <v>17.35062408447266</v>
+        <v>17.35062217712402</v>
       </c>
       <c r="C413" t="n">
-        <v>18.11169991144759</v>
+        <v>18.11169792043414</v>
       </c>
       <c r="D413" t="n">
-        <v>17.19648209831274</v>
+        <v>17.19648020790888</v>
       </c>
       <c r="E413" t="n">
-        <v>17.73597904987246</v>
+        <v>17.73597710016188</v>
       </c>
       <c r="F413" t="n">
         <v>15810900</v>
@@ -8692,16 +8692,16 @@
         <v>44855</v>
       </c>
       <c r="B414" t="n">
-        <v>17.91902160644531</v>
+        <v>17.91902351379395</v>
       </c>
       <c r="C414" t="n">
-        <v>18.25620785747724</v>
+        <v>18.25620980071688</v>
       </c>
       <c r="D414" t="n">
-        <v>17.34098829575019</v>
+        <v>17.34099014157141</v>
       </c>
       <c r="E414" t="n">
-        <v>17.53366667848764</v>
+        <v>17.53366854481807</v>
       </c>
       <c r="F414" t="n">
         <v>27105700</v>
@@ -8712,16 +8712,16 @@
         <v>44858</v>
       </c>
       <c r="B415" t="n">
-        <v>18.0057258605957</v>
+        <v>18.00572776794434</v>
       </c>
       <c r="C415" t="n">
-        <v>18.36217846337067</v>
+        <v>18.36218040847837</v>
       </c>
       <c r="D415" t="n">
-        <v>17.54329813095674</v>
+        <v>17.54329998932035</v>
       </c>
       <c r="E415" t="n">
-        <v>17.91902077613322</v>
+        <v>17.91902267429717</v>
       </c>
       <c r="F415" t="n">
         <v>16227000</v>
@@ -8732,16 +8732,16 @@
         <v>44859</v>
       </c>
       <c r="B416" t="n">
-        <v>17.04233741760254</v>
+        <v>17.04233932495117</v>
       </c>
       <c r="C416" t="n">
-        <v>18.00572559754023</v>
+        <v>18.00572761270958</v>
       </c>
       <c r="D416" t="n">
-        <v>16.80149037261812</v>
+        <v>16.80149225301157</v>
       </c>
       <c r="E416" t="n">
-        <v>18.00572559754023</v>
+        <v>18.00572761270958</v>
       </c>
       <c r="F416" t="n">
         <v>27810400</v>
@@ -8752,16 +8752,16 @@
         <v>44860</v>
       </c>
       <c r="B417" t="n">
-        <v>16.45467185974121</v>
+        <v>16.45466995239258</v>
       </c>
       <c r="C417" t="n">
-        <v>17.07123977508899</v>
+        <v>17.07123779627069</v>
       </c>
       <c r="D417" t="n">
-        <v>16.36796676695576</v>
+        <v>16.36796486965758</v>
       </c>
       <c r="E417" t="n">
-        <v>17.0423393025054</v>
+        <v>17.0423373270371</v>
       </c>
       <c r="F417" t="n">
         <v>12823000</v>
@@ -8772,16 +8772,16 @@
         <v>44861</v>
       </c>
       <c r="B418" t="n">
-        <v>17.47586059570312</v>
+        <v>17.47586250305176</v>
       </c>
       <c r="C418" t="n">
-        <v>17.74560994141206</v>
+        <v>17.74561187820164</v>
       </c>
       <c r="D418" t="n">
-        <v>15.99224378809673</v>
+        <v>15.9922455335206</v>
       </c>
       <c r="E418" t="n">
-        <v>16.13675164427337</v>
+        <v>16.13675340546911</v>
       </c>
       <c r="F418" t="n">
         <v>30122400</v>
@@ -8792,16 +8792,16 @@
         <v>44862</v>
       </c>
       <c r="B419" t="n">
-        <v>18.1213321685791</v>
+        <v>18.12133026123047</v>
       </c>
       <c r="C419" t="n">
-        <v>18.21767135949075</v>
+        <v>18.21766944200201</v>
       </c>
       <c r="D419" t="n">
-        <v>17.27355133109445</v>
+        <v>17.27354951297842</v>
       </c>
       <c r="E419" t="n">
-        <v>17.40842509586043</v>
+        <v>17.40842326354835</v>
       </c>
       <c r="F419" t="n">
         <v>12193800</v>
@@ -8872,16 +8872,16 @@
         <v>44869</v>
       </c>
       <c r="B423" t="n">
-        <v>19.79762840270996</v>
+        <v>19.79763031005859</v>
       </c>
       <c r="C423" t="n">
-        <v>19.98067269026426</v>
+        <v>19.9806746152478</v>
       </c>
       <c r="D423" t="n">
-        <v>19.60495184937882</v>
+        <v>19.60495373816456</v>
       </c>
       <c r="E423" t="n">
-        <v>19.81689660929827</v>
+        <v>19.81689851850324</v>
       </c>
       <c r="F423" t="n">
         <v>15655600</v>
@@ -8912,16 +8912,16 @@
         <v>44873</v>
       </c>
       <c r="B425" t="n">
-        <v>19.22922897338867</v>
+        <v>19.2292308807373</v>
       </c>
       <c r="C425" t="n">
-        <v>19.45080967184277</v>
+        <v>19.45081160117001</v>
       </c>
       <c r="D425" t="n">
-        <v>19.0750869973007</v>
+        <v>19.07508888935998</v>
       </c>
       <c r="E425" t="n">
-        <v>19.26776538616931</v>
+        <v>19.26776729734038</v>
       </c>
       <c r="F425" t="n">
         <v>10214300</v>
@@ -8952,16 +8952,16 @@
         <v>44875</v>
       </c>
       <c r="B427" t="n">
-        <v>18.80533790588379</v>
+        <v>18.80533981323242</v>
       </c>
       <c r="C427" t="n">
-        <v>19.64348460199946</v>
+        <v>19.64348659435789</v>
       </c>
       <c r="D427" t="n">
-        <v>18.43924936475051</v>
+        <v>18.43925123496827</v>
       </c>
       <c r="E427" t="n">
-        <v>19.64348460199946</v>
+        <v>19.64348659435789</v>
       </c>
       <c r="F427" t="n">
         <v>13893700</v>
@@ -9032,16 +9032,16 @@
         <v>44882</v>
       </c>
       <c r="B431" t="n">
-        <v>18.78607177734375</v>
+        <v>18.78606986999512</v>
       </c>
       <c r="C431" t="n">
-        <v>18.90167918140427</v>
+        <v>18.90167726231802</v>
       </c>
       <c r="D431" t="n">
-        <v>18.0538964516734</v>
+        <v>18.05389461866248</v>
       </c>
       <c r="E431" t="n">
-        <v>18.66083210733576</v>
+        <v>18.6608302127027</v>
       </c>
       <c r="F431" t="n">
         <v>10826800</v>
@@ -9072,16 +9072,16 @@
         <v>44886</v>
       </c>
       <c r="B433" t="n">
-        <v>18.98838043212891</v>
+        <v>18.98838233947754</v>
       </c>
       <c r="C433" t="n">
-        <v>19.02691684191824</v>
+        <v>19.02691875313779</v>
       </c>
       <c r="D433" t="n">
-        <v>18.58375915444382</v>
+        <v>18.58376102114898</v>
       </c>
       <c r="E433" t="n">
-        <v>18.60302552182134</v>
+        <v>18.60302739046176</v>
       </c>
       <c r="F433" t="n">
         <v>10461100</v>
@@ -9092,16 +9092,16 @@
         <v>44887</v>
       </c>
       <c r="B434" t="n">
-        <v>18.75716972351074</v>
+        <v>18.75716781616211</v>
       </c>
       <c r="C434" t="n">
-        <v>19.39300586074722</v>
+        <v>19.39300388874271</v>
       </c>
       <c r="D434" t="n">
-        <v>18.62229594819312</v>
+        <v>18.62229405455931</v>
       </c>
       <c r="E434" t="n">
-        <v>19.07508779212898</v>
+        <v>19.07508585245241</v>
       </c>
       <c r="F434" t="n">
         <v>9653000</v>
@@ -9152,16 +9152,16 @@
         <v>44890</v>
       </c>
       <c r="B437" t="n">
-        <v>18.50668716430664</v>
+        <v>18.50668907165527</v>
       </c>
       <c r="C437" t="n">
-        <v>19.16179145994887</v>
+        <v>19.1617934348143</v>
       </c>
       <c r="D437" t="n">
-        <v>18.41998391342904</v>
+        <v>18.4199858118418</v>
       </c>
       <c r="E437" t="n">
-        <v>19.16179145994887</v>
+        <v>19.1617934348143</v>
       </c>
       <c r="F437" t="n">
         <v>6509300</v>
@@ -9172,16 +9172,16 @@
         <v>44893</v>
       </c>
       <c r="B438" t="n">
-        <v>18.6126594543457</v>
+        <v>18.61266136169434</v>
       </c>
       <c r="C438" t="n">
-        <v>19.0461848729321</v>
+        <v>19.04618682470663</v>
       </c>
       <c r="D438" t="n">
-        <v>18.21767044519682</v>
+        <v>18.21767231206861</v>
       </c>
       <c r="E438" t="n">
-        <v>18.35254420319387</v>
+        <v>18.35254608388696</v>
       </c>
       <c r="F438" t="n">
         <v>12132600</v>
@@ -9252,16 +9252,16 @@
         <v>44897</v>
       </c>
       <c r="B442" t="n">
-        <v>19.78799247741699</v>
+        <v>19.78799629211426</v>
       </c>
       <c r="C442" t="n">
-        <v>19.97103489360281</v>
+        <v>19.97103874358669</v>
       </c>
       <c r="D442" t="n">
-        <v>19.01728089407297</v>
+        <v>19.01728456019369</v>
       </c>
       <c r="E442" t="n">
-        <v>19.11362007168059</v>
+        <v>19.11362375637343</v>
       </c>
       <c r="F442" t="n">
         <v>24428900</v>
@@ -9292,16 +9292,16 @@
         <v>44901</v>
       </c>
       <c r="B444" t="n">
-        <v>19.22922897338867</v>
+        <v>19.2292308807373</v>
       </c>
       <c r="C444" t="n">
-        <v>19.81689640567237</v>
+        <v>19.81689837131178</v>
       </c>
       <c r="D444" t="n">
-        <v>18.97874964038369</v>
+        <v>18.97875152288726</v>
       </c>
       <c r="E444" t="n">
-        <v>19.74945952082355</v>
+        <v>19.74946147977388</v>
       </c>
       <c r="F444" t="n">
         <v>9745600</v>
@@ -9332,16 +9332,16 @@
         <v>44903</v>
       </c>
       <c r="B446" t="n">
-        <v>18.63192939758301</v>
+        <v>18.63192749023438</v>
       </c>
       <c r="C446" t="n">
-        <v>19.16179221416967</v>
+        <v>19.16179025257903</v>
       </c>
       <c r="D446" t="n">
-        <v>18.43925100745114</v>
+        <v>18.43924911982698</v>
       </c>
       <c r="E446" t="n">
-        <v>19.07508712236206</v>
+        <v>19.07508516964742</v>
       </c>
       <c r="F446" t="n">
         <v>15335300</v>
@@ -9392,16 +9392,16 @@
         <v>44908</v>
       </c>
       <c r="B449" t="n">
-        <v>17.94792366027832</v>
+        <v>17.94792175292969</v>
       </c>
       <c r="C449" t="n">
-        <v>18.5259570219456</v>
+        <v>18.52595505316863</v>
       </c>
       <c r="D449" t="n">
-        <v>17.89975497910497</v>
+        <v>17.89975307687528</v>
       </c>
       <c r="E449" t="n">
-        <v>18.5259570219456</v>
+        <v>18.52595505316863</v>
       </c>
       <c r="F449" t="n">
         <v>13648600</v>
@@ -9432,16 +9432,16 @@
         <v>44910</v>
       </c>
       <c r="B451" t="n">
-        <v>18.41998291015625</v>
+        <v>18.41998481750488</v>
       </c>
       <c r="C451" t="n">
-        <v>18.75716730497398</v>
+        <v>18.75716924723731</v>
       </c>
       <c r="D451" t="n">
-        <v>18.09243078017577</v>
+        <v>18.0924326536071</v>
       </c>
       <c r="E451" t="n">
-        <v>18.1116971473674</v>
+        <v>18.11169902279372</v>
       </c>
       <c r="F451" t="n">
         <v>15735500</v>
@@ -9452,16 +9452,16 @@
         <v>44911</v>
       </c>
       <c r="B452" t="n">
-        <v>18.02499389648438</v>
+        <v>18.02499198913574</v>
       </c>
       <c r="C452" t="n">
-        <v>18.69936642972459</v>
+        <v>18.69936445101596</v>
       </c>
       <c r="D452" t="n">
-        <v>17.55293385822315</v>
+        <v>17.55293200082644</v>
       </c>
       <c r="E452" t="n">
-        <v>18.38144836977245</v>
+        <v>18.38144642470492</v>
       </c>
       <c r="F452" t="n">
         <v>14090800</v>
@@ -9472,16 +9472,16 @@
         <v>44914</v>
       </c>
       <c r="B453" t="n">
-        <v>18.83424186706543</v>
+        <v>18.83423805236816</v>
       </c>
       <c r="C453" t="n">
-        <v>18.90168059636759</v>
+        <v>18.90167676801125</v>
       </c>
       <c r="D453" t="n">
-        <v>18.13096879914314</v>
+        <v>18.13096512688717</v>
       </c>
       <c r="E453" t="n">
-        <v>18.15023700751518</v>
+        <v>18.15023333135662</v>
       </c>
       <c r="F453" t="n">
         <v>7150400</v>
@@ -9512,16 +9512,16 @@
         <v>44916</v>
       </c>
       <c r="B455" t="n">
-        <v>19.44117736816406</v>
+        <v>19.4411735534668</v>
       </c>
       <c r="C455" t="n">
-        <v>19.67239035369758</v>
+        <v>19.6723864936323</v>
       </c>
       <c r="D455" t="n">
-        <v>19.07508876293122</v>
+        <v>19.07508502006691</v>
       </c>
       <c r="E455" t="n">
-        <v>19.30630358598221</v>
+        <v>19.30629979774953</v>
       </c>
       <c r="F455" t="n">
         <v>13319200</v>
@@ -9532,16 +9532,16 @@
         <v>44917</v>
       </c>
       <c r="B456" t="n">
-        <v>19.38337135314941</v>
+        <v>19.38337326049805</v>
       </c>
       <c r="C456" t="n">
-        <v>19.52787921535256</v>
+        <v>19.52788113692095</v>
       </c>
       <c r="D456" t="n">
-        <v>19.07508558626097</v>
+        <v>19.07508746327389</v>
       </c>
       <c r="E456" t="n">
-        <v>19.52787921535256</v>
+        <v>19.52788113692095</v>
       </c>
       <c r="F456" t="n">
         <v>7183700</v>
@@ -9612,16 +9612,16 @@
         <v>44923</v>
       </c>
       <c r="B460" t="n">
-        <v>18.7186336517334</v>
+        <v>18.71863174438477</v>
       </c>
       <c r="C460" t="n">
-        <v>18.94984660703449</v>
+        <v>18.94984467612624</v>
       </c>
       <c r="D460" t="n">
-        <v>18.26584000644119</v>
+        <v>18.26583814523029</v>
       </c>
       <c r="E460" t="n">
-        <v>18.6897313432518</v>
+        <v>18.68972943884819</v>
       </c>
       <c r="F460" t="n">
         <v>8329700</v>
@@ -27635,16 +27635,36 @@
         <v>8</v>
       </c>
       <c r="C1361" t="n">
-        <v>8.199999999999999</v>
+        <v>8.199999809265137</v>
       </c>
       <c r="D1361" t="n">
-        <v>7.95</v>
+        <v>7.949999809265137</v>
       </c>
       <c r="E1361" t="n">
-        <v>8.119999999999999</v>
+        <v>8.119999885559082</v>
       </c>
       <c r="F1361" t="n">
         <v>8426200</v>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B1362" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="C1362" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="D1362" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="E1362" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="F1362" t="n">
+        <v>8987000</v>
       </c>
     </row>
   </sheetData>

--- a/database/ASAI3.xlsx
+++ b/database/ASAI3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1366"/>
+  <dimension ref="A1:F1365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>44257</v>
       </c>
       <c r="B3" t="n">
-        <v>13.76804447174072</v>
+        <v>13.76804256439209</v>
       </c>
       <c r="C3" t="n">
-        <v>14.05290074536612</v>
+        <v>14.05289879855508</v>
       </c>
       <c r="D3" t="n">
-        <v>13.00463023796586</v>
+        <v>13.0046284363764</v>
       </c>
       <c r="E3" t="n">
-        <v>13.37114477274755</v>
+        <v>13.3711429203832</v>
       </c>
       <c r="F3" t="n">
         <v>14717000</v>
@@ -512,16 +512,16 @@
         <v>44259</v>
       </c>
       <c r="B5" t="n">
-        <v>13.90097713470459</v>
+        <v>13.90097618103027</v>
       </c>
       <c r="C5" t="n">
-        <v>14.04340481356423</v>
+        <v>14.04340385011868</v>
       </c>
       <c r="D5" t="n">
-        <v>13.44330802948757</v>
+        <v>13.44330710721157</v>
       </c>
       <c r="E5" t="n">
-        <v>13.53256280482981</v>
+        <v>13.53256187643049</v>
       </c>
       <c r="F5" t="n">
         <v>12300000</v>
@@ -532,16 +532,16 @@
         <v>44260</v>
       </c>
       <c r="B6" t="n">
-        <v>14.24280261993408</v>
+        <v>14.2428035736084</v>
       </c>
       <c r="C6" t="n">
-        <v>14.90746656109107</v>
+        <v>14.90746755927018</v>
       </c>
       <c r="D6" t="n">
-        <v>13.67309015292352</v>
+        <v>13.67309106845084</v>
       </c>
       <c r="E6" t="n">
-        <v>13.76994143531125</v>
+        <v>13.76994235732357</v>
       </c>
       <c r="F6" t="n">
         <v>18499500</v>
@@ -592,16 +592,16 @@
         <v>44265</v>
       </c>
       <c r="B9" t="n">
-        <v>13.48318862915039</v>
+        <v>13.48318672180176</v>
       </c>
       <c r="C9" t="n">
-        <v>13.95794879852564</v>
+        <v>13.95794682401684</v>
       </c>
       <c r="D9" t="n">
-        <v>13.2363131237473</v>
+        <v>13.23631125132199</v>
       </c>
       <c r="E9" t="n">
-        <v>13.48508753218685</v>
+        <v>13.4850856245696</v>
       </c>
       <c r="F9" t="n">
         <v>15699500</v>
@@ -612,16 +612,16 @@
         <v>44266</v>
       </c>
       <c r="B10" t="n">
-        <v>13.95604801177979</v>
+        <v>13.9560489654541</v>
       </c>
       <c r="C10" t="n">
-        <v>14.15544729222492</v>
+        <v>14.15544825952501</v>
       </c>
       <c r="D10" t="n">
-        <v>13.63510989807421</v>
+        <v>13.6351108298175</v>
       </c>
       <c r="E10" t="n">
-        <v>13.71297125079192</v>
+        <v>13.7129721878558</v>
       </c>
       <c r="F10" t="n">
         <v>16646000</v>
@@ -632,16 +632,16 @@
         <v>44267</v>
       </c>
       <c r="B11" t="n">
-        <v>13.82121562957764</v>
+        <v>13.82121658325195</v>
       </c>
       <c r="C11" t="n">
-        <v>14.06049457939686</v>
+        <v>14.06049554958161</v>
       </c>
       <c r="D11" t="n">
-        <v>13.57813887428711</v>
+        <v>13.57813981118895</v>
       </c>
       <c r="E11" t="n">
-        <v>13.57813887428711</v>
+        <v>13.57813981118895</v>
       </c>
       <c r="F11" t="n">
         <v>7509000</v>
@@ -652,16 +652,16 @@
         <v>44270</v>
       </c>
       <c r="B12" t="n">
-        <v>13.83450984954834</v>
+        <v>13.83450889587402</v>
       </c>
       <c r="C12" t="n">
-        <v>14.01681810828169</v>
+        <v>14.01681714204006</v>
       </c>
       <c r="D12" t="n">
-        <v>13.62181733379263</v>
+        <v>13.62181639478016</v>
       </c>
       <c r="E12" t="n">
-        <v>13.81931772103716</v>
+        <v>13.81931676841011</v>
       </c>
       <c r="F12" t="n">
         <v>11593000</v>
@@ -672,16 +672,16 @@
         <v>44271</v>
       </c>
       <c r="B13" t="n">
-        <v>13.58763599395752</v>
+        <v>13.5876350402832</v>
       </c>
       <c r="C13" t="n">
-        <v>13.9104721377456</v>
+        <v>13.9104711614124</v>
       </c>
       <c r="D13" t="n">
-        <v>13.49458250400112</v>
+        <v>13.49458155685794</v>
       </c>
       <c r="E13" t="n">
-        <v>13.84400600601469</v>
+        <v>13.84400503434655</v>
       </c>
       <c r="F13" t="n">
         <v>7789500</v>
@@ -692,16 +692,16 @@
         <v>44272</v>
       </c>
       <c r="B14" t="n">
-        <v>14.05290031433105</v>
+        <v>14.05289936065674</v>
       </c>
       <c r="C14" t="n">
-        <v>14.07189024903928</v>
+        <v>14.07188929407625</v>
       </c>
       <c r="D14" t="n">
-        <v>13.49458210759284</v>
+        <v>13.49458119180776</v>
       </c>
       <c r="E14" t="n">
-        <v>13.58763559481576</v>
+        <v>13.58763467271578</v>
       </c>
       <c r="F14" t="n">
         <v>4753000</v>
@@ -712,16 +712,16 @@
         <v>44273</v>
       </c>
       <c r="B15" t="n">
-        <v>13.91047191619873</v>
+        <v>13.91047096252441</v>
       </c>
       <c r="C15" t="n">
-        <v>14.01302082492147</v>
+        <v>14.0130198642166</v>
       </c>
       <c r="D15" t="n">
-        <v>13.69018378074197</v>
+        <v>13.69018284217017</v>
       </c>
       <c r="E15" t="n">
-        <v>13.69018378074197</v>
+        <v>13.69018284217017</v>
       </c>
       <c r="F15" t="n">
         <v>2304000</v>
@@ -732,16 +732,16 @@
         <v>44274</v>
       </c>
       <c r="B16" t="n">
-        <v>13.54775238037109</v>
+        <v>13.54775524139404</v>
       </c>
       <c r="C16" t="n">
-        <v>14.03580565118024</v>
+        <v>14.03580861527059</v>
       </c>
       <c r="D16" t="n">
-        <v>13.46419523502917</v>
+        <v>13.46419807840647</v>
       </c>
       <c r="E16" t="n">
-        <v>13.95414740838706</v>
+        <v>13.95415035523277</v>
       </c>
       <c r="F16" t="n">
         <v>14098000</v>
@@ -812,16 +812,16 @@
         <v>44280</v>
       </c>
       <c r="B20" t="n">
-        <v>13.64840507507324</v>
+        <v>13.64840221405029</v>
       </c>
       <c r="C20" t="n">
-        <v>13.6730926258122</v>
+        <v>13.67308975961416</v>
       </c>
       <c r="D20" t="n">
-        <v>12.83941442090934</v>
+        <v>12.83941172946964</v>
       </c>
       <c r="E20" t="n">
-        <v>12.9134770731262</v>
+        <v>12.91347436616125</v>
       </c>
       <c r="F20" t="n">
         <v>6602000</v>
@@ -832,16 +832,16 @@
         <v>44281</v>
       </c>
       <c r="B21" t="n">
-        <v>13.80602359771729</v>
+        <v>13.80602550506592</v>
       </c>
       <c r="C21" t="n">
-        <v>14.12696170612194</v>
+        <v>14.12696365780925</v>
       </c>
       <c r="D21" t="n">
-        <v>13.48888420034324</v>
+        <v>13.488886063878</v>
       </c>
       <c r="E21" t="n">
-        <v>13.54965361596974</v>
+        <v>13.54965548789999</v>
       </c>
       <c r="F21" t="n">
         <v>4396500</v>
@@ -852,16 +852,16 @@
         <v>44284</v>
       </c>
       <c r="B22" t="n">
-        <v>13.95794677734375</v>
+        <v>13.95794773101807</v>
       </c>
       <c r="C22" t="n">
-        <v>13.95794677734375</v>
+        <v>13.95794773101807</v>
       </c>
       <c r="D22" t="n">
-        <v>13.4869853877722</v>
+        <v>13.48698630926816</v>
       </c>
       <c r="E22" t="n">
-        <v>13.7148700187455</v>
+        <v>13.71487095581164</v>
       </c>
       <c r="F22" t="n">
         <v>6557000</v>
@@ -872,16 +872,16 @@
         <v>44285</v>
       </c>
       <c r="B23" t="n">
-        <v>13.95794677734375</v>
+        <v>13.95794773101807</v>
       </c>
       <c r="C23" t="n">
-        <v>14.08138451217088</v>
+        <v>14.08138547427906</v>
       </c>
       <c r="D23" t="n">
-        <v>13.76804291819933</v>
+        <v>13.7680438588985</v>
       </c>
       <c r="E23" t="n">
-        <v>13.76804291819933</v>
+        <v>13.7680438588985</v>
       </c>
       <c r="F23" t="n">
         <v>8433000</v>
@@ -892,16 +892,16 @@
         <v>44286</v>
       </c>
       <c r="B24" t="n">
-        <v>14.02251434326172</v>
+        <v>14.02251529693604</v>
       </c>
       <c r="C24" t="n">
-        <v>14.04150518240905</v>
+        <v>14.04150613737493</v>
       </c>
       <c r="D24" t="n">
-        <v>13.67499067998287</v>
+        <v>13.67499161002203</v>
       </c>
       <c r="E24" t="n">
-        <v>13.96744253969395</v>
+        <v>13.96744348962283</v>
       </c>
       <c r="F24" t="n">
         <v>3663000</v>
@@ -992,16 +992,16 @@
         <v>44294</v>
       </c>
       <c r="B29" t="n">
-        <v>14.70237159729004</v>
+        <v>14.70237255096436</v>
       </c>
       <c r="C29" t="n">
-        <v>14.74035237068301</v>
+        <v>14.74035332682097</v>
       </c>
       <c r="D29" t="n">
-        <v>14.26559225050429</v>
+        <v>14.26559317584676</v>
       </c>
       <c r="E29" t="n">
-        <v>14.43270747232676</v>
+        <v>14.43270840850923</v>
       </c>
       <c r="F29" t="n">
         <v>6395000</v>
@@ -1052,16 +1052,16 @@
         <v>44299</v>
       </c>
       <c r="B32" t="n">
-        <v>14.67008686065674</v>
+        <v>14.67008781433105</v>
       </c>
       <c r="C32" t="n">
-        <v>14.81251543350823</v>
+        <v>14.81251639644156</v>
       </c>
       <c r="D32" t="n">
-        <v>14.52765919333826</v>
+        <v>14.52766013775363</v>
       </c>
       <c r="E32" t="n">
-        <v>14.69667331026109</v>
+        <v>14.69667426566374</v>
       </c>
       <c r="F32" t="n">
         <v>5449500</v>
@@ -1152,16 +1152,16 @@
         <v>44306</v>
       </c>
       <c r="B37" t="n">
-        <v>15.47718143463135</v>
+        <v>15.47717952728271</v>
       </c>
       <c r="C37" t="n">
-        <v>15.65569281594117</v>
+        <v>15.65569088659348</v>
       </c>
       <c r="D37" t="n">
-        <v>15.06698938480104</v>
+        <v>15.06698752800291</v>
       </c>
       <c r="E37" t="n">
-        <v>15.35944219725644</v>
+        <v>15.35944030441754</v>
       </c>
       <c r="F37" t="n">
         <v>6029000</v>
@@ -1232,16 +1232,16 @@
         <v>44313</v>
       </c>
       <c r="B41" t="n">
-        <v>15.12775707244873</v>
+        <v>15.12775611877441</v>
       </c>
       <c r="C41" t="n">
-        <v>15.29677210768214</v>
+        <v>15.29677114335289</v>
       </c>
       <c r="D41" t="n">
-        <v>15.10117062083444</v>
+        <v>15.10116966883617</v>
       </c>
       <c r="E41" t="n">
-        <v>15.24929500760934</v>
+        <v>15.24929404627311</v>
       </c>
       <c r="F41" t="n">
         <v>4986500</v>
@@ -1252,16 +1252,16 @@
         <v>44314</v>
       </c>
       <c r="B42" t="n">
-        <v>15.18852615356445</v>
+        <v>15.18852710723877</v>
       </c>
       <c r="C42" t="n">
-        <v>15.35564228216909</v>
+        <v>15.35564324633648</v>
       </c>
       <c r="D42" t="n">
-        <v>15.04799647598031</v>
+        <v>15.04799742083089</v>
       </c>
       <c r="E42" t="n">
-        <v>15.14864647703371</v>
+        <v>15.14864742820402</v>
       </c>
       <c r="F42" t="n">
         <v>5371500</v>
@@ -1272,16 +1272,16 @@
         <v>44315</v>
       </c>
       <c r="B43" t="n">
-        <v>15.21646499633789</v>
+        <v>15.21646404266357</v>
       </c>
       <c r="C43" t="n">
-        <v>15.32323336252505</v>
+        <v>15.32323240215915</v>
       </c>
       <c r="D43" t="n">
-        <v>14.90950503441863</v>
+        <v>14.90950409998268</v>
       </c>
       <c r="E43" t="n">
-        <v>15.26222338706449</v>
+        <v>15.26222243052232</v>
       </c>
       <c r="F43" t="n">
         <v>5343000</v>
@@ -1292,16 +1292,16 @@
         <v>44316</v>
       </c>
       <c r="B44" t="n">
-        <v>15.42237567901611</v>
+        <v>15.42237663269043</v>
       </c>
       <c r="C44" t="n">
-        <v>15.46813406897922</v>
+        <v>15.46813502548309</v>
       </c>
       <c r="D44" t="n">
-        <v>14.92857017537751</v>
+        <v>14.92857109851635</v>
       </c>
       <c r="E44" t="n">
-        <v>15.10016322860797</v>
+        <v>15.10016416235762</v>
       </c>
       <c r="F44" t="n">
         <v>22683000</v>
@@ -1312,16 +1312,16 @@
         <v>44319</v>
       </c>
       <c r="B45" t="n">
-        <v>15.53295993804932</v>
+        <v>15.532958984375</v>
       </c>
       <c r="C45" t="n">
-        <v>15.67023330010677</v>
+        <v>15.6702323380043</v>
       </c>
       <c r="D45" t="n">
-        <v>15.29463663895672</v>
+        <v>15.29463569991469</v>
       </c>
       <c r="E45" t="n">
-        <v>15.4433505085054</v>
+        <v>15.44334956033281</v>
       </c>
       <c r="F45" t="n">
         <v>8474000</v>
@@ -1332,16 +1332,16 @@
         <v>44320</v>
       </c>
       <c r="B46" t="n">
-        <v>15.72933578491211</v>
+        <v>15.72933673858643</v>
       </c>
       <c r="C46" t="n">
-        <v>15.74840208285252</v>
+        <v>15.74840303768283</v>
       </c>
       <c r="D46" t="n">
-        <v>15.35945760522207</v>
+        <v>15.35945853647056</v>
       </c>
       <c r="E46" t="n">
-        <v>15.63400611347231</v>
+        <v>15.63400706136676</v>
       </c>
       <c r="F46" t="n">
         <v>9407500</v>
@@ -1352,16 +1352,16 @@
         <v>44321</v>
       </c>
       <c r="B47" t="n">
-        <v>16.32228660583496</v>
+        <v>16.3222827911377</v>
       </c>
       <c r="C47" t="n">
-        <v>16.58730201015107</v>
+        <v>16.58729813351679</v>
       </c>
       <c r="D47" t="n">
-        <v>16.01532570257429</v>
+        <v>16.01532195961715</v>
       </c>
       <c r="E47" t="n">
-        <v>16.08396329586652</v>
+        <v>16.08395953686802</v>
       </c>
       <c r="F47" t="n">
         <v>17262500</v>
@@ -1372,16 +1372,16 @@
         <v>44322</v>
       </c>
       <c r="B48" t="n">
-        <v>16.61971473693848</v>
+        <v>16.61971282958984</v>
       </c>
       <c r="C48" t="n">
-        <v>16.64449947442742</v>
+        <v>16.64449756423438</v>
       </c>
       <c r="D48" t="n">
-        <v>16.16022705029641</v>
+        <v>16.16022519568053</v>
       </c>
       <c r="E48" t="n">
-        <v>16.31847408082518</v>
+        <v>16.31847220804819</v>
       </c>
       <c r="F48" t="n">
         <v>9404500</v>
@@ -1412,16 +1412,16 @@
         <v>44326</v>
       </c>
       <c r="B50" t="n">
-        <v>16.81418609619141</v>
+        <v>16.81418418884277</v>
       </c>
       <c r="C50" t="n">
-        <v>17.0162841548014</v>
+        <v>17.01628222452739</v>
       </c>
       <c r="D50" t="n">
-        <v>16.55298359675715</v>
+        <v>16.55298171903851</v>
       </c>
       <c r="E50" t="n">
-        <v>16.97052576072697</v>
+        <v>16.97052383564365</v>
       </c>
       <c r="F50" t="n">
         <v>7669500</v>
@@ -1432,16 +1432,16 @@
         <v>44327</v>
       </c>
       <c r="B51" t="n">
-        <v>16.58729934692383</v>
+        <v>16.58730125427246</v>
       </c>
       <c r="C51" t="n">
-        <v>16.78367894467991</v>
+        <v>16.78368087460993</v>
       </c>
       <c r="D51" t="n">
-        <v>16.4919696745899</v>
+        <v>16.49197157097672</v>
       </c>
       <c r="E51" t="n">
-        <v>16.6254319431623</v>
+        <v>16.62543385489575</v>
       </c>
       <c r="F51" t="n">
         <v>6191000</v>
@@ -1452,16 +1452,16 @@
         <v>44328</v>
       </c>
       <c r="B52" t="n">
-        <v>16.12590789794922</v>
+        <v>16.12590599060059</v>
       </c>
       <c r="C52" t="n">
-        <v>16.57776793756821</v>
+        <v>16.57776597677424</v>
       </c>
       <c r="D52" t="n">
-        <v>16.04201690472579</v>
+        <v>16.04201500729966</v>
       </c>
       <c r="E52" t="n">
-        <v>16.49006586623571</v>
+        <v>16.49006391581501</v>
       </c>
       <c r="F52" t="n">
         <v>6728500</v>
@@ -1492,16 +1492,16 @@
         <v>44330</v>
       </c>
       <c r="B54" t="n">
-        <v>16.52628898620605</v>
+        <v>16.52629089355469</v>
       </c>
       <c r="C54" t="n">
-        <v>16.66356232925931</v>
+        <v>16.66356425245107</v>
       </c>
       <c r="D54" t="n">
-        <v>16.13734451407442</v>
+        <v>16.13734637653381</v>
       </c>
       <c r="E54" t="n">
-        <v>16.54726082268666</v>
+        <v>16.54726273245572</v>
       </c>
       <c r="F54" t="n">
         <v>5923000</v>
@@ -1512,16 +1512,16 @@
         <v>44333</v>
       </c>
       <c r="B55" t="n">
-        <v>16.34706878662109</v>
+        <v>16.34707260131836</v>
       </c>
       <c r="C55" t="n">
-        <v>16.52819314458002</v>
+        <v>16.52819700154386</v>
       </c>
       <c r="D55" t="n">
-        <v>16.06107980023078</v>
+        <v>16.06108354819061</v>
       </c>
       <c r="E55" t="n">
-        <v>16.50531395293831</v>
+        <v>16.50531780456314</v>
       </c>
       <c r="F55" t="n">
         <v>4728000</v>
@@ -1552,16 +1552,16 @@
         <v>44335</v>
       </c>
       <c r="B57" t="n">
-        <v>15.82848072052002</v>
+        <v>15.82847785949707</v>
       </c>
       <c r="C57" t="n">
-        <v>16.36804466877901</v>
+        <v>16.36804171022903</v>
       </c>
       <c r="D57" t="n">
-        <v>15.67595395070043</v>
+        <v>15.67595111724694</v>
       </c>
       <c r="E57" t="n">
-        <v>15.98482038684572</v>
+        <v>15.98481749756413</v>
       </c>
       <c r="F57" t="n">
         <v>6358000</v>
@@ -1572,16 +1572,16 @@
         <v>44336</v>
       </c>
       <c r="B58" t="n">
-        <v>16.03248596191406</v>
+        <v>16.03248405456543</v>
       </c>
       <c r="C58" t="n">
-        <v>16.03248596191406</v>
+        <v>16.03248405456543</v>
       </c>
       <c r="D58" t="n">
-        <v>15.69692561740377</v>
+        <v>15.69692374997599</v>
       </c>
       <c r="E58" t="n">
-        <v>15.90283657256179</v>
+        <v>15.90283468063725</v>
       </c>
       <c r="F58" t="n">
         <v>7278000</v>
@@ -1592,16 +1592,16 @@
         <v>44337</v>
       </c>
       <c r="B59" t="n">
-        <v>16.43477439880371</v>
+        <v>16.43477249145508</v>
       </c>
       <c r="C59" t="n">
-        <v>16.6254337643569</v>
+        <v>16.62543183488117</v>
       </c>
       <c r="D59" t="n">
-        <v>15.75984264485187</v>
+        <v>15.75984081583289</v>
       </c>
       <c r="E59" t="n">
-        <v>16.03439118575198</v>
+        <v>16.03438932487009</v>
       </c>
       <c r="F59" t="n">
         <v>10145000</v>
@@ -1652,16 +1652,16 @@
         <v>44342</v>
       </c>
       <c r="B62" t="n">
-        <v>16.94192695617676</v>
+        <v>16.94192314147949</v>
       </c>
       <c r="C62" t="n">
-        <v>17.11161449219801</v>
+        <v>17.11161063929336</v>
       </c>
       <c r="D62" t="n">
-        <v>16.65975260630318</v>
+        <v>16.65974885514118</v>
       </c>
       <c r="E62" t="n">
-        <v>17.02391059716581</v>
+        <v>17.02390676400885</v>
       </c>
       <c r="F62" t="n">
         <v>5462000</v>
@@ -1712,16 +1712,16 @@
         <v>44347</v>
       </c>
       <c r="B65" t="n">
-        <v>17.05441093444824</v>
+        <v>17.05441474914551</v>
       </c>
       <c r="C65" t="n">
-        <v>17.2546034069664</v>
+        <v>17.25460726644232</v>
       </c>
       <c r="D65" t="n">
-        <v>16.87137921937667</v>
+        <v>16.87138299313376</v>
       </c>
       <c r="E65" t="n">
-        <v>17.09254352664678</v>
+        <v>17.09254734987347</v>
       </c>
       <c r="F65" t="n">
         <v>4641000</v>
@@ -1732,16 +1732,16 @@
         <v>44348</v>
       </c>
       <c r="B66" t="n">
-        <v>16.9686164855957</v>
+        <v>16.96862030029297</v>
       </c>
       <c r="C66" t="n">
-        <v>17.41094515397386</v>
+        <v>17.41094906811058</v>
       </c>
       <c r="D66" t="n">
-        <v>16.82562288397091</v>
+        <v>16.82562666652193</v>
       </c>
       <c r="E66" t="n">
-        <v>17.17834213169021</v>
+        <v>17.17834599353568</v>
       </c>
       <c r="F66" t="n">
         <v>13722000</v>
@@ -1772,16 +1772,16 @@
         <v>44351</v>
       </c>
       <c r="B68" t="n">
-        <v>16.77223777770996</v>
+        <v>16.77223968505859</v>
       </c>
       <c r="C68" t="n">
-        <v>16.81608880704675</v>
+        <v>16.81609071938215</v>
       </c>
       <c r="D68" t="n">
-        <v>16.40617250494436</v>
+        <v>16.40617437066384</v>
       </c>
       <c r="E68" t="n">
-        <v>16.72266649551031</v>
+        <v>16.72266839722167</v>
       </c>
       <c r="F68" t="n">
         <v>8097000</v>
@@ -1792,16 +1792,16 @@
         <v>44354</v>
       </c>
       <c r="B69" t="n">
-        <v>16.53772735595703</v>
+        <v>16.53772926330566</v>
       </c>
       <c r="C69" t="n">
-        <v>16.77223772166646</v>
+        <v>16.77223965606192</v>
       </c>
       <c r="D69" t="n">
-        <v>16.03057584819165</v>
+        <v>16.03057769704888</v>
       </c>
       <c r="E69" t="n">
-        <v>16.77223772166646</v>
+        <v>16.77223965606192</v>
       </c>
       <c r="F69" t="n">
         <v>10336000</v>
@@ -1812,16 +1812,16 @@
         <v>44355</v>
       </c>
       <c r="B70" t="n">
-        <v>16.08205795288086</v>
+        <v>16.08205413818359</v>
       </c>
       <c r="C70" t="n">
-        <v>16.61018141053224</v>
+        <v>16.610177470563</v>
       </c>
       <c r="D70" t="n">
-        <v>15.9295293598389</v>
+        <v>15.92952558132173</v>
       </c>
       <c r="E70" t="n">
-        <v>16.60064825982571</v>
+        <v>16.60064432211775</v>
       </c>
       <c r="F70" t="n">
         <v>9246000</v>
@@ -1832,16 +1832,16 @@
         <v>44356</v>
       </c>
       <c r="B71" t="n">
-        <v>16.16403770446777</v>
+        <v>16.16403579711914</v>
       </c>
       <c r="C71" t="n">
-        <v>16.39664255171839</v>
+        <v>16.3966406169225</v>
       </c>
       <c r="D71" t="n">
-        <v>15.82466631047011</v>
+        <v>15.82466444316714</v>
       </c>
       <c r="E71" t="n">
-        <v>16.08205589177119</v>
+        <v>16.08205399409637</v>
       </c>
       <c r="F71" t="n">
         <v>10294500</v>
@@ -1872,16 +1872,16 @@
         <v>44358</v>
       </c>
       <c r="B73" t="n">
-        <v>16.07061576843262</v>
+        <v>16.07061386108398</v>
       </c>
       <c r="C73" t="n">
-        <v>16.30512616021678</v>
+        <v>16.30512422503518</v>
       </c>
       <c r="D73" t="n">
-        <v>15.87423797549705</v>
+        <v>15.8742360914556</v>
       </c>
       <c r="E73" t="n">
-        <v>16.3032188029694</v>
+        <v>16.30321686801416</v>
       </c>
       <c r="F73" t="n">
         <v>5133000</v>
@@ -1912,16 +1912,16 @@
         <v>44362</v>
       </c>
       <c r="B75" t="n">
-        <v>15.85898303985596</v>
+        <v>15.85898494720459</v>
       </c>
       <c r="C75" t="n">
-        <v>16.02676318570492</v>
+        <v>16.02676511323235</v>
       </c>
       <c r="D75" t="n">
-        <v>15.48719932831946</v>
+        <v>15.48720119095393</v>
       </c>
       <c r="E75" t="n">
-        <v>16.01532267985088</v>
+        <v>16.01532460600237</v>
       </c>
       <c r="F75" t="n">
         <v>8432500</v>
@@ -1932,16 +1932,16 @@
         <v>44363</v>
       </c>
       <c r="B76" t="n">
-        <v>15.89902305603027</v>
+        <v>15.89902210235596</v>
       </c>
       <c r="C76" t="n">
-        <v>16.11446715307724</v>
+        <v>16.1144661864799</v>
       </c>
       <c r="D76" t="n">
-        <v>15.66260712011776</v>
+        <v>15.66260618062443</v>
       </c>
       <c r="E76" t="n">
-        <v>15.7026452588224</v>
+        <v>15.70264431692745</v>
       </c>
       <c r="F76" t="n">
         <v>10606500</v>
@@ -1952,16 +1952,16 @@
         <v>44364</v>
       </c>
       <c r="B77" t="n">
-        <v>15.97719383239746</v>
+        <v>15.97719192504883</v>
       </c>
       <c r="C77" t="n">
-        <v>16.00769882125508</v>
+        <v>16.00769691026478</v>
       </c>
       <c r="D77" t="n">
-        <v>15.69120478891841</v>
+        <v>15.691202915711</v>
       </c>
       <c r="E77" t="n">
-        <v>15.8971175547978</v>
+        <v>15.89711565700863</v>
       </c>
       <c r="F77" t="n">
         <v>7246000</v>
@@ -1972,16 +1972,16 @@
         <v>44365</v>
       </c>
       <c r="B78" t="n">
-        <v>16.2078914642334</v>
+        <v>16.20788955688477</v>
       </c>
       <c r="C78" t="n">
-        <v>16.36423112436919</v>
+        <v>16.36422919862247</v>
       </c>
       <c r="D78" t="n">
-        <v>15.67976622640263</v>
+        <v>15.67976438120391</v>
       </c>
       <c r="E78" t="n">
-        <v>15.98863265031907</v>
+        <v>15.98863076877287</v>
       </c>
       <c r="F78" t="n">
         <v>12012000</v>
@@ -1992,16 +1992,16 @@
         <v>44368</v>
       </c>
       <c r="B79" t="n">
-        <v>16.48434638977051</v>
+        <v>16.48434448242188</v>
       </c>
       <c r="C79" t="n">
-        <v>16.59302212366407</v>
+        <v>16.59302020374093</v>
       </c>
       <c r="D79" t="n">
-        <v>16.0000739807668</v>
+        <v>16.00007212945171</v>
       </c>
       <c r="E79" t="n">
-        <v>16.20789229804439</v>
+        <v>16.20789042268334</v>
       </c>
       <c r="F79" t="n">
         <v>6798000</v>
@@ -2012,16 +2012,16 @@
         <v>44369</v>
       </c>
       <c r="B80" t="n">
-        <v>16.47290802001953</v>
+        <v>16.47290420532227</v>
       </c>
       <c r="C80" t="n">
-        <v>16.4957872180342</v>
+        <v>16.49578339803871</v>
       </c>
       <c r="D80" t="n">
-        <v>16.13162922550603</v>
+        <v>16.13162548984007</v>
       </c>
       <c r="E80" t="n">
-        <v>16.46718776595022</v>
+        <v>16.46718395257762</v>
       </c>
       <c r="F80" t="n">
         <v>6518000</v>
@@ -2052,16 +2052,16 @@
         <v>44371</v>
       </c>
       <c r="B82" t="n">
-        <v>16.64640426635742</v>
+        <v>16.64640617370605</v>
       </c>
       <c r="C82" t="n">
-        <v>16.72648053888243</v>
+        <v>16.72648245540622</v>
       </c>
       <c r="D82" t="n">
-        <v>16.39664229944431</v>
+        <v>16.39664417817516</v>
       </c>
       <c r="E82" t="n">
-        <v>16.46909096154148</v>
+        <v>16.46909284857351</v>
       </c>
       <c r="F82" t="n">
         <v>8527500</v>
@@ -2072,16 +2072,16 @@
         <v>44372</v>
       </c>
       <c r="B83" t="n">
-        <v>16.18501091003418</v>
+        <v>16.18500900268555</v>
       </c>
       <c r="C83" t="n">
-        <v>16.74745398613881</v>
+        <v>16.74745201250817</v>
       </c>
       <c r="D83" t="n">
-        <v>16.05345599637458</v>
+        <v>16.05345410452925</v>
       </c>
       <c r="E83" t="n">
-        <v>16.64640405902371</v>
+        <v>16.64640209730146</v>
       </c>
       <c r="F83" t="n">
         <v>6078000</v>
@@ -2132,16 +2132,16 @@
         <v>44377</v>
       </c>
       <c r="B86" t="n">
-        <v>16.49959945678711</v>
+        <v>16.49960136413574</v>
       </c>
       <c r="C86" t="n">
-        <v>16.49959945678711</v>
+        <v>16.49960136413574</v>
       </c>
       <c r="D86" t="n">
-        <v>16.19073120503556</v>
+        <v>16.19073307667912</v>
       </c>
       <c r="E86" t="n">
-        <v>16.38901636774828</v>
+        <v>16.38901826231355</v>
       </c>
       <c r="F86" t="n">
         <v>6685000</v>
@@ -2192,16 +2192,16 @@
         <v>44382</v>
       </c>
       <c r="B89" t="n">
-        <v>16.41570663452148</v>
+        <v>16.41570854187012</v>
       </c>
       <c r="C89" t="n">
-        <v>16.54726154865489</v>
+        <v>16.54726347128895</v>
       </c>
       <c r="D89" t="n">
-        <v>16.25174119484036</v>
+        <v>16.25174308313778</v>
       </c>
       <c r="E89" t="n">
-        <v>16.40808084242347</v>
+        <v>16.40808274888606</v>
       </c>
       <c r="F89" t="n">
         <v>3871000</v>
@@ -2232,16 +2232,16 @@
         <v>44384</v>
       </c>
       <c r="B91" t="n">
-        <v>16.44430541992188</v>
+        <v>16.44430732727051</v>
       </c>
       <c r="C91" t="n">
-        <v>16.58348612054724</v>
+        <v>16.58348804403921</v>
       </c>
       <c r="D91" t="n">
-        <v>16.15069061682722</v>
+        <v>16.15069249011994</v>
       </c>
       <c r="E91" t="n">
-        <v>16.39664149383569</v>
+        <v>16.39664339565586</v>
       </c>
       <c r="F91" t="n">
         <v>12086500</v>
@@ -2252,16 +2252,16 @@
         <v>44385</v>
       </c>
       <c r="B92" t="n">
-        <v>16.43477439880371</v>
+        <v>16.43477249145508</v>
       </c>
       <c r="C92" t="n">
-        <v>16.79893236876558</v>
+        <v>16.79893041915436</v>
       </c>
       <c r="D92" t="n">
-        <v>16.24411685151298</v>
+        <v>16.24411496629124</v>
       </c>
       <c r="E92" t="n">
-        <v>16.26318133345833</v>
+        <v>16.26317944602405</v>
       </c>
       <c r="F92" t="n">
         <v>7435000</v>
@@ -2292,16 +2292,16 @@
         <v>44390</v>
       </c>
       <c r="B94" t="n">
-        <v>16.7874927520752</v>
+        <v>16.78749465942383</v>
       </c>
       <c r="C94" t="n">
-        <v>16.91142006005396</v>
+        <v>16.91142198148287</v>
       </c>
       <c r="D94" t="n">
-        <v>16.43096059459017</v>
+        <v>16.4309624614306</v>
       </c>
       <c r="E94" t="n">
-        <v>16.45383978992295</v>
+        <v>16.45384165936285</v>
       </c>
       <c r="F94" t="n">
         <v>6446000</v>
@@ -2332,16 +2332,16 @@
         <v>44392</v>
       </c>
       <c r="B96" t="n">
-        <v>16.45002555847168</v>
+        <v>16.45002937316895</v>
       </c>
       <c r="C96" t="n">
-        <v>16.86375476157448</v>
+        <v>16.86375867221395</v>
       </c>
       <c r="D96" t="n">
-        <v>16.44049240966831</v>
+        <v>16.44049622215487</v>
       </c>
       <c r="E96" t="n">
-        <v>16.72266670485169</v>
+        <v>16.72267058277338</v>
       </c>
       <c r="F96" t="n">
         <v>3746000</v>
@@ -2372,16 +2372,16 @@
         <v>44396</v>
       </c>
       <c r="B98" t="n">
-        <v>16.65402984619141</v>
+        <v>16.65403175354004</v>
       </c>
       <c r="C98" t="n">
-        <v>16.79702526617702</v>
+        <v>16.7970271899026</v>
       </c>
       <c r="D98" t="n">
-        <v>16.40426788246265</v>
+        <v>16.40426976120661</v>
       </c>
       <c r="E98" t="n">
-        <v>16.58539408105208</v>
+        <v>16.58539598054001</v>
       </c>
       <c r="F98" t="n">
         <v>7763500</v>
@@ -2392,16 +2392,16 @@
         <v>44397</v>
       </c>
       <c r="B99" t="n">
-        <v>16.51103782653809</v>
+        <v>16.51103591918945</v>
       </c>
       <c r="C99" t="n">
-        <v>16.71694877821082</v>
+        <v>16.71694684707543</v>
       </c>
       <c r="D99" t="n">
-        <v>16.45956099775114</v>
+        <v>16.45955909634909</v>
       </c>
       <c r="E99" t="n">
-        <v>16.6540314419629</v>
+        <v>16.6540295180957</v>
       </c>
       <c r="F99" t="n">
         <v>3835500</v>
@@ -2432,16 +2432,16 @@
         <v>44399</v>
       </c>
       <c r="B101" t="n">
-        <v>16.64450073242188</v>
+        <v>16.64449310302734</v>
       </c>
       <c r="C101" t="n">
-        <v>16.68072598092255</v>
+        <v>16.68071833492333</v>
       </c>
       <c r="D101" t="n">
-        <v>16.44431000512559</v>
+        <v>16.44430246749314</v>
       </c>
       <c r="E101" t="n">
-        <v>16.58730364151761</v>
+        <v>16.5872960383407</v>
       </c>
       <c r="F101" t="n">
         <v>2829500</v>
@@ -2452,16 +2452,16 @@
         <v>44400</v>
       </c>
       <c r="B102" t="n">
-        <v>16.68263053894043</v>
+        <v>16.6826286315918</v>
       </c>
       <c r="C102" t="n">
-        <v>16.73029447031815</v>
+        <v>16.73029255752003</v>
       </c>
       <c r="D102" t="n">
-        <v>16.56060876542906</v>
+        <v>16.56060687203135</v>
       </c>
       <c r="E102" t="n">
-        <v>16.64449793922831</v>
+        <v>16.64449603623943</v>
       </c>
       <c r="F102" t="n">
         <v>4154500</v>
@@ -2472,16 +2472,16 @@
         <v>44403</v>
       </c>
       <c r="B103" t="n">
-        <v>17.19741058349609</v>
+        <v>17.19740867614746</v>
       </c>
       <c r="C103" t="n">
-        <v>17.21647506604089</v>
+        <v>17.21647315657783</v>
       </c>
       <c r="D103" t="n">
-        <v>16.56060959167434</v>
+        <v>16.5606077549527</v>
       </c>
       <c r="E103" t="n">
-        <v>16.75126896322247</v>
+        <v>16.75126710535498</v>
       </c>
       <c r="F103" t="n">
         <v>9987000</v>
@@ -2492,16 +2492,16 @@
         <v>44404</v>
       </c>
       <c r="B104" t="n">
-        <v>16.9686164855957</v>
+        <v>16.96862030029297</v>
       </c>
       <c r="C104" t="n">
-        <v>17.30036389601047</v>
+        <v>17.30036778528753</v>
       </c>
       <c r="D104" t="n">
-        <v>16.8732886300207</v>
+        <v>16.87329242328741</v>
       </c>
       <c r="E104" t="n">
-        <v>17.1440224308819</v>
+        <v>17.14402628501199</v>
       </c>
       <c r="F104" t="n">
         <v>6666500</v>
@@ -2532,16 +2532,16 @@
         <v>44406</v>
       </c>
       <c r="B106" t="n">
-        <v>16.62543106079102</v>
+        <v>16.62543296813965</v>
       </c>
       <c r="C106" t="n">
-        <v>16.77795780112525</v>
+        <v>16.77795972597248</v>
       </c>
       <c r="D106" t="n">
-        <v>16.27461919436984</v>
+        <v>16.27462106147167</v>
       </c>
       <c r="E106" t="n">
-        <v>16.77795780112525</v>
+        <v>16.77795972597248</v>
       </c>
       <c r="F106" t="n">
         <v>12625000</v>
@@ -2552,16 +2552,16 @@
         <v>44407</v>
       </c>
       <c r="B107" t="n">
-        <v>16.52628898620605</v>
+        <v>16.52629089355469</v>
       </c>
       <c r="C107" t="n">
-        <v>16.73219990991705</v>
+        <v>16.73220184103048</v>
       </c>
       <c r="D107" t="n">
-        <v>16.30893755658766</v>
+        <v>16.30893943885111</v>
       </c>
       <c r="E107" t="n">
-        <v>16.62543155217983</v>
+        <v>16.6254334709708</v>
       </c>
       <c r="F107" t="n">
         <v>16469000</v>
@@ -2572,16 +2572,16 @@
         <v>44410</v>
       </c>
       <c r="B108" t="n">
-        <v>16.5224781036377</v>
+        <v>16.52247619628906</v>
       </c>
       <c r="C108" t="n">
-        <v>16.83897031953316</v>
+        <v>16.83896837564879</v>
       </c>
       <c r="D108" t="n">
-        <v>16.36232372925435</v>
+        <v>16.36232184039388</v>
       </c>
       <c r="E108" t="n">
-        <v>16.6826306597586</v>
+        <v>16.68262873392202</v>
       </c>
       <c r="F108" t="n">
         <v>8100500</v>
@@ -2592,16 +2592,16 @@
         <v>44411</v>
       </c>
       <c r="B109" t="n">
-        <v>16.53010368347168</v>
+        <v>16.53010559082031</v>
       </c>
       <c r="C109" t="n">
-        <v>16.68072308765598</v>
+        <v>16.68072501238404</v>
       </c>
       <c r="D109" t="n">
-        <v>16.26127540276083</v>
+        <v>16.26127727909034</v>
       </c>
       <c r="E109" t="n">
-        <v>16.68072308765598</v>
+        <v>16.68072501238404</v>
       </c>
       <c r="F109" t="n">
         <v>5450500</v>
@@ -2612,16 +2612,16 @@
         <v>44412</v>
       </c>
       <c r="B110" t="n">
-        <v>16.60255241394043</v>
+        <v>16.60255432128906</v>
       </c>
       <c r="C110" t="n">
-        <v>16.83134253196625</v>
+        <v>16.83134446559894</v>
       </c>
       <c r="D110" t="n">
-        <v>16.34897574520748</v>
+        <v>16.3489776234245</v>
       </c>
       <c r="E110" t="n">
-        <v>16.48243801108588</v>
+        <v>16.48243990463543</v>
       </c>
       <c r="F110" t="n">
         <v>6533500</v>
@@ -2632,16 +2632,16 @@
         <v>44413</v>
       </c>
       <c r="B111" t="n">
-        <v>16.58729934692383</v>
+        <v>16.58730125427246</v>
       </c>
       <c r="C111" t="n">
-        <v>16.93811123196384</v>
+        <v>16.93811317965181</v>
       </c>
       <c r="D111" t="n">
-        <v>16.47481073358749</v>
+        <v>16.47481262800123</v>
       </c>
       <c r="E111" t="n">
-        <v>16.59301960001205</v>
+        <v>16.59302150801845</v>
       </c>
       <c r="F111" t="n">
         <v>13427000</v>
@@ -2672,16 +2672,16 @@
         <v>44417</v>
       </c>
       <c r="B113" t="n">
-        <v>17.31942749023438</v>
+        <v>17.31942939758301</v>
       </c>
       <c r="C113" t="n">
-        <v>17.35756008512363</v>
+        <v>17.35756199667172</v>
       </c>
       <c r="D113" t="n">
-        <v>16.61780374497947</v>
+        <v>16.6178055750599</v>
       </c>
       <c r="E113" t="n">
-        <v>16.61780374497947</v>
+        <v>16.6178055750599</v>
       </c>
       <c r="F113" t="n">
         <v>10558500</v>
@@ -2712,16 +2712,16 @@
         <v>44419</v>
       </c>
       <c r="B115" t="n">
-        <v>17.20884704589844</v>
+        <v>17.20884895324707</v>
       </c>
       <c r="C115" t="n">
-        <v>17.57872523333663</v>
+        <v>17.57872718168084</v>
       </c>
       <c r="D115" t="n">
-        <v>17.19740835785192</v>
+        <v>17.19741026393275</v>
       </c>
       <c r="E115" t="n">
-        <v>17.57872523333663</v>
+        <v>17.57872718168084</v>
       </c>
       <c r="F115" t="n">
         <v>6265000</v>
@@ -2752,16 +2752,16 @@
         <v>44421</v>
       </c>
       <c r="B117" t="n">
-        <v>16.91142082214355</v>
+        <v>16.91141700744629</v>
       </c>
       <c r="C117" t="n">
-        <v>17.27367324935177</v>
+        <v>17.27366935294148</v>
       </c>
       <c r="D117" t="n">
-        <v>16.53010391318421</v>
+        <v>16.53010018450033</v>
       </c>
       <c r="E117" t="n">
-        <v>16.82562429034489</v>
+        <v>16.82562049500069</v>
       </c>
       <c r="F117" t="n">
         <v>5547600</v>
@@ -2772,16 +2772,16 @@
         <v>44424</v>
       </c>
       <c r="B118" t="n">
-        <v>16.44430541992188</v>
+        <v>16.44430732727051</v>
       </c>
       <c r="C118" t="n">
-        <v>17.04487925261408</v>
+        <v>17.04488122962231</v>
       </c>
       <c r="D118" t="n">
-        <v>16.27271237679204</v>
+        <v>16.27271426423787</v>
       </c>
       <c r="E118" t="n">
-        <v>16.86375487887679</v>
+        <v>16.86375683487669</v>
       </c>
       <c r="F118" t="n">
         <v>7814500</v>
@@ -2812,16 +2812,16 @@
         <v>44426</v>
       </c>
       <c r="B120" t="n">
-        <v>15.88186264038086</v>
+        <v>15.88186550140381</v>
       </c>
       <c r="C120" t="n">
-        <v>16.30131210662337</v>
+        <v>16.30131504320764</v>
       </c>
       <c r="D120" t="n">
-        <v>15.64353936928479</v>
+        <v>15.64354218737522</v>
       </c>
       <c r="E120" t="n">
-        <v>16.16784983839123</v>
+        <v>16.16785275093307</v>
       </c>
       <c r="F120" t="n">
         <v>10736900</v>
@@ -2872,16 +2872,16 @@
         <v>44431</v>
       </c>
       <c r="B123" t="n">
-        <v>16.69216346740723</v>
+        <v>16.69215965270996</v>
       </c>
       <c r="C123" t="n">
-        <v>17.16881004791025</v>
+        <v>17.16880612428388</v>
       </c>
       <c r="D123" t="n">
-        <v>16.52057040750415</v>
+        <v>16.52056663202143</v>
       </c>
       <c r="E123" t="n">
-        <v>16.97815068840407</v>
+        <v>16.97814680834951</v>
       </c>
       <c r="F123" t="n">
         <v>5050600</v>
@@ -2892,16 +2892,16 @@
         <v>44432</v>
       </c>
       <c r="B124" t="n">
-        <v>16.91142082214355</v>
+        <v>16.91141700744629</v>
       </c>
       <c r="C124" t="n">
-        <v>17.05441443572051</v>
+        <v>17.05441058876827</v>
       </c>
       <c r="D124" t="n">
-        <v>16.66356437675437</v>
+        <v>16.6635606179659</v>
       </c>
       <c r="E124" t="n">
-        <v>16.78749350858018</v>
+        <v>16.78748972183712</v>
       </c>
       <c r="F124" t="n">
         <v>4198100</v>
@@ -2912,16 +2912,16 @@
         <v>44433</v>
       </c>
       <c r="B125" t="n">
-        <v>17.01628303527832</v>
+        <v>17.01628494262695</v>
       </c>
       <c r="C125" t="n">
-        <v>17.19740924229705</v>
+        <v>17.19741116994805</v>
       </c>
       <c r="D125" t="n">
-        <v>16.78749289822105</v>
+        <v>16.78749477992469</v>
       </c>
       <c r="E125" t="n">
-        <v>17.0258161849385</v>
+        <v>17.0258180933557</v>
       </c>
       <c r="F125" t="n">
         <v>4269900</v>
@@ -2952,16 +2952,16 @@
         <v>44435</v>
       </c>
       <c r="B127" t="n">
-        <v>16.58729934692383</v>
+        <v>16.58730125427246</v>
       </c>
       <c r="C127" t="n">
-        <v>16.72076161549623</v>
+        <v>16.72076353819149</v>
       </c>
       <c r="D127" t="n">
-        <v>16.39664182051824</v>
+        <v>16.39664370594345</v>
       </c>
       <c r="E127" t="n">
-        <v>16.55870171800724</v>
+        <v>16.55870362206747</v>
       </c>
       <c r="F127" t="n">
         <v>5662600</v>
@@ -2992,16 +2992,16 @@
         <v>44439</v>
       </c>
       <c r="B129" t="n">
-        <v>16.02485847473145</v>
+        <v>16.02485656738281</v>
       </c>
       <c r="C129" t="n">
-        <v>16.63496737026124</v>
+        <v>16.63496539029478</v>
       </c>
       <c r="D129" t="n">
-        <v>16.02485847473145</v>
+        <v>16.02485656738281</v>
       </c>
       <c r="E129" t="n">
-        <v>16.37757776519067</v>
+        <v>16.37757581585984</v>
       </c>
       <c r="F129" t="n">
         <v>8477100</v>
@@ -3012,16 +3012,16 @@
         <v>44440</v>
       </c>
       <c r="B130" t="n">
-        <v>16.23458290100098</v>
+        <v>16.23458099365234</v>
       </c>
       <c r="C130" t="n">
-        <v>16.77795970229644</v>
+        <v>16.77795773110823</v>
       </c>
       <c r="D130" t="n">
-        <v>15.89139678723021</v>
+        <v>15.8913949202014</v>
       </c>
       <c r="E130" t="n">
-        <v>16.30131313017587</v>
+        <v>16.30131121498732</v>
       </c>
       <c r="F130" t="n">
         <v>7651500</v>
@@ -3032,16 +3032,16 @@
         <v>44441</v>
       </c>
       <c r="B131" t="n">
-        <v>16.72076225280762</v>
+        <v>16.72076034545898</v>
       </c>
       <c r="C131" t="n">
-        <v>17.03534891071645</v>
+        <v>17.0353469674827</v>
       </c>
       <c r="D131" t="n">
-        <v>16.10112026815059</v>
+        <v>16.10111843148494</v>
       </c>
       <c r="E131" t="n">
-        <v>16.16785049584908</v>
+        <v>16.16784865157147</v>
       </c>
       <c r="F131" t="n">
         <v>17566400</v>
@@ -3052,16 +3052,16 @@
         <v>44442</v>
       </c>
       <c r="B132" t="n">
-        <v>17.31180572509766</v>
+        <v>17.31180191040039</v>
       </c>
       <c r="C132" t="n">
-        <v>17.35946966153313</v>
+        <v>17.359465836333</v>
       </c>
       <c r="D132" t="n">
-        <v>16.69216546012336</v>
+        <v>16.69216178196529</v>
       </c>
       <c r="E132" t="n">
-        <v>16.90188932600712</v>
+        <v>16.9018856016359</v>
       </c>
       <c r="F132" t="n">
         <v>19565300</v>
@@ -3072,16 +3072,16 @@
         <v>44445</v>
       </c>
       <c r="B133" t="n">
-        <v>17.49292945861816</v>
+        <v>17.49292755126953</v>
       </c>
       <c r="C133" t="n">
-        <v>17.66452251450438</v>
+        <v>17.66452058844603</v>
       </c>
       <c r="D133" t="n">
-        <v>17.04488051974584</v>
+        <v>17.04487866125041</v>
       </c>
       <c r="E133" t="n">
-        <v>17.30227010357517</v>
+        <v>17.30226821701516</v>
       </c>
       <c r="F133" t="n">
         <v>6471000</v>
@@ -3092,16 +3092,16 @@
         <v>44447</v>
       </c>
       <c r="B134" t="n">
-        <v>17.07347869873047</v>
+        <v>17.0734806060791</v>
       </c>
       <c r="C134" t="n">
-        <v>17.55012523262749</v>
+        <v>17.55012719322427</v>
       </c>
       <c r="D134" t="n">
-        <v>16.84468858065136</v>
+        <v>16.84469046244091</v>
       </c>
       <c r="E134" t="n">
-        <v>17.49292815767328</v>
+        <v>17.49293011188033</v>
       </c>
       <c r="F134" t="n">
         <v>11069100</v>
@@ -3172,16 +3172,16 @@
         <v>44453</v>
       </c>
       <c r="B138" t="n">
-        <v>17.47386169433594</v>
+        <v>17.47386360168457</v>
       </c>
       <c r="C138" t="n">
-        <v>18.15070071155172</v>
+        <v>18.1507026927803</v>
       </c>
       <c r="D138" t="n">
-        <v>17.39759832236565</v>
+        <v>17.3976002213898</v>
       </c>
       <c r="E138" t="n">
-        <v>17.82658092611242</v>
+        <v>17.82658287196191</v>
       </c>
       <c r="F138" t="n">
         <v>6594500</v>
@@ -3252,16 +3252,16 @@
         <v>44459</v>
       </c>
       <c r="B142" t="n">
-        <v>17.94097709655762</v>
+        <v>17.94097518920898</v>
       </c>
       <c r="C142" t="n">
-        <v>18.12210330724501</v>
+        <v>18.12210138064041</v>
       </c>
       <c r="D142" t="n">
-        <v>17.63592357430248</v>
+        <v>17.63592169938482</v>
       </c>
       <c r="E142" t="n">
-        <v>18.02677362697468</v>
+        <v>18.02677171050481</v>
       </c>
       <c r="F142" t="n">
         <v>15522000</v>
@@ -3272,16 +3272,16 @@
         <v>44460</v>
       </c>
       <c r="B143" t="n">
-        <v>18.57968330383301</v>
+        <v>18.57968139648438</v>
       </c>
       <c r="C143" t="n">
-        <v>18.7417432123123</v>
+        <v>18.74174128832697</v>
       </c>
       <c r="D143" t="n">
-        <v>17.82658265967325</v>
+        <v>17.82658082963624</v>
       </c>
       <c r="E143" t="n">
-        <v>18.06490594753913</v>
+        <v>18.06490409303639</v>
       </c>
       <c r="F143" t="n">
         <v>17756900</v>
@@ -3292,16 +3292,16 @@
         <v>44461</v>
       </c>
       <c r="B144" t="n">
-        <v>18.3890266418457</v>
+        <v>18.38902282714844</v>
       </c>
       <c r="C144" t="n">
-        <v>18.68454702378533</v>
+        <v>18.68454314778407</v>
       </c>
       <c r="D144" t="n">
-        <v>18.21743357547351</v>
+        <v>18.21742979637223</v>
       </c>
       <c r="E144" t="n">
-        <v>18.61781679092114</v>
+        <v>18.61781292876268</v>
       </c>
       <c r="F144" t="n">
         <v>5973600</v>
@@ -3412,16 +3412,16 @@
         <v>44469</v>
       </c>
       <c r="B150" t="n">
-        <v>18.15070152282715</v>
+        <v>18.15069770812988</v>
       </c>
       <c r="C150" t="n">
-        <v>18.62734807351153</v>
+        <v>18.62734415863839</v>
       </c>
       <c r="D150" t="n">
-        <v>18.04583869983265</v>
+        <v>18.0458349071742</v>
       </c>
       <c r="E150" t="n">
-        <v>18.30322827358517</v>
+        <v>18.30322442683165</v>
       </c>
       <c r="F150" t="n">
         <v>10293000</v>
@@ -3432,16 +3432,16 @@
         <v>44470</v>
       </c>
       <c r="B151" t="n">
-        <v>18.45575714111328</v>
+        <v>18.45575523376465</v>
       </c>
       <c r="C151" t="n">
-        <v>18.56061815787245</v>
+        <v>18.56061623968673</v>
       </c>
       <c r="D151" t="n">
-        <v>18.00770816839343</v>
+        <v>18.00770630734936</v>
       </c>
       <c r="E151" t="n">
-        <v>18.19836753783964</v>
+        <v>18.19836565709148</v>
       </c>
       <c r="F151" t="n">
         <v>5841800</v>
@@ -3452,16 +3452,16 @@
         <v>44473</v>
       </c>
       <c r="B152" t="n">
-        <v>18.41762542724609</v>
+        <v>18.41762161254883</v>
       </c>
       <c r="C152" t="n">
-        <v>18.49388881504631</v>
+        <v>18.49388498455321</v>
       </c>
       <c r="D152" t="n">
-        <v>18.07443927301384</v>
+        <v>18.07443552939801</v>
       </c>
       <c r="E152" t="n">
-        <v>18.38902779323513</v>
+        <v>18.38902398446107</v>
       </c>
       <c r="F152" t="n">
         <v>9789400</v>
@@ -3472,16 +3472,16 @@
         <v>44474</v>
       </c>
       <c r="B153" t="n">
-        <v>18.32229423522949</v>
+        <v>18.32229232788086</v>
       </c>
       <c r="C153" t="n">
-        <v>18.49388729827244</v>
+        <v>18.49388537306099</v>
       </c>
       <c r="D153" t="n">
-        <v>18.04584015897554</v>
+        <v>18.04583828040574</v>
       </c>
       <c r="E153" t="n">
-        <v>18.34136053518147</v>
+        <v>18.34135862584804</v>
       </c>
       <c r="F153" t="n">
         <v>8000200</v>
@@ -3512,16 +3512,16 @@
         <v>44476</v>
       </c>
       <c r="B155" t="n">
-        <v>18.0805492401123</v>
+        <v>18.08055114746094</v>
       </c>
       <c r="C155" t="n">
-        <v>18.36723797984786</v>
+        <v>18.36723991743979</v>
       </c>
       <c r="D155" t="n">
-        <v>17.99454225364713</v>
+        <v>17.99454415192273</v>
       </c>
       <c r="E155" t="n">
-        <v>18.27167628175104</v>
+        <v>18.271678209262</v>
       </c>
       <c r="F155" t="n">
         <v>7169200</v>
@@ -3552,16 +3552,16 @@
         <v>44480</v>
       </c>
       <c r="B157" t="n">
-        <v>16.62799072265625</v>
+        <v>16.62798881530762</v>
       </c>
       <c r="C157" t="n">
-        <v>17.52628500439614</v>
+        <v>17.52628299400677</v>
       </c>
       <c r="D157" t="n">
-        <v>16.47508980100556</v>
+        <v>16.47508791119575</v>
       </c>
       <c r="E157" t="n">
-        <v>17.42116493724025</v>
+        <v>17.4211629389089</v>
       </c>
       <c r="F157" t="n">
         <v>31512800</v>
@@ -3572,16 +3572,16 @@
         <v>44482</v>
       </c>
       <c r="B158" t="n">
-        <v>17.12491798400879</v>
+        <v>17.12491989135742</v>
       </c>
       <c r="C158" t="n">
-        <v>17.40205019435258</v>
+        <v>17.4020521325678</v>
       </c>
       <c r="D158" t="n">
-        <v>16.62798912502792</v>
+        <v>16.62799097702933</v>
       </c>
       <c r="E158" t="n">
-        <v>16.62798912502792</v>
+        <v>16.62799097702933</v>
       </c>
       <c r="F158" t="n">
         <v>10150700</v>
@@ -3612,16 +3612,16 @@
         <v>44484</v>
       </c>
       <c r="B160" t="n">
-        <v>16.76177787780762</v>
+        <v>16.76177978515625</v>
       </c>
       <c r="C160" t="n">
-        <v>16.933790021779</v>
+        <v>16.93379194870116</v>
       </c>
       <c r="D160" t="n">
-        <v>15.86348373102988</v>
+        <v>15.86348553616024</v>
       </c>
       <c r="E160" t="n">
-        <v>15.95904724838453</v>
+        <v>15.95904906438921</v>
       </c>
       <c r="F160" t="n">
         <v>78021300</v>
@@ -3632,16 +3632,16 @@
         <v>44487</v>
       </c>
       <c r="B161" t="n">
-        <v>16.20751190185547</v>
+        <v>16.2075138092041</v>
       </c>
       <c r="C161" t="n">
-        <v>16.67577301414236</v>
+        <v>16.67577497659736</v>
       </c>
       <c r="D161" t="n">
-        <v>16.10239365985386</v>
+        <v>16.10239555483187</v>
       </c>
       <c r="E161" t="n">
-        <v>16.58976601986295</v>
+        <v>16.58976797219639</v>
       </c>
       <c r="F161" t="n">
         <v>13070300</v>
@@ -3652,16 +3652,16 @@
         <v>44488</v>
       </c>
       <c r="B162" t="n">
-        <v>15.81570529937744</v>
+        <v>15.81570339202881</v>
       </c>
       <c r="C162" t="n">
-        <v>16.07372631856425</v>
+        <v>16.0737243800987</v>
       </c>
       <c r="D162" t="n">
-        <v>15.63413657274048</v>
+        <v>15.63413468728875</v>
       </c>
       <c r="E162" t="n">
-        <v>16.05461324542679</v>
+        <v>16.05461130926624</v>
       </c>
       <c r="F162" t="n">
         <v>17605400</v>
@@ -3672,16 +3672,16 @@
         <v>44489</v>
       </c>
       <c r="B163" t="n">
-        <v>15.98771572113037</v>
+        <v>15.98771667480469</v>
       </c>
       <c r="C163" t="n">
-        <v>16.21706707909584</v>
+        <v>16.21706804645106</v>
       </c>
       <c r="D163" t="n">
-        <v>15.71058351377639</v>
+        <v>15.71058445091965</v>
       </c>
       <c r="E163" t="n">
-        <v>15.93993487174186</v>
+        <v>15.93993582256603</v>
       </c>
       <c r="F163" t="n">
         <v>11472200</v>
@@ -3732,16 +3732,16 @@
         <v>44494</v>
       </c>
       <c r="B166" t="n">
-        <v>15.41433715820312</v>
+        <v>15.41433620452881</v>
       </c>
       <c r="C166" t="n">
-        <v>15.66280159699508</v>
+        <v>15.66280062794844</v>
       </c>
       <c r="D166" t="n">
-        <v>15.1372049374846</v>
+        <v>15.13720400095626</v>
       </c>
       <c r="E166" t="n">
-        <v>15.39522591115963</v>
+        <v>15.39522495866771</v>
       </c>
       <c r="F166" t="n">
         <v>20484500</v>
@@ -3772,16 +3772,16 @@
         <v>44496</v>
       </c>
       <c r="B168" t="n">
-        <v>14.94607925415039</v>
+        <v>14.94608020782471</v>
       </c>
       <c r="C168" t="n">
-        <v>15.38566984725368</v>
+        <v>15.38567082897724</v>
       </c>
       <c r="D168" t="n">
-        <v>14.81229049577588</v>
+        <v>14.81229144091344</v>
       </c>
       <c r="E168" t="n">
-        <v>15.38566984725368</v>
+        <v>15.38567082897724</v>
       </c>
       <c r="F168" t="n">
         <v>9783700</v>
@@ -3792,16 +3792,16 @@
         <v>44497</v>
       </c>
       <c r="B169" t="n">
-        <v>14.95563507080078</v>
+        <v>14.95563411712646</v>
       </c>
       <c r="C169" t="n">
-        <v>15.13720559603315</v>
+        <v>15.13720463078065</v>
       </c>
       <c r="D169" t="n">
-        <v>14.69761499726184</v>
+        <v>14.69761406004066</v>
       </c>
       <c r="E169" t="n">
-        <v>15.02252990653125</v>
+        <v>15.02252894859126</v>
       </c>
       <c r="F169" t="n">
         <v>8208600</v>
@@ -3812,16 +3812,16 @@
         <v>44498</v>
       </c>
       <c r="B170" t="n">
-        <v>14.61160659790039</v>
+        <v>14.61160755157471</v>
       </c>
       <c r="C170" t="n">
-        <v>15.21365459344056</v>
+        <v>15.21365558640951</v>
       </c>
       <c r="D170" t="n">
-        <v>14.50648745380085</v>
+        <v>14.50648840061422</v>
       </c>
       <c r="E170" t="n">
-        <v>15.0034153938802</v>
+        <v>15.0034163731272</v>
       </c>
       <c r="F170" t="n">
         <v>13706000</v>
@@ -3832,16 +3832,16 @@
         <v>44501</v>
       </c>
       <c r="B171" t="n">
-        <v>14.31536102294922</v>
+        <v>14.31536197662354</v>
       </c>
       <c r="C171" t="n">
-        <v>14.77406466781794</v>
+        <v>14.77406565205061</v>
       </c>
       <c r="D171" t="n">
-        <v>14.20068533957237</v>
+        <v>14.20068628560711</v>
       </c>
       <c r="E171" t="n">
-        <v>14.76450813302954</v>
+        <v>14.76450911662556</v>
       </c>
       <c r="F171" t="n">
         <v>10277500</v>
@@ -3852,16 +3852,16 @@
         <v>44503</v>
       </c>
       <c r="B172" t="n">
-        <v>14.74539566040039</v>
+        <v>14.74539661407471</v>
       </c>
       <c r="C172" t="n">
-        <v>14.86962787591666</v>
+        <v>14.86962883762583</v>
       </c>
       <c r="D172" t="n">
-        <v>14.07645282125721</v>
+        <v>14.07645373166693</v>
       </c>
       <c r="E172" t="n">
-        <v>14.14334765198831</v>
+        <v>14.14334856672452</v>
       </c>
       <c r="F172" t="n">
         <v>21906500</v>
@@ -3892,16 +3892,16 @@
         <v>44505</v>
       </c>
       <c r="B174" t="n">
-        <v>14.5638256072998</v>
+        <v>14.56382656097412</v>
       </c>
       <c r="C174" t="n">
-        <v>14.71672652002295</v>
+        <v>14.71672748370959</v>
       </c>
       <c r="D174" t="n">
-        <v>14.1720167906064</v>
+        <v>14.17201771862414</v>
       </c>
       <c r="E174" t="n">
-        <v>14.54471344889008</v>
+        <v>14.54471440131288</v>
       </c>
       <c r="F174" t="n">
         <v>8161700</v>
@@ -3932,16 +3932,16 @@
         <v>44509</v>
       </c>
       <c r="B176" t="n">
-        <v>14.81228923797607</v>
+        <v>14.81229019165039</v>
       </c>
       <c r="C176" t="n">
-        <v>15.08942235500634</v>
+        <v>15.08942332652359</v>
       </c>
       <c r="D176" t="n">
-        <v>14.66894486795953</v>
+        <v>14.66894581240476</v>
       </c>
       <c r="E176" t="n">
-        <v>14.80273270361196</v>
+        <v>14.80273365667099</v>
       </c>
       <c r="F176" t="n">
         <v>6124400</v>
@@ -3952,16 +3952,16 @@
         <v>44510</v>
       </c>
       <c r="B177" t="n">
-        <v>15.26143646240234</v>
+        <v>15.26143836975098</v>
       </c>
       <c r="C177" t="n">
-        <v>15.38566867614508</v>
+        <v>15.38567059902005</v>
       </c>
       <c r="D177" t="n">
-        <v>14.71672584655168</v>
+        <v>14.7167276858233</v>
       </c>
       <c r="E177" t="n">
-        <v>14.84095806029442</v>
+        <v>14.84095991509237</v>
       </c>
       <c r="F177" t="n">
         <v>10223900</v>
@@ -3972,16 +3972,16 @@
         <v>44511</v>
       </c>
       <c r="B178" t="n">
-        <v>15.19454193115234</v>
+        <v>15.19454288482666</v>
       </c>
       <c r="C178" t="n">
-        <v>15.51945681788442</v>
+        <v>15.51945779195179</v>
       </c>
       <c r="D178" t="n">
-        <v>15.07986624960478</v>
+        <v>15.07986719608156</v>
       </c>
       <c r="E178" t="n">
-        <v>15.43344982888343</v>
+        <v>15.43345079755262</v>
       </c>
       <c r="F178" t="n">
         <v>5555700</v>
@@ -3992,16 +3992,16 @@
         <v>44512</v>
       </c>
       <c r="B179" t="n">
-        <v>14.84095859527588</v>
+        <v>14.8409595489502</v>
       </c>
       <c r="C179" t="n">
-        <v>15.23276740816299</v>
+        <v>15.23276838701479</v>
       </c>
       <c r="D179" t="n">
-        <v>14.82184643705182</v>
+        <v>14.82184738949799</v>
       </c>
       <c r="E179" t="n">
-        <v>15.08942303171791</v>
+        <v>15.08942400135846</v>
       </c>
       <c r="F179" t="n">
         <v>7831400</v>
@@ -4012,16 +4012,16 @@
         <v>44516</v>
       </c>
       <c r="B180" t="n">
-        <v>14.18157291412354</v>
+        <v>14.18157386779785</v>
       </c>
       <c r="C180" t="n">
-        <v>14.86007137817213</v>
+        <v>14.86007237747372</v>
       </c>
       <c r="D180" t="n">
-        <v>14.00000240201066</v>
+        <v>14.00000334347483</v>
       </c>
       <c r="E180" t="n">
-        <v>14.81228961649183</v>
+        <v>14.81229061258022</v>
       </c>
       <c r="F180" t="n">
         <v>11424100</v>
@@ -4152,16 +4152,16 @@
         <v>44525</v>
       </c>
       <c r="B187" t="n">
-        <v>13.23549747467041</v>
+        <v>13.23549842834473</v>
       </c>
       <c r="C187" t="n">
-        <v>13.27372270062788</v>
+        <v>13.27372365705648</v>
       </c>
       <c r="D187" t="n">
-        <v>12.89146952969195</v>
+        <v>12.89147045857758</v>
       </c>
       <c r="E187" t="n">
-        <v>13.13037741976643</v>
+        <v>13.13037836586639</v>
       </c>
       <c r="F187" t="n">
         <v>5547700</v>
@@ -4172,16 +4172,16 @@
         <v>44526</v>
       </c>
       <c r="B188" t="n">
-        <v>12.76723766326904</v>
+        <v>12.76723861694336</v>
       </c>
       <c r="C188" t="n">
-        <v>13.02525862899095</v>
+        <v>13.02525960193866</v>
       </c>
       <c r="D188" t="n">
-        <v>12.64300544770234</v>
+        <v>12.64300639209688</v>
       </c>
       <c r="E188" t="n">
-        <v>12.93925164041698</v>
+        <v>12.93925260694023</v>
       </c>
       <c r="F188" t="n">
         <v>6311300</v>
@@ -4192,16 +4192,16 @@
         <v>44529</v>
       </c>
       <c r="B189" t="n">
-        <v>12.47099208831787</v>
+        <v>12.47099494934082</v>
       </c>
       <c r="C189" t="n">
-        <v>13.11126530889348</v>
+        <v>13.11126831680421</v>
       </c>
       <c r="D189" t="n">
-        <v>12.42321032786153</v>
+        <v>12.42321317792267</v>
       </c>
       <c r="E189" t="n">
-        <v>12.88191304097531</v>
+        <v>12.88191599626937</v>
       </c>
       <c r="F189" t="n">
         <v>13464500</v>
@@ -4212,16 +4212,16 @@
         <v>44530</v>
       </c>
       <c r="B190" t="n">
-        <v>12.18430233001709</v>
+        <v>12.18430328369141</v>
       </c>
       <c r="C190" t="n">
-        <v>12.44232328740027</v>
+        <v>12.44232426127008</v>
       </c>
       <c r="D190" t="n">
-        <v>11.84027529820078</v>
+        <v>11.84027622494785</v>
       </c>
       <c r="E190" t="n">
-        <v>12.38498499308359</v>
+        <v>12.38498596246548</v>
       </c>
       <c r="F190" t="n">
         <v>16793700</v>
@@ -4232,16 +4232,16 @@
         <v>44531</v>
       </c>
       <c r="B191" t="n">
-        <v>11.91672706604004</v>
+        <v>11.91672611236572</v>
       </c>
       <c r="C191" t="n">
-        <v>12.37542982579687</v>
+        <v>12.37542883541339</v>
       </c>
       <c r="D191" t="n">
-        <v>11.81160700007474</v>
+        <v>11.81160605481299</v>
       </c>
       <c r="E191" t="n">
-        <v>12.2989793658374</v>
+        <v>12.29897838157211</v>
       </c>
       <c r="F191" t="n">
         <v>5991300</v>
@@ -4252,16 +4252,16 @@
         <v>44532</v>
       </c>
       <c r="B192" t="n">
-        <v>11.89761257171631</v>
+        <v>11.89761352539062</v>
       </c>
       <c r="C192" t="n">
-        <v>12.14607699253434</v>
+        <v>12.14607796612476</v>
       </c>
       <c r="D192" t="n">
-        <v>11.71604297887929</v>
+        <v>11.71604391799958</v>
       </c>
       <c r="E192" t="n">
-        <v>12.14607699253434</v>
+        <v>12.14607796612476</v>
       </c>
       <c r="F192" t="n">
         <v>7306700</v>
@@ -4272,16 +4272,16 @@
         <v>44533</v>
       </c>
       <c r="B193" t="n">
-        <v>12.70990180969238</v>
+        <v>12.70990085601807</v>
       </c>
       <c r="C193" t="n">
-        <v>12.74812704129032</v>
+        <v>12.74812608474781</v>
       </c>
       <c r="D193" t="n">
-        <v>11.95495280211211</v>
+        <v>11.95495190508461</v>
       </c>
       <c r="E193" t="n">
-        <v>11.99317803371005</v>
+        <v>11.99317713381436</v>
       </c>
       <c r="F193" t="n">
         <v>16852000</v>
@@ -4292,16 +4292,16 @@
         <v>44536</v>
       </c>
       <c r="B194" t="n">
-        <v>13.13993644714355</v>
+        <v>13.13993549346924</v>
       </c>
       <c r="C194" t="n">
-        <v>13.28328084384054</v>
+        <v>13.28327987976253</v>
       </c>
       <c r="D194" t="n">
-        <v>12.77679627596821</v>
+        <v>12.77679534865</v>
       </c>
       <c r="E194" t="n">
-        <v>12.83413458146388</v>
+        <v>12.83413364998414</v>
       </c>
       <c r="F194" t="n">
         <v>6605800</v>
@@ -4312,16 +4312,16 @@
         <v>44537</v>
       </c>
       <c r="B195" t="n">
-        <v>13.42662525177002</v>
+        <v>13.4266242980957</v>
       </c>
       <c r="C195" t="n">
-        <v>13.7610957920937</v>
+        <v>13.76109481466241</v>
       </c>
       <c r="D195" t="n">
-        <v>13.40751218076567</v>
+        <v>13.40751122844893</v>
       </c>
       <c r="E195" t="n">
-        <v>13.56996963885711</v>
+        <v>13.56996867500125</v>
       </c>
       <c r="F195" t="n">
         <v>14090400</v>
@@ -4332,16 +4332,16 @@
         <v>44538</v>
       </c>
       <c r="B196" t="n">
-        <v>13.75153923034668</v>
+        <v>13.751540184021</v>
       </c>
       <c r="C196" t="n">
-        <v>14.02867236148461</v>
+        <v>14.02867333437821</v>
       </c>
       <c r="D196" t="n">
-        <v>13.27372342415291</v>
+        <v>13.27372434469053</v>
       </c>
       <c r="E196" t="n">
-        <v>13.42662433631711</v>
+        <v>13.42662526745845</v>
       </c>
       <c r="F196" t="n">
         <v>14295000</v>
@@ -4352,16 +4352,16 @@
         <v>44539</v>
       </c>
       <c r="B197" t="n">
-        <v>13.58908271789551</v>
+        <v>13.58908176422119</v>
       </c>
       <c r="C197" t="n">
-        <v>13.74198364057517</v>
+        <v>13.74198267617036</v>
       </c>
       <c r="D197" t="n">
-        <v>13.43618179521584</v>
+        <v>13.43618085227203</v>
       </c>
       <c r="E197" t="n">
-        <v>13.74198364057517</v>
+        <v>13.74198267617036</v>
       </c>
       <c r="F197" t="n">
         <v>9843600</v>
@@ -4372,16 +4372,16 @@
         <v>44540</v>
       </c>
       <c r="B198" t="n">
-        <v>13.91399574279785</v>
+        <v>13.91399765014648</v>
       </c>
       <c r="C198" t="n">
-        <v>14.19112885532154</v>
+        <v>14.19113080065994</v>
       </c>
       <c r="D198" t="n">
-        <v>13.74198177248616</v>
+        <v>13.7419836562549</v>
       </c>
       <c r="E198" t="n">
-        <v>13.74198177248616</v>
+        <v>13.7419836562549</v>
       </c>
       <c r="F198" t="n">
         <v>8247400</v>
@@ -4392,16 +4392,16 @@
         <v>44543</v>
       </c>
       <c r="B199" t="n">
-        <v>13.74198150634766</v>
+        <v>13.74198341369629</v>
       </c>
       <c r="C199" t="n">
-        <v>14.12423375368033</v>
+        <v>14.12423571408451</v>
       </c>
       <c r="D199" t="n">
-        <v>13.66553105688112</v>
+        <v>13.66553295361865</v>
       </c>
       <c r="E199" t="n">
-        <v>13.96177632072363</v>
+        <v>13.96177825857917</v>
       </c>
       <c r="F199" t="n">
         <v>11783000</v>
@@ -4412,16 +4412,16 @@
         <v>44544</v>
       </c>
       <c r="B200" t="n">
-        <v>13.76109504699707</v>
+        <v>13.76109409332275</v>
       </c>
       <c r="C200" t="n">
-        <v>14.14334824413447</v>
+        <v>14.14334726396917</v>
       </c>
       <c r="D200" t="n">
-        <v>13.56996890410904</v>
+        <v>13.56996796368018</v>
       </c>
       <c r="E200" t="n">
-        <v>13.88532726771463</v>
+        <v>13.88532630543074</v>
       </c>
       <c r="F200" t="n">
         <v>6761100</v>
@@ -4432,16 +4432,16 @@
         <v>44545</v>
       </c>
       <c r="B201" t="n">
-        <v>14.03822994232178</v>
+        <v>14.03822803497314</v>
       </c>
       <c r="C201" t="n">
-        <v>14.0573430146879</v>
+        <v>14.0573411047424</v>
       </c>
       <c r="D201" t="n">
-        <v>13.73242807535549</v>
+        <v>13.7324262095556</v>
       </c>
       <c r="E201" t="n">
-        <v>13.92355424220942</v>
+        <v>13.92355235044156</v>
       </c>
       <c r="F201" t="n">
         <v>6373000</v>
@@ -4472,16 +4472,16 @@
         <v>44547</v>
       </c>
       <c r="B203" t="n">
-        <v>13.81843280792236</v>
+        <v>13.81843376159668</v>
       </c>
       <c r="C203" t="n">
-        <v>14.00955894337442</v>
+        <v>14.00955991023924</v>
       </c>
       <c r="D203" t="n">
-        <v>13.64641883033486</v>
+        <v>13.6464197721377</v>
       </c>
       <c r="E203" t="n">
-        <v>13.84710150039985</v>
+        <v>13.84710245605272</v>
       </c>
       <c r="F203" t="n">
         <v>8250000</v>
@@ -4492,16 +4492,16 @@
         <v>44550</v>
       </c>
       <c r="B204" t="n">
-        <v>13.47440719604492</v>
+        <v>13.47440624237061</v>
       </c>
       <c r="C204" t="n">
-        <v>13.8662160431998</v>
+        <v>13.86621506179454</v>
       </c>
       <c r="D204" t="n">
-        <v>13.29283666454885</v>
+        <v>13.29283572372549</v>
       </c>
       <c r="E204" t="n">
-        <v>13.81843427641866</v>
+        <v>13.81843329839523</v>
       </c>
       <c r="F204" t="n">
         <v>6680500</v>
@@ -4572,16 +4572,16 @@
         <v>44557</v>
       </c>
       <c r="B208" t="n">
-        <v>13.03481483459473</v>
+        <v>13.03481674194336</v>
       </c>
       <c r="C208" t="n">
-        <v>13.56041146463896</v>
+        <v>13.5604134488967</v>
       </c>
       <c r="D208" t="n">
-        <v>12.9010260878162</v>
+        <v>12.9010279755879</v>
       </c>
       <c r="E208" t="n">
-        <v>13.46484885524968</v>
+        <v>13.46485082552401</v>
       </c>
       <c r="F208" t="n">
         <v>14666400</v>
@@ -4592,16 +4592,16 @@
         <v>44558</v>
       </c>
       <c r="B209" t="n">
-        <v>12.51877498626709</v>
+        <v>12.51877403259277</v>
       </c>
       <c r="C209" t="n">
-        <v>13.12082212409239</v>
+        <v>13.12082112455441</v>
       </c>
       <c r="D209" t="n">
-        <v>12.31809230320487</v>
+        <v>12.31809136481846</v>
       </c>
       <c r="E209" t="n">
-        <v>13.12082212409239</v>
+        <v>13.12082112455441</v>
       </c>
       <c r="F209" t="n">
         <v>22962600</v>
@@ -4632,16 +4632,16 @@
         <v>44560</v>
       </c>
       <c r="B211" t="n">
-        <v>12.38498497009277</v>
+        <v>12.38498592376709</v>
       </c>
       <c r="C211" t="n">
-        <v>12.499660647152</v>
+        <v>12.49966160965662</v>
       </c>
       <c r="D211" t="n">
-        <v>12.25119622450971</v>
+        <v>12.25119716788196</v>
       </c>
       <c r="E211" t="n">
-        <v>12.32764667588253</v>
+        <v>12.32764762514165</v>
       </c>
       <c r="F211" t="n">
         <v>5913100</v>
@@ -4652,16 +4652,16 @@
         <v>44564</v>
       </c>
       <c r="B212" t="n">
-        <v>12.1556339263916</v>
+        <v>12.15563488006592</v>
       </c>
       <c r="C212" t="n">
-        <v>12.49966096635466</v>
+        <v>12.49966194701974</v>
       </c>
       <c r="D212" t="n">
-        <v>11.84983120172981</v>
+        <v>11.84983213141227</v>
       </c>
       <c r="E212" t="n">
-        <v>12.49966096635466</v>
+        <v>12.49966194701974</v>
       </c>
       <c r="F212" t="n">
         <v>16124600</v>
@@ -4672,16 +4672,16 @@
         <v>44565</v>
       </c>
       <c r="B213" t="n">
-        <v>12.1556339263916</v>
+        <v>12.15563488006592</v>
       </c>
       <c r="C213" t="n">
-        <v>12.25119653736736</v>
+        <v>12.25119749853907</v>
       </c>
       <c r="D213" t="n">
-        <v>11.89761296289834</v>
+        <v>11.89761389632953</v>
       </c>
       <c r="E213" t="n">
-        <v>12.20341568756013</v>
+        <v>12.20341664498318</v>
       </c>
       <c r="F213" t="n">
         <v>9389900</v>
@@ -4712,16 +4712,16 @@
         <v>44567</v>
       </c>
       <c r="B215" t="n">
-        <v>11.07577037811279</v>
+        <v>11.07577133178711</v>
       </c>
       <c r="C215" t="n">
-        <v>11.62048009790152</v>
+        <v>11.62048109847782</v>
       </c>
       <c r="D215" t="n">
-        <v>11.02798861589103</v>
+        <v>11.02798956545112</v>
       </c>
       <c r="E215" t="n">
-        <v>11.56314271232445</v>
+        <v>11.56314370796374</v>
       </c>
       <c r="F215" t="n">
         <v>15779400</v>
@@ -4792,16 +4792,16 @@
         <v>44573</v>
       </c>
       <c r="B219" t="n">
-        <v>11.27645301818848</v>
+        <v>11.27645492553711</v>
       </c>
       <c r="C219" t="n">
-        <v>11.28600955287783</v>
+        <v>11.2860114618429</v>
       </c>
       <c r="D219" t="n">
-        <v>10.80819375474579</v>
+        <v>10.808195582891</v>
       </c>
       <c r="E219" t="n">
-        <v>10.94198159495152</v>
+        <v>10.9419834457262</v>
       </c>
       <c r="F219" t="n">
         <v>7862000</v>
@@ -4812,16 +4812,16 @@
         <v>44574</v>
       </c>
       <c r="B220" t="n">
-        <v>11.48669147491455</v>
+        <v>11.48669338226318</v>
       </c>
       <c r="C220" t="n">
-        <v>11.57269754742197</v>
+        <v>11.57269946905179</v>
       </c>
       <c r="D220" t="n">
-        <v>11.15222007350554</v>
+        <v>11.15222192531568</v>
       </c>
       <c r="E220" t="n">
-        <v>11.27645228227571</v>
+        <v>11.27645415471443</v>
       </c>
       <c r="F220" t="n">
         <v>9668300</v>
@@ -4832,16 +4832,16 @@
         <v>44575</v>
       </c>
       <c r="B221" t="n">
-        <v>11.59181118011475</v>
+        <v>11.59181308746338</v>
       </c>
       <c r="C221" t="n">
-        <v>11.65870509911001</v>
+        <v>11.65870701746556</v>
       </c>
       <c r="D221" t="n">
-        <v>11.39112851176765</v>
+        <v>11.3911303860954</v>
       </c>
       <c r="E221" t="n">
-        <v>11.4102406694686</v>
+        <v>11.41024254694112</v>
       </c>
       <c r="F221" t="n">
         <v>7586600</v>
@@ -4872,16 +4872,16 @@
         <v>44579</v>
       </c>
       <c r="B223" t="n">
-        <v>11.39112854003906</v>
+        <v>11.39112949371338</v>
       </c>
       <c r="C223" t="n">
-        <v>11.49624768605842</v>
+        <v>11.49624864853339</v>
       </c>
       <c r="D223" t="n">
-        <v>11.29556501721325</v>
+        <v>11.29556596288691</v>
       </c>
       <c r="E223" t="n">
-        <v>11.47713552831003</v>
+        <v>11.47713648918492</v>
       </c>
       <c r="F223" t="n">
         <v>7771300</v>
@@ -4932,16 +4932,16 @@
         <v>44582</v>
       </c>
       <c r="B226" t="n">
-        <v>11.48669147491455</v>
+        <v>11.48669338226318</v>
       </c>
       <c r="C226" t="n">
-        <v>11.63003584045484</v>
+        <v>11.6300377716056</v>
       </c>
       <c r="D226" t="n">
-        <v>11.21911398924284</v>
+        <v>11.21911585216062</v>
       </c>
       <c r="E226" t="n">
-        <v>11.37201488884882</v>
+        <v>11.37201677715557</v>
       </c>
       <c r="F226" t="n">
         <v>8537100</v>
@@ -4952,16 +4952,16 @@
         <v>44585</v>
       </c>
       <c r="B227" t="n">
-        <v>11.50580501556396</v>
+        <v>11.50580596923828</v>
       </c>
       <c r="C227" t="n">
-        <v>11.63959377449148</v>
+        <v>11.63959473925506</v>
       </c>
       <c r="D227" t="n">
-        <v>11.3242354032836</v>
+        <v>11.32423634190827</v>
       </c>
       <c r="E227" t="n">
-        <v>11.46757978606487</v>
+        <v>11.46758073657084</v>
       </c>
       <c r="F227" t="n">
         <v>6551900</v>
@@ -4992,16 +4992,16 @@
         <v>44587</v>
       </c>
       <c r="B229" t="n">
-        <v>11.73515605926514</v>
+        <v>11.73515701293945</v>
       </c>
       <c r="C229" t="n">
-        <v>12.21297187011393</v>
+        <v>12.21297286261863</v>
       </c>
       <c r="D229" t="n">
-        <v>11.73515605926514</v>
+        <v>11.73515701293945</v>
       </c>
       <c r="E229" t="n">
-        <v>11.81160651609204</v>
+        <v>11.81160747597921</v>
       </c>
       <c r="F229" t="n">
         <v>11052300</v>
@@ -5012,16 +5012,16 @@
         <v>44588</v>
       </c>
       <c r="B230" t="n">
-        <v>11.99317836761475</v>
+        <v>11.99317741394043</v>
       </c>
       <c r="C230" t="n">
-        <v>12.13652276225753</v>
+        <v>12.13652179718475</v>
       </c>
       <c r="D230" t="n">
-        <v>11.66826343430557</v>
+        <v>11.66826250646786</v>
       </c>
       <c r="E230" t="n">
-        <v>11.85938959761643</v>
+        <v>11.85938865458074</v>
       </c>
       <c r="F230" t="n">
         <v>13761300</v>
@@ -5032,16 +5032,16 @@
         <v>44589</v>
       </c>
       <c r="B231" t="n">
-        <v>11.83071994781494</v>
+        <v>11.83071804046631</v>
       </c>
       <c r="C231" t="n">
-        <v>12.04095916619962</v>
+        <v>12.04095722495622</v>
       </c>
       <c r="D231" t="n">
-        <v>11.4580232758641</v>
+        <v>11.45802142860162</v>
       </c>
       <c r="E231" t="n">
-        <v>11.94539563656258</v>
+        <v>11.94539371072593</v>
       </c>
       <c r="F231" t="n">
         <v>14924100</v>
@@ -5052,16 +5052,16 @@
         <v>44592</v>
       </c>
       <c r="B232" t="n">
-        <v>11.97406387329102</v>
+        <v>11.9740629196167</v>
       </c>
       <c r="C232" t="n">
-        <v>12.12696478577772</v>
+        <v>12.12696381992561</v>
       </c>
       <c r="D232" t="n">
-        <v>11.76382557430247</v>
+        <v>11.76382463737258</v>
       </c>
       <c r="E232" t="n">
-        <v>11.81160642593357</v>
+        <v>11.81160548519817</v>
       </c>
       <c r="F232" t="n">
         <v>12073700</v>
@@ -5092,16 +5092,16 @@
         <v>44594</v>
       </c>
       <c r="B234" t="n">
-        <v>11.94539546966553</v>
+        <v>11.94539451599121</v>
       </c>
       <c r="C234" t="n">
-        <v>12.2798669073607</v>
+        <v>12.27986592698347</v>
       </c>
       <c r="D234" t="n">
-        <v>11.81160671231519</v>
+        <v>11.81160576932205</v>
       </c>
       <c r="E234" t="n">
-        <v>12.02184592776248</v>
+        <v>12.02184496798465</v>
       </c>
       <c r="F234" t="n">
         <v>9442200</v>
@@ -5112,16 +5112,16 @@
         <v>44595</v>
       </c>
       <c r="B235" t="n">
-        <v>11.94539546966553</v>
+        <v>11.94539451599121</v>
       </c>
       <c r="C235" t="n">
-        <v>12.21297207300486</v>
+        <v>12.21297109796826</v>
       </c>
       <c r="D235" t="n">
-        <v>11.8976137055146</v>
+        <v>11.89761275565499</v>
       </c>
       <c r="E235" t="n">
-        <v>12.04095899796739</v>
+        <v>12.04095803666365</v>
       </c>
       <c r="F235" t="n">
         <v>8796800</v>
@@ -5132,16 +5132,16 @@
         <v>44596</v>
       </c>
       <c r="B236" t="n">
-        <v>12.3276481628418</v>
+        <v>12.32764720916748</v>
       </c>
       <c r="C236" t="n">
-        <v>12.3276481628418</v>
+        <v>12.32764720916748</v>
       </c>
       <c r="D236" t="n">
-        <v>11.56314355689919</v>
+        <v>11.56314266236741</v>
       </c>
       <c r="E236" t="n">
-        <v>11.91672716498799</v>
+        <v>11.91672624310277</v>
       </c>
       <c r="F236" t="n">
         <v>17676100</v>
@@ -5152,16 +5152,16 @@
         <v>44599</v>
       </c>
       <c r="B237" t="n">
-        <v>12.20341682434082</v>
+        <v>12.2034158706665</v>
       </c>
       <c r="C237" t="n">
-        <v>12.60478128600524</v>
+        <v>12.60478030096504</v>
       </c>
       <c r="D237" t="n">
-        <v>12.20341682434082</v>
+        <v>12.2034158706665</v>
       </c>
       <c r="E237" t="n">
-        <v>12.29897944421849</v>
+        <v>12.29897848307614</v>
       </c>
       <c r="F237" t="n">
         <v>7212000</v>
@@ -5192,16 +5192,16 @@
         <v>44601</v>
       </c>
       <c r="B239" t="n">
-        <v>12.05051422119141</v>
+        <v>12.05051517486572</v>
       </c>
       <c r="C239" t="n">
-        <v>12.28942212264425</v>
+        <v>12.28942309522567</v>
       </c>
       <c r="D239" t="n">
-        <v>11.91672637964906</v>
+        <v>11.91672732273544</v>
       </c>
       <c r="E239" t="n">
-        <v>11.95495160742706</v>
+        <v>11.95495255353858</v>
       </c>
       <c r="F239" t="n">
         <v>9060800</v>
@@ -5212,16 +5212,16 @@
         <v>44602</v>
       </c>
       <c r="B240" t="n">
-        <v>12.11740970611572</v>
+        <v>12.11740875244141</v>
       </c>
       <c r="C240" t="n">
-        <v>12.29897932000246</v>
+        <v>12.29897835203811</v>
       </c>
       <c r="D240" t="n">
-        <v>11.88805741573067</v>
+        <v>11.88805648010703</v>
       </c>
       <c r="E240" t="n">
-        <v>11.95495225146694</v>
+        <v>11.95495131057848</v>
       </c>
       <c r="F240" t="n">
         <v>4310600</v>
@@ -5232,16 +5232,16 @@
         <v>44603</v>
       </c>
       <c r="B241" t="n">
-        <v>11.79249668121338</v>
+        <v>11.79249477386475</v>
       </c>
       <c r="C241" t="n">
-        <v>12.21297427661415</v>
+        <v>12.2129723012564</v>
       </c>
       <c r="D241" t="n">
-        <v>11.74471490844109</v>
+        <v>11.74471300882081</v>
       </c>
       <c r="E241" t="n">
-        <v>12.18430557749539</v>
+        <v>12.18430360677458</v>
       </c>
       <c r="F241" t="n">
         <v>7316000</v>
@@ -5252,16 +5252,16 @@
         <v>44606</v>
       </c>
       <c r="B242" t="n">
-        <v>11.78293800354004</v>
+        <v>11.78293704986572</v>
       </c>
       <c r="C242" t="n">
-        <v>11.97406414854188</v>
+        <v>11.97406317939841</v>
       </c>
       <c r="D242" t="n">
-        <v>11.639593622629</v>
+        <v>11.63959268055653</v>
       </c>
       <c r="E242" t="n">
-        <v>11.79249453863047</v>
+        <v>11.79249358418268</v>
       </c>
       <c r="F242" t="n">
         <v>5445000</v>
@@ -5292,16 +5292,16 @@
         <v>44608</v>
       </c>
       <c r="B244" t="n">
-        <v>12.47099208831787</v>
+        <v>12.47099494934082</v>
       </c>
       <c r="C244" t="n">
-        <v>12.6430051500549</v>
+        <v>12.64300805054009</v>
       </c>
       <c r="D244" t="n">
-        <v>11.56314228509255</v>
+        <v>11.56314493784184</v>
       </c>
       <c r="E244" t="n">
-        <v>11.65870489464395</v>
+        <v>11.65870756931667</v>
       </c>
       <c r="F244" t="n">
         <v>21489000</v>
@@ -5312,16 +5312,16 @@
         <v>44609</v>
       </c>
       <c r="B245" t="n">
-        <v>12.66211891174316</v>
+        <v>12.66211795806885</v>
       </c>
       <c r="C245" t="n">
-        <v>12.94880857880961</v>
+        <v>12.94880760354266</v>
       </c>
       <c r="D245" t="n">
-        <v>12.46143623593278</v>
+        <v>12.46143529737331</v>
       </c>
       <c r="E245" t="n">
-        <v>12.46143623593278</v>
+        <v>12.46143529737331</v>
       </c>
       <c r="F245" t="n">
         <v>10362100</v>
@@ -5352,16 +5352,16 @@
         <v>44613</v>
       </c>
       <c r="B247" t="n">
-        <v>11.90717029571533</v>
+        <v>11.90716934204102</v>
       </c>
       <c r="C247" t="n">
-        <v>12.27986696418357</v>
+        <v>12.27986598065907</v>
       </c>
       <c r="D247" t="n">
-        <v>11.72560068473523</v>
+        <v>11.72559974560327</v>
       </c>
       <c r="E247" t="n">
-        <v>12.13652167106747</v>
+        <v>12.13652069902384</v>
       </c>
       <c r="F247" t="n">
         <v>4718800</v>
@@ -5372,16 +5372,16 @@
         <v>44614</v>
       </c>
       <c r="B248" t="n">
-        <v>12.51877498626709</v>
+        <v>12.51877403259277</v>
       </c>
       <c r="C248" t="n">
-        <v>12.63345067496531</v>
+        <v>12.63344971255505</v>
       </c>
       <c r="D248" t="n">
-        <v>12.08874001444707</v>
+        <v>12.08873909353262</v>
       </c>
       <c r="E248" t="n">
-        <v>12.14607831447686</v>
+        <v>12.1460773891944</v>
       </c>
       <c r="F248" t="n">
         <v>15416600</v>
@@ -5392,16 +5392,16 @@
         <v>44615</v>
       </c>
       <c r="B249" t="n">
-        <v>12.73856830596924</v>
+        <v>12.73856925964355</v>
       </c>
       <c r="C249" t="n">
-        <v>12.87235704914128</v>
+        <v>12.87235801283171</v>
       </c>
       <c r="D249" t="n">
-        <v>12.51877349007365</v>
+        <v>12.51877442729301</v>
       </c>
       <c r="E249" t="n">
-        <v>12.51877349007365</v>
+        <v>12.51877442729301</v>
       </c>
       <c r="F249" t="n">
         <v>5598100</v>
@@ -5412,16 +5412,16 @@
         <v>44616</v>
       </c>
       <c r="B250" t="n">
-        <v>12.93925380706787</v>
+        <v>12.93925285339355</v>
       </c>
       <c r="C250" t="n">
-        <v>13.04437297105954</v>
+        <v>13.04437200963752</v>
       </c>
       <c r="D250" t="n">
-        <v>12.21297346123056</v>
+        <v>12.21297256108599</v>
       </c>
       <c r="E250" t="n">
-        <v>12.41365616438662</v>
+        <v>12.41365524945094</v>
       </c>
       <c r="F250" t="n">
         <v>6603100</v>
@@ -5432,16 +5432,16 @@
         <v>44617</v>
       </c>
       <c r="B251" t="n">
-        <v>12.86280059814453</v>
+        <v>12.86280155181885</v>
       </c>
       <c r="C251" t="n">
-        <v>13.13993370900733</v>
+        <v>13.13993468322886</v>
       </c>
       <c r="D251" t="n">
-        <v>12.72901185410822</v>
+        <v>12.72901279786317</v>
       </c>
       <c r="E251" t="n">
-        <v>12.83413190705149</v>
+        <v>12.83413285860025</v>
       </c>
       <c r="F251" t="n">
         <v>8089600</v>
@@ -5472,16 +5472,16 @@
         <v>44623</v>
       </c>
       <c r="B253" t="n">
-        <v>12.56655502319336</v>
+        <v>12.56655406951904</v>
       </c>
       <c r="C253" t="n">
-        <v>12.95836473998952</v>
+        <v>12.95836375658081</v>
       </c>
       <c r="D253" t="n">
-        <v>12.337203660699</v>
+        <v>12.33720272443013</v>
       </c>
       <c r="E253" t="n">
-        <v>12.80546292029864</v>
+        <v>12.80546194849363</v>
       </c>
       <c r="F253" t="n">
         <v>12631200</v>
@@ -5512,16 +5512,16 @@
         <v>44627</v>
       </c>
       <c r="B255" t="n">
-        <v>11.73515605926514</v>
+        <v>11.73515701293945</v>
       </c>
       <c r="C255" t="n">
-        <v>12.17474664170048</v>
+        <v>12.17474763109875</v>
       </c>
       <c r="D255" t="n">
-        <v>11.68737429590799</v>
+        <v>11.68737524569925</v>
       </c>
       <c r="E255" t="n">
-        <v>12.08873964992988</v>
+        <v>12.08874063233868</v>
       </c>
       <c r="F255" t="n">
         <v>12255900</v>
@@ -5552,16 +5552,16 @@
         <v>44629</v>
       </c>
       <c r="B257" t="n">
-        <v>12.80546283721924</v>
+        <v>12.80546379089355</v>
       </c>
       <c r="C257" t="n">
-        <v>13.0348151095869</v>
+        <v>13.03481608034201</v>
       </c>
       <c r="D257" t="n">
-        <v>11.75426864359272</v>
+        <v>11.75426951898038</v>
       </c>
       <c r="E257" t="n">
-        <v>11.89761301638138</v>
+        <v>11.89761390244447</v>
       </c>
       <c r="F257" t="n">
         <v>14771600</v>
@@ -5612,16 +5612,16 @@
         <v>44634</v>
       </c>
       <c r="B260" t="n">
-        <v>12.51877498626709</v>
+        <v>12.51877403259277</v>
       </c>
       <c r="C260" t="n">
-        <v>12.74812636366353</v>
+        <v>12.74812539251733</v>
       </c>
       <c r="D260" t="n">
-        <v>12.38498622710516</v>
+        <v>12.3849852836228</v>
       </c>
       <c r="E260" t="n">
-        <v>12.43276799190309</v>
+        <v>12.43276704478074</v>
       </c>
       <c r="F260" t="n">
         <v>4274300</v>
@@ -5632,16 +5632,16 @@
         <v>44635</v>
       </c>
       <c r="B261" t="n">
-        <v>12.82457637786865</v>
+        <v>12.82457733154297</v>
       </c>
       <c r="C261" t="n">
-        <v>12.90102683434848</v>
+        <v>12.90102779370788</v>
       </c>
       <c r="D261" t="n">
-        <v>12.29897880604886</v>
+        <v>12.29897972063815</v>
       </c>
       <c r="E261" t="n">
-        <v>12.29897880604886</v>
+        <v>12.29897972063815</v>
       </c>
       <c r="F261" t="n">
         <v>8181800</v>
@@ -5652,16 +5652,16 @@
         <v>44636</v>
       </c>
       <c r="B262" t="n">
-        <v>12.99659061431885</v>
+        <v>12.99659156799316</v>
       </c>
       <c r="C262" t="n">
-        <v>13.09215323110332</v>
+        <v>13.09215419178991</v>
       </c>
       <c r="D262" t="n">
-        <v>12.73856963514194</v>
+        <v>12.73857056988299</v>
       </c>
       <c r="E262" t="n">
-        <v>12.91058362125988</v>
+        <v>12.91058456862311</v>
       </c>
       <c r="F262" t="n">
         <v>7731200</v>
@@ -5692,16 +5692,16 @@
         <v>44638</v>
       </c>
       <c r="B264" t="n">
-        <v>13.58908271789551</v>
+        <v>13.58908176422119</v>
       </c>
       <c r="C264" t="n">
-        <v>13.78020887124509</v>
+        <v>13.78020790415765</v>
       </c>
       <c r="D264" t="n">
-        <v>12.98703465132328</v>
+        <v>12.98703373990036</v>
       </c>
       <c r="E264" t="n">
-        <v>13.04437204164746</v>
+        <v>13.04437112620064</v>
       </c>
       <c r="F264" t="n">
         <v>10366600</v>
@@ -5752,16 +5752,16 @@
         <v>44643</v>
       </c>
       <c r="B267" t="n">
-        <v>14.3822546005249</v>
+        <v>14.38225650787354</v>
       </c>
       <c r="C267" t="n">
-        <v>14.5924937907237</v>
+        <v>14.59249572595387</v>
       </c>
       <c r="D267" t="n">
-        <v>13.87577014861808</v>
+        <v>13.87577198879766</v>
       </c>
       <c r="E267" t="n">
-        <v>14.02867104644948</v>
+        <v>14.0286729069065</v>
       </c>
       <c r="F267" t="n">
         <v>8813400</v>
@@ -5772,16 +5772,16 @@
         <v>44644</v>
       </c>
       <c r="B268" t="n">
-        <v>14.63071918487549</v>
+        <v>14.63072204589844</v>
       </c>
       <c r="C268" t="n">
-        <v>14.7453948595791</v>
+        <v>14.74539774302677</v>
       </c>
       <c r="D268" t="n">
-        <v>14.35358607650145</v>
+        <v>14.35358888333129</v>
       </c>
       <c r="E268" t="n">
-        <v>14.39181130140265</v>
+        <v>14.3918141157074</v>
       </c>
       <c r="F268" t="n">
         <v>7986800</v>
@@ -5792,16 +5792,16 @@
         <v>44645</v>
       </c>
       <c r="B269" t="n">
-        <v>15.13720512390137</v>
+        <v>15.13720607757568</v>
       </c>
       <c r="C269" t="n">
-        <v>15.24232427482575</v>
+        <v>15.24232523512279</v>
       </c>
       <c r="D269" t="n">
-        <v>14.64027624019771</v>
+        <v>14.64027716256451</v>
       </c>
       <c r="E269" t="n">
-        <v>14.71672669748114</v>
+        <v>14.71672762466447</v>
       </c>
       <c r="F269" t="n">
         <v>8426200</v>
@@ -5892,16 +5892,16 @@
         <v>44652</v>
       </c>
       <c r="B274" t="n">
-        <v>15.74880981445312</v>
+        <v>15.74880886077881</v>
       </c>
       <c r="C274" t="n">
-        <v>15.97816120133668</v>
+        <v>15.97816023377391</v>
       </c>
       <c r="D274" t="n">
-        <v>15.47167757215655</v>
+        <v>15.47167663526406</v>
       </c>
       <c r="E274" t="n">
-        <v>15.72014203029443</v>
+        <v>15.7201410783561</v>
       </c>
       <c r="F274" t="n">
         <v>8302400</v>
@@ -6012,16 +6012,16 @@
         <v>44662</v>
       </c>
       <c r="B280" t="n">
-        <v>15.29010581970215</v>
+        <v>15.29010677337646</v>
       </c>
       <c r="C280" t="n">
-        <v>15.49078758367887</v>
+        <v>15.4907885498701</v>
       </c>
       <c r="D280" t="n">
-        <v>15.21365536351254</v>
+        <v>15.21365631241849</v>
       </c>
       <c r="E280" t="n">
-        <v>15.38566934561982</v>
+        <v>15.38567030525462</v>
       </c>
       <c r="F280" t="n">
         <v>10289300</v>
@@ -6032,16 +6032,16 @@
         <v>44663</v>
       </c>
       <c r="B281" t="n">
-        <v>15.72013854980469</v>
+        <v>15.720139503479</v>
       </c>
       <c r="C281" t="n">
-        <v>15.82525677298439</v>
+        <v>15.82525773303578</v>
       </c>
       <c r="D281" t="n">
-        <v>15.39522370130949</v>
+        <v>15.3952246352726</v>
       </c>
       <c r="E281" t="n">
-        <v>15.48123068018895</v>
+        <v>15.48123161936973</v>
       </c>
       <c r="F281" t="n">
         <v>9798400</v>
@@ -6052,16 +6052,16 @@
         <v>44664</v>
       </c>
       <c r="B282" t="n">
-        <v>15.76791954040527</v>
+        <v>15.76792144775391</v>
       </c>
       <c r="C282" t="n">
-        <v>16.02594047942892</v>
+        <v>16.02594241798877</v>
       </c>
       <c r="D282" t="n">
-        <v>15.69146909433039</v>
+        <v>15.69147099243128</v>
       </c>
       <c r="E282" t="n">
-        <v>15.7870326076046</v>
+        <v>15.78703451726522</v>
       </c>
       <c r="F282" t="n">
         <v>7212700</v>
@@ -6072,16 +6072,16 @@
         <v>44665</v>
       </c>
       <c r="B283" t="n">
-        <v>15.64369106292725</v>
+        <v>15.64368915557861</v>
       </c>
       <c r="C283" t="n">
-        <v>15.79659198257972</v>
+        <v>15.79659005658872</v>
       </c>
       <c r="D283" t="n">
-        <v>15.48123360795615</v>
+        <v>15.48123172041506</v>
       </c>
       <c r="E283" t="n">
-        <v>15.72014152275348</v>
+        <v>15.72013960608367</v>
       </c>
       <c r="F283" t="n">
         <v>4607000</v>
@@ -6132,16 +6132,16 @@
         <v>44671</v>
       </c>
       <c r="B286" t="n">
-        <v>15.853928565979</v>
+        <v>15.85393047332764</v>
       </c>
       <c r="C286" t="n">
-        <v>16.33174437128826</v>
+        <v>16.33174633612178</v>
       </c>
       <c r="D286" t="n">
-        <v>15.72014072376366</v>
+        <v>15.72014261501659</v>
       </c>
       <c r="E286" t="n">
-        <v>15.74880850553972</v>
+        <v>15.74881040024161</v>
       </c>
       <c r="F286" t="n">
         <v>12326800</v>
@@ -6172,16 +6172,16 @@
         <v>44676</v>
       </c>
       <c r="B288" t="n">
-        <v>15.29966259002686</v>
+        <v>15.29966163635254</v>
       </c>
       <c r="C288" t="n">
-        <v>15.4621200397703</v>
+        <v>15.46211907596952</v>
       </c>
       <c r="D288" t="n">
-        <v>15.01297291922304</v>
+        <v>15.01297198341896</v>
       </c>
       <c r="E288" t="n">
-        <v>15.28054952000464</v>
+        <v>15.2805485675217</v>
       </c>
       <c r="F288" t="n">
         <v>6454900</v>
@@ -6192,16 +6192,16 @@
         <v>44677</v>
       </c>
       <c r="B289" t="n">
-        <v>15.12764930725098</v>
+        <v>15.12764835357666</v>
       </c>
       <c r="C289" t="n">
-        <v>15.30921983544218</v>
+        <v>15.30921887032133</v>
       </c>
       <c r="D289" t="n">
-        <v>15.02253015133491</v>
+        <v>15.02252920428749</v>
       </c>
       <c r="E289" t="n">
-        <v>15.2136563036193</v>
+        <v>15.21365534452294</v>
       </c>
       <c r="F289" t="n">
         <v>9387600</v>
@@ -6212,16 +6212,16 @@
         <v>44678</v>
       </c>
       <c r="B290" t="n">
-        <v>15.18498802185059</v>
+        <v>15.18498611450195</v>
       </c>
       <c r="C290" t="n">
-        <v>15.48123424947426</v>
+        <v>15.48123230491487</v>
       </c>
       <c r="D290" t="n">
-        <v>14.96519225722114</v>
+        <v>14.9651903774805</v>
       </c>
       <c r="E290" t="n">
-        <v>15.29010718062729</v>
+        <v>15.2901052600749</v>
       </c>
       <c r="F290" t="n">
         <v>7959000</v>
@@ -6232,16 +6232,16 @@
         <v>44679</v>
       </c>
       <c r="B291" t="n">
-        <v>14.84095859527588</v>
+        <v>14.8409595489502</v>
       </c>
       <c r="C291" t="n">
-        <v>15.38566923076207</v>
+        <v>15.38567021943929</v>
       </c>
       <c r="D291" t="n">
-        <v>14.84095859527588</v>
+        <v>14.8409595489502</v>
       </c>
       <c r="E291" t="n">
-        <v>15.32833184472857</v>
+        <v>15.3283328297213</v>
       </c>
       <c r="F291" t="n">
         <v>5384600</v>
@@ -6292,16 +6292,16 @@
         <v>44684</v>
       </c>
       <c r="B294" t="n">
-        <v>14.62423419952393</v>
+        <v>14.62423515319824</v>
       </c>
       <c r="C294" t="n">
-        <v>14.85544716329886</v>
+        <v>14.85544813205102</v>
       </c>
       <c r="D294" t="n">
-        <v>14.4797254080956</v>
+        <v>14.47972635234622</v>
       </c>
       <c r="E294" t="n">
-        <v>14.70130518744891</v>
+        <v>14.70130614614917</v>
       </c>
       <c r="F294" t="n">
         <v>5388000</v>
@@ -6312,16 +6312,16 @@
         <v>44685</v>
       </c>
       <c r="B295" t="n">
-        <v>14.79764270782471</v>
+        <v>14.79764175415039</v>
       </c>
       <c r="C295" t="n">
-        <v>14.95178559456712</v>
+        <v>14.95178463095864</v>
       </c>
       <c r="D295" t="n">
-        <v>14.25814581988137</v>
+        <v>14.2581449009764</v>
       </c>
       <c r="E295" t="n">
-        <v>14.43155507448386</v>
+        <v>14.43155414440306</v>
       </c>
       <c r="F295" t="n">
         <v>5127000</v>
@@ -6332,16 +6332,16 @@
         <v>44686</v>
       </c>
       <c r="B296" t="n">
-        <v>14.47009181976318</v>
+        <v>14.4700927734375</v>
       </c>
       <c r="C296" t="n">
-        <v>14.74947437288235</v>
+        <v>14.74947534496982</v>
       </c>
       <c r="D296" t="n">
-        <v>14.32558303236861</v>
+        <v>14.32558397651884</v>
       </c>
       <c r="E296" t="n">
-        <v>14.54716280553684</v>
+        <v>14.54716376429064</v>
       </c>
       <c r="F296" t="n">
         <v>6151000</v>
@@ -6372,16 +6372,16 @@
         <v>44690</v>
       </c>
       <c r="B298" t="n">
-        <v>14.21961212158203</v>
+        <v>14.21961116790771</v>
       </c>
       <c r="C298" t="n">
-        <v>14.32558450824887</v>
+        <v>14.32558354746724</v>
       </c>
       <c r="D298" t="n">
-        <v>13.92096133187191</v>
+        <v>13.92096039822737</v>
       </c>
       <c r="E298" t="n">
-        <v>14.04620192634656</v>
+        <v>14.04620098430244</v>
       </c>
       <c r="F298" t="n">
         <v>11844800</v>
@@ -6412,16 +6412,16 @@
         <v>44692</v>
       </c>
       <c r="B300" t="n">
-        <v>14.60496711730957</v>
+        <v>14.60496616363525</v>
       </c>
       <c r="C300" t="n">
-        <v>14.78801141678933</v>
+        <v>14.7880104511626</v>
       </c>
       <c r="D300" t="n">
-        <v>14.40265552874489</v>
+        <v>14.4026545882811</v>
       </c>
       <c r="E300" t="n">
-        <v>14.45082512959528</v>
+        <v>14.45082418598612</v>
       </c>
       <c r="F300" t="n">
         <v>6181500</v>
@@ -6472,16 +6472,16 @@
         <v>44697</v>
       </c>
       <c r="B303" t="n">
-        <v>14.80727672576904</v>
+        <v>14.80727767944336</v>
       </c>
       <c r="C303" t="n">
-        <v>14.93251730372877</v>
+        <v>14.9325182654693</v>
       </c>
       <c r="D303" t="n">
-        <v>14.64350065603391</v>
+        <v>14.6435015991601</v>
       </c>
       <c r="E303" t="n">
-        <v>14.93251730372877</v>
+        <v>14.9325182654693</v>
       </c>
       <c r="F303" t="n">
         <v>6824600</v>
@@ -6572,16 +6572,16 @@
         <v>44704</v>
       </c>
       <c r="B308" t="n">
-        <v>15.28897094726562</v>
+        <v>15.28897190093994</v>
       </c>
       <c r="C308" t="n">
-        <v>15.63579037585128</v>
+        <v>15.63579135115902</v>
       </c>
       <c r="D308" t="n">
-        <v>15.17336447107041</v>
+        <v>15.17336541753358</v>
       </c>
       <c r="E308" t="n">
-        <v>15.52981892112058</v>
+        <v>15.52981988981818</v>
       </c>
       <c r="F308" t="n">
         <v>8474400</v>
@@ -6592,16 +6592,16 @@
         <v>44705</v>
       </c>
       <c r="B309" t="n">
-        <v>15.31787204742432</v>
+        <v>15.31787300109863</v>
       </c>
       <c r="C309" t="n">
-        <v>15.3467743549964</v>
+        <v>15.34677531047014</v>
       </c>
       <c r="D309" t="n">
-        <v>14.99995401420009</v>
+        <v>14.99995494808117</v>
       </c>
       <c r="E309" t="n">
-        <v>15.1926323896463</v>
+        <v>15.19263333552333</v>
       </c>
       <c r="F309" t="n">
         <v>5652100</v>
@@ -6612,16 +6612,16 @@
         <v>44706</v>
       </c>
       <c r="B310" t="n">
-        <v>15.14446449279785</v>
+        <v>15.14446353912354</v>
       </c>
       <c r="C310" t="n">
-        <v>15.44311527319793</v>
+        <v>15.44311430071703</v>
       </c>
       <c r="D310" t="n">
-        <v>14.94215291091617</v>
+        <v>14.94215196998178</v>
       </c>
       <c r="E310" t="n">
-        <v>15.16373178124632</v>
+        <v>15.16373082635871</v>
       </c>
       <c r="F310" t="n">
         <v>8129200</v>
@@ -6632,16 +6632,16 @@
         <v>44707</v>
       </c>
       <c r="B311" t="n">
-        <v>15.50091552734375</v>
+        <v>15.50091648101807</v>
       </c>
       <c r="C311" t="n">
-        <v>15.60688881216945</v>
+        <v>15.60688977236364</v>
       </c>
       <c r="D311" t="n">
-        <v>15.0384887361919</v>
+        <v>15.03848966141599</v>
       </c>
       <c r="E311" t="n">
-        <v>15.07702422555801</v>
+        <v>15.07702515315295</v>
       </c>
       <c r="F311" t="n">
         <v>6641000</v>
@@ -6692,16 +6692,16 @@
         <v>44712</v>
       </c>
       <c r="B314" t="n">
-        <v>15.26006984710693</v>
+        <v>15.26007080078125</v>
       </c>
       <c r="C314" t="n">
-        <v>15.39494361251144</v>
+        <v>15.39494457461466</v>
       </c>
       <c r="D314" t="n">
-        <v>15.05775828024155</v>
+        <v>15.05775922127246</v>
       </c>
       <c r="E314" t="n">
-        <v>15.29860533990231</v>
+        <v>15.29860629598489</v>
       </c>
       <c r="F314" t="n">
         <v>5708500</v>
@@ -6772,16 +6772,16 @@
         <v>44718</v>
       </c>
       <c r="B318" t="n">
-        <v>14.90361595153809</v>
+        <v>14.9036169052124</v>
       </c>
       <c r="C318" t="n">
-        <v>15.13482890276379</v>
+        <v>15.1348298712333</v>
       </c>
       <c r="D318" t="n">
-        <v>14.84581225435236</v>
+        <v>14.84581320432785</v>
       </c>
       <c r="E318" t="n">
-        <v>15.01922242715094</v>
+        <v>15.01922338822285</v>
       </c>
       <c r="F318" t="n">
         <v>2626600</v>
@@ -6812,16 +6812,16 @@
         <v>44720</v>
       </c>
       <c r="B320" t="n">
-        <v>15.35640811920166</v>
+        <v>15.35640716552734</v>
       </c>
       <c r="C320" t="n">
-        <v>15.74176396590114</v>
+        <v>15.74176298829518</v>
       </c>
       <c r="D320" t="n">
-        <v>14.99032139703716</v>
+        <v>14.99032046609781</v>
       </c>
       <c r="E320" t="n">
-        <v>15.00958868405489</v>
+        <v>15.00958775191899</v>
       </c>
       <c r="F320" t="n">
         <v>10420600</v>
@@ -6892,16 +6892,16 @@
         <v>44726</v>
       </c>
       <c r="B324" t="n">
-        <v>14.05583477020264</v>
+        <v>14.05583572387695</v>
       </c>
       <c r="C324" t="n">
-        <v>14.2099767438121</v>
+        <v>14.20997770794479</v>
       </c>
       <c r="D324" t="n">
-        <v>13.84388909711031</v>
+        <v>13.84389003640432</v>
       </c>
       <c r="E324" t="n">
-        <v>14.01729927680027</v>
+        <v>14.01730022785999</v>
       </c>
       <c r="F324" t="n">
         <v>10130900</v>
@@ -6952,16 +6952,16 @@
         <v>44732</v>
       </c>
       <c r="B327" t="n">
-        <v>15.31787204742432</v>
+        <v>15.31787300109863</v>
       </c>
       <c r="C327" t="n">
-        <v>15.5009163203465</v>
+        <v>15.50091728541696</v>
       </c>
       <c r="D327" t="n">
-        <v>14.83617794632596</v>
+        <v>14.83617887001052</v>
       </c>
       <c r="E327" t="n">
-        <v>15.09629320192319</v>
+        <v>15.09629414180225</v>
       </c>
       <c r="F327" t="n">
         <v>7611300</v>
@@ -7032,16 +7032,16 @@
         <v>44736</v>
       </c>
       <c r="B331" t="n">
-        <v>14.42192077636719</v>
+        <v>14.4219217300415</v>
       </c>
       <c r="C331" t="n">
-        <v>14.86507935946307</v>
+        <v>14.86508034244202</v>
       </c>
       <c r="D331" t="n">
-        <v>14.2581447183475</v>
+        <v>14.25814566119184</v>
       </c>
       <c r="E331" t="n">
-        <v>14.86507935946307</v>
+        <v>14.86508034244202</v>
       </c>
       <c r="F331" t="n">
         <v>5803600</v>
@@ -7072,16 +7072,16 @@
         <v>44740</v>
       </c>
       <c r="B333" t="n">
-        <v>14.08473587036133</v>
+        <v>14.08473682403564</v>
       </c>
       <c r="C333" t="n">
-        <v>14.48935900212858</v>
+        <v>14.48935998319984</v>
       </c>
       <c r="D333" t="n">
-        <v>13.9691293925362</v>
+        <v>13.96913033838283</v>
       </c>
       <c r="E333" t="n">
-        <v>14.23887784079483</v>
+        <v>14.23887880490607</v>
       </c>
       <c r="F333" t="n">
         <v>7081400</v>
@@ -7092,16 +7092,16 @@
         <v>44741</v>
       </c>
       <c r="B334" t="n">
-        <v>13.85352230072021</v>
+        <v>13.85352325439453</v>
       </c>
       <c r="C334" t="n">
-        <v>14.18107443275354</v>
+        <v>14.1810754089765</v>
       </c>
       <c r="D334" t="n">
-        <v>13.59340704807308</v>
+        <v>13.5934079838411</v>
       </c>
       <c r="E334" t="n">
-        <v>14.18107443275354</v>
+        <v>14.1810754089765</v>
       </c>
       <c r="F334" t="n">
         <v>8408900</v>
@@ -7112,16 +7112,16 @@
         <v>44742</v>
       </c>
       <c r="B335" t="n">
-        <v>13.74755096435547</v>
+        <v>13.74755001068115</v>
       </c>
       <c r="C335" t="n">
-        <v>13.88242473327139</v>
+        <v>13.88242377024082</v>
       </c>
       <c r="D335" t="n">
-        <v>13.34292782009041</v>
+        <v>13.34292689448499</v>
       </c>
       <c r="E335" t="n">
-        <v>13.58377488602158</v>
+        <v>13.58377394370849</v>
       </c>
       <c r="F335" t="n">
         <v>10650900</v>
@@ -7132,16 +7132,16 @@
         <v>44743</v>
       </c>
       <c r="B336" t="n">
-        <v>14.06546974182129</v>
+        <v>14.06546878814697</v>
       </c>
       <c r="C336" t="n">
-        <v>14.28704861287829</v>
+        <v>14.28704764418037</v>
       </c>
       <c r="D336" t="n">
-        <v>13.54524008938454</v>
+        <v>13.54523917098311</v>
       </c>
       <c r="E336" t="n">
-        <v>13.64157836946027</v>
+        <v>13.64157744452686</v>
       </c>
       <c r="F336" t="n">
         <v>10271400</v>
@@ -7152,16 +7152,16 @@
         <v>44746</v>
       </c>
       <c r="B337" t="n">
-        <v>13.87279033660889</v>
+        <v>13.87278938293457</v>
       </c>
       <c r="C337" t="n">
-        <v>14.14253970625061</v>
+        <v>14.14253873403259</v>
       </c>
       <c r="D337" t="n">
-        <v>13.76681796059447</v>
+        <v>13.76681701420514</v>
       </c>
       <c r="E337" t="n">
-        <v>13.95949542551097</v>
+        <v>13.95949446587618</v>
       </c>
       <c r="F337" t="n">
         <v>1980900</v>
@@ -7192,16 +7192,16 @@
         <v>44748</v>
       </c>
       <c r="B339" t="n">
-        <v>14.35448455810547</v>
+        <v>14.35448360443115</v>
       </c>
       <c r="C339" t="n">
-        <v>14.63386711386697</v>
+        <v>14.63386614163121</v>
       </c>
       <c r="D339" t="n">
-        <v>13.9209600293388</v>
+        <v>13.92095910446672</v>
       </c>
       <c r="E339" t="n">
-        <v>13.96912962559257</v>
+        <v>13.96912869752023</v>
       </c>
       <c r="F339" t="n">
         <v>11107300</v>
@@ -7252,16 +7252,16 @@
         <v>44753</v>
       </c>
       <c r="B342" t="n">
-        <v>14.788010597229</v>
+        <v>14.78800964355469</v>
       </c>
       <c r="C342" t="n">
-        <v>14.89398297821984</v>
+        <v>14.8939820177114</v>
       </c>
       <c r="D342" t="n">
-        <v>14.52789531830785</v>
+        <v>14.52789438140829</v>
       </c>
       <c r="E342" t="n">
-        <v>14.57606491648865</v>
+        <v>14.57606397648265</v>
       </c>
       <c r="F342" t="n">
         <v>3654100</v>
@@ -7292,16 +7292,16 @@
         <v>44755</v>
       </c>
       <c r="B344" t="n">
-        <v>14.77837467193604</v>
+        <v>14.77837562561035</v>
       </c>
       <c r="C344" t="n">
-        <v>15.01922171438934</v>
+        <v>15.01922268360593</v>
       </c>
       <c r="D344" t="n">
-        <v>14.44118844499799</v>
+        <v>14.44118937691309</v>
       </c>
       <c r="E344" t="n">
-        <v>14.5856972217251</v>
+        <v>14.58569816296561</v>
       </c>
       <c r="F344" t="n">
         <v>3964800</v>
@@ -7312,16 +7312,16 @@
         <v>44756</v>
       </c>
       <c r="B345" t="n">
-        <v>14.75910758972168</v>
+        <v>14.75910663604736</v>
       </c>
       <c r="C345" t="n">
-        <v>14.99995465048742</v>
+        <v>14.99995368125053</v>
       </c>
       <c r="D345" t="n">
-        <v>14.51826052895594</v>
+        <v>14.5182595908442</v>
       </c>
       <c r="E345" t="n">
-        <v>14.52789463188864</v>
+        <v>14.52789369315438</v>
       </c>
       <c r="F345" t="n">
         <v>8175300</v>
@@ -7372,16 +7372,16 @@
         <v>44761</v>
       </c>
       <c r="B348" t="n">
-        <v>14.92288494110107</v>
+        <v>14.92288398742676</v>
       </c>
       <c r="C348" t="n">
-        <v>15.10592923744614</v>
+        <v>15.10592827207404</v>
       </c>
       <c r="D348" t="n">
-        <v>14.72057335600104</v>
+        <v>14.72057241525581</v>
       </c>
       <c r="E348" t="n">
-        <v>14.91325083734424</v>
+        <v>14.91324988428561</v>
       </c>
       <c r="F348" t="n">
         <v>3342100</v>
@@ -7432,16 +7432,16 @@
         <v>44764</v>
       </c>
       <c r="B351" t="n">
-        <v>15.0770263671875</v>
+        <v>15.07702541351318</v>
       </c>
       <c r="C351" t="n">
-        <v>15.14446417222636</v>
+        <v>15.14446321428636</v>
       </c>
       <c r="D351" t="n">
-        <v>14.78801061526745</v>
+        <v>14.78800967987438</v>
       </c>
       <c r="E351" t="n">
-        <v>14.84581339814799</v>
+        <v>14.8458124590987</v>
       </c>
       <c r="F351" t="n">
         <v>3071000</v>
@@ -7452,16 +7452,16 @@
         <v>44767</v>
       </c>
       <c r="B352" t="n">
-        <v>14.93251705169678</v>
+        <v>14.93251800537109</v>
       </c>
       <c r="C352" t="n">
-        <v>15.4334793550804</v>
+        <v>15.43348034074898</v>
       </c>
       <c r="D352" t="n">
-        <v>14.91324884675499</v>
+        <v>14.91324979919873</v>
       </c>
       <c r="E352" t="n">
-        <v>15.2118995920427</v>
+        <v>15.21190056355995</v>
       </c>
       <c r="F352" t="n">
         <v>6226600</v>
@@ -7472,16 +7472,16 @@
         <v>44768</v>
       </c>
       <c r="B353" t="n">
-        <v>14.95178604125977</v>
+        <v>14.95178508758545</v>
       </c>
       <c r="C353" t="n">
-        <v>15.03849021177204</v>
+        <v>15.03848925256745</v>
       </c>
       <c r="D353" t="n">
-        <v>14.76874175974149</v>
+        <v>14.76874081774235</v>
       </c>
       <c r="E353" t="n">
-        <v>14.82654545884164</v>
+        <v>14.82654451315558</v>
       </c>
       <c r="F353" t="n">
         <v>3874000</v>
@@ -7492,16 +7492,16 @@
         <v>44769</v>
       </c>
       <c r="B354" t="n">
-        <v>15.76103019714355</v>
+        <v>15.76103115081787</v>
       </c>
       <c r="C354" t="n">
-        <v>15.93444035237151</v>
+        <v>15.9344413165386</v>
       </c>
       <c r="D354" t="n">
-        <v>15.03848818994657</v>
+        <v>15.03848909990104</v>
       </c>
       <c r="E354" t="n">
-        <v>15.04812229162779</v>
+        <v>15.04812320216521</v>
       </c>
       <c r="F354" t="n">
         <v>22102600</v>
@@ -7512,16 +7512,16 @@
         <v>44770</v>
       </c>
       <c r="B355" t="n">
-        <v>15.59725666046143</v>
+        <v>15.59725761413574</v>
       </c>
       <c r="C355" t="n">
-        <v>16.13675357904711</v>
+        <v>16.13675456570828</v>
       </c>
       <c r="D355" t="n">
-        <v>15.31787317917409</v>
+        <v>15.31787411576586</v>
       </c>
       <c r="E355" t="n">
-        <v>15.9151747171748</v>
+        <v>15.91517569028781</v>
       </c>
       <c r="F355" t="n">
         <v>25902000</v>
@@ -7552,16 +7552,16 @@
         <v>44774</v>
       </c>
       <c r="B357" t="n">
-        <v>15.05775833129883</v>
+        <v>15.05775928497314</v>
       </c>
       <c r="C357" t="n">
-        <v>15.4045777676332</v>
+        <v>15.40457874327312</v>
       </c>
       <c r="D357" t="n">
-        <v>14.85544676374746</v>
+        <v>14.85544770460849</v>
       </c>
       <c r="E357" t="n">
-        <v>14.96141913960441</v>
+        <v>14.96142008717714</v>
       </c>
       <c r="F357" t="n">
         <v>9649400</v>
@@ -7592,16 +7592,16 @@
         <v>44776</v>
       </c>
       <c r="B359" t="n">
-        <v>15.95370864868164</v>
+        <v>15.95370960235596</v>
       </c>
       <c r="C359" t="n">
-        <v>16.00187916291658</v>
+        <v>16.00188011947041</v>
       </c>
       <c r="D359" t="n">
-        <v>15.06739231820699</v>
+        <v>15.06739321889945</v>
       </c>
       <c r="E359" t="n">
-        <v>15.12519509777168</v>
+        <v>15.12519600191945</v>
       </c>
       <c r="F359" t="n">
         <v>9465300</v>
@@ -7652,16 +7652,16 @@
         <v>44781</v>
       </c>
       <c r="B362" t="n">
-        <v>16.68588256835938</v>
+        <v>16.68588447570801</v>
       </c>
       <c r="C362" t="n">
-        <v>16.88819503663362</v>
+        <v>16.88819696710841</v>
       </c>
       <c r="D362" t="n">
-        <v>16.26199126520336</v>
+        <v>16.26199312409735</v>
       </c>
       <c r="E362" t="n">
-        <v>16.53174061039666</v>
+        <v>16.53174250012546</v>
       </c>
       <c r="F362" t="n">
         <v>10381400</v>
@@ -7692,16 +7692,16 @@
         <v>44783</v>
       </c>
       <c r="B364" t="n">
-        <v>16.89782905578613</v>
+        <v>16.89783096313477</v>
       </c>
       <c r="C364" t="n">
-        <v>17.20611297019896</v>
+        <v>17.20611491234526</v>
       </c>
       <c r="D364" t="n">
-        <v>16.73405299656468</v>
+        <v>16.73405488542704</v>
       </c>
       <c r="E364" t="n">
-        <v>17.16757656213882</v>
+        <v>17.1675784999353</v>
       </c>
       <c r="F364" t="n">
         <v>6533000</v>
@@ -7792,16 +7792,16 @@
         <v>44790</v>
       </c>
       <c r="B369" t="n">
-        <v>17.2735538482666</v>
+        <v>17.27355194091797</v>
       </c>
       <c r="C369" t="n">
-        <v>17.52403504613114</v>
+        <v>17.52403311112434</v>
       </c>
       <c r="D369" t="n">
-        <v>17.1675805390692</v>
+        <v>17.16757864342216</v>
       </c>
       <c r="E369" t="n">
-        <v>17.31208842773634</v>
+        <v>17.31208651613271</v>
       </c>
       <c r="F369" t="n">
         <v>8548600</v>
@@ -7812,16 +7812,16 @@
         <v>44791</v>
       </c>
       <c r="B370" t="n">
-        <v>17.45659446716309</v>
+        <v>17.45659637451172</v>
       </c>
       <c r="C370" t="n">
-        <v>17.59146822309866</v>
+        <v>17.59147014518392</v>
       </c>
       <c r="D370" t="n">
-        <v>17.29281840459113</v>
+        <v>17.2928202940452</v>
       </c>
       <c r="E370" t="n">
-        <v>17.34098707813466</v>
+        <v>17.34098897285176</v>
       </c>
       <c r="F370" t="n">
         <v>13968800</v>
@@ -7872,16 +7872,16 @@
         <v>44796</v>
       </c>
       <c r="B373" t="n">
-        <v>17.20611190795898</v>
+        <v>17.20611381530762</v>
       </c>
       <c r="C373" t="n">
-        <v>17.7937773944593</v>
+        <v>17.7937793669524</v>
       </c>
       <c r="D373" t="n">
-        <v>17.10977273127332</v>
+        <v>17.10977462794247</v>
       </c>
       <c r="E373" t="n">
-        <v>17.49512760049901</v>
+        <v>17.49512953988589</v>
       </c>
       <c r="F373" t="n">
         <v>12142000</v>
@@ -7892,16 +7892,16 @@
         <v>44797</v>
       </c>
       <c r="B374" t="n">
-        <v>17.1483097076416</v>
+        <v>17.14831161499023</v>
       </c>
       <c r="C374" t="n">
-        <v>17.26391710340299</v>
+        <v>17.26391902361024</v>
       </c>
       <c r="D374" t="n">
-        <v>16.99416773830457</v>
+        <v>16.99416962850851</v>
       </c>
       <c r="E374" t="n">
-        <v>17.1483097076416</v>
+        <v>17.14831161499023</v>
       </c>
       <c r="F374" t="n">
         <v>5807100</v>
@@ -7952,16 +7952,16 @@
         <v>44802</v>
       </c>
       <c r="B377" t="n">
-        <v>17.68781089782715</v>
+        <v>17.68780899047852</v>
       </c>
       <c r="C377" t="n">
-        <v>17.98646077526369</v>
+        <v>17.98645883571042</v>
       </c>
       <c r="D377" t="n">
-        <v>17.19648261316334</v>
+        <v>17.19648075879664</v>
       </c>
       <c r="E377" t="n">
-        <v>17.29282181677697</v>
+        <v>17.29281995202162</v>
       </c>
       <c r="F377" t="n">
         <v>7263100</v>
@@ -7972,16 +7972,16 @@
         <v>44803</v>
       </c>
       <c r="B378" t="n">
-        <v>17.6300048828125</v>
+        <v>17.63000297546387</v>
       </c>
       <c r="C378" t="n">
-        <v>17.95755704675698</v>
+        <v>17.95755510397125</v>
       </c>
       <c r="D378" t="n">
-        <v>17.55293389350305</v>
+        <v>17.55293199449255</v>
       </c>
       <c r="E378" t="n">
-        <v>17.68780950293258</v>
+        <v>17.6878075893302</v>
       </c>
       <c r="F378" t="n">
         <v>6440300</v>
@@ -8112,16 +8112,16 @@
         <v>44813</v>
       </c>
       <c r="B385" t="n">
-        <v>18.15987014770508</v>
+        <v>18.15986824035645</v>
       </c>
       <c r="C385" t="n">
-        <v>18.6222960989819</v>
+        <v>18.62229414306423</v>
       </c>
       <c r="D385" t="n">
-        <v>18.08279915582561</v>
+        <v>18.08279725657182</v>
       </c>
       <c r="E385" t="n">
-        <v>18.47778821889757</v>
+        <v>18.47778627815769</v>
       </c>
       <c r="F385" t="n">
         <v>8752700</v>
@@ -8172,16 +8172,16 @@
         <v>44818</v>
       </c>
       <c r="B388" t="n">
-        <v>17.70707321166992</v>
+        <v>17.70707511901855</v>
       </c>
       <c r="C388" t="n">
-        <v>17.87084926903514</v>
+        <v>17.8708511940252</v>
       </c>
       <c r="D388" t="n">
-        <v>17.3698888325507</v>
+        <v>17.36989070357892</v>
       </c>
       <c r="E388" t="n">
-        <v>17.44695981028038</v>
+        <v>17.44696168961044</v>
       </c>
       <c r="F388" t="n">
         <v>7347400</v>
@@ -8212,16 +8212,16 @@
         <v>44820</v>
       </c>
       <c r="B390" t="n">
-        <v>17.24464797973633</v>
+        <v>17.2446460723877</v>
       </c>
       <c r="C390" t="n">
-        <v>17.62037061781912</v>
+        <v>17.62036866891358</v>
       </c>
       <c r="D390" t="n">
-        <v>17.06160371182508</v>
+        <v>17.0616018247221</v>
       </c>
       <c r="E390" t="n">
-        <v>17.49512912595248</v>
+        <v>17.49512719089932</v>
       </c>
       <c r="F390" t="n">
         <v>10140200</v>
@@ -8232,16 +8232,16 @@
         <v>44823</v>
       </c>
       <c r="B391" t="n">
-        <v>17.46623039245605</v>
+        <v>17.46622848510742</v>
       </c>
       <c r="C391" t="n">
-        <v>17.58183780571365</v>
+        <v>17.58183588574045</v>
       </c>
       <c r="D391" t="n">
-        <v>17.14831230289454</v>
+        <v>17.14831043026322</v>
       </c>
       <c r="E391" t="n">
-        <v>17.14831230289454</v>
+        <v>17.14831043026322</v>
       </c>
       <c r="F391" t="n">
         <v>7719100</v>
@@ -8272,16 +8272,16 @@
         <v>44825</v>
       </c>
       <c r="B393" t="n">
-        <v>17.6300048828125</v>
+        <v>17.63000297546387</v>
       </c>
       <c r="C393" t="n">
-        <v>17.95755704675698</v>
+        <v>17.95755510397125</v>
       </c>
       <c r="D393" t="n">
-        <v>17.54329979014971</v>
+        <v>17.54329789218149</v>
       </c>
       <c r="E393" t="n">
-        <v>17.6300048828125</v>
+        <v>17.63000297546387</v>
       </c>
       <c r="F393" t="n">
         <v>11282800</v>
@@ -8472,16 +8472,16 @@
         <v>44839</v>
       </c>
       <c r="B403" t="n">
-        <v>17.45659446716309</v>
+        <v>17.45659637451172</v>
       </c>
       <c r="C403" t="n">
-        <v>17.74561018345848</v>
+        <v>17.74561212238566</v>
       </c>
       <c r="D403" t="n">
-        <v>17.14830870892632</v>
+        <v>17.14831058259092</v>
       </c>
       <c r="E403" t="n">
-        <v>17.4276921605267</v>
+        <v>17.4276940647174</v>
       </c>
       <c r="F403" t="n">
         <v>8852300</v>
@@ -8512,16 +8512,16 @@
         <v>44841</v>
       </c>
       <c r="B405" t="n">
-        <v>17.49513053894043</v>
+        <v>17.4951286315918</v>
       </c>
       <c r="C405" t="n">
-        <v>17.68780892467357</v>
+        <v>17.68780699631881</v>
       </c>
       <c r="D405" t="n">
-        <v>17.32172035928406</v>
+        <v>17.3217184708409</v>
       </c>
       <c r="E405" t="n">
-        <v>17.44696186126578</v>
+        <v>17.44695995916858</v>
       </c>
       <c r="F405" t="n">
         <v>11897600</v>
@@ -8532,16 +8532,16 @@
         <v>44844</v>
       </c>
       <c r="B406" t="n">
-        <v>18.1020679473877</v>
+        <v>18.10206604003906</v>
       </c>
       <c r="C406" t="n">
-        <v>18.12133431784131</v>
+        <v>18.12133240846265</v>
       </c>
       <c r="D406" t="n">
-        <v>17.58183735727369</v>
+        <v>17.58183550473985</v>
       </c>
       <c r="E406" t="n">
-        <v>17.73597934600729</v>
+        <v>17.73597747723208</v>
       </c>
       <c r="F406" t="n">
         <v>7333800</v>
@@ -8612,16 +8612,16 @@
         <v>44851</v>
       </c>
       <c r="B410" t="n">
-        <v>19.01728439331055</v>
+        <v>19.01728248596191</v>
       </c>
       <c r="C410" t="n">
-        <v>19.06545490973637</v>
+        <v>19.06545299755645</v>
       </c>
       <c r="D410" t="n">
-        <v>18.3621800700579</v>
+        <v>18.3621782284133</v>
       </c>
       <c r="E410" t="n">
-        <v>18.49705567853288</v>
+        <v>18.49705382336087</v>
       </c>
       <c r="F410" t="n">
         <v>20683400</v>
@@ -8672,16 +8672,16 @@
         <v>44854</v>
       </c>
       <c r="B413" t="n">
-        <v>17.35062217712402</v>
+        <v>17.35062408447266</v>
       </c>
       <c r="C413" t="n">
-        <v>18.11169792043414</v>
+        <v>18.11169991144759</v>
       </c>
       <c r="D413" t="n">
-        <v>17.19648020790888</v>
+        <v>17.19648209831274</v>
       </c>
       <c r="E413" t="n">
-        <v>17.73597710016188</v>
+        <v>17.73597904987246</v>
       </c>
       <c r="F413" t="n">
         <v>15810900</v>
@@ -8692,16 +8692,16 @@
         <v>44855</v>
       </c>
       <c r="B414" t="n">
-        <v>17.91902160644531</v>
+        <v>17.91902351379395</v>
       </c>
       <c r="C414" t="n">
-        <v>18.25620785747724</v>
+        <v>18.25620980071688</v>
       </c>
       <c r="D414" t="n">
-        <v>17.34098829575019</v>
+        <v>17.34099014157141</v>
       </c>
       <c r="E414" t="n">
-        <v>17.53366667848764</v>
+        <v>17.53366854481807</v>
       </c>
       <c r="F414" t="n">
         <v>27105700</v>
@@ -8732,16 +8732,16 @@
         <v>44859</v>
       </c>
       <c r="B416" t="n">
-        <v>17.04233741760254</v>
+        <v>17.04233932495117</v>
       </c>
       <c r="C416" t="n">
-        <v>18.00572559754023</v>
+        <v>18.00572761270958</v>
       </c>
       <c r="D416" t="n">
-        <v>16.80149037261812</v>
+        <v>16.80149225301157</v>
       </c>
       <c r="E416" t="n">
-        <v>18.00572559754023</v>
+        <v>18.00572761270958</v>
       </c>
       <c r="F416" t="n">
         <v>27810400</v>
@@ -8792,16 +8792,16 @@
         <v>44862</v>
       </c>
       <c r="B419" t="n">
-        <v>18.1213321685791</v>
+        <v>18.12133407592773</v>
       </c>
       <c r="C419" t="n">
-        <v>18.21767135949075</v>
+        <v>18.2176732769795</v>
       </c>
       <c r="D419" t="n">
-        <v>17.27355133109445</v>
+        <v>17.27355314921048</v>
       </c>
       <c r="E419" t="n">
-        <v>17.40842509586043</v>
+        <v>17.40842692817251</v>
       </c>
       <c r="F419" t="n">
         <v>12193800</v>
@@ -8812,16 +8812,16 @@
         <v>44865</v>
       </c>
       <c r="B420" t="n">
-        <v>19.0943546295166</v>
+        <v>19.09435653686523</v>
       </c>
       <c r="C420" t="n">
-        <v>19.24849660096946</v>
+        <v>19.24849852371545</v>
       </c>
       <c r="D420" t="n">
-        <v>18.13096638917758</v>
+        <v>18.13096820029268</v>
       </c>
       <c r="E420" t="n">
-        <v>18.2947424635359</v>
+        <v>18.29474429101071</v>
       </c>
       <c r="F420" t="n">
         <v>18379300</v>
@@ -8852,16 +8852,16 @@
         <v>44868</v>
       </c>
       <c r="B422" t="n">
-        <v>19.62422180175781</v>
+        <v>19.62421989440918</v>
       </c>
       <c r="C422" t="n">
-        <v>19.74946148068863</v>
+        <v>19.74945956116751</v>
       </c>
       <c r="D422" t="n">
-        <v>18.69936801593355</v>
+        <v>18.69936619847478</v>
       </c>
       <c r="E422" t="n">
-        <v>18.69936801593355</v>
+        <v>18.69936619847478</v>
       </c>
       <c r="F422" t="n">
         <v>9732300</v>
@@ -8892,16 +8892,16 @@
         <v>44872</v>
       </c>
       <c r="B424" t="n">
-        <v>19.51824951171875</v>
+        <v>19.51824760437012</v>
       </c>
       <c r="C424" t="n">
-        <v>19.9421409288957</v>
+        <v>19.94213898012385</v>
       </c>
       <c r="D424" t="n">
-        <v>19.14252861781053</v>
+        <v>19.14252674717783</v>
       </c>
       <c r="E424" t="n">
-        <v>19.69165972045103</v>
+        <v>19.69165779615653</v>
       </c>
       <c r="F424" t="n">
         <v>17754600</v>
@@ -8932,16 +8932,16 @@
         <v>44874</v>
       </c>
       <c r="B426" t="n">
-        <v>19.65312004089355</v>
+        <v>19.65311813354492</v>
       </c>
       <c r="C426" t="n">
-        <v>20.09627959384678</v>
+        <v>20.09627764348921</v>
       </c>
       <c r="D426" t="n">
-        <v>19.1328913385332</v>
+        <v>19.13288948167312</v>
       </c>
       <c r="E426" t="n">
-        <v>19.1328913385332</v>
+        <v>19.13288948167312</v>
       </c>
       <c r="F426" t="n">
         <v>19633400</v>
@@ -8972,16 +8972,16 @@
         <v>44876</v>
       </c>
       <c r="B428" t="n">
-        <v>18.64156150817871</v>
+        <v>18.64156341552734</v>
       </c>
       <c r="C428" t="n">
-        <v>18.96911363387929</v>
+        <v>18.96911557474207</v>
       </c>
       <c r="D428" t="n">
-        <v>18.03462593040296</v>
+        <v>18.03462777565176</v>
       </c>
       <c r="E428" t="n">
-        <v>18.88240855133989</v>
+        <v>18.88241048333127</v>
       </c>
       <c r="F428" t="n">
         <v>19344200</v>
@@ -9032,16 +9032,16 @@
         <v>44882</v>
       </c>
       <c r="B431" t="n">
-        <v>18.78606986999512</v>
+        <v>18.78607177734375</v>
       </c>
       <c r="C431" t="n">
-        <v>18.90167726231802</v>
+        <v>18.90167918140427</v>
       </c>
       <c r="D431" t="n">
-        <v>18.05389461866248</v>
+        <v>18.0538964516734</v>
       </c>
       <c r="E431" t="n">
-        <v>18.6608302127027</v>
+        <v>18.66083210733576</v>
       </c>
       <c r="F431" t="n">
         <v>10826800</v>
@@ -9112,16 +9112,16 @@
         <v>44888</v>
       </c>
       <c r="B435" t="n">
-        <v>18.64156150817871</v>
+        <v>18.64156341552734</v>
       </c>
       <c r="C435" t="n">
-        <v>19.14252379895807</v>
+        <v>19.14252575756366</v>
       </c>
       <c r="D435" t="n">
-        <v>18.46815134309992</v>
+        <v>18.46815323270575</v>
       </c>
       <c r="E435" t="n">
-        <v>18.6993642840326</v>
+        <v>18.69936619729544</v>
       </c>
       <c r="F435" t="n">
         <v>10423000</v>
@@ -9192,16 +9192,16 @@
         <v>44894</v>
       </c>
       <c r="B439" t="n">
-        <v>18.68972969055176</v>
+        <v>18.68973159790039</v>
       </c>
       <c r="C439" t="n">
-        <v>18.98837950171693</v>
+        <v>18.98838143954377</v>
       </c>
       <c r="D439" t="n">
-        <v>18.29474069715092</v>
+        <v>18.29474256418963</v>
       </c>
       <c r="E439" t="n">
-        <v>18.53558773398153</v>
+        <v>18.53558962559947</v>
       </c>
       <c r="F439" t="n">
         <v>13403400</v>
@@ -9232,16 +9232,16 @@
         <v>44896</v>
       </c>
       <c r="B441" t="n">
-        <v>18.95948219299316</v>
+        <v>18.95948028564453</v>
       </c>
       <c r="C441" t="n">
-        <v>19.08472186450934</v>
+        <v>19.08471994456143</v>
       </c>
       <c r="D441" t="n">
-        <v>18.41998525508773</v>
+        <v>18.41998340201319</v>
       </c>
       <c r="E441" t="n">
-        <v>19.0750877609285</v>
+        <v>19.0750858419498</v>
       </c>
       <c r="F441" t="n">
         <v>25518700</v>
@@ -9352,16 +9352,16 @@
         <v>44904</v>
       </c>
       <c r="B447" t="n">
-        <v>18.57412528991699</v>
+        <v>18.57412338256836</v>
       </c>
       <c r="C447" t="n">
-        <v>18.7571677262095</v>
+        <v>18.75716580006452</v>
       </c>
       <c r="D447" t="n">
-        <v>18.25620725515131</v>
+        <v>18.2562053804492</v>
       </c>
       <c r="E447" t="n">
-        <v>18.57412528991699</v>
+        <v>18.57412338256836</v>
       </c>
       <c r="F447" t="n">
         <v>14833900</v>
@@ -9452,16 +9452,16 @@
         <v>44911</v>
       </c>
       <c r="B452" t="n">
-        <v>18.02499389648438</v>
+        <v>18.02499580383301</v>
       </c>
       <c r="C452" t="n">
-        <v>18.69936642972459</v>
+        <v>18.69936840843323</v>
       </c>
       <c r="D452" t="n">
-        <v>17.55293385822315</v>
+        <v>17.55293571561986</v>
       </c>
       <c r="E452" t="n">
-        <v>18.38144836977245</v>
+        <v>18.38145031483998</v>
       </c>
       <c r="F452" t="n">
         <v>14090800</v>
@@ -9492,16 +9492,16 @@
         <v>44915</v>
       </c>
       <c r="B454" t="n">
-        <v>19.26776695251465</v>
+        <v>19.26776504516602</v>
       </c>
       <c r="C454" t="n">
-        <v>19.66275602803981</v>
+        <v>19.66275408159054</v>
       </c>
       <c r="D454" t="n">
-        <v>18.86314377301114</v>
+        <v>18.86314190571684</v>
       </c>
       <c r="E454" t="n">
-        <v>18.91131245538545</v>
+        <v>18.91131058332285</v>
       </c>
       <c r="F454" t="n">
         <v>10658900</v>
@@ -9572,16 +9572,16 @@
         <v>44921</v>
       </c>
       <c r="B458" t="n">
-        <v>19.20032691955566</v>
+        <v>19.2003288269043</v>
       </c>
       <c r="C458" t="n">
-        <v>19.32556657574064</v>
+        <v>19.3255684955305</v>
       </c>
       <c r="D458" t="n">
-        <v>18.84387248076942</v>
+        <v>18.84387435270808</v>
       </c>
       <c r="E458" t="n">
-        <v>19.07508542585354</v>
+        <v>19.07508732076077</v>
       </c>
       <c r="F458" t="n">
         <v>2369600</v>
@@ -27509,242 +27509,222 @@
     </row>
     <row r="1355">
       <c r="A1355" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B1355" t="n">
-        <v>8.5</v>
+        <v>8.550000190734863</v>
       </c>
       <c r="C1355" t="n">
-        <v>8.510000228881836</v>
+        <v>8.680000305175781</v>
       </c>
       <c r="D1355" t="n">
-        <v>8.340000152587891</v>
+        <v>8.439999580383301</v>
       </c>
       <c r="E1355" t="n">
-        <v>8.510000228881836</v>
+        <v>8.600000381469727</v>
       </c>
       <c r="F1355" t="n">
-        <v>3774300</v>
+        <v>5991300</v>
       </c>
     </row>
     <row r="1356">
       <c r="A1356" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B1356" t="n">
-        <v>8.550000190734863</v>
+        <v>8.659999847412109</v>
       </c>
       <c r="C1356" t="n">
-        <v>8.680000305175781</v>
+        <v>8.770000457763672</v>
       </c>
       <c r="D1356" t="n">
-        <v>8.439999580383301</v>
+        <v>8.590000152587891</v>
       </c>
       <c r="E1356" t="n">
-        <v>8.600000381469727</v>
+        <v>8.729999542236328</v>
       </c>
       <c r="F1356" t="n">
-        <v>5991300</v>
+        <v>5728800</v>
       </c>
     </row>
     <row r="1357">
       <c r="A1357" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B1357" t="n">
-        <v>8.659999847412109</v>
+        <v>8.829999923706055</v>
       </c>
       <c r="C1357" t="n">
-        <v>8.770000457763672</v>
+        <v>8.909999847412109</v>
       </c>
       <c r="D1357" t="n">
-        <v>8.590000152587891</v>
+        <v>8.670000076293945</v>
       </c>
       <c r="E1357" t="n">
-        <v>8.729999542236328</v>
+        <v>8.710000038146973</v>
       </c>
       <c r="F1357" t="n">
-        <v>5728800</v>
+        <v>8653300</v>
       </c>
     </row>
     <row r="1358">
       <c r="A1358" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B1358" t="n">
-        <v>8.829999923706055</v>
+        <v>8.489999771118164</v>
       </c>
       <c r="C1358" t="n">
-        <v>8.909999847412109</v>
+        <v>8.869999885559082</v>
       </c>
       <c r="D1358" t="n">
-        <v>8.670000076293945</v>
+        <v>8.489999771118164</v>
       </c>
       <c r="E1358" t="n">
-        <v>8.710000038146973</v>
+        <v>8.739999771118164</v>
       </c>
       <c r="F1358" t="n">
-        <v>8653300</v>
+        <v>9598300</v>
       </c>
     </row>
     <row r="1359">
       <c r="A1359" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B1359" t="n">
-        <v>8.489999771118164</v>
+        <v>8.239999771118164</v>
       </c>
       <c r="C1359" t="n">
-        <v>8.869999885559082</v>
+        <v>8.630000114440918</v>
       </c>
       <c r="D1359" t="n">
-        <v>8.489999771118164</v>
+        <v>7.929999828338623</v>
       </c>
       <c r="E1359" t="n">
-        <v>8.739999771118164</v>
+        <v>8.619999885559082</v>
       </c>
       <c r="F1359" t="n">
-        <v>9598300</v>
+        <v>15405900</v>
       </c>
     </row>
     <row r="1360">
       <c r="A1360" s="1" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B1360" t="n">
-        <v>8.239999771118164</v>
+        <v>8.079999923706055</v>
       </c>
       <c r="C1360" t="n">
-        <v>8.630000114440918</v>
+        <v>8.189999580383301</v>
       </c>
       <c r="D1360" t="n">
-        <v>7.929999828338623</v>
+        <v>7.949999809265137</v>
       </c>
       <c r="E1360" t="n">
-        <v>8.619999885559082</v>
+        <v>8.060000419616699</v>
       </c>
       <c r="F1360" t="n">
-        <v>15405900</v>
+        <v>14248700</v>
       </c>
     </row>
     <row r="1361">
       <c r="A1361" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B1361" t="n">
-        <v>8.060000419616699</v>
+        <v>8</v>
       </c>
       <c r="C1361" t="n">
-        <v>8.229999542236328</v>
+        <v>8.199999809265137</v>
       </c>
       <c r="D1361" t="n">
-        <v>7.960000038146973</v>
+        <v>7.949999809265137</v>
       </c>
       <c r="E1361" t="n">
-        <v>8.229999542236328</v>
+        <v>8.119999885559082</v>
       </c>
       <c r="F1361" t="n">
-        <v>10741500</v>
+        <v>8426200</v>
       </c>
     </row>
     <row r="1362">
       <c r="A1362" s="1" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B1362" t="n">
-        <v>8.079999923706055</v>
+        <v>7.960000038146973</v>
       </c>
       <c r="C1362" t="n">
-        <v>8.189999580383301</v>
+        <v>8.210000038146973</v>
       </c>
       <c r="D1362" t="n">
         <v>7.949999809265137</v>
       </c>
       <c r="E1362" t="n">
-        <v>8.060000419616699</v>
+        <v>7.949999809265137</v>
       </c>
       <c r="F1362" t="n">
-        <v>14248700</v>
+        <v>8987000</v>
       </c>
     </row>
     <row r="1363">
       <c r="A1363" s="1" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B1363" t="n">
-        <v>8</v>
+        <v>8.100000381469727</v>
       </c>
       <c r="C1363" t="n">
-        <v>8.199999809265137</v>
+        <v>8.100000381469727</v>
       </c>
       <c r="D1363" t="n">
-        <v>7.949999809265137</v>
+        <v>7.800000190734863</v>
       </c>
       <c r="E1363" t="n">
-        <v>8.119999885559082</v>
+        <v>7.900000095367432</v>
       </c>
       <c r="F1363" t="n">
-        <v>8426200</v>
+        <v>11232000</v>
       </c>
     </row>
     <row r="1364">
       <c r="A1364" s="1" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B1364" t="n">
-        <v>7.960000038146973</v>
+        <v>8.140000343322754</v>
       </c>
       <c r="C1364" t="n">
         <v>8.210000038146973</v>
       </c>
       <c r="D1364" t="n">
-        <v>7.949999809265137</v>
+        <v>8</v>
       </c>
       <c r="E1364" t="n">
-        <v>7.949999809265137</v>
+        <v>8.100000381469727</v>
       </c>
       <c r="F1364" t="n">
-        <v>8987000</v>
+        <v>12268500</v>
       </c>
     </row>
     <row r="1365">
       <c r="A1365" s="1" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="B1365" t="n">
-        <v>8.100000381469727</v>
+        <v>7.9</v>
       </c>
       <c r="C1365" t="n">
-        <v>8.100000381469727</v>
+        <v>8.18</v>
       </c>
       <c r="D1365" t="n">
-        <v>7.800000190734863</v>
+        <v>7.88</v>
       </c>
       <c r="E1365" t="n">
-        <v>7.900000095367432</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="F1365" t="n">
-        <v>11232000</v>
-      </c>
-    </row>
-    <row r="1366">
-      <c r="A1366" s="1" t="n">
-        <v>46251</v>
-      </c>
-      <c r="B1366" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="C1366" t="n">
-        <v>8.210000000000001</v>
-      </c>
-      <c r="D1366" t="n">
-        <v>8</v>
-      </c>
-      <c r="E1366" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="F1366" t="n">
-        <v>12268500</v>
+        <v>11021500</v>
       </c>
     </row>
   </sheetData>

--- a/database/ASAI3.xlsx
+++ b/database/ASAI3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1368"/>
+  <dimension ref="A1:F1367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44256</v>
       </c>
       <c r="B2" t="n">
-        <v>13.55914878845215</v>
+        <v>13.55914783477783</v>
       </c>
       <c r="C2" t="n">
-        <v>14.43840509670459</v>
+        <v>14.43840408118833</v>
       </c>
       <c r="D2" t="n">
-        <v>13.17554324856868</v>
+        <v>13.17554232187502</v>
       </c>
       <c r="E2" t="n">
-        <v>13.67499091708668</v>
+        <v>13.67498995526467</v>
       </c>
       <c r="F2" t="n">
         <v>64088000</v>
@@ -532,16 +532,16 @@
         <v>44260</v>
       </c>
       <c r="B6" t="n">
-        <v>14.24280261993408</v>
+        <v>14.2428035736084</v>
       </c>
       <c r="C6" t="n">
-        <v>14.90746656109107</v>
+        <v>14.90746755927018</v>
       </c>
       <c r="D6" t="n">
-        <v>13.67309015292352</v>
+        <v>13.67309106845084</v>
       </c>
       <c r="E6" t="n">
-        <v>13.76994143531125</v>
+        <v>13.76994235732357</v>
       </c>
       <c r="F6" t="n">
         <v>18499500</v>
@@ -572,16 +572,16 @@
         <v>44264</v>
       </c>
       <c r="B8" t="n">
-        <v>13.4452075958252</v>
+        <v>13.44520568847656</v>
       </c>
       <c r="C8" t="n">
-        <v>13.4452075958252</v>
+        <v>13.44520568847656</v>
       </c>
       <c r="D8" t="n">
-        <v>13.01032711509522</v>
+        <v>13.0103252694391</v>
       </c>
       <c r="E8" t="n">
-        <v>13.29138558640273</v>
+        <v>13.29138370087542</v>
       </c>
       <c r="F8" t="n">
         <v>10167000</v>
@@ -592,16 +592,16 @@
         <v>44265</v>
       </c>
       <c r="B9" t="n">
-        <v>13.48318672180176</v>
+        <v>13.48318767547607</v>
       </c>
       <c r="C9" t="n">
-        <v>13.95794682401684</v>
+        <v>13.95794781127124</v>
       </c>
       <c r="D9" t="n">
-        <v>13.23631125132199</v>
+        <v>13.23631218753465</v>
       </c>
       <c r="E9" t="n">
-        <v>13.4850856245696</v>
+        <v>13.48508657837822</v>
       </c>
       <c r="F9" t="n">
         <v>15699500</v>
@@ -612,16 +612,16 @@
         <v>44266</v>
       </c>
       <c r="B10" t="n">
-        <v>13.9560489654541</v>
+        <v>13.95604705810547</v>
       </c>
       <c r="C10" t="n">
-        <v>14.15544825952501</v>
+        <v>14.15544632492482</v>
       </c>
       <c r="D10" t="n">
-        <v>13.6351108298175</v>
+        <v>13.63510896633091</v>
       </c>
       <c r="E10" t="n">
-        <v>13.7129721878558</v>
+        <v>13.71297031372804</v>
       </c>
       <c r="F10" t="n">
         <v>16646000</v>
@@ -632,16 +632,16 @@
         <v>44267</v>
       </c>
       <c r="B11" t="n">
-        <v>13.82121658325195</v>
+        <v>13.82121562957764</v>
       </c>
       <c r="C11" t="n">
-        <v>14.06049554958161</v>
+        <v>14.06049457939686</v>
       </c>
       <c r="D11" t="n">
-        <v>13.57813981118895</v>
+        <v>13.57813887428711</v>
       </c>
       <c r="E11" t="n">
-        <v>13.57813981118895</v>
+        <v>13.57813887428711</v>
       </c>
       <c r="F11" t="n">
         <v>7509000</v>
@@ -692,16 +692,16 @@
         <v>44272</v>
       </c>
       <c r="B14" t="n">
-        <v>14.05290031433105</v>
+        <v>14.05289840698242</v>
       </c>
       <c r="C14" t="n">
-        <v>14.07189024903928</v>
+        <v>14.07188833911321</v>
       </c>
       <c r="D14" t="n">
-        <v>13.49458210759284</v>
+        <v>13.49458027602269</v>
       </c>
       <c r="E14" t="n">
-        <v>13.58763559481576</v>
+        <v>13.5876337506158</v>
       </c>
       <c r="F14" t="n">
         <v>4753000</v>
@@ -732,16 +732,16 @@
         <v>44274</v>
       </c>
       <c r="B16" t="n">
-        <v>13.54775428771973</v>
+        <v>13.54775333404541</v>
       </c>
       <c r="C16" t="n">
-        <v>14.03580762724047</v>
+        <v>14.03580663921036</v>
       </c>
       <c r="D16" t="n">
-        <v>13.46419713061404</v>
+        <v>13.46419618282161</v>
       </c>
       <c r="E16" t="n">
-        <v>13.95414937295086</v>
+        <v>13.95414839066896</v>
       </c>
       <c r="F16" t="n">
         <v>14098000</v>
@@ -752,16 +752,16 @@
         <v>44277</v>
       </c>
       <c r="B17" t="n">
-        <v>13.29328441619873</v>
+        <v>13.29328346252441</v>
       </c>
       <c r="C17" t="n">
-        <v>13.6351114037662</v>
+        <v>13.63511042556885</v>
       </c>
       <c r="D17" t="n">
-        <v>13.15655344006512</v>
+        <v>13.15655249620002</v>
       </c>
       <c r="E17" t="n">
-        <v>13.6351114037662</v>
+        <v>13.63511042556885</v>
       </c>
       <c r="F17" t="n">
         <v>5803000</v>
@@ -812,16 +812,16 @@
         <v>44280</v>
       </c>
       <c r="B20" t="n">
-        <v>13.64840412139893</v>
+        <v>13.64840316772461</v>
       </c>
       <c r="C20" t="n">
-        <v>13.67309167041285</v>
+        <v>13.67309071501351</v>
       </c>
       <c r="D20" t="n">
-        <v>12.83941352376278</v>
+        <v>12.83941262661621</v>
       </c>
       <c r="E20" t="n">
-        <v>12.91347617080455</v>
+        <v>12.9134752684829</v>
       </c>
       <c r="F20" t="n">
         <v>6602000</v>
@@ -832,16 +832,16 @@
         <v>44281</v>
       </c>
       <c r="B21" t="n">
-        <v>13.80602264404297</v>
+        <v>13.8060245513916</v>
       </c>
       <c r="C21" t="n">
-        <v>14.12696073027828</v>
+        <v>14.1269626819656</v>
       </c>
       <c r="D21" t="n">
-        <v>13.48888326857586</v>
+        <v>13.48888513211062</v>
       </c>
       <c r="E21" t="n">
-        <v>13.54965268000461</v>
+        <v>13.54965455193487</v>
       </c>
       <c r="F21" t="n">
         <v>4396500</v>
@@ -912,16 +912,16 @@
         <v>44287</v>
       </c>
       <c r="B25" t="n">
-        <v>14.25419616699219</v>
+        <v>14.25419807434082</v>
       </c>
       <c r="C25" t="n">
-        <v>14.40232143658555</v>
+        <v>14.40232336375477</v>
       </c>
       <c r="D25" t="n">
-        <v>14.02631155478684</v>
+        <v>14.02631343164232</v>
       </c>
       <c r="E25" t="n">
-        <v>14.09087877102506</v>
+        <v>14.09088065652025</v>
       </c>
       <c r="F25" t="n">
         <v>9940000</v>
@@ -932,16 +932,16 @@
         <v>44291</v>
       </c>
       <c r="B26" t="n">
-        <v>14.71756362915039</v>
+        <v>14.71756267547607</v>
       </c>
       <c r="C26" t="n">
-        <v>14.88657865823869</v>
+        <v>14.88657769361247</v>
       </c>
       <c r="D26" t="n">
-        <v>14.29977512456389</v>
+        <v>14.2997741979616</v>
       </c>
       <c r="E26" t="n">
-        <v>14.29977512456389</v>
+        <v>14.2997741979616</v>
       </c>
       <c r="F26" t="n">
         <v>6073500</v>
@@ -952,16 +952,16 @@
         <v>44292</v>
       </c>
       <c r="B27" t="n">
-        <v>14.58653163909912</v>
+        <v>14.58652973175049</v>
       </c>
       <c r="C27" t="n">
-        <v>14.72136280773917</v>
+        <v>14.72136088275989</v>
       </c>
       <c r="D27" t="n">
-        <v>14.52766111829865</v>
+        <v>14.52765921864798</v>
       </c>
       <c r="E27" t="n">
-        <v>14.71756500173048</v>
+        <v>14.7175630772478</v>
       </c>
       <c r="F27" t="n">
         <v>5821500</v>
@@ -972,16 +972,16 @@
         <v>44293</v>
       </c>
       <c r="B28" t="n">
-        <v>14.4934778213501</v>
+        <v>14.49347686767578</v>
       </c>
       <c r="C28" t="n">
-        <v>14.78023299581345</v>
+        <v>14.78023202327058</v>
       </c>
       <c r="D28" t="n">
-        <v>13.92756398980291</v>
+        <v>13.92756307336586</v>
       </c>
       <c r="E28" t="n">
-        <v>14.45359814255714</v>
+        <v>14.45359719150692</v>
       </c>
       <c r="F28" t="n">
         <v>10992000</v>
@@ -1012,16 +1012,16 @@
         <v>44295</v>
       </c>
       <c r="B30" t="n">
-        <v>14.71756362915039</v>
+        <v>14.71756267547607</v>
       </c>
       <c r="C30" t="n">
-        <v>14.73655446848903</v>
+        <v>14.73655351358414</v>
       </c>
       <c r="D30" t="n">
-        <v>14.40801982998176</v>
+        <v>14.40801889636538</v>
       </c>
       <c r="E30" t="n">
-        <v>14.63210666319261</v>
+        <v>14.63210571505577</v>
       </c>
       <c r="F30" t="n">
         <v>7012500</v>
@@ -1052,16 +1052,16 @@
         <v>44299</v>
       </c>
       <c r="B32" t="n">
-        <v>14.67008686065674</v>
+        <v>14.67008781433105</v>
       </c>
       <c r="C32" t="n">
-        <v>14.81251543350823</v>
+        <v>14.81251639644156</v>
       </c>
       <c r="D32" t="n">
-        <v>14.52765919333826</v>
+        <v>14.52766013775363</v>
       </c>
       <c r="E32" t="n">
-        <v>14.69667331026109</v>
+        <v>14.69667426566374</v>
       </c>
       <c r="F32" t="n">
         <v>5449500</v>
@@ -1072,16 +1072,16 @@
         <v>44300</v>
       </c>
       <c r="B33" t="n">
-        <v>14.93785285949707</v>
+        <v>14.93785190582275</v>
       </c>
       <c r="C33" t="n">
-        <v>14.9454484709092</v>
+        <v>14.94544751674995</v>
       </c>
       <c r="D33" t="n">
-        <v>14.62261144203403</v>
+        <v>14.62261050848561</v>
       </c>
       <c r="E33" t="n">
-        <v>14.65109770142871</v>
+        <v>14.65109676606165</v>
       </c>
       <c r="F33" t="n">
         <v>5841000</v>
@@ -1172,16 +1172,16 @@
         <v>44308</v>
       </c>
       <c r="B38" t="n">
-        <v>15.27967929840088</v>
+        <v>15.27967834472656</v>
       </c>
       <c r="C38" t="n">
-        <v>15.75254143640172</v>
+        <v>15.75254045321392</v>
       </c>
       <c r="D38" t="n">
-        <v>15.1942241402155</v>
+        <v>15.19422319187483</v>
       </c>
       <c r="E38" t="n">
-        <v>15.50376614024878</v>
+        <v>15.50376517258819</v>
       </c>
       <c r="F38" t="n">
         <v>8470500</v>
@@ -1192,16 +1192,16 @@
         <v>44309</v>
       </c>
       <c r="B39" t="n">
-        <v>15.41261291503906</v>
+        <v>15.41261386871338</v>
       </c>
       <c r="C39" t="n">
-        <v>15.53794955811708</v>
+        <v>15.53795051954675</v>
       </c>
       <c r="D39" t="n">
-        <v>15.218910336355</v>
+        <v>15.21891127804373</v>
       </c>
       <c r="E39" t="n">
-        <v>15.45819020544309</v>
+        <v>15.45819116193756</v>
       </c>
       <c r="F39" t="n">
         <v>4653000</v>
@@ -1232,16 +1232,16 @@
         <v>44313</v>
       </c>
       <c r="B41" t="n">
-        <v>15.12775611877441</v>
+        <v>15.1277551651001</v>
       </c>
       <c r="C41" t="n">
-        <v>15.29677114335289</v>
+        <v>15.29677017902364</v>
       </c>
       <c r="D41" t="n">
-        <v>15.10116966883617</v>
+        <v>15.1011687168379</v>
       </c>
       <c r="E41" t="n">
-        <v>15.24929404627311</v>
+        <v>15.24929308493688</v>
       </c>
       <c r="F41" t="n">
         <v>4986500</v>
@@ -1252,16 +1252,16 @@
         <v>44314</v>
       </c>
       <c r="B42" t="n">
-        <v>15.18852710723877</v>
+        <v>15.18852615356445</v>
       </c>
       <c r="C42" t="n">
-        <v>15.35564324633648</v>
+        <v>15.35564228216909</v>
       </c>
       <c r="D42" t="n">
-        <v>15.04799742083089</v>
+        <v>15.04799647598031</v>
       </c>
       <c r="E42" t="n">
-        <v>15.14864742820402</v>
+        <v>15.14864647703371</v>
       </c>
       <c r="F42" t="n">
         <v>5371500</v>
@@ -1272,16 +1272,16 @@
         <v>44315</v>
       </c>
       <c r="B43" t="n">
-        <v>15.21646404266357</v>
+        <v>15.21646595001221</v>
       </c>
       <c r="C43" t="n">
-        <v>15.32323240215915</v>
+        <v>15.32323432289095</v>
       </c>
       <c r="D43" t="n">
-        <v>14.90950409998268</v>
+        <v>14.90950596885459</v>
       </c>
       <c r="E43" t="n">
-        <v>15.26222243052232</v>
+        <v>15.26222434360666</v>
       </c>
       <c r="F43" t="n">
         <v>5343000</v>
@@ -1312,16 +1312,16 @@
         <v>44319</v>
       </c>
       <c r="B45" t="n">
-        <v>15.532958984375</v>
+        <v>15.53295803070068</v>
       </c>
       <c r="C45" t="n">
-        <v>15.6702323380043</v>
+        <v>15.67023137590184</v>
       </c>
       <c r="D45" t="n">
-        <v>15.29463569991469</v>
+        <v>15.29463476087267</v>
       </c>
       <c r="E45" t="n">
-        <v>15.44334956033281</v>
+        <v>15.44334861216023</v>
       </c>
       <c r="F45" t="n">
         <v>8474000</v>
@@ -1332,16 +1332,16 @@
         <v>44320</v>
       </c>
       <c r="B46" t="n">
-        <v>15.72933673858643</v>
+        <v>15.72933578491211</v>
       </c>
       <c r="C46" t="n">
-        <v>15.74840303768283</v>
+        <v>15.74840208285252</v>
       </c>
       <c r="D46" t="n">
-        <v>15.35945853647056</v>
+        <v>15.35945760522207</v>
       </c>
       <c r="E46" t="n">
-        <v>15.63400706136676</v>
+        <v>15.63400611347231</v>
       </c>
       <c r="F46" t="n">
         <v>9407500</v>
@@ -1392,16 +1392,16 @@
         <v>44323</v>
       </c>
       <c r="B49" t="n">
-        <v>16.96289825439453</v>
+        <v>16.96290016174316</v>
       </c>
       <c r="C49" t="n">
-        <v>17.0448800657126</v>
+        <v>17.04488198227947</v>
       </c>
       <c r="D49" t="n">
-        <v>16.42905280179942</v>
+        <v>16.4290546491212</v>
       </c>
       <c r="E49" t="n">
-        <v>16.66356318404632</v>
+        <v>16.663565057737</v>
       </c>
       <c r="F49" t="n">
         <v>8422500</v>
@@ -1412,16 +1412,16 @@
         <v>44326</v>
       </c>
       <c r="B50" t="n">
-        <v>16.81418609619141</v>
+        <v>16.81418418884277</v>
       </c>
       <c r="C50" t="n">
-        <v>17.0162841548014</v>
+        <v>17.01628222452739</v>
       </c>
       <c r="D50" t="n">
-        <v>16.55298359675715</v>
+        <v>16.55298171903851</v>
       </c>
       <c r="E50" t="n">
-        <v>16.97052576072697</v>
+        <v>16.97052383564365</v>
       </c>
       <c r="F50" t="n">
         <v>7669500</v>
@@ -1452,16 +1452,16 @@
         <v>44328</v>
       </c>
       <c r="B52" t="n">
-        <v>16.12590599060059</v>
+        <v>16.12590408325195</v>
       </c>
       <c r="C52" t="n">
-        <v>16.57776597677424</v>
+        <v>16.57776401598027</v>
       </c>
       <c r="D52" t="n">
-        <v>16.04201500729966</v>
+        <v>16.04201310987353</v>
       </c>
       <c r="E52" t="n">
-        <v>16.49006391581501</v>
+        <v>16.49006196539431</v>
       </c>
       <c r="F52" t="n">
         <v>6728500</v>
@@ -1532,16 +1532,16 @@
         <v>44334</v>
       </c>
       <c r="B56" t="n">
-        <v>16.06108283996582</v>
+        <v>16.06108093261719</v>
       </c>
       <c r="C56" t="n">
-        <v>16.39092291515271</v>
+        <v>16.39092096863362</v>
       </c>
       <c r="D56" t="n">
-        <v>15.88758424029694</v>
+        <v>15.88758235355229</v>
       </c>
       <c r="E56" t="n">
-        <v>16.34897741949393</v>
+        <v>16.34897547795611</v>
       </c>
       <c r="F56" t="n">
         <v>6527500</v>
@@ -1552,16 +1552,16 @@
         <v>44335</v>
       </c>
       <c r="B57" t="n">
-        <v>15.8284797668457</v>
+        <v>15.82848072052002</v>
       </c>
       <c r="C57" t="n">
-        <v>16.36804368259568</v>
+        <v>16.36804466877901</v>
       </c>
       <c r="D57" t="n">
-        <v>15.67595300621593</v>
+        <v>15.67595395070043</v>
       </c>
       <c r="E57" t="n">
-        <v>15.98481942375186</v>
+        <v>15.98482038684572</v>
       </c>
       <c r="F57" t="n">
         <v>6358000</v>
@@ -1572,16 +1572,16 @@
         <v>44336</v>
       </c>
       <c r="B58" t="n">
-        <v>16.03248596191406</v>
+        <v>16.0324821472168</v>
       </c>
       <c r="C58" t="n">
-        <v>16.03248596191406</v>
+        <v>16.0324821472168</v>
       </c>
       <c r="D58" t="n">
-        <v>15.69692561740377</v>
+        <v>15.69692188254822</v>
       </c>
       <c r="E58" t="n">
-        <v>15.90283657256179</v>
+        <v>15.90283278871271</v>
       </c>
       <c r="F58" t="n">
         <v>7278000</v>
@@ -1592,16 +1592,16 @@
         <v>44337</v>
       </c>
       <c r="B59" t="n">
-        <v>16.43477439880371</v>
+        <v>16.43477249145508</v>
       </c>
       <c r="C59" t="n">
-        <v>16.6254337643569</v>
+        <v>16.62543183488117</v>
       </c>
       <c r="D59" t="n">
-        <v>15.75984264485187</v>
+        <v>15.75984081583289</v>
       </c>
       <c r="E59" t="n">
-        <v>16.03439118575198</v>
+        <v>16.03438932487009</v>
       </c>
       <c r="F59" t="n">
         <v>10145000</v>
@@ -1612,16 +1612,16 @@
         <v>44340</v>
       </c>
       <c r="B60" t="n">
-        <v>17.00865364074707</v>
+        <v>17.0086555480957</v>
       </c>
       <c r="C60" t="n">
-        <v>17.06203963689752</v>
+        <v>17.06204155023285</v>
       </c>
       <c r="D60" t="n">
-        <v>16.39664113380684</v>
+        <v>16.39664297252445</v>
       </c>
       <c r="E60" t="n">
-        <v>16.5415402659626</v>
+        <v>16.54154212092919</v>
       </c>
       <c r="F60" t="n">
         <v>10386000</v>
@@ -1632,16 +1632,16 @@
         <v>44341</v>
       </c>
       <c r="B61" t="n">
-        <v>16.88472938537598</v>
+        <v>16.88472747802734</v>
       </c>
       <c r="C61" t="n">
-        <v>17.06394824863613</v>
+        <v>17.06394632104241</v>
       </c>
       <c r="D61" t="n">
-        <v>16.77986654948997</v>
+        <v>16.77986465398696</v>
       </c>
       <c r="E61" t="n">
-        <v>17.01628431501296</v>
+        <v>17.0162823928035</v>
       </c>
       <c r="F61" t="n">
         <v>5307000</v>
@@ -1652,16 +1652,16 @@
         <v>44342</v>
       </c>
       <c r="B62" t="n">
-        <v>16.94192504882812</v>
+        <v>16.94192314147949</v>
       </c>
       <c r="C62" t="n">
-        <v>17.11161256574568</v>
+        <v>17.11161063929336</v>
       </c>
       <c r="D62" t="n">
-        <v>16.65975073072218</v>
+        <v>16.65974885514118</v>
       </c>
       <c r="E62" t="n">
-        <v>17.02390868058733</v>
+        <v>17.02390676400885</v>
       </c>
       <c r="F62" t="n">
         <v>5462000</v>
@@ -1692,16 +1692,16 @@
         <v>44344</v>
       </c>
       <c r="B64" t="n">
-        <v>16.98577499389648</v>
+        <v>16.98577880859375</v>
       </c>
       <c r="C64" t="n">
-        <v>17.14974041109441</v>
+        <v>17.14974426261534</v>
       </c>
       <c r="D64" t="n">
-        <v>16.564418218668</v>
+        <v>16.56442193873616</v>
       </c>
       <c r="E64" t="n">
-        <v>16.91141716721885</v>
+        <v>16.91142096521669</v>
       </c>
       <c r="F64" t="n">
         <v>4590500</v>
@@ -1712,16 +1712,16 @@
         <v>44347</v>
       </c>
       <c r="B65" t="n">
-        <v>17.05441093444824</v>
+        <v>17.05441284179688</v>
       </c>
       <c r="C65" t="n">
-        <v>17.2546034069664</v>
+        <v>17.25460533670436</v>
       </c>
       <c r="D65" t="n">
-        <v>16.87137921937667</v>
+        <v>16.87138110625522</v>
       </c>
       <c r="E65" t="n">
-        <v>17.09254352664678</v>
+        <v>17.09254543826012</v>
       </c>
       <c r="F65" t="n">
         <v>4641000</v>
@@ -1732,16 +1732,16 @@
         <v>44348</v>
       </c>
       <c r="B66" t="n">
-        <v>16.96861839294434</v>
+        <v>16.9686164855957</v>
       </c>
       <c r="C66" t="n">
-        <v>17.41094711104222</v>
+        <v>17.41094515397386</v>
       </c>
       <c r="D66" t="n">
-        <v>16.82562477524642</v>
+        <v>16.82562288397091</v>
       </c>
       <c r="E66" t="n">
-        <v>17.17834406261295</v>
+        <v>17.17834213169021</v>
       </c>
       <c r="F66" t="n">
         <v>13722000</v>
@@ -1752,16 +1752,16 @@
         <v>44349</v>
       </c>
       <c r="B67" t="n">
-        <v>16.76651954650879</v>
+        <v>16.76651763916016</v>
       </c>
       <c r="C67" t="n">
-        <v>17.26032688926774</v>
+        <v>17.26032492574389</v>
       </c>
       <c r="D67" t="n">
-        <v>16.73982745427992</v>
+        <v>16.73982554996776</v>
       </c>
       <c r="E67" t="n">
-        <v>17.06394727556971</v>
+        <v>17.06394533438589</v>
       </c>
       <c r="F67" t="n">
         <v>9352500</v>
@@ -1772,16 +1772,16 @@
         <v>44351</v>
       </c>
       <c r="B68" t="n">
-        <v>16.77224159240723</v>
+        <v>16.77223777770996</v>
       </c>
       <c r="C68" t="n">
-        <v>16.81609263171755</v>
+        <v>16.81608880704675</v>
       </c>
       <c r="D68" t="n">
-        <v>16.40617623638331</v>
+        <v>16.40617250494436</v>
       </c>
       <c r="E68" t="n">
-        <v>16.72267029893303</v>
+        <v>16.72266649551031</v>
       </c>
       <c r="F68" t="n">
         <v>8097000</v>
@@ -1792,16 +1792,16 @@
         <v>44354</v>
       </c>
       <c r="B69" t="n">
-        <v>16.53772735595703</v>
+        <v>16.53772926330566</v>
       </c>
       <c r="C69" t="n">
-        <v>16.77223772166646</v>
+        <v>16.77223965606192</v>
       </c>
       <c r="D69" t="n">
-        <v>16.03057584819165</v>
+        <v>16.03057769704888</v>
       </c>
       <c r="E69" t="n">
-        <v>16.77223772166646</v>
+        <v>16.77223965606192</v>
       </c>
       <c r="F69" t="n">
         <v>10336000</v>
@@ -1832,16 +1832,16 @@
         <v>44356</v>
       </c>
       <c r="B71" t="n">
-        <v>16.16403961181641</v>
+        <v>16.16403770446777</v>
       </c>
       <c r="C71" t="n">
-        <v>16.39664448651429</v>
+        <v>16.39664255171839</v>
       </c>
       <c r="D71" t="n">
-        <v>15.82466817777308</v>
+        <v>15.82466631047011</v>
       </c>
       <c r="E71" t="n">
-        <v>16.08205778944601</v>
+        <v>16.08205589177119</v>
       </c>
       <c r="F71" t="n">
         <v>10294500</v>
@@ -1872,16 +1872,16 @@
         <v>44358</v>
       </c>
       <c r="B73" t="n">
-        <v>16.07061576843262</v>
+        <v>16.07061386108398</v>
       </c>
       <c r="C73" t="n">
-        <v>16.30512616021678</v>
+        <v>16.30512422503518</v>
       </c>
       <c r="D73" t="n">
-        <v>15.87423797549705</v>
+        <v>15.8742360914556</v>
       </c>
       <c r="E73" t="n">
-        <v>16.3032188029694</v>
+        <v>16.30321686801416</v>
       </c>
       <c r="F73" t="n">
         <v>5133000</v>
@@ -1912,16 +1912,16 @@
         <v>44362</v>
       </c>
       <c r="B75" t="n">
-        <v>15.85898303985596</v>
+        <v>15.85898590087891</v>
       </c>
       <c r="C75" t="n">
-        <v>16.02676318570492</v>
+        <v>16.02676607699607</v>
       </c>
       <c r="D75" t="n">
-        <v>15.48719932831946</v>
+        <v>15.48720212227117</v>
       </c>
       <c r="E75" t="n">
-        <v>16.01532267985088</v>
+        <v>16.01532556907812</v>
       </c>
       <c r="F75" t="n">
         <v>8432500</v>
@@ -1932,16 +1932,16 @@
         <v>44363</v>
       </c>
       <c r="B76" t="n">
-        <v>15.89902305603027</v>
+        <v>15.89902210235596</v>
       </c>
       <c r="C76" t="n">
-        <v>16.11446715307724</v>
+        <v>16.1144661864799</v>
       </c>
       <c r="D76" t="n">
-        <v>15.66260712011776</v>
+        <v>15.66260618062443</v>
       </c>
       <c r="E76" t="n">
-        <v>15.7026452588224</v>
+        <v>15.70264431692745</v>
       </c>
       <c r="F76" t="n">
         <v>10606500</v>
@@ -1972,16 +1972,16 @@
         <v>44365</v>
       </c>
       <c r="B78" t="n">
-        <v>16.2078914642334</v>
+        <v>16.20788955688477</v>
       </c>
       <c r="C78" t="n">
-        <v>16.36423112436919</v>
+        <v>16.36422919862247</v>
       </c>
       <c r="D78" t="n">
-        <v>15.67976622640263</v>
+        <v>15.67976438120391</v>
       </c>
       <c r="E78" t="n">
-        <v>15.98863265031907</v>
+        <v>15.98863076877287</v>
       </c>
       <c r="F78" t="n">
         <v>12012000</v>
@@ -1992,16 +1992,16 @@
         <v>44368</v>
       </c>
       <c r="B79" t="n">
-        <v>16.48434448242188</v>
+        <v>16.48434638977051</v>
       </c>
       <c r="C79" t="n">
-        <v>16.59302020374093</v>
+        <v>16.59302212366407</v>
       </c>
       <c r="D79" t="n">
-        <v>16.00007212945171</v>
+        <v>16.0000739807668</v>
       </c>
       <c r="E79" t="n">
-        <v>16.20789042268334</v>
+        <v>16.20789229804439</v>
       </c>
       <c r="F79" t="n">
         <v>6798000</v>
@@ -2012,16 +2012,16 @@
         <v>44369</v>
       </c>
       <c r="B80" t="n">
-        <v>16.47290420532227</v>
+        <v>16.47290229797363</v>
       </c>
       <c r="C80" t="n">
-        <v>16.49578339803871</v>
+        <v>16.49578148804096</v>
       </c>
       <c r="D80" t="n">
-        <v>16.13162548984007</v>
+        <v>16.13162362200708</v>
       </c>
       <c r="E80" t="n">
-        <v>16.46718395257762</v>
+        <v>16.46718204589131</v>
       </c>
       <c r="F80" t="n">
         <v>6518000</v>
@@ -2092,16 +2092,16 @@
         <v>44375</v>
       </c>
       <c r="B84" t="n">
-        <v>16.3737621307373</v>
+        <v>16.37376403808594</v>
       </c>
       <c r="C84" t="n">
-        <v>16.37948056539015</v>
+        <v>16.37948247340491</v>
       </c>
       <c r="D84" t="n">
-        <v>15.9390592744375</v>
+        <v>15.93906113114842</v>
       </c>
       <c r="E84" t="n">
-        <v>16.2250482827814</v>
+        <v>16.22505017280664</v>
       </c>
       <c r="F84" t="n">
         <v>6202500</v>
@@ -2192,16 +2192,16 @@
         <v>44382</v>
       </c>
       <c r="B89" t="n">
-        <v>16.41570854187012</v>
+        <v>16.41570472717285</v>
       </c>
       <c r="C89" t="n">
-        <v>16.54726347128895</v>
+        <v>16.54725962602083</v>
       </c>
       <c r="D89" t="n">
-        <v>16.25174308313778</v>
+        <v>16.25173930654295</v>
       </c>
       <c r="E89" t="n">
-        <v>16.40808274888606</v>
+        <v>16.40807893596088</v>
       </c>
       <c r="F89" t="n">
         <v>3871000</v>
@@ -2212,16 +2212,16 @@
         <v>44383</v>
       </c>
       <c r="B90" t="n">
-        <v>16.33944129943848</v>
+        <v>16.33944320678711</v>
       </c>
       <c r="C90" t="n">
-        <v>16.38901257865592</v>
+        <v>16.38901449179115</v>
       </c>
       <c r="D90" t="n">
-        <v>16.11255855649923</v>
+        <v>16.11256043736321</v>
       </c>
       <c r="E90" t="n">
-        <v>16.38901257865592</v>
+        <v>16.38901449179115</v>
       </c>
       <c r="F90" t="n">
         <v>3828000</v>
@@ -2252,16 +2252,16 @@
         <v>44385</v>
       </c>
       <c r="B92" t="n">
-        <v>16.43477439880371</v>
+        <v>16.43477249145508</v>
       </c>
       <c r="C92" t="n">
-        <v>16.79893236876558</v>
+        <v>16.79893041915436</v>
       </c>
       <c r="D92" t="n">
-        <v>16.24411685151298</v>
+        <v>16.24411496629124</v>
       </c>
       <c r="E92" t="n">
-        <v>16.26318133345833</v>
+        <v>16.26317944602405</v>
       </c>
       <c r="F92" t="n">
         <v>7435000</v>
@@ -2272,16 +2272,16 @@
         <v>44389</v>
       </c>
       <c r="B93" t="n">
-        <v>16.50150299072266</v>
+        <v>16.50150108337402</v>
       </c>
       <c r="C93" t="n">
-        <v>16.60255291716791</v>
+        <v>16.60255099813928</v>
       </c>
       <c r="D93" t="n">
-        <v>16.2746202228983</v>
+        <v>16.27461834177422</v>
       </c>
       <c r="E93" t="n">
-        <v>16.43095986888196</v>
+        <v>16.43095796968715</v>
       </c>
       <c r="F93" t="n">
         <v>4327500</v>
@@ -2292,16 +2292,16 @@
         <v>44390</v>
       </c>
       <c r="B94" t="n">
-        <v>16.78749084472656</v>
+        <v>16.78749465942383</v>
       </c>
       <c r="C94" t="n">
-        <v>16.91141813862505</v>
+        <v>16.91142198148287</v>
       </c>
       <c r="D94" t="n">
-        <v>16.43095872774974</v>
+        <v>16.4309624614306</v>
       </c>
       <c r="E94" t="n">
-        <v>16.45383792048305</v>
+        <v>16.45384165936285</v>
       </c>
       <c r="F94" t="n">
         <v>6446000</v>
@@ -2372,16 +2372,16 @@
         <v>44396</v>
       </c>
       <c r="B98" t="n">
-        <v>16.65403175354004</v>
+        <v>16.65403366088867</v>
       </c>
       <c r="C98" t="n">
-        <v>16.7970271899026</v>
+        <v>16.79702911362818</v>
       </c>
       <c r="D98" t="n">
-        <v>16.40426976120661</v>
+        <v>16.40427163995056</v>
       </c>
       <c r="E98" t="n">
-        <v>16.58539598054001</v>
+        <v>16.58539788002795</v>
       </c>
       <c r="F98" t="n">
         <v>7763500</v>
@@ -2392,16 +2392,16 @@
         <v>44397</v>
       </c>
       <c r="B99" t="n">
-        <v>16.51103782653809</v>
+        <v>16.51103591918945</v>
       </c>
       <c r="C99" t="n">
-        <v>16.71694877821082</v>
+        <v>16.71694684707543</v>
       </c>
       <c r="D99" t="n">
-        <v>16.45956099775114</v>
+        <v>16.45955909634909</v>
       </c>
       <c r="E99" t="n">
-        <v>16.6540314419629</v>
+        <v>16.6540295180957</v>
       </c>
       <c r="F99" t="n">
         <v>3835500</v>
@@ -2412,16 +2412,16 @@
         <v>44398</v>
       </c>
       <c r="B100" t="n">
-        <v>16.59683227539062</v>
+        <v>16.59683418273926</v>
       </c>
       <c r="C100" t="n">
-        <v>16.59683227539062</v>
+        <v>16.59683418273926</v>
       </c>
       <c r="D100" t="n">
-        <v>16.41570608218979</v>
+        <v>16.41570796872296</v>
       </c>
       <c r="E100" t="n">
-        <v>16.51675600626886</v>
+        <v>16.51675790441493</v>
       </c>
       <c r="F100" t="n">
         <v>4032000</v>
@@ -2432,16 +2432,16 @@
         <v>44399</v>
       </c>
       <c r="B101" t="n">
-        <v>16.64449691772461</v>
+        <v>16.64449882507324</v>
       </c>
       <c r="C101" t="n">
-        <v>16.68072215792294</v>
+        <v>16.68072406942274</v>
       </c>
       <c r="D101" t="n">
-        <v>16.44430623630937</v>
+        <v>16.44430812071748</v>
       </c>
       <c r="E101" t="n">
-        <v>16.58729983992916</v>
+        <v>16.58730174072338</v>
       </c>
       <c r="F101" t="n">
         <v>2829500</v>
@@ -2452,16 +2452,16 @@
         <v>44400</v>
       </c>
       <c r="B102" t="n">
-        <v>16.68262672424316</v>
+        <v>16.68263244628906</v>
       </c>
       <c r="C102" t="n">
-        <v>16.73029064472191</v>
+        <v>16.73029638311626</v>
       </c>
       <c r="D102" t="n">
-        <v>16.56060497863364</v>
+        <v>16.56061065882677</v>
       </c>
       <c r="E102" t="n">
-        <v>16.64449413325056</v>
+        <v>16.64449984221719</v>
       </c>
       <c r="F102" t="n">
         <v>4154500</v>
@@ -2472,16 +2472,16 @@
         <v>44403</v>
       </c>
       <c r="B103" t="n">
-        <v>17.19740867614746</v>
+        <v>17.19740676879883</v>
       </c>
       <c r="C103" t="n">
-        <v>17.21647315657783</v>
+        <v>17.21647124711478</v>
       </c>
       <c r="D103" t="n">
-        <v>16.5606077549527</v>
+        <v>16.56060591823107</v>
       </c>
       <c r="E103" t="n">
-        <v>16.75126710535498</v>
+        <v>16.7512652474875</v>
       </c>
       <c r="F103" t="n">
         <v>9987000</v>
@@ -2492,16 +2492,16 @@
         <v>44404</v>
       </c>
       <c r="B104" t="n">
-        <v>16.96861839294434</v>
+        <v>16.9686164855957</v>
       </c>
       <c r="C104" t="n">
-        <v>17.300365840649</v>
+        <v>17.30036389601047</v>
       </c>
       <c r="D104" t="n">
-        <v>16.87329052665406</v>
+        <v>16.8732886300207</v>
       </c>
       <c r="E104" t="n">
-        <v>17.14402435794695</v>
+        <v>17.1440224308819</v>
       </c>
       <c r="F104" t="n">
         <v>6666500</v>
@@ -2532,16 +2532,16 @@
         <v>44406</v>
       </c>
       <c r="B106" t="n">
-        <v>16.62543487548828</v>
+        <v>16.62543296813965</v>
       </c>
       <c r="C106" t="n">
-        <v>16.7779616508197</v>
+        <v>16.77795972597248</v>
       </c>
       <c r="D106" t="n">
-        <v>16.27462292857349</v>
+        <v>16.27462106147167</v>
       </c>
       <c r="E106" t="n">
-        <v>16.7779616508197</v>
+        <v>16.77795972597248</v>
       </c>
       <c r="F106" t="n">
         <v>12625000</v>
@@ -2572,16 +2572,16 @@
         <v>44410</v>
       </c>
       <c r="B108" t="n">
-        <v>16.52247619628906</v>
+        <v>16.5224781036377</v>
       </c>
       <c r="C108" t="n">
-        <v>16.83896837564879</v>
+        <v>16.83897031953316</v>
       </c>
       <c r="D108" t="n">
-        <v>16.36232184039388</v>
+        <v>16.36232372925435</v>
       </c>
       <c r="E108" t="n">
-        <v>16.68262873392202</v>
+        <v>16.6826306597586</v>
       </c>
       <c r="F108" t="n">
         <v>8100500</v>
@@ -2592,16 +2592,16 @@
         <v>44411</v>
       </c>
       <c r="B109" t="n">
-        <v>16.53010177612305</v>
+        <v>16.53009986877441</v>
       </c>
       <c r="C109" t="n">
-        <v>16.68072116292792</v>
+        <v>16.68071923819987</v>
       </c>
       <c r="D109" t="n">
-        <v>16.26127352643131</v>
+        <v>16.2612716501018</v>
       </c>
       <c r="E109" t="n">
-        <v>16.68072116292792</v>
+        <v>16.68071923819987</v>
       </c>
       <c r="F109" t="n">
         <v>5450500</v>
@@ -2612,16 +2612,16 @@
         <v>44412</v>
       </c>
       <c r="B110" t="n">
-        <v>16.60255241394043</v>
+        <v>16.6025562286377</v>
       </c>
       <c r="C110" t="n">
-        <v>16.83134253196625</v>
+        <v>16.83134639923163</v>
       </c>
       <c r="D110" t="n">
-        <v>16.34897574520748</v>
+        <v>16.34897950164152</v>
       </c>
       <c r="E110" t="n">
-        <v>16.48243801108588</v>
+        <v>16.48244179818497</v>
       </c>
       <c r="F110" t="n">
         <v>6533500</v>
@@ -2672,16 +2672,16 @@
         <v>44417</v>
       </c>
       <c r="B113" t="n">
-        <v>17.31942939758301</v>
+        <v>17.31942749023438</v>
       </c>
       <c r="C113" t="n">
-        <v>17.35756199667172</v>
+        <v>17.35756008512363</v>
       </c>
       <c r="D113" t="n">
-        <v>16.6178055750599</v>
+        <v>16.61780374497947</v>
       </c>
       <c r="E113" t="n">
-        <v>16.6178055750599</v>
+        <v>16.61780374497947</v>
       </c>
       <c r="F113" t="n">
         <v>10558500</v>
@@ -2692,16 +2692,16 @@
         <v>44418</v>
       </c>
       <c r="B114" t="n">
-        <v>17.55012512207031</v>
+        <v>17.55012702941895</v>
       </c>
       <c r="C114" t="n">
-        <v>17.66452108952034</v>
+        <v>17.66452300930153</v>
       </c>
       <c r="D114" t="n">
-        <v>17.10589093347529</v>
+        <v>17.10589279254452</v>
       </c>
       <c r="E114" t="n">
-        <v>17.22219243972985</v>
+        <v>17.22219431143875</v>
       </c>
       <c r="F114" t="n">
         <v>10281500</v>
@@ -2712,16 +2712,16 @@
         <v>44419</v>
       </c>
       <c r="B115" t="n">
-        <v>17.20884704589844</v>
+        <v>17.20884895324707</v>
       </c>
       <c r="C115" t="n">
-        <v>17.57872523333663</v>
+        <v>17.57872718168084</v>
       </c>
       <c r="D115" t="n">
-        <v>17.19740835785192</v>
+        <v>17.19741026393275</v>
       </c>
       <c r="E115" t="n">
-        <v>17.57872523333663</v>
+        <v>17.57872718168084</v>
       </c>
       <c r="F115" t="n">
         <v>6265000</v>
@@ -2752,16 +2752,16 @@
         <v>44421</v>
       </c>
       <c r="B117" t="n">
-        <v>16.91142272949219</v>
+        <v>16.91141891479492</v>
       </c>
       <c r="C117" t="n">
-        <v>17.27367519755692</v>
+        <v>17.27367130114663</v>
       </c>
       <c r="D117" t="n">
-        <v>16.53010577752615</v>
+        <v>16.53010204884227</v>
       </c>
       <c r="E117" t="n">
-        <v>16.825626188017</v>
+        <v>16.82562239267279</v>
       </c>
       <c r="F117" t="n">
         <v>5547600</v>
@@ -2792,16 +2792,16 @@
         <v>44425</v>
       </c>
       <c r="B119" t="n">
-        <v>16.16784858703613</v>
+        <v>16.1678524017334</v>
       </c>
       <c r="C119" t="n">
-        <v>16.39664050965117</v>
+        <v>16.39664437833038</v>
       </c>
       <c r="D119" t="n">
-        <v>15.70073523003284</v>
+        <v>15.70073893451779</v>
       </c>
       <c r="E119" t="n">
-        <v>16.16784858703613</v>
+        <v>16.1678524017334</v>
       </c>
       <c r="F119" t="n">
         <v>9967800</v>
@@ -2812,16 +2812,16 @@
         <v>44426</v>
       </c>
       <c r="B120" t="n">
-        <v>15.88186264038086</v>
+        <v>15.88186550140381</v>
       </c>
       <c r="C120" t="n">
-        <v>16.30131210662337</v>
+        <v>16.30131504320764</v>
       </c>
       <c r="D120" t="n">
-        <v>15.64353936928479</v>
+        <v>15.64354218737522</v>
       </c>
       <c r="E120" t="n">
-        <v>16.16784983839123</v>
+        <v>16.16785275093307</v>
       </c>
       <c r="F120" t="n">
         <v>10736900</v>
@@ -2832,16 +2832,16 @@
         <v>44427</v>
       </c>
       <c r="B121" t="n">
-        <v>16.6635627746582</v>
+        <v>16.66356468200684</v>
       </c>
       <c r="C121" t="n">
-        <v>16.87328841811889</v>
+        <v>16.87329034947318</v>
       </c>
       <c r="D121" t="n">
-        <v>15.57680923404292</v>
+        <v>15.57681101699932</v>
       </c>
       <c r="E121" t="n">
-        <v>15.71026968478171</v>
+        <v>15.71027148301428</v>
       </c>
       <c r="F121" t="n">
         <v>14455000</v>
@@ -2892,16 +2892,16 @@
         <v>44432</v>
       </c>
       <c r="B124" t="n">
-        <v>16.91142272949219</v>
+        <v>16.91141891479492</v>
       </c>
       <c r="C124" t="n">
-        <v>17.05441635919662</v>
+        <v>17.05441251224439</v>
       </c>
       <c r="D124" t="n">
-        <v>16.6635662561486</v>
+        <v>16.66356249736014</v>
       </c>
       <c r="E124" t="n">
-        <v>16.78749540195172</v>
+        <v>16.78749161520865</v>
       </c>
       <c r="F124" t="n">
         <v>4198100</v>
@@ -2912,16 +2912,16 @@
         <v>44433</v>
       </c>
       <c r="B125" t="n">
-        <v>17.01628303527832</v>
+        <v>17.01628494262695</v>
       </c>
       <c r="C125" t="n">
-        <v>17.19740924229705</v>
+        <v>17.19741116994805</v>
       </c>
       <c r="D125" t="n">
-        <v>16.78749289822105</v>
+        <v>16.78749477992469</v>
       </c>
       <c r="E125" t="n">
-        <v>17.0258161849385</v>
+        <v>17.0258180933557</v>
       </c>
       <c r="F125" t="n">
         <v>4269900</v>
@@ -3032,16 +3032,16 @@
         <v>44441</v>
       </c>
       <c r="B131" t="n">
-        <v>16.72076034545898</v>
+        <v>16.72076416015625</v>
       </c>
       <c r="C131" t="n">
-        <v>17.0353469674827</v>
+        <v>17.03535085395019</v>
       </c>
       <c r="D131" t="n">
-        <v>16.10111843148494</v>
+        <v>16.10112210481625</v>
       </c>
       <c r="E131" t="n">
-        <v>16.16784865157147</v>
+        <v>16.1678523401267</v>
       </c>
       <c r="F131" t="n">
         <v>17566400</v>
@@ -3092,16 +3092,16 @@
         <v>44447</v>
       </c>
       <c r="B134" t="n">
-        <v>17.0734806060791</v>
+        <v>17.07347869873047</v>
       </c>
       <c r="C134" t="n">
-        <v>17.55012719322427</v>
+        <v>17.55012523262749</v>
       </c>
       <c r="D134" t="n">
-        <v>16.84469046244091</v>
+        <v>16.84468858065136</v>
       </c>
       <c r="E134" t="n">
-        <v>17.49293011188033</v>
+        <v>17.49292815767328</v>
       </c>
       <c r="F134" t="n">
         <v>11069100</v>
@@ -3112,16 +3112,16 @@
         <v>44448</v>
       </c>
       <c r="B135" t="n">
-        <v>17.34993553161621</v>
+        <v>17.34993934631348</v>
       </c>
       <c r="C135" t="n">
-        <v>17.44526338911795</v>
+        <v>17.44526722477477</v>
       </c>
       <c r="D135" t="n">
-        <v>16.92095289980908</v>
+        <v>16.92095662018675</v>
       </c>
       <c r="E135" t="n">
-        <v>17.07347965372665</v>
+        <v>17.07348340764009</v>
       </c>
       <c r="F135" t="n">
         <v>12544000</v>
@@ -3132,16 +3132,16 @@
         <v>44449</v>
       </c>
       <c r="B136" t="n">
-        <v>17.33087158203125</v>
+        <v>17.33086967468262</v>
       </c>
       <c r="C136" t="n">
-        <v>17.60732567913216</v>
+        <v>17.60732374135838</v>
       </c>
       <c r="D136" t="n">
-        <v>17.01628488215086</v>
+        <v>17.01628300942406</v>
       </c>
       <c r="E136" t="n">
-        <v>17.33087158203125</v>
+        <v>17.33086967468262</v>
       </c>
       <c r="F136" t="n">
         <v>19125200</v>
@@ -3152,16 +3152,16 @@
         <v>44452</v>
       </c>
       <c r="B137" t="n">
-        <v>17.79798316955566</v>
+        <v>17.79798126220703</v>
       </c>
       <c r="C137" t="n">
-        <v>17.9695762273458</v>
+        <v>17.96957430160813</v>
       </c>
       <c r="D137" t="n">
-        <v>17.49292965271203</v>
+        <v>17.49292777805493</v>
       </c>
       <c r="E137" t="n">
-        <v>17.5787261816071</v>
+        <v>17.57872429775548</v>
       </c>
       <c r="F137" t="n">
         <v>17075500</v>
@@ -3192,16 +3192,16 @@
         <v>44454</v>
       </c>
       <c r="B139" t="n">
-        <v>17.72171974182129</v>
+        <v>17.72171783447266</v>
       </c>
       <c r="C139" t="n">
-        <v>17.82658256979756</v>
+        <v>17.82658065116278</v>
       </c>
       <c r="D139" t="n">
-        <v>17.27367261746679</v>
+        <v>17.27367075834045</v>
       </c>
       <c r="E139" t="n">
-        <v>17.46433015584083</v>
+        <v>17.46432827619446</v>
       </c>
       <c r="F139" t="n">
         <v>8756500</v>
@@ -3232,16 +3232,16 @@
         <v>44456</v>
       </c>
       <c r="B141" t="n">
-        <v>18.11256790161133</v>
+        <v>18.11256980895996</v>
       </c>
       <c r="C141" t="n">
-        <v>18.4462208318724</v>
+        <v>18.44622277435644</v>
       </c>
       <c r="D141" t="n">
-        <v>18.11256790161133</v>
+        <v>18.11256980895996</v>
       </c>
       <c r="E141" t="n">
-        <v>18.28416094107486</v>
+        <v>18.28416286649314</v>
       </c>
       <c r="F141" t="n">
         <v>23104900</v>
@@ -3252,16 +3252,16 @@
         <v>44459</v>
       </c>
       <c r="B142" t="n">
-        <v>17.94097709655762</v>
+        <v>17.94097518920898</v>
       </c>
       <c r="C142" t="n">
-        <v>18.12210330724501</v>
+        <v>18.12210138064041</v>
       </c>
       <c r="D142" t="n">
-        <v>17.63592357430248</v>
+        <v>17.63592169938482</v>
       </c>
       <c r="E142" t="n">
-        <v>18.02677362697468</v>
+        <v>18.02677171050481</v>
       </c>
       <c r="F142" t="n">
         <v>15522000</v>
@@ -3312,16 +3312,16 @@
         <v>44462</v>
       </c>
       <c r="B145" t="n">
-        <v>18.2936954498291</v>
+        <v>18.29369735717773</v>
       </c>
       <c r="C145" t="n">
-        <v>18.53201872941112</v>
+        <v>18.53202066160796</v>
       </c>
       <c r="D145" t="n">
-        <v>18.07443665073428</v>
+        <v>18.07443853522241</v>
       </c>
       <c r="E145" t="n">
-        <v>18.34135937844058</v>
+        <v>18.34136129075877</v>
       </c>
       <c r="F145" t="n">
         <v>20822300</v>
@@ -3372,16 +3372,16 @@
         <v>44467</v>
       </c>
       <c r="B148" t="n">
-        <v>18.2841625213623</v>
+        <v>18.28416442871094</v>
       </c>
       <c r="C148" t="n">
-        <v>18.29369567085224</v>
+        <v>18.29369757919535</v>
       </c>
       <c r="D148" t="n">
-        <v>18.01723979043107</v>
+        <v>18.01724166993512</v>
       </c>
       <c r="E148" t="n">
-        <v>18.23649677391261</v>
+        <v>18.2364986762889</v>
       </c>
       <c r="F148" t="n">
         <v>11310100</v>
@@ -3432,16 +3432,16 @@
         <v>44470</v>
       </c>
       <c r="B151" t="n">
-        <v>18.45575523376465</v>
+        <v>18.45575714111328</v>
       </c>
       <c r="C151" t="n">
-        <v>18.56061623968673</v>
+        <v>18.56061815787245</v>
       </c>
       <c r="D151" t="n">
-        <v>18.00770630734936</v>
+        <v>18.00770816839343</v>
       </c>
       <c r="E151" t="n">
-        <v>18.19836565709148</v>
+        <v>18.19836753783964</v>
       </c>
       <c r="F151" t="n">
         <v>5841800</v>
@@ -3472,16 +3472,16 @@
         <v>44474</v>
       </c>
       <c r="B153" t="n">
-        <v>18.32229423522949</v>
+        <v>18.32229232788086</v>
       </c>
       <c r="C153" t="n">
-        <v>18.49388729827244</v>
+        <v>18.49388537306099</v>
       </c>
       <c r="D153" t="n">
-        <v>18.04584015897554</v>
+        <v>18.04583828040574</v>
       </c>
       <c r="E153" t="n">
-        <v>18.34136053518147</v>
+        <v>18.34135862584804</v>
       </c>
       <c r="F153" t="n">
         <v>8000200</v>
@@ -3512,16 +3512,16 @@
         <v>44476</v>
       </c>
       <c r="B155" t="n">
-        <v>18.08055114746094</v>
+        <v>18.0805492401123</v>
       </c>
       <c r="C155" t="n">
-        <v>18.36723991743979</v>
+        <v>18.36723797984786</v>
       </c>
       <c r="D155" t="n">
-        <v>17.99454415192273</v>
+        <v>17.99454225364713</v>
       </c>
       <c r="E155" t="n">
-        <v>18.271678209262</v>
+        <v>18.27167628175104</v>
       </c>
       <c r="F155" t="n">
         <v>7169200</v>
@@ -3552,16 +3552,16 @@
         <v>44480</v>
       </c>
       <c r="B157" t="n">
-        <v>16.62798881530762</v>
+        <v>16.62799072265625</v>
       </c>
       <c r="C157" t="n">
-        <v>17.52628299400677</v>
+        <v>17.52628500439614</v>
       </c>
       <c r="D157" t="n">
-        <v>16.47508791119575</v>
+        <v>16.47508980100556</v>
       </c>
       <c r="E157" t="n">
-        <v>17.4211629389089</v>
+        <v>17.42116493724025</v>
       </c>
       <c r="F157" t="n">
         <v>31512800</v>
@@ -3632,16 +3632,16 @@
         <v>44487</v>
       </c>
       <c r="B161" t="n">
-        <v>16.20750999450684</v>
+        <v>16.20751190185547</v>
       </c>
       <c r="C161" t="n">
-        <v>16.67577105168735</v>
+        <v>16.67577301414236</v>
       </c>
       <c r="D161" t="n">
-        <v>16.10239176487586</v>
+        <v>16.10239365985386</v>
       </c>
       <c r="E161" t="n">
-        <v>16.5897640675295</v>
+        <v>16.58976601986295</v>
       </c>
       <c r="F161" t="n">
         <v>13070300</v>
@@ -3672,16 +3672,16 @@
         <v>44489</v>
       </c>
       <c r="B163" t="n">
-        <v>15.98771858215332</v>
+        <v>15.98771953582764</v>
       </c>
       <c r="C163" t="n">
-        <v>16.21706998116152</v>
+        <v>16.21707094851675</v>
       </c>
       <c r="D163" t="n">
-        <v>15.71058632520617</v>
+        <v>15.71058726234942</v>
       </c>
       <c r="E163" t="n">
-        <v>15.93993772421437</v>
+        <v>15.93993867503853</v>
       </c>
       <c r="F163" t="n">
         <v>11472200</v>
@@ -3752,16 +3752,16 @@
         <v>44495</v>
       </c>
       <c r="B167" t="n">
-        <v>15.24232387542725</v>
+        <v>15.24232482910156</v>
       </c>
       <c r="C167" t="n">
-        <v>15.44300654837805</v>
+        <v>15.44300751460859</v>
       </c>
       <c r="D167" t="n">
-        <v>15.0129725095867</v>
+        <v>15.01297344891107</v>
       </c>
       <c r="E167" t="n">
-        <v>15.38566916259858</v>
+        <v>15.38567012524165</v>
       </c>
       <c r="F167" t="n">
         <v>7090300</v>
@@ -3852,16 +3852,16 @@
         <v>44503</v>
       </c>
       <c r="B172" t="n">
-        <v>14.74539566040039</v>
+        <v>14.74539661407471</v>
       </c>
       <c r="C172" t="n">
-        <v>14.86962787591666</v>
+        <v>14.86962883762583</v>
       </c>
       <c r="D172" t="n">
-        <v>14.07645282125721</v>
+        <v>14.07645373166693</v>
       </c>
       <c r="E172" t="n">
-        <v>14.14334765198831</v>
+        <v>14.14334856672452</v>
       </c>
       <c r="F172" t="n">
         <v>21906500</v>
@@ -3872,16 +3872,16 @@
         <v>44504</v>
       </c>
       <c r="B173" t="n">
-        <v>14.52560043334961</v>
+        <v>14.52559947967529</v>
       </c>
       <c r="C173" t="n">
-        <v>14.73583964480952</v>
+        <v>14.735838677332</v>
       </c>
       <c r="D173" t="n">
-        <v>14.30580559832982</v>
+        <v>14.30580465908607</v>
       </c>
       <c r="E173" t="n">
-        <v>14.69761441648602</v>
+        <v>14.69761345151817</v>
       </c>
       <c r="F173" t="n">
         <v>4262500</v>
@@ -3912,16 +3912,16 @@
         <v>44508</v>
       </c>
       <c r="B175" t="n">
-        <v>14.73583984375</v>
+        <v>14.73584079742432</v>
       </c>
       <c r="C175" t="n">
-        <v>14.89829729415845</v>
+        <v>14.89829825834669</v>
       </c>
       <c r="D175" t="n">
-        <v>14.2866927213642</v>
+        <v>14.28669364597061</v>
       </c>
       <c r="E175" t="n">
-        <v>14.39181278419399</v>
+        <v>14.39181371560356</v>
       </c>
       <c r="F175" t="n">
         <v>8290300</v>
@@ -3932,16 +3932,16 @@
         <v>44509</v>
       </c>
       <c r="B176" t="n">
-        <v>14.81229114532471</v>
+        <v>14.81229019165039</v>
       </c>
       <c r="C176" t="n">
-        <v>15.08942429804084</v>
+        <v>15.08942332652359</v>
       </c>
       <c r="D176" t="n">
-        <v>14.66894675684999</v>
+        <v>14.66894581240476</v>
       </c>
       <c r="E176" t="n">
-        <v>14.80273460973002</v>
+        <v>14.80273365667099</v>
       </c>
       <c r="F176" t="n">
         <v>6124400</v>
@@ -3992,16 +3992,16 @@
         <v>44512</v>
       </c>
       <c r="B179" t="n">
-        <v>14.84095859527588</v>
+        <v>14.8409595489502</v>
       </c>
       <c r="C179" t="n">
-        <v>15.23276740816299</v>
+        <v>15.23276838701479</v>
       </c>
       <c r="D179" t="n">
-        <v>14.82184643705182</v>
+        <v>14.82184738949799</v>
       </c>
       <c r="E179" t="n">
-        <v>15.08942303171791</v>
+        <v>15.08942400135846</v>
       </c>
       <c r="F179" t="n">
         <v>7831400</v>
@@ -4112,16 +4112,16 @@
         <v>44523</v>
       </c>
       <c r="B185" t="n">
-        <v>13.24505519866943</v>
+        <v>13.24505424499512</v>
       </c>
       <c r="C185" t="n">
-        <v>13.41706919844482</v>
+        <v>13.4170682323851</v>
       </c>
       <c r="D185" t="n">
-        <v>12.99659164621339</v>
+        <v>12.99659071042901</v>
       </c>
       <c r="E185" t="n">
-        <v>13.23549957418524</v>
+        <v>13.23549862119895</v>
       </c>
       <c r="F185" t="n">
         <v>3755200</v>
@@ -4312,16 +4312,16 @@
         <v>44537</v>
       </c>
       <c r="B195" t="n">
-        <v>13.42662334442139</v>
+        <v>13.4266242980957</v>
       </c>
       <c r="C195" t="n">
-        <v>13.76109383723112</v>
+        <v>13.76109481466241</v>
       </c>
       <c r="D195" t="n">
-        <v>13.40751027613218</v>
+        <v>13.40751122844893</v>
       </c>
       <c r="E195" t="n">
-        <v>13.56996771114538</v>
+        <v>13.56996867500125</v>
       </c>
       <c r="F195" t="n">
         <v>14090400</v>
@@ -4392,16 +4392,16 @@
         <v>44543</v>
       </c>
       <c r="B199" t="n">
-        <v>13.74198341369629</v>
+        <v>13.74198436737061</v>
       </c>
       <c r="C199" t="n">
-        <v>14.12423571408451</v>
+        <v>14.12423669428659</v>
       </c>
       <c r="D199" t="n">
-        <v>13.66553295361865</v>
+        <v>13.66553390198741</v>
       </c>
       <c r="E199" t="n">
-        <v>13.96177825857917</v>
+        <v>13.96177922750694</v>
       </c>
       <c r="F199" t="n">
         <v>11783000</v>
@@ -4412,16 +4412,16 @@
         <v>44544</v>
       </c>
       <c r="B200" t="n">
-        <v>13.76109504699707</v>
+        <v>13.76109600067139</v>
       </c>
       <c r="C200" t="n">
-        <v>14.14334824413447</v>
+        <v>14.14334922429978</v>
       </c>
       <c r="D200" t="n">
-        <v>13.56996890410904</v>
+        <v>13.56996984453789</v>
       </c>
       <c r="E200" t="n">
-        <v>13.88532726771463</v>
+        <v>13.88532822999851</v>
       </c>
       <c r="F200" t="n">
         <v>6761100</v>
@@ -4452,16 +4452,16 @@
         <v>44546</v>
       </c>
       <c r="B202" t="n">
-        <v>13.89488410949707</v>
+        <v>13.89488315582275</v>
       </c>
       <c r="C202" t="n">
-        <v>14.28669293890897</v>
+        <v>14.28669195834289</v>
       </c>
       <c r="D202" t="n">
-        <v>13.82799018584958</v>
+        <v>13.82798923676653</v>
       </c>
       <c r="E202" t="n">
-        <v>14.21024248006574</v>
+        <v>14.21024150474683</v>
       </c>
       <c r="F202" t="n">
         <v>5287600</v>
@@ -4472,16 +4472,16 @@
         <v>44547</v>
       </c>
       <c r="B203" t="n">
-        <v>13.81843280792236</v>
+        <v>13.81843185424805</v>
       </c>
       <c r="C203" t="n">
-        <v>14.00955894337442</v>
+        <v>14.0095579765096</v>
       </c>
       <c r="D203" t="n">
-        <v>13.64641883033486</v>
+        <v>13.64641788853203</v>
       </c>
       <c r="E203" t="n">
-        <v>13.84710150039985</v>
+        <v>13.84710054474697</v>
       </c>
       <c r="F203" t="n">
         <v>8250000</v>
@@ -4492,16 +4492,16 @@
         <v>44550</v>
       </c>
       <c r="B204" t="n">
-        <v>13.47440624237061</v>
+        <v>13.47440528869629</v>
       </c>
       <c r="C204" t="n">
-        <v>13.86621506179454</v>
+        <v>13.86621408038928</v>
       </c>
       <c r="D204" t="n">
-        <v>13.29283572372549</v>
+        <v>13.29283478290215</v>
       </c>
       <c r="E204" t="n">
-        <v>13.81843329839523</v>
+        <v>13.81843232037181</v>
       </c>
       <c r="F204" t="n">
         <v>6680500</v>
@@ -4512,16 +4512,16 @@
         <v>44551</v>
       </c>
       <c r="B205" t="n">
-        <v>13.61775016784668</v>
+        <v>13.617751121521</v>
       </c>
       <c r="C205" t="n">
-        <v>13.66553192965524</v>
+        <v>13.6655328866758</v>
       </c>
       <c r="D205" t="n">
-        <v>13.36928573553119</v>
+        <v>13.36928667180511</v>
       </c>
       <c r="E205" t="n">
-        <v>13.48396141705496</v>
+        <v>13.48396236135982</v>
       </c>
       <c r="F205" t="n">
         <v>4083800</v>
@@ -4532,16 +4532,16 @@
         <v>44552</v>
       </c>
       <c r="B206" t="n">
-        <v>13.5317440032959</v>
+        <v>13.53174304962158</v>
       </c>
       <c r="C206" t="n">
-        <v>13.66553276223881</v>
+        <v>13.66553179913548</v>
       </c>
       <c r="D206" t="n">
-        <v>13.29283609105872</v>
+        <v>13.29283515422187</v>
       </c>
       <c r="E206" t="n">
-        <v>13.58908230323182</v>
+        <v>13.58908134551648</v>
       </c>
       <c r="F206" t="n">
         <v>6990400</v>
@@ -4552,16 +4552,16 @@
         <v>44553</v>
       </c>
       <c r="B207" t="n">
-        <v>13.4648494720459</v>
+        <v>13.46484851837158</v>
       </c>
       <c r="C207" t="n">
-        <v>13.65597561094082</v>
+        <v>13.65597464372962</v>
       </c>
       <c r="D207" t="n">
-        <v>13.32150418435372</v>
+        <v>13.32150324083211</v>
       </c>
       <c r="E207" t="n">
-        <v>13.41706770948184</v>
+        <v>13.41706675919176</v>
       </c>
       <c r="F207" t="n">
         <v>4198000</v>
@@ -4612,16 +4612,16 @@
         <v>44559</v>
       </c>
       <c r="B210" t="n">
-        <v>12.2703104019165</v>
+        <v>12.27031135559082</v>
       </c>
       <c r="C210" t="n">
-        <v>12.53788700590259</v>
+        <v>12.53788798037352</v>
       </c>
       <c r="D210" t="n">
-        <v>12.2511973316654</v>
+        <v>12.2511982838542</v>
       </c>
       <c r="E210" t="n">
-        <v>12.51877484701283</v>
+        <v>12.51877581999832</v>
       </c>
       <c r="F210" t="n">
         <v>10451000</v>
@@ -4632,16 +4632,16 @@
         <v>44560</v>
       </c>
       <c r="B211" t="n">
-        <v>12.38498592376709</v>
+        <v>12.38498687744141</v>
       </c>
       <c r="C211" t="n">
-        <v>12.49966160965662</v>
+        <v>12.49966257216125</v>
       </c>
       <c r="D211" t="n">
-        <v>12.25119716788196</v>
+        <v>12.25119811125422</v>
       </c>
       <c r="E211" t="n">
-        <v>12.32764762514165</v>
+        <v>12.32764857440078</v>
       </c>
       <c r="F211" t="n">
         <v>5913100</v>
@@ -4652,16 +4652,16 @@
         <v>44564</v>
       </c>
       <c r="B212" t="n">
-        <v>12.1556339263916</v>
+        <v>12.15563488006592</v>
       </c>
       <c r="C212" t="n">
-        <v>12.49966096635466</v>
+        <v>12.49966194701974</v>
       </c>
       <c r="D212" t="n">
-        <v>11.84983120172981</v>
+        <v>11.84983213141227</v>
       </c>
       <c r="E212" t="n">
-        <v>12.49966096635466</v>
+        <v>12.49966194701974</v>
       </c>
       <c r="F212" t="n">
         <v>16124600</v>
@@ -4672,16 +4672,16 @@
         <v>44565</v>
       </c>
       <c r="B213" t="n">
-        <v>12.1556339263916</v>
+        <v>12.15563488006592</v>
       </c>
       <c r="C213" t="n">
-        <v>12.25119653736736</v>
+        <v>12.25119749853907</v>
       </c>
       <c r="D213" t="n">
-        <v>11.89761296289834</v>
+        <v>11.89761389632953</v>
       </c>
       <c r="E213" t="n">
-        <v>12.20341568756013</v>
+        <v>12.20341664498318</v>
       </c>
       <c r="F213" t="n">
         <v>9389900</v>
@@ -4692,16 +4692,16 @@
         <v>44566</v>
       </c>
       <c r="B214" t="n">
-        <v>11.45802307128906</v>
+        <v>11.45802402496338</v>
       </c>
       <c r="C214" t="n">
-        <v>12.13652156778615</v>
+        <v>12.13652257793327</v>
       </c>
       <c r="D214" t="n">
-        <v>11.41024130732365</v>
+        <v>11.41024225702099</v>
       </c>
       <c r="E214" t="n">
-        <v>12.1174094090168</v>
+        <v>12.11741041757316</v>
       </c>
       <c r="F214" t="n">
         <v>11220000</v>
@@ -4712,16 +4712,16 @@
         <v>44567</v>
       </c>
       <c r="B215" t="n">
-        <v>11.07577133178711</v>
+        <v>11.07577037811279</v>
       </c>
       <c r="C215" t="n">
-        <v>11.62048109847782</v>
+        <v>11.62048009790152</v>
       </c>
       <c r="D215" t="n">
-        <v>11.02798956545112</v>
+        <v>11.02798861589103</v>
       </c>
       <c r="E215" t="n">
-        <v>11.56314370796374</v>
+        <v>11.56314271232445</v>
       </c>
       <c r="F215" t="n">
         <v>15779400</v>
@@ -4732,16 +4732,16 @@
         <v>44568</v>
       </c>
       <c r="B216" t="n">
-        <v>10.85597610473633</v>
+        <v>10.85597515106201</v>
       </c>
       <c r="C216" t="n">
-        <v>11.11399710881509</v>
+        <v>11.11399613247418</v>
       </c>
       <c r="D216" t="n">
-        <v>10.71263171004464</v>
+        <v>10.71263076896282</v>
       </c>
       <c r="E216" t="n">
-        <v>11.00887794679861</v>
+        <v>11.0088769796922</v>
       </c>
       <c r="F216" t="n">
         <v>11641900</v>
@@ -4772,16 +4772,16 @@
         <v>44572</v>
       </c>
       <c r="B218" t="n">
-        <v>10.94198322296143</v>
+        <v>10.94198226928711</v>
       </c>
       <c r="C218" t="n">
-        <v>10.96109629518389</v>
+        <v>10.96109533984372</v>
       </c>
       <c r="D218" t="n">
-        <v>10.66485005526586</v>
+        <v>10.66484912574574</v>
       </c>
       <c r="E218" t="n">
-        <v>10.70307528834934</v>
+        <v>10.7030743554976</v>
       </c>
       <c r="F218" t="n">
         <v>6045500</v>
@@ -4812,16 +4812,16 @@
         <v>44574</v>
       </c>
       <c r="B220" t="n">
-        <v>11.48669242858887</v>
+        <v>11.48669338226318</v>
       </c>
       <c r="C220" t="n">
-        <v>11.57269850823688</v>
+        <v>11.57269946905179</v>
       </c>
       <c r="D220" t="n">
-        <v>11.15222099941061</v>
+        <v>11.15222192531568</v>
       </c>
       <c r="E220" t="n">
-        <v>11.27645321849507</v>
+        <v>11.27645415471443</v>
       </c>
       <c r="F220" t="n">
         <v>9668300</v>
@@ -4832,16 +4832,16 @@
         <v>44575</v>
       </c>
       <c r="B221" t="n">
-        <v>11.59181213378906</v>
+        <v>11.59181308746338</v>
       </c>
       <c r="C221" t="n">
-        <v>11.65870605828779</v>
+        <v>11.65870701746556</v>
       </c>
       <c r="D221" t="n">
-        <v>11.39112944893152</v>
+        <v>11.3911303860954</v>
       </c>
       <c r="E221" t="n">
-        <v>11.41024160820486</v>
+        <v>11.41024254694112</v>
       </c>
       <c r="F221" t="n">
         <v>7586600</v>
@@ -4852,16 +4852,16 @@
         <v>44578</v>
       </c>
       <c r="B222" t="n">
-        <v>11.47713565826416</v>
+        <v>11.47713661193848</v>
       </c>
       <c r="C222" t="n">
-        <v>11.6109234981016</v>
+        <v>11.61092446289281</v>
       </c>
       <c r="D222" t="n">
-        <v>11.41024082698413</v>
+        <v>11.41024177509993</v>
       </c>
       <c r="E222" t="n">
-        <v>11.59181134013681</v>
+        <v>11.59181230333992</v>
       </c>
       <c r="F222" t="n">
         <v>4569300</v>
@@ -4872,16 +4872,16 @@
         <v>44579</v>
       </c>
       <c r="B223" t="n">
-        <v>11.39112854003906</v>
+        <v>11.39112949371338</v>
       </c>
       <c r="C223" t="n">
-        <v>11.49624768605842</v>
+        <v>11.49624864853339</v>
       </c>
       <c r="D223" t="n">
-        <v>11.29556501721325</v>
+        <v>11.29556596288691</v>
       </c>
       <c r="E223" t="n">
-        <v>11.47713552831003</v>
+        <v>11.47713648918492</v>
       </c>
       <c r="F223" t="n">
         <v>7771300</v>
@@ -4892,16 +4892,16 @@
         <v>44580</v>
       </c>
       <c r="B224" t="n">
-        <v>11.49624824523926</v>
+        <v>11.49624919891357</v>
       </c>
       <c r="C224" t="n">
-        <v>11.69693092384569</v>
+        <v>11.69693189416769</v>
       </c>
       <c r="D224" t="n">
-        <v>11.41979778780455</v>
+        <v>11.4197987351369</v>
       </c>
       <c r="E224" t="n">
-        <v>11.41979778780455</v>
+        <v>11.4197987351369</v>
       </c>
       <c r="F224" t="n">
         <v>5074700</v>
@@ -4912,16 +4912,16 @@
         <v>44581</v>
       </c>
       <c r="B225" t="n">
-        <v>11.41979885101318</v>
+        <v>11.41979789733887</v>
       </c>
       <c r="C225" t="n">
-        <v>11.69693201285603</v>
+        <v>11.69693103603816</v>
       </c>
       <c r="D225" t="n">
-        <v>11.36246145827959</v>
+        <v>11.36246050939355</v>
       </c>
       <c r="E225" t="n">
-        <v>11.56314415557002</v>
+        <v>11.56314318992485</v>
       </c>
       <c r="F225" t="n">
         <v>7365800</v>
@@ -4932,16 +4932,16 @@
         <v>44582</v>
       </c>
       <c r="B226" t="n">
-        <v>11.48669242858887</v>
+        <v>11.48669338226318</v>
       </c>
       <c r="C226" t="n">
-        <v>11.63003680603022</v>
+        <v>11.6300377716056</v>
       </c>
       <c r="D226" t="n">
-        <v>11.21911492070173</v>
+        <v>11.21911585216062</v>
       </c>
       <c r="E226" t="n">
-        <v>11.37201583300219</v>
+        <v>11.37201677715557</v>
       </c>
       <c r="F226" t="n">
         <v>8537100</v>
@@ -4952,16 +4952,16 @@
         <v>44585</v>
       </c>
       <c r="B227" t="n">
-        <v>11.50580406188965</v>
+        <v>11.50580501556396</v>
       </c>
       <c r="C227" t="n">
-        <v>11.6395928097279</v>
+        <v>11.63959377449148</v>
       </c>
       <c r="D227" t="n">
-        <v>11.32423446465893</v>
+        <v>11.3242354032836</v>
       </c>
       <c r="E227" t="n">
-        <v>11.4675788355589</v>
+        <v>11.46757978606487</v>
       </c>
       <c r="F227" t="n">
         <v>6551900</v>
@@ -4992,16 +4992,16 @@
         <v>44587</v>
       </c>
       <c r="B229" t="n">
-        <v>11.73515701293945</v>
+        <v>11.73515605926514</v>
       </c>
       <c r="C229" t="n">
-        <v>12.21297286261863</v>
+        <v>12.21297187011393</v>
       </c>
       <c r="D229" t="n">
-        <v>11.73515701293945</v>
+        <v>11.73515605926514</v>
       </c>
       <c r="E229" t="n">
-        <v>11.81160747597921</v>
+        <v>11.81160651609204</v>
       </c>
       <c r="F229" t="n">
         <v>11052300</v>
@@ -5092,16 +5092,16 @@
         <v>44594</v>
       </c>
       <c r="B234" t="n">
-        <v>11.94539451599121</v>
+        <v>11.94539546966553</v>
       </c>
       <c r="C234" t="n">
-        <v>12.27986592698347</v>
+        <v>12.2798669073607</v>
       </c>
       <c r="D234" t="n">
-        <v>11.81160576932205</v>
+        <v>11.81160671231519</v>
       </c>
       <c r="E234" t="n">
-        <v>12.02184496798465</v>
+        <v>12.02184592776248</v>
       </c>
       <c r="F234" t="n">
         <v>9442200</v>
@@ -5112,16 +5112,16 @@
         <v>44595</v>
       </c>
       <c r="B235" t="n">
-        <v>11.94539451599121</v>
+        <v>11.94539546966553</v>
       </c>
       <c r="C235" t="n">
-        <v>12.21297109796826</v>
+        <v>12.21297207300486</v>
       </c>
       <c r="D235" t="n">
-        <v>11.89761275565499</v>
+        <v>11.8976137055146</v>
       </c>
       <c r="E235" t="n">
-        <v>12.04095803666365</v>
+        <v>12.04095899796739</v>
       </c>
       <c r="F235" t="n">
         <v>8796800</v>
@@ -5172,16 +5172,16 @@
         <v>44600</v>
       </c>
       <c r="B238" t="n">
-        <v>11.9549503326416</v>
+        <v>11.95495128631592</v>
       </c>
       <c r="C238" t="n">
-        <v>12.20341474238491</v>
+        <v>12.20341571587981</v>
       </c>
       <c r="D238" t="n">
-        <v>11.83071812776995</v>
+        <v>11.83071907153397</v>
       </c>
       <c r="E238" t="n">
-        <v>12.14607645115137</v>
+        <v>12.14607742007226</v>
       </c>
       <c r="F238" t="n">
         <v>8002100</v>
@@ -5192,16 +5192,16 @@
         <v>44601</v>
       </c>
       <c r="B239" t="n">
-        <v>12.05051422119141</v>
+        <v>12.05051326751709</v>
       </c>
       <c r="C239" t="n">
-        <v>12.28942212264425</v>
+        <v>12.28942115006283</v>
       </c>
       <c r="D239" t="n">
-        <v>11.91672637964906</v>
+        <v>11.91672543656267</v>
       </c>
       <c r="E239" t="n">
-        <v>11.95495160742706</v>
+        <v>11.95495066131554</v>
       </c>
       <c r="F239" t="n">
         <v>9060800</v>
@@ -5272,16 +5272,16 @@
         <v>44607</v>
       </c>
       <c r="B243" t="n">
-        <v>11.63959407806396</v>
+        <v>11.63959312438965</v>
       </c>
       <c r="C243" t="n">
-        <v>11.95495245749671</v>
+        <v>11.95495147798393</v>
       </c>
       <c r="D243" t="n">
-        <v>11.5344740106788</v>
+        <v>11.53447306561735</v>
       </c>
       <c r="E243" t="n">
-        <v>11.92628285110363</v>
+        <v>11.92628187393986</v>
       </c>
       <c r="F243" t="n">
         <v>11329100</v>
@@ -5312,16 +5312,16 @@
         <v>44609</v>
       </c>
       <c r="B245" t="n">
-        <v>12.66211891174316</v>
+        <v>12.66211795806885</v>
       </c>
       <c r="C245" t="n">
-        <v>12.94880857880961</v>
+        <v>12.94880760354266</v>
       </c>
       <c r="D245" t="n">
-        <v>12.46143623593278</v>
+        <v>12.46143529737331</v>
       </c>
       <c r="E245" t="n">
-        <v>12.46143623593278</v>
+        <v>12.46143529737331</v>
       </c>
       <c r="F245" t="n">
         <v>10362100</v>
@@ -5332,16 +5332,16 @@
         <v>44610</v>
       </c>
       <c r="B246" t="n">
-        <v>12.1365213394165</v>
+        <v>12.13652229309082</v>
       </c>
       <c r="C246" t="n">
-        <v>12.83413289291753</v>
+        <v>12.83413390140938</v>
       </c>
       <c r="D246" t="n">
-        <v>12.1365213394165</v>
+        <v>12.13652229309082</v>
       </c>
       <c r="E246" t="n">
-        <v>12.80546328826094</v>
+        <v>12.80546429449997</v>
       </c>
       <c r="F246" t="n">
         <v>11604500</v>
@@ -5352,16 +5352,16 @@
         <v>44613</v>
       </c>
       <c r="B247" t="n">
-        <v>11.90717124938965</v>
+        <v>11.90717029571533</v>
       </c>
       <c r="C247" t="n">
-        <v>12.27986794770807</v>
+        <v>12.27986696418357</v>
       </c>
       <c r="D247" t="n">
-        <v>11.72560162386719</v>
+        <v>11.72560068473523</v>
       </c>
       <c r="E247" t="n">
-        <v>12.1365226431111</v>
+        <v>12.13652167106747</v>
       </c>
       <c r="F247" t="n">
         <v>4718800</v>
@@ -5412,16 +5412,16 @@
         <v>44616</v>
       </c>
       <c r="B250" t="n">
-        <v>12.93925094604492</v>
+        <v>12.93925189971924</v>
       </c>
       <c r="C250" t="n">
-        <v>13.04437008679349</v>
+        <v>13.04437104821551</v>
       </c>
       <c r="D250" t="n">
-        <v>12.21297076079684</v>
+        <v>12.21297166094141</v>
       </c>
       <c r="E250" t="n">
-        <v>12.41365341957957</v>
+        <v>12.41365433451525</v>
       </c>
       <c r="F250" t="n">
         <v>6603100</v>
@@ -5452,16 +5452,16 @@
         <v>44622</v>
       </c>
       <c r="B252" t="n">
-        <v>12.68123245239258</v>
+        <v>12.68123149871826</v>
       </c>
       <c r="C252" t="n">
-        <v>12.95836559486294</v>
+        <v>12.95836462034722</v>
       </c>
       <c r="D252" t="n">
-        <v>12.64300631142708</v>
+        <v>12.6430053606275</v>
       </c>
       <c r="E252" t="n">
-        <v>12.86280206517191</v>
+        <v>12.8628010978429</v>
       </c>
       <c r="F252" t="n">
         <v>4196000</v>
@@ -5472,16 +5472,16 @@
         <v>44623</v>
       </c>
       <c r="B253" t="n">
-        <v>12.56655597686768</v>
+        <v>12.56655502319336</v>
       </c>
       <c r="C253" t="n">
-        <v>12.95836572339823</v>
+        <v>12.95836473998952</v>
       </c>
       <c r="D253" t="n">
-        <v>12.33720459696787</v>
+        <v>12.337203660699</v>
       </c>
       <c r="E253" t="n">
-        <v>12.80546389210365</v>
+        <v>12.80546292029864</v>
       </c>
       <c r="F253" t="n">
         <v>12631200</v>
@@ -5512,16 +5512,16 @@
         <v>44627</v>
       </c>
       <c r="B255" t="n">
-        <v>11.73515701293945</v>
+        <v>11.73515605926514</v>
       </c>
       <c r="C255" t="n">
-        <v>12.17474763109875</v>
+        <v>12.17474664170048</v>
       </c>
       <c r="D255" t="n">
-        <v>11.68737524569925</v>
+        <v>11.68737429590799</v>
       </c>
       <c r="E255" t="n">
-        <v>12.08874063233868</v>
+        <v>12.08873964992988</v>
       </c>
       <c r="F255" t="n">
         <v>12255900</v>
@@ -5552,16 +5552,16 @@
         <v>44629</v>
       </c>
       <c r="B257" t="n">
-        <v>12.80546283721924</v>
+        <v>12.80546379089355</v>
       </c>
       <c r="C257" t="n">
-        <v>13.0348151095869</v>
+        <v>13.03481608034201</v>
       </c>
       <c r="D257" t="n">
-        <v>11.75426864359272</v>
+        <v>11.75426951898038</v>
       </c>
       <c r="E257" t="n">
-        <v>11.89761301638138</v>
+        <v>11.89761390244447</v>
       </c>
       <c r="F257" t="n">
         <v>14771600</v>
@@ -5632,16 +5632,16 @@
         <v>44635</v>
       </c>
       <c r="B261" t="n">
-        <v>12.82457637786865</v>
+        <v>12.82457542419434</v>
       </c>
       <c r="C261" t="n">
-        <v>12.90102683434848</v>
+        <v>12.90102587498907</v>
       </c>
       <c r="D261" t="n">
-        <v>12.29897880604886</v>
+        <v>12.29897789145957</v>
       </c>
       <c r="E261" t="n">
-        <v>12.29897880604886</v>
+        <v>12.29897789145957</v>
       </c>
       <c r="F261" t="n">
         <v>8181800</v>
@@ -5712,16 +5712,16 @@
         <v>44641</v>
       </c>
       <c r="B265" t="n">
-        <v>13.56041240692139</v>
+        <v>13.56041145324707</v>
       </c>
       <c r="C265" t="n">
-        <v>13.62730724063966</v>
+        <v>13.62730628226077</v>
       </c>
       <c r="D265" t="n">
-        <v>13.18771665509124</v>
+        <v>13.1877157276278</v>
       </c>
       <c r="E265" t="n">
-        <v>13.58908201195551</v>
+        <v>13.58908105626492</v>
       </c>
       <c r="F265" t="n">
         <v>3916100</v>
@@ -5732,16 +5732,16 @@
         <v>44642</v>
       </c>
       <c r="B266" t="n">
-        <v>14.08600902557373</v>
+        <v>14.08600997924805</v>
       </c>
       <c r="C266" t="n">
-        <v>14.26757953297927</v>
+        <v>14.26758049894657</v>
       </c>
       <c r="D266" t="n">
-        <v>13.62730631260216</v>
+        <v>13.62730723522063</v>
       </c>
       <c r="E266" t="n">
-        <v>13.66553153868313</v>
+        <v>13.66553246388958</v>
       </c>
       <c r="F266" t="n">
         <v>13737200</v>
@@ -5752,16 +5752,16 @@
         <v>44643</v>
       </c>
       <c r="B267" t="n">
-        <v>14.38225746154785</v>
+        <v>14.38225650787354</v>
       </c>
       <c r="C267" t="n">
-        <v>14.59249669356896</v>
+        <v>14.59249572595387</v>
       </c>
       <c r="D267" t="n">
-        <v>13.87577290888745</v>
+        <v>13.87577198879766</v>
       </c>
       <c r="E267" t="n">
-        <v>14.02867383713501</v>
+        <v>14.0286729069065</v>
       </c>
       <c r="F267" t="n">
         <v>8813400</v>
@@ -5792,16 +5792,16 @@
         <v>44645</v>
       </c>
       <c r="B269" t="n">
-        <v>15.13720512390137</v>
+        <v>15.13720321655273</v>
       </c>
       <c r="C269" t="n">
-        <v>15.24232427482575</v>
+        <v>15.24232235423169</v>
       </c>
       <c r="D269" t="n">
-        <v>14.64027624019771</v>
+        <v>14.64027439546411</v>
       </c>
       <c r="E269" t="n">
-        <v>14.71672669748114</v>
+        <v>14.71672484311448</v>
       </c>
       <c r="F269" t="n">
         <v>8426200</v>
@@ -5832,16 +5832,16 @@
         <v>44649</v>
       </c>
       <c r="B271" t="n">
-        <v>15.50034523010254</v>
+        <v>15.50034427642822</v>
       </c>
       <c r="C271" t="n">
-        <v>15.93038021620936</v>
+        <v>15.93037923607671</v>
       </c>
       <c r="D271" t="n">
-        <v>15.43345130397987</v>
+        <v>15.43345035442127</v>
       </c>
       <c r="E271" t="n">
-        <v>15.72969661511858</v>
+        <v>15.72969564733319</v>
       </c>
       <c r="F271" t="n">
         <v>7323700</v>
@@ -5852,16 +5852,16 @@
         <v>44650</v>
       </c>
       <c r="B272" t="n">
-        <v>15.45256328582764</v>
+        <v>15.45256423950195</v>
       </c>
       <c r="C272" t="n">
-        <v>15.82525903236704</v>
+        <v>15.82526000904275</v>
       </c>
       <c r="D272" t="n">
-        <v>15.39522589929603</v>
+        <v>15.3952268494317</v>
       </c>
       <c r="E272" t="n">
-        <v>15.51945720723495</v>
+        <v>15.51945816503771</v>
       </c>
       <c r="F272" t="n">
         <v>8944100</v>
@@ -5872,16 +5872,16 @@
         <v>44651</v>
       </c>
       <c r="B273" t="n">
-        <v>15.56723976135254</v>
+        <v>15.56724071502686</v>
       </c>
       <c r="C273" t="n">
-        <v>15.81570237531094</v>
+        <v>15.81570334420647</v>
       </c>
       <c r="D273" t="n">
-        <v>15.42389356204693</v>
+        <v>15.42389450693963</v>
       </c>
       <c r="E273" t="n">
-        <v>15.42389356204693</v>
+        <v>15.42389450693963</v>
       </c>
       <c r="F273" t="n">
         <v>17319900</v>
@@ -5912,16 +5912,16 @@
         <v>44655</v>
       </c>
       <c r="B275" t="n">
-        <v>15.56723976135254</v>
+        <v>15.56724071502686</v>
       </c>
       <c r="C275" t="n">
-        <v>15.86348504932035</v>
+        <v>15.86348602114313</v>
       </c>
       <c r="D275" t="n">
-        <v>15.52901362214501</v>
+        <v>15.52901457347753</v>
       </c>
       <c r="E275" t="n">
-        <v>15.75836498922228</v>
+        <v>15.75836595460524</v>
       </c>
       <c r="F275" t="n">
         <v>2672100</v>
@@ -5932,16 +5932,16 @@
         <v>44656</v>
       </c>
       <c r="B276" t="n">
-        <v>15.45256328582764</v>
+        <v>15.45256423950195</v>
       </c>
       <c r="C276" t="n">
-        <v>15.65324505004958</v>
+        <v>15.65324601610922</v>
       </c>
       <c r="D276" t="n">
-        <v>15.35699975979319</v>
+        <v>15.35700070756969</v>
       </c>
       <c r="E276" t="n">
-        <v>15.57679459376655</v>
+        <v>15.57679555510796</v>
       </c>
       <c r="F276" t="n">
         <v>10716200</v>
@@ -5952,16 +5952,16 @@
         <v>44657</v>
       </c>
       <c r="B277" t="n">
-        <v>15.56723976135254</v>
+        <v>15.56724071502686</v>
       </c>
       <c r="C277" t="n">
-        <v>15.70102760313362</v>
+        <v>15.701028565004</v>
       </c>
       <c r="D277" t="n">
-        <v>15.13720480888101</v>
+        <v>15.13720573621069</v>
       </c>
       <c r="E277" t="n">
-        <v>15.38566924556204</v>
+        <v>15.38567018811306</v>
       </c>
       <c r="F277" t="n">
         <v>10924400</v>
@@ -5992,16 +5992,16 @@
         <v>44659</v>
       </c>
       <c r="B279" t="n">
-        <v>15.40478134155273</v>
+        <v>15.40478229522705</v>
       </c>
       <c r="C279" t="n">
-        <v>15.5767934889472</v>
+        <v>15.57679445327038</v>
       </c>
       <c r="D279" t="n">
-        <v>15.07030993551665</v>
+        <v>15.07031086848462</v>
       </c>
       <c r="E279" t="n">
-        <v>15.32833089069213</v>
+        <v>15.32833183963358</v>
       </c>
       <c r="F279" t="n">
         <v>3069100</v>
@@ -6112,16 +6112,16 @@
         <v>44670</v>
       </c>
       <c r="B285" t="n">
-        <v>15.61502170562744</v>
+        <v>15.61502265930176</v>
       </c>
       <c r="C285" t="n">
-        <v>15.77747916318553</v>
+        <v>15.7774801267818</v>
       </c>
       <c r="D285" t="n">
-        <v>15.18498763441659</v>
+        <v>15.18498856182694</v>
       </c>
       <c r="E285" t="n">
-        <v>15.32833293239446</v>
+        <v>15.3283338685595</v>
       </c>
       <c r="F285" t="n">
         <v>7756800</v>
@@ -6132,16 +6132,16 @@
         <v>44671</v>
       </c>
       <c r="B286" t="n">
-        <v>15.85392951965332</v>
+        <v>15.853928565979</v>
       </c>
       <c r="C286" t="n">
-        <v>16.33174535370502</v>
+        <v>16.33174437128826</v>
       </c>
       <c r="D286" t="n">
-        <v>15.72014166939012</v>
+        <v>15.72014072376366</v>
       </c>
       <c r="E286" t="n">
-        <v>15.74880945289066</v>
+        <v>15.74880850553972</v>
       </c>
       <c r="F286" t="n">
         <v>12326800</v>
@@ -6172,16 +6172,16 @@
         <v>44676</v>
       </c>
       <c r="B288" t="n">
-        <v>15.29966259002686</v>
+        <v>15.29966163635254</v>
       </c>
       <c r="C288" t="n">
-        <v>15.4621200397703</v>
+        <v>15.46211907596952</v>
       </c>
       <c r="D288" t="n">
-        <v>15.01297291922304</v>
+        <v>15.01297198341896</v>
       </c>
       <c r="E288" t="n">
-        <v>15.28054952000464</v>
+        <v>15.2805485675217</v>
       </c>
       <c r="F288" t="n">
         <v>6454900</v>
@@ -6192,16 +6192,16 @@
         <v>44677</v>
       </c>
       <c r="B289" t="n">
-        <v>15.12764739990234</v>
+        <v>15.12764835357666</v>
       </c>
       <c r="C289" t="n">
-        <v>15.30921790520048</v>
+        <v>15.30921887032133</v>
       </c>
       <c r="D289" t="n">
-        <v>15.02252825724008</v>
+        <v>15.02252920428749</v>
       </c>
       <c r="E289" t="n">
-        <v>15.21365438542659</v>
+        <v>15.21365534452294</v>
       </c>
       <c r="F289" t="n">
         <v>9387600</v>
@@ -6232,16 +6232,16 @@
         <v>44679</v>
       </c>
       <c r="B291" t="n">
-        <v>14.84095859527588</v>
+        <v>14.8409595489502</v>
       </c>
       <c r="C291" t="n">
-        <v>15.38566923076207</v>
+        <v>15.38567021943929</v>
       </c>
       <c r="D291" t="n">
-        <v>14.84095859527588</v>
+        <v>14.8409595489502</v>
       </c>
       <c r="E291" t="n">
-        <v>15.32833184472857</v>
+        <v>15.3283328297213</v>
       </c>
       <c r="F291" t="n">
         <v>5384600</v>
@@ -6272,16 +6272,16 @@
         <v>44683</v>
       </c>
       <c r="B293" t="n">
-        <v>14.69167041778564</v>
+        <v>14.69167137145996</v>
       </c>
       <c r="C293" t="n">
-        <v>14.97105296602926</v>
+        <v>14.97105393783902</v>
       </c>
       <c r="D293" t="n">
-        <v>14.44118925901314</v>
+        <v>14.44119019642807</v>
       </c>
       <c r="E293" t="n">
-        <v>14.54716255167152</v>
+        <v>14.54716349596546</v>
       </c>
       <c r="F293" t="n">
         <v>5536000</v>
@@ -6372,16 +6372,16 @@
         <v>44690</v>
       </c>
       <c r="B298" t="n">
-        <v>14.2196102142334</v>
+        <v>14.21961116790771</v>
       </c>
       <c r="C298" t="n">
-        <v>14.32558258668562</v>
+        <v>14.32558354746724</v>
       </c>
       <c r="D298" t="n">
-        <v>13.92095946458282</v>
+        <v>13.92096039822737</v>
       </c>
       <c r="E298" t="n">
-        <v>14.04620004225831</v>
+        <v>14.04620098430244</v>
       </c>
       <c r="F298" t="n">
         <v>11844800</v>
@@ -6392,16 +6392,16 @@
         <v>44691</v>
       </c>
       <c r="B299" t="n">
-        <v>14.71093845367432</v>
+        <v>14.71093940734863</v>
       </c>
       <c r="C299" t="n">
-        <v>14.97105279343268</v>
+        <v>14.97105376396958</v>
       </c>
       <c r="D299" t="n">
-        <v>14.14253926099675</v>
+        <v>14.14254017782313</v>
       </c>
       <c r="E299" t="n">
-        <v>14.2196102445369</v>
+        <v>14.21961116635961</v>
       </c>
       <c r="F299" t="n">
         <v>13119700</v>
@@ -6452,16 +6452,16 @@
         <v>44694</v>
       </c>
       <c r="B302" t="n">
-        <v>14.91324901580811</v>
+        <v>14.91325092315674</v>
       </c>
       <c r="C302" t="n">
-        <v>15.09629328979575</v>
+        <v>15.09629522055506</v>
       </c>
       <c r="D302" t="n">
-        <v>14.62423328847366</v>
+        <v>14.62423515885826</v>
       </c>
       <c r="E302" t="n">
-        <v>14.72057155799894</v>
+        <v>14.72057344070485</v>
       </c>
       <c r="F302" t="n">
         <v>5016200</v>
@@ -6492,16 +6492,16 @@
         <v>44698</v>
       </c>
       <c r="B304" t="n">
-        <v>15.25043678283691</v>
+        <v>15.2504358291626</v>
       </c>
       <c r="C304" t="n">
-        <v>15.26970498992616</v>
+        <v>15.26970403504692</v>
       </c>
       <c r="D304" t="n">
-        <v>14.84581362154963</v>
+        <v>14.84581269317811</v>
       </c>
       <c r="E304" t="n">
-        <v>14.84581362154963</v>
+        <v>14.84581269317811</v>
       </c>
       <c r="F304" t="n">
         <v>7407200</v>
@@ -6512,16 +6512,16 @@
         <v>44699</v>
       </c>
       <c r="B305" t="n">
-        <v>14.83617782592773</v>
+        <v>14.83617973327637</v>
       </c>
       <c r="C305" t="n">
-        <v>15.2504350435133</v>
+        <v>15.25043700411911</v>
       </c>
       <c r="D305" t="n">
-        <v>14.81691053979462</v>
+        <v>14.81691244466624</v>
       </c>
       <c r="E305" t="n">
-        <v>15.23116775738018</v>
+        <v>15.23116971550898</v>
       </c>
       <c r="F305" t="n">
         <v>6842800</v>
@@ -6592,16 +6592,16 @@
         <v>44705</v>
       </c>
       <c r="B309" t="n">
-        <v>15.31787300109863</v>
+        <v>15.31787204742432</v>
       </c>
       <c r="C309" t="n">
-        <v>15.34677531047014</v>
+        <v>15.3467743549964</v>
       </c>
       <c r="D309" t="n">
-        <v>14.99995494808117</v>
+        <v>14.99995401420009</v>
       </c>
       <c r="E309" t="n">
-        <v>15.19263333552333</v>
+        <v>15.1926323896463</v>
       </c>
       <c r="F309" t="n">
         <v>5652100</v>
@@ -6832,16 +6832,16 @@
         <v>44721</v>
       </c>
       <c r="B321" t="n">
-        <v>15.02885627746582</v>
+        <v>15.02885723114014</v>
       </c>
       <c r="C321" t="n">
-        <v>15.50091627464848</v>
+        <v>15.50091725827793</v>
       </c>
       <c r="D321" t="n">
-        <v>14.76874102263543</v>
+        <v>14.76874195980382</v>
       </c>
       <c r="E321" t="n">
-        <v>15.38530980097672</v>
+        <v>15.38531077727023</v>
       </c>
       <c r="F321" t="n">
         <v>9688900</v>
@@ -6852,16 +6852,16 @@
         <v>44722</v>
       </c>
       <c r="B322" t="n">
-        <v>14.48935890197754</v>
+        <v>14.48935985565186</v>
       </c>
       <c r="C322" t="n">
-        <v>15.01922261074923</v>
+        <v>15.01922359929862</v>
       </c>
       <c r="D322" t="n">
-        <v>14.22924455835858</v>
+        <v>14.22924549491244</v>
       </c>
       <c r="E322" t="n">
-        <v>14.85544653860601</v>
+        <v>14.85544751637582</v>
       </c>
       <c r="F322" t="n">
         <v>15101900</v>
@@ -6872,16 +6872,16 @@
         <v>44725</v>
       </c>
       <c r="B323" t="n">
-        <v>14.03656673431396</v>
+        <v>14.03656578063965</v>
       </c>
       <c r="C323" t="n">
-        <v>14.35448478842786</v>
+        <v>14.35448381315351</v>
       </c>
       <c r="D323" t="n">
-        <v>13.89205886199261</v>
+        <v>13.89205791813647</v>
       </c>
       <c r="E323" t="n">
-        <v>14.25814651313317</v>
+        <v>14.25814554440425</v>
       </c>
       <c r="F323" t="n">
         <v>9104400</v>
@@ -6912,16 +6912,16 @@
         <v>44727</v>
       </c>
       <c r="B325" t="n">
-        <v>14.91324901580811</v>
+        <v>14.91325092315674</v>
       </c>
       <c r="C325" t="n">
-        <v>15.06739190081403</v>
+        <v>15.06739382787696</v>
       </c>
       <c r="D325" t="n">
-        <v>14.25814565925695</v>
+        <v>14.25814748282032</v>
       </c>
       <c r="E325" t="n">
-        <v>14.34485074496072</v>
+        <v>14.34485257961335</v>
       </c>
       <c r="F325" t="n">
         <v>25461900</v>
@@ -6952,16 +6952,16 @@
         <v>44732</v>
       </c>
       <c r="B327" t="n">
-        <v>15.31787300109863</v>
+        <v>15.31787204742432</v>
       </c>
       <c r="C327" t="n">
-        <v>15.50091728541696</v>
+        <v>15.5009163203465</v>
       </c>
       <c r="D327" t="n">
-        <v>14.83617887001052</v>
+        <v>14.83617794632596</v>
       </c>
       <c r="E327" t="n">
-        <v>15.09629414180225</v>
+        <v>15.09629320192319</v>
       </c>
       <c r="F327" t="n">
         <v>7611300</v>
@@ -6972,16 +6972,16 @@
         <v>44733</v>
       </c>
       <c r="B328" t="n">
-        <v>14.84581184387207</v>
+        <v>14.84581279754639</v>
       </c>
       <c r="C328" t="n">
-        <v>15.64542396715431</v>
+        <v>15.6454249721946</v>
       </c>
       <c r="D328" t="n">
-        <v>14.81691045545762</v>
+        <v>14.81691140727535</v>
       </c>
       <c r="E328" t="n">
-        <v>15.37567553151609</v>
+        <v>15.37567651922811</v>
       </c>
       <c r="F328" t="n">
         <v>9398400</v>
@@ -7092,16 +7092,16 @@
         <v>44741</v>
       </c>
       <c r="B334" t="n">
-        <v>13.85352420806885</v>
+        <v>13.85352325439453</v>
       </c>
       <c r="C334" t="n">
-        <v>14.18107638519945</v>
+        <v>14.1810754089765</v>
       </c>
       <c r="D334" t="n">
-        <v>13.59340891960912</v>
+        <v>13.5934079838411</v>
       </c>
       <c r="E334" t="n">
-        <v>14.18107638519945</v>
+        <v>14.1810754089765</v>
       </c>
       <c r="F334" t="n">
         <v>8408900</v>
@@ -7292,16 +7292,16 @@
         <v>44755</v>
       </c>
       <c r="B344" t="n">
-        <v>14.77837562561035</v>
+        <v>14.77837657928467</v>
       </c>
       <c r="C344" t="n">
-        <v>15.01922268360593</v>
+        <v>15.01922365282253</v>
       </c>
       <c r="D344" t="n">
-        <v>14.44118937691309</v>
+        <v>14.44119030882819</v>
       </c>
       <c r="E344" t="n">
-        <v>14.58569816296561</v>
+        <v>14.58569910420611</v>
       </c>
       <c r="F344" t="n">
         <v>3964800</v>
@@ -7392,16 +7392,16 @@
         <v>44762</v>
       </c>
       <c r="B349" t="n">
-        <v>14.82654571533203</v>
+        <v>14.82654476165771</v>
       </c>
       <c r="C349" t="n">
-        <v>15.10592827517219</v>
+        <v>15.10592730352741</v>
       </c>
       <c r="D349" t="n">
-        <v>14.57606454616261</v>
+        <v>14.57606360859976</v>
       </c>
       <c r="E349" t="n">
-        <v>14.89398259981663</v>
+        <v>14.89398164180463</v>
       </c>
       <c r="F349" t="n">
         <v>5599700</v>
@@ -7412,16 +7412,16 @@
         <v>44763</v>
       </c>
       <c r="B350" t="n">
-        <v>14.84581184387207</v>
+        <v>14.84581279754639</v>
       </c>
       <c r="C350" t="n">
-        <v>14.95178513265602</v>
+        <v>14.95178609313791</v>
       </c>
       <c r="D350" t="n">
-        <v>14.6049647966483</v>
+        <v>14.60496573485093</v>
       </c>
       <c r="E350" t="n">
-        <v>14.7494735762377</v>
+        <v>14.74947452372338</v>
       </c>
       <c r="F350" t="n">
         <v>4662200</v>
@@ -7432,16 +7432,16 @@
         <v>44764</v>
       </c>
       <c r="B351" t="n">
-        <v>15.0770263671875</v>
+        <v>15.07702541351318</v>
       </c>
       <c r="C351" t="n">
-        <v>15.14446417222636</v>
+        <v>15.14446321428636</v>
       </c>
       <c r="D351" t="n">
-        <v>14.78801061526745</v>
+        <v>14.78800967987438</v>
       </c>
       <c r="E351" t="n">
-        <v>14.84581339814799</v>
+        <v>14.8458124590987</v>
       </c>
       <c r="F351" t="n">
         <v>3071000</v>
@@ -7492,16 +7492,16 @@
         <v>44769</v>
       </c>
       <c r="B354" t="n">
-        <v>15.7610330581665</v>
+        <v>15.76103210449219</v>
       </c>
       <c r="C354" t="n">
-        <v>15.93444324487276</v>
+        <v>15.93444228070568</v>
       </c>
       <c r="D354" t="n">
-        <v>15.03849091980999</v>
+        <v>15.03849000985551</v>
       </c>
       <c r="E354" t="n">
-        <v>15.04812502324004</v>
+        <v>15.04812411270262</v>
       </c>
       <c r="F354" t="n">
         <v>22102600</v>
@@ -7572,16 +7572,16 @@
         <v>44775</v>
       </c>
       <c r="B358" t="n">
-        <v>15.09629440307617</v>
+        <v>15.09629344940186</v>
       </c>
       <c r="C358" t="n">
-        <v>15.2119008862871</v>
+        <v>15.21189992530961</v>
       </c>
       <c r="D358" t="n">
-        <v>14.80727773566952</v>
+        <v>14.80727680025318</v>
       </c>
       <c r="E358" t="n">
-        <v>15.04812480538195</v>
+        <v>15.04812385475064</v>
       </c>
       <c r="F358" t="n">
         <v>7865200</v>
@@ -7592,16 +7592,16 @@
         <v>44776</v>
       </c>
       <c r="B359" t="n">
-        <v>15.95370864868164</v>
+        <v>15.95370960235596</v>
       </c>
       <c r="C359" t="n">
-        <v>16.00187916291658</v>
+        <v>16.00188011947041</v>
       </c>
       <c r="D359" t="n">
-        <v>15.06739231820699</v>
+        <v>15.06739321889945</v>
       </c>
       <c r="E359" t="n">
-        <v>15.12519509777168</v>
+        <v>15.12519600191945</v>
       </c>
       <c r="F359" t="n">
         <v>9465300</v>
@@ -7632,16 +7632,16 @@
         <v>44778</v>
       </c>
       <c r="B361" t="n">
-        <v>16.40650177001953</v>
+        <v>16.40650367736816</v>
       </c>
       <c r="C361" t="n">
-        <v>16.57027783814425</v>
+        <v>16.57027976453278</v>
       </c>
       <c r="D361" t="n">
-        <v>16.10785010386923</v>
+        <v>16.10785197649791</v>
       </c>
       <c r="E361" t="n">
-        <v>16.26199206945518</v>
+        <v>16.26199396000374</v>
       </c>
       <c r="F361" t="n">
         <v>6244900</v>
@@ -7652,16 +7652,16 @@
         <v>44781</v>
       </c>
       <c r="B362" t="n">
-        <v>16.68588256835938</v>
+        <v>16.68588638305664</v>
       </c>
       <c r="C362" t="n">
-        <v>16.88819503663362</v>
+        <v>16.88819889758321</v>
       </c>
       <c r="D362" t="n">
-        <v>16.26199126520336</v>
+        <v>16.26199498299134</v>
       </c>
       <c r="E362" t="n">
-        <v>16.53174061039666</v>
+        <v>16.53174438985426</v>
       </c>
       <c r="F362" t="n">
         <v>10381400</v>
@@ -7692,16 +7692,16 @@
         <v>44783</v>
       </c>
       <c r="B364" t="n">
-        <v>16.89783096313477</v>
+        <v>16.89782905578613</v>
       </c>
       <c r="C364" t="n">
-        <v>17.20611491234526</v>
+        <v>17.20611297019896</v>
       </c>
       <c r="D364" t="n">
-        <v>16.73405488542704</v>
+        <v>16.73405299656468</v>
       </c>
       <c r="E364" t="n">
-        <v>17.1675784999353</v>
+        <v>17.16757656213882</v>
       </c>
       <c r="F364" t="n">
         <v>6533000</v>
@@ -7712,16 +7712,16 @@
         <v>44784</v>
       </c>
       <c r="B365" t="n">
-        <v>16.99416732788086</v>
+        <v>16.99417114257812</v>
       </c>
       <c r="C365" t="n">
-        <v>17.34098766927179</v>
+        <v>17.34099156182016</v>
       </c>
       <c r="D365" t="n">
-        <v>16.86892766988812</v>
+        <v>16.86893145647272</v>
       </c>
       <c r="E365" t="n">
-        <v>16.91709634507367</v>
+        <v>16.91710014247074</v>
       </c>
       <c r="F365" t="n">
         <v>8667500</v>
@@ -7852,16 +7852,16 @@
         <v>44795</v>
       </c>
       <c r="B372" t="n">
-        <v>17.36025810241699</v>
+        <v>17.36025619506836</v>
       </c>
       <c r="C372" t="n">
-        <v>17.45659730266971</v>
+        <v>17.45659538473642</v>
       </c>
       <c r="D372" t="n">
-        <v>16.82075931600872</v>
+        <v>16.82075746793411</v>
       </c>
       <c r="E372" t="n">
-        <v>16.98453540518312</v>
+        <v>16.98453353911465</v>
       </c>
       <c r="F372" t="n">
         <v>10077700</v>
@@ -7872,16 +7872,16 @@
         <v>44796</v>
       </c>
       <c r="B373" t="n">
-        <v>17.20611572265625</v>
+        <v>17.20611381530762</v>
       </c>
       <c r="C373" t="n">
-        <v>17.7937813394455</v>
+        <v>17.7937793669524</v>
       </c>
       <c r="D373" t="n">
-        <v>17.10977652461162</v>
+        <v>17.10977462794247</v>
       </c>
       <c r="E373" t="n">
-        <v>17.49513147927278</v>
+        <v>17.49512953988589</v>
       </c>
       <c r="F373" t="n">
         <v>12142000</v>
@@ -7892,16 +7892,16 @@
         <v>44797</v>
       </c>
       <c r="B374" t="n">
-        <v>17.14831161499023</v>
+        <v>17.1483097076416</v>
       </c>
       <c r="C374" t="n">
-        <v>17.26391902361024</v>
+        <v>17.26391710340299</v>
       </c>
       <c r="D374" t="n">
-        <v>16.99416962850851</v>
+        <v>16.99416773830457</v>
       </c>
       <c r="E374" t="n">
-        <v>17.14831161499023</v>
+        <v>17.1483097076416</v>
       </c>
       <c r="F374" t="n">
         <v>5807100</v>
@@ -7912,16 +7912,16 @@
         <v>44798</v>
       </c>
       <c r="B375" t="n">
-        <v>17.29282188415527</v>
+        <v>17.29281997680664</v>
       </c>
       <c r="C375" t="n">
-        <v>17.32172235908974</v>
+        <v>17.32172044855347</v>
       </c>
       <c r="D375" t="n">
-        <v>16.98453606388697</v>
+        <v>16.98453419054138</v>
       </c>
       <c r="E375" t="n">
-        <v>17.19648268016627</v>
+        <v>17.19648078344358</v>
       </c>
       <c r="F375" t="n">
         <v>6074000</v>
@@ -7932,16 +7932,16 @@
         <v>44799</v>
       </c>
       <c r="B376" t="n">
-        <v>17.29282188415527</v>
+        <v>17.29281997680664</v>
       </c>
       <c r="C376" t="n">
-        <v>17.41806156307874</v>
+        <v>17.41805964191653</v>
       </c>
       <c r="D376" t="n">
-        <v>17.10977758032792</v>
+        <v>17.10977569316855</v>
       </c>
       <c r="E376" t="n">
-        <v>17.30245415078844</v>
+        <v>17.3024522423774</v>
       </c>
       <c r="F376" t="n">
         <v>3647900</v>
@@ -8052,16 +8052,16 @@
         <v>44809</v>
       </c>
       <c r="B382" t="n">
-        <v>18.73790168762207</v>
+        <v>18.7379035949707</v>
       </c>
       <c r="C382" t="n">
-        <v>18.91131002438889</v>
+        <v>18.91131194938891</v>
       </c>
       <c r="D382" t="n">
-        <v>18.12133197488807</v>
+        <v>18.12133381947549</v>
       </c>
       <c r="E382" t="n">
-        <v>18.39108133905402</v>
+        <v>18.39108321109948</v>
       </c>
       <c r="F382" t="n">
         <v>11861400</v>
@@ -8072,16 +8072,16 @@
         <v>44810</v>
       </c>
       <c r="B383" t="n">
-        <v>18.75716781616211</v>
+        <v>18.75716972351074</v>
       </c>
       <c r="C383" t="n">
-        <v>18.83423879958045</v>
+        <v>18.83424071476615</v>
       </c>
       <c r="D383" t="n">
-        <v>18.33327832611984</v>
+        <v>18.33328019036468</v>
       </c>
       <c r="E383" t="n">
-        <v>18.68973093536071</v>
+        <v>18.68973283585193</v>
       </c>
       <c r="F383" t="n">
         <v>7863100</v>
@@ -8092,16 +8092,16 @@
         <v>44812</v>
       </c>
       <c r="B384" t="n">
-        <v>18.40071678161621</v>
+        <v>18.40071487426758</v>
       </c>
       <c r="C384" t="n">
-        <v>18.94984781515502</v>
+        <v>18.94984585088554</v>
       </c>
       <c r="D384" t="n">
-        <v>18.34291399848511</v>
+        <v>18.3429120971281</v>
       </c>
       <c r="E384" t="n">
-        <v>18.91131140138939</v>
+        <v>18.91130944111445</v>
       </c>
       <c r="F384" t="n">
         <v>6653400</v>
@@ -8152,16 +8152,16 @@
         <v>44817</v>
       </c>
       <c r="B387" t="n">
-        <v>17.48549842834473</v>
+        <v>17.48549652099609</v>
       </c>
       <c r="C387" t="n">
-        <v>17.84195293131323</v>
+        <v>17.84195098508192</v>
       </c>
       <c r="D387" t="n">
-        <v>17.32172233306473</v>
+        <v>17.32172044358108</v>
       </c>
       <c r="E387" t="n">
-        <v>17.64927452362472</v>
+        <v>17.64927259841111</v>
       </c>
       <c r="F387" t="n">
         <v>10161300</v>
@@ -8192,16 +8192,16 @@
         <v>44819</v>
       </c>
       <c r="B389" t="n">
-        <v>17.6203727722168</v>
+        <v>17.62037086486816</v>
       </c>
       <c r="C389" t="n">
-        <v>17.84195163874396</v>
+        <v>17.84194970741013</v>
       </c>
       <c r="D389" t="n">
-        <v>17.48549716159898</v>
+        <v>17.4854952688502</v>
       </c>
       <c r="E389" t="n">
-        <v>17.69744376220526</v>
+        <v>17.69744184651394</v>
       </c>
       <c r="F389" t="n">
         <v>7203900</v>
@@ -8292,16 +8292,16 @@
         <v>44826</v>
       </c>
       <c r="B394" t="n">
-        <v>17.36025810241699</v>
+        <v>17.36025619506836</v>
       </c>
       <c r="C394" t="n">
-        <v>17.88048684375383</v>
+        <v>17.88048487924835</v>
       </c>
       <c r="D394" t="n">
-        <v>16.94600082759248</v>
+        <v>16.94599896575775</v>
       </c>
       <c r="E394" t="n">
-        <v>17.66854207321177</v>
+        <v>17.66854013199238</v>
       </c>
       <c r="F394" t="n">
         <v>12903600</v>
@@ -8372,16 +8372,16 @@
         <v>44832</v>
       </c>
       <c r="B398" t="n">
-        <v>17.29282188415527</v>
+        <v>17.29281997680664</v>
       </c>
       <c r="C398" t="n">
-        <v>17.36025877569233</v>
+        <v>17.3602568609056</v>
       </c>
       <c r="D398" t="n">
-        <v>16.9749037972538</v>
+        <v>16.97490192497062</v>
       </c>
       <c r="E398" t="n">
-        <v>17.13867989277986</v>
+        <v>17.13867800243265</v>
       </c>
       <c r="F398" t="n">
         <v>11092900</v>
@@ -8392,16 +8392,16 @@
         <v>44833</v>
       </c>
       <c r="B399" t="n">
-        <v>17.29282188415527</v>
+        <v>17.29281997680664</v>
       </c>
       <c r="C399" t="n">
-        <v>17.45659797968133</v>
+        <v>17.45659605426867</v>
       </c>
       <c r="D399" t="n">
-        <v>16.95563558895251</v>
+        <v>16.95563371879456</v>
       </c>
       <c r="E399" t="n">
-        <v>17.11941168447856</v>
+        <v>17.11940979625658</v>
       </c>
       <c r="F399" t="n">
         <v>8404000</v>
@@ -8452,16 +8452,16 @@
         <v>44838</v>
       </c>
       <c r="B402" t="n">
-        <v>17.41806030273438</v>
+        <v>17.41805839538574</v>
       </c>
       <c r="C402" t="n">
-        <v>18.07316463743626</v>
+        <v>18.07316265835103</v>
       </c>
       <c r="D402" t="n">
-        <v>17.33135520916987</v>
+        <v>17.3313533113158</v>
       </c>
       <c r="E402" t="n">
-        <v>17.98645954387175</v>
+        <v>17.98645757428108</v>
       </c>
       <c r="F402" t="n">
         <v>18594600</v>
@@ -8512,16 +8512,16 @@
         <v>44841</v>
       </c>
       <c r="B405" t="n">
-        <v>17.49513053894043</v>
+        <v>17.4951286315918</v>
       </c>
       <c r="C405" t="n">
-        <v>17.68780892467357</v>
+        <v>17.68780699631881</v>
       </c>
       <c r="D405" t="n">
-        <v>17.32172035928406</v>
+        <v>17.3217184708409</v>
       </c>
       <c r="E405" t="n">
-        <v>17.44696186126578</v>
+        <v>17.44695995916858</v>
       </c>
       <c r="F405" t="n">
         <v>11897600</v>
@@ -8532,16 +8532,16 @@
         <v>44844</v>
       </c>
       <c r="B406" t="n">
-        <v>18.10206604003906</v>
+        <v>18.10206413269043</v>
       </c>
       <c r="C406" t="n">
-        <v>18.12133240846265</v>
+        <v>18.12133049908399</v>
       </c>
       <c r="D406" t="n">
-        <v>17.58183550473985</v>
+        <v>17.58183365220601</v>
       </c>
       <c r="E406" t="n">
-        <v>17.73597747723208</v>
+        <v>17.73597560845686</v>
       </c>
       <c r="F406" t="n">
         <v>7333800</v>
@@ -8552,16 +8552,16 @@
         <v>44845</v>
       </c>
       <c r="B407" t="n">
-        <v>18.32364463806152</v>
+        <v>18.32364654541016</v>
       </c>
       <c r="C407" t="n">
-        <v>18.59339216736995</v>
+        <v>18.5933941027972</v>
       </c>
       <c r="D407" t="n">
-        <v>17.85158462425454</v>
+        <v>17.8515864824654</v>
       </c>
       <c r="E407" t="n">
-        <v>18.15023446206769</v>
+        <v>18.15023635136567</v>
       </c>
       <c r="F407" t="n">
         <v>12287200</v>
@@ -8572,16 +8572,16 @@
         <v>44847</v>
       </c>
       <c r="B408" t="n">
-        <v>18.75716781616211</v>
+        <v>18.75716972351074</v>
       </c>
       <c r="C408" t="n">
-        <v>18.99801486903407</v>
+        <v>18.99801680087357</v>
       </c>
       <c r="D408" t="n">
-        <v>17.93828930641119</v>
+        <v>17.93829113049103</v>
       </c>
       <c r="E408" t="n">
-        <v>18.17913635928316</v>
+        <v>18.17913820785386</v>
       </c>
       <c r="F408" t="n">
         <v>20665700</v>
@@ -8592,16 +8592,16 @@
         <v>44848</v>
       </c>
       <c r="B409" t="n">
-        <v>18.39108276367188</v>
+        <v>18.39108085632324</v>
       </c>
       <c r="C409" t="n">
-        <v>18.9402137997635</v>
+        <v>18.94021183546421</v>
       </c>
       <c r="D409" t="n">
-        <v>18.29474356632728</v>
+        <v>18.29474166897004</v>
       </c>
       <c r="E409" t="n">
-        <v>18.80534002599148</v>
+        <v>18.80533807568002</v>
       </c>
       <c r="F409" t="n">
         <v>11391600</v>
@@ -8612,16 +8612,16 @@
         <v>44851</v>
       </c>
       <c r="B410" t="n">
-        <v>19.01728248596191</v>
+        <v>19.01728439331055</v>
       </c>
       <c r="C410" t="n">
-        <v>19.06545299755645</v>
+        <v>19.06545490973637</v>
       </c>
       <c r="D410" t="n">
-        <v>18.3621782284133</v>
+        <v>18.3621800700579</v>
       </c>
       <c r="E410" t="n">
-        <v>18.49705382336087</v>
+        <v>18.49705567853288</v>
       </c>
       <c r="F410" t="n">
         <v>20683400</v>
@@ -8692,16 +8692,16 @@
         <v>44855</v>
       </c>
       <c r="B414" t="n">
-        <v>17.91902351379395</v>
+        <v>17.91902160644531</v>
       </c>
       <c r="C414" t="n">
-        <v>18.25620980071688</v>
+        <v>18.25620785747724</v>
       </c>
       <c r="D414" t="n">
-        <v>17.34099014157141</v>
+        <v>17.34098829575019</v>
       </c>
       <c r="E414" t="n">
-        <v>17.53366854481807</v>
+        <v>17.53366667848764</v>
       </c>
       <c r="F414" t="n">
         <v>27105700</v>
@@ -8732,16 +8732,16 @@
         <v>44859</v>
       </c>
       <c r="B416" t="n">
-        <v>17.04233932495117</v>
+        <v>17.04233741760254</v>
       </c>
       <c r="C416" t="n">
-        <v>18.00572761270958</v>
+        <v>18.00572559754023</v>
       </c>
       <c r="D416" t="n">
-        <v>16.80149225301157</v>
+        <v>16.80149037261812</v>
       </c>
       <c r="E416" t="n">
-        <v>18.00572761270958</v>
+        <v>18.00572559754023</v>
       </c>
       <c r="F416" t="n">
         <v>27810400</v>
@@ -8752,16 +8752,16 @@
         <v>44860</v>
       </c>
       <c r="B417" t="n">
-        <v>16.45466995239258</v>
+        <v>16.45467185974121</v>
       </c>
       <c r="C417" t="n">
-        <v>17.07123779627069</v>
+        <v>17.07123977508899</v>
       </c>
       <c r="D417" t="n">
-        <v>16.36796486965758</v>
+        <v>16.36796676695576</v>
       </c>
       <c r="E417" t="n">
-        <v>17.0423373270371</v>
+        <v>17.0423393025054</v>
       </c>
       <c r="F417" t="n">
         <v>12823000</v>
@@ -8932,16 +8932,16 @@
         <v>44874</v>
       </c>
       <c r="B426" t="n">
-        <v>19.65312194824219</v>
+        <v>19.65312004089355</v>
       </c>
       <c r="C426" t="n">
-        <v>20.09628154420435</v>
+        <v>20.09627959384678</v>
       </c>
       <c r="D426" t="n">
-        <v>19.13289319539329</v>
+        <v>19.1328913385332</v>
       </c>
       <c r="E426" t="n">
-        <v>19.13289319539329</v>
+        <v>19.1328913385332</v>
       </c>
       <c r="F426" t="n">
         <v>19633400</v>
@@ -8992,16 +8992,16 @@
         <v>44879</v>
       </c>
       <c r="B429" t="n">
-        <v>18.88241004943848</v>
+        <v>18.88241195678711</v>
       </c>
       <c r="C429" t="n">
-        <v>19.19069399514078</v>
+        <v>19.19069593362977</v>
       </c>
       <c r="D429" t="n">
-        <v>18.47778691132489</v>
+        <v>18.47778877780176</v>
       </c>
       <c r="E429" t="n">
-        <v>18.87277594644562</v>
+        <v>18.87277785282109</v>
       </c>
       <c r="F429" t="n">
         <v>8802100</v>
@@ -9052,16 +9052,16 @@
         <v>44883</v>
       </c>
       <c r="B432" t="n">
-        <v>18.44888305664062</v>
+        <v>18.44888496398926</v>
       </c>
       <c r="C432" t="n">
-        <v>19.02691632516161</v>
+        <v>19.02691829227056</v>
       </c>
       <c r="D432" t="n">
-        <v>18.44888305664062</v>
+        <v>18.44888496398926</v>
       </c>
       <c r="E432" t="n">
-        <v>18.78606928307096</v>
+        <v>18.78607122527979</v>
       </c>
       <c r="F432" t="n">
         <v>9969800</v>
@@ -9072,16 +9072,16 @@
         <v>44886</v>
       </c>
       <c r="B433" t="n">
-        <v>18.98838043212891</v>
+        <v>18.98838233947754</v>
       </c>
       <c r="C433" t="n">
-        <v>19.02691684191824</v>
+        <v>19.02691875313779</v>
       </c>
       <c r="D433" t="n">
-        <v>18.58375915444382</v>
+        <v>18.58376102114898</v>
       </c>
       <c r="E433" t="n">
-        <v>18.60302552182134</v>
+        <v>18.60302739046176</v>
       </c>
       <c r="F433" t="n">
         <v>10461100</v>
@@ -9092,16 +9092,16 @@
         <v>44887</v>
       </c>
       <c r="B434" t="n">
-        <v>18.75716781616211</v>
+        <v>18.75716972351074</v>
       </c>
       <c r="C434" t="n">
-        <v>19.39300388874271</v>
+        <v>19.39300586074722</v>
       </c>
       <c r="D434" t="n">
-        <v>18.62229405455931</v>
+        <v>18.62229594819312</v>
       </c>
       <c r="E434" t="n">
-        <v>19.07508585245241</v>
+        <v>19.07508779212898</v>
       </c>
       <c r="F434" t="n">
         <v>9653000</v>
@@ -9152,16 +9152,16 @@
         <v>44890</v>
       </c>
       <c r="B437" t="n">
-        <v>18.50668716430664</v>
+        <v>18.50668907165527</v>
       </c>
       <c r="C437" t="n">
-        <v>19.16179145994887</v>
+        <v>19.1617934348143</v>
       </c>
       <c r="D437" t="n">
-        <v>18.41998391342904</v>
+        <v>18.4199858118418</v>
       </c>
       <c r="E437" t="n">
-        <v>19.16179145994887</v>
+        <v>19.1617934348143</v>
       </c>
       <c r="F437" t="n">
         <v>6509300</v>
@@ -9192,16 +9192,16 @@
         <v>44894</v>
       </c>
       <c r="B439" t="n">
-        <v>18.68973159790039</v>
+        <v>18.68972969055176</v>
       </c>
       <c r="C439" t="n">
-        <v>18.98838143954377</v>
+        <v>18.98837950171693</v>
       </c>
       <c r="D439" t="n">
-        <v>18.29474256418963</v>
+        <v>18.29474069715092</v>
       </c>
       <c r="E439" t="n">
-        <v>18.53558962559947</v>
+        <v>18.53558773398153</v>
       </c>
       <c r="F439" t="n">
         <v>13403400</v>
@@ -9212,16 +9212,16 @@
         <v>44895</v>
       </c>
       <c r="B440" t="n">
-        <v>19.31593132019043</v>
+        <v>19.31593322753906</v>
       </c>
       <c r="C440" t="n">
-        <v>19.38337003297476</v>
+        <v>19.38337194698261</v>
       </c>
       <c r="D440" t="n">
-        <v>18.1598666637861</v>
+        <v>18.15986845697931</v>
       </c>
       <c r="E440" t="n">
-        <v>18.30437451614701</v>
+        <v>18.30437632360963</v>
       </c>
       <c r="F440" t="n">
         <v>128079800</v>
@@ -9252,16 +9252,16 @@
         <v>44897</v>
       </c>
       <c r="B442" t="n">
-        <v>19.78799629211426</v>
+        <v>19.78799438476562</v>
       </c>
       <c r="C442" t="n">
-        <v>19.97103874358669</v>
+        <v>19.97103681859475</v>
       </c>
       <c r="D442" t="n">
-        <v>19.01728456019369</v>
+        <v>19.01728272713333</v>
       </c>
       <c r="E442" t="n">
-        <v>19.11362375637343</v>
+        <v>19.11362191402701</v>
       </c>
       <c r="F442" t="n">
         <v>24428900</v>
@@ -9332,16 +9332,16 @@
         <v>44903</v>
       </c>
       <c r="B446" t="n">
-        <v>18.63192749023438</v>
+        <v>18.63192939758301</v>
       </c>
       <c r="C446" t="n">
-        <v>19.16179025257903</v>
+        <v>19.16179221416967</v>
       </c>
       <c r="D446" t="n">
-        <v>18.43924911982698</v>
+        <v>18.43925100745114</v>
       </c>
       <c r="E446" t="n">
-        <v>19.07508516964742</v>
+        <v>19.07508712236206</v>
       </c>
       <c r="F446" t="n">
         <v>15335300</v>
@@ -9352,16 +9352,16 @@
         <v>44904</v>
       </c>
       <c r="B447" t="n">
-        <v>18.57412528991699</v>
+        <v>18.57412719726562</v>
       </c>
       <c r="C447" t="n">
-        <v>18.7571677262095</v>
+        <v>18.75716965235448</v>
       </c>
       <c r="D447" t="n">
-        <v>18.25620725515131</v>
+        <v>18.25620912985342</v>
       </c>
       <c r="E447" t="n">
-        <v>18.57412528991699</v>
+        <v>18.57412719726562</v>
       </c>
       <c r="F447" t="n">
         <v>14833900</v>
@@ -9372,16 +9372,16 @@
         <v>44907</v>
       </c>
       <c r="B448" t="n">
-        <v>18.2562084197998</v>
+        <v>18.25620651245117</v>
       </c>
       <c r="C448" t="n">
-        <v>18.6704638316658</v>
+        <v>18.67046188103712</v>
       </c>
       <c r="D448" t="n">
-        <v>17.87085164245525</v>
+        <v>17.87084977536743</v>
       </c>
       <c r="E448" t="n">
-        <v>18.45851907414013</v>
+        <v>18.45851714565475</v>
       </c>
       <c r="F448" t="n">
         <v>10851800</v>
@@ -9412,16 +9412,16 @@
         <v>44909</v>
       </c>
       <c r="B450" t="n">
-        <v>18.37181282043457</v>
+        <v>18.37181091308594</v>
       </c>
       <c r="C450" t="n">
-        <v>18.46815200867444</v>
+        <v>18.46815009132394</v>
       </c>
       <c r="D450" t="n">
-        <v>17.64927166491134</v>
+        <v>17.64926983257642</v>
       </c>
       <c r="E450" t="n">
-        <v>17.86121824654248</v>
+        <v>17.86121639220342</v>
       </c>
       <c r="F450" t="n">
         <v>10673700</v>
@@ -9432,16 +9432,16 @@
         <v>44910</v>
       </c>
       <c r="B451" t="n">
-        <v>18.41998291015625</v>
+        <v>18.41998481750488</v>
       </c>
       <c r="C451" t="n">
-        <v>18.75716730497398</v>
+        <v>18.75716924723731</v>
       </c>
       <c r="D451" t="n">
-        <v>18.09243078017577</v>
+        <v>18.0924326536071</v>
       </c>
       <c r="E451" t="n">
-        <v>18.1116971473674</v>
+        <v>18.11169902279372</v>
       </c>
       <c r="F451" t="n">
         <v>15735500</v>
@@ -9452,16 +9452,16 @@
         <v>44911</v>
       </c>
       <c r="B452" t="n">
-        <v>18.02499389648438</v>
+        <v>18.02499198913574</v>
       </c>
       <c r="C452" t="n">
-        <v>18.69936642972459</v>
+        <v>18.69936445101596</v>
       </c>
       <c r="D452" t="n">
-        <v>17.55293385822315</v>
+        <v>17.55293200082644</v>
       </c>
       <c r="E452" t="n">
-        <v>18.38144836977245</v>
+        <v>18.38144642470492</v>
       </c>
       <c r="F452" t="n">
         <v>14090800</v>
@@ -9512,16 +9512,16 @@
         <v>44916</v>
       </c>
       <c r="B455" t="n">
-        <v>19.4411735534668</v>
+        <v>19.44117546081543</v>
       </c>
       <c r="C455" t="n">
-        <v>19.6723864936323</v>
+        <v>19.67238842366494</v>
       </c>
       <c r="D455" t="n">
-        <v>19.07508502006691</v>
+        <v>19.07508689149907</v>
       </c>
       <c r="E455" t="n">
-        <v>19.30629979774953</v>
+        <v>19.30630169186587</v>
       </c>
       <c r="F455" t="n">
         <v>13319200</v>
@@ -9632,16 +9632,16 @@
         <v>44924</v>
       </c>
       <c r="B461" t="n">
-        <v>18.79301261901855</v>
+        <v>18.79301452636719</v>
       </c>
       <c r="C461" t="n">
-        <v>18.97640668990154</v>
+        <v>18.97640861586329</v>
       </c>
       <c r="D461" t="n">
-        <v>18.59031536253894</v>
+        <v>18.59031724931533</v>
       </c>
       <c r="E461" t="n">
-        <v>18.8605802122071</v>
+        <v>18.86058212641333</v>
       </c>
       <c r="F461" t="n">
         <v>7547800</v>
@@ -9652,16 +9652,16 @@
         <v>44928</v>
       </c>
       <c r="B462" t="n">
-        <v>18.32970237731934</v>
+        <v>18.32970428466797</v>
       </c>
       <c r="C462" t="n">
-        <v>18.50344392873929</v>
+        <v>18.50344585416709</v>
       </c>
       <c r="D462" t="n">
-        <v>17.90500101174039</v>
+        <v>17.90500287489553</v>
       </c>
       <c r="E462" t="n">
-        <v>18.33935489029029</v>
+        <v>18.33935679864334</v>
       </c>
       <c r="F462" t="n">
         <v>4837200</v>
@@ -9672,16 +9672,16 @@
         <v>44929</v>
       </c>
       <c r="B463" t="n">
-        <v>17.96291732788086</v>
+        <v>17.96291923522949</v>
       </c>
       <c r="C463" t="n">
-        <v>18.3972693953452</v>
+        <v>18.39727134881445</v>
       </c>
       <c r="D463" t="n">
-        <v>17.73126252369413</v>
+        <v>17.73126440644506</v>
       </c>
       <c r="E463" t="n">
-        <v>18.26213788649346</v>
+        <v>18.2621398256141</v>
       </c>
       <c r="F463" t="n">
         <v>7978600</v>
@@ -9792,16 +9792,16 @@
         <v>44937</v>
       </c>
       <c r="B469" t="n">
-        <v>19.07292938232422</v>
+        <v>19.07293128967285</v>
       </c>
       <c r="C469" t="n">
-        <v>19.14049513235975</v>
+        <v>19.14049704646515</v>
       </c>
       <c r="D469" t="n">
-        <v>18.3586599889037</v>
+        <v>18.3586618248233</v>
       </c>
       <c r="E469" t="n">
-        <v>18.51309651499307</v>
+        <v>18.51309836635679</v>
       </c>
       <c r="F469" t="n">
         <v>7095500</v>
@@ -9812,16 +9812,16 @@
         <v>44938</v>
       </c>
       <c r="B470" t="n">
-        <v>19.30458641052246</v>
+        <v>19.30458450317383</v>
       </c>
       <c r="C470" t="n">
-        <v>19.7775485566568</v>
+        <v>19.77754660257815</v>
       </c>
       <c r="D470" t="n">
-        <v>18.84127677851684</v>
+        <v>18.84127491694453</v>
       </c>
       <c r="E470" t="n">
-        <v>19.09223662277709</v>
+        <v>19.09223473640923</v>
       </c>
       <c r="F470" t="n">
         <v>10710500</v>
@@ -9832,16 +9832,16 @@
         <v>44939</v>
       </c>
       <c r="B471" t="n">
-        <v>19.26597595214844</v>
+        <v>19.2659740447998</v>
       </c>
       <c r="C471" t="n">
-        <v>19.60380657549171</v>
+        <v>19.60380463469755</v>
       </c>
       <c r="D471" t="n">
-        <v>18.94745035665993</v>
+        <v>18.94744848084562</v>
       </c>
       <c r="E471" t="n">
-        <v>19.23702025139507</v>
+        <v>19.23701834691308</v>
       </c>
       <c r="F471" t="n">
         <v>6794900</v>
@@ -9852,16 +9852,16 @@
         <v>44942</v>
       </c>
       <c r="B472" t="n">
-        <v>19.36249732971191</v>
+        <v>19.36249923706055</v>
       </c>
       <c r="C472" t="n">
-        <v>19.57484893299235</v>
+        <v>19.57485086125918</v>
       </c>
       <c r="D472" t="n">
-        <v>19.14049505449018</v>
+        <v>19.14049693996996</v>
       </c>
       <c r="E472" t="n">
-        <v>19.15014756746008</v>
+        <v>19.15014945389069</v>
       </c>
       <c r="F472" t="n">
         <v>4350100</v>
@@ -9872,16 +9872,16 @@
         <v>44943</v>
       </c>
       <c r="B473" t="n">
-        <v>19.36249732971191</v>
+        <v>19.36249923706055</v>
       </c>
       <c r="C473" t="n">
-        <v>19.48797815729192</v>
+        <v>19.48798007700134</v>
       </c>
       <c r="D473" t="n">
-        <v>19.11153751558051</v>
+        <v>19.11153939820775</v>
       </c>
       <c r="E473" t="n">
-        <v>19.44936810541235</v>
+        <v>19.44937002131839</v>
       </c>
       <c r="F473" t="n">
         <v>5372600</v>
@@ -9892,16 +9892,16 @@
         <v>44944</v>
       </c>
       <c r="B474" t="n">
-        <v>19.7003288269043</v>
+        <v>19.70033073425293</v>
       </c>
       <c r="C474" t="n">
-        <v>19.96094116600892</v>
+        <v>19.96094309858955</v>
       </c>
       <c r="D474" t="n">
-        <v>19.40110827517049</v>
+        <v>19.40111015354915</v>
       </c>
       <c r="E474" t="n">
-        <v>19.59415302037382</v>
+        <v>19.59415491744271</v>
       </c>
       <c r="F474" t="n">
         <v>9224700</v>
@@ -9932,16 +9932,16 @@
         <v>44946</v>
       </c>
       <c r="B476" t="n">
-        <v>19.30458641052246</v>
+        <v>19.30458450317383</v>
       </c>
       <c r="C476" t="n">
-        <v>19.43971792626689</v>
+        <v>19.43971600556688</v>
       </c>
       <c r="D476" t="n">
-        <v>19.03432153800477</v>
+        <v>19.03431965735908</v>
       </c>
       <c r="E476" t="n">
-        <v>19.39145719665212</v>
+        <v>19.3914552807204</v>
       </c>
       <c r="F476" t="n">
         <v>5910600</v>
@@ -9952,16 +9952,16 @@
         <v>44949</v>
       </c>
       <c r="B477" t="n">
-        <v>19.5651969909668</v>
+        <v>19.56519889831543</v>
       </c>
       <c r="C477" t="n">
-        <v>19.78719927266691</v>
+        <v>19.78720120165784</v>
       </c>
       <c r="D477" t="n">
-        <v>19.25632393103121</v>
+        <v>19.2563258082688</v>
       </c>
       <c r="E477" t="n">
-        <v>19.28527962975727</v>
+        <v>19.28528150981765</v>
       </c>
       <c r="F477" t="n">
         <v>3499900</v>
@@ -9972,16 +9972,16 @@
         <v>44950</v>
       </c>
       <c r="B478" t="n">
-        <v>20.31807708740234</v>
+        <v>20.31807518005371</v>
       </c>
       <c r="C478" t="n">
-        <v>20.46286296277044</v>
+        <v>20.46286104183011</v>
       </c>
       <c r="D478" t="n">
-        <v>19.66172267566264</v>
+        <v>19.66172082992893</v>
       </c>
       <c r="E478" t="n">
-        <v>19.67137334906023</v>
+        <v>19.67137150242056</v>
       </c>
       <c r="F478" t="n">
         <v>6625300</v>
@@ -10012,16 +10012,16 @@
         <v>44952</v>
       </c>
       <c r="B480" t="n">
-        <v>20.26981544494629</v>
+        <v>20.26981353759766</v>
       </c>
       <c r="C480" t="n">
-        <v>20.43390450076081</v>
+        <v>20.43390257797174</v>
       </c>
       <c r="D480" t="n">
-        <v>19.96094236130219</v>
+        <v>19.96094048301789</v>
       </c>
       <c r="E480" t="n">
-        <v>20.37599125783475</v>
+        <v>20.37598934049518</v>
       </c>
       <c r="F480" t="n">
         <v>7475700</v>
@@ -10032,16 +10032,16 @@
         <v>44953</v>
       </c>
       <c r="B481" t="n">
-        <v>20.28911972045898</v>
+        <v>20.28911781311035</v>
       </c>
       <c r="C481" t="n">
-        <v>20.51112201096608</v>
+        <v>20.51112008274735</v>
       </c>
       <c r="D481" t="n">
-        <v>20.10572564346113</v>
+        <v>20.10572375335309</v>
       </c>
       <c r="E481" t="n">
-        <v>20.21190145241179</v>
+        <v>20.21189955232233</v>
       </c>
       <c r="F481" t="n">
         <v>6872200</v>
@@ -10112,16 +10112,16 @@
         <v>44959</v>
       </c>
       <c r="B485" t="n">
-        <v>18.84127426147461</v>
+        <v>18.84127616882324</v>
       </c>
       <c r="C485" t="n">
-        <v>19.19840803138294</v>
+        <v>19.19840997488511</v>
       </c>
       <c r="D485" t="n">
-        <v>18.55170439938368</v>
+        <v>18.55170627741844</v>
       </c>
       <c r="E485" t="n">
-        <v>18.60961947641901</v>
+        <v>18.60962136031666</v>
       </c>
       <c r="F485" t="n">
         <v>8708800</v>
@@ -10152,16 +10152,16 @@
         <v>44963</v>
       </c>
       <c r="B487" t="n">
-        <v>18.55170631408691</v>
+        <v>18.55170440673828</v>
       </c>
       <c r="C487" t="n">
-        <v>18.66753463908353</v>
+        <v>18.66753271982629</v>
       </c>
       <c r="D487" t="n">
-        <v>18.24283323546763</v>
+        <v>18.24283135987503</v>
       </c>
       <c r="E487" t="n">
-        <v>18.45518485778996</v>
+        <v>18.45518296036495</v>
       </c>
       <c r="F487" t="n">
         <v>7136600</v>
@@ -10212,16 +10212,16 @@
         <v>44966</v>
       </c>
       <c r="B490" t="n">
-        <v>17.87604904174805</v>
+        <v>17.87604713439941</v>
       </c>
       <c r="C490" t="n">
-        <v>18.04979062940028</v>
+        <v>18.04978870351367</v>
       </c>
       <c r="D490" t="n">
-        <v>17.69265493911191</v>
+        <v>17.69265305133117</v>
       </c>
       <c r="E490" t="n">
-        <v>17.91465726065466</v>
+        <v>17.91465534918659</v>
       </c>
       <c r="F490" t="n">
         <v>11653900</v>
@@ -10232,16 +10232,16 @@
         <v>44967</v>
       </c>
       <c r="B491" t="n">
-        <v>17.98221969604492</v>
+        <v>17.98222160339355</v>
       </c>
       <c r="C491" t="n">
-        <v>18.09804801338318</v>
+        <v>18.09804993301756</v>
       </c>
       <c r="D491" t="n">
-        <v>17.6250859128902</v>
+        <v>17.62508778235816</v>
       </c>
       <c r="E491" t="n">
-        <v>17.79882746838327</v>
+        <v>17.79882935627974</v>
       </c>
       <c r="F491" t="n">
         <v>6326900</v>
@@ -10252,16 +10252,16 @@
         <v>44970</v>
       </c>
       <c r="B492" t="n">
-        <v>18.02083015441895</v>
+        <v>18.02083206176758</v>
       </c>
       <c r="C492" t="n">
-        <v>18.13665847436409</v>
+        <v>18.13666039397214</v>
       </c>
       <c r="D492" t="n">
-        <v>17.76021781531389</v>
+        <v>17.76021969507897</v>
       </c>
       <c r="E492" t="n">
-        <v>17.91465434788829</v>
+        <v>17.91465624399913</v>
       </c>
       <c r="F492" t="n">
         <v>6817800</v>
@@ -10272,16 +10272,16 @@
         <v>44971</v>
       </c>
       <c r="B493" t="n">
-        <v>17.80848121643066</v>
+        <v>17.80847930908203</v>
       </c>
       <c r="C493" t="n">
-        <v>18.11735429604525</v>
+        <v>18.11735235561527</v>
       </c>
       <c r="D493" t="n">
-        <v>17.71195791879391</v>
+        <v>17.71195602178325</v>
       </c>
       <c r="E493" t="n">
-        <v>18.0208309984085</v>
+        <v>18.02082906831649</v>
       </c>
       <c r="F493" t="n">
         <v>9612400</v>
@@ -10292,16 +10292,16 @@
         <v>44972</v>
       </c>
       <c r="B494" t="n">
-        <v>18.55170631408691</v>
+        <v>18.55170440673828</v>
       </c>
       <c r="C494" t="n">
-        <v>18.7737104502447</v>
+        <v>18.77370852007125</v>
       </c>
       <c r="D494" t="n">
-        <v>17.7602185898678</v>
+        <v>17.76021676389406</v>
       </c>
       <c r="E494" t="n">
-        <v>17.80848115904505</v>
+        <v>17.8084793281093</v>
       </c>
       <c r="F494" t="n">
         <v>12677500</v>
@@ -10312,16 +10312,16 @@
         <v>44973</v>
       </c>
       <c r="B495" t="n">
-        <v>18.34900856018066</v>
+        <v>18.3490104675293</v>
       </c>
       <c r="C495" t="n">
-        <v>18.5517058222651</v>
+        <v>18.55170775068378</v>
       </c>
       <c r="D495" t="n">
-        <v>17.88569895453448</v>
+        <v>17.88570081372285</v>
       </c>
       <c r="E495" t="n">
-        <v>18.43587934136792</v>
+        <v>18.43588125774662</v>
       </c>
       <c r="F495" t="n">
         <v>33990600</v>
@@ -10352,16 +10352,16 @@
         <v>44979</v>
       </c>
       <c r="B497" t="n">
-        <v>18.17526817321777</v>
+        <v>18.17526626586914</v>
       </c>
       <c r="C497" t="n">
-        <v>18.42622801942978</v>
+        <v>18.42622608574493</v>
       </c>
       <c r="D497" t="n">
-        <v>18.03048414221861</v>
+        <v>18.0304822500639</v>
       </c>
       <c r="E497" t="n">
-        <v>18.32970471842073</v>
+        <v>18.32970279486522</v>
       </c>
       <c r="F497" t="n">
         <v>5044700</v>
@@ -10432,16 +10432,16 @@
         <v>44985</v>
       </c>
       <c r="B501" t="n">
-        <v>17.50925827026367</v>
+        <v>17.50925636291504</v>
       </c>
       <c r="C501" t="n">
-        <v>17.81813134036312</v>
+        <v>17.81812939936779</v>
       </c>
       <c r="D501" t="n">
-        <v>17.23899525444101</v>
+        <v>17.23899337653314</v>
       </c>
       <c r="E501" t="n">
-        <v>17.74091307283826</v>
+        <v>17.7409111402546</v>
       </c>
       <c r="F501" t="n">
         <v>18187200</v>
@@ -10452,16 +10452,16 @@
         <v>44986</v>
       </c>
       <c r="B502" t="n">
-        <v>17.02664375305176</v>
+        <v>17.02664184570312</v>
       </c>
       <c r="C502" t="n">
-        <v>17.77952324727908</v>
+        <v>17.77952125559183</v>
       </c>
       <c r="D502" t="n">
-        <v>16.67916246735577</v>
+        <v>16.67916059893248</v>
       </c>
       <c r="E502" t="n">
-        <v>17.5092583886011</v>
+        <v>17.5092564271893</v>
       </c>
       <c r="F502" t="n">
         <v>19714300</v>
@@ -10472,16 +10472,16 @@
         <v>44987</v>
       </c>
       <c r="B503" t="n">
-        <v>16.89151191711426</v>
+        <v>16.89151382446289</v>
       </c>
       <c r="C503" t="n">
-        <v>17.21969001021477</v>
+        <v>17.21969195462048</v>
       </c>
       <c r="D503" t="n">
-        <v>16.84325119090541</v>
+        <v>16.84325309280456</v>
       </c>
       <c r="E503" t="n">
-        <v>17.02664342332199</v>
+        <v>17.02664534592935</v>
       </c>
       <c r="F503" t="n">
         <v>7002300</v>
@@ -10492,16 +10492,16 @@
         <v>44988</v>
       </c>
       <c r="B504" t="n">
-        <v>16.92047119140625</v>
+        <v>16.92046928405762</v>
       </c>
       <c r="C504" t="n">
-        <v>17.22934428926396</v>
+        <v>17.22934234709782</v>
       </c>
       <c r="D504" t="n">
-        <v>16.72742458473074</v>
+        <v>16.72742269914315</v>
       </c>
       <c r="E504" t="n">
-        <v>16.92047119140625</v>
+        <v>16.92046928405762</v>
       </c>
       <c r="F504" t="n">
         <v>8320600</v>
@@ -10532,16 +10532,16 @@
         <v>44992</v>
       </c>
       <c r="B506" t="n">
-        <v>17.13282012939453</v>
+        <v>17.1328182220459</v>
       </c>
       <c r="C506" t="n">
-        <v>17.22934342790674</v>
+        <v>17.22934150981244</v>
       </c>
       <c r="D506" t="n">
-        <v>16.85290274781201</v>
+        <v>16.85290087162579</v>
       </c>
       <c r="E506" t="n">
-        <v>17.06525437274463</v>
+        <v>17.0652524729179</v>
       </c>
       <c r="F506" t="n">
         <v>12726400</v>
@@ -10572,16 +10572,16 @@
         <v>44994</v>
       </c>
       <c r="B508" t="n">
-        <v>17.24864959716797</v>
+        <v>17.24864768981934</v>
       </c>
       <c r="C508" t="n">
-        <v>17.80848255634869</v>
+        <v>17.80848058709395</v>
       </c>
       <c r="D508" t="n">
-        <v>17.18108199501829</v>
+        <v>17.18108009514125</v>
       </c>
       <c r="E508" t="n">
-        <v>17.36447609022389</v>
+        <v>17.36447417006721</v>
       </c>
       <c r="F508" t="n">
         <v>10746400</v>
@@ -10592,16 +10592,16 @@
         <v>44995</v>
       </c>
       <c r="B509" t="n">
-        <v>16.28341674804688</v>
+        <v>16.28341865539551</v>
       </c>
       <c r="C509" t="n">
-        <v>17.200383345925</v>
+        <v>17.20038536068198</v>
       </c>
       <c r="D509" t="n">
-        <v>16.10967520458848</v>
+        <v>16.10967709158599</v>
       </c>
       <c r="E509" t="n">
-        <v>17.1135125741958</v>
+        <v>17.11351457877723</v>
       </c>
       <c r="F509" t="n">
         <v>24597700</v>
@@ -10632,16 +10632,16 @@
         <v>44999</v>
       </c>
       <c r="B511" t="n">
-        <v>15.98419666290283</v>
+        <v>15.98419570922852</v>
       </c>
       <c r="C511" t="n">
-        <v>16.40889806960417</v>
+        <v>16.40889709059065</v>
       </c>
       <c r="D511" t="n">
-        <v>15.80080442178327</v>
+        <v>15.80080347905079</v>
       </c>
       <c r="E511" t="n">
-        <v>16.17724325895675</v>
+        <v>16.17724229376458</v>
       </c>
       <c r="F511" t="n">
         <v>10544400</v>
@@ -10652,16 +10652,16 @@
         <v>45000</v>
       </c>
       <c r="B512" t="n">
-        <v>16.15793991088867</v>
+        <v>16.15793800354004</v>
       </c>
       <c r="C512" t="n">
-        <v>16.43785732016355</v>
+        <v>16.43785537977234</v>
       </c>
       <c r="D512" t="n">
-        <v>15.60775944827691</v>
+        <v>15.6077576058738</v>
       </c>
       <c r="E512" t="n">
-        <v>15.79115354949049</v>
+        <v>15.7911516854388</v>
       </c>
       <c r="F512" t="n">
         <v>24755700</v>
@@ -10672,16 +10672,16 @@
         <v>45001</v>
       </c>
       <c r="B513" t="n">
-        <v>15.68497467041016</v>
+        <v>15.68497562408447</v>
       </c>
       <c r="C513" t="n">
-        <v>16.33167831507744</v>
+        <v>16.33167930807249</v>
       </c>
       <c r="D513" t="n">
-        <v>15.64636461829695</v>
+        <v>15.64636556962371</v>
       </c>
       <c r="E513" t="n">
-        <v>16.03245777531455</v>
+        <v>16.03245875011646</v>
       </c>
       <c r="F513" t="n">
         <v>11501700</v>
@@ -10712,16 +10712,16 @@
         <v>45005</v>
       </c>
       <c r="B515" t="n">
-        <v>15.49193000793457</v>
+        <v>15.49192905426025</v>
       </c>
       <c r="C515" t="n">
-        <v>15.59810582334904</v>
+        <v>15.5981048631386</v>
       </c>
       <c r="D515" t="n">
-        <v>15.31818935450853</v>
+        <v>15.31818841152959</v>
       </c>
       <c r="E515" t="n">
-        <v>15.44366927785282</v>
+        <v>15.4436683271494</v>
       </c>
       <c r="F515" t="n">
         <v>20828100</v>
@@ -10832,16 +10832,16 @@
         <v>45013</v>
       </c>
       <c r="B521" t="n">
-        <v>14.82592010498047</v>
+        <v>14.82592105865479</v>
       </c>
       <c r="C521" t="n">
-        <v>14.99000914178451</v>
+        <v>14.99001010601382</v>
       </c>
       <c r="D521" t="n">
-        <v>14.41087217704756</v>
+        <v>14.410873104024</v>
       </c>
       <c r="E521" t="n">
-        <v>14.5749612138516</v>
+        <v>14.57496215138304</v>
       </c>
       <c r="F521" t="n">
         <v>12984500</v>
@@ -10912,16 +10912,16 @@
         <v>45019</v>
       </c>
       <c r="B525" t="n">
-        <v>14.25643730163574</v>
+        <v>14.25643634796143</v>
       </c>
       <c r="C525" t="n">
-        <v>14.97070676766176</v>
+        <v>14.97070576620689</v>
       </c>
       <c r="D525" t="n">
-        <v>14.23713227365506</v>
+        <v>14.23713132127214</v>
       </c>
       <c r="E525" t="n">
-        <v>14.96105425367142</v>
+        <v>14.96105325286225</v>
       </c>
       <c r="F525" t="n">
         <v>17443100</v>
@@ -10972,16 +10972,16 @@
         <v>45022</v>
       </c>
       <c r="B528" t="n">
-        <v>13.15607452392578</v>
+        <v>13.1560754776001</v>
       </c>
       <c r="C528" t="n">
-        <v>13.57112338766055</v>
+        <v>13.57112437142145</v>
       </c>
       <c r="D528" t="n">
-        <v>13.00163799430754</v>
+        <v>13.00163893678686</v>
       </c>
       <c r="E528" t="n">
-        <v>13.33946767271886</v>
+        <v>13.33946863968721</v>
       </c>
       <c r="F528" t="n">
         <v>26117400</v>
@@ -11052,16 +11052,16 @@
         <v>45029</v>
       </c>
       <c r="B532" t="n">
-        <v>13.27190208435059</v>
+        <v>13.2719030380249</v>
       </c>
       <c r="C532" t="n">
-        <v>14.14060803439325</v>
+        <v>14.14060905048986</v>
       </c>
       <c r="D532" t="n">
-        <v>13.27190208435059</v>
+        <v>13.2719030380249</v>
       </c>
       <c r="E532" t="n">
-        <v>14.09234730867981</v>
+        <v>14.09234832130857</v>
       </c>
       <c r="F532" t="n">
         <v>20136100</v>
@@ -11072,16 +11072,16 @@
         <v>45030</v>
       </c>
       <c r="B533" t="n">
-        <v>12.76033115386963</v>
+        <v>12.76033210754395</v>
       </c>
       <c r="C533" t="n">
-        <v>13.29120743425609</v>
+        <v>13.29120842760674</v>
       </c>
       <c r="D533" t="n">
-        <v>12.59624210501355</v>
+        <v>12.59624304642427</v>
       </c>
       <c r="E533" t="n">
-        <v>13.20433665303648</v>
+        <v>13.20433763989463</v>
       </c>
       <c r="F533" t="n">
         <v>26653800</v>
@@ -11132,16 +11132,16 @@
         <v>45035</v>
       </c>
       <c r="B536" t="n">
-        <v>12.44180583953857</v>
+        <v>12.44180488586426</v>
       </c>
       <c r="C536" t="n">
-        <v>12.69276475454189</v>
+        <v>12.69276378163138</v>
       </c>
       <c r="D536" t="n">
-        <v>12.27771678712426</v>
+        <v>12.2777158460275</v>
       </c>
       <c r="E536" t="n">
-        <v>12.58658986436797</v>
+        <v>12.58658889959584</v>
       </c>
       <c r="F536" t="n">
         <v>13110300</v>
@@ -11232,16 +11232,16 @@
         <v>45043</v>
       </c>
       <c r="B541" t="n">
-        <v>11.87231922149658</v>
+        <v>11.87232112884521</v>
       </c>
       <c r="C541" t="n">
-        <v>12.16188816260904</v>
+        <v>12.1618901164784</v>
       </c>
       <c r="D541" t="n">
-        <v>11.65996854194554</v>
+        <v>11.65997041517895</v>
       </c>
       <c r="E541" t="n">
-        <v>12.00745071897192</v>
+        <v>12.00745264803012</v>
       </c>
       <c r="F541" t="n">
         <v>19434000</v>
@@ -11252,16 +11252,16 @@
         <v>45044</v>
       </c>
       <c r="B542" t="n">
-        <v>11.91110515594482</v>
+        <v>11.91110610961914</v>
       </c>
       <c r="C542" t="n">
-        <v>12.04678935581152</v>
+        <v>12.04679032034952</v>
       </c>
       <c r="D542" t="n">
-        <v>11.70757931828128</v>
+        <v>11.7075802556601</v>
       </c>
       <c r="E542" t="n">
-        <v>11.8723383737362</v>
+        <v>11.87233932430661</v>
       </c>
       <c r="F542" t="n">
         <v>15072900</v>
@@ -11312,16 +11312,16 @@
         <v>45050</v>
       </c>
       <c r="B545" t="n">
-        <v>11.12607669830322</v>
+        <v>11.12607765197754</v>
       </c>
       <c r="C545" t="n">
-        <v>11.50405351931347</v>
+        <v>11.50405450538616</v>
       </c>
       <c r="D545" t="n">
-        <v>10.64149145692891</v>
+        <v>10.64149236906689</v>
       </c>
       <c r="E545" t="n">
-        <v>11.31991153427135</v>
+        <v>11.31991250456026</v>
       </c>
       <c r="F545" t="n">
         <v>26954400</v>
@@ -11332,16 +11332,16 @@
         <v>45051</v>
       </c>
       <c r="B546" t="n">
-        <v>10.17629051208496</v>
+        <v>10.17628955841064</v>
       </c>
       <c r="C546" t="n">
-        <v>10.95162711690795</v>
+        <v>10.95162609057271</v>
       </c>
       <c r="D546" t="n">
-        <v>10.05999016000247</v>
+        <v>10.05998921722728</v>
       </c>
       <c r="E546" t="n">
-        <v>10.84501776762755</v>
+        <v>10.84501675128325</v>
       </c>
       <c r="F546" t="n">
         <v>52976300</v>
@@ -11372,16 +11372,16 @@
         <v>45055</v>
       </c>
       <c r="B548" t="n">
-        <v>11.26176071166992</v>
+        <v>11.26176166534424</v>
       </c>
       <c r="C548" t="n">
-        <v>11.59127881821781</v>
+        <v>11.59127979979655</v>
       </c>
       <c r="D548" t="n">
-        <v>10.59303349635502</v>
+        <v>10.59303439339983</v>
       </c>
       <c r="E548" t="n">
-        <v>10.80625033354355</v>
+        <v>10.8062512486441</v>
       </c>
       <c r="F548" t="n">
         <v>38878100</v>
@@ -11512,16 +11512,16 @@
         <v>45064</v>
       </c>
       <c r="B555" t="n">
-        <v>10.95162773132324</v>
+        <v>10.95162677764893</v>
       </c>
       <c r="C555" t="n">
-        <v>10.96131965894212</v>
+        <v>10.96131870442382</v>
       </c>
       <c r="D555" t="n">
-        <v>10.6511844450497</v>
+        <v>10.65118351753816</v>
       </c>
       <c r="E555" t="n">
-        <v>10.79656058651357</v>
+        <v>10.7965596463426</v>
       </c>
       <c r="F555" t="n">
         <v>10867600</v>
@@ -11572,16 +11572,16 @@
         <v>45069</v>
       </c>
       <c r="B558" t="n">
-        <v>11.21330165863037</v>
+        <v>11.21330261230469</v>
       </c>
       <c r="C558" t="n">
-        <v>11.89172170384635</v>
+        <v>11.89172271521926</v>
       </c>
       <c r="D558" t="n">
-        <v>11.17453487812714</v>
+        <v>11.1745358285044</v>
       </c>
       <c r="E558" t="n">
-        <v>11.76572943614261</v>
+        <v>11.76573043680007</v>
       </c>
       <c r="F558" t="n">
         <v>12722500</v>
@@ -11792,16 +11792,16 @@
         <v>45084</v>
       </c>
       <c r="B569" t="n">
-        <v>12.3859977722168</v>
+        <v>12.38599872589111</v>
       </c>
       <c r="C569" t="n">
-        <v>13.10318458913605</v>
+        <v>13.103185598031</v>
       </c>
       <c r="D569" t="n">
-        <v>12.09524645987364</v>
+        <v>12.09524739116122</v>
       </c>
       <c r="E569" t="n">
-        <v>12.42476455224435</v>
+        <v>12.42476550890357</v>
       </c>
       <c r="F569" t="n">
         <v>35775900</v>
@@ -11832,16 +11832,16 @@
         <v>45089</v>
       </c>
       <c r="B571" t="n">
-        <v>13.29701900482178</v>
+        <v>13.29701995849609</v>
       </c>
       <c r="C571" t="n">
-        <v>13.52961969400545</v>
+        <v>13.5296206643621</v>
       </c>
       <c r="D571" t="n">
-        <v>12.72520828404051</v>
+        <v>12.72520919670404</v>
       </c>
       <c r="E571" t="n">
-        <v>12.80274184710173</v>
+        <v>12.80274276532604</v>
       </c>
       <c r="F571" t="n">
         <v>31653900</v>
@@ -11892,16 +11892,16 @@
         <v>45092</v>
       </c>
       <c r="B574" t="n">
-        <v>13.66530418395996</v>
+        <v>13.66530323028564</v>
       </c>
       <c r="C574" t="n">
-        <v>13.89790487812169</v>
+        <v>13.89790390821463</v>
       </c>
       <c r="D574" t="n">
-        <v>13.14195215995957</v>
+        <v>13.14195124280895</v>
       </c>
       <c r="E574" t="n">
-        <v>13.27763543608408</v>
+        <v>13.2776345094644</v>
       </c>
       <c r="F574" t="n">
         <v>25113500</v>
@@ -11952,16 +11952,16 @@
         <v>45097</v>
       </c>
       <c r="B577" t="n">
-        <v>12.91904163360596</v>
+        <v>12.91904258728027</v>
       </c>
       <c r="C577" t="n">
-        <v>13.00626711935004</v>
+        <v>13.00626807946328</v>
       </c>
       <c r="D577" t="n">
-        <v>12.6089073947585</v>
+        <v>12.60890832553893</v>
       </c>
       <c r="E577" t="n">
-        <v>12.77366644021444</v>
+        <v>12.77366738315727</v>
       </c>
       <c r="F577" t="n">
         <v>13900100</v>
@@ -11972,16 +11972,16 @@
         <v>45098</v>
       </c>
       <c r="B578" t="n">
-        <v>12.98688507080078</v>
+        <v>12.98688411712646</v>
       </c>
       <c r="C578" t="n">
-        <v>13.03534378341849</v>
+        <v>13.03534282618567</v>
       </c>
       <c r="D578" t="n">
-        <v>12.70582564674574</v>
+        <v>12.70582471371064</v>
       </c>
       <c r="E578" t="n">
-        <v>12.99657699817894</v>
+        <v>12.99657604379291</v>
       </c>
       <c r="F578" t="n">
         <v>18033300</v>
@@ -12032,16 +12032,16 @@
         <v>45103</v>
       </c>
       <c r="B581" t="n">
-        <v>13.47146987915039</v>
+        <v>13.47146892547607</v>
       </c>
       <c r="C581" t="n">
-        <v>14.14019805657877</v>
+        <v>14.14019705556374</v>
       </c>
       <c r="D581" t="n">
-        <v>13.35516952748307</v>
+        <v>13.35516858204191</v>
       </c>
       <c r="E581" t="n">
-        <v>13.85913864231449</v>
+        <v>13.85913766119627</v>
       </c>
       <c r="F581" t="n">
         <v>23023000</v>
@@ -12052,16 +12052,16 @@
         <v>45104</v>
       </c>
       <c r="B582" t="n">
-        <v>12.68644142150879</v>
+        <v>12.68644237518311</v>
       </c>
       <c r="C582" t="n">
-        <v>13.85913771066354</v>
+        <v>13.85913875249263</v>
       </c>
       <c r="D582" t="n">
-        <v>12.5604491512705</v>
+        <v>12.56045009547363</v>
       </c>
       <c r="E582" t="n">
-        <v>13.77191222170834</v>
+        <v>13.77191325698045</v>
       </c>
       <c r="F582" t="n">
         <v>64278500</v>
@@ -12092,16 +12092,16 @@
         <v>45106</v>
       </c>
       <c r="B584" t="n">
-        <v>12.93842697143555</v>
+        <v>12.93842601776123</v>
       </c>
       <c r="C584" t="n">
-        <v>13.19041060729881</v>
+        <v>13.19040963505111</v>
       </c>
       <c r="D584" t="n">
-        <v>12.5798330612484</v>
+        <v>12.57983213400556</v>
       </c>
       <c r="E584" t="n">
-        <v>12.74459212562421</v>
+        <v>12.7445911862372</v>
       </c>
       <c r="F584" t="n">
         <v>22969900</v>
@@ -12132,16 +12132,16 @@
         <v>45110</v>
       </c>
       <c r="B586" t="n">
-        <v>13.20010089874268</v>
+        <v>13.20010185241699</v>
       </c>
       <c r="C586" t="n">
-        <v>13.46177735359831</v>
+        <v>13.46177832617809</v>
       </c>
       <c r="D586" t="n">
-        <v>13.09349248617534</v>
+        <v>13.09349343214747</v>
       </c>
       <c r="E586" t="n">
-        <v>13.46177735359831</v>
+        <v>13.46177832617809</v>
       </c>
       <c r="F586" t="n">
         <v>9654100</v>
@@ -12172,16 +12172,16 @@
         <v>45112</v>
       </c>
       <c r="B588" t="n">
-        <v>13.29701900482178</v>
+        <v>13.29701995849609</v>
       </c>
       <c r="C588" t="n">
-        <v>13.59746133061578</v>
+        <v>13.59746230583809</v>
       </c>
       <c r="D588" t="n">
-        <v>13.14195187869933</v>
+        <v>13.14195282125209</v>
       </c>
       <c r="E588" t="n">
-        <v>13.17102673377904</v>
+        <v>13.17102767841708</v>
       </c>
       <c r="F588" t="n">
         <v>9442900</v>
@@ -12192,16 +12192,16 @@
         <v>45113</v>
       </c>
       <c r="B589" t="n">
-        <v>13.17102718353271</v>
+        <v>13.17102813720703</v>
       </c>
       <c r="C589" t="n">
-        <v>13.32609431495027</v>
+        <v>13.32609527985253</v>
       </c>
       <c r="D589" t="n">
-        <v>13.03534298140585</v>
+        <v>13.03534392525568</v>
       </c>
       <c r="E589" t="n">
-        <v>13.22917689567779</v>
+        <v>13.22917785356256</v>
       </c>
       <c r="F589" t="n">
         <v>10770700</v>
@@ -12212,16 +12212,16 @@
         <v>45114</v>
       </c>
       <c r="B590" t="n">
-        <v>13.56838798522949</v>
+        <v>13.56838703155518</v>
       </c>
       <c r="C590" t="n">
-        <v>13.88821419951091</v>
+        <v>13.88821322335713</v>
       </c>
       <c r="D590" t="n">
-        <v>13.13226141341602</v>
+        <v>13.1322604903955</v>
       </c>
       <c r="E590" t="n">
-        <v>13.28732855679209</v>
+        <v>13.28732762287245</v>
       </c>
       <c r="F590" t="n">
         <v>12191300</v>
@@ -12412,16 +12412,16 @@
         <v>45128</v>
       </c>
       <c r="B600" t="n">
-        <v>12.15339756011963</v>
+        <v>12.15339851379395</v>
       </c>
       <c r="C600" t="n">
-        <v>12.16308948656802</v>
+        <v>12.16309044100286</v>
       </c>
       <c r="D600" t="n">
-        <v>11.80449652643425</v>
+        <v>11.80449745273038</v>
       </c>
       <c r="E600" t="n">
-        <v>11.88203008947544</v>
+        <v>11.88203102185562</v>
       </c>
       <c r="F600" t="n">
         <v>8594300</v>
@@ -12432,16 +12432,16 @@
         <v>45131</v>
       </c>
       <c r="B601" t="n">
-        <v>12.3859977722168</v>
+        <v>12.38599872589111</v>
       </c>
       <c r="C601" t="n">
-        <v>12.54106489232703</v>
+        <v>12.54106585794092</v>
       </c>
       <c r="D601" t="n">
-        <v>12.03709675196877</v>
+        <v>12.03709767877904</v>
       </c>
       <c r="E601" t="n">
-        <v>12.192163872079</v>
+        <v>12.19216481082885</v>
       </c>
       <c r="F601" t="n">
         <v>10834500</v>
@@ -12532,16 +12532,16 @@
         <v>45138</v>
       </c>
       <c r="B606" t="n">
-        <v>13.05472755432129</v>
+        <v>13.05472660064697</v>
       </c>
       <c r="C606" t="n">
-        <v>13.18071983660883</v>
+        <v>13.18071887373052</v>
       </c>
       <c r="D606" t="n">
-        <v>12.72520941976511</v>
+        <v>12.72520849016276</v>
       </c>
       <c r="E606" t="n">
-        <v>12.8996604143591</v>
+        <v>12.89965947201275</v>
       </c>
       <c r="F606" t="n">
         <v>32856600</v>
@@ -12752,16 +12752,16 @@
         <v>45153</v>
       </c>
       <c r="B617" t="n">
-        <v>12.70582580566406</v>
+        <v>12.70582485198975</v>
       </c>
       <c r="C617" t="n">
-        <v>12.87058487606116</v>
+        <v>12.87058391002036</v>
       </c>
       <c r="D617" t="n">
-        <v>12.57014251776509</v>
+        <v>12.5701415742749</v>
       </c>
       <c r="E617" t="n">
-        <v>12.78335937711292</v>
+        <v>12.78335841761909</v>
       </c>
       <c r="F617" t="n">
         <v>15018500</v>
@@ -12792,16 +12792,16 @@
         <v>45155</v>
       </c>
       <c r="B619" t="n">
-        <v>12.60890865325928</v>
+        <v>12.60890769958496</v>
       </c>
       <c r="C619" t="n">
-        <v>12.81243449888516</v>
+        <v>12.81243352981718</v>
       </c>
       <c r="D619" t="n">
-        <v>12.45384151835823</v>
+        <v>12.45384057641241</v>
       </c>
       <c r="E619" t="n">
-        <v>12.67675029371023</v>
+        <v>12.67674933490471</v>
       </c>
       <c r="F619" t="n">
         <v>17965700</v>
@@ -12832,16 +12832,16 @@
         <v>45159</v>
       </c>
       <c r="B621" t="n">
-        <v>12.68644142150879</v>
+        <v>12.68644237518311</v>
       </c>
       <c r="C621" t="n">
-        <v>13.07410923433971</v>
+        <v>13.07411021715607</v>
       </c>
       <c r="D621" t="n">
-        <v>12.68644142150879</v>
+        <v>12.68644237518311</v>
       </c>
       <c r="E621" t="n">
-        <v>13.03534245305662</v>
+        <v>13.03534343295877</v>
       </c>
       <c r="F621" t="n">
         <v>19861900</v>
@@ -12872,16 +12872,16 @@
         <v>45161</v>
       </c>
       <c r="B623" t="n">
-        <v>12.65736770629883</v>
+        <v>12.65736675262451</v>
       </c>
       <c r="C623" t="n">
-        <v>12.66705870928746</v>
+        <v>12.66705775488297</v>
       </c>
       <c r="D623" t="n">
-        <v>12.32784957358586</v>
+        <v>12.32784864473922</v>
       </c>
       <c r="E623" t="n">
-        <v>12.57014220948974</v>
+        <v>12.57014126238746</v>
       </c>
       <c r="F623" t="n">
         <v>19525000</v>
@@ -12912,16 +12912,16 @@
         <v>45163</v>
       </c>
       <c r="B625" t="n">
-        <v>11.98863792419434</v>
+        <v>11.98863887786865</v>
       </c>
       <c r="C625" t="n">
-        <v>12.50229798541463</v>
+        <v>12.50229897994967</v>
       </c>
       <c r="D625" t="n">
-        <v>11.94017921858345</v>
+        <v>11.94018016840297</v>
       </c>
       <c r="E625" t="n">
-        <v>12.4053814984658</v>
+        <v>12.40538248529131</v>
       </c>
       <c r="F625" t="n">
         <v>23324500</v>
@@ -13012,16 +13012,16 @@
         <v>45170</v>
       </c>
       <c r="B630" t="n">
-        <v>11.49436092376709</v>
+        <v>11.49436187744141</v>
       </c>
       <c r="C630" t="n">
-        <v>11.68819574845535</v>
+        <v>11.68819671821193</v>
       </c>
       <c r="D630" t="n">
-        <v>11.30052702335177</v>
+        <v>11.30052796094391</v>
       </c>
       <c r="E630" t="n">
-        <v>11.33929380343484</v>
+        <v>11.33929474424341</v>
       </c